--- a/Excel/Enterprises/Enterprise_Dairy_Template_WIP_v01.xlsx
+++ b/Excel/Enterprises/Enterprise_Dairy_Template_WIP_v01.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\htdocs\zneagcrc\GAF-VEERG-Functions\Excel\Enterprises\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{969924AD-98CF-4A17-9E73-C8E1CBE419AF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3C53693E-BAEA-4112-BDD8-5094217B1264}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1065" yWindow="735" windowWidth="36255" windowHeight="19140" activeTab="5" xr2:uid="{992023F3-CAB7-4E5B-A348-08D563A0EF40}"/>
+    <workbookView xWindow="2145" yWindow="2460" windowWidth="36255" windowHeight="19140" activeTab="3" xr2:uid="{992023F3-CAB7-4E5B-A348-08D563A0EF40}"/>
   </bookViews>
   <sheets>
     <sheet name="Home" sheetId="71" r:id="rId1"/>
@@ -236,19 +236,6 @@
     <definedName name="Enterprise_PastureBeef_InputFunctions.multiplyCorrespondingCells">_xlfn.LAMBDA(_xlpm.range1,_xlpm.range2,_xlpm.range3, _xlfn.LET(_xlpm.numRows, ROWS(_xlpm.range1), _xlpm.numCols, COLUMNS(_xlpm.range1), _xlpm.result, _xlfn.MAKEARRAY(_xlpm.numRows, _xlpm.numCols, _xlfn.LAMBDA(_xlpm.r,_xlpm.c, IF(ISNUMBER(INDEX(_xlpm.range1, _xlpm.r, _xlpm.c)), INDEX(_xlpm.range1, _xlpm.r, _xlpm.c), 0) * IF(ISNUMBER(INDEX(_xlpm.range2, _xlpm.r, _xlpm.c)), INDEX(_xlpm.range2, _xlpm.r, _xlpm.c), 0) * IF(ISNUMBER(INDEX(_xlpm.range3, _xlpm.r, _xlpm.c)), INDEX(_xlpm.range3, _xlpm.r, _xlpm.c), 0))), _xlpm.result))</definedName>
     <definedName name="getOverlappingReportingCycles" localSheetId="4">_xlfn.LAMBDA(_xlpm.ProductionCycleStart,_xlpm.ProductionCycleEnd,_xlpm.ReportingStartMonth,_xlpm.ReportingStartDay, _xlfn.LET(_xlpm.S, _xlpm.ProductionCycleStart, _xlpm.E, _xlpm.ProductionCycleEnd, _xlpm.m, _xlpm.ReportingStartMonth, _xlpm.d, _xlpm.ReportingStartDay, _xlpm.A, _xlpm.S - 364, _xlpm.ya, YEAR(_xlpm.A), _xlpm.yb, YEAR(_xlpm.E), _xlpm.firstYear, _xlpm.ya + (DATE(_xlpm.ya, _xlpm.m, _xlpm.d) &lt; _xlpm.A), _xlpm.lastYear, _xlpm.yb - (DATE(_xlpm.yb, _xlpm.m, _xlpm.d) &gt; _xlpm.E), MAX(0, _xlpm.lastYear - _xlpm.firstYear + 1)))</definedName>
     <definedName name="getOverlappingReportingCycles">_xlfn.LAMBDA(_xlpm.ProductionCycleStart,_xlpm.ProductionCycleEnd,_xlpm.ReportingStartMonth,_xlpm.ReportingStartDay, _xlfn.LET(_xlpm.S, _xlpm.ProductionCycleStart, _xlpm.E, _xlpm.ProductionCycleEnd, _xlpm.m, _xlpm.ReportingStartMonth, _xlpm.d, _xlpm.ReportingStartDay, _xlpm.A, _xlpm.S - 364, _xlpm.ya, YEAR(_xlpm.A), _xlpm.yb, YEAR(_xlpm.E), _xlpm.firstYear, _xlpm.ya + (DATE(_xlpm.ya, _xlpm.m, _xlpm.d) &lt; _xlpm.A), _xlpm.lastYear, _xlpm.yb - (DATE(_xlpm.yb, _xlpm.m, _xlpm.d) &gt; _xlpm.E), MAX(0, _xlpm.lastYear - _xlpm.firstYear + 1)))</definedName>
-    <definedName name="Inoput_Cell_Livestock_antibiotics">#REF!</definedName>
-    <definedName name="Inoput_Cell_Livestockantibiotics">#REF!</definedName>
-    <definedName name="Input_Cell_CO2_for_carbonation">#REF!</definedName>
-    <definedName name="Input_Cell_CO2forcarbonation">#REF!</definedName>
-    <definedName name="Input_Cell_Livestock_antibiotics">#REF!</definedName>
-    <definedName name="Input_Cell_Livestock_tags">#REF!</definedName>
-    <definedName name="Input_Cell_LivestockAntibiotics">#REF!</definedName>
-    <definedName name="Input_Cell_Nylon_netting_for_horticulture">#REF!</definedName>
-    <definedName name="Input_Cell_Nylonnettingforhorticulture">#REF!</definedName>
-    <definedName name="Input_Cell_Pallets__Plastic">#REF!</definedName>
-    <definedName name="Input_Cell_Pallets__Wood">#REF!</definedName>
-    <definedName name="Input_Cell_Pallets_Plastic">#REF!</definedName>
-    <definedName name="Input_Cell_Pallets_Wood">#REF!</definedName>
     <definedName name="InputFunctions_PastureBeef.ConvertMonthlyCalvingToSeason" localSheetId="4">_xlfn.LAMBDA(_xlpm.Season,_xlpm.SumArray,_xlpm.CalvingMonthArray,_xlpm.MonthArray,_xlpm.MonthToSeasonArray, _xlfn.LET(_xlpm.MonthText, TEXT(_xlpm.CalvingMonthArray, "mmmm"), _xlpm.SeasonPerRow, _xlfn.XLOOKUP(_xlpm.MonthText, _xlpm.MonthArray, _xlpm.MonthToSeasonArray, "", 0), SUM(_xlpm.SumArray * (_xlpm.SeasonPerRow = _xlpm.Season))))</definedName>
     <definedName name="InputFunctions_PastureBeef.ConvertMonthlyCalvingToSeason">_xlfn.LAMBDA(_xlpm.Season,_xlpm.SumArray,_xlpm.CalvingMonthArray,_xlpm.MonthArray,_xlpm.MonthToSeasonArray, _xlfn.LET(_xlpm.MonthText, TEXT(_xlpm.CalvingMonthArray, "mmmm"), _xlpm.SeasonPerRow, _xlfn.XLOOKUP(_xlpm.MonthText, _xlpm.MonthArray, _xlpm.MonthToSeasonArray, "", 0), SUM(_xlpm.SumArray * (_xlpm.SeasonPerRow = _xlpm.Season))))</definedName>
     <definedName name="InputFunctions_PastureBeef.LookupLiveweightFromMonth" localSheetId="4">_xlfn.LAMBDA(_xlpm.State,_xlpm.Region,_xlpm.Month,_xlpm.LivestockClass,_xlpm.StateArray,_xlpm.RegionArray,_xlpm.SeasonArray,_xlpm.LivestockClassArray,_xlpm.ReturnArray,_xlpm.StateCommonNameArray,_xlpm.StateAbbreviationArray,_xlpm.MonthArray,_xlpm.MonthToSeasonArray, _xlfn.LET(_xlpm.Month, TEXT(_xlpm.Month, "mmmm"), _xlpm.State, _xlfn.XLOOKUP(_xlpm.State, _xlpm.StateCommonNameArray, _xlpm.StateAbbreviationArray), _xlpm.Season, _xlfn.XLOOKUP(_xlpm.Month, _xlpm.MonthArray, _xlpm.MonthToSeasonArray), _xlfn.XLOOKUP(1, (_xlpm.StateArray = _xlpm.State) * (_xlpm.RegionArray = _xlpm.Region) * (_xlpm.SeasonArray = _xlpm.Season), _xlfn.XLOOKUP(_xlpm.LivestockClass, _xlpm.LivestockClassArray, _xlpm.ReturnArray))))</definedName>
@@ -259,10 +246,6 @@
     <definedName name="InputFunctions_PastureBeef.LookupValueFromStateRegionMonth">_xlfn.LAMBDA(_xlpm.State,_xlpm.Region,_xlpm.Month,_xlpm.StateArray,_xlpm.RegionArray,_xlpm.SeasonArray,_xlpm.ReturnArray,_xlpm.StateCommonNameArray,_xlpm.StateAbbreviationArray,_xlpm.MonthArray,_xlpm.MonthToSeasonArray, _xlfn.LET(_xlpm.State, _xlfn.XLOOKUP(_xlpm.State, _xlpm.StateCommonNameArray, _xlpm.StateAbbreviationArray), _xlpm.Season, _xlfn.XLOOKUP(TEXT(_xlpm.Month, "mmmm"), _xlpm.MonthArray, _xlpm.MonthToSeasonArray), _xlfn.XLOOKUP(1, (_xlpm.StateArray = _xlpm.State) * (_xlpm.RegionArray = _xlpm.Region), _xlfn.XLOOKUP(_xlpm.Season, _xlpm.SeasonArray, _xlpm.ReturnArray))))</definedName>
     <definedName name="InputFunctions_PastureBeef.LookupValueFromStateRegionSeason" localSheetId="4">_xlfn.LAMBDA(_xlpm.State,_xlpm.Region,_xlpm.Season,_xlpm.StateArray,_xlpm.RegionArray,_xlpm.SeasonArray,_xlpm.ReturnArray,_xlpm.StateCommonNameArray,_xlpm.StateAbbreviationArray, _xlfn.LET(_xlpm.State, _xlfn.XLOOKUP(_xlpm.State, _xlpm.StateCommonNameArray, _xlpm.StateAbbreviationArray), _xlfn.XLOOKUP(1, (_xlpm.StateArray = _xlpm.State) * (_xlpm.RegionArray = _xlpm.Region), _xlfn.XLOOKUP(_xlpm.Season, _xlpm.SeasonArray, _xlpm.ReturnArray))))</definedName>
     <definedName name="InputFunctions_PastureBeef.LookupValueFromStateRegionSeason">_xlfn.LAMBDA(_xlpm.State,_xlpm.Region,_xlpm.Season,_xlpm.StateArray,_xlpm.RegionArray,_xlpm.SeasonArray,_xlpm.ReturnArray,_xlpm.StateCommonNameArray,_xlpm.StateAbbreviationArray, _xlfn.LET(_xlpm.State, _xlfn.XLOOKUP(_xlpm.State, _xlpm.StateCommonNameArray, _xlpm.StateAbbreviationArray), _xlfn.XLOOKUP(1, (_xlpm.StateArray = _xlpm.State) * (_xlpm.RegionArray = _xlpm.Region), _xlfn.XLOOKUP(_xlpm.Season, _xlpm.SeasonArray, _xlpm.ReturnArray))))</definedName>
-    <definedName name="M1_Table_I_j_k_l">#REF!</definedName>
-    <definedName name="M1_Table_MA_j_k45">#REF!</definedName>
-    <definedName name="M1_Table_VS_j_k_l">#REF!</definedName>
-    <definedName name="M2_Table_I_j_k_l">#REF!</definedName>
     <definedName name="Result_CarbonRemovalsFromPlantings">Results!$E$56</definedName>
     <definedName name="Result_EmissionsForWholeProductionCycle_Method1" localSheetId="4">[1]Results!$E$42</definedName>
     <definedName name="Result_EmissionsForWholeProductionCycle_Method1">Results!$E$45</definedName>
@@ -287,6 +270,7 @@
     <definedName name="X_Cell_Site_AverageTemperature">'Input - Site'!$E$14</definedName>
     <definedName name="X_Cell_Site_ClimateZone">'Input - Site'!$E$20</definedName>
     <definedName name="X_Cell_Site_Elevation">'Input - Site'!$E$13</definedName>
+    <definedName name="X_Cell_Site_EndDate">'Input - Enterprise'!$E$13</definedName>
     <definedName name="X_Cell_Site_FarmName">'Input - Enterprise'!$E$7</definedName>
     <definedName name="X_Cell_Site_FrostDays">'Input - Site'!$E$17</definedName>
     <definedName name="X_Cell_Site_LeachingZone">'Input - Site'!$E$12</definedName>
@@ -2218,9 +2202,6 @@
     <cellStyle name="Variable type other" xfId="64" xr:uid="{105BD9DE-B567-4DA0-87E6-C60A0ECC1C65}"/>
   </cellStyles>
   <dxfs count="49">
-    <dxf>
-      <numFmt numFmtId="170" formatCode="[$-F800]dddd\,\ mmmm\ dd\,\ yyyy"/>
-    </dxf>
     <dxf>
       <font>
         <b val="0"/>
@@ -3086,6 +3067,9 @@
       </fill>
     </dxf>
     <dxf>
+      <numFmt numFmtId="170" formatCode="[$-F800]dddd\,\ mmmm\ dd\,\ yyyy"/>
+    </dxf>
+    <dxf>
       <font>
         <color theme="1" tint="0.24994659260841701"/>
       </font>
@@ -3475,7 +3459,7 @@
   <tableColumns count="6">
     <tableColumn id="6" xr3:uid="{84D8E3C0-97CA-4CF1-A63F-3CF6AAE07330}" name="Transaction name" dataCellStyle="Input text"/>
     <tableColumn id="1" xr3:uid="{E41B3FA3-55C1-4BBF-A477-D8EDBC89025E}" name="Class (select)" dataCellStyle="Input select"/>
-    <tableColumn id="2" xr3:uid="{3F9F09B6-E6B3-4323-AB6A-249C77DAFA51}" name="Sale date" dataDxfId="0"/>
+    <tableColumn id="2" xr3:uid="{3F9F09B6-E6B3-4323-AB6A-249C77DAFA51}" name="Sale date" dataDxfId="36"/>
     <tableColumn id="3" xr3:uid="{48DB24D2-2F89-4EEB-911F-2F24089C3918}" name="Head sold"/>
     <tableColumn id="4" xr3:uid="{879FC871-5C62-44BF-952F-ACBA1C3B6AE4}" name="Average weight per head (kg)"/>
     <tableColumn id="5" xr3:uid="{B8588D76-BACA-4516-8963-B7E8E5A87B93}" name="Total liveweight sold" dataCellStyle="Input number general calculated">
@@ -3532,7 +3516,7 @@
     <tableColumn id="1" xr3:uid="{AEB37CE8-5689-4CCA-AF1D-E45E37F37CC1}" name="Is in leaching zone">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_FracWET_Data(),Table_SourceData_FracWET[[#Headers],[Is in leaching zone]],0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="2" xr3:uid="{8ABB6BDF-FE17-4B3B-BDE2-B9AAF30FF3BD}" name="FracWET" dataDxfId="20">
+    <tableColumn id="2" xr3:uid="{8ABB6BDF-FE17-4B3B-BDE2-B9AAF30FF3BD}" name="FracWET" dataDxfId="19">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_FracWET_Data(),Table_SourceData_FracWET[[#Headers],[Is in leaching zone]],0)</calculatedColumnFormula>
     </tableColumn>
   </tableColumns>
@@ -3580,7 +3564,7 @@
     <tableColumn id="1" xr3:uid="{1EE4C9C2-CE36-41D3-A67F-CC85678D8B80}" name="Irrigation type i">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_FracWETIrrigation_Data(), Table_SourceData_FracWETIrrigation[[#Headers],[Irrigation type i]], 0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="2" xr3:uid="{DD5CBEE2-8756-4D0C-9A90-6E931CF609D0}" name="FracWET" dataDxfId="19" dataCellStyle="Content normal">
+    <tableColumn id="2" xr3:uid="{DD5CBEE2-8756-4D0C-9A90-6E931CF609D0}" name="FracWET" dataDxfId="18" dataCellStyle="Content normal">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_FracWETIrrigation_Data(), Table_SourceData_FracWETIrrigation[[#Headers],[Irrigation type i]], 0)</calculatedColumnFormula>
     </tableColumn>
   </tableColumns>
@@ -3598,7 +3582,7 @@
     <tableColumn id="1" xr3:uid="{76483A9E-91D3-4695-AB70-E830E24596D9}" name="Climate zone">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_EFPastureRangeAndPaddock_Data(), Table_SourceData_EFPastureRangeAndPaddock[[#Headers],[Climate zone]], 0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="2" xr3:uid="{1127A673-CAEF-41F9-A48A-D438D3FFF619}" name="EFPRP" dataDxfId="18" dataCellStyle="Content normal">
+    <tableColumn id="2" xr3:uid="{1127A673-CAEF-41F9-A48A-D438D3FFF619}" name="EFPRP" dataDxfId="17" dataCellStyle="Content normal">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_EFPastureRangeAndPaddock_Data(), Table_SourceData_EFPastureRangeAndPaddock[[#Headers],[Climate zone]], 0)</calculatedColumnFormula>
     </tableColumn>
   </tableColumns>
@@ -3616,7 +3600,7 @@
     <tableColumn id="1" xr3:uid="{A2A66992-064C-4170-856F-B81D835CEE21}" name="Month">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MonthsToSeasons_Data(), Table_SourceData_Common_MonthToSeason[[#Headers],[Month]], 0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="2" xr3:uid="{48B6FC8D-6503-4BB2-B07D-00597C808CB0}" name="Season" dataDxfId="17" dataCellStyle="Content normal">
+    <tableColumn id="2" xr3:uid="{48B6FC8D-6503-4BB2-B07D-00597C808CB0}" name="Season" dataDxfId="16" dataCellStyle="Content normal">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MonthsToSeasons_Data(), Table_SourceData_Common_MonthToSeason[[#Headers],[Month]], 0)</calculatedColumnFormula>
     </tableColumn>
   </tableColumns>
@@ -3648,49 +3632,49 @@
     <tableColumn id="1" xr3:uid="{D344A8E3-CBAD-4F7E-B0CA-85C4550A31FF}" name="Temperature zone">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="2" xr3:uid="{4C26B9B4-F509-4ACF-A306-F52C2D83B94C}" name="MAT (ºC)" dataDxfId="16" dataCellStyle="Content normal">
+    <tableColumn id="2" xr3:uid="{4C26B9B4-F509-4ACF-A306-F52C2D83B94C}" name="MAT (ºC)" dataDxfId="15" dataCellStyle="Content normal">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="3" xr3:uid="{06D3FCFB-672E-43AB-BAD6-C5F3A36DC255}" name="Anaerobic lagoon" dataDxfId="15" dataCellStyle="Content normal">
+    <tableColumn id="3" xr3:uid="{06D3FCFB-672E-43AB-BAD6-C5F3A36DC255}" name="Anaerobic lagoon" dataDxfId="14" dataCellStyle="Content normal">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="4" xr3:uid="{286B0E39-9F46-4519-A952-1FCC90F0A23E}" name="Digester / covered lagoons" dataDxfId="14" dataCellStyle="Content normal">
+    <tableColumn id="4" xr3:uid="{286B0E39-9F46-4519-A952-1FCC90F0A23E}" name="Digester / covered lagoons" dataDxfId="13" dataCellStyle="Content normal">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="5" xr3:uid="{CAB3566B-B894-433E-9D4A-4CA76B82C3BD}" name="Liquid systems" dataDxfId="13" dataCellStyle="Content normal">
+    <tableColumn id="5" xr3:uid="{CAB3566B-B894-433E-9D4A-4CA76B82C3BD}" name="Liquid systems" dataDxfId="12" dataCellStyle="Content normal">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="6" xr3:uid="{6D655DEC-7C3C-4046-9046-7ABE03AF26CA}" name="Daily spread" dataDxfId="12" dataCellStyle="Content normal">
+    <tableColumn id="6" xr3:uid="{6D655DEC-7C3C-4046-9046-7ABE03AF26CA}" name="Daily spread" dataDxfId="11" dataCellStyle="Content normal">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="7" xr3:uid="{DC01C908-9F78-404B-A8A9-081231B6DBAF}" name="Composting (passive windrow)" dataDxfId="11" dataCellStyle="Content normal">
+    <tableColumn id="7" xr3:uid="{DC01C908-9F78-404B-A8A9-081231B6DBAF}" name="Composting (passive windrow)" dataDxfId="10" dataCellStyle="Content normal">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="8" xr3:uid="{016BC200-DE2E-4607-9A3A-E48F6A72FB0F}" name="Solid storage" dataDxfId="10" dataCellStyle="Content normal">
+    <tableColumn id="8" xr3:uid="{016BC200-DE2E-4607-9A3A-E48F6A72FB0F}" name="Solid storage" dataDxfId="9" dataCellStyle="Content normal">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="9" xr3:uid="{3D073AF2-25E0-49BE-825D-D38FD86B34D8}" name="Pit storage" dataDxfId="9" dataCellStyle="Content normal">
+    <tableColumn id="9" xr3:uid="{3D073AF2-25E0-49BE-825D-D38FD86B34D8}" name="Pit storage" dataDxfId="8" dataCellStyle="Content normal">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="10" xr3:uid="{2C00D039-8FF7-4CF7-B97D-987BAE97BA35}" name="Deep litter" dataDxfId="8" dataCellStyle="Content normal">
+    <tableColumn id="10" xr3:uid="{2C00D039-8FF7-4CF7-B97D-987BAE97BA35}" name="Deep litter" dataDxfId="7" dataCellStyle="Content normal">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="11" xr3:uid="{C3FD2E13-24D5-402A-8C77-E324B6925825}" name="Poultry manure with bedding" dataDxfId="7" dataCellStyle="Content normal">
+    <tableColumn id="11" xr3:uid="{C3FD2E13-24D5-402A-8C77-E324B6925825}" name="Poultry manure with bedding" dataDxfId="6" dataCellStyle="Content normal">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="12" xr3:uid="{6CCAA4CD-85BD-481B-A987-0719DD47798C}" name="Poultry manure without bedding" dataDxfId="6" dataCellStyle="Content normal">
+    <tableColumn id="12" xr3:uid="{6CCAA4CD-85BD-481B-A987-0719DD47798C}" name="Poultry manure without bedding" dataDxfId="5" dataCellStyle="Content normal">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="13" xr3:uid="{12540CA2-E51E-45F0-A036-45D45913194C}" name="Direct processing" dataDxfId="5" dataCellStyle="Content normal">
+    <tableColumn id="13" xr3:uid="{12540CA2-E51E-45F0-A036-45D45913194C}" name="Direct processing" dataDxfId="4" dataCellStyle="Content normal">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="14" xr3:uid="{393A0B3F-42CD-412F-B1E5-79CF90491213}" name="Direct application" dataDxfId="4" dataCellStyle="Content normal">
+    <tableColumn id="14" xr3:uid="{393A0B3F-42CD-412F-B1E5-79CF90491213}" name="Direct application" dataDxfId="3" dataCellStyle="Content normal">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="15" xr3:uid="{44E9918F-2DF8-4DE9-AD76-C61362285599}" name="Pasture range and paddock" dataDxfId="3" dataCellStyle="Content normal">
+    <tableColumn id="15" xr3:uid="{44E9918F-2DF8-4DE9-AD76-C61362285599}" name="Pasture range and paddock" dataDxfId="2" dataCellStyle="Content normal">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="16" xr3:uid="{FE671AF8-F8E0-4322-B78A-1B6A3A96A4E0}" name="MAT raw" dataDxfId="2" dataCellStyle="Content normal">
+    <tableColumn id="16" xr3:uid="{FE671AF8-F8E0-4322-B78A-1B6A3A96A4E0}" name="MAT raw" dataDxfId="1" dataCellStyle="Content normal">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</calculatedColumnFormula>
     </tableColumn>
   </tableColumns>
@@ -3708,7 +3692,7 @@
     <tableColumn id="1" xr3:uid="{82DE88A1-FD3E-429F-81D0-81A0580D58D8}" name="Climate Zone">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_EFOrganicFertiliserAndCropResidues_Data(), Table_SourceData_Common_EFOrganicFertCropResidues[[#Headers],[Climate Zone]], 0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="2" xr3:uid="{3505652E-76CD-41ED-BC1F-830404A5E233}" name="EFNi &amp; EFN2Oi" dataDxfId="1" dataCellStyle="Content normal">
+    <tableColumn id="2" xr3:uid="{3505652E-76CD-41ED-BC1F-830404A5E233}" name="EFNi &amp; EFN2Oi" dataDxfId="0" dataCellStyle="Content normal">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_EFOrganicFertiliserAndCropResidues_Data(), Table_SourceData_Common_EFOrganicFertCropResidues[[#Headers],[Climate Zone]], 0)</calculatedColumnFormula>
     </tableColumn>
   </tableColumns>
@@ -3824,49 +3808,49 @@
     <tableColumn id="1" xr3:uid="{ED61DF3B-A431-4956-B923-158AD5BF4554}" name="Climate zone" totalsRowCellStyle="Content bold">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ClimateZones_Data(), Table_SourceData_ClimateZones[[#Headers],[Climate zone]], 0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="2" xr3:uid="{277D098C-8B59-4F56-B373-2BF7AAA9A607}" name="MAT" totalsRowDxfId="36" totalsRowCellStyle="Content bold">
+    <tableColumn id="2" xr3:uid="{277D098C-8B59-4F56-B373-2BF7AAA9A607}" name="MAT" totalsRowDxfId="35" totalsRowCellStyle="Content bold">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ClimateZones_Data(), Table_SourceData_ClimateZones[[#Headers],[Climate zone]], 0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="3" xr3:uid="{827CC720-B781-4728-ABFA-68C972B57850}" name="MAP" totalsRowDxfId="35" totalsRowCellStyle="Content bold">
+    <tableColumn id="3" xr3:uid="{827CC720-B781-4728-ABFA-68C972B57850}" name="MAP" totalsRowDxfId="34" totalsRowCellStyle="Content bold">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ClimateZones_Data(), Table_SourceData_ClimateZones[[#Headers],[Climate zone]], 0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="4" xr3:uid="{38653B97-E186-444A-AFBD-15CE44DEBED7}" name="Frost days per year" totalsRowDxfId="34" totalsRowCellStyle="Content bold">
+    <tableColumn id="4" xr3:uid="{38653B97-E186-444A-AFBD-15CE44DEBED7}" name="Frost days per year" totalsRowDxfId="33" totalsRowCellStyle="Content bold">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ClimateZones_Data(), Table_SourceData_ClimateZones[[#Headers],[Climate zone]], 0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="5" xr3:uid="{735BA31E-1D4B-45A4-B9FF-7F8ED5243D20}" name="Elevation" totalsRowDxfId="33" totalsRowCellStyle="Content bold">
+    <tableColumn id="5" xr3:uid="{735BA31E-1D4B-45A4-B9FF-7F8ED5243D20}" name="Elevation" totalsRowDxfId="32" totalsRowCellStyle="Content bold">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ClimateZones_Data(), Table_SourceData_ClimateZones[[#Headers],[Climate zone]], 0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="6" xr3:uid="{370BE1BB-C3DF-4E43-B8DD-B18D69884A4B}" name="MAP:PET" totalsRowDxfId="32" totalsRowCellStyle="Content bold">
+    <tableColumn id="6" xr3:uid="{370BE1BB-C3DF-4E43-B8DD-B18D69884A4B}" name="MAP:PET" totalsRowDxfId="31" totalsRowCellStyle="Content bold">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ClimateZones_Data(), Table_SourceData_ClimateZones[[#Headers],[Climate zone]], 0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="7" xr3:uid="{37A53713-47F8-4F27-9505-8BED300E0222}" name="Min temp" totalsRowDxfId="31" totalsRowCellStyle="Content bold">
+    <tableColumn id="7" xr3:uid="{37A53713-47F8-4F27-9505-8BED300E0222}" name="Min temp" totalsRowDxfId="30" totalsRowCellStyle="Content bold">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ClimateZones_Data(), Table_SourceData_ClimateZones[[#Headers],[Climate zone]], 0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="8" xr3:uid="{D9399681-9FC5-41A0-A367-D4D41BBB28CA}" name="Max temp" totalsRowDxfId="30" totalsRowCellStyle="Content bold">
+    <tableColumn id="8" xr3:uid="{D9399681-9FC5-41A0-A367-D4D41BBB28CA}" name="Max temp" totalsRowDxfId="29" totalsRowCellStyle="Content bold">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ClimateZones_Data(), Table_SourceData_ClimateZones[[#Headers],[Climate zone]], 0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="9" xr3:uid="{65211A71-1ABE-4E6D-843C-B0028543D400}" name="Min rainfall" totalsRowDxfId="29" totalsRowCellStyle="Content bold">
+    <tableColumn id="9" xr3:uid="{65211A71-1ABE-4E6D-843C-B0028543D400}" name="Min rainfall" totalsRowDxfId="28" totalsRowCellStyle="Content bold">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ClimateZones_Data(), Table_SourceData_ClimateZones[[#Headers],[Climate zone]], 0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="10" xr3:uid="{8ED03576-B413-4D12-B37A-5F11E15AA54D}" name="Max rainfall" totalsRowDxfId="28" totalsRowCellStyle="Content bold">
+    <tableColumn id="10" xr3:uid="{8ED03576-B413-4D12-B37A-5F11E15AA54D}" name="Max rainfall" totalsRowDxfId="27" totalsRowCellStyle="Content bold">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ClimateZones_Data(), Table_SourceData_ClimateZones[[#Headers],[Climate zone]], 0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="11" xr3:uid="{E749576A-EB5F-4709-BD15-9BD4E87548D5}" name="Min frost days" totalsRowDxfId="27" totalsRowCellStyle="Content bold">
+    <tableColumn id="11" xr3:uid="{E749576A-EB5F-4709-BD15-9BD4E87548D5}" name="Min frost days" totalsRowDxfId="26" totalsRowCellStyle="Content bold">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ClimateZones_Data(), Table_SourceData_ClimateZones[[#Headers],[Climate zone]], 0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="15" xr3:uid="{61CC0B40-56FD-487C-A589-45456757E8A1}" name="Max frost days" totalsRowDxfId="26" totalsRowCellStyle="Content bold">
+    <tableColumn id="15" xr3:uid="{61CC0B40-56FD-487C-A589-45456757E8A1}" name="Max frost days" totalsRowDxfId="25" totalsRowCellStyle="Content bold">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ClimateZones_Data(), Table_SourceData_ClimateZones[[#Headers],[Climate zone]], 0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="12" xr3:uid="{32B52E24-5576-47A4-A024-CDC090D88746}" name="Min elevation" totalsRowDxfId="25" totalsRowCellStyle="Content bold">
+    <tableColumn id="12" xr3:uid="{32B52E24-5576-47A4-A024-CDC090D88746}" name="Min elevation" totalsRowDxfId="24" totalsRowCellStyle="Content bold">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ClimateZones_Data(), Table_SourceData_ClimateZones[[#Headers],[Climate zone]], 0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="16" xr3:uid="{B4341912-AB7E-4E58-9B4D-9791D45FB352}" name="Max elevation" totalsRowDxfId="24" totalsRowCellStyle="Content bold">
+    <tableColumn id="16" xr3:uid="{B4341912-AB7E-4E58-9B4D-9791D45FB352}" name="Max elevation" totalsRowDxfId="23" totalsRowCellStyle="Content bold">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ClimateZones_Data(), Table_SourceData_ClimateZones[[#Headers],[Climate zone]], 0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="13" xr3:uid="{67418986-6C11-45D0-A4DC-D7861BD61C09}" name="Min MAP:PET" totalsRowDxfId="23" totalsRowCellStyle="Content bold">
+    <tableColumn id="13" xr3:uid="{67418986-6C11-45D0-A4DC-D7861BD61C09}" name="Min MAP:PET" totalsRowDxfId="22" totalsRowCellStyle="Content bold">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ClimateZones_Data(), Table_SourceData_ClimateZones[[#Headers],[Climate zone]], 0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="17" xr3:uid="{90614980-AE79-4306-A6ED-229525821D94}" name="Max MAP:PET" totalsRowDxfId="22" totalsRowCellStyle="Content bold">
+    <tableColumn id="17" xr3:uid="{90614980-AE79-4306-A6ED-229525821D94}" name="Max MAP:PET" totalsRowDxfId="21" totalsRowCellStyle="Content bold">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ClimateZones_Data(), Table_SourceData_ClimateZones[[#Headers],[Climate zone]], 0)</calculatedColumnFormula>
     </tableColumn>
   </tableColumns>
@@ -3884,7 +3868,7 @@
     <tableColumn id="1" xr3:uid="{FEB61CA1-B375-461F-AD5A-5B01A03F7A14}" name="Climate zone" totalsRowCellStyle="Content bold">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_WetAndDryZones_Data(), Table_SourceData_WetDryZones[[#Headers],[Climate zone]], 0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="2" xr3:uid="{EE3C7A00-6DDA-427C-9573-7908B05111FB}" name="Wet or Dry Zone" totalsRowDxfId="21" totalsRowCellStyle="Content bold">
+    <tableColumn id="2" xr3:uid="{EE3C7A00-6DDA-427C-9573-7908B05111FB}" name="Wet or Dry Zone" totalsRowDxfId="20" totalsRowCellStyle="Content bold">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_WetAndDryZones_Data(), Table_SourceData_WetDryZones[[#Headers],[Climate zone]], 0)</calculatedColumnFormula>
     </tableColumn>
   </tableColumns>

--- a/Excel/Enterprises/Enterprise_Dairy_Template_WIP_v01.xlsx
+++ b/Excel/Enterprises/Enterprise_Dairy_Template_WIP_v01.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\htdocs\zneagcrc\GAF-VEERG-Functions\Excel\Enterprises\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3C53693E-BAEA-4112-BDD8-5094217B1264}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7D71B0AC-45A4-4F70-8D83-38B32B724417}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="2145" yWindow="2460" windowWidth="36255" windowHeight="19140" activeTab="3" xr2:uid="{992023F3-CAB7-4E5B-A348-08D563A0EF40}"/>
+    <workbookView xWindow="1320" yWindow="195" windowWidth="36255" windowHeight="19140" activeTab="1" xr2:uid="{992023F3-CAB7-4E5B-A348-08D563A0EF40}"/>
   </bookViews>
   <sheets>
     <sheet name="Home" sheetId="71" r:id="rId1"/>
@@ -346,7 +346,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="340" uniqueCount="210">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="330" uniqueCount="203">
   <si>
     <t>Home</t>
   </si>
@@ -409,21 +409,6 @@
   </si>
   <si>
     <t>Liveweight sold</t>
-  </si>
-  <si>
-    <t>Liveweight grown - method 1</t>
-  </si>
-  <si>
-    <t>Liveweight grown - method 2</t>
-  </si>
-  <si>
-    <t>Percent manure sold</t>
-  </si>
-  <si>
-    <t>Percent manure applied as fertiliser on own farm</t>
-  </si>
-  <si>
-    <t>Percent manure applied to soil with no purpose (as waste)</t>
   </si>
   <si>
     <t>tonnes</t>
@@ -810,15 +795,9 @@
     <t>Co-product</t>
   </si>
   <si>
-    <t>Manure used as fertiliser on own farm</t>
-  </si>
-  <si>
     <t>N/A</t>
   </si>
   <si>
-    <t>Residual product</t>
-  </si>
-  <si>
     <t>Carbon removals from plantings</t>
   </si>
   <si>
@@ -909,33 +888,12 @@
     <t>percent</t>
   </si>
   <si>
-    <t>Manure produced - method 1</t>
-  </si>
-  <si>
-    <t>Manure produced - method 2</t>
-  </si>
-  <si>
     <t>Percentage of income from liveweight sold</t>
   </si>
   <si>
     <t>Percentage of income from manure sold</t>
   </si>
   <si>
-    <t>=SUM(Enterprise_PastureBeef_InputFunctions.multiplyCorrespondingCells('Input - Pasture Beef'!X_Table_PastureBeef_Head_Method1, 'Input - Pasture Beef'!X_Table_PastureBeef_Duration_Method1, 'Input - Pasture Beef'!X_Table_PastureBeef_LiveweightGain_Method1))*10^-3</t>
-  </si>
-  <si>
-    <t>=SUM(Enterprise_PastureBeef_InputFunctions.multiplyCorrespondingCells('Input - Pasture Beef'!X_Table_PastureBeef_Head_Method2, 'Input - Pasture Beef'!X_Table_PastureBeef_Duration_Method2, 'Input - Pasture Beef'!X_Table_PastureBeef_LiveweightGain_Method2))*10^-3</t>
-  </si>
-  <si>
-    <t>=SUM(Enterprise_PastureBeef_InputFunctions.multiplyCorrespondingCells('Input - Pasture Beef'!X_Table_PastureBeef_Head_Method2, 'Input - Pasture Beef'!X_Table_PastureBeef_Duration_Method2, M2_Table_VS_j_k_l))*10^-3</t>
-  </si>
-  <si>
-    <t>=SUM(Table_Input_LivestockSales[Total liveweight sold])*10^-3</t>
-  </si>
-  <si>
-    <t>=SUM(Enterprise_PastureBeef_InputFunctions.multiplyCorrespondingCells('Input - Pasture Beef'!X_Table_PastureBeef_Head_Method1, 'Input - Pasture Beef'!X_Table_PastureBeef_Duration_Method1, '4.2.1.1-2 Methane'!M1_Table_VS_j_k_l))*10^-3</t>
-  </si>
-  <si>
     <t>Product emissions - Mass</t>
   </si>
   <si>
@@ -1030,6 +988,27 @@
   </si>
   <si>
     <t>Total liveweight sold</t>
+  </si>
+  <si>
+    <t>Milk produced</t>
+  </si>
+  <si>
+    <t>Milk produced unit</t>
+  </si>
+  <si>
+    <t>Percentage of income from milk sold</t>
+  </si>
+  <si>
+    <t>Manure sold</t>
+  </si>
+  <si>
+    <t>Milk sold - excluding removals</t>
+  </si>
+  <si>
+    <t>Milk sold - net emissions</t>
+  </si>
+  <si>
+    <t>t co2e/t milk solids</t>
   </si>
 </sst>
 </file>
@@ -1948,9 +1927,6 @@
     <xf numFmtId="9" fontId="2" fillId="0" borderId="2" xfId="16">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="9" fontId="25" fillId="4" borderId="2" xfId="68" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="8" applyFont="1" applyFill="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
@@ -2129,6 +2105,7 @@
     <xf numFmtId="170" fontId="0" fillId="0" borderId="0" xfId="8" applyNumberFormat="1" applyFont="1" applyFill="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="69">
     <cellStyle name="Alert" xfId="59" xr:uid="{34EFE908-8095-4010-8F93-8CFE88055637}"/>
@@ -4205,7 +4182,7 @@
     <tabColor rgb="FF0C769E"/>
     <pageSetUpPr autoPageBreaks="0"/>
   </sheetPr>
-  <dimension ref="A1:K87"/>
+  <dimension ref="A1:K88"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="30.7109375" customWidth="1"/>
@@ -4221,7 +4198,7 @@
         <v>#VALUE!</v>
       </c>
       <c r="C1" s="22" t="s">
-        <v>193</v>
+        <v>179</v>
       </c>
     </row>
     <row r="2" spans="1:11" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
@@ -4306,7 +4283,7 @@
       </c>
       <c r="C7" s="9"/>
       <c r="D7" s="1" t="s">
-        <v>194</v>
+        <v>180</v>
       </c>
       <c r="E7" s="19" t="e" cm="1">
         <f t="array" ref="E7">VEERG_3_3_1_1__1_TotalAnnualMethaneFromEntericFermentationVariation_Result_Method1</f>
@@ -4339,7 +4316,7 @@
       </c>
       <c r="C8" s="9"/>
       <c r="D8" s="1" t="s">
-        <v>195</v>
+        <v>181</v>
       </c>
       <c r="E8" s="19" t="e" cm="1">
         <f t="array" ref="E8">VEERG_4_3_1_1__1_TotalAnnualMethaneFromManureManagement_Result_Method1</f>
@@ -4369,7 +4346,7 @@
       <c r="A9" s="5"/>
       <c r="C9" s="9"/>
       <c r="D9" s="1" t="s">
-        <v>196</v>
+        <v>182</v>
       </c>
       <c r="E9" s="19" t="e" cm="1">
         <f t="array" ref="E9">VEERG_4_3_1_3__1_TotalAnnualDirectNitrousOxideEmissionsFromMMS_Result_Method1</f>
@@ -4401,7 +4378,7 @@
       </c>
       <c r="C10" s="9"/>
       <c r="D10" s="1" t="s">
-        <v>197</v>
+        <v>183</v>
       </c>
       <c r="E10" s="19" t="e" cm="1">
         <f t="array" ref="E10">VEERG_4_3_1_5__1_AnnualAtmosphericDepositionEmissionsFromMMS_Result_Method1</f>
@@ -4434,7 +4411,7 @@
       </c>
       <c r="C11" s="9"/>
       <c r="D11" s="1" t="s">
-        <v>198</v>
+        <v>184</v>
       </c>
       <c r="E11" s="19" t="e" cm="1">
         <f t="array" ref="E11">VEERG_4_3_1_6__1_AnnualEmissionsFromLeachingAndRunoffFromMMS_Result_Method1</f>
@@ -4467,7 +4444,7 @@
       </c>
       <c r="C12" s="9"/>
       <c r="D12" s="1" t="s">
-        <v>199</v>
+        <v>185</v>
       </c>
       <c r="E12" s="19" t="e" cm="1">
         <f t="array" ref="E12">VEERG_4_3_1_9__1_DirectNitrousOxideEmissionsOnPasture_Result_Method1</f>
@@ -4500,7 +4477,7 @@
       </c>
       <c r="C13" s="9"/>
       <c r="D13" s="1" t="s">
-        <v>200</v>
+        <v>186</v>
       </c>
       <c r="E13" s="19" t="e" cm="1">
         <f t="array" ref="E13">VEERG_4_3_1_10__1_AtmosphericDepositionEmissionsFromUrineAndDungOnPasture_Result_Method1</f>
@@ -4533,7 +4510,7 @@
       </c>
       <c r="C14" s="9"/>
       <c r="D14" s="1" t="s">
-        <v>201</v>
+        <v>187</v>
       </c>
       <c r="E14" s="19" t="e" cm="1">
         <f t="array" ref="E14">VEERG_4_3_1_12__1_LeachingAndRunoffEmissionsFromUrineAndDungOnPasture_Result_Method1</f>
@@ -4563,7 +4540,7 @@
       <c r="A15" s="5"/>
       <c r="C15" s="9"/>
       <c r="D15" s="1" t="s">
-        <v>151</v>
+        <v>144</v>
       </c>
       <c r="E15" s="19" t="e" cm="1">
         <f t="array" ref="E15">VEERG_5_1_1_1__1_InorganicFertiliserApplicationN2OEmissions_Result_Method1</f>
@@ -4595,7 +4572,7 @@
       </c>
       <c r="C16" s="9"/>
       <c r="D16" s="1" t="s">
-        <v>152</v>
+        <v>145</v>
       </c>
       <c r="E16" s="19" t="e" cm="1">
         <f t="array" ref="E16">VEERG_5_1_1_3__1_InorganicFertiliserApplicationCO2Emissions_Result_Method1</f>
@@ -4606,7 +4583,7 @@
         <v>#NAME?</v>
       </c>
       <c r="G16" s="16" t="s">
-        <v>141</v>
+        <v>134</v>
       </c>
       <c r="H16" s="19" t="e">
         <f>E16</f>
@@ -4628,7 +4605,7 @@
       </c>
       <c r="C17" s="9"/>
       <c r="D17" s="1" t="s">
-        <v>153</v>
+        <v>146</v>
       </c>
       <c r="E17" s="19" t="e" cm="1">
         <f t="array" ref="E17">VEERG_5_2_1_1__2_MassOfNitrogenInOrganicFertiliser_Result_Method1</f>
@@ -4661,7 +4638,7 @@
       </c>
       <c r="C18" s="9"/>
       <c r="D18" s="1" t="s">
-        <v>154</v>
+        <v>147</v>
       </c>
       <c r="E18" s="19" t="e" cm="1">
         <f t="array" ref="E18">VEERG_5_3_1_1__1_LimeApplicationCO2Emissions_Result_Method1</f>
@@ -4672,7 +4649,7 @@
         <v>#NAME?</v>
       </c>
       <c r="G18" s="16" t="s">
-        <v>141</v>
+        <v>134</v>
       </c>
       <c r="H18" s="19" t="e">
         <f>E18</f>
@@ -4694,7 +4671,7 @@
       </c>
       <c r="C19" s="9"/>
       <c r="D19" s="1" t="s">
-        <v>155</v>
+        <v>148</v>
       </c>
       <c r="E19" s="19" t="e" cm="1">
         <f t="array" ref="E19">VEERG_5_4_1_3__1_OrganicFertiliserAtmosphericDepositionN2OEmissions_Result_Method1</f>
@@ -4727,7 +4704,7 @@
       </c>
       <c r="C20" s="9"/>
       <c r="D20" s="1" t="s">
-        <v>156</v>
+        <v>149</v>
       </c>
       <c r="E20" s="19" t="e" cm="1">
         <f t="array" ref="E20">VEERG_5_5_1_1__1_FertiliserLeachingAndRunoffN2OEmissions_result_Method1</f>
@@ -4756,7 +4733,7 @@
     <row r="21" spans="1:11" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C21" s="9"/>
       <c r="D21" s="1" t="s">
-        <v>157</v>
+        <v>150</v>
       </c>
       <c r="E21" s="19" t="e" cm="1">
         <f t="array" ref="E21">VEERG_6_2_1_1__1__NitrousOxideEmissionsFromPastureResidues_Result_Method1</f>
@@ -4786,7 +4763,7 @@
       <c r="A22" s="5"/>
       <c r="C22" s="9"/>
       <c r="D22" s="1" t="s">
-        <v>158</v>
+        <v>151</v>
       </c>
       <c r="E22" s="19" t="e" cm="1">
         <f t="array" ref="E22">VEERG_6_3_1_1__1__LeachingAndRunoffEmissionsCropAndPastureResidue_PastureOnly_Result_Method1</f>
@@ -4816,7 +4793,7 @@
       <c r="A23" s="5"/>
       <c r="C23" s="9"/>
       <c r="D23" s="1" t="s">
-        <v>159</v>
+        <v>152</v>
       </c>
       <c r="E23" s="19" t="e" cm="1">
         <f t="array" ref="E23">VEERG_8_1_1_1__1_FuelCombustionTransport_Result_CO2</f>
@@ -4827,7 +4804,7 @@
         <v>#NAME?</v>
       </c>
       <c r="G23" s="16" t="s">
-        <v>141</v>
+        <v>134</v>
       </c>
       <c r="H23" s="19" t="e">
         <f>E23</f>
@@ -4846,7 +4823,7 @@
       <c r="A24" s="5"/>
       <c r="C24" s="9"/>
       <c r="D24" s="1" t="s">
-        <v>161</v>
+        <v>154</v>
       </c>
       <c r="E24" s="19" t="e" cm="1">
         <f t="array" ref="E24">VEERG_8_1_1_1__1_FuelCombustionTransport_Result_CH4</f>
@@ -4875,7 +4852,7 @@
     <row r="25" spans="1:11" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C25" s="9"/>
       <c r="D25" s="1" t="s">
-        <v>160</v>
+        <v>153</v>
       </c>
       <c r="E25" s="19" t="e" cm="1">
         <f t="array" ref="E25">VEERG_8_1_1_1__1_FuelCombustionTransport_Result_N2O</f>
@@ -4904,7 +4881,7 @@
     <row r="26" spans="1:11" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C26" s="9"/>
       <c r="D26" s="1" t="s">
-        <v>162</v>
+        <v>155</v>
       </c>
       <c r="E26" s="19" t="e" cm="1">
         <f t="array" ref="E26">VEERG_8_2_1_1__1_FuelCombustionStationary_Result_CO2</f>
@@ -4915,7 +4892,7 @@
         <v>#NAME?</v>
       </c>
       <c r="G26" s="16" t="s">
-        <v>141</v>
+        <v>134</v>
       </c>
       <c r="H26" s="19" t="e">
         <f>E26</f>
@@ -4933,7 +4910,7 @@
     <row r="27" spans="1:11" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C27" s="9"/>
       <c r="D27" s="1" t="s">
-        <v>163</v>
+        <v>156</v>
       </c>
       <c r="E27" s="19" t="e" cm="1">
         <f t="array" ref="E27">VEERG_8_2_1_1__1_FuelCombustionStationary_Result_CH4</f>
@@ -4962,7 +4939,7 @@
     <row r="28" spans="1:11" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C28" s="9"/>
       <c r="D28" s="1" t="s">
-        <v>164</v>
+        <v>157</v>
       </c>
       <c r="E28" s="19" t="e" cm="1">
         <f t="array" ref="E28">VEERG_8_2_1_1__1_FuelCombustionStationary_Result_N2O</f>
@@ -4991,7 +4968,7 @@
     <row r="29" spans="1:11" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C29" s="9"/>
       <c r="D29" s="1" t="s">
-        <v>165</v>
+        <v>158</v>
       </c>
       <c r="E29" s="19" t="e" cm="1">
         <f t="array" ref="E29">VEERG_14_1_1__1_LocationBasedScopeElectricityEmissions_Result_Method1</f>
@@ -5020,7 +4997,7 @@
     <row r="30" spans="1:11" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C30" s="9"/>
       <c r="D30" s="1" t="s">
-        <v>166</v>
+        <v>159</v>
       </c>
       <c r="E30" s="19" t="e" cm="1">
         <f t="array" ref="E30">VEERG_14_1_2__1_MarketBasedScopeElectricityEmissionsVariation_Result_Method1</f>
@@ -5103,7 +5080,7 @@
     <row r="35" spans="3:11" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C35" s="9"/>
       <c r="D35" s="2" t="s">
-        <v>122</v>
+        <v>117</v>
       </c>
       <c r="E35" s="1"/>
       <c r="F35" s="1"/>
@@ -5115,7 +5092,7 @@
     </row>
     <row r="36" spans="3:11" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C36" s="9"/>
-      <c r="D36" s="89" t="str" cm="1">
+      <c r="D36" s="88" t="str" cm="1">
         <f t="array" ref="D36">"There are " &amp; Common_InputFunctions.getOverlappingReportingCycles(X_Cell_Enterprise_ProductionTimeframeStart,X_Cell_Enterprise_ProductionTimeframeEnd,X_Cell_Site_StartDate) &amp; " emissions calculation periods that need to be completed before total product emissions can be determined."</f>
         <v>There are 3 emissions calculation periods that need to be completed before total product emissions can be determined.</v>
       </c>
@@ -5130,7 +5107,7 @@
     <row r="37" spans="3:11" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C37" s="9"/>
       <c r="D37" s="1" t="s">
-        <v>124</v>
+        <v>119</v>
       </c>
       <c r="E37" s="1"/>
       <c r="F37" s="1"/>
@@ -5154,7 +5131,7 @@
     <row r="39" spans="3:11" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C39" s="9"/>
       <c r="D39" s="21" t="s">
-        <v>123</v>
+        <v>118</v>
       </c>
       <c r="E39" s="21" t="s">
         <v>11</v>
@@ -5174,11 +5151,11 @@
         <f t="array" ref="D40:D42">Common_InputFunctions.getOverlappingReportingPeriods(X_Cell_Enterprise_ProductionTimeframeStart,X_Cell_Enterprise_ProductionTimeframeEnd,X_Cell_Site_StartDate)</f>
         <v>01 Jan 2023 to 31 Dec 2023</v>
       </c>
-      <c r="E40" s="87" t="str">
+      <c r="E40" s="86" t="str">
         <f>IF(ISBLANK($D40), "", IF(ISNUMBER(SEARCH("reporting", $D40)), Result_Enterprise_Method1, "Enter value"))</f>
         <v>Enter value</v>
       </c>
-      <c r="F40" s="87" t="str">
+      <c r="F40" s="86" t="str">
         <f>IF(ISBLANK($D40), "", IF(ISNUMBER(SEARCH("reporting", $D40)), Result_Enterprise_Method2, "Enter value"))</f>
         <v>Enter value</v>
       </c>
@@ -5195,11 +5172,11 @@
       <c r="D41" s="1" t="str">
         <v>01 Jan 2024 to 31 Dec 2024 (This reporting cycle)</v>
       </c>
-      <c r="E41" s="87" t="e">
+      <c r="E41" s="86" t="e">
         <f>IF(ISBLANK($D41), "", IF(ISNUMBER(SEARCH("reporting", $D41)), Result_Enterprise_Method1, "Enter value"))</f>
         <v>#NAME?</v>
       </c>
-      <c r="F41" s="87" t="e">
+      <c r="F41" s="86" t="e">
         <f>IF(ISBLANK($D41), "", IF(ISNUMBER(SEARCH("reporting", $D41)), Result_Enterprise_Method2, "Enter value"))</f>
         <v>#NAME?</v>
       </c>
@@ -5216,11 +5193,11 @@
       <c r="D42" s="1" t="str">
         <v>01 Jan 2025 to 31 Dec 2025</v>
       </c>
-      <c r="E42" s="87" t="str">
+      <c r="E42" s="86" t="str">
         <f>IF(ISBLANK($D42), "", IF(ISNUMBER(SEARCH("reporting", $D42)), Result_Enterprise_Method1, "Enter value"))</f>
         <v>Enter value</v>
       </c>
-      <c r="F42" s="87" t="str">
+      <c r="F42" s="86" t="str">
         <f>IF(ISBLANK($D42), "", IF(ISNUMBER(SEARCH("reporting", $D42)), Result_Enterprise_Method2, "Enter value"))</f>
         <v>Enter value</v>
       </c>
@@ -5235,11 +5212,11 @@
     <row r="43" spans="3:11" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C43" s="9"/>
       <c r="D43" s="1"/>
-      <c r="E43" s="87" t="str">
+      <c r="E43" s="86" t="str">
         <f>IF(ISBLANK($D43), "", IF(ISNUMBER(SEARCH("reporting", $D43)), Result_Enterprise_Method1, "Enter value"))</f>
         <v/>
       </c>
-      <c r="F43" s="87" t="str">
+      <c r="F43" s="86" t="str">
         <f>IF(ISBLANK($D43), "", IF(ISNUMBER(SEARCH("reporting", $D43)), Result_Enterprise_Method2, "Enter value"))</f>
         <v/>
       </c>
@@ -5253,12 +5230,12 @@
     </row>
     <row r="44" spans="3:11" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C44" s="9"/>
-      <c r="D44" s="89"/>
-      <c r="E44" s="87" t="str">
+      <c r="D44" s="88"/>
+      <c r="E44" s="86" t="str">
         <f>IF(ISBLANK($D44), "", IF(ISNUMBER(SEARCH("reporting", $D44)), Result_Enterprise_Method1, "Enter value"))</f>
         <v/>
       </c>
-      <c r="F44" s="87" t="str">
+      <c r="F44" s="86" t="str">
         <f>IF(ISBLANK($D44), "", IF(ISNUMBER(SEARCH("reporting", $D44)), Result_Enterprise_Method2, "Enter value"))</f>
         <v/>
       </c>
@@ -5273,7 +5250,7 @@
     <row r="45" spans="3:11" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C45" s="9"/>
       <c r="D45" s="15" t="s">
-        <v>142</v>
+        <v>135</v>
       </c>
       <c r="E45" s="20" t="e">
         <f>SUM(E40:E44)</f>
@@ -5314,7 +5291,7 @@
     <row r="48" spans="3:11" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C48" s="9"/>
       <c r="D48" s="2" t="s">
-        <v>139</v>
+        <v>132</v>
       </c>
       <c r="E48" s="1"/>
       <c r="F48" s="1"/>
@@ -5338,10 +5315,10 @@
     <row r="50" spans="3:11" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C50" s="9"/>
       <c r="D50" s="21" t="s">
-        <v>123</v>
+        <v>118</v>
       </c>
       <c r="E50" s="21" t="s">
-        <v>140</v>
+        <v>133</v>
       </c>
       <c r="F50" s="1"/>
       <c r="G50" s="1"/>
@@ -5356,12 +5333,12 @@
         <f t="array" ref="D51:D53">Common_InputFunctions.getOverlappingReportingPeriods(X_Cell_Enterprise_ProductionTimeframeStart,X_Cell_Enterprise_ProductionTimeframeEnd,X_Cell_Site_StartDate)</f>
         <v>01 Jan 2023 to 31 Dec 2023</v>
       </c>
-      <c r="E51" s="87" t="str">
+      <c r="E51" s="86" t="str">
         <f>IF(ISBLANK(D51), "", "Enter value")</f>
         <v>Enter value</v>
       </c>
       <c r="F51" s="16" t="s">
-        <v>141</v>
+        <v>134</v>
       </c>
       <c r="G51" s="1"/>
       <c r="H51" s="1"/>
@@ -5374,12 +5351,12 @@
       <c r="D52" s="1" t="str">
         <v>01 Jan 2024 to 31 Dec 2024 (This reporting cycle)</v>
       </c>
-      <c r="E52" s="87" t="str">
+      <c r="E52" s="86" t="str">
         <f t="shared" ref="E52:E55" si="1">IF(ISBLANK(D52), "", "Enter value")</f>
         <v>Enter value</v>
       </c>
       <c r="F52" s="16" t="s">
-        <v>141</v>
+        <v>134</v>
       </c>
       <c r="G52" s="1"/>
       <c r="H52" s="1"/>
@@ -5392,12 +5369,12 @@
       <c r="D53" s="1" t="str">
         <v>01 Jan 2025 to 31 Dec 2025</v>
       </c>
-      <c r="E53" s="87" t="str">
+      <c r="E53" s="86" t="str">
         <f t="shared" si="1"/>
         <v>Enter value</v>
       </c>
       <c r="F53" s="16" t="s">
-        <v>141</v>
+        <v>134</v>
       </c>
       <c r="G53" s="1"/>
       <c r="H53" s="1"/>
@@ -5408,12 +5385,12 @@
     <row r="54" spans="3:11" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C54" s="9"/>
       <c r="D54" s="1"/>
-      <c r="E54" s="87" t="str">
+      <c r="E54" s="86" t="str">
         <f t="shared" si="1"/>
         <v/>
       </c>
       <c r="F54" s="16" t="s">
-        <v>141</v>
+        <v>134</v>
       </c>
       <c r="G54" s="1"/>
       <c r="H54" s="1"/>
@@ -5424,12 +5401,12 @@
     <row r="55" spans="3:11" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C55" s="9"/>
       <c r="D55" s="1"/>
-      <c r="E55" s="87" t="str">
+      <c r="E55" s="86" t="str">
         <f t="shared" si="1"/>
         <v/>
       </c>
       <c r="F55" s="16" t="s">
-        <v>141</v>
+        <v>134</v>
       </c>
       <c r="G55" s="1"/>
       <c r="H55" s="1"/>
@@ -5440,7 +5417,7 @@
     <row r="56" spans="3:11" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C56" s="9"/>
       <c r="D56" s="15" t="s">
-        <v>143</v>
+        <v>136</v>
       </c>
       <c r="E56" s="20">
         <f>SUM(E51:E54)</f>
@@ -5478,7 +5455,7 @@
     <row r="59" spans="3:11" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C59" s="9"/>
       <c r="D59" s="2" t="s">
-        <v>126</v>
+        <v>121</v>
       </c>
       <c r="E59" s="1"/>
       <c r="F59" s="1"/>
@@ -5503,10 +5480,10 @@
       <c r="C61" s="9"/>
       <c r="D61" s="21"/>
       <c r="E61" s="21" t="s">
-        <v>145</v>
+        <v>138</v>
       </c>
       <c r="F61" s="21" t="s">
-        <v>146</v>
+        <v>139</v>
       </c>
       <c r="G61" s="1"/>
       <c r="H61" s="1"/>
@@ -5516,14 +5493,14 @@
     </row>
     <row r="62" spans="3:11" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C62" s="9"/>
-      <c r="D62" s="90" t="s">
-        <v>144</v>
-      </c>
-      <c r="E62" s="88" t="e">
+      <c r="D62" s="89" t="s">
+        <v>137</v>
+      </c>
+      <c r="E62" s="87" t="e">
         <f>E45-E56</f>
         <v>#NAME?</v>
       </c>
-      <c r="F62" s="88" t="e">
+      <c r="F62" s="87" t="e">
         <f>F45-E56</f>
         <v>#NAME?</v>
       </c>
@@ -5557,8 +5534,8 @@
     </row>
     <row r="65" spans="3:11" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C65" s="9"/>
-      <c r="D65" s="92" t="s">
-        <v>178</v>
+      <c r="D65" s="91" t="s">
+        <v>164</v>
       </c>
       <c r="E65" s="1"/>
       <c r="F65" s="1"/>
@@ -5571,43 +5548,43 @@
     <row r="66" spans="3:11" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C66" s="9"/>
       <c r="D66" s="21" t="s">
-        <v>149</v>
+        <v>142</v>
       </c>
       <c r="E66" s="21" t="s">
-        <v>133</v>
+        <v>128</v>
       </c>
       <c r="F66" s="21" t="s">
+        <v>122</v>
+      </c>
+      <c r="G66" s="21" t="s">
+        <v>166</v>
+      </c>
+      <c r="H66" s="21" t="s">
+        <v>126</v>
+      </c>
+      <c r="I66" s="21" t="s">
         <v>127</v>
       </c>
-      <c r="G66" s="21" t="s">
-        <v>180</v>
-      </c>
-      <c r="H66" s="21" t="s">
-        <v>131</v>
-      </c>
-      <c r="I66" s="21" t="s">
-        <v>132</v>
-      </c>
       <c r="J66" s="21" t="s">
-        <v>128</v>
+        <v>123</v>
       </c>
       <c r="K66" s="9"/>
     </row>
     <row r="67" spans="3:11" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C67" s="9"/>
       <c r="D67" s="1" t="s">
-        <v>183</v>
+        <v>200</v>
       </c>
       <c r="E67" s="1" t="s">
-        <v>134</v>
-      </c>
-      <c r="F67" s="19" t="str">
-        <f>'Input - Enterprise'!E22</f>
-        <v>=SUM(Table_Input_LivestockSales[Total liveweight sold])*10^-3</v>
+        <v>129</v>
+      </c>
+      <c r="F67" s="19" t="e">
+        <f>'Input - Enterprise'!E24</f>
+        <v>#NAME?</v>
       </c>
       <c r="G67" s="19" t="e">
-        <f>F67/(F67+F69)</f>
-        <v>#VALUE!</v>
+        <f>F67/(F67+F69+F71)</f>
+        <v>#NAME?</v>
       </c>
       <c r="H67" s="19" t="e">
         <f>(Result_EmissionsForWholeProductionCycle_Method1/F67)*G67</f>
@@ -5618,25 +5595,25 @@
         <v>#NAME?</v>
       </c>
       <c r="J67" s="16" t="s">
-        <v>129</v>
+        <v>202</v>
       </c>
       <c r="K67" s="9"/>
     </row>
     <row r="68" spans="3:11" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C68" s="9"/>
       <c r="D68" s="1" t="s">
-        <v>184</v>
+        <v>201</v>
       </c>
       <c r="E68" s="1" t="s">
-        <v>134</v>
-      </c>
-      <c r="F68" s="19" t="str">
+        <v>129</v>
+      </c>
+      <c r="F68" s="19" t="e">
         <f>F67</f>
-        <v>=SUM(Table_Input_LivestockSales[Total liveweight sold])*10^-3</v>
+        <v>#NAME?</v>
       </c>
       <c r="G68" s="19" t="e">
         <f>G67</f>
-        <v>#VALUE!</v>
+        <v>#NAME?</v>
       </c>
       <c r="H68" s="19" t="e">
         <f>(Result_NetEmissions_Method1/F68)*G68</f>
@@ -5647,25 +5624,25 @@
         <v>#NAME?</v>
       </c>
       <c r="J68" s="16" t="s">
-        <v>129</v>
+        <v>202</v>
       </c>
       <c r="K68" s="9"/>
     </row>
     <row r="69" spans="3:11" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C69" s="9"/>
       <c r="D69" s="1" t="s">
-        <v>185</v>
+        <v>169</v>
       </c>
       <c r="E69" s="1" t="s">
-        <v>135</v>
-      </c>
-      <c r="F69" s="19" t="e">
-        <f>'Input - Enterprise'!E25*'Input - Enterprise'!E26</f>
-        <v>#VALUE!</v>
+        <v>129</v>
+      </c>
+      <c r="F69" s="19">
+        <f>'Input - Enterprise'!E22</f>
+        <v>5</v>
       </c>
       <c r="G69" s="19" t="e">
-        <f>F69/(F67+F69)</f>
-        <v>#VALUE!</v>
+        <f>F69/(F67+F69+F71)</f>
+        <v>#NAME?</v>
       </c>
       <c r="H69" s="19" t="e">
         <f>(Result_EmissionsForWholeProductionCycle_Method1/F69)*G69</f>
@@ -5676,25 +5653,25 @@
         <v>#NAME?</v>
       </c>
       <c r="J69" s="16" t="s">
-        <v>130</v>
+        <v>124</v>
       </c>
       <c r="K69" s="9"/>
     </row>
     <row r="70" spans="3:11" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C70" s="9"/>
       <c r="D70" s="1" t="s">
-        <v>186</v>
+        <v>170</v>
       </c>
       <c r="E70" s="1" t="s">
-        <v>135</v>
-      </c>
-      <c r="F70" s="19" t="e">
+        <v>129</v>
+      </c>
+      <c r="F70" s="19">
         <f>F69</f>
-        <v>#VALUE!</v>
+        <v>5</v>
       </c>
       <c r="G70" s="19" t="e">
         <f>G69</f>
-        <v>#VALUE!</v>
+        <v>#NAME?</v>
       </c>
       <c r="H70" s="19" t="e">
         <f>(Result_NetEmissions_Method1/F70)*G70</f>
@@ -5705,156 +5682,143 @@
         <v>#NAME?</v>
       </c>
       <c r="J70" s="16" t="s">
-        <v>130</v>
+        <v>124</v>
       </c>
       <c r="K70" s="9"/>
     </row>
     <row r="71" spans="3:11" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C71" s="9"/>
       <c r="D71" s="1" t="s">
-        <v>136</v>
+        <v>171</v>
       </c>
       <c r="E71" s="1" t="s">
-        <v>138</v>
-      </c>
-      <c r="F71" s="19" t="e">
-        <f>'Input - Enterprise'!E25*'Input - Enterprise'!E27</f>
-        <v>#VALUE!</v>
-      </c>
-      <c r="G71" s="19" t="s">
-        <v>137</v>
-      </c>
-      <c r="H71" s="19" t="s">
-        <v>137</v>
-      </c>
-      <c r="I71" s="19" t="s">
-        <v>137</v>
-      </c>
-      <c r="J71" s="9"/>
+        <v>130</v>
+      </c>
+      <c r="F71" s="19">
+        <f>'Input - Enterprise'!E25</f>
+        <v>1</v>
+      </c>
+      <c r="G71" s="19" t="e">
+        <f>F71/(F67+F69+F71)</f>
+        <v>#NAME?</v>
+      </c>
+      <c r="H71" s="19" t="e">
+        <f>(Result_EmissionsForWholeProductionCycle_Method1/F71)*G71</f>
+        <v>#NAME?</v>
+      </c>
+      <c r="I71" s="19" t="e">
+        <f>(Result_EmissionsForWholeProductionCycle_Method2/F71)*G71</f>
+        <v>#NAME?</v>
+      </c>
+      <c r="J71" s="16" t="s">
+        <v>125</v>
+      </c>
       <c r="K71" s="9"/>
     </row>
     <row r="72" spans="3:11" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C72" s="9"/>
-      <c r="D72" s="1"/>
-      <c r="E72" s="1"/>
-      <c r="F72" s="19"/>
-      <c r="G72" s="19"/>
-      <c r="H72" s="19"/>
-      <c r="I72" s="19"/>
-      <c r="J72" s="18"/>
+      <c r="D72" s="1" t="s">
+        <v>172</v>
+      </c>
+      <c r="E72" s="1" t="s">
+        <v>130</v>
+      </c>
+      <c r="F72" s="19">
+        <f>F71</f>
+        <v>1</v>
+      </c>
+      <c r="G72" s="19" t="e">
+        <f>G71</f>
+        <v>#NAME?</v>
+      </c>
+      <c r="H72" s="19" t="e">
+        <f>(Result_NetEmissions_Method1/F72)*G72</f>
+        <v>#NAME?</v>
+      </c>
+      <c r="I72" s="19" t="e">
+        <f>(Result_NetEmissions_Method2/F72)*G72</f>
+        <v>#NAME?</v>
+      </c>
+      <c r="J72" s="16" t="s">
+        <v>125</v>
+      </c>
       <c r="K72" s="9"/>
     </row>
     <row r="73" spans="3:11" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C73" s="9"/>
-      <c r="D73" s="92" t="s">
-        <v>179</v>
-      </c>
+      <c r="D73" s="1"/>
       <c r="E73" s="1"/>
-      <c r="F73" s="1"/>
-      <c r="G73" s="1"/>
-      <c r="H73" s="1"/>
-      <c r="I73" s="1"/>
-      <c r="J73" s="1"/>
+      <c r="F73" s="19"/>
+      <c r="G73" s="19"/>
+      <c r="H73" s="19"/>
+      <c r="I73" s="19"/>
+      <c r="J73" s="9"/>
       <c r="K73" s="9"/>
     </row>
     <row r="74" spans="3:11" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C74" s="9"/>
-      <c r="D74" s="21" t="s">
-        <v>149</v>
-      </c>
-      <c r="E74" s="21" t="s">
-        <v>133</v>
-      </c>
-      <c r="F74" s="21" t="s">
-        <v>127</v>
-      </c>
-      <c r="G74" s="21" t="s">
-        <v>181</v>
-      </c>
-      <c r="H74" s="21" t="s">
-        <v>131</v>
-      </c>
-      <c r="I74" s="21" t="s">
-        <v>132</v>
-      </c>
-      <c r="J74" s="21" t="s">
-        <v>128</v>
-      </c>
+      <c r="D74" s="1"/>
+      <c r="E74" s="1"/>
+      <c r="F74" s="19"/>
+      <c r="G74" s="19"/>
+      <c r="H74" s="19"/>
+      <c r="I74" s="19"/>
+      <c r="J74" s="18"/>
       <c r="K74" s="9"/>
     </row>
     <row r="75" spans="3:11" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C75" s="9"/>
-      <c r="D75" s="1" t="s">
-        <v>183</v>
-      </c>
-      <c r="E75" s="1" t="s">
-        <v>134</v>
-      </c>
-      <c r="F75" s="19" t="str">
-        <f>F67</f>
-        <v>=SUM(Table_Input_LivestockSales[Total liveweight sold])*10^-3</v>
-      </c>
-      <c r="G75" s="19">
-        <f>'Input - Enterprise'!E31</f>
-        <v>0.8</v>
-      </c>
-      <c r="H75" s="19" t="e">
-        <f>(Result_EmissionsForWholeProductionCycle_Method1/F75)*G75</f>
-        <v>#NAME?</v>
-      </c>
-      <c r="I75" s="19" t="e">
-        <f>(Result_EmissionsForWholeProductionCycle_Method2/F75)*G75</f>
-        <v>#NAME?</v>
-      </c>
-      <c r="J75" s="16" t="s">
-        <v>129</v>
-      </c>
+      <c r="D75" s="91" t="s">
+        <v>165</v>
+      </c>
+      <c r="E75" s="1"/>
+      <c r="F75" s="1"/>
+      <c r="G75" s="1"/>
+      <c r="H75" s="1"/>
+      <c r="I75" s="1"/>
+      <c r="J75" s="1"/>
       <c r="K75" s="9"/>
     </row>
     <row r="76" spans="3:11" ht="15.75" x14ac:dyDescent="0.25">
       <c r="C76" s="9"/>
-      <c r="D76" s="1" t="s">
-        <v>184</v>
-      </c>
-      <c r="E76" s="1" t="s">
-        <v>134</v>
-      </c>
-      <c r="F76" s="19" t="str">
-        <f>F67</f>
-        <v>=SUM(Table_Input_LivestockSales[Total liveweight sold])*10^-3</v>
-      </c>
-      <c r="G76" s="19">
-        <f>G75</f>
-        <v>0.8</v>
-      </c>
-      <c r="H76" s="19" t="e">
-        <f>(Result_NetEmissions_Method1/F76)*G76</f>
-        <v>#NAME?</v>
-      </c>
-      <c r="I76" s="19" t="e">
-        <f>(Result_NetEmissions_Method2/F76)*G76</f>
-        <v>#NAME?</v>
-      </c>
-      <c r="J76" s="16" t="s">
-        <v>129</v>
+      <c r="D76" s="21" t="s">
+        <v>142</v>
+      </c>
+      <c r="E76" s="21" t="s">
+        <v>128</v>
+      </c>
+      <c r="F76" s="21" t="s">
+        <v>122</v>
+      </c>
+      <c r="G76" s="21" t="s">
+        <v>167</v>
+      </c>
+      <c r="H76" s="21" t="s">
+        <v>126</v>
+      </c>
+      <c r="I76" s="21" t="s">
+        <v>127</v>
+      </c>
+      <c r="J76" s="21" t="s">
+        <v>123</v>
       </c>
       <c r="K76" s="9"/>
     </row>
     <row r="77" spans="3:11" ht="15.75" x14ac:dyDescent="0.25">
       <c r="C77" s="9"/>
       <c r="D77" s="1" t="s">
-        <v>185</v>
+        <v>200</v>
       </c>
       <c r="E77" s="1" t="s">
-        <v>135</v>
-      </c>
-      <c r="F77" s="19" t="e">
-        <f>F69</f>
-        <v>#VALUE!</v>
+        <v>129</v>
+      </c>
+      <c r="F77" s="94" t="e">
+        <f>F67</f>
+        <v>#NAME?</v>
       </c>
       <c r="G77" s="19">
-        <f>'Input - Enterprise'!E32</f>
-        <v>0.2</v>
+        <f>'Input - Enterprise'!E29</f>
+        <v>0.8</v>
       </c>
       <c r="H77" s="19" t="e">
         <f>(Result_EmissionsForWholeProductionCycle_Method1/F77)*G77</f>
@@ -5865,25 +5829,25 @@
         <v>#NAME?</v>
       </c>
       <c r="J77" s="16" t="s">
-        <v>130</v>
+        <v>202</v>
       </c>
       <c r="K77" s="9"/>
     </row>
     <row r="78" spans="3:11" ht="15.75" x14ac:dyDescent="0.25">
       <c r="C78" s="9"/>
       <c r="D78" s="1" t="s">
-        <v>186</v>
+        <v>201</v>
       </c>
       <c r="E78" s="1" t="s">
-        <v>135</v>
-      </c>
-      <c r="F78" s="19" t="e">
-        <f>F70</f>
-        <v>#VALUE!</v>
+        <v>129</v>
+      </c>
+      <c r="F78" s="94" t="e">
+        <f t="shared" ref="F78:I78" si="2">F68</f>
+        <v>#NAME?</v>
       </c>
       <c r="G78" s="19">
         <f>G77</f>
-        <v>0.2</v>
+        <v>0.8</v>
       </c>
       <c r="H78" s="19" t="e">
         <f>(Result_NetEmissions_Method1/F78)*G78</f>
@@ -5894,140 +5858,153 @@
         <v>#NAME?</v>
       </c>
       <c r="J78" s="16" t="s">
-        <v>130</v>
+        <v>202</v>
       </c>
       <c r="K78" s="9"/>
     </row>
     <row r="79" spans="3:11" ht="15.75" x14ac:dyDescent="0.25">
       <c r="C79" s="9"/>
       <c r="D79" s="1" t="s">
-        <v>136</v>
+        <v>169</v>
       </c>
       <c r="E79" s="1" t="s">
-        <v>138</v>
-      </c>
-      <c r="F79" s="19" t="e">
-        <f>F71</f>
-        <v>#VALUE!</v>
-      </c>
-      <c r="G79" s="19" t="s">
-        <v>137</v>
-      </c>
-      <c r="H79" s="19" t="s">
-        <v>137</v>
-      </c>
-      <c r="I79" s="19" t="s">
-        <v>137</v>
-      </c>
-      <c r="J79" s="9"/>
+        <v>129</v>
+      </c>
+      <c r="F79" s="19">
+        <f>F69</f>
+        <v>5</v>
+      </c>
+      <c r="G79" s="19">
+        <f>'Input - Enterprise'!E27</f>
+        <v>0.15</v>
+      </c>
+      <c r="H79" s="19" t="e">
+        <f>(Result_EmissionsForWholeProductionCycle_Method1/F79)*G79</f>
+        <v>#NAME?</v>
+      </c>
+      <c r="I79" s="19" t="e">
+        <f>(Result_EmissionsForWholeProductionCycle_Method2/F79)*G79</f>
+        <v>#NAME?</v>
+      </c>
+      <c r="J79" s="16" t="s">
+        <v>124</v>
+      </c>
       <c r="K79" s="9"/>
     </row>
     <row r="80" spans="3:11" ht="15.75" x14ac:dyDescent="0.25">
       <c r="C80" s="9"/>
-      <c r="D80" s="1"/>
-      <c r="E80" s="1"/>
-      <c r="F80" s="1"/>
-      <c r="G80" s="1"/>
-      <c r="H80" s="1"/>
-      <c r="I80" s="1"/>
-      <c r="J80" s="1"/>
+      <c r="D80" s="1" t="s">
+        <v>170</v>
+      </c>
+      <c r="E80" s="1" t="s">
+        <v>129</v>
+      </c>
+      <c r="F80" s="19">
+        <f>F69</f>
+        <v>5</v>
+      </c>
+      <c r="G80" s="19">
+        <f>G79</f>
+        <v>0.15</v>
+      </c>
+      <c r="H80" s="19" t="e">
+        <f>(Result_NetEmissions_Method1/F80)*G80</f>
+        <v>#NAME?</v>
+      </c>
+      <c r="I80" s="19" t="e">
+        <f>(Result_NetEmissions_Method2/F80)*G80</f>
+        <v>#NAME?</v>
+      </c>
+      <c r="J80" s="16" t="s">
+        <v>124</v>
+      </c>
       <c r="K80" s="9"/>
     </row>
-    <row r="81" spans="3:11" ht="18.75" x14ac:dyDescent="0.25">
+    <row r="81" spans="3:11" ht="15.75" x14ac:dyDescent="0.25">
       <c r="C81" s="9"/>
-      <c r="D81" s="92" t="s">
-        <v>182</v>
-      </c>
-      <c r="E81" s="1"/>
-      <c r="F81" s="1"/>
-      <c r="G81" s="1"/>
-      <c r="H81" s="1"/>
-      <c r="I81" s="1"/>
-      <c r="J81" s="1"/>
+      <c r="D81" s="1" t="s">
+        <v>171</v>
+      </c>
+      <c r="E81" s="1" t="s">
+        <v>130</v>
+      </c>
+      <c r="F81" s="19">
+        <f>F71</f>
+        <v>1</v>
+      </c>
+      <c r="G81" s="19">
+        <f>'Input - Enterprise'!E28</f>
+        <v>0.05</v>
+      </c>
+      <c r="H81" s="19" t="e">
+        <f>(Result_EmissionsForWholeProductionCycle_Method1/F81)*G81</f>
+        <v>#NAME?</v>
+      </c>
+      <c r="I81" s="19" t="e">
+        <f>(Result_EmissionsForWholeProductionCycle_Method2/F81)*G81</f>
+        <v>#NAME?</v>
+      </c>
+      <c r="J81" s="16" t="s">
+        <v>125</v>
+      </c>
       <c r="K81" s="9"/>
     </row>
     <row r="82" spans="3:11" ht="15.75" x14ac:dyDescent="0.25">
       <c r="C82" s="9"/>
-      <c r="D82" s="21" t="s">
-        <v>149</v>
-      </c>
-      <c r="E82" s="21" t="s">
-        <v>133</v>
-      </c>
-      <c r="F82" s="21" t="s">
-        <v>127</v>
-      </c>
-      <c r="G82" s="21" t="s">
-        <v>181</v>
-      </c>
-      <c r="H82" s="21" t="s">
-        <v>131</v>
-      </c>
-      <c r="I82" s="21" t="s">
-        <v>132</v>
-      </c>
-      <c r="J82" s="21" t="s">
-        <v>128</v>
+      <c r="D82" s="1" t="s">
+        <v>172</v>
+      </c>
+      <c r="E82" s="1" t="s">
+        <v>130</v>
+      </c>
+      <c r="F82" s="19">
+        <f>F72</f>
+        <v>1</v>
+      </c>
+      <c r="G82" s="19">
+        <f>G81</f>
+        <v>0.05</v>
+      </c>
+      <c r="H82" s="19" t="e">
+        <f>(Result_NetEmissions_Method1/F82)*G82</f>
+        <v>#NAME?</v>
+      </c>
+      <c r="I82" s="19" t="e">
+        <f>(Result_NetEmissions_Method2/F82)*G82</f>
+        <v>#NAME?</v>
+      </c>
+      <c r="J82" s="16" t="s">
+        <v>125</v>
       </c>
       <c r="K82" s="9"/>
     </row>
     <row r="83" spans="3:11" ht="15.75" x14ac:dyDescent="0.25">
       <c r="C83" s="9"/>
-      <c r="D83" s="1" t="s">
-        <v>147</v>
-      </c>
-      <c r="E83" s="1" t="s">
-        <v>137</v>
-      </c>
-      <c r="F83" s="19" t="str">
-        <f>'Input - Enterprise'!E23</f>
-        <v>=SUM(Enterprise_PastureBeef_InputFunctions.multiplyCorrespondingCells('Input - Pasture Beef'!X_Table_PastureBeef_Head_Method1, 'Input - Pasture Beef'!X_Table_PastureBeef_Duration_Method1, 'Input - Pasture Beef'!X_Table_PastureBeef_LiveweightGain_Method1))*10^-3</v>
-      </c>
-      <c r="G83" s="19" t="s">
-        <v>137</v>
-      </c>
-      <c r="H83" s="19" t="e">
-        <f>E62/F83</f>
-        <v>#NAME?</v>
-      </c>
-      <c r="I83" s="19" t="s">
-        <v>137</v>
-      </c>
-      <c r="J83" s="16" t="s">
-        <v>150</v>
-      </c>
+      <c r="D83" s="1"/>
+      <c r="E83" s="1"/>
+      <c r="F83" s="19"/>
+      <c r="G83" s="19"/>
+      <c r="H83" s="19"/>
+      <c r="I83" s="19"/>
+      <c r="J83" s="9"/>
       <c r="K83" s="9"/>
     </row>
     <row r="84" spans="3:11" ht="15.75" x14ac:dyDescent="0.25">
       <c r="C84" s="9"/>
-      <c r="D84" s="1" t="s">
-        <v>148</v>
-      </c>
-      <c r="E84" s="1" t="s">
-        <v>137</v>
-      </c>
-      <c r="F84" s="19" t="str">
-        <f>'Input - Enterprise'!E24</f>
-        <v>=SUM(Enterprise_PastureBeef_InputFunctions.multiplyCorrespondingCells('Input - Pasture Beef'!X_Table_PastureBeef_Head_Method2, 'Input - Pasture Beef'!X_Table_PastureBeef_Duration_Method2, 'Input - Pasture Beef'!X_Table_PastureBeef_LiveweightGain_Method2))*10^-3</v>
-      </c>
-      <c r="G84" s="19" t="s">
-        <v>137</v>
-      </c>
-      <c r="H84" s="19" t="s">
-        <v>137</v>
-      </c>
-      <c r="I84" s="19" t="e">
-        <f>F62/F84</f>
-        <v>#NAME?</v>
-      </c>
-      <c r="J84" s="16" t="s">
-        <v>150</v>
-      </c>
+      <c r="D84" s="1"/>
+      <c r="E84" s="1"/>
+      <c r="F84" s="1"/>
+      <c r="G84" s="1"/>
+      <c r="H84" s="1"/>
+      <c r="I84" s="1"/>
+      <c r="J84" s="1"/>
       <c r="K84" s="9"/>
     </row>
-    <row r="85" spans="3:11" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="85" spans="3:11" ht="18.75" x14ac:dyDescent="0.25">
       <c r="C85" s="9"/>
-      <c r="D85" s="1"/>
+      <c r="D85" s="91" t="s">
+        <v>168</v>
+      </c>
       <c r="E85" s="1"/>
       <c r="F85" s="1"/>
       <c r="G85" s="1"/>
@@ -6038,25 +6015,80 @@
     </row>
     <row r="86" spans="3:11" ht="15.75" x14ac:dyDescent="0.25">
       <c r="C86" s="9"/>
-      <c r="D86" s="1"/>
-      <c r="E86" s="1"/>
-      <c r="F86" s="1"/>
-      <c r="G86" s="1"/>
-      <c r="H86" s="1"/>
-      <c r="I86" s="1"/>
-      <c r="J86" s="1"/>
+      <c r="D86" s="21" t="s">
+        <v>142</v>
+      </c>
+      <c r="E86" s="21" t="s">
+        <v>128</v>
+      </c>
+      <c r="F86" s="21" t="s">
+        <v>122</v>
+      </c>
+      <c r="G86" s="21" t="s">
+        <v>167</v>
+      </c>
+      <c r="H86" s="21" t="s">
+        <v>126</v>
+      </c>
+      <c r="I86" s="21" t="s">
+        <v>127</v>
+      </c>
+      <c r="J86" s="21" t="s">
+        <v>123</v>
+      </c>
       <c r="K86" s="9"/>
     </row>
-    <row r="87" spans="3:11" x14ac:dyDescent="0.25">
+    <row r="87" spans="3:11" ht="15.75" x14ac:dyDescent="0.25">
       <c r="C87" s="9"/>
-      <c r="D87" s="9"/>
-      <c r="E87" s="9"/>
-      <c r="F87" s="9"/>
-      <c r="G87" s="9"/>
-      <c r="H87" s="9"/>
-      <c r="I87" s="9"/>
-      <c r="J87" s="9"/>
+      <c r="D87" s="1" t="s">
+        <v>140</v>
+      </c>
+      <c r="E87" s="1" t="s">
+        <v>131</v>
+      </c>
+      <c r="F87" s="19" t="e">
+        <f>'Input - Enterprise'!E23</f>
+        <v>#NAME?</v>
+      </c>
+      <c r="G87" s="19" t="s">
+        <v>131</v>
+      </c>
+      <c r="H87" s="19" t="e">
+        <f>E62/F87</f>
+        <v>#NAME?</v>
+      </c>
+      <c r="I87" s="19" t="s">
+        <v>131</v>
+      </c>
+      <c r="J87" s="16" t="s">
+        <v>143</v>
+      </c>
       <c r="K87" s="9"/>
+    </row>
+    <row r="88" spans="3:11" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="D88" s="1" t="s">
+        <v>141</v>
+      </c>
+      <c r="E88" s="1" t="s">
+        <v>131</v>
+      </c>
+      <c r="F88" s="19" t="e">
+        <f>'Input - Enterprise'!E24</f>
+        <v>#NAME?</v>
+      </c>
+      <c r="G88" s="19" t="s">
+        <v>131</v>
+      </c>
+      <c r="H88" s="19" t="s">
+        <v>131</v>
+      </c>
+      <c r="I88" s="19" t="e">
+        <f>F62/F88</f>
+        <v>#NAME?</v>
+      </c>
+      <c r="J88" s="16" t="s">
+        <v>143</v>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -6074,25 +6106,25 @@
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15.75" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="30.7109375" style="4" customWidth="1"/>
-    <col min="2" max="2" width="4.7109375" style="33" customWidth="1"/>
-    <col min="3" max="3" width="4.7109375" style="36" customWidth="1"/>
-    <col min="4" max="4" width="60.7109375" style="36" customWidth="1"/>
-    <col min="5" max="5" width="50.7109375" style="36" customWidth="1"/>
-    <col min="6" max="11" width="28.7109375" style="36" customWidth="1"/>
-    <col min="12" max="25" width="28.7109375" style="33" customWidth="1"/>
-    <col min="26" max="27" width="9.140625" style="33"/>
-    <col min="28" max="16384" width="9.140625" style="36"/>
+    <col min="2" max="2" width="4.7109375" style="32" customWidth="1"/>
+    <col min="3" max="3" width="4.7109375" style="35" customWidth="1"/>
+    <col min="4" max="4" width="60.7109375" style="35" customWidth="1"/>
+    <col min="5" max="5" width="50.7109375" style="35" customWidth="1"/>
+    <col min="6" max="11" width="28.7109375" style="35" customWidth="1"/>
+    <col min="12" max="25" width="28.7109375" style="32" customWidth="1"/>
+    <col min="26" max="27" width="9.140625" style="32"/>
+    <col min="28" max="16384" width="9.140625" style="35"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:24" s="33" customFormat="1" ht="30" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:24" s="32" customFormat="1" ht="30" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A1" s="17" t="e" vm="1">
         <v>#VALUE!</v>
       </c>
-      <c r="C1" s="39" t="s">
-        <v>93</v>
-      </c>
-    </row>
-    <row r="2" spans="1:24" s="33" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="C1" s="38" t="s">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="2" spans="1:24" s="32" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="3"/>
       <c r="C2" s="3"/>
       <c r="D2" s="3"/>
@@ -6108,100 +6140,100 @@
         <f>HYPERLINK("#'Home'!A1", "Home")</f>
         <v>Home</v>
       </c>
-      <c r="C3" s="40"/>
-      <c r="D3" s="40"/>
-      <c r="E3" s="40"/>
-      <c r="F3" s="40"/>
-      <c r="G3" s="40"/>
-      <c r="H3" s="40"/>
-      <c r="I3" s="40"/>
-      <c r="J3" s="40"/>
-      <c r="K3" s="40"/>
-      <c r="M3" s="35"/>
-      <c r="N3" s="35"/>
-      <c r="O3" s="35"/>
-      <c r="P3" s="35"/>
-      <c r="Q3" s="35"/>
-      <c r="R3" s="35"/>
-      <c r="S3" s="35"/>
-      <c r="T3" s="35"/>
-      <c r="U3" s="35"/>
-      <c r="V3" s="35"/>
-      <c r="W3" s="35"/>
-      <c r="X3" s="35"/>
+      <c r="C3" s="39"/>
+      <c r="D3" s="39"/>
+      <c r="E3" s="39"/>
+      <c r="F3" s="39"/>
+      <c r="G3" s="39"/>
+      <c r="H3" s="39"/>
+      <c r="I3" s="39"/>
+      <c r="J3" s="39"/>
+      <c r="K3" s="39"/>
+      <c r="M3" s="34"/>
+      <c r="N3" s="34"/>
+      <c r="O3" s="34"/>
+      <c r="P3" s="34"/>
+      <c r="Q3" s="34"/>
+      <c r="R3" s="34"/>
+      <c r="S3" s="34"/>
+      <c r="T3" s="34"/>
+      <c r="U3" s="34"/>
+      <c r="V3" s="34"/>
+      <c r="W3" s="34"/>
+      <c r="X3" s="34"/>
     </row>
     <row r="4" spans="1:24" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4" s="5" t="str">
         <f>HYPERLINK("#'Results'!A1", "Results")</f>
         <v>Results</v>
       </c>
-      <c r="C4" s="41"/>
-      <c r="D4" s="41"/>
-      <c r="E4" s="41"/>
-      <c r="F4" s="41"/>
-      <c r="G4" s="41"/>
-      <c r="H4" s="41"/>
-      <c r="I4" s="41"/>
-      <c r="J4" s="41"/>
-      <c r="K4" s="41"/>
+      <c r="C4" s="40"/>
+      <c r="D4" s="40"/>
+      <c r="E4" s="40"/>
+      <c r="F4" s="40"/>
+      <c r="G4" s="40"/>
+      <c r="H4" s="40"/>
+      <c r="I4" s="40"/>
+      <c r="J4" s="40"/>
+      <c r="K4" s="40"/>
     </row>
     <row r="5" spans="1:24" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D5" s="2" t="s">
-        <v>102</v>
-      </c>
-      <c r="N5" s="42"/>
+        <v>97</v>
+      </c>
+      <c r="N5" s="41"/>
     </row>
     <row r="6" spans="1:24" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6" s="8" t="s">
         <v>1</v>
       </c>
-      <c r="N6" s="44"/>
+      <c r="N6" s="43"/>
     </row>
     <row r="7" spans="1:24" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A7" s="5" t="str">
         <f>HYPERLINK("#'Input - Site'!A1", "Site")</f>
         <v>Site</v>
       </c>
-      <c r="D7" s="54" t="s">
-        <v>103</v>
-      </c>
-      <c r="E7" s="55"/>
-      <c r="F7" s="55"/>
-      <c r="G7" s="56"/>
+      <c r="D7" s="53" t="s">
+        <v>98</v>
+      </c>
+      <c r="E7" s="54"/>
+      <c r="F7" s="54"/>
+      <c r="G7" s="55"/>
     </row>
     <row r="8" spans="1:24" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A8" s="5" t="str">
         <f>HYPERLINK("#'Input - Pasture Beef'!A1", "Pasture Beef")</f>
         <v>Pasture Beef</v>
       </c>
-      <c r="D8" s="57" t="s">
-        <v>104</v>
-      </c>
-      <c r="E8" s="58"/>
-      <c r="F8" s="58"/>
-      <c r="G8" s="59"/>
+      <c r="D8" s="56" t="s">
+        <v>99</v>
+      </c>
+      <c r="E8" s="57"/>
+      <c r="F8" s="57"/>
+      <c r="G8" s="58"/>
     </row>
     <row r="9" spans="1:24" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A9" s="5"/>
       <c r="D9" s="1"/>
-      <c r="E9" s="60"/>
+      <c r="E9" s="59"/>
       <c r="F9" s="27"/>
-      <c r="N9" s="46"/>
+      <c r="N9" s="45"/>
     </row>
     <row r="10" spans="1:24" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A10" s="7" t="s">
         <v>3</v>
       </c>
       <c r="D10" s="1" t="s">
-        <v>105</v>
+        <v>100</v>
       </c>
       <c r="E10" s="24" t="s">
-        <v>106</v>
+        <v>101</v>
       </c>
       <c r="F10" s="27" t="s">
-        <v>107</v>
-      </c>
-      <c r="N10" s="46"/>
+        <v>102</v>
+      </c>
+      <c r="N10" s="45"/>
     </row>
     <row r="11" spans="1:24" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A11" s="5" t="str">
@@ -6209,16 +6241,16 @@
         <v>4.2.1.1-2 Methane</v>
       </c>
       <c r="D11" s="1" t="s">
-        <v>108</v>
+        <v>103</v>
       </c>
       <c r="E11" s="24" t="s">
-        <v>109</v>
+        <v>104</v>
       </c>
       <c r="F11" s="27" t="s">
-        <v>107</v>
+        <v>102</v>
       </c>
       <c r="G11" s="1"/>
-      <c r="N11" s="51"/>
+      <c r="N11" s="50"/>
     </row>
     <row r="12" spans="1:24" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A12" s="5" t="str">
@@ -6226,13 +6258,13 @@
         <v>4.2.1.3-4 Soil direct N2O</v>
       </c>
       <c r="D12" s="1" t="s">
-        <v>110</v>
+        <v>105</v>
       </c>
       <c r="E12" s="24" t="s">
-        <v>111</v>
+        <v>106</v>
       </c>
       <c r="F12" s="27" t="s">
-        <v>107</v>
+        <v>102</v>
       </c>
     </row>
     <row r="13" spans="1:24" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
@@ -6241,16 +6273,16 @@
         <v>4.2.1.5-6 Soil atm. deposition</v>
       </c>
       <c r="D13" s="1" t="s">
-        <v>43</v>
-      </c>
-      <c r="E13" s="45">
+        <v>38</v>
+      </c>
+      <c r="E13" s="44">
         <v>307.7</v>
       </c>
       <c r="F13" s="27" t="s">
-        <v>112</v>
-      </c>
-      <c r="N13" s="53"/>
-      <c r="O13" s="53"/>
+        <v>107</v>
+      </c>
+      <c r="N13" s="52"/>
+      <c r="O13" s="52"/>
     </row>
     <row r="14" spans="1:24" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A14" s="5" t="str">
@@ -6258,46 +6290,46 @@
         <v>4.2.1.7-8 Soil leach &amp; runoff</v>
       </c>
       <c r="D14" s="1" t="s">
-        <v>113</v>
-      </c>
-      <c r="E14" s="45">
+        <v>108</v>
+      </c>
+      <c r="E14" s="44">
         <v>18</v>
       </c>
       <c r="F14" s="27" t="s">
-        <v>114</v>
-      </c>
-      <c r="N14" s="53"/>
-      <c r="O14" s="53"/>
+        <v>109</v>
+      </c>
+      <c r="N14" s="52"/>
+      <c r="O14" s="52"/>
     </row>
     <row r="15" spans="1:24" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A15" s="5"/>
       <c r="D15" s="1" t="s">
-        <v>115</v>
-      </c>
-      <c r="E15" s="45">
+        <v>110</v>
+      </c>
+      <c r="E15" s="44">
         <v>601</v>
       </c>
       <c r="F15" s="27" t="s">
-        <v>116</v>
-      </c>
-      <c r="N15" s="53"/>
-      <c r="O15" s="53"/>
+        <v>111</v>
+      </c>
+      <c r="N15" s="52"/>
+      <c r="O15" s="52"/>
     </row>
     <row r="16" spans="1:24" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A16" s="6" t="s">
         <v>2</v>
       </c>
       <c r="D16" s="23" t="s">
-        <v>117</v>
-      </c>
-      <c r="E16" s="45">
+        <v>112</v>
+      </c>
+      <c r="E16" s="44">
         <v>1326</v>
       </c>
       <c r="F16" s="27" t="s">
-        <v>116</v>
-      </c>
-      <c r="N16" s="53"/>
-      <c r="O16" s="53"/>
+        <v>111</v>
+      </c>
+      <c r="N16" s="52"/>
+      <c r="O16" s="52"/>
     </row>
     <row r="17" spans="1:25" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A17" s="5" t="str">
@@ -6305,13 +6337,13 @@
         <v>Constants - Pasture Beef</v>
       </c>
       <c r="D17" s="1" t="s">
-        <v>118</v>
-      </c>
-      <c r="E17" s="45">
+        <v>113</v>
+      </c>
+      <c r="E17" s="44">
         <v>7</v>
       </c>
       <c r="F17" s="27" t="s">
-        <v>119</v>
+        <v>114</v>
       </c>
     </row>
     <row r="18" spans="1:25" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
@@ -6320,7 +6352,7 @@
         <v>Constants - Livestock</v>
       </c>
       <c r="D18" s="23" t="s">
-        <v>120</v>
+        <v>115</v>
       </c>
       <c r="E18" s="26">
         <f>E15/E16</f>
@@ -6334,14 +6366,14 @@
         <v>Constants - Common</v>
       </c>
       <c r="D19" s="23" t="s">
-        <v>71</v>
+        <v>66</v>
       </c>
       <c r="E19" s="26" t="str">
         <f>Common_InputFunctions.Utility_LookupItemFromMinMax(E15,Table_SourceData_RainfallZones[Min rainfall],Table_SourceData_RainfallZones[Max rainfall],Table_SourceData_RainfallZones[Rainfall Zone])</f>
         <v>High rainfall</v>
       </c>
-      <c r="G19" s="61"/>
-      <c r="N19" s="42"/>
+      <c r="G19" s="60"/>
+      <c r="N19" s="41"/>
     </row>
     <row r="20" spans="1:25" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A20" s="5" t="str">
@@ -6349,38 +6381,38 @@
         <v>Acknowledgements</v>
       </c>
       <c r="D20" s="1" t="s">
-        <v>38</v>
+        <v>33</v>
       </c>
       <c r="E20" s="26" t="str">
         <f>Common_InputFunctions.Utility_GetClimateZone(E14,E15,E17,E13,E18,Table_SourceData_ClimateZones[Min temp],Table_SourceData_ClimateZones[Max temp],Table_SourceData_ClimateZones[Min rainfall],Table_SourceData_ClimateZones[Max rainfall],Table_SourceData_ClimateZones[Min frost days],Table_SourceData_ClimateZones[Max frost days],Table_SourceData_ClimateZones[Min elevation],Table_SourceData_ClimateZones[Max elevation],Table_SourceData_ClimateZones[Min MAP:PET],Table_SourceData_ClimateZones[Max MAP:PET],Table_SourceData_ClimateZones[Climate zone])</f>
         <v>Warm temperate dry</v>
       </c>
       <c r="F20" s="1"/>
-      <c r="G20" s="60"/>
-      <c r="N20" s="44"/>
+      <c r="G20" s="59"/>
+      <c r="N20" s="43"/>
     </row>
     <row r="21" spans="1:25" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A21"/>
       <c r="D21" s="1" t="s">
-        <v>121</v>
+        <v>116</v>
       </c>
       <c r="E21" s="26" t="str">
         <f>Common_InputFunctions.Utility_LookupValueInTable($E$20,Table_SourceData_WetDryZones[Climate zone],Table_SourceData_WetDryZones[Wet or Dry Zone])</f>
         <v>Dry climate zone</v>
       </c>
       <c r="F21" s="1"/>
-      <c r="G21" s="60"/>
+      <c r="G21" s="59"/>
     </row>
     <row r="22" spans="1:25" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A22" s="5"/>
       <c r="D22" s="1" t="s">
-        <v>75</v>
+        <v>70</v>
       </c>
       <c r="E22" s="26" t="str">
         <f>Common_InputFunctions.Utility_LookupItemFromMinMax(E14,Table_SourceData_TemperatureZones[Min MAT],Table_SourceData_TemperatureZones[Max MAT],Table_SourceData_TemperatureZones[Temperature Zone])</f>
         <v>Temperate</v>
       </c>
-      <c r="G22" s="64"/>
+      <c r="G22" s="63"/>
     </row>
     <row r="23" spans="1:25" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A23" s="5"/>
@@ -6390,7 +6422,7 @@
     </row>
     <row r="25" spans="1:25" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A25"/>
-      <c r="N25" s="44"/>
+      <c r="N25" s="43"/>
     </row>
     <row r="26" spans="1:25" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A26"/>
@@ -6406,234 +6438,234 @@
     </row>
     <row r="30" spans="1:25" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A30"/>
-      <c r="L30" s="62"/>
-      <c r="M30" s="62"/>
-      <c r="N30" s="62"/>
-      <c r="O30" s="62"/>
-      <c r="P30" s="62"/>
-      <c r="Q30" s="62"/>
-      <c r="R30" s="62"/>
-      <c r="S30" s="62"/>
-      <c r="T30" s="62"/>
-      <c r="U30" s="62"/>
-      <c r="V30" s="62"/>
-      <c r="W30" s="62"/>
-      <c r="X30" s="62"/>
-      <c r="Y30" s="62"/>
+      <c r="L30" s="61"/>
+      <c r="M30" s="61"/>
+      <c r="N30" s="61"/>
+      <c r="O30" s="61"/>
+      <c r="P30" s="61"/>
+      <c r="Q30" s="61"/>
+      <c r="R30" s="61"/>
+      <c r="S30" s="61"/>
+      <c r="T30" s="61"/>
+      <c r="U30" s="61"/>
+      <c r="V30" s="61"/>
+      <c r="W30" s="61"/>
+      <c r="X30" s="61"/>
+      <c r="Y30" s="61"/>
     </row>
     <row r="31" spans="1:25" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A31"/>
-      <c r="L31" s="63"/>
-      <c r="M31" s="63"/>
-      <c r="N31" s="63"/>
-      <c r="O31" s="63"/>
-      <c r="P31" s="63"/>
-      <c r="Q31" s="63"/>
-      <c r="R31" s="63"/>
-      <c r="S31" s="63"/>
-      <c r="T31" s="63"/>
-      <c r="U31" s="63"/>
-      <c r="V31" s="63"/>
-      <c r="W31" s="63"/>
-      <c r="X31" s="63"/>
-      <c r="Y31" s="63"/>
+      <c r="L31" s="62"/>
+      <c r="M31" s="62"/>
+      <c r="N31" s="62"/>
+      <c r="O31" s="62"/>
+      <c r="P31" s="62"/>
+      <c r="Q31" s="62"/>
+      <c r="R31" s="62"/>
+      <c r="S31" s="62"/>
+      <c r="T31" s="62"/>
+      <c r="U31" s="62"/>
+      <c r="V31" s="62"/>
+      <c r="W31" s="62"/>
+      <c r="X31" s="62"/>
+      <c r="Y31" s="62"/>
     </row>
     <row r="32" spans="1:25" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A32"/>
-      <c r="L32" s="63"/>
-      <c r="M32" s="63"/>
-      <c r="N32" s="63"/>
-      <c r="O32" s="63"/>
-      <c r="P32" s="63"/>
-      <c r="Q32" s="63"/>
-      <c r="R32" s="63"/>
-      <c r="S32" s="63"/>
-      <c r="T32" s="63"/>
-      <c r="U32" s="63"/>
-      <c r="V32" s="63"/>
-      <c r="W32" s="63"/>
-      <c r="X32" s="63"/>
-      <c r="Y32" s="63"/>
+      <c r="L32" s="62"/>
+      <c r="M32" s="62"/>
+      <c r="N32" s="62"/>
+      <c r="O32" s="62"/>
+      <c r="P32" s="62"/>
+      <c r="Q32" s="62"/>
+      <c r="R32" s="62"/>
+      <c r="S32" s="62"/>
+      <c r="T32" s="62"/>
+      <c r="U32" s="62"/>
+      <c r="V32" s="62"/>
+      <c r="W32" s="62"/>
+      <c r="X32" s="62"/>
+      <c r="Y32" s="62"/>
     </row>
     <row r="33" spans="1:25" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A33"/>
-      <c r="L33" s="63"/>
-      <c r="M33" s="63"/>
-      <c r="N33" s="63"/>
-      <c r="O33" s="63"/>
-      <c r="P33" s="63"/>
-      <c r="Q33" s="63"/>
-      <c r="R33" s="63"/>
-      <c r="S33" s="63"/>
-      <c r="T33" s="63"/>
-      <c r="U33" s="63"/>
-      <c r="V33" s="63"/>
-      <c r="W33" s="63"/>
-      <c r="X33" s="63"/>
-      <c r="Y33" s="63"/>
+      <c r="L33" s="62"/>
+      <c r="M33" s="62"/>
+      <c r="N33" s="62"/>
+      <c r="O33" s="62"/>
+      <c r="P33" s="62"/>
+      <c r="Q33" s="62"/>
+      <c r="R33" s="62"/>
+      <c r="S33" s="62"/>
+      <c r="T33" s="62"/>
+      <c r="U33" s="62"/>
+      <c r="V33" s="62"/>
+      <c r="W33" s="62"/>
+      <c r="X33" s="62"/>
+      <c r="Y33" s="62"/>
     </row>
     <row r="34" spans="1:25" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A34"/>
-      <c r="J34" s="65"/>
-      <c r="K34" s="66"/>
-      <c r="L34" s="63"/>
-      <c r="M34" s="63"/>
-      <c r="N34" s="63"/>
-      <c r="O34" s="63"/>
-      <c r="P34" s="63"/>
-      <c r="Q34" s="63"/>
-      <c r="R34" s="63"/>
-      <c r="S34" s="63"/>
-      <c r="T34" s="63"/>
-      <c r="U34" s="63"/>
-      <c r="V34" s="63"/>
-      <c r="W34" s="63"/>
-      <c r="X34" s="63"/>
-      <c r="Y34" s="63"/>
+      <c r="J34" s="64"/>
+      <c r="K34" s="65"/>
+      <c r="L34" s="62"/>
+      <c r="M34" s="62"/>
+      <c r="N34" s="62"/>
+      <c r="O34" s="62"/>
+      <c r="P34" s="62"/>
+      <c r="Q34" s="62"/>
+      <c r="R34" s="62"/>
+      <c r="S34" s="62"/>
+      <c r="T34" s="62"/>
+      <c r="U34" s="62"/>
+      <c r="V34" s="62"/>
+      <c r="W34" s="62"/>
+      <c r="X34" s="62"/>
+      <c r="Y34" s="62"/>
     </row>
     <row r="35" spans="1:25" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A35"/>
-      <c r="J35" s="65"/>
-      <c r="K35" s="66"/>
-      <c r="L35" s="63"/>
-      <c r="M35" s="63"/>
-      <c r="N35" s="63"/>
-      <c r="O35" s="63"/>
-      <c r="P35" s="63"/>
-      <c r="Q35" s="63"/>
-      <c r="R35" s="63"/>
-      <c r="S35" s="63"/>
-      <c r="T35" s="63"/>
-      <c r="U35" s="63"/>
-      <c r="V35" s="63"/>
-      <c r="W35" s="63"/>
-      <c r="X35" s="63"/>
-      <c r="Y35" s="63"/>
+      <c r="J35" s="64"/>
+      <c r="K35" s="65"/>
+      <c r="L35" s="62"/>
+      <c r="M35" s="62"/>
+      <c r="N35" s="62"/>
+      <c r="O35" s="62"/>
+      <c r="P35" s="62"/>
+      <c r="Q35" s="62"/>
+      <c r="R35" s="62"/>
+      <c r="S35" s="62"/>
+      <c r="T35" s="62"/>
+      <c r="U35" s="62"/>
+      <c r="V35" s="62"/>
+      <c r="W35" s="62"/>
+      <c r="X35" s="62"/>
+      <c r="Y35" s="62"/>
     </row>
     <row r="36" spans="1:25" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A36"/>
-      <c r="D36" s="67"/>
-      <c r="E36" s="67"/>
-      <c r="F36" s="68"/>
-      <c r="G36" s="65"/>
-      <c r="H36" s="65"/>
-      <c r="I36" s="69"/>
-      <c r="J36" s="65"/>
-      <c r="K36" s="66"/>
-      <c r="L36" s="63"/>
-      <c r="M36" s="63"/>
-      <c r="N36" s="63"/>
-      <c r="O36" s="63"/>
-      <c r="P36" s="63"/>
-      <c r="Q36" s="63"/>
-      <c r="R36" s="63"/>
-      <c r="S36" s="63"/>
-      <c r="T36" s="63"/>
-      <c r="U36" s="63"/>
-      <c r="V36" s="63"/>
-      <c r="W36" s="63"/>
-      <c r="X36" s="63"/>
-      <c r="Y36" s="63"/>
+      <c r="D36" s="66"/>
+      <c r="E36" s="66"/>
+      <c r="F36" s="67"/>
+      <c r="G36" s="64"/>
+      <c r="H36" s="64"/>
+      <c r="I36" s="68"/>
+      <c r="J36" s="64"/>
+      <c r="K36" s="65"/>
+      <c r="L36" s="62"/>
+      <c r="M36" s="62"/>
+      <c r="N36" s="62"/>
+      <c r="O36" s="62"/>
+      <c r="P36" s="62"/>
+      <c r="Q36" s="62"/>
+      <c r="R36" s="62"/>
+      <c r="S36" s="62"/>
+      <c r="T36" s="62"/>
+      <c r="U36" s="62"/>
+      <c r="V36" s="62"/>
+      <c r="W36" s="62"/>
+      <c r="X36" s="62"/>
+      <c r="Y36" s="62"/>
     </row>
     <row r="37" spans="1:25" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A37"/>
-      <c r="D37" s="67"/>
-      <c r="E37" s="67"/>
-      <c r="F37" s="68"/>
-      <c r="G37" s="65"/>
-      <c r="H37" s="65"/>
-      <c r="I37" s="69"/>
-      <c r="J37" s="65"/>
-      <c r="K37" s="66"/>
-      <c r="L37" s="63"/>
-      <c r="M37" s="63"/>
-      <c r="N37" s="63"/>
-      <c r="O37" s="63"/>
-      <c r="P37" s="63"/>
-      <c r="Q37" s="63"/>
-      <c r="R37" s="63"/>
-      <c r="S37" s="63"/>
-      <c r="T37" s="63"/>
-      <c r="U37" s="63"/>
-      <c r="V37" s="63"/>
-      <c r="W37" s="63"/>
-      <c r="X37" s="63"/>
-      <c r="Y37" s="63"/>
+      <c r="D37" s="66"/>
+      <c r="E37" s="66"/>
+      <c r="F37" s="67"/>
+      <c r="G37" s="64"/>
+      <c r="H37" s="64"/>
+      <c r="I37" s="68"/>
+      <c r="J37" s="64"/>
+      <c r="K37" s="65"/>
+      <c r="L37" s="62"/>
+      <c r="M37" s="62"/>
+      <c r="N37" s="62"/>
+      <c r="O37" s="62"/>
+      <c r="P37" s="62"/>
+      <c r="Q37" s="62"/>
+      <c r="R37" s="62"/>
+      <c r="S37" s="62"/>
+      <c r="T37" s="62"/>
+      <c r="U37" s="62"/>
+      <c r="V37" s="62"/>
+      <c r="W37" s="62"/>
+      <c r="X37" s="62"/>
+      <c r="Y37" s="62"/>
     </row>
     <row r="38" spans="1:25" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A38"/>
-      <c r="D38" s="67"/>
-      <c r="E38" s="67"/>
-      <c r="F38" s="68"/>
-      <c r="G38" s="65"/>
-      <c r="H38" s="65"/>
-      <c r="I38" s="69"/>
-      <c r="J38" s="65"/>
-      <c r="K38" s="66"/>
-      <c r="L38" s="63"/>
-      <c r="M38" s="63"/>
-      <c r="N38" s="63"/>
-      <c r="O38" s="63"/>
-      <c r="P38" s="63"/>
-      <c r="Q38" s="63"/>
-      <c r="R38" s="63"/>
-      <c r="S38" s="63"/>
-      <c r="T38" s="63"/>
-      <c r="U38" s="63"/>
-      <c r="V38" s="63"/>
-      <c r="W38" s="63"/>
-      <c r="X38" s="63"/>
-      <c r="Y38" s="63"/>
+      <c r="D38" s="66"/>
+      <c r="E38" s="66"/>
+      <c r="F38" s="67"/>
+      <c r="G38" s="64"/>
+      <c r="H38" s="64"/>
+      <c r="I38" s="68"/>
+      <c r="J38" s="64"/>
+      <c r="K38" s="65"/>
+      <c r="L38" s="62"/>
+      <c r="M38" s="62"/>
+      <c r="N38" s="62"/>
+      <c r="O38" s="62"/>
+      <c r="P38" s="62"/>
+      <c r="Q38" s="62"/>
+      <c r="R38" s="62"/>
+      <c r="S38" s="62"/>
+      <c r="T38" s="62"/>
+      <c r="U38" s="62"/>
+      <c r="V38" s="62"/>
+      <c r="W38" s="62"/>
+      <c r="X38" s="62"/>
+      <c r="Y38" s="62"/>
     </row>
     <row r="39" spans="1:25" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A39"/>
-      <c r="D39" s="67"/>
-      <c r="E39" s="67"/>
-      <c r="F39" s="68"/>
-      <c r="G39" s="65"/>
-      <c r="H39" s="65"/>
-      <c r="I39" s="69"/>
-      <c r="J39" s="65"/>
-      <c r="K39" s="66"/>
-      <c r="L39" s="63"/>
-      <c r="M39" s="63"/>
-      <c r="N39" s="63"/>
-      <c r="O39" s="63"/>
-      <c r="P39" s="63"/>
-      <c r="Q39" s="63"/>
-      <c r="R39" s="63"/>
-      <c r="S39" s="63"/>
-      <c r="T39" s="63"/>
-      <c r="U39" s="63"/>
-      <c r="V39" s="63"/>
-      <c r="W39" s="63"/>
-      <c r="X39" s="63"/>
-      <c r="Y39" s="63"/>
+      <c r="D39" s="66"/>
+      <c r="E39" s="66"/>
+      <c r="F39" s="67"/>
+      <c r="G39" s="64"/>
+      <c r="H39" s="64"/>
+      <c r="I39" s="68"/>
+      <c r="J39" s="64"/>
+      <c r="K39" s="65"/>
+      <c r="L39" s="62"/>
+      <c r="M39" s="62"/>
+      <c r="N39" s="62"/>
+      <c r="O39" s="62"/>
+      <c r="P39" s="62"/>
+      <c r="Q39" s="62"/>
+      <c r="R39" s="62"/>
+      <c r="S39" s="62"/>
+      <c r="T39" s="62"/>
+      <c r="U39" s="62"/>
+      <c r="V39" s="62"/>
+      <c r="W39" s="62"/>
+      <c r="X39" s="62"/>
+      <c r="Y39" s="62"/>
     </row>
     <row r="40" spans="1:25" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A40"/>
-      <c r="D40" s="70"/>
-      <c r="E40" s="70"/>
-      <c r="F40" s="70"/>
-      <c r="G40" s="71"/>
-      <c r="H40" s="72"/>
-      <c r="I40" s="72"/>
-      <c r="J40" s="72"/>
-      <c r="K40" s="72"/>
-      <c r="L40" s="73"/>
-      <c r="M40" s="73"/>
-      <c r="N40" s="73"/>
-      <c r="O40" s="73"/>
-      <c r="P40" s="73"/>
-      <c r="Q40" s="73"/>
-      <c r="R40" s="73"/>
-      <c r="S40" s="73"/>
-      <c r="T40" s="73"/>
-      <c r="U40" s="73"/>
-      <c r="V40" s="73"/>
-      <c r="W40" s="73"/>
-      <c r="X40" s="73"/>
-      <c r="Y40" s="73"/>
+      <c r="D40" s="69"/>
+      <c r="E40" s="69"/>
+      <c r="F40" s="69"/>
+      <c r="G40" s="70"/>
+      <c r="H40" s="71"/>
+      <c r="I40" s="71"/>
+      <c r="J40" s="71"/>
+      <c r="K40" s="71"/>
+      <c r="L40" s="72"/>
+      <c r="M40" s="72"/>
+      <c r="N40" s="72"/>
+      <c r="O40" s="72"/>
+      <c r="P40" s="72"/>
+      <c r="Q40" s="72"/>
+      <c r="R40" s="72"/>
+      <c r="S40" s="72"/>
+      <c r="T40" s="72"/>
+      <c r="U40" s="72"/>
+      <c r="V40" s="72"/>
+      <c r="W40" s="72"/>
+      <c r="X40" s="72"/>
+      <c r="Y40" s="72"/>
     </row>
     <row r="41" spans="1:25" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A41"/>
@@ -6652,117 +6684,117 @@
       <c r="D46" s="2"/>
     </row>
     <row r="47" spans="1:25" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="D47" s="74"/>
-      <c r="E47" s="74"/>
-      <c r="F47" s="74"/>
-      <c r="G47" s="74"/>
-      <c r="H47" s="74"/>
+      <c r="D47" s="73"/>
+      <c r="E47" s="73"/>
+      <c r="F47" s="73"/>
+      <c r="G47" s="73"/>
+      <c r="H47" s="73"/>
     </row>
     <row r="48" spans="1:25" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="D48" s="75"/>
-      <c r="E48" s="75"/>
-      <c r="F48" s="76"/>
-      <c r="G48" s="76"/>
-      <c r="H48" s="75"/>
+      <c r="D48" s="74"/>
+      <c r="E48" s="74"/>
+      <c r="F48" s="75"/>
+      <c r="G48" s="75"/>
+      <c r="H48" s="74"/>
     </row>
     <row r="49" spans="4:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="D49" s="75"/>
-      <c r="E49" s="75"/>
-      <c r="F49" s="76"/>
-      <c r="G49" s="76"/>
-      <c r="H49" s="75"/>
+      <c r="D49" s="74"/>
+      <c r="E49" s="74"/>
+      <c r="F49" s="75"/>
+      <c r="G49" s="75"/>
+      <c r="H49" s="74"/>
     </row>
     <row r="50" spans="4:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="D50" s="75"/>
-      <c r="E50" s="75"/>
-      <c r="F50" s="76"/>
-      <c r="G50" s="76"/>
-      <c r="H50" s="75"/>
+      <c r="D50" s="74"/>
+      <c r="E50" s="74"/>
+      <c r="F50" s="75"/>
+      <c r="G50" s="75"/>
+      <c r="H50" s="74"/>
     </row>
     <row r="51" spans="4:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="D51" s="77"/>
-      <c r="E51" s="78"/>
-      <c r="F51" s="78"/>
-      <c r="G51" s="78"/>
-      <c r="H51" s="79"/>
+      <c r="D51" s="76"/>
+      <c r="E51" s="77"/>
+      <c r="F51" s="77"/>
+      <c r="G51" s="77"/>
+      <c r="H51" s="78"/>
     </row>
     <row r="52" spans="4:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="53" spans="4:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="54" spans="4:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="G54" s="80"/>
+      <c r="G54" s="79"/>
     </row>
     <row r="55" spans="4:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D55" s="2"/>
     </row>
     <row r="56" spans="4:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="57" spans="4:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="D57" s="81"/>
-      <c r="F57" s="82"/>
+      <c r="D57" s="80"/>
+      <c r="F57" s="81"/>
     </row>
     <row r="58" spans="4:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D58" s="1"/>
-      <c r="E58" s="83"/>
+      <c r="E58" s="82"/>
     </row>
     <row r="59" spans="4:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D59" s="1"/>
-      <c r="E59" s="83"/>
+      <c r="E59" s="82"/>
     </row>
     <row r="60" spans="4:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D60" s="1"/>
-      <c r="E60" s="84"/>
+      <c r="E60" s="83"/>
     </row>
     <row r="61" spans="4:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D61" s="1"/>
     </row>
     <row r="62" spans="4:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="63" spans="4:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="D63" s="81"/>
+      <c r="D63" s="80"/>
     </row>
     <row r="64" spans="4:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D64" s="1"/>
-      <c r="E64" s="83"/>
+      <c r="E64" s="82"/>
     </row>
     <row r="65" spans="4:9" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D65" s="1"/>
-      <c r="E65" s="83"/>
+      <c r="E65" s="82"/>
     </row>
     <row r="66" spans="4:9" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D66" s="1"/>
-      <c r="E66" s="84"/>
+      <c r="E66" s="83"/>
     </row>
     <row r="67" spans="4:9" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="68" spans="4:9" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="69" spans="4:9" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="D69" s="85"/>
-      <c r="E69" s="85"/>
-      <c r="F69" s="85"/>
-      <c r="G69" s="85"/>
-      <c r="H69" s="85"/>
-      <c r="I69" s="85"/>
+      <c r="D69" s="84"/>
+      <c r="E69" s="84"/>
+      <c r="F69" s="84"/>
+      <c r="G69" s="84"/>
+      <c r="H69" s="84"/>
+      <c r="I69" s="84"/>
     </row>
     <row r="70" spans="4:9" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="D70" s="85"/>
-      <c r="E70" s="85"/>
-      <c r="F70" s="85"/>
-      <c r="G70" s="85"/>
-      <c r="H70" s="85"/>
-      <c r="I70" s="85"/>
+      <c r="D70" s="84"/>
+      <c r="E70" s="84"/>
+      <c r="F70" s="84"/>
+      <c r="G70" s="84"/>
+      <c r="H70" s="84"/>
+      <c r="I70" s="84"/>
     </row>
     <row r="71" spans="4:9" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="D71" s="85"/>
-      <c r="E71" s="85"/>
-      <c r="F71" s="85"/>
-      <c r="G71" s="85"/>
-      <c r="H71" s="85"/>
-      <c r="I71" s="85"/>
+      <c r="D71" s="84"/>
+      <c r="E71" s="84"/>
+      <c r="F71" s="84"/>
+      <c r="G71" s="84"/>
+      <c r="H71" s="84"/>
+      <c r="I71" s="84"/>
     </row>
     <row r="72" spans="4:9" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="D72" s="85"/>
-      <c r="E72" s="85"/>
-      <c r="F72" s="85"/>
-      <c r="G72" s="85"/>
-      <c r="H72" s="85"/>
-      <c r="I72" s="85"/>
+      <c r="D72" s="84"/>
+      <c r="E72" s="84"/>
+      <c r="F72" s="84"/>
+      <c r="G72" s="84"/>
+      <c r="H72" s="84"/>
+      <c r="I72" s="84"/>
     </row>
     <row r="73" spans="4:9" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="74" spans="4:9" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
@@ -6770,19 +6802,19 @@
     <row r="76" spans="4:9" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="77" spans="4:9" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="78" spans="4:9" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="D78" s="86"/>
+      <c r="D78" s="85"/>
     </row>
     <row r="79" spans="4:9" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="D79" s="86"/>
+      <c r="D79" s="85"/>
     </row>
     <row r="80" spans="4:9" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="D80" s="86"/>
+      <c r="D80" s="85"/>
     </row>
     <row r="81" spans="4:4" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="D81" s="86"/>
+      <c r="D81" s="85"/>
     </row>
     <row r="82" spans="4:4" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="D82" s="86"/>
+      <c r="D82" s="85"/>
     </row>
     <row r="83" spans="4:4" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="84" spans="4:4" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
@@ -6841,7 +6873,7 @@
   <sheetPr>
     <tabColor rgb="FFCC6600"/>
   </sheetPr>
-  <dimension ref="C1:J32"/>
+  <dimension ref="C1:J29"/>
   <sheetFormatPr defaultRowHeight="15.75" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="30.7109375" customWidth="1"/>
@@ -6854,16 +6886,16 @@
   </cols>
   <sheetData>
     <row r="1" spans="3:10" ht="25.5" x14ac:dyDescent="0.35">
-      <c r="C1" s="39" t="s">
-        <v>167</v>
-      </c>
-      <c r="D1" s="33"/>
-      <c r="E1" s="33"/>
-      <c r="F1" s="33"/>
-      <c r="G1" s="33"/>
-      <c r="H1" s="33"/>
-      <c r="I1" s="33"/>
-      <c r="J1" s="33"/>
+      <c r="C1" s="38" t="s">
+        <v>160</v>
+      </c>
+      <c r="D1" s="32"/>
+      <c r="E1" s="32"/>
+      <c r="F1" s="32"/>
+      <c r="G1" s="32"/>
+      <c r="H1" s="32"/>
+      <c r="I1" s="32"/>
+      <c r="J1" s="32"/>
     </row>
     <row r="2" spans="3:10" x14ac:dyDescent="0.25">
       <c r="C2" s="3"/>
@@ -6876,68 +6908,68 @@
       <c r="J2" s="3"/>
     </row>
     <row r="3" spans="3:10" ht="20.25" x14ac:dyDescent="0.25">
-      <c r="C3" s="40"/>
-      <c r="D3" s="40"/>
-      <c r="E3" s="40"/>
-      <c r="F3" s="40"/>
-      <c r="G3" s="40"/>
-      <c r="H3" s="40"/>
-      <c r="I3" s="40"/>
-      <c r="J3" s="40"/>
+      <c r="C3" s="39"/>
+      <c r="D3" s="39"/>
+      <c r="E3" s="39"/>
+      <c r="F3" s="39"/>
+      <c r="G3" s="39"/>
+      <c r="H3" s="39"/>
+      <c r="I3" s="39"/>
+      <c r="J3" s="39"/>
     </row>
     <row r="5" spans="3:10" ht="23.25" x14ac:dyDescent="0.25">
       <c r="D5" s="2" t="s">
-        <v>94</v>
-      </c>
-      <c r="E5" s="36"/>
-      <c r="F5" s="36"/>
-      <c r="G5" s="36"/>
+        <v>89</v>
+      </c>
+      <c r="E5" s="35"/>
+      <c r="F5" s="35"/>
+      <c r="G5" s="35"/>
     </row>
     <row r="6" spans="3:10" x14ac:dyDescent="0.25">
-      <c r="D6" s="43"/>
-      <c r="E6" s="36"/>
-      <c r="F6" s="36"/>
-      <c r="G6" s="36"/>
+      <c r="D6" s="42"/>
+      <c r="E6" s="35"/>
+      <c r="F6" s="35"/>
+      <c r="G6" s="35"/>
     </row>
     <row r="7" spans="3:10" x14ac:dyDescent="0.25">
       <c r="D7" s="1" t="s">
-        <v>95</v>
-      </c>
-      <c r="E7" s="45" t="s">
-        <v>96</v>
+        <v>90</v>
+      </c>
+      <c r="E7" s="44" t="s">
+        <v>91</v>
       </c>
       <c r="F7" s="27"/>
-      <c r="G7" s="36"/>
+      <c r="G7" s="35"/>
     </row>
     <row r="8" spans="3:10" x14ac:dyDescent="0.25">
       <c r="D8" s="23" t="s">
-        <v>97</v>
-      </c>
-      <c r="E8" s="45" t="s">
-        <v>98</v>
-      </c>
-      <c r="F8" s="36"/>
-      <c r="G8" s="36"/>
+        <v>92</v>
+      </c>
+      <c r="E8" s="44" t="s">
+        <v>93</v>
+      </c>
+      <c r="F8" s="35"/>
+      <c r="G8" s="35"/>
     </row>
     <row r="9" spans="3:10" x14ac:dyDescent="0.25">
-      <c r="D9" s="36"/>
-      <c r="E9" s="36"/>
-      <c r="F9" s="36"/>
-      <c r="G9" s="36"/>
+      <c r="D9" s="35"/>
+      <c r="E9" s="35"/>
+      <c r="F9" s="35"/>
+      <c r="G9" s="35"/>
     </row>
     <row r="10" spans="3:10" x14ac:dyDescent="0.25">
-      <c r="D10" s="47" t="s">
-        <v>99</v>
-      </c>
-      <c r="E10" s="48"/>
-      <c r="F10" s="49"/>
-      <c r="G10" s="50"/>
+      <c r="D10" s="46" t="s">
+        <v>94</v>
+      </c>
+      <c r="E10" s="47"/>
+      <c r="F10" s="48"/>
+      <c r="G10" s="49"/>
     </row>
     <row r="11" spans="3:10" x14ac:dyDescent="0.25">
-      <c r="D11" s="36"/>
-      <c r="E11" s="36"/>
-      <c r="F11" s="36"/>
-      <c r="G11" s="36"/>
+      <c r="D11" s="35"/>
+      <c r="E11" s="35"/>
+      <c r="F11" s="35"/>
+      <c r="G11" s="35"/>
     </row>
     <row r="12" spans="3:10" x14ac:dyDescent="0.25">
       <c r="D12" s="23" t="s">
@@ -6947,26 +6979,26 @@
         <v>45292</v>
       </c>
       <c r="F12" s="27" t="s">
-        <v>100</v>
-      </c>
-      <c r="G12" s="36"/>
+        <v>95</v>
+      </c>
+      <c r="G12" s="35"/>
     </row>
     <row r="13" spans="3:10" x14ac:dyDescent="0.25">
       <c r="D13" s="23" t="s">
         <v>18</v>
       </c>
-      <c r="E13" s="52">
+      <c r="E13" s="51">
         <f>DATE(YEAR(E12)+1,MONTH(E12),DAY(E12))-1</f>
         <v>45657</v>
       </c>
       <c r="F13" s="27" t="s">
-        <v>101</v>
-      </c>
-      <c r="G13" s="36"/>
+        <v>96</v>
+      </c>
+      <c r="G13" s="35"/>
     </row>
     <row r="14" spans="3:10" x14ac:dyDescent="0.25">
-      <c r="F14" s="36"/>
-      <c r="G14" s="36"/>
+      <c r="F14" s="35"/>
+      <c r="G14" s="35"/>
     </row>
     <row r="16" spans="3:10" ht="23.25" x14ac:dyDescent="0.25">
       <c r="D16" s="2" t="s">
@@ -6981,7 +7013,7 @@
         <v>45231</v>
       </c>
       <c r="F18" s="27" t="s">
-        <v>100</v>
+        <v>95</v>
       </c>
     </row>
     <row r="19" spans="4:7" x14ac:dyDescent="0.25">
@@ -6992,7 +7024,7 @@
         <v>45747</v>
       </c>
       <c r="F19" s="27" t="s">
-        <v>100</v>
+        <v>95</v>
       </c>
     </row>
     <row r="20" spans="4:7" x14ac:dyDescent="0.25">
@@ -7004,118 +7036,85 @@
         <v>17</v>
       </c>
       <c r="F20" s="27" t="s">
-        <v>125</v>
+        <v>120</v>
       </c>
     </row>
     <row r="22" spans="4:7" x14ac:dyDescent="0.25">
       <c r="D22" s="1" t="s">
         <v>20</v>
       </c>
-      <c r="E22" s="91" t="s">
-        <v>176</v>
+      <c r="E22" s="90">
+        <f>SUM(Table_Input_LivestockSales[Total liveweight sold])*10^-3</f>
+        <v>5</v>
       </c>
       <c r="G22" s="27" t="s">
-        <v>26</v>
+        <v>21</v>
       </c>
     </row>
     <row r="23" spans="4:7" x14ac:dyDescent="0.25">
       <c r="D23" s="1" t="s">
-        <v>21</v>
-      </c>
-      <c r="E23" s="91" t="s">
-        <v>173</v>
-      </c>
-      <c r="G23" s="27" t="s">
-        <v>26</v>
-      </c>
+        <v>197</v>
+      </c>
+      <c r="E23" s="90" t="e" cm="1">
+        <f t="array" ref="E23">X_Cell_Dairy_MilkProductionUnit</f>
+        <v>#NAME?</v>
+      </c>
+      <c r="G23" s="27"/>
     </row>
     <row r="24" spans="4:7" x14ac:dyDescent="0.25">
       <c r="D24" s="1" t="s">
-        <v>22</v>
-      </c>
-      <c r="E24" s="91" t="s">
-        <v>174</v>
+        <v>196</v>
+      </c>
+      <c r="E24" s="90" t="e" cm="1">
+        <f t="array" ref="E24">X_Cell_Dairy_MilkProductionAmount*365*IF(E23="Milk solds", 1, 1.03)</f>
+        <v>#NAME?</v>
       </c>
       <c r="G24" s="27" t="s">
-        <v>26</v>
+        <v>21</v>
       </c>
     </row>
     <row r="25" spans="4:7" x14ac:dyDescent="0.25">
       <c r="D25" s="1" t="s">
-        <v>169</v>
-      </c>
-      <c r="E25" s="91" t="s">
-        <v>177</v>
+        <v>199</v>
+      </c>
+      <c r="E25" s="86">
+        <v>1</v>
       </c>
       <c r="G25" s="27" t="s">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="26" spans="4:7" x14ac:dyDescent="0.25">
-      <c r="D26" s="1" t="s">
-        <v>170</v>
-      </c>
-      <c r="E26" s="91" t="s">
-        <v>175</v>
-      </c>
-      <c r="G26" s="27" t="s">
-        <v>26</v>
+        <v>21</v>
       </c>
     </row>
     <row r="27" spans="4:7" x14ac:dyDescent="0.25">
       <c r="D27" s="1" t="s">
-        <v>23</v>
+        <v>162</v>
       </c>
       <c r="E27" s="29">
-        <v>0.1</v>
+        <v>0.15</v>
       </c>
       <c r="G27" s="27" t="s">
-        <v>168</v>
+        <v>161</v>
       </c>
     </row>
     <row r="28" spans="4:7" x14ac:dyDescent="0.25">
       <c r="D28" s="1" t="s">
-        <v>24</v>
+        <v>163</v>
       </c>
       <c r="E28" s="29">
-        <v>0.2</v>
+        <v>0.05</v>
       </c>
       <c r="G28" s="27" t="s">
-        <v>168</v>
+        <v>161</v>
       </c>
     </row>
     <row r="29" spans="4:7" x14ac:dyDescent="0.25">
       <c r="D29" s="1" t="s">
-        <v>25</v>
-      </c>
-      <c r="E29" s="30">
-        <f>100%-E27-E28</f>
-        <v>0.7</v>
+        <v>198</v>
+      </c>
+      <c r="E29" s="29">
+        <v>0.8</v>
       </c>
       <c r="G29" s="27" t="s">
-        <v>168</v>
-      </c>
-    </row>
-    <row r="31" spans="4:7" x14ac:dyDescent="0.25">
-      <c r="D31" s="1" t="s">
-        <v>171</v>
-      </c>
-      <c r="E31" s="29">
-        <v>0.8</v>
-      </c>
-      <c r="G31" s="27" t="s">
-        <v>168</v>
-      </c>
-    </row>
-    <row r="32" spans="4:7" x14ac:dyDescent="0.25">
-      <c r="D32" s="1" t="s">
-        <v>172</v>
-      </c>
-      <c r="E32" s="29">
-        <v>0.2</v>
-      </c>
-      <c r="G32" s="27" t="s">
-        <v>168</v>
+        <v>161</v>
       </c>
     </row>
   </sheetData>
@@ -7143,58 +7142,58 @@
         <v>#VALUE!</v>
       </c>
       <c r="C1" s="17" t="s">
-        <v>202</v>
+        <v>188</v>
       </c>
     </row>
     <row r="2" spans="1:13" s="3" customFormat="1" x14ac:dyDescent="0.25"/>
     <row r="3" spans="1:13" ht="20.25" x14ac:dyDescent="0.25">
-      <c r="C3" s="40"/>
-      <c r="D3" s="40"/>
-      <c r="E3" s="40"/>
-      <c r="F3" s="40"/>
-      <c r="G3" s="40"/>
-      <c r="H3" s="40"/>
-      <c r="I3" s="40"/>
-      <c r="J3" s="40"/>
-      <c r="K3" s="40"/>
-      <c r="L3" s="40"/>
-      <c r="M3" s="40"/>
+      <c r="C3" s="39"/>
+      <c r="D3" s="39"/>
+      <c r="E3" s="39"/>
+      <c r="F3" s="39"/>
+      <c r="G3" s="39"/>
+      <c r="H3" s="39"/>
+      <c r="I3" s="39"/>
+      <c r="J3" s="39"/>
+      <c r="K3" s="39"/>
+      <c r="L3" s="39"/>
+      <c r="M3" s="39"/>
     </row>
     <row r="5" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="D5" s="93" t="s">
-        <v>203</v>
+      <c r="D5" s="92" t="s">
+        <v>189</v>
       </c>
     </row>
     <row r="6" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="D6" s="31" t="s">
-        <v>204</v>
-      </c>
-      <c r="E6" s="31" t="s">
-        <v>205</v>
-      </c>
-      <c r="F6" s="31" t="s">
-        <v>206</v>
-      </c>
-      <c r="G6" s="31" t="s">
-        <v>207</v>
-      </c>
-      <c r="H6" s="31" t="s">
-        <v>208</v>
-      </c>
-      <c r="I6" s="31" t="s">
-        <v>209</v>
+      <c r="D6" s="30" t="s">
+        <v>190</v>
+      </c>
+      <c r="E6" s="30" t="s">
+        <v>191</v>
+      </c>
+      <c r="F6" s="30" t="s">
+        <v>192</v>
+      </c>
+      <c r="G6" s="30" t="s">
+        <v>193</v>
+      </c>
+      <c r="H6" s="30" t="s">
+        <v>194</v>
+      </c>
+      <c r="I6" s="30" t="s">
+        <v>195</v>
       </c>
     </row>
     <row r="7" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="D7" s="45"/>
+      <c r="D7" s="44"/>
       <c r="E7" s="24"/>
-      <c r="F7" s="94">
+      <c r="F7" s="93">
         <v>45566</v>
       </c>
-      <c r="G7" s="31">
+      <c r="G7" s="30">
         <v>10</v>
       </c>
-      <c r="H7" s="31">
+      <c r="H7" s="30">
         <v>500</v>
       </c>
       <c r="I7" s="26">
@@ -7203,99 +7202,99 @@
       </c>
     </row>
     <row r="8" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="D8" s="45"/>
+      <c r="D8" s="44"/>
       <c r="E8" s="24"/>
-      <c r="F8" s="94"/>
-      <c r="G8" s="31"/>
-      <c r="H8" s="31"/>
+      <c r="F8" s="93"/>
+      <c r="G8" s="30"/>
+      <c r="H8" s="30"/>
       <c r="I8" s="26">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
     </row>
     <row r="9" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="D9" s="45"/>
+      <c r="D9" s="44"/>
       <c r="E9" s="24"/>
-      <c r="F9" s="94"/>
-      <c r="G9" s="31"/>
-      <c r="H9" s="31"/>
+      <c r="F9" s="93"/>
+      <c r="G9" s="30"/>
+      <c r="H9" s="30"/>
       <c r="I9" s="26">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
     </row>
     <row r="10" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="D10" s="45"/>
+      <c r="D10" s="44"/>
       <c r="E10" s="24"/>
-      <c r="F10" s="94"/>
-      <c r="G10" s="31"/>
-      <c r="H10" s="31"/>
+      <c r="F10" s="93"/>
+      <c r="G10" s="30"/>
+      <c r="H10" s="30"/>
       <c r="I10" s="26">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
     </row>
     <row r="11" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="D11" s="45"/>
+      <c r="D11" s="44"/>
       <c r="E11" s="24"/>
-      <c r="F11" s="94"/>
-      <c r="G11" s="31"/>
-      <c r="H11" s="31"/>
+      <c r="F11" s="93"/>
+      <c r="G11" s="30"/>
+      <c r="H11" s="30"/>
       <c r="I11" s="26">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
     </row>
     <row r="12" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="D12" s="45"/>
+      <c r="D12" s="44"/>
       <c r="E12" s="24"/>
-      <c r="F12" s="94"/>
-      <c r="G12" s="31"/>
-      <c r="H12" s="31"/>
+      <c r="F12" s="93"/>
+      <c r="G12" s="30"/>
+      <c r="H12" s="30"/>
       <c r="I12" s="26">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
     </row>
     <row r="13" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="D13" s="45"/>
+      <c r="D13" s="44"/>
       <c r="E13" s="24"/>
-      <c r="F13" s="94"/>
-      <c r="G13" s="31"/>
-      <c r="H13" s="31"/>
+      <c r="F13" s="93"/>
+      <c r="G13" s="30"/>
+      <c r="H13" s="30"/>
       <c r="I13" s="26">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
     </row>
     <row r="14" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="D14" s="45"/>
+      <c r="D14" s="44"/>
       <c r="E14" s="24"/>
-      <c r="F14" s="94"/>
-      <c r="G14" s="31"/>
-      <c r="H14" s="31"/>
+      <c r="F14" s="93"/>
+      <c r="G14" s="30"/>
+      <c r="H14" s="30"/>
       <c r="I14" s="26">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
     </row>
     <row r="15" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="D15" s="45"/>
+      <c r="D15" s="44"/>
       <c r="E15" s="24"/>
-      <c r="F15" s="94"/>
-      <c r="G15" s="31"/>
-      <c r="H15" s="31"/>
+      <c r="F15" s="93"/>
+      <c r="G15" s="30"/>
+      <c r="H15" s="30"/>
       <c r="I15" s="26">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
     </row>
     <row r="16" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="D16" s="45"/>
+      <c r="D16" s="44"/>
       <c r="E16" s="24"/>
-      <c r="F16" s="94"/>
-      <c r="G16" s="31"/>
-      <c r="H16" s="31"/>
+      <c r="F16" s="93"/>
+      <c r="G16" s="30"/>
+      <c r="H16" s="30"/>
       <c r="I16" s="26">
         <f t="shared" si="0"/>
         <v>0</v>
@@ -7334,53 +7333,53 @@
         <v>#VALUE!</v>
       </c>
       <c r="C1" s="17" t="s">
-        <v>187</v>
+        <v>173</v>
       </c>
     </row>
     <row r="2" spans="1:11" s="3" customFormat="1" x14ac:dyDescent="0.25"/>
     <row r="3" spans="1:11" ht="20.25" x14ac:dyDescent="0.25">
-      <c r="C3" s="40"/>
-      <c r="D3" s="40"/>
-      <c r="E3" s="40"/>
-      <c r="F3" s="40"/>
-      <c r="G3" s="40"/>
-      <c r="H3" s="40"/>
-      <c r="I3" s="40"/>
-      <c r="J3" s="40"/>
-      <c r="K3" s="40"/>
+      <c r="C3" s="39"/>
+      <c r="D3" s="39"/>
+      <c r="E3" s="39"/>
+      <c r="F3" s="39"/>
+      <c r="G3" s="39"/>
+      <c r="H3" s="39"/>
+      <c r="I3" s="39"/>
+      <c r="J3" s="39"/>
+      <c r="K3" s="39"/>
     </row>
     <row r="5" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="D5" s="81" t="s">
-        <v>192</v>
-      </c>
-      <c r="E5" s="81"/>
-      <c r="F5" s="81"/>
-      <c r="G5" s="81"/>
+      <c r="D5" s="80" t="s">
+        <v>178</v>
+      </c>
+      <c r="E5" s="80"/>
+      <c r="F5" s="80"/>
+      <c r="G5" s="80"/>
     </row>
     <row r="6" spans="1:11" x14ac:dyDescent="0.25">
       <c r="F6" s="27"/>
     </row>
     <row r="7" spans="1:11" x14ac:dyDescent="0.25">
       <c r="D7" s="1" t="s">
-        <v>188</v>
+        <v>174</v>
       </c>
       <c r="E7" s="26" t="s">
-        <v>191</v>
+        <v>177</v>
       </c>
       <c r="F7" s="27"/>
     </row>
     <row r="8" spans="1:11" x14ac:dyDescent="0.25">
       <c r="D8" s="1" t="s">
-        <v>189</v>
+        <v>175</v>
       </c>
       <c r="E8" s="26" t="s">
-        <v>191</v>
+        <v>177</v>
       </c>
       <c r="F8" s="27"/>
     </row>
     <row r="9" spans="1:11" x14ac:dyDescent="0.25">
       <c r="D9" s="1" t="s">
-        <v>70</v>
+        <v>65</v>
       </c>
       <c r="E9" s="26" t="e" cm="1">
         <f t="array" ref="E9">X_Cell_Pasture_IrrigationMethod</f>
@@ -7389,7 +7388,7 @@
     </row>
     <row r="10" spans="1:11" x14ac:dyDescent="0.25">
       <c r="D10" s="1" t="s">
-        <v>190</v>
+        <v>176</v>
       </c>
       <c r="E10" s="26" t="e" cm="1">
         <f t="array" ref="E10">X_Cell_Pasture_AreaUnderPasture</f>
@@ -7409,8 +7408,8 @@
   <dimension ref="A1:BY259"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15.75" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="30.7109375" style="33" customWidth="1"/>
-    <col min="2" max="2" width="2.7109375" style="33" customWidth="1"/>
+    <col min="1" max="1" width="30.7109375" style="32" customWidth="1"/>
+    <col min="2" max="2" width="2.7109375" style="32" customWidth="1"/>
     <col min="3" max="3" width="4.7109375" style="1" customWidth="1"/>
     <col min="4" max="4" width="48" style="1" customWidth="1"/>
     <col min="5" max="6" width="20.7109375" style="1" customWidth="1"/>
@@ -7425,49 +7424,49 @@
     <col min="18" max="18" width="31.140625" style="1" customWidth="1"/>
     <col min="19" max="20" width="20.7109375" style="1" customWidth="1"/>
     <col min="21" max="21" width="4.7109375" style="1" customWidth="1"/>
-    <col min="22" max="33" width="20.7109375" style="33" customWidth="1"/>
-    <col min="34" max="39" width="21.85546875" style="33" customWidth="1"/>
-    <col min="40" max="44" width="20.7109375" style="33" customWidth="1"/>
-    <col min="45" max="65" width="9.140625" style="33"/>
-    <col min="66" max="16384" width="9.140625" style="36"/>
+    <col min="22" max="33" width="20.7109375" style="32" customWidth="1"/>
+    <col min="34" max="39" width="21.85546875" style="32" customWidth="1"/>
+    <col min="40" max="44" width="20.7109375" style="32" customWidth="1"/>
+    <col min="45" max="65" width="9.140625" style="32"/>
+    <col min="66" max="16384" width="9.140625" style="35"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:65" s="32" customFormat="1" ht="30" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A1" s="32" t="e" vm="1">
+    <row r="1" spans="1:65" s="31" customFormat="1" ht="30" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A1" s="31" t="e" vm="1">
         <v>#VALUE!</v>
       </c>
-      <c r="C1" s="32" t="s">
-        <v>27</v>
+      <c r="C1" s="31" t="s">
+        <v>22</v>
       </c>
     </row>
     <row r="2" spans="1:65" s="3" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="3" spans="1:65" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3"/>
-      <c r="C3" s="34"/>
-      <c r="D3" s="34"/>
-      <c r="E3" s="34"/>
-      <c r="F3" s="34"/>
-      <c r="G3" s="34"/>
-      <c r="H3" s="34"/>
-      <c r="I3" s="34"/>
-      <c r="J3" s="34"/>
-      <c r="K3" s="34"/>
-      <c r="L3" s="34"/>
-      <c r="M3" s="34"/>
-      <c r="N3" s="34"/>
-      <c r="O3" s="34"/>
-      <c r="P3" s="34"/>
-      <c r="Q3" s="34"/>
-      <c r="R3" s="34"/>
-      <c r="S3" s="34"/>
-      <c r="T3" s="34"/>
-      <c r="U3" s="34"/>
-      <c r="V3" s="35"/>
-      <c r="W3" s="35"/>
+      <c r="C3" s="33"/>
+      <c r="D3" s="33"/>
+      <c r="E3" s="33"/>
+      <c r="F3" s="33"/>
+      <c r="G3" s="33"/>
+      <c r="H3" s="33"/>
+      <c r="I3" s="33"/>
+      <c r="J3" s="33"/>
+      <c r="K3" s="33"/>
+      <c r="L3" s="33"/>
+      <c r="M3" s="33"/>
+      <c r="N3" s="33"/>
+      <c r="O3" s="33"/>
+      <c r="P3" s="33"/>
+      <c r="Q3" s="33"/>
+      <c r="R3" s="33"/>
+      <c r="S3" s="33"/>
+      <c r="T3" s="33"/>
+      <c r="U3" s="33"/>
+      <c r="V3" s="34"/>
+      <c r="W3" s="34"/>
     </row>
     <row r="4" spans="1:65" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4"/>
-      <c r="BM4" s="36"/>
+      <c r="BM4" s="35"/>
     </row>
     <row r="5" spans="1:65" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5"/>
@@ -7475,138 +7474,138 @@
         <f t="array" ref="D5">Common_SourceData.Common_SourceData_AustralianStatesTerritories_Title()</f>
         <v>Australian states and territories</v>
       </c>
-      <c r="BM5" s="36"/>
+      <c r="BM5" s="35"/>
     </row>
     <row r="6" spans="1:65" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6"/>
-      <c r="D6" s="31" t="s">
-        <v>28</v>
-      </c>
-      <c r="E6" s="31" t="s">
-        <v>29</v>
-      </c>
-      <c r="F6" s="31" t="s">
-        <v>30</v>
+      <c r="D6" s="30" t="s">
+        <v>23</v>
+      </c>
+      <c r="E6" s="30" t="s">
+        <v>24</v>
+      </c>
+      <c r="F6" s="30" t="s">
+        <v>25</v>
       </c>
     </row>
     <row r="7" spans="1:65" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A7"/>
-      <c r="D7" s="31" t="str" cm="1">
+      <c r="D7" s="30" t="str" cm="1">
         <f t="array" ref="D7">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_AustralianStatesTerritories_Data(),Table_AustralianStates[[#Headers],[State/Territory]],0)</f>
         <v>New South Wales</v>
       </c>
-      <c r="E7" s="31" t="str" cm="1">
+      <c r="E7" s="30" t="str" cm="1">
         <f t="array" ref="E7">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_AustralianStatesTerritories_Data(),Table_AustralianStates[[#Headers],[State/Territory]],0)</f>
         <v>New South Wales</v>
       </c>
-      <c r="F7" s="31" t="str" cm="1">
+      <c r="F7" s="30" t="str" cm="1">
         <f t="array" ref="F7">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_AustralianStatesTerritories_Data(),Table_AustralianStates[[#Headers],[State/Territory]],0)</f>
         <v>NSW</v>
       </c>
     </row>
     <row r="8" spans="1:65" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A8"/>
-      <c r="D8" s="31" t="str" cm="1">
+      <c r="D8" s="30" t="str" cm="1">
         <f t="array" ref="D8">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_AustralianStatesTerritories_Data(),Table_AustralianStates[[#Headers],[State/Territory]],0)</f>
         <v>Australian Capital Territory</v>
       </c>
-      <c r="E8" s="31" t="str" cm="1">
+      <c r="E8" s="30" t="str" cm="1">
         <f t="array" ref="E8">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_AustralianStatesTerritories_Data(),Table_AustralianStates[[#Headers],[State/Territory]],0)</f>
         <v>ACT</v>
       </c>
-      <c r="F8" s="31" t="str" cm="1">
+      <c r="F8" s="30" t="str" cm="1">
         <f t="array" ref="F8">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_AustralianStatesTerritories_Data(),Table_AustralianStates[[#Headers],[State/Territory]],0)</f>
         <v>ACT</v>
       </c>
     </row>
     <row r="9" spans="1:65" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A9"/>
-      <c r="D9" s="31" t="str" cm="1">
+      <c r="D9" s="30" t="str" cm="1">
         <f t="array" ref="D9">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_AustralianStatesTerritories_Data(),Table_AustralianStates[[#Headers],[State/Territory]],0)</f>
         <v>Victoria</v>
       </c>
-      <c r="E9" s="31" t="str" cm="1">
+      <c r="E9" s="30" t="str" cm="1">
         <f t="array" ref="E9">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_AustralianStatesTerritories_Data(),Table_AustralianStates[[#Headers],[State/Territory]],0)</f>
         <v>Victoria</v>
       </c>
-      <c r="F9" s="31" t="str" cm="1">
+      <c r="F9" s="30" t="str" cm="1">
         <f t="array" ref="F9">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_AustralianStatesTerritories_Data(),Table_AustralianStates[[#Headers],[State/Territory]],0)</f>
         <v>VIC</v>
       </c>
     </row>
     <row r="10" spans="1:65" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A10"/>
-      <c r="D10" s="31" t="str" cm="1">
+      <c r="D10" s="30" t="str" cm="1">
         <f t="array" ref="D10">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_AustralianStatesTerritories_Data(),Table_AustralianStates[[#Headers],[State/Territory]],0)</f>
         <v>Queensland</v>
       </c>
-      <c r="E10" s="31" t="str" cm="1">
+      <c r="E10" s="30" t="str" cm="1">
         <f t="array" ref="E10">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_AustralianStatesTerritories_Data(),Table_AustralianStates[[#Headers],[State/Territory]],0)</f>
         <v>Queensland</v>
       </c>
-      <c r="F10" s="31" t="str" cm="1">
+      <c r="F10" s="30" t="str" cm="1">
         <f t="array" ref="F10">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_AustralianStatesTerritories_Data(),Table_AustralianStates[[#Headers],[State/Territory]],0)</f>
         <v>QLD</v>
       </c>
     </row>
     <row r="11" spans="1:65" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A11"/>
-      <c r="D11" s="31" t="str" cm="1">
+      <c r="D11" s="30" t="str" cm="1">
         <f t="array" ref="D11">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_AustralianStatesTerritories_Data(),Table_AustralianStates[[#Headers],[State/Territory]],0)</f>
         <v>South Australia</v>
       </c>
-      <c r="E11" s="31" t="str" cm="1">
+      <c r="E11" s="30" t="str" cm="1">
         <f t="array" ref="E11">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_AustralianStatesTerritories_Data(),Table_AustralianStates[[#Headers],[State/Territory]],0)</f>
         <v>South Australia</v>
       </c>
-      <c r="F11" s="31" t="str" cm="1">
+      <c r="F11" s="30" t="str" cm="1">
         <f t="array" ref="F11">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_AustralianStatesTerritories_Data(),Table_AustralianStates[[#Headers],[State/Territory]],0)</f>
         <v>SA</v>
       </c>
-      <c r="BM11" s="36"/>
+      <c r="BM11" s="35"/>
     </row>
     <row r="12" spans="1:65" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A12"/>
-      <c r="D12" s="31" t="str" cm="1">
+      <c r="D12" s="30" t="str" cm="1">
         <f t="array" ref="D12">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_AustralianStatesTerritories_Data(),Table_AustralianStates[[#Headers],[State/Territory]],0)</f>
         <v>Western Australia</v>
       </c>
-      <c r="E12" s="31" t="str" cm="1">
+      <c r="E12" s="30" t="str" cm="1">
         <f t="array" ref="E12">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_AustralianStatesTerritories_Data(),Table_AustralianStates[[#Headers],[State/Territory]],0)</f>
         <v>Western Australia</v>
       </c>
-      <c r="F12" s="31" t="str" cm="1">
+      <c r="F12" s="30" t="str" cm="1">
         <f t="array" ref="F12">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_AustralianStatesTerritories_Data(),Table_AustralianStates[[#Headers],[State/Territory]],0)</f>
         <v>WA</v>
       </c>
-      <c r="BM12" s="36"/>
+      <c r="BM12" s="35"/>
     </row>
     <row r="13" spans="1:65" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A13"/>
-      <c r="D13" s="31" t="str" cm="1">
+      <c r="D13" s="30" t="str" cm="1">
         <f t="array" ref="D13">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_AustralianStatesTerritories_Data(),Table_AustralianStates[[#Headers],[State/Territory]],0)</f>
         <v>Tasmania</v>
       </c>
-      <c r="E13" s="31" t="str" cm="1">
+      <c r="E13" s="30" t="str" cm="1">
         <f t="array" ref="E13">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_AustralianStatesTerritories_Data(),Table_AustralianStates[[#Headers],[State/Territory]],0)</f>
         <v>Tasmania</v>
       </c>
-      <c r="F13" s="31" t="str" cm="1">
+      <c r="F13" s="30" t="str" cm="1">
         <f t="array" ref="F13">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_AustralianStatesTerritories_Data(),Table_AustralianStates[[#Headers],[State/Territory]],0)</f>
         <v>TAS</v>
       </c>
     </row>
     <row r="14" spans="1:65" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A14"/>
-      <c r="D14" s="31" t="str" cm="1">
+      <c r="D14" s="30" t="str" cm="1">
         <f t="array" ref="D14">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_AustralianStatesTerritories_Data(),Table_AustralianStates[[#Headers],[State/Territory]],0)</f>
         <v>Northern Territory</v>
       </c>
-      <c r="E14" s="31" t="str" cm="1">
+      <c r="E14" s="30" t="str" cm="1">
         <f t="array" ref="E14">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_AustralianStatesTerritories_Data(),Table_AustralianStates[[#Headers],[State/Territory]],0)</f>
         <v>Northern Territory</v>
       </c>
-      <c r="F14" s="31" t="str" cm="1">
+      <c r="F14" s="30" t="str" cm="1">
         <f t="array" ref="F14">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_AustralianStatesTerritories_Data(),Table_AustralianStates[[#Headers],[State/Territory]],0)</f>
         <v>NT</v>
       </c>
@@ -7636,76 +7635,76 @@
     </row>
     <row r="20" spans="1:4" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A20"/>
-      <c r="D20" s="31" t="s">
-        <v>31</v>
+      <c r="D20" s="30" t="s">
+        <v>26</v>
       </c>
     </row>
     <row r="21" spans="1:4" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A21"/>
-      <c r="D21" s="31" t="str" cm="1">
+      <c r="D21" s="30" t="str" cm="1">
         <f t="array" ref="D21">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_WASA4Areas_Data(), Table_WASA4Areas[[#Headers],[SA 4 Name]], 0)</f>
         <v>Bunbury</v>
       </c>
     </row>
     <row r="22" spans="1:4" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A22"/>
-      <c r="D22" s="31" t="str" cm="1">
+      <c r="D22" s="30" t="str" cm="1">
         <f t="array" ref="D22">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_WASA4Areas_Data(), Table_WASA4Areas[[#Headers],[SA 4 Name]], 0)</f>
         <v>Mandurah</v>
       </c>
     </row>
     <row r="23" spans="1:4" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A23"/>
-      <c r="D23" s="31" t="str" cm="1">
+      <c r="D23" s="30" t="str" cm="1">
         <f t="array" ref="D23">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_WASA4Areas_Data(), Table_WASA4Areas[[#Headers],[SA 4 Name]], 0)</f>
         <v>Perth - Inner</v>
       </c>
     </row>
     <row r="24" spans="1:4" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A24"/>
-      <c r="D24" s="31" t="str" cm="1">
+      <c r="D24" s="30" t="str" cm="1">
         <f t="array" ref="D24">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_WASA4Areas_Data(), Table_WASA4Areas[[#Headers],[SA 4 Name]], 0)</f>
         <v>Perth - North East</v>
       </c>
     </row>
     <row r="25" spans="1:4" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A25"/>
-      <c r="D25" s="31" t="str" cm="1">
+      <c r="D25" s="30" t="str" cm="1">
         <f t="array" ref="D25">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_WASA4Areas_Data(), Table_WASA4Areas[[#Headers],[SA 4 Name]], 0)</f>
         <v>Perth - North West</v>
       </c>
     </row>
     <row r="26" spans="1:4" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A26"/>
-      <c r="D26" s="31" t="str" cm="1">
+      <c r="D26" s="30" t="str" cm="1">
         <f t="array" ref="D26">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_WASA4Areas_Data(), Table_WASA4Areas[[#Headers],[SA 4 Name]], 0)</f>
         <v>Perth - South East</v>
       </c>
     </row>
     <row r="27" spans="1:4" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A27"/>
-      <c r="D27" s="31" t="str" cm="1">
+      <c r="D27" s="30" t="str" cm="1">
         <f t="array" ref="D27">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_WASA4Areas_Data(), Table_WASA4Areas[[#Headers],[SA 4 Name]], 0)</f>
         <v>Perth - South West</v>
       </c>
     </row>
     <row r="28" spans="1:4" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A28"/>
-      <c r="D28" s="31" t="str" cm="1">
+      <c r="D28" s="30" t="str" cm="1">
         <f t="array" ref="D28">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_WASA4Areas_Data(), Table_WASA4Areas[[#Headers],[SA 4 Name]], 0)</f>
         <v>Western Australia - Wheat Belt</v>
       </c>
     </row>
     <row r="29" spans="1:4" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A29"/>
-      <c r="D29" s="31" t="str" cm="1">
+      <c r="D29" s="30" t="str" cm="1">
         <f t="array" ref="D29">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_WASA4Areas_Data(), Table_WASA4Areas[[#Headers],[SA 4 Name]], 0)</f>
         <v>Western Australia - Outback (North)</v>
       </c>
     </row>
     <row r="30" spans="1:4" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A30"/>
-      <c r="D30" s="31" t="str" cm="1">
+      <c r="D30" s="30" t="str" cm="1">
         <f t="array" ref="D30">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_WASA4Areas_Data(), Table_WASA4Areas[[#Headers],[SA 4 Name]], 0)</f>
         <v>Western Australia - Outback (South)</v>
       </c>
@@ -7735,84 +7734,84 @@
     </row>
     <row r="36" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A36"/>
-      <c r="D36" s="31" t="s">
-        <v>32</v>
-      </c>
-      <c r="E36" s="31" t="s">
-        <v>33</v>
+      <c r="D36" s="30" t="s">
+        <v>27</v>
+      </c>
+      <c r="E36" s="30" t="s">
+        <v>28</v>
       </c>
     </row>
     <row r="37" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A37"/>
-      <c r="D37" s="31" t="str" cm="1">
+      <c r="D37" s="30" t="str" cm="1">
         <f t="array" ref="D37">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_GWP_Data(), Table_GWPData[[#Headers],[Gas]], 0)</f>
         <v>CO2</v>
       </c>
-      <c r="E37" s="31" cm="1">
+      <c r="E37" s="30" cm="1">
         <f t="array" ref="E37">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_GWP_Data(), Table_GWPData[[#Headers],[Gas]], 0)</f>
         <v>1</v>
       </c>
     </row>
     <row r="38" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A38"/>
-      <c r="D38" s="31" t="str" cm="1">
+      <c r="D38" s="30" t="str" cm="1">
         <f t="array" ref="D38">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_GWP_Data(), Table_GWPData[[#Headers],[Gas]], 0)</f>
         <v>CH4</v>
       </c>
-      <c r="E38" s="31" cm="1">
+      <c r="E38" s="30" cm="1">
         <f t="array" ref="E38">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_GWP_Data(), Table_GWPData[[#Headers],[Gas]], 0)</f>
         <v>28</v>
       </c>
     </row>
     <row r="39" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A39"/>
-      <c r="D39" s="31" t="str" cm="1">
+      <c r="D39" s="30" t="str" cm="1">
         <f t="array" ref="D39">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_GWP_Data(), Table_GWPData[[#Headers],[Gas]], 0)</f>
         <v>N2O</v>
       </c>
-      <c r="E39" s="31" cm="1">
+      <c r="E39" s="30" cm="1">
         <f t="array" ref="E39">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_GWP_Data(), Table_GWPData[[#Headers],[Gas]], 0)</f>
         <v>265</v>
       </c>
     </row>
     <row r="40" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A40"/>
-      <c r="D40" s="31" t="str" cm="1">
+      <c r="D40" s="30" t="str" cm="1">
         <f t="array" ref="D40">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_GWP_Data(), Table_GWPData[[#Headers],[Gas]], 0)</f>
         <v>CF4</v>
       </c>
-      <c r="E40" s="31" cm="1">
+      <c r="E40" s="30" cm="1">
         <f t="array" ref="E40">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_GWP_Data(), Table_GWPData[[#Headers],[Gas]], 0)</f>
         <v>6630</v>
       </c>
     </row>
     <row r="41" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A41"/>
-      <c r="D41" s="31" t="str" cm="1">
+      <c r="D41" s="30" t="str" cm="1">
         <f t="array" ref="D41">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_GWP_Data(), Table_GWPData[[#Headers],[Gas]], 0)</f>
         <v>C2F6</v>
       </c>
-      <c r="E41" s="31" cm="1">
+      <c r="E41" s="30" cm="1">
         <f t="array" ref="E41">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_GWP_Data(), Table_GWPData[[#Headers],[Gas]], 0)</f>
         <v>12200</v>
       </c>
     </row>
     <row r="42" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="D42" s="31" t="str" cm="1">
+      <c r="D42" s="30" t="str" cm="1">
         <f t="array" ref="D42">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_GWP_Data(), Table_GWPData[[#Headers],[Gas]], 0)</f>
         <v>SF6</v>
       </c>
-      <c r="E42" s="31" cm="1">
+      <c r="E42" s="30" cm="1">
         <f t="array" ref="E42">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_GWP_Data(), Table_GWPData[[#Headers],[Gas]], 0)</f>
         <v>22800</v>
       </c>
     </row>
     <row r="43" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="D43" s="31" t="str" cm="1">
+      <c r="D43" s="30" t="str" cm="1">
         <f t="array" ref="D43">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_GWP_Data(), Table_GWPData[[#Headers],[Gas]], 0)</f>
         <v>NF3</v>
       </c>
-      <c r="E43" s="31" cm="1">
+      <c r="E43" s="30" cm="1">
         <f t="array" ref="E43">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_GWP_Data(), Table_GWPData[[#Headers],[Gas]], 0)</f>
         <v>17200</v>
       </c>
@@ -7831,172 +7830,172 @@
       </c>
     </row>
     <row r="47" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="D47" s="31" t="s">
+      <c r="D47" s="30" t="s">
+        <v>27</v>
+      </c>
+      <c r="E47" s="30" t="s">
+        <v>29</v>
+      </c>
+      <c r="F47" s="30" t="s">
+        <v>30</v>
+      </c>
+      <c r="G47" s="30" t="s">
+        <v>31</v>
+      </c>
+      <c r="H47" s="30" t="s">
         <v>32</v>
       </c>
-      <c r="E47" s="31" t="s">
-        <v>34</v>
-      </c>
-      <c r="F47" s="31" t="s">
-        <v>35</v>
-      </c>
-      <c r="G47" s="31" t="s">
-        <v>36</v>
-      </c>
-      <c r="H47" s="31" t="s">
-        <v>37</v>
-      </c>
     </row>
     <row r="48" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="D48" s="31" t="str" cm="1">
+      <c r="D48" s="30" t="str" cm="1">
         <f t="array" ref="D48">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ConvertGasElementalToMolecular_Data(),Table_GasToMolecularConversionFactor[[#Headers],[Gas]], 0)</f>
         <v>CO2</v>
       </c>
-      <c r="E48" s="31" t="str" cm="1">
+      <c r="E48" s="30" t="str" cm="1">
         <f t="array" ref="E48">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ConvertGasElementalToMolecular_Data(),Table_GasToMolecularConversionFactor[[#Headers],[Gas]], 0)</f>
         <v>44/12</v>
       </c>
-      <c r="F48" s="31" cm="1">
+      <c r="F48" s="30" cm="1">
         <f t="array" ref="F48">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ConvertGasElementalToMolecular_Data(),Table_GasToMolecularConversionFactor[[#Headers],[Gas]], 0)</f>
         <v>44</v>
       </c>
-      <c r="G48" s="31" cm="1">
+      <c r="G48" s="30" cm="1">
         <f t="array" ref="G48">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ConvertGasElementalToMolecular_Data(),Table_GasToMolecularConversionFactor[[#Headers],[Gas]], 0)</f>
         <v>12</v>
       </c>
-      <c r="H48" s="31">
+      <c r="H48" s="30">
         <f>Table_GasToMolecularConversionFactor[[#This Row],[Conversion factor 1]]/Table_GasToMolecularConversionFactor[[#This Row],[Conversion factor 2]]</f>
         <v>3.6666666666666665</v>
       </c>
     </row>
     <row r="49" spans="4:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="D49" s="31" t="str" cm="1">
+      <c r="D49" s="30" t="str" cm="1">
         <f t="array" ref="D49">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ConvertGasElementalToMolecular_Data(),Table_GasToMolecularConversionFactor[[#Headers],[Gas]], 0)</f>
         <v>CH4</v>
       </c>
-      <c r="E49" s="31" t="str" cm="1">
+      <c r="E49" s="30" t="str" cm="1">
         <f t="array" ref="E49">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ConvertGasElementalToMolecular_Data(),Table_GasToMolecularConversionFactor[[#Headers],[Gas]], 0)</f>
         <v>16/12</v>
       </c>
-      <c r="F49" s="31" cm="1">
+      <c r="F49" s="30" cm="1">
         <f t="array" ref="F49">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ConvertGasElementalToMolecular_Data(),Table_GasToMolecularConversionFactor[[#Headers],[Gas]], 0)</f>
         <v>16</v>
       </c>
-      <c r="G49" s="31" cm="1">
+      <c r="G49" s="30" cm="1">
         <f t="array" ref="G49">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ConvertGasElementalToMolecular_Data(),Table_GasToMolecularConversionFactor[[#Headers],[Gas]], 0)</f>
         <v>12</v>
       </c>
-      <c r="H49" s="31">
+      <c r="H49" s="30">
         <f>Table_GasToMolecularConversionFactor[[#This Row],[Conversion factor 1]]/Table_GasToMolecularConversionFactor[[#This Row],[Conversion factor 2]]</f>
         <v>1.3333333333333333</v>
       </c>
     </row>
     <row r="50" spans="4:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="D50" s="31" t="str" cm="1">
+      <c r="D50" s="30" t="str" cm="1">
         <f t="array" ref="D50">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ConvertGasElementalToMolecular_Data(),Table_GasToMolecularConversionFactor[[#Headers],[Gas]], 0)</f>
         <v>N2O</v>
       </c>
-      <c r="E50" s="31" t="str" cm="1">
+      <c r="E50" s="30" t="str" cm="1">
         <f t="array" ref="E50">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ConvertGasElementalToMolecular_Data(),Table_GasToMolecularConversionFactor[[#Headers],[Gas]], 0)</f>
         <v>44/28</v>
       </c>
-      <c r="F50" s="31" cm="1">
+      <c r="F50" s="30" cm="1">
         <f t="array" ref="F50">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ConvertGasElementalToMolecular_Data(),Table_GasToMolecularConversionFactor[[#Headers],[Gas]], 0)</f>
         <v>44</v>
       </c>
-      <c r="G50" s="31" cm="1">
+      <c r="G50" s="30" cm="1">
         <f t="array" ref="G50">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ConvertGasElementalToMolecular_Data(),Table_GasToMolecularConversionFactor[[#Headers],[Gas]], 0)</f>
         <v>28</v>
       </c>
-      <c r="H50" s="31">
+      <c r="H50" s="30">
         <f>Table_GasToMolecularConversionFactor[[#This Row],[Conversion factor 1]]/Table_GasToMolecularConversionFactor[[#This Row],[Conversion factor 2]]</f>
         <v>1.5714285714285714</v>
       </c>
     </row>
     <row r="51" spans="4:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="D51" s="31" t="str" cm="1">
+      <c r="D51" s="30" t="str" cm="1">
         <f t="array" ref="D51">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ConvertGasElementalToMolecular_Data(),Table_GasToMolecularConversionFactor[[#Headers],[Gas]], 0)</f>
         <v>Nox</v>
       </c>
-      <c r="E51" s="31" t="str" cm="1">
+      <c r="E51" s="30" t="str" cm="1">
         <f t="array" ref="E51">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ConvertGasElementalToMolecular_Data(),Table_GasToMolecularConversionFactor[[#Headers],[Gas]], 0)</f>
         <v>46/14</v>
       </c>
-      <c r="F51" s="31" cm="1">
+      <c r="F51" s="30" cm="1">
         <f t="array" ref="F51">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ConvertGasElementalToMolecular_Data(),Table_GasToMolecularConversionFactor[[#Headers],[Gas]], 0)</f>
         <v>46</v>
       </c>
-      <c r="G51" s="31" cm="1">
+      <c r="G51" s="30" cm="1">
         <f t="array" ref="G51">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ConvertGasElementalToMolecular_Data(),Table_GasToMolecularConversionFactor[[#Headers],[Gas]], 0)</f>
         <v>14</v>
       </c>
-      <c r="H51" s="31">
+      <c r="H51" s="30">
         <f>Table_GasToMolecularConversionFactor[[#This Row],[Conversion factor 1]]/Table_GasToMolecularConversionFactor[[#This Row],[Conversion factor 2]]</f>
         <v>3.2857142857142856</v>
       </c>
     </row>
     <row r="52" spans="4:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="D52" s="31" t="str" cm="1">
+      <c r="D52" s="30" t="str" cm="1">
         <f t="array" ref="D52">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ConvertGasElementalToMolecular_Data(),Table_GasToMolecularConversionFactor[[#Headers],[Gas]], 0)</f>
         <v>CO</v>
       </c>
-      <c r="E52" s="31" t="str" cm="1">
+      <c r="E52" s="30" t="str" cm="1">
         <f t="array" ref="E52">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ConvertGasElementalToMolecular_Data(),Table_GasToMolecularConversionFactor[[#Headers],[Gas]], 0)</f>
         <v>28/12</v>
       </c>
-      <c r="F52" s="31" cm="1">
+      <c r="F52" s="30" cm="1">
         <f t="array" ref="F52">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ConvertGasElementalToMolecular_Data(),Table_GasToMolecularConversionFactor[[#Headers],[Gas]], 0)</f>
         <v>28</v>
       </c>
-      <c r="G52" s="31" cm="1">
+      <c r="G52" s="30" cm="1">
         <f t="array" ref="G52">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ConvertGasElementalToMolecular_Data(),Table_GasToMolecularConversionFactor[[#Headers],[Gas]], 0)</f>
         <v>12</v>
       </c>
-      <c r="H52" s="31">
+      <c r="H52" s="30">
         <f>Table_GasToMolecularConversionFactor[[#This Row],[Conversion factor 1]]/Table_GasToMolecularConversionFactor[[#This Row],[Conversion factor 2]]</f>
         <v>2.3333333333333335</v>
       </c>
     </row>
     <row r="53" spans="4:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="D53" s="31" t="str" cm="1">
+      <c r="D53" s="30" t="str" cm="1">
         <f t="array" ref="D53">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ConvertGasElementalToMolecular_Data(),Table_GasToMolecularConversionFactor[[#Headers],[Gas]], 0)</f>
         <v>CO2 Lime</v>
       </c>
-      <c r="E53" s="31" t="str" cm="1">
+      <c r="E53" s="30" t="str" cm="1">
         <f t="array" ref="E53">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ConvertGasElementalToMolecular_Data(),Table_GasToMolecularConversionFactor[[#Headers],[Gas]], 0)</f>
         <v>44/12</v>
       </c>
-      <c r="F53" s="31" cm="1">
+      <c r="F53" s="30" cm="1">
         <f t="array" ref="F53">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ConvertGasElementalToMolecular_Data(),Table_GasToMolecularConversionFactor[[#Headers],[Gas]], 0)</f>
         <v>44</v>
       </c>
-      <c r="G53" s="31" cm="1">
+      <c r="G53" s="30" cm="1">
         <f t="array" ref="G53">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ConvertGasElementalToMolecular_Data(),Table_GasToMolecularConversionFactor[[#Headers],[Gas]], 0)</f>
         <v>12</v>
       </c>
-      <c r="H53" s="31">
+      <c r="H53" s="30">
         <f>Table_GasToMolecularConversionFactor[[#This Row],[Conversion factor 1]]/Table_GasToMolecularConversionFactor[[#This Row],[Conversion factor 2]]</f>
         <v>3.6666666666666665</v>
       </c>
     </row>
     <row r="54" spans="4:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="D54" s="31" t="str" cm="1">
+      <c r="D54" s="30" t="str" cm="1">
         <f t="array" ref="D54">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ConvertGasElementalToMolecular_Data(),Table_GasToMolecularConversionFactor[[#Headers],[Gas]], 0)</f>
         <v>NMVOC</v>
       </c>
-      <c r="E54" s="31" t="str" cm="1">
+      <c r="E54" s="30" t="str" cm="1">
         <f t="array" ref="E54">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ConvertGasElementalToMolecular_Data(),Table_GasToMolecularConversionFactor[[#Headers],[Gas]], 0)</f>
         <v>14/12</v>
       </c>
-      <c r="F54" s="31" cm="1">
+      <c r="F54" s="30" cm="1">
         <f t="array" ref="F54">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ConvertGasElementalToMolecular_Data(),Table_GasToMolecularConversionFactor[[#Headers],[Gas]], 0)</f>
         <v>14</v>
       </c>
-      <c r="G54" s="31" cm="1">
+      <c r="G54" s="30" cm="1">
         <f t="array" ref="G54">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ConvertGasElementalToMolecular_Data(),Table_GasToMolecularConversionFactor[[#Headers],[Gas]], 0)</f>
         <v>12</v>
       </c>
-      <c r="H54" s="31">
+      <c r="H54" s="30">
         <f>Table_GasToMolecularConversionFactor[[#This Row],[Conversion factor 1]]/Table_GasToMolecularConversionFactor[[#This Row],[Conversion factor 2]]</f>
         <v>1.1666666666666667</v>
       </c>
@@ -8016,166 +8015,166 @@
       </c>
     </row>
     <row r="59" spans="4:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="D59" s="37" t="str" cm="1">
+      <c r="D59" s="36" t="str" cm="1">
         <f t="array" ref="D59:D61">"⚠️" &amp; Common_SourceData.Common_SourceData_WetAndDryZones_Variation()</f>
         <v>⚠️VARIATION OF SOURCE DATA:</v>
       </c>
     </row>
     <row r="60" spans="4:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="D60" s="37" t="str">
+      <c r="D60" s="36" t="str">
         <v>⚠️Added warm / cool temperate moist / dry - low frost and high temp classes to accommodate climate scenarios excluded by VEERG criteria.</v>
       </c>
     </row>
     <row r="61" spans="4:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="D61" s="37" t="str">
+      <c r="D61" s="36" t="str">
         <v>⚠️Fixed typo - Changed 'Fry' to 'Dry'.</v>
       </c>
     </row>
     <row r="62" spans="4:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="63" spans="4:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="D63" s="31" t="s">
-        <v>38</v>
-      </c>
-      <c r="E63" s="31" t="s">
-        <v>39</v>
+      <c r="D63" s="30" t="s">
+        <v>33</v>
+      </c>
+      <c r="E63" s="30" t="s">
+        <v>34</v>
       </c>
     </row>
     <row r="64" spans="4:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="D64" s="31" t="str" cm="1">
+      <c r="D64" s="30" t="str" cm="1">
         <f t="array" ref="D64">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_WetAndDryZones_Data(), Table_SourceData_WetDryZones[[#Headers],[Climate zone]], 0)</f>
         <v>Tropical montane</v>
       </c>
-      <c r="E64" s="31" t="str" cm="1">
+      <c r="E64" s="30" t="str" cm="1">
         <f t="array" ref="E64">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_WetAndDryZones_Data(), Table_SourceData_WetDryZones[[#Headers],[Climate zone]], 0)</f>
         <v>Wet climate zone</v>
       </c>
     </row>
     <row r="65" spans="4:5" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="D65" s="31" t="str" cm="1">
+      <c r="D65" s="30" t="str" cm="1">
         <f t="array" ref="D65">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_WetAndDryZones_Data(), Table_SourceData_WetDryZones[[#Headers],[Climate zone]], 0)</f>
         <v>Tropical wet</v>
       </c>
-      <c r="E65" s="31" t="str" cm="1">
+      <c r="E65" s="30" t="str" cm="1">
         <f t="array" ref="E65">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_WetAndDryZones_Data(), Table_SourceData_WetDryZones[[#Headers],[Climate zone]], 0)</f>
         <v>Wet climate zone</v>
       </c>
     </row>
     <row r="66" spans="4:5" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="D66" s="31" t="str" cm="1">
+      <c r="D66" s="30" t="str" cm="1">
         <f t="array" ref="D66">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_WetAndDryZones_Data(), Table_SourceData_WetDryZones[[#Headers],[Climate zone]], 0)</f>
         <v>Tropical moist</v>
       </c>
-      <c r="E66" s="31" t="str" cm="1">
+      <c r="E66" s="30" t="str" cm="1">
         <f t="array" ref="E66">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_WetAndDryZones_Data(), Table_SourceData_WetDryZones[[#Headers],[Climate zone]], 0)</f>
         <v>Wet climate zone</v>
       </c>
     </row>
     <row r="67" spans="4:5" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="D67" s="31" t="str" cm="1">
+      <c r="D67" s="30" t="str" cm="1">
         <f t="array" ref="D67">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_WetAndDryZones_Data(), Table_SourceData_WetDryZones[[#Headers],[Climate zone]], 0)</f>
         <v>Tropical dry</v>
       </c>
-      <c r="E67" s="31" t="str" cm="1">
+      <c r="E67" s="30" t="str" cm="1">
         <f t="array" ref="E67">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_WetAndDryZones_Data(), Table_SourceData_WetDryZones[[#Headers],[Climate zone]], 0)</f>
         <v>Dry climate zone</v>
       </c>
     </row>
     <row r="68" spans="4:5" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="D68" s="31" t="str" cm="1">
+      <c r="D68" s="30" t="str" cm="1">
         <f t="array" ref="D68">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_WetAndDryZones_Data(), Table_SourceData_WetDryZones[[#Headers],[Climate zone]], 0)</f>
         <v>Warm temperate moist</v>
       </c>
-      <c r="E68" s="31" t="str" cm="1">
+      <c r="E68" s="30" t="str" cm="1">
         <f t="array" ref="E68">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_WetAndDryZones_Data(), Table_SourceData_WetDryZones[[#Headers],[Climate zone]], 0)</f>
         <v>Wet climate zone</v>
       </c>
     </row>
     <row r="69" spans="4:5" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="D69" s="31" t="str" cm="1">
+      <c r="D69" s="30" t="str" cm="1">
         <f t="array" ref="D69">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_WetAndDryZones_Data(), Table_SourceData_WetDryZones[[#Headers],[Climate zone]], 0)</f>
         <v>Warm temperate dry</v>
       </c>
-      <c r="E69" s="31" t="str" cm="1">
+      <c r="E69" s="30" t="str" cm="1">
         <f t="array" ref="E69">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_WetAndDryZones_Data(), Table_SourceData_WetDryZones[[#Headers],[Climate zone]], 0)</f>
         <v>Dry climate zone</v>
       </c>
     </row>
     <row r="70" spans="4:5" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="D70" s="31" t="str" cm="1">
+      <c r="D70" s="30" t="str" cm="1">
         <f t="array" ref="D70">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_WetAndDryZones_Data(), Table_SourceData_WetDryZones[[#Headers],[Climate zone]], 0)</f>
         <v>Cool temperate moist</v>
       </c>
-      <c r="E70" s="31" t="str" cm="1">
+      <c r="E70" s="30" t="str" cm="1">
         <f t="array" ref="E70">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_WetAndDryZones_Data(), Table_SourceData_WetDryZones[[#Headers],[Climate zone]], 0)</f>
         <v>Wet climate zone</v>
       </c>
     </row>
     <row r="71" spans="4:5" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="D71" s="31" t="str" cm="1">
+      <c r="D71" s="30" t="str" cm="1">
         <f t="array" ref="D71">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_WetAndDryZones_Data(), Table_SourceData_WetDryZones[[#Headers],[Climate zone]], 0)</f>
         <v>Cool temperate dry</v>
       </c>
-      <c r="E71" s="31" t="str" cm="1">
+      <c r="E71" s="30" t="str" cm="1">
         <f t="array" ref="E71">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_WetAndDryZones_Data(), Table_SourceData_WetDryZones[[#Headers],[Climate zone]], 0)</f>
         <v>Dry climate zone</v>
       </c>
     </row>
     <row r="72" spans="4:5" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="D72" s="31" t="str" cm="1">
+      <c r="D72" s="30" t="str" cm="1">
         <f t="array" ref="D72">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_WetAndDryZones_Data(), Table_SourceData_WetDryZones[[#Headers],[Climate zone]], 0)</f>
         <v>Warm temperate moist - low frost</v>
       </c>
-      <c r="E72" s="31" t="str" cm="1">
+      <c r="E72" s="30" t="str" cm="1">
         <f t="array" ref="E72">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_WetAndDryZones_Data(), Table_SourceData_WetDryZones[[#Headers],[Climate zone]], 0)</f>
         <v>Wet climate zone</v>
       </c>
     </row>
     <row r="73" spans="4:5" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="D73" s="31" t="str" cm="1">
+      <c r="D73" s="30" t="str" cm="1">
         <f t="array" ref="D73">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_WetAndDryZones_Data(), Table_SourceData_WetDryZones[[#Headers],[Climate zone]], 0)</f>
         <v>Warm temperate dry - low frost</v>
       </c>
-      <c r="E73" s="31" t="str" cm="1">
+      <c r="E73" s="30" t="str" cm="1">
         <f t="array" ref="E73">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_WetAndDryZones_Data(), Table_SourceData_WetDryZones[[#Headers],[Climate zone]], 0)</f>
         <v>Dry climate zone</v>
       </c>
     </row>
     <row r="74" spans="4:5" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="D74" s="31" t="str" cm="1">
+      <c r="D74" s="30" t="str" cm="1">
         <f t="array" ref="D74">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_WetAndDryZones_Data(), Table_SourceData_WetDryZones[[#Headers],[Climate zone]], 0)</f>
         <v>Warm temperate moist - high temp</v>
       </c>
-      <c r="E74" s="31" t="str" cm="1">
+      <c r="E74" s="30" t="str" cm="1">
         <f t="array" ref="E74">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_WetAndDryZones_Data(), Table_SourceData_WetDryZones[[#Headers],[Climate zone]], 0)</f>
         <v>Wet climate zone</v>
       </c>
     </row>
     <row r="75" spans="4:5" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="D75" s="31" t="str" cm="1">
+      <c r="D75" s="30" t="str" cm="1">
         <f t="array" ref="D75">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_WetAndDryZones_Data(), Table_SourceData_WetDryZones[[#Headers],[Climate zone]], 0)</f>
         <v>Warm temperate dry - high temp</v>
       </c>
-      <c r="E75" s="31" t="str" cm="1">
+      <c r="E75" s="30" t="str" cm="1">
         <f t="array" ref="E75">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_WetAndDryZones_Data(), Table_SourceData_WetDryZones[[#Headers],[Climate zone]], 0)</f>
         <v>Dry climate zone</v>
       </c>
     </row>
     <row r="76" spans="4:5" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="D76" s="31" t="str" cm="1">
+      <c r="D76" s="30" t="str" cm="1">
         <f t="array" ref="D76">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_WetAndDryZones_Data(), Table_SourceData_WetDryZones[[#Headers],[Climate zone]], 0)</f>
         <v>Cool temperate moist - low frost</v>
       </c>
-      <c r="E76" s="31" t="str" cm="1">
+      <c r="E76" s="30" t="str" cm="1">
         <f t="array" ref="E76">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_WetAndDryZones_Data(), Table_SourceData_WetDryZones[[#Headers],[Climate zone]], 0)</f>
         <v>Wet climate zone</v>
       </c>
     </row>
     <row r="77" spans="4:5" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="D77" s="31" t="str" cm="1">
+      <c r="D77" s="30" t="str" cm="1">
         <f t="array" ref="D77">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_WetAndDryZones_Data(), Table_SourceData_WetDryZones[[#Headers],[Climate zone]], 0)</f>
         <v>Cool temperate dry - low frost</v>
       </c>
-      <c r="E77" s="31" t="str" cm="1">
+      <c r="E77" s="30" t="str" cm="1">
         <f t="array" ref="E77">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_WetAndDryZones_Data(), Table_SourceData_WetDryZones[[#Headers],[Climate zone]], 0)</f>
         <v>Dry climate zone</v>
       </c>
@@ -8196,618 +8195,618 @@
       </c>
     </row>
     <row r="83" spans="4:20" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="D83" s="37" t="str" cm="1">
+      <c r="D83" s="36" t="str" cm="1">
         <f t="array" ref="D83:D87">"⚠️" &amp; Common_SourceData.Common_SourceData_ClimateZones_Variation()</f>
         <v>⚠️VARIATION OF SOURCE DATA:</v>
       </c>
     </row>
     <row r="84" spans="4:20" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="D84" s="37" t="str">
+      <c r="D84" s="36" t="str">
         <v>⚠️Added warm / cool temperate moist / dry - low frost and high temp classes to accommodate climate scenarios excluded by VEERG criteria.</v>
       </c>
     </row>
     <row r="85" spans="4:20" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="D85" s="37" t="str">
+      <c r="D85" s="36" t="str">
         <v>⚠️Fixed typo in MAT value for warm temperate dry - changed 10 to 11.</v>
       </c>
     </row>
     <row r="86" spans="4:20" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="D86" s="37" t="str">
+      <c r="D86" s="36" t="str">
         <v>⚠️Added min and max columns for MAT, MAP, frost days per year, elevation, MAP:PET to calculate zones from real climate data.</v>
       </c>
     </row>
     <row r="87" spans="4:20" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="D87" s="37" t="str">
+      <c r="D87" s="36" t="str">
         <v>⚠️GAF accepts rainfall as a proxy for precipitation.</v>
       </c>
     </row>
     <row r="88" spans="4:20" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="89" spans="4:20" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="D89" s="31" t="s">
+      <c r="D89" s="30" t="s">
+        <v>33</v>
+      </c>
+      <c r="E89" s="30" t="s">
+        <v>35</v>
+      </c>
+      <c r="F89" s="30" t="s">
+        <v>36</v>
+      </c>
+      <c r="G89" s="30" t="s">
+        <v>37</v>
+      </c>
+      <c r="H89" s="30" t="s">
         <v>38</v>
       </c>
-      <c r="E89" s="31" t="s">
+      <c r="I89" s="30" t="s">
+        <v>39</v>
+      </c>
+      <c r="J89" s="30" t="s">
         <v>40</v>
       </c>
-      <c r="F89" s="31" t="s">
+      <c r="K89" s="30" t="s">
         <v>41</v>
       </c>
-      <c r="G89" s="31" t="s">
+      <c r="L89" s="30" t="s">
         <v>42</v>
       </c>
-      <c r="H89" s="31" t="s">
+      <c r="M89" s="30" t="s">
         <v>43</v>
       </c>
-      <c r="I89" s="31" t="s">
+      <c r="N89" s="30" t="s">
         <v>44</v>
       </c>
-      <c r="J89" s="31" t="s">
+      <c r="O89" s="30" t="s">
         <v>45</v>
       </c>
-      <c r="K89" s="31" t="s">
+      <c r="P89" s="30" t="s">
         <v>46</v>
       </c>
-      <c r="L89" s="31" t="s">
+      <c r="Q89" s="30" t="s">
         <v>47</v>
       </c>
-      <c r="M89" s="31" t="s">
+      <c r="R89" s="30" t="s">
         <v>48</v>
       </c>
-      <c r="N89" s="31" t="s">
+      <c r="S89" s="30" t="s">
         <v>49</v>
       </c>
-      <c r="O89" s="31" t="s">
-        <v>50</v>
-      </c>
-      <c r="P89" s="31" t="s">
-        <v>51</v>
-      </c>
-      <c r="Q89" s="31" t="s">
-        <v>52</v>
-      </c>
-      <c r="R89" s="31" t="s">
-        <v>53</v>
-      </c>
-      <c r="S89" s="31" t="s">
-        <v>54</v>
-      </c>
-      <c r="T89" s="31"/>
+      <c r="T89" s="30"/>
     </row>
     <row r="90" spans="4:20" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="D90" s="31" t="str" cm="1">
+      <c r="D90" s="30" t="str" cm="1">
         <f t="array" ref="D90">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ClimateZones_Data(), Table_SourceData_ClimateZones[[#Headers],[Climate zone]], 0)</f>
         <v>Tropical montane</v>
       </c>
-      <c r="E90" s="31" t="str" cm="1">
+      <c r="E90" s="30" t="str" cm="1">
         <f t="array" ref="E90">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ClimateZones_Data(), Table_SourceData_ClimateZones[[#Headers],[Climate zone]], 0)</f>
         <v>&gt; 18 C</v>
       </c>
-      <c r="F90" s="31" t="str" cm="1">
+      <c r="F90" s="30" t="str" cm="1">
         <f t="array" ref="F90">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ClimateZones_Data(), Table_SourceData_ClimateZones[[#Headers],[Climate zone]], 0)</f>
         <v>Any</v>
       </c>
-      <c r="G90" s="31" t="str" cm="1">
+      <c r="G90" s="30" t="str" cm="1">
         <f t="array" ref="G90">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ClimateZones_Data(), Table_SourceData_ClimateZones[[#Headers],[Climate zone]], 0)</f>
         <v>≤ 7</v>
       </c>
-      <c r="H90" s="31" t="str" cm="1">
+      <c r="H90" s="30" t="str" cm="1">
         <f t="array" ref="H90">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ClimateZones_Data(), Table_SourceData_ClimateZones[[#Headers],[Climate zone]], 0)</f>
         <v>&gt; 1000 m</v>
       </c>
-      <c r="I90" s="31" t="str" cm="1">
+      <c r="I90" s="30" t="str" cm="1">
         <f t="array" ref="I90">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ClimateZones_Data(), Table_SourceData_ClimateZones[[#Headers],[Climate zone]], 0)</f>
         <v>Any</v>
       </c>
-      <c r="J90" s="31" cm="1">
+      <c r="J90" s="30" cm="1">
         <f t="array" ref="J90">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ClimateZones_Data(), Table_SourceData_ClimateZones[[#Headers],[Climate zone]], 0)</f>
         <v>18.001000000000001</v>
       </c>
-      <c r="K90" s="31" cm="1">
+      <c r="K90" s="30" cm="1">
         <f t="array" ref="K90">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ClimateZones_Data(), Table_SourceData_ClimateZones[[#Headers],[Climate zone]], 0)</f>
         <v>999999</v>
       </c>
-      <c r="L90" s="31" cm="1">
+      <c r="L90" s="30" cm="1">
         <f t="array" ref="L90">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ClimateZones_Data(), Table_SourceData_ClimateZones[[#Headers],[Climate zone]], 0)</f>
         <v>-999999</v>
       </c>
-      <c r="M90" s="31" cm="1">
+      <c r="M90" s="30" cm="1">
         <f t="array" ref="M90">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ClimateZones_Data(), Table_SourceData_ClimateZones[[#Headers],[Climate zone]], 0)</f>
         <v>999999</v>
       </c>
-      <c r="N90" s="31" cm="1">
+      <c r="N90" s="30" cm="1">
         <f t="array" ref="N90">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ClimateZones_Data(), Table_SourceData_ClimateZones[[#Headers],[Climate zone]], 0)</f>
         <v>-999999</v>
       </c>
-      <c r="O90" s="31" cm="1">
+      <c r="O90" s="30" cm="1">
         <f t="array" ref="O90">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ClimateZones_Data(), Table_SourceData_ClimateZones[[#Headers],[Climate zone]], 0)</f>
         <v>7</v>
       </c>
-      <c r="P90" s="31" cm="1">
+      <c r="P90" s="30" cm="1">
         <f t="array" ref="P90">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ClimateZones_Data(), Table_SourceData_ClimateZones[[#Headers],[Climate zone]], 0)</f>
         <v>1000</v>
       </c>
-      <c r="Q90" s="31" cm="1">
+      <c r="Q90" s="30" cm="1">
         <f t="array" ref="Q90">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ClimateZones_Data(), Table_SourceData_ClimateZones[[#Headers],[Climate zone]], 0)</f>
         <v>999999</v>
       </c>
-      <c r="R90" s="31" cm="1">
+      <c r="R90" s="30" cm="1">
         <f t="array" ref="R90">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ClimateZones_Data(), Table_SourceData_ClimateZones[[#Headers],[Climate zone]], 0)</f>
         <v>-999999</v>
       </c>
-      <c r="S90" s="31" cm="1">
+      <c r="S90" s="30" cm="1">
         <f t="array" ref="S90">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ClimateZones_Data(), Table_SourceData_ClimateZones[[#Headers],[Climate zone]], 0)</f>
         <v>999999</v>
       </c>
-      <c r="T90" s="31"/>
+      <c r="T90" s="30"/>
     </row>
     <row r="91" spans="4:20" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="D91" s="31" t="str" cm="1">
+      <c r="D91" s="30" t="str" cm="1">
         <f t="array" ref="D91">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ClimateZones_Data(), Table_SourceData_ClimateZones[[#Headers],[Climate zone]], 0)</f>
         <v>Tropical wet</v>
       </c>
-      <c r="E91" s="31" t="str" cm="1">
+      <c r="E91" s="30" t="str" cm="1">
         <f t="array" ref="E91">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ClimateZones_Data(), Table_SourceData_ClimateZones[[#Headers],[Climate zone]], 0)</f>
         <v>&gt; 18 C</v>
       </c>
-      <c r="F91" s="31" t="str" cm="1">
+      <c r="F91" s="30" t="str" cm="1">
         <f t="array" ref="F91">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ClimateZones_Data(), Table_SourceData_ClimateZones[[#Headers],[Climate zone]], 0)</f>
         <v>&gt; 2000 mm</v>
       </c>
-      <c r="G91" s="31" t="str" cm="1">
+      <c r="G91" s="30" t="str" cm="1">
         <f t="array" ref="G91">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ClimateZones_Data(), Table_SourceData_ClimateZones[[#Headers],[Climate zone]], 0)</f>
         <v>≤ 7</v>
       </c>
-      <c r="H91" s="31" t="str" cm="1">
+      <c r="H91" s="30" t="str" cm="1">
         <f t="array" ref="H91">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ClimateZones_Data(), Table_SourceData_ClimateZones[[#Headers],[Climate zone]], 0)</f>
         <v>≤ 1000 m</v>
       </c>
-      <c r="I91" s="31" t="str" cm="1">
+      <c r="I91" s="30" t="str" cm="1">
         <f t="array" ref="I91">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ClimateZones_Data(), Table_SourceData_ClimateZones[[#Headers],[Climate zone]], 0)</f>
         <v>Any</v>
       </c>
-      <c r="J91" s="31" cm="1">
+      <c r="J91" s="30" cm="1">
         <f t="array" ref="J91">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ClimateZones_Data(), Table_SourceData_ClimateZones[[#Headers],[Climate zone]], 0)</f>
         <v>18.001000000000001</v>
       </c>
-      <c r="K91" s="31" cm="1">
+      <c r="K91" s="30" cm="1">
         <f t="array" ref="K91">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ClimateZones_Data(), Table_SourceData_ClimateZones[[#Headers],[Climate zone]], 0)</f>
         <v>999999</v>
       </c>
-      <c r="L91" s="31" cm="1">
+      <c r="L91" s="30" cm="1">
         <f t="array" ref="L91">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ClimateZones_Data(), Table_SourceData_ClimateZones[[#Headers],[Climate zone]], 0)</f>
         <v>2000.001</v>
       </c>
-      <c r="M91" s="31" cm="1">
+      <c r="M91" s="30" cm="1">
         <f t="array" ref="M91">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ClimateZones_Data(), Table_SourceData_ClimateZones[[#Headers],[Climate zone]], 0)</f>
         <v>999999</v>
       </c>
-      <c r="N91" s="31" cm="1">
+      <c r="N91" s="30" cm="1">
         <f t="array" ref="N91">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ClimateZones_Data(), Table_SourceData_ClimateZones[[#Headers],[Climate zone]], 0)</f>
         <v>-999999</v>
       </c>
-      <c r="O91" s="31" cm="1">
+      <c r="O91" s="30" cm="1">
         <f t="array" ref="O91">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ClimateZones_Data(), Table_SourceData_ClimateZones[[#Headers],[Climate zone]], 0)</f>
         <v>7</v>
       </c>
-      <c r="P91" s="31" cm="1">
+      <c r="P91" s="30" cm="1">
         <f t="array" ref="P91">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ClimateZones_Data(), Table_SourceData_ClimateZones[[#Headers],[Climate zone]], 0)</f>
         <v>-999999</v>
       </c>
-      <c r="Q91" s="31" cm="1">
+      <c r="Q91" s="30" cm="1">
         <f t="array" ref="Q91">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ClimateZones_Data(), Table_SourceData_ClimateZones[[#Headers],[Climate zone]], 0)</f>
         <v>999.99900000000002</v>
       </c>
-      <c r="R91" s="31" cm="1">
+      <c r="R91" s="30" cm="1">
         <f t="array" ref="R91">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ClimateZones_Data(), Table_SourceData_ClimateZones[[#Headers],[Climate zone]], 0)</f>
         <v>-999999</v>
       </c>
-      <c r="S91" s="31" cm="1">
+      <c r="S91" s="30" cm="1">
         <f t="array" ref="S91">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ClimateZones_Data(), Table_SourceData_ClimateZones[[#Headers],[Climate zone]], 0)</f>
         <v>999999</v>
       </c>
-      <c r="T91" s="31"/>
+      <c r="T91" s="30"/>
     </row>
     <row r="92" spans="4:20" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="D92" s="31" t="str" cm="1">
+      <c r="D92" s="30" t="str" cm="1">
         <f t="array" ref="D92">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ClimateZones_Data(), Table_SourceData_ClimateZones[[#Headers],[Climate zone]], 0)</f>
         <v>Tropical moist</v>
       </c>
-      <c r="E92" s="31" t="str" cm="1">
+      <c r="E92" s="30" t="str" cm="1">
         <f t="array" ref="E92">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ClimateZones_Data(), Table_SourceData_ClimateZones[[#Headers],[Climate zone]], 0)</f>
         <v>&gt; 18 C</v>
       </c>
-      <c r="F92" s="31" t="str" cm="1">
+      <c r="F92" s="30" t="str" cm="1">
         <f t="array" ref="F92">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ClimateZones_Data(), Table_SourceData_ClimateZones[[#Headers],[Climate zone]], 0)</f>
         <v>&gt; 1000 mm - ≤ 2000 mm</v>
       </c>
-      <c r="G92" s="31" t="str" cm="1">
+      <c r="G92" s="30" t="str" cm="1">
         <f t="array" ref="G92">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ClimateZones_Data(), Table_SourceData_ClimateZones[[#Headers],[Climate zone]], 0)</f>
         <v>≤ 7</v>
       </c>
-      <c r="H92" s="31" t="str" cm="1">
+      <c r="H92" s="30" t="str" cm="1">
         <f t="array" ref="H92">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ClimateZones_Data(), Table_SourceData_ClimateZones[[#Headers],[Climate zone]], 0)</f>
         <v>≤ 1000 m</v>
       </c>
-      <c r="I92" s="31" t="str" cm="1">
+      <c r="I92" s="30" t="str" cm="1">
         <f t="array" ref="I92">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ClimateZones_Data(), Table_SourceData_ClimateZones[[#Headers],[Climate zone]], 0)</f>
         <v>Any</v>
       </c>
-      <c r="J92" s="31" cm="1">
+      <c r="J92" s="30" cm="1">
         <f t="array" ref="J92">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ClimateZones_Data(), Table_SourceData_ClimateZones[[#Headers],[Climate zone]], 0)</f>
         <v>18.001000000000001</v>
       </c>
-      <c r="K92" s="31" cm="1">
+      <c r="K92" s="30" cm="1">
         <f t="array" ref="K92">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ClimateZones_Data(), Table_SourceData_ClimateZones[[#Headers],[Climate zone]], 0)</f>
         <v>999999</v>
       </c>
-      <c r="L92" s="31" cm="1">
+      <c r="L92" s="30" cm="1">
         <f t="array" ref="L92">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ClimateZones_Data(), Table_SourceData_ClimateZones[[#Headers],[Climate zone]], 0)</f>
         <v>1000.001</v>
       </c>
-      <c r="M92" s="31" cm="1">
+      <c r="M92" s="30" cm="1">
         <f t="array" ref="M92">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ClimateZones_Data(), Table_SourceData_ClimateZones[[#Headers],[Climate zone]], 0)</f>
         <v>2000</v>
       </c>
-      <c r="N92" s="31" cm="1">
+      <c r="N92" s="30" cm="1">
         <f t="array" ref="N92">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ClimateZones_Data(), Table_SourceData_ClimateZones[[#Headers],[Climate zone]], 0)</f>
         <v>-999999</v>
       </c>
-      <c r="O92" s="31" cm="1">
+      <c r="O92" s="30" cm="1">
         <f t="array" ref="O92">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ClimateZones_Data(), Table_SourceData_ClimateZones[[#Headers],[Climate zone]], 0)</f>
         <v>7</v>
       </c>
-      <c r="P92" s="31" cm="1">
+      <c r="P92" s="30" cm="1">
         <f t="array" ref="P92">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ClimateZones_Data(), Table_SourceData_ClimateZones[[#Headers],[Climate zone]], 0)</f>
         <v>-999999</v>
       </c>
-      <c r="Q92" s="31" cm="1">
+      <c r="Q92" s="30" cm="1">
         <f t="array" ref="Q92">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ClimateZones_Data(), Table_SourceData_ClimateZones[[#Headers],[Climate zone]], 0)</f>
         <v>999.99900000000002</v>
       </c>
-      <c r="R92" s="31" cm="1">
+      <c r="R92" s="30" cm="1">
         <f t="array" ref="R92">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ClimateZones_Data(), Table_SourceData_ClimateZones[[#Headers],[Climate zone]], 0)</f>
         <v>-999999</v>
       </c>
-      <c r="S92" s="31" cm="1">
+      <c r="S92" s="30" cm="1">
         <f t="array" ref="S92">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ClimateZones_Data(), Table_SourceData_ClimateZones[[#Headers],[Climate zone]], 0)</f>
         <v>999999</v>
       </c>
-      <c r="T92" s="31"/>
+      <c r="T92" s="30"/>
     </row>
     <row r="93" spans="4:20" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="D93" s="31" t="str" cm="1">
+      <c r="D93" s="30" t="str" cm="1">
         <f t="array" ref="D93">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ClimateZones_Data(), Table_SourceData_ClimateZones[[#Headers],[Climate zone]], 0)</f>
         <v>Tropical dry</v>
       </c>
-      <c r="E93" s="31" t="str" cm="1">
+      <c r="E93" s="30" t="str" cm="1">
         <f t="array" ref="E93">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ClimateZones_Data(), Table_SourceData_ClimateZones[[#Headers],[Climate zone]], 0)</f>
         <v>&gt; 18 C</v>
       </c>
-      <c r="F93" s="31" t="str" cm="1">
+      <c r="F93" s="30" t="str" cm="1">
         <f t="array" ref="F93">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ClimateZones_Data(), Table_SourceData_ClimateZones[[#Headers],[Climate zone]], 0)</f>
         <v>≤ 1000 mm</v>
       </c>
-      <c r="G93" s="31" t="str" cm="1">
+      <c r="G93" s="30" t="str" cm="1">
         <f t="array" ref="G93">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ClimateZones_Data(), Table_SourceData_ClimateZones[[#Headers],[Climate zone]], 0)</f>
         <v>≤ 7</v>
       </c>
-      <c r="H93" s="31" t="str" cm="1">
+      <c r="H93" s="30" t="str" cm="1">
         <f t="array" ref="H93">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ClimateZones_Data(), Table_SourceData_ClimateZones[[#Headers],[Climate zone]], 0)</f>
         <v>≤ 1000 m</v>
       </c>
-      <c r="I93" s="31" t="str" cm="1">
+      <c r="I93" s="30" t="str" cm="1">
         <f t="array" ref="I93">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ClimateZones_Data(), Table_SourceData_ClimateZones[[#Headers],[Climate zone]], 0)</f>
         <v>Any</v>
       </c>
-      <c r="J93" s="31" cm="1">
+      <c r="J93" s="30" cm="1">
         <f t="array" ref="J93">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ClimateZones_Data(), Table_SourceData_ClimateZones[[#Headers],[Climate zone]], 0)</f>
         <v>18.001000000000001</v>
       </c>
-      <c r="K93" s="31" cm="1">
+      <c r="K93" s="30" cm="1">
         <f t="array" ref="K93">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ClimateZones_Data(), Table_SourceData_ClimateZones[[#Headers],[Climate zone]], 0)</f>
         <v>999999</v>
       </c>
-      <c r="L93" s="31" cm="1">
+      <c r="L93" s="30" cm="1">
         <f t="array" ref="L93">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ClimateZones_Data(), Table_SourceData_ClimateZones[[#Headers],[Climate zone]], 0)</f>
         <v>-999999</v>
       </c>
-      <c r="M93" s="31" cm="1">
+      <c r="M93" s="30" cm="1">
         <f t="array" ref="M93">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ClimateZones_Data(), Table_SourceData_ClimateZones[[#Headers],[Climate zone]], 0)</f>
         <v>1000</v>
       </c>
-      <c r="N93" s="31" cm="1">
+      <c r="N93" s="30" cm="1">
         <f t="array" ref="N93">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ClimateZones_Data(), Table_SourceData_ClimateZones[[#Headers],[Climate zone]], 0)</f>
         <v>-999999</v>
       </c>
-      <c r="O93" s="31" cm="1">
+      <c r="O93" s="30" cm="1">
         <f t="array" ref="O93">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ClimateZones_Data(), Table_SourceData_ClimateZones[[#Headers],[Climate zone]], 0)</f>
         <v>7</v>
       </c>
-      <c r="P93" s="31" cm="1">
+      <c r="P93" s="30" cm="1">
         <f t="array" ref="P93">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ClimateZones_Data(), Table_SourceData_ClimateZones[[#Headers],[Climate zone]], 0)</f>
         <v>-999999</v>
       </c>
-      <c r="Q93" s="31" cm="1">
+      <c r="Q93" s="30" cm="1">
         <f t="array" ref="Q93">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ClimateZones_Data(), Table_SourceData_ClimateZones[[#Headers],[Climate zone]], 0)</f>
         <v>999.99900000000002</v>
       </c>
-      <c r="R93" s="31" cm="1">
+      <c r="R93" s="30" cm="1">
         <f t="array" ref="R93">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ClimateZones_Data(), Table_SourceData_ClimateZones[[#Headers],[Climate zone]], 0)</f>
         <v>-999999</v>
       </c>
-      <c r="S93" s="31" cm="1">
+      <c r="S93" s="30" cm="1">
         <f t="array" ref="S93">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ClimateZones_Data(), Table_SourceData_ClimateZones[[#Headers],[Climate zone]], 0)</f>
         <v>999999</v>
       </c>
-      <c r="T93" s="31"/>
+      <c r="T93" s="30"/>
     </row>
     <row r="94" spans="4:20" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="D94" s="31" t="str" cm="1">
+      <c r="D94" s="30" t="str" cm="1">
         <f t="array" ref="D94">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ClimateZones_Data(), Table_SourceData_ClimateZones[[#Headers],[Climate zone]], 0)</f>
         <v>Warm temperate moist</v>
       </c>
-      <c r="E94" s="31" t="str" cm="1">
+      <c r="E94" s="30" t="str" cm="1">
         <f t="array" ref="E94">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ClimateZones_Data(), Table_SourceData_ClimateZones[[#Headers],[Climate zone]], 0)</f>
         <v>&gt; 10 C</v>
       </c>
-      <c r="F94" s="31" t="str" cm="1">
+      <c r="F94" s="30" t="str" cm="1">
         <f t="array" ref="F94">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ClimateZones_Data(), Table_SourceData_ClimateZones[[#Headers],[Climate zone]], 0)</f>
         <v>Any</v>
       </c>
-      <c r="G94" s="31" t="str" cm="1">
+      <c r="G94" s="30" t="str" cm="1">
         <f t="array" ref="G94">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ClimateZones_Data(), Table_SourceData_ClimateZones[[#Headers],[Climate zone]], 0)</f>
         <v>Any</v>
       </c>
-      <c r="H94" s="31" t="str" cm="1">
+      <c r="H94" s="30" t="str" cm="1">
         <f t="array" ref="H94">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ClimateZones_Data(), Table_SourceData_ClimateZones[[#Headers],[Climate zone]], 0)</f>
         <v>Any</v>
       </c>
-      <c r="I94" s="31" t="str" cm="1">
+      <c r="I94" s="30" t="str" cm="1">
         <f t="array" ref="I94">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ClimateZones_Data(), Table_SourceData_ClimateZones[[#Headers],[Climate zone]], 0)</f>
         <v>&gt; 1</v>
       </c>
-      <c r="J94" s="31" cm="1">
+      <c r="J94" s="30" cm="1">
         <f t="array" ref="J94">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ClimateZones_Data(), Table_SourceData_ClimateZones[[#Headers],[Climate zone]], 0)</f>
         <v>10.000999999999999</v>
       </c>
-      <c r="K94" s="31" cm="1">
+      <c r="K94" s="30" cm="1">
         <f t="array" ref="K94">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ClimateZones_Data(), Table_SourceData_ClimateZones[[#Headers],[Climate zone]], 0)</f>
         <v>999999</v>
       </c>
-      <c r="L94" s="31" cm="1">
+      <c r="L94" s="30" cm="1">
         <f t="array" ref="L94">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ClimateZones_Data(), Table_SourceData_ClimateZones[[#Headers],[Climate zone]], 0)</f>
         <v>-999999</v>
       </c>
-      <c r="M94" s="31" cm="1">
+      <c r="M94" s="30" cm="1">
         <f t="array" ref="M94">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ClimateZones_Data(), Table_SourceData_ClimateZones[[#Headers],[Climate zone]], 0)</f>
         <v>999999</v>
       </c>
-      <c r="N94" s="31" cm="1">
+      <c r="N94" s="30" cm="1">
         <f t="array" ref="N94">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ClimateZones_Data(), Table_SourceData_ClimateZones[[#Headers],[Climate zone]], 0)</f>
         <v>-999999</v>
       </c>
-      <c r="O94" s="31" cm="1">
+      <c r="O94" s="30" cm="1">
         <f t="array" ref="O94">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ClimateZones_Data(), Table_SourceData_ClimateZones[[#Headers],[Climate zone]], 0)</f>
         <v>999999</v>
       </c>
-      <c r="P94" s="31" cm="1">
+      <c r="P94" s="30" cm="1">
         <f t="array" ref="P94">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ClimateZones_Data(), Table_SourceData_ClimateZones[[#Headers],[Climate zone]], 0)</f>
         <v>-999999</v>
       </c>
-      <c r="Q94" s="31" cm="1">
+      <c r="Q94" s="30" cm="1">
         <f t="array" ref="Q94">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ClimateZones_Data(), Table_SourceData_ClimateZones[[#Headers],[Climate zone]], 0)</f>
         <v>999999</v>
       </c>
-      <c r="R94" s="31" cm="1">
+      <c r="R94" s="30" cm="1">
         <f t="array" ref="R94">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ClimateZones_Data(), Table_SourceData_ClimateZones[[#Headers],[Climate zone]], 0)</f>
         <v>1.0009999999999999</v>
       </c>
-      <c r="S94" s="31" cm="1">
+      <c r="S94" s="30" cm="1">
         <f t="array" ref="S94">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ClimateZones_Data(), Table_SourceData_ClimateZones[[#Headers],[Climate zone]], 0)</f>
         <v>999999</v>
       </c>
-      <c r="T94" s="31"/>
+      <c r="T94" s="30"/>
     </row>
     <row r="95" spans="4:20" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="D95" s="31" t="str" cm="1">
+      <c r="D95" s="30" t="str" cm="1">
         <f t="array" ref="D95">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ClimateZones_Data(), Table_SourceData_ClimateZones[[#Headers],[Climate zone]], 0)</f>
         <v>Warm temperate dry</v>
       </c>
-      <c r="E95" s="31" t="str" cm="1">
+      <c r="E95" s="30" t="str" cm="1">
         <f t="array" ref="E95">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ClimateZones_Data(), Table_SourceData_ClimateZones[[#Headers],[Climate zone]], 0)</f>
         <v>&gt; 10 C</v>
       </c>
-      <c r="F95" s="31" t="str" cm="1">
+      <c r="F95" s="30" t="str" cm="1">
         <f t="array" ref="F95">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ClimateZones_Data(), Table_SourceData_ClimateZones[[#Headers],[Climate zone]], 0)</f>
         <v>Any</v>
       </c>
-      <c r="G95" s="31" t="str" cm="1">
+      <c r="G95" s="30" t="str" cm="1">
         <f t="array" ref="G95">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ClimateZones_Data(), Table_SourceData_ClimateZones[[#Headers],[Climate zone]], 0)</f>
         <v>Any</v>
       </c>
-      <c r="H95" s="31" t="str" cm="1">
+      <c r="H95" s="30" t="str" cm="1">
         <f t="array" ref="H95">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ClimateZones_Data(), Table_SourceData_ClimateZones[[#Headers],[Climate zone]], 0)</f>
         <v>Any</v>
       </c>
-      <c r="I95" s="31" t="str" cm="1">
+      <c r="I95" s="30" t="str" cm="1">
         <f t="array" ref="I95">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ClimateZones_Data(), Table_SourceData_ClimateZones[[#Headers],[Climate zone]], 0)</f>
         <v>≤ 1</v>
       </c>
-      <c r="J95" s="31" cm="1">
+      <c r="J95" s="30" cm="1">
         <f t="array" ref="J95">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ClimateZones_Data(), Table_SourceData_ClimateZones[[#Headers],[Climate zone]], 0)</f>
         <v>10.000999999999999</v>
       </c>
-      <c r="K95" s="31" cm="1">
+      <c r="K95" s="30" cm="1">
         <f t="array" ref="K95">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ClimateZones_Data(), Table_SourceData_ClimateZones[[#Headers],[Climate zone]], 0)</f>
         <v>999999</v>
       </c>
-      <c r="L95" s="31" cm="1">
+      <c r="L95" s="30" cm="1">
         <f t="array" ref="L95">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ClimateZones_Data(), Table_SourceData_ClimateZones[[#Headers],[Climate zone]], 0)</f>
         <v>-999999</v>
       </c>
-      <c r="M95" s="31" cm="1">
+      <c r="M95" s="30" cm="1">
         <f t="array" ref="M95">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ClimateZones_Data(), Table_SourceData_ClimateZones[[#Headers],[Climate zone]], 0)</f>
         <v>999999</v>
       </c>
-      <c r="N95" s="31" cm="1">
+      <c r="N95" s="30" cm="1">
         <f t="array" ref="N95">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ClimateZones_Data(), Table_SourceData_ClimateZones[[#Headers],[Climate zone]], 0)</f>
         <v>-999999</v>
       </c>
-      <c r="O95" s="31" cm="1">
+      <c r="O95" s="30" cm="1">
         <f t="array" ref="O95">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ClimateZones_Data(), Table_SourceData_ClimateZones[[#Headers],[Climate zone]], 0)</f>
         <v>999999</v>
       </c>
-      <c r="P95" s="31" cm="1">
+      <c r="P95" s="30" cm="1">
         <f t="array" ref="P95">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ClimateZones_Data(), Table_SourceData_ClimateZones[[#Headers],[Climate zone]], 0)</f>
         <v>-999999</v>
       </c>
-      <c r="Q95" s="31" cm="1">
+      <c r="Q95" s="30" cm="1">
         <f t="array" ref="Q95">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ClimateZones_Data(), Table_SourceData_ClimateZones[[#Headers],[Climate zone]], 0)</f>
         <v>999999</v>
       </c>
-      <c r="R95" s="31" cm="1">
+      <c r="R95" s="30" cm="1">
         <f t="array" ref="R95">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ClimateZones_Data(), Table_SourceData_ClimateZones[[#Headers],[Climate zone]], 0)</f>
         <v>-999999</v>
       </c>
-      <c r="S95" s="31" cm="1">
+      <c r="S95" s="30" cm="1">
         <f t="array" ref="S95">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ClimateZones_Data(), Table_SourceData_ClimateZones[[#Headers],[Climate zone]], 0)</f>
         <v>1</v>
       </c>
-      <c r="T95" s="31"/>
+      <c r="T95" s="30"/>
     </row>
     <row r="96" spans="4:20" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="D96" s="31" t="str" cm="1">
+      <c r="D96" s="30" t="str" cm="1">
         <f t="array" ref="D96">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ClimateZones_Data(), Table_SourceData_ClimateZones[[#Headers],[Climate zone]], 0)</f>
         <v>Cool temperate moist</v>
       </c>
-      <c r="E96" s="31" t="str" cm="1">
+      <c r="E96" s="30" t="str" cm="1">
         <f t="array" ref="E96">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ClimateZones_Data(), Table_SourceData_ClimateZones[[#Headers],[Climate zone]], 0)</f>
         <v>&gt; 0 C - ≤ 10 C</v>
       </c>
-      <c r="F96" s="31" t="str" cm="1">
+      <c r="F96" s="30" t="str" cm="1">
         <f t="array" ref="F96">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ClimateZones_Data(), Table_SourceData_ClimateZones[[#Headers],[Climate zone]], 0)</f>
         <v>Any</v>
       </c>
-      <c r="G96" s="31" t="str" cm="1">
+      <c r="G96" s="30" t="str" cm="1">
         <f t="array" ref="G96">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ClimateZones_Data(), Table_SourceData_ClimateZones[[#Headers],[Climate zone]], 0)</f>
         <v>Any</v>
       </c>
-      <c r="H96" s="31" t="str" cm="1">
+      <c r="H96" s="30" t="str" cm="1">
         <f t="array" ref="H96">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ClimateZones_Data(), Table_SourceData_ClimateZones[[#Headers],[Climate zone]], 0)</f>
         <v>Any</v>
       </c>
-      <c r="I96" s="31" t="str" cm="1">
+      <c r="I96" s="30" t="str" cm="1">
         <f t="array" ref="I96">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ClimateZones_Data(), Table_SourceData_ClimateZones[[#Headers],[Climate zone]], 0)</f>
         <v>&gt; 1</v>
       </c>
-      <c r="J96" s="31" cm="1">
+      <c r="J96" s="30" cm="1">
         <f t="array" ref="J96">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ClimateZones_Data(), Table_SourceData_ClimateZones[[#Headers],[Climate zone]], 0)</f>
         <v>-999999</v>
       </c>
-      <c r="K96" s="31" cm="1">
+      <c r="K96" s="30" cm="1">
         <f t="array" ref="K96">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ClimateZones_Data(), Table_SourceData_ClimateZones[[#Headers],[Climate zone]], 0)</f>
         <v>10</v>
       </c>
-      <c r="L96" s="31" cm="1">
+      <c r="L96" s="30" cm="1">
         <f t="array" ref="L96">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ClimateZones_Data(), Table_SourceData_ClimateZones[[#Headers],[Climate zone]], 0)</f>
         <v>-999999</v>
       </c>
-      <c r="M96" s="31" cm="1">
+      <c r="M96" s="30" cm="1">
         <f t="array" ref="M96">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ClimateZones_Data(), Table_SourceData_ClimateZones[[#Headers],[Climate zone]], 0)</f>
         <v>999999</v>
       </c>
-      <c r="N96" s="31" cm="1">
+      <c r="N96" s="30" cm="1">
         <f t="array" ref="N96">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ClimateZones_Data(), Table_SourceData_ClimateZones[[#Headers],[Climate zone]], 0)</f>
         <v>-999999</v>
       </c>
-      <c r="O96" s="31" cm="1">
+      <c r="O96" s="30" cm="1">
         <f t="array" ref="O96">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ClimateZones_Data(), Table_SourceData_ClimateZones[[#Headers],[Climate zone]], 0)</f>
         <v>999999</v>
       </c>
-      <c r="P96" s="31" cm="1">
+      <c r="P96" s="30" cm="1">
         <f t="array" ref="P96">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ClimateZones_Data(), Table_SourceData_ClimateZones[[#Headers],[Climate zone]], 0)</f>
         <v>-999999</v>
       </c>
-      <c r="Q96" s="31" cm="1">
+      <c r="Q96" s="30" cm="1">
         <f t="array" ref="Q96">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ClimateZones_Data(), Table_SourceData_ClimateZones[[#Headers],[Climate zone]], 0)</f>
         <v>999999</v>
       </c>
-      <c r="R96" s="31" cm="1">
+      <c r="R96" s="30" cm="1">
         <f t="array" ref="R96">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ClimateZones_Data(), Table_SourceData_ClimateZones[[#Headers],[Climate zone]], 0)</f>
         <v>1.0009999999999999</v>
       </c>
-      <c r="S96" s="31" cm="1">
+      <c r="S96" s="30" cm="1">
         <f t="array" ref="S96">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ClimateZones_Data(), Table_SourceData_ClimateZones[[#Headers],[Climate zone]], 0)</f>
         <v>999999</v>
       </c>
-      <c r="T96" s="31"/>
+      <c r="T96" s="30"/>
     </row>
     <row r="97" spans="4:20" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="D97" s="31" t="str" cm="1">
+      <c r="D97" s="30" t="str" cm="1">
         <f t="array" ref="D97">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ClimateZones_Data(), Table_SourceData_ClimateZones[[#Headers],[Climate zone]], 0)</f>
         <v>Cool temperate dry</v>
       </c>
-      <c r="E97" s="31" t="str" cm="1">
+      <c r="E97" s="30" t="str" cm="1">
         <f t="array" ref="E97">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ClimateZones_Data(), Table_SourceData_ClimateZones[[#Headers],[Climate zone]], 0)</f>
         <v>&gt; 0 C - ≤ 10 C</v>
       </c>
-      <c r="F97" s="31" t="str" cm="1">
+      <c r="F97" s="30" t="str" cm="1">
         <f t="array" ref="F97">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ClimateZones_Data(), Table_SourceData_ClimateZones[[#Headers],[Climate zone]], 0)</f>
         <v>Any</v>
       </c>
-      <c r="G97" s="31" t="str" cm="1">
+      <c r="G97" s="30" t="str" cm="1">
         <f t="array" ref="G97">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ClimateZones_Data(), Table_SourceData_ClimateZones[[#Headers],[Climate zone]], 0)</f>
         <v>Any</v>
       </c>
-      <c r="H97" s="31" t="str" cm="1">
+      <c r="H97" s="30" t="str" cm="1">
         <f t="array" ref="H97">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ClimateZones_Data(), Table_SourceData_ClimateZones[[#Headers],[Climate zone]], 0)</f>
         <v>Any</v>
       </c>
-      <c r="I97" s="31" t="str" cm="1">
+      <c r="I97" s="30" t="str" cm="1">
         <f t="array" ref="I97">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ClimateZones_Data(), Table_SourceData_ClimateZones[[#Headers],[Climate zone]], 0)</f>
         <v>≤ 1</v>
       </c>
-      <c r="J97" s="31" cm="1">
+      <c r="J97" s="30" cm="1">
         <f t="array" ref="J97">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ClimateZones_Data(), Table_SourceData_ClimateZones[[#Headers],[Climate zone]], 0)</f>
         <v>-999999</v>
       </c>
-      <c r="K97" s="31" cm="1">
+      <c r="K97" s="30" cm="1">
         <f t="array" ref="K97">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ClimateZones_Data(), Table_SourceData_ClimateZones[[#Headers],[Climate zone]], 0)</f>
         <v>10</v>
       </c>
-      <c r="L97" s="31" cm="1">
+      <c r="L97" s="30" cm="1">
         <f t="array" ref="L97">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ClimateZones_Data(), Table_SourceData_ClimateZones[[#Headers],[Climate zone]], 0)</f>
         <v>-999999</v>
       </c>
-      <c r="M97" s="31" cm="1">
+      <c r="M97" s="30" cm="1">
         <f t="array" ref="M97">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ClimateZones_Data(), Table_SourceData_ClimateZones[[#Headers],[Climate zone]], 0)</f>
         <v>999999</v>
       </c>
-      <c r="N97" s="31" cm="1">
+      <c r="N97" s="30" cm="1">
         <f t="array" ref="N97">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ClimateZones_Data(), Table_SourceData_ClimateZones[[#Headers],[Climate zone]], 0)</f>
         <v>-999999</v>
       </c>
-      <c r="O97" s="31" cm="1">
+      <c r="O97" s="30" cm="1">
         <f t="array" ref="O97">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ClimateZones_Data(), Table_SourceData_ClimateZones[[#Headers],[Climate zone]], 0)</f>
         <v>999999</v>
       </c>
-      <c r="P97" s="31" cm="1">
+      <c r="P97" s="30" cm="1">
         <f t="array" ref="P97">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ClimateZones_Data(), Table_SourceData_ClimateZones[[#Headers],[Climate zone]], 0)</f>
         <v>-999999</v>
       </c>
-      <c r="Q97" s="31" cm="1">
+      <c r="Q97" s="30" cm="1">
         <f t="array" ref="Q97">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ClimateZones_Data(), Table_SourceData_ClimateZones[[#Headers],[Climate zone]], 0)</f>
         <v>999999</v>
       </c>
-      <c r="R97" s="31" cm="1">
+      <c r="R97" s="30" cm="1">
         <f t="array" ref="R97">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ClimateZones_Data(), Table_SourceData_ClimateZones[[#Headers],[Climate zone]], 0)</f>
         <v>-999999</v>
       </c>
-      <c r="S97" s="31" cm="1">
+      <c r="S97" s="30" cm="1">
         <f t="array" ref="S97">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ClimateZones_Data(), Table_SourceData_ClimateZones[[#Headers],[Climate zone]], 0)</f>
         <v>1</v>
       </c>
-      <c r="T97" s="31"/>
+      <c r="T97" s="30"/>
     </row>
     <row r="98" spans="4:20" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="99" spans="4:20" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
@@ -8848,76 +8847,76 @@
       </c>
     </row>
     <row r="107" spans="4:20" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="D107" s="37" t="str" cm="1">
+      <c r="D107" s="36" t="str" cm="1">
         <f t="array" ref="D107">"⚠️" &amp; Common_SourceData.Common_SourceData_TemperatureZones_Variation()</f>
         <v>⚠️VARIATION OF SOURCE DATA: Added extra MAT min and MAT max columns to calculate zone from real temperature data.</v>
       </c>
     </row>
     <row r="108" spans="4:20" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="109" spans="4:20" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="D109" s="31" t="s">
-        <v>55</v>
-      </c>
-      <c r="E109" s="31" t="s">
-        <v>40</v>
-      </c>
-      <c r="F109" s="31" t="s">
-        <v>56</v>
-      </c>
-      <c r="G109" s="31" t="s">
-        <v>57</v>
+      <c r="D109" s="30" t="s">
+        <v>50</v>
+      </c>
+      <c r="E109" s="30" t="s">
+        <v>35</v>
+      </c>
+      <c r="F109" s="30" t="s">
+        <v>51</v>
+      </c>
+      <c r="G109" s="30" t="s">
+        <v>52</v>
       </c>
     </row>
     <row r="110" spans="4:20" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="D110" s="31" t="str" cm="1">
+      <c r="D110" s="30" t="str" cm="1">
         <f t="array" ref="D110">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_TemperatureZones_Data(),Table_SourceData_TemperatureZones[[#Headers],[Temperature Zone]],0)</f>
         <v>Warm</v>
       </c>
-      <c r="E110" s="31" t="str" cm="1">
+      <c r="E110" s="30" t="str" cm="1">
         <f t="array" ref="E110">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_TemperatureZones_Data(),Table_SourceData_TemperatureZones[[#Headers],[Temperature Zone]],0)</f>
         <v>≥ 26 C</v>
       </c>
-      <c r="F110" s="31" cm="1">
+      <c r="F110" s="30" cm="1">
         <f t="array" ref="F110">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_TemperatureZones_Data(),Table_SourceData_TemperatureZones[[#Headers],[Temperature Zone]],0)</f>
         <v>26</v>
       </c>
-      <c r="G110" s="31" cm="1">
+      <c r="G110" s="30" cm="1">
         <f t="array" ref="G110">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_TemperatureZones_Data(),Table_SourceData_TemperatureZones[[#Headers],[Temperature Zone]],0)</f>
         <v>999999</v>
       </c>
     </row>
     <row r="111" spans="4:20" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="D111" s="31" t="str" cm="1">
+      <c r="D111" s="30" t="str" cm="1">
         <f t="array" ref="D111">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_TemperatureZones_Data(),Table_SourceData_TemperatureZones[[#Headers],[Temperature Zone]],0)</f>
         <v>Temperate</v>
       </c>
-      <c r="E111" s="31" t="str" cm="1">
+      <c r="E111" s="30" t="str" cm="1">
         <f t="array" ref="E111">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_TemperatureZones_Data(),Table_SourceData_TemperatureZones[[#Headers],[Temperature Zone]],0)</f>
         <v>15 - 25 C</v>
       </c>
-      <c r="F111" s="31" cm="1">
+      <c r="F111" s="30" cm="1">
         <f t="array" ref="F111">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_TemperatureZones_Data(),Table_SourceData_TemperatureZones[[#Headers],[Temperature Zone]],0)</f>
         <v>15</v>
       </c>
-      <c r="G111" s="31" cm="1">
+      <c r="G111" s="30" cm="1">
         <f t="array" ref="G111">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_TemperatureZones_Data(),Table_SourceData_TemperatureZones[[#Headers],[Temperature Zone]],0)</f>
         <v>25.998999999999999</v>
       </c>
     </row>
     <row r="112" spans="4:20" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="D112" s="31" t="str" cm="1">
+      <c r="D112" s="30" t="str" cm="1">
         <f t="array" ref="D112">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_TemperatureZones_Data(),Table_SourceData_TemperatureZones[[#Headers],[Temperature Zone]],0)</f>
         <v>Cool</v>
       </c>
-      <c r="E112" s="31" t="str" cm="1">
+      <c r="E112" s="30" t="str" cm="1">
         <f t="array" ref="E112">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_TemperatureZones_Data(),Table_SourceData_TemperatureZones[[#Headers],[Temperature Zone]],0)</f>
         <v>≤ 14 C</v>
       </c>
-      <c r="F112" s="31" cm="1">
+      <c r="F112" s="30" cm="1">
         <f t="array" ref="F112">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_TemperatureZones_Data(),Table_SourceData_TemperatureZones[[#Headers],[Temperature Zone]],0)</f>
         <v>-999999</v>
       </c>
-      <c r="G112" s="31" cm="1">
+      <c r="G112" s="30" cm="1">
         <f t="array" ref="G112">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_TemperatureZones_Data(),Table_SourceData_TemperatureZones[[#Headers],[Temperature Zone]],0)</f>
         <v>14.999000000000001</v>
       </c>
@@ -8929,80 +8928,80 @@
         <f t="array" ref="D115">Common_SourceData.Common_SourceData_RainfallZones_Title()</f>
         <v>VEERG Australian rainfall zones</v>
       </c>
-      <c r="BN115" s="33"/>
+      <c r="BN115" s="32"/>
     </row>
     <row r="116" spans="4:66" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D116" s="28" t="str" cm="1">
         <f t="array" ref="D116">Common_SourceData.Common_SourceData_RainfallZones_Source()</f>
         <v>VEERG 2026: Table 1.3: Climate and Rainfall zone classifications and definitions</v>
       </c>
-      <c r="BN116" s="33"/>
+      <c r="BN116" s="32"/>
     </row>
     <row r="117" spans="4:66" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="D117" s="37" t="str" cm="1">
+      <c r="D117" s="36" t="str" cm="1">
         <f t="array" ref="D117">"⚠️" &amp; Common_SourceData.Common_SourceData_RainfallZones_Variation()</f>
         <v>⚠️VARIATION OF SOURCE DATA: Added extra Rainfall min and Rainfall max columns to calculate zone from real rainfall data.</v>
       </c>
-      <c r="BN117" s="33"/>
+      <c r="BN117" s="32"/>
     </row>
     <row r="118" spans="4:66" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="BN118" s="33"/>
+      <c r="BN118" s="32"/>
     </row>
     <row r="119" spans="4:66" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="D119" s="31" t="s">
-        <v>58</v>
-      </c>
-      <c r="E119" s="31" t="s">
-        <v>59</v>
-      </c>
-      <c r="F119" s="31" t="s">
-        <v>47</v>
-      </c>
-      <c r="G119" s="31" t="s">
-        <v>48</v>
-      </c>
-      <c r="BN119" s="33"/>
+      <c r="D119" s="30" t="s">
+        <v>53</v>
+      </c>
+      <c r="E119" s="30" t="s">
+        <v>54</v>
+      </c>
+      <c r="F119" s="30" t="s">
+        <v>42</v>
+      </c>
+      <c r="G119" s="30" t="s">
+        <v>43</v>
+      </c>
+      <c r="BN119" s="32"/>
     </row>
     <row r="120" spans="4:66" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="D120" s="31" t="str" cm="1">
+      <c r="D120" s="30" t="str" cm="1">
         <f t="array" ref="D120">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_RainfallZones_Data(),Table_SourceData_RainfallZones[[#Headers],[Rainfall Zone]],0)</f>
         <v>High rainfall</v>
       </c>
-      <c r="E120" s="31" t="str" cm="1">
+      <c r="E120" s="30" t="str" cm="1">
         <f t="array" ref="E120">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_RainfallZones_Data(),Table_SourceData_RainfallZones[[#Headers],[Rainfall Zone]],0)</f>
         <v>Annual rainfall &gt; 600mm</v>
       </c>
-      <c r="F120" s="31" cm="1">
+      <c r="F120" s="30" cm="1">
         <f t="array" ref="F120">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_RainfallZones_Data(),Table_SourceData_RainfallZones[[#Headers],[Rainfall Zone]],0)</f>
         <v>600.00099999999998</v>
       </c>
-      <c r="G120" s="31" cm="1">
+      <c r="G120" s="30" cm="1">
         <f t="array" ref="G120">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_RainfallZones_Data(),Table_SourceData_RainfallZones[[#Headers],[Rainfall Zone]],0)</f>
         <v>999999</v>
       </c>
-      <c r="BN120" s="33"/>
+      <c r="BN120" s="32"/>
     </row>
     <row r="121" spans="4:66" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="D121" s="31" t="str" cm="1">
+      <c r="D121" s="30" t="str" cm="1">
         <f t="array" ref="D121">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_RainfallZones_Data(),Table_SourceData_RainfallZones[[#Headers],[Rainfall Zone]],0)</f>
         <v>Low rainfall</v>
       </c>
-      <c r="E121" s="31" t="str" cm="1">
+      <c r="E121" s="30" t="str" cm="1">
         <f t="array" ref="E121">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_RainfallZones_Data(),Table_SourceData_RainfallZones[[#Headers],[Rainfall Zone]],0)</f>
         <v>Annual rainfall ≤ 600mm</v>
       </c>
-      <c r="F121" s="31" cm="1">
+      <c r="F121" s="30" cm="1">
         <f t="array" ref="F121">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_RainfallZones_Data(),Table_SourceData_RainfallZones[[#Headers],[Rainfall Zone]],0)</f>
         <v>-999999</v>
       </c>
-      <c r="G121" s="31" cm="1">
+      <c r="G121" s="30" cm="1">
         <f t="array" ref="G121">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_RainfallZones_Data(),Table_SourceData_RainfallZones[[#Headers],[Rainfall Zone]],0)</f>
         <v>600</v>
       </c>
-      <c r="BN121" s="33"/>
+      <c r="BN121" s="32"/>
     </row>
     <row r="122" spans="4:66" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="BN122" s="33"/>
+      <c r="BN122" s="32"/>
     </row>
     <row r="123" spans="4:66" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="124" spans="4:66" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
@@ -9019,29 +9018,29 @@
     </row>
     <row r="126" spans="4:66" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="127" spans="4:66" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="D127" s="31" t="s">
-        <v>60</v>
-      </c>
-      <c r="E127" s="31" t="s">
-        <v>61</v>
+      <c r="D127" s="30" t="s">
+        <v>55</v>
+      </c>
+      <c r="E127" s="30" t="s">
+        <v>56</v>
       </c>
     </row>
     <row r="128" spans="4:66" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="D128" s="31" t="str" cm="1">
+      <c r="D128" s="30" t="str" cm="1">
         <f t="array" ref="D128">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_LeachingZones_Data(), Table_SourceData_LeachingZones[[#Headers],[Leaching Zone]], 0)</f>
         <v>Leaching occurs</v>
       </c>
-      <c r="E128" s="31" t="str" cm="1">
+      <c r="E128" s="30" t="str" cm="1">
         <f t="array" ref="E128">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_LeachingZones_Data(), Table_SourceData_LeachingZones[[#Headers],[Leaching Zone]], 0)</f>
         <v>Σ(𝑟𝑎𝑖𝑛)&gt;Σ(𝐸𝑇0)+𝑠𝑜𝑖𝑙 𝑤𝑎𝑡𝑒𝑟 ℎ𝑜𝑙𝑑𝑖𝑛𝑔 𝑐𝑎𝑝𝑎𝑐𝑖𝑡𝑦</v>
       </c>
     </row>
     <row r="129" spans="4:77" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="D129" s="31" t="str" cm="1">
+      <c r="D129" s="30" t="str" cm="1">
         <f t="array" ref="D129">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_LeachingZones_Data(), Table_SourceData_LeachingZones[[#Headers],[Leaching Zone]], 0)</f>
         <v>Leaching does not occur</v>
       </c>
-      <c r="E129" s="31" t="str" cm="1">
+      <c r="E129" s="30" t="str" cm="1">
         <f t="array" ref="E129">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_LeachingZones_Data(), Table_SourceData_LeachingZones[[#Headers],[Leaching Zone]], 0)</f>
         <v>Σ(𝑟𝑎𝑖𝑛)≤Σ(𝐸𝑇0)+𝑠𝑜𝑖𝑙 𝑤𝑎𝑡𝑒𝑟 ℎ𝑜𝑙𝑑𝑖𝑛𝑔 𝑐𝑎𝑝𝑎𝑐𝑖𝑡𝑦</v>
       </c>
@@ -9064,10 +9063,10 @@
     </row>
     <row r="134" spans="4:77" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D134" t="s">
-        <v>62</v>
+        <v>57</v>
       </c>
       <c r="E134" t="s">
-        <v>63</v>
+        <v>58</v>
       </c>
     </row>
     <row r="135" spans="4:77" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
@@ -9085,243 +9084,243 @@
         <f t="array" ref="D136">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_FracWET_Data(),Table_SourceData_FracWET[[#Headers],[Is in leaching zone]],0)</f>
         <v>No - not in leaching zone</v>
       </c>
-      <c r="E136" s="31" cm="1">
+      <c r="E136" s="30" cm="1">
         <f t="array" ref="E136">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_FracWET_Data(),Table_SourceData_FracWET[[#Headers],[Is in leaching zone]],0)</f>
         <v>0</v>
       </c>
     </row>
     <row r="137" spans="4:77" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="138" spans="4:77" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="BN138" s="33"/>
-      <c r="BO138" s="33"/>
-      <c r="BP138" s="33"/>
-      <c r="BQ138" s="33"/>
-      <c r="BR138" s="33"/>
-      <c r="BS138" s="33"/>
-      <c r="BT138" s="33"/>
-      <c r="BU138" s="33"/>
-      <c r="BV138" s="33"/>
-      <c r="BW138" s="33"/>
-      <c r="BX138" s="33"/>
-      <c r="BY138" s="33"/>
+      <c r="BN138" s="32"/>
+      <c r="BO138" s="32"/>
+      <c r="BP138" s="32"/>
+      <c r="BQ138" s="32"/>
+      <c r="BR138" s="32"/>
+      <c r="BS138" s="32"/>
+      <c r="BT138" s="32"/>
+      <c r="BU138" s="32"/>
+      <c r="BV138" s="32"/>
+      <c r="BW138" s="32"/>
+      <c r="BX138" s="32"/>
+      <c r="BY138" s="32"/>
     </row>
     <row r="139" spans="4:77" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D139" s="2" t="str" cm="1">
         <f t="array" ref="D139">Common_SourceData.Common_SourceData_FracWETIrrigation_Title()</f>
         <v>FracWET for irrigation types</v>
       </c>
-      <c r="BN139" s="33"/>
-      <c r="BO139" s="33"/>
-      <c r="BP139" s="33"/>
-      <c r="BQ139" s="33"/>
-      <c r="BR139" s="33"/>
-      <c r="BS139" s="33"/>
-      <c r="BT139" s="33"/>
-      <c r="BU139" s="33"/>
-      <c r="BV139" s="33"/>
-      <c r="BW139" s="33"/>
-      <c r="BX139" s="33"/>
-      <c r="BY139" s="33"/>
+      <c r="BN139" s="32"/>
+      <c r="BO139" s="32"/>
+      <c r="BP139" s="32"/>
+      <c r="BQ139" s="32"/>
+      <c r="BR139" s="32"/>
+      <c r="BS139" s="32"/>
+      <c r="BT139" s="32"/>
+      <c r="BU139" s="32"/>
+      <c r="BV139" s="32"/>
+      <c r="BW139" s="32"/>
+      <c r="BX139" s="32"/>
+      <c r="BY139" s="32"/>
     </row>
     <row r="140" spans="4:77" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D140" s="28" t="str" cm="1">
         <f t="array" ref="D140">Common_SourceData.Common_SourceData_FracWETIrrigation_Source()</f>
         <v>VEERG 2026: Chapter 1, section 1.8.2 Leaching, climate and rainfall zones</v>
       </c>
-      <c r="BN140" s="33"/>
-      <c r="BO140" s="33"/>
-      <c r="BP140" s="33"/>
-      <c r="BQ140" s="33"/>
-      <c r="BR140" s="33"/>
-      <c r="BS140" s="33"/>
-      <c r="BT140" s="33"/>
-      <c r="BU140" s="33"/>
-      <c r="BV140" s="33"/>
-      <c r="BW140" s="33"/>
-      <c r="BX140" s="33"/>
-      <c r="BY140" s="33"/>
+      <c r="BN140" s="32"/>
+      <c r="BO140" s="32"/>
+      <c r="BP140" s="32"/>
+      <c r="BQ140" s="32"/>
+      <c r="BR140" s="32"/>
+      <c r="BS140" s="32"/>
+      <c r="BT140" s="32"/>
+      <c r="BU140" s="32"/>
+      <c r="BV140" s="32"/>
+      <c r="BW140" s="32"/>
+      <c r="BX140" s="32"/>
+      <c r="BY140" s="32"/>
     </row>
     <row r="141" spans="4:77" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="D141" s="37" t="str" cm="1">
+      <c r="D141" s="36" t="str" cm="1">
         <f t="array" ref="D141">Common_SourceData.Common_SourceData_FracWETIrrigation_Variation()</f>
         <v>VARIATION FROM SOURCE DATA: Table created based on VEERG text 'Areas are subject to leaching (i.e., in the leaching zone) when... the land is irrigated (except drip irrigation).'</v>
       </c>
-      <c r="BN141" s="33"/>
+      <c r="BN141" s="32"/>
     </row>
     <row r="142" spans="4:77" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="D142" s="31" t="s">
-        <v>64</v>
-      </c>
-      <c r="E142" s="31" t="s">
-        <v>63</v>
-      </c>
-      <c r="BN142" s="33"/>
+      <c r="D142" s="30" t="s">
+        <v>59</v>
+      </c>
+      <c r="E142" s="30" t="s">
+        <v>58</v>
+      </c>
+      <c r="BN142" s="32"/>
     </row>
     <row r="143" spans="4:77" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="D143" s="31" t="str" cm="1">
+      <c r="D143" s="30" t="str" cm="1">
         <f t="array" ref="D143">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_FracWETIrrigation_Data(), Table_SourceData_FracWETIrrigation[[#Headers],[Irrigation type i]], 0)</f>
         <v>Not irrigated</v>
       </c>
-      <c r="E143" s="31" cm="1">
+      <c r="E143" s="30" cm="1">
         <f t="array" ref="E143">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_FracWETIrrigation_Data(), Table_SourceData_FracWETIrrigation[[#Headers],[Irrigation type i]], 0)</f>
         <v>0</v>
       </c>
-      <c r="BN143" s="33"/>
+      <c r="BN143" s="32"/>
     </row>
     <row r="144" spans="4:77" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D144" s="1" t="str" cm="1">
         <f t="array" ref="D144">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_FracWETIrrigation_Data(), Table_SourceData_FracWETIrrigation[[#Headers],[Irrigation type i]], 0)</f>
         <v>Drip irrigation</v>
       </c>
-      <c r="E144" s="31" cm="1">
+      <c r="E144" s="30" cm="1">
         <f t="array" ref="E144">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_FracWETIrrigation_Data(), Table_SourceData_FracWETIrrigation[[#Headers],[Irrigation type i]], 0)</f>
         <v>0</v>
       </c>
-      <c r="BN144" s="33"/>
+      <c r="BN144" s="32"/>
     </row>
     <row r="145" spans="4:66" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D145" s="1" t="str" cm="1">
         <f t="array" ref="D145">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_FracWETIrrigation_Data(), Table_SourceData_FracWETIrrigation[[#Headers],[Irrigation type i]], 0)</f>
         <v>Sprinkler irrigation</v>
       </c>
-      <c r="E145" s="31" cm="1">
+      <c r="E145" s="30" cm="1">
         <f t="array" ref="E145">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_FracWETIrrigation_Data(), Table_SourceData_FracWETIrrigation[[#Headers],[Irrigation type i]], 0)</f>
         <v>1</v>
       </c>
-      <c r="BN145" s="33"/>
+      <c r="BN145" s="32"/>
     </row>
     <row r="146" spans="4:66" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D146" s="1" t="str" cm="1">
         <f t="array" ref="D146">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_FracWETIrrigation_Data(), Table_SourceData_FracWETIrrigation[[#Headers],[Irrigation type i]], 0)</f>
         <v>Surface irrigation</v>
       </c>
-      <c r="E146" s="31" cm="1">
+      <c r="E146" s="30" cm="1">
         <f t="array" ref="E146">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_FracWETIrrigation_Data(), Table_SourceData_FracWETIrrigation[[#Headers],[Irrigation type i]], 0)</f>
         <v>1</v>
       </c>
-      <c r="BN146" s="33"/>
+      <c r="BN146" s="32"/>
     </row>
     <row r="147" spans="4:66" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D147" s="1" t="str" cm="1">
         <f t="array" ref="D147">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_FracWETIrrigation_Data(), Table_SourceData_FracWETIrrigation[[#Headers],[Irrigation type i]], 0)</f>
         <v>Other irrigation</v>
       </c>
-      <c r="E147" s="31" cm="1">
+      <c r="E147" s="30" cm="1">
         <f t="array" ref="E147">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_FracWETIrrigation_Data(), Table_SourceData_FracWETIrrigation[[#Headers],[Irrigation type i]], 0)</f>
         <v>1</v>
       </c>
-      <c r="BN147" s="33"/>
+      <c r="BN147" s="32"/>
     </row>
     <row r="148" spans="4:66" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="BN148" s="33"/>
+      <c r="BN148" s="32"/>
     </row>
     <row r="149" spans="4:66" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="BN149" s="33"/>
+      <c r="BN149" s="32"/>
     </row>
     <row r="150" spans="4:66" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D150" s="2" t="str" cm="1">
         <f t="array" ref="D150">Common_SourceData.Common_SourceData_DataScores_Scope3_Title()</f>
         <v>Australian data scores for scope 3</v>
       </c>
-      <c r="BN150" s="33"/>
+      <c r="BN150" s="32"/>
     </row>
     <row r="151" spans="4:66" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D151" s="28" t="str" cm="1">
         <f t="array" ref="D151">Common_SourceData.Common_SourceData_DataScores_Scope3_Source()</f>
         <v>VEERG 2026: XXXXXXXX</v>
       </c>
-      <c r="BN151" s="33"/>
+      <c r="BN151" s="32"/>
     </row>
     <row r="152" spans="4:66" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="BN152" s="33"/>
+      <c r="BN152" s="32"/>
     </row>
     <row r="153" spans="4:66" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="D153" s="31" t="s">
-        <v>65</v>
-      </c>
-      <c r="E153" s="31" t="s">
-        <v>66</v>
-      </c>
-      <c r="BC153" s="36"/>
-      <c r="BD153" s="36"/>
-      <c r="BE153" s="36"/>
-      <c r="BF153" s="36"/>
-      <c r="BG153" s="36"/>
-      <c r="BH153" s="36"/>
-      <c r="BI153" s="36"/>
-      <c r="BJ153" s="36"/>
-      <c r="BK153" s="36"/>
-      <c r="BL153" s="36"/>
-      <c r="BM153" s="36"/>
+      <c r="D153" s="30" t="s">
+        <v>60</v>
+      </c>
+      <c r="E153" s="30" t="s">
+        <v>61</v>
+      </c>
+      <c r="BC153" s="35"/>
+      <c r="BD153" s="35"/>
+      <c r="BE153" s="35"/>
+      <c r="BF153" s="35"/>
+      <c r="BG153" s="35"/>
+      <c r="BH153" s="35"/>
+      <c r="BI153" s="35"/>
+      <c r="BJ153" s="35"/>
+      <c r="BK153" s="35"/>
+      <c r="BL153" s="35"/>
+      <c r="BM153" s="35"/>
     </row>
     <row r="154" spans="4:66" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="D154" s="31" t="str" cm="1">
+      <c r="D154" s="30" t="str" cm="1">
         <f t="array" ref="D154">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_DataScores_Scope3_Data(), Table_SourceData_DataScores_Scope3[[#Headers],[Data source]], 0)</f>
         <v>International scope 3 database</v>
       </c>
-      <c r="E154" s="31" cm="1">
+      <c r="E154" s="30" cm="1">
         <f t="array" ref="E154">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_DataScores_Scope3_Data(), Table_SourceData_DataScores_Scope3[[#Headers],[Data source]], 0)</f>
         <v>1</v>
       </c>
-      <c r="BC154" s="36"/>
-      <c r="BD154" s="36"/>
-      <c r="BE154" s="36"/>
-      <c r="BF154" s="36"/>
-      <c r="BG154" s="36"/>
-      <c r="BH154" s="36"/>
-      <c r="BI154" s="36"/>
-      <c r="BJ154" s="36"/>
-      <c r="BK154" s="36"/>
-      <c r="BL154" s="36"/>
-      <c r="BM154" s="36"/>
+      <c r="BC154" s="35"/>
+      <c r="BD154" s="35"/>
+      <c r="BE154" s="35"/>
+      <c r="BF154" s="35"/>
+      <c r="BG154" s="35"/>
+      <c r="BH154" s="35"/>
+      <c r="BI154" s="35"/>
+      <c r="BJ154" s="35"/>
+      <c r="BK154" s="35"/>
+      <c r="BL154" s="35"/>
+      <c r="BM154" s="35"/>
     </row>
     <row r="155" spans="4:66" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="D155" s="31" t="str" cm="1">
+      <c r="D155" s="30" t="str" cm="1">
         <f t="array" ref="D155">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_DataScores_Scope3_Data(), Table_SourceData_DataScores_Scope3[[#Headers],[Data source]], 0)</f>
         <v>Australian scope 3 database</v>
       </c>
-      <c r="E155" s="31" cm="1">
+      <c r="E155" s="30" cm="1">
         <f t="array" ref="E155">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_DataScores_Scope3_Data(), Table_SourceData_DataScores_Scope3[[#Headers],[Data source]], 0)</f>
         <v>2</v>
       </c>
-      <c r="BC155" s="36"/>
-      <c r="BD155" s="36"/>
-      <c r="BE155" s="36"/>
-      <c r="BF155" s="36"/>
-      <c r="BG155" s="36"/>
-      <c r="BH155" s="36"/>
-      <c r="BI155" s="36"/>
-      <c r="BJ155" s="36"/>
-      <c r="BK155" s="36"/>
-      <c r="BL155" s="36"/>
-      <c r="BM155" s="36"/>
+      <c r="BC155" s="35"/>
+      <c r="BD155" s="35"/>
+      <c r="BE155" s="35"/>
+      <c r="BF155" s="35"/>
+      <c r="BG155" s="35"/>
+      <c r="BH155" s="35"/>
+      <c r="BI155" s="35"/>
+      <c r="BJ155" s="35"/>
+      <c r="BK155" s="35"/>
+      <c r="BL155" s="35"/>
+      <c r="BM155" s="35"/>
     </row>
     <row r="156" spans="4:66" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="D156" s="31" t="str" cm="1">
+      <c r="D156" s="30" t="str" cm="1">
         <f t="array" ref="D156">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_DataScores_Scope3_Data(), Table_SourceData_DataScores_Scope3[[#Headers],[Data source]], 0)</f>
         <v>State or regional scope 3 database</v>
       </c>
-      <c r="E156" s="31" cm="1">
+      <c r="E156" s="30" cm="1">
         <f t="array" ref="E156">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_DataScores_Scope3_Data(), Table_SourceData_DataScores_Scope3[[#Headers],[Data source]], 0)</f>
         <v>3</v>
       </c>
     </row>
     <row r="157" spans="4:66" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="D157" s="31" t="str" cm="1">
+      <c r="D157" s="30" t="str" cm="1">
         <f t="array" ref="D157">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_DataScores_Scope3_Data(), Table_SourceData_DataScores_Scope3[[#Headers],[Data source]], 0)</f>
         <v>Emissions intensity calculated from approved method</v>
       </c>
-      <c r="E157" s="31" cm="1">
+      <c r="E157" s="30" cm="1">
         <f t="array" ref="E157">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_DataScores_Scope3_Data(), Table_SourceData_DataScores_Scope3[[#Headers],[Data source]], 0)</f>
         <v>4</v>
       </c>
     </row>
     <row r="158" spans="4:66" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="D158" s="31" t="str" cm="1">
+      <c r="D158" s="30" t="str" cm="1">
         <f t="array" ref="D158">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_DataScores_Scope3_Data(), Table_SourceData_DataScores_Scope3[[#Headers],[Data source]], 0)</f>
         <v>Verified credential matching ISO14067</v>
       </c>
-      <c r="E158" s="31" cm="1">
+      <c r="E158" s="30" cm="1">
         <f t="array" ref="E158">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_DataScores_Scope3_Data(), Table_SourceData_DataScores_Scope3[[#Headers],[Data source]], 0)</f>
         <v>5</v>
       </c>
@@ -9359,41 +9358,41 @@
       </c>
     </row>
     <row r="165" spans="4:68" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="BN165" s="33"/>
-      <c r="BO165" s="33"/>
-      <c r="BP165" s="33"/>
+      <c r="BN165" s="32"/>
+      <c r="BO165" s="32"/>
+      <c r="BP165" s="32"/>
     </row>
     <row r="166" spans="4:68" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="BN166" s="33"/>
-      <c r="BO166" s="33"/>
-      <c r="BP166" s="33"/>
+      <c r="BN166" s="32"/>
+      <c r="BO166" s="32"/>
+      <c r="BP166" s="32"/>
     </row>
     <row r="167" spans="4:68" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D167" s="2" t="str" cm="1">
         <f t="array" ref="D167">Common_SourceData.Common_SourceData_EFleach_Title()</f>
         <v>Emission factor for nitrogen leaching and runoff</v>
       </c>
-      <c r="BN167" s="33"/>
-      <c r="BO167" s="33"/>
-      <c r="BP167" s="33"/>
+      <c r="BN167" s="32"/>
+      <c r="BO167" s="32"/>
+      <c r="BP167" s="32"/>
     </row>
     <row r="168" spans="4:68" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D168" s="28" t="str" cm="1">
         <f t="array" ref="D168">Common_SourceData.Common_SourceData_EFleach_Source()</f>
         <v>VEERG 2026:5.5.2.3 Constant Parameters</v>
       </c>
-      <c r="BN168" s="33"/>
-      <c r="BO168" s="33"/>
-      <c r="BP168" s="33"/>
+      <c r="BN168" s="32"/>
+      <c r="BO168" s="32"/>
+      <c r="BP168" s="32"/>
     </row>
     <row r="169" spans="4:68" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D169" s="28" t="str" cm="1">
         <f t="array" ref="D169">Common_SourceData.Common_SourceData_EFleach_NIRReference()</f>
         <v>National Inventory Report Volume 1: Equation 3.D.B_10</v>
       </c>
-      <c r="BN169" s="33"/>
-      <c r="BO169" s="33"/>
-      <c r="BP169" s="33"/>
+      <c r="BN169" s="32"/>
+      <c r="BO169" s="32"/>
+      <c r="BP169" s="32"/>
     </row>
     <row r="170" spans="4:68" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D170" s="1" t="str" cm="1">
@@ -9403,37 +9402,37 @@
       <c r="E170" s="1">
         <v>1.0999999999999999E-2</v>
       </c>
-      <c r="BN170" s="33"/>
-      <c r="BO170" s="33"/>
-      <c r="BP170" s="33"/>
+      <c r="BN170" s="32"/>
+      <c r="BO170" s="32"/>
+      <c r="BP170" s="32"/>
     </row>
     <row r="171" spans="4:68" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="BN171" s="33"/>
-      <c r="BO171" s="33"/>
-      <c r="BP171" s="33"/>
+      <c r="BN171" s="32"/>
+      <c r="BO171" s="32"/>
+      <c r="BP171" s="32"/>
     </row>
     <row r="172" spans="4:68" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="BN172" s="33"/>
-      <c r="BO172" s="33"/>
-      <c r="BP172" s="33"/>
+      <c r="BN172" s="32"/>
+      <c r="BO172" s="32"/>
+      <c r="BP172" s="32"/>
     </row>
     <row r="173" spans="4:68" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D173" s="2" t="str" cm="1">
         <f t="array" ref="D173">Common_SourceData.Common_SourceData_DensityOfMethane_Title()</f>
         <v>p = density of methane</v>
       </c>
-      <c r="BN173" s="33"/>
-      <c r="BO173" s="33"/>
-      <c r="BP173" s="33"/>
+      <c r="BN173" s="32"/>
+      <c r="BO173" s="32"/>
+      <c r="BP173" s="32"/>
     </row>
     <row r="174" spans="4:68" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D174" s="28" t="str" cm="1">
         <f t="array" ref="D174">Common_SourceData.Common_SourceData_DensityOfMethane_Source()</f>
         <v>National Inventory Report 2023 Volume 1: Equations 3.B.1a_2, 3.B.1c_2, 3.B.3_1, 3.B.4g_2</v>
       </c>
-      <c r="BN174" s="33"/>
-      <c r="BO174" s="33"/>
-      <c r="BP174" s="33"/>
+      <c r="BN174" s="32"/>
+      <c r="BO174" s="32"/>
+      <c r="BP174" s="32"/>
     </row>
     <row r="175" spans="4:68" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D175" s="1" cm="1">
@@ -9444,37 +9443,37 @@
         <f t="array" ref="E175">Common_SourceData.Common_SourceData_DensityOfMethane_Unit()</f>
         <v>kg/m3</v>
       </c>
-      <c r="BN175" s="33"/>
-      <c r="BO175" s="33"/>
-      <c r="BP175" s="33"/>
+      <c r="BN175" s="32"/>
+      <c r="BO175" s="32"/>
+      <c r="BP175" s="32"/>
     </row>
     <row r="176" spans="4:68" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="BN176" s="33"/>
-      <c r="BO176" s="33"/>
-      <c r="BP176" s="33"/>
+      <c r="BN176" s="32"/>
+      <c r="BO176" s="32"/>
+      <c r="BP176" s="32"/>
     </row>
     <row r="177" spans="4:68" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="BN177" s="33"/>
-      <c r="BO177" s="33"/>
-      <c r="BP177" s="33"/>
+      <c r="BN177" s="32"/>
+      <c r="BO177" s="32"/>
+      <c r="BP177" s="32"/>
     </row>
     <row r="178" spans="4:68" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D178" s="2" t="str" cm="1">
         <f t="array" ref="D178">Common_SourceData.Common_SourceData_EFN2O_Title()</f>
         <v>Nitrous oxide emission factors for inorganic fertiliser application</v>
       </c>
-      <c r="BN178" s="33"/>
-      <c r="BO178" s="33"/>
-      <c r="BP178" s="33"/>
+      <c r="BN178" s="32"/>
+      <c r="BO178" s="32"/>
+      <c r="BP178" s="32"/>
     </row>
     <row r="179" spans="4:68" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D179" s="28" t="str" cm="1">
         <f t="array" ref="D179">Common_SourceData.Common_SourceData_EFN2O_Source()</f>
         <v>VEERG 2026: Table A.2.2.1</v>
       </c>
-      <c r="BN179" s="33"/>
-      <c r="BO179" s="33"/>
-      <c r="BP179" s="33"/>
+      <c r="BN179" s="32"/>
+      <c r="BO179" s="32"/>
+      <c r="BP179" s="32"/>
     </row>
     <row r="180" spans="4:68" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D180" s="16" t="str" cm="1">
@@ -9483,330 +9482,330 @@
       </c>
     </row>
     <row r="181" spans="4:68" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="D181" s="37" t="str" cm="1">
+      <c r="D181" s="36" t="str" cm="1">
         <f t="array" ref="D181:D185">Common_SourceData.Common_SourceData_EFN2O_Variation()</f>
         <v>VARIATION OF SOURCE DATA:</v>
       </c>
     </row>
     <row r="182" spans="4:68" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="D182" s="37" t="str">
+      <c r="D182" s="36" t="str">
         <v>Removed duplicate 'Aquaculture' row.</v>
       </c>
     </row>
     <row r="183" spans="4:68" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="D183" s="37" t="str">
+      <c r="D183" s="36" t="str">
         <v>Removed asterisks to aid lookup.</v>
       </c>
     </row>
     <row r="184" spans="4:68" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="D184" s="37" t="str">
+      <c r="D184" s="36" t="str">
         <v>Added 'production system only', 'rainfall zone' and 'irrigation method' columns to aid lookup.</v>
       </c>
     </row>
     <row r="185" spans="4:68" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="D185" s="37" t="str">
+      <c r="D185" s="36" t="str">
         <v>Duplicated 'non-irrigated pasture' row with same EF for low and high rainfall zones to aid lookup.</v>
       </c>
     </row>
     <row r="186" spans="4:68" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="D186" s="31" t="s">
-        <v>67</v>
-      </c>
-      <c r="E186" s="31" t="s">
-        <v>68</v>
-      </c>
-      <c r="F186" s="31" t="s">
-        <v>69</v>
-      </c>
-      <c r="G186" s="31" t="s">
-        <v>70</v>
-      </c>
-      <c r="H186" s="31" t="s">
-        <v>71</v>
+      <c r="D186" s="30" t="s">
+        <v>62</v>
+      </c>
+      <c r="E186" s="30" t="s">
+        <v>63</v>
+      </c>
+      <c r="F186" s="30" t="s">
+        <v>64</v>
+      </c>
+      <c r="G186" s="30" t="s">
+        <v>65</v>
+      </c>
+      <c r="H186" s="30" t="s">
+        <v>66</v>
       </c>
     </row>
     <row r="187" spans="4:68" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="D187" s="31" t="str" cm="1">
+      <c r="D187" s="30" t="str" cm="1">
         <f t="array" ref="D187">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_EFN2O_Data(), Table_SourceData_Common_EFN2O[[#Headers],[Production system j]], 0)</f>
         <v>Irrigated pasture</v>
       </c>
-      <c r="E187" s="31" cm="1">
+      <c r="E187" s="30" cm="1">
         <f t="array" ref="E187">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_EFN2O_Data(), Table_SourceData_Common_EFN2O[[#Headers],[Production system j]], 0)</f>
         <v>5.8999999999999999E-3</v>
       </c>
-      <c r="F187" s="31" t="str" cm="1">
+      <c r="F187" s="30" t="str" cm="1">
         <f t="array" ref="F187">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_EFN2O_Data(), Table_SourceData_Common_EFN2O[[#Headers],[Production system j]], 0)</f>
         <v>Pasture</v>
       </c>
-      <c r="G187" s="31" t="str" cm="1">
+      <c r="G187" s="30" t="str" cm="1">
         <f t="array" ref="G187">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_EFN2O_Data(), Table_SourceData_Common_EFN2O[[#Headers],[Production system j]], 0)</f>
         <v>Any</v>
       </c>
-      <c r="H187" s="31" t="str" cm="1">
+      <c r="H187" s="30" t="str" cm="1">
         <f t="array" ref="H187">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_EFN2O_Data(), Table_SourceData_Common_EFN2O[[#Headers],[Production system j]], 0)</f>
         <v>Any</v>
       </c>
     </row>
     <row r="188" spans="4:68" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="D188" s="31" t="str" cm="1">
+      <c r="D188" s="30" t="str" cm="1">
         <f t="array" ref="D188">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_EFN2O_Data(), Table_SourceData_Common_EFN2O[[#Headers],[Production system j]], 0)</f>
         <v>Irrigated crop</v>
       </c>
-      <c r="E188" s="31" cm="1">
+      <c r="E188" s="30" cm="1">
         <f t="array" ref="E188">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_EFN2O_Data(), Table_SourceData_Common_EFN2O[[#Headers],[Production system j]], 0)</f>
         <v>7.0000000000000001E-3</v>
       </c>
-      <c r="F188" s="31" t="str" cm="1">
+      <c r="F188" s="30" t="str" cm="1">
         <f t="array" ref="F188">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_EFN2O_Data(), Table_SourceData_Common_EFN2O[[#Headers],[Production system j]], 0)</f>
         <v>Crop</v>
       </c>
-      <c r="G188" s="31" t="str" cm="1">
+      <c r="G188" s="30" t="str" cm="1">
         <f t="array" ref="G188">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_EFN2O_Data(), Table_SourceData_Common_EFN2O[[#Headers],[Production system j]], 0)</f>
         <v>Any</v>
       </c>
-      <c r="H188" s="31" t="str" cm="1">
+      <c r="H188" s="30" t="str" cm="1">
         <f t="array" ref="H188">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_EFN2O_Data(), Table_SourceData_Common_EFN2O[[#Headers],[Production system j]], 0)</f>
         <v>Any</v>
       </c>
     </row>
     <row r="189" spans="4:68" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="D189" s="31" t="str" cm="1">
+      <c r="D189" s="30" t="str" cm="1">
         <f t="array" ref="D189">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_EFN2O_Data(), Table_SourceData_Common_EFN2O[[#Headers],[Production system j]], 0)</f>
         <v>Non-irrigated pasture</v>
       </c>
-      <c r="E189" s="31" cm="1">
+      <c r="E189" s="30" cm="1">
         <f t="array" ref="E189">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_EFN2O_Data(), Table_SourceData_Common_EFN2O[[#Headers],[Production system j]], 0)</f>
         <v>1.8E-3</v>
       </c>
-      <c r="F189" s="31" t="str" cm="1">
+      <c r="F189" s="30" t="str" cm="1">
         <f t="array" ref="F189">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_EFN2O_Data(), Table_SourceData_Common_EFN2O[[#Headers],[Production system j]], 0)</f>
         <v>Pasture</v>
       </c>
-      <c r="G189" s="31" t="str" cm="1">
+      <c r="G189" s="30" t="str" cm="1">
         <f t="array" ref="G189">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_EFN2O_Data(), Table_SourceData_Common_EFN2O[[#Headers],[Production system j]], 0)</f>
         <v>Not irrigated</v>
       </c>
-      <c r="H189" s="31" t="str" cm="1">
+      <c r="H189" s="30" t="str" cm="1">
         <f t="array" ref="H189">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_EFN2O_Data(), Table_SourceData_Common_EFN2O[[#Headers],[Production system j]], 0)</f>
         <v>Low rainfall</v>
       </c>
     </row>
     <row r="190" spans="4:68" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="D190" s="31" t="str" cm="1">
+      <c r="D190" s="30" t="str" cm="1">
         <f t="array" ref="D190">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_EFN2O_Data(), Table_SourceData_Common_EFN2O[[#Headers],[Production system j]], 0)</f>
         <v>Non-irrigated pasture</v>
       </c>
-      <c r="E190" s="31" cm="1">
+      <c r="E190" s="30" cm="1">
         <f t="array" ref="E190">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_EFN2O_Data(), Table_SourceData_Common_EFN2O[[#Headers],[Production system j]], 0)</f>
         <v>1.8E-3</v>
       </c>
-      <c r="F190" s="31" t="str" cm="1">
+      <c r="F190" s="30" t="str" cm="1">
         <f t="array" ref="F190">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_EFN2O_Data(), Table_SourceData_Common_EFN2O[[#Headers],[Production system j]], 0)</f>
         <v>Pasture</v>
       </c>
-      <c r="G190" s="31" t="str" cm="1">
+      <c r="G190" s="30" t="str" cm="1">
         <f t="array" ref="G190">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_EFN2O_Data(), Table_SourceData_Common_EFN2O[[#Headers],[Production system j]], 0)</f>
         <v>Not irrigated</v>
       </c>
-      <c r="H190" s="31" t="str" cm="1">
+      <c r="H190" s="30" t="str" cm="1">
         <f t="array" ref="H190">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_EFN2O_Data(), Table_SourceData_Common_EFN2O[[#Headers],[Production system j]], 0)</f>
         <v>High rainfall</v>
       </c>
     </row>
     <row r="191" spans="4:68" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="D191" s="31" t="str" cm="1">
+      <c r="D191" s="30" t="str" cm="1">
         <f t="array" ref="D191">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_EFN2O_Data(), Table_SourceData_Common_EFN2O[[#Headers],[Production system j]], 0)</f>
         <v>Non-irrigated crop (low rainfall)</v>
       </c>
-      <c r="E191" s="31" cm="1">
+      <c r="E191" s="30" cm="1">
         <f t="array" ref="E191">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_EFN2O_Data(), Table_SourceData_Common_EFN2O[[#Headers],[Production system j]], 0)</f>
         <v>2.8999999999999998E-3</v>
       </c>
-      <c r="F191" s="31" t="str" cm="1">
+      <c r="F191" s="30" t="str" cm="1">
         <f t="array" ref="F191">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_EFN2O_Data(), Table_SourceData_Common_EFN2O[[#Headers],[Production system j]], 0)</f>
         <v>Crop</v>
       </c>
-      <c r="G191" s="31" t="str" cm="1">
+      <c r="G191" s="30" t="str" cm="1">
         <f t="array" ref="G191">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_EFN2O_Data(), Table_SourceData_Common_EFN2O[[#Headers],[Production system j]], 0)</f>
         <v>Not irrigated</v>
       </c>
-      <c r="H191" s="31" t="str" cm="1">
+      <c r="H191" s="30" t="str" cm="1">
         <f t="array" ref="H191">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_EFN2O_Data(), Table_SourceData_Common_EFN2O[[#Headers],[Production system j]], 0)</f>
         <v>Low rainfall</v>
       </c>
     </row>
     <row r="192" spans="4:68" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="D192" s="31" t="str" cm="1">
+      <c r="D192" s="30" t="str" cm="1">
         <f t="array" ref="D192">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_EFN2O_Data(), Table_SourceData_Common_EFN2O[[#Headers],[Production system j]], 0)</f>
         <v>Non-irrigated crop (high rainfall)</v>
       </c>
-      <c r="E192" s="31" cm="1">
+      <c r="E192" s="30" cm="1">
         <f t="array" ref="E192">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_EFN2O_Data(), Table_SourceData_Common_EFN2O[[#Headers],[Production system j]], 0)</f>
         <v>8.0000000000000002E-3</v>
       </c>
-      <c r="F192" s="31" t="str" cm="1">
+      <c r="F192" s="30" t="str" cm="1">
         <f t="array" ref="F192">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_EFN2O_Data(), Table_SourceData_Common_EFN2O[[#Headers],[Production system j]], 0)</f>
         <v>Crop</v>
       </c>
-      <c r="G192" s="31" t="str" cm="1">
+      <c r="G192" s="30" t="str" cm="1">
         <f t="array" ref="G192">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_EFN2O_Data(), Table_SourceData_Common_EFN2O[[#Headers],[Production system j]], 0)</f>
         <v>Not irrigated</v>
       </c>
-      <c r="H192" s="31" t="str" cm="1">
+      <c r="H192" s="30" t="str" cm="1">
         <f t="array" ref="H192">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_EFN2O_Data(), Table_SourceData_Common_EFN2O[[#Headers],[Production system j]], 0)</f>
         <v>High rainfall</v>
       </c>
     </row>
     <row r="193" spans="4:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="D193" s="31" t="str" cm="1">
+      <c r="D193" s="30" t="str" cm="1">
         <f t="array" ref="D193">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_EFN2O_Data(), Table_SourceData_Common_EFN2O[[#Headers],[Production system j]], 0)</f>
         <v>Sugar</v>
       </c>
-      <c r="E193" s="31" cm="1">
+      <c r="E193" s="30" cm="1">
         <f t="array" ref="E193">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_EFN2O_Data(), Table_SourceData_Common_EFN2O[[#Headers],[Production system j]], 0)</f>
         <v>1.9900000000000001E-2</v>
       </c>
-      <c r="F193" s="31" t="str" cm="1">
+      <c r="F193" s="30" t="str" cm="1">
         <f t="array" ref="F193">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_EFN2O_Data(), Table_SourceData_Common_EFN2O[[#Headers],[Production system j]], 0)</f>
         <v>Sugar</v>
       </c>
-      <c r="G193" s="31" t="str" cm="1">
+      <c r="G193" s="30" t="str" cm="1">
         <f t="array" ref="G193">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_EFN2O_Data(), Table_SourceData_Common_EFN2O[[#Headers],[Production system j]], 0)</f>
         <v>Any</v>
       </c>
-      <c r="H193" s="31" t="str" cm="1">
+      <c r="H193" s="30" t="str" cm="1">
         <f t="array" ref="H193">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_EFN2O_Data(), Table_SourceData_Common_EFN2O[[#Headers],[Production system j]], 0)</f>
         <v>Any</v>
       </c>
     </row>
     <row r="194" spans="4:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="D194" s="31" t="str" cm="1">
+      <c r="D194" s="30" t="str" cm="1">
         <f t="array" ref="D194">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_EFN2O_Data(), Table_SourceData_Common_EFN2O[[#Headers],[Production system j]], 0)</f>
         <v>Cotton</v>
       </c>
-      <c r="E194" s="31" cm="1">
+      <c r="E194" s="30" cm="1">
         <f t="array" ref="E194">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_EFN2O_Data(), Table_SourceData_Common_EFN2O[[#Headers],[Production system j]], 0)</f>
         <v>5.3E-3</v>
       </c>
-      <c r="F194" s="31" t="str" cm="1">
+      <c r="F194" s="30" t="str" cm="1">
         <f t="array" ref="F194">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_EFN2O_Data(), Table_SourceData_Common_EFN2O[[#Headers],[Production system j]], 0)</f>
         <v>Cotton</v>
       </c>
-      <c r="G194" s="31" t="str" cm="1">
+      <c r="G194" s="30" t="str" cm="1">
         <f t="array" ref="G194">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_EFN2O_Data(), Table_SourceData_Common_EFN2O[[#Headers],[Production system j]], 0)</f>
         <v>Any</v>
       </c>
-      <c r="H194" s="31" t="str" cm="1">
+      <c r="H194" s="30" t="str" cm="1">
         <f t="array" ref="H194">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_EFN2O_Data(), Table_SourceData_Common_EFN2O[[#Headers],[Production system j]], 0)</f>
         <v>Any</v>
       </c>
     </row>
     <row r="195" spans="4:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="D195" s="31" t="str" cm="1">
+      <c r="D195" s="30" t="str" cm="1">
         <f t="array" ref="D195">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_EFN2O_Data(), Table_SourceData_Common_EFN2O[[#Headers],[Production system j]], 0)</f>
         <v>Horticultural crops</v>
       </c>
-      <c r="E195" s="31" cm="1">
+      <c r="E195" s="30" cm="1">
         <f t="array" ref="E195">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_EFN2O_Data(), Table_SourceData_Common_EFN2O[[#Headers],[Production system j]], 0)</f>
         <v>6.4000000000000003E-3</v>
       </c>
-      <c r="F195" s="31" t="str" cm="1">
+      <c r="F195" s="30" t="str" cm="1">
         <f t="array" ref="F195">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_EFN2O_Data(), Table_SourceData_Common_EFN2O[[#Headers],[Production system j]], 0)</f>
         <v>Horticultural crops</v>
       </c>
-      <c r="G195" s="31" t="str" cm="1">
+      <c r="G195" s="30" t="str" cm="1">
         <f t="array" ref="G195">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_EFN2O_Data(), Table_SourceData_Common_EFN2O[[#Headers],[Production system j]], 0)</f>
         <v>Any</v>
       </c>
-      <c r="H195" s="31" t="str" cm="1">
+      <c r="H195" s="30" t="str" cm="1">
         <f t="array" ref="H195">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_EFN2O_Data(), Table_SourceData_Common_EFN2O[[#Headers],[Production system j]], 0)</f>
         <v>Any</v>
       </c>
     </row>
     <row r="196" spans="4:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="D196" s="31" t="str" cm="1">
+      <c r="D196" s="30" t="str" cm="1">
         <f t="array" ref="D196">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_EFN2O_Data(), Table_SourceData_Common_EFN2O[[#Headers],[Production system j]], 0)</f>
         <v>Rice (continuous flooding)</v>
       </c>
-      <c r="E196" s="31" cm="1">
+      <c r="E196" s="30" cm="1">
         <f t="array" ref="E196">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_EFN2O_Data(), Table_SourceData_Common_EFN2O[[#Headers],[Production system j]], 0)</f>
         <v>3.0000000000000001E-3</v>
       </c>
-      <c r="F196" s="31" t="str" cm="1">
+      <c r="F196" s="30" t="str" cm="1">
         <f t="array" ref="F196">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_EFN2O_Data(), Table_SourceData_Common_EFN2O[[#Headers],[Production system j]], 0)</f>
         <v>Rice</v>
       </c>
-      <c r="G196" s="31" t="str" cm="1">
+      <c r="G196" s="30" t="str" cm="1">
         <f t="array" ref="G196">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_EFN2O_Data(), Table_SourceData_Common_EFN2O[[#Headers],[Production system j]], 0)</f>
         <v>Continuous flooding</v>
       </c>
-      <c r="H196" s="31" t="str" cm="1">
+      <c r="H196" s="30" t="str" cm="1">
         <f t="array" ref="H196">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_EFN2O_Data(), Table_SourceData_Common_EFN2O[[#Headers],[Production system j]], 0)</f>
         <v>Any</v>
       </c>
     </row>
     <row r="197" spans="4:8" x14ac:dyDescent="0.25">
-      <c r="D197" s="31" t="str" cm="1">
+      <c r="D197" s="30" t="str" cm="1">
         <f t="array" ref="D197">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_EFN2O_Data(), Table_SourceData_Common_EFN2O[[#Headers],[Production system j]], 0)</f>
         <v>Rice (single and multiple drainage, or alternate wetting and drying)</v>
       </c>
-      <c r="E197" s="31" cm="1">
+      <c r="E197" s="30" cm="1">
         <f t="array" ref="E197">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_EFN2O_Data(), Table_SourceData_Common_EFN2O[[#Headers],[Production system j]], 0)</f>
         <v>5.0000000000000001E-3</v>
       </c>
-      <c r="F197" s="31" t="str" cm="1">
+      <c r="F197" s="30" t="str" cm="1">
         <f t="array" ref="F197">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_EFN2O_Data(), Table_SourceData_Common_EFN2O[[#Headers],[Production system j]], 0)</f>
         <v>Rice</v>
       </c>
-      <c r="G197" s="31" t="str" cm="1">
+      <c r="G197" s="30" t="str" cm="1">
         <f t="array" ref="G197">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_EFN2O_Data(), Table_SourceData_Common_EFN2O[[#Headers],[Production system j]], 0)</f>
         <v>Single and multiple drainage, or alternate wetting and drying</v>
       </c>
-      <c r="H197" s="31" t="str" cm="1">
+      <c r="H197" s="30" t="str" cm="1">
         <f t="array" ref="H197">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_EFN2O_Data(), Table_SourceData_Common_EFN2O[[#Headers],[Production system j]], 0)</f>
         <v>Any</v>
       </c>
     </row>
     <row r="198" spans="4:8" x14ac:dyDescent="0.25">
-      <c r="D198" s="31" t="str" cm="1">
+      <c r="D198" s="30" t="str" cm="1">
         <f t="array" ref="D198">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_EFN2O_Data(), Table_SourceData_Common_EFN2O[[#Headers],[Production system j]], 0)</f>
         <v>Aquaculture</v>
       </c>
-      <c r="E198" s="31" cm="1">
+      <c r="E198" s="30" cm="1">
         <f t="array" ref="E198">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_EFN2O_Data(), Table_SourceData_Common_EFN2O[[#Headers],[Production system j]], 0)</f>
         <v>2.5999999999999999E-3</v>
       </c>
-      <c r="F198" s="31" t="str" cm="1">
+      <c r="F198" s="30" t="str" cm="1">
         <f t="array" ref="F198">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_EFN2O_Data(), Table_SourceData_Common_EFN2O[[#Headers],[Production system j]], 0)</f>
         <v>Aquaculture</v>
       </c>
-      <c r="G198" s="31" t="str" cm="1">
+      <c r="G198" s="30" t="str" cm="1">
         <f t="array" ref="G198">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_EFN2O_Data(), Table_SourceData_Common_EFN2O[[#Headers],[Production system j]], 0)</f>
         <v>Any</v>
       </c>
-      <c r="H198" s="31" t="str" cm="1">
+      <c r="H198" s="30" t="str" cm="1">
         <f t="array" ref="H198">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_EFN2O_Data(), Table_SourceData_Common_EFN2O[[#Headers],[Production system j]], 0)</f>
         <v>Any</v>
       </c>
     </row>
     <row r="199" spans="4:8" x14ac:dyDescent="0.25">
-      <c r="D199" s="31" t="str" cm="1">
+      <c r="D199" s="30" t="str" cm="1">
         <f t="array" ref="D199">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_EFN2O_Data(), Table_SourceData_Common_EFN2O[[#Headers],[Production system j]], 0)</f>
         <v>Forestry</v>
       </c>
-      <c r="E199" s="31" cm="1">
+      <c r="E199" s="30" cm="1">
         <f t="array" ref="E199">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_EFN2O_Data(), Table_SourceData_Common_EFN2O[[#Headers],[Production system j]], 0)</f>
         <v>1.8E-3</v>
       </c>
-      <c r="F199" s="31" t="str" cm="1">
+      <c r="F199" s="30" t="str" cm="1">
         <f t="array" ref="F199">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_EFN2O_Data(), Table_SourceData_Common_EFN2O[[#Headers],[Production system j]], 0)</f>
         <v>Forestry</v>
       </c>
-      <c r="G199" s="31" t="str" cm="1">
+      <c r="G199" s="30" t="str" cm="1">
         <f t="array" ref="G199">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_EFN2O_Data(), Table_SourceData_Common_EFN2O[[#Headers],[Production system j]], 0)</f>
         <v>Any</v>
       </c>
-      <c r="H199" s="31" t="str" cm="1">
+      <c r="H199" s="30" t="str" cm="1">
         <f t="array" ref="H199">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_EFN2O_Data(), Table_SourceData_Common_EFN2O[[#Headers],[Production system j]], 0)</f>
         <v>Any</v>
       </c>
@@ -9824,7 +9823,7 @@
       </c>
     </row>
     <row r="204" spans="4:8" x14ac:dyDescent="0.25">
-      <c r="D204" s="37" t="str" cm="1">
+      <c r="D204" s="36" t="str" cm="1">
         <f t="array" ref="D204">Common_SourceData.Common_SourceData_EFPastureRangeAndPaddock_Variation()</f>
         <v>VARIATION FROM SOURCE DATA: Changed 'Dry climate zones' to singular 'Dry climate zone' to aid lookup.</v>
       </c>
@@ -9836,19 +9835,19 @@
       </c>
     </row>
     <row r="206" spans="4:8" x14ac:dyDescent="0.25">
-      <c r="D206" s="31" t="s">
-        <v>38</v>
-      </c>
-      <c r="E206" s="31" t="s">
-        <v>72</v>
+      <c r="D206" s="30" t="s">
+        <v>33</v>
+      </c>
+      <c r="E206" s="30" t="s">
+        <v>67</v>
       </c>
     </row>
     <row r="207" spans="4:8" x14ac:dyDescent="0.25">
-      <c r="D207" s="31" t="str" cm="1">
+      <c r="D207" s="30" t="str" cm="1">
         <f t="array" ref="D207">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_EFPastureRangeAndPaddock_Data(), Table_SourceData_EFPastureRangeAndPaddock[[#Headers],[Climate zone]], 0)</f>
         <v>Wet climate zone</v>
       </c>
-      <c r="E207" s="31" cm="1">
+      <c r="E207" s="30" cm="1">
         <f t="array" ref="E207">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_EFPastureRangeAndPaddock_Data(), Table_SourceData_EFPastureRangeAndPaddock[[#Headers],[Climate zone]], 0)</f>
         <v>6.0000000000000001E-3</v>
       </c>
@@ -9858,7 +9857,7 @@
         <f t="array" ref="D208">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_EFPastureRangeAndPaddock_Data(), Table_SourceData_EFPastureRangeAndPaddock[[#Headers],[Climate zone]], 0)</f>
         <v>Dry climate zone</v>
       </c>
-      <c r="E208" s="31" cm="1">
+      <c r="E208" s="30" cm="1">
         <f t="array" ref="E208">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_EFPastureRangeAndPaddock_Data(), Table_SourceData_EFPastureRangeAndPaddock[[#Headers],[Climate zone]], 0)</f>
         <v>2E-3</v>
       </c>
@@ -9870,19 +9869,19 @@
       </c>
     </row>
     <row r="212" spans="4:5" x14ac:dyDescent="0.25">
-      <c r="D212" s="31" t="s">
-        <v>73</v>
-      </c>
-      <c r="E212" s="31" t="s">
-        <v>74</v>
+      <c r="D212" s="30" t="s">
+        <v>68</v>
+      </c>
+      <c r="E212" s="30" t="s">
+        <v>69</v>
       </c>
     </row>
     <row r="213" spans="4:5" x14ac:dyDescent="0.25">
-      <c r="D213" s="31" t="str" cm="1">
+      <c r="D213" s="30" t="str" cm="1">
         <f t="array" ref="D213">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MonthsToSeasons_Data(), Table_SourceData_Common_MonthToSeason[[#Headers],[Month]], 0)</f>
         <v>January</v>
       </c>
-      <c r="E213" s="31" t="str" cm="1">
+      <c r="E213" s="30" t="str" cm="1">
         <f t="array" ref="E213">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MonthsToSeasons_Data(), Table_SourceData_Common_MonthToSeason[[#Headers],[Month]], 0)</f>
         <v>Summer</v>
       </c>
@@ -9892,7 +9891,7 @@
         <f t="array" ref="D214">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MonthsToSeasons_Data(), Table_SourceData_Common_MonthToSeason[[#Headers],[Month]], 0)</f>
         <v>February</v>
       </c>
-      <c r="E214" s="31" t="str" cm="1">
+      <c r="E214" s="30" t="str" cm="1">
         <f t="array" ref="E214">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MonthsToSeasons_Data(), Table_SourceData_Common_MonthToSeason[[#Headers],[Month]], 0)</f>
         <v>Summer</v>
       </c>
@@ -9902,7 +9901,7 @@
         <f t="array" ref="D215">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MonthsToSeasons_Data(), Table_SourceData_Common_MonthToSeason[[#Headers],[Month]], 0)</f>
         <v>March</v>
       </c>
-      <c r="E215" s="31" t="str" cm="1">
+      <c r="E215" s="30" t="str" cm="1">
         <f t="array" ref="E215">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MonthsToSeasons_Data(), Table_SourceData_Common_MonthToSeason[[#Headers],[Month]], 0)</f>
         <v>Autumn</v>
       </c>
@@ -9912,7 +9911,7 @@
         <f t="array" ref="D216">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MonthsToSeasons_Data(), Table_SourceData_Common_MonthToSeason[[#Headers],[Month]], 0)</f>
         <v>April</v>
       </c>
-      <c r="E216" s="31" t="str" cm="1">
+      <c r="E216" s="30" t="str" cm="1">
         <f t="array" ref="E216">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MonthsToSeasons_Data(), Table_SourceData_Common_MonthToSeason[[#Headers],[Month]], 0)</f>
         <v>Autumn</v>
       </c>
@@ -9922,7 +9921,7 @@
         <f t="array" ref="D217">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MonthsToSeasons_Data(), Table_SourceData_Common_MonthToSeason[[#Headers],[Month]], 0)</f>
         <v>May</v>
       </c>
-      <c r="E217" s="31" t="str" cm="1">
+      <c r="E217" s="30" t="str" cm="1">
         <f t="array" ref="E217">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MonthsToSeasons_Data(), Table_SourceData_Common_MonthToSeason[[#Headers],[Month]], 0)</f>
         <v>Autumn</v>
       </c>
@@ -9932,7 +9931,7 @@
         <f t="array" ref="D218">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MonthsToSeasons_Data(), Table_SourceData_Common_MonthToSeason[[#Headers],[Month]], 0)</f>
         <v>June</v>
       </c>
-      <c r="E218" s="31" t="str" cm="1">
+      <c r="E218" s="30" t="str" cm="1">
         <f t="array" ref="E218">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MonthsToSeasons_Data(), Table_SourceData_Common_MonthToSeason[[#Headers],[Month]], 0)</f>
         <v>Winter</v>
       </c>
@@ -9942,7 +9941,7 @@
         <f t="array" ref="D219">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MonthsToSeasons_Data(), Table_SourceData_Common_MonthToSeason[[#Headers],[Month]], 0)</f>
         <v>July</v>
       </c>
-      <c r="E219" s="31" t="str" cm="1">
+      <c r="E219" s="30" t="str" cm="1">
         <f t="array" ref="E219">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MonthsToSeasons_Data(), Table_SourceData_Common_MonthToSeason[[#Headers],[Month]], 0)</f>
         <v>Winter</v>
       </c>
@@ -9952,7 +9951,7 @@
         <f t="array" ref="D220">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MonthsToSeasons_Data(), Table_SourceData_Common_MonthToSeason[[#Headers],[Month]], 0)</f>
         <v>August</v>
       </c>
-      <c r="E220" s="31" t="str" cm="1">
+      <c r="E220" s="30" t="str" cm="1">
         <f t="array" ref="E220">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MonthsToSeasons_Data(), Table_SourceData_Common_MonthToSeason[[#Headers],[Month]], 0)</f>
         <v>Winter</v>
       </c>
@@ -9962,7 +9961,7 @@
         <f t="array" ref="D221">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MonthsToSeasons_Data(), Table_SourceData_Common_MonthToSeason[[#Headers],[Month]], 0)</f>
         <v>September</v>
       </c>
-      <c r="E221" s="31" t="str" cm="1">
+      <c r="E221" s="30" t="str" cm="1">
         <f t="array" ref="E221">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MonthsToSeasons_Data(), Table_SourceData_Common_MonthToSeason[[#Headers],[Month]], 0)</f>
         <v>Spring</v>
       </c>
@@ -9972,7 +9971,7 @@
         <f t="array" ref="D222">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MonthsToSeasons_Data(), Table_SourceData_Common_MonthToSeason[[#Headers],[Month]], 0)</f>
         <v>October</v>
       </c>
-      <c r="E222" s="31" t="str" cm="1">
+      <c r="E222" s="30" t="str" cm="1">
         <f t="array" ref="E222">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MonthsToSeasons_Data(), Table_SourceData_Common_MonthToSeason[[#Headers],[Month]], 0)</f>
         <v>Spring</v>
       </c>
@@ -9982,7 +9981,7 @@
         <f t="array" ref="D223">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MonthsToSeasons_Data(), Table_SourceData_Common_MonthToSeason[[#Headers],[Month]], 0)</f>
         <v>November</v>
       </c>
-      <c r="E223" s="31" t="str" cm="1">
+      <c r="E223" s="30" t="str" cm="1">
         <f t="array" ref="E223">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MonthsToSeasons_Data(), Table_SourceData_Common_MonthToSeason[[#Headers],[Month]], 0)</f>
         <v>Spring</v>
       </c>
@@ -9992,7 +9991,7 @@
         <f t="array" ref="D224">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MonthsToSeasons_Data(), Table_SourceData_Common_MonthToSeason[[#Headers],[Month]], 0)</f>
         <v>December</v>
       </c>
-      <c r="E224" s="31" t="str" cm="1">
+      <c r="E224" s="30" t="str" cm="1">
         <f t="array" ref="E224">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MonthsToSeasons_Data(), Table_SourceData_Common_MonthToSeason[[#Headers],[Month]], 0)</f>
         <v>Summer</v>
       </c>
@@ -10010,123 +10009,123 @@
       </c>
     </row>
     <row r="229" spans="4:19" x14ac:dyDescent="0.25">
-      <c r="D229" s="37" t="str" cm="1">
+      <c r="D229" s="36" t="str" cm="1">
         <f t="array" ref="D229">Common_SourceData.Common_SourceData_MCFTemperatureZone_Variation()</f>
         <v>VARIATION FROM SOURCE: Added row of NIR MMA definitions to aid lookup. Duplicated 'Poultry with and without litter' column with separate NIR definitions to aid lookup. Added 'MAT raw' column to allow lookup of numbers.</v>
       </c>
     </row>
     <row r="231" spans="4:19" x14ac:dyDescent="0.25">
-      <c r="D231" s="31" t="s">
+      <c r="D231" s="30" t="s">
+        <v>70</v>
+      </c>
+      <c r="E231" s="30" t="s">
+        <v>71</v>
+      </c>
+      <c r="F231" s="37" t="s">
+        <v>72</v>
+      </c>
+      <c r="G231" s="30" t="s">
+        <v>73</v>
+      </c>
+      <c r="H231" s="30" t="s">
+        <v>74</v>
+      </c>
+      <c r="I231" s="30" t="s">
         <v>75</v>
       </c>
-      <c r="E231" s="31" t="s">
+      <c r="J231" s="30" t="s">
         <v>76</v>
       </c>
-      <c r="F231" s="38" t="s">
+      <c r="K231" s="30" t="s">
         <v>77</v>
       </c>
-      <c r="G231" s="31" t="s">
+      <c r="L231" s="30" t="s">
         <v>78</v>
       </c>
-      <c r="H231" s="31" t="s">
+      <c r="M231" s="30" t="s">
         <v>79</v>
       </c>
-      <c r="I231" s="31" t="s">
+      <c r="N231" s="30" t="s">
         <v>80</v>
       </c>
-      <c r="J231" s="31" t="s">
+      <c r="O231" s="30" t="s">
         <v>81</v>
       </c>
-      <c r="K231" s="31" t="s">
+      <c r="P231" s="30" t="s">
         <v>82</v>
       </c>
-      <c r="L231" s="31" t="s">
+      <c r="Q231" s="30" t="s">
         <v>83</v>
       </c>
-      <c r="M231" s="31" t="s">
+      <c r="R231" s="30" t="s">
         <v>84</v>
       </c>
-      <c r="N231" s="31" t="s">
+      <c r="S231" s="30" t="s">
         <v>85</v>
       </c>
-      <c r="O231" s="31" t="s">
-        <v>86</v>
-      </c>
-      <c r="P231" s="31" t="s">
-        <v>87</v>
-      </c>
-      <c r="Q231" s="31" t="s">
-        <v>88</v>
-      </c>
-      <c r="R231" s="31" t="s">
-        <v>89</v>
-      </c>
-      <c r="S231" s="31" t="s">
-        <v>90</v>
-      </c>
     </row>
     <row r="232" spans="4:19" x14ac:dyDescent="0.25">
-      <c r="D232" s="31" t="str" cm="1">
+      <c r="D232" s="30" t="str" cm="1">
         <f t="array" ref="D232">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
         <v>Cool</v>
       </c>
-      <c r="E232" s="31" t="str" cm="1">
+      <c r="E232" s="30" t="str" cm="1">
         <f t="array" ref="E232">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
         <v>≤10</v>
       </c>
-      <c r="F232" s="31" cm="1">
+      <c r="F232" s="30" cm="1">
         <f t="array" ref="F232">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
         <v>0.66</v>
       </c>
-      <c r="G232" s="31" cm="1">
+      <c r="G232" s="30" cm="1">
         <f t="array" ref="G232">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
         <v>0.1</v>
       </c>
-      <c r="H232" s="31" cm="1">
+      <c r="H232" s="30" cm="1">
         <f t="array" ref="H232">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
         <v>0.1</v>
       </c>
-      <c r="I232" s="31" cm="1">
+      <c r="I232" s="30" cm="1">
         <f t="array" ref="I232">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
         <v>1E-3</v>
       </c>
-      <c r="J232" s="31" cm="1">
+      <c r="J232" s="30" cm="1">
         <f t="array" ref="J232">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
         <v>5.0000000000000001E-3</v>
       </c>
-      <c r="K232" s="31" cm="1">
+      <c r="K232" s="30" cm="1">
         <f t="array" ref="K232">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
         <v>0.02</v>
       </c>
-      <c r="L232" s="31" cm="1">
+      <c r="L232" s="30" cm="1">
         <f t="array" ref="L232">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
         <v>0.03</v>
       </c>
-      <c r="M232" s="31" cm="1">
+      <c r="M232" s="30" cm="1">
         <f t="array" ref="M232">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
         <v>0.04</v>
       </c>
-      <c r="N232" s="31" cm="1">
+      <c r="N232" s="30" cm="1">
         <f t="array" ref="N232">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
         <v>1.4999999999999999E-2</v>
       </c>
-      <c r="O232" s="31" cm="1">
+      <c r="O232" s="30" cm="1">
         <f t="array" ref="O232">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
         <v>1.4999999999999999E-2</v>
       </c>
-      <c r="P232" s="31" cm="1">
+      <c r="P232" s="30" cm="1">
         <f t="array" ref="P232">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
         <v>0</v>
       </c>
-      <c r="Q232" s="31" cm="1">
+      <c r="Q232" s="30" cm="1">
         <f t="array" ref="Q232">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
         <v>0</v>
       </c>
-      <c r="R232" s="31" cm="1">
+      <c r="R232" s="30" cm="1">
         <f t="array" ref="R232">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
         <v>4.7000000000000002E-3</v>
       </c>
-      <c r="S232" s="31" cm="1">
+      <c r="S232" s="30" cm="1">
         <f t="array" ref="S232">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
         <v>10</v>
       </c>
@@ -10136,63 +10135,63 @@
         <f t="array" ref="D233">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
         <v>Cool</v>
       </c>
-      <c r="E233" s="31" cm="1">
+      <c r="E233" s="30" cm="1">
         <f t="array" ref="E233">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
         <v>11</v>
       </c>
-      <c r="F233" s="31" cm="1">
+      <c r="F233" s="30" cm="1">
         <f t="array" ref="F233">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
         <v>0.68</v>
       </c>
-      <c r="G233" s="31" cm="1">
+      <c r="G233" s="30" cm="1">
         <f t="array" ref="G233">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
         <v>0.1</v>
       </c>
-      <c r="H233" s="31" cm="1">
+      <c r="H233" s="30" cm="1">
         <f t="array" ref="H233">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
         <v>0.11</v>
       </c>
-      <c r="I233" s="31" cm="1">
+      <c r="I233" s="30" cm="1">
         <f t="array" ref="I233">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
         <v>1E-3</v>
       </c>
-      <c r="J233" s="31" cm="1">
+      <c r="J233" s="30" cm="1">
         <f t="array" ref="J233">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
         <v>5.0000000000000001E-3</v>
       </c>
-      <c r="K233" s="31" cm="1">
+      <c r="K233" s="30" cm="1">
         <f t="array" ref="K233">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
         <v>0.02</v>
       </c>
-      <c r="L233" s="31" cm="1">
+      <c r="L233" s="30" cm="1">
         <f t="array" ref="L233">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
         <v>0.03</v>
       </c>
-      <c r="M233" s="31" cm="1">
+      <c r="M233" s="30" cm="1">
         <f t="array" ref="M233">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
         <v>0.04</v>
       </c>
-      <c r="N233" s="31" cm="1">
+      <c r="N233" s="30" cm="1">
         <f t="array" ref="N233">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
         <v>1.4999999999999999E-2</v>
       </c>
-      <c r="O233" s="31" cm="1">
+      <c r="O233" s="30" cm="1">
         <f t="array" ref="O233">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
         <v>1.4999999999999999E-2</v>
       </c>
-      <c r="P233" s="31" cm="1">
+      <c r="P233" s="30" cm="1">
         <f t="array" ref="P233">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
         <v>0</v>
       </c>
-      <c r="Q233" s="31" cm="1">
+      <c r="Q233" s="30" cm="1">
         <f t="array" ref="Q233">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
         <v>0</v>
       </c>
-      <c r="R233" s="31" cm="1">
+      <c r="R233" s="30" cm="1">
         <f t="array" ref="R233">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
         <v>4.7000000000000002E-3</v>
       </c>
-      <c r="S233" s="31" cm="1">
+      <c r="S233" s="30" cm="1">
         <f t="array" ref="S233">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
         <v>11</v>
       </c>
@@ -10202,63 +10201,63 @@
         <f t="array" ref="D234">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
         <v>Cool</v>
       </c>
-      <c r="E234" s="31" cm="1">
+      <c r="E234" s="30" cm="1">
         <f t="array" ref="E234">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
         <v>12</v>
       </c>
-      <c r="F234" s="31" cm="1">
+      <c r="F234" s="30" cm="1">
         <f t="array" ref="F234">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
         <v>0.7</v>
       </c>
-      <c r="G234" s="31" cm="1">
+      <c r="G234" s="30" cm="1">
         <f t="array" ref="G234">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
         <v>0.1</v>
       </c>
-      <c r="H234" s="31" cm="1">
+      <c r="H234" s="30" cm="1">
         <f t="array" ref="H234">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
         <v>0.13</v>
       </c>
-      <c r="I234" s="31" cm="1">
+      <c r="I234" s="30" cm="1">
         <f t="array" ref="I234">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
         <v>1E-3</v>
       </c>
-      <c r="J234" s="31" cm="1">
+      <c r="J234" s="30" cm="1">
         <f t="array" ref="J234">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
         <v>5.0000000000000001E-3</v>
       </c>
-      <c r="K234" s="31" cm="1">
+      <c r="K234" s="30" cm="1">
         <f t="array" ref="K234">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
         <v>0.02</v>
       </c>
-      <c r="L234" s="31" cm="1">
+      <c r="L234" s="30" cm="1">
         <f t="array" ref="L234">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
         <v>0.03</v>
       </c>
-      <c r="M234" s="31" cm="1">
+      <c r="M234" s="30" cm="1">
         <f t="array" ref="M234">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
         <v>0.04</v>
       </c>
-      <c r="N234" s="31" cm="1">
+      <c r="N234" s="30" cm="1">
         <f t="array" ref="N234">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
         <v>1.4999999999999999E-2</v>
       </c>
-      <c r="O234" s="31" cm="1">
+      <c r="O234" s="30" cm="1">
         <f t="array" ref="O234">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
         <v>1.4999999999999999E-2</v>
       </c>
-      <c r="P234" s="31" cm="1">
+      <c r="P234" s="30" cm="1">
         <f t="array" ref="P234">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
         <v>0</v>
       </c>
-      <c r="Q234" s="31" cm="1">
+      <c r="Q234" s="30" cm="1">
         <f t="array" ref="Q234">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
         <v>0</v>
       </c>
-      <c r="R234" s="31" cm="1">
+      <c r="R234" s="30" cm="1">
         <f t="array" ref="R234">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
         <v>4.7000000000000002E-3</v>
       </c>
-      <c r="S234" s="31" cm="1">
+      <c r="S234" s="30" cm="1">
         <f t="array" ref="S234">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
         <v>12</v>
       </c>
@@ -10268,63 +10267,63 @@
         <f t="array" ref="D235">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
         <v>Cool</v>
       </c>
-      <c r="E235" s="31" cm="1">
+      <c r="E235" s="30" cm="1">
         <f t="array" ref="E235">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
         <v>13</v>
       </c>
-      <c r="F235" s="31" cm="1">
+      <c r="F235" s="30" cm="1">
         <f t="array" ref="F235">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
         <v>0.71</v>
       </c>
-      <c r="G235" s="31" cm="1">
+      <c r="G235" s="30" cm="1">
         <f t="array" ref="G235">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
         <v>0.1</v>
       </c>
-      <c r="H235" s="31" cm="1">
+      <c r="H235" s="30" cm="1">
         <f t="array" ref="H235">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
         <v>0.14000000000000001</v>
       </c>
-      <c r="I235" s="31" cm="1">
+      <c r="I235" s="30" cm="1">
         <f t="array" ref="I235">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
         <v>1E-3</v>
       </c>
-      <c r="J235" s="31" cm="1">
+      <c r="J235" s="30" cm="1">
         <f t="array" ref="J235">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
         <v>5.0000000000000001E-3</v>
       </c>
-      <c r="K235" s="31" cm="1">
+      <c r="K235" s="30" cm="1">
         <f t="array" ref="K235">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
         <v>0.02</v>
       </c>
-      <c r="L235" s="31" cm="1">
+      <c r="L235" s="30" cm="1">
         <f t="array" ref="L235">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
         <v>0.03</v>
       </c>
-      <c r="M235" s="31" cm="1">
+      <c r="M235" s="30" cm="1">
         <f t="array" ref="M235">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
         <v>0.04</v>
       </c>
-      <c r="N235" s="31" cm="1">
+      <c r="N235" s="30" cm="1">
         <f t="array" ref="N235">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
         <v>1.4999999999999999E-2</v>
       </c>
-      <c r="O235" s="31" cm="1">
+      <c r="O235" s="30" cm="1">
         <f t="array" ref="O235">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
         <v>1.4999999999999999E-2</v>
       </c>
-      <c r="P235" s="31" cm="1">
+      <c r="P235" s="30" cm="1">
         <f t="array" ref="P235">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
         <v>0</v>
       </c>
-      <c r="Q235" s="31" cm="1">
+      <c r="Q235" s="30" cm="1">
         <f t="array" ref="Q235">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
         <v>0</v>
       </c>
-      <c r="R235" s="31" cm="1">
+      <c r="R235" s="30" cm="1">
         <f t="array" ref="R235">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
         <v>4.7000000000000002E-3</v>
       </c>
-      <c r="S235" s="31" cm="1">
+      <c r="S235" s="30" cm="1">
         <f t="array" ref="S235">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
         <v>13</v>
       </c>
@@ -10334,63 +10333,63 @@
         <f t="array" ref="D236">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
         <v>Cool</v>
       </c>
-      <c r="E236" s="31" cm="1">
+      <c r="E236" s="30" cm="1">
         <f t="array" ref="E236">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
         <v>14</v>
       </c>
-      <c r="F236" s="31" cm="1">
+      <c r="F236" s="30" cm="1">
         <f t="array" ref="F236">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
         <v>0.73</v>
       </c>
-      <c r="G236" s="31" cm="1">
+      <c r="G236" s="30" cm="1">
         <f t="array" ref="G236">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
         <v>0.1</v>
       </c>
-      <c r="H236" s="31" cm="1">
+      <c r="H236" s="30" cm="1">
         <f t="array" ref="H236">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
         <v>0.15</v>
       </c>
-      <c r="I236" s="31" cm="1">
+      <c r="I236" s="30" cm="1">
         <f t="array" ref="I236">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
         <v>1E-3</v>
       </c>
-      <c r="J236" s="31" cm="1">
+      <c r="J236" s="30" cm="1">
         <f t="array" ref="J236">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
         <v>5.0000000000000001E-3</v>
       </c>
-      <c r="K236" s="31" cm="1">
+      <c r="K236" s="30" cm="1">
         <f t="array" ref="K236">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
         <v>0.02</v>
       </c>
-      <c r="L236" s="31" cm="1">
+      <c r="L236" s="30" cm="1">
         <f t="array" ref="L236">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
         <v>0.03</v>
       </c>
-      <c r="M236" s="31" cm="1">
+      <c r="M236" s="30" cm="1">
         <f t="array" ref="M236">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
         <v>0.04</v>
       </c>
-      <c r="N236" s="31" cm="1">
+      <c r="N236" s="30" cm="1">
         <f t="array" ref="N236">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
         <v>1.4999999999999999E-2</v>
       </c>
-      <c r="O236" s="31" cm="1">
+      <c r="O236" s="30" cm="1">
         <f t="array" ref="O236">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
         <v>1.4999999999999999E-2</v>
       </c>
-      <c r="P236" s="31" cm="1">
+      <c r="P236" s="30" cm="1">
         <f t="array" ref="P236">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
         <v>0</v>
       </c>
-      <c r="Q236" s="31" cm="1">
+      <c r="Q236" s="30" cm="1">
         <f t="array" ref="Q236">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
         <v>0</v>
       </c>
-      <c r="R236" s="31" cm="1">
+      <c r="R236" s="30" cm="1">
         <f t="array" ref="R236">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
         <v>4.7000000000000002E-3</v>
       </c>
-      <c r="S236" s="31" cm="1">
+      <c r="S236" s="30" cm="1">
         <f t="array" ref="S236">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
         <v>14</v>
       </c>
@@ -10400,63 +10399,63 @@
         <f t="array" ref="D237">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
         <v>Temperate</v>
       </c>
-      <c r="E237" s="31" cm="1">
+      <c r="E237" s="30" cm="1">
         <f t="array" ref="E237">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
         <v>15</v>
       </c>
-      <c r="F237" s="31" cm="1">
+      <c r="F237" s="30" cm="1">
         <f t="array" ref="F237">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
         <v>0.74</v>
       </c>
-      <c r="G237" s="31" cm="1">
+      <c r="G237" s="30" cm="1">
         <f t="array" ref="G237">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
         <v>0.1</v>
       </c>
-      <c r="H237" s="31" cm="1">
+      <c r="H237" s="30" cm="1">
         <f t="array" ref="H237">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
         <v>0.17</v>
       </c>
-      <c r="I237" s="31" cm="1">
+      <c r="I237" s="30" cm="1">
         <f t="array" ref="I237">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
         <v>5.0000000000000001E-3</v>
       </c>
-      <c r="J237" s="31" cm="1">
+      <c r="J237" s="30" cm="1">
         <f t="array" ref="J237">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
         <v>0.01</v>
       </c>
-      <c r="K237" s="31" cm="1">
+      <c r="K237" s="30" cm="1">
         <f t="array" ref="K237">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
         <v>0.02</v>
       </c>
-      <c r="L237" s="31" cm="1">
+      <c r="L237" s="30" cm="1">
         <f t="array" ref="L237">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
         <v>0.03</v>
       </c>
-      <c r="M237" s="31" cm="1">
+      <c r="M237" s="30" cm="1">
         <f t="array" ref="M237">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
         <v>0.04</v>
       </c>
-      <c r="N237" s="31" cm="1">
+      <c r="N237" s="30" cm="1">
         <f t="array" ref="N237">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
         <v>1.4999999999999999E-2</v>
       </c>
-      <c r="O237" s="31" cm="1">
+      <c r="O237" s="30" cm="1">
         <f t="array" ref="O237">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
         <v>1.4999999999999999E-2</v>
       </c>
-      <c r="P237" s="31" cm="1">
+      <c r="P237" s="30" cm="1">
         <f t="array" ref="P237">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
         <v>0</v>
       </c>
-      <c r="Q237" s="31" cm="1">
+      <c r="Q237" s="30" cm="1">
         <f t="array" ref="Q237">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
         <v>0</v>
       </c>
-      <c r="R237" s="31" cm="1">
+      <c r="R237" s="30" cm="1">
         <f t="array" ref="R237">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
         <v>4.7000000000000002E-3</v>
       </c>
-      <c r="S237" s="31" cm="1">
+      <c r="S237" s="30" cm="1">
         <f t="array" ref="S237">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
         <v>15</v>
       </c>
@@ -10466,63 +10465,63 @@
         <f t="array" ref="D238">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
         <v>Temperate</v>
       </c>
-      <c r="E238" s="31" cm="1">
+      <c r="E238" s="30" cm="1">
         <f t="array" ref="E238">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
         <v>16</v>
       </c>
-      <c r="F238" s="31" cm="1">
+      <c r="F238" s="30" cm="1">
         <f t="array" ref="F238">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
         <v>0.75</v>
       </c>
-      <c r="G238" s="31" cm="1">
+      <c r="G238" s="30" cm="1">
         <f t="array" ref="G238">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
         <v>0.1</v>
       </c>
-      <c r="H238" s="31" cm="1">
+      <c r="H238" s="30" cm="1">
         <f t="array" ref="H238">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
         <v>0.18</v>
       </c>
-      <c r="I238" s="31" cm="1">
+      <c r="I238" s="30" cm="1">
         <f t="array" ref="I238">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
         <v>5.0000000000000001E-3</v>
       </c>
-      <c r="J238" s="31" cm="1">
+      <c r="J238" s="30" cm="1">
         <f t="array" ref="J238">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
         <v>0.01</v>
       </c>
-      <c r="K238" s="31" cm="1">
+      <c r="K238" s="30" cm="1">
         <f t="array" ref="K238">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
         <v>0.02</v>
       </c>
-      <c r="L238" s="31" cm="1">
+      <c r="L238" s="30" cm="1">
         <f t="array" ref="L238">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
         <v>0.03</v>
       </c>
-      <c r="M238" s="31" cm="1">
+      <c r="M238" s="30" cm="1">
         <f t="array" ref="M238">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
         <v>0.04</v>
       </c>
-      <c r="N238" s="31" cm="1">
+      <c r="N238" s="30" cm="1">
         <f t="array" ref="N238">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
         <v>1.4999999999999999E-2</v>
       </c>
-      <c r="O238" s="31" cm="1">
+      <c r="O238" s="30" cm="1">
         <f t="array" ref="O238">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
         <v>1.4999999999999999E-2</v>
       </c>
-      <c r="P238" s="31" cm="1">
+      <c r="P238" s="30" cm="1">
         <f t="array" ref="P238">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
         <v>0</v>
       </c>
-      <c r="Q238" s="31" cm="1">
+      <c r="Q238" s="30" cm="1">
         <f t="array" ref="Q238">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
         <v>0</v>
       </c>
-      <c r="R238" s="31" cm="1">
+      <c r="R238" s="30" cm="1">
         <f t="array" ref="R238">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
         <v>4.7000000000000002E-3</v>
       </c>
-      <c r="S238" s="31" cm="1">
+      <c r="S238" s="30" cm="1">
         <f t="array" ref="S238">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
         <v>16</v>
       </c>
@@ -10532,63 +10531,63 @@
         <f t="array" ref="D239">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
         <v>Temperate</v>
       </c>
-      <c r="E239" s="31" cm="1">
+      <c r="E239" s="30" cm="1">
         <f t="array" ref="E239">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
         <v>17</v>
       </c>
-      <c r="F239" s="31" cm="1">
+      <c r="F239" s="30" cm="1">
         <f t="array" ref="F239">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
         <v>0.76</v>
       </c>
-      <c r="G239" s="31" cm="1">
+      <c r="G239" s="30" cm="1">
         <f t="array" ref="G239">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
         <v>0.1</v>
       </c>
-      <c r="H239" s="31" cm="1">
+      <c r="H239" s="30" cm="1">
         <f t="array" ref="H239">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
         <v>0.2</v>
       </c>
-      <c r="I239" s="31" cm="1">
+      <c r="I239" s="30" cm="1">
         <f t="array" ref="I239">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
         <v>5.0000000000000001E-3</v>
       </c>
-      <c r="J239" s="31" cm="1">
+      <c r="J239" s="30" cm="1">
         <f t="array" ref="J239">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
         <v>0.01</v>
       </c>
-      <c r="K239" s="31" cm="1">
+      <c r="K239" s="30" cm="1">
         <f t="array" ref="K239">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
         <v>0.02</v>
       </c>
-      <c r="L239" s="31" cm="1">
+      <c r="L239" s="30" cm="1">
         <f t="array" ref="L239">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
         <v>0.03</v>
       </c>
-      <c r="M239" s="31" cm="1">
+      <c r="M239" s="30" cm="1">
         <f t="array" ref="M239">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
         <v>0.04</v>
       </c>
-      <c r="N239" s="31" cm="1">
+      <c r="N239" s="30" cm="1">
         <f t="array" ref="N239">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
         <v>1.4999999999999999E-2</v>
       </c>
-      <c r="O239" s="31" cm="1">
+      <c r="O239" s="30" cm="1">
         <f t="array" ref="O239">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
         <v>1.4999999999999999E-2</v>
       </c>
-      <c r="P239" s="31" cm="1">
+      <c r="P239" s="30" cm="1">
         <f t="array" ref="P239">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
         <v>0</v>
       </c>
-      <c r="Q239" s="31" cm="1">
+      <c r="Q239" s="30" cm="1">
         <f t="array" ref="Q239">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
         <v>0</v>
       </c>
-      <c r="R239" s="31" cm="1">
+      <c r="R239" s="30" cm="1">
         <f t="array" ref="R239">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
         <v>4.7000000000000002E-3</v>
       </c>
-      <c r="S239" s="31" cm="1">
+      <c r="S239" s="30" cm="1">
         <f t="array" ref="S239">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
         <v>17</v>
       </c>
@@ -10598,63 +10597,63 @@
         <f t="array" ref="D240">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
         <v>Temperate</v>
       </c>
-      <c r="E240" s="31" cm="1">
+      <c r="E240" s="30" cm="1">
         <f t="array" ref="E240">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
         <v>18</v>
       </c>
-      <c r="F240" s="31" cm="1">
+      <c r="F240" s="30" cm="1">
         <f t="array" ref="F240">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
         <v>0.77</v>
       </c>
-      <c r="G240" s="31" cm="1">
+      <c r="G240" s="30" cm="1">
         <f t="array" ref="G240">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
         <v>0.1</v>
       </c>
-      <c r="H240" s="31" cm="1">
+      <c r="H240" s="30" cm="1">
         <f t="array" ref="H240">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
         <v>0.22</v>
       </c>
-      <c r="I240" s="31" cm="1">
+      <c r="I240" s="30" cm="1">
         <f t="array" ref="I240">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
         <v>5.0000000000000001E-3</v>
       </c>
-      <c r="J240" s="31" cm="1">
+      <c r="J240" s="30" cm="1">
         <f t="array" ref="J240">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
         <v>0.01</v>
       </c>
-      <c r="K240" s="31" cm="1">
+      <c r="K240" s="30" cm="1">
         <f t="array" ref="K240">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
         <v>0.02</v>
       </c>
-      <c r="L240" s="31" cm="1">
+      <c r="L240" s="30" cm="1">
         <f t="array" ref="L240">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
         <v>0.03</v>
       </c>
-      <c r="M240" s="31" cm="1">
+      <c r="M240" s="30" cm="1">
         <f t="array" ref="M240">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
         <v>0.04</v>
       </c>
-      <c r="N240" s="31" cm="1">
+      <c r="N240" s="30" cm="1">
         <f t="array" ref="N240">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
         <v>1.4999999999999999E-2</v>
       </c>
-      <c r="O240" s="31" cm="1">
+      <c r="O240" s="30" cm="1">
         <f t="array" ref="O240">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
         <v>1.4999999999999999E-2</v>
       </c>
-      <c r="P240" s="31" cm="1">
+      <c r="P240" s="30" cm="1">
         <f t="array" ref="P240">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
         <v>0</v>
       </c>
-      <c r="Q240" s="31" cm="1">
+      <c r="Q240" s="30" cm="1">
         <f t="array" ref="Q240">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
         <v>0</v>
       </c>
-      <c r="R240" s="31" cm="1">
+      <c r="R240" s="30" cm="1">
         <f t="array" ref="R240">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
         <v>4.7000000000000002E-3</v>
       </c>
-      <c r="S240" s="31" cm="1">
+      <c r="S240" s="30" cm="1">
         <f t="array" ref="S240">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
         <v>18</v>
       </c>
@@ -10664,63 +10663,63 @@
         <f t="array" ref="D241">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
         <v>Temperate</v>
       </c>
-      <c r="E241" s="31" cm="1">
+      <c r="E241" s="30" cm="1">
         <f t="array" ref="E241">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
         <v>19</v>
       </c>
-      <c r="F241" s="31" cm="1">
+      <c r="F241" s="30" cm="1">
         <f t="array" ref="F241">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
         <v>0.77</v>
       </c>
-      <c r="G241" s="31" cm="1">
+      <c r="G241" s="30" cm="1">
         <f t="array" ref="G241">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
         <v>0.1</v>
       </c>
-      <c r="H241" s="31" cm="1">
+      <c r="H241" s="30" cm="1">
         <f t="array" ref="H241">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
         <v>0.24</v>
       </c>
-      <c r="I241" s="31" cm="1">
+      <c r="I241" s="30" cm="1">
         <f t="array" ref="I241">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
         <v>5.0000000000000001E-3</v>
       </c>
-      <c r="J241" s="31" cm="1">
+      <c r="J241" s="30" cm="1">
         <f t="array" ref="J241">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
         <v>0.01</v>
       </c>
-      <c r="K241" s="31" cm="1">
+      <c r="K241" s="30" cm="1">
         <f t="array" ref="K241">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
         <v>0.02</v>
       </c>
-      <c r="L241" s="31" cm="1">
+      <c r="L241" s="30" cm="1">
         <f t="array" ref="L241">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
         <v>0.03</v>
       </c>
-      <c r="M241" s="31" cm="1">
+      <c r="M241" s="30" cm="1">
         <f t="array" ref="M241">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
         <v>0.04</v>
       </c>
-      <c r="N241" s="31" cm="1">
+      <c r="N241" s="30" cm="1">
         <f t="array" ref="N241">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
         <v>1.4999999999999999E-2</v>
       </c>
-      <c r="O241" s="31" cm="1">
+      <c r="O241" s="30" cm="1">
         <f t="array" ref="O241">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
         <v>1.4999999999999999E-2</v>
       </c>
-      <c r="P241" s="31" cm="1">
+      <c r="P241" s="30" cm="1">
         <f t="array" ref="P241">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
         <v>0</v>
       </c>
-      <c r="Q241" s="31" cm="1">
+      <c r="Q241" s="30" cm="1">
         <f t="array" ref="Q241">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
         <v>0</v>
       </c>
-      <c r="R241" s="31" cm="1">
+      <c r="R241" s="30" cm="1">
         <f t="array" ref="R241">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
         <v>4.7000000000000002E-3</v>
       </c>
-      <c r="S241" s="31" cm="1">
+      <c r="S241" s="30" cm="1">
         <f t="array" ref="S241">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
         <v>19</v>
       </c>
@@ -10730,63 +10729,63 @@
         <f t="array" ref="D242">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
         <v>Temperate</v>
       </c>
-      <c r="E242" s="31" cm="1">
+      <c r="E242" s="30" cm="1">
         <f t="array" ref="E242">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
         <v>20</v>
       </c>
-      <c r="F242" s="31" cm="1">
+      <c r="F242" s="30" cm="1">
         <f t="array" ref="F242">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
         <v>0.78</v>
       </c>
-      <c r="G242" s="31" cm="1">
+      <c r="G242" s="30" cm="1">
         <f t="array" ref="G242">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
         <v>0.1</v>
       </c>
-      <c r="H242" s="31" cm="1">
+      <c r="H242" s="30" cm="1">
         <f t="array" ref="H242">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
         <v>0.26</v>
       </c>
-      <c r="I242" s="31" cm="1">
+      <c r="I242" s="30" cm="1">
         <f t="array" ref="I242">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
         <v>5.0000000000000001E-3</v>
       </c>
-      <c r="J242" s="31" cm="1">
+      <c r="J242" s="30" cm="1">
         <f t="array" ref="J242">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
         <v>0.01</v>
       </c>
-      <c r="K242" s="31" cm="1">
+      <c r="K242" s="30" cm="1">
         <f t="array" ref="K242">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
         <v>0.02</v>
       </c>
-      <c r="L242" s="31" cm="1">
+      <c r="L242" s="30" cm="1">
         <f t="array" ref="L242">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
         <v>0.03</v>
       </c>
-      <c r="M242" s="31" cm="1">
+      <c r="M242" s="30" cm="1">
         <f t="array" ref="M242">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
         <v>0.04</v>
       </c>
-      <c r="N242" s="31" cm="1">
+      <c r="N242" s="30" cm="1">
         <f t="array" ref="N242">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
         <v>1.4999999999999999E-2</v>
       </c>
-      <c r="O242" s="31" cm="1">
+      <c r="O242" s="30" cm="1">
         <f t="array" ref="O242">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
         <v>1.4999999999999999E-2</v>
       </c>
-      <c r="P242" s="31" cm="1">
+      <c r="P242" s="30" cm="1">
         <f t="array" ref="P242">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
         <v>0</v>
       </c>
-      <c r="Q242" s="31" cm="1">
+      <c r="Q242" s="30" cm="1">
         <f t="array" ref="Q242">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
         <v>0</v>
       </c>
-      <c r="R242" s="31" cm="1">
+      <c r="R242" s="30" cm="1">
         <f t="array" ref="R242">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
         <v>4.7000000000000002E-3</v>
       </c>
-      <c r="S242" s="31" cm="1">
+      <c r="S242" s="30" cm="1">
         <f t="array" ref="S242">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
         <v>20</v>
       </c>
@@ -10796,63 +10795,63 @@
         <f t="array" ref="D243">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
         <v>Temperate</v>
       </c>
-      <c r="E243" s="31" cm="1">
+      <c r="E243" s="30" cm="1">
         <f t="array" ref="E243">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
         <v>21</v>
       </c>
-      <c r="F243" s="31" cm="1">
+      <c r="F243" s="30" cm="1">
         <f t="array" ref="F243">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
         <v>0.78</v>
       </c>
-      <c r="G243" s="31" cm="1">
+      <c r="G243" s="30" cm="1">
         <f t="array" ref="G243">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
         <v>0.1</v>
       </c>
-      <c r="H243" s="31" cm="1">
+      <c r="H243" s="30" cm="1">
         <f t="array" ref="H243">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
         <v>0.28999999999999998</v>
       </c>
-      <c r="I243" s="31" cm="1">
+      <c r="I243" s="30" cm="1">
         <f t="array" ref="I243">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
         <v>5.0000000000000001E-3</v>
       </c>
-      <c r="J243" s="31" cm="1">
+      <c r="J243" s="30" cm="1">
         <f t="array" ref="J243">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
         <v>0.01</v>
       </c>
-      <c r="K243" s="31" cm="1">
+      <c r="K243" s="30" cm="1">
         <f t="array" ref="K243">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
         <v>0.02</v>
       </c>
-      <c r="L243" s="31" cm="1">
+      <c r="L243" s="30" cm="1">
         <f t="array" ref="L243">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
         <v>0.03</v>
       </c>
-      <c r="M243" s="31" cm="1">
+      <c r="M243" s="30" cm="1">
         <f t="array" ref="M243">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
         <v>0.04</v>
       </c>
-      <c r="N243" s="31" cm="1">
+      <c r="N243" s="30" cm="1">
         <f t="array" ref="N243">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
         <v>1.4999999999999999E-2</v>
       </c>
-      <c r="O243" s="31" cm="1">
+      <c r="O243" s="30" cm="1">
         <f t="array" ref="O243">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
         <v>1.4999999999999999E-2</v>
       </c>
-      <c r="P243" s="31" cm="1">
+      <c r="P243" s="30" cm="1">
         <f t="array" ref="P243">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
         <v>0</v>
       </c>
-      <c r="Q243" s="31" cm="1">
+      <c r="Q243" s="30" cm="1">
         <f t="array" ref="Q243">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
         <v>0</v>
       </c>
-      <c r="R243" s="31" cm="1">
+      <c r="R243" s="30" cm="1">
         <f t="array" ref="R243">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
         <v>4.7000000000000002E-3</v>
       </c>
-      <c r="S243" s="31" cm="1">
+      <c r="S243" s="30" cm="1">
         <f t="array" ref="S243">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
         <v>21</v>
       </c>
@@ -10862,63 +10861,63 @@
         <f t="array" ref="D244">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
         <v>Temperate</v>
       </c>
-      <c r="E244" s="31" cm="1">
+      <c r="E244" s="30" cm="1">
         <f t="array" ref="E244">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
         <v>22</v>
       </c>
-      <c r="F244" s="31" cm="1">
+      <c r="F244" s="30" cm="1">
         <f t="array" ref="F244">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
         <v>0.78</v>
       </c>
-      <c r="G244" s="31" cm="1">
+      <c r="G244" s="30" cm="1">
         <f t="array" ref="G244">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
         <v>0.1</v>
       </c>
-      <c r="H244" s="31" cm="1">
+      <c r="H244" s="30" cm="1">
         <f t="array" ref="H244">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
         <v>0.31</v>
       </c>
-      <c r="I244" s="31" cm="1">
+      <c r="I244" s="30" cm="1">
         <f t="array" ref="I244">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
         <v>5.0000000000000001E-3</v>
       </c>
-      <c r="J244" s="31" cm="1">
+      <c r="J244" s="30" cm="1">
         <f t="array" ref="J244">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
         <v>0.01</v>
       </c>
-      <c r="K244" s="31" cm="1">
+      <c r="K244" s="30" cm="1">
         <f t="array" ref="K244">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
         <v>0.02</v>
       </c>
-      <c r="L244" s="31" cm="1">
+      <c r="L244" s="30" cm="1">
         <f t="array" ref="L244">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
         <v>0.03</v>
       </c>
-      <c r="M244" s="31" cm="1">
+      <c r="M244" s="30" cm="1">
         <f t="array" ref="M244">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
         <v>0.04</v>
       </c>
-      <c r="N244" s="31" cm="1">
+      <c r="N244" s="30" cm="1">
         <f t="array" ref="N244">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
         <v>1.4999999999999999E-2</v>
       </c>
-      <c r="O244" s="31" cm="1">
+      <c r="O244" s="30" cm="1">
         <f t="array" ref="O244">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
         <v>1.4999999999999999E-2</v>
       </c>
-      <c r="P244" s="31" cm="1">
+      <c r="P244" s="30" cm="1">
         <f t="array" ref="P244">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
         <v>0</v>
       </c>
-      <c r="Q244" s="31" cm="1">
+      <c r="Q244" s="30" cm="1">
         <f t="array" ref="Q244">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
         <v>0</v>
       </c>
-      <c r="R244" s="31" cm="1">
+      <c r="R244" s="30" cm="1">
         <f t="array" ref="R244">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
         <v>4.7000000000000002E-3</v>
       </c>
-      <c r="S244" s="31" cm="1">
+      <c r="S244" s="30" cm="1">
         <f t="array" ref="S244">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
         <v>22</v>
       </c>
@@ -10928,63 +10927,63 @@
         <f t="array" ref="D245">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
         <v>Temperate</v>
       </c>
-      <c r="E245" s="31" cm="1">
+      <c r="E245" s="30" cm="1">
         <f t="array" ref="E245">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
         <v>23</v>
       </c>
-      <c r="F245" s="31" cm="1">
+      <c r="F245" s="30" cm="1">
         <f t="array" ref="F245">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
         <v>0.79</v>
       </c>
-      <c r="G245" s="31" cm="1">
+      <c r="G245" s="30" cm="1">
         <f t="array" ref="G245">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
         <v>0.1</v>
       </c>
-      <c r="H245" s="31" cm="1">
+      <c r="H245" s="30" cm="1">
         <f t="array" ref="H245">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
         <v>0.34</v>
       </c>
-      <c r="I245" s="31" cm="1">
+      <c r="I245" s="30" cm="1">
         <f t="array" ref="I245">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
         <v>5.0000000000000001E-3</v>
       </c>
-      <c r="J245" s="31" cm="1">
+      <c r="J245" s="30" cm="1">
         <f t="array" ref="J245">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
         <v>0.01</v>
       </c>
-      <c r="K245" s="31" cm="1">
+      <c r="K245" s="30" cm="1">
         <f t="array" ref="K245">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
         <v>0.02</v>
       </c>
-      <c r="L245" s="31" cm="1">
+      <c r="L245" s="30" cm="1">
         <f t="array" ref="L245">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
         <v>0.03</v>
       </c>
-      <c r="M245" s="31" cm="1">
+      <c r="M245" s="30" cm="1">
         <f t="array" ref="M245">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
         <v>0.04</v>
       </c>
-      <c r="N245" s="31" cm="1">
+      <c r="N245" s="30" cm="1">
         <f t="array" ref="N245">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
         <v>1.4999999999999999E-2</v>
       </c>
-      <c r="O245" s="31" cm="1">
+      <c r="O245" s="30" cm="1">
         <f t="array" ref="O245">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
         <v>1.4999999999999999E-2</v>
       </c>
-      <c r="P245" s="31" cm="1">
+      <c r="P245" s="30" cm="1">
         <f t="array" ref="P245">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
         <v>0</v>
       </c>
-      <c r="Q245" s="31" cm="1">
+      <c r="Q245" s="30" cm="1">
         <f t="array" ref="Q245">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
         <v>0</v>
       </c>
-      <c r="R245" s="31" cm="1">
+      <c r="R245" s="30" cm="1">
         <f t="array" ref="R245">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
         <v>4.7000000000000002E-3</v>
       </c>
-      <c r="S245" s="31" cm="1">
+      <c r="S245" s="30" cm="1">
         <f t="array" ref="S245">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
         <v>23</v>
       </c>
@@ -10994,63 +10993,63 @@
         <f t="array" ref="D246">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
         <v>Temperate</v>
       </c>
-      <c r="E246" s="31" cm="1">
+      <c r="E246" s="30" cm="1">
         <f t="array" ref="E246">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
         <v>24</v>
       </c>
-      <c r="F246" s="31" cm="1">
+      <c r="F246" s="30" cm="1">
         <f t="array" ref="F246">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
         <v>0.79</v>
       </c>
-      <c r="G246" s="31" cm="1">
+      <c r="G246" s="30" cm="1">
         <f t="array" ref="G246">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
         <v>0.1</v>
       </c>
-      <c r="H246" s="31" cm="1">
+      <c r="H246" s="30" cm="1">
         <f t="array" ref="H246">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
         <v>0.37</v>
       </c>
-      <c r="I246" s="31" cm="1">
+      <c r="I246" s="30" cm="1">
         <f t="array" ref="I246">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
         <v>5.0000000000000001E-3</v>
       </c>
-      <c r="J246" s="31" cm="1">
+      <c r="J246" s="30" cm="1">
         <f t="array" ref="J246">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
         <v>0.01</v>
       </c>
-      <c r="K246" s="31" cm="1">
+      <c r="K246" s="30" cm="1">
         <f t="array" ref="K246">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
         <v>0.02</v>
       </c>
-      <c r="L246" s="31" cm="1">
+      <c r="L246" s="30" cm="1">
         <f t="array" ref="L246">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
         <v>0.03</v>
       </c>
-      <c r="M246" s="31" cm="1">
+      <c r="M246" s="30" cm="1">
         <f t="array" ref="M246">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
         <v>0.04</v>
       </c>
-      <c r="N246" s="31" cm="1">
+      <c r="N246" s="30" cm="1">
         <f t="array" ref="N246">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
         <v>1.4999999999999999E-2</v>
       </c>
-      <c r="O246" s="31" cm="1">
+      <c r="O246" s="30" cm="1">
         <f t="array" ref="O246">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
         <v>1.4999999999999999E-2</v>
       </c>
-      <c r="P246" s="31" cm="1">
+      <c r="P246" s="30" cm="1">
         <f t="array" ref="P246">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
         <v>0</v>
       </c>
-      <c r="Q246" s="31" cm="1">
+      <c r="Q246" s="30" cm="1">
         <f t="array" ref="Q246">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
         <v>0</v>
       </c>
-      <c r="R246" s="31" cm="1">
+      <c r="R246" s="30" cm="1">
         <f t="array" ref="R246">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
         <v>4.7000000000000002E-3</v>
       </c>
-      <c r="S246" s="31" cm="1">
+      <c r="S246" s="30" cm="1">
         <f t="array" ref="S246">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
         <v>24</v>
       </c>
@@ -11060,63 +11059,63 @@
         <f t="array" ref="D247">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
         <v>Temperate</v>
       </c>
-      <c r="E247" s="31" cm="1">
+      <c r="E247" s="30" cm="1">
         <f t="array" ref="E247">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
         <v>25</v>
       </c>
-      <c r="F247" s="31" cm="1">
+      <c r="F247" s="30" cm="1">
         <f t="array" ref="F247">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
         <v>0.79</v>
       </c>
-      <c r="G247" s="31" cm="1">
+      <c r="G247" s="30" cm="1">
         <f t="array" ref="G247">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
         <v>0.1</v>
       </c>
-      <c r="H247" s="31" cm="1">
+      <c r="H247" s="30" cm="1">
         <f t="array" ref="H247">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
         <v>0.41</v>
       </c>
-      <c r="I247" s="31" cm="1">
+      <c r="I247" s="30" cm="1">
         <f t="array" ref="I247">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
         <v>5.0000000000000001E-3</v>
       </c>
-      <c r="J247" s="31" cm="1">
+      <c r="J247" s="30" cm="1">
         <f t="array" ref="J247">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
         <v>0.01</v>
       </c>
-      <c r="K247" s="31" cm="1">
+      <c r="K247" s="30" cm="1">
         <f t="array" ref="K247">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
         <v>0.02</v>
       </c>
-      <c r="L247" s="31" cm="1">
+      <c r="L247" s="30" cm="1">
         <f t="array" ref="L247">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
         <v>0.03</v>
       </c>
-      <c r="M247" s="31" cm="1">
+      <c r="M247" s="30" cm="1">
         <f t="array" ref="M247">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
         <v>0.04</v>
       </c>
-      <c r="N247" s="31" cm="1">
+      <c r="N247" s="30" cm="1">
         <f t="array" ref="N247">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
         <v>1.4999999999999999E-2</v>
       </c>
-      <c r="O247" s="31" cm="1">
+      <c r="O247" s="30" cm="1">
         <f t="array" ref="O247">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
         <v>1.4999999999999999E-2</v>
       </c>
-      <c r="P247" s="31" cm="1">
+      <c r="P247" s="30" cm="1">
         <f t="array" ref="P247">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
         <v>0</v>
       </c>
-      <c r="Q247" s="31" cm="1">
+      <c r="Q247" s="30" cm="1">
         <f t="array" ref="Q247">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
         <v>0</v>
       </c>
-      <c r="R247" s="31" cm="1">
+      <c r="R247" s="30" cm="1">
         <f t="array" ref="R247">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
         <v>4.7000000000000002E-3</v>
       </c>
-      <c r="S247" s="31" cm="1">
+      <c r="S247" s="30" cm="1">
         <f t="array" ref="S247">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
         <v>25</v>
       </c>
@@ -11126,63 +11125,63 @@
         <f t="array" ref="D248">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
         <v>Warm</v>
       </c>
-      <c r="E248" s="31" cm="1">
+      <c r="E248" s="30" cm="1">
         <f t="array" ref="E248">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
         <v>26</v>
       </c>
-      <c r="F248" s="31" cm="1">
+      <c r="F248" s="30" cm="1">
         <f t="array" ref="F248">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
         <v>0.79</v>
       </c>
-      <c r="G248" s="31" cm="1">
+      <c r="G248" s="30" cm="1">
         <f t="array" ref="G248">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
         <v>0.1</v>
       </c>
-      <c r="H248" s="31" cm="1">
+      <c r="H248" s="30" cm="1">
         <f t="array" ref="H248">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
         <v>0.44</v>
       </c>
-      <c r="I248" s="31" cm="1">
+      <c r="I248" s="30" cm="1">
         <f t="array" ref="I248">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
         <v>0.01</v>
       </c>
-      <c r="J248" s="31" cm="1">
+      <c r="J248" s="30" cm="1">
         <f t="array" ref="J248">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
         <v>1.4999999999999999E-2</v>
       </c>
-      <c r="K248" s="31" cm="1">
+      <c r="K248" s="30" cm="1">
         <f t="array" ref="K248">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
         <v>0.02</v>
       </c>
-      <c r="L248" s="31" cm="1">
+      <c r="L248" s="30" cm="1">
         <f t="array" ref="L248">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
         <v>0.03</v>
       </c>
-      <c r="M248" s="31" cm="1">
+      <c r="M248" s="30" cm="1">
         <f t="array" ref="M248">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
         <v>0.04</v>
       </c>
-      <c r="N248" s="31" cm="1">
+      <c r="N248" s="30" cm="1">
         <f t="array" ref="N248">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
         <v>1.4999999999999999E-2</v>
       </c>
-      <c r="O248" s="31" cm="1">
+      <c r="O248" s="30" cm="1">
         <f t="array" ref="O248">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
         <v>1.4999999999999999E-2</v>
       </c>
-      <c r="P248" s="31" cm="1">
+      <c r="P248" s="30" cm="1">
         <f t="array" ref="P248">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
         <v>0</v>
       </c>
-      <c r="Q248" s="31" cm="1">
+      <c r="Q248" s="30" cm="1">
         <f t="array" ref="Q248">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
         <v>0</v>
       </c>
-      <c r="R248" s="31" cm="1">
+      <c r="R248" s="30" cm="1">
         <f t="array" ref="R248">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
         <v>4.7000000000000002E-3</v>
       </c>
-      <c r="S248" s="31" cm="1">
+      <c r="S248" s="30" cm="1">
         <f t="array" ref="S248">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
         <v>26</v>
       </c>
@@ -11192,63 +11191,63 @@
         <f t="array" ref="D249">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
         <v>Warm</v>
       </c>
-      <c r="E249" s="31" cm="1">
+      <c r="E249" s="30" cm="1">
         <f t="array" ref="E249">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
         <v>27</v>
       </c>
-      <c r="F249" s="31" cm="1">
+      <c r="F249" s="30" cm="1">
         <f t="array" ref="F249">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
         <v>0.8</v>
       </c>
-      <c r="G249" s="31" cm="1">
+      <c r="G249" s="30" cm="1">
         <f t="array" ref="G249">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
         <v>0.1</v>
       </c>
-      <c r="H249" s="31" cm="1">
+      <c r="H249" s="30" cm="1">
         <f t="array" ref="H249">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
         <v>0.48</v>
       </c>
-      <c r="I249" s="31" cm="1">
+      <c r="I249" s="30" cm="1">
         <f t="array" ref="I249">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
         <v>0.01</v>
       </c>
-      <c r="J249" s="31" cm="1">
+      <c r="J249" s="30" cm="1">
         <f t="array" ref="J249">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
         <v>1.4999999999999999E-2</v>
       </c>
-      <c r="K249" s="31" cm="1">
+      <c r="K249" s="30" cm="1">
         <f t="array" ref="K249">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
         <v>0.02</v>
       </c>
-      <c r="L249" s="31" cm="1">
+      <c r="L249" s="30" cm="1">
         <f t="array" ref="L249">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
         <v>0.03</v>
       </c>
-      <c r="M249" s="31" cm="1">
+      <c r="M249" s="30" cm="1">
         <f t="array" ref="M249">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
         <v>0.04</v>
       </c>
-      <c r="N249" s="31" cm="1">
+      <c r="N249" s="30" cm="1">
         <f t="array" ref="N249">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
         <v>1.4999999999999999E-2</v>
       </c>
-      <c r="O249" s="31" cm="1">
+      <c r="O249" s="30" cm="1">
         <f t="array" ref="O249">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
         <v>1.4999999999999999E-2</v>
       </c>
-      <c r="P249" s="31" cm="1">
+      <c r="P249" s="30" cm="1">
         <f t="array" ref="P249">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
         <v>0</v>
       </c>
-      <c r="Q249" s="31" cm="1">
+      <c r="Q249" s="30" cm="1">
         <f t="array" ref="Q249">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
         <v>0</v>
       </c>
-      <c r="R249" s="31" cm="1">
+      <c r="R249" s="30" cm="1">
         <f t="array" ref="R249">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
         <v>4.7000000000000002E-3</v>
       </c>
-      <c r="S249" s="31" cm="1">
+      <c r="S249" s="30" cm="1">
         <f t="array" ref="S249">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
         <v>27</v>
       </c>
@@ -11258,63 +11257,63 @@
         <f t="array" ref="D250">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
         <v>Warm</v>
       </c>
-      <c r="E250" s="31" t="str" cm="1">
+      <c r="E250" s="30" t="str" cm="1">
         <f t="array" ref="E250">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
         <v>≥28</v>
       </c>
-      <c r="F250" s="31" cm="1">
+      <c r="F250" s="30" cm="1">
         <f t="array" ref="F250">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
         <v>0.8</v>
       </c>
-      <c r="G250" s="31" cm="1">
+      <c r="G250" s="30" cm="1">
         <f t="array" ref="G250">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
         <v>0.1</v>
       </c>
-      <c r="H250" s="31" cm="1">
+      <c r="H250" s="30" cm="1">
         <f t="array" ref="H250">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
         <v>0.5</v>
       </c>
-      <c r="I250" s="31" cm="1">
+      <c r="I250" s="30" cm="1">
         <f t="array" ref="I250">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
         <v>0.01</v>
       </c>
-      <c r="J250" s="31" cm="1">
+      <c r="J250" s="30" cm="1">
         <f t="array" ref="J250">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
         <v>1.4999999999999999E-2</v>
       </c>
-      <c r="K250" s="31" cm="1">
+      <c r="K250" s="30" cm="1">
         <f t="array" ref="K250">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
         <v>0.02</v>
       </c>
-      <c r="L250" s="31" cm="1">
+      <c r="L250" s="30" cm="1">
         <f t="array" ref="L250">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
         <v>0.03</v>
       </c>
-      <c r="M250" s="31" cm="1">
+      <c r="M250" s="30" cm="1">
         <f t="array" ref="M250">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
         <v>0.04</v>
       </c>
-      <c r="N250" s="31" cm="1">
+      <c r="N250" s="30" cm="1">
         <f t="array" ref="N250">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
         <v>1.4999999999999999E-2</v>
       </c>
-      <c r="O250" s="31" cm="1">
+      <c r="O250" s="30" cm="1">
         <f t="array" ref="O250">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
         <v>1.4999999999999999E-2</v>
       </c>
-      <c r="P250" s="31" cm="1">
+      <c r="P250" s="30" cm="1">
         <f t="array" ref="P250">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
         <v>0</v>
       </c>
-      <c r="Q250" s="31" cm="1">
+      <c r="Q250" s="30" cm="1">
         <f t="array" ref="Q250">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
         <v>0</v>
       </c>
-      <c r="R250" s="31" cm="1">
+      <c r="R250" s="30" cm="1">
         <f t="array" ref="R250">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
         <v>4.7000000000000002E-3</v>
       </c>
-      <c r="S250" s="31" cm="1">
+      <c r="S250" s="30" cm="1">
         <f t="array" ref="S250">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
         <v>28</v>
       </c>
@@ -11344,19 +11343,19 @@
       </c>
     </row>
     <row r="257" spans="4:5" x14ac:dyDescent="0.25">
-      <c r="D257" s="31" t="s">
-        <v>91</v>
-      </c>
-      <c r="E257" s="31" t="s">
-        <v>92</v>
+      <c r="D257" s="30" t="s">
+        <v>86</v>
+      </c>
+      <c r="E257" s="30" t="s">
+        <v>87</v>
       </c>
     </row>
     <row r="258" spans="4:5" x14ac:dyDescent="0.25">
-      <c r="D258" s="31" t="str" cm="1">
+      <c r="D258" s="30" t="str" cm="1">
         <f t="array" ref="D258">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_EFOrganicFertiliserAndCropResidues_Data(), Table_SourceData_Common_EFOrganicFertCropResidues[[#Headers],[Climate Zone]], 0)</f>
         <v>Wet climate zone</v>
       </c>
-      <c r="E258" s="31" cm="1">
+      <c r="E258" s="30" cm="1">
         <f t="array" ref="E258">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_EFOrganicFertiliserAndCropResidues_Data(), Table_SourceData_Common_EFOrganicFertCropResidues[[#Headers],[Climate Zone]], 0)</f>
         <v>6.0000000000000001E-3</v>
       </c>
@@ -11366,7 +11365,7 @@
         <f t="array" ref="D259">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_EFOrganicFertiliserAndCropResidues_Data(), Table_SourceData_Common_EFOrganicFertCropResidues[[#Headers],[Climate Zone]], 0)</f>
         <v>Dry climate zone</v>
       </c>
-      <c r="E259" s="31" cm="1">
+      <c r="E259" s="30" cm="1">
         <f t="array" ref="E259">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_EFOrganicFertiliserAndCropResidues_Data(), Table_SourceData_Common_EFOrganicFertCropResidues[[#Headers],[Climate Zone]], 0)</f>
         <v>5.0000000000000001E-3</v>
       </c>
@@ -11397,6 +11396,26 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <TaxCatchAll xmlns="09eef6d6-daa8-4301-8f9f-b1ec38079286" xsi:nil="true"/>
+    <lcf76f155ced4ddcb4097134ff3c332f xmlns="7291119c-fce9-4911-96ae-b800be5dccd8">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    </lcf76f155ced4ddcb4097134ff3c332f>
+  </documentManagement>
+</p:properties>
+</file>
+
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x010100ACB660BB23738846A00119B5826AC974" ma:contentTypeVersion="11" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="3e3613359d4ae7f6bda6c57be713f101">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="7291119c-fce9-4911-96ae-b800be5dccd8" xmlns:ns3="09eef6d6-daa8-4301-8f9f-b1ec38079286" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="87491bfad7f11426ad96486e70428b3e" ns2:_="" ns3:_="">
     <xsd:import namespace="7291119c-fce9-4911-96ae-b800be5dccd8"/>
@@ -11591,31 +11610,30 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <TaxCatchAll xmlns="09eef6d6-daa8-4301-8f9f-b1ec38079286" xsi:nil="true"/>
-    <lcf76f155ced4ddcb4097134ff3c332f xmlns="7291119c-fce9-4911-96ae-b800be5dccd8">
-      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    </lcf76f155ced4ddcb4097134ff3c332f>
-  </documentManagement>
-</p:properties>
-</file>
-
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
 <file path=customXml/item4.xml><?xml version="1.0" encoding="utf-8"?>
 <AFEJSONBlob xmlns="http://schemas.advancedformulaenvironment.officeapps.live.com/afejsonblob/1.0">ewAiAHMAYwBoAGUAbQBhACIAOgAiAGgAdAB0AHAAOgAvAC8AcwBjAGgAZQBtAGEAcwAuAGEAZAB2AGEAbgBjAGUAZABmAG8AcgBtAHUAbABhAGUAbgB2AGkAcgBvAG4AbQBlAG4AdAAuAG8AZgBmAGkAYwBlAGEAcABwAHMALgBsAGkAdgBlAC4AYwBvAG0ALwBhAGYAZQBwAHIAbwBqAGUAYwB0AHMALwAwAC4AMgAiACwAIgBmAGkAbABlAHMAIgA6AFsAewAiAHAAYQB0AGgAIgA6ACIALwBwAHIAbwBqAGUAYwB0AHMALwBXAG8AcgBrAGIAbwBvAGsAIgAsACIAdABlAHgAdAAiADoAIgAvAC8AIAAtAC0ALQAgAFcAbwByAGsAYgBvAG8AawAgAG0AbwBkAHUAbABlACAALQAtAC0AXABuAC8ALwAgAEEAIABmAGkAbABlACAAbwBmACAAbgBhAG0AZQAgAGQAZQBmAGkAbgBpAHQAaQBvAG4AcwAgAG8AZgAgAHQAaABlACAAZgBvAHIAbQA6AFwAbgAvAC8AIAAgACAAIABuAGEAbQBlACAAPQAgAGQAZQBmAGkAbgBpAHQAaQBvAG4AOwBcAG4AIgB9ACwAewAiAHAAYQB0AGgAIgA6ACIALwBwAHIAbwBqAGUAYwB0AHMALwBDAG8AbQBtAG8AbgBfAEUAcQB1AGEAdABpAG8AbgBzACIALAAiAHQAZQB4AHQAIgA6ACIAXABuAC8AKgAgAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuAEMAbwBtAG0AbwBuAF8AQwBvAG4AdgBlAHIAdABOADIATwBUAG8AQwBPADIAZQBcAG4AQwBvAG4AdgBlAHIAdAAgAG4AaQB0AHIAbwB1AHMAIABvAHgAaQBkAGUAIABlAG0AaQBzAHMAaQBvAG4AcwAgAHQAbwAgAGMAYQByAGIAbwBuACAAZABpAG8AeABpAGQAZQAgAGUAcQB1AGkAdgBhAGwAZQBuAHQAIABlAG0AaQBzAHMAaQBvAG4AcwBcAG4ARQBOADIATwAgAEMATwAyAGUAXABuAHQAIABDAE8AMgBlAFwAbgBFAE4AMgBPADoAIABuAGkAdAByAG8AdQBzACAAbwB4AGkAZABlACAAZQBtAGkAcwBzAGkAbwBuAHMAIAAoAHQAIABOADIATwApAFwAbgBHAFcAUABOADIATwA6ACAAZwBsAG8AYgBhAGwAIAB3AGEAcgBtAGkAbgBnACAAcABvAHQAZQBuAHQAaQBhAGwAIABmAG8AcgAgAG4AaQB0AHIAbwB1AHMAIABvAHgAaQBkAGUAIAAoAHQAIABDAE8AMgAtAGUAIAAvACAAdAAgAE4AMgBPACkAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AKgAvAFwAbgBcAG4AXABuAEMAbwBtAG0AbwBuAF8AQwBvAG4AdgBlAHIAdABOADIATwBUAG8AQwBPADIAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABFAF8ATgAyAE8ALAAgAEcAVwBQAF8ATgAyAE8ALABcAG4AIAAgACAAIABFAF8ATgAyAE8AIAAqACAARwBXAFAAXwBOADIATwBcAG4AIAAgACkAXABuADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAEMAbwBuAHYAZQByAHQATgAyAE8AVABvAEMATwAyAGUAXwBUAGkAdABsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAEMAbwBuAHYAZQByAHQAIABuAGkAdAByAG8AdQBzACAAbwB4AGkAZABlACAAZQBtAGkAcwBzAGkAbwBuAHMAIAB0AG8AIABjAGEAcgBiAG8AbgAgAGQAaQBvAHgAaQBkAGUAIABlAHEAdQBpAHYAYQBsAGUAbgB0ACAAZQBtAGkAcwBzAGkAbwBuAHMAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AQwBvAG4AdgBlAHIAdABOADIATwBUAG8AQwBPADIAZQBfAFYAYQByAGkAYQBiAGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIARQBOADIATwAgAEMATwAyAGUAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AQwBvAG4AdgBlAHIAdABOADIATwBUAG8AQwBPADIAZQBfAFUAbgBpAHQAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAHQAIABDAE8AMgBlAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAEMAbwBuAHYAZQByAHQATgAyAE8AVABvAEMATwAyAGUAXwBOAEkAUgBSAGUAZgBlAHIAZQBuAGMAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AQwBvAG4AdgBlAHIAdABOADIATwBUAG8AQwBPADIAZQBfAEwAYQB0AGUAeABFAHEAdQBhAHQAaQBvAG4AXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAEMATwAyAF8AZQAgAD0AIABFAF8AewBOADIATwB9ACAAXABcAHQAaQBtAGUAcwAgAEcAVwBQAF8AewBOADIATwB9AFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAEMAbwBuAHYAZQByAHQATgAyAE8AVABvAEMATwAyAGUAXwBBAHIAZwB1AG0AZQBuAHQAcwBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABNAEEASwBFAEEAUgBSAEEAWQAoADIALAAgADIALAAgAFwAbgAgACAAIAAgACAAIABMAEEATQBCAEQAQQAoAHIALABjACwAIABcAG4AIAAgACAAIAAgACAAIAAgAEkATgBEAEUAWAAoAHsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEUATgAyAE8AXAAiACwAXAAiAE4AaQB0AHIAbwB1AHMAIABvAHgAaQBkAGUAIABlAG0AaQBzAHMAaQBvAG4AcwAgACgAdAAgAE4AMgBPACkAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEcAVwBQAE4AMgBPAFwAIgAsAFwAIgBHAGwAbwBiAGEAbAAgAHcAYQByAG0AaQBuAGcAIABwAG8AdABlAG4AdABpAGEAbAAgAGYAbwByACAAbgBpAHQAcgBvAHUAcwAgAG8AeABpAGQAZQAgACgAdAAgAEMATwAyAC0AZQAgAC8AIAB0ACAATgAyAE8AKQBcACIAXABuACAAIAAgACAAIAAgACAAIAB9ACwAIAByACwAIABjACkAXABuACAAIAAgACAAIAAgACkAXABuACAAIAAgACAAKQBcAG4AIAAgACkAOwBcAG4AXABuAC8AKgAgAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuAEMAbwBtAG0AbwBuAF8AQwBvAG4AdgBlAHIAdABDAEgANABUAG8AQwBPADIAZQBcAG4AQwBvAG4AdgBlAHIAdAAgAG0AZQB0AGgAYQBuAGUAIABlAG0AaQBzAHMAaQBvAG4AcwAgAHQAbwAgAGMAYQByAGIAbwBuACAAZABpAG8AeABpAGQAZQAgAGUAcQB1AGkAdgBhAGwAZQBuAHQAIABlAG0AaQBzAHMAaQBvAG4AcwBcAG4ARQBDAEgANAAgAEMATwAyAGUAXABuAHQAIABDAE8AMgBlAFwAbgBFAEMASAA0ADoAIABtAGUAdABoAGEAbgBlACAAZQBtAGkAcwBzAGkAbwBuAHMAIAAoAHQAIABDAEgANAApAFwAbgBHAFcAUABDAEgANAA6ACAAZwBsAG8AYgBhAGwAIAB3AGEAcgBtAGkAbgBnACAAcABvAHQAZQBuAHQAaQBhAGwAIABmAG8AcgAgAG0AZQB0AGgAYQBuAGUAIAAoAHQAIABDAE8AMgAtAGUAIAAvACAAdAAgAEMASAA0ACkAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AKgAvAFwAbgBcAG4AXABuAEMAbwBtAG0AbwBuAF8AQwBvAG4AdgBlAHIAdABDAEgANABUAG8AQwBPADIAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABFAF8AQwBIADQALAAgAEcAVwBQAF8AQwBIADQALABcAG4AIAAgACAAIABFAF8AQwBIADQAIAAqACAARwBXAFAAXwBDAEgANABcAG4AIAAgACkAXABuADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAEMAbwBuAHYAZQByAHQAQwBIADQAVABvAEMATwAyAGUAXwBUAGkAdABsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAEMAbwBuAHYAZQByAHQAIABtAGUAdABoAGEAbgBlACAAZQBtAGkAcwBzAGkAbwBuAHMAIAB0AG8AIABjAGEAcgBiAG8AbgAgAGQAaQBvAHgAaQBkAGUAIABlAHEAdQBpAHYAYQBsAGUAbgB0ACAAZQBtAGkAcwBzAGkAbwBuAHMAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AQwBvAG4AdgBlAHIAdABDAEgANABUAG8AQwBPADIAZQBfAFYAYQByAGkAYQBiAGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIARQBDAEgANAAgAEMATwAyAGUAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AQwBvAG4AdgBlAHIAdABDAEgANABUAG8AQwBPADIAZQBfAFUAbgBpAHQAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAHQAIABDAE8AMgBlAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAEMAbwBuAHYAZQByAHQAQwBIADQAVABvAEMATwAyAGUAXwBOAEkAUgBSAGUAZgBlAHIAZQBuAGMAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AQwBvAG4AdgBlAHIAdABDAEgANABUAG8AQwBPADIAZQBfAEwAYQB0AGUAeABFAHEAdQBhAHQAaQBvAG4AXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAEMATwAyAF8AZQAgAD0AIABFAF8AewBDAEgANAB9ACAAXABcAHQAaQBtAGUAcwAgAEcAVwBQAF8AewBDAEgANAB9AFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAEMAbwBuAHYAZQByAHQAQwBIADQAVABvAEMATwAyAGUAXwBBAHIAZwB1AG0AZQBuAHQAcwBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABNAEEASwBFAEEAUgBSAEEAWQAoADIALAAgADIALAAgAFwAbgAgACAAIAAgACAAIABMAEEATQBCAEQAQQAoAHIALABjACwAIABcAG4AIAAgACAAIAAgACAAIAAgAEkATgBEAEUAWAAoAHsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEUAQwBIADQAXAAiACwAXAAiAE0AZQB0AGgAYQBuAGUAIABlAG0AaQBzAHMAaQBvAG4AcwAgACgAdAAgAEMASAA0ACkAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEcAVwBQAEMASAA0AFwAIgAsAFwAIgBHAGwAbwBiAGEAbAAgAHcAYQByAG0AaQBuAGcAIABwAG8AdABlAG4AdABpAGEAbAAgAGYAbwByACAAbQBlAHQAaABhAG4AZQAgACgAdAAgAEMATwAyAC0AZQAgAC8AIAB0ACAAQwBIADQAKQBcACIAXABuACAAIAAgACAAIAAgACAAIAB9ACwAIAByACwAIABjACkAXABuACAAIAAgACAAIAAgACkAXABuACAAIAAgACAAKQBcAG4AIAAgACkAOwAiAH0ALAB7ACIAcABhAHQAaAAiADoAIgAvAHAAcgBvAGoAZQBjAHQAcwAvAEMAbwBtAG0AbwBuAF8ASQBuAHAAdQB0AEYAdQBuAGMAdABpAG8AbgBzACIALAAiAHQAZQB4AHQAIgA6ACIAVQB0AGkAbABpAHQAeQBfAEcAZQB0AEEAcgByAGEAeQBUAGEAYgBsAGUAUgBvAHcAUwB0AGEAcgB0AE4AdQBtAGIAZQByAFwAbgA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAAVABhAGIAbABlAGgAZQBhAGQAZQByAEMAZQBsAGwALABSAG8AdwBzAEIAZQB0AHcAZQBlAG4ASABlAGEAZABlAHIAYQBuAGQAQQByAHIAYQB5ACwAXABuACAAIAAgACAAUgBPAFcAKABUAGEAYgBsAGUAaABlAGEAZABlAHIAQwBlAGwAbAApACAAKwAgAFIAbwB3AHMAQgBlAHQAdwBlAGUAbgBIAGUAYQBkAGUAcgBhAG4AZABBAHIAcgBhAHkAIAAtACAAMQBcAG4AKQA7AFwAbgBcAG4AVQB0AGkAbABpAHQAeQBfAEcAZQB0AEEAcgByAGEAeQBUAGEAYgBsAGUAQwBvAGwAdQBtAG4AUwB0AGEAcgB0AE4AdQBtAGIAZQByAFwAbgA9AEwAQQBNAEIARABBACgAXABuACAAIABUAGEAYgBsAGUASABlAGEAZABlAHIAQwBlAGwAbAAsAFwAbgAgACAAQwBPAEwAVQBNAE4AKABUAGEAYgBsAGUASABlAGEAZABlAHIAQwBlAGwAbAApAFwAbgApADsAXABuAFwAbgBVAHQAaQBsAGkAdAB5AF8ARABpAHMAcABsAGEAeQBBAHIAcgBhAHkASQBuAFQAYQBiAGwAZQBcAG4APQBMAEEATQBCAEQAQQAoAFwAbgAgAEEAcgByAGEAeQBEAGEAdABhACwAIABUAGEAYgBsAGUAaABlAGEAZABlAHIAQwBlAGwAbAAsACAAUgBvAHcAcwBCAGUAdAB3AGUAZQBuAEgAZQBhAGQAZQByAGEAbgBkAEEAcgByAGEAeQAsACAAWwBDAG8AbAB1AG0AbgBzAEIAZQB0AHcAZQBlAG4ASABlAGEAZABlAHIAQQBuAGQAQQByAHIAYQB5AF0ALABcAG4AIABJAEYARQBSAFIATwBSACgAXABuACAAIAAgACAAIABJAE4ARABFAFgAKABcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAVQBOAEkAUQBVAEUAKABBAHIAcgBhAHkARABhAHQAYQApACwAIABcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAUgBPAFcAKAApAC0AVQB0AGkAbABpAHQAeQBfAEcAZQB0AEEAcgByAGEAeQBUAGEAYgBsAGUAUgBvAHcAUwB0AGEAcgB0AE4AdQBtAGIAZQByACgAVABhAGIAbABlAGgAZQBhAGQAZQByAEMAZQBsAGwALAAgAFIAbwB3AHMAQgBlAHQAdwBlAGUAbgBIAGUAYQBkAGUAcgBhAG4AZABBAHIAcgBhAHkAKQAsACAAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgAEMATwBMAFUATQBOACgAKQAtAFUAdABpAGwAaQB0AHkAXwBHAGUAdABBAHIAcgBhAHkAVABhAGIAbABlAEMAbwBsAHUAbQBuAFMAdABhAHIAdABOAHUAbQBiAGUAcgAoAFQAYQBiAGwAZQBoAGUAYQBkAGUAcgBDAGUAbABsACkAIAArAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIABJAEYAKABJAFMATwBNAEkAVABUAEUARAAoAEMAbwBsAHUAbQBuAHMAQgBlAHQAdwBlAGUAbgBIAGUAYQBkAGUAcgBBAG4AZABBAHIAcgBhAHkAKQAsACAAMQAsACAAQwBvAGwAdQBtAG4AcwBCAGUAdAB3AGUAZQBuAEgAZQBhAGQAZQByAEEAbgBkAEEAcgByAGEAeQApAFwAbgAgACAAIAAgACAAIAAgACAAKQAsACAAXAAiAFwAIgBcAG4AIAAgACAAIAApAFwAbgApADsAXABuAFwAbgBVAHQAaQBsAGkAdAB5AF8ATABvAG8AawB1AHAAVgBhAGwAdQBlAEkAbgBUAGEAYgBsAGUAXABuAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABMAG8AbwBrAHUAcABWAGEAbAB1AGUALAAgAEwAbwBvAGsAdQBwAEEAcgByAGEAeQAsACAAUgBlAHQAdQByAG4AQQByAHIAYQB5ACwAXABuACAAIAAgACAAWABMAE8ATwBLAFUAUAAoAEwAbwBvAGsAdQBwAFYAYQBsAHUAZQAsACAATABvAG8AawB1AHAAQQByAHIAYQB5ACwAIABSAGUAdAB1AHIAbgBBAHIAcgBhAHkALAAgAFwAIgBcACIAKQBcAG4AKQA7AFwAbgBcAG4AVQB0AGkAbABpAHQAeQBfAEwAbwBvAGsAdQBwAFYAYQBsAHUAZQBJAG4AVABhAGIAbABlAE4AdQBtAGIAZQByAFwAbgA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAATABvAG8AawB1AHAAVgBhAGwAdQBlACwAIABMAG8AbwBrAHUAcABBAHIAcgBhAHkALAAgAFIAZQB0AHUAcgBuAEEAcgByAGEAeQAsAFwAbgAgACAAIAAgAEkARgAoAEkAUwBOAFUATQBCAEUAUgAoAFwAbgAgACAAIAAgACAAIAAgACAAWABMAE8ATwBLAFUAUAAoAEwAbwBvAGsAdQBwAFYAYQBsAHUAZQAsACAATABvAG8AawB1AHAAQQByAHIAYQB5ACwAIABSAGUAdAB1AHIAbgBBAHIAcgBhAHkALAAgAFwAIgBcACIAKQBcAG4AIAAgACAAIAApACwAIABYAEwATwBPAEsAVQBQACgATABvAG8AawB1AHAAVgBhAGwAdQBlACwAIABMAG8AbwBrAHUAcABBAHIAcgBhAHkALAAgAFIAZQB0AHUAcgBuAEEAcgByAGEAeQAsACAAXAAiAFwAIgApACwAIAAwACkAXABuACkAOwBcAG4AXABuAFUAdABpAGwAaQB0AHkAXwBMAG8AbwBrAHUAcABWAGEAbAB1AGUASQBuAFQAYQBiAGwAZQBUAHcAbwBDAG8AbAB1AG0AbgBzAFwAbgA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAATABvAG8AawB1AHAAVgBhAGwAdQBlADEALAAgAEwAbwBvAGsAdQBwAFYAYQBsAHUAZQAyACwAIABMAG8AbwBrAHUAcABBAHIAcgBhAHkAMQAsACAATABvAG8AawB1AHAAQQByAHIAYQB5ADIALAAgAFIAZQB0AHUAcgBuAEEAcgByAGEAeQAsACAAWwBWAGEAbAB1AGUASQBGAEYAYQBsAHMAZQBdACwAXABuACAAIAAgACAAWABMAE8ATwBLAFUAUAAoADEALAAgACgATABvAG8AawB1AHAAQQByAHIAYQB5ADEAPQBMAG8AbwBrAHUAcABWAGEAbAB1AGUAMQApACoAKABMAG8AbwBrAHUAcABBAHIAcgBhAHkAMgA9AEwAbwBvAGsAdQBwAFYAYQBsAHUAZQAyACkALAAgAFIAZQB0AHUAcgBuAEEAcgByAGEAeQAsACAASQBGACgASQBTAE8ATQBJAFQAVABFAEQAKABWAGEAbAB1AGUASQBGAEYAYQBsAHMAZQApACwAIABcACIAXAAiACwAIABWAGEAbAB1AGUASQBGAEYAYQBsAHMAZQApACkAXABuACkAOwBcAG4AXABuAFUAdABpAGwAaQB0AHkAXwBMAG8AbwBrAHUAcABWAGEAbAB1AGUASQBuAFQAYQBiAGwAZQBPAG4AZQBDAG8AbAB1AG0AbgBBAG4AZABIAGUAYQBkAGUAcgBcAG4APQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAEwAbwBvAGsAdQBwAFYAYQBsAHUAZQAxACwAIABMAG8AbwBrAHUAcABWAGEAbAB1AGUAMgAsACAATABvAG8AawB1AHAAQQByAHIAYQB5ADEALAAgAEwAbwBvAGsAdQBwAEEAcgByAGEAeQAyACwAIABSAGUAdAB1AHIAbgBBAHIAcgBhAHkALAAgAFsAVgBhAGwAdQBlAEkAZgBGAGEAbABzAGUAXQAsAFwAbgAgACAAIAAgAEkARgBFAFIAUgBPAFIAKABcAG4AIAAgACAAIAAgACAAIAAgAFgATABPAE8ASwBVAFAAKABMAG8AbwBrAHUAcABWAGEAbAB1AGUAMQAsACAATABvAG8AawB1AHAAQQByAHIAYQB5ADEALABcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAWABMAE8ATwBLAFUAUAAoAEwAbwBvAGsAdQBwAFYAYQBsAHUAZQAyACwAIABMAG8AbwBrAHUAcABBAHIAcgBhAHkAMgAsACAAUgBlAHQAdQByAG4AQQByAHIAYQB5ACkAXABuACAAIAAgACAAIAAgACAAIAApACwAXABuACAAIAAgACAAIAAgACAAIABJAEYAKABJAFMATwBNAEkAVABUAEUARAAoAFYAYQBsAHUAZQBJAGYARgBhAGwAcwBlACkALAAgAFwAIgBcACIALAAgAFYAYQBsAHUAZQBJAGYARgBhAGwAcwBlACkAXABuACAAIAAgACAAKQBcAG4AKQA7AFwAbgBcAG4AVQB0AGkAbABpAHQAeQBfAFMAcABsAGkAdABTAHQAcgBpAG4AZwBJAG4AdABvAEEAcgByAGEAeQBcAG4APQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAEMAZQBsAGwALAAgAEQAZQBsAGkAbQBpAHQAZQByACwAIABbAEMAaABhAHIAYQBjAHQAZQByAFQAbwBSAGUAbQBvAHYAZQAxAF0ALAAgAFsAQwBoAGEAcgBhAGMAdABlAHIAVABvAFIAZQBtAG8AdgBlADIAXQAsAFwAbgAgACAAIAAgACAAIAAgACAARgBJAEwAVABFAFIAWABNAEwAKABcAG4AIAAgACAAIAAgACAAIAAgAFwAIgA8AHQAPgA8AHMAPgBcACIAIAAmAFwAbgAgACAAIAAgACAAIAAgACAAUwBVAEIAUwBUAEkAVABVAFQARQAoAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIABTAFUAQgBTAFQASQBUAFUAVABFACgAUwBVAEIAUwBUAEkAVABVAFQARQAoAEMAZQBsAGwALABDAGgAYQByAGEAYwB0AGUAcgBUAG8AUgBlAG0AbwB2AGUAMQAsAFwAIgBcACIAKQAsAEMAaABhAHIAYQBjAHQAZQByAFQAbwBSAGUAbQBvAHYAZQAyACwAXAAiAFwAIgApACwAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgAEQAZQBsAGkAbQBpAHQAZQByACwAXAAiADwALwBzAD4APABzAD4AXAAiAFwAbgAgACAAIAAgACAAIAAgACAAKQAgACYAXABuACAAIAAgACAAIAAgACAAIABcACIAPAAvAHMAPgA8AC8AdAA+AFwAIgAsAFwAbgAgACAAIAAgACAAIAAgACAAXAAiAC8ALwBzAFwAIgBcAG4AIAAgACAAIAApAFwAbgApADsAXABuAFwAbgBVAHQAaQBsAGkAdAB5AF8ARwBlAHQAQwBsAGkAbQBhAHQAZQBaAG8AbgBlAFwAbgA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAAYQB2AGcAVABlAG0AcAAsAGEAdgBnAFIAYQBpAG4ALABmAHIAbwBzAHQARABhAHkAcwAsAGUAbABlAHYALABtAGEAcABfAHAAZQB0ACwAXABuACAAIAAgACAAbQBpAG4AVABlAG0AcABBAHIAcgBhAHkALABtAGEAeABUAGUAbQBwAEEAcgByAGEAeQAsAFwAbgAgACAAIAAgAG0AaQBuAFIAYQBpAG4AZgBhAGwAbABBAHIAcgBhAHkALABtAGEAeABSAGEAaQBuAGYAYQBsAGwAQQByAHIAYQB5ACwAXABuACAAIAAgACAAbQBpAG4ARgByAG8AcwB0AEEAcgByAGEAeQAsAG0AYQB4AEYAcgBvAHMAdABBAHIAcgBhAHkALABcAG4AIAAgACAAIABtAGkAbgBFAGwAZQB2AGEAdABpAG8AbgBBAHIAcgBhAHkALABtAGEAeABFAGwAZQB2AGEAdABpAG8AbgBBAHIAcgBhAHkALABcAG4AIAAgACAAIABtAGkAbgBQAEUAVABBAHIAcgBhAHkALABtAGEAeABQAEUAVABBAHIAcgBhAHkALABcAG4AIAAgACAAIABjAGwAaQBtAGEAdABlAFoAbwBuAGUAQQByAHIAYQB5ACwAXABuACAAIAAgACAATABFAFQAKABcAG4AIAAgACAAIAAgACAAIAAgAG0AYQBzAGsALABcAG4AIAAgACAAIAAgACAAIAAgACgAVgBBAEwAVQBFACgAbQBpAG4AVABlAG0AcABBAHIAcgBhAHkAKQA8AD0AYQB2AGcAVABlAG0AcAApACoAXABuACAAIAAgACAAIAAgACAAIAAoAFYAQQBMAFUARQAoAG0AYQB4AFQAZQBtAHAAQQByAHIAYQB5ACkAPgA9AGEAdgBnAFQAZQBtAHAAKQAqAFwAbgAgACAAIAAgACAAIAAgACAAKABWAEEATABVAEUAKABtAGkAbgBSAGEAaQBuAGYAYQBsAGwAQQByAHIAYQB5ACkAPAA9AGEAdgBnAFIAYQBpAG4AKQAqAFwAbgAgACAAIAAgACAAIAAgACAAKABWAEEATABVAEUAKABtAGEAeABSAGEAaQBuAGYAYQBsAGwAQQByAHIAYQB5ACkAPgA9AGEAdgBnAFIAYQBpAG4AKQAqAFwAbgAgACAAIAAgACAAIAAgACAAKABWAEEATABVAEUAKABtAGkAbgBGAHIAbwBzAHQAQQByAHIAYQB5ACkAPAA9AGYAcgBvAHMAdABEAGEAeQBzACkAKgBcAG4AIAAgACAAIAAgACAAIAAgACgAVgBBAEwAVQBFACgAbQBhAHgARgByAG8AcwB0AEEAcgByAGEAeQApAD4APQBmAHIAbwBzAHQARABhAHkAcwApACoAXABuACAAIAAgACAAIAAgACAAIAAoAFYAQQBMAFUARQAoAG0AaQBuAEUAbABlAHYAYQB0AGkAbwBuAEEAcgByAGEAeQApADwAPQBlAGwAZQB2ACkAKgBcAG4AIAAgACAAIAAgACAAIAAgACgAVgBBAEwAVQBFACgAbQBhAHgARQBsAGUAdgBhAHQAaQBvAG4AQQByAHIAYQB5ACkAPgA9AGUAbABlAHYAKQAqAFwAbgAgACAAIAAgACAAIAAgACAAKABWAEEATABVAEUAKABtAGkAbgBQAEUAVABBAHIAcgBhAHkAKQA8AD0AbQBhAHAAXwBwAGUAdAApACoAXABuACAAIAAgACAAIAAgACAAIAAoAFYAQQBMAFUARQAoAG0AYQB4AFAARQBUAEEAcgByAGEAeQApAD4APQBtAGEAcABfAHAAZQB0ACkALABcAG4AIAAgACAAIAAgACAAIAAgAFQAQQBLAEUAKABcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAARgBJAEwAVABFAFIAKABjAGwAaQBtAGEAdABlAFoAbwBuAGUAQQByAHIAYQB5ACwAbQBhAHMAawAsACAAXAAiAE4AbwAgAG0AYQB0AGMAaABcACIAKQAsAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIAAxAFwAbgAgACAAIAAgACAAIAAgACAAKQBcAG4AIAAgACAAIAApAFwAbgApADsAXABuAFwAbgBVAHQAaQBsAGkAdAB5AF8ATABvAG8AawB1AHAASQB0AGUAbQBGAHIAbwBtAE0AaQBuAE0AYQB4AFwAbgA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAATABvAG8AawB1AHAAVgBhAGwAdQBlACwAIABNAGkAbgBBAHIAcgBhAHkALAAgAE0AYQB4AEEAcgByAGEAeQAsACAASQB0AGUAbQBBAHIAcgBhAHkALABcAG4AIAAgACAAIABMAEUAVAAoAFwAbgAgACAAIAAgACAAIAAgACAAbQBhAHMAawAsAFwAbgAgACAAIAAgACAAIAAgACAAKABWAEEATABVAEUAKABNAGkAbgBBAHIAcgBhAHkAKQA8AD0ATABvAG8AawB1AHAAVgBhAGwAdQBlACkAKgBcAG4AIAAgACAAIAAgACAAIAAgACgAVgBBAEwAVQBFACgATQBhAHgAQQByAHIAYQB5ACkAPgA9AEwAbwBvAGsAdQBwAFYAYQBsAHUAZQApACwAXABuACAAIAAgACAAIAAgACAAIABGAEkATABUAEUAUgAoAEkAdABlAG0AQQByAHIAYQB5ACwAIABtAGEAcwBrACwAIABcACIATgBvACAAbQBhAHQAYwBoAFwAIgApAFwAbgAgACAAIAAgACkAXABuACkAOwBcAG4AXABuAFwAbgBVAHQAaQBsAGkAdAB5AF8AUwB1AG0AUQB1AGEAbgB0AGkAdAB5AEYAcgBvAG0AQwByAGkAdABlAHIAaQBhAFwAbgA9AEwAQQBNAEIARABBACgAXABuACAAIABDAHIAaQB0AGUAcgBpAGEAMQAsACAAQwByAGkAdABlAHIAaQBhADEAVAB5AHAAZQBBAHIAcgBhAHkALAAgAFEAdQBhAG4AdABpAHQAeQAsACAAWwBNAHUAbAB0AGkAcABsAGkAZQByAF0ALAAgAFsAQwByAGkAdABlAHIAaQBhADIAXQAsAFsAQwByAGkAdABlAHIAaQBhADIAQQByAHIAYQB5AF0ALABcAG4AIAAgAEwARQBUACgAXABuACAAIAAgACAAbQB1AGwAdABpAHAAbABpAGUAcgAsACAASQBGACgASQBTAE8ATQBJAFQAVABFAEQAKABNAHUAbAB0AGkAcABsAGkAZQByACkALAAxACwATQB1AGwAdABpAHAAbABpAGUAcgApACwAXABuACAAIAAgACAAcQB1AGEAbgB0AGkAdAB5ACwAIABRAHUAYQBuAHQAaQB0AHkAKgBNAHUAbAB0AGkAcABsAGkAZQByACwAXABuACAAIAAgACAAYwByAGkAdABlAHIAaQBhADEALAAtAC0AKABDAHIAaQB0AGUAcgBpAGEAMQBUAHkAcABlAEEAcgByAGEAeQA9AEMAcgBpAHQAZQByAGkAYQAxACkALABcAG4AIAAgACAAIABjAHIAaQB0AGUAcgBpAGEAMgAsAEkARgAoAEkAUwBPAE0ASQBUAFQARQBEACgAQwByAGkAdABlAHIAaQBhADIAKQAsADEALAAtAC0AKABDAHIAaQB0AGUAcgBpAGEAMgBBAHIAcgBhAHkAPQBDAHIAaQB0AGUAcgBpAGEAMgApACkALABcAG4AIAAgACAAIABTAFUATQBQAFIATwBEAFUAQwBUACgAYwByAGkAdABlAHIAaQBhADEAKgBjAHIAaQB0AGUAcgBpAGEAMgAqAHEAdQBhAG4AdABpAHQAeQApAFwAbgAgACAAKQBcAG4AKQA7AFwAbgBcAG4AZwBlAHQATwB2AGUAcgBsAGEAcABwAGkAbgBnAFIAZQBwAG8AcgB0AGkAbgBnAEMAeQBjAGwAZQBzAFwAbgA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAAUAByAG8AZAB1AGMAdABpAG8AbgBDAHkAYwBsAGUAUwB0AGEAcgB0ACwAUAByAG8AZAB1AGMAdABpAG8AbgBDAHkAYwBsAGUARQBuAGQALABSAGUAcABvAHIAdABpAG4AZwBDAHkAYwBsAGUAUwB0AGEAcgB0ACwAXABuACAAIAAgACAATABFAFQAKABcAG4AIAAgACAAIAAgACAAIAAgAFMALABQAHIAbwBkAHUAYwB0AGkAbwBuAEMAeQBjAGwAZQBTAHQAYQByAHQALABcAG4AIAAgACAAIAAgACAAIAAgAEUALABQAHIAbwBkAHUAYwB0AGkAbwBuAEMAeQBjAGwAZQBFAG4AZAAsAFwAbgAgACAAIAAgACAAIAAgACAAbQAsAE0ATwBOAFQASAAoAFIAZQBwAG8AcgB0AGkAbgBnAEMAeQBjAGwAZQBTAHQAYQByAHQAKQAsAFwAbgAgACAAIAAgACAAIAAgACAAZAAsAEQAQQBZACgAUgBlAHAAbwByAHQAaQBuAGcAQwB5AGMAbABlAFMAdABhAHIAdAApACwAXABuACAAIAAgACAAIAAgACAAIABQAGUAcgBpAG8AZABFAG4AZAAsAEwAQQBNAEIARABBACgAcwB0ACwARQBEAEEAVABFACgAcwB0ACwAMQAyACkALQAxACkALABcAG4AIAAgACAAIAAgACAAIAAgAEEALABTAC0AMwA2ADUALABcAG4AIAAgACAAIAAgACAAIAAgAHkAYQAsAFkARQBBAFIAKABBACkALABcAG4AIAAgACAAIAAgACAAIAAgAHkAYgAsAFkARQBBAFIAKABFACkALABcAG4AIAAgACAAIAAgACAAIAAgAGYAaQByAHMAdABZAGUAYQByACwAeQBhACsAKABQAGUAcgBpAG8AZABFAG4AZAAoAEQAQQBUAEUAKAB5AGEALABtACwAZAApACkAPAAgAFMAKQAsAFwAbgAgACAAIAAgACAAIAAgACAAbABhAHMAdABZAGUAYQByACwAeQBiAC0AKABEAEEAVABFACgAeQBiACwAbQAsAGQAKQA+ACAARQApACwAXABuACAAIAAgACAAIAAgACAAIABNAEEAWAAoADAALABsAGEAcwB0AFkAZQBhAHIALQBmAGkAcgBzAHQAWQBlAGEAcgArADEAKQBcAG4AIAAgACAAIAApAFwAbgApADsAXABuAFwAbgBnAGUAdABPAHYAZQByAGwAYQBwAHAAaQBuAGcAUgBlAHAAbwByAHQAaQBuAGcAUABlAHIAaQBvAGQAcwBcAG4APQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAFAAcgBvAGQAdQBjAHQAaQBvAG4AQwB5AGMAbABlAFMAdABhAHIAdAAsAFAAcgBvAGQAdQBjAHQAaQBvAG4AQwB5AGMAbABlAEUAbgBkACwAUgBlAHAAbwByAHQAaQBuAGcAQwB5AGMAbABlAFMAdABhAHIAdAAsAFwAbgAgACAAIAAgAEwARQBUACgAXABuACAAIAAgACAAIAAgACAAIABTACwAUAByAG8AZAB1AGMAdABpAG8AbgBDAHkAYwBsAGUAUwB0AGEAcgB0ACwAXABuACAAIAAgACAAIAAgACAAIABFACwAUAByAG8AZAB1AGMAdABpAG8AbgBDAHkAYwBsAGUARQBuAGQALABcAG4AIAAgACAAIAAgACAAIAAgAG0ALABNAE8ATgBUAEgAKABSAGUAcABvAHIAdABpAG4AZwBDAHkAYwBsAGUAUwB0AGEAcgB0ACkALABcAG4AIAAgACAAIAAgACAAIAAgAGQALABEAEEAWQAoAFIAZQBwAG8AcgB0AGkAbgBnAEMAeQBjAGwAZQBTAHQAYQByAHQAKQAsACAALwAqAGgAZQBsAHAAZQByADoAIABlAG4AZAAgAGQAYQB0AGUAIABmAG8AcgAgAGEAIAByAGUAcABvAHIAdABpAG4AZwAgAHAAZQByAGkAbwBkACAAcwB0AGEAcgB0AGkAbgBnACAAYQB0ACAAYQAgAGcAaQB2AGUAbgAgAGQAYQB0AGUAKgAvAFwAbgAgACAAIAAgACAAIAAgACAAUABlAHIAaQBvAGQARQBuAGQALABMAEEATQBCAEQAQQAoAHMAdAAsAEUARABBAFQARQAoAHMAdAAsADEAMgApAC0AMQApACwAIAAvACoAbwBuAGwAeQAgAG4AZQBlAGQAIAB0AG8AIABsAG8AbwBrACAAYgBhAGMAawAgADMANgA1ACAAZABhAHkAcwAoAG0AYQB4ACAAbwB2AGUAcgBsAGEAcAAgAHcAaQBuAGQAbwB3ACkAKgAvAFwAbgAgACAAIAAgACAAIAAgACAAQQAsAFMALQAzADYANQAsAFwAbgAgACAAIAAgACAAIAAgACAAeQBhACwAWQBFAEEAUgAoAEEAKQAsAFwAbgAgACAAIAAgACAAIAAgACAAeQBiACwAWQBFAEEAUgAoAEUAKQAsACAALwAqAGkAZgAgAHQAaABlACAAYQBuAGMAaABvAHIAIABmAG8AcgAgAHkAYQAgAGUAbgBkAHMAIABiAGUAZgBvAHIAZQAgAFMALABpAHQAIABjAGEAbgAnAHQAIABvAHYAZQByAGwAYQBwADsAIABtAG8AdgBlACAAdABvACAAbgBlAHgAdAAgAHkAZQBhAHIAKgAvAFwAbgAgACAAIAAgACAAIAAgACAAZgBpAHIAcwB0AFkAZQBhAHIALAB5AGEAKwAoAFAAZQByAGkAbwBkAEUAbgBkACgARABBAFQARQAoAHkAYQAsAG0ALABkACkAKQA8AFMAKQAsACAALwAqAGkAZgAgAHQAaABlACAAYQBuAGMAaABvAHIAIABmAG8AcgAgAHkAYgAgAHMAdABhAHIAdABzACAAYQBmAHQAZQByACAARQAsAGkAdAAgAGMAYQBuACcAdAAgAG8AdgBlAHIAbABhAHAAOwAgAG0AbwB2AGUAIAB0AG8AIABwAHIAZQB2AGkAbwB1AHMAIAB5AGUAYQByACoALwBcAG4AIAAgACAAIAAgACAAIAAgAGwAYQBzAHQAWQBlAGEAcgAsAHkAYgAtACgARABBAFQARQAoAHkAYgAsAG0ALABkACkAPgBFACkALABcAG4AIAAgACAAIAAgACAAIAAgAG4ALABNAEEAWAAoADAALABsAGEAcwB0AFkAZQBhAHIALQBmAGkAcgBzAHQAWQBlAGEAcgArADEAKQAsAFwAbgAgACAAIAAgACAAIAAgACAAeQByAHMALABTAEUAUQBVAEUATgBDAEUAKABuACwAMQAsAGYAaQByAHMAdABZAGUAYQByACwAMQApACwAXABuACAAIAAgACAAIAAgACAAIABzAHQAYQByAHQAcwAsAEQAQQBUAEUAKAB5AHIAcwAsAG0ALABkACkALABcAG4AIAAgACAAIAAgACAAIAAgAGUAbgBkAHMALABNAEEAUAAoAHMAdABhAHIAdABzACwAUABlAHIAaQBvAGQARQBuAGQAKQAsAFwAbgAgACAAIAAgACAAIAAgACAAdABhAGcALABJAEYAKABzAHQAYQByAHQAcwA9AFIAZQBwAG8AcgB0AGkAbgBnAEMAeQBjAGwAZQBTAHQAYQByAHQALABcACIAIAAoAFQAaABpAHMAIAByAGUAcABvAHIAdABpAG4AZwAgAGMAeQBjAGwAZQApAFwAIgAsAFwAIgBcACIAKQAsAFwAbgAgACAAIAAgACAAIAAgACAAcwB0AGEAcgB0AHMAVABlAHgAdAAsAFQARQBYAFQAKABzAHQAYQByAHQAcwAsAFwAIgBkAGQAIABtAG0AbQAgAHkAeQB5AHkAXAAiACkALABcAG4AIAAgACAAIAAgACAAIAAgAGUAbgBkAHMAVABlAHgAdAAsAFQARQBYAFQAKABlAG4AZABzACwAXAAiAGQAZAAgAG0AbQBtACAAeQB5AHkAeQBcACIAKQAsAFwAbgAgACAAIAAgACAAIAAgACAAcgBvAHcAcwAsAEkARgAoAG4APQAwACwAXAAiAFwAIgAsAEgAUwBUAEEAQwBLACgAcwB0AGEAcgB0AHMAVABlAHgAdAAgACYAIABcACIAIAB0AG8AIABcACIAIAAmACAAZQBuAGQAcwBUAGUAeAB0ACAAJgAgAHQAYQBnACkAKQAsAFwAbgAgACAAIAAgACAAIAAgACAAcgBvAHcAcwBcAG4AIAAgACAAIAApAFwAbgApADsAXABuAFwAbgBcAG4AVQB0AGkAbABpAHQAeQBfAEQAaQBzAHAAbABhAHkARgB1AG4AYwB0AGkAbwBuAE4AYQBtAGUAXABuAD0ATABBAE0AQgBEAEEAKABGAHUAbgBjAHQAaQBvAG4ALAAgAFQARQBYAFQAQgBFAEYATwBSAEUAKABGAE8AUgBNAFUATABBAFQARQBYAFQAKABGAHUAbgBjAHQAaQBvAG4AKQAsACAAXAAiACgAXAAiACkAKQA7AFwAbgBcAG4AVQB0AGkAbABpAHQAeQBfAEwAbwBvAGsAdQBwAE4AMgBPAEUARgBGAHIAbwBtAFAAcgBvAGQASQByAHIAaQBnAGEAdABpAG8AbgBSAGEAaQBuAGYAYQBsAGwAXABuAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABQAHIAbwBkAHUAYwB0AGkAbwBuAFMAeQBzAHQAZQBtACwAIABJAHIAcgBpAGcAYQB0AGkAbwBuAE0AZQB0AGgAbwBkACwAIABSAGEAaQBuAGYAYQBsAGwAWgBvAG4AZQAsAFwAbgAgACAAIAAgAFAAcgBvAGQAdQBjAHQAaQBvAG4AUwB5AHMAdABlAG0AQQByAHIAYQB5ACwAIABJAHIAcgBpAGcAYQB0AGkAbwBuAE0AZQB0AGgAbwBkAEEAcgByAGEAeQAsACAAUgBhAGkAbgBmAGEAbABsAFoAbwBuAGUAQQByAHIAYQB5ACwAUgBlAHQAdQByAG4AQQByAHIAYQB5ACwAXABuACAAIAAgACAATABFAFQAKABcAG4AIAAgACAAIAAgACAAIAAgAEkAcgByAGkAZwBhAHQAaQBvAG4ATQBlAHQAaABvAGQALAAgAEkARgAoAEkAcgByAGkAZwBhAHQAaQBvAG4ATQBlAHQAaABvAGQAPQBcACIATgBvAHQAIABpAHIAcgBpAGcAYQB0AGUAZABcACIALAAgAFwAIgBOAG8AdAAgAGkAcgByAGkAZwBhAHQAZQBkAFwAIgAsACAAXAAiAEEAbgB5AFwAIgApACwAXABuACAAIAAgACAAIAAgACAAIABSAGEAaQBuAGYAYQBsAGwAWgBvAG4AZQAsACAASQBGACgASQByAHIAaQBnAGEAdABpAG8AbgBNAGUAdABoAG8AZAAgAD0AIABcACIATgBvAHQAIABpAHIAcgBpAGcAYQB0AGUAZABcACIALAAgAFIAYQBpAG4AZgBhAGwAbABaAG8AbgBlACwAIABcACIAQQBuAHkAXAAiACkALABcAG4AIAAgACAAIAAgACAAIAAgAFgATABPAE8ASwBVAFAAKAAxACwAIABcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAKABQAHIAbwBkAHUAYwB0AGkAbwBuAFMAeQBzAHQAZQBtAEEAcgByAGEAeQA9AFAAcgBvAGQAdQBjAHQAaQBvAG4AUwB5AHMAdABlAG0AKQAqAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIAAoAEkAcgByAGkAZwBhAHQAaQBvAG4ATQBlAHQAaABvAGQAQQByAHIAYQB5AD0ASQByAHIAaQBnAGEAdABpAG8AbgBNAGUAdABoAG8AZAApACoAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgACgAUgBhAGkAbgBmAGEAbABsAFoAbwBuAGUAQQByAHIAYQB5AD0AUgBhAGkAbgBmAGEAbABsAFoAbwBuAGUAKQAsACAAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgAFIAZQB0AHUAcgBuAEEAcgByAGEAeQApAFwAbgAgACAAIAAgACkAXABuACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAEMAcgBvAHAAcABpAG4AZwBfAEcAZQB0AEYAcgBhAGMAVwBFAFQAXABuAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABMAGUAYQBjAGgAaQBuAGcAWgBvAG4AZQAsAFwAbgAgACAAIAAgAFAAcgBvAGQAdQBjAHQAaQBvAG4AUwB5AHMAdABlAG0ALABcAG4AIAAgACAAIABMAGUAYQBjAGgAaQBuAGcAWgBvAG4AZQBMAG8AbwBrAHUAcAAsAFwAbgAgACAAIAAgAEwAZQBhAGMAaABpAG4AZwBaAG8AbgBlAEYAcgBhAGMAVwBFAFQATABvAG8AawB1AHAALABcAG4AIAAgACAAIABQAHIAbwBkAHUAYwB0AGkAbwBuAFMAeQBzAHQAZQBtAEwAbwBvAGsAdQBwACwAXABuACAAIAAgACAAUAByAG8AZAB1AGMAdABpAG8AbgBTAHkAcwB0AGUAbQBGAHIAYQBjAFcARQBUAEwAbwBvAGsAdQBwACwAXABuACAAIAAgACAATABFAFQAKABcAG4AIAAgACAAIAAgACAAIAAgAEwAZQBhAGMAaABpAG4AZwBaAG8AbgBlAEYAcgBhAGMAVwBFAFQALAAgAFwAbgAgACAAIAAgACAAIAAgACAAQwBvAG0AbQBvAG4AXwBJAG4AcAB1AHQARgB1AG4AYwB0AGkAbwBuAHMALgBVAHQAaQBsAGkAdAB5AF8ATABvAG8AawB1AHAAVgBhAGwAdQBlAEkAbgBUAGEAYgBsAGUATgB1AG0AYgBlAHIAKABcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAATABlAGEAYwBoAGkAbgBnAFoAbwBuAGUALABMAGUAYQBjAGgAaQBuAGcAWgBvAG4AZQBMAG8AbwBrAHUAcAAsAEwAZQBhAGMAaABpAG4AZwBaAG8AbgBlAEYAcgBhAGMAVwBFAFQATABvAG8AawB1AHAAXABuACAAIAAgACAAIAAgACAAIAApACwAXABuACAAIAAgACAAIAAgACAAIABQAHIAbwBkAHUAYwB0AGkAbwBuAFMAeQBzAHQAZQBtAEYAcgBhAGMAVwBFAFQALAAgAFwAbgAgACAAIAAgACAAIAAgACAAQwBvAG0AbQBvAG4AXwBJAG4AcAB1AHQARgB1AG4AYwB0AGkAbwBuAHMALgBVAHQAaQBsAGkAdAB5AF8ATABvAG8AawB1AHAAVgBhAGwAdQBlAEkAbgBUAGEAYgBsAGUATgB1AG0AYgBlAHIAKABcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAUAByAG8AZAB1AGMAdABpAG8AbgBTAHkAcwB0AGUAbQAsAFAAcgBvAGQAdQBjAHQAaQBvAG4AUwB5AHMAdABlAG0ATABvAG8AawB1AHAALABQAHIAbwBkAHUAYwB0AGkAbwBuAFMAeQBzAHQAZQBtAEYAcgBhAGMAVwBFAFQATABvAG8AawB1AHAAXABuACAAIAAgACAAIAAgACAAIAApACwAXABuACAAIAAgACAAIAAgACAAIABJAEYAKABMAGUAYQBjAGgAaQBuAGcAWgBvAG4AZQBGAHIAYQBjAFcARQBUACAAKwAgAFAAcgBvAGQAdQBjAHQAaQBvAG4AUwB5AHMAdABlAG0ARgByAGEAYwBXAEUAVAA+ADAALAAgADEALAAgADAAKQBcAG4AIAAgACAAIAApACkAOwBcAG4AXABuAFwAbgBVAHQAaQBsAGkAdAB5AF8AQwBvAG4AdgBlAHIAdABTAHQAYQB0AGUAQwBvAG0AbQBvAG4ATgBhAG0AZQBUAG8AQQBiAGIAcgBlAHYAaQBhAHQAaQBvAG4AXABuAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABTAHQAYQB0AGUAQwBvAG0AbQBvAG4ATgBhAG0AZQAsAFwAbgAgACAAIAAgAFMAdABhAHQAZQBDAG8AbQBtAG8AbgBOAGEAbQBlAEEAcgByAGEAeQAsACAAUwB0AGEAdABlAEEAYgBiAHIAZQB2AGkAYQB0AGkAbwBuAEEAcgByAGEAeQAsAFwAbgAgACAAIAAgAFgATABPAE8ASwBVAFAAKABTAHQAYQB0AGUAQwBvAG0AbQBvAG4ATgBhAG0AZQAsACAAUwB0AGEAdABlAEMAbwBtAG0AbwBuAE4AYQBtAGUAQQByAHIAYQB5ACwAIABTAHQAYQB0AGUAQQBiAGIAcgBlAHYAaQBhAHQAaQBvAG4AQQByAHIAYQB5ACwAIABcACIAXAAiACkAXABuACkAOwBcAG4AXABuAFUAdABpAGwAaQB0AHkAXwBTAG8AdQByAGMAZQBIAHkAcABlAHIAbABpAG4AawBcAG4APQBMAEEATQBCAEQAQQAoAFQAYQByAGcAZQB0AEMAZQBsAGwALABcAG4AIAAgAEwARQBUACgAXABuACAAIAAgACAAcwBoACwAIABUAEUAWABUAEEARgBUAEUAUgAoAEMARQBMAEwAKABcACIAZgBpAGwAZQBuAGEAbQBlAFwAIgAsACAAVABhAHIAZwBlAHQAQwBlAGwAbAApACwAIABcACIAXQBcACIAKQAsAFwAbgAgACAAIAAgAGEAZABkAHIALAAgAEMARQBMAEwAKABcACIAYQBkAGQAcgBlAHMAcwBcACIALAAgAFQAYQByAGcAZQB0AEMAZQBsAGwAKQAsAFwAbgAgACAAIAAgAFwAIgAjACcAXAAiACAAJgAgAHMAaAAgACYAIABcACIAJwAhAFwAIgAgACYAIABhAGQAZAByAFwAbgAgACAAKQBcAG4AKQA7AFwAbgBcAG4AVQB0AGkAbABpAHQAeQBfAFMAbwB1AHIAYwBlAEgAeQBwAGUAcgBsAGkAbgBrAEQAaQBmAGYAZQByAGUAbgB0AFMAaABlAGUAdABcAG4APQBMAEEATQBCAEQAQQAoAFQAYQByAGcAZQB0AEMAZQBsAGwALABcAG4AIAAgAEwARQBUACgAXABuACAAIAAgACAAcwBoACwAIABUAEUAWABUAEEARgBUAEUAUgAoAEMARQBMAEwAKABcACIAZgBpAGwAZQBuAGEAbQBlAFwAIgAsACAAVABhAHIAZwBlAHQAQwBlAGwAbAApACwAIABcACIAXQBcACIAKQAsAFwAbgAgACAAIAAgAGEAZABkAHIALAAgAEMARQBMAEwAKABcACIAYQBkAGQAcgBlAHMAcwBcACIALAAgAFQAYQByAGcAZQB0AEMAZQBsAGwAKQAsAFwAbgAgACAAIAAgAFwAIgAjAFwAIgAgACYAIABhAGQAZAByAFwAbgAgACAAKQBcAG4AKQA7AFwAbgBcAG4AVQB0AGkAbABpAHQAeQBfAEQAaQBzAHAAbABhAHkAQQByAGcAdQBtAGUAbgB0AHMAXwAxAF8AMgBcAG4APQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAEEAcgBnAHUAbQBlAG4AdABzAEEAcgByAGEAeQAsAFwAbgAgACAAIAAgAEMASABPAE8AUwBFAEMATwBMAFMAKABBAHIAZwB1AG0AZQBuAHQAcwBBAHIAcgBhAHkALAAgADEALAAgADIAKQBcAG4AKQA7AFwAbgBcAG4AVQB0AGkAbABpAHQAeQBfAEQAaQBzAHAAbABhAHkAQQByAGcAdQBtAGUAbgB0AHMAXwAzAF8ANABcAG4APQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAEEAcgBnAHUAbQBlAG4AdABzAEEAcgByAGEAeQAsAFwAbgAgACAAIAAgAEMASABPAE8AUwBFAEMATwBMAFMAKABBAHIAZwB1AG0AZQBuAHQAcwBBAHIAcgBhAHkALAAgADMALAAgADQAKQBcAG4AKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBHAGUAdABNAEMARgBUAGUAbQBwAGUAcgBhAHQAdQByAGUAWgBvAG4AZQBcAG4APQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAFQAZQBtAHAAZQByAGEAdAB1AHIAZQAsACAATQBNAFMALAAgAFQAZQBtAHAAZQByAGEAdAB1AHIAZQBBAHIAcgBhAHkALAAgAE0ATQBTAEEAcgByAGEAeQAsACAAUgBlAHQAdQByAG4AQQByAHIAYQB5ACwAXABuACAAIAAgACAAWABMAE8ATwBLAFUAUAAoAFwAbgAgACAAIAAgACAAIAAgACAATQBFAEQASQBBAE4AKABcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAVABlAG0AcABlAHIAYQB0AHUAcgBlACwAIABcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAATQBJAE4AKABUAGUAbQBwAGUAcgBhAHQAdQByAGUAQQByAHIAYQB5ACkALAAgAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIABNAEEAWAAoAFQAZQBtAHAAZQByAGEAdAB1AHIAZQBBAHIAcgBhAHkAKQBcAG4AIAAgACAAIAAgACAAIAAgACkALABcAG4AIAAgACAAIAAgACAAIAAgAFQAZQBtAHAAZQByAGEAdAB1AHIAZQBBAHIAcgBhAHkALABcAG4AIAAgACAAIAAgACAAIAAgAFgATABPAE8ASwBVAFAAKABNAE0AUwAsACAATQBNAFMAQQByAHIAYQB5ACwAIABSAGUAdAB1AHIAbgBBAHIAcgBhAHkAKQBcAG4AIAAgACAAIAApAFwAbgApADsAXABuAFwAbgBcAG4AVQB0AGkAbABpAHQAeQBfAFIAZQBzAHUAbAB0AHMASQB0AGUAbQBGAHIAbwBtAEUAcQB1AGEAdABpAG8AbgBUAGkAdABsAGUAQQBuAGQAUwBvAHUAcgBjAGUAXABuAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABUAGkAdABsAGUAQwBlAGwAbAAsACAAUwBvAHUAcgBjAGUAQwBlAGwAbAAsAFwAbgAgACAAIAAgAFMAVQBCAFMAVABJAFQAVQBUAEUAKABMAEUARgBUACgAUwBvAHUAcgBjAGUAQwBlAGwAbAAsACAARgBJAE4ARAAoAFwAIgAsAFwAIgAsACAAUwBvAHUAcgBjAGUAQwBlAGwAbAApACAALQAxACkALAAgAFwAIgBWAEUARQBSAEcAIAAyADAAMgA2ADoAIABcACIALAAgAFwAIgBcACIAKQAgACYAIABcACIAIABcACIAIAAmACAAVABpAHQAbABlAEMAZQBsAGwAXABuACkAOwAiAH0ALAB7ACIAcABhAHQAaAAiADoAIgAvAHAAcgBvAGoAZQBjAHQAcwAvAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAiACwAIgB0AGUAeAB0ACIAOgAiAC8AKgBcAG4APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQBcAG4APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQBcAG4AUwBvAHUAcgBjAGUAIABkAGEAdABhACAAdABoAGEAdAAgAGkAcwAgAGMAbwBtAG0AbwBuACAAYQBjAHIAbwBzAHMAIABhAGwAbAAgAGUAbgB0AGUAcgBwAHIAaQBzAGUAIAB0AHkAcABlAHMAXABuAEUAeABjAGUAbAAgAG0AbwBkAHUAbABlACAAbgBhAG0AZQA6ACAAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAFwAbgA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AFwAbgA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AFwAbgAqAC8AXABuAFwAbgAvACoAXABuAD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQBcAG4APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AFwAbgBTAG8AdQByAGMAZQA6ACAATgBhAHQAaQBvAG4AYQBsACAASQBuAHYAZQBuAHQAbwByAHkAIABSAGUAcABvAHIAdAAgADIAMAAyADMAIABWAG8AbAB1AG0AZQAgADEAXABuAE4ASQBSAF8AMgAwADIAMwBfAFYAbwBsADEAXABuAD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQBcAG4APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AFwAbgAqAC8AXABuAFwAbgAvACoAIABcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGUAbgBzAGkAdAB5AE8AZgBNAGUAdABoAGEAbgBlAFwAbgBwACAAPQAgAGQAZQBuAHMAaQB0AHkAIABvAGYAIABtAGUAdABoAGEAbgBlACAAKAAwAC4ANgA3ADgANAAgAGsAZwAvAG0AMwApAFwAbgBUAGEAawBlAG4AIABmAHIAbwBtACAAdABoAGUAIABOAGEAdABpAG8AbgBhAGwAIABHAHIAZQBlAG4AaABvAHUAcwBlACAAYQBuAGQAIABFAG4AZQByAGcAeQAgAFIAZQBwAG8AcgB0AGkAbgBnACAAXABuACgATQBlAGEAcwB1AHIAZQBtAGUAbgB0ACkAIABEAGUAdABlAHIAbQBpAG4AYQB0AGkAbwBuACAAMgAwADAAOABcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgAqAC8AXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGUAbgBzAGkAdAB5AE8AZgBNAGUAdABoAGEAbgBlAF8AVABpAHQAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBwACAAPQAgAGQAZQBuAHMAaQB0AHkAIABvAGYAIABtAGUAdABoAGEAbgBlAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGUAbgBzAGkAdAB5AE8AZgBNAGUAdABoAGEAbgBlAF8AVQBuAGkAdABcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAawBnAC8AbQAzAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGUAbgBzAGkAdAB5AE8AZgBNAGUAdABoAGEAbgBlAF8AUwBvAHUAcgBjAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAE4AYQB0AGkAbwBuAGEAbAAgAEkAbgB2AGUAbgB0AG8AcgB5ACAAUgBlAHAAbwByAHQAIAAyADAAMgAzACAAVgBvAGwAdQBtAGUAIAAxADoAIABFAHEAdQBhAHQAaQBvAG4AcwAgADMALgBCAC4AMQBhAF8AMgAsACAAMwAuAEIALgAxAGMAXwAyACwAIAAzAC4AQgAuADMAXwAxACwAIAAzAC4AQgAuADQAZwBfADIAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEQAZQBuAHMAaQB0AHkATwBmAE0AZQB0AGgAYQBuAGUAXwBEAGEAdABhAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoADAALgA2ADcAOAA0ACkAOwBcAG4AXABuAC8AKgAgAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEMAbwBuAHYAZQByAHQATgAyAG8ARQBsAGUAbQBlAG4AdABhAGwAVABvAE0AbwBsAGUAYwB1AGwAYQByAEMAZwBcAG4AQwBnACAAPQAgADQANAAvADIAOAAgAGYAYQBjAHQAbwByACAAdABvACAAYwBvAG4AdgBlAHIAdAAgAGUAbABlAG0AZQBuAHQAYQBsACAAbQBhAHMAcwAgAG8AZgAgAE4AMgBPACAAdABvACAAbQBvAGwAZQBjAHUAbABhAHIAIABtAGEAcwBzAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuACoALwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEMAbwBuAHYAZQByAHQATgAyAG8ARQBsAGUAbQBlAG4AdABhAGwAVABvAE0AbwBsAGUAYwB1AGwAYQByAEMAZwBfAFQAaQB0AGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIARgBhAGMAdABvAHIAIAB0AG8AIABjAG8AbgB2AGUAcgB0ACAAZQBsAGUAbQBlAG4AdABhAGwAIABtAGEAcwBzACAAbwBmACAATgAyAE8AIAB0AG8AIABtAG8AbABlAGMAdQBsAGEAcgAgAG0AYQBzAHMAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEMAbwBuAHYAZQByAHQATgAyAG8ARQBsAGUAbQBlAG4AdABhAGwAVABvAE0AbwBsAGUAYwB1AGwAYQByAEMAZwBfAFYAYQByAGkAYQBiAGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAQwBnAE4AMgBPAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBDAG8AbgB2AGUAcgB0AE4AMgBvAEUAbABlAG0AZQBuAHQAYQBsAFQAbwBNAG8AbABlAGMAdQBsAGEAcgBDAGcAXwBVAG4AaQB0AFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBmAGEAYwB0AG8AcgBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQwBvAG4AdgBlAHIAdABOADIAbwBFAGwAZQBtAGUAbgB0AGEAbABUAG8ATQBvAGwAZQBjAHUAbABhAHIAQwBnAF8AUwBvAHUAcgBjAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAE4AYQB0AGkAbwBuAGEAbAAgAEkAbgB2AGUAbgB0AG8AcgB5ACAAUgBlAHAAbwByAHQAIAAyADAAMgAzACAAVgBvAGwAdQBtAGUAIAAxAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBDAG8AbgB2AGUAcgB0AE4AMgBvAEUAbABlAG0AZQBuAHQAYQBsAFQAbwBNAG8AbABlAGMAdQBsAGEAcgBDAGcAXwBEAGEAdABhAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoADQANAAvADIAOAApADsAXABuAFwAbgAvACoAIABcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBDAG8AbgB2AGUAcgB0AEcAYQBzAEUAbABlAG0AZQBuAHQAYQBsAFQAbwBNAG8AbABlAGMAdQBsAGEAcgBcAG4ARgBhAGMAdABvAHIAIAB0AG8AIABjAG8AbgB2AGUAcgB0ACAAZQBsAGUAbQBlAG4AdABhAGwAIABtAGEAcwBzACAAbwBmACAAZwBhAHMAIAB0AG8AIABtAG8AbABlAGMAdQBsAGEAcgAgAG0AYQBzAHMAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AKgAvAFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQwBvAG4AdgBlAHIAdABHAGEAcwBFAGwAZQBtAGUAbgB0AGEAbABUAG8ATQBvAGwAZQBjAHUAbABhAHIAXwBUAGkAdABsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAEYAYQBjAHQAbwByACAAdABvACAAYwBvAG4AdgBlAHIAdAAgAGUAbABlAG0AZQBuAHQAYQBsACAAbQBhAHMAcwAgAG8AZgAgAGcAYQBzACAAdABvACAAbQBvAGwAZQBjAHUAbABhAHIAIABtAGEAcwBzAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBDAG8AbgB2AGUAcgB0AEcAYQBzAEUAbABlAG0AZQBuAHQAYQBsAFQAbwBNAG8AbABlAGMAdQBsAGEAcgBfAFYAYQByAGkAYQBiAGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAQwBnAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBDAG8AbgB2AGUAcgB0AEcAYQBzAEUAbABlAG0AZQBuAHQAYQBsAFQAbwBNAG8AbABlAGMAdQBsAGEAcgBfAFUAbgBpAHQAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAGYAYQBjAHQAbwByAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBDAG8AbgB2AGUAcgB0AEcAYQBzAEUAbABlAG0AZQBuAHQAYQBsAFQAbwBNAG8AbABlAGMAdQBsAGEAcgBfAFMAbwB1AHIAYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBYAFgAWABYAFgAWABYAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBDAG8AbgB2AGUAcgB0AEcAYQBzAEUAbABlAG0AZQBuAHQAYQBsAFQAbwBNAG8AbABlAGMAdQBsAGEAcgBfAEQAYQB0AGEAXABuACAAIAA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAATQBBAEsARQBBAFIAUgBBAFkAKAA4ACwAIAA0ACwAIABcAG4AIAAgACAAIAAgACAATABBAE0AQgBEAEEAKAByACwAYwAsACAAXABuACAAIAAgACAAIAAgACAAIABJAE4ARABFAFgAKAB7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBHAGEAcwBcACIALAAgAFwAIgBDAG8AbgB2AGUAcgBzAGkAbwBuACAAZgBhAGMAdABvAHIAXAAiACwAIABcACIAQwBvAG4AdgBlAHIAcwBpAG8AbgAgAGYAYQBjAHQAbwByACAAMQBcACIALAAgAFwAIgBDAG8AbgB2AGUAcgBzAGkAbwBuACAAZgBhAGMAdABvAHIAIAAyAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBDAE8AMgBcACIALAAgAFwAIgA0ADQALwAxADIAXAAiACwAIAA0ADQALAAgADEAMgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBDAEgANABcACIALAAgAFwAIgAxADYALwAxADIAXAAiACwAIAAxADYALAAgADEAMgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBOADIATwBcACIALAAgAFwAIgA0ADQALwAyADgAXAAiACwAIAA0ADQALAAgADIAOAA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBOAG8AeABcACIALAAgAFwAIgA0ADYALwAxADQAXAAiACwAIAA0ADYALAAgADEANAA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBDAE8AXAAiACwAIABcACIAMgA4AC8AMQAyAFwAIgAsACAAMgA4ACwAIAAxADIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAQwBPADIAIABMAGkAbQBlAFwAIgAsACAAXAAiADQANAAvADEAMgBcACIALAAgADQANAAsACAAMQAyADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAE4ATQBWAE8AQwBcACIALAAgAFwAIgAxADQALwAxADIAXAAiACwAIAAxADQALAAgADEAMgBcAG4AIAAgACAAIAAgACAAIAAgAH0ALAAgAHIALAAgAGMAKQBcAG4AIAAgACAAIAAgACAAKQBcAG4AIAAgACAAIAApAFwAbgAgACAAKQA7AFwAbgBcAG4ALwAqACAAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARwBXAFAATgAyAE8AXABuAEcAbABvAGIAYQBsACAAdwBhAHIAbQBpAG4AZwAgAHAAbwB0AGUAbgB0AGkAYQBsACAAZgBvAHIAIABnAHIAZQBlAG4AaABvAHUAcwBlACAAZwBhAHMAZQBzAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuACoALwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEcAVwBQAF8AVABpAHQAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBHAGwAbwBiAGEAbAAgAHcAYQByAG0AaQBuAGcAIABwAG8AdABlAG4AdABpAGEAbAAgAGYAbwByACAAZwByAGUAZQBuAGgAbwB1AHMAZQAgAGcAYQBzAGUAcwBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARwBXAFAAXwBWAGEAcgBpAGEAYgBsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAEcAVwBQAE4AMgBPAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBHAFcAUABfAFUAbgBpAHQAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAGYAYQBjAHQAbwByAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBHAFcAUABfAFMAbwB1AHIAYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBYAFgAWABYAFgAWABYAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBHAFcAUABfAEQAYQB0AGEAXABuACAAIAA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAATQBBAEsARQBBAFIAUgBBAFkAKAA4ACwAIAAyACwAIABcAG4AIAAgACAAIAAgACAATABBAE0AQgBEAEEAKAByACwAYwAsACAAXABuACAAIAAgACAAIAAgACAAIABJAE4ARABFAFgAKAB7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBHAGEAcwBcACIALAAgAFwAIgBDAE8AMgAtAGUAIABmAGEAYwB0AG8AcgBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAQwBPADIAXAAiACwAIAAxADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEMASAA0AFwAIgAsACAAMgA4ADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAE4AMgBPAFwAIgAsACAAMgA2ADUAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAQwBGADQAXAAiACwAIAA2ADYAMwAwADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEMAMgBGADYAXAAiACwAIAAxADIAMgAwADAAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAUwBGADYAXAAiACwAIAAyADIAOAAwADAAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIATgBGADMAXAAiACwAIAAxADcAMgAwADAAXABuACAAIAAgACAAIAAgACAAIAB9ACwAIAByACwAIABjACkAXABuACAAIAAgACAAIAAgACkAXABuACAAIAAgACAAKQBcAG4AIAAgACkAOwBcAG4AXABuAFwAbgAvACoAIABcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBBAHUAcwB0AHIAYQBsAGkAYQBuAFMAdABhAHQAZQBzAFQAZQByAHIAaQB0AG8AcgBpAGUAcwBcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgAqAC8AXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBBAHUAcwB0AHIAYQBsAGkAYQBuAFMAdABhAHQAZQBzAFQAZQByAHIAaQB0AG8AcgBpAGUAcwBfAFQAaQB0AGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAQQB1AHMAdAByAGEAbABpAGEAbgAgAHMAdABhAHQAZQBzACAAYQBuAGQAIAB0AGUAcgByAGkAdABvAHIAaQBlAHMAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEEAdQBzAHQAcgBhAGwAaQBhAG4AUwB0AGEAdABlAHMAVABlAHIAcgBpAHQAbwByAGkAZQBzAF8AVgBhAHIAaQBhAGIAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQQB1AHMAdAByAGEAbABpAGEAbgBTAHQAYQB0AGUAcwBUAGUAcgByAGkAdABvAHIAaQBlAHMAXwBVAG4AaQB0AFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQQB1AHMAdAByAGEAbABpAGEAbgBTAHQAYQB0AGUAcwBUAGUAcgByAGkAdABvAHIAaQBlAHMAXwBTAG8AdQByAGMAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEEAdQBzAHQAcgBhAGwAaQBhAG4AUwB0AGEAdABlAHMAVABlAHIAcgBpAHQAbwByAGkAZQBzAF8ARABhAHQAYQBcAG4AIAAgACAAPQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAE0AQQBLAEUAQQBSAFIAQQBZACgAOQAsACAAMwAsACAAXABuACAAIAAgACAAIAAgAEwAQQBNAEIARABBACgAcgAsAGMALAAgAFwAbgAgACAAIAAgACAAIAAgACAASQBOAEQARQBYACgAewBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAUwB0AGEAdABlAC8AVABlAHIAcgBpAHQAbwByAHkAXAAiACwAIABcACIAQwBvAG0AbQBvAG4AIABOAGEAbQBlAFwAIgAsACAAXAAiAEEAYgBiAHIAZQB2AGkAYQB0AGkAbwBuAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBOAGUAdwAgAFMAbwB1AHQAaAAgAFcAYQBsAGUAcwBcACIALAAgAFwAIgBOAGUAdwAgAFMAbwB1AHQAaAAgAFcAYQBsAGUAcwBcACIALAAgAFwAIgBOAFMAVwBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAQQB1AHMAdAByAGEAbABpAGEAbgAgAEMAYQBwAGkAdABhAGwAIABUAGUAcgByAGkAdABvAHIAeQBcACIALAAgAFwAIgBBAEMAVABcACIALAAgAFwAIgBBAEMAVABcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVgBpAGMAdABvAHIAaQBhAFwAIgAsACAAXAAiAFYAaQBjAHQAbwByAGkAYQBcACIALAAgAFwAIgBWAEkAQwBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAUQB1AGUAZQBuAHMAbABhAG4AZABcACIALAAgAFwAIgBRAHUAZQBlAG4AcwBsAGEAbgBkAFwAIgAsACAAXAAiAFEATABEAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBTAG8AdQB0AGgAIABBAHUAcwB0AHIAYQBsAGkAYQBcACIALAAgAFwAIgBTAG8AdQB0AGgAIABBAHUAcwB0AHIAYQBsAGkAYQBcACIALAAgAFwAIgBTAEEAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFcAZQBzAHQAZQByAG4AIABBAHUAcwB0AHIAYQBsAGkAYQBcACIALAAgAFwAIgBXAGUAcwB0AGUAcgBuACAAQQB1AHMAdAByAGEAbABpAGEAXAAiACwAIABcACIAVwBBAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBUAGEAcwBtAGEAbgBpAGEAXAAiACwAIABcACIAVABhAHMAbQBhAG4AaQBhAFwAIgAsACAAXAAiAFQAQQBTAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBOAG8AcgB0AGgAZQByAG4AIABUAGUAcgByAGkAdABvAHIAeQBcACIALAAgAFwAIgBOAG8AcgB0AGgAZQByAG4AIABUAGUAcgByAGkAdABvAHIAeQBcACIALAAgAFwAIgBOAFQAXAAiAFwAbgAgACAAIAAgACAAIAAgACAAfQAsACAAcgAsACAAYwApAFwAbgAgACAAIAAgACAAIAApAFwAbgAgACAAIAAgACkAXABuACAAIAApADsAXABuAFwAbgAvACoAIABcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBXAEEAUwBBADQAQQByAGUAYQBzAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuACoALwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFcAQQBTAEEANABBAHIAZQBhAHMAXwBUAGkAdABsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAEEAQgBTACAAUwB0AGEAdABpAHMAdABjAGEAbAAgAEEAcgBlAGEAcwAgAEwAZQB2AGUAbAAgADQAIAAtACAAVwBlAHMAdABlAHIAbgAgAEEAdQBzAHQAcgBhAGwAaQBhAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBXAEEAUwBBADQAQQByAGUAYQBzAF8AVgBhAHIAaQBhAGIAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AVwBBAFMAQQA0AEEAcgBlAGEAcwBfAFUAbgBpAHQAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBXAEEAUwBBADQAQQByAGUAYQBzAF8AUwBvAHUAcgBjAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAEEAdQBzAHQAcgBhAGwAaQBhAG4AIABCAHUAcgBlAGEAdQAgAG8AZgAgAFMAdABhAHQAaQBzAHQAaQBjAHMAIAAoAEEAQgBTACkAIAAtACAAUwB0AGEAdABpAHMAdABpAGMAYQBsACAAQQByAGUAYQBzACAATABlAHYAZQBsACAAMgAgAC0AIAAyADAAMgAxACAALQAgAFMAaABhAHAAZQBmAGkAbABlAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBXAEEAUwBBADQAQQByAGUAYQBzAF8ARABhAHQAYQBcAG4AIAAgACAAPQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAE0AQQBLAEUAQQBSAFIAQQBZACgAMQAxACwAIAAxACwAIABcAG4AIAAgACAAIAAgACAATABBAE0AQgBEAEEAKAByACwAYwAsACAAXABuACAAIAAgACAAIAAgACAAIABJAE4ARABFAFgAKAB7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBTAEEAIAA0ACAATgBhAG0AZQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAQgB1AG4AYgB1AHIAeQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIATQBhAG4AZAB1AHIAYQBoAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBQAGUAcgB0AGgAIAAtACAASQBuAG4AZQByAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBQAGUAcgB0AGgAIAAtACAATgBvAHIAdABoACAARQBhAHMAdABcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAUABlAHIAdABoACAALQAgAE4AbwByAHQAaAAgAFcAZQBzAHQAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFAAZQByAHQAaAAgAC0AIABTAG8AdQB0AGgAIABFAGEAcwB0AFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBQAGUAcgB0AGgAIAAtACAAUwBvAHUAdABoACAAVwBlAHMAdABcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVwBlAHMAdABlAHIAbgAgAEEAdQBzAHQAcgBhAGwAaQBhACAALQAgAFcAaABlAGEAdAAgAEIAZQBsAHQAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFcAZQBzAHQAZQByAG4AIABBAHUAcwB0AHIAYQBsAGkAYQAgAC0AIABPAHUAdABiAGEAYwBrACAAKABOAG8AcgB0AGgAKQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVwBlAHMAdABlAHIAbgAgAEEAdQBzAHQAcgBhAGwAaQBhACAALQAgAE8AdQB0AGIAYQBjAGsAIAAoAFMAbwB1AHQAaAApAFwAIgBcAG4AIAAgACAAIAAgACAAIAAgAH0ALAAgAHIALAAgAGMAKQBcAG4AIAAgACAAIAAgACAAKQBcAG4AIAAgACAAIAApAFwAbgAgACAAKQA7AFwAbgBcAG4ALwAqACAAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AVwBlAHQAQQBuAGQARAByAHkAWgBvAG4AZQBzAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuACoALwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFcAZQB0AEEAbgBkAEQAcgB5AFoAbwBuAGUAcwBfAFQAaQB0AGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAVgBFAEUAUgBHACAAQQB1AHMAdAByAGEAbABpAGEAbgAgAHcAZQB0ACAAYQBuAGQAIABkAHIAeQAgAHoAbwBuAGUAcwBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AVwBlAHQAQQBuAGQARAByAHkAWgBvAG4AZQBzAF8AVgBhAHIAaQBhAGIAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AVwBlAHQAQQBuAGQARAByAHkAWgBvAG4AZQBzAF8AVQBuAGkAdABcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFcAZQB0AEEAbgBkAEQAcgB5AFoAbwBuAGUAcwBfAFMAbwB1AHIAYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBWAEUARQBSAEcAIAAyADAAMgA2ADoAIABUAGEAYgBsAGUAIAAxAC4AMgA6ACAAVAByAGEAbgBzAGwAYQB0AGkAbgBnACAAYwBsAGkAbQBhAHQAZQAgAHoAbwBuAGUAcwAgAHQAbwAgAHcAZQB0ACAAYQBuAGQAIABkAHIAeQAgAHoAbwBuAGUAcwBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AVwBlAHQAQQBuAGQARAByAHkAWgBvAG4AZQBzAF8AVgBhAHIAaQBhAHQAaQBvAG4AXABuACAAIAAgAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABNAEEASwBFAEEAUgBSAEEAWQAoADMALAAgADEALAAgAFwAbgAgACAAIAAgACAAIABMAEEATQBCAEQAQQAoAHIALABjACwAIABcAG4AIAAgACAAIAAgACAAIAAgAEkATgBEAEUAWAAoAHsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFYAQQBSAEkAQQBUAEkATwBOACAATwBGACAAUwBPAFUAUgBDAEUAIABEAEEAVABBADoAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEEAZABkAGUAZAAgAHcAYQByAG0AIAAvACAAYwBvAG8AbAAgAHQAZQBtAHAAZQByAGEAdABlACAAbQBvAGkAcwB0ACAALwAgAGQAcgB5ACAALQAgAGwAbwB3ACAAZgByAG8AcwB0ACAAYQBuAGQAIABoAGkAZwBoACAAdABlAG0AcAAgAGMAbABhAHMAcwBlAHMAIAB0AG8AIABhAGMAYwBvAG0AbQBvAGQAYQB0AGUAIABjAGwAaQBtAGEAdABlACAAcwBjAGUAbgBhAHIAaQBvAHMAIABlAHgAYwBsAHUAZABlAGQAIABiAHkAIABWAEUARQBSAEcAIABjAHIAaQB0AGUAcgBpAGEALgBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIARgBpAHgAZQBkACAAdAB5AHAAbwAgAC0AIABDAGgAYQBuAGcAZQBkACAAJwBGAHIAeQAnACAAdABvACAAJwBEAHIAeQAnAC4AXAAiAFwAbgAgACAAIAAgACAAIAAgACAAfQAsACAAcgAsACAAYwApAFwAbgAgACAAIAAgACAAIAApAFwAbgAgACAAIAAgACkAXABuACAAIAApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBXAGUAdABBAG4AZABEAHIAeQBaAG8AbgBlAHMAXwBEAGEAdABhAFwAbgAgACAAIAA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAATQBBAEsARQBBAFIAUgBBAFkAKAAxADUALAAgADIALAAgAFwAbgAgACAAIAAgACAAIABMAEEATQBCAEQAQQAoAHIALABjACwAIABcAG4AIAAgACAAIAAgACAAIAAgAEkATgBEAEUAWAAoAHsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEMAbABpAG0AYQB0AGUAIABaAG8AbgBlAFwAIgAsACAAXAAiAFcAZQB0ACAAbwByACAARAByAHkAIABaAG8AbgBlAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBUAHIAbwBwAGkAYwBhAGwAIABtAG8AbgB0AGEAbgBlAFwAIgAsACAAXAAiAFcAZQB0ACAAYwBsAGkAbQBhAHQAZQAgAHoAbwBuAGUAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFQAcgBvAHAAaQBjAGEAbAAgAHcAZQB0AFwAIgAsACAAXAAiAFcAZQB0ACAAYwBsAGkAbQBhAHQAZQAgAHoAbwBuAGUAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFQAcgBvAHAAaQBjAGEAbAAgAG0AbwBpAHMAdABcACIALAAgAFwAIgBXAGUAdAAgAGMAbABpAG0AYQB0AGUAIAB6AG8AbgBlAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBUAHIAbwBwAGkAYwBhAGwAIABkAHIAeQBcACIALAAgAFwAIgBEAHIAeQAgAGMAbABpAG0AYQB0AGUAIAB6AG8AbgBlAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBXAGEAcgBtACAAdABlAG0AcABlAHIAYQB0AGUAIABtAG8AaQBzAHQAXAAiACwAIABcACIAVwBlAHQAIABjAGwAaQBtAGEAdABlACAAegBvAG4AZQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVwBhAHIAbQAgAHQAZQBtAHAAZQByAGEAdABlACAAZAByAHkAXAAiACwAIABcACIARAByAHkAIABjAGwAaQBtAGEAdABlACAAegBvAG4AZQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAQwBvAG8AbAAgAHQAZQBtAHAAZQByAGEAdABlACAAbQBvAGkAcwB0AFwAIgAsACAAXAAiAFcAZQB0ACAAYwBsAGkAbQBhAHQAZQAgAHoAbwBuAGUAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEMAbwBvAGwAIAB0AGUAbQBwAGUAcgBhAHQAZQAgAGQAcgB5AFwAIgAsACAAXAAiAEQAcgB5ACAAYwBsAGkAbQBhAHQAZQAgAHoAbwBuAGUAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFcAYQByAG0AIAB0AGUAbQBwAGUAcgBhAHQAZQAgAG0AbwBpAHMAdAAgAC0AIABsAG8AdwAgAGYAcgBvAHMAdABcACIALAAgAFwAIgBXAGUAdAAgAGMAbABpAG0AYQB0AGUAIAB6AG8AbgBlAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBXAGEAcgBtACAAdABlAG0AcABlAHIAYQB0AGUAIABkAHIAeQAgAC0AIABsAG8AdwAgAGYAcgBvAHMAdABcACIALAAgAFwAIgBEAHIAeQAgAGMAbABpAG0AYQB0AGUAIAB6AG8AbgBlAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBXAGEAcgBtACAAdABlAG0AcABlAHIAYQB0AGUAIABtAG8AaQBzAHQAIAAtACAAaABpAGcAaAAgAHQAZQBtAHAAXAAiACwAIABcACIAVwBlAHQAIABjAGwAaQBtAGEAdABlACAAegBvAG4AZQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVwBhAHIAbQAgAHQAZQBtAHAAZQByAGEAdABlACAAZAByAHkAIAAtACAAaABpAGcAaAAgAHQAZQBtAHAAXAAiACwAIABcACIARAByAHkAIABjAGwAaQBtAGEAdABlACAAegBvAG4AZQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAQwBvAG8AbAAgAHQAZQBtAHAAZQByAGEAdABlACAAbQBvAGkAcwB0ACAALQAgAGwAbwB3ACAAZgByAG8AcwB0AFwAIgAsACAAXAAiAFcAZQB0ACAAYwBsAGkAbQBhAHQAZQAgAHoAbwBuAGUAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEMAbwBvAGwAIAB0AGUAbQBwAGUAcgBhAHQAZQAgAGQAcgB5ACAALQAgAGwAbwB3ACAAZgByAG8AcwB0AFwAIgAsACAAXAAiAEQAcgB5ACAAYwBsAGkAbQBhAHQAZQAgAHoAbwBuAGUAXAAiAFwAbgAgACAAIAAgACAAIAAgACAAfQAsACAAcgAsACAAYwApAFwAbgAgACAAIAAgACAAIAApAFwAbgAgACAAIAAgACkAXABuACAAIAApADsAXABuAFwAbgAvACoAIABcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBDAGwAaQBtAGEAdABlAFoAbwBuAGUAcwBcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgAqAC8AXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBDAGwAaQBtAGEAdABlAFoAbwBuAGUAcwBfAFQAaQB0AGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAVgBFAEUAUgBHACAAQQB1AHMAdAByAGEAbABpAGEAbgAgAGMAbABpAG0AYQB0AGUAIAB6AG8AbgBlAHMAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEMAbABpAG0AYQB0AGUAWgBvAG4AZQBzAF8AVgBhAHIAaQBhAGIAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQwBsAGkAbQBhAHQAZQBaAG8AbgBlAHMAXwBVAG4AaQB0AFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQwBsAGkAbQBhAHQAZQBaAG8AbgBlAHMAXwBTAG8AdQByAGMAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAVgBFAEUAUgBHACAAMgAwADIANgA6ACAAVABhAGIAbABlACAAMQAuADMAOgAgAEMAbABpAG0AYQB0AGUAIABhAG4AZAAgAFIAYQBpAG4AZgBhAGwAbAAgAHoAbwBuAGUAIABjAGwAYQBzAHMAaQBmAGkAYwBhAHQAaQBvAG4AcwAgAGEAbgBkACAAZABlAGYAaQBuAGkAdABpAG8AbgBzAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBDAGwAaQBtAGEAdABlAFoAbwBuAGUAcwBfAFYAYQByAGkAYQB0AGkAbwBuAFwAbgAgACAAIAA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAATQBBAEsARQBBAFIAUgBBAFkAKAA1ACwAIAAxACwAIABcAG4AIAAgACAAIAAgACAATABBAE0AQgBEAEEAKAByACwAYwAsACAAXABuACAAIAAgACAAIAAgACAAIABJAE4ARABFAFgAKAB7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBWAEEAUgBJAEEAVABJAE8ATgAgAE8ARgAgAFMATwBVAFIAQwBFACAARABBAFQAQQA6AFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBBAGQAZABlAGQAIAB3AGEAcgBtACAALwAgAGMAbwBvAGwAIAB0AGUAbQBwAGUAcgBhAHQAZQAgAG0AbwBpAHMAdAAgAC8AIABkAHIAeQAgAC0AIABsAG8AdwAgAGYAcgBvAHMAdAAgAGEAbgBkACAAaABpAGcAaAAgAHQAZQBtAHAAIABjAGwAYQBzAHMAZQBzACAAdABvACAAYQBjAGMAbwBtAG0AbwBkAGEAdABlACAAYwBsAGkAbQBhAHQAZQAgAHMAYwBlAG4AYQByAGkAbwBzACAAZQB4AGMAbAB1AGQAZQBkACAAYgB5ACAAVgBFAEUAUgBHACAAYwByAGkAdABlAHIAaQBhAC4AXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEYAaQB4AGUAZAAgAHQAeQBwAG8AIABpAG4AIABNAEEAVAAgAHYAYQBsAHUAZQAgAGYAbwByACAAdwBhAHIAbQAgAHQAZQBtAHAAZQByAGEAdABlACAAZAByAHkAIAAtACAAYwBoAGEAbgBnAGUAZAAgADEAMAAgAHQAbwAgADEAMQAuAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBBAGQAZABlAGQAIABtAGkAbgAgAGEAbgBkACAAbQBhAHgAIABjAG8AbAB1AG0AbgBzACAAZgBvAHIAIABNAEEAVAAsACAATQBBAFAALAAgAGYAcgBvAHMAdAAgAGQAYQB5AHMAIABwAGUAcgAgAHkAZQBhAHIALAAgAGUAbABlAHYAYQB0AGkAbwBuACwAIABNAEEAUAA6AFAARQBUACAAdABvACAAYwBhAGwAYwB1AGwAYQB0AGUAIAB6AG8AbgBlAHMAIABmAHIAbwBtACAAcgBlAGEAbAAgAGMAbABpAG0AYQB0AGUAIABkAGEAdABhAC4AXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEcAQQBGACAAYQBjAGMAZQBwAHQAcwAgAHIAYQBpAG4AZgBhAGwAbAAgAGEAcwAgAGEAIABwAHIAbwB4AHkAIABmAG8AcgAgAHAAcgBlAGMAaQBwAGkAdABhAHQAaQBvAG4ALgBcACIAXABuACAAIAAgACAAIAAgACAAIAB9ACwAIAByACwAIABjACkAXABuACAAIAAgACAAIAAgACkAXABuACAAIAAgACAAKQBcAG4AIAAgACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEMAbABpAG0AYQB0AGUAWgBvAG4AZQBzAF8ARABhAHQAYQBcAG4AIAAgACAAPQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAE0AQQBLAEUAQQBSAFIAQQBZACgAOQAsACAAMQA2ACwAIABcAG4AIAAgACAAIAAgACAATABBAE0AQgBEAEEAKAByACwAYwAsACAAXABuACAAIAAgACAAIAAgACAAIABJAE4ARABFAFgAKAB7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBDAGwAaQBtAGEAdABlACAAWgBvAG4AZQBcACIALAAgAFwAIgBNAEEAVABcACIALAAgAFwAIgBNAEEAUABcACIALAAgAFwAIgBGAHIAbwBzAHQAIABkAGEAeQBzACAAcABlAHIAIAB5AGUAYQByAFwAIgAsACAAXAAiAEUAbABlAHYAYQB0AGkAbwBuAFwAIgAsACAAXAAiAE0AQQBQADoAUABFAFQAXAAiACwAIABcACIATQBpAG4AIAB0AGUAbQBwAFwAIgAsACAAXAAiAE0AYQB4ACAAdABlAG0AcABcACIALAAgAFwAIgBNAGkAbgAgAHIAYQBpAG4AZgBhAGwAbABcACIALAAgAFwAIgBNAGEAeAAgAHIAYQBpAG4AZgBhAGwAbABcACIALAAgAFwAIgBNAGkAbgAgAGYAcgBvAHMAdAAgAGQAYQB5AHMAXAAiACwAIABcACIATQBhAHgAIABmAHIAbwBzAHQAIABkAGEAeQBzAFwAIgAsACAAXAAiAE0AaQBuACAAZQBsAGUAdgBhAHQAaQBvAG4AXAAiACwAIABcACIATQBhAHgAIABlAGwAZQB2AGEAdABpAG8AbgBcACIALAAgAFwAIgBNAGkAbgAgAE0AQQBQADoAUABFAFQAXAAiACwAIABcACIATQBpAG4AIABNAEEAUAA6AFAARQBUAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBUAHIAbwBwAGkAYwBhAGwAIABtAG8AbgB0AGEAbgBlAFwAIgAsACAAXAAiAD4AIAAxADgAIABDAFwAIgAsACAAXAAiAEEAbgB5AFwAIgAsACAAXAAiAGQiIAA3AFwAIgAsACAAXAAiAD4AIAAxADAAMAAwACAAbQBcACIALAAgAFwAIgBBAG4AeQBcACIALAAgADEAOAAuADAAMAAxACwAIAA5ADkAOQA5ADkAOQAsACAALQA5ADkAOQA5ADkAOQAsACAAOQA5ADkAOQA5ADkALAAgAC0AOQA5ADkAOQA5ADkALAAgADcALAAgADEAMAAwADAALAAgADkAOQA5ADkAOQA5ACwAIAAtADkAOQA5ADkAOQA5ACwAIAA5ADkAOQA5ADkAOQA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBUAHIAbwBwAGkAYwBhAGwAIAB3AGUAdABcACIALAAgAFwAIgA+ACAAMQA4ACAAQwBcACIALAAgAFwAIgA+ACAAMgAwADAAMAAgAG0AbQBcACIALAAgAFwAIgBkIiAANwBcACIALAAgAFwAIgBkIiAAMQAwADAAMAAgAG0AXAAiACwAIABcACIAQQBuAHkAXAAiACwAIAAxADgALgAwADAAMQAsACAAOQA5ADkAOQA5ADkALAAgADIAMAAwADAALgAwADAAMQAsACAAOQA5ADkAOQA5ADkALAAgAC0AOQA5ADkAOQA5ADkALAAgADcALAAgAC0AOQA5ADkAOQA5ADkALAAgADkAOQA5AC4AOQA5ADkALAAgACAALQA5ADkAOQA5ADkAOQAsACAAOQA5ADkAOQA5ADkAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVAByAG8AcABpAGMAYQBsACAAbQBvAGkAcwB0AFwAIgAsACAAXAAiAD4AIAAxADgAIABDAFwAIgAsACAAXAAiAD4AIAAxADAAMAAwACAAbQBtACAALQAgAGQiIAAyADAAMAAwACAAbQBtAFwAIgAsACAAXAAiAGQiIAA3AFwAIgAsACAAXAAiAGQiIAAxADAAMAAwACAAbQBcACIALAAgAFwAIgBBAG4AeQBcACIALAAgADEAOAAuADAAMAAxACwAIAA5ADkAOQA5ADkAOQAsACAAMQAwADAAMAAuADAAMAAxACwAIAAyADAAMAAwACwAIAAtADkAOQA5ADkAOQA5ACwAIAA3ACwAIAAtADkAOQA5ADkAOQA5ACwAIAA5ADkAOQAuADkAOQA5ACwAIAAgAC0AOQA5ADkAOQA5ADkALAAgADkAOQA5ADkAOQA5ADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFQAcgBvAHAAaQBjAGEAbAAgAGQAcgB5AFwAIgAsACAAXAAiAD4AIAAxADgAIABDAFwAIgAsACAAXAAiAGQiIAAxADAAMAAwACAAbQBtAFwAIgAsACAAXAAiAGQiIAA3AFwAIgAsACAAXAAiAGQiIAAxADAAMAAwACAAbQBcACIALAAgAFwAIgBBAG4AeQBcACIALAAgADEAOAAuADAAMAAxACwAIAA5ADkAOQA5ADkAOQAsACAALQA5ADkAOQA5ADkAOQAsACAAMQAwADAAMAAsACAALQA5ADkAOQA5ADkAOQAsACAANwAsACAALQA5ADkAOQA5ADkAOQAsACAAOQA5ADkALgA5ADkAOQAsACAAIAAtADkAOQA5ADkAOQA5ACwAIAA5ADkAOQA5ADkAOQA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBXAGEAcgBtACAAdABlAG0AcABlAHIAYQB0AGUAIABtAG8AaQBzAHQAXAAiACwAIABcACIAPgAgADEAMAAgAEMAXAAiACwAIABcACIAQQBuAHkAXAAiACwAIABcACIAQQBuAHkAXAAiACwAIABcACIAQQBuAHkAXAAiACwAIABcACIAPgAgADEAXAAiACwAIAAxADAALgAwADAAMQAsACAAOQA5ADkAOQA5ADkALAAgAC0AOQA5ADkAOQA5ADkALAAgADkAOQA5ADkAOQA5ACwAIAAtADkAOQA5ADkAOQA5ACwAIAA5ADkAOQA5ADkAOQAsACAALQA5ADkAOQA5ADkAOQAsACAAOQA5ADkAOQA5ADkALAAgADEALgAwADAAMQAsACAAOQA5ADkAOQA5ADkAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVwBhAHIAbQAgAHQAZQBtAHAAZQByAGEAdABlACAAZAByAHkAXAAiACwAIABcACIAPgAgADEAMAAgAEMAXAAiACwAIABcACIAQQBuAHkAXAAiACwAIABcACIAQQBuAHkAXAAiACwAIABcACIAQQBuAHkAXAAiACwAIABcACIAZCIgADEAXAAiACwAIAAxADAALgAwADAAMQAsACAAOQA5ADkAOQA5ADkALAAgAC0AOQA5ADkAOQA5ADkALAAgADkAOQA5ADkAOQA5ACwAIAAtADkAOQA5ADkAOQA5ACwAIAA5ADkAOQA5ADkAOQAsACAALQA5ADkAOQA5ADkAOQAsACAAOQA5ADkAOQA5ADkALAAgACAALQA5ADkAOQA5ADkAOQAsACAAMQA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBDAG8AbwBsACAAdABlAG0AcABlAHIAYQB0AGUAIABtAG8AaQBzAHQAXAAiACwAIABcACIAPgAgADAAIABDACAALQAgAGQiIAAxADAAIABDAFwAIgAsACAAXAAiAEEAbgB5AFwAIgAsACAAXAAiAEEAbgB5AFwAIgAsACAAXAAiAEEAbgB5AFwAIgAsACAAXAAiAD4AIAAxAFwAIgAsACAALQA5ADkAOQA5ADkAOQAsACAAMQAwACwAIAAtADkAOQA5ADkAOQA5ACwAIAA5ADkAOQA5ADkAOQAsACAALQA5ADkAOQA5ADkAOQAsACAAOQA5ADkAOQA5ADkALAAgAC0AOQA5ADkAOQA5ADkALAAgADkAOQA5ADkAOQA5ACwAIAAxAC4AMAAwADEALAAgADkAOQA5ADkAOQA5ADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEMAbwBvAGwAIAB0AGUAbQBwAGUAcgBhAHQAZQAgAGQAcgB5AFwAIgAsACAAXAAiAD4AIAAwACAAQwAgAC0AIABkIiAAMQAwACAAQwBcACIALAAgAFwAIgBBAG4AeQBcACIALAAgAFwAIgBBAG4AeQBcACIALAAgAFwAIgBBAG4AeQBcACIALAAgAFwAIgBkIiAAMQBcACIALAAgAC0AOQA5ADkAOQA5ADkALAAgADEAMAAsACAALQA5ADkAOQA5ADkAOQAsACAAOQA5ADkAOQA5ADkALAAgAC0AOQA5ADkAOQA5ADkALAAgADkAOQA5ADkAOQA5ACwAIAAtADkAOQA5ADkAOQA5ACwAIAA5ADkAOQA5ADkAOQAsACAAIAAtADkAOQA5ADkAOQA5ACwAIAAxAFwAbgAgACAAIAAgACAAIAAgACAAfQAsACAAcgAsACAAYwApAFwAbgAgACAAIAAgACAAIAApAFwAbgAgACAAIAAgACkAXABuACAAIAApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBDAGwAaQBtAGEAdABlAFoAbwBuAGUAcwBfAEEAcABwAGUAbgBkAGkAYwBlAHMAXABuACAAIAAgAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABNAEEASwBFAEEAUgBSAEEAWQAoADQALAAgADEALAAgAFwAbgAgACAAIAAgACAAIABMAEEATQBCAEQAQQAoAHIALABjACwAIABcAG4AIAAgACAAIAAgACAAIAAgAEkATgBEAEUAWAAoAHsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAE4AbwB0AGUAOgBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIATQBBAFQAIAA9ACAAbQBlAGEAbgAgAGEAbgBuAHUAYQBsACAAdABlAG0AcABlAHIAYQB0AHUAcgBlAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBNAEEAUAAgAD0AIABtAGUAYQBuACAAYQBuAG4AdQBhAGwAIABwAHIAZQBjAGkAcABpAHQAYQB0AGkAbwBuAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBQAEUAVAAgAD0AIABwAG8AdABlAG4AdABpAGEAbAAgAGUAdgBhAHAAbwB0AHIAYQBuAHMAcABpAHIAYQB0AGkAbwBuAFwAIgBcAG4AIAAgACAAIAAgACAAIAAgAH0ALAAgAHIALAAgAGMAKQBcAG4AIAAgACAAIAAgACAAKQBcAG4AIAAgACAAIAApAFwAbgAgACAAKQA7AFwAbgBcAG4AXABuAC8AKgAgAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFQAZQBtAHAAZQByAGEAdAB1AHIAZQBaAG8AbgBlAHMAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AKgAvAFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AVABlAG0AcABlAHIAYQB0AHUAcgBlAFoAbwBuAGUAcwBfAFQAaQB0AGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAVgBFAEUAUgBHACAAQQB1AHMAdAByAGEAbABpAGEAbgAgAHQAZQBtAHAAZQByAGEAdAB1AHIAZQAgAHoAbwBuAGUAcwBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AVABlAG0AcABlAHIAYQB0AHUAcgBlAFoAbwBuAGUAcwBfAFYAYQByAGkAYQBiAGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFQAZQBtAHAAZQByAGEAdAB1AHIAZQBaAG8AbgBlAHMAXwBVAG4AaQB0AFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AVABlAG0AcABlAHIAYQB0AHUAcgBlAFoAbwBuAGUAcwBfAFMAbwB1AHIAYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBWAEUARQBSAEcAIAAyADAAMgA2ADoAIABUAGEAYgBsAGUAIAAxAC4AMwA6ACAAQwBsAGkAbQBhAHQAZQAgAGEAbgBkACAAUgBhAGkAbgBmAGEAbABsACAAegBvAG4AZQAgAGMAbABhAHMAcwBpAGYAaQBjAGEAdABpAG8AbgBzACAAYQBuAGQAIABkAGUAZgBpAG4AaQB0AGkAbwBuAHMAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFQAZQBtAHAAZQByAGEAdAB1AHIAZQBaAG8AbgBlAHMAXwBWAGEAcgBpAGEAdABpAG8AbgBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAVgBBAFIASQBBAFQASQBPAE4AIABPAEYAIABTAE8AVQBSAEMARQAgAEQAQQBUAEEAOgAgAEEAZABkAGUAZAAgAGUAeAB0AHIAYQAgAE0AQQBUACAAbQBpAG4AIABhAG4AZAAgAE0AQQBUACAAbQBhAHgAIABjAG8AbAB1AG0AbgBzACAAdABvACAAYwBhAGwAYwB1AGwAYQB0AGUAIAB6AG8AbgBlACAAZgByAG8AbQAgAHIAZQBhAGwAIAB0AGUAbQBwAGUAcgBhAHQAdQByAGUAIABkAGEAdABhAC4AXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFQAZQBtAHAAZQByAGEAdAB1AHIAZQBaAG8AbgBlAHMAXwBEAGEAdABhAFwAbgAgACAAIAA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAATQBBAEsARQBBAFIAUgBBAFkAKAA0ACwAIAA0ACwAIABcAG4AIAAgACAAIAAgACAATABBAE0AQgBEAEEAKAByACwAYwAsACAAXABuACAAIAAgACAAIAAgACAAIABJAE4ARABFAFgAKAB7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBUAGUAbQBwAGUAcgBhAHQAdQByAGUAIABaAG8AbgBlAFwAIgAsACAAXAAiAE0AZQBkAGkAYQBuACAAQQBuAG4AdQBhAGwAIABUAGUAbQBwAGUAcgBhAHQAdQByAGUAIAAoAE0AQQBUACkAXAAiACwAIABcACIATQBpAG4AIABNAEEAVABcACIALAAgAFwAIgBNAGEAeAAgAE0AQQBUAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBXAGEAcgBtAFwAIgAsACAAXAAiAGUiIAAyADYAIABDAFwAIgAsACAAMgA2ACwAIAA5ADkAOQA5ADkAOQA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBUAGUAbQBwAGUAcgBhAHQAZQBcACIALAAgAFwAIgAxADUAIAAtACAAMgA1ACAAQwBcACIALAAgADEANQAsACAAMgA1AC4AOQA5ADkAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAQwBvAG8AbABcACIALAAgAFwAIgBkIiAAMQA0ACAAQwBcACIALAAgAC0AOQA5ADkAOQA5ADkALAAgADEANAAuADkAOQA5AFwAbgAgACAAIAAgACAAIAAgACAAfQAsACAAcgAsACAAYwApAFwAbgAgACAAIAAgACAAIAApAFwAbgAgACAAIAAgACkAXABuACAAIAApADsAXABuAFwAbgAvACoAIABcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBSAGEAaQBuAGYAYQBsAGwAWgBvAG4AZQBzAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuACoALwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFIAYQBpAG4AZgBhAGwAbABaAG8AbgBlAHMAXwBUAGkAdABsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFYARQBFAFIARwAgAEEAdQBzAHQAcgBhAGwAaQBhAG4AIAByAGEAaQBuAGYAYQBsAGwAIAB6AG8AbgBlAHMAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFIAYQBpAG4AZgBhAGwAbABaAG8AbgBlAHMAXwBWAGEAcgBpAGEAYgBsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBSAGEAaQBuAGYAYQBsAGwAWgBvAG4AZQBzAF8AVQBuAGkAdABcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFIAYQBpAG4AZgBhAGwAbABaAG8AbgBlAHMAXwBTAG8AdQByAGMAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAVgBFAEUAUgBHACAAMgAwADIANgA6ACAAVABhAGIAbABlACAAMQAuADMAOgAgAEMAbABpAG0AYQB0AGUAIABhAG4AZAAgAFIAYQBpAG4AZgBhAGwAbAAgAHoAbwBuAGUAIABjAGwAYQBzAHMAaQBmAGkAYwBhAHQAaQBvAG4AcwAgAGEAbgBkACAAZABlAGYAaQBuAGkAdABpAG8AbgBzAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBSAGEAaQBuAGYAYQBsAGwAWgBvAG4AZQBzAF8AVgBhAHIAaQBhAHQAaQBvAG4AXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFYAQQBSAEkAQQBUAEkATwBOACAATwBGACAAUwBPAFUAUgBDAEUAIABEAEEAVABBADoAIABBAGQAZABlAGQAIABlAHgAdAByAGEAIABSAGEAaQBuAGYAYQBsAGwAIABtAGkAbgAgAGEAbgBkACAAUgBhAGkAbgBmAGEAbABsACAAbQBhAHgAIABjAG8AbAB1AG0AbgBzACAAdABvACAAYwBhAGwAYwB1AGwAYQB0AGUAIAB6AG8AbgBlACAAZgByAG8AbQAgAHIAZQBhAGwAIAByAGEAaQBuAGYAYQBsAGwAIABkAGEAdABhAC4AXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFIAYQBpAG4AZgBhAGwAbABaAG8AbgBlAHMAXwBEAGEAdABhAFwAbgAgACAAIAA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAATQBBAEsARQBBAFIAUgBBAFkAKAAzACwAIAA0ACwAIABcAG4AIAAgACAAIAAgACAATABBAE0AQgBEAEEAKAByACwAYwAsACAAXABuACAAIAAgACAAIAAgACAAIABJAE4ARABFAFgAKAB7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBSAGEAaQBuAGYAYQBsAGwAIABaAG8AbgBlAFwAIgAsACAAXAAiAEEAbgBuAHUAYQBsACAAcgBhAGkAbgBmAGEAbABsAFwAIgAsACAAXAAiAFIAYQBpAG4AZgBhAGwAbAAgAG0AaQBuAFwAIgAsACAAXAAiAFIAYQBpAG4AZgBhAGwAbAAgAG0AYQB4AFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBIAGkAZwBoACAAcgBhAGkAbgBmAGEAbABsAFwAIgAsACAAXAAiAEEAbgBuAHUAYQBsACAAcgBhAGkAbgBmAGEAbABsACAAPgAgADYAMAAwAG0AbQBcACIALAAgADYAMAAwAC4AMAAwADEALAAgADkAOQA5ADkAOQA5ADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEwAbwB3ACAAcgBhAGkAbgBmAGEAbABsAFwAIgAsACAAXAAiAEEAbgBuAHUAYQBsACAAcgBhAGkAbgBmAGEAbABsACAAZCIgADYAMAAwAG0AbQBcACIALAAgAC0AOQA5ADkAOQA5ADkALAAgADYAMAAwAFwAbgAgACAAIAAgACAAIAAgACAAfQAsACAAcgAsACAAYwApAFwAbgAgACAAIAAgACAAIAApAFwAbgAgACAAIAAgACkAXABuACAAIAApADsAXABuAFwAbgAvACoAIABcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBMAGUAYQBjAGgAaQBuAGcAWgBvAG4AZQBzAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuACoALwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEwAZQBhAGMAaABpAG4AZwBaAG8AbgBlAHMAXwBUAGkAdABsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFYARQBFAFIARwAgAEEAdQBzAHQAcgBhAGwAaQBhAG4AIABsAGUAYQBjAGgAaQBuAGcAIAB6AG8AbgBlAHMAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEwAZQBhAGMAaABpAG4AZwBaAG8AbgBlAHMAXwBWAGEAcgBpAGEAYgBsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBMAGUAYQBjAGgAaQBuAGcAWgBvAG4AZQBzAF8AVQBuAGkAdABcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEwAZQBhAGMAaABpAG4AZwBaAG8AbgBlAHMAXwBTAG8AdQByAGMAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAVgBFAEUAUgBHACAAMgAwADIANgA6ACAAVABhAGIAbABlACAAMQAuADMAOgAgAEMAbABpAG0AYQB0AGUAIABhAG4AZAAgAFIAYQBpAG4AZgBhAGwAbAAgAHoAbwBuAGUAIABjAGwAYQBzAHMAaQBmAGkAYwBhAHQAaQBvAG4AcwAgAGEAbgBkACAAZABlAGYAaQBuAGkAdABpAG8AbgBzAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBMAGUAYQBjAGgAaQBuAGcAWgBvAG4AZQBzAF8AVgBhAHIAaQBhAHQAaQBvAG4AXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBMAGUAYQBjAGgAaQBuAGcAWgBvAG4AZQBzAF8ARABhAHQAYQBcAG4AIAAgACAAPQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAE0AQQBLAEUAQQBSAFIAQQBZACgANAAsACAAMgAsACAAXABuACAAIAAgACAAIAAgAEwAQQBNAEIARABBACgAcgAsAGMALAAgAFwAbgAgACAAIAAgACAAIAAgACAASQBOAEQARQBYACgAewBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIATABlAGEAYwBoAGkAbgBnACAAWgBvAG4AZQBcACIALAAgAFwAIgBMAGUAYQBjAGgAaQBuAGcAIABjAHIAaQB0AGUAcgBpAGEAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEwAZQBhAGMAaABpAG4AZwAgAG8AYwBjAHUAcgBzAFwAIgAsACAAXAAiAKMDKAA12F/cNdhO3DXYVtw12FvcKQA+AKMDKAA12DjcNdhH3DAAKQArADXYYNw12FzcNdhW3DXYWdwgADXYZNw12E7cNdhh3DXYUtw12F/cIAAOITXYXNw12FncNdhR3DXYVtw12FvcNdhU3CAANdhQ3DXYTtw12F3cNdhO3DXYUNw12FbcNdhh3DXYZtxcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIATABlAGEAYwBoAGkAbgBnACAAZABvAGUAcwAgAG4AbwB0ACAAbwBjAGMAdQByAFwAIgAsACAAXAAiAKMDKAA12F/cNdhO3DXYVtw12FvcKQBkIqMDKAA12DjcNdhH3DAAKQArADXYYNw12FzcNdhW3DXYWdwgADXYZNw12E7cNdhh3DXYUtw12F/cIAAOITXYXNw12FncNdhR3DXYVtw12FvcNdhU3CAANdhQ3DXYTtw12F3cNdhO3DXYUNw12FbcNdhh3DXYZtxcACIAXABuACAAIAAgACAAIAAgACAAIAB9ACwAIAByACwAIABjACkAXABuACAAIAAgACAAIAAgACkAXABuACAAIAAgACAAKQBcAG4AIAAgACkAOwBcAG4AXABuAC8AKgAgAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAcgBhAGMAVwBFAFQAXABuADUALgA1AC4AMgAuADMAIABDAG8AbgBzAHQAYQBuAHQAIABQAGEAcgBhAG0AZQB0AGUAcgBzAFwAbgBGAHIAYQBjAHQAaQBvAG4AIABvAGYAIABOACAAdABoAGEAdAAgAGkAcwAgAGEAdgBhAGkAbABhAGIAbABlACAAZgBvAHIAIABsAGUAYQBjAGgAaQBuAGcAIABhAG4AZAAgAHIAdQBuAG8AZgBmAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuACoALwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAcgBhAGMAVwBFAFQAXwBUAGkAdABsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAEYAcgBhAGMAdABpAG8AbgAgAG8AZgAgAE4AIAB0AGgAYQB0ACAAaQBzACAAYQB2AGEAaQBsAGEAYgBsAGUAIABmAG8AcgAgAGwAZQBhAGMAaABpAG4AZwAgAGEAbgBkACAAcgB1AG4AbwBmAGYAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAcgBhAGMAVwBFAFQAXwBVAG4AaQB0AFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgAoAEQAaQBtAGUAbgBzAGkAbwBuAGwAZQBzAHMAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAcgBhAGMAVwBFAFQAXwBTAG8AdQByAGMAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAVgBFAEUAUgBHACAAMgAwADIANgA6ADUALgA1AC4AMgAuADMAIABDAG8AbgBzAHQAYQBuAHQAIABQAGEAcgBhAG0AZQB0AGUAcgBzAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAHIAYQBjAFcARQBUAF8ATgBJAFIAUgBlAGYAZQByAGUAbgBjAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAHIAYQBjAFcARQBUAF8ARABhAHQAYQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABNAEEASwBFAEEAUgBSAEEAWQAoADMALAAgADIALAAgAFwAbgAgACAAIAAgACAAIABMAEEATQBCAEQAQQAoAHIALABjACwAIABcAG4AIAAgACAAIAAgACAAIAAgAEkATgBEAEUAWAAoAHsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEkAcwAgAGkAbgAgAGwAZQBhAGMAaABpAG4AZwAgAHoAbwBuAGUAXAAiACwAXAAiAEYAcgBhAGMAVwBFAFQAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFkAZQBzACAALQAgAGkAbgAgAGwAZQBhAGMAaABpAG4AZwAgAHoAbwBuAGUAXAAiACwAIAAxADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAE4AbwAgAC0AIABuAG8AdAAgAGkAbgAgAGwAZQBhAGMAaABpAG4AZwAgAHoAbwBuAGUAXAAiACwAIAAwAFwAbgAgACAAIAAgACAAIAAgACAAfQAsACAAcgAsACAAYwApAFwAbgAgACAAIAAgACAAIAApAFwAbgAgACAAIAAgACkAXABuACAAIAApADsAXABuAFwAbgAgACAAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgByAGEAYwBXAEUAVABfAFYAYQByAGkAYQB0AGkAbwBuAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoACgAXAAiAFwAIgApACkAOwBcAG4AXABuAFwAbgBcAG4ALwAqACAAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABhAHQAYQBTAGMAbwByAGUAcwBfAFMAYwBvAHAAZQAzAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuACoALwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEQAYQB0AGEAUwBjAG8AcgBlAHMAXwBTAGMAbwBwAGUAMwBfAFQAaQB0AGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAQQB1AHMAdAByAGEAbABpAGEAbgAgAGQAYQB0AGEAIABzAGMAbwByAGUAcwAgAGYAbwByACAAcwBjAG8AcABlACAAMwBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABhAHQAYQBTAGMAbwByAGUAcwBfAFMAYwBvAHAAZQAzAF8AVgBhAHIAaQBhAGIAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABhAHQAYQBTAGMAbwByAGUAcwBfAFMAYwBvAHAAZQAzAF8AVQBuAGkAdABcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEQAYQB0AGEAUwBjAG8AcgBlAHMAXwBTAGMAbwBwAGUAMwBfAFMAbwB1AHIAYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBWAEUARQBSAEcAIAAyADAAMgA2ADoAIABYAFgAWABYAFgAWABYAFgAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEQAYQB0AGEAUwBjAG8AcgBlAHMAXwBTAGMAbwBwAGUAMwBfAFYAYQByAGkAYQB0AGkAbwBuAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABhAHQAYQBTAGMAbwByAGUAcwBfAFMAYwBvAHAAZQAzAF8ARABhAHQAYQBcAG4AIAAgACAAPQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAE0AQQBLAEUAQQBSAFIAQQBZACgANgAsACAAMgAsACAAXABuACAAIAAgACAAIAAgAEwAQQBNAEIARABBACgAcgAsAGMALAAgAFwAbgAgACAAIAAgACAAIAAgACAASQBOAEQARQBYACgAewBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIARABhAHQAYQAgAHMAbwB1AHIAYwBlAFwAIgAsACAAXAAiAEQAYQB0AGEAIABzAGMAbwByAGUAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEkAbgB0AGUAcgBuAGEAdABpAG8AbgBhAGwAIABzAGMAbwBwAGUAIAAzACAAZABhAHQAYQBiAGEAcwBlAFwAIgAsACAAMQA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBBAHUAcwB0AHIAYQBsAGkAYQBuACAAcwBjAG8AcABlACAAMwAgAGQAYQB0AGEAYgBhAHMAZQBcACIALAAgADIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAUwB0AGEAdABlACAAbwByACAAcgBlAGcAaQBvAG4AYQBsACAAcwBjAG8AcABlACAAMwAgAGQAYQB0AGEAYgBhAHMAZQBcACIALAAgADMAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIARQBtAGkAcwBzAGkAbwBuAHMAIABpAG4AdABlAG4AcwBpAHQAeQAgAGMAYQBsAGMAdQBsAGEAdABlAGQAIABmAHIAbwBtACAAYQBwAHAAcgBvAHYAZQBkACAAbQBlAHQAaABvAGQAXAAiACwAIAA0ADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFYAZQByAGkAZgBpAGUAZAAgAGMAcgBlAGQAZQBuAHQAaQBhAGwAIABtAGEAdABjAGgAaQBuAGcAIABJAFMATwAxADQAMAA2ADcAXAAiACwAIAA1AFwAbgAgACAAIAAgACAAIAAgACAAfQAsACAAcgAsACAAYwApAFwAbgAgACAAIAAgACAAIAApAFwAbgAgACAAIAAgACkAXABuACAAIAApADsAXABuAFwAbgBcAG4ALwAqACAAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgByAGEAYwBMAEUAQQBDAEgAXABuADUALgA1AC4AMgAuADMAIABDAG8AbgBzAHQAYQBuAHQAIABQAGEAcgBhAG0AZQB0AGUAcgBzAFwAbgBGAHIAYQBjAHQAaQBvAG4AIABvAGYAIABOACAAdABoAGEAdAAgAGkAcwAgAGEAdgBhAGkAbABhAGIAbABlACAAZgBvAHIAIABsAGUAYQBjAGgAaQBuAGcAIABhAG4AZAAgAHIAdQBuAG8AZgBmAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuACoALwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAcgBhAGMATABFAEEAQwBIAF8AVABpAHQAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBGAHIAYQBjAHQAaQBvAG4AIABvAGYAIABOACAAdABoAGEAdAAgAGkAcwAgAGEAdgBhAGkAbABhAGIAbABlACAAZgBvAHIAIABsAGUAYQBjAGgAaQBuAGcAIABhAG4AZAAgAHIAdQBuAG8AZgBmAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAHIAYQBjAEwARQBBAEMASABfAFUAbgBpAHQAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiACgARABpAG0AZQBuAHMAaQBvAG4AbABlAHMAcwBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgByAGEAYwBMAEUAQQBDAEgAXwBTAG8AdQByAGMAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAVgBFAEUAUgBHACAAMgAwADIANgA6ADUALgA1AC4AMgAuADMAIABDAG8AbgBzAHQAYQBuAHQAIABQAGEAcgBhAG0AZQB0AGUAcgBzAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAHIAYQBjAEwARQBBAEMASABfAE4ASQBSAFIAZQBmAGUAcgBlAG4AYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBOAGEAdABpAG8AbgBhAGwAIABJAG4AdgBlAG4AdABvAHIAeQAgAFIAZQBwAG8AcgB0ACAAVgBvAGwAdQBtAGUAIAAxADoAIABMAGUAYQBjAGgAaQBuAGcAIABhAG4AZAAgAHIAdQBuAG8AZgBmACAAKAAzAC4ARAAuAGIALgAyACkAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAcgBhAGMATABFAEEAQwBIAF8ARABhAHQAYQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABNAEEASwBFAEEAUgBSAEEAWQAoADEALAAgADIALAAgAFwAbgAgACAAIAAgACAAIABMAEEATQBCAEQAQQAoAHIALABjACwAIABcAG4AIAAgACAAIAAgACAAIAAgAEkATgBEAEUAWAAoAHsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEYAcgBhAGMATABFAEEAQwBIAFwAIgAsADAALgAyADQAXABuACAAIAAgACAAIAAgACAAIAB9ACwAIAByACwAIABjACkAXABuACAAIAAgACAAIAAgACkAXABuACAAIAAgACAAKQBcAG4AIAAgACkAOwBcAG4AXABuACAAIABDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAHIAYQBjAEwARQBBAEMASABfAFYAYQByAGkAYQB0AGkAbwBuAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoACgAXAAiAFwAIgApACkAOwBcAG4AXABuAFwAbgBcAG4ALwAqACAAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAGwAZQBhAGMAaABcAG4ANQAuADUALgAyAC4AMwAgAEMAbwBuAHMAdABhAG4AdAAgAFAAYQByAGEAbQBlAHQAZQByAHMAXABuAEUAbQBpAHMAcwBpAG8AbgAgAGYAYQBjAHQAbwByACAAZgBvAHIAIABuAGkAdAByAG8AZwBlAG4AIABsAGUAYQBjAGgAaQBuAGcAIABhAG4AZAAgAHIAdQBuAG8AZgBmAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuACoALwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEUARgBsAGUAYQBjAGgAXwBUAGkAdABsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAEUAbQBpAHMAcwBpAG8AbgAgAGYAYQBjAHQAbwByACAAZgBvAHIAIABuAGkAdAByAG8AZwBlAG4AIABsAGUAYQBjAGgAaQBuAGcAIABhAG4AZAAgAHIAdQBuAG8AZgBmAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYAbABlAGEAYwBoAF8AVQBuAGkAdABcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAKABrAGcAIABOADIATwAtAE4AIAAvACAAawBnACAATgBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAGwAZQBhAGMAaABfAFMAbwB1AHIAYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBWAEUARQBSAEcAIAAyADAAMgA2ADoANQAuADUALgAyAC4AMwAgAEMAbwBuAHMAdABhAG4AdAAgAFAAYQByAGEAbQBlAHQAZQByAHMAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEUARgBsAGUAYQBjAGgAXwBOAEkAUgBSAGUAZgBlAHIAZQBuAGMAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIATgBhAHQAaQBvAG4AYQBsACAASQBuAHYAZQBuAHQAbwByAHkAIABSAGUAcABvAHIAdAAgAFYAbwBsAHUAbQBlACAAMQA6ACAARQBxAHUAYQB0AGkAbwBuACAAMwAuAEQALgBCAF8AMQAwAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYAbABlAGEAYwBoAF8ARABhAHQAYQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABNAEEASwBFAEEAUgBSAEEAWQAoADEALAAgADIALAAgAFwAbgAgACAAIAAgACAAIABMAEEATQBCAEQAQQAoAHIALABjACwAIABcAG4AIAAgACAAIAAgACAAIAAgAEkATgBEAEUAWAAoAHsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEUARgBsAGUAYQBjAGgAXAAiACwAMAAuADAAMQAxAFwAbgAgACAAIAAgACAAIAAgACAAfQAsACAAcgAsACAAYwApAFwAbgAgACAAIAAgACAAIAApAFwAbgAgACAAIAAgACkAXABuACAAIAApADsAXABuAFwAbgAgACAAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAGwAZQBhAGMAaABfAFYAYQByAGkAYQB0AGkAbwBuAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoACgAXAAiAFwAIgApACkAOwBcAG4AXABuAFwAbgAvACoAIABcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYATgAyAE8AXABuAFQAYQBiAGwAZQAgAEEALgAyAC4AMgAuADEAXABuAE4AaQB0AHIAbwB1AHMAIABvAHgAaQBkAGUAIABlAG0AaQBzAHMAaQBvAG4AIABmAGEAYwB0AG8AcgBzACAAZgBvAHIAIABpAG4AbwByAGcAYQBuAGkAYwAgAGYAZQByAHQAaQBsAGkAcwBlAHIAIABhAHAAcABsAGkAYwBhAHQAaQBvAG4AIAAoAGsAZwAgAE4AMgBPAC0ATgAvAGsAZwAgAE4AKQAgACgARQBGAE4AMgBPACkAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AKgAvAFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAE4AMgBPAF8AVABpAHQAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBOAGkAdAByAG8AdQBzACAAbwB4AGkAZABlACAAZQBtAGkAcwBzAGkAbwBuACAAZgBhAGMAdABvAHIAcwAgAGYAbwByACAAaQBuAG8AcgBnAGEAbgBpAGMAIABmAGUAcgB0AGkAbABpAHMAZQByACAAYQBwAHAAbABpAGMAYQB0AGkAbwBuAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYATgAyAE8AXwBVAG4AaQB0AFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgAoAGsAZwAgAE4AMgBPAC0ATgAgAC8AIABrAGcAIABOAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYATgAyAE8AXwBTAG8AdQByAGMAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAVgBFAEUAUgBHACAAMgAwADIANgA6ACAAVABhAGIAbABlACAAQQAuADIALgAyAC4AMQBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAE4AMgBPAF8ATgBJAFIAUgBlAGYAZQByAGUAbgBjAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYATgAyAE8AXwBEAGEAdABhAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAE0AQQBLAEUAQQBSAFIAQQBZACgAMQA1ACwAIAA1ACwAIABcAG4AIAAgACAAIAAgACAATABBAE0AQgBEAEEAKAByACwAYwAsACAAXABuACAAIAAgACAAIAAgACAAIABJAE4ARABFAFgAKAB7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBQAHIAbwBkAHUAYwB0AGkAbwBuACAAcwB5AHMAdABlAG0AIABqAFwAIgAsAFwAIgBFAEYATgAyAE8AXAAiACwAIABcACIAUAByAG8AZAB1AGMAdABpAG8AbgAgAHMAeQBzAHQAZQBtACAAbwBuAGwAeQBcACIALAAgAFwAIgBJAHIAcgBpAGcAYQB0AGkAbwBuACAAbQBlAHQAaABvAGQAXAAiACwAIABcACIAUgBhAGkAbgBmAGEAbABsACAAegBvAG4AZQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIASQByAHIAaQBnAGEAdABlAGQAIABwAGEAcwB0AHUAcgBlAFwAIgAsADAALgAwADAANQA5ACwAIABcACIAUABhAHMAdAB1AHIAZQBcACIALAAgAFwAIgBBAG4AeQBcACIALAAgAFwAIgBBAG4AeQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIASQByAHIAaQBnAGEAdABlAGQAIABjAHIAbwBwAFwAIgAsADAALgAwADAANwAsACAAXAAiAEMAcgBvAHAAXAAiACwAIABcACIAQQBuAHkAXAAiACwAIABcACIAQQBuAHkAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAE4AbwBuAC0AaQByAHIAaQBnAGEAdABlAGQAIABwAGEAcwB0AHUAcgBlAFwAIgAsADAALgAwADAAMQA4ACwAIABcACIAUABhAHMAdAB1AHIAZQBcACIALAAgAFwAIgBOAG8AdAAgAGkAcgByAGkAZwBhAHQAZQBkAFwAIgAsACAAXAAiAEwAbwB3ACAAcgBhAGkAbgBmAGEAbABsAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBOAG8AbgAtAGkAcgByAGkAZwBhAHQAZQBkACAAcABhAHMAdAB1AHIAZQBcACIALAAwAC4AMAAwADEAOAAsACAAXAAiAFAAYQBzAHQAdQByAGUAXAAiACwAIABcACIATgBvAHQAIABpAHIAcgBpAGcAYQB0AGUAZABcACIALAAgAFwAIgBIAGkAZwBoACAAcgBhAGkAbgBmAGEAbABsAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBOAG8AbgAtAGkAcgByAGkAZwBhAHQAZQBkACAAYwByAG8AcAAgACgAbABvAHcAIAByAGEAaQBuAGYAYQBsAGwAKQBcACIALAAwAC4AMAAwADIAOQAsACAAXAAiAEMAcgBvAHAAXAAiACwAIABcACIATgBvAHQAIABpAHIAcgBpAGcAYQB0AGUAZABcACIALAAgAFwAIgBMAG8AdwAgAHIAYQBpAG4AZgBhAGwAbABcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIATgBvAG4ALQBpAHIAcgBpAGcAYQB0AGUAZAAgAGMAcgBvAHAAIAAoAGgAaQBnAGgAIAByAGEAaQBuAGYAYQBsAGwAKQBcACIALAAwAC4AMAAwADgALAAgAFwAIgBDAHIAbwBwAFwAIgAsACAAXAAiAE4AbwB0ACAAaQByAHIAaQBnAGEAdABlAGQAXAAiACwAIABcACIASABpAGcAaAAgAHIAYQBpAG4AZgBhAGwAbABcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAUwB1AGcAYQByAFwAIgAsADAALgAwADEAOQA5ACwAIABcACIAUwB1AGcAYQByAFwAIgAsACAAXAAiAEEAbgB5AFwAIgAsACAAXAAiAEEAbgB5AFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBDAG8AdAB0AG8AbgBcACIALAAwAC4AMAAwADUAMwAsACAAXAAiAEMAbwB0AHQAbwBuAFwAIgAsACAAXAAiAEEAbgB5AFwAIgAsACAAXAAiAEEAbgB5AFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBIAG8AcgB0AGkAYwB1AGwAdAB1AHIAYQBsACAAYwByAG8AcABzAFwAIgAsADAALgAwADAANgA0ACwAIABcACIASABvAHIAdABpAGMAdQBsAHQAdQByAGEAbAAgAGMAcgBvAHAAcwBcACIALAAgAFwAIgBBAG4AeQBcACIALAAgAFwAIgBBAG4AeQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAUgBpAGMAZQAgACgAYwBvAG4AdABpAG4AdQBvAHUAcwAgAGYAbABvAG8AZABpAG4AZwApAFwAIgAsADAALgAwADAAMwAsACAAXAAiAFIAaQBjAGUAXAAiACwAIABcACIAQwBvAG4AdABpAG4AdQBvAHUAcwAgAGYAbABvAG8AZABpAG4AZwBcACIALAAgAFwAIgBBAG4AeQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAUgBpAGMAZQAgACgAcwBpAG4AZwBsAGUAIABhAG4AZAAgAG0AdQBsAHQAaQBwAGwAZQAgAGQAcgBhAGkAbgBhAGcAZQAsACAAbwByACAAYQBsAHQAZQByAG4AYQB0AGUAIAB3AGUAdAB0AGkAbgBnACAAYQBuAGQAIABkAHIAeQBpAG4AZwApAFwAIgAsADAALgAwADAANQAsACAAXAAiAFIAaQBjAGUAXAAiACwAIABcACIAUwBpAG4AZwBsAGUAIABhAG4AZAAgAG0AdQBsAHQAaQBwAGwAZQAgAGQAcgBhAGkAbgBhAGcAZQAsACAAbwByACAAYQBsAHQAZQByAG4AYQB0AGUAIAB3AGUAdAB0AGkAbgBnACAAYQBuAGQAIABkAHIAeQBpAG4AZwBcACIALAAgAFwAIgBBAG4AeQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAQQBxAHUAYQBjAHUAbAB0AHUAcgBlAFwAIgAsADAALgAwADAAMgA2ACwAIABcACIAQQBxAHUAYQBjAHUAbAB0AHUAcgBlAFwAIgAsACAAXAAiAEEAbgB5AFwAIgAsACAAXAAiAEEAbgB5AFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBGAG8AcgBlAHMAdAByAHkAXAAiACwAMAAuADAAMAAxADgALAAgAFwAIgBGAG8AcgBlAHMAdAByAHkAXAAiACwAIABcACIAQQBuAHkAXAAiACwAIABcACIAQQBuAHkAXAAiAFwAbgAgACAAIAAgACAAIAAgACAAfQAsACAAcgAsACAAYwApAFwAbgAgACAAIAAgACAAIAApAFwAbgAgACAAIAAgACkAXABuACAAIAApADsAXABuAFwAbgAgACAAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAE4AMgBPAF8AVgBhAHIAaQBhAHQAaQBvAG4AXABuACAAIAA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAATQBBAEsARQBBAFIAUgBBAFkAKAA1ACwAIAAxACwAIABcAG4AIAAgACAAIAAgACAATABBAE0AQgBEAEEAKAByACwAYwAsACAAXABuACAAIAAgACAAIAAgACAAIABJAE4ARABFAFgAKAB7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBWAEEAUgBJAEEAVABJAE8ATgAgAE8ARgAgAFMATwBVAFIAQwBFACAARABBAFQAQQA6AFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBSAGUAbQBvAHYAZQBkACAAZAB1AHAAbABpAGMAYQB0AGUAIAAnAEEAcQB1AGEAYwB1AGwAdAB1AHIAZQAnACAAcgBvAHcALgBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAUgBlAG0AbwB2AGUAZAAgAGEAcwB0AGUAcgBpAHMAawBzACAAdABvACAAYQBpAGQAIABsAG8AbwBrAHUAcAAuAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBBAGQAZABlAGQAIAAnAHAAcgBvAGQAdQBjAHQAaQBvAG4AIABzAHkAcwB0AGUAbQAgAG8AbgBsAHkAJwAsACAAJwByAGEAaQBuAGYAYQBsAGwAIAB6AG8AbgBlACcAIABhAG4AZAAgACcAaQByAHIAaQBnAGEAdABpAG8AbgAgAG0AZQB0AGgAbwBkACcAIABjAG8AbAB1AG0AbgBzACAAdABvACAAYQBpAGQAIABsAG8AbwBrAHUAcAAuAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBEAHUAcABsAGkAYwBhAHQAZQBkACAAJwBuAG8AbgAtAGkAcgByAGkAZwBhAHQAZQBkACAAcABhAHMAdAB1AHIAZQAnACAAcgBvAHcAIAB3AGkAdABoACAAcwBhAG0AZQAgAEUARgAgAGYAbwByACAAbABvAHcAIABhAG4AZAAgAGgAaQBnAGgAIAByAGEAaQBuAGYAYQBsAGwAIAB6AG8AbgBlAHMAIAB0AG8AIABhAGkAZAAgAGwAbwBvAGsAdQBwAC4AXAAiAFwAbgAgACAAIAAgACAAIAAgACAAfQAsACAAcgAsACAAYwApAFwAbgAgACAAIAAgACAAIAApAFwAbgAgACAAIAAgACkAXABuACAAIAApADsAXABuAFwAbgAvACoAIABcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAHIAYQBjAFcARQBUAEkAcgByAGkAZwBhAHQAaQBvAG4AXABuAFYARQBFAFIARwAgADIAMAAyADYAOgAgAEMAaABhAHAAdABlAHIAIAAxACwAIABzAGUAYwB0AGkAbwBuACAAMQAuADgALgAyACAATABlAGEAYwBoAGkAbgBnACwAIABjAGwAaQBtAGEAdABlACAAYQBuAGQAIAByAGEAaQBuAGYAYQBsAGwAIAB6AG8AbgBlAHMAXABuAEkAUABDAEMAOgAgAE4AMgBPACAARQBNAEkAUwBTAEkATwBOAFMAIABGAFIATwBNACAATQBBAE4AQQBHAEUARAAgAFMATwBJAEwAUwAsACAAQQBOAEQAIABDAE8AMgAgAEUATQBJAFMAUwBJAE8ATgBTACAARgBSAE8ATQAgAEwASQBNAEUAIABBAE4ARAAgAFUAUgBFAEEAIABBAFAAUABMAEkAQwBBAFQASQBPAE4AXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AKgAvAFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgByAGEAYwBXAEUAVABJAHIAcgBpAGcAYQB0AGkAbwBuAF8AVABpAHQAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBGAHIAYQBjAFcARQBUACAAZgBvAHIAIABpAHIAcgBpAGcAYQB0AGkAbwBuACAAdAB5AHAAZQBzAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAHIAYQBjAFcARQBUAEkAcgByAGkAZwBhAHQAaQBvAG4AXwBVAG4AaQB0AFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBkAGkAbQBlAG4AcwBpAG8AbgBsAGUAcwBzAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAHIAYQBjAFcARQBUAEkAcgByAGkAZwBhAHQAaQBvAG4AXwBTAG8AdQByAGMAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAVgBFAEUAUgBHACAAMgAwADIANgA6ACAAQwBoAGEAcAB0AGUAcgAgADEALAAgAHMAZQBjAHQAaQBvAG4AIAAxAC4AOAAuADIAIABMAGUAYQBjAGgAaQBuAGcALAAgAGMAbABpAG0AYQB0AGUAIABhAG4AZAAgAHIAYQBpAG4AZgBhAGwAbAAgAHoAbwBuAGUAcwBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgByAGEAYwBXAEUAVABJAHIAcgBpAGcAYQB0AGkAbwBuAF8ATgBJAFIAUgBlAGYAZQByAGUAbgBjAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAEkAUABDAEMAIAAyADAAMQA5ACAAUgBlAGYAaQBuAGUAbQBlAG4AdAAgAFYAbwBsAHUAbQBlACAANAA6ACAAQwBoAGEAcAB0AGUAcgAgADEAMQA6ACAATgAyAE8AIABFAG0AaQBzAHMAaQBvAG4AcwAgAGYAcgBvAG0AIABNAGEAbgBhAGcAZQBkACAAUwBvAGkAbABzACwAIABhAG4AZAAgAEMATwAyACAARQBtAGkAcwBzAGkAbwBuAHMAIABmAHIAbwBtACAATABpAG0AZQAgAGEAbgBkACAAVQByAGUAYQAgAEEAcABwAGwAaQBjAGEAdABpAG8AbgBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgByAGEAYwBXAEUAVABJAHIAcgBpAGcAYQB0AGkAbwBuAF8ARABhAHQAYQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABNAEEASwBFAEEAUgBSAEEAWQAoADYALAAgADIALAAgAFwAbgAgACAAIAAgACAAIABMAEEATQBCAEQAQQAoAHIALABjACwAIABcAG4AIAAgACAAIAAgACAAIAAgAEkATgBEAEUAWAAoAHsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEkAcgByAGkAZwBhAHQAaQBvAG4AIAB0AHkAcABlACAAaQByAFwAIgAsAFwAIgBGAHIAYQBjAFcARQBUAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBOAG8AdAAgAGkAcgByAGkAZwBhAHQAZQBkAFwAIgAsACAAMAA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBEAHIAaQBwACAAaQByAHIAaQBnAGEAdABpAG8AbgBcACIALAAgADAAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAUwBwAHIAaQBuAGsAbABlAHIAIABpAHIAcgBpAGcAYQB0AGkAbwBuAFwAIgAsACAAMQA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBTAHUAcgBmAGEAYwBlACAAaQByAHIAaQBnAGEAdABpAG8AbgBcACIALAAgADEAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIATwB0AGgAZQByACAAaQByAHIAaQBnAGEAdABpAG8AbgBcACIALAAgADEAXABuACAAIAAgACAAIAAgACAAIAB9ACwAIAByACwAIABjACkAXABuACAAIAAgACAAIAAgACkAXABuACAAIAAgACAAKQBcAG4AIAAgACkAOwBcAG4AXABuACAAIABDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAHIAYQBjAFcARQBUAEkAcgByAGkAZwBhAHQAaQBvAG4AXwBWAGEAcgBpAGEAdABpAG8AbgBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAVgBBAFIASQBBAFQASQBPAE4AIABGAFIATwBNACAAUwBPAFUAUgBDAEUAIABEAEEAVABBADoAIABUAGEAYgBsAGUAIABjAHIAZQBhAHQAZQBkACAAYgBhAHMAZQBkACAAbwBuACAAVgBFAEUAUgBHACAAdABlAHgAdAAgACcAQQByAGUAYQBzACAAYQByAGUAIABzAHUAYgBqAGUAYwB0ACAAdABvACAAbABlAGEAYwBoAGkAbgBnACAAKABpAC4AZQAuACwAIABpAG4AIAB0AGgAZQAgAGwAZQBhAGMAaABpAG4AZwAgAHoAbwBuAGUAKQAgAHcAaABlAG4ALgAuAC4AIAB0AGgAZQAgAGwAYQBuAGQAIABpAHMAIABpAHIAcgBpAGcAYQB0AGUAZAAgACgAZQB4AGMAZQBwAHQAIABkAHIAaQBwACAAaQByAHIAaQBnAGEAdABpAG8AbgApAC4AJwBcACIAKQA7AFwAbgBcAG4AXABuAC8AKgAgAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEUARgBQAGEAcwB0AHUAcgBlAFIAYQBuAGcAZQBBAG4AZABQAGEAZABkAG8AYwBrAFwAbgBUAGEAYgBsAGUAIABBAC4AMgAuADIALgAyADoAIABFAG0AaQBzAHMAaQBvAG4AIABmAGEAYwB0AG8AcgAgAGYAbwByACAAdQByAGkAbgBlACAAYQBuAGQAIABkAHUAbgBnACAAZABlAHAAbwBzAGkAdABlAGQAIABvAG4AIABwAGEAcwB0AHUAcgBlACwAIAByAGEAbgBnAGUAIABvAHIAIABwAGEAZABkAG8AYwBrACAAKABrAGcAIABOADIATwAtAE4ALwBrAGcAIABOACkAIAAoAEUARgBQAFIAUAApAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuACoALwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEUARgBQAGEAcwB0AHUAcgBlAFIAYQBuAGcAZQBBAG4AZABQAGEAZABkAG8AYwBrAF8AVABpAHQAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBFAG0AaQBzAHMAaQBvAG4AIABmAGEAYwB0AG8AcgAgAGYAbwByACAAdQByAGkAbgBlACAAYQBuAGQAIABkAHUAbgBnACAAZABlAHAAbwBzAGkAdABlAGQAIABvAG4AIABwAGEAcwB0AHUAcgBlACwAIAByAGEAbgBnAGUAIABvAHIAIABwAGEAZABkAG8AYwBrAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYAUABhAHMAdAB1AHIAZQBSAGEAbgBnAGUAQQBuAGQAUABhAGQAZABvAGMAawBfAFUAbgBpAHQAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAGsAZwAgAE4AMgBPACAALQAgAE4AIAAvACAAawBnACAATgBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAFAAYQBzAHQAdQByAGUAUgBhAG4AZwBlAEEAbgBkAFAAYQBkAGQAbwBjAGsAXwBTAG8AdQByAGMAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAVgBFAEUAUgBHACAAMgAwADIANgA6ACAAVABhAGIAbABlACAAQQAuADIALgAyAC4AMgBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAFAAYQBzAHQAdQByAGUAUgBhAG4AZwBlAEEAbgBkAFAAYQBkAGQAbwBjAGsAXwBOAEkAUgBSAGUAZgBlAHIAZQBuAGMAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEUARgBQAGEAcwB0AHUAcgBlAFIAYQBuAGcAZQBBAG4AZABQAGEAZABkAG8AYwBrAF8ARABhAHQAYQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABNAEEASwBFAEEAUgBSAEEAWQAoADMALAAgADIALAAgAFwAbgAgACAAIAAgACAAIABMAEEATQBCAEQAQQAoAHIALABjACwAIABcAG4AIAAgACAAIAAgACAAIAAgAEkATgBEAEUAWAAoAHsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEMAbABpAG0AYQB0AGUAIAB6AG8AbgBlAFwAIgAsACAAXAAiAEUARgBQAFIAUABcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVwBlAHQAIABjAGwAaQBtAGEAdABlACAAegBvAG4AZQBcACIALAAgADAALgAwADAANgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBEAHIAeQAgAGMAbABpAG0AYQB0AGUAIAB6AG8AbgBlAFwAIgAsACAAMAAuADAAMAAyAFwAbgAgACAAIAAgACAAIAAgACAAfQAsACAAcgAsACAAYwApAFwAbgAgACAAIAAgACAAIAApAFwAbgAgACAAIAAgACkAXABuACAAIAApADsAXABuAFwAbgAgACAAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAFAAYQBzAHQAdQByAGUAUgBhAG4AZwBlAEEAbgBkAFAAYQBkAGQAbwBjAGsAXwBWAGEAcgBpAGEAdABpAG8AbgBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAVgBBAFIASQBBAFQASQBPAE4AIABGAFIATwBNACAAUwBPAFUAUgBDAEUAIABEAEEAVABBADoAIABDAGgAYQBuAGcAZQBkACAAJwBEAHIAeQAgAGMAbABpAG0AYQB0AGUAIAB6AG8AbgBlAHMAJwAgAHQAbwAgAHMAaQBuAGcAdQBsAGEAcgAgACcARAByAHkAIABjAGwAaQBtAGEAdABlACAAegBvAG4AZQAnACAAdABvACAAYQBpAGQAIABsAG8AbwBrAHUAcAAuAFwAIgApADsAXABuAFwAbgBcAG4ALwAqACAAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ATQBvAG4AdABoAHMAVABvAFMAZQBhAHMAbwBuAHMAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AKgAvAFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ATQBvAG4AdABoAHMAVABvAFMAZQBhAHMAbwBuAHMAXwBUAGkAdABsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAE0AbwBuAHQAaABzACAAdABvACAAUwBlAGEAcwBvAG4AcwAgAE0AYQBwAHAAaQBuAGcAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAE0AbwBuAHQAaABzAFQAbwBTAGUAYQBzAG8AbgBzAF8AVQBuAGkAdABcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAE0AbwBuAHQAaABzAFQAbwBTAGUAYQBzAG8AbgBzAF8AUwBvAHUAcgBjAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBNAG8AbgB0AGgAcwBUAG8AUwBlAGEAcwBvAG4AcwBfAE4ASQBSAFIAZQBmAGUAcgBlAG4AYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ATQBvAG4AdABoAHMAVABvAFMAZQBhAHMAbwBuAHMAXwBEAGEAdABhAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAE0AQQBLAEUAQQBSAFIAQQBZACgAMQAzACwAIAAyACwAIABcAG4AIAAgACAAIAAgACAATABBAE0AQgBEAEEAKAByACwAYwAsACAAXABuACAAIAAgACAAIAAgACAAIABJAE4ARABFAFgAKAB7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBNAG8AbgB0AGgAXAAiACwAIABcACIAUwBlAGEAcwBvAG4AXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEoAYQBuAHUAYQByAHkAXAAiACwAIABcACIAUwB1AG0AbQBlAHIAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEYAZQBiAHIAdQBhAHIAeQBcACIALAAgAFwAIgBTAHUAbQBtAGUAcgBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIATQBhAHIAYwBoAFwAIgAsACAAXAAiAEEAdQB0AHUAbQBuAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBBAHAAcgBpAGwAXAAiACwAIABcACIAQQB1AHQAdQBtAG4AXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAE0AYQB5AFwAIgAsACAAXAAiAEEAdQB0AHUAbQBuAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBKAHUAbgBlAFwAIgAsACAAXAAiAFcAaQBuAHQAZQByAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBKAHUAbAB5AFwAIgAsACAAXAAiAFcAaQBuAHQAZQByAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBBAHUAZwB1AHMAdABcACIALAAgAFwAIgBXAGkAbgB0AGUAcgBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAUwBlAHAAdABlAG0AYgBlAHIAXAAiACwAIABcACIAUwBwAHIAaQBuAGcAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAE8AYwB0AG8AYgBlAHIAXAAiACwAIABcACIAUwBwAHIAaQBuAGcAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAE4AbwB2AGUAbQBiAGUAcgBcACIALAAgAFwAIgBTAHAAcgBpAG4AZwBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIARABlAGMAZQBtAGIAZQByAFwAIgAsACAAXAAiAFMAdQBtAG0AZQByAFwAIgBcAG4AIAAgACAAIAAgACAAIAAgAH0ALAAgAHIALAAgAGMAKQBcAG4AIAAgACAAIAAgACAAKQBcAG4AIAAgACAAIAApAFwAbgAgACAAKQA7AFwAbgBcAG4AIAAgAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAE0AbwBuAHQAaABzAFQAbwBTAGUAYQBzAG8AbgBzAF8AVgBhAHIAaQBhAHQAaQBvAG4AXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFwAIgApADsAXABuAFwAbgBcAG4AXABuAC8AKgAgAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAE0AQwBGAFQAZQBtAHAAZQByAGEAdAB1AHIAZQBaAG8AbgBlAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuACoALwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAE0AQwBGAFQAZQBtAHAAZQByAGEAdAB1AHIAZQBaAG8AbgBlAF8AVABpAHQAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBNAGEAbgB1AHIAZQAgAE0AYQBuAGEAZwBlAG0AZQBuAHQAIAATICAATQBlAHQAaABhAG4AZQAgAGMAbwBuAHYAZQByAHMAaQBvAG4AIABmAGEAYwB0AG8AcgAgAHAAZQByACAAdABlAG0AcABlAHIAYQB0AHUAcgBlACAAegBvAG4AZQAgACgAZgByAGEAYwB0AGkAbwBuACkAIAAoAE0AQwBGAGkAbQApAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBNAEMARgBUAGUAbQBwAGUAcgBhAHQAdQByAGUAWgBvAG4AZQBfAFUAbgBpAHQAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAGYAcgBhAGMAdABpAG8AbgBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ATQBDAEYAVABlAG0AcABlAHIAYQB0AHUAcgBlAFoAbwBuAGUAXwBTAG8AdQByAGMAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAVgBFAEUAUgBHACAAMgAwADIANgA6ACAAVABhAGIAbABlACAAQQAuADEALgA4AC4AMQBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ATQBDAEYAVABlAG0AcABlAHIAYQB0AHUAcgBlAFoAbwBuAGUAXwBEAGEAdABhAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAE0AQQBLAEUAQQBSAFIAQQBZACgAMgAyACwAIAAxADYALAAgAFwAbgAgACAAIAAgACAAIABMAEEATQBCAEQAQQAoAHIALABjACwAIABcAG4AIAAgACAAIAAgACAAIAAgAEkATgBEAEUAWAAoAHsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFQAZQBtAHAAZQByAGEAdAB1AHIAZQAgAHoAbwBuAGUAXAAiACwAIABcACIATQBBAFQAIAAoALoAQwApAFwAIgAsACAAXAAiAFUAbgBjAG8AdgBlAHIAZQBkACAAYQBuAGUAcgBvAGIAaQBjACAAbABhAGcAbwBvAG4AXAAiACwAIABcACIAQwBvAHYAZQByAGUAZAAgAGwAYQBnAG8AbwBuAFwAIgAsACAAXAAiAEwAaQBxAHUAaQBkACAAUwBsAHUAcgByAHkAIAAoAHcAaQB0AGgAbwB1AHQAIABuAGEAdAB1AHIAYQBsACAAYwByAHUAcwB0ACkAXAAiACwAIABcACIARABhAGkAbAB5ACAAcwBwAHIAZQBhAGQAIAAoAGIAKQBcACIALAAgAFwAIgBDAG8AbQBwAG8AcwB0AGkAbgBnACAAKABwAGEAcwBzAGkAdgBlACAAdwBpAG4AZAByAG8AdwApAFwAIgAsACAAXAAiAFMAbwBsAGkAZAAgAFMAdABvAHIAYQBnAGUAXAAiACwAIABcACIAUABpAHQAIABTAHQAbwByAGEAZwBlACAAPAAxACAAbQBvAG4AdABoAFwAIgAsACAAXAAiAEQAZQBlAHAAIABMAGkAdAB0AGUAcgBcACIALAAgAFwAIgBQAG8AdQBsAHQAcgB5ACAATQBhAG4AdQByAGUAIAAoAHcAaQB0AGgALwB3AGkAdABoAG8AdQB0ACAAbABpAHQAdABlAHIAKQBcACIALAAgAFwAIgBcACIALAAgAFwAIgBEAGkAcgBlAGMAdAAgAHAAcgBvAGMAZQBzAHMAaQBuAGcAIABpAG4AdABvACAAcABlAGwAbABlAHQAaQB6AGUAZAAgAGYAZQByAHQAaQBsAGkAcwBlAHIAXAAiACwAIABcACIARABpAHIAZQBjAHQAIABhAHAAcABsAGkAYwBhAHQAaQBvAG4AIAB0AG8AIABzAG8AaQBsAFwAIgAsACAAXAAiAFAAYQBzAHQAdQByAGUALAAgAFIAYQBuAGcAZQAgAGEAbgBkACAAUABhAGQAZABvAGMAawAgACgAYwApACgAZAApAFwAIgAsACAAXAAiAE0AQQBUACAAcgBhAHcAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEMAbwBvAGwAXAAiACwAIABcACIAZCIxADAAXAAiACwAIAAwAC4ANgA2ACwAIAAwAC4AMQAsACAAMAAuADEALAAgADAALgAwADAAMQAsACAAMAAuADAAMAA1ACwAIAAwAC4AMAAyACwAIAAwAC4AMAAzACwAIAAwAC4AMAA0ACwAIAAwAC4AMAAxADUALAAgADAALgAwADEANQAsACAAMAAsACAAMAAsACAAMAAuADAAMAA0ADcALAAgADEAMAA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBDAG8AbwBsAFwAIgAsACAAMQAxACwAIAAwAC4ANgA4ACwAIAAwAC4AMQAsACAAMAAuADEAMQAsACAAMAAuADAAMAAxACwAIAAwAC4AMAAwADUALAAgADAALgAwADIALAAgADAALgAwADMALAAgADAALgAwADQALAAgADAALgAwADEANQAsACAAMAAuADAAMQA1ACwAIAAwACwAIAAwACwAIAAwAC4AMAAwADQANwAsACAAMQAxADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEMAbwBvAGwAXAAiACwAIAAxADIALAAgADAALgA3ACwAIAAwAC4AMQAsACAAMAAuADEAMwAsACAAMAAuADAAMAAxACwAIAAwAC4AMAAwADUALAAgADAALgAwADIALAAgADAALgAwADMALAAgADAALgAwADQALAAgADAALgAwADEANQAsACAAMAAuADAAMQA1ACwAIAAwACwAIAAwACwAIAAwAC4AMAAwADQANwAsACAAMQAyADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEMAbwBvAGwAXAAiACwAIAAxADMALAAgADAALgA3ADEALAAgADAALgAxACwAIAAwAC4AMQA0ACwAIAAwAC4AMAAwADEALAAgADAALgAwADAANQAsACAAMAAuADAAMgAsACAAMAAuADAAMwAsACAAMAAuADAANAAsACAAMAAuADAAMQA1ACwAIAAwAC4AMAAxADUALAAgADAALAAgADAALAAgADAALgAwADAANAA3ACwAIAAxADMAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAQwBvAG8AbABcACIALAAgADEANAAsACAAMAAuADcAMwAsACAAMAAuADEALAAgADAALgAxADUALAAgADAALgAwADAAMQAsACAAMAAuADAAMAA1ACwAIAAwAC4AMAAyACwAIAAwAC4AMAAzACwAIAAwAC4AMAA0ACwAIAAwAC4AMAAxADUALAAgADAALgAwADEANQAsACAAMAAsACAAMAAsACAAMAAuADAAMAA0ADcALAAgADEANAA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBUAGUAbQBwAGUAcgBhAHQAZQBcACIALAAgADEANQAsACAAMAAuADcANAAsACAAMAAuADEALAAgADAALgAxADcALAAgADAALgAwADAANQAsACAAMAAuADAAMQAsACAAMAAuADAAMgAsACAAMAAuADAAMwAsACAAMAAuADAANAAsACAAMAAuADAAMQA1ACwAIAAwAC4AMAAxADUALAAgADAALAAgADAALAAgADAALgAwADAANAA3ACwAIAAxADUAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVABlAG0AcABlAHIAYQB0AGUAXAAiACwAIAAxADYALAAgADAALgA3ADUALAAgADAALgAxACwAIAAwAC4AMQA4ACwAIAAwAC4AMAAwADUALAAgADAALgAwADEALAAgADAALgAwADIALAAgADAALgAwADMALAAgADAALgAwADQALAAgADAALgAwADEANQAsACAAMAAuADAAMQA1ACwAIAAwACwAIAAwACwAIAAwAC4AMAAwADQANwAsACAAMQA2ADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFQAZQBtAHAAZQByAGEAdABlAFwAIgAsACAAMQA3ACwAIAAwAC4ANwA2ACwAIAAwAC4AMQAsACAAMAAuADIALAAgADAALgAwADAANQAsACAAMAAuADAAMQAsACAAMAAuADAAMgAsACAAMAAuADAAMwAsACAAMAAuADAANAAsACAAMAAuADAAMQA1ACwAIAAwAC4AMAAxADUALAAgADAALAAgADAALAAgADAALgAwADAANAA3ACwAIAAxADcAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVABlAG0AcABlAHIAYQB0AGUAXAAiACwAIAAxADgALAAgADAALgA3ADcALAAgADAALgAxACwAIAAwAC4AMgAyACwAIAAwAC4AMAAwADUALAAgADAALgAwADEALAAgADAALgAwADIALAAgADAALgAwADMALAAgADAALgAwADQALAAgADAALgAwADEANQAsACAAMAAuADAAMQA1ACwAIAAwACwAIAAwACwAIAAwAC4AMAAwADQANwAsACAAMQA4ADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFQAZQBtAHAAZQByAGEAdABlAFwAIgAsACAAMQA5ACwAIAAwAC4ANwA3ACwAIAAwAC4AMQAsACAAMAAuADIANAAsACAAMAAuADAAMAA1ACwAIAAwAC4AMAAxACwAIAAwAC4AMAAyACwAIAAwAC4AMAAzACwAIAAwAC4AMAA0ACwAIAAwAC4AMAAxADUALAAgADAALgAwADEANQAsACAAMAAsACAAMAAsACAAMAAuADAAMAA0ADcALAAgADEAOQA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBUAGUAbQBwAGUAcgBhAHQAZQBcACIALAAgADIAMAAsACAAMAAuADcAOAAsACAAMAAuADEALAAgADAALgAyADYALAAgADAALgAwADAANQAsACAAMAAuADAAMQAsACAAMAAuADAAMgAsACAAMAAuADAAMwAsACAAMAAuADAANAAsACAAMAAuADAAMQA1ACwAIAAwAC4AMAAxADUALAAgADAALAAgADAALAAgADAALgAwADAANAA3ACwAIAAyADAAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVABlAG0AcABlAHIAYQB0AGUAXAAiACwAIAAyADEALAAgADAALgA3ADgALAAgADAALgAxACwAIAAwAC4AMgA5ACwAIAAwAC4AMAAwADUALAAgADAALgAwADEALAAgADAALgAwADIALAAgADAALgAwADMALAAgADAALgAwADQALAAgADAALgAwADEANQAsACAAMAAuADAAMQA1ACwAIAAwACwAIAAwACwAIAAwAC4AMAAwADQANwAsACAAMgAxADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFQAZQBtAHAAZQByAGEAdABlAFwAIgAsACAAMgAyACwAIAAwAC4ANwA4ACwAIAAwAC4AMQAsACAAMAAuADMAMQAsACAAMAAuADAAMAA1ACwAIAAwAC4AMAAxACwAIAAwAC4AMAAyACwAIAAwAC4AMAAzACwAIAAwAC4AMAA0ACwAIAAwAC4AMAAxADUALAAgADAALgAwADEANQAsACAAMAAsACAAMAAsACAAMAAuADAAMAA0ADcALAAgADIAMgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBUAGUAbQBwAGUAcgBhAHQAZQBcACIALAAgADIAMwAsACAAMAAuADcAOQAsACAAMAAuADEALAAgADAALgAzADQALAAgADAALgAwADAANQAsACAAMAAuADAAMQAsACAAMAAuADAAMgAsACAAMAAuADAAMwAsACAAMAAuADAANAAsACAAMAAuADAAMQA1ACwAIAAwAC4AMAAxADUALAAgADAALAAgADAALAAgADAALgAwADAANAA3ACwAIAAyADMAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVABlAG0AcABlAHIAYQB0AGUAXAAiACwAIAAyADQALAAgADAALgA3ADkALAAgADAALgAxACwAIAAwAC4AMwA3ACwAIAAwAC4AMAAwADUALAAgADAALgAwADEALAAgADAALgAwADIALAAgADAALgAwADMALAAgADAALgAwADQALAAgADAALgAwADEANQAsACAAMAAuADAAMQA1ACwAIAAwACwAIAAwACwAIAAwAC4AMAAwADQANwAsACAAMgA0ADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFQAZQBtAHAAZQByAGEAdABlAFwAIgAsACAAMgA1ACwAIAAwAC4ANwA5ACwAIAAwAC4AMQAsACAAMAAuADQAMQAsACAAMAAuADAAMAA1ACwAIAAwAC4AMAAxACwAIAAwAC4AMAAyACwAIAAwAC4AMAAzACwAIAAwAC4AMAA0ACwAIAAwAC4AMAAxADUALAAgADAALgAwADEANQAsACAAMAAsACAAMAAsACAAMAAuADAAMAA0ADcALAAgADIANQA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBXAGEAcgBtAFwAIgAsACAAMgA2ACwAIAAwAC4ANwA5ACwAIAAwAC4AMQAsACAAMAAuADQANAAsACAAMAAuADAAMQAsACAAMAAuADAAMQA1ACwAIAAwAC4AMAAyACwAIAAwAC4AMAAzACwAIAAwAC4AMAA0ACwAIAAwAC4AMAAxADUALAAgADAALgAwADEANQAsACAAMAAsACAAMAAsACAAMAAuADAAMAA0ADcALAAgADIANgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBXAGEAcgBtAFwAIgAsACAAMgA3ACwAIAAwAC4AOAAsACAAMAAuADEALAAgADAALgA0ADgALAAgADAALgAwADEALAAgADAALgAwADEANQAsACAAMAAuADAAMgAsACAAMAAuADAAMwAsACAAMAAuADAANAAsACAAMAAuADAAMQA1ACwAIAAwAC4AMAAxADUALAAgADAALAAgADAALAAgADAALgAwADAANAA3ACwAIAAyADcAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVwBhAHIAbQBcACIALAAgAFwAIgBlIjIAOABcACIALAAgADAALgA4ACwAIAAwAC4AMQAsACAAMAAuADUALAAgADAALgAwADEALAAgADAALgAwADEANQAsACAAMAAuADAAMgAsACAAMAAuADAAMwAsACAAMAAuADAANAAsACAAMAAuADAAMQA1ACwAIAAwAC4AMAAxADUALAAgADAALAAgADAALAAgADAALgAwADAANAA3ACwAIAAyADgAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAXAAiACwAIABcACIAXAAiACwAIABcACIAQQBuAGEAZQByAG8AYgBpAGMAIABsAGEAZwBvAG8AbgBcACIALAAgAFwAIgBEAGkAZwBlAHMAdABlAHIAIAAvACAAYwBvAHYAZQByAGUAZAAgAGwAYQBnAG8AbwBuAHMAXAAiACwAIABcACIATABpAHEAdQBpAGQAIABzAHkAcwB0AGUAbQBzAFwAIgAsACAAXAAiAEQAYQBpAGwAeQAgAHMAcAByAGUAYQBkAFwAIgAsACAAXAAiAEMAbwBtAHAAbwBzAHQAaQBuAGcAIAAoAHAAYQBzAHMAaQB2AGUAIAB3AGkAbgBkAHIAbwB3ACkAXAAiACwAIABcACIAUwBvAGwAaQBkACAAcwB0AG8AcgBhAGcAZQBcACIALAAgAFwAIgBQAGkAdAAgAHMAdABvAHIAYQBnAGUAXAAiACwAIABcACIARABlAGUAcAAgAGwAaQB0AHQAZQByAFwAIgAsACAAXAAiAFAAbwB1AGwAdAByAHkAIABtAGEAbgB1AHIAZQAgAHcAaQB0AGgAIABiAGUAZABkAGkAbgBnAFwAIgAsACAAXAAiAFAAbwB1AGwAdAByAHkAIABtAGEAbgB1AHIAZQAgAHcAaQB0AGgAbwB1AHQAIABiAGUAZABkAGkAbgBnAFwAIgAsACAAXAAiAEQAaQByAGUAYwB0ACAAcAByAG8AYwBlAHMAcwBpAG4AZwBcACIALAAgAFwAIgBEAGkAcgBlAGMAdAAgAGEAcABwAGwAaQBjAGEAdABpAG8AbgBcACIALAAgAFwAIgBQAGEAcwB0AHUAcgBlACAAcgBhAG4AZwBlACAAYQBuAGQAIABwAGEAZABkAG8AYwBrAFwAIgAsACAAXAAiAE0AQQBUACAAcgBhAHcAXAAiACAAXABuACAAIAAgACAAIAAgACAAIAB9ACwAIAByACwAIABjACkAXABuACAAIAAgACAAIAAgACkAXABuACAAIAAgACAAKQBcAG4AIAAgACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAE0AQwBGAFQAZQBtAHAAZQByAGEAdAB1AHIAZQBaAG8AbgBlAF8AVgBhAHIAaQBhAHQAaQBvAG4AXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFYAQQBSAEkAQQBUAEkATwBOACAARgBSAE8ATQAgAFMATwBVAFIAQwBFADoAIABBAGQAZABlAGQAIAByAG8AdwAgAG8AZgAgAE4ASQBSACAATQBNAEEAIABkAGUAZgBpAG4AaQB0AGkAbwBuAHMAIAB0AG8AIABhAGkAZAAgAGwAbwBvAGsAdQBwAC4AIABEAHUAcABsAGkAYwBhAHQAZQBkACAAJwBQAG8AdQBsAHQAcgB5ACAAdwBpAHQAaAAgAGEAbgBkACAAdwBpAHQAaABvAHUAdAAgAGwAaQB0AHQAZQByACcAIABjAG8AbAB1AG0AbgAgAHcAaQB0AGgAIABzAGUAcABhAHIAYQB0AGUAIABOAEkAUgAgAGQAZQBmAGkAbgBpAHQAaQBvAG4AcwAgAHQAbwAgAGEAaQBkACAAbABvAG8AawB1AHAALgAgAEEAZABkAGUAZAAgACcATQBBAFQAIAByAGEAdwAnACAAYwBvAGwAdQBtAG4AIAB0AG8AIABhAGwAbABvAHcAIABsAG8AbwBrAHUAcAAgAG8AZgAgAG4AdQBtAGIAZQByAHMALgBcACIAKQA7AFwAbgBcAG4AXABuAFwAbgAvACoAIABcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYATwByAGcAYQBuAGkAYwBGAGUAcgB0AGkAbABpAHMAZQByAEEAbgBkAEMAcgBvAHAAUgBlAHMAaQBkAHUAZQBzAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuACoALwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEUARgBPAHIAZwBhAG4AaQBjAEYAZQByAHQAaQBsAGkAcwBlAHIAQQBuAGQAQwByAG8AcABSAGUAcwBpAGQAdQBlAHMAXwBUAGkAdABsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAEUAbQBpAHMAcwBpAG8AbgAgAGYAYQBjAHQAbwByACAAZgBvAHIAIABvAHIAZwBhAG4AaQBjACAAZgBlAHIAdABpAGwAaQBzAGUAcgAgAGEAbgBkACAAYwByAG8AcAAgAHIAZQBzAGkAZAB1AGUAcwAgAHIAZQB0AHUAcgBuAGUAZAAgAHQAbwAgAHQAaABlACAAcwBvAGkAbABcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAE8AcgBnAGEAbgBpAGMARgBlAHIAdABpAGwAaQBzAGUAcgBBAG4AZABDAHIAbwBwAFIAZQBzAGkAZAB1AGUAcwBfAFYAYQByAGkAYQBiAGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIARQBGAE4AaQAgACYAIABFAEYATgAyAE8AaQBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAE8AcgBnAGEAbgBpAGMARgBlAHIAdABpAGwAaQBzAGUAcgBBAG4AZABDAHIAbwBwAFIAZQBzAGkAZAB1AGUAcwBfAFUAbgBpAHQAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAGsAZwAgAE4AMgBPACAALQAgAE4AIAAvACAAawBnACAATgBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAE8AcgBnAGEAbgBpAGMARgBlAHIAdABpAGwAaQBzAGUAcgBBAG4AZABDAHIAbwBwAFIAZQBzAGkAZAB1AGUAcwBfAFMAbwB1AHIAYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBWAEUARQBSAEcAIAAyADAAMgA2ADoAIABUAGEAYgBsAGUAIABBAC4AMgAuADEALgA0AFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYATwByAGcAYQBuAGkAYwBGAGUAcgB0AGkAbABpAHMAZQByAEEAbgBkAEMAcgBvAHAAUgBlAHMAaQBkAHUAZQBzAF8ATgBJAFIAUgBlAGYAZQByAGUAbgBjAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYATwByAGcAYQBuAGkAYwBGAGUAcgB0AGkAbABpAHMAZQByAEEAbgBkAEMAcgBvAHAAUgBlAHMAaQBkAHUAZQBzAF8ARABhAHQAYQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABNAEEASwBFAEEAUgBSAEEAWQAoADMALAAgADIALAAgAFwAbgAgACAAIAAgACAAIABMAEEATQBCAEQAQQAoAHIALABjACwAIABcAG4AIAAgACAAIAAgACAAIAAgAEkATgBEAEUAWAAoAHsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEMAbABpAG0AYQB0AGUAIAB6AG8AbgBlAFwAIgAsACAAXAAiAEUARgBOAGkAIAAmACAARQBGAE4AMgBPAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBXAGUAdAAgAGMAbABpAG0AYQB0AGUAIAB6AG8AbgBlAFwAIgAsACAAMAAuADAAMAA2ADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEQAcgB5ACAAYwBsAGkAbQBhAHQAZQAgAHoAbwBuAGUAXAAiACwAIAAwAC4AMAAwADUAXABuACAAIAAgACAAIAAgACAAIAB9ACwAIAByACwAIABjACkAXABuACAAIAAgACAAIAAgACkAXABuACAAIAAgACAAKQBcAG4AIAAgACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEUARgBPAHIAZwBhAG4AaQBjAEYAZQByAHQAaQBsAGkAcwBlAHIAQQBuAGQAQwByAG8AcABSAGUAcwBpAGQAdQBlAHMAXwBWAGEAcgBpAGEAdABpAG8AbgBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAXAAiACkAOwBcAG4AXABuAFwAbgBcAG4AXABuAFwAbgBcAG4AXABuAFwAbgBcAG4AXABuAFwAbgBcAG4AXABuAFwAbgBcAG4AXABuACIAfQBdACwAIgBwAHIAbwBqAGUAYwB0AE4AYQBtAGUAcwAiADoAWwAiAEMAbwBtAG0AbwBuAF8ARQBxAHUAYQB0AGkAbwBuAHMALgBDAG8AbQBtAG8AbgBfAEMAbwBuAHYAZQByAHQATgAyAE8AVABvAEMATwAyAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBFAHEAdQBhAHQAaQBvAG4AcwAuAEMAbwBtAG0AbwBuAF8AQwBvAG4AdgBlAHIAdABOADIATwBUAG8AQwBPADIAZQBfAFQAaQB0AGwAZQAiACwAIgBDAG8AbQBtAG8AbgBfAEUAcQB1AGEAdABpAG8AbgBzAC4AQwBvAG0AbQBvAG4AXwBDAG8AbgB2AGUAcgB0AE4AMgBPAFQAbwBDAE8AMgBlAF8AVgBhAHIAaQBhAGIAbABlACIALAAiAEMAbwBtAG0AbwBuAF8ARQBxAHUAYQB0AGkAbwBuAHMALgBDAG8AbQBtAG8AbgBfAEMAbwBuAHYAZQByAHQATgAyAE8AVABvAEMATwAyAGUAXwBVAG4AaQB0ACIALAAiAEMAbwBtAG0AbwBuAF8ARQBxAHUAYQB0AGkAbwBuAHMALgBDAG8AbQBtAG8AbgBfAEMAbwBuAHYAZQByAHQATgAyAE8AVABvAEMATwAyAGUAXwBOAEkAUgBSAGUAZgBlAHIAZQBuAGMAZQAiACwAIgBDAG8AbQBtAG8AbgBfAEUAcQB1AGEAdABpAG8AbgBzAC4AQwBvAG0AbQBvAG4AXwBDAG8AbgB2AGUAcgB0AE4AMgBPAFQAbwBDAE8AMgBlAF8ATABhAHQAZQB4AEUAcQB1AGEAdABpAG8AbgAiACwAIgBDAG8AbQBtAG8AbgBfAEUAcQB1AGEAdABpAG8AbgBzAC4AQwBvAG0AbQBvAG4AXwBDAG8AbgB2AGUAcgB0AE4AMgBPAFQAbwBDAE8AMgBlAF8AQQByAGcAdQBtAGUAbgB0AHMAIgAsACIAQwBvAG0AbQBvAG4AXwBFAHEAdQBhAHQAaQBvAG4AcwAuAEMAbwBtAG0AbwBuAF8AQwBvAG4AdgBlAHIAdABDAEgANABUAG8AQwBPADIAZQAiACwAIgBDAG8AbQBtAG8AbgBfAEUAcQB1AGEAdABpAG8AbgBzAC4AQwBvAG0AbQBvAG4AXwBDAG8AbgB2AGUAcgB0AEMASAA0AFQAbwBDAE8AMgBlAF8AVABpAHQAbABlACIALAAiAEMAbwBtAG0AbwBuAF8ARQBxAHUAYQB0AGkAbwBuAHMALgBDAG8AbQBtAG8AbgBfAEMAbwBuAHYAZQByAHQAQwBIADQAVABvAEMATwAyAGUAXwBWAGEAcgBpAGEAYgBsAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBFAHEAdQBhAHQAaQBvAG4AcwAuAEMAbwBtAG0AbwBuAF8AQwBvAG4AdgBlAHIAdABDAEgANABUAG8AQwBPADIAZQBfAFUAbgBpAHQAIgAsACIAQwBvAG0AbQBvAG4AXwBFAHEAdQBhAHQAaQBvAG4AcwAuAEMAbwBtAG0AbwBuAF8AQwBvAG4AdgBlAHIAdABDAEgANABUAG8AQwBPADIAZQBfAE4ASQBSAFIAZQBmAGUAcgBlAG4AYwBlACIALAAiAEMAbwBtAG0AbwBuAF8ARQBxAHUAYQB0AGkAbwBuAHMALgBDAG8AbQBtAG8AbgBfAEMAbwBuAHYAZQByAHQAQwBIADQAVABvAEMATwAyAGUAXwBMAGEAdABlAHgARQBxAHUAYQB0AGkAbwBuACIALAAiAEMAbwBtAG0AbwBuAF8ARQBxAHUAYQB0AGkAbwBuAHMALgBDAG8AbQBtAG8AbgBfAEMAbwBuAHYAZQByAHQAQwBIADQAVABvAEMATwAyAGUAXwBBAHIAZwB1AG0AZQBuAHQAcwAiACwAIgBDAG8AbQBtAG8AbgBfAEkAbgBwAHUAdABGAHUAbgBjAHQAaQBvAG4AcwAuAFUAdABpAGwAaQB0AHkAXwBHAGUAdABBAHIAcgBhAHkAVABhAGIAbABlAFIAbwB3AFMAdABhAHIAdABOAHUAbQBiAGUAcgAiACwAIgBDAG8AbQBtAG8AbgBfAEkAbgBwAHUAdABGAHUAbgBjAHQAaQBvAG4AcwAuAFUAdABpAGwAaQB0AHkAXwBHAGUAdABBAHIAcgBhAHkAVABhAGIAbABlAEMAbwBsAHUAbQBuAFMAdABhAHIAdABOAHUAbQBiAGUAcgAiACwAIgBDAG8AbQBtAG8AbgBfAEkAbgBwAHUAdABGAHUAbgBjAHQAaQBvAG4AcwAuAFUAdABpAGwAaQB0AHkAXwBEAGkAcwBwAGwAYQB5AEEAcgByAGEAeQBJAG4AVABhAGIAbABlACIALAAiAEMAbwBtAG0AbwBuAF8ASQBuAHAAdQB0AEYAdQBuAGMAdABpAG8AbgBzAC4AVQB0AGkAbABpAHQAeQBfAEwAbwBvAGsAdQBwAFYAYQBsAHUAZQBJAG4AVABhAGIAbABlACIALAAiAEMAbwBtAG0AbwBuAF8ASQBuAHAAdQB0AEYAdQBuAGMAdABpAG8AbgBzAC4AVQB0AGkAbABpAHQAeQBfAEwAbwBvAGsAdQBwAFYAYQBsAHUAZQBJAG4AVABhAGIAbABlAE4AdQBtAGIAZQByACIALAAiAEMAbwBtAG0AbwBuAF8ASQBuAHAAdQB0AEYAdQBuAGMAdABpAG8AbgBzAC4AVQB0AGkAbABpAHQAeQBfAEwAbwBvAGsAdQBwAFYAYQBsAHUAZQBJAG4AVABhAGIAbABlAFQAdwBvAEMAbwBsAHUAbQBuAHMAIgAsACIAQwBvAG0AbQBvAG4AXwBJAG4AcAB1AHQARgB1AG4AYwB0AGkAbwBuAHMALgBVAHQAaQBsAGkAdAB5AF8ATABvAG8AawB1AHAAVgBhAGwAdQBlAEkAbgBUAGEAYgBsAGUATwBuAGUAQwBvAGwAdQBtAG4AQQBuAGQASABlAGEAZABlAHIAIgAsACIAQwBvAG0AbQBvAG4AXwBJAG4AcAB1AHQARgB1AG4AYwB0AGkAbwBuAHMALgBVAHQAaQBsAGkAdAB5AF8AUwBwAGwAaQB0AFMAdAByAGkAbgBnAEkAbgB0AG8AQQByAHIAYQB5ACIALAAiAEMAbwBtAG0AbwBuAF8ASQBuAHAAdQB0AEYAdQBuAGMAdABpAG8AbgBzAC4AVQB0AGkAbABpAHQAeQBfAEcAZQB0AEMAbABpAG0AYQB0AGUAWgBvAG4AZQAiACwAIgBDAG8AbQBtAG8AbgBfAEkAbgBwAHUAdABGAHUAbgBjAHQAaQBvAG4AcwAuAFUAdABpAGwAaQB0AHkAXwBMAG8AbwBrAHUAcABJAHQAZQBtAEYAcgBvAG0ATQBpAG4ATQBhAHgAIgAsACIAQwBvAG0AbQBvAG4AXwBJAG4AcAB1AHQARgB1AG4AYwB0AGkAbwBuAHMALgBVAHQAaQBsAGkAdAB5AF8AUwB1AG0AUQB1AGEAbgB0AGkAdAB5AEYAcgBvAG0AQwByAGkAdABlAHIAaQBhACIALAAiAEMAbwBtAG0AbwBuAF8ASQBuAHAAdQB0AEYAdQBuAGMAdABpAG8AbgBzAC4AZwBlAHQATwB2AGUAcgBsAGEAcABwAGkAbgBnAFIAZQBwAG8AcgB0AGkAbgBnAFAAZQByAGkAbwBkAHMAIgAsACIAQwBvAG0AbQBvAG4AXwBJAG4AcAB1AHQARgB1AG4AYwB0AGkAbwBuAHMALgBVAHQAaQBsAGkAdAB5AF8ARABpAHMAcABsAGEAeQBGAHUAbgBjAHQAaQBvAG4ATgBhAG0AZQAiACwAIgBDAG8AbQBtAG8AbgBfAEkAbgBwAHUAdABGAHUAbgBjAHQAaQBvAG4AcwAuAFUAdABpAGwAaQB0AHkAXwBMAG8AbwBrAHUAcABOADIATwBFAEYARgByAG8AbQBQAHIAbwBkAEkAcgByAGkAZwBhAHQAaQBvAG4AUgBhAGkAbgBmAGEAbABsACIALAAiAEMAbwBtAG0AbwBuAF8ASQBuAHAAdQB0AEYAdQBuAGMAdABpAG8AbgBzAC4AQwBvAG0AbQBvAG4AQwByAG8AcABwAGkAbgBnAF8ARwBlAHQARgByAGEAYwBXAEUAVAAiACwAIgBDAG8AbQBtAG8AbgBfAEkAbgBwAHUAdABGAHUAbgBjAHQAaQBvAG4AcwAuAFUAdABpAGwAaQB0AHkAXwBDAG8AbgB2AGUAcgB0AFMAdABhAHQAZQBDAG8AbQBtAG8AbgBOAGEAbQBlAFQAbwBBAGIAYgByAGUAdgBpAGEAdABpAG8AbgAiACwAIgBDAG8AbQBtAG8AbgBfAEkAbgBwAHUAdABGAHUAbgBjAHQAaQBvAG4AcwAuAFUAdABpAGwAaQB0AHkAXwBTAG8AdQByAGMAZQBIAHkAcABlAHIAbABpAG4AawBEAGkAZgBmAGUAcgBlAG4AdABTAGgAZQBlAHQAIgAsACIAQwBvAG0AbQBvAG4AXwBJAG4AcAB1AHQARgB1AG4AYwB0AGkAbwBuAHMALgBVAHQAaQBsAGkAdAB5AF8AUgBlAHMAdQBsAHQAcwBJAHQAZQBtAEYAcgBvAG0ARQBxAHUAYQB0AGkAbwBuAFQAaQB0AGwAZQBBAG4AZABTAG8AdQByAGMAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGUAbgBzAGkAdAB5AE8AZgBNAGUAdABoAGEAbgBlAF8AVABpAHQAbABlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEQAZQBuAHMAaQB0AHkATwBmAE0AZQB0AGgAYQBuAGUAXwBVAG4AaQB0ACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEQAZQBuAHMAaQB0AHkATwBmAE0AZQB0AGgAYQBuAGUAXwBTAG8AdQByAGMAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGUAbgBzAGkAdAB5AE8AZgBNAGUAdABoAGEAbgBlAF8ARABhAHQAYQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBDAG8AbgB2AGUAcgB0AE4AMgBvAEUAbABlAG0AZQBuAHQAYQBsAFQAbwBNAG8AbABlAGMAdQBsAGEAcgBDAGcAXwBUAGkAdABsAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQwBvAG4AdgBlAHIAdABOADIAbwBFAGwAZQBtAGUAbgB0AGEAbABUAG8ATQBvAGwAZQBjAHUAbABhAHIAQwBnAF8AVgBhAHIAaQBhAGIAbABlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEMAbwBuAHYAZQByAHQATgAyAG8ARQBsAGUAbQBlAG4AdABhAGwAVABvAE0AbwBsAGUAYwB1AGwAYQByAEMAZwBfAFUAbgBpAHQAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQwBvAG4AdgBlAHIAdABOADIAbwBFAGwAZQBtAGUAbgB0AGEAbABUAG8ATQBvAGwAZQBjAHUAbABhAHIAQwBnAF8AUwBvAHUAcgBjAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQwBvAG4AdgBlAHIAdABOADIAbwBFAGwAZQBtAGUAbgB0AGEAbABUAG8ATQBvAGwAZQBjAHUAbABhAHIAQwBnAF8ARABhAHQAYQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBDAG8AbgB2AGUAcgB0AEcAYQBzAEUAbABlAG0AZQBuAHQAYQBsAFQAbwBNAG8AbABlAGMAdQBsAGEAcgBfAFQAaQB0AGwAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBDAG8AbgB2AGUAcgB0AEcAYQBzAEUAbABlAG0AZQBuAHQAYQBsAFQAbwBNAG8AbABlAGMAdQBsAGEAcgBfAFYAYQByAGkAYQBiAGwAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBDAG8AbgB2AGUAcgB0AEcAYQBzAEUAbABlAG0AZQBuAHQAYQBsAFQAbwBNAG8AbABlAGMAdQBsAGEAcgBfAFUAbgBpAHQAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQwBvAG4AdgBlAHIAdABHAGEAcwBFAGwAZQBtAGUAbgB0AGEAbABUAG8ATQBvAGwAZQBjAHUAbABhAHIAXwBTAG8AdQByAGMAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBDAG8AbgB2AGUAcgB0AEcAYQBzAEUAbABlAG0AZQBuAHQAYQBsAFQAbwBNAG8AbABlAGMAdQBsAGEAcgBfAEQAYQB0AGEAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARwBXAFAAXwBUAGkAdABsAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARwBXAFAAXwBWAGEAcgBpAGEAYgBsAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARwBXAFAAXwBVAG4AaQB0ACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEcAVwBQAF8AUwBvAHUAcgBjAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARwBXAFAAXwBEAGEAdABhACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEEAdQBzAHQAcgBhAGwAaQBhAG4AUwB0AGEAdABlAHMAVABlAHIAcgBpAHQAbwByAGkAZQBzAF8AVABpAHQAbABlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEEAdQBzAHQAcgBhAGwAaQBhAG4AUwB0AGEAdABlAHMAVABlAHIAcgBpAHQAbwByAGkAZQBzAF8AVgBhAHIAaQBhAGIAbABlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEEAdQBzAHQAcgBhAGwAaQBhAG4AUwB0AGEAdABlAHMAVABlAHIAcgBpAHQAbwByAGkAZQBzAF8AVQBuAGkAdAAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBBAHUAcwB0AHIAYQBsAGkAYQBuAFMAdABhAHQAZQBzAFQAZQByAHIAaQB0AG8AcgBpAGUAcwBfAFMAbwB1AHIAYwBlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEEAdQBzAHQAcgBhAGwAaQBhAG4AUwB0AGEAdABlAHMAVABlAHIAcgBpAHQAbwByAGkAZQBzAF8ARABhAHQAYQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBXAEEAUwBBADQAQQByAGUAYQBzAF8AVABpAHQAbABlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFcAQQBTAEEANABBAHIAZQBhAHMAXwBWAGEAcgBpAGEAYgBsAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AVwBBAFMAQQA0AEEAcgBlAGEAcwBfAFUAbgBpAHQAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AVwBBAFMAQQA0AEEAcgBlAGEAcwBfAFMAbwB1AHIAYwBlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFcAQQBTAEEANABBAHIAZQBhAHMAXwBEAGEAdABhACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFcAZQB0AEEAbgBkAEQAcgB5AFoAbwBuAGUAcwBfAFQAaQB0AGwAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBXAGUAdABBAG4AZABEAHIAeQBaAG8AbgBlAHMAXwBWAGEAcgBpAGEAYgBsAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AVwBlAHQAQQBuAGQARAByAHkAWgBvAG4AZQBzAF8AVQBuAGkAdAAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBXAGUAdABBAG4AZABEAHIAeQBaAG8AbgBlAHMAXwBTAG8AdQByAGMAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBXAGUAdABBAG4AZABEAHIAeQBaAG8AbgBlAHMAXwBWAGEAcgBpAGEAdABpAG8AbgAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBXAGUAdABBAG4AZABEAHIAeQBaAG8AbgBlAHMAXwBEAGEAdABhACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEMAbABpAG0AYQB0AGUAWgBvAG4AZQBzAF8AVABpAHQAbABlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEMAbABpAG0AYQB0AGUAWgBvAG4AZQBzAF8AVgBhAHIAaQBhAGIAbABlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEMAbABpAG0AYQB0AGUAWgBvAG4AZQBzAF8AVQBuAGkAdAAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBDAGwAaQBtAGEAdABlAFoAbwBuAGUAcwBfAFMAbwB1AHIAYwBlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEMAbABpAG0AYQB0AGUAWgBvAG4AZQBzAF8AVgBhAHIAaQBhAHQAaQBvAG4AIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQwBsAGkAbQBhAHQAZQBaAG8AbgBlAHMAXwBEAGEAdABhACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEMAbABpAG0AYQB0AGUAWgBvAG4AZQBzAF8AQQBwAHAAZQBuAGQAaQBjAGUAcwAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBUAGUAbQBwAGUAcgBhAHQAdQByAGUAWgBvAG4AZQBzAF8AVABpAHQAbABlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFQAZQBtAHAAZQByAGEAdAB1AHIAZQBaAG8AbgBlAHMAXwBWAGEAcgBpAGEAYgBsAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AVABlAG0AcABlAHIAYQB0AHUAcgBlAFoAbwBuAGUAcwBfAFUAbgBpAHQAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AVABlAG0AcABlAHIAYQB0AHUAcgBlAFoAbwBuAGUAcwBfAFMAbwB1AHIAYwBlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFQAZQBtAHAAZQByAGEAdAB1AHIAZQBaAG8AbgBlAHMAXwBWAGEAcgBpAGEAdABpAG8AbgAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBUAGUAbQBwAGUAcgBhAHQAdQByAGUAWgBvAG4AZQBzAF8ARABhAHQAYQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBSAGEAaQBuAGYAYQBsAGwAWgBvAG4AZQBzAF8AVABpAHQAbABlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFIAYQBpAG4AZgBhAGwAbABaAG8AbgBlAHMAXwBWAGEAcgBpAGEAYgBsAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AUgBhAGkAbgBmAGEAbABsAFoAbwBuAGUAcwBfAFUAbgBpAHQAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AUgBhAGkAbgBmAGEAbABsAFoAbwBuAGUAcwBfAFMAbwB1AHIAYwBlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFIAYQBpAG4AZgBhAGwAbABaAG8AbgBlAHMAXwBWAGEAcgBpAGEAdABpAG8AbgAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBSAGEAaQBuAGYAYQBsAGwAWgBvAG4AZQBzAF8ARABhAHQAYQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBMAGUAYQBjAGgAaQBuAGcAWgBvAG4AZQBzAF8AVABpAHQAbABlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEwAZQBhAGMAaABpAG4AZwBaAG8AbgBlAHMAXwBWAGEAcgBpAGEAYgBsAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ATABlAGEAYwBoAGkAbgBnAFoAbwBuAGUAcwBfAFUAbgBpAHQAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ATABlAGEAYwBoAGkAbgBnAFoAbwBuAGUAcwBfAFMAbwB1AHIAYwBlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEwAZQBhAGMAaABpAG4AZwBaAG8AbgBlAHMAXwBWAGEAcgBpAGEAdABpAG8AbgAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBMAGUAYQBjAGgAaQBuAGcAWgBvAG4AZQBzAF8ARABhAHQAYQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAHIAYQBjAFcARQBUAF8AVABpAHQAbABlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAcgBhAGMAVwBFAFQAXwBVAG4AaQB0ACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAcgBhAGMAVwBFAFQAXwBTAG8AdQByAGMAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAHIAYQBjAFcARQBUAF8ATgBJAFIAUgBlAGYAZQByAGUAbgBjAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgByAGEAYwBXAEUAVABfAEQAYQB0AGEAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgByAGEAYwBXAEUAVABfAFYAYQByAGkAYQB0AGkAbwBuACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEQAYQB0AGEAUwBjAG8AcgBlAHMAXwBTAGMAbwBwAGUAMwBfAFQAaQB0AGwAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGEAdABhAFMAYwBvAHIAZQBzAF8AUwBjAG8AcABlADMAXwBWAGEAcgBpAGEAYgBsAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABhAHQAYQBTAGMAbwByAGUAcwBfAFMAYwBvAHAAZQAzAF8AVQBuAGkAdAAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGEAdABhAFMAYwBvAHIAZQBzAF8AUwBjAG8AcABlADMAXwBTAG8AdQByAGMAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGEAdABhAFMAYwBvAHIAZQBzAF8AUwBjAG8AcABlADMAXwBWAGEAcgBpAGEAdABpAG8AbgAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGEAdABhAFMAYwBvAHIAZQBzAF8AUwBjAG8AcABlADMAXwBEAGEAdABhACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAcgBhAGMATABFAEEAQwBIAF8AVABpAHQAbABlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAcgBhAGMATABFAEEAQwBIAF8AVQBuAGkAdAAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAHIAYQBjAEwARQBBAEMASABfAFMAbwB1AHIAYwBlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAcgBhAGMATABFAEEAQwBIAF8ATgBJAFIAUgBlAGYAZQByAGUAbgBjAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgByAGEAYwBMAEUAQQBDAEgAXwBEAGEAdABhACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAcgBhAGMATABFAEEAQwBIAF8AVgBhAHIAaQBhAHQAaQBvAG4AIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAGwAZQBhAGMAaABfAFQAaQB0AGwAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYAbABlAGEAYwBoAF8AVQBuAGkAdAAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYAbABlAGEAYwBoAF8AUwBvAHUAcgBjAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAGwAZQBhAGMAaABfAE4ASQBSAFIAZQBmAGUAcgBlAG4AYwBlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEUARgBsAGUAYQBjAGgAXwBEAGEAdABhACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEUARgBsAGUAYQBjAGgAXwBWAGEAcgBpAGEAdABpAG8AbgAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYATgAyAE8AXwBUAGkAdABsAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAE4AMgBPAF8AVQBuAGkAdAAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYATgAyAE8AXwBTAG8AdQByAGMAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYATgAyAE8AXwBOAEkAUgBSAGUAZgBlAHIAZQBuAGMAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYATgAyAE8AXwBEAGEAdABhACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEUARgBOADIATwBfAFYAYQByAGkAYQB0AGkAbwBuACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAcgBhAGMAVwBFAFQASQByAHIAaQBnAGEAdABpAG8AbgBfAFQAaQB0AGwAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAHIAYQBjAFcARQBUAEkAcgByAGkAZwBhAHQAaQBvAG4AXwBVAG4AaQB0ACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAcgBhAGMAVwBFAFQASQByAHIAaQBnAGEAdABpAG8AbgBfAFMAbwB1AHIAYwBlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAcgBhAGMAVwBFAFQASQByAHIAaQBnAGEAdABpAG8AbgBfAE4ASQBSAFIAZQBmAGUAcgBlAG4AYwBlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAcgBhAGMAVwBFAFQASQByAHIAaQBnAGEAdABpAG8AbgBfAEQAYQB0AGEAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgByAGEAYwBXAEUAVABJAHIAcgBpAGcAYQB0AGkAbwBuAF8AVgBhAHIAaQBhAHQAaQBvAG4AIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAFAAYQBzAHQAdQByAGUAUgBhAG4AZwBlAEEAbgBkAFAAYQBkAGQAbwBjAGsAXwBUAGkAdABsAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAFAAYQBzAHQAdQByAGUAUgBhAG4AZwBlAEEAbgBkAFAAYQBkAGQAbwBjAGsAXwBVAG4AaQB0ACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEUARgBQAGEAcwB0AHUAcgBlAFIAYQBuAGcAZQBBAG4AZABQAGEAZABkAG8AYwBrAF8AUwBvAHUAcgBjAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAFAAYQBzAHQAdQByAGUAUgBhAG4AZwBlAEEAbgBkAFAAYQBkAGQAbwBjAGsAXwBOAEkAUgBSAGUAZgBlAHIAZQBuAGMAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYAUABhAHMAdAB1AHIAZQBSAGEAbgBnAGUAQQBuAGQAUABhAGQAZABvAGMAawBfAEQAYQB0AGEAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAFAAYQBzAHQAdQByAGUAUgBhAG4AZwBlAEEAbgBkAFAAYQBkAGQAbwBjAGsAXwBWAGEAcgBpAGEAdABpAG8AbgAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBNAG8AbgB0AGgAcwBUAG8AUwBlAGEAcwBvAG4AcwBfAFQAaQB0AGwAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBNAG8AbgB0AGgAcwBUAG8AUwBlAGEAcwBvAG4AcwBfAFUAbgBpAHQAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ATQBvAG4AdABoAHMAVABvAFMAZQBhAHMAbwBuAHMAXwBTAG8AdQByAGMAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBNAG8AbgB0AGgAcwBUAG8AUwBlAGEAcwBvAG4AcwBfAE4ASQBSAFIAZQBmAGUAcgBlAG4AYwBlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAE0AbwBuAHQAaABzAFQAbwBTAGUAYQBzAG8AbgBzAF8ARABhAHQAYQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBNAG8AbgB0AGgAcwBUAG8AUwBlAGEAcwBvAG4AcwBfAFYAYQByAGkAYQB0AGkAbwBuACIAXQAsACIAbABvAGMAYQBsAGUAIgA6AHsAIgBsAGkAcwB0AFMAZQBwAGEAcgBhAHQAbwByACIAOgAiACwAIgAsACIAcgBvAHcAUwBlAHAAYQByAGEAdABvAHIAIgA6ACIAOwAiACwAIgBjAG8AbAB1AG0AbgBTAGUAcABhAHIAYQB0AG8AcgAiADoAIgAsACIALAAiAHQAaABvAHUAcwBhAG4AZABzAFMAZQBwAGEAcgBhAHQAbwByACIAOgAiACwAIgAsACIAdABoAG8AdQBzAGEAbgBkAHMAUABvAHMAaQB0AGkAbwBuAHMAIgA6AFsAMwBdACwAIgBkAGUAYwBpAG0AYQBsAFMAZQBwAGEAcgBhAHQAbwByACIAOgAiAC4AIgAsACIAZABhAHQAZQBPAHIAZABlAHIAIgA6ACIARABNAFkAIgAsACIAYwB1AHIAcgBlAG4AYwB5AFMAeQBtAGIAbwBsACIAOgAiACQAIgAsACIAaQBzAEMAdQByAHIAZQBuAGMAeQBTAHkAbQBiAG8AbABMAGUAYQBkACIAOgB0AHIAdQBlACwAIgBpAHMAQwB1AHIAcgBlAG4AYwB5AFMAZQBwAEIAeQBTAHAAYQBjAGUAIgA6AGYAYQBsAHMAZQAsACIAcgBvAHcATABlAHQAdABlAHIAIgA6ACIAUgAiACwAIgBjAG8AbAB1AG0AbgBMAGUAdAB0AGUAcgAiADoAIgBDACIALAAiAHIAYwBMAGUAZgB0AEIAcgBhAGMAawBlAHQAIgA6ACIAWwAiACwAIgByAGMAUgBpAGcAaAB0AEIAcgBhAGMAawBlAHQAIgA6ACIAXQAiACwAIgBzAHQAYQB0AGUAbQBlAG4AdABTAGUAcABhAHIAYQB0AG8AcgAiADoAIgA7ACIALAAiAGwAbwBjAGEAbABlAE4AYQBtAGUAIgA6ACIAZQBuAC0AdQBzACIAfQB9AA==</AFEJSONBlob>
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{9A9CF321-0D35-4044-BC72-33748FE2B865}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{CD460F9D-420A-4723-B323-396E4D19EC9B}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="09eef6d6-daa8-4301-8f9f-b1ec38079286"/>
+    <ds:schemaRef ds:uri="7291119c-fce9-4911-96ae-b800be5dccd8"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{809E3D44-A88D-4EBF-A307-6B8CE77A3361}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -11634,25 +11652,6 @@
 </ds:datastoreItem>
 </file>
 
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{CD460F9D-420A-4723-B323-396E4D19EC9B}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="09eef6d6-daa8-4301-8f9f-b1ec38079286"/>
-    <ds:schemaRef ds:uri="7291119c-fce9-4911-96ae-b800be5dccd8"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{9A9CF321-0D35-4044-BC72-33748FE2B865}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
-</file>
-
 <file path=customXml/itemProps4.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{B6BE249C-20B1-4A62-BBCD-F2A46D88BCAB}">
   <ds:schemaRefs>

--- a/Excel/Enterprises/Enterprise_Dairy_Template_WIP_v01.xlsx
+++ b/Excel/Enterprises/Enterprise_Dairy_Template_WIP_v01.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\htdocs\zneagcrc\GAF-VEERG-Functions\Excel\Enterprises\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7D71B0AC-45A4-4F70-8D83-38B32B724417}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E0E4F344-6AEF-44BB-B4E3-D8BBE908E514}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1320" yWindow="195" windowWidth="36255" windowHeight="19140" activeTab="1" xr2:uid="{992023F3-CAB7-4E5B-A348-08D563A0EF40}"/>
+    <workbookView xWindow="2085" yWindow="1065" windowWidth="36255" windowHeight="19140" activeTab="1" xr2:uid="{992023F3-CAB7-4E5B-A348-08D563A0EF40}"/>
   </bookViews>
   <sheets>
     <sheet name="Home" sheetId="71" r:id="rId1"/>
@@ -346,7 +346,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="330" uniqueCount="203">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="312" uniqueCount="198">
   <si>
     <t>Home</t>
   </si>
@@ -795,9 +795,6 @@
     <t>Co-product</t>
   </si>
   <si>
-    <t>N/A</t>
-  </si>
-  <si>
     <t>Carbon removals from plantings</t>
   </si>
   <si>
@@ -822,18 +819,9 @@
     <t>Method 2</t>
   </si>
   <si>
-    <t>Liveweight grown - Method 1</t>
-  </si>
-  <si>
-    <t>Liveweight grown - Method 2</t>
-  </si>
-  <si>
     <t>Product</t>
   </si>
   <si>
-    <t>t co2e/t liveweight grown</t>
-  </si>
-  <si>
     <t>5.1.1.1-2 Inorganic fert N2O</t>
   </si>
   <si>
@@ -904,9 +892,6 @@
   </si>
   <si>
     <t>Economic emissions assignment</t>
-  </si>
-  <si>
-    <t>Emissions per tonne liveweight grown</t>
   </si>
   <si>
     <t>Liveweight sold - excluding removals</t>
@@ -4182,7 +4167,7 @@
     <tabColor rgb="FF0C769E"/>
     <pageSetUpPr autoPageBreaks="0"/>
   </sheetPr>
-  <dimension ref="A1:K88"/>
+  <dimension ref="A1:K84"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="30.7109375" customWidth="1"/>
@@ -4198,7 +4183,7 @@
         <v>#VALUE!</v>
       </c>
       <c r="C1" s="22" t="s">
-        <v>179</v>
+        <v>174</v>
       </c>
     </row>
     <row r="2" spans="1:11" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
@@ -4283,7 +4268,7 @@
       </c>
       <c r="C7" s="9"/>
       <c r="D7" s="1" t="s">
-        <v>180</v>
+        <v>175</v>
       </c>
       <c r="E7" s="19" t="e" cm="1">
         <f t="array" ref="E7">VEERG_3_3_1_1__1_TotalAnnualMethaneFromEntericFermentationVariation_Result_Method1</f>
@@ -4316,7 +4301,7 @@
       </c>
       <c r="C8" s="9"/>
       <c r="D8" s="1" t="s">
-        <v>181</v>
+        <v>176</v>
       </c>
       <c r="E8" s="19" t="e" cm="1">
         <f t="array" ref="E8">VEERG_4_3_1_1__1_TotalAnnualMethaneFromManureManagement_Result_Method1</f>
@@ -4346,7 +4331,7 @@
       <c r="A9" s="5"/>
       <c r="C9" s="9"/>
       <c r="D9" s="1" t="s">
-        <v>182</v>
+        <v>177</v>
       </c>
       <c r="E9" s="19" t="e" cm="1">
         <f t="array" ref="E9">VEERG_4_3_1_3__1_TotalAnnualDirectNitrousOxideEmissionsFromMMS_Result_Method1</f>
@@ -4378,7 +4363,7 @@
       </c>
       <c r="C10" s="9"/>
       <c r="D10" s="1" t="s">
-        <v>183</v>
+        <v>178</v>
       </c>
       <c r="E10" s="19" t="e" cm="1">
         <f t="array" ref="E10">VEERG_4_3_1_5__1_AnnualAtmosphericDepositionEmissionsFromMMS_Result_Method1</f>
@@ -4411,7 +4396,7 @@
       </c>
       <c r="C11" s="9"/>
       <c r="D11" s="1" t="s">
-        <v>184</v>
+        <v>179</v>
       </c>
       <c r="E11" s="19" t="e" cm="1">
         <f t="array" ref="E11">VEERG_4_3_1_6__1_AnnualEmissionsFromLeachingAndRunoffFromMMS_Result_Method1</f>
@@ -4444,7 +4429,7 @@
       </c>
       <c r="C12" s="9"/>
       <c r="D12" s="1" t="s">
-        <v>185</v>
+        <v>180</v>
       </c>
       <c r="E12" s="19" t="e" cm="1">
         <f t="array" ref="E12">VEERG_4_3_1_9__1_DirectNitrousOxideEmissionsOnPasture_Result_Method1</f>
@@ -4477,7 +4462,7 @@
       </c>
       <c r="C13" s="9"/>
       <c r="D13" s="1" t="s">
-        <v>186</v>
+        <v>181</v>
       </c>
       <c r="E13" s="19" t="e" cm="1">
         <f t="array" ref="E13">VEERG_4_3_1_10__1_AtmosphericDepositionEmissionsFromUrineAndDungOnPasture_Result_Method1</f>
@@ -4510,7 +4495,7 @@
       </c>
       <c r="C14" s="9"/>
       <c r="D14" s="1" t="s">
-        <v>187</v>
+        <v>182</v>
       </c>
       <c r="E14" s="19" t="e" cm="1">
         <f t="array" ref="E14">VEERG_4_3_1_12__1_LeachingAndRunoffEmissionsFromUrineAndDungOnPasture_Result_Method1</f>
@@ -4540,7 +4525,7 @@
       <c r="A15" s="5"/>
       <c r="C15" s="9"/>
       <c r="D15" s="1" t="s">
-        <v>144</v>
+        <v>140</v>
       </c>
       <c r="E15" s="19" t="e" cm="1">
         <f t="array" ref="E15">VEERG_5_1_1_1__1_InorganicFertiliserApplicationN2OEmissions_Result_Method1</f>
@@ -4572,7 +4557,7 @@
       </c>
       <c r="C16" s="9"/>
       <c r="D16" s="1" t="s">
-        <v>145</v>
+        <v>141</v>
       </c>
       <c r="E16" s="19" t="e" cm="1">
         <f t="array" ref="E16">VEERG_5_1_1_3__1_InorganicFertiliserApplicationCO2Emissions_Result_Method1</f>
@@ -4583,7 +4568,7 @@
         <v>#NAME?</v>
       </c>
       <c r="G16" s="16" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="H16" s="19" t="e">
         <f>E16</f>
@@ -4605,7 +4590,7 @@
       </c>
       <c r="C17" s="9"/>
       <c r="D17" s="1" t="s">
-        <v>146</v>
+        <v>142</v>
       </c>
       <c r="E17" s="19" t="e" cm="1">
         <f t="array" ref="E17">VEERG_5_2_1_1__2_MassOfNitrogenInOrganicFertiliser_Result_Method1</f>
@@ -4638,7 +4623,7 @@
       </c>
       <c r="C18" s="9"/>
       <c r="D18" s="1" t="s">
-        <v>147</v>
+        <v>143</v>
       </c>
       <c r="E18" s="19" t="e" cm="1">
         <f t="array" ref="E18">VEERG_5_3_1_1__1_LimeApplicationCO2Emissions_Result_Method1</f>
@@ -4649,7 +4634,7 @@
         <v>#NAME?</v>
       </c>
       <c r="G18" s="16" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="H18" s="19" t="e">
         <f>E18</f>
@@ -4671,7 +4656,7 @@
       </c>
       <c r="C19" s="9"/>
       <c r="D19" s="1" t="s">
-        <v>148</v>
+        <v>144</v>
       </c>
       <c r="E19" s="19" t="e" cm="1">
         <f t="array" ref="E19">VEERG_5_4_1_3__1_OrganicFertiliserAtmosphericDepositionN2OEmissions_Result_Method1</f>
@@ -4704,7 +4689,7 @@
       </c>
       <c r="C20" s="9"/>
       <c r="D20" s="1" t="s">
-        <v>149</v>
+        <v>145</v>
       </c>
       <c r="E20" s="19" t="e" cm="1">
         <f t="array" ref="E20">VEERG_5_5_1_1__1_FertiliserLeachingAndRunoffN2OEmissions_result_Method1</f>
@@ -4733,7 +4718,7 @@
     <row r="21" spans="1:11" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C21" s="9"/>
       <c r="D21" s="1" t="s">
-        <v>150</v>
+        <v>146</v>
       </c>
       <c r="E21" s="19" t="e" cm="1">
         <f t="array" ref="E21">VEERG_6_2_1_1__1__NitrousOxideEmissionsFromPastureResidues_Result_Method1</f>
@@ -4763,7 +4748,7 @@
       <c r="A22" s="5"/>
       <c r="C22" s="9"/>
       <c r="D22" s="1" t="s">
-        <v>151</v>
+        <v>147</v>
       </c>
       <c r="E22" s="19" t="e" cm="1">
         <f t="array" ref="E22">VEERG_6_3_1_1__1__LeachingAndRunoffEmissionsCropAndPastureResidue_PastureOnly_Result_Method1</f>
@@ -4793,7 +4778,7 @@
       <c r="A23" s="5"/>
       <c r="C23" s="9"/>
       <c r="D23" s="1" t="s">
-        <v>152</v>
+        <v>148</v>
       </c>
       <c r="E23" s="19" t="e" cm="1">
         <f t="array" ref="E23">VEERG_8_1_1_1__1_FuelCombustionTransport_Result_CO2</f>
@@ -4804,7 +4789,7 @@
         <v>#NAME?</v>
       </c>
       <c r="G23" s="16" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="H23" s="19" t="e">
         <f>E23</f>
@@ -4823,7 +4808,7 @@
       <c r="A24" s="5"/>
       <c r="C24" s="9"/>
       <c r="D24" s="1" t="s">
-        <v>154</v>
+        <v>150</v>
       </c>
       <c r="E24" s="19" t="e" cm="1">
         <f t="array" ref="E24">VEERG_8_1_1_1__1_FuelCombustionTransport_Result_CH4</f>
@@ -4852,7 +4837,7 @@
     <row r="25" spans="1:11" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C25" s="9"/>
       <c r="D25" s="1" t="s">
-        <v>153</v>
+        <v>149</v>
       </c>
       <c r="E25" s="19" t="e" cm="1">
         <f t="array" ref="E25">VEERG_8_1_1_1__1_FuelCombustionTransport_Result_N2O</f>
@@ -4881,7 +4866,7 @@
     <row r="26" spans="1:11" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C26" s="9"/>
       <c r="D26" s="1" t="s">
-        <v>155</v>
+        <v>151</v>
       </c>
       <c r="E26" s="19" t="e" cm="1">
         <f t="array" ref="E26">VEERG_8_2_1_1__1_FuelCombustionStationary_Result_CO2</f>
@@ -4892,7 +4877,7 @@
         <v>#NAME?</v>
       </c>
       <c r="G26" s="16" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="H26" s="19" t="e">
         <f>E26</f>
@@ -4910,7 +4895,7 @@
     <row r="27" spans="1:11" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C27" s="9"/>
       <c r="D27" s="1" t="s">
-        <v>156</v>
+        <v>152</v>
       </c>
       <c r="E27" s="19" t="e" cm="1">
         <f t="array" ref="E27">VEERG_8_2_1_1__1_FuelCombustionStationary_Result_CH4</f>
@@ -4939,7 +4924,7 @@
     <row r="28" spans="1:11" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C28" s="9"/>
       <c r="D28" s="1" t="s">
-        <v>157</v>
+        <v>153</v>
       </c>
       <c r="E28" s="19" t="e" cm="1">
         <f t="array" ref="E28">VEERG_8_2_1_1__1_FuelCombustionStationary_Result_N2O</f>
@@ -4968,7 +4953,7 @@
     <row r="29" spans="1:11" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C29" s="9"/>
       <c r="D29" s="1" t="s">
-        <v>158</v>
+        <v>154</v>
       </c>
       <c r="E29" s="19" t="e" cm="1">
         <f t="array" ref="E29">VEERG_14_1_1__1_LocationBasedScopeElectricityEmissions_Result_Method1</f>
@@ -4997,7 +4982,7 @@
     <row r="30" spans="1:11" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C30" s="9"/>
       <c r="D30" s="1" t="s">
-        <v>159</v>
+        <v>155</v>
       </c>
       <c r="E30" s="19" t="e" cm="1">
         <f t="array" ref="E30">VEERG_14_1_2__1_MarketBasedScopeElectricityEmissionsVariation_Result_Method1</f>
@@ -5250,7 +5235,7 @@
     <row r="45" spans="3:11" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C45" s="9"/>
       <c r="D45" s="15" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="E45" s="20" t="e">
         <f>SUM(E40:E44)</f>
@@ -5291,7 +5276,7 @@
     <row r="48" spans="3:11" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C48" s="9"/>
       <c r="D48" s="2" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="E48" s="1"/>
       <c r="F48" s="1"/>
@@ -5318,7 +5303,7 @@
         <v>118</v>
       </c>
       <c r="E50" s="21" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="F50" s="1"/>
       <c r="G50" s="1"/>
@@ -5338,7 +5323,7 @@
         <v>Enter value</v>
       </c>
       <c r="F51" s="16" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="G51" s="1"/>
       <c r="H51" s="1"/>
@@ -5356,7 +5341,7 @@
         <v>Enter value</v>
       </c>
       <c r="F52" s="16" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="G52" s="1"/>
       <c r="H52" s="1"/>
@@ -5374,7 +5359,7 @@
         <v>Enter value</v>
       </c>
       <c r="F53" s="16" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="G53" s="1"/>
       <c r="H53" s="1"/>
@@ -5390,7 +5375,7 @@
         <v/>
       </c>
       <c r="F54" s="16" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="G54" s="1"/>
       <c r="H54" s="1"/>
@@ -5406,7 +5391,7 @@
         <v/>
       </c>
       <c r="F55" s="16" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="G55" s="1"/>
       <c r="H55" s="1"/>
@@ -5417,7 +5402,7 @@
     <row r="56" spans="3:11" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C56" s="9"/>
       <c r="D56" s="15" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="E56" s="20">
         <f>SUM(E51:E54)</f>
@@ -5480,10 +5465,10 @@
       <c r="C61" s="9"/>
       <c r="D61" s="21"/>
       <c r="E61" s="21" t="s">
+        <v>137</v>
+      </c>
+      <c r="F61" s="21" t="s">
         <v>138</v>
-      </c>
-      <c r="F61" s="21" t="s">
-        <v>139</v>
       </c>
       <c r="G61" s="1"/>
       <c r="H61" s="1"/>
@@ -5494,7 +5479,7 @@
     <row r="62" spans="3:11" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C62" s="9"/>
       <c r="D62" s="89" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="E62" s="87" t="e">
         <f>E45-E56</f>
@@ -5535,7 +5520,7 @@
     <row r="65" spans="3:11" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C65" s="9"/>
       <c r="D65" s="91" t="s">
-        <v>164</v>
+        <v>160</v>
       </c>
       <c r="E65" s="1"/>
       <c r="F65" s="1"/>
@@ -5548,7 +5533,7 @@
     <row r="66" spans="3:11" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C66" s="9"/>
       <c r="D66" s="21" t="s">
-        <v>142</v>
+        <v>139</v>
       </c>
       <c r="E66" s="21" t="s">
         <v>128</v>
@@ -5557,7 +5542,7 @@
         <v>122</v>
       </c>
       <c r="G66" s="21" t="s">
-        <v>166</v>
+        <v>162</v>
       </c>
       <c r="H66" s="21" t="s">
         <v>126</v>
@@ -5573,7 +5558,7 @@
     <row r="67" spans="3:11" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C67" s="9"/>
       <c r="D67" s="1" t="s">
-        <v>200</v>
+        <v>195</v>
       </c>
       <c r="E67" s="1" t="s">
         <v>129</v>
@@ -5595,14 +5580,14 @@
         <v>#NAME?</v>
       </c>
       <c r="J67" s="16" t="s">
-        <v>202</v>
+        <v>197</v>
       </c>
       <c r="K67" s="9"/>
     </row>
     <row r="68" spans="3:11" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C68" s="9"/>
       <c r="D68" s="1" t="s">
-        <v>201</v>
+        <v>196</v>
       </c>
       <c r="E68" s="1" t="s">
         <v>129</v>
@@ -5624,14 +5609,14 @@
         <v>#NAME?</v>
       </c>
       <c r="J68" s="16" t="s">
-        <v>202</v>
+        <v>197</v>
       </c>
       <c r="K68" s="9"/>
     </row>
     <row r="69" spans="3:11" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C69" s="9"/>
       <c r="D69" s="1" t="s">
-        <v>169</v>
+        <v>164</v>
       </c>
       <c r="E69" s="1" t="s">
         <v>129</v>
@@ -5660,7 +5645,7 @@
     <row r="70" spans="3:11" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C70" s="9"/>
       <c r="D70" s="1" t="s">
-        <v>170</v>
+        <v>165</v>
       </c>
       <c r="E70" s="1" t="s">
         <v>129</v>
@@ -5689,7 +5674,7 @@
     <row r="71" spans="3:11" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C71" s="9"/>
       <c r="D71" s="1" t="s">
-        <v>171</v>
+        <v>166</v>
       </c>
       <c r="E71" s="1" t="s">
         <v>130</v>
@@ -5718,7 +5703,7 @@
     <row r="72" spans="3:11" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C72" s="9"/>
       <c r="D72" s="1" t="s">
-        <v>172</v>
+        <v>167</v>
       </c>
       <c r="E72" s="1" t="s">
         <v>130</v>
@@ -5769,7 +5754,7 @@
     <row r="75" spans="3:11" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C75" s="9"/>
       <c r="D75" s="91" t="s">
-        <v>165</v>
+        <v>161</v>
       </c>
       <c r="E75" s="1"/>
       <c r="F75" s="1"/>
@@ -5782,7 +5767,7 @@
     <row r="76" spans="3:11" ht="15.75" x14ac:dyDescent="0.25">
       <c r="C76" s="9"/>
       <c r="D76" s="21" t="s">
-        <v>142</v>
+        <v>139</v>
       </c>
       <c r="E76" s="21" t="s">
         <v>128</v>
@@ -5791,7 +5776,7 @@
         <v>122</v>
       </c>
       <c r="G76" s="21" t="s">
-        <v>167</v>
+        <v>163</v>
       </c>
       <c r="H76" s="21" t="s">
         <v>126</v>
@@ -5807,7 +5792,7 @@
     <row r="77" spans="3:11" ht="15.75" x14ac:dyDescent="0.25">
       <c r="C77" s="9"/>
       <c r="D77" s="1" t="s">
-        <v>200</v>
+        <v>195</v>
       </c>
       <c r="E77" s="1" t="s">
         <v>129</v>
@@ -5829,20 +5814,20 @@
         <v>#NAME?</v>
       </c>
       <c r="J77" s="16" t="s">
-        <v>202</v>
+        <v>197</v>
       </c>
       <c r="K77" s="9"/>
     </row>
     <row r="78" spans="3:11" ht="15.75" x14ac:dyDescent="0.25">
       <c r="C78" s="9"/>
       <c r="D78" s="1" t="s">
-        <v>201</v>
+        <v>196</v>
       </c>
       <c r="E78" s="1" t="s">
         <v>129</v>
       </c>
       <c r="F78" s="94" t="e">
-        <f t="shared" ref="F78:I78" si="2">F68</f>
+        <f t="shared" ref="F78" si="2">F68</f>
         <v>#NAME?</v>
       </c>
       <c r="G78" s="19">
@@ -5858,14 +5843,14 @@
         <v>#NAME?</v>
       </c>
       <c r="J78" s="16" t="s">
-        <v>202</v>
+        <v>197</v>
       </c>
       <c r="K78" s="9"/>
     </row>
     <row r="79" spans="3:11" ht="15.75" x14ac:dyDescent="0.25">
       <c r="C79" s="9"/>
       <c r="D79" s="1" t="s">
-        <v>169</v>
+        <v>164</v>
       </c>
       <c r="E79" s="1" t="s">
         <v>129</v>
@@ -5894,7 +5879,7 @@
     <row r="80" spans="3:11" ht="15.75" x14ac:dyDescent="0.25">
       <c r="C80" s="9"/>
       <c r="D80" s="1" t="s">
-        <v>170</v>
+        <v>165</v>
       </c>
       <c r="E80" s="1" t="s">
         <v>129</v>
@@ -5923,7 +5908,7 @@
     <row r="81" spans="3:11" ht="15.75" x14ac:dyDescent="0.25">
       <c r="C81" s="9"/>
       <c r="D81" s="1" t="s">
-        <v>171</v>
+        <v>166</v>
       </c>
       <c r="E81" s="1" t="s">
         <v>130</v>
@@ -5952,7 +5937,7 @@
     <row r="82" spans="3:11" ht="15.75" x14ac:dyDescent="0.25">
       <c r="C82" s="9"/>
       <c r="D82" s="1" t="s">
-        <v>172</v>
+        <v>167</v>
       </c>
       <c r="E82" s="1" t="s">
         <v>130</v>
@@ -5999,96 +5984,6 @@
       <c r="I84" s="1"/>
       <c r="J84" s="1"/>
       <c r="K84" s="9"/>
-    </row>
-    <row r="85" spans="3:11" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="C85" s="9"/>
-      <c r="D85" s="91" t="s">
-        <v>168</v>
-      </c>
-      <c r="E85" s="1"/>
-      <c r="F85" s="1"/>
-      <c r="G85" s="1"/>
-      <c r="H85" s="1"/>
-      <c r="I85" s="1"/>
-      <c r="J85" s="1"/>
-      <c r="K85" s="9"/>
-    </row>
-    <row r="86" spans="3:11" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="C86" s="9"/>
-      <c r="D86" s="21" t="s">
-        <v>142</v>
-      </c>
-      <c r="E86" s="21" t="s">
-        <v>128</v>
-      </c>
-      <c r="F86" s="21" t="s">
-        <v>122</v>
-      </c>
-      <c r="G86" s="21" t="s">
-        <v>167</v>
-      </c>
-      <c r="H86" s="21" t="s">
-        <v>126</v>
-      </c>
-      <c r="I86" s="21" t="s">
-        <v>127</v>
-      </c>
-      <c r="J86" s="21" t="s">
-        <v>123</v>
-      </c>
-      <c r="K86" s="9"/>
-    </row>
-    <row r="87" spans="3:11" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="C87" s="9"/>
-      <c r="D87" s="1" t="s">
-        <v>140</v>
-      </c>
-      <c r="E87" s="1" t="s">
-        <v>131</v>
-      </c>
-      <c r="F87" s="19" t="e">
-        <f>'Input - Enterprise'!E23</f>
-        <v>#NAME?</v>
-      </c>
-      <c r="G87" s="19" t="s">
-        <v>131</v>
-      </c>
-      <c r="H87" s="19" t="e">
-        <f>E62/F87</f>
-        <v>#NAME?</v>
-      </c>
-      <c r="I87" s="19" t="s">
-        <v>131</v>
-      </c>
-      <c r="J87" s="16" t="s">
-        <v>143</v>
-      </c>
-      <c r="K87" s="9"/>
-    </row>
-    <row r="88" spans="3:11" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="D88" s="1" t="s">
-        <v>141</v>
-      </c>
-      <c r="E88" s="1" t="s">
-        <v>131</v>
-      </c>
-      <c r="F88" s="19" t="e">
-        <f>'Input - Enterprise'!E24</f>
-        <v>#NAME?</v>
-      </c>
-      <c r="G88" s="19" t="s">
-        <v>131</v>
-      </c>
-      <c r="H88" s="19" t="s">
-        <v>131</v>
-      </c>
-      <c r="I88" s="19" t="e">
-        <f>F62/F88</f>
-        <v>#NAME?</v>
-      </c>
-      <c r="J88" s="16" t="s">
-        <v>143</v>
-      </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -6887,7 +6782,7 @@
   <sheetData>
     <row r="1" spans="3:10" ht="25.5" x14ac:dyDescent="0.35">
       <c r="C1" s="38" t="s">
-        <v>160</v>
+        <v>156</v>
       </c>
       <c r="D1" s="32"/>
       <c r="E1" s="32"/>
@@ -7053,7 +6948,7 @@
     </row>
     <row r="23" spans="4:7" x14ac:dyDescent="0.25">
       <c r="D23" s="1" t="s">
-        <v>197</v>
+        <v>192</v>
       </c>
       <c r="E23" s="90" t="e" cm="1">
         <f t="array" ref="E23">X_Cell_Dairy_MilkProductionUnit</f>
@@ -7063,7 +6958,7 @@
     </row>
     <row r="24" spans="4:7" x14ac:dyDescent="0.25">
       <c r="D24" s="1" t="s">
-        <v>196</v>
+        <v>191</v>
       </c>
       <c r="E24" s="90" t="e" cm="1">
         <f t="array" ref="E24">X_Cell_Dairy_MilkProductionAmount*365*IF(E23="Milk solds", 1, 1.03)</f>
@@ -7075,7 +6970,7 @@
     </row>
     <row r="25" spans="4:7" x14ac:dyDescent="0.25">
       <c r="D25" s="1" t="s">
-        <v>199</v>
+        <v>194</v>
       </c>
       <c r="E25" s="86">
         <v>1</v>
@@ -7086,35 +6981,35 @@
     </row>
     <row r="27" spans="4:7" x14ac:dyDescent="0.25">
       <c r="D27" s="1" t="s">
-        <v>162</v>
+        <v>158</v>
       </c>
       <c r="E27" s="29">
         <v>0.15</v>
       </c>
       <c r="G27" s="27" t="s">
-        <v>161</v>
+        <v>157</v>
       </c>
     </row>
     <row r="28" spans="4:7" x14ac:dyDescent="0.25">
       <c r="D28" s="1" t="s">
-        <v>163</v>
+        <v>159</v>
       </c>
       <c r="E28" s="29">
         <v>0.05</v>
       </c>
       <c r="G28" s="27" t="s">
-        <v>161</v>
+        <v>157</v>
       </c>
     </row>
     <row r="29" spans="4:7" x14ac:dyDescent="0.25">
       <c r="D29" s="1" t="s">
-        <v>198</v>
+        <v>193</v>
       </c>
       <c r="E29" s="29">
         <v>0.8</v>
       </c>
       <c r="G29" s="27" t="s">
-        <v>161</v>
+        <v>157</v>
       </c>
     </row>
   </sheetData>
@@ -7142,7 +7037,7 @@
         <v>#VALUE!</v>
       </c>
       <c r="C1" s="17" t="s">
-        <v>188</v>
+        <v>183</v>
       </c>
     </row>
     <row r="2" spans="1:13" s="3" customFormat="1" x14ac:dyDescent="0.25"/>
@@ -7161,27 +7056,27 @@
     </row>
     <row r="5" spans="1:13" x14ac:dyDescent="0.25">
       <c r="D5" s="92" t="s">
-        <v>189</v>
+        <v>184</v>
       </c>
     </row>
     <row r="6" spans="1:13" x14ac:dyDescent="0.25">
       <c r="D6" s="30" t="s">
+        <v>185</v>
+      </c>
+      <c r="E6" s="30" t="s">
+        <v>186</v>
+      </c>
+      <c r="F6" s="30" t="s">
+        <v>187</v>
+      </c>
+      <c r="G6" s="30" t="s">
+        <v>188</v>
+      </c>
+      <c r="H6" s="30" t="s">
+        <v>189</v>
+      </c>
+      <c r="I6" s="30" t="s">
         <v>190</v>
-      </c>
-      <c r="E6" s="30" t="s">
-        <v>191</v>
-      </c>
-      <c r="F6" s="30" t="s">
-        <v>192</v>
-      </c>
-      <c r="G6" s="30" t="s">
-        <v>193</v>
-      </c>
-      <c r="H6" s="30" t="s">
-        <v>194</v>
-      </c>
-      <c r="I6" s="30" t="s">
-        <v>195</v>
       </c>
     </row>
     <row r="7" spans="1:13" x14ac:dyDescent="0.25">
@@ -7333,7 +7228,7 @@
         <v>#VALUE!</v>
       </c>
       <c r="C1" s="17" t="s">
-        <v>173</v>
+        <v>168</v>
       </c>
     </row>
     <row r="2" spans="1:11" s="3" customFormat="1" x14ac:dyDescent="0.25"/>
@@ -7350,7 +7245,7 @@
     </row>
     <row r="5" spans="1:11" x14ac:dyDescent="0.25">
       <c r="D5" s="80" t="s">
-        <v>178</v>
+        <v>173</v>
       </c>
       <c r="E5" s="80"/>
       <c r="F5" s="80"/>
@@ -7361,19 +7256,19 @@
     </row>
     <row r="7" spans="1:11" x14ac:dyDescent="0.25">
       <c r="D7" s="1" t="s">
-        <v>174</v>
+        <v>169</v>
       </c>
       <c r="E7" s="26" t="s">
-        <v>177</v>
+        <v>172</v>
       </c>
       <c r="F7" s="27"/>
     </row>
     <row r="8" spans="1:11" x14ac:dyDescent="0.25">
       <c r="D8" s="1" t="s">
-        <v>175</v>
+        <v>170</v>
       </c>
       <c r="E8" s="26" t="s">
-        <v>177</v>
+        <v>172</v>
       </c>
       <c r="F8" s="27"/>
     </row>
@@ -7388,7 +7283,7 @@
     </row>
     <row r="10" spans="1:11" x14ac:dyDescent="0.25">
       <c r="D10" s="1" t="s">
-        <v>176</v>
+        <v>171</v>
       </c>
       <c r="E10" s="26" t="e" cm="1">
         <f t="array" ref="E10">X_Cell_Pasture_AreaUnderPasture</f>
@@ -11405,14 +11300,7 @@
 </file>
 
 <file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <TaxCatchAll xmlns="09eef6d6-daa8-4301-8f9f-b1ec38079286" xsi:nil="true"/>
-    <lcf76f155ced4ddcb4097134ff3c332f xmlns="7291119c-fce9-4911-96ae-b800be5dccd8">
-      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    </lcf76f155ced4ddcb4097134ff3c332f>
-  </documentManagement>
-</p:properties>
+<AFEJSONBlob xmlns="http://schemas.advancedformulaenvironment.officeapps.live.com/afejsonblob/1.0">ewAiAHMAYwBoAGUAbQBhACIAOgAiAGgAdAB0AHAAOgAvAC8AcwBjAGgAZQBtAGEAcwAuAGEAZAB2AGEAbgBjAGUAZABmAG8AcgBtAHUAbABhAGUAbgB2AGkAcgBvAG4AbQBlAG4AdAAuAG8AZgBmAGkAYwBlAGEAcABwAHMALgBsAGkAdgBlAC4AYwBvAG0ALwBhAGYAZQBwAHIAbwBqAGUAYwB0AHMALwAwAC4AMgAiACwAIgBmAGkAbABlAHMAIgA6AFsAewAiAHAAYQB0AGgAIgA6ACIALwBwAHIAbwBqAGUAYwB0AHMALwBXAG8AcgBrAGIAbwBvAGsAIgAsACIAdABlAHgAdAAiADoAIgAvAC8AIAAtAC0ALQAgAFcAbwByAGsAYgBvAG8AawAgAG0AbwBkAHUAbABlACAALQAtAC0AXABuAC8ALwAgAEEAIABmAGkAbABlACAAbwBmACAAbgBhAG0AZQAgAGQAZQBmAGkAbgBpAHQAaQBvAG4AcwAgAG8AZgAgAHQAaABlACAAZgBvAHIAbQA6AFwAbgAvAC8AIAAgACAAIABuAGEAbQBlACAAPQAgAGQAZQBmAGkAbgBpAHQAaQBvAG4AOwBcAG4AIgB9ACwAewAiAHAAYQB0AGgAIgA6ACIALwBwAHIAbwBqAGUAYwB0AHMALwBDAG8AbQBtAG8AbgBfAEUAcQB1AGEAdABpAG8AbgBzACIALAAiAHQAZQB4AHQAIgA6ACIAXABuAC8AKgAgAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuAEMAbwBtAG0AbwBuAF8AQwBvAG4AdgBlAHIAdABOADIATwBUAG8AQwBPADIAZQBcAG4AQwBvAG4AdgBlAHIAdAAgAG4AaQB0AHIAbwB1AHMAIABvAHgAaQBkAGUAIABlAG0AaQBzAHMAaQBvAG4AcwAgAHQAbwAgAGMAYQByAGIAbwBuACAAZABpAG8AeABpAGQAZQAgAGUAcQB1AGkAdgBhAGwAZQBuAHQAIABlAG0AaQBzAHMAaQBvAG4AcwBcAG4ARQBOADIATwAgAEMATwAyAGUAXABuAHQAIABDAE8AMgBlAFwAbgBFAE4AMgBPADoAIABuAGkAdAByAG8AdQBzACAAbwB4AGkAZABlACAAZQBtAGkAcwBzAGkAbwBuAHMAIAAoAHQAIABOADIATwApAFwAbgBHAFcAUABOADIATwA6ACAAZwBsAG8AYgBhAGwAIAB3AGEAcgBtAGkAbgBnACAAcABvAHQAZQBuAHQAaQBhAGwAIABmAG8AcgAgAG4AaQB0AHIAbwB1AHMAIABvAHgAaQBkAGUAIAAoAHQAIABDAE8AMgAtAGUAIAAvACAAdAAgAE4AMgBPACkAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AKgAvAFwAbgBcAG4AXABuAEMAbwBtAG0AbwBuAF8AQwBvAG4AdgBlAHIAdABOADIATwBUAG8AQwBPADIAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABFAF8ATgAyAE8ALAAgAEcAVwBQAF8ATgAyAE8ALABcAG4AIAAgACAAIABFAF8ATgAyAE8AIAAqACAARwBXAFAAXwBOADIATwBcAG4AIAAgACkAXABuADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAEMAbwBuAHYAZQByAHQATgAyAE8AVABvAEMATwAyAGUAXwBUAGkAdABsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAEMAbwBuAHYAZQByAHQAIABuAGkAdAByAG8AdQBzACAAbwB4AGkAZABlACAAZQBtAGkAcwBzAGkAbwBuAHMAIAB0AG8AIABjAGEAcgBiAG8AbgAgAGQAaQBvAHgAaQBkAGUAIABlAHEAdQBpAHYAYQBsAGUAbgB0ACAAZQBtAGkAcwBzAGkAbwBuAHMAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AQwBvAG4AdgBlAHIAdABOADIATwBUAG8AQwBPADIAZQBfAFYAYQByAGkAYQBiAGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIARQBOADIATwAgAEMATwAyAGUAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AQwBvAG4AdgBlAHIAdABOADIATwBUAG8AQwBPADIAZQBfAFUAbgBpAHQAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAHQAIABDAE8AMgBlAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAEMAbwBuAHYAZQByAHQATgAyAE8AVABvAEMATwAyAGUAXwBOAEkAUgBSAGUAZgBlAHIAZQBuAGMAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AQwBvAG4AdgBlAHIAdABOADIATwBUAG8AQwBPADIAZQBfAEwAYQB0AGUAeABFAHEAdQBhAHQAaQBvAG4AXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAEMATwAyAF8AZQAgAD0AIABFAF8AewBOADIATwB9ACAAXABcAHQAaQBtAGUAcwAgAEcAVwBQAF8AewBOADIATwB9AFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAEMAbwBuAHYAZQByAHQATgAyAE8AVABvAEMATwAyAGUAXwBBAHIAZwB1AG0AZQBuAHQAcwBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABNAEEASwBFAEEAUgBSAEEAWQAoADIALAAgADIALAAgAFwAbgAgACAAIAAgACAAIABMAEEATQBCAEQAQQAoAHIALABjACwAIABcAG4AIAAgACAAIAAgACAAIAAgAEkATgBEAEUAWAAoAHsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEUATgAyAE8AXAAiACwAXAAiAE4AaQB0AHIAbwB1AHMAIABvAHgAaQBkAGUAIABlAG0AaQBzAHMAaQBvAG4AcwAgACgAdAAgAE4AMgBPACkAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEcAVwBQAE4AMgBPAFwAIgAsAFwAIgBHAGwAbwBiAGEAbAAgAHcAYQByAG0AaQBuAGcAIABwAG8AdABlAG4AdABpAGEAbAAgAGYAbwByACAAbgBpAHQAcgBvAHUAcwAgAG8AeABpAGQAZQAgACgAdAAgAEMATwAyAC0AZQAgAC8AIAB0ACAATgAyAE8AKQBcACIAXABuACAAIAAgACAAIAAgACAAIAB9ACwAIAByACwAIABjACkAXABuACAAIAAgACAAIAAgACkAXABuACAAIAAgACAAKQBcAG4AIAAgACkAOwBcAG4AXABuAC8AKgAgAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuAEMAbwBtAG0AbwBuAF8AQwBvAG4AdgBlAHIAdABDAEgANABUAG8AQwBPADIAZQBcAG4AQwBvAG4AdgBlAHIAdAAgAG0AZQB0AGgAYQBuAGUAIABlAG0AaQBzAHMAaQBvAG4AcwAgAHQAbwAgAGMAYQByAGIAbwBuACAAZABpAG8AeABpAGQAZQAgAGUAcQB1AGkAdgBhAGwAZQBuAHQAIABlAG0AaQBzAHMAaQBvAG4AcwBcAG4ARQBDAEgANAAgAEMATwAyAGUAXABuAHQAIABDAE8AMgBlAFwAbgBFAEMASAA0ADoAIABtAGUAdABoAGEAbgBlACAAZQBtAGkAcwBzAGkAbwBuAHMAIAAoAHQAIABDAEgANAApAFwAbgBHAFcAUABDAEgANAA6ACAAZwBsAG8AYgBhAGwAIAB3AGEAcgBtAGkAbgBnACAAcABvAHQAZQBuAHQAaQBhAGwAIABmAG8AcgAgAG0AZQB0AGgAYQBuAGUAIAAoAHQAIABDAE8AMgAtAGUAIAAvACAAdAAgAEMASAA0ACkAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AKgAvAFwAbgBcAG4AXABuAEMAbwBtAG0AbwBuAF8AQwBvAG4AdgBlAHIAdABDAEgANABUAG8AQwBPADIAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABFAF8AQwBIADQALAAgAEcAVwBQAF8AQwBIADQALABcAG4AIAAgACAAIABFAF8AQwBIADQAIAAqACAARwBXAFAAXwBDAEgANABcAG4AIAAgACkAXABuADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAEMAbwBuAHYAZQByAHQAQwBIADQAVABvAEMATwAyAGUAXwBUAGkAdABsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAEMAbwBuAHYAZQByAHQAIABtAGUAdABoAGEAbgBlACAAZQBtAGkAcwBzAGkAbwBuAHMAIAB0AG8AIABjAGEAcgBiAG8AbgAgAGQAaQBvAHgAaQBkAGUAIABlAHEAdQBpAHYAYQBsAGUAbgB0ACAAZQBtAGkAcwBzAGkAbwBuAHMAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AQwBvAG4AdgBlAHIAdABDAEgANABUAG8AQwBPADIAZQBfAFYAYQByAGkAYQBiAGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIARQBDAEgANAAgAEMATwAyAGUAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AQwBvAG4AdgBlAHIAdABDAEgANABUAG8AQwBPADIAZQBfAFUAbgBpAHQAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAHQAIABDAE8AMgBlAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAEMAbwBuAHYAZQByAHQAQwBIADQAVABvAEMATwAyAGUAXwBOAEkAUgBSAGUAZgBlAHIAZQBuAGMAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AQwBvAG4AdgBlAHIAdABDAEgANABUAG8AQwBPADIAZQBfAEwAYQB0AGUAeABFAHEAdQBhAHQAaQBvAG4AXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAEMATwAyAF8AZQAgAD0AIABFAF8AewBDAEgANAB9ACAAXABcAHQAaQBtAGUAcwAgAEcAVwBQAF8AewBDAEgANAB9AFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAEMAbwBuAHYAZQByAHQAQwBIADQAVABvAEMATwAyAGUAXwBBAHIAZwB1AG0AZQBuAHQAcwBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABNAEEASwBFAEEAUgBSAEEAWQAoADIALAAgADIALAAgAFwAbgAgACAAIAAgACAAIABMAEEATQBCAEQAQQAoAHIALABjACwAIABcAG4AIAAgACAAIAAgACAAIAAgAEkATgBEAEUAWAAoAHsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEUAQwBIADQAXAAiACwAXAAiAE0AZQB0AGgAYQBuAGUAIABlAG0AaQBzAHMAaQBvAG4AcwAgACgAdAAgAEMASAA0ACkAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEcAVwBQAEMASAA0AFwAIgAsAFwAIgBHAGwAbwBiAGEAbAAgAHcAYQByAG0AaQBuAGcAIABwAG8AdABlAG4AdABpAGEAbAAgAGYAbwByACAAbQBlAHQAaABhAG4AZQAgACgAdAAgAEMATwAyAC0AZQAgAC8AIAB0ACAAQwBIADQAKQBcACIAXABuACAAIAAgACAAIAAgACAAIAB9ACwAIAByACwAIABjACkAXABuACAAIAAgACAAIAAgACkAXABuACAAIAAgACAAKQBcAG4AIAAgACkAOwAiAH0ALAB7ACIAcABhAHQAaAAiADoAIgAvAHAAcgBvAGoAZQBjAHQAcwAvAEMAbwBtAG0AbwBuAF8ASQBuAHAAdQB0AEYAdQBuAGMAdABpAG8AbgBzACIALAAiAHQAZQB4AHQAIgA6ACIAVQB0AGkAbABpAHQAeQBfAEcAZQB0AEEAcgByAGEAeQBUAGEAYgBsAGUAUgBvAHcAUwB0AGEAcgB0AE4AdQBtAGIAZQByAFwAbgA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAAVABhAGIAbABlAGgAZQBhAGQAZQByAEMAZQBsAGwALABSAG8AdwBzAEIAZQB0AHcAZQBlAG4ASABlAGEAZABlAHIAYQBuAGQAQQByAHIAYQB5ACwAXABuACAAIAAgACAAUgBPAFcAKABUAGEAYgBsAGUAaABlAGEAZABlAHIAQwBlAGwAbAApACAAKwAgAFIAbwB3AHMAQgBlAHQAdwBlAGUAbgBIAGUAYQBkAGUAcgBhAG4AZABBAHIAcgBhAHkAIAAtACAAMQBcAG4AKQA7AFwAbgBcAG4AVQB0AGkAbABpAHQAeQBfAEcAZQB0AEEAcgByAGEAeQBUAGEAYgBsAGUAQwBvAGwAdQBtAG4AUwB0AGEAcgB0AE4AdQBtAGIAZQByAFwAbgA9AEwAQQBNAEIARABBACgAXABuACAAIABUAGEAYgBsAGUASABlAGEAZABlAHIAQwBlAGwAbAAsAFwAbgAgACAAQwBPAEwAVQBNAE4AKABUAGEAYgBsAGUASABlAGEAZABlAHIAQwBlAGwAbAApAFwAbgApADsAXABuAFwAbgBVAHQAaQBsAGkAdAB5AF8ARABpAHMAcABsAGEAeQBBAHIAcgBhAHkASQBuAFQAYQBiAGwAZQBcAG4APQBMAEEATQBCAEQAQQAoAFwAbgAgAEEAcgByAGEAeQBEAGEAdABhACwAIABUAGEAYgBsAGUAaABlAGEAZABlAHIAQwBlAGwAbAAsACAAUgBvAHcAcwBCAGUAdAB3AGUAZQBuAEgAZQBhAGQAZQByAGEAbgBkAEEAcgByAGEAeQAsACAAWwBDAG8AbAB1AG0AbgBzAEIAZQB0AHcAZQBlAG4ASABlAGEAZABlAHIAQQBuAGQAQQByAHIAYQB5AF0ALABcAG4AIABJAEYARQBSAFIATwBSACgAXABuACAAIAAgACAAIABJAE4ARABFAFgAKABcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAVQBOAEkAUQBVAEUAKABBAHIAcgBhAHkARABhAHQAYQApACwAIABcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAUgBPAFcAKAApAC0AVQB0AGkAbABpAHQAeQBfAEcAZQB0AEEAcgByAGEAeQBUAGEAYgBsAGUAUgBvAHcAUwB0AGEAcgB0AE4AdQBtAGIAZQByACgAVABhAGIAbABlAGgAZQBhAGQAZQByAEMAZQBsAGwALAAgAFIAbwB3AHMAQgBlAHQAdwBlAGUAbgBIAGUAYQBkAGUAcgBhAG4AZABBAHIAcgBhAHkAKQAsACAAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgAEMATwBMAFUATQBOACgAKQAtAFUAdABpAGwAaQB0AHkAXwBHAGUAdABBAHIAcgBhAHkAVABhAGIAbABlAEMAbwBsAHUAbQBuAFMAdABhAHIAdABOAHUAbQBiAGUAcgAoAFQAYQBiAGwAZQBoAGUAYQBkAGUAcgBDAGUAbABsACkAIAArAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIABJAEYAKABJAFMATwBNAEkAVABUAEUARAAoAEMAbwBsAHUAbQBuAHMAQgBlAHQAdwBlAGUAbgBIAGUAYQBkAGUAcgBBAG4AZABBAHIAcgBhAHkAKQAsACAAMQAsACAAQwBvAGwAdQBtAG4AcwBCAGUAdAB3AGUAZQBuAEgAZQBhAGQAZQByAEEAbgBkAEEAcgByAGEAeQApAFwAbgAgACAAIAAgACAAIAAgACAAKQAsACAAXAAiAFwAIgBcAG4AIAAgACAAIAApAFwAbgApADsAXABuAFwAbgBVAHQAaQBsAGkAdAB5AF8ATABvAG8AawB1AHAAVgBhAGwAdQBlAEkAbgBUAGEAYgBsAGUAXABuAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABMAG8AbwBrAHUAcABWAGEAbAB1AGUALAAgAEwAbwBvAGsAdQBwAEEAcgByAGEAeQAsACAAUgBlAHQAdQByAG4AQQByAHIAYQB5ACwAXABuACAAIAAgACAAWABMAE8ATwBLAFUAUAAoAEwAbwBvAGsAdQBwAFYAYQBsAHUAZQAsACAATABvAG8AawB1AHAAQQByAHIAYQB5ACwAIABSAGUAdAB1AHIAbgBBAHIAcgBhAHkALAAgAFwAIgBcACIAKQBcAG4AKQA7AFwAbgBcAG4AVQB0AGkAbABpAHQAeQBfAEwAbwBvAGsAdQBwAFYAYQBsAHUAZQBJAG4AVABhAGIAbABlAE4AdQBtAGIAZQByAFwAbgA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAATABvAG8AawB1AHAAVgBhAGwAdQBlACwAIABMAG8AbwBrAHUAcABBAHIAcgBhAHkALAAgAFIAZQB0AHUAcgBuAEEAcgByAGEAeQAsAFwAbgAgACAAIAAgAEkARgAoAEkAUwBOAFUATQBCAEUAUgAoAFwAbgAgACAAIAAgACAAIAAgACAAWABMAE8ATwBLAFUAUAAoAEwAbwBvAGsAdQBwAFYAYQBsAHUAZQAsACAATABvAG8AawB1AHAAQQByAHIAYQB5ACwAIABSAGUAdAB1AHIAbgBBAHIAcgBhAHkALAAgAFwAIgBcACIAKQBcAG4AIAAgACAAIAApACwAIABYAEwATwBPAEsAVQBQACgATABvAG8AawB1AHAAVgBhAGwAdQBlACwAIABMAG8AbwBrAHUAcABBAHIAcgBhAHkALAAgAFIAZQB0AHUAcgBuAEEAcgByAGEAeQAsACAAXAAiAFwAIgApACwAIAAwACkAXABuACkAOwBcAG4AXABuAFUAdABpAGwAaQB0AHkAXwBMAG8AbwBrAHUAcABWAGEAbAB1AGUASQBuAFQAYQBiAGwAZQBUAHcAbwBDAG8AbAB1AG0AbgBzAFwAbgA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAATABvAG8AawB1AHAAVgBhAGwAdQBlADEALAAgAEwAbwBvAGsAdQBwAFYAYQBsAHUAZQAyACwAIABMAG8AbwBrAHUAcABBAHIAcgBhAHkAMQAsACAATABvAG8AawB1AHAAQQByAHIAYQB5ADIALAAgAFIAZQB0AHUAcgBuAEEAcgByAGEAeQAsACAAWwBWAGEAbAB1AGUASQBGAEYAYQBsAHMAZQBdACwAXABuACAAIAAgACAAWABMAE8ATwBLAFUAUAAoADEALAAgACgATABvAG8AawB1AHAAQQByAHIAYQB5ADEAPQBMAG8AbwBrAHUAcABWAGEAbAB1AGUAMQApACoAKABMAG8AbwBrAHUAcABBAHIAcgBhAHkAMgA9AEwAbwBvAGsAdQBwAFYAYQBsAHUAZQAyACkALAAgAFIAZQB0AHUAcgBuAEEAcgByAGEAeQAsACAASQBGACgASQBTAE8ATQBJAFQAVABFAEQAKABWAGEAbAB1AGUASQBGAEYAYQBsAHMAZQApACwAIABcACIAXAAiACwAIABWAGEAbAB1AGUASQBGAEYAYQBsAHMAZQApACkAXABuACkAOwBcAG4AXABuAFUAdABpAGwAaQB0AHkAXwBMAG8AbwBrAHUAcABWAGEAbAB1AGUASQBuAFQAYQBiAGwAZQBPAG4AZQBDAG8AbAB1AG0AbgBBAG4AZABIAGUAYQBkAGUAcgBcAG4APQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAEwAbwBvAGsAdQBwAFYAYQBsAHUAZQAxACwAIABMAG8AbwBrAHUAcABWAGEAbAB1AGUAMgAsACAATABvAG8AawB1AHAAQQByAHIAYQB5ADEALAAgAEwAbwBvAGsAdQBwAEEAcgByAGEAeQAyACwAIABSAGUAdAB1AHIAbgBBAHIAcgBhAHkALAAgAFsAVgBhAGwAdQBlAEkAZgBGAGEAbABzAGUAXQAsAFwAbgAgACAAIAAgAEkARgBFAFIAUgBPAFIAKABcAG4AIAAgACAAIAAgACAAIAAgAFgATABPAE8ASwBVAFAAKABMAG8AbwBrAHUAcABWAGEAbAB1AGUAMQAsACAATABvAG8AawB1AHAAQQByAHIAYQB5ADEALABcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAWABMAE8ATwBLAFUAUAAoAEwAbwBvAGsAdQBwAFYAYQBsAHUAZQAyACwAIABMAG8AbwBrAHUAcABBAHIAcgBhAHkAMgAsACAAUgBlAHQAdQByAG4AQQByAHIAYQB5ACkAXABuACAAIAAgACAAIAAgACAAIAApACwAXABuACAAIAAgACAAIAAgACAAIABJAEYAKABJAFMATwBNAEkAVABUAEUARAAoAFYAYQBsAHUAZQBJAGYARgBhAGwAcwBlACkALAAgAFwAIgBcACIALAAgAFYAYQBsAHUAZQBJAGYARgBhAGwAcwBlACkAXABuACAAIAAgACAAKQBcAG4AKQA7AFwAbgBcAG4AVQB0AGkAbABpAHQAeQBfAFMAcABsAGkAdABTAHQAcgBpAG4AZwBJAG4AdABvAEEAcgByAGEAeQBcAG4APQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAEMAZQBsAGwALAAgAEQAZQBsAGkAbQBpAHQAZQByACwAIABbAEMAaABhAHIAYQBjAHQAZQByAFQAbwBSAGUAbQBvAHYAZQAxAF0ALAAgAFsAQwBoAGEAcgBhAGMAdABlAHIAVABvAFIAZQBtAG8AdgBlADIAXQAsAFwAbgAgACAAIAAgACAAIAAgACAARgBJAEwAVABFAFIAWABNAEwAKABcAG4AIAAgACAAIAAgACAAIAAgAFwAIgA8AHQAPgA8AHMAPgBcACIAIAAmAFwAbgAgACAAIAAgACAAIAAgACAAUwBVAEIAUwBUAEkAVABVAFQARQAoAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIABTAFUAQgBTAFQASQBUAFUAVABFACgAUwBVAEIAUwBUAEkAVABVAFQARQAoAEMAZQBsAGwALABDAGgAYQByAGEAYwB0AGUAcgBUAG8AUgBlAG0AbwB2AGUAMQAsAFwAIgBcACIAKQAsAEMAaABhAHIAYQBjAHQAZQByAFQAbwBSAGUAbQBvAHYAZQAyACwAXAAiAFwAIgApACwAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgAEQAZQBsAGkAbQBpAHQAZQByACwAXAAiADwALwBzAD4APABzAD4AXAAiAFwAbgAgACAAIAAgACAAIAAgACAAKQAgACYAXABuACAAIAAgACAAIAAgACAAIABcACIAPAAvAHMAPgA8AC8AdAA+AFwAIgAsAFwAbgAgACAAIAAgACAAIAAgACAAXAAiAC8ALwBzAFwAIgBcAG4AIAAgACAAIAApAFwAbgApADsAXABuAFwAbgBVAHQAaQBsAGkAdAB5AF8ARwBlAHQAQwBsAGkAbQBhAHQAZQBaAG8AbgBlAFwAbgA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAAYQB2AGcAVABlAG0AcAAsAGEAdgBnAFIAYQBpAG4ALABmAHIAbwBzAHQARABhAHkAcwAsAGUAbABlAHYALABtAGEAcABfAHAAZQB0ACwAXABuACAAIAAgACAAbQBpAG4AVABlAG0AcABBAHIAcgBhAHkALABtAGEAeABUAGUAbQBwAEEAcgByAGEAeQAsAFwAbgAgACAAIAAgAG0AaQBuAFIAYQBpAG4AZgBhAGwAbABBAHIAcgBhAHkALABtAGEAeABSAGEAaQBuAGYAYQBsAGwAQQByAHIAYQB5ACwAXABuACAAIAAgACAAbQBpAG4ARgByAG8AcwB0AEEAcgByAGEAeQAsAG0AYQB4AEYAcgBvAHMAdABBAHIAcgBhAHkALABcAG4AIAAgACAAIABtAGkAbgBFAGwAZQB2AGEAdABpAG8AbgBBAHIAcgBhAHkALABtAGEAeABFAGwAZQB2AGEAdABpAG8AbgBBAHIAcgBhAHkALABcAG4AIAAgACAAIABtAGkAbgBQAEUAVABBAHIAcgBhAHkALABtAGEAeABQAEUAVABBAHIAcgBhAHkALABcAG4AIAAgACAAIABjAGwAaQBtAGEAdABlAFoAbwBuAGUAQQByAHIAYQB5ACwAXABuACAAIAAgACAATABFAFQAKABcAG4AIAAgACAAIAAgACAAIAAgAG0AYQBzAGsALABcAG4AIAAgACAAIAAgACAAIAAgACgAVgBBAEwAVQBFACgAbQBpAG4AVABlAG0AcABBAHIAcgBhAHkAKQA8AD0AYQB2AGcAVABlAG0AcAApACoAXABuACAAIAAgACAAIAAgACAAIAAoAFYAQQBMAFUARQAoAG0AYQB4AFQAZQBtAHAAQQByAHIAYQB5ACkAPgA9AGEAdgBnAFQAZQBtAHAAKQAqAFwAbgAgACAAIAAgACAAIAAgACAAKABWAEEATABVAEUAKABtAGkAbgBSAGEAaQBuAGYAYQBsAGwAQQByAHIAYQB5ACkAPAA9AGEAdgBnAFIAYQBpAG4AKQAqAFwAbgAgACAAIAAgACAAIAAgACAAKABWAEEATABVAEUAKABtAGEAeABSAGEAaQBuAGYAYQBsAGwAQQByAHIAYQB5ACkAPgA9AGEAdgBnAFIAYQBpAG4AKQAqAFwAbgAgACAAIAAgACAAIAAgACAAKABWAEEATABVAEUAKABtAGkAbgBGAHIAbwBzAHQAQQByAHIAYQB5ACkAPAA9AGYAcgBvAHMAdABEAGEAeQBzACkAKgBcAG4AIAAgACAAIAAgACAAIAAgACgAVgBBAEwAVQBFACgAbQBhAHgARgByAG8AcwB0AEEAcgByAGEAeQApAD4APQBmAHIAbwBzAHQARABhAHkAcwApACoAXABuACAAIAAgACAAIAAgACAAIAAoAFYAQQBMAFUARQAoAG0AaQBuAEUAbABlAHYAYQB0AGkAbwBuAEEAcgByAGEAeQApADwAPQBlAGwAZQB2ACkAKgBcAG4AIAAgACAAIAAgACAAIAAgACgAVgBBAEwAVQBFACgAbQBhAHgARQBsAGUAdgBhAHQAaQBvAG4AQQByAHIAYQB5ACkAPgA9AGUAbABlAHYAKQAqAFwAbgAgACAAIAAgACAAIAAgACAAKABWAEEATABVAEUAKABtAGkAbgBQAEUAVABBAHIAcgBhAHkAKQA8AD0AbQBhAHAAXwBwAGUAdAApACoAXABuACAAIAAgACAAIAAgACAAIAAoAFYAQQBMAFUARQAoAG0AYQB4AFAARQBUAEEAcgByAGEAeQApAD4APQBtAGEAcABfAHAAZQB0ACkALABcAG4AIAAgACAAIAAgACAAIAAgAFQAQQBLAEUAKABcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAARgBJAEwAVABFAFIAKABjAGwAaQBtAGEAdABlAFoAbwBuAGUAQQByAHIAYQB5ACwAbQBhAHMAawAsACAAXAAiAE4AbwAgAG0AYQB0AGMAaABcACIAKQAsAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIAAxAFwAbgAgACAAIAAgACAAIAAgACAAKQBcAG4AIAAgACAAIAApAFwAbgApADsAXABuAFwAbgBVAHQAaQBsAGkAdAB5AF8ATABvAG8AawB1AHAASQB0AGUAbQBGAHIAbwBtAE0AaQBuAE0AYQB4AFwAbgA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAATABvAG8AawB1AHAAVgBhAGwAdQBlACwAIABNAGkAbgBBAHIAcgBhAHkALAAgAE0AYQB4AEEAcgByAGEAeQAsACAASQB0AGUAbQBBAHIAcgBhAHkALABcAG4AIAAgACAAIABMAEUAVAAoAFwAbgAgACAAIAAgACAAIAAgACAAbQBhAHMAawAsAFwAbgAgACAAIAAgACAAIAAgACAAKABWAEEATABVAEUAKABNAGkAbgBBAHIAcgBhAHkAKQA8AD0ATABvAG8AawB1AHAAVgBhAGwAdQBlACkAKgBcAG4AIAAgACAAIAAgACAAIAAgACgAVgBBAEwAVQBFACgATQBhAHgAQQByAHIAYQB5ACkAPgA9AEwAbwBvAGsAdQBwAFYAYQBsAHUAZQApACwAXABuACAAIAAgACAAIAAgACAAIABGAEkATABUAEUAUgAoAEkAdABlAG0AQQByAHIAYQB5ACwAIABtAGEAcwBrACwAIABcACIATgBvACAAbQBhAHQAYwBoAFwAIgApAFwAbgAgACAAIAAgACkAXABuACkAOwBcAG4AXABuAFwAbgBVAHQAaQBsAGkAdAB5AF8AUwB1AG0AUQB1AGEAbgB0AGkAdAB5AEYAcgBvAG0AQwByAGkAdABlAHIAaQBhAFwAbgA9AEwAQQBNAEIARABBACgAXABuACAAIABDAHIAaQB0AGUAcgBpAGEAMQAsACAAQwByAGkAdABlAHIAaQBhADEAVAB5AHAAZQBBAHIAcgBhAHkALAAgAFEAdQBhAG4AdABpAHQAeQAsACAAWwBNAHUAbAB0AGkAcABsAGkAZQByAF0ALAAgAFsAQwByAGkAdABlAHIAaQBhADIAXQAsAFsAQwByAGkAdABlAHIAaQBhADIAQQByAHIAYQB5AF0ALABcAG4AIAAgAEwARQBUACgAXABuACAAIAAgACAAbQB1AGwAdABpAHAAbABpAGUAcgAsACAASQBGACgASQBTAE8ATQBJAFQAVABFAEQAKABNAHUAbAB0AGkAcABsAGkAZQByACkALAAxACwATQB1AGwAdABpAHAAbABpAGUAcgApACwAXABuACAAIAAgACAAcQB1AGEAbgB0AGkAdAB5ACwAIABRAHUAYQBuAHQAaQB0AHkAKgBNAHUAbAB0AGkAcABsAGkAZQByACwAXABuACAAIAAgACAAYwByAGkAdABlAHIAaQBhADEALAAtAC0AKABDAHIAaQB0AGUAcgBpAGEAMQBUAHkAcABlAEEAcgByAGEAeQA9AEMAcgBpAHQAZQByAGkAYQAxACkALABcAG4AIAAgACAAIABjAHIAaQB0AGUAcgBpAGEAMgAsAEkARgAoAEkAUwBPAE0ASQBUAFQARQBEACgAQwByAGkAdABlAHIAaQBhADIAKQAsADEALAAtAC0AKABDAHIAaQB0AGUAcgBpAGEAMgBBAHIAcgBhAHkAPQBDAHIAaQB0AGUAcgBpAGEAMgApACkALABcAG4AIAAgACAAIABTAFUATQBQAFIATwBEAFUAQwBUACgAYwByAGkAdABlAHIAaQBhADEAKgBjAHIAaQB0AGUAcgBpAGEAMgAqAHEAdQBhAG4AdABpAHQAeQApAFwAbgAgACAAKQBcAG4AKQA7AFwAbgBcAG4AZwBlAHQATwB2AGUAcgBsAGEAcABwAGkAbgBnAFIAZQBwAG8AcgB0AGkAbgBnAEMAeQBjAGwAZQBzAFwAbgA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAAUAByAG8AZAB1AGMAdABpAG8AbgBDAHkAYwBsAGUAUwB0AGEAcgB0ACwAUAByAG8AZAB1AGMAdABpAG8AbgBDAHkAYwBsAGUARQBuAGQALABSAGUAcABvAHIAdABpAG4AZwBDAHkAYwBsAGUAUwB0AGEAcgB0ACwAXABuACAAIAAgACAATABFAFQAKABcAG4AIAAgACAAIAAgACAAIAAgAFMALABQAHIAbwBkAHUAYwB0AGkAbwBuAEMAeQBjAGwAZQBTAHQAYQByAHQALABcAG4AIAAgACAAIAAgACAAIAAgAEUALABQAHIAbwBkAHUAYwB0AGkAbwBuAEMAeQBjAGwAZQBFAG4AZAAsAFwAbgAgACAAIAAgACAAIAAgACAAbQAsAE0ATwBOAFQASAAoAFIAZQBwAG8AcgB0AGkAbgBnAEMAeQBjAGwAZQBTAHQAYQByAHQAKQAsAFwAbgAgACAAIAAgACAAIAAgACAAZAAsAEQAQQBZACgAUgBlAHAAbwByAHQAaQBuAGcAQwB5AGMAbABlAFMAdABhAHIAdAApACwAXABuACAAIAAgACAAIAAgACAAIABQAGUAcgBpAG8AZABFAG4AZAAsAEwAQQBNAEIARABBACgAcwB0ACwARQBEAEEAVABFACgAcwB0ACwAMQAyACkALQAxACkALABcAG4AIAAgACAAIAAgACAAIAAgAEEALABTAC0AMwA2ADUALABcAG4AIAAgACAAIAAgACAAIAAgAHkAYQAsAFkARQBBAFIAKABBACkALABcAG4AIAAgACAAIAAgACAAIAAgAHkAYgAsAFkARQBBAFIAKABFACkALABcAG4AIAAgACAAIAAgACAAIAAgAGYAaQByAHMAdABZAGUAYQByACwAeQBhACsAKABQAGUAcgBpAG8AZABFAG4AZAAoAEQAQQBUAEUAKAB5AGEALABtACwAZAApACkAPAAgAFMAKQAsAFwAbgAgACAAIAAgACAAIAAgACAAbABhAHMAdABZAGUAYQByACwAeQBiAC0AKABEAEEAVABFACgAeQBiACwAbQAsAGQAKQA+ACAARQApACwAXABuACAAIAAgACAAIAAgACAAIABNAEEAWAAoADAALABsAGEAcwB0AFkAZQBhAHIALQBmAGkAcgBzAHQAWQBlAGEAcgArADEAKQBcAG4AIAAgACAAIAApAFwAbgApADsAXABuAFwAbgBnAGUAdABPAHYAZQByAGwAYQBwAHAAaQBuAGcAUgBlAHAAbwByAHQAaQBuAGcAUABlAHIAaQBvAGQAcwBcAG4APQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAFAAcgBvAGQAdQBjAHQAaQBvAG4AQwB5AGMAbABlAFMAdABhAHIAdAAsAFAAcgBvAGQAdQBjAHQAaQBvAG4AQwB5AGMAbABlAEUAbgBkACwAUgBlAHAAbwByAHQAaQBuAGcAQwB5AGMAbABlAFMAdABhAHIAdAAsAFwAbgAgACAAIAAgAEwARQBUACgAXABuACAAIAAgACAAIAAgACAAIABTACwAUAByAG8AZAB1AGMAdABpAG8AbgBDAHkAYwBsAGUAUwB0AGEAcgB0ACwAXABuACAAIAAgACAAIAAgACAAIABFACwAUAByAG8AZAB1AGMAdABpAG8AbgBDAHkAYwBsAGUARQBuAGQALABcAG4AIAAgACAAIAAgACAAIAAgAG0ALABNAE8ATgBUAEgAKABSAGUAcABvAHIAdABpAG4AZwBDAHkAYwBsAGUAUwB0AGEAcgB0ACkALABcAG4AIAAgACAAIAAgACAAIAAgAGQALABEAEEAWQAoAFIAZQBwAG8AcgB0AGkAbgBnAEMAeQBjAGwAZQBTAHQAYQByAHQAKQAsACAALwAqAGgAZQBsAHAAZQByADoAIABlAG4AZAAgAGQAYQB0AGUAIABmAG8AcgAgAGEAIAByAGUAcABvAHIAdABpAG4AZwAgAHAAZQByAGkAbwBkACAAcwB0AGEAcgB0AGkAbgBnACAAYQB0ACAAYQAgAGcAaQB2AGUAbgAgAGQAYQB0AGUAKgAvAFwAbgAgACAAIAAgACAAIAAgACAAUABlAHIAaQBvAGQARQBuAGQALABMAEEATQBCAEQAQQAoAHMAdAAsAEUARABBAFQARQAoAHMAdAAsADEAMgApAC0AMQApACwAIAAvACoAbwBuAGwAeQAgAG4AZQBlAGQAIAB0AG8AIABsAG8AbwBrACAAYgBhAGMAawAgADMANgA1ACAAZABhAHkAcwAoAG0AYQB4ACAAbwB2AGUAcgBsAGEAcAAgAHcAaQBuAGQAbwB3ACkAKgAvAFwAbgAgACAAIAAgACAAIAAgACAAQQAsAFMALQAzADYANQAsAFwAbgAgACAAIAAgACAAIAAgACAAeQBhACwAWQBFAEEAUgAoAEEAKQAsAFwAbgAgACAAIAAgACAAIAAgACAAeQBiACwAWQBFAEEAUgAoAEUAKQAsACAALwAqAGkAZgAgAHQAaABlACAAYQBuAGMAaABvAHIAIABmAG8AcgAgAHkAYQAgAGUAbgBkAHMAIABiAGUAZgBvAHIAZQAgAFMALABpAHQAIABjAGEAbgAnAHQAIABvAHYAZQByAGwAYQBwADsAIABtAG8AdgBlACAAdABvACAAbgBlAHgAdAAgAHkAZQBhAHIAKgAvAFwAbgAgACAAIAAgACAAIAAgACAAZgBpAHIAcwB0AFkAZQBhAHIALAB5AGEAKwAoAFAAZQByAGkAbwBkAEUAbgBkACgARABBAFQARQAoAHkAYQAsAG0ALABkACkAKQA8AFMAKQAsACAALwAqAGkAZgAgAHQAaABlACAAYQBuAGMAaABvAHIAIABmAG8AcgAgAHkAYgAgAHMAdABhAHIAdABzACAAYQBmAHQAZQByACAARQAsAGkAdAAgAGMAYQBuACcAdAAgAG8AdgBlAHIAbABhAHAAOwAgAG0AbwB2AGUAIAB0AG8AIABwAHIAZQB2AGkAbwB1AHMAIAB5AGUAYQByACoALwBcAG4AIAAgACAAIAAgACAAIAAgAGwAYQBzAHQAWQBlAGEAcgAsAHkAYgAtACgARABBAFQARQAoAHkAYgAsAG0ALABkACkAPgBFACkALABcAG4AIAAgACAAIAAgACAAIAAgAG4ALABNAEEAWAAoADAALABsAGEAcwB0AFkAZQBhAHIALQBmAGkAcgBzAHQAWQBlAGEAcgArADEAKQAsAFwAbgAgACAAIAAgACAAIAAgACAAeQByAHMALABTAEUAUQBVAEUATgBDAEUAKABuACwAMQAsAGYAaQByAHMAdABZAGUAYQByACwAMQApACwAXABuACAAIAAgACAAIAAgACAAIABzAHQAYQByAHQAcwAsAEQAQQBUAEUAKAB5AHIAcwAsAG0ALABkACkALABcAG4AIAAgACAAIAAgACAAIAAgAGUAbgBkAHMALABNAEEAUAAoAHMAdABhAHIAdABzACwAUABlAHIAaQBvAGQARQBuAGQAKQAsAFwAbgAgACAAIAAgACAAIAAgACAAdABhAGcALABJAEYAKABzAHQAYQByAHQAcwA9AFIAZQBwAG8AcgB0AGkAbgBnAEMAeQBjAGwAZQBTAHQAYQByAHQALABcACIAIAAoAFQAaABpAHMAIAByAGUAcABvAHIAdABpAG4AZwAgAGMAeQBjAGwAZQApAFwAIgAsAFwAIgBcACIAKQAsAFwAbgAgACAAIAAgACAAIAAgACAAcwB0AGEAcgB0AHMAVABlAHgAdAAsAFQARQBYAFQAKABzAHQAYQByAHQAcwAsAFwAIgBkAGQAIABtAG0AbQAgAHkAeQB5AHkAXAAiACkALABcAG4AIAAgACAAIAAgACAAIAAgAGUAbgBkAHMAVABlAHgAdAAsAFQARQBYAFQAKABlAG4AZABzACwAXAAiAGQAZAAgAG0AbQBtACAAeQB5AHkAeQBcACIAKQAsAFwAbgAgACAAIAAgACAAIAAgACAAcgBvAHcAcwAsAEkARgAoAG4APQAwACwAXAAiAFwAIgAsAEgAUwBUAEEAQwBLACgAcwB0AGEAcgB0AHMAVABlAHgAdAAgACYAIABcACIAIAB0AG8AIABcACIAIAAmACAAZQBuAGQAcwBUAGUAeAB0ACAAJgAgAHQAYQBnACkAKQAsAFwAbgAgACAAIAAgACAAIAAgACAAcgBvAHcAcwBcAG4AIAAgACAAIAApAFwAbgApADsAXABuAFwAbgBcAG4AVQB0AGkAbABpAHQAeQBfAEQAaQBzAHAAbABhAHkARgB1AG4AYwB0AGkAbwBuAE4AYQBtAGUAXABuAD0ATABBAE0AQgBEAEEAKABGAHUAbgBjAHQAaQBvAG4ALAAgAFQARQBYAFQAQgBFAEYATwBSAEUAKABGAE8AUgBNAFUATABBAFQARQBYAFQAKABGAHUAbgBjAHQAaQBvAG4AKQAsACAAXAAiACgAXAAiACkAKQA7AFwAbgBcAG4AVQB0AGkAbABpAHQAeQBfAEwAbwBvAGsAdQBwAE4AMgBPAEUARgBGAHIAbwBtAFAAcgBvAGQASQByAHIAaQBnAGEAdABpAG8AbgBSAGEAaQBuAGYAYQBsAGwAXABuAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABQAHIAbwBkAHUAYwB0AGkAbwBuAFMAeQBzAHQAZQBtACwAIABJAHIAcgBpAGcAYQB0AGkAbwBuAE0AZQB0AGgAbwBkACwAIABSAGEAaQBuAGYAYQBsAGwAWgBvAG4AZQAsAFwAbgAgACAAIAAgAFAAcgBvAGQAdQBjAHQAaQBvAG4AUwB5AHMAdABlAG0AQQByAHIAYQB5ACwAIABJAHIAcgBpAGcAYQB0AGkAbwBuAE0AZQB0AGgAbwBkAEEAcgByAGEAeQAsACAAUgBhAGkAbgBmAGEAbABsAFoAbwBuAGUAQQByAHIAYQB5ACwAUgBlAHQAdQByAG4AQQByAHIAYQB5ACwAXABuACAAIAAgACAATABFAFQAKABcAG4AIAAgACAAIAAgACAAIAAgAEkAcgByAGkAZwBhAHQAaQBvAG4ATQBlAHQAaABvAGQALAAgAEkARgAoAEkAcgByAGkAZwBhAHQAaQBvAG4ATQBlAHQAaABvAGQAPQBcACIATgBvAHQAIABpAHIAcgBpAGcAYQB0AGUAZABcACIALAAgAFwAIgBOAG8AdAAgAGkAcgByAGkAZwBhAHQAZQBkAFwAIgAsACAAXAAiAEEAbgB5AFwAIgApACwAXABuACAAIAAgACAAIAAgACAAIABSAGEAaQBuAGYAYQBsAGwAWgBvAG4AZQAsACAASQBGACgASQByAHIAaQBnAGEAdABpAG8AbgBNAGUAdABoAG8AZAAgAD0AIABcACIATgBvAHQAIABpAHIAcgBpAGcAYQB0AGUAZABcACIALAAgAFIAYQBpAG4AZgBhAGwAbABaAG8AbgBlACwAIABcACIAQQBuAHkAXAAiACkALABcAG4AIAAgACAAIAAgACAAIAAgAFgATABPAE8ASwBVAFAAKAAxACwAIABcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAKABQAHIAbwBkAHUAYwB0AGkAbwBuAFMAeQBzAHQAZQBtAEEAcgByAGEAeQA9AFAAcgBvAGQAdQBjAHQAaQBvAG4AUwB5AHMAdABlAG0AKQAqAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIAAoAEkAcgByAGkAZwBhAHQAaQBvAG4ATQBlAHQAaABvAGQAQQByAHIAYQB5AD0ASQByAHIAaQBnAGEAdABpAG8AbgBNAGUAdABoAG8AZAApACoAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgACgAUgBhAGkAbgBmAGEAbABsAFoAbwBuAGUAQQByAHIAYQB5AD0AUgBhAGkAbgBmAGEAbABsAFoAbwBuAGUAKQAsACAAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgAFIAZQB0AHUAcgBuAEEAcgByAGEAeQApAFwAbgAgACAAIAAgACkAXABuACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAEMAcgBvAHAAcABpAG4AZwBfAEcAZQB0AEYAcgBhAGMAVwBFAFQAXABuAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABMAGUAYQBjAGgAaQBuAGcAWgBvAG4AZQAsAFwAbgAgACAAIAAgAFAAcgBvAGQAdQBjAHQAaQBvAG4AUwB5AHMAdABlAG0ALABcAG4AIAAgACAAIABMAGUAYQBjAGgAaQBuAGcAWgBvAG4AZQBMAG8AbwBrAHUAcAAsAFwAbgAgACAAIAAgAEwAZQBhAGMAaABpAG4AZwBaAG8AbgBlAEYAcgBhAGMAVwBFAFQATABvAG8AawB1AHAALABcAG4AIAAgACAAIABQAHIAbwBkAHUAYwB0AGkAbwBuAFMAeQBzAHQAZQBtAEwAbwBvAGsAdQBwACwAXABuACAAIAAgACAAUAByAG8AZAB1AGMAdABpAG8AbgBTAHkAcwB0AGUAbQBGAHIAYQBjAFcARQBUAEwAbwBvAGsAdQBwACwAXABuACAAIAAgACAATABFAFQAKABcAG4AIAAgACAAIAAgACAAIAAgAEwAZQBhAGMAaABpAG4AZwBaAG8AbgBlAEYAcgBhAGMAVwBFAFQALAAgAFwAbgAgACAAIAAgACAAIAAgACAAQwBvAG0AbQBvAG4AXwBJAG4AcAB1AHQARgB1AG4AYwB0AGkAbwBuAHMALgBVAHQAaQBsAGkAdAB5AF8ATABvAG8AawB1AHAAVgBhAGwAdQBlAEkAbgBUAGEAYgBsAGUATgB1AG0AYgBlAHIAKABcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAATABlAGEAYwBoAGkAbgBnAFoAbwBuAGUALABMAGUAYQBjAGgAaQBuAGcAWgBvAG4AZQBMAG8AbwBrAHUAcAAsAEwAZQBhAGMAaABpAG4AZwBaAG8AbgBlAEYAcgBhAGMAVwBFAFQATABvAG8AawB1AHAAXABuACAAIAAgACAAIAAgACAAIAApACwAXABuACAAIAAgACAAIAAgACAAIABQAHIAbwBkAHUAYwB0AGkAbwBuAFMAeQBzAHQAZQBtAEYAcgBhAGMAVwBFAFQALAAgAFwAbgAgACAAIAAgACAAIAAgACAAQwBvAG0AbQBvAG4AXwBJAG4AcAB1AHQARgB1AG4AYwB0AGkAbwBuAHMALgBVAHQAaQBsAGkAdAB5AF8ATABvAG8AawB1AHAAVgBhAGwAdQBlAEkAbgBUAGEAYgBsAGUATgB1AG0AYgBlAHIAKABcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAUAByAG8AZAB1AGMAdABpAG8AbgBTAHkAcwB0AGUAbQAsAFAAcgBvAGQAdQBjAHQAaQBvAG4AUwB5AHMAdABlAG0ATABvAG8AawB1AHAALABQAHIAbwBkAHUAYwB0AGkAbwBuAFMAeQBzAHQAZQBtAEYAcgBhAGMAVwBFAFQATABvAG8AawB1AHAAXABuACAAIAAgACAAIAAgACAAIAApACwAXABuACAAIAAgACAAIAAgACAAIABJAEYAKABMAGUAYQBjAGgAaQBuAGcAWgBvAG4AZQBGAHIAYQBjAFcARQBUACAAKwAgAFAAcgBvAGQAdQBjAHQAaQBvAG4AUwB5AHMAdABlAG0ARgByAGEAYwBXAEUAVAA+ADAALAAgADEALAAgADAAKQBcAG4AIAAgACAAIAApACkAOwBcAG4AXABuAFwAbgBVAHQAaQBsAGkAdAB5AF8AQwBvAG4AdgBlAHIAdABTAHQAYQB0AGUAQwBvAG0AbQBvAG4ATgBhAG0AZQBUAG8AQQBiAGIAcgBlAHYAaQBhAHQAaQBvAG4AXABuAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABTAHQAYQB0AGUAQwBvAG0AbQBvAG4ATgBhAG0AZQAsAFwAbgAgACAAIAAgAFMAdABhAHQAZQBDAG8AbQBtAG8AbgBOAGEAbQBlAEEAcgByAGEAeQAsACAAUwB0AGEAdABlAEEAYgBiAHIAZQB2AGkAYQB0AGkAbwBuAEEAcgByAGEAeQAsAFwAbgAgACAAIAAgAFgATABPAE8ASwBVAFAAKABTAHQAYQB0AGUAQwBvAG0AbQBvAG4ATgBhAG0AZQAsACAAUwB0AGEAdABlAEMAbwBtAG0AbwBuAE4AYQBtAGUAQQByAHIAYQB5ACwAIABTAHQAYQB0AGUAQQBiAGIAcgBlAHYAaQBhAHQAaQBvAG4AQQByAHIAYQB5ACwAIABcACIAXAAiACkAXABuACkAOwBcAG4AXABuAFUAdABpAGwAaQB0AHkAXwBTAG8AdQByAGMAZQBIAHkAcABlAHIAbABpAG4AawBcAG4APQBMAEEATQBCAEQAQQAoAFQAYQByAGcAZQB0AEMAZQBsAGwALABcAG4AIAAgAEwARQBUACgAXABuACAAIAAgACAAcwBoACwAIABUAEUAWABUAEEARgBUAEUAUgAoAEMARQBMAEwAKABcACIAZgBpAGwAZQBuAGEAbQBlAFwAIgAsACAAVABhAHIAZwBlAHQAQwBlAGwAbAApACwAIABcACIAXQBcACIAKQAsAFwAbgAgACAAIAAgAGEAZABkAHIALAAgAEMARQBMAEwAKABcACIAYQBkAGQAcgBlAHMAcwBcACIALAAgAFQAYQByAGcAZQB0AEMAZQBsAGwAKQAsAFwAbgAgACAAIAAgAFwAIgAjACcAXAAiACAAJgAgAHMAaAAgACYAIABcACIAJwAhAFwAIgAgACYAIABhAGQAZAByAFwAbgAgACAAKQBcAG4AKQA7AFwAbgBcAG4AVQB0AGkAbABpAHQAeQBfAFMAbwB1AHIAYwBlAEgAeQBwAGUAcgBsAGkAbgBrAEQAaQBmAGYAZQByAGUAbgB0AFMAaABlAGUAdABcAG4APQBMAEEATQBCAEQAQQAoAFQAYQByAGcAZQB0AEMAZQBsAGwALABcAG4AIAAgAEwARQBUACgAXABuACAAIAAgACAAcwBoACwAIABUAEUAWABUAEEARgBUAEUAUgAoAEMARQBMAEwAKABcACIAZgBpAGwAZQBuAGEAbQBlAFwAIgAsACAAVABhAHIAZwBlAHQAQwBlAGwAbAApACwAIABcACIAXQBcACIAKQAsAFwAbgAgACAAIAAgAGEAZABkAHIALAAgAEMARQBMAEwAKABcACIAYQBkAGQAcgBlAHMAcwBcACIALAAgAFQAYQByAGcAZQB0AEMAZQBsAGwAKQAsAFwAbgAgACAAIAAgAFwAIgAjAFwAIgAgACYAIABhAGQAZAByAFwAbgAgACAAKQBcAG4AKQA7AFwAbgBcAG4AVQB0AGkAbABpAHQAeQBfAEQAaQBzAHAAbABhAHkAQQByAGcAdQBtAGUAbgB0AHMAXwAxAF8AMgBcAG4APQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAEEAcgBnAHUAbQBlAG4AdABzAEEAcgByAGEAeQAsAFwAbgAgACAAIAAgAEMASABPAE8AUwBFAEMATwBMAFMAKABBAHIAZwB1AG0AZQBuAHQAcwBBAHIAcgBhAHkALAAgADEALAAgADIAKQBcAG4AKQA7AFwAbgBcAG4AVQB0AGkAbABpAHQAeQBfAEQAaQBzAHAAbABhAHkAQQByAGcAdQBtAGUAbgB0AHMAXwAzAF8ANABcAG4APQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAEEAcgBnAHUAbQBlAG4AdABzAEEAcgByAGEAeQAsAFwAbgAgACAAIAAgAEMASABPAE8AUwBFAEMATwBMAFMAKABBAHIAZwB1AG0AZQBuAHQAcwBBAHIAcgBhAHkALAAgADMALAAgADQAKQBcAG4AKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBHAGUAdABNAEMARgBUAGUAbQBwAGUAcgBhAHQAdQByAGUAWgBvAG4AZQBcAG4APQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAFQAZQBtAHAAZQByAGEAdAB1AHIAZQAsACAATQBNAFMALAAgAFQAZQBtAHAAZQByAGEAdAB1AHIAZQBBAHIAcgBhAHkALAAgAE0ATQBTAEEAcgByAGEAeQAsACAAUgBlAHQAdQByAG4AQQByAHIAYQB5ACwAXABuACAAIAAgACAAWABMAE8ATwBLAFUAUAAoAFwAbgAgACAAIAAgACAAIAAgACAATQBFAEQASQBBAE4AKABcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAVABlAG0AcABlAHIAYQB0AHUAcgBlACwAIABcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAATQBJAE4AKABUAGUAbQBwAGUAcgBhAHQAdQByAGUAQQByAHIAYQB5ACkALAAgAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIABNAEEAWAAoAFQAZQBtAHAAZQByAGEAdAB1AHIAZQBBAHIAcgBhAHkAKQBcAG4AIAAgACAAIAAgACAAIAAgACkALABcAG4AIAAgACAAIAAgACAAIAAgAFQAZQBtAHAAZQByAGEAdAB1AHIAZQBBAHIAcgBhAHkALABcAG4AIAAgACAAIAAgACAAIAAgAFgATABPAE8ASwBVAFAAKABNAE0AUwAsACAATQBNAFMAQQByAHIAYQB5ACwAIABSAGUAdAB1AHIAbgBBAHIAcgBhAHkAKQBcAG4AIAAgACAAIAApAFwAbgApADsAXABuAFwAbgBcAG4AVQB0AGkAbABpAHQAeQBfAFIAZQBzAHUAbAB0AHMASQB0AGUAbQBGAHIAbwBtAEUAcQB1AGEAdABpAG8AbgBUAGkAdABsAGUAQQBuAGQAUwBvAHUAcgBjAGUAXABuAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABUAGkAdABsAGUAQwBlAGwAbAAsACAAUwBvAHUAcgBjAGUAQwBlAGwAbAAsAFwAbgAgACAAIAAgAFMAVQBCAFMAVABJAFQAVQBUAEUAKABMAEUARgBUACgAUwBvAHUAcgBjAGUAQwBlAGwAbAAsACAARgBJAE4ARAAoAFwAIgAsAFwAIgAsACAAUwBvAHUAcgBjAGUAQwBlAGwAbAApACAALQAxACkALAAgAFwAIgBWAEUARQBSAEcAIAAyADAAMgA2ADoAIABcACIALAAgAFwAIgBcACIAKQAgACYAIABcACIAIABcACIAIAAmACAAVABpAHQAbABlAEMAZQBsAGwAXABuACkAOwAiAH0ALAB7ACIAcABhAHQAaAAiADoAIgAvAHAAcgBvAGoAZQBjAHQAcwAvAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAiACwAIgB0AGUAeAB0ACIAOgAiAC8AKgBcAG4APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQBcAG4APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQBcAG4AUwBvAHUAcgBjAGUAIABkAGEAdABhACAAdABoAGEAdAAgAGkAcwAgAGMAbwBtAG0AbwBuACAAYQBjAHIAbwBzAHMAIABhAGwAbAAgAGUAbgB0AGUAcgBwAHIAaQBzAGUAIAB0AHkAcABlAHMAXABuAEUAeABjAGUAbAAgAG0AbwBkAHUAbABlACAAbgBhAG0AZQA6ACAAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAFwAbgA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AFwAbgA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AFwAbgAqAC8AXABuAFwAbgAvACoAXABuAD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQBcAG4APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AFwAbgBTAG8AdQByAGMAZQA6ACAATgBhAHQAaQBvAG4AYQBsACAASQBuAHYAZQBuAHQAbwByAHkAIABSAGUAcABvAHIAdAAgADIAMAAyADMAIABWAG8AbAB1AG0AZQAgADEAXABuAE4ASQBSAF8AMgAwADIAMwBfAFYAbwBsADEAXABuAD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQBcAG4APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AFwAbgAqAC8AXABuAFwAbgAvACoAIABcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGUAbgBzAGkAdAB5AE8AZgBNAGUAdABoAGEAbgBlAFwAbgBwACAAPQAgAGQAZQBuAHMAaQB0AHkAIABvAGYAIABtAGUAdABoAGEAbgBlACAAKAAwAC4ANgA3ADgANAAgAGsAZwAvAG0AMwApAFwAbgBUAGEAawBlAG4AIABmAHIAbwBtACAAdABoAGUAIABOAGEAdABpAG8AbgBhAGwAIABHAHIAZQBlAG4AaABvAHUAcwBlACAAYQBuAGQAIABFAG4AZQByAGcAeQAgAFIAZQBwAG8AcgB0AGkAbgBnACAAXABuACgATQBlAGEAcwB1AHIAZQBtAGUAbgB0ACkAIABEAGUAdABlAHIAbQBpAG4AYQB0AGkAbwBuACAAMgAwADAAOABcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgAqAC8AXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGUAbgBzAGkAdAB5AE8AZgBNAGUAdABoAGEAbgBlAF8AVABpAHQAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBwACAAPQAgAGQAZQBuAHMAaQB0AHkAIABvAGYAIABtAGUAdABoAGEAbgBlAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGUAbgBzAGkAdAB5AE8AZgBNAGUAdABoAGEAbgBlAF8AVQBuAGkAdABcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAawBnAC8AbQAzAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGUAbgBzAGkAdAB5AE8AZgBNAGUAdABoAGEAbgBlAF8AUwBvAHUAcgBjAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAE4AYQB0AGkAbwBuAGEAbAAgAEkAbgB2AGUAbgB0AG8AcgB5ACAAUgBlAHAAbwByAHQAIAAyADAAMgAzACAAVgBvAGwAdQBtAGUAIAAxADoAIABFAHEAdQBhAHQAaQBvAG4AcwAgADMALgBCAC4AMQBhAF8AMgAsACAAMwAuAEIALgAxAGMAXwAyACwAIAAzAC4AQgAuADMAXwAxACwAIAAzAC4AQgAuADQAZwBfADIAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEQAZQBuAHMAaQB0AHkATwBmAE0AZQB0AGgAYQBuAGUAXwBEAGEAdABhAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoADAALgA2ADcAOAA0ACkAOwBcAG4AXABuAC8AKgAgAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEMAbwBuAHYAZQByAHQATgAyAG8ARQBsAGUAbQBlAG4AdABhAGwAVABvAE0AbwBsAGUAYwB1AGwAYQByAEMAZwBcAG4AQwBnACAAPQAgADQANAAvADIAOAAgAGYAYQBjAHQAbwByACAAdABvACAAYwBvAG4AdgBlAHIAdAAgAGUAbABlAG0AZQBuAHQAYQBsACAAbQBhAHMAcwAgAG8AZgAgAE4AMgBPACAAdABvACAAbQBvAGwAZQBjAHUAbABhAHIAIABtAGEAcwBzAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuACoALwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEMAbwBuAHYAZQByAHQATgAyAG8ARQBsAGUAbQBlAG4AdABhAGwAVABvAE0AbwBsAGUAYwB1AGwAYQByAEMAZwBfAFQAaQB0AGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIARgBhAGMAdABvAHIAIAB0AG8AIABjAG8AbgB2AGUAcgB0ACAAZQBsAGUAbQBlAG4AdABhAGwAIABtAGEAcwBzACAAbwBmACAATgAyAE8AIAB0AG8AIABtAG8AbABlAGMAdQBsAGEAcgAgAG0AYQBzAHMAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEMAbwBuAHYAZQByAHQATgAyAG8ARQBsAGUAbQBlAG4AdABhAGwAVABvAE0AbwBsAGUAYwB1AGwAYQByAEMAZwBfAFYAYQByAGkAYQBiAGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAQwBnAE4AMgBPAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBDAG8AbgB2AGUAcgB0AE4AMgBvAEUAbABlAG0AZQBuAHQAYQBsAFQAbwBNAG8AbABlAGMAdQBsAGEAcgBDAGcAXwBVAG4AaQB0AFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBmAGEAYwB0AG8AcgBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQwBvAG4AdgBlAHIAdABOADIAbwBFAGwAZQBtAGUAbgB0AGEAbABUAG8ATQBvAGwAZQBjAHUAbABhAHIAQwBnAF8AUwBvAHUAcgBjAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAE4AYQB0AGkAbwBuAGEAbAAgAEkAbgB2AGUAbgB0AG8AcgB5ACAAUgBlAHAAbwByAHQAIAAyADAAMgAzACAAVgBvAGwAdQBtAGUAIAAxAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBDAG8AbgB2AGUAcgB0AE4AMgBvAEUAbABlAG0AZQBuAHQAYQBsAFQAbwBNAG8AbABlAGMAdQBsAGEAcgBDAGcAXwBEAGEAdABhAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoADQANAAvADIAOAApADsAXABuAFwAbgAvACoAIABcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBDAG8AbgB2AGUAcgB0AEcAYQBzAEUAbABlAG0AZQBuAHQAYQBsAFQAbwBNAG8AbABlAGMAdQBsAGEAcgBcAG4ARgBhAGMAdABvAHIAIAB0AG8AIABjAG8AbgB2AGUAcgB0ACAAZQBsAGUAbQBlAG4AdABhAGwAIABtAGEAcwBzACAAbwBmACAAZwBhAHMAIAB0AG8AIABtAG8AbABlAGMAdQBsAGEAcgAgAG0AYQBzAHMAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AKgAvAFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQwBvAG4AdgBlAHIAdABHAGEAcwBFAGwAZQBtAGUAbgB0AGEAbABUAG8ATQBvAGwAZQBjAHUAbABhAHIAXwBUAGkAdABsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAEYAYQBjAHQAbwByACAAdABvACAAYwBvAG4AdgBlAHIAdAAgAGUAbABlAG0AZQBuAHQAYQBsACAAbQBhAHMAcwAgAG8AZgAgAGcAYQBzACAAdABvACAAbQBvAGwAZQBjAHUAbABhAHIAIABtAGEAcwBzAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBDAG8AbgB2AGUAcgB0AEcAYQBzAEUAbABlAG0AZQBuAHQAYQBsAFQAbwBNAG8AbABlAGMAdQBsAGEAcgBfAFYAYQByAGkAYQBiAGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAQwBnAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBDAG8AbgB2AGUAcgB0AEcAYQBzAEUAbABlAG0AZQBuAHQAYQBsAFQAbwBNAG8AbABlAGMAdQBsAGEAcgBfAFUAbgBpAHQAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAGYAYQBjAHQAbwByAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBDAG8AbgB2AGUAcgB0AEcAYQBzAEUAbABlAG0AZQBuAHQAYQBsAFQAbwBNAG8AbABlAGMAdQBsAGEAcgBfAFMAbwB1AHIAYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBYAFgAWABYAFgAWABYAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBDAG8AbgB2AGUAcgB0AEcAYQBzAEUAbABlAG0AZQBuAHQAYQBsAFQAbwBNAG8AbABlAGMAdQBsAGEAcgBfAEQAYQB0AGEAXABuACAAIAA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAATQBBAEsARQBBAFIAUgBBAFkAKAA4ACwAIAA0ACwAIABcAG4AIAAgACAAIAAgACAATABBAE0AQgBEAEEAKAByACwAYwAsACAAXABuACAAIAAgACAAIAAgACAAIABJAE4ARABFAFgAKAB7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBHAGEAcwBcACIALAAgAFwAIgBDAG8AbgB2AGUAcgBzAGkAbwBuACAAZgBhAGMAdABvAHIAXAAiACwAIABcACIAQwBvAG4AdgBlAHIAcwBpAG8AbgAgAGYAYQBjAHQAbwByACAAMQBcACIALAAgAFwAIgBDAG8AbgB2AGUAcgBzAGkAbwBuACAAZgBhAGMAdABvAHIAIAAyAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBDAE8AMgBcACIALAAgAFwAIgA0ADQALwAxADIAXAAiACwAIAA0ADQALAAgADEAMgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBDAEgANABcACIALAAgAFwAIgAxADYALwAxADIAXAAiACwAIAAxADYALAAgADEAMgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBOADIATwBcACIALAAgAFwAIgA0ADQALwAyADgAXAAiACwAIAA0ADQALAAgADIAOAA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBOAG8AeABcACIALAAgAFwAIgA0ADYALwAxADQAXAAiACwAIAA0ADYALAAgADEANAA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBDAE8AXAAiACwAIABcACIAMgA4AC8AMQAyAFwAIgAsACAAMgA4ACwAIAAxADIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAQwBPADIAIABMAGkAbQBlAFwAIgAsACAAXAAiADQANAAvADEAMgBcACIALAAgADQANAAsACAAMQAyADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAE4ATQBWAE8AQwBcACIALAAgAFwAIgAxADQALwAxADIAXAAiACwAIAAxADQALAAgADEAMgBcAG4AIAAgACAAIAAgACAAIAAgAH0ALAAgAHIALAAgAGMAKQBcAG4AIAAgACAAIAAgACAAKQBcAG4AIAAgACAAIAApAFwAbgAgACAAKQA7AFwAbgBcAG4ALwAqACAAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARwBXAFAATgAyAE8AXABuAEcAbABvAGIAYQBsACAAdwBhAHIAbQBpAG4AZwAgAHAAbwB0AGUAbgB0AGkAYQBsACAAZgBvAHIAIABnAHIAZQBlAG4AaABvAHUAcwBlACAAZwBhAHMAZQBzAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuACoALwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEcAVwBQAF8AVABpAHQAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBHAGwAbwBiAGEAbAAgAHcAYQByAG0AaQBuAGcAIABwAG8AdABlAG4AdABpAGEAbAAgAGYAbwByACAAZwByAGUAZQBuAGgAbwB1AHMAZQAgAGcAYQBzAGUAcwBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARwBXAFAAXwBWAGEAcgBpAGEAYgBsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAEcAVwBQAE4AMgBPAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBHAFcAUABfAFUAbgBpAHQAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAGYAYQBjAHQAbwByAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBHAFcAUABfAFMAbwB1AHIAYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBYAFgAWABYAFgAWABYAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBHAFcAUABfAEQAYQB0AGEAXABuACAAIAA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAATQBBAEsARQBBAFIAUgBBAFkAKAA4ACwAIAAyACwAIABcAG4AIAAgACAAIAAgACAATABBAE0AQgBEAEEAKAByACwAYwAsACAAXABuACAAIAAgACAAIAAgACAAIABJAE4ARABFAFgAKAB7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBHAGEAcwBcACIALAAgAFwAIgBDAE8AMgAtAGUAIABmAGEAYwB0AG8AcgBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAQwBPADIAXAAiACwAIAAxADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEMASAA0AFwAIgAsACAAMgA4ADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAE4AMgBPAFwAIgAsACAAMgA2ADUAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAQwBGADQAXAAiACwAIAA2ADYAMwAwADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEMAMgBGADYAXAAiACwAIAAxADIAMgAwADAAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAUwBGADYAXAAiACwAIAAyADIAOAAwADAAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIATgBGADMAXAAiACwAIAAxADcAMgAwADAAXABuACAAIAAgACAAIAAgACAAIAB9ACwAIAByACwAIABjACkAXABuACAAIAAgACAAIAAgACkAXABuACAAIAAgACAAKQBcAG4AIAAgACkAOwBcAG4AXABuAFwAbgAvACoAIABcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBBAHUAcwB0AHIAYQBsAGkAYQBuAFMAdABhAHQAZQBzAFQAZQByAHIAaQB0AG8AcgBpAGUAcwBcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgAqAC8AXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBBAHUAcwB0AHIAYQBsAGkAYQBuAFMAdABhAHQAZQBzAFQAZQByAHIAaQB0AG8AcgBpAGUAcwBfAFQAaQB0AGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAQQB1AHMAdAByAGEAbABpAGEAbgAgAHMAdABhAHQAZQBzACAAYQBuAGQAIAB0AGUAcgByAGkAdABvAHIAaQBlAHMAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEEAdQBzAHQAcgBhAGwAaQBhAG4AUwB0AGEAdABlAHMAVABlAHIAcgBpAHQAbwByAGkAZQBzAF8AVgBhAHIAaQBhAGIAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQQB1AHMAdAByAGEAbABpAGEAbgBTAHQAYQB0AGUAcwBUAGUAcgByAGkAdABvAHIAaQBlAHMAXwBVAG4AaQB0AFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQQB1AHMAdAByAGEAbABpAGEAbgBTAHQAYQB0AGUAcwBUAGUAcgByAGkAdABvAHIAaQBlAHMAXwBTAG8AdQByAGMAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEEAdQBzAHQAcgBhAGwAaQBhAG4AUwB0AGEAdABlAHMAVABlAHIAcgBpAHQAbwByAGkAZQBzAF8ARABhAHQAYQBcAG4AIAAgACAAPQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAE0AQQBLAEUAQQBSAFIAQQBZACgAOQAsACAAMwAsACAAXABuACAAIAAgACAAIAAgAEwAQQBNAEIARABBACgAcgAsAGMALAAgAFwAbgAgACAAIAAgACAAIAAgACAASQBOAEQARQBYACgAewBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAUwB0AGEAdABlAC8AVABlAHIAcgBpAHQAbwByAHkAXAAiACwAIABcACIAQwBvAG0AbQBvAG4AIABOAGEAbQBlAFwAIgAsACAAXAAiAEEAYgBiAHIAZQB2AGkAYQB0AGkAbwBuAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBOAGUAdwAgAFMAbwB1AHQAaAAgAFcAYQBsAGUAcwBcACIALAAgAFwAIgBOAGUAdwAgAFMAbwB1AHQAaAAgAFcAYQBsAGUAcwBcACIALAAgAFwAIgBOAFMAVwBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAQQB1AHMAdAByAGEAbABpAGEAbgAgAEMAYQBwAGkAdABhAGwAIABUAGUAcgByAGkAdABvAHIAeQBcACIALAAgAFwAIgBBAEMAVABcACIALAAgAFwAIgBBAEMAVABcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVgBpAGMAdABvAHIAaQBhAFwAIgAsACAAXAAiAFYAaQBjAHQAbwByAGkAYQBcACIALAAgAFwAIgBWAEkAQwBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAUQB1AGUAZQBuAHMAbABhAG4AZABcACIALAAgAFwAIgBRAHUAZQBlAG4AcwBsAGEAbgBkAFwAIgAsACAAXAAiAFEATABEAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBTAG8AdQB0AGgAIABBAHUAcwB0AHIAYQBsAGkAYQBcACIALAAgAFwAIgBTAG8AdQB0AGgAIABBAHUAcwB0AHIAYQBsAGkAYQBcACIALAAgAFwAIgBTAEEAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFcAZQBzAHQAZQByAG4AIABBAHUAcwB0AHIAYQBsAGkAYQBcACIALAAgAFwAIgBXAGUAcwB0AGUAcgBuACAAQQB1AHMAdAByAGEAbABpAGEAXAAiACwAIABcACIAVwBBAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBUAGEAcwBtAGEAbgBpAGEAXAAiACwAIABcACIAVABhAHMAbQBhAG4AaQBhAFwAIgAsACAAXAAiAFQAQQBTAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBOAG8AcgB0AGgAZQByAG4AIABUAGUAcgByAGkAdABvAHIAeQBcACIALAAgAFwAIgBOAG8AcgB0AGgAZQByAG4AIABUAGUAcgByAGkAdABvAHIAeQBcACIALAAgAFwAIgBOAFQAXAAiAFwAbgAgACAAIAAgACAAIAAgACAAfQAsACAAcgAsACAAYwApAFwAbgAgACAAIAAgACAAIAApAFwAbgAgACAAIAAgACkAXABuACAAIAApADsAXABuAFwAbgAvACoAIABcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBXAEEAUwBBADQAQQByAGUAYQBzAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuACoALwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFcAQQBTAEEANABBAHIAZQBhAHMAXwBUAGkAdABsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAEEAQgBTACAAUwB0AGEAdABpAHMAdABjAGEAbAAgAEEAcgBlAGEAcwAgAEwAZQB2AGUAbAAgADQAIAAtACAAVwBlAHMAdABlAHIAbgAgAEEAdQBzAHQAcgBhAGwAaQBhAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBXAEEAUwBBADQAQQByAGUAYQBzAF8AVgBhAHIAaQBhAGIAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AVwBBAFMAQQA0AEEAcgBlAGEAcwBfAFUAbgBpAHQAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBXAEEAUwBBADQAQQByAGUAYQBzAF8AUwBvAHUAcgBjAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAEEAdQBzAHQAcgBhAGwAaQBhAG4AIABCAHUAcgBlAGEAdQAgAG8AZgAgAFMAdABhAHQAaQBzAHQAaQBjAHMAIAAoAEEAQgBTACkAIAAtACAAUwB0AGEAdABpAHMAdABpAGMAYQBsACAAQQByAGUAYQBzACAATABlAHYAZQBsACAAMgAgAC0AIAAyADAAMgAxACAALQAgAFMAaABhAHAAZQBmAGkAbABlAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBXAEEAUwBBADQAQQByAGUAYQBzAF8ARABhAHQAYQBcAG4AIAAgACAAPQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAE0AQQBLAEUAQQBSAFIAQQBZACgAMQAxACwAIAAxACwAIABcAG4AIAAgACAAIAAgACAATABBAE0AQgBEAEEAKAByACwAYwAsACAAXABuACAAIAAgACAAIAAgACAAIABJAE4ARABFAFgAKAB7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBTAEEAIAA0ACAATgBhAG0AZQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAQgB1AG4AYgB1AHIAeQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIATQBhAG4AZAB1AHIAYQBoAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBQAGUAcgB0AGgAIAAtACAASQBuAG4AZQByAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBQAGUAcgB0AGgAIAAtACAATgBvAHIAdABoACAARQBhAHMAdABcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAUABlAHIAdABoACAALQAgAE4AbwByAHQAaAAgAFcAZQBzAHQAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFAAZQByAHQAaAAgAC0AIABTAG8AdQB0AGgAIABFAGEAcwB0AFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBQAGUAcgB0AGgAIAAtACAAUwBvAHUAdABoACAAVwBlAHMAdABcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVwBlAHMAdABlAHIAbgAgAEEAdQBzAHQAcgBhAGwAaQBhACAALQAgAFcAaABlAGEAdAAgAEIAZQBsAHQAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFcAZQBzAHQAZQByAG4AIABBAHUAcwB0AHIAYQBsAGkAYQAgAC0AIABPAHUAdABiAGEAYwBrACAAKABOAG8AcgB0AGgAKQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVwBlAHMAdABlAHIAbgAgAEEAdQBzAHQAcgBhAGwAaQBhACAALQAgAE8AdQB0AGIAYQBjAGsAIAAoAFMAbwB1AHQAaAApAFwAIgBcAG4AIAAgACAAIAAgACAAIAAgAH0ALAAgAHIALAAgAGMAKQBcAG4AIAAgACAAIAAgACAAKQBcAG4AIAAgACAAIAApAFwAbgAgACAAKQA7AFwAbgBcAG4ALwAqACAAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AVwBlAHQAQQBuAGQARAByAHkAWgBvAG4AZQBzAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuACoALwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFcAZQB0AEEAbgBkAEQAcgB5AFoAbwBuAGUAcwBfAFQAaQB0AGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAVgBFAEUAUgBHACAAQQB1AHMAdAByAGEAbABpAGEAbgAgAHcAZQB0ACAAYQBuAGQAIABkAHIAeQAgAHoAbwBuAGUAcwBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AVwBlAHQAQQBuAGQARAByAHkAWgBvAG4AZQBzAF8AVgBhAHIAaQBhAGIAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AVwBlAHQAQQBuAGQARAByAHkAWgBvAG4AZQBzAF8AVQBuAGkAdABcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFcAZQB0AEEAbgBkAEQAcgB5AFoAbwBuAGUAcwBfAFMAbwB1AHIAYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBWAEUARQBSAEcAIAAyADAAMgA2ADoAIABUAGEAYgBsAGUAIAAxAC4AMgA6ACAAVAByAGEAbgBzAGwAYQB0AGkAbgBnACAAYwBsAGkAbQBhAHQAZQAgAHoAbwBuAGUAcwAgAHQAbwAgAHcAZQB0ACAAYQBuAGQAIABkAHIAeQAgAHoAbwBuAGUAcwBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AVwBlAHQAQQBuAGQARAByAHkAWgBvAG4AZQBzAF8AVgBhAHIAaQBhAHQAaQBvAG4AXABuACAAIAAgAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABNAEEASwBFAEEAUgBSAEEAWQAoADMALAAgADEALAAgAFwAbgAgACAAIAAgACAAIABMAEEATQBCAEQAQQAoAHIALABjACwAIABcAG4AIAAgACAAIAAgACAAIAAgAEkATgBEAEUAWAAoAHsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFYAQQBSAEkAQQBUAEkATwBOACAATwBGACAAUwBPAFUAUgBDAEUAIABEAEEAVABBADoAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEEAZABkAGUAZAAgAHcAYQByAG0AIAAvACAAYwBvAG8AbAAgAHQAZQBtAHAAZQByAGEAdABlACAAbQBvAGkAcwB0ACAALwAgAGQAcgB5ACAALQAgAGwAbwB3ACAAZgByAG8AcwB0ACAAYQBuAGQAIABoAGkAZwBoACAAdABlAG0AcAAgAGMAbABhAHMAcwBlAHMAIAB0AG8AIABhAGMAYwBvAG0AbQBvAGQAYQB0AGUAIABjAGwAaQBtAGEAdABlACAAcwBjAGUAbgBhAHIAaQBvAHMAIABlAHgAYwBsAHUAZABlAGQAIABiAHkAIABWAEUARQBSAEcAIABjAHIAaQB0AGUAcgBpAGEALgBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIARgBpAHgAZQBkACAAdAB5AHAAbwAgAC0AIABDAGgAYQBuAGcAZQBkACAAJwBGAHIAeQAnACAAdABvACAAJwBEAHIAeQAnAC4AXAAiAFwAbgAgACAAIAAgACAAIAAgACAAfQAsACAAcgAsACAAYwApAFwAbgAgACAAIAAgACAAIAApAFwAbgAgACAAIAAgACkAXABuACAAIAApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBXAGUAdABBAG4AZABEAHIAeQBaAG8AbgBlAHMAXwBEAGEAdABhAFwAbgAgACAAIAA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAATQBBAEsARQBBAFIAUgBBAFkAKAAxADUALAAgADIALAAgAFwAbgAgACAAIAAgACAAIABMAEEATQBCAEQAQQAoAHIALABjACwAIABcAG4AIAAgACAAIAAgACAAIAAgAEkATgBEAEUAWAAoAHsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEMAbABpAG0AYQB0AGUAIABaAG8AbgBlAFwAIgAsACAAXAAiAFcAZQB0ACAAbwByACAARAByAHkAIABaAG8AbgBlAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBUAHIAbwBwAGkAYwBhAGwAIABtAG8AbgB0AGEAbgBlAFwAIgAsACAAXAAiAFcAZQB0ACAAYwBsAGkAbQBhAHQAZQAgAHoAbwBuAGUAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFQAcgBvAHAAaQBjAGEAbAAgAHcAZQB0AFwAIgAsACAAXAAiAFcAZQB0ACAAYwBsAGkAbQBhAHQAZQAgAHoAbwBuAGUAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFQAcgBvAHAAaQBjAGEAbAAgAG0AbwBpAHMAdABcACIALAAgAFwAIgBXAGUAdAAgAGMAbABpAG0AYQB0AGUAIAB6AG8AbgBlAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBUAHIAbwBwAGkAYwBhAGwAIABkAHIAeQBcACIALAAgAFwAIgBEAHIAeQAgAGMAbABpAG0AYQB0AGUAIAB6AG8AbgBlAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBXAGEAcgBtACAAdABlAG0AcABlAHIAYQB0AGUAIABtAG8AaQBzAHQAXAAiACwAIABcACIAVwBlAHQAIABjAGwAaQBtAGEAdABlACAAegBvAG4AZQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVwBhAHIAbQAgAHQAZQBtAHAAZQByAGEAdABlACAAZAByAHkAXAAiACwAIABcACIARAByAHkAIABjAGwAaQBtAGEAdABlACAAegBvAG4AZQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAQwBvAG8AbAAgAHQAZQBtAHAAZQByAGEAdABlACAAbQBvAGkAcwB0AFwAIgAsACAAXAAiAFcAZQB0ACAAYwBsAGkAbQBhAHQAZQAgAHoAbwBuAGUAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEMAbwBvAGwAIAB0AGUAbQBwAGUAcgBhAHQAZQAgAGQAcgB5AFwAIgAsACAAXAAiAEQAcgB5ACAAYwBsAGkAbQBhAHQAZQAgAHoAbwBuAGUAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFcAYQByAG0AIAB0AGUAbQBwAGUAcgBhAHQAZQAgAG0AbwBpAHMAdAAgAC0AIABsAG8AdwAgAGYAcgBvAHMAdABcACIALAAgAFwAIgBXAGUAdAAgAGMAbABpAG0AYQB0AGUAIAB6AG8AbgBlAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBXAGEAcgBtACAAdABlAG0AcABlAHIAYQB0AGUAIABkAHIAeQAgAC0AIABsAG8AdwAgAGYAcgBvAHMAdABcACIALAAgAFwAIgBEAHIAeQAgAGMAbABpAG0AYQB0AGUAIAB6AG8AbgBlAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBXAGEAcgBtACAAdABlAG0AcABlAHIAYQB0AGUAIABtAG8AaQBzAHQAIAAtACAAaABpAGcAaAAgAHQAZQBtAHAAXAAiACwAIABcACIAVwBlAHQAIABjAGwAaQBtAGEAdABlACAAegBvAG4AZQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVwBhAHIAbQAgAHQAZQBtAHAAZQByAGEAdABlACAAZAByAHkAIAAtACAAaABpAGcAaAAgAHQAZQBtAHAAXAAiACwAIABcACIARAByAHkAIABjAGwAaQBtAGEAdABlACAAegBvAG4AZQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAQwBvAG8AbAAgAHQAZQBtAHAAZQByAGEAdABlACAAbQBvAGkAcwB0ACAALQAgAGwAbwB3ACAAZgByAG8AcwB0AFwAIgAsACAAXAAiAFcAZQB0ACAAYwBsAGkAbQBhAHQAZQAgAHoAbwBuAGUAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEMAbwBvAGwAIAB0AGUAbQBwAGUAcgBhAHQAZQAgAGQAcgB5ACAALQAgAGwAbwB3ACAAZgByAG8AcwB0AFwAIgAsACAAXAAiAEQAcgB5ACAAYwBsAGkAbQBhAHQAZQAgAHoAbwBuAGUAXAAiAFwAbgAgACAAIAAgACAAIAAgACAAfQAsACAAcgAsACAAYwApAFwAbgAgACAAIAAgACAAIAApAFwAbgAgACAAIAAgACkAXABuACAAIAApADsAXABuAFwAbgAvACoAIABcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBDAGwAaQBtAGEAdABlAFoAbwBuAGUAcwBcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgAqAC8AXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBDAGwAaQBtAGEAdABlAFoAbwBuAGUAcwBfAFQAaQB0AGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAVgBFAEUAUgBHACAAQQB1AHMAdAByAGEAbABpAGEAbgAgAGMAbABpAG0AYQB0AGUAIAB6AG8AbgBlAHMAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEMAbABpAG0AYQB0AGUAWgBvAG4AZQBzAF8AVgBhAHIAaQBhAGIAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQwBsAGkAbQBhAHQAZQBaAG8AbgBlAHMAXwBVAG4AaQB0AFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQwBsAGkAbQBhAHQAZQBaAG8AbgBlAHMAXwBTAG8AdQByAGMAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAVgBFAEUAUgBHACAAMgAwADIANgA6ACAAVABhAGIAbABlACAAMQAuADMAOgAgAEMAbABpAG0AYQB0AGUAIABhAG4AZAAgAFIAYQBpAG4AZgBhAGwAbAAgAHoAbwBuAGUAIABjAGwAYQBzAHMAaQBmAGkAYwBhAHQAaQBvAG4AcwAgAGEAbgBkACAAZABlAGYAaQBuAGkAdABpAG8AbgBzAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBDAGwAaQBtAGEAdABlAFoAbwBuAGUAcwBfAFYAYQByAGkAYQB0AGkAbwBuAFwAbgAgACAAIAA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAATQBBAEsARQBBAFIAUgBBAFkAKAA1ACwAIAAxACwAIABcAG4AIAAgACAAIAAgACAATABBAE0AQgBEAEEAKAByACwAYwAsACAAXABuACAAIAAgACAAIAAgACAAIABJAE4ARABFAFgAKAB7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBWAEEAUgBJAEEAVABJAE8ATgAgAE8ARgAgAFMATwBVAFIAQwBFACAARABBAFQAQQA6AFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBBAGQAZABlAGQAIAB3AGEAcgBtACAALwAgAGMAbwBvAGwAIAB0AGUAbQBwAGUAcgBhAHQAZQAgAG0AbwBpAHMAdAAgAC8AIABkAHIAeQAgAC0AIABsAG8AdwAgAGYAcgBvAHMAdAAgAGEAbgBkACAAaABpAGcAaAAgAHQAZQBtAHAAIABjAGwAYQBzAHMAZQBzACAAdABvACAAYQBjAGMAbwBtAG0AbwBkAGEAdABlACAAYwBsAGkAbQBhAHQAZQAgAHMAYwBlAG4AYQByAGkAbwBzACAAZQB4AGMAbAB1AGQAZQBkACAAYgB5ACAAVgBFAEUAUgBHACAAYwByAGkAdABlAHIAaQBhAC4AXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEYAaQB4AGUAZAAgAHQAeQBwAG8AIABpAG4AIABNAEEAVAAgAHYAYQBsAHUAZQAgAGYAbwByACAAdwBhAHIAbQAgAHQAZQBtAHAAZQByAGEAdABlACAAZAByAHkAIAAtACAAYwBoAGEAbgBnAGUAZAAgADEAMAAgAHQAbwAgADEAMQAuAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBBAGQAZABlAGQAIABtAGkAbgAgAGEAbgBkACAAbQBhAHgAIABjAG8AbAB1AG0AbgBzACAAZgBvAHIAIABNAEEAVAAsACAATQBBAFAALAAgAGYAcgBvAHMAdAAgAGQAYQB5AHMAIABwAGUAcgAgAHkAZQBhAHIALAAgAGUAbABlAHYAYQB0AGkAbwBuACwAIABNAEEAUAA6AFAARQBUACAAdABvACAAYwBhAGwAYwB1AGwAYQB0AGUAIAB6AG8AbgBlAHMAIABmAHIAbwBtACAAcgBlAGEAbAAgAGMAbABpAG0AYQB0AGUAIABkAGEAdABhAC4AXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEcAQQBGACAAYQBjAGMAZQBwAHQAcwAgAHIAYQBpAG4AZgBhAGwAbAAgAGEAcwAgAGEAIABwAHIAbwB4AHkAIABmAG8AcgAgAHAAcgBlAGMAaQBwAGkAdABhAHQAaQBvAG4ALgBcACIAXABuACAAIAAgACAAIAAgACAAIAB9ACwAIAByACwAIABjACkAXABuACAAIAAgACAAIAAgACkAXABuACAAIAAgACAAKQBcAG4AIAAgACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEMAbABpAG0AYQB0AGUAWgBvAG4AZQBzAF8ARABhAHQAYQBcAG4AIAAgACAAPQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAE0AQQBLAEUAQQBSAFIAQQBZACgAOQAsACAAMQA2ACwAIABcAG4AIAAgACAAIAAgACAATABBAE0AQgBEAEEAKAByACwAYwAsACAAXABuACAAIAAgACAAIAAgACAAIABJAE4ARABFAFgAKAB7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBDAGwAaQBtAGEAdABlACAAWgBvAG4AZQBcACIALAAgAFwAIgBNAEEAVABcACIALAAgAFwAIgBNAEEAUABcACIALAAgAFwAIgBGAHIAbwBzAHQAIABkAGEAeQBzACAAcABlAHIAIAB5AGUAYQByAFwAIgAsACAAXAAiAEUAbABlAHYAYQB0AGkAbwBuAFwAIgAsACAAXAAiAE0AQQBQADoAUABFAFQAXAAiACwAIABcACIATQBpAG4AIAB0AGUAbQBwAFwAIgAsACAAXAAiAE0AYQB4ACAAdABlAG0AcABcACIALAAgAFwAIgBNAGkAbgAgAHIAYQBpAG4AZgBhAGwAbABcACIALAAgAFwAIgBNAGEAeAAgAHIAYQBpAG4AZgBhAGwAbABcACIALAAgAFwAIgBNAGkAbgAgAGYAcgBvAHMAdAAgAGQAYQB5AHMAXAAiACwAIABcACIATQBhAHgAIABmAHIAbwBzAHQAIABkAGEAeQBzAFwAIgAsACAAXAAiAE0AaQBuACAAZQBsAGUAdgBhAHQAaQBvAG4AXAAiACwAIABcACIATQBhAHgAIABlAGwAZQB2AGEAdABpAG8AbgBcACIALAAgAFwAIgBNAGkAbgAgAE0AQQBQADoAUABFAFQAXAAiACwAIABcACIATQBpAG4AIABNAEEAUAA6AFAARQBUAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBUAHIAbwBwAGkAYwBhAGwAIABtAG8AbgB0AGEAbgBlAFwAIgAsACAAXAAiAD4AIAAxADgAIABDAFwAIgAsACAAXAAiAEEAbgB5AFwAIgAsACAAXAAiAGQiIAA3AFwAIgAsACAAXAAiAD4AIAAxADAAMAAwACAAbQBcACIALAAgAFwAIgBBAG4AeQBcACIALAAgADEAOAAuADAAMAAxACwAIAA5ADkAOQA5ADkAOQAsACAALQA5ADkAOQA5ADkAOQAsACAAOQA5ADkAOQA5ADkALAAgAC0AOQA5ADkAOQA5ADkALAAgADcALAAgADEAMAAwADAALAAgADkAOQA5ADkAOQA5ACwAIAAtADkAOQA5ADkAOQA5ACwAIAA5ADkAOQA5ADkAOQA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBUAHIAbwBwAGkAYwBhAGwAIAB3AGUAdABcACIALAAgAFwAIgA+ACAAMQA4ACAAQwBcACIALAAgAFwAIgA+ACAAMgAwADAAMAAgAG0AbQBcACIALAAgAFwAIgBkIiAANwBcACIALAAgAFwAIgBkIiAAMQAwADAAMAAgAG0AXAAiACwAIABcACIAQQBuAHkAXAAiACwAIAAxADgALgAwADAAMQAsACAAOQA5ADkAOQA5ADkALAAgADIAMAAwADAALgAwADAAMQAsACAAOQA5ADkAOQA5ADkALAAgAC0AOQA5ADkAOQA5ADkALAAgADcALAAgAC0AOQA5ADkAOQA5ADkALAAgADkAOQA5AC4AOQA5ADkALAAgACAALQA5ADkAOQA5ADkAOQAsACAAOQA5ADkAOQA5ADkAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVAByAG8AcABpAGMAYQBsACAAbQBvAGkAcwB0AFwAIgAsACAAXAAiAD4AIAAxADgAIABDAFwAIgAsACAAXAAiAD4AIAAxADAAMAAwACAAbQBtACAALQAgAGQiIAAyADAAMAAwACAAbQBtAFwAIgAsACAAXAAiAGQiIAA3AFwAIgAsACAAXAAiAGQiIAAxADAAMAAwACAAbQBcACIALAAgAFwAIgBBAG4AeQBcACIALAAgADEAOAAuADAAMAAxACwAIAA5ADkAOQA5ADkAOQAsACAAMQAwADAAMAAuADAAMAAxACwAIAAyADAAMAAwACwAIAAtADkAOQA5ADkAOQA5ACwAIAA3ACwAIAAtADkAOQA5ADkAOQA5ACwAIAA5ADkAOQAuADkAOQA5ACwAIAAgAC0AOQA5ADkAOQA5ADkALAAgADkAOQA5ADkAOQA5ADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFQAcgBvAHAAaQBjAGEAbAAgAGQAcgB5AFwAIgAsACAAXAAiAD4AIAAxADgAIABDAFwAIgAsACAAXAAiAGQiIAAxADAAMAAwACAAbQBtAFwAIgAsACAAXAAiAGQiIAA3AFwAIgAsACAAXAAiAGQiIAAxADAAMAAwACAAbQBcACIALAAgAFwAIgBBAG4AeQBcACIALAAgADEAOAAuADAAMAAxACwAIAA5ADkAOQA5ADkAOQAsACAALQA5ADkAOQA5ADkAOQAsACAAMQAwADAAMAAsACAALQA5ADkAOQA5ADkAOQAsACAANwAsACAALQA5ADkAOQA5ADkAOQAsACAAOQA5ADkALgA5ADkAOQAsACAAIAAtADkAOQA5ADkAOQA5ACwAIAA5ADkAOQA5ADkAOQA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBXAGEAcgBtACAAdABlAG0AcABlAHIAYQB0AGUAIABtAG8AaQBzAHQAXAAiACwAIABcACIAPgAgADEAMAAgAEMAXAAiACwAIABcACIAQQBuAHkAXAAiACwAIABcACIAQQBuAHkAXAAiACwAIABcACIAQQBuAHkAXAAiACwAIABcACIAPgAgADEAXAAiACwAIAAxADAALgAwADAAMQAsACAAOQA5ADkAOQA5ADkALAAgAC0AOQA5ADkAOQA5ADkALAAgADkAOQA5ADkAOQA5ACwAIAAtADkAOQA5ADkAOQA5ACwAIAA5ADkAOQA5ADkAOQAsACAALQA5ADkAOQA5ADkAOQAsACAAOQA5ADkAOQA5ADkALAAgADEALgAwADAAMQAsACAAOQA5ADkAOQA5ADkAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVwBhAHIAbQAgAHQAZQBtAHAAZQByAGEAdABlACAAZAByAHkAXAAiACwAIABcACIAPgAgADEAMAAgAEMAXAAiACwAIABcACIAQQBuAHkAXAAiACwAIABcACIAQQBuAHkAXAAiACwAIABcACIAQQBuAHkAXAAiACwAIABcACIAZCIgADEAXAAiACwAIAAxADAALgAwADAAMQAsACAAOQA5ADkAOQA5ADkALAAgAC0AOQA5ADkAOQA5ADkALAAgADkAOQA5ADkAOQA5ACwAIAAtADkAOQA5ADkAOQA5ACwAIAA5ADkAOQA5ADkAOQAsACAALQA5ADkAOQA5ADkAOQAsACAAOQA5ADkAOQA5ADkALAAgACAALQA5ADkAOQA5ADkAOQAsACAAMQA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBDAG8AbwBsACAAdABlAG0AcABlAHIAYQB0AGUAIABtAG8AaQBzAHQAXAAiACwAIABcACIAPgAgADAAIABDACAALQAgAGQiIAAxADAAIABDAFwAIgAsACAAXAAiAEEAbgB5AFwAIgAsACAAXAAiAEEAbgB5AFwAIgAsACAAXAAiAEEAbgB5AFwAIgAsACAAXAAiAD4AIAAxAFwAIgAsACAALQA5ADkAOQA5ADkAOQAsACAAMQAwACwAIAAtADkAOQA5ADkAOQA5ACwAIAA5ADkAOQA5ADkAOQAsACAALQA5ADkAOQA5ADkAOQAsACAAOQA5ADkAOQA5ADkALAAgAC0AOQA5ADkAOQA5ADkALAAgADkAOQA5ADkAOQA5ACwAIAAxAC4AMAAwADEALAAgADkAOQA5ADkAOQA5ADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEMAbwBvAGwAIAB0AGUAbQBwAGUAcgBhAHQAZQAgAGQAcgB5AFwAIgAsACAAXAAiAD4AIAAwACAAQwAgAC0AIABkIiAAMQAwACAAQwBcACIALAAgAFwAIgBBAG4AeQBcACIALAAgAFwAIgBBAG4AeQBcACIALAAgAFwAIgBBAG4AeQBcACIALAAgAFwAIgBkIiAAMQBcACIALAAgAC0AOQA5ADkAOQA5ADkALAAgADEAMAAsACAALQA5ADkAOQA5ADkAOQAsACAAOQA5ADkAOQA5ADkALAAgAC0AOQA5ADkAOQA5ADkALAAgADkAOQA5ADkAOQA5ACwAIAAtADkAOQA5ADkAOQA5ACwAIAA5ADkAOQA5ADkAOQAsACAAIAAtADkAOQA5ADkAOQA5ACwAIAAxAFwAbgAgACAAIAAgACAAIAAgACAAfQAsACAAcgAsACAAYwApAFwAbgAgACAAIAAgACAAIAApAFwAbgAgACAAIAAgACkAXABuACAAIAApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBDAGwAaQBtAGEAdABlAFoAbwBuAGUAcwBfAEEAcABwAGUAbgBkAGkAYwBlAHMAXABuACAAIAAgAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABNAEEASwBFAEEAUgBSAEEAWQAoADQALAAgADEALAAgAFwAbgAgACAAIAAgACAAIABMAEEATQBCAEQAQQAoAHIALABjACwAIABcAG4AIAAgACAAIAAgACAAIAAgAEkATgBEAEUAWAAoAHsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAE4AbwB0AGUAOgBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIATQBBAFQAIAA9ACAAbQBlAGEAbgAgAGEAbgBuAHUAYQBsACAAdABlAG0AcABlAHIAYQB0AHUAcgBlAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBNAEEAUAAgAD0AIABtAGUAYQBuACAAYQBuAG4AdQBhAGwAIABwAHIAZQBjAGkAcABpAHQAYQB0AGkAbwBuAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBQAEUAVAAgAD0AIABwAG8AdABlAG4AdABpAGEAbAAgAGUAdgBhAHAAbwB0AHIAYQBuAHMAcABpAHIAYQB0AGkAbwBuAFwAIgBcAG4AIAAgACAAIAAgACAAIAAgAH0ALAAgAHIALAAgAGMAKQBcAG4AIAAgACAAIAAgACAAKQBcAG4AIAAgACAAIAApAFwAbgAgACAAKQA7AFwAbgBcAG4AXABuAC8AKgAgAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFQAZQBtAHAAZQByAGEAdAB1AHIAZQBaAG8AbgBlAHMAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AKgAvAFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AVABlAG0AcABlAHIAYQB0AHUAcgBlAFoAbwBuAGUAcwBfAFQAaQB0AGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAVgBFAEUAUgBHACAAQQB1AHMAdAByAGEAbABpAGEAbgAgAHQAZQBtAHAAZQByAGEAdAB1AHIAZQAgAHoAbwBuAGUAcwBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AVABlAG0AcABlAHIAYQB0AHUAcgBlAFoAbwBuAGUAcwBfAFYAYQByAGkAYQBiAGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFQAZQBtAHAAZQByAGEAdAB1AHIAZQBaAG8AbgBlAHMAXwBVAG4AaQB0AFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AVABlAG0AcABlAHIAYQB0AHUAcgBlAFoAbwBuAGUAcwBfAFMAbwB1AHIAYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBWAEUARQBSAEcAIAAyADAAMgA2ADoAIABUAGEAYgBsAGUAIAAxAC4AMwA6ACAAQwBsAGkAbQBhAHQAZQAgAGEAbgBkACAAUgBhAGkAbgBmAGEAbABsACAAegBvAG4AZQAgAGMAbABhAHMAcwBpAGYAaQBjAGEAdABpAG8AbgBzACAAYQBuAGQAIABkAGUAZgBpAG4AaQB0AGkAbwBuAHMAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFQAZQBtAHAAZQByAGEAdAB1AHIAZQBaAG8AbgBlAHMAXwBWAGEAcgBpAGEAdABpAG8AbgBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAVgBBAFIASQBBAFQASQBPAE4AIABPAEYAIABTAE8AVQBSAEMARQAgAEQAQQBUAEEAOgAgAEEAZABkAGUAZAAgAGUAeAB0AHIAYQAgAE0AQQBUACAAbQBpAG4AIABhAG4AZAAgAE0AQQBUACAAbQBhAHgAIABjAG8AbAB1AG0AbgBzACAAdABvACAAYwBhAGwAYwB1AGwAYQB0AGUAIAB6AG8AbgBlACAAZgByAG8AbQAgAHIAZQBhAGwAIAB0AGUAbQBwAGUAcgBhAHQAdQByAGUAIABkAGEAdABhAC4AXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFQAZQBtAHAAZQByAGEAdAB1AHIAZQBaAG8AbgBlAHMAXwBEAGEAdABhAFwAbgAgACAAIAA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAATQBBAEsARQBBAFIAUgBBAFkAKAA0ACwAIAA0ACwAIABcAG4AIAAgACAAIAAgACAATABBAE0AQgBEAEEAKAByACwAYwAsACAAXABuACAAIAAgACAAIAAgACAAIABJAE4ARABFAFgAKAB7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBUAGUAbQBwAGUAcgBhAHQAdQByAGUAIABaAG8AbgBlAFwAIgAsACAAXAAiAE0AZQBkAGkAYQBuACAAQQBuAG4AdQBhAGwAIABUAGUAbQBwAGUAcgBhAHQAdQByAGUAIAAoAE0AQQBUACkAXAAiACwAIABcACIATQBpAG4AIABNAEEAVABcACIALAAgAFwAIgBNAGEAeAAgAE0AQQBUAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBXAGEAcgBtAFwAIgAsACAAXAAiAGUiIAAyADYAIABDAFwAIgAsACAAMgA2ACwAIAA5ADkAOQA5ADkAOQA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBUAGUAbQBwAGUAcgBhAHQAZQBcACIALAAgAFwAIgAxADUAIAAtACAAMgA1ACAAQwBcACIALAAgADEANQAsACAAMgA1AC4AOQA5ADkAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAQwBvAG8AbABcACIALAAgAFwAIgBkIiAAMQA0ACAAQwBcACIALAAgAC0AOQA5ADkAOQA5ADkALAAgADEANAAuADkAOQA5AFwAbgAgACAAIAAgACAAIAAgACAAfQAsACAAcgAsACAAYwApAFwAbgAgACAAIAAgACAAIAApAFwAbgAgACAAIAAgACkAXABuACAAIAApADsAXABuAFwAbgAvACoAIABcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBSAGEAaQBuAGYAYQBsAGwAWgBvAG4AZQBzAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuACoALwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFIAYQBpAG4AZgBhAGwAbABaAG8AbgBlAHMAXwBUAGkAdABsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFYARQBFAFIARwAgAEEAdQBzAHQAcgBhAGwAaQBhAG4AIAByAGEAaQBuAGYAYQBsAGwAIAB6AG8AbgBlAHMAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFIAYQBpAG4AZgBhAGwAbABaAG8AbgBlAHMAXwBWAGEAcgBpAGEAYgBsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBSAGEAaQBuAGYAYQBsAGwAWgBvAG4AZQBzAF8AVQBuAGkAdABcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFIAYQBpAG4AZgBhAGwAbABaAG8AbgBlAHMAXwBTAG8AdQByAGMAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAVgBFAEUAUgBHACAAMgAwADIANgA6ACAAVABhAGIAbABlACAAMQAuADMAOgAgAEMAbABpAG0AYQB0AGUAIABhAG4AZAAgAFIAYQBpAG4AZgBhAGwAbAAgAHoAbwBuAGUAIABjAGwAYQBzAHMAaQBmAGkAYwBhAHQAaQBvAG4AcwAgAGEAbgBkACAAZABlAGYAaQBuAGkAdABpAG8AbgBzAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBSAGEAaQBuAGYAYQBsAGwAWgBvAG4AZQBzAF8AVgBhAHIAaQBhAHQAaQBvAG4AXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFYAQQBSAEkAQQBUAEkATwBOACAATwBGACAAUwBPAFUAUgBDAEUAIABEAEEAVABBADoAIABBAGQAZABlAGQAIABlAHgAdAByAGEAIABSAGEAaQBuAGYAYQBsAGwAIABtAGkAbgAgAGEAbgBkACAAUgBhAGkAbgBmAGEAbABsACAAbQBhAHgAIABjAG8AbAB1AG0AbgBzACAAdABvACAAYwBhAGwAYwB1AGwAYQB0AGUAIAB6AG8AbgBlACAAZgByAG8AbQAgAHIAZQBhAGwAIAByAGEAaQBuAGYAYQBsAGwAIABkAGEAdABhAC4AXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFIAYQBpAG4AZgBhAGwAbABaAG8AbgBlAHMAXwBEAGEAdABhAFwAbgAgACAAIAA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAATQBBAEsARQBBAFIAUgBBAFkAKAAzACwAIAA0ACwAIABcAG4AIAAgACAAIAAgACAATABBAE0AQgBEAEEAKAByACwAYwAsACAAXABuACAAIAAgACAAIAAgACAAIABJAE4ARABFAFgAKAB7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBSAGEAaQBuAGYAYQBsAGwAIABaAG8AbgBlAFwAIgAsACAAXAAiAEEAbgBuAHUAYQBsACAAcgBhAGkAbgBmAGEAbABsAFwAIgAsACAAXAAiAFIAYQBpAG4AZgBhAGwAbAAgAG0AaQBuAFwAIgAsACAAXAAiAFIAYQBpAG4AZgBhAGwAbAAgAG0AYQB4AFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBIAGkAZwBoACAAcgBhAGkAbgBmAGEAbABsAFwAIgAsACAAXAAiAEEAbgBuAHUAYQBsACAAcgBhAGkAbgBmAGEAbABsACAAPgAgADYAMAAwAG0AbQBcACIALAAgADYAMAAwAC4AMAAwADEALAAgADkAOQA5ADkAOQA5ADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEwAbwB3ACAAcgBhAGkAbgBmAGEAbABsAFwAIgAsACAAXAAiAEEAbgBuAHUAYQBsACAAcgBhAGkAbgBmAGEAbABsACAAZCIgADYAMAAwAG0AbQBcACIALAAgAC0AOQA5ADkAOQA5ADkALAAgADYAMAAwAFwAbgAgACAAIAAgACAAIAAgACAAfQAsACAAcgAsACAAYwApAFwAbgAgACAAIAAgACAAIAApAFwAbgAgACAAIAAgACkAXABuACAAIAApADsAXABuAFwAbgAvACoAIABcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBMAGUAYQBjAGgAaQBuAGcAWgBvAG4AZQBzAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuACoALwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEwAZQBhAGMAaABpAG4AZwBaAG8AbgBlAHMAXwBUAGkAdABsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFYARQBFAFIARwAgAEEAdQBzAHQAcgBhAGwAaQBhAG4AIABsAGUAYQBjAGgAaQBuAGcAIAB6AG8AbgBlAHMAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEwAZQBhAGMAaABpAG4AZwBaAG8AbgBlAHMAXwBWAGEAcgBpAGEAYgBsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBMAGUAYQBjAGgAaQBuAGcAWgBvAG4AZQBzAF8AVQBuAGkAdABcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEwAZQBhAGMAaABpAG4AZwBaAG8AbgBlAHMAXwBTAG8AdQByAGMAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAVgBFAEUAUgBHACAAMgAwADIANgA6ACAAVABhAGIAbABlACAAMQAuADMAOgAgAEMAbABpAG0AYQB0AGUAIABhAG4AZAAgAFIAYQBpAG4AZgBhAGwAbAAgAHoAbwBuAGUAIABjAGwAYQBzAHMAaQBmAGkAYwBhAHQAaQBvAG4AcwAgAGEAbgBkACAAZABlAGYAaQBuAGkAdABpAG8AbgBzAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBMAGUAYQBjAGgAaQBuAGcAWgBvAG4AZQBzAF8AVgBhAHIAaQBhAHQAaQBvAG4AXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBMAGUAYQBjAGgAaQBuAGcAWgBvAG4AZQBzAF8ARABhAHQAYQBcAG4AIAAgACAAPQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAE0AQQBLAEUAQQBSAFIAQQBZACgANAAsACAAMgAsACAAXABuACAAIAAgACAAIAAgAEwAQQBNAEIARABBACgAcgAsAGMALAAgAFwAbgAgACAAIAAgACAAIAAgACAASQBOAEQARQBYACgAewBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIATABlAGEAYwBoAGkAbgBnACAAWgBvAG4AZQBcACIALAAgAFwAIgBMAGUAYQBjAGgAaQBuAGcAIABjAHIAaQB0AGUAcgBpAGEAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEwAZQBhAGMAaABpAG4AZwAgAG8AYwBjAHUAcgBzAFwAIgAsACAAXAAiAKMDKAA12F/cNdhO3DXYVtw12FvcKQA+AKMDKAA12DjcNdhH3DAAKQArADXYYNw12FzcNdhW3DXYWdwgADXYZNw12E7cNdhh3DXYUtw12F/cIAAOITXYXNw12FncNdhR3DXYVtw12FvcNdhU3CAANdhQ3DXYTtw12F3cNdhO3DXYUNw12FbcNdhh3DXYZtxcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIATABlAGEAYwBoAGkAbgBnACAAZABvAGUAcwAgAG4AbwB0ACAAbwBjAGMAdQByAFwAIgAsACAAXAAiAKMDKAA12F/cNdhO3DXYVtw12FvcKQBkIqMDKAA12DjcNdhH3DAAKQArADXYYNw12FzcNdhW3DXYWdwgADXYZNw12E7cNdhh3DXYUtw12F/cIAAOITXYXNw12FncNdhR3DXYVtw12FvcNdhU3CAANdhQ3DXYTtw12F3cNdhO3DXYUNw12FbcNdhh3DXYZtxcACIAXABuACAAIAAgACAAIAAgACAAIAB9ACwAIAByACwAIABjACkAXABuACAAIAAgACAAIAAgACkAXABuACAAIAAgACAAKQBcAG4AIAAgACkAOwBcAG4AXABuAC8AKgAgAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAcgBhAGMAVwBFAFQAXABuADUALgA1AC4AMgAuADMAIABDAG8AbgBzAHQAYQBuAHQAIABQAGEAcgBhAG0AZQB0AGUAcgBzAFwAbgBGAHIAYQBjAHQAaQBvAG4AIABvAGYAIABOACAAdABoAGEAdAAgAGkAcwAgAGEAdgBhAGkAbABhAGIAbABlACAAZgBvAHIAIABsAGUAYQBjAGgAaQBuAGcAIABhAG4AZAAgAHIAdQBuAG8AZgBmAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuACoALwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAcgBhAGMAVwBFAFQAXwBUAGkAdABsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAEYAcgBhAGMAdABpAG8AbgAgAG8AZgAgAE4AIAB0AGgAYQB0ACAAaQBzACAAYQB2AGEAaQBsAGEAYgBsAGUAIABmAG8AcgAgAGwAZQBhAGMAaABpAG4AZwAgAGEAbgBkACAAcgB1AG4AbwBmAGYAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAcgBhAGMAVwBFAFQAXwBVAG4AaQB0AFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgAoAEQAaQBtAGUAbgBzAGkAbwBuAGwAZQBzAHMAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAcgBhAGMAVwBFAFQAXwBTAG8AdQByAGMAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAVgBFAEUAUgBHACAAMgAwADIANgA6ADUALgA1AC4AMgAuADMAIABDAG8AbgBzAHQAYQBuAHQAIABQAGEAcgBhAG0AZQB0AGUAcgBzAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAHIAYQBjAFcARQBUAF8ATgBJAFIAUgBlAGYAZQByAGUAbgBjAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAHIAYQBjAFcARQBUAF8ARABhAHQAYQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABNAEEASwBFAEEAUgBSAEEAWQAoADMALAAgADIALAAgAFwAbgAgACAAIAAgACAAIABMAEEATQBCAEQAQQAoAHIALABjACwAIABcAG4AIAAgACAAIAAgACAAIAAgAEkATgBEAEUAWAAoAHsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEkAcwAgAGkAbgAgAGwAZQBhAGMAaABpAG4AZwAgAHoAbwBuAGUAXAAiACwAXAAiAEYAcgBhAGMAVwBFAFQAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFkAZQBzACAALQAgAGkAbgAgAGwAZQBhAGMAaABpAG4AZwAgAHoAbwBuAGUAXAAiACwAIAAxADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAE4AbwAgAC0AIABuAG8AdAAgAGkAbgAgAGwAZQBhAGMAaABpAG4AZwAgAHoAbwBuAGUAXAAiACwAIAAwAFwAbgAgACAAIAAgACAAIAAgACAAfQAsACAAcgAsACAAYwApAFwAbgAgACAAIAAgACAAIAApAFwAbgAgACAAIAAgACkAXABuACAAIAApADsAXABuAFwAbgAgACAAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgByAGEAYwBXAEUAVABfAFYAYQByAGkAYQB0AGkAbwBuAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoACgAXAAiAFwAIgApACkAOwBcAG4AXABuAFwAbgBcAG4ALwAqACAAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABhAHQAYQBTAGMAbwByAGUAcwBfAFMAYwBvAHAAZQAzAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuACoALwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEQAYQB0AGEAUwBjAG8AcgBlAHMAXwBTAGMAbwBwAGUAMwBfAFQAaQB0AGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAQQB1AHMAdAByAGEAbABpAGEAbgAgAGQAYQB0AGEAIABzAGMAbwByAGUAcwAgAGYAbwByACAAcwBjAG8AcABlACAAMwBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABhAHQAYQBTAGMAbwByAGUAcwBfAFMAYwBvAHAAZQAzAF8AVgBhAHIAaQBhAGIAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABhAHQAYQBTAGMAbwByAGUAcwBfAFMAYwBvAHAAZQAzAF8AVQBuAGkAdABcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEQAYQB0AGEAUwBjAG8AcgBlAHMAXwBTAGMAbwBwAGUAMwBfAFMAbwB1AHIAYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBWAEUARQBSAEcAIAAyADAAMgA2ADoAIABYAFgAWABYAFgAWABYAFgAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEQAYQB0AGEAUwBjAG8AcgBlAHMAXwBTAGMAbwBwAGUAMwBfAFYAYQByAGkAYQB0AGkAbwBuAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABhAHQAYQBTAGMAbwByAGUAcwBfAFMAYwBvAHAAZQAzAF8ARABhAHQAYQBcAG4AIAAgACAAPQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAE0AQQBLAEUAQQBSAFIAQQBZACgANgAsACAAMgAsACAAXABuACAAIAAgACAAIAAgAEwAQQBNAEIARABBACgAcgAsAGMALAAgAFwAbgAgACAAIAAgACAAIAAgACAASQBOAEQARQBYACgAewBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIARABhAHQAYQAgAHMAbwB1AHIAYwBlAFwAIgAsACAAXAAiAEQAYQB0AGEAIABzAGMAbwByAGUAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEkAbgB0AGUAcgBuAGEAdABpAG8AbgBhAGwAIABzAGMAbwBwAGUAIAAzACAAZABhAHQAYQBiAGEAcwBlAFwAIgAsACAAMQA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBBAHUAcwB0AHIAYQBsAGkAYQBuACAAcwBjAG8AcABlACAAMwAgAGQAYQB0AGEAYgBhAHMAZQBcACIALAAgADIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAUwB0AGEAdABlACAAbwByACAAcgBlAGcAaQBvAG4AYQBsACAAcwBjAG8AcABlACAAMwAgAGQAYQB0AGEAYgBhAHMAZQBcACIALAAgADMAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIARQBtAGkAcwBzAGkAbwBuAHMAIABpAG4AdABlAG4AcwBpAHQAeQAgAGMAYQBsAGMAdQBsAGEAdABlAGQAIABmAHIAbwBtACAAYQBwAHAAcgBvAHYAZQBkACAAbQBlAHQAaABvAGQAXAAiACwAIAA0ADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFYAZQByAGkAZgBpAGUAZAAgAGMAcgBlAGQAZQBuAHQAaQBhAGwAIABtAGEAdABjAGgAaQBuAGcAIABJAFMATwAxADQAMAA2ADcAXAAiACwAIAA1AFwAbgAgACAAIAAgACAAIAAgACAAfQAsACAAcgAsACAAYwApAFwAbgAgACAAIAAgACAAIAApAFwAbgAgACAAIAAgACkAXABuACAAIAApADsAXABuAFwAbgBcAG4ALwAqACAAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgByAGEAYwBMAEUAQQBDAEgAXABuADUALgA1AC4AMgAuADMAIABDAG8AbgBzAHQAYQBuAHQAIABQAGEAcgBhAG0AZQB0AGUAcgBzAFwAbgBGAHIAYQBjAHQAaQBvAG4AIABvAGYAIABOACAAdABoAGEAdAAgAGkAcwAgAGEAdgBhAGkAbABhAGIAbABlACAAZgBvAHIAIABsAGUAYQBjAGgAaQBuAGcAIABhAG4AZAAgAHIAdQBuAG8AZgBmAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuACoALwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAcgBhAGMATABFAEEAQwBIAF8AVABpAHQAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBGAHIAYQBjAHQAaQBvAG4AIABvAGYAIABOACAAdABoAGEAdAAgAGkAcwAgAGEAdgBhAGkAbABhAGIAbABlACAAZgBvAHIAIABsAGUAYQBjAGgAaQBuAGcAIABhAG4AZAAgAHIAdQBuAG8AZgBmAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAHIAYQBjAEwARQBBAEMASABfAFUAbgBpAHQAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiACgARABpAG0AZQBuAHMAaQBvAG4AbABlAHMAcwBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgByAGEAYwBMAEUAQQBDAEgAXwBTAG8AdQByAGMAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAVgBFAEUAUgBHACAAMgAwADIANgA6ADUALgA1AC4AMgAuADMAIABDAG8AbgBzAHQAYQBuAHQAIABQAGEAcgBhAG0AZQB0AGUAcgBzAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAHIAYQBjAEwARQBBAEMASABfAE4ASQBSAFIAZQBmAGUAcgBlAG4AYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBOAGEAdABpAG8AbgBhAGwAIABJAG4AdgBlAG4AdABvAHIAeQAgAFIAZQBwAG8AcgB0ACAAVgBvAGwAdQBtAGUAIAAxADoAIABMAGUAYQBjAGgAaQBuAGcAIABhAG4AZAAgAHIAdQBuAG8AZgBmACAAKAAzAC4ARAAuAGIALgAyACkAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAcgBhAGMATABFAEEAQwBIAF8ARABhAHQAYQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABNAEEASwBFAEEAUgBSAEEAWQAoADEALAAgADIALAAgAFwAbgAgACAAIAAgACAAIABMAEEATQBCAEQAQQAoAHIALABjACwAIABcAG4AIAAgACAAIAAgACAAIAAgAEkATgBEAEUAWAAoAHsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEYAcgBhAGMATABFAEEAQwBIAFwAIgAsADAALgAyADQAXABuACAAIAAgACAAIAAgACAAIAB9ACwAIAByACwAIABjACkAXABuACAAIAAgACAAIAAgACkAXABuACAAIAAgACAAKQBcAG4AIAAgACkAOwBcAG4AXABuACAAIABDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAHIAYQBjAEwARQBBAEMASABfAFYAYQByAGkAYQB0AGkAbwBuAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoACgAXAAiAFwAIgApACkAOwBcAG4AXABuAFwAbgBcAG4ALwAqACAAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAGwAZQBhAGMAaABcAG4ANQAuADUALgAyAC4AMwAgAEMAbwBuAHMAdABhAG4AdAAgAFAAYQByAGEAbQBlAHQAZQByAHMAXABuAEUAbQBpAHMAcwBpAG8AbgAgAGYAYQBjAHQAbwByACAAZgBvAHIAIABuAGkAdAByAG8AZwBlAG4AIABsAGUAYQBjAGgAaQBuAGcAIABhAG4AZAAgAHIAdQBuAG8AZgBmAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuACoALwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEUARgBsAGUAYQBjAGgAXwBUAGkAdABsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAEUAbQBpAHMAcwBpAG8AbgAgAGYAYQBjAHQAbwByACAAZgBvAHIAIABuAGkAdAByAG8AZwBlAG4AIABsAGUAYQBjAGgAaQBuAGcAIABhAG4AZAAgAHIAdQBuAG8AZgBmAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYAbABlAGEAYwBoAF8AVQBuAGkAdABcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAKABrAGcAIABOADIATwAtAE4AIAAvACAAawBnACAATgBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAGwAZQBhAGMAaABfAFMAbwB1AHIAYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBWAEUARQBSAEcAIAAyADAAMgA2ADoANQAuADUALgAyAC4AMwAgAEMAbwBuAHMAdABhAG4AdAAgAFAAYQByAGEAbQBlAHQAZQByAHMAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEUARgBsAGUAYQBjAGgAXwBOAEkAUgBSAGUAZgBlAHIAZQBuAGMAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIATgBhAHQAaQBvAG4AYQBsACAASQBuAHYAZQBuAHQAbwByAHkAIABSAGUAcABvAHIAdAAgAFYAbwBsAHUAbQBlACAAMQA6ACAARQBxAHUAYQB0AGkAbwBuACAAMwAuAEQALgBCAF8AMQAwAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYAbABlAGEAYwBoAF8ARABhAHQAYQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABNAEEASwBFAEEAUgBSAEEAWQAoADEALAAgADIALAAgAFwAbgAgACAAIAAgACAAIABMAEEATQBCAEQAQQAoAHIALABjACwAIABcAG4AIAAgACAAIAAgACAAIAAgAEkATgBEAEUAWAAoAHsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEUARgBsAGUAYQBjAGgAXAAiACwAMAAuADAAMQAxAFwAbgAgACAAIAAgACAAIAAgACAAfQAsACAAcgAsACAAYwApAFwAbgAgACAAIAAgACAAIAApAFwAbgAgACAAIAAgACkAXABuACAAIAApADsAXABuAFwAbgAgACAAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAGwAZQBhAGMAaABfAFYAYQByAGkAYQB0AGkAbwBuAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoACgAXAAiAFwAIgApACkAOwBcAG4AXABuAFwAbgAvACoAIABcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYATgAyAE8AXABuAFQAYQBiAGwAZQAgAEEALgAyAC4AMgAuADEAXABuAE4AaQB0AHIAbwB1AHMAIABvAHgAaQBkAGUAIABlAG0AaQBzAHMAaQBvAG4AIABmAGEAYwB0AG8AcgBzACAAZgBvAHIAIABpAG4AbwByAGcAYQBuAGkAYwAgAGYAZQByAHQAaQBsAGkAcwBlAHIAIABhAHAAcABsAGkAYwBhAHQAaQBvAG4AIAAoAGsAZwAgAE4AMgBPAC0ATgAvAGsAZwAgAE4AKQAgACgARQBGAE4AMgBPACkAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AKgAvAFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAE4AMgBPAF8AVABpAHQAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBOAGkAdAByAG8AdQBzACAAbwB4AGkAZABlACAAZQBtAGkAcwBzAGkAbwBuACAAZgBhAGMAdABvAHIAcwAgAGYAbwByACAAaQBuAG8AcgBnAGEAbgBpAGMAIABmAGUAcgB0AGkAbABpAHMAZQByACAAYQBwAHAAbABpAGMAYQB0AGkAbwBuAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYATgAyAE8AXwBVAG4AaQB0AFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgAoAGsAZwAgAE4AMgBPAC0ATgAgAC8AIABrAGcAIABOAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYATgAyAE8AXwBTAG8AdQByAGMAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAVgBFAEUAUgBHACAAMgAwADIANgA6ACAAVABhAGIAbABlACAAQQAuADIALgAyAC4AMQBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAE4AMgBPAF8ATgBJAFIAUgBlAGYAZQByAGUAbgBjAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYATgAyAE8AXwBEAGEAdABhAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAE0AQQBLAEUAQQBSAFIAQQBZACgAMQA1ACwAIAA1ACwAIABcAG4AIAAgACAAIAAgACAATABBAE0AQgBEAEEAKAByACwAYwAsACAAXABuACAAIAAgACAAIAAgACAAIABJAE4ARABFAFgAKAB7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBQAHIAbwBkAHUAYwB0AGkAbwBuACAAcwB5AHMAdABlAG0AIABqAFwAIgAsAFwAIgBFAEYATgAyAE8AXAAiACwAIABcACIAUAByAG8AZAB1AGMAdABpAG8AbgAgAHMAeQBzAHQAZQBtACAAbwBuAGwAeQBcACIALAAgAFwAIgBJAHIAcgBpAGcAYQB0AGkAbwBuACAAbQBlAHQAaABvAGQAXAAiACwAIABcACIAUgBhAGkAbgBmAGEAbABsACAAegBvAG4AZQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIASQByAHIAaQBnAGEAdABlAGQAIABwAGEAcwB0AHUAcgBlAFwAIgAsADAALgAwADAANQA5ACwAIABcACIAUABhAHMAdAB1AHIAZQBcACIALAAgAFwAIgBBAG4AeQBcACIALAAgAFwAIgBBAG4AeQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIASQByAHIAaQBnAGEAdABlAGQAIABjAHIAbwBwAFwAIgAsADAALgAwADAANwAsACAAXAAiAEMAcgBvAHAAXAAiACwAIABcACIAQQBuAHkAXAAiACwAIABcACIAQQBuAHkAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAE4AbwBuAC0AaQByAHIAaQBnAGEAdABlAGQAIABwAGEAcwB0AHUAcgBlAFwAIgAsADAALgAwADAAMQA4ACwAIABcACIAUABhAHMAdAB1AHIAZQBcACIALAAgAFwAIgBOAG8AdAAgAGkAcgByAGkAZwBhAHQAZQBkAFwAIgAsACAAXAAiAEwAbwB3ACAAcgBhAGkAbgBmAGEAbABsAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBOAG8AbgAtAGkAcgByAGkAZwBhAHQAZQBkACAAcABhAHMAdAB1AHIAZQBcACIALAAwAC4AMAAwADEAOAAsACAAXAAiAFAAYQBzAHQAdQByAGUAXAAiACwAIABcACIATgBvAHQAIABpAHIAcgBpAGcAYQB0AGUAZABcACIALAAgAFwAIgBIAGkAZwBoACAAcgBhAGkAbgBmAGEAbABsAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBOAG8AbgAtAGkAcgByAGkAZwBhAHQAZQBkACAAYwByAG8AcAAgACgAbABvAHcAIAByAGEAaQBuAGYAYQBsAGwAKQBcACIALAAwAC4AMAAwADIAOQAsACAAXAAiAEMAcgBvAHAAXAAiACwAIABcACIATgBvAHQAIABpAHIAcgBpAGcAYQB0AGUAZABcACIALAAgAFwAIgBMAG8AdwAgAHIAYQBpAG4AZgBhAGwAbABcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIATgBvAG4ALQBpAHIAcgBpAGcAYQB0AGUAZAAgAGMAcgBvAHAAIAAoAGgAaQBnAGgAIAByAGEAaQBuAGYAYQBsAGwAKQBcACIALAAwAC4AMAAwADgALAAgAFwAIgBDAHIAbwBwAFwAIgAsACAAXAAiAE4AbwB0ACAAaQByAHIAaQBnAGEAdABlAGQAXAAiACwAIABcACIASABpAGcAaAAgAHIAYQBpAG4AZgBhAGwAbABcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAUwB1AGcAYQByAFwAIgAsADAALgAwADEAOQA5ACwAIABcACIAUwB1AGcAYQByAFwAIgAsACAAXAAiAEEAbgB5AFwAIgAsACAAXAAiAEEAbgB5AFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBDAG8AdAB0AG8AbgBcACIALAAwAC4AMAAwADUAMwAsACAAXAAiAEMAbwB0AHQAbwBuAFwAIgAsACAAXAAiAEEAbgB5AFwAIgAsACAAXAAiAEEAbgB5AFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBIAG8AcgB0AGkAYwB1AGwAdAB1AHIAYQBsACAAYwByAG8AcABzAFwAIgAsADAALgAwADAANgA0ACwAIABcACIASABvAHIAdABpAGMAdQBsAHQAdQByAGEAbAAgAGMAcgBvAHAAcwBcACIALAAgAFwAIgBBAG4AeQBcACIALAAgAFwAIgBBAG4AeQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAUgBpAGMAZQAgACgAYwBvAG4AdABpAG4AdQBvAHUAcwAgAGYAbABvAG8AZABpAG4AZwApAFwAIgAsADAALgAwADAAMwAsACAAXAAiAFIAaQBjAGUAXAAiACwAIABcACIAQwBvAG4AdABpAG4AdQBvAHUAcwAgAGYAbABvAG8AZABpAG4AZwBcACIALAAgAFwAIgBBAG4AeQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAUgBpAGMAZQAgACgAcwBpAG4AZwBsAGUAIABhAG4AZAAgAG0AdQBsAHQAaQBwAGwAZQAgAGQAcgBhAGkAbgBhAGcAZQAsACAAbwByACAAYQBsAHQAZQByAG4AYQB0AGUAIAB3AGUAdAB0AGkAbgBnACAAYQBuAGQAIABkAHIAeQBpAG4AZwApAFwAIgAsADAALgAwADAANQAsACAAXAAiAFIAaQBjAGUAXAAiACwAIABcACIAUwBpAG4AZwBsAGUAIABhAG4AZAAgAG0AdQBsAHQAaQBwAGwAZQAgAGQAcgBhAGkAbgBhAGcAZQAsACAAbwByACAAYQBsAHQAZQByAG4AYQB0AGUAIAB3AGUAdAB0AGkAbgBnACAAYQBuAGQAIABkAHIAeQBpAG4AZwBcACIALAAgAFwAIgBBAG4AeQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAQQBxAHUAYQBjAHUAbAB0AHUAcgBlAFwAIgAsADAALgAwADAAMgA2ACwAIABcACIAQQBxAHUAYQBjAHUAbAB0AHUAcgBlAFwAIgAsACAAXAAiAEEAbgB5AFwAIgAsACAAXAAiAEEAbgB5AFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBGAG8AcgBlAHMAdAByAHkAXAAiACwAMAAuADAAMAAxADgALAAgAFwAIgBGAG8AcgBlAHMAdAByAHkAXAAiACwAIABcACIAQQBuAHkAXAAiACwAIABcACIAQQBuAHkAXAAiAFwAbgAgACAAIAAgACAAIAAgACAAfQAsACAAcgAsACAAYwApAFwAbgAgACAAIAAgACAAIAApAFwAbgAgACAAIAAgACkAXABuACAAIAApADsAXABuAFwAbgAgACAAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAE4AMgBPAF8AVgBhAHIAaQBhAHQAaQBvAG4AXABuACAAIAA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAATQBBAEsARQBBAFIAUgBBAFkAKAA1ACwAIAAxACwAIABcAG4AIAAgACAAIAAgACAATABBAE0AQgBEAEEAKAByACwAYwAsACAAXABuACAAIAAgACAAIAAgACAAIABJAE4ARABFAFgAKAB7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBWAEEAUgBJAEEAVABJAE8ATgAgAE8ARgAgAFMATwBVAFIAQwBFACAARABBAFQAQQA6AFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBSAGUAbQBvAHYAZQBkACAAZAB1AHAAbABpAGMAYQB0AGUAIAAnAEEAcQB1AGEAYwB1AGwAdAB1AHIAZQAnACAAcgBvAHcALgBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAUgBlAG0AbwB2AGUAZAAgAGEAcwB0AGUAcgBpAHMAawBzACAAdABvACAAYQBpAGQAIABsAG8AbwBrAHUAcAAuAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBBAGQAZABlAGQAIAAnAHAAcgBvAGQAdQBjAHQAaQBvAG4AIABzAHkAcwB0AGUAbQAgAG8AbgBsAHkAJwAsACAAJwByAGEAaQBuAGYAYQBsAGwAIAB6AG8AbgBlACcAIABhAG4AZAAgACcAaQByAHIAaQBnAGEAdABpAG8AbgAgAG0AZQB0AGgAbwBkACcAIABjAG8AbAB1AG0AbgBzACAAdABvACAAYQBpAGQAIABsAG8AbwBrAHUAcAAuAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBEAHUAcABsAGkAYwBhAHQAZQBkACAAJwBuAG8AbgAtAGkAcgByAGkAZwBhAHQAZQBkACAAcABhAHMAdAB1AHIAZQAnACAAcgBvAHcAIAB3AGkAdABoACAAcwBhAG0AZQAgAEUARgAgAGYAbwByACAAbABvAHcAIABhAG4AZAAgAGgAaQBnAGgAIAByAGEAaQBuAGYAYQBsAGwAIAB6AG8AbgBlAHMAIAB0AG8AIABhAGkAZAAgAGwAbwBvAGsAdQBwAC4AXAAiAFwAbgAgACAAIAAgACAAIAAgACAAfQAsACAAcgAsACAAYwApAFwAbgAgACAAIAAgACAAIAApAFwAbgAgACAAIAAgACkAXABuACAAIAApADsAXABuAFwAbgAvACoAIABcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAHIAYQBjAFcARQBUAEkAcgByAGkAZwBhAHQAaQBvAG4AXABuAFYARQBFAFIARwAgADIAMAAyADYAOgAgAEMAaABhAHAAdABlAHIAIAAxACwAIABzAGUAYwB0AGkAbwBuACAAMQAuADgALgAyACAATABlAGEAYwBoAGkAbgBnACwAIABjAGwAaQBtAGEAdABlACAAYQBuAGQAIAByAGEAaQBuAGYAYQBsAGwAIAB6AG8AbgBlAHMAXABuAEkAUABDAEMAOgAgAE4AMgBPACAARQBNAEkAUwBTAEkATwBOAFMAIABGAFIATwBNACAATQBBAE4AQQBHAEUARAAgAFMATwBJAEwAUwAsACAAQQBOAEQAIABDAE8AMgAgAEUATQBJAFMAUwBJAE8ATgBTACAARgBSAE8ATQAgAEwASQBNAEUAIABBAE4ARAAgAFUAUgBFAEEAIABBAFAAUABMAEkAQwBBAFQASQBPAE4AXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AKgAvAFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgByAGEAYwBXAEUAVABJAHIAcgBpAGcAYQB0AGkAbwBuAF8AVABpAHQAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBGAHIAYQBjAFcARQBUACAAZgBvAHIAIABpAHIAcgBpAGcAYQB0AGkAbwBuACAAdAB5AHAAZQBzAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAHIAYQBjAFcARQBUAEkAcgByAGkAZwBhAHQAaQBvAG4AXwBVAG4AaQB0AFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBkAGkAbQBlAG4AcwBpAG8AbgBsAGUAcwBzAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAHIAYQBjAFcARQBUAEkAcgByAGkAZwBhAHQAaQBvAG4AXwBTAG8AdQByAGMAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAVgBFAEUAUgBHACAAMgAwADIANgA6ACAAQwBoAGEAcAB0AGUAcgAgADEALAAgAHMAZQBjAHQAaQBvAG4AIAAxAC4AOAAuADIAIABMAGUAYQBjAGgAaQBuAGcALAAgAGMAbABpAG0AYQB0AGUAIABhAG4AZAAgAHIAYQBpAG4AZgBhAGwAbAAgAHoAbwBuAGUAcwBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgByAGEAYwBXAEUAVABJAHIAcgBpAGcAYQB0AGkAbwBuAF8ATgBJAFIAUgBlAGYAZQByAGUAbgBjAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAEkAUABDAEMAIAAyADAAMQA5ACAAUgBlAGYAaQBuAGUAbQBlAG4AdAAgAFYAbwBsAHUAbQBlACAANAA6ACAAQwBoAGEAcAB0AGUAcgAgADEAMQA6ACAATgAyAE8AIABFAG0AaQBzAHMAaQBvAG4AcwAgAGYAcgBvAG0AIABNAGEAbgBhAGcAZQBkACAAUwBvAGkAbABzACwAIABhAG4AZAAgAEMATwAyACAARQBtAGkAcwBzAGkAbwBuAHMAIABmAHIAbwBtACAATABpAG0AZQAgAGEAbgBkACAAVQByAGUAYQAgAEEAcABwAGwAaQBjAGEAdABpAG8AbgBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgByAGEAYwBXAEUAVABJAHIAcgBpAGcAYQB0AGkAbwBuAF8ARABhAHQAYQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABNAEEASwBFAEEAUgBSAEEAWQAoADYALAAgADIALAAgAFwAbgAgACAAIAAgACAAIABMAEEATQBCAEQAQQAoAHIALABjACwAIABcAG4AIAAgACAAIAAgACAAIAAgAEkATgBEAEUAWAAoAHsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEkAcgByAGkAZwBhAHQAaQBvAG4AIAB0AHkAcABlACAAaQByAFwAIgAsAFwAIgBGAHIAYQBjAFcARQBUAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBOAG8AdAAgAGkAcgByAGkAZwBhAHQAZQBkAFwAIgAsACAAMAA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBEAHIAaQBwACAAaQByAHIAaQBnAGEAdABpAG8AbgBcACIALAAgADAAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAUwBwAHIAaQBuAGsAbABlAHIAIABpAHIAcgBpAGcAYQB0AGkAbwBuAFwAIgAsACAAMQA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBTAHUAcgBmAGEAYwBlACAAaQByAHIAaQBnAGEAdABpAG8AbgBcACIALAAgADEAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIATwB0AGgAZQByACAAaQByAHIAaQBnAGEAdABpAG8AbgBcACIALAAgADEAXABuACAAIAAgACAAIAAgACAAIAB9ACwAIAByACwAIABjACkAXABuACAAIAAgACAAIAAgACkAXABuACAAIAAgACAAKQBcAG4AIAAgACkAOwBcAG4AXABuACAAIABDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAHIAYQBjAFcARQBUAEkAcgByAGkAZwBhAHQAaQBvAG4AXwBWAGEAcgBpAGEAdABpAG8AbgBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAVgBBAFIASQBBAFQASQBPAE4AIABGAFIATwBNACAAUwBPAFUAUgBDAEUAIABEAEEAVABBADoAIABUAGEAYgBsAGUAIABjAHIAZQBhAHQAZQBkACAAYgBhAHMAZQBkACAAbwBuACAAVgBFAEUAUgBHACAAdABlAHgAdAAgACcAQQByAGUAYQBzACAAYQByAGUAIABzAHUAYgBqAGUAYwB0ACAAdABvACAAbABlAGEAYwBoAGkAbgBnACAAKABpAC4AZQAuACwAIABpAG4AIAB0AGgAZQAgAGwAZQBhAGMAaABpAG4AZwAgAHoAbwBuAGUAKQAgAHcAaABlAG4ALgAuAC4AIAB0AGgAZQAgAGwAYQBuAGQAIABpAHMAIABpAHIAcgBpAGcAYQB0AGUAZAAgACgAZQB4AGMAZQBwAHQAIABkAHIAaQBwACAAaQByAHIAaQBnAGEAdABpAG8AbgApAC4AJwBcACIAKQA7AFwAbgBcAG4AXABuAC8AKgAgAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEUARgBQAGEAcwB0AHUAcgBlAFIAYQBuAGcAZQBBAG4AZABQAGEAZABkAG8AYwBrAFwAbgBUAGEAYgBsAGUAIABBAC4AMgAuADIALgAyADoAIABFAG0AaQBzAHMAaQBvAG4AIABmAGEAYwB0AG8AcgAgAGYAbwByACAAdQByAGkAbgBlACAAYQBuAGQAIABkAHUAbgBnACAAZABlAHAAbwBzAGkAdABlAGQAIABvAG4AIABwAGEAcwB0AHUAcgBlACwAIAByAGEAbgBnAGUAIABvAHIAIABwAGEAZABkAG8AYwBrACAAKABrAGcAIABOADIATwAtAE4ALwBrAGcAIABOACkAIAAoAEUARgBQAFIAUAApAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuACoALwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEUARgBQAGEAcwB0AHUAcgBlAFIAYQBuAGcAZQBBAG4AZABQAGEAZABkAG8AYwBrAF8AVABpAHQAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBFAG0AaQBzAHMAaQBvAG4AIABmAGEAYwB0AG8AcgAgAGYAbwByACAAdQByAGkAbgBlACAAYQBuAGQAIABkAHUAbgBnACAAZABlAHAAbwBzAGkAdABlAGQAIABvAG4AIABwAGEAcwB0AHUAcgBlACwAIAByAGEAbgBnAGUAIABvAHIAIABwAGEAZABkAG8AYwBrAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYAUABhAHMAdAB1AHIAZQBSAGEAbgBnAGUAQQBuAGQAUABhAGQAZABvAGMAawBfAFUAbgBpAHQAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAGsAZwAgAE4AMgBPACAALQAgAE4AIAAvACAAawBnACAATgBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAFAAYQBzAHQAdQByAGUAUgBhAG4AZwBlAEEAbgBkAFAAYQBkAGQAbwBjAGsAXwBTAG8AdQByAGMAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAVgBFAEUAUgBHACAAMgAwADIANgA6ACAAVABhAGIAbABlACAAQQAuADIALgAyAC4AMgBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAFAAYQBzAHQAdQByAGUAUgBhAG4AZwBlAEEAbgBkAFAAYQBkAGQAbwBjAGsAXwBOAEkAUgBSAGUAZgBlAHIAZQBuAGMAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEUARgBQAGEAcwB0AHUAcgBlAFIAYQBuAGcAZQBBAG4AZABQAGEAZABkAG8AYwBrAF8ARABhAHQAYQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABNAEEASwBFAEEAUgBSAEEAWQAoADMALAAgADIALAAgAFwAbgAgACAAIAAgACAAIABMAEEATQBCAEQAQQAoAHIALABjACwAIABcAG4AIAAgACAAIAAgACAAIAAgAEkATgBEAEUAWAAoAHsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEMAbABpAG0AYQB0AGUAIAB6AG8AbgBlAFwAIgAsACAAXAAiAEUARgBQAFIAUABcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVwBlAHQAIABjAGwAaQBtAGEAdABlACAAegBvAG4AZQBcACIALAAgADAALgAwADAANgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBEAHIAeQAgAGMAbABpAG0AYQB0AGUAIAB6AG8AbgBlAFwAIgAsACAAMAAuADAAMAAyAFwAbgAgACAAIAAgACAAIAAgACAAfQAsACAAcgAsACAAYwApAFwAbgAgACAAIAAgACAAIAApAFwAbgAgACAAIAAgACkAXABuACAAIAApADsAXABuAFwAbgAgACAAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAFAAYQBzAHQAdQByAGUAUgBhAG4AZwBlAEEAbgBkAFAAYQBkAGQAbwBjAGsAXwBWAGEAcgBpAGEAdABpAG8AbgBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAVgBBAFIASQBBAFQASQBPAE4AIABGAFIATwBNACAAUwBPAFUAUgBDAEUAIABEAEEAVABBADoAIABDAGgAYQBuAGcAZQBkACAAJwBEAHIAeQAgAGMAbABpAG0AYQB0AGUAIAB6AG8AbgBlAHMAJwAgAHQAbwAgAHMAaQBuAGcAdQBsAGEAcgAgACcARAByAHkAIABjAGwAaQBtAGEAdABlACAAegBvAG4AZQAnACAAdABvACAAYQBpAGQAIABsAG8AbwBrAHUAcAAuAFwAIgApADsAXABuAFwAbgBcAG4ALwAqACAAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ATQBvAG4AdABoAHMAVABvAFMAZQBhAHMAbwBuAHMAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AKgAvAFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ATQBvAG4AdABoAHMAVABvAFMAZQBhAHMAbwBuAHMAXwBUAGkAdABsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAE0AbwBuAHQAaABzACAAdABvACAAUwBlAGEAcwBvAG4AcwAgAE0AYQBwAHAAaQBuAGcAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAE0AbwBuAHQAaABzAFQAbwBTAGUAYQBzAG8AbgBzAF8AVQBuAGkAdABcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAE0AbwBuAHQAaABzAFQAbwBTAGUAYQBzAG8AbgBzAF8AUwBvAHUAcgBjAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBNAG8AbgB0AGgAcwBUAG8AUwBlAGEAcwBvAG4AcwBfAE4ASQBSAFIAZQBmAGUAcgBlAG4AYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ATQBvAG4AdABoAHMAVABvAFMAZQBhAHMAbwBuAHMAXwBEAGEAdABhAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAE0AQQBLAEUAQQBSAFIAQQBZACgAMQAzACwAIAAyACwAIABcAG4AIAAgACAAIAAgACAATABBAE0AQgBEAEEAKAByACwAYwAsACAAXABuACAAIAAgACAAIAAgACAAIABJAE4ARABFAFgAKAB7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBNAG8AbgB0AGgAXAAiACwAIABcACIAUwBlAGEAcwBvAG4AXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEoAYQBuAHUAYQByAHkAXAAiACwAIABcACIAUwB1AG0AbQBlAHIAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEYAZQBiAHIAdQBhAHIAeQBcACIALAAgAFwAIgBTAHUAbQBtAGUAcgBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIATQBhAHIAYwBoAFwAIgAsACAAXAAiAEEAdQB0AHUAbQBuAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBBAHAAcgBpAGwAXAAiACwAIABcACIAQQB1AHQAdQBtAG4AXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAE0AYQB5AFwAIgAsACAAXAAiAEEAdQB0AHUAbQBuAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBKAHUAbgBlAFwAIgAsACAAXAAiAFcAaQBuAHQAZQByAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBKAHUAbAB5AFwAIgAsACAAXAAiAFcAaQBuAHQAZQByAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBBAHUAZwB1AHMAdABcACIALAAgAFwAIgBXAGkAbgB0AGUAcgBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAUwBlAHAAdABlAG0AYgBlAHIAXAAiACwAIABcACIAUwBwAHIAaQBuAGcAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAE8AYwB0AG8AYgBlAHIAXAAiACwAIABcACIAUwBwAHIAaQBuAGcAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAE4AbwB2AGUAbQBiAGUAcgBcACIALAAgAFwAIgBTAHAAcgBpAG4AZwBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIARABlAGMAZQBtAGIAZQByAFwAIgAsACAAXAAiAFMAdQBtAG0AZQByAFwAIgBcAG4AIAAgACAAIAAgACAAIAAgAH0ALAAgAHIALAAgAGMAKQBcAG4AIAAgACAAIAAgACAAKQBcAG4AIAAgACAAIAApAFwAbgAgACAAKQA7AFwAbgBcAG4AIAAgAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAE0AbwBuAHQAaABzAFQAbwBTAGUAYQBzAG8AbgBzAF8AVgBhAHIAaQBhAHQAaQBvAG4AXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFwAIgApADsAXABuAFwAbgBcAG4AXABuAC8AKgAgAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAE0AQwBGAFQAZQBtAHAAZQByAGEAdAB1AHIAZQBaAG8AbgBlAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuACoALwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAE0AQwBGAFQAZQBtAHAAZQByAGEAdAB1AHIAZQBaAG8AbgBlAF8AVABpAHQAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBNAGEAbgB1AHIAZQAgAE0AYQBuAGEAZwBlAG0AZQBuAHQAIAATICAATQBlAHQAaABhAG4AZQAgAGMAbwBuAHYAZQByAHMAaQBvAG4AIABmAGEAYwB0AG8AcgAgAHAAZQByACAAdABlAG0AcABlAHIAYQB0AHUAcgBlACAAegBvAG4AZQAgACgAZgByAGEAYwB0AGkAbwBuACkAIAAoAE0AQwBGAGkAbQApAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBNAEMARgBUAGUAbQBwAGUAcgBhAHQAdQByAGUAWgBvAG4AZQBfAFUAbgBpAHQAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAGYAcgBhAGMAdABpAG8AbgBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ATQBDAEYAVABlAG0AcABlAHIAYQB0AHUAcgBlAFoAbwBuAGUAXwBTAG8AdQByAGMAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAVgBFAEUAUgBHACAAMgAwADIANgA6ACAAVABhAGIAbABlACAAQQAuADEALgA4AC4AMQBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ATQBDAEYAVABlAG0AcABlAHIAYQB0AHUAcgBlAFoAbwBuAGUAXwBEAGEAdABhAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAE0AQQBLAEUAQQBSAFIAQQBZACgAMgAyACwAIAAxADYALAAgAFwAbgAgACAAIAAgACAAIABMAEEATQBCAEQAQQAoAHIALABjACwAIABcAG4AIAAgACAAIAAgACAAIAAgAEkATgBEAEUAWAAoAHsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFQAZQBtAHAAZQByAGEAdAB1AHIAZQAgAHoAbwBuAGUAXAAiACwAIABcACIATQBBAFQAIAAoALoAQwApAFwAIgAsACAAXAAiAFUAbgBjAG8AdgBlAHIAZQBkACAAYQBuAGUAcgBvAGIAaQBjACAAbABhAGcAbwBvAG4AXAAiACwAIABcACIAQwBvAHYAZQByAGUAZAAgAGwAYQBnAG8AbwBuAFwAIgAsACAAXAAiAEwAaQBxAHUAaQBkACAAUwBsAHUAcgByAHkAIAAoAHcAaQB0AGgAbwB1AHQAIABuAGEAdAB1AHIAYQBsACAAYwByAHUAcwB0ACkAXAAiACwAIABcACIARABhAGkAbAB5ACAAcwBwAHIAZQBhAGQAIAAoAGIAKQBcACIALAAgAFwAIgBDAG8AbQBwAG8AcwB0AGkAbgBnACAAKABwAGEAcwBzAGkAdgBlACAAdwBpAG4AZAByAG8AdwApAFwAIgAsACAAXAAiAFMAbwBsAGkAZAAgAFMAdABvAHIAYQBnAGUAXAAiACwAIABcACIAUABpAHQAIABTAHQAbwByAGEAZwBlACAAPAAxACAAbQBvAG4AdABoAFwAIgAsACAAXAAiAEQAZQBlAHAAIABMAGkAdAB0AGUAcgBcACIALAAgAFwAIgBQAG8AdQBsAHQAcgB5ACAATQBhAG4AdQByAGUAIAAoAHcAaQB0AGgALwB3AGkAdABoAG8AdQB0ACAAbABpAHQAdABlAHIAKQBcACIALAAgAFwAIgBcACIALAAgAFwAIgBEAGkAcgBlAGMAdAAgAHAAcgBvAGMAZQBzAHMAaQBuAGcAIABpAG4AdABvACAAcABlAGwAbABlAHQAaQB6AGUAZAAgAGYAZQByAHQAaQBsAGkAcwBlAHIAXAAiACwAIABcACIARABpAHIAZQBjAHQAIABhAHAAcABsAGkAYwBhAHQAaQBvAG4AIAB0AG8AIABzAG8AaQBsAFwAIgAsACAAXAAiAFAAYQBzAHQAdQByAGUALAAgAFIAYQBuAGcAZQAgAGEAbgBkACAAUABhAGQAZABvAGMAawAgACgAYwApACgAZAApAFwAIgAsACAAXAAiAE0AQQBUACAAcgBhAHcAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEMAbwBvAGwAXAAiACwAIABcACIAZCIxADAAXAAiACwAIAAwAC4ANgA2ACwAIAAwAC4AMQAsACAAMAAuADEALAAgADAALgAwADAAMQAsACAAMAAuADAAMAA1ACwAIAAwAC4AMAAyACwAIAAwAC4AMAAzACwAIAAwAC4AMAA0ACwAIAAwAC4AMAAxADUALAAgADAALgAwADEANQAsACAAMAAsACAAMAAsACAAMAAuADAAMAA0ADcALAAgADEAMAA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBDAG8AbwBsAFwAIgAsACAAMQAxACwAIAAwAC4ANgA4ACwAIAAwAC4AMQAsACAAMAAuADEAMQAsACAAMAAuADAAMAAxACwAIAAwAC4AMAAwADUALAAgADAALgAwADIALAAgADAALgAwADMALAAgADAALgAwADQALAAgADAALgAwADEANQAsACAAMAAuADAAMQA1ACwAIAAwACwAIAAwACwAIAAwAC4AMAAwADQANwAsACAAMQAxADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEMAbwBvAGwAXAAiACwAIAAxADIALAAgADAALgA3ACwAIAAwAC4AMQAsACAAMAAuADEAMwAsACAAMAAuADAAMAAxACwAIAAwAC4AMAAwADUALAAgADAALgAwADIALAAgADAALgAwADMALAAgADAALgAwADQALAAgADAALgAwADEANQAsACAAMAAuADAAMQA1ACwAIAAwACwAIAAwACwAIAAwAC4AMAAwADQANwAsACAAMQAyADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEMAbwBvAGwAXAAiACwAIAAxADMALAAgADAALgA3ADEALAAgADAALgAxACwAIAAwAC4AMQA0ACwAIAAwAC4AMAAwADEALAAgADAALgAwADAANQAsACAAMAAuADAAMgAsACAAMAAuADAAMwAsACAAMAAuADAANAAsACAAMAAuADAAMQA1ACwAIAAwAC4AMAAxADUALAAgADAALAAgADAALAAgADAALgAwADAANAA3ACwAIAAxADMAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAQwBvAG8AbABcACIALAAgADEANAAsACAAMAAuADcAMwAsACAAMAAuADEALAAgADAALgAxADUALAAgADAALgAwADAAMQAsACAAMAAuADAAMAA1ACwAIAAwAC4AMAAyACwAIAAwAC4AMAAzACwAIAAwAC4AMAA0ACwAIAAwAC4AMAAxADUALAAgADAALgAwADEANQAsACAAMAAsACAAMAAsACAAMAAuADAAMAA0ADcALAAgADEANAA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBUAGUAbQBwAGUAcgBhAHQAZQBcACIALAAgADEANQAsACAAMAAuADcANAAsACAAMAAuADEALAAgADAALgAxADcALAAgADAALgAwADAANQAsACAAMAAuADAAMQAsACAAMAAuADAAMgAsACAAMAAuADAAMwAsACAAMAAuADAANAAsACAAMAAuADAAMQA1ACwAIAAwAC4AMAAxADUALAAgADAALAAgADAALAAgADAALgAwADAANAA3ACwAIAAxADUAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVABlAG0AcABlAHIAYQB0AGUAXAAiACwAIAAxADYALAAgADAALgA3ADUALAAgADAALgAxACwAIAAwAC4AMQA4ACwAIAAwAC4AMAAwADUALAAgADAALgAwADEALAAgADAALgAwADIALAAgADAALgAwADMALAAgADAALgAwADQALAAgADAALgAwADEANQAsACAAMAAuADAAMQA1ACwAIAAwACwAIAAwACwAIAAwAC4AMAAwADQANwAsACAAMQA2ADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFQAZQBtAHAAZQByAGEAdABlAFwAIgAsACAAMQA3ACwAIAAwAC4ANwA2ACwAIAAwAC4AMQAsACAAMAAuADIALAAgADAALgAwADAANQAsACAAMAAuADAAMQAsACAAMAAuADAAMgAsACAAMAAuADAAMwAsACAAMAAuADAANAAsACAAMAAuADAAMQA1ACwAIAAwAC4AMAAxADUALAAgADAALAAgADAALAAgADAALgAwADAANAA3ACwAIAAxADcAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVABlAG0AcABlAHIAYQB0AGUAXAAiACwAIAAxADgALAAgADAALgA3ADcALAAgADAALgAxACwAIAAwAC4AMgAyACwAIAAwAC4AMAAwADUALAAgADAALgAwADEALAAgADAALgAwADIALAAgADAALgAwADMALAAgADAALgAwADQALAAgADAALgAwADEANQAsACAAMAAuADAAMQA1ACwAIAAwACwAIAAwACwAIAAwAC4AMAAwADQANwAsACAAMQA4ADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFQAZQBtAHAAZQByAGEAdABlAFwAIgAsACAAMQA5ACwAIAAwAC4ANwA3ACwAIAAwAC4AMQAsACAAMAAuADIANAAsACAAMAAuADAAMAA1ACwAIAAwAC4AMAAxACwAIAAwAC4AMAAyACwAIAAwAC4AMAAzACwAIAAwAC4AMAA0ACwAIAAwAC4AMAAxADUALAAgADAALgAwADEANQAsACAAMAAsACAAMAAsACAAMAAuADAAMAA0ADcALAAgADEAOQA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBUAGUAbQBwAGUAcgBhAHQAZQBcACIALAAgADIAMAAsACAAMAAuADcAOAAsACAAMAAuADEALAAgADAALgAyADYALAAgADAALgAwADAANQAsACAAMAAuADAAMQAsACAAMAAuADAAMgAsACAAMAAuADAAMwAsACAAMAAuADAANAAsACAAMAAuADAAMQA1ACwAIAAwAC4AMAAxADUALAAgADAALAAgADAALAAgADAALgAwADAANAA3ACwAIAAyADAAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVABlAG0AcABlAHIAYQB0AGUAXAAiACwAIAAyADEALAAgADAALgA3ADgALAAgADAALgAxACwAIAAwAC4AMgA5ACwAIAAwAC4AMAAwADUALAAgADAALgAwADEALAAgADAALgAwADIALAAgADAALgAwADMALAAgADAALgAwADQALAAgADAALgAwADEANQAsACAAMAAuADAAMQA1ACwAIAAwACwAIAAwACwAIAAwAC4AMAAwADQANwAsACAAMgAxADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFQAZQBtAHAAZQByAGEAdABlAFwAIgAsACAAMgAyACwAIAAwAC4ANwA4ACwAIAAwAC4AMQAsACAAMAAuADMAMQAsACAAMAAuADAAMAA1ACwAIAAwAC4AMAAxACwAIAAwAC4AMAAyACwAIAAwAC4AMAAzACwAIAAwAC4AMAA0ACwAIAAwAC4AMAAxADUALAAgADAALgAwADEANQAsACAAMAAsACAAMAAsACAAMAAuADAAMAA0ADcALAAgADIAMgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBUAGUAbQBwAGUAcgBhAHQAZQBcACIALAAgADIAMwAsACAAMAAuADcAOQAsACAAMAAuADEALAAgADAALgAzADQALAAgADAALgAwADAANQAsACAAMAAuADAAMQAsACAAMAAuADAAMgAsACAAMAAuADAAMwAsACAAMAAuADAANAAsACAAMAAuADAAMQA1ACwAIAAwAC4AMAAxADUALAAgADAALAAgADAALAAgADAALgAwADAANAA3ACwAIAAyADMAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVABlAG0AcABlAHIAYQB0AGUAXAAiACwAIAAyADQALAAgADAALgA3ADkALAAgADAALgAxACwAIAAwAC4AMwA3ACwAIAAwAC4AMAAwADUALAAgADAALgAwADEALAAgADAALgAwADIALAAgADAALgAwADMALAAgADAALgAwADQALAAgADAALgAwADEANQAsACAAMAAuADAAMQA1ACwAIAAwACwAIAAwACwAIAAwAC4AMAAwADQANwAsACAAMgA0ADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFQAZQBtAHAAZQByAGEAdABlAFwAIgAsACAAMgA1ACwAIAAwAC4ANwA5ACwAIAAwAC4AMQAsACAAMAAuADQAMQAsACAAMAAuADAAMAA1ACwAIAAwAC4AMAAxACwAIAAwAC4AMAAyACwAIAAwAC4AMAAzACwAIAAwAC4AMAA0ACwAIAAwAC4AMAAxADUALAAgADAALgAwADEANQAsACAAMAAsACAAMAAsACAAMAAuADAAMAA0ADcALAAgADIANQA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBXAGEAcgBtAFwAIgAsACAAMgA2ACwAIAAwAC4ANwA5ACwAIAAwAC4AMQAsACAAMAAuADQANAAsACAAMAAuADAAMQAsACAAMAAuADAAMQA1ACwAIAAwAC4AMAAyACwAIAAwAC4AMAAzACwAIAAwAC4AMAA0ACwAIAAwAC4AMAAxADUALAAgADAALgAwADEANQAsACAAMAAsACAAMAAsACAAMAAuADAAMAA0ADcALAAgADIANgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBXAGEAcgBtAFwAIgAsACAAMgA3ACwAIAAwAC4AOAAsACAAMAAuADEALAAgADAALgA0ADgALAAgADAALgAwADEALAAgADAALgAwADEANQAsACAAMAAuADAAMgAsACAAMAAuADAAMwAsACAAMAAuADAANAAsACAAMAAuADAAMQA1ACwAIAAwAC4AMAAxADUALAAgADAALAAgADAALAAgADAALgAwADAANAA3ACwAIAAyADcAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVwBhAHIAbQBcACIALAAgAFwAIgBlIjIAOABcACIALAAgADAALgA4ACwAIAAwAC4AMQAsACAAMAAuADUALAAgADAALgAwADEALAAgADAALgAwADEANQAsACAAMAAuADAAMgAsACAAMAAuADAAMwAsACAAMAAuADAANAAsACAAMAAuADAAMQA1ACwAIAAwAC4AMAAxADUALAAgADAALAAgADAALAAgADAALgAwADAANAA3ACwAIAAyADgAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAXAAiACwAIABcACIAXAAiACwAIABcACIAQQBuAGEAZQByAG8AYgBpAGMAIABsAGEAZwBvAG8AbgBcACIALAAgAFwAIgBEAGkAZwBlAHMAdABlAHIAIAAvACAAYwBvAHYAZQByAGUAZAAgAGwAYQBnAG8AbwBuAHMAXAAiACwAIABcACIATABpAHEAdQBpAGQAIABzAHkAcwB0AGUAbQBzAFwAIgAsACAAXAAiAEQAYQBpAGwAeQAgAHMAcAByAGUAYQBkAFwAIgAsACAAXAAiAEMAbwBtAHAAbwBzAHQAaQBuAGcAIAAoAHAAYQBzAHMAaQB2AGUAIAB3AGkAbgBkAHIAbwB3ACkAXAAiACwAIABcACIAUwBvAGwAaQBkACAAcwB0AG8AcgBhAGcAZQBcACIALAAgAFwAIgBQAGkAdAAgAHMAdABvAHIAYQBnAGUAXAAiACwAIABcACIARABlAGUAcAAgAGwAaQB0AHQAZQByAFwAIgAsACAAXAAiAFAAbwB1AGwAdAByAHkAIABtAGEAbgB1AHIAZQAgAHcAaQB0AGgAIABiAGUAZABkAGkAbgBnAFwAIgAsACAAXAAiAFAAbwB1AGwAdAByAHkAIABtAGEAbgB1AHIAZQAgAHcAaQB0AGgAbwB1AHQAIABiAGUAZABkAGkAbgBnAFwAIgAsACAAXAAiAEQAaQByAGUAYwB0ACAAcAByAG8AYwBlAHMAcwBpAG4AZwBcACIALAAgAFwAIgBEAGkAcgBlAGMAdAAgAGEAcABwAGwAaQBjAGEAdABpAG8AbgBcACIALAAgAFwAIgBQAGEAcwB0AHUAcgBlACAAcgBhAG4AZwBlACAAYQBuAGQAIABwAGEAZABkAG8AYwBrAFwAIgAsACAAXAAiAE0AQQBUACAAcgBhAHcAXAAiACAAXABuACAAIAAgACAAIAAgACAAIAB9ACwAIAByACwAIABjACkAXABuACAAIAAgACAAIAAgACkAXABuACAAIAAgACAAKQBcAG4AIAAgACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAE0AQwBGAFQAZQBtAHAAZQByAGEAdAB1AHIAZQBaAG8AbgBlAF8AVgBhAHIAaQBhAHQAaQBvAG4AXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFYAQQBSAEkAQQBUAEkATwBOACAARgBSAE8ATQAgAFMATwBVAFIAQwBFADoAIABBAGQAZABlAGQAIAByAG8AdwAgAG8AZgAgAE4ASQBSACAATQBNAEEAIABkAGUAZgBpAG4AaQB0AGkAbwBuAHMAIAB0AG8AIABhAGkAZAAgAGwAbwBvAGsAdQBwAC4AIABEAHUAcABsAGkAYwBhAHQAZQBkACAAJwBQAG8AdQBsAHQAcgB5ACAAdwBpAHQAaAAgAGEAbgBkACAAdwBpAHQAaABvAHUAdAAgAGwAaQB0AHQAZQByACcAIABjAG8AbAB1AG0AbgAgAHcAaQB0AGgAIABzAGUAcABhAHIAYQB0AGUAIABOAEkAUgAgAGQAZQBmAGkAbgBpAHQAaQBvAG4AcwAgAHQAbwAgAGEAaQBkACAAbABvAG8AawB1AHAALgAgAEEAZABkAGUAZAAgACcATQBBAFQAIAByAGEAdwAnACAAYwBvAGwAdQBtAG4AIAB0AG8AIABhAGwAbABvAHcAIABsAG8AbwBrAHUAcAAgAG8AZgAgAG4AdQBtAGIAZQByAHMALgBcACIAKQA7AFwAbgBcAG4AXABuAFwAbgAvACoAIABcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYATwByAGcAYQBuAGkAYwBGAGUAcgB0AGkAbABpAHMAZQByAEEAbgBkAEMAcgBvAHAAUgBlAHMAaQBkAHUAZQBzAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuACoALwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEUARgBPAHIAZwBhAG4AaQBjAEYAZQByAHQAaQBsAGkAcwBlAHIAQQBuAGQAQwByAG8AcABSAGUAcwBpAGQAdQBlAHMAXwBUAGkAdABsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAEUAbQBpAHMAcwBpAG8AbgAgAGYAYQBjAHQAbwByACAAZgBvAHIAIABvAHIAZwBhAG4AaQBjACAAZgBlAHIAdABpAGwAaQBzAGUAcgAgAGEAbgBkACAAYwByAG8AcAAgAHIAZQBzAGkAZAB1AGUAcwAgAHIAZQB0AHUAcgBuAGUAZAAgAHQAbwAgAHQAaABlACAAcwBvAGkAbABcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAE8AcgBnAGEAbgBpAGMARgBlAHIAdABpAGwAaQBzAGUAcgBBAG4AZABDAHIAbwBwAFIAZQBzAGkAZAB1AGUAcwBfAFYAYQByAGkAYQBiAGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIARQBGAE4AaQAgACYAIABFAEYATgAyAE8AaQBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAE8AcgBnAGEAbgBpAGMARgBlAHIAdABpAGwAaQBzAGUAcgBBAG4AZABDAHIAbwBwAFIAZQBzAGkAZAB1AGUAcwBfAFUAbgBpAHQAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAGsAZwAgAE4AMgBPACAALQAgAE4AIAAvACAAawBnACAATgBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAE8AcgBnAGEAbgBpAGMARgBlAHIAdABpAGwAaQBzAGUAcgBBAG4AZABDAHIAbwBwAFIAZQBzAGkAZAB1AGUAcwBfAFMAbwB1AHIAYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBWAEUARQBSAEcAIAAyADAAMgA2ADoAIABUAGEAYgBsAGUAIABBAC4AMgAuADEALgA0AFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYATwByAGcAYQBuAGkAYwBGAGUAcgB0AGkAbABpAHMAZQByAEEAbgBkAEMAcgBvAHAAUgBlAHMAaQBkAHUAZQBzAF8ATgBJAFIAUgBlAGYAZQByAGUAbgBjAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYATwByAGcAYQBuAGkAYwBGAGUAcgB0AGkAbABpAHMAZQByAEEAbgBkAEMAcgBvAHAAUgBlAHMAaQBkAHUAZQBzAF8ARABhAHQAYQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABNAEEASwBFAEEAUgBSAEEAWQAoADMALAAgADIALAAgAFwAbgAgACAAIAAgACAAIABMAEEATQBCAEQAQQAoAHIALABjACwAIABcAG4AIAAgACAAIAAgACAAIAAgAEkATgBEAEUAWAAoAHsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEMAbABpAG0AYQB0AGUAIAB6AG8AbgBlAFwAIgAsACAAXAAiAEUARgBOAGkAIAAmACAARQBGAE4AMgBPAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBXAGUAdAAgAGMAbABpAG0AYQB0AGUAIAB6AG8AbgBlAFwAIgAsACAAMAAuADAAMAA2ADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEQAcgB5ACAAYwBsAGkAbQBhAHQAZQAgAHoAbwBuAGUAXAAiACwAIAAwAC4AMAAwADUAXABuACAAIAAgACAAIAAgACAAIAB9ACwAIAByACwAIABjACkAXABuACAAIAAgACAAIAAgACkAXABuACAAIAAgACAAKQBcAG4AIAAgACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEUARgBPAHIAZwBhAG4AaQBjAEYAZQByAHQAaQBsAGkAcwBlAHIAQQBuAGQAQwByAG8AcABSAGUAcwBpAGQAdQBlAHMAXwBWAGEAcgBpAGEAdABpAG8AbgBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAXAAiACkAOwBcAG4AXABuAFwAbgBcAG4AXABuAFwAbgBcAG4AXABuAFwAbgBcAG4AXABuAFwAbgBcAG4AXABuAFwAbgBcAG4AXABuACIAfQBdACwAIgBwAHIAbwBqAGUAYwB0AE4AYQBtAGUAcwAiADoAWwAiAEMAbwBtAG0AbwBuAF8ARQBxAHUAYQB0AGkAbwBuAHMALgBDAG8AbQBtAG8AbgBfAEMAbwBuAHYAZQByAHQATgAyAE8AVABvAEMATwAyAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBFAHEAdQBhAHQAaQBvAG4AcwAuAEMAbwBtAG0AbwBuAF8AQwBvAG4AdgBlAHIAdABOADIATwBUAG8AQwBPADIAZQBfAFQAaQB0AGwAZQAiACwAIgBDAG8AbQBtAG8AbgBfAEUAcQB1AGEAdABpAG8AbgBzAC4AQwBvAG0AbQBvAG4AXwBDAG8AbgB2AGUAcgB0AE4AMgBPAFQAbwBDAE8AMgBlAF8AVgBhAHIAaQBhAGIAbABlACIALAAiAEMAbwBtAG0AbwBuAF8ARQBxAHUAYQB0AGkAbwBuAHMALgBDAG8AbQBtAG8AbgBfAEMAbwBuAHYAZQByAHQATgAyAE8AVABvAEMATwAyAGUAXwBVAG4AaQB0ACIALAAiAEMAbwBtAG0AbwBuAF8ARQBxAHUAYQB0AGkAbwBuAHMALgBDAG8AbQBtAG8AbgBfAEMAbwBuAHYAZQByAHQATgAyAE8AVABvAEMATwAyAGUAXwBOAEkAUgBSAGUAZgBlAHIAZQBuAGMAZQAiACwAIgBDAG8AbQBtAG8AbgBfAEUAcQB1AGEAdABpAG8AbgBzAC4AQwBvAG0AbQBvAG4AXwBDAG8AbgB2AGUAcgB0AE4AMgBPAFQAbwBDAE8AMgBlAF8ATABhAHQAZQB4AEUAcQB1AGEAdABpAG8AbgAiACwAIgBDAG8AbQBtAG8AbgBfAEUAcQB1AGEAdABpAG8AbgBzAC4AQwBvAG0AbQBvAG4AXwBDAG8AbgB2AGUAcgB0AE4AMgBPAFQAbwBDAE8AMgBlAF8AQQByAGcAdQBtAGUAbgB0AHMAIgAsACIAQwBvAG0AbQBvAG4AXwBFAHEAdQBhAHQAaQBvAG4AcwAuAEMAbwBtAG0AbwBuAF8AQwBvAG4AdgBlAHIAdABDAEgANABUAG8AQwBPADIAZQAiACwAIgBDAG8AbQBtAG8AbgBfAEUAcQB1AGEAdABpAG8AbgBzAC4AQwBvAG0AbQBvAG4AXwBDAG8AbgB2AGUAcgB0AEMASAA0AFQAbwBDAE8AMgBlAF8AVABpAHQAbABlACIALAAiAEMAbwBtAG0AbwBuAF8ARQBxAHUAYQB0AGkAbwBuAHMALgBDAG8AbQBtAG8AbgBfAEMAbwBuAHYAZQByAHQAQwBIADQAVABvAEMATwAyAGUAXwBWAGEAcgBpAGEAYgBsAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBFAHEAdQBhAHQAaQBvAG4AcwAuAEMAbwBtAG0AbwBuAF8AQwBvAG4AdgBlAHIAdABDAEgANABUAG8AQwBPADIAZQBfAFUAbgBpAHQAIgAsACIAQwBvAG0AbQBvAG4AXwBFAHEAdQBhAHQAaQBvAG4AcwAuAEMAbwBtAG0AbwBuAF8AQwBvAG4AdgBlAHIAdABDAEgANABUAG8AQwBPADIAZQBfAE4ASQBSAFIAZQBmAGUAcgBlAG4AYwBlACIALAAiAEMAbwBtAG0AbwBuAF8ARQBxAHUAYQB0AGkAbwBuAHMALgBDAG8AbQBtAG8AbgBfAEMAbwBuAHYAZQByAHQAQwBIADQAVABvAEMATwAyAGUAXwBMAGEAdABlAHgARQBxAHUAYQB0AGkAbwBuACIALAAiAEMAbwBtAG0AbwBuAF8ARQBxAHUAYQB0AGkAbwBuAHMALgBDAG8AbQBtAG8AbgBfAEMAbwBuAHYAZQByAHQAQwBIADQAVABvAEMATwAyAGUAXwBBAHIAZwB1AG0AZQBuAHQAcwAiACwAIgBDAG8AbQBtAG8AbgBfAEkAbgBwAHUAdABGAHUAbgBjAHQAaQBvAG4AcwAuAFUAdABpAGwAaQB0AHkAXwBHAGUAdABBAHIAcgBhAHkAVABhAGIAbABlAFIAbwB3AFMAdABhAHIAdABOAHUAbQBiAGUAcgAiACwAIgBDAG8AbQBtAG8AbgBfAEkAbgBwAHUAdABGAHUAbgBjAHQAaQBvAG4AcwAuAFUAdABpAGwAaQB0AHkAXwBHAGUAdABBAHIAcgBhAHkAVABhAGIAbABlAEMAbwBsAHUAbQBuAFMAdABhAHIAdABOAHUAbQBiAGUAcgAiACwAIgBDAG8AbQBtAG8AbgBfAEkAbgBwAHUAdABGAHUAbgBjAHQAaQBvAG4AcwAuAFUAdABpAGwAaQB0AHkAXwBEAGkAcwBwAGwAYQB5AEEAcgByAGEAeQBJAG4AVABhAGIAbABlACIALAAiAEMAbwBtAG0AbwBuAF8ASQBuAHAAdQB0AEYAdQBuAGMAdABpAG8AbgBzAC4AVQB0AGkAbABpAHQAeQBfAEwAbwBvAGsAdQBwAFYAYQBsAHUAZQBJAG4AVABhAGIAbABlACIALAAiAEMAbwBtAG0AbwBuAF8ASQBuAHAAdQB0AEYAdQBuAGMAdABpAG8AbgBzAC4AVQB0AGkAbABpAHQAeQBfAEwAbwBvAGsAdQBwAFYAYQBsAHUAZQBJAG4AVABhAGIAbABlAE4AdQBtAGIAZQByACIALAAiAEMAbwBtAG0AbwBuAF8ASQBuAHAAdQB0AEYAdQBuAGMAdABpAG8AbgBzAC4AVQB0AGkAbABpAHQAeQBfAEwAbwBvAGsAdQBwAFYAYQBsAHUAZQBJAG4AVABhAGIAbABlAFQAdwBvAEMAbwBsAHUAbQBuAHMAIgAsACIAQwBvAG0AbQBvAG4AXwBJAG4AcAB1AHQARgB1AG4AYwB0AGkAbwBuAHMALgBVAHQAaQBsAGkAdAB5AF8ATABvAG8AawB1AHAAVgBhAGwAdQBlAEkAbgBUAGEAYgBsAGUATwBuAGUAQwBvAGwAdQBtAG4AQQBuAGQASABlAGEAZABlAHIAIgAsACIAQwBvAG0AbQBvAG4AXwBJAG4AcAB1AHQARgB1AG4AYwB0AGkAbwBuAHMALgBVAHQAaQBsAGkAdAB5AF8AUwBwAGwAaQB0AFMAdAByAGkAbgBnAEkAbgB0AG8AQQByAHIAYQB5ACIALAAiAEMAbwBtAG0AbwBuAF8ASQBuAHAAdQB0AEYAdQBuAGMAdABpAG8AbgBzAC4AVQB0AGkAbABpAHQAeQBfAEcAZQB0AEMAbABpAG0AYQB0AGUAWgBvAG4AZQAiACwAIgBDAG8AbQBtAG8AbgBfAEkAbgBwAHUAdABGAHUAbgBjAHQAaQBvAG4AcwAuAFUAdABpAGwAaQB0AHkAXwBMAG8AbwBrAHUAcABJAHQAZQBtAEYAcgBvAG0ATQBpAG4ATQBhAHgAIgAsACIAQwBvAG0AbQBvAG4AXwBJAG4AcAB1AHQARgB1AG4AYwB0AGkAbwBuAHMALgBVAHQAaQBsAGkAdAB5AF8AUwB1AG0AUQB1AGEAbgB0AGkAdAB5AEYAcgBvAG0AQwByAGkAdABlAHIAaQBhACIALAAiAEMAbwBtAG0AbwBuAF8ASQBuAHAAdQB0AEYAdQBuAGMAdABpAG8AbgBzAC4AZwBlAHQATwB2AGUAcgBsAGEAcABwAGkAbgBnAFIAZQBwAG8AcgB0AGkAbgBnAFAAZQByAGkAbwBkAHMAIgAsACIAQwBvAG0AbQBvAG4AXwBJAG4AcAB1AHQARgB1AG4AYwB0AGkAbwBuAHMALgBVAHQAaQBsAGkAdAB5AF8ARABpAHMAcABsAGEAeQBGAHUAbgBjAHQAaQBvAG4ATgBhAG0AZQAiACwAIgBDAG8AbQBtAG8AbgBfAEkAbgBwAHUAdABGAHUAbgBjAHQAaQBvAG4AcwAuAFUAdABpAGwAaQB0AHkAXwBMAG8AbwBrAHUAcABOADIATwBFAEYARgByAG8AbQBQAHIAbwBkAEkAcgByAGkAZwBhAHQAaQBvAG4AUgBhAGkAbgBmAGEAbABsACIALAAiAEMAbwBtAG0AbwBuAF8ASQBuAHAAdQB0AEYAdQBuAGMAdABpAG8AbgBzAC4AQwBvAG0AbQBvAG4AQwByAG8AcABwAGkAbgBnAF8ARwBlAHQARgByAGEAYwBXAEUAVAAiACwAIgBDAG8AbQBtAG8AbgBfAEkAbgBwAHUAdABGAHUAbgBjAHQAaQBvAG4AcwAuAFUAdABpAGwAaQB0AHkAXwBDAG8AbgB2AGUAcgB0AFMAdABhAHQAZQBDAG8AbQBtAG8AbgBOAGEAbQBlAFQAbwBBAGIAYgByAGUAdgBpAGEAdABpAG8AbgAiACwAIgBDAG8AbQBtAG8AbgBfAEkAbgBwAHUAdABGAHUAbgBjAHQAaQBvAG4AcwAuAFUAdABpAGwAaQB0AHkAXwBTAG8AdQByAGMAZQBIAHkAcABlAHIAbABpAG4AawBEAGkAZgBmAGUAcgBlAG4AdABTAGgAZQBlAHQAIgAsACIAQwBvAG0AbQBvAG4AXwBJAG4AcAB1AHQARgB1AG4AYwB0AGkAbwBuAHMALgBVAHQAaQBsAGkAdAB5AF8AUgBlAHMAdQBsAHQAcwBJAHQAZQBtAEYAcgBvAG0ARQBxAHUAYQB0AGkAbwBuAFQAaQB0AGwAZQBBAG4AZABTAG8AdQByAGMAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGUAbgBzAGkAdAB5AE8AZgBNAGUAdABoAGEAbgBlAF8AVABpAHQAbABlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEQAZQBuAHMAaQB0AHkATwBmAE0AZQB0AGgAYQBuAGUAXwBVAG4AaQB0ACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEQAZQBuAHMAaQB0AHkATwBmAE0AZQB0AGgAYQBuAGUAXwBTAG8AdQByAGMAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGUAbgBzAGkAdAB5AE8AZgBNAGUAdABoAGEAbgBlAF8ARABhAHQAYQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBDAG8AbgB2AGUAcgB0AE4AMgBvAEUAbABlAG0AZQBuAHQAYQBsAFQAbwBNAG8AbABlAGMAdQBsAGEAcgBDAGcAXwBUAGkAdABsAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQwBvAG4AdgBlAHIAdABOADIAbwBFAGwAZQBtAGUAbgB0AGEAbABUAG8ATQBvAGwAZQBjAHUAbABhAHIAQwBnAF8AVgBhAHIAaQBhAGIAbABlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEMAbwBuAHYAZQByAHQATgAyAG8ARQBsAGUAbQBlAG4AdABhAGwAVABvAE0AbwBsAGUAYwB1AGwAYQByAEMAZwBfAFUAbgBpAHQAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQwBvAG4AdgBlAHIAdABOADIAbwBFAGwAZQBtAGUAbgB0AGEAbABUAG8ATQBvAGwAZQBjAHUAbABhAHIAQwBnAF8AUwBvAHUAcgBjAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQwBvAG4AdgBlAHIAdABOADIAbwBFAGwAZQBtAGUAbgB0AGEAbABUAG8ATQBvAGwAZQBjAHUAbABhAHIAQwBnAF8ARABhAHQAYQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBDAG8AbgB2AGUAcgB0AEcAYQBzAEUAbABlAG0AZQBuAHQAYQBsAFQAbwBNAG8AbABlAGMAdQBsAGEAcgBfAFQAaQB0AGwAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBDAG8AbgB2AGUAcgB0AEcAYQBzAEUAbABlAG0AZQBuAHQAYQBsAFQAbwBNAG8AbABlAGMAdQBsAGEAcgBfAFYAYQByAGkAYQBiAGwAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBDAG8AbgB2AGUAcgB0AEcAYQBzAEUAbABlAG0AZQBuAHQAYQBsAFQAbwBNAG8AbABlAGMAdQBsAGEAcgBfAFUAbgBpAHQAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQwBvAG4AdgBlAHIAdABHAGEAcwBFAGwAZQBtAGUAbgB0AGEAbABUAG8ATQBvAGwAZQBjAHUAbABhAHIAXwBTAG8AdQByAGMAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBDAG8AbgB2AGUAcgB0AEcAYQBzAEUAbABlAG0AZQBuAHQAYQBsAFQAbwBNAG8AbABlAGMAdQBsAGEAcgBfAEQAYQB0AGEAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARwBXAFAAXwBUAGkAdABsAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARwBXAFAAXwBWAGEAcgBpAGEAYgBsAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARwBXAFAAXwBVAG4AaQB0ACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEcAVwBQAF8AUwBvAHUAcgBjAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARwBXAFAAXwBEAGEAdABhACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEEAdQBzAHQAcgBhAGwAaQBhAG4AUwB0AGEAdABlAHMAVABlAHIAcgBpAHQAbwByAGkAZQBzAF8AVABpAHQAbABlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEEAdQBzAHQAcgBhAGwAaQBhAG4AUwB0AGEAdABlAHMAVABlAHIAcgBpAHQAbwByAGkAZQBzAF8AVgBhAHIAaQBhAGIAbABlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEEAdQBzAHQAcgBhAGwAaQBhAG4AUwB0AGEAdABlAHMAVABlAHIAcgBpAHQAbwByAGkAZQBzAF8AVQBuAGkAdAAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBBAHUAcwB0AHIAYQBsAGkAYQBuAFMAdABhAHQAZQBzAFQAZQByAHIAaQB0AG8AcgBpAGUAcwBfAFMAbwB1AHIAYwBlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEEAdQBzAHQAcgBhAGwAaQBhAG4AUwB0AGEAdABlAHMAVABlAHIAcgBpAHQAbwByAGkAZQBzAF8ARABhAHQAYQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBXAEEAUwBBADQAQQByAGUAYQBzAF8AVABpAHQAbABlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFcAQQBTAEEANABBAHIAZQBhAHMAXwBWAGEAcgBpAGEAYgBsAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AVwBBAFMAQQA0AEEAcgBlAGEAcwBfAFUAbgBpAHQAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AVwBBAFMAQQA0AEEAcgBlAGEAcwBfAFMAbwB1AHIAYwBlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFcAQQBTAEEANABBAHIAZQBhAHMAXwBEAGEAdABhACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFcAZQB0AEEAbgBkAEQAcgB5AFoAbwBuAGUAcwBfAFQAaQB0AGwAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBXAGUAdABBAG4AZABEAHIAeQBaAG8AbgBlAHMAXwBWAGEAcgBpAGEAYgBsAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AVwBlAHQAQQBuAGQARAByAHkAWgBvAG4AZQBzAF8AVQBuAGkAdAAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBXAGUAdABBAG4AZABEAHIAeQBaAG8AbgBlAHMAXwBTAG8AdQByAGMAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBXAGUAdABBAG4AZABEAHIAeQBaAG8AbgBlAHMAXwBWAGEAcgBpAGEAdABpAG8AbgAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBXAGUAdABBAG4AZABEAHIAeQBaAG8AbgBlAHMAXwBEAGEAdABhACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEMAbABpAG0AYQB0AGUAWgBvAG4AZQBzAF8AVABpAHQAbABlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEMAbABpAG0AYQB0AGUAWgBvAG4AZQBzAF8AVgBhAHIAaQBhAGIAbABlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEMAbABpAG0AYQB0AGUAWgBvAG4AZQBzAF8AVQBuAGkAdAAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBDAGwAaQBtAGEAdABlAFoAbwBuAGUAcwBfAFMAbwB1AHIAYwBlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEMAbABpAG0AYQB0AGUAWgBvAG4AZQBzAF8AVgBhAHIAaQBhAHQAaQBvAG4AIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQwBsAGkAbQBhAHQAZQBaAG8AbgBlAHMAXwBEAGEAdABhACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEMAbABpAG0AYQB0AGUAWgBvAG4AZQBzAF8AQQBwAHAAZQBuAGQAaQBjAGUAcwAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBUAGUAbQBwAGUAcgBhAHQAdQByAGUAWgBvAG4AZQBzAF8AVABpAHQAbABlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFQAZQBtAHAAZQByAGEAdAB1AHIAZQBaAG8AbgBlAHMAXwBWAGEAcgBpAGEAYgBsAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AVABlAG0AcABlAHIAYQB0AHUAcgBlAFoAbwBuAGUAcwBfAFUAbgBpAHQAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AVABlAG0AcABlAHIAYQB0AHUAcgBlAFoAbwBuAGUAcwBfAFMAbwB1AHIAYwBlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFQAZQBtAHAAZQByAGEAdAB1AHIAZQBaAG8AbgBlAHMAXwBWAGEAcgBpAGEAdABpAG8AbgAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBUAGUAbQBwAGUAcgBhAHQAdQByAGUAWgBvAG4AZQBzAF8ARABhAHQAYQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBSAGEAaQBuAGYAYQBsAGwAWgBvAG4AZQBzAF8AVABpAHQAbABlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFIAYQBpAG4AZgBhAGwAbABaAG8AbgBlAHMAXwBWAGEAcgBpAGEAYgBsAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AUgBhAGkAbgBmAGEAbABsAFoAbwBuAGUAcwBfAFUAbgBpAHQAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AUgBhAGkAbgBmAGEAbABsAFoAbwBuAGUAcwBfAFMAbwB1AHIAYwBlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFIAYQBpAG4AZgBhAGwAbABaAG8AbgBlAHMAXwBWAGEAcgBpAGEAdABpAG8AbgAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBSAGEAaQBuAGYAYQBsAGwAWgBvAG4AZQBzAF8ARABhAHQAYQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBMAGUAYQBjAGgAaQBuAGcAWgBvAG4AZQBzAF8AVABpAHQAbABlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEwAZQBhAGMAaABpAG4AZwBaAG8AbgBlAHMAXwBWAGEAcgBpAGEAYgBsAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ATABlAGEAYwBoAGkAbgBnAFoAbwBuAGUAcwBfAFUAbgBpAHQAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ATABlAGEAYwBoAGkAbgBnAFoAbwBuAGUAcwBfAFMAbwB1AHIAYwBlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEwAZQBhAGMAaABpAG4AZwBaAG8AbgBlAHMAXwBWAGEAcgBpAGEAdABpAG8AbgAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBMAGUAYQBjAGgAaQBuAGcAWgBvAG4AZQBzAF8ARABhAHQAYQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAHIAYQBjAFcARQBUAF8AVABpAHQAbABlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAcgBhAGMAVwBFAFQAXwBVAG4AaQB0ACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAcgBhAGMAVwBFAFQAXwBTAG8AdQByAGMAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAHIAYQBjAFcARQBUAF8ATgBJAFIAUgBlAGYAZQByAGUAbgBjAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgByAGEAYwBXAEUAVABfAEQAYQB0AGEAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgByAGEAYwBXAEUAVABfAFYAYQByAGkAYQB0AGkAbwBuACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEQAYQB0AGEAUwBjAG8AcgBlAHMAXwBTAGMAbwBwAGUAMwBfAFQAaQB0AGwAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGEAdABhAFMAYwBvAHIAZQBzAF8AUwBjAG8AcABlADMAXwBWAGEAcgBpAGEAYgBsAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABhAHQAYQBTAGMAbwByAGUAcwBfAFMAYwBvAHAAZQAzAF8AVQBuAGkAdAAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGEAdABhAFMAYwBvAHIAZQBzAF8AUwBjAG8AcABlADMAXwBTAG8AdQByAGMAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGEAdABhAFMAYwBvAHIAZQBzAF8AUwBjAG8AcABlADMAXwBWAGEAcgBpAGEAdABpAG8AbgAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGEAdABhAFMAYwBvAHIAZQBzAF8AUwBjAG8AcABlADMAXwBEAGEAdABhACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAcgBhAGMATABFAEEAQwBIAF8AVABpAHQAbABlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAcgBhAGMATABFAEEAQwBIAF8AVQBuAGkAdAAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAHIAYQBjAEwARQBBAEMASABfAFMAbwB1AHIAYwBlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAcgBhAGMATABFAEEAQwBIAF8ATgBJAFIAUgBlAGYAZQByAGUAbgBjAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgByAGEAYwBMAEUAQQBDAEgAXwBEAGEAdABhACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAcgBhAGMATABFAEEAQwBIAF8AVgBhAHIAaQBhAHQAaQBvAG4AIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAGwAZQBhAGMAaABfAFQAaQB0AGwAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYAbABlAGEAYwBoAF8AVQBuAGkAdAAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYAbABlAGEAYwBoAF8AUwBvAHUAcgBjAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAGwAZQBhAGMAaABfAE4ASQBSAFIAZQBmAGUAcgBlAG4AYwBlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEUARgBsAGUAYQBjAGgAXwBEAGEAdABhACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEUARgBsAGUAYQBjAGgAXwBWAGEAcgBpAGEAdABpAG8AbgAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYATgAyAE8AXwBUAGkAdABsAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAE4AMgBPAF8AVQBuAGkAdAAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYATgAyAE8AXwBTAG8AdQByAGMAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYATgAyAE8AXwBOAEkAUgBSAGUAZgBlAHIAZQBuAGMAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYATgAyAE8AXwBEAGEAdABhACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEUARgBOADIATwBfAFYAYQByAGkAYQB0AGkAbwBuACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAcgBhAGMAVwBFAFQASQByAHIAaQBnAGEAdABpAG8AbgBfAFQAaQB0AGwAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAHIAYQBjAFcARQBUAEkAcgByAGkAZwBhAHQAaQBvAG4AXwBVAG4AaQB0ACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAcgBhAGMAVwBFAFQASQByAHIAaQBnAGEAdABpAG8AbgBfAFMAbwB1AHIAYwBlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAcgBhAGMAVwBFAFQASQByAHIAaQBnAGEAdABpAG8AbgBfAE4ASQBSAFIAZQBmAGUAcgBlAG4AYwBlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAcgBhAGMAVwBFAFQASQByAHIAaQBnAGEAdABpAG8AbgBfAEQAYQB0AGEAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgByAGEAYwBXAEUAVABJAHIAcgBpAGcAYQB0AGkAbwBuAF8AVgBhAHIAaQBhAHQAaQBvAG4AIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAFAAYQBzAHQAdQByAGUAUgBhAG4AZwBlAEEAbgBkAFAAYQBkAGQAbwBjAGsAXwBUAGkAdABsAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAFAAYQBzAHQAdQByAGUAUgBhAG4AZwBlAEEAbgBkAFAAYQBkAGQAbwBjAGsAXwBVAG4AaQB0ACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEUARgBQAGEAcwB0AHUAcgBlAFIAYQBuAGcAZQBBAG4AZABQAGEAZABkAG8AYwBrAF8AUwBvAHUAcgBjAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAFAAYQBzAHQAdQByAGUAUgBhAG4AZwBlAEEAbgBkAFAAYQBkAGQAbwBjAGsAXwBOAEkAUgBSAGUAZgBlAHIAZQBuAGMAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYAUABhAHMAdAB1AHIAZQBSAGEAbgBnAGUAQQBuAGQAUABhAGQAZABvAGMAawBfAEQAYQB0AGEAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAFAAYQBzAHQAdQByAGUAUgBhAG4AZwBlAEEAbgBkAFAAYQBkAGQAbwBjAGsAXwBWAGEAcgBpAGEAdABpAG8AbgAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBNAG8AbgB0AGgAcwBUAG8AUwBlAGEAcwBvAG4AcwBfAFQAaQB0AGwAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBNAG8AbgB0AGgAcwBUAG8AUwBlAGEAcwBvAG4AcwBfAFUAbgBpAHQAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ATQBvAG4AdABoAHMAVABvAFMAZQBhAHMAbwBuAHMAXwBTAG8AdQByAGMAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBNAG8AbgB0AGgAcwBUAG8AUwBlAGEAcwBvAG4AcwBfAE4ASQBSAFIAZQBmAGUAcgBlAG4AYwBlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAE0AbwBuAHQAaABzAFQAbwBTAGUAYQBzAG8AbgBzAF8ARABhAHQAYQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBNAG8AbgB0AGgAcwBUAG8AUwBlAGEAcwBvAG4AcwBfAFYAYQByAGkAYQB0AGkAbwBuACIAXQAsACIAbABvAGMAYQBsAGUAIgA6AHsAIgBsAGkAcwB0AFMAZQBwAGEAcgBhAHQAbwByACIAOgAiACwAIgAsACIAcgBvAHcAUwBlAHAAYQByAGEAdABvAHIAIgA6ACIAOwAiACwAIgBjAG8AbAB1AG0AbgBTAGUAcABhAHIAYQB0AG8AcgAiADoAIgAsACIALAAiAHQAaABvAHUAcwBhAG4AZABzAFMAZQBwAGEAcgBhAHQAbwByACIAOgAiACwAIgAsACIAdABoAG8AdQBzAGEAbgBkAHMAUABvAHMAaQB0AGkAbwBuAHMAIgA6AFsAMwBdACwAIgBkAGUAYwBpAG0AYQBsAFMAZQBwAGEAcgBhAHQAbwByACIAOgAiAC4AIgAsACIAZABhAHQAZQBPAHIAZABlAHIAIgA6ACIARABNAFkAIgAsACIAYwB1AHIAcgBlAG4AYwB5AFMAeQBtAGIAbwBsACIAOgAiACQAIgAsACIAaQBzAEMAdQByAHIAZQBuAGMAeQBTAHkAbQBiAG8AbABMAGUAYQBkACIAOgB0AHIAdQBlACwAIgBpAHMAQwB1AHIAcgBlAG4AYwB5AFMAZQBwAEIAeQBTAHAAYQBjAGUAIgA6AGYAYQBsAHMAZQAsACIAcgBvAHcATABlAHQAdABlAHIAIgA6ACIAUgAiACwAIgBjAG8AbAB1AG0AbgBMAGUAdAB0AGUAcgAiADoAIgBDACIALAAiAHIAYwBMAGUAZgB0AEIAcgBhAGMAawBlAHQAIgA6ACIAWwAiACwAIgByAGMAUgBpAGcAaAB0AEIAcgBhAGMAawBlAHQAIgA6ACIAXQAiACwAIgBzAHQAYQB0AGUAbQBlAG4AdABTAGUAcABhAHIAYQB0AG8AcgAiADoAIgA7ACIALAAiAGwAbwBjAGEAbABlAE4AYQBtAGUAIgA6ACIAZQBuAC0AdQBzACIAfQB9AA==</AFEJSONBlob>
 </file>
 
 <file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
@@ -11611,7 +11499,14 @@
 </file>
 
 <file path=customXml/item4.xml><?xml version="1.0" encoding="utf-8"?>
-<AFEJSONBlob xmlns="http://schemas.advancedformulaenvironment.officeapps.live.com/afejsonblob/1.0">ewAiAHMAYwBoAGUAbQBhACIAOgAiAGgAdAB0AHAAOgAvAC8AcwBjAGgAZQBtAGEAcwAuAGEAZAB2AGEAbgBjAGUAZABmAG8AcgBtAHUAbABhAGUAbgB2AGkAcgBvAG4AbQBlAG4AdAAuAG8AZgBmAGkAYwBlAGEAcABwAHMALgBsAGkAdgBlAC4AYwBvAG0ALwBhAGYAZQBwAHIAbwBqAGUAYwB0AHMALwAwAC4AMgAiACwAIgBmAGkAbABlAHMAIgA6AFsAewAiAHAAYQB0AGgAIgA6ACIALwBwAHIAbwBqAGUAYwB0AHMALwBXAG8AcgBrAGIAbwBvAGsAIgAsACIAdABlAHgAdAAiADoAIgAvAC8AIAAtAC0ALQAgAFcAbwByAGsAYgBvAG8AawAgAG0AbwBkAHUAbABlACAALQAtAC0AXABuAC8ALwAgAEEAIABmAGkAbABlACAAbwBmACAAbgBhAG0AZQAgAGQAZQBmAGkAbgBpAHQAaQBvAG4AcwAgAG8AZgAgAHQAaABlACAAZgBvAHIAbQA6AFwAbgAvAC8AIAAgACAAIABuAGEAbQBlACAAPQAgAGQAZQBmAGkAbgBpAHQAaQBvAG4AOwBcAG4AIgB9ACwAewAiAHAAYQB0AGgAIgA6ACIALwBwAHIAbwBqAGUAYwB0AHMALwBDAG8AbQBtAG8AbgBfAEUAcQB1AGEAdABpAG8AbgBzACIALAAiAHQAZQB4AHQAIgA6ACIAXABuAC8AKgAgAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuAEMAbwBtAG0AbwBuAF8AQwBvAG4AdgBlAHIAdABOADIATwBUAG8AQwBPADIAZQBcAG4AQwBvAG4AdgBlAHIAdAAgAG4AaQB0AHIAbwB1AHMAIABvAHgAaQBkAGUAIABlAG0AaQBzAHMAaQBvAG4AcwAgAHQAbwAgAGMAYQByAGIAbwBuACAAZABpAG8AeABpAGQAZQAgAGUAcQB1AGkAdgBhAGwAZQBuAHQAIABlAG0AaQBzAHMAaQBvAG4AcwBcAG4ARQBOADIATwAgAEMATwAyAGUAXABuAHQAIABDAE8AMgBlAFwAbgBFAE4AMgBPADoAIABuAGkAdAByAG8AdQBzACAAbwB4AGkAZABlACAAZQBtAGkAcwBzAGkAbwBuAHMAIAAoAHQAIABOADIATwApAFwAbgBHAFcAUABOADIATwA6ACAAZwBsAG8AYgBhAGwAIAB3AGEAcgBtAGkAbgBnACAAcABvAHQAZQBuAHQAaQBhAGwAIABmAG8AcgAgAG4AaQB0AHIAbwB1AHMAIABvAHgAaQBkAGUAIAAoAHQAIABDAE8AMgAtAGUAIAAvACAAdAAgAE4AMgBPACkAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AKgAvAFwAbgBcAG4AXABuAEMAbwBtAG0AbwBuAF8AQwBvAG4AdgBlAHIAdABOADIATwBUAG8AQwBPADIAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABFAF8ATgAyAE8ALAAgAEcAVwBQAF8ATgAyAE8ALABcAG4AIAAgACAAIABFAF8ATgAyAE8AIAAqACAARwBXAFAAXwBOADIATwBcAG4AIAAgACkAXABuADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAEMAbwBuAHYAZQByAHQATgAyAE8AVABvAEMATwAyAGUAXwBUAGkAdABsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAEMAbwBuAHYAZQByAHQAIABuAGkAdAByAG8AdQBzACAAbwB4AGkAZABlACAAZQBtAGkAcwBzAGkAbwBuAHMAIAB0AG8AIABjAGEAcgBiAG8AbgAgAGQAaQBvAHgAaQBkAGUAIABlAHEAdQBpAHYAYQBsAGUAbgB0ACAAZQBtAGkAcwBzAGkAbwBuAHMAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AQwBvAG4AdgBlAHIAdABOADIATwBUAG8AQwBPADIAZQBfAFYAYQByAGkAYQBiAGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIARQBOADIATwAgAEMATwAyAGUAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AQwBvAG4AdgBlAHIAdABOADIATwBUAG8AQwBPADIAZQBfAFUAbgBpAHQAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAHQAIABDAE8AMgBlAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAEMAbwBuAHYAZQByAHQATgAyAE8AVABvAEMATwAyAGUAXwBOAEkAUgBSAGUAZgBlAHIAZQBuAGMAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AQwBvAG4AdgBlAHIAdABOADIATwBUAG8AQwBPADIAZQBfAEwAYQB0AGUAeABFAHEAdQBhAHQAaQBvAG4AXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAEMATwAyAF8AZQAgAD0AIABFAF8AewBOADIATwB9ACAAXABcAHQAaQBtAGUAcwAgAEcAVwBQAF8AewBOADIATwB9AFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAEMAbwBuAHYAZQByAHQATgAyAE8AVABvAEMATwAyAGUAXwBBAHIAZwB1AG0AZQBuAHQAcwBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABNAEEASwBFAEEAUgBSAEEAWQAoADIALAAgADIALAAgAFwAbgAgACAAIAAgACAAIABMAEEATQBCAEQAQQAoAHIALABjACwAIABcAG4AIAAgACAAIAAgACAAIAAgAEkATgBEAEUAWAAoAHsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEUATgAyAE8AXAAiACwAXAAiAE4AaQB0AHIAbwB1AHMAIABvAHgAaQBkAGUAIABlAG0AaQBzAHMAaQBvAG4AcwAgACgAdAAgAE4AMgBPACkAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEcAVwBQAE4AMgBPAFwAIgAsAFwAIgBHAGwAbwBiAGEAbAAgAHcAYQByAG0AaQBuAGcAIABwAG8AdABlAG4AdABpAGEAbAAgAGYAbwByACAAbgBpAHQAcgBvAHUAcwAgAG8AeABpAGQAZQAgACgAdAAgAEMATwAyAC0AZQAgAC8AIAB0ACAATgAyAE8AKQBcACIAXABuACAAIAAgACAAIAAgACAAIAB9ACwAIAByACwAIABjACkAXABuACAAIAAgACAAIAAgACkAXABuACAAIAAgACAAKQBcAG4AIAAgACkAOwBcAG4AXABuAC8AKgAgAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuAEMAbwBtAG0AbwBuAF8AQwBvAG4AdgBlAHIAdABDAEgANABUAG8AQwBPADIAZQBcAG4AQwBvAG4AdgBlAHIAdAAgAG0AZQB0AGgAYQBuAGUAIABlAG0AaQBzAHMAaQBvAG4AcwAgAHQAbwAgAGMAYQByAGIAbwBuACAAZABpAG8AeABpAGQAZQAgAGUAcQB1AGkAdgBhAGwAZQBuAHQAIABlAG0AaQBzAHMAaQBvAG4AcwBcAG4ARQBDAEgANAAgAEMATwAyAGUAXABuAHQAIABDAE8AMgBlAFwAbgBFAEMASAA0ADoAIABtAGUAdABoAGEAbgBlACAAZQBtAGkAcwBzAGkAbwBuAHMAIAAoAHQAIABDAEgANAApAFwAbgBHAFcAUABDAEgANAA6ACAAZwBsAG8AYgBhAGwAIAB3AGEAcgBtAGkAbgBnACAAcABvAHQAZQBuAHQAaQBhAGwAIABmAG8AcgAgAG0AZQB0AGgAYQBuAGUAIAAoAHQAIABDAE8AMgAtAGUAIAAvACAAdAAgAEMASAA0ACkAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AKgAvAFwAbgBcAG4AXABuAEMAbwBtAG0AbwBuAF8AQwBvAG4AdgBlAHIAdABDAEgANABUAG8AQwBPADIAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABFAF8AQwBIADQALAAgAEcAVwBQAF8AQwBIADQALABcAG4AIAAgACAAIABFAF8AQwBIADQAIAAqACAARwBXAFAAXwBDAEgANABcAG4AIAAgACkAXABuADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAEMAbwBuAHYAZQByAHQAQwBIADQAVABvAEMATwAyAGUAXwBUAGkAdABsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAEMAbwBuAHYAZQByAHQAIABtAGUAdABoAGEAbgBlACAAZQBtAGkAcwBzAGkAbwBuAHMAIAB0AG8AIABjAGEAcgBiAG8AbgAgAGQAaQBvAHgAaQBkAGUAIABlAHEAdQBpAHYAYQBsAGUAbgB0ACAAZQBtAGkAcwBzAGkAbwBuAHMAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AQwBvAG4AdgBlAHIAdABDAEgANABUAG8AQwBPADIAZQBfAFYAYQByAGkAYQBiAGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIARQBDAEgANAAgAEMATwAyAGUAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AQwBvAG4AdgBlAHIAdABDAEgANABUAG8AQwBPADIAZQBfAFUAbgBpAHQAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAHQAIABDAE8AMgBlAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAEMAbwBuAHYAZQByAHQAQwBIADQAVABvAEMATwAyAGUAXwBOAEkAUgBSAGUAZgBlAHIAZQBuAGMAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AQwBvAG4AdgBlAHIAdABDAEgANABUAG8AQwBPADIAZQBfAEwAYQB0AGUAeABFAHEAdQBhAHQAaQBvAG4AXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAEMATwAyAF8AZQAgAD0AIABFAF8AewBDAEgANAB9ACAAXABcAHQAaQBtAGUAcwAgAEcAVwBQAF8AewBDAEgANAB9AFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAEMAbwBuAHYAZQByAHQAQwBIADQAVABvAEMATwAyAGUAXwBBAHIAZwB1AG0AZQBuAHQAcwBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABNAEEASwBFAEEAUgBSAEEAWQAoADIALAAgADIALAAgAFwAbgAgACAAIAAgACAAIABMAEEATQBCAEQAQQAoAHIALABjACwAIABcAG4AIAAgACAAIAAgACAAIAAgAEkATgBEAEUAWAAoAHsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEUAQwBIADQAXAAiACwAXAAiAE0AZQB0AGgAYQBuAGUAIABlAG0AaQBzAHMAaQBvAG4AcwAgACgAdAAgAEMASAA0ACkAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEcAVwBQAEMASAA0AFwAIgAsAFwAIgBHAGwAbwBiAGEAbAAgAHcAYQByAG0AaQBuAGcAIABwAG8AdABlAG4AdABpAGEAbAAgAGYAbwByACAAbQBlAHQAaABhAG4AZQAgACgAdAAgAEMATwAyAC0AZQAgAC8AIAB0ACAAQwBIADQAKQBcACIAXABuACAAIAAgACAAIAAgACAAIAB9ACwAIAByACwAIABjACkAXABuACAAIAAgACAAIAAgACkAXABuACAAIAAgACAAKQBcAG4AIAAgACkAOwAiAH0ALAB7ACIAcABhAHQAaAAiADoAIgAvAHAAcgBvAGoAZQBjAHQAcwAvAEMAbwBtAG0AbwBuAF8ASQBuAHAAdQB0AEYAdQBuAGMAdABpAG8AbgBzACIALAAiAHQAZQB4AHQAIgA6ACIAVQB0AGkAbABpAHQAeQBfAEcAZQB0AEEAcgByAGEAeQBUAGEAYgBsAGUAUgBvAHcAUwB0AGEAcgB0AE4AdQBtAGIAZQByAFwAbgA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAAVABhAGIAbABlAGgAZQBhAGQAZQByAEMAZQBsAGwALABSAG8AdwBzAEIAZQB0AHcAZQBlAG4ASABlAGEAZABlAHIAYQBuAGQAQQByAHIAYQB5ACwAXABuACAAIAAgACAAUgBPAFcAKABUAGEAYgBsAGUAaABlAGEAZABlAHIAQwBlAGwAbAApACAAKwAgAFIAbwB3AHMAQgBlAHQAdwBlAGUAbgBIAGUAYQBkAGUAcgBhAG4AZABBAHIAcgBhAHkAIAAtACAAMQBcAG4AKQA7AFwAbgBcAG4AVQB0AGkAbABpAHQAeQBfAEcAZQB0AEEAcgByAGEAeQBUAGEAYgBsAGUAQwBvAGwAdQBtAG4AUwB0AGEAcgB0AE4AdQBtAGIAZQByAFwAbgA9AEwAQQBNAEIARABBACgAXABuACAAIABUAGEAYgBsAGUASABlAGEAZABlAHIAQwBlAGwAbAAsAFwAbgAgACAAQwBPAEwAVQBNAE4AKABUAGEAYgBsAGUASABlAGEAZABlAHIAQwBlAGwAbAApAFwAbgApADsAXABuAFwAbgBVAHQAaQBsAGkAdAB5AF8ARABpAHMAcABsAGEAeQBBAHIAcgBhAHkASQBuAFQAYQBiAGwAZQBcAG4APQBMAEEATQBCAEQAQQAoAFwAbgAgAEEAcgByAGEAeQBEAGEAdABhACwAIABUAGEAYgBsAGUAaABlAGEAZABlAHIAQwBlAGwAbAAsACAAUgBvAHcAcwBCAGUAdAB3AGUAZQBuAEgAZQBhAGQAZQByAGEAbgBkAEEAcgByAGEAeQAsACAAWwBDAG8AbAB1AG0AbgBzAEIAZQB0AHcAZQBlAG4ASABlAGEAZABlAHIAQQBuAGQAQQByAHIAYQB5AF0ALABcAG4AIABJAEYARQBSAFIATwBSACgAXABuACAAIAAgACAAIABJAE4ARABFAFgAKABcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAVQBOAEkAUQBVAEUAKABBAHIAcgBhAHkARABhAHQAYQApACwAIABcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAUgBPAFcAKAApAC0AVQB0AGkAbABpAHQAeQBfAEcAZQB0AEEAcgByAGEAeQBUAGEAYgBsAGUAUgBvAHcAUwB0AGEAcgB0AE4AdQBtAGIAZQByACgAVABhAGIAbABlAGgAZQBhAGQAZQByAEMAZQBsAGwALAAgAFIAbwB3AHMAQgBlAHQAdwBlAGUAbgBIAGUAYQBkAGUAcgBhAG4AZABBAHIAcgBhAHkAKQAsACAAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgAEMATwBMAFUATQBOACgAKQAtAFUAdABpAGwAaQB0AHkAXwBHAGUAdABBAHIAcgBhAHkAVABhAGIAbABlAEMAbwBsAHUAbQBuAFMAdABhAHIAdABOAHUAbQBiAGUAcgAoAFQAYQBiAGwAZQBoAGUAYQBkAGUAcgBDAGUAbABsACkAIAArAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIABJAEYAKABJAFMATwBNAEkAVABUAEUARAAoAEMAbwBsAHUAbQBuAHMAQgBlAHQAdwBlAGUAbgBIAGUAYQBkAGUAcgBBAG4AZABBAHIAcgBhAHkAKQAsACAAMQAsACAAQwBvAGwAdQBtAG4AcwBCAGUAdAB3AGUAZQBuAEgAZQBhAGQAZQByAEEAbgBkAEEAcgByAGEAeQApAFwAbgAgACAAIAAgACAAIAAgACAAKQAsACAAXAAiAFwAIgBcAG4AIAAgACAAIAApAFwAbgApADsAXABuAFwAbgBVAHQAaQBsAGkAdAB5AF8ATABvAG8AawB1AHAAVgBhAGwAdQBlAEkAbgBUAGEAYgBsAGUAXABuAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABMAG8AbwBrAHUAcABWAGEAbAB1AGUALAAgAEwAbwBvAGsAdQBwAEEAcgByAGEAeQAsACAAUgBlAHQAdQByAG4AQQByAHIAYQB5ACwAXABuACAAIAAgACAAWABMAE8ATwBLAFUAUAAoAEwAbwBvAGsAdQBwAFYAYQBsAHUAZQAsACAATABvAG8AawB1AHAAQQByAHIAYQB5ACwAIABSAGUAdAB1AHIAbgBBAHIAcgBhAHkALAAgAFwAIgBcACIAKQBcAG4AKQA7AFwAbgBcAG4AVQB0AGkAbABpAHQAeQBfAEwAbwBvAGsAdQBwAFYAYQBsAHUAZQBJAG4AVABhAGIAbABlAE4AdQBtAGIAZQByAFwAbgA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAATABvAG8AawB1AHAAVgBhAGwAdQBlACwAIABMAG8AbwBrAHUAcABBAHIAcgBhAHkALAAgAFIAZQB0AHUAcgBuAEEAcgByAGEAeQAsAFwAbgAgACAAIAAgAEkARgAoAEkAUwBOAFUATQBCAEUAUgAoAFwAbgAgACAAIAAgACAAIAAgACAAWABMAE8ATwBLAFUAUAAoAEwAbwBvAGsAdQBwAFYAYQBsAHUAZQAsACAATABvAG8AawB1AHAAQQByAHIAYQB5ACwAIABSAGUAdAB1AHIAbgBBAHIAcgBhAHkALAAgAFwAIgBcACIAKQBcAG4AIAAgACAAIAApACwAIABYAEwATwBPAEsAVQBQACgATABvAG8AawB1AHAAVgBhAGwAdQBlACwAIABMAG8AbwBrAHUAcABBAHIAcgBhAHkALAAgAFIAZQB0AHUAcgBuAEEAcgByAGEAeQAsACAAXAAiAFwAIgApACwAIAAwACkAXABuACkAOwBcAG4AXABuAFUAdABpAGwAaQB0AHkAXwBMAG8AbwBrAHUAcABWAGEAbAB1AGUASQBuAFQAYQBiAGwAZQBUAHcAbwBDAG8AbAB1AG0AbgBzAFwAbgA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAATABvAG8AawB1AHAAVgBhAGwAdQBlADEALAAgAEwAbwBvAGsAdQBwAFYAYQBsAHUAZQAyACwAIABMAG8AbwBrAHUAcABBAHIAcgBhAHkAMQAsACAATABvAG8AawB1AHAAQQByAHIAYQB5ADIALAAgAFIAZQB0AHUAcgBuAEEAcgByAGEAeQAsACAAWwBWAGEAbAB1AGUASQBGAEYAYQBsAHMAZQBdACwAXABuACAAIAAgACAAWABMAE8ATwBLAFUAUAAoADEALAAgACgATABvAG8AawB1AHAAQQByAHIAYQB5ADEAPQBMAG8AbwBrAHUAcABWAGEAbAB1AGUAMQApACoAKABMAG8AbwBrAHUAcABBAHIAcgBhAHkAMgA9AEwAbwBvAGsAdQBwAFYAYQBsAHUAZQAyACkALAAgAFIAZQB0AHUAcgBuAEEAcgByAGEAeQAsACAASQBGACgASQBTAE8ATQBJAFQAVABFAEQAKABWAGEAbAB1AGUASQBGAEYAYQBsAHMAZQApACwAIABcACIAXAAiACwAIABWAGEAbAB1AGUASQBGAEYAYQBsAHMAZQApACkAXABuACkAOwBcAG4AXABuAFUAdABpAGwAaQB0AHkAXwBMAG8AbwBrAHUAcABWAGEAbAB1AGUASQBuAFQAYQBiAGwAZQBPAG4AZQBDAG8AbAB1AG0AbgBBAG4AZABIAGUAYQBkAGUAcgBcAG4APQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAEwAbwBvAGsAdQBwAFYAYQBsAHUAZQAxACwAIABMAG8AbwBrAHUAcABWAGEAbAB1AGUAMgAsACAATABvAG8AawB1AHAAQQByAHIAYQB5ADEALAAgAEwAbwBvAGsAdQBwAEEAcgByAGEAeQAyACwAIABSAGUAdAB1AHIAbgBBAHIAcgBhAHkALAAgAFsAVgBhAGwAdQBlAEkAZgBGAGEAbABzAGUAXQAsAFwAbgAgACAAIAAgAEkARgBFAFIAUgBPAFIAKABcAG4AIAAgACAAIAAgACAAIAAgAFgATABPAE8ASwBVAFAAKABMAG8AbwBrAHUAcABWAGEAbAB1AGUAMQAsACAATABvAG8AawB1AHAAQQByAHIAYQB5ADEALABcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAWABMAE8ATwBLAFUAUAAoAEwAbwBvAGsAdQBwAFYAYQBsAHUAZQAyACwAIABMAG8AbwBrAHUAcABBAHIAcgBhAHkAMgAsACAAUgBlAHQAdQByAG4AQQByAHIAYQB5ACkAXABuACAAIAAgACAAIAAgACAAIAApACwAXABuACAAIAAgACAAIAAgACAAIABJAEYAKABJAFMATwBNAEkAVABUAEUARAAoAFYAYQBsAHUAZQBJAGYARgBhAGwAcwBlACkALAAgAFwAIgBcACIALAAgAFYAYQBsAHUAZQBJAGYARgBhAGwAcwBlACkAXABuACAAIAAgACAAKQBcAG4AKQA7AFwAbgBcAG4AVQB0AGkAbABpAHQAeQBfAFMAcABsAGkAdABTAHQAcgBpAG4AZwBJAG4AdABvAEEAcgByAGEAeQBcAG4APQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAEMAZQBsAGwALAAgAEQAZQBsAGkAbQBpAHQAZQByACwAIABbAEMAaABhAHIAYQBjAHQAZQByAFQAbwBSAGUAbQBvAHYAZQAxAF0ALAAgAFsAQwBoAGEAcgBhAGMAdABlAHIAVABvAFIAZQBtAG8AdgBlADIAXQAsAFwAbgAgACAAIAAgACAAIAAgACAARgBJAEwAVABFAFIAWABNAEwAKABcAG4AIAAgACAAIAAgACAAIAAgAFwAIgA8AHQAPgA8AHMAPgBcACIAIAAmAFwAbgAgACAAIAAgACAAIAAgACAAUwBVAEIAUwBUAEkAVABVAFQARQAoAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIABTAFUAQgBTAFQASQBUAFUAVABFACgAUwBVAEIAUwBUAEkAVABVAFQARQAoAEMAZQBsAGwALABDAGgAYQByAGEAYwB0AGUAcgBUAG8AUgBlAG0AbwB2AGUAMQAsAFwAIgBcACIAKQAsAEMAaABhAHIAYQBjAHQAZQByAFQAbwBSAGUAbQBvAHYAZQAyACwAXAAiAFwAIgApACwAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgAEQAZQBsAGkAbQBpAHQAZQByACwAXAAiADwALwBzAD4APABzAD4AXAAiAFwAbgAgACAAIAAgACAAIAAgACAAKQAgACYAXABuACAAIAAgACAAIAAgACAAIABcACIAPAAvAHMAPgA8AC8AdAA+AFwAIgAsAFwAbgAgACAAIAAgACAAIAAgACAAXAAiAC8ALwBzAFwAIgBcAG4AIAAgACAAIAApAFwAbgApADsAXABuAFwAbgBVAHQAaQBsAGkAdAB5AF8ARwBlAHQAQwBsAGkAbQBhAHQAZQBaAG8AbgBlAFwAbgA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAAYQB2AGcAVABlAG0AcAAsAGEAdgBnAFIAYQBpAG4ALABmAHIAbwBzAHQARABhAHkAcwAsAGUAbABlAHYALABtAGEAcABfAHAAZQB0ACwAXABuACAAIAAgACAAbQBpAG4AVABlAG0AcABBAHIAcgBhAHkALABtAGEAeABUAGUAbQBwAEEAcgByAGEAeQAsAFwAbgAgACAAIAAgAG0AaQBuAFIAYQBpAG4AZgBhAGwAbABBAHIAcgBhAHkALABtAGEAeABSAGEAaQBuAGYAYQBsAGwAQQByAHIAYQB5ACwAXABuACAAIAAgACAAbQBpAG4ARgByAG8AcwB0AEEAcgByAGEAeQAsAG0AYQB4AEYAcgBvAHMAdABBAHIAcgBhAHkALABcAG4AIAAgACAAIABtAGkAbgBFAGwAZQB2AGEAdABpAG8AbgBBAHIAcgBhAHkALABtAGEAeABFAGwAZQB2AGEAdABpAG8AbgBBAHIAcgBhAHkALABcAG4AIAAgACAAIABtAGkAbgBQAEUAVABBAHIAcgBhAHkALABtAGEAeABQAEUAVABBAHIAcgBhAHkALABcAG4AIAAgACAAIABjAGwAaQBtAGEAdABlAFoAbwBuAGUAQQByAHIAYQB5ACwAXABuACAAIAAgACAATABFAFQAKABcAG4AIAAgACAAIAAgACAAIAAgAG0AYQBzAGsALABcAG4AIAAgACAAIAAgACAAIAAgACgAVgBBAEwAVQBFACgAbQBpAG4AVABlAG0AcABBAHIAcgBhAHkAKQA8AD0AYQB2AGcAVABlAG0AcAApACoAXABuACAAIAAgACAAIAAgACAAIAAoAFYAQQBMAFUARQAoAG0AYQB4AFQAZQBtAHAAQQByAHIAYQB5ACkAPgA9AGEAdgBnAFQAZQBtAHAAKQAqAFwAbgAgACAAIAAgACAAIAAgACAAKABWAEEATABVAEUAKABtAGkAbgBSAGEAaQBuAGYAYQBsAGwAQQByAHIAYQB5ACkAPAA9AGEAdgBnAFIAYQBpAG4AKQAqAFwAbgAgACAAIAAgACAAIAAgACAAKABWAEEATABVAEUAKABtAGEAeABSAGEAaQBuAGYAYQBsAGwAQQByAHIAYQB5ACkAPgA9AGEAdgBnAFIAYQBpAG4AKQAqAFwAbgAgACAAIAAgACAAIAAgACAAKABWAEEATABVAEUAKABtAGkAbgBGAHIAbwBzAHQAQQByAHIAYQB5ACkAPAA9AGYAcgBvAHMAdABEAGEAeQBzACkAKgBcAG4AIAAgACAAIAAgACAAIAAgACgAVgBBAEwAVQBFACgAbQBhAHgARgByAG8AcwB0AEEAcgByAGEAeQApAD4APQBmAHIAbwBzAHQARABhAHkAcwApACoAXABuACAAIAAgACAAIAAgACAAIAAoAFYAQQBMAFUARQAoAG0AaQBuAEUAbABlAHYAYQB0AGkAbwBuAEEAcgByAGEAeQApADwAPQBlAGwAZQB2ACkAKgBcAG4AIAAgACAAIAAgACAAIAAgACgAVgBBAEwAVQBFACgAbQBhAHgARQBsAGUAdgBhAHQAaQBvAG4AQQByAHIAYQB5ACkAPgA9AGUAbABlAHYAKQAqAFwAbgAgACAAIAAgACAAIAAgACAAKABWAEEATABVAEUAKABtAGkAbgBQAEUAVABBAHIAcgBhAHkAKQA8AD0AbQBhAHAAXwBwAGUAdAApACoAXABuACAAIAAgACAAIAAgACAAIAAoAFYAQQBMAFUARQAoAG0AYQB4AFAARQBUAEEAcgByAGEAeQApAD4APQBtAGEAcABfAHAAZQB0ACkALABcAG4AIAAgACAAIAAgACAAIAAgAFQAQQBLAEUAKABcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAARgBJAEwAVABFAFIAKABjAGwAaQBtAGEAdABlAFoAbwBuAGUAQQByAHIAYQB5ACwAbQBhAHMAawAsACAAXAAiAE4AbwAgAG0AYQB0AGMAaABcACIAKQAsAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIAAxAFwAbgAgACAAIAAgACAAIAAgACAAKQBcAG4AIAAgACAAIAApAFwAbgApADsAXABuAFwAbgBVAHQAaQBsAGkAdAB5AF8ATABvAG8AawB1AHAASQB0AGUAbQBGAHIAbwBtAE0AaQBuAE0AYQB4AFwAbgA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAATABvAG8AawB1AHAAVgBhAGwAdQBlACwAIABNAGkAbgBBAHIAcgBhAHkALAAgAE0AYQB4AEEAcgByAGEAeQAsACAASQB0AGUAbQBBAHIAcgBhAHkALABcAG4AIAAgACAAIABMAEUAVAAoAFwAbgAgACAAIAAgACAAIAAgACAAbQBhAHMAawAsAFwAbgAgACAAIAAgACAAIAAgACAAKABWAEEATABVAEUAKABNAGkAbgBBAHIAcgBhAHkAKQA8AD0ATABvAG8AawB1AHAAVgBhAGwAdQBlACkAKgBcAG4AIAAgACAAIAAgACAAIAAgACgAVgBBAEwAVQBFACgATQBhAHgAQQByAHIAYQB5ACkAPgA9AEwAbwBvAGsAdQBwAFYAYQBsAHUAZQApACwAXABuACAAIAAgACAAIAAgACAAIABGAEkATABUAEUAUgAoAEkAdABlAG0AQQByAHIAYQB5ACwAIABtAGEAcwBrACwAIABcACIATgBvACAAbQBhAHQAYwBoAFwAIgApAFwAbgAgACAAIAAgACkAXABuACkAOwBcAG4AXABuAFwAbgBVAHQAaQBsAGkAdAB5AF8AUwB1AG0AUQB1AGEAbgB0AGkAdAB5AEYAcgBvAG0AQwByAGkAdABlAHIAaQBhAFwAbgA9AEwAQQBNAEIARABBACgAXABuACAAIABDAHIAaQB0AGUAcgBpAGEAMQAsACAAQwByAGkAdABlAHIAaQBhADEAVAB5AHAAZQBBAHIAcgBhAHkALAAgAFEAdQBhAG4AdABpAHQAeQAsACAAWwBNAHUAbAB0AGkAcABsAGkAZQByAF0ALAAgAFsAQwByAGkAdABlAHIAaQBhADIAXQAsAFsAQwByAGkAdABlAHIAaQBhADIAQQByAHIAYQB5AF0ALABcAG4AIAAgAEwARQBUACgAXABuACAAIAAgACAAbQB1AGwAdABpAHAAbABpAGUAcgAsACAASQBGACgASQBTAE8ATQBJAFQAVABFAEQAKABNAHUAbAB0AGkAcABsAGkAZQByACkALAAxACwATQB1AGwAdABpAHAAbABpAGUAcgApACwAXABuACAAIAAgACAAcQB1AGEAbgB0AGkAdAB5ACwAIABRAHUAYQBuAHQAaQB0AHkAKgBNAHUAbAB0AGkAcABsAGkAZQByACwAXABuACAAIAAgACAAYwByAGkAdABlAHIAaQBhADEALAAtAC0AKABDAHIAaQB0AGUAcgBpAGEAMQBUAHkAcABlAEEAcgByAGEAeQA9AEMAcgBpAHQAZQByAGkAYQAxACkALABcAG4AIAAgACAAIABjAHIAaQB0AGUAcgBpAGEAMgAsAEkARgAoAEkAUwBPAE0ASQBUAFQARQBEACgAQwByAGkAdABlAHIAaQBhADIAKQAsADEALAAtAC0AKABDAHIAaQB0AGUAcgBpAGEAMgBBAHIAcgBhAHkAPQBDAHIAaQB0AGUAcgBpAGEAMgApACkALABcAG4AIAAgACAAIABTAFUATQBQAFIATwBEAFUAQwBUACgAYwByAGkAdABlAHIAaQBhADEAKgBjAHIAaQB0AGUAcgBpAGEAMgAqAHEAdQBhAG4AdABpAHQAeQApAFwAbgAgACAAKQBcAG4AKQA7AFwAbgBcAG4AZwBlAHQATwB2AGUAcgBsAGEAcABwAGkAbgBnAFIAZQBwAG8AcgB0AGkAbgBnAEMAeQBjAGwAZQBzAFwAbgA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAAUAByAG8AZAB1AGMAdABpAG8AbgBDAHkAYwBsAGUAUwB0AGEAcgB0ACwAUAByAG8AZAB1AGMAdABpAG8AbgBDAHkAYwBsAGUARQBuAGQALABSAGUAcABvAHIAdABpAG4AZwBDAHkAYwBsAGUAUwB0AGEAcgB0ACwAXABuACAAIAAgACAATABFAFQAKABcAG4AIAAgACAAIAAgACAAIAAgAFMALABQAHIAbwBkAHUAYwB0AGkAbwBuAEMAeQBjAGwAZQBTAHQAYQByAHQALABcAG4AIAAgACAAIAAgACAAIAAgAEUALABQAHIAbwBkAHUAYwB0AGkAbwBuAEMAeQBjAGwAZQBFAG4AZAAsAFwAbgAgACAAIAAgACAAIAAgACAAbQAsAE0ATwBOAFQASAAoAFIAZQBwAG8AcgB0AGkAbgBnAEMAeQBjAGwAZQBTAHQAYQByAHQAKQAsAFwAbgAgACAAIAAgACAAIAAgACAAZAAsAEQAQQBZACgAUgBlAHAAbwByAHQAaQBuAGcAQwB5AGMAbABlAFMAdABhAHIAdAApACwAXABuACAAIAAgACAAIAAgACAAIABQAGUAcgBpAG8AZABFAG4AZAAsAEwAQQBNAEIARABBACgAcwB0ACwARQBEAEEAVABFACgAcwB0ACwAMQAyACkALQAxACkALABcAG4AIAAgACAAIAAgACAAIAAgAEEALABTAC0AMwA2ADUALABcAG4AIAAgACAAIAAgACAAIAAgAHkAYQAsAFkARQBBAFIAKABBACkALABcAG4AIAAgACAAIAAgACAAIAAgAHkAYgAsAFkARQBBAFIAKABFACkALABcAG4AIAAgACAAIAAgACAAIAAgAGYAaQByAHMAdABZAGUAYQByACwAeQBhACsAKABQAGUAcgBpAG8AZABFAG4AZAAoAEQAQQBUAEUAKAB5AGEALABtACwAZAApACkAPAAgAFMAKQAsAFwAbgAgACAAIAAgACAAIAAgACAAbABhAHMAdABZAGUAYQByACwAeQBiAC0AKABEAEEAVABFACgAeQBiACwAbQAsAGQAKQA+ACAARQApACwAXABuACAAIAAgACAAIAAgACAAIABNAEEAWAAoADAALABsAGEAcwB0AFkAZQBhAHIALQBmAGkAcgBzAHQAWQBlAGEAcgArADEAKQBcAG4AIAAgACAAIAApAFwAbgApADsAXABuAFwAbgBnAGUAdABPAHYAZQByAGwAYQBwAHAAaQBuAGcAUgBlAHAAbwByAHQAaQBuAGcAUABlAHIAaQBvAGQAcwBcAG4APQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAFAAcgBvAGQAdQBjAHQAaQBvAG4AQwB5AGMAbABlAFMAdABhAHIAdAAsAFAAcgBvAGQAdQBjAHQAaQBvAG4AQwB5AGMAbABlAEUAbgBkACwAUgBlAHAAbwByAHQAaQBuAGcAQwB5AGMAbABlAFMAdABhAHIAdAAsAFwAbgAgACAAIAAgAEwARQBUACgAXABuACAAIAAgACAAIAAgACAAIABTACwAUAByAG8AZAB1AGMAdABpAG8AbgBDAHkAYwBsAGUAUwB0AGEAcgB0ACwAXABuACAAIAAgACAAIAAgACAAIABFACwAUAByAG8AZAB1AGMAdABpAG8AbgBDAHkAYwBsAGUARQBuAGQALABcAG4AIAAgACAAIAAgACAAIAAgAG0ALABNAE8ATgBUAEgAKABSAGUAcABvAHIAdABpAG4AZwBDAHkAYwBsAGUAUwB0AGEAcgB0ACkALABcAG4AIAAgACAAIAAgACAAIAAgAGQALABEAEEAWQAoAFIAZQBwAG8AcgB0AGkAbgBnAEMAeQBjAGwAZQBTAHQAYQByAHQAKQAsACAALwAqAGgAZQBsAHAAZQByADoAIABlAG4AZAAgAGQAYQB0AGUAIABmAG8AcgAgAGEAIAByAGUAcABvAHIAdABpAG4AZwAgAHAAZQByAGkAbwBkACAAcwB0AGEAcgB0AGkAbgBnACAAYQB0ACAAYQAgAGcAaQB2AGUAbgAgAGQAYQB0AGUAKgAvAFwAbgAgACAAIAAgACAAIAAgACAAUABlAHIAaQBvAGQARQBuAGQALABMAEEATQBCAEQAQQAoAHMAdAAsAEUARABBAFQARQAoAHMAdAAsADEAMgApAC0AMQApACwAIAAvACoAbwBuAGwAeQAgAG4AZQBlAGQAIAB0AG8AIABsAG8AbwBrACAAYgBhAGMAawAgADMANgA1ACAAZABhAHkAcwAoAG0AYQB4ACAAbwB2AGUAcgBsAGEAcAAgAHcAaQBuAGQAbwB3ACkAKgAvAFwAbgAgACAAIAAgACAAIAAgACAAQQAsAFMALQAzADYANQAsAFwAbgAgACAAIAAgACAAIAAgACAAeQBhACwAWQBFAEEAUgAoAEEAKQAsAFwAbgAgACAAIAAgACAAIAAgACAAeQBiACwAWQBFAEEAUgAoAEUAKQAsACAALwAqAGkAZgAgAHQAaABlACAAYQBuAGMAaABvAHIAIABmAG8AcgAgAHkAYQAgAGUAbgBkAHMAIABiAGUAZgBvAHIAZQAgAFMALABpAHQAIABjAGEAbgAnAHQAIABvAHYAZQByAGwAYQBwADsAIABtAG8AdgBlACAAdABvACAAbgBlAHgAdAAgAHkAZQBhAHIAKgAvAFwAbgAgACAAIAAgACAAIAAgACAAZgBpAHIAcwB0AFkAZQBhAHIALAB5AGEAKwAoAFAAZQByAGkAbwBkAEUAbgBkACgARABBAFQARQAoAHkAYQAsAG0ALABkACkAKQA8AFMAKQAsACAALwAqAGkAZgAgAHQAaABlACAAYQBuAGMAaABvAHIAIABmAG8AcgAgAHkAYgAgAHMAdABhAHIAdABzACAAYQBmAHQAZQByACAARQAsAGkAdAAgAGMAYQBuACcAdAAgAG8AdgBlAHIAbABhAHAAOwAgAG0AbwB2AGUAIAB0AG8AIABwAHIAZQB2AGkAbwB1AHMAIAB5AGUAYQByACoALwBcAG4AIAAgACAAIAAgACAAIAAgAGwAYQBzAHQAWQBlAGEAcgAsAHkAYgAtACgARABBAFQARQAoAHkAYgAsAG0ALABkACkAPgBFACkALABcAG4AIAAgACAAIAAgACAAIAAgAG4ALABNAEEAWAAoADAALABsAGEAcwB0AFkAZQBhAHIALQBmAGkAcgBzAHQAWQBlAGEAcgArADEAKQAsAFwAbgAgACAAIAAgACAAIAAgACAAeQByAHMALABTAEUAUQBVAEUATgBDAEUAKABuACwAMQAsAGYAaQByAHMAdABZAGUAYQByACwAMQApACwAXABuACAAIAAgACAAIAAgACAAIABzAHQAYQByAHQAcwAsAEQAQQBUAEUAKAB5AHIAcwAsAG0ALABkACkALABcAG4AIAAgACAAIAAgACAAIAAgAGUAbgBkAHMALABNAEEAUAAoAHMAdABhAHIAdABzACwAUABlAHIAaQBvAGQARQBuAGQAKQAsAFwAbgAgACAAIAAgACAAIAAgACAAdABhAGcALABJAEYAKABzAHQAYQByAHQAcwA9AFIAZQBwAG8AcgB0AGkAbgBnAEMAeQBjAGwAZQBTAHQAYQByAHQALABcACIAIAAoAFQAaABpAHMAIAByAGUAcABvAHIAdABpAG4AZwAgAGMAeQBjAGwAZQApAFwAIgAsAFwAIgBcACIAKQAsAFwAbgAgACAAIAAgACAAIAAgACAAcwB0AGEAcgB0AHMAVABlAHgAdAAsAFQARQBYAFQAKABzAHQAYQByAHQAcwAsAFwAIgBkAGQAIABtAG0AbQAgAHkAeQB5AHkAXAAiACkALABcAG4AIAAgACAAIAAgACAAIAAgAGUAbgBkAHMAVABlAHgAdAAsAFQARQBYAFQAKABlAG4AZABzACwAXAAiAGQAZAAgAG0AbQBtACAAeQB5AHkAeQBcACIAKQAsAFwAbgAgACAAIAAgACAAIAAgACAAcgBvAHcAcwAsAEkARgAoAG4APQAwACwAXAAiAFwAIgAsAEgAUwBUAEEAQwBLACgAcwB0AGEAcgB0AHMAVABlAHgAdAAgACYAIABcACIAIAB0AG8AIABcACIAIAAmACAAZQBuAGQAcwBUAGUAeAB0ACAAJgAgAHQAYQBnACkAKQAsAFwAbgAgACAAIAAgACAAIAAgACAAcgBvAHcAcwBcAG4AIAAgACAAIAApAFwAbgApADsAXABuAFwAbgBcAG4AVQB0AGkAbABpAHQAeQBfAEQAaQBzAHAAbABhAHkARgB1AG4AYwB0AGkAbwBuAE4AYQBtAGUAXABuAD0ATABBAE0AQgBEAEEAKABGAHUAbgBjAHQAaQBvAG4ALAAgAFQARQBYAFQAQgBFAEYATwBSAEUAKABGAE8AUgBNAFUATABBAFQARQBYAFQAKABGAHUAbgBjAHQAaQBvAG4AKQAsACAAXAAiACgAXAAiACkAKQA7AFwAbgBcAG4AVQB0AGkAbABpAHQAeQBfAEwAbwBvAGsAdQBwAE4AMgBPAEUARgBGAHIAbwBtAFAAcgBvAGQASQByAHIAaQBnAGEAdABpAG8AbgBSAGEAaQBuAGYAYQBsAGwAXABuAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABQAHIAbwBkAHUAYwB0AGkAbwBuAFMAeQBzAHQAZQBtACwAIABJAHIAcgBpAGcAYQB0AGkAbwBuAE0AZQB0AGgAbwBkACwAIABSAGEAaQBuAGYAYQBsAGwAWgBvAG4AZQAsAFwAbgAgACAAIAAgAFAAcgBvAGQAdQBjAHQAaQBvAG4AUwB5AHMAdABlAG0AQQByAHIAYQB5ACwAIABJAHIAcgBpAGcAYQB0AGkAbwBuAE0AZQB0AGgAbwBkAEEAcgByAGEAeQAsACAAUgBhAGkAbgBmAGEAbABsAFoAbwBuAGUAQQByAHIAYQB5ACwAUgBlAHQAdQByAG4AQQByAHIAYQB5ACwAXABuACAAIAAgACAATABFAFQAKABcAG4AIAAgACAAIAAgACAAIAAgAEkAcgByAGkAZwBhAHQAaQBvAG4ATQBlAHQAaABvAGQALAAgAEkARgAoAEkAcgByAGkAZwBhAHQAaQBvAG4ATQBlAHQAaABvAGQAPQBcACIATgBvAHQAIABpAHIAcgBpAGcAYQB0AGUAZABcACIALAAgAFwAIgBOAG8AdAAgAGkAcgByAGkAZwBhAHQAZQBkAFwAIgAsACAAXAAiAEEAbgB5AFwAIgApACwAXABuACAAIAAgACAAIAAgACAAIABSAGEAaQBuAGYAYQBsAGwAWgBvAG4AZQAsACAASQBGACgASQByAHIAaQBnAGEAdABpAG8AbgBNAGUAdABoAG8AZAAgAD0AIABcACIATgBvAHQAIABpAHIAcgBpAGcAYQB0AGUAZABcACIALAAgAFIAYQBpAG4AZgBhAGwAbABaAG8AbgBlACwAIABcACIAQQBuAHkAXAAiACkALABcAG4AIAAgACAAIAAgACAAIAAgAFgATABPAE8ASwBVAFAAKAAxACwAIABcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAKABQAHIAbwBkAHUAYwB0AGkAbwBuAFMAeQBzAHQAZQBtAEEAcgByAGEAeQA9AFAAcgBvAGQAdQBjAHQAaQBvAG4AUwB5AHMAdABlAG0AKQAqAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIAAoAEkAcgByAGkAZwBhAHQAaQBvAG4ATQBlAHQAaABvAGQAQQByAHIAYQB5AD0ASQByAHIAaQBnAGEAdABpAG8AbgBNAGUAdABoAG8AZAApACoAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgACgAUgBhAGkAbgBmAGEAbABsAFoAbwBuAGUAQQByAHIAYQB5AD0AUgBhAGkAbgBmAGEAbABsAFoAbwBuAGUAKQAsACAAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgAFIAZQB0AHUAcgBuAEEAcgByAGEAeQApAFwAbgAgACAAIAAgACkAXABuACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAEMAcgBvAHAAcABpAG4AZwBfAEcAZQB0AEYAcgBhAGMAVwBFAFQAXABuAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABMAGUAYQBjAGgAaQBuAGcAWgBvAG4AZQAsAFwAbgAgACAAIAAgAFAAcgBvAGQAdQBjAHQAaQBvAG4AUwB5AHMAdABlAG0ALABcAG4AIAAgACAAIABMAGUAYQBjAGgAaQBuAGcAWgBvAG4AZQBMAG8AbwBrAHUAcAAsAFwAbgAgACAAIAAgAEwAZQBhAGMAaABpAG4AZwBaAG8AbgBlAEYAcgBhAGMAVwBFAFQATABvAG8AawB1AHAALABcAG4AIAAgACAAIABQAHIAbwBkAHUAYwB0AGkAbwBuAFMAeQBzAHQAZQBtAEwAbwBvAGsAdQBwACwAXABuACAAIAAgACAAUAByAG8AZAB1AGMAdABpAG8AbgBTAHkAcwB0AGUAbQBGAHIAYQBjAFcARQBUAEwAbwBvAGsAdQBwACwAXABuACAAIAAgACAATABFAFQAKABcAG4AIAAgACAAIAAgACAAIAAgAEwAZQBhAGMAaABpAG4AZwBaAG8AbgBlAEYAcgBhAGMAVwBFAFQALAAgAFwAbgAgACAAIAAgACAAIAAgACAAQwBvAG0AbQBvAG4AXwBJAG4AcAB1AHQARgB1AG4AYwB0AGkAbwBuAHMALgBVAHQAaQBsAGkAdAB5AF8ATABvAG8AawB1AHAAVgBhAGwAdQBlAEkAbgBUAGEAYgBsAGUATgB1AG0AYgBlAHIAKABcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAATABlAGEAYwBoAGkAbgBnAFoAbwBuAGUALABMAGUAYQBjAGgAaQBuAGcAWgBvAG4AZQBMAG8AbwBrAHUAcAAsAEwAZQBhAGMAaABpAG4AZwBaAG8AbgBlAEYAcgBhAGMAVwBFAFQATABvAG8AawB1AHAAXABuACAAIAAgACAAIAAgACAAIAApACwAXABuACAAIAAgACAAIAAgACAAIABQAHIAbwBkAHUAYwB0AGkAbwBuAFMAeQBzAHQAZQBtAEYAcgBhAGMAVwBFAFQALAAgAFwAbgAgACAAIAAgACAAIAAgACAAQwBvAG0AbQBvAG4AXwBJAG4AcAB1AHQARgB1AG4AYwB0AGkAbwBuAHMALgBVAHQAaQBsAGkAdAB5AF8ATABvAG8AawB1AHAAVgBhAGwAdQBlAEkAbgBUAGEAYgBsAGUATgB1AG0AYgBlAHIAKABcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAUAByAG8AZAB1AGMAdABpAG8AbgBTAHkAcwB0AGUAbQAsAFAAcgBvAGQAdQBjAHQAaQBvAG4AUwB5AHMAdABlAG0ATABvAG8AawB1AHAALABQAHIAbwBkAHUAYwB0AGkAbwBuAFMAeQBzAHQAZQBtAEYAcgBhAGMAVwBFAFQATABvAG8AawB1AHAAXABuACAAIAAgACAAIAAgACAAIAApACwAXABuACAAIAAgACAAIAAgACAAIABJAEYAKABMAGUAYQBjAGgAaQBuAGcAWgBvAG4AZQBGAHIAYQBjAFcARQBUACAAKwAgAFAAcgBvAGQAdQBjAHQAaQBvAG4AUwB5AHMAdABlAG0ARgByAGEAYwBXAEUAVAA+ADAALAAgADEALAAgADAAKQBcAG4AIAAgACAAIAApACkAOwBcAG4AXABuAFwAbgBVAHQAaQBsAGkAdAB5AF8AQwBvAG4AdgBlAHIAdABTAHQAYQB0AGUAQwBvAG0AbQBvAG4ATgBhAG0AZQBUAG8AQQBiAGIAcgBlAHYAaQBhAHQAaQBvAG4AXABuAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABTAHQAYQB0AGUAQwBvAG0AbQBvAG4ATgBhAG0AZQAsAFwAbgAgACAAIAAgAFMAdABhAHQAZQBDAG8AbQBtAG8AbgBOAGEAbQBlAEEAcgByAGEAeQAsACAAUwB0AGEAdABlAEEAYgBiAHIAZQB2AGkAYQB0AGkAbwBuAEEAcgByAGEAeQAsAFwAbgAgACAAIAAgAFgATABPAE8ASwBVAFAAKABTAHQAYQB0AGUAQwBvAG0AbQBvAG4ATgBhAG0AZQAsACAAUwB0AGEAdABlAEMAbwBtAG0AbwBuAE4AYQBtAGUAQQByAHIAYQB5ACwAIABTAHQAYQB0AGUAQQBiAGIAcgBlAHYAaQBhAHQAaQBvAG4AQQByAHIAYQB5ACwAIABcACIAXAAiACkAXABuACkAOwBcAG4AXABuAFUAdABpAGwAaQB0AHkAXwBTAG8AdQByAGMAZQBIAHkAcABlAHIAbABpAG4AawBcAG4APQBMAEEATQBCAEQAQQAoAFQAYQByAGcAZQB0AEMAZQBsAGwALABcAG4AIAAgAEwARQBUACgAXABuACAAIAAgACAAcwBoACwAIABUAEUAWABUAEEARgBUAEUAUgAoAEMARQBMAEwAKABcACIAZgBpAGwAZQBuAGEAbQBlAFwAIgAsACAAVABhAHIAZwBlAHQAQwBlAGwAbAApACwAIABcACIAXQBcACIAKQAsAFwAbgAgACAAIAAgAGEAZABkAHIALAAgAEMARQBMAEwAKABcACIAYQBkAGQAcgBlAHMAcwBcACIALAAgAFQAYQByAGcAZQB0AEMAZQBsAGwAKQAsAFwAbgAgACAAIAAgAFwAIgAjACcAXAAiACAAJgAgAHMAaAAgACYAIABcACIAJwAhAFwAIgAgACYAIABhAGQAZAByAFwAbgAgACAAKQBcAG4AKQA7AFwAbgBcAG4AVQB0AGkAbABpAHQAeQBfAFMAbwB1AHIAYwBlAEgAeQBwAGUAcgBsAGkAbgBrAEQAaQBmAGYAZQByAGUAbgB0AFMAaABlAGUAdABcAG4APQBMAEEATQBCAEQAQQAoAFQAYQByAGcAZQB0AEMAZQBsAGwALABcAG4AIAAgAEwARQBUACgAXABuACAAIAAgACAAcwBoACwAIABUAEUAWABUAEEARgBUAEUAUgAoAEMARQBMAEwAKABcACIAZgBpAGwAZQBuAGEAbQBlAFwAIgAsACAAVABhAHIAZwBlAHQAQwBlAGwAbAApACwAIABcACIAXQBcACIAKQAsAFwAbgAgACAAIAAgAGEAZABkAHIALAAgAEMARQBMAEwAKABcACIAYQBkAGQAcgBlAHMAcwBcACIALAAgAFQAYQByAGcAZQB0AEMAZQBsAGwAKQAsAFwAbgAgACAAIAAgAFwAIgAjAFwAIgAgACYAIABhAGQAZAByAFwAbgAgACAAKQBcAG4AKQA7AFwAbgBcAG4AVQB0AGkAbABpAHQAeQBfAEQAaQBzAHAAbABhAHkAQQByAGcAdQBtAGUAbgB0AHMAXwAxAF8AMgBcAG4APQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAEEAcgBnAHUAbQBlAG4AdABzAEEAcgByAGEAeQAsAFwAbgAgACAAIAAgAEMASABPAE8AUwBFAEMATwBMAFMAKABBAHIAZwB1AG0AZQBuAHQAcwBBAHIAcgBhAHkALAAgADEALAAgADIAKQBcAG4AKQA7AFwAbgBcAG4AVQB0AGkAbABpAHQAeQBfAEQAaQBzAHAAbABhAHkAQQByAGcAdQBtAGUAbgB0AHMAXwAzAF8ANABcAG4APQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAEEAcgBnAHUAbQBlAG4AdABzAEEAcgByAGEAeQAsAFwAbgAgACAAIAAgAEMASABPAE8AUwBFAEMATwBMAFMAKABBAHIAZwB1AG0AZQBuAHQAcwBBAHIAcgBhAHkALAAgADMALAAgADQAKQBcAG4AKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBHAGUAdABNAEMARgBUAGUAbQBwAGUAcgBhAHQAdQByAGUAWgBvAG4AZQBcAG4APQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAFQAZQBtAHAAZQByAGEAdAB1AHIAZQAsACAATQBNAFMALAAgAFQAZQBtAHAAZQByAGEAdAB1AHIAZQBBAHIAcgBhAHkALAAgAE0ATQBTAEEAcgByAGEAeQAsACAAUgBlAHQAdQByAG4AQQByAHIAYQB5ACwAXABuACAAIAAgACAAWABMAE8ATwBLAFUAUAAoAFwAbgAgACAAIAAgACAAIAAgACAATQBFAEQASQBBAE4AKABcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAVABlAG0AcABlAHIAYQB0AHUAcgBlACwAIABcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAATQBJAE4AKABUAGUAbQBwAGUAcgBhAHQAdQByAGUAQQByAHIAYQB5ACkALAAgAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIABNAEEAWAAoAFQAZQBtAHAAZQByAGEAdAB1AHIAZQBBAHIAcgBhAHkAKQBcAG4AIAAgACAAIAAgACAAIAAgACkALABcAG4AIAAgACAAIAAgACAAIAAgAFQAZQBtAHAAZQByAGEAdAB1AHIAZQBBAHIAcgBhAHkALABcAG4AIAAgACAAIAAgACAAIAAgAFgATABPAE8ASwBVAFAAKABNAE0AUwAsACAATQBNAFMAQQByAHIAYQB5ACwAIABSAGUAdAB1AHIAbgBBAHIAcgBhAHkAKQBcAG4AIAAgACAAIAApAFwAbgApADsAXABuAFwAbgBcAG4AVQB0AGkAbABpAHQAeQBfAFIAZQBzAHUAbAB0AHMASQB0AGUAbQBGAHIAbwBtAEUAcQB1AGEAdABpAG8AbgBUAGkAdABsAGUAQQBuAGQAUwBvAHUAcgBjAGUAXABuAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABUAGkAdABsAGUAQwBlAGwAbAAsACAAUwBvAHUAcgBjAGUAQwBlAGwAbAAsAFwAbgAgACAAIAAgAFMAVQBCAFMAVABJAFQAVQBUAEUAKABMAEUARgBUACgAUwBvAHUAcgBjAGUAQwBlAGwAbAAsACAARgBJAE4ARAAoAFwAIgAsAFwAIgAsACAAUwBvAHUAcgBjAGUAQwBlAGwAbAApACAALQAxACkALAAgAFwAIgBWAEUARQBSAEcAIAAyADAAMgA2ADoAIABcACIALAAgAFwAIgBcACIAKQAgACYAIABcACIAIABcACIAIAAmACAAVABpAHQAbABlAEMAZQBsAGwAXABuACkAOwAiAH0ALAB7ACIAcABhAHQAaAAiADoAIgAvAHAAcgBvAGoAZQBjAHQAcwAvAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAiACwAIgB0AGUAeAB0ACIAOgAiAC8AKgBcAG4APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQBcAG4APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQBcAG4AUwBvAHUAcgBjAGUAIABkAGEAdABhACAAdABoAGEAdAAgAGkAcwAgAGMAbwBtAG0AbwBuACAAYQBjAHIAbwBzAHMAIABhAGwAbAAgAGUAbgB0AGUAcgBwAHIAaQBzAGUAIAB0AHkAcABlAHMAXABuAEUAeABjAGUAbAAgAG0AbwBkAHUAbABlACAAbgBhAG0AZQA6ACAAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAFwAbgA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AFwAbgA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AFwAbgAqAC8AXABuAFwAbgAvACoAXABuAD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQBcAG4APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AFwAbgBTAG8AdQByAGMAZQA6ACAATgBhAHQAaQBvAG4AYQBsACAASQBuAHYAZQBuAHQAbwByAHkAIABSAGUAcABvAHIAdAAgADIAMAAyADMAIABWAG8AbAB1AG0AZQAgADEAXABuAE4ASQBSAF8AMgAwADIAMwBfAFYAbwBsADEAXABuAD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQBcAG4APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AFwAbgAqAC8AXABuAFwAbgAvACoAIABcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGUAbgBzAGkAdAB5AE8AZgBNAGUAdABoAGEAbgBlAFwAbgBwACAAPQAgAGQAZQBuAHMAaQB0AHkAIABvAGYAIABtAGUAdABoAGEAbgBlACAAKAAwAC4ANgA3ADgANAAgAGsAZwAvAG0AMwApAFwAbgBUAGEAawBlAG4AIABmAHIAbwBtACAAdABoAGUAIABOAGEAdABpAG8AbgBhAGwAIABHAHIAZQBlAG4AaABvAHUAcwBlACAAYQBuAGQAIABFAG4AZQByAGcAeQAgAFIAZQBwAG8AcgB0AGkAbgBnACAAXABuACgATQBlAGEAcwB1AHIAZQBtAGUAbgB0ACkAIABEAGUAdABlAHIAbQBpAG4AYQB0AGkAbwBuACAAMgAwADAAOABcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgAqAC8AXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGUAbgBzAGkAdAB5AE8AZgBNAGUAdABoAGEAbgBlAF8AVABpAHQAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBwACAAPQAgAGQAZQBuAHMAaQB0AHkAIABvAGYAIABtAGUAdABoAGEAbgBlAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGUAbgBzAGkAdAB5AE8AZgBNAGUAdABoAGEAbgBlAF8AVQBuAGkAdABcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAawBnAC8AbQAzAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGUAbgBzAGkAdAB5AE8AZgBNAGUAdABoAGEAbgBlAF8AUwBvAHUAcgBjAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAE4AYQB0AGkAbwBuAGEAbAAgAEkAbgB2AGUAbgB0AG8AcgB5ACAAUgBlAHAAbwByAHQAIAAyADAAMgAzACAAVgBvAGwAdQBtAGUAIAAxADoAIABFAHEAdQBhAHQAaQBvAG4AcwAgADMALgBCAC4AMQBhAF8AMgAsACAAMwAuAEIALgAxAGMAXwAyACwAIAAzAC4AQgAuADMAXwAxACwAIAAzAC4AQgAuADQAZwBfADIAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEQAZQBuAHMAaQB0AHkATwBmAE0AZQB0AGgAYQBuAGUAXwBEAGEAdABhAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoADAALgA2ADcAOAA0ACkAOwBcAG4AXABuAC8AKgAgAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEMAbwBuAHYAZQByAHQATgAyAG8ARQBsAGUAbQBlAG4AdABhAGwAVABvAE0AbwBsAGUAYwB1AGwAYQByAEMAZwBcAG4AQwBnACAAPQAgADQANAAvADIAOAAgAGYAYQBjAHQAbwByACAAdABvACAAYwBvAG4AdgBlAHIAdAAgAGUAbABlAG0AZQBuAHQAYQBsACAAbQBhAHMAcwAgAG8AZgAgAE4AMgBPACAAdABvACAAbQBvAGwAZQBjAHUAbABhAHIAIABtAGEAcwBzAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuACoALwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEMAbwBuAHYAZQByAHQATgAyAG8ARQBsAGUAbQBlAG4AdABhAGwAVABvAE0AbwBsAGUAYwB1AGwAYQByAEMAZwBfAFQAaQB0AGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIARgBhAGMAdABvAHIAIAB0AG8AIABjAG8AbgB2AGUAcgB0ACAAZQBsAGUAbQBlAG4AdABhAGwAIABtAGEAcwBzACAAbwBmACAATgAyAE8AIAB0AG8AIABtAG8AbABlAGMAdQBsAGEAcgAgAG0AYQBzAHMAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEMAbwBuAHYAZQByAHQATgAyAG8ARQBsAGUAbQBlAG4AdABhAGwAVABvAE0AbwBsAGUAYwB1AGwAYQByAEMAZwBfAFYAYQByAGkAYQBiAGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAQwBnAE4AMgBPAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBDAG8AbgB2AGUAcgB0AE4AMgBvAEUAbABlAG0AZQBuAHQAYQBsAFQAbwBNAG8AbABlAGMAdQBsAGEAcgBDAGcAXwBVAG4AaQB0AFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBmAGEAYwB0AG8AcgBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQwBvAG4AdgBlAHIAdABOADIAbwBFAGwAZQBtAGUAbgB0AGEAbABUAG8ATQBvAGwAZQBjAHUAbABhAHIAQwBnAF8AUwBvAHUAcgBjAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAE4AYQB0AGkAbwBuAGEAbAAgAEkAbgB2AGUAbgB0AG8AcgB5ACAAUgBlAHAAbwByAHQAIAAyADAAMgAzACAAVgBvAGwAdQBtAGUAIAAxAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBDAG8AbgB2AGUAcgB0AE4AMgBvAEUAbABlAG0AZQBuAHQAYQBsAFQAbwBNAG8AbABlAGMAdQBsAGEAcgBDAGcAXwBEAGEAdABhAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoADQANAAvADIAOAApADsAXABuAFwAbgAvACoAIABcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBDAG8AbgB2AGUAcgB0AEcAYQBzAEUAbABlAG0AZQBuAHQAYQBsAFQAbwBNAG8AbABlAGMAdQBsAGEAcgBcAG4ARgBhAGMAdABvAHIAIAB0AG8AIABjAG8AbgB2AGUAcgB0ACAAZQBsAGUAbQBlAG4AdABhAGwAIABtAGEAcwBzACAAbwBmACAAZwBhAHMAIAB0AG8AIABtAG8AbABlAGMAdQBsAGEAcgAgAG0AYQBzAHMAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AKgAvAFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQwBvAG4AdgBlAHIAdABHAGEAcwBFAGwAZQBtAGUAbgB0AGEAbABUAG8ATQBvAGwAZQBjAHUAbABhAHIAXwBUAGkAdABsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAEYAYQBjAHQAbwByACAAdABvACAAYwBvAG4AdgBlAHIAdAAgAGUAbABlAG0AZQBuAHQAYQBsACAAbQBhAHMAcwAgAG8AZgAgAGcAYQBzACAAdABvACAAbQBvAGwAZQBjAHUAbABhAHIAIABtAGEAcwBzAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBDAG8AbgB2AGUAcgB0AEcAYQBzAEUAbABlAG0AZQBuAHQAYQBsAFQAbwBNAG8AbABlAGMAdQBsAGEAcgBfAFYAYQByAGkAYQBiAGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAQwBnAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBDAG8AbgB2AGUAcgB0AEcAYQBzAEUAbABlAG0AZQBuAHQAYQBsAFQAbwBNAG8AbABlAGMAdQBsAGEAcgBfAFUAbgBpAHQAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAGYAYQBjAHQAbwByAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBDAG8AbgB2AGUAcgB0AEcAYQBzAEUAbABlAG0AZQBuAHQAYQBsAFQAbwBNAG8AbABlAGMAdQBsAGEAcgBfAFMAbwB1AHIAYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBYAFgAWABYAFgAWABYAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBDAG8AbgB2AGUAcgB0AEcAYQBzAEUAbABlAG0AZQBuAHQAYQBsAFQAbwBNAG8AbABlAGMAdQBsAGEAcgBfAEQAYQB0AGEAXABuACAAIAA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAATQBBAEsARQBBAFIAUgBBAFkAKAA4ACwAIAA0ACwAIABcAG4AIAAgACAAIAAgACAATABBAE0AQgBEAEEAKAByACwAYwAsACAAXABuACAAIAAgACAAIAAgACAAIABJAE4ARABFAFgAKAB7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBHAGEAcwBcACIALAAgAFwAIgBDAG8AbgB2AGUAcgBzAGkAbwBuACAAZgBhAGMAdABvAHIAXAAiACwAIABcACIAQwBvAG4AdgBlAHIAcwBpAG8AbgAgAGYAYQBjAHQAbwByACAAMQBcACIALAAgAFwAIgBDAG8AbgB2AGUAcgBzAGkAbwBuACAAZgBhAGMAdABvAHIAIAAyAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBDAE8AMgBcACIALAAgAFwAIgA0ADQALwAxADIAXAAiACwAIAA0ADQALAAgADEAMgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBDAEgANABcACIALAAgAFwAIgAxADYALwAxADIAXAAiACwAIAAxADYALAAgADEAMgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBOADIATwBcACIALAAgAFwAIgA0ADQALwAyADgAXAAiACwAIAA0ADQALAAgADIAOAA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBOAG8AeABcACIALAAgAFwAIgA0ADYALwAxADQAXAAiACwAIAA0ADYALAAgADEANAA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBDAE8AXAAiACwAIABcACIAMgA4AC8AMQAyAFwAIgAsACAAMgA4ACwAIAAxADIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAQwBPADIAIABMAGkAbQBlAFwAIgAsACAAXAAiADQANAAvADEAMgBcACIALAAgADQANAAsACAAMQAyADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAE4ATQBWAE8AQwBcACIALAAgAFwAIgAxADQALwAxADIAXAAiACwAIAAxADQALAAgADEAMgBcAG4AIAAgACAAIAAgACAAIAAgAH0ALAAgAHIALAAgAGMAKQBcAG4AIAAgACAAIAAgACAAKQBcAG4AIAAgACAAIAApAFwAbgAgACAAKQA7AFwAbgBcAG4ALwAqACAAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARwBXAFAATgAyAE8AXABuAEcAbABvAGIAYQBsACAAdwBhAHIAbQBpAG4AZwAgAHAAbwB0AGUAbgB0AGkAYQBsACAAZgBvAHIAIABnAHIAZQBlAG4AaABvAHUAcwBlACAAZwBhAHMAZQBzAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuACoALwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEcAVwBQAF8AVABpAHQAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBHAGwAbwBiAGEAbAAgAHcAYQByAG0AaQBuAGcAIABwAG8AdABlAG4AdABpAGEAbAAgAGYAbwByACAAZwByAGUAZQBuAGgAbwB1AHMAZQAgAGcAYQBzAGUAcwBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARwBXAFAAXwBWAGEAcgBpAGEAYgBsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAEcAVwBQAE4AMgBPAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBHAFcAUABfAFUAbgBpAHQAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAGYAYQBjAHQAbwByAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBHAFcAUABfAFMAbwB1AHIAYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBYAFgAWABYAFgAWABYAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBHAFcAUABfAEQAYQB0AGEAXABuACAAIAA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAATQBBAEsARQBBAFIAUgBBAFkAKAA4ACwAIAAyACwAIABcAG4AIAAgACAAIAAgACAATABBAE0AQgBEAEEAKAByACwAYwAsACAAXABuACAAIAAgACAAIAAgACAAIABJAE4ARABFAFgAKAB7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBHAGEAcwBcACIALAAgAFwAIgBDAE8AMgAtAGUAIABmAGEAYwB0AG8AcgBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAQwBPADIAXAAiACwAIAAxADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEMASAA0AFwAIgAsACAAMgA4ADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAE4AMgBPAFwAIgAsACAAMgA2ADUAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAQwBGADQAXAAiACwAIAA2ADYAMwAwADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEMAMgBGADYAXAAiACwAIAAxADIAMgAwADAAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAUwBGADYAXAAiACwAIAAyADIAOAAwADAAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIATgBGADMAXAAiACwAIAAxADcAMgAwADAAXABuACAAIAAgACAAIAAgACAAIAB9ACwAIAByACwAIABjACkAXABuACAAIAAgACAAIAAgACkAXABuACAAIAAgACAAKQBcAG4AIAAgACkAOwBcAG4AXABuAFwAbgAvACoAIABcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBBAHUAcwB0AHIAYQBsAGkAYQBuAFMAdABhAHQAZQBzAFQAZQByAHIAaQB0AG8AcgBpAGUAcwBcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgAqAC8AXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBBAHUAcwB0AHIAYQBsAGkAYQBuAFMAdABhAHQAZQBzAFQAZQByAHIAaQB0AG8AcgBpAGUAcwBfAFQAaQB0AGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAQQB1AHMAdAByAGEAbABpAGEAbgAgAHMAdABhAHQAZQBzACAAYQBuAGQAIAB0AGUAcgByAGkAdABvAHIAaQBlAHMAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEEAdQBzAHQAcgBhAGwAaQBhAG4AUwB0AGEAdABlAHMAVABlAHIAcgBpAHQAbwByAGkAZQBzAF8AVgBhAHIAaQBhAGIAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQQB1AHMAdAByAGEAbABpAGEAbgBTAHQAYQB0AGUAcwBUAGUAcgByAGkAdABvAHIAaQBlAHMAXwBVAG4AaQB0AFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQQB1AHMAdAByAGEAbABpAGEAbgBTAHQAYQB0AGUAcwBUAGUAcgByAGkAdABvAHIAaQBlAHMAXwBTAG8AdQByAGMAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEEAdQBzAHQAcgBhAGwAaQBhAG4AUwB0AGEAdABlAHMAVABlAHIAcgBpAHQAbwByAGkAZQBzAF8ARABhAHQAYQBcAG4AIAAgACAAPQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAE0AQQBLAEUAQQBSAFIAQQBZACgAOQAsACAAMwAsACAAXABuACAAIAAgACAAIAAgAEwAQQBNAEIARABBACgAcgAsAGMALAAgAFwAbgAgACAAIAAgACAAIAAgACAASQBOAEQARQBYACgAewBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAUwB0AGEAdABlAC8AVABlAHIAcgBpAHQAbwByAHkAXAAiACwAIABcACIAQwBvAG0AbQBvAG4AIABOAGEAbQBlAFwAIgAsACAAXAAiAEEAYgBiAHIAZQB2AGkAYQB0AGkAbwBuAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBOAGUAdwAgAFMAbwB1AHQAaAAgAFcAYQBsAGUAcwBcACIALAAgAFwAIgBOAGUAdwAgAFMAbwB1AHQAaAAgAFcAYQBsAGUAcwBcACIALAAgAFwAIgBOAFMAVwBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAQQB1AHMAdAByAGEAbABpAGEAbgAgAEMAYQBwAGkAdABhAGwAIABUAGUAcgByAGkAdABvAHIAeQBcACIALAAgAFwAIgBBAEMAVABcACIALAAgAFwAIgBBAEMAVABcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVgBpAGMAdABvAHIAaQBhAFwAIgAsACAAXAAiAFYAaQBjAHQAbwByAGkAYQBcACIALAAgAFwAIgBWAEkAQwBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAUQB1AGUAZQBuAHMAbABhAG4AZABcACIALAAgAFwAIgBRAHUAZQBlAG4AcwBsAGEAbgBkAFwAIgAsACAAXAAiAFEATABEAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBTAG8AdQB0AGgAIABBAHUAcwB0AHIAYQBsAGkAYQBcACIALAAgAFwAIgBTAG8AdQB0AGgAIABBAHUAcwB0AHIAYQBsAGkAYQBcACIALAAgAFwAIgBTAEEAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFcAZQBzAHQAZQByAG4AIABBAHUAcwB0AHIAYQBsAGkAYQBcACIALAAgAFwAIgBXAGUAcwB0AGUAcgBuACAAQQB1AHMAdAByAGEAbABpAGEAXAAiACwAIABcACIAVwBBAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBUAGEAcwBtAGEAbgBpAGEAXAAiACwAIABcACIAVABhAHMAbQBhAG4AaQBhAFwAIgAsACAAXAAiAFQAQQBTAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBOAG8AcgB0AGgAZQByAG4AIABUAGUAcgByAGkAdABvAHIAeQBcACIALAAgAFwAIgBOAG8AcgB0AGgAZQByAG4AIABUAGUAcgByAGkAdABvAHIAeQBcACIALAAgAFwAIgBOAFQAXAAiAFwAbgAgACAAIAAgACAAIAAgACAAfQAsACAAcgAsACAAYwApAFwAbgAgACAAIAAgACAAIAApAFwAbgAgACAAIAAgACkAXABuACAAIAApADsAXABuAFwAbgAvACoAIABcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBXAEEAUwBBADQAQQByAGUAYQBzAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuACoALwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFcAQQBTAEEANABBAHIAZQBhAHMAXwBUAGkAdABsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAEEAQgBTACAAUwB0AGEAdABpAHMAdABjAGEAbAAgAEEAcgBlAGEAcwAgAEwAZQB2AGUAbAAgADQAIAAtACAAVwBlAHMAdABlAHIAbgAgAEEAdQBzAHQAcgBhAGwAaQBhAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBXAEEAUwBBADQAQQByAGUAYQBzAF8AVgBhAHIAaQBhAGIAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AVwBBAFMAQQA0AEEAcgBlAGEAcwBfAFUAbgBpAHQAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBXAEEAUwBBADQAQQByAGUAYQBzAF8AUwBvAHUAcgBjAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAEEAdQBzAHQAcgBhAGwAaQBhAG4AIABCAHUAcgBlAGEAdQAgAG8AZgAgAFMAdABhAHQAaQBzAHQAaQBjAHMAIAAoAEEAQgBTACkAIAAtACAAUwB0AGEAdABpAHMAdABpAGMAYQBsACAAQQByAGUAYQBzACAATABlAHYAZQBsACAAMgAgAC0AIAAyADAAMgAxACAALQAgAFMAaABhAHAAZQBmAGkAbABlAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBXAEEAUwBBADQAQQByAGUAYQBzAF8ARABhAHQAYQBcAG4AIAAgACAAPQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAE0AQQBLAEUAQQBSAFIAQQBZACgAMQAxACwAIAAxACwAIABcAG4AIAAgACAAIAAgACAATABBAE0AQgBEAEEAKAByACwAYwAsACAAXABuACAAIAAgACAAIAAgACAAIABJAE4ARABFAFgAKAB7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBTAEEAIAA0ACAATgBhAG0AZQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAQgB1AG4AYgB1AHIAeQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIATQBhAG4AZAB1AHIAYQBoAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBQAGUAcgB0AGgAIAAtACAASQBuAG4AZQByAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBQAGUAcgB0AGgAIAAtACAATgBvAHIAdABoACAARQBhAHMAdABcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAUABlAHIAdABoACAALQAgAE4AbwByAHQAaAAgAFcAZQBzAHQAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFAAZQByAHQAaAAgAC0AIABTAG8AdQB0AGgAIABFAGEAcwB0AFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBQAGUAcgB0AGgAIAAtACAAUwBvAHUAdABoACAAVwBlAHMAdABcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVwBlAHMAdABlAHIAbgAgAEEAdQBzAHQAcgBhAGwAaQBhACAALQAgAFcAaABlAGEAdAAgAEIAZQBsAHQAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFcAZQBzAHQAZQByAG4AIABBAHUAcwB0AHIAYQBsAGkAYQAgAC0AIABPAHUAdABiAGEAYwBrACAAKABOAG8AcgB0AGgAKQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVwBlAHMAdABlAHIAbgAgAEEAdQBzAHQAcgBhAGwAaQBhACAALQAgAE8AdQB0AGIAYQBjAGsAIAAoAFMAbwB1AHQAaAApAFwAIgBcAG4AIAAgACAAIAAgACAAIAAgAH0ALAAgAHIALAAgAGMAKQBcAG4AIAAgACAAIAAgACAAKQBcAG4AIAAgACAAIAApAFwAbgAgACAAKQA7AFwAbgBcAG4ALwAqACAAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AVwBlAHQAQQBuAGQARAByAHkAWgBvAG4AZQBzAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuACoALwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFcAZQB0AEEAbgBkAEQAcgB5AFoAbwBuAGUAcwBfAFQAaQB0AGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAVgBFAEUAUgBHACAAQQB1AHMAdAByAGEAbABpAGEAbgAgAHcAZQB0ACAAYQBuAGQAIABkAHIAeQAgAHoAbwBuAGUAcwBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AVwBlAHQAQQBuAGQARAByAHkAWgBvAG4AZQBzAF8AVgBhAHIAaQBhAGIAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AVwBlAHQAQQBuAGQARAByAHkAWgBvAG4AZQBzAF8AVQBuAGkAdABcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFcAZQB0AEEAbgBkAEQAcgB5AFoAbwBuAGUAcwBfAFMAbwB1AHIAYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBWAEUARQBSAEcAIAAyADAAMgA2ADoAIABUAGEAYgBsAGUAIAAxAC4AMgA6ACAAVAByAGEAbgBzAGwAYQB0AGkAbgBnACAAYwBsAGkAbQBhAHQAZQAgAHoAbwBuAGUAcwAgAHQAbwAgAHcAZQB0ACAAYQBuAGQAIABkAHIAeQAgAHoAbwBuAGUAcwBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AVwBlAHQAQQBuAGQARAByAHkAWgBvAG4AZQBzAF8AVgBhAHIAaQBhAHQAaQBvAG4AXABuACAAIAAgAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABNAEEASwBFAEEAUgBSAEEAWQAoADMALAAgADEALAAgAFwAbgAgACAAIAAgACAAIABMAEEATQBCAEQAQQAoAHIALABjACwAIABcAG4AIAAgACAAIAAgACAAIAAgAEkATgBEAEUAWAAoAHsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFYAQQBSAEkAQQBUAEkATwBOACAATwBGACAAUwBPAFUAUgBDAEUAIABEAEEAVABBADoAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEEAZABkAGUAZAAgAHcAYQByAG0AIAAvACAAYwBvAG8AbAAgAHQAZQBtAHAAZQByAGEAdABlACAAbQBvAGkAcwB0ACAALwAgAGQAcgB5ACAALQAgAGwAbwB3ACAAZgByAG8AcwB0ACAAYQBuAGQAIABoAGkAZwBoACAAdABlAG0AcAAgAGMAbABhAHMAcwBlAHMAIAB0AG8AIABhAGMAYwBvAG0AbQBvAGQAYQB0AGUAIABjAGwAaQBtAGEAdABlACAAcwBjAGUAbgBhAHIAaQBvAHMAIABlAHgAYwBsAHUAZABlAGQAIABiAHkAIABWAEUARQBSAEcAIABjAHIAaQB0AGUAcgBpAGEALgBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIARgBpAHgAZQBkACAAdAB5AHAAbwAgAC0AIABDAGgAYQBuAGcAZQBkACAAJwBGAHIAeQAnACAAdABvACAAJwBEAHIAeQAnAC4AXAAiAFwAbgAgACAAIAAgACAAIAAgACAAfQAsACAAcgAsACAAYwApAFwAbgAgACAAIAAgACAAIAApAFwAbgAgACAAIAAgACkAXABuACAAIAApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBXAGUAdABBAG4AZABEAHIAeQBaAG8AbgBlAHMAXwBEAGEAdABhAFwAbgAgACAAIAA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAATQBBAEsARQBBAFIAUgBBAFkAKAAxADUALAAgADIALAAgAFwAbgAgACAAIAAgACAAIABMAEEATQBCAEQAQQAoAHIALABjACwAIABcAG4AIAAgACAAIAAgACAAIAAgAEkATgBEAEUAWAAoAHsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEMAbABpAG0AYQB0AGUAIABaAG8AbgBlAFwAIgAsACAAXAAiAFcAZQB0ACAAbwByACAARAByAHkAIABaAG8AbgBlAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBUAHIAbwBwAGkAYwBhAGwAIABtAG8AbgB0AGEAbgBlAFwAIgAsACAAXAAiAFcAZQB0ACAAYwBsAGkAbQBhAHQAZQAgAHoAbwBuAGUAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFQAcgBvAHAAaQBjAGEAbAAgAHcAZQB0AFwAIgAsACAAXAAiAFcAZQB0ACAAYwBsAGkAbQBhAHQAZQAgAHoAbwBuAGUAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFQAcgBvAHAAaQBjAGEAbAAgAG0AbwBpAHMAdABcACIALAAgAFwAIgBXAGUAdAAgAGMAbABpAG0AYQB0AGUAIAB6AG8AbgBlAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBUAHIAbwBwAGkAYwBhAGwAIABkAHIAeQBcACIALAAgAFwAIgBEAHIAeQAgAGMAbABpAG0AYQB0AGUAIAB6AG8AbgBlAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBXAGEAcgBtACAAdABlAG0AcABlAHIAYQB0AGUAIABtAG8AaQBzAHQAXAAiACwAIABcACIAVwBlAHQAIABjAGwAaQBtAGEAdABlACAAegBvAG4AZQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVwBhAHIAbQAgAHQAZQBtAHAAZQByAGEAdABlACAAZAByAHkAXAAiACwAIABcACIARAByAHkAIABjAGwAaQBtAGEAdABlACAAegBvAG4AZQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAQwBvAG8AbAAgAHQAZQBtAHAAZQByAGEAdABlACAAbQBvAGkAcwB0AFwAIgAsACAAXAAiAFcAZQB0ACAAYwBsAGkAbQBhAHQAZQAgAHoAbwBuAGUAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEMAbwBvAGwAIAB0AGUAbQBwAGUAcgBhAHQAZQAgAGQAcgB5AFwAIgAsACAAXAAiAEQAcgB5ACAAYwBsAGkAbQBhAHQAZQAgAHoAbwBuAGUAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFcAYQByAG0AIAB0AGUAbQBwAGUAcgBhAHQAZQAgAG0AbwBpAHMAdAAgAC0AIABsAG8AdwAgAGYAcgBvAHMAdABcACIALAAgAFwAIgBXAGUAdAAgAGMAbABpAG0AYQB0AGUAIAB6AG8AbgBlAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBXAGEAcgBtACAAdABlAG0AcABlAHIAYQB0AGUAIABkAHIAeQAgAC0AIABsAG8AdwAgAGYAcgBvAHMAdABcACIALAAgAFwAIgBEAHIAeQAgAGMAbABpAG0AYQB0AGUAIAB6AG8AbgBlAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBXAGEAcgBtACAAdABlAG0AcABlAHIAYQB0AGUAIABtAG8AaQBzAHQAIAAtACAAaABpAGcAaAAgAHQAZQBtAHAAXAAiACwAIABcACIAVwBlAHQAIABjAGwAaQBtAGEAdABlACAAegBvAG4AZQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVwBhAHIAbQAgAHQAZQBtAHAAZQByAGEAdABlACAAZAByAHkAIAAtACAAaABpAGcAaAAgAHQAZQBtAHAAXAAiACwAIABcACIARAByAHkAIABjAGwAaQBtAGEAdABlACAAegBvAG4AZQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAQwBvAG8AbAAgAHQAZQBtAHAAZQByAGEAdABlACAAbQBvAGkAcwB0ACAALQAgAGwAbwB3ACAAZgByAG8AcwB0AFwAIgAsACAAXAAiAFcAZQB0ACAAYwBsAGkAbQBhAHQAZQAgAHoAbwBuAGUAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEMAbwBvAGwAIAB0AGUAbQBwAGUAcgBhAHQAZQAgAGQAcgB5ACAALQAgAGwAbwB3ACAAZgByAG8AcwB0AFwAIgAsACAAXAAiAEQAcgB5ACAAYwBsAGkAbQBhAHQAZQAgAHoAbwBuAGUAXAAiAFwAbgAgACAAIAAgACAAIAAgACAAfQAsACAAcgAsACAAYwApAFwAbgAgACAAIAAgACAAIAApAFwAbgAgACAAIAAgACkAXABuACAAIAApADsAXABuAFwAbgAvACoAIABcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBDAGwAaQBtAGEAdABlAFoAbwBuAGUAcwBcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgAqAC8AXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBDAGwAaQBtAGEAdABlAFoAbwBuAGUAcwBfAFQAaQB0AGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAVgBFAEUAUgBHACAAQQB1AHMAdAByAGEAbABpAGEAbgAgAGMAbABpAG0AYQB0AGUAIAB6AG8AbgBlAHMAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEMAbABpAG0AYQB0AGUAWgBvAG4AZQBzAF8AVgBhAHIAaQBhAGIAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQwBsAGkAbQBhAHQAZQBaAG8AbgBlAHMAXwBVAG4AaQB0AFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQwBsAGkAbQBhAHQAZQBaAG8AbgBlAHMAXwBTAG8AdQByAGMAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAVgBFAEUAUgBHACAAMgAwADIANgA6ACAAVABhAGIAbABlACAAMQAuADMAOgAgAEMAbABpAG0AYQB0AGUAIABhAG4AZAAgAFIAYQBpAG4AZgBhAGwAbAAgAHoAbwBuAGUAIABjAGwAYQBzAHMAaQBmAGkAYwBhAHQAaQBvAG4AcwAgAGEAbgBkACAAZABlAGYAaQBuAGkAdABpAG8AbgBzAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBDAGwAaQBtAGEAdABlAFoAbwBuAGUAcwBfAFYAYQByAGkAYQB0AGkAbwBuAFwAbgAgACAAIAA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAATQBBAEsARQBBAFIAUgBBAFkAKAA1ACwAIAAxACwAIABcAG4AIAAgACAAIAAgACAATABBAE0AQgBEAEEAKAByACwAYwAsACAAXABuACAAIAAgACAAIAAgACAAIABJAE4ARABFAFgAKAB7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBWAEEAUgBJAEEAVABJAE8ATgAgAE8ARgAgAFMATwBVAFIAQwBFACAARABBAFQAQQA6AFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBBAGQAZABlAGQAIAB3AGEAcgBtACAALwAgAGMAbwBvAGwAIAB0AGUAbQBwAGUAcgBhAHQAZQAgAG0AbwBpAHMAdAAgAC8AIABkAHIAeQAgAC0AIABsAG8AdwAgAGYAcgBvAHMAdAAgAGEAbgBkACAAaABpAGcAaAAgAHQAZQBtAHAAIABjAGwAYQBzAHMAZQBzACAAdABvACAAYQBjAGMAbwBtAG0AbwBkAGEAdABlACAAYwBsAGkAbQBhAHQAZQAgAHMAYwBlAG4AYQByAGkAbwBzACAAZQB4AGMAbAB1AGQAZQBkACAAYgB5ACAAVgBFAEUAUgBHACAAYwByAGkAdABlAHIAaQBhAC4AXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEYAaQB4AGUAZAAgAHQAeQBwAG8AIABpAG4AIABNAEEAVAAgAHYAYQBsAHUAZQAgAGYAbwByACAAdwBhAHIAbQAgAHQAZQBtAHAAZQByAGEAdABlACAAZAByAHkAIAAtACAAYwBoAGEAbgBnAGUAZAAgADEAMAAgAHQAbwAgADEAMQAuAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBBAGQAZABlAGQAIABtAGkAbgAgAGEAbgBkACAAbQBhAHgAIABjAG8AbAB1AG0AbgBzACAAZgBvAHIAIABNAEEAVAAsACAATQBBAFAALAAgAGYAcgBvAHMAdAAgAGQAYQB5AHMAIABwAGUAcgAgAHkAZQBhAHIALAAgAGUAbABlAHYAYQB0AGkAbwBuACwAIABNAEEAUAA6AFAARQBUACAAdABvACAAYwBhAGwAYwB1AGwAYQB0AGUAIAB6AG8AbgBlAHMAIABmAHIAbwBtACAAcgBlAGEAbAAgAGMAbABpAG0AYQB0AGUAIABkAGEAdABhAC4AXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEcAQQBGACAAYQBjAGMAZQBwAHQAcwAgAHIAYQBpAG4AZgBhAGwAbAAgAGEAcwAgAGEAIABwAHIAbwB4AHkAIABmAG8AcgAgAHAAcgBlAGMAaQBwAGkAdABhAHQAaQBvAG4ALgBcACIAXABuACAAIAAgACAAIAAgACAAIAB9ACwAIAByACwAIABjACkAXABuACAAIAAgACAAIAAgACkAXABuACAAIAAgACAAKQBcAG4AIAAgACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEMAbABpAG0AYQB0AGUAWgBvAG4AZQBzAF8ARABhAHQAYQBcAG4AIAAgACAAPQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAE0AQQBLAEUAQQBSAFIAQQBZACgAOQAsACAAMQA2ACwAIABcAG4AIAAgACAAIAAgACAATABBAE0AQgBEAEEAKAByACwAYwAsACAAXABuACAAIAAgACAAIAAgACAAIABJAE4ARABFAFgAKAB7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBDAGwAaQBtAGEAdABlACAAWgBvAG4AZQBcACIALAAgAFwAIgBNAEEAVABcACIALAAgAFwAIgBNAEEAUABcACIALAAgAFwAIgBGAHIAbwBzAHQAIABkAGEAeQBzACAAcABlAHIAIAB5AGUAYQByAFwAIgAsACAAXAAiAEUAbABlAHYAYQB0AGkAbwBuAFwAIgAsACAAXAAiAE0AQQBQADoAUABFAFQAXAAiACwAIABcACIATQBpAG4AIAB0AGUAbQBwAFwAIgAsACAAXAAiAE0AYQB4ACAAdABlAG0AcABcACIALAAgAFwAIgBNAGkAbgAgAHIAYQBpAG4AZgBhAGwAbABcACIALAAgAFwAIgBNAGEAeAAgAHIAYQBpAG4AZgBhAGwAbABcACIALAAgAFwAIgBNAGkAbgAgAGYAcgBvAHMAdAAgAGQAYQB5AHMAXAAiACwAIABcACIATQBhAHgAIABmAHIAbwBzAHQAIABkAGEAeQBzAFwAIgAsACAAXAAiAE0AaQBuACAAZQBsAGUAdgBhAHQAaQBvAG4AXAAiACwAIABcACIATQBhAHgAIABlAGwAZQB2AGEAdABpAG8AbgBcACIALAAgAFwAIgBNAGkAbgAgAE0AQQBQADoAUABFAFQAXAAiACwAIABcACIATQBpAG4AIABNAEEAUAA6AFAARQBUAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBUAHIAbwBwAGkAYwBhAGwAIABtAG8AbgB0AGEAbgBlAFwAIgAsACAAXAAiAD4AIAAxADgAIABDAFwAIgAsACAAXAAiAEEAbgB5AFwAIgAsACAAXAAiAGQiIAA3AFwAIgAsACAAXAAiAD4AIAAxADAAMAAwACAAbQBcACIALAAgAFwAIgBBAG4AeQBcACIALAAgADEAOAAuADAAMAAxACwAIAA5ADkAOQA5ADkAOQAsACAALQA5ADkAOQA5ADkAOQAsACAAOQA5ADkAOQA5ADkALAAgAC0AOQA5ADkAOQA5ADkALAAgADcALAAgADEAMAAwADAALAAgADkAOQA5ADkAOQA5ACwAIAAtADkAOQA5ADkAOQA5ACwAIAA5ADkAOQA5ADkAOQA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBUAHIAbwBwAGkAYwBhAGwAIAB3AGUAdABcACIALAAgAFwAIgA+ACAAMQA4ACAAQwBcACIALAAgAFwAIgA+ACAAMgAwADAAMAAgAG0AbQBcACIALAAgAFwAIgBkIiAANwBcACIALAAgAFwAIgBkIiAAMQAwADAAMAAgAG0AXAAiACwAIABcACIAQQBuAHkAXAAiACwAIAAxADgALgAwADAAMQAsACAAOQA5ADkAOQA5ADkALAAgADIAMAAwADAALgAwADAAMQAsACAAOQA5ADkAOQA5ADkALAAgAC0AOQA5ADkAOQA5ADkALAAgADcALAAgAC0AOQA5ADkAOQA5ADkALAAgADkAOQA5AC4AOQA5ADkALAAgACAALQA5ADkAOQA5ADkAOQAsACAAOQA5ADkAOQA5ADkAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVAByAG8AcABpAGMAYQBsACAAbQBvAGkAcwB0AFwAIgAsACAAXAAiAD4AIAAxADgAIABDAFwAIgAsACAAXAAiAD4AIAAxADAAMAAwACAAbQBtACAALQAgAGQiIAAyADAAMAAwACAAbQBtAFwAIgAsACAAXAAiAGQiIAA3AFwAIgAsACAAXAAiAGQiIAAxADAAMAAwACAAbQBcACIALAAgAFwAIgBBAG4AeQBcACIALAAgADEAOAAuADAAMAAxACwAIAA5ADkAOQA5ADkAOQAsACAAMQAwADAAMAAuADAAMAAxACwAIAAyADAAMAAwACwAIAAtADkAOQA5ADkAOQA5ACwAIAA3ACwAIAAtADkAOQA5ADkAOQA5ACwAIAA5ADkAOQAuADkAOQA5ACwAIAAgAC0AOQA5ADkAOQA5ADkALAAgADkAOQA5ADkAOQA5ADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFQAcgBvAHAAaQBjAGEAbAAgAGQAcgB5AFwAIgAsACAAXAAiAD4AIAAxADgAIABDAFwAIgAsACAAXAAiAGQiIAAxADAAMAAwACAAbQBtAFwAIgAsACAAXAAiAGQiIAA3AFwAIgAsACAAXAAiAGQiIAAxADAAMAAwACAAbQBcACIALAAgAFwAIgBBAG4AeQBcACIALAAgADEAOAAuADAAMAAxACwAIAA5ADkAOQA5ADkAOQAsACAALQA5ADkAOQA5ADkAOQAsACAAMQAwADAAMAAsACAALQA5ADkAOQA5ADkAOQAsACAANwAsACAALQA5ADkAOQA5ADkAOQAsACAAOQA5ADkALgA5ADkAOQAsACAAIAAtADkAOQA5ADkAOQA5ACwAIAA5ADkAOQA5ADkAOQA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBXAGEAcgBtACAAdABlAG0AcABlAHIAYQB0AGUAIABtAG8AaQBzAHQAXAAiACwAIABcACIAPgAgADEAMAAgAEMAXAAiACwAIABcACIAQQBuAHkAXAAiACwAIABcACIAQQBuAHkAXAAiACwAIABcACIAQQBuAHkAXAAiACwAIABcACIAPgAgADEAXAAiACwAIAAxADAALgAwADAAMQAsACAAOQA5ADkAOQA5ADkALAAgAC0AOQA5ADkAOQA5ADkALAAgADkAOQA5ADkAOQA5ACwAIAAtADkAOQA5ADkAOQA5ACwAIAA5ADkAOQA5ADkAOQAsACAALQA5ADkAOQA5ADkAOQAsACAAOQA5ADkAOQA5ADkALAAgADEALgAwADAAMQAsACAAOQA5ADkAOQA5ADkAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVwBhAHIAbQAgAHQAZQBtAHAAZQByAGEAdABlACAAZAByAHkAXAAiACwAIABcACIAPgAgADEAMAAgAEMAXAAiACwAIABcACIAQQBuAHkAXAAiACwAIABcACIAQQBuAHkAXAAiACwAIABcACIAQQBuAHkAXAAiACwAIABcACIAZCIgADEAXAAiACwAIAAxADAALgAwADAAMQAsACAAOQA5ADkAOQA5ADkALAAgAC0AOQA5ADkAOQA5ADkALAAgADkAOQA5ADkAOQA5ACwAIAAtADkAOQA5ADkAOQA5ACwAIAA5ADkAOQA5ADkAOQAsACAALQA5ADkAOQA5ADkAOQAsACAAOQA5ADkAOQA5ADkALAAgACAALQA5ADkAOQA5ADkAOQAsACAAMQA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBDAG8AbwBsACAAdABlAG0AcABlAHIAYQB0AGUAIABtAG8AaQBzAHQAXAAiACwAIABcACIAPgAgADAAIABDACAALQAgAGQiIAAxADAAIABDAFwAIgAsACAAXAAiAEEAbgB5AFwAIgAsACAAXAAiAEEAbgB5AFwAIgAsACAAXAAiAEEAbgB5AFwAIgAsACAAXAAiAD4AIAAxAFwAIgAsACAALQA5ADkAOQA5ADkAOQAsACAAMQAwACwAIAAtADkAOQA5ADkAOQA5ACwAIAA5ADkAOQA5ADkAOQAsACAALQA5ADkAOQA5ADkAOQAsACAAOQA5ADkAOQA5ADkALAAgAC0AOQA5ADkAOQA5ADkALAAgADkAOQA5ADkAOQA5ACwAIAAxAC4AMAAwADEALAAgADkAOQA5ADkAOQA5ADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEMAbwBvAGwAIAB0AGUAbQBwAGUAcgBhAHQAZQAgAGQAcgB5AFwAIgAsACAAXAAiAD4AIAAwACAAQwAgAC0AIABkIiAAMQAwACAAQwBcACIALAAgAFwAIgBBAG4AeQBcACIALAAgAFwAIgBBAG4AeQBcACIALAAgAFwAIgBBAG4AeQBcACIALAAgAFwAIgBkIiAAMQBcACIALAAgAC0AOQA5ADkAOQA5ADkALAAgADEAMAAsACAALQA5ADkAOQA5ADkAOQAsACAAOQA5ADkAOQA5ADkALAAgAC0AOQA5ADkAOQA5ADkALAAgADkAOQA5ADkAOQA5ACwAIAAtADkAOQA5ADkAOQA5ACwAIAA5ADkAOQA5ADkAOQAsACAAIAAtADkAOQA5ADkAOQA5ACwAIAAxAFwAbgAgACAAIAAgACAAIAAgACAAfQAsACAAcgAsACAAYwApAFwAbgAgACAAIAAgACAAIAApAFwAbgAgACAAIAAgACkAXABuACAAIAApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBDAGwAaQBtAGEAdABlAFoAbwBuAGUAcwBfAEEAcABwAGUAbgBkAGkAYwBlAHMAXABuACAAIAAgAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABNAEEASwBFAEEAUgBSAEEAWQAoADQALAAgADEALAAgAFwAbgAgACAAIAAgACAAIABMAEEATQBCAEQAQQAoAHIALABjACwAIABcAG4AIAAgACAAIAAgACAAIAAgAEkATgBEAEUAWAAoAHsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAE4AbwB0AGUAOgBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIATQBBAFQAIAA9ACAAbQBlAGEAbgAgAGEAbgBuAHUAYQBsACAAdABlAG0AcABlAHIAYQB0AHUAcgBlAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBNAEEAUAAgAD0AIABtAGUAYQBuACAAYQBuAG4AdQBhAGwAIABwAHIAZQBjAGkAcABpAHQAYQB0AGkAbwBuAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBQAEUAVAAgAD0AIABwAG8AdABlAG4AdABpAGEAbAAgAGUAdgBhAHAAbwB0AHIAYQBuAHMAcABpAHIAYQB0AGkAbwBuAFwAIgBcAG4AIAAgACAAIAAgACAAIAAgAH0ALAAgAHIALAAgAGMAKQBcAG4AIAAgACAAIAAgACAAKQBcAG4AIAAgACAAIAApAFwAbgAgACAAKQA7AFwAbgBcAG4AXABuAC8AKgAgAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFQAZQBtAHAAZQByAGEAdAB1AHIAZQBaAG8AbgBlAHMAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AKgAvAFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AVABlAG0AcABlAHIAYQB0AHUAcgBlAFoAbwBuAGUAcwBfAFQAaQB0AGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAVgBFAEUAUgBHACAAQQB1AHMAdAByAGEAbABpAGEAbgAgAHQAZQBtAHAAZQByAGEAdAB1AHIAZQAgAHoAbwBuAGUAcwBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AVABlAG0AcABlAHIAYQB0AHUAcgBlAFoAbwBuAGUAcwBfAFYAYQByAGkAYQBiAGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFQAZQBtAHAAZQByAGEAdAB1AHIAZQBaAG8AbgBlAHMAXwBVAG4AaQB0AFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AVABlAG0AcABlAHIAYQB0AHUAcgBlAFoAbwBuAGUAcwBfAFMAbwB1AHIAYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBWAEUARQBSAEcAIAAyADAAMgA2ADoAIABUAGEAYgBsAGUAIAAxAC4AMwA6ACAAQwBsAGkAbQBhAHQAZQAgAGEAbgBkACAAUgBhAGkAbgBmAGEAbABsACAAegBvAG4AZQAgAGMAbABhAHMAcwBpAGYAaQBjAGEAdABpAG8AbgBzACAAYQBuAGQAIABkAGUAZgBpAG4AaQB0AGkAbwBuAHMAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFQAZQBtAHAAZQByAGEAdAB1AHIAZQBaAG8AbgBlAHMAXwBWAGEAcgBpAGEAdABpAG8AbgBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAVgBBAFIASQBBAFQASQBPAE4AIABPAEYAIABTAE8AVQBSAEMARQAgAEQAQQBUAEEAOgAgAEEAZABkAGUAZAAgAGUAeAB0AHIAYQAgAE0AQQBUACAAbQBpAG4AIABhAG4AZAAgAE0AQQBUACAAbQBhAHgAIABjAG8AbAB1AG0AbgBzACAAdABvACAAYwBhAGwAYwB1AGwAYQB0AGUAIAB6AG8AbgBlACAAZgByAG8AbQAgAHIAZQBhAGwAIAB0AGUAbQBwAGUAcgBhAHQAdQByAGUAIABkAGEAdABhAC4AXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFQAZQBtAHAAZQByAGEAdAB1AHIAZQBaAG8AbgBlAHMAXwBEAGEAdABhAFwAbgAgACAAIAA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAATQBBAEsARQBBAFIAUgBBAFkAKAA0ACwAIAA0ACwAIABcAG4AIAAgACAAIAAgACAATABBAE0AQgBEAEEAKAByACwAYwAsACAAXABuACAAIAAgACAAIAAgACAAIABJAE4ARABFAFgAKAB7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBUAGUAbQBwAGUAcgBhAHQAdQByAGUAIABaAG8AbgBlAFwAIgAsACAAXAAiAE0AZQBkAGkAYQBuACAAQQBuAG4AdQBhAGwAIABUAGUAbQBwAGUAcgBhAHQAdQByAGUAIAAoAE0AQQBUACkAXAAiACwAIABcACIATQBpAG4AIABNAEEAVABcACIALAAgAFwAIgBNAGEAeAAgAE0AQQBUAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBXAGEAcgBtAFwAIgAsACAAXAAiAGUiIAAyADYAIABDAFwAIgAsACAAMgA2ACwAIAA5ADkAOQA5ADkAOQA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBUAGUAbQBwAGUAcgBhAHQAZQBcACIALAAgAFwAIgAxADUAIAAtACAAMgA1ACAAQwBcACIALAAgADEANQAsACAAMgA1AC4AOQA5ADkAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAQwBvAG8AbABcACIALAAgAFwAIgBkIiAAMQA0ACAAQwBcACIALAAgAC0AOQA5ADkAOQA5ADkALAAgADEANAAuADkAOQA5AFwAbgAgACAAIAAgACAAIAAgACAAfQAsACAAcgAsACAAYwApAFwAbgAgACAAIAAgACAAIAApAFwAbgAgACAAIAAgACkAXABuACAAIAApADsAXABuAFwAbgAvACoAIABcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBSAGEAaQBuAGYAYQBsAGwAWgBvAG4AZQBzAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuACoALwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFIAYQBpAG4AZgBhAGwAbABaAG8AbgBlAHMAXwBUAGkAdABsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFYARQBFAFIARwAgAEEAdQBzAHQAcgBhAGwAaQBhAG4AIAByAGEAaQBuAGYAYQBsAGwAIAB6AG8AbgBlAHMAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFIAYQBpAG4AZgBhAGwAbABaAG8AbgBlAHMAXwBWAGEAcgBpAGEAYgBsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBSAGEAaQBuAGYAYQBsAGwAWgBvAG4AZQBzAF8AVQBuAGkAdABcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFIAYQBpAG4AZgBhAGwAbABaAG8AbgBlAHMAXwBTAG8AdQByAGMAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAVgBFAEUAUgBHACAAMgAwADIANgA6ACAAVABhAGIAbABlACAAMQAuADMAOgAgAEMAbABpAG0AYQB0AGUAIABhAG4AZAAgAFIAYQBpAG4AZgBhAGwAbAAgAHoAbwBuAGUAIABjAGwAYQBzAHMAaQBmAGkAYwBhAHQAaQBvAG4AcwAgAGEAbgBkACAAZABlAGYAaQBuAGkAdABpAG8AbgBzAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBSAGEAaQBuAGYAYQBsAGwAWgBvAG4AZQBzAF8AVgBhAHIAaQBhAHQAaQBvAG4AXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFYAQQBSAEkAQQBUAEkATwBOACAATwBGACAAUwBPAFUAUgBDAEUAIABEAEEAVABBADoAIABBAGQAZABlAGQAIABlAHgAdAByAGEAIABSAGEAaQBuAGYAYQBsAGwAIABtAGkAbgAgAGEAbgBkACAAUgBhAGkAbgBmAGEAbABsACAAbQBhAHgAIABjAG8AbAB1AG0AbgBzACAAdABvACAAYwBhAGwAYwB1AGwAYQB0AGUAIAB6AG8AbgBlACAAZgByAG8AbQAgAHIAZQBhAGwAIAByAGEAaQBuAGYAYQBsAGwAIABkAGEAdABhAC4AXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFIAYQBpAG4AZgBhAGwAbABaAG8AbgBlAHMAXwBEAGEAdABhAFwAbgAgACAAIAA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAATQBBAEsARQBBAFIAUgBBAFkAKAAzACwAIAA0ACwAIABcAG4AIAAgACAAIAAgACAATABBAE0AQgBEAEEAKAByACwAYwAsACAAXABuACAAIAAgACAAIAAgACAAIABJAE4ARABFAFgAKAB7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBSAGEAaQBuAGYAYQBsAGwAIABaAG8AbgBlAFwAIgAsACAAXAAiAEEAbgBuAHUAYQBsACAAcgBhAGkAbgBmAGEAbABsAFwAIgAsACAAXAAiAFIAYQBpAG4AZgBhAGwAbAAgAG0AaQBuAFwAIgAsACAAXAAiAFIAYQBpAG4AZgBhAGwAbAAgAG0AYQB4AFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBIAGkAZwBoACAAcgBhAGkAbgBmAGEAbABsAFwAIgAsACAAXAAiAEEAbgBuAHUAYQBsACAAcgBhAGkAbgBmAGEAbABsACAAPgAgADYAMAAwAG0AbQBcACIALAAgADYAMAAwAC4AMAAwADEALAAgADkAOQA5ADkAOQA5ADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEwAbwB3ACAAcgBhAGkAbgBmAGEAbABsAFwAIgAsACAAXAAiAEEAbgBuAHUAYQBsACAAcgBhAGkAbgBmAGEAbABsACAAZCIgADYAMAAwAG0AbQBcACIALAAgAC0AOQA5ADkAOQA5ADkALAAgADYAMAAwAFwAbgAgACAAIAAgACAAIAAgACAAfQAsACAAcgAsACAAYwApAFwAbgAgACAAIAAgACAAIAApAFwAbgAgACAAIAAgACkAXABuACAAIAApADsAXABuAFwAbgAvACoAIABcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBMAGUAYQBjAGgAaQBuAGcAWgBvAG4AZQBzAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuACoALwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEwAZQBhAGMAaABpAG4AZwBaAG8AbgBlAHMAXwBUAGkAdABsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFYARQBFAFIARwAgAEEAdQBzAHQAcgBhAGwAaQBhAG4AIABsAGUAYQBjAGgAaQBuAGcAIAB6AG8AbgBlAHMAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEwAZQBhAGMAaABpAG4AZwBaAG8AbgBlAHMAXwBWAGEAcgBpAGEAYgBsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBMAGUAYQBjAGgAaQBuAGcAWgBvAG4AZQBzAF8AVQBuAGkAdABcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEwAZQBhAGMAaABpAG4AZwBaAG8AbgBlAHMAXwBTAG8AdQByAGMAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAVgBFAEUAUgBHACAAMgAwADIANgA6ACAAVABhAGIAbABlACAAMQAuADMAOgAgAEMAbABpAG0AYQB0AGUAIABhAG4AZAAgAFIAYQBpAG4AZgBhAGwAbAAgAHoAbwBuAGUAIABjAGwAYQBzAHMAaQBmAGkAYwBhAHQAaQBvAG4AcwAgAGEAbgBkACAAZABlAGYAaQBuAGkAdABpAG8AbgBzAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBMAGUAYQBjAGgAaQBuAGcAWgBvAG4AZQBzAF8AVgBhAHIAaQBhAHQAaQBvAG4AXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBMAGUAYQBjAGgAaQBuAGcAWgBvAG4AZQBzAF8ARABhAHQAYQBcAG4AIAAgACAAPQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAE0AQQBLAEUAQQBSAFIAQQBZACgANAAsACAAMgAsACAAXABuACAAIAAgACAAIAAgAEwAQQBNAEIARABBACgAcgAsAGMALAAgAFwAbgAgACAAIAAgACAAIAAgACAASQBOAEQARQBYACgAewBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIATABlAGEAYwBoAGkAbgBnACAAWgBvAG4AZQBcACIALAAgAFwAIgBMAGUAYQBjAGgAaQBuAGcAIABjAHIAaQB0AGUAcgBpAGEAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEwAZQBhAGMAaABpAG4AZwAgAG8AYwBjAHUAcgBzAFwAIgAsACAAXAAiAKMDKAA12F/cNdhO3DXYVtw12FvcKQA+AKMDKAA12DjcNdhH3DAAKQArADXYYNw12FzcNdhW3DXYWdwgADXYZNw12E7cNdhh3DXYUtw12F/cIAAOITXYXNw12FncNdhR3DXYVtw12FvcNdhU3CAANdhQ3DXYTtw12F3cNdhO3DXYUNw12FbcNdhh3DXYZtxcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIATABlAGEAYwBoAGkAbgBnACAAZABvAGUAcwAgAG4AbwB0ACAAbwBjAGMAdQByAFwAIgAsACAAXAAiAKMDKAA12F/cNdhO3DXYVtw12FvcKQBkIqMDKAA12DjcNdhH3DAAKQArADXYYNw12FzcNdhW3DXYWdwgADXYZNw12E7cNdhh3DXYUtw12F/cIAAOITXYXNw12FncNdhR3DXYVtw12FvcNdhU3CAANdhQ3DXYTtw12F3cNdhO3DXYUNw12FbcNdhh3DXYZtxcACIAXABuACAAIAAgACAAIAAgACAAIAB9ACwAIAByACwAIABjACkAXABuACAAIAAgACAAIAAgACkAXABuACAAIAAgACAAKQBcAG4AIAAgACkAOwBcAG4AXABuAC8AKgAgAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAcgBhAGMAVwBFAFQAXABuADUALgA1AC4AMgAuADMAIABDAG8AbgBzAHQAYQBuAHQAIABQAGEAcgBhAG0AZQB0AGUAcgBzAFwAbgBGAHIAYQBjAHQAaQBvAG4AIABvAGYAIABOACAAdABoAGEAdAAgAGkAcwAgAGEAdgBhAGkAbABhAGIAbABlACAAZgBvAHIAIABsAGUAYQBjAGgAaQBuAGcAIABhAG4AZAAgAHIAdQBuAG8AZgBmAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuACoALwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAcgBhAGMAVwBFAFQAXwBUAGkAdABsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAEYAcgBhAGMAdABpAG8AbgAgAG8AZgAgAE4AIAB0AGgAYQB0ACAAaQBzACAAYQB2AGEAaQBsAGEAYgBsAGUAIABmAG8AcgAgAGwAZQBhAGMAaABpAG4AZwAgAGEAbgBkACAAcgB1AG4AbwBmAGYAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAcgBhAGMAVwBFAFQAXwBVAG4AaQB0AFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgAoAEQAaQBtAGUAbgBzAGkAbwBuAGwAZQBzAHMAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAcgBhAGMAVwBFAFQAXwBTAG8AdQByAGMAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAVgBFAEUAUgBHACAAMgAwADIANgA6ADUALgA1AC4AMgAuADMAIABDAG8AbgBzAHQAYQBuAHQAIABQAGEAcgBhAG0AZQB0AGUAcgBzAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAHIAYQBjAFcARQBUAF8ATgBJAFIAUgBlAGYAZQByAGUAbgBjAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAHIAYQBjAFcARQBUAF8ARABhAHQAYQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABNAEEASwBFAEEAUgBSAEEAWQAoADMALAAgADIALAAgAFwAbgAgACAAIAAgACAAIABMAEEATQBCAEQAQQAoAHIALABjACwAIABcAG4AIAAgACAAIAAgACAAIAAgAEkATgBEAEUAWAAoAHsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEkAcwAgAGkAbgAgAGwAZQBhAGMAaABpAG4AZwAgAHoAbwBuAGUAXAAiACwAXAAiAEYAcgBhAGMAVwBFAFQAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFkAZQBzACAALQAgAGkAbgAgAGwAZQBhAGMAaABpAG4AZwAgAHoAbwBuAGUAXAAiACwAIAAxADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAE4AbwAgAC0AIABuAG8AdAAgAGkAbgAgAGwAZQBhAGMAaABpAG4AZwAgAHoAbwBuAGUAXAAiACwAIAAwAFwAbgAgACAAIAAgACAAIAAgACAAfQAsACAAcgAsACAAYwApAFwAbgAgACAAIAAgACAAIAApAFwAbgAgACAAIAAgACkAXABuACAAIAApADsAXABuAFwAbgAgACAAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgByAGEAYwBXAEUAVABfAFYAYQByAGkAYQB0AGkAbwBuAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoACgAXAAiAFwAIgApACkAOwBcAG4AXABuAFwAbgBcAG4ALwAqACAAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABhAHQAYQBTAGMAbwByAGUAcwBfAFMAYwBvAHAAZQAzAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuACoALwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEQAYQB0AGEAUwBjAG8AcgBlAHMAXwBTAGMAbwBwAGUAMwBfAFQAaQB0AGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAQQB1AHMAdAByAGEAbABpAGEAbgAgAGQAYQB0AGEAIABzAGMAbwByAGUAcwAgAGYAbwByACAAcwBjAG8AcABlACAAMwBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABhAHQAYQBTAGMAbwByAGUAcwBfAFMAYwBvAHAAZQAzAF8AVgBhAHIAaQBhAGIAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABhAHQAYQBTAGMAbwByAGUAcwBfAFMAYwBvAHAAZQAzAF8AVQBuAGkAdABcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEQAYQB0AGEAUwBjAG8AcgBlAHMAXwBTAGMAbwBwAGUAMwBfAFMAbwB1AHIAYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBWAEUARQBSAEcAIAAyADAAMgA2ADoAIABYAFgAWABYAFgAWABYAFgAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEQAYQB0AGEAUwBjAG8AcgBlAHMAXwBTAGMAbwBwAGUAMwBfAFYAYQByAGkAYQB0AGkAbwBuAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABhAHQAYQBTAGMAbwByAGUAcwBfAFMAYwBvAHAAZQAzAF8ARABhAHQAYQBcAG4AIAAgACAAPQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAE0AQQBLAEUAQQBSAFIAQQBZACgANgAsACAAMgAsACAAXABuACAAIAAgACAAIAAgAEwAQQBNAEIARABBACgAcgAsAGMALAAgAFwAbgAgACAAIAAgACAAIAAgACAASQBOAEQARQBYACgAewBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIARABhAHQAYQAgAHMAbwB1AHIAYwBlAFwAIgAsACAAXAAiAEQAYQB0AGEAIABzAGMAbwByAGUAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEkAbgB0AGUAcgBuAGEAdABpAG8AbgBhAGwAIABzAGMAbwBwAGUAIAAzACAAZABhAHQAYQBiAGEAcwBlAFwAIgAsACAAMQA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBBAHUAcwB0AHIAYQBsAGkAYQBuACAAcwBjAG8AcABlACAAMwAgAGQAYQB0AGEAYgBhAHMAZQBcACIALAAgADIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAUwB0AGEAdABlACAAbwByACAAcgBlAGcAaQBvAG4AYQBsACAAcwBjAG8AcABlACAAMwAgAGQAYQB0AGEAYgBhAHMAZQBcACIALAAgADMAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIARQBtAGkAcwBzAGkAbwBuAHMAIABpAG4AdABlAG4AcwBpAHQAeQAgAGMAYQBsAGMAdQBsAGEAdABlAGQAIABmAHIAbwBtACAAYQBwAHAAcgBvAHYAZQBkACAAbQBlAHQAaABvAGQAXAAiACwAIAA0ADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFYAZQByAGkAZgBpAGUAZAAgAGMAcgBlAGQAZQBuAHQAaQBhAGwAIABtAGEAdABjAGgAaQBuAGcAIABJAFMATwAxADQAMAA2ADcAXAAiACwAIAA1AFwAbgAgACAAIAAgACAAIAAgACAAfQAsACAAcgAsACAAYwApAFwAbgAgACAAIAAgACAAIAApAFwAbgAgACAAIAAgACkAXABuACAAIAApADsAXABuAFwAbgBcAG4ALwAqACAAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgByAGEAYwBMAEUAQQBDAEgAXABuADUALgA1AC4AMgAuADMAIABDAG8AbgBzAHQAYQBuAHQAIABQAGEAcgBhAG0AZQB0AGUAcgBzAFwAbgBGAHIAYQBjAHQAaQBvAG4AIABvAGYAIABOACAAdABoAGEAdAAgAGkAcwAgAGEAdgBhAGkAbABhAGIAbABlACAAZgBvAHIAIABsAGUAYQBjAGgAaQBuAGcAIABhAG4AZAAgAHIAdQBuAG8AZgBmAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuACoALwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAcgBhAGMATABFAEEAQwBIAF8AVABpAHQAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBGAHIAYQBjAHQAaQBvAG4AIABvAGYAIABOACAAdABoAGEAdAAgAGkAcwAgAGEAdgBhAGkAbABhAGIAbABlACAAZgBvAHIAIABsAGUAYQBjAGgAaQBuAGcAIABhAG4AZAAgAHIAdQBuAG8AZgBmAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAHIAYQBjAEwARQBBAEMASABfAFUAbgBpAHQAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiACgARABpAG0AZQBuAHMAaQBvAG4AbABlAHMAcwBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgByAGEAYwBMAEUAQQBDAEgAXwBTAG8AdQByAGMAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAVgBFAEUAUgBHACAAMgAwADIANgA6ADUALgA1AC4AMgAuADMAIABDAG8AbgBzAHQAYQBuAHQAIABQAGEAcgBhAG0AZQB0AGUAcgBzAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAHIAYQBjAEwARQBBAEMASABfAE4ASQBSAFIAZQBmAGUAcgBlAG4AYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBOAGEAdABpAG8AbgBhAGwAIABJAG4AdgBlAG4AdABvAHIAeQAgAFIAZQBwAG8AcgB0ACAAVgBvAGwAdQBtAGUAIAAxADoAIABMAGUAYQBjAGgAaQBuAGcAIABhAG4AZAAgAHIAdQBuAG8AZgBmACAAKAAzAC4ARAAuAGIALgAyACkAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAcgBhAGMATABFAEEAQwBIAF8ARABhAHQAYQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABNAEEASwBFAEEAUgBSAEEAWQAoADEALAAgADIALAAgAFwAbgAgACAAIAAgACAAIABMAEEATQBCAEQAQQAoAHIALABjACwAIABcAG4AIAAgACAAIAAgACAAIAAgAEkATgBEAEUAWAAoAHsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEYAcgBhAGMATABFAEEAQwBIAFwAIgAsADAALgAyADQAXABuACAAIAAgACAAIAAgACAAIAB9ACwAIAByACwAIABjACkAXABuACAAIAAgACAAIAAgACkAXABuACAAIAAgACAAKQBcAG4AIAAgACkAOwBcAG4AXABuACAAIABDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAHIAYQBjAEwARQBBAEMASABfAFYAYQByAGkAYQB0AGkAbwBuAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoACgAXAAiAFwAIgApACkAOwBcAG4AXABuAFwAbgBcAG4ALwAqACAAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAGwAZQBhAGMAaABcAG4ANQAuADUALgAyAC4AMwAgAEMAbwBuAHMAdABhAG4AdAAgAFAAYQByAGEAbQBlAHQAZQByAHMAXABuAEUAbQBpAHMAcwBpAG8AbgAgAGYAYQBjAHQAbwByACAAZgBvAHIAIABuAGkAdAByAG8AZwBlAG4AIABsAGUAYQBjAGgAaQBuAGcAIABhAG4AZAAgAHIAdQBuAG8AZgBmAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuACoALwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEUARgBsAGUAYQBjAGgAXwBUAGkAdABsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAEUAbQBpAHMAcwBpAG8AbgAgAGYAYQBjAHQAbwByACAAZgBvAHIAIABuAGkAdAByAG8AZwBlAG4AIABsAGUAYQBjAGgAaQBuAGcAIABhAG4AZAAgAHIAdQBuAG8AZgBmAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYAbABlAGEAYwBoAF8AVQBuAGkAdABcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAKABrAGcAIABOADIATwAtAE4AIAAvACAAawBnACAATgBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAGwAZQBhAGMAaABfAFMAbwB1AHIAYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBWAEUARQBSAEcAIAAyADAAMgA2ADoANQAuADUALgAyAC4AMwAgAEMAbwBuAHMAdABhAG4AdAAgAFAAYQByAGEAbQBlAHQAZQByAHMAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEUARgBsAGUAYQBjAGgAXwBOAEkAUgBSAGUAZgBlAHIAZQBuAGMAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIATgBhAHQAaQBvAG4AYQBsACAASQBuAHYAZQBuAHQAbwByAHkAIABSAGUAcABvAHIAdAAgAFYAbwBsAHUAbQBlACAAMQA6ACAARQBxAHUAYQB0AGkAbwBuACAAMwAuAEQALgBCAF8AMQAwAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYAbABlAGEAYwBoAF8ARABhAHQAYQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABNAEEASwBFAEEAUgBSAEEAWQAoADEALAAgADIALAAgAFwAbgAgACAAIAAgACAAIABMAEEATQBCAEQAQQAoAHIALABjACwAIABcAG4AIAAgACAAIAAgACAAIAAgAEkATgBEAEUAWAAoAHsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEUARgBsAGUAYQBjAGgAXAAiACwAMAAuADAAMQAxAFwAbgAgACAAIAAgACAAIAAgACAAfQAsACAAcgAsACAAYwApAFwAbgAgACAAIAAgACAAIAApAFwAbgAgACAAIAAgACkAXABuACAAIAApADsAXABuAFwAbgAgACAAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAGwAZQBhAGMAaABfAFYAYQByAGkAYQB0AGkAbwBuAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoACgAXAAiAFwAIgApACkAOwBcAG4AXABuAFwAbgAvACoAIABcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYATgAyAE8AXABuAFQAYQBiAGwAZQAgAEEALgAyAC4AMgAuADEAXABuAE4AaQB0AHIAbwB1AHMAIABvAHgAaQBkAGUAIABlAG0AaQBzAHMAaQBvAG4AIABmAGEAYwB0AG8AcgBzACAAZgBvAHIAIABpAG4AbwByAGcAYQBuAGkAYwAgAGYAZQByAHQAaQBsAGkAcwBlAHIAIABhAHAAcABsAGkAYwBhAHQAaQBvAG4AIAAoAGsAZwAgAE4AMgBPAC0ATgAvAGsAZwAgAE4AKQAgACgARQBGAE4AMgBPACkAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AKgAvAFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAE4AMgBPAF8AVABpAHQAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBOAGkAdAByAG8AdQBzACAAbwB4AGkAZABlACAAZQBtAGkAcwBzAGkAbwBuACAAZgBhAGMAdABvAHIAcwAgAGYAbwByACAAaQBuAG8AcgBnAGEAbgBpAGMAIABmAGUAcgB0AGkAbABpAHMAZQByACAAYQBwAHAAbABpAGMAYQB0AGkAbwBuAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYATgAyAE8AXwBVAG4AaQB0AFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgAoAGsAZwAgAE4AMgBPAC0ATgAgAC8AIABrAGcAIABOAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYATgAyAE8AXwBTAG8AdQByAGMAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAVgBFAEUAUgBHACAAMgAwADIANgA6ACAAVABhAGIAbABlACAAQQAuADIALgAyAC4AMQBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAE4AMgBPAF8ATgBJAFIAUgBlAGYAZQByAGUAbgBjAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYATgAyAE8AXwBEAGEAdABhAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAE0AQQBLAEUAQQBSAFIAQQBZACgAMQA1ACwAIAA1ACwAIABcAG4AIAAgACAAIAAgACAATABBAE0AQgBEAEEAKAByACwAYwAsACAAXABuACAAIAAgACAAIAAgACAAIABJAE4ARABFAFgAKAB7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBQAHIAbwBkAHUAYwB0AGkAbwBuACAAcwB5AHMAdABlAG0AIABqAFwAIgAsAFwAIgBFAEYATgAyAE8AXAAiACwAIABcACIAUAByAG8AZAB1AGMAdABpAG8AbgAgAHMAeQBzAHQAZQBtACAAbwBuAGwAeQBcACIALAAgAFwAIgBJAHIAcgBpAGcAYQB0AGkAbwBuACAAbQBlAHQAaABvAGQAXAAiACwAIABcACIAUgBhAGkAbgBmAGEAbABsACAAegBvAG4AZQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIASQByAHIAaQBnAGEAdABlAGQAIABwAGEAcwB0AHUAcgBlAFwAIgAsADAALgAwADAANQA5ACwAIABcACIAUABhAHMAdAB1AHIAZQBcACIALAAgAFwAIgBBAG4AeQBcACIALAAgAFwAIgBBAG4AeQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIASQByAHIAaQBnAGEAdABlAGQAIABjAHIAbwBwAFwAIgAsADAALgAwADAANwAsACAAXAAiAEMAcgBvAHAAXAAiACwAIABcACIAQQBuAHkAXAAiACwAIABcACIAQQBuAHkAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAE4AbwBuAC0AaQByAHIAaQBnAGEAdABlAGQAIABwAGEAcwB0AHUAcgBlAFwAIgAsADAALgAwADAAMQA4ACwAIABcACIAUABhAHMAdAB1AHIAZQBcACIALAAgAFwAIgBOAG8AdAAgAGkAcgByAGkAZwBhAHQAZQBkAFwAIgAsACAAXAAiAEwAbwB3ACAAcgBhAGkAbgBmAGEAbABsAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBOAG8AbgAtAGkAcgByAGkAZwBhAHQAZQBkACAAcABhAHMAdAB1AHIAZQBcACIALAAwAC4AMAAwADEAOAAsACAAXAAiAFAAYQBzAHQAdQByAGUAXAAiACwAIABcACIATgBvAHQAIABpAHIAcgBpAGcAYQB0AGUAZABcACIALAAgAFwAIgBIAGkAZwBoACAAcgBhAGkAbgBmAGEAbABsAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBOAG8AbgAtAGkAcgByAGkAZwBhAHQAZQBkACAAYwByAG8AcAAgACgAbABvAHcAIAByAGEAaQBuAGYAYQBsAGwAKQBcACIALAAwAC4AMAAwADIAOQAsACAAXAAiAEMAcgBvAHAAXAAiACwAIABcACIATgBvAHQAIABpAHIAcgBpAGcAYQB0AGUAZABcACIALAAgAFwAIgBMAG8AdwAgAHIAYQBpAG4AZgBhAGwAbABcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIATgBvAG4ALQBpAHIAcgBpAGcAYQB0AGUAZAAgAGMAcgBvAHAAIAAoAGgAaQBnAGgAIAByAGEAaQBuAGYAYQBsAGwAKQBcACIALAAwAC4AMAAwADgALAAgAFwAIgBDAHIAbwBwAFwAIgAsACAAXAAiAE4AbwB0ACAAaQByAHIAaQBnAGEAdABlAGQAXAAiACwAIABcACIASABpAGcAaAAgAHIAYQBpAG4AZgBhAGwAbABcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAUwB1AGcAYQByAFwAIgAsADAALgAwADEAOQA5ACwAIABcACIAUwB1AGcAYQByAFwAIgAsACAAXAAiAEEAbgB5AFwAIgAsACAAXAAiAEEAbgB5AFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBDAG8AdAB0AG8AbgBcACIALAAwAC4AMAAwADUAMwAsACAAXAAiAEMAbwB0AHQAbwBuAFwAIgAsACAAXAAiAEEAbgB5AFwAIgAsACAAXAAiAEEAbgB5AFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBIAG8AcgB0AGkAYwB1AGwAdAB1AHIAYQBsACAAYwByAG8AcABzAFwAIgAsADAALgAwADAANgA0ACwAIABcACIASABvAHIAdABpAGMAdQBsAHQAdQByAGEAbAAgAGMAcgBvAHAAcwBcACIALAAgAFwAIgBBAG4AeQBcACIALAAgAFwAIgBBAG4AeQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAUgBpAGMAZQAgACgAYwBvAG4AdABpAG4AdQBvAHUAcwAgAGYAbABvAG8AZABpAG4AZwApAFwAIgAsADAALgAwADAAMwAsACAAXAAiAFIAaQBjAGUAXAAiACwAIABcACIAQwBvAG4AdABpAG4AdQBvAHUAcwAgAGYAbABvAG8AZABpAG4AZwBcACIALAAgAFwAIgBBAG4AeQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAUgBpAGMAZQAgACgAcwBpAG4AZwBsAGUAIABhAG4AZAAgAG0AdQBsAHQAaQBwAGwAZQAgAGQAcgBhAGkAbgBhAGcAZQAsACAAbwByACAAYQBsAHQAZQByAG4AYQB0AGUAIAB3AGUAdAB0AGkAbgBnACAAYQBuAGQAIABkAHIAeQBpAG4AZwApAFwAIgAsADAALgAwADAANQAsACAAXAAiAFIAaQBjAGUAXAAiACwAIABcACIAUwBpAG4AZwBsAGUAIABhAG4AZAAgAG0AdQBsAHQAaQBwAGwAZQAgAGQAcgBhAGkAbgBhAGcAZQAsACAAbwByACAAYQBsAHQAZQByAG4AYQB0AGUAIAB3AGUAdAB0AGkAbgBnACAAYQBuAGQAIABkAHIAeQBpAG4AZwBcACIALAAgAFwAIgBBAG4AeQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAQQBxAHUAYQBjAHUAbAB0AHUAcgBlAFwAIgAsADAALgAwADAAMgA2ACwAIABcACIAQQBxAHUAYQBjAHUAbAB0AHUAcgBlAFwAIgAsACAAXAAiAEEAbgB5AFwAIgAsACAAXAAiAEEAbgB5AFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBGAG8AcgBlAHMAdAByAHkAXAAiACwAMAAuADAAMAAxADgALAAgAFwAIgBGAG8AcgBlAHMAdAByAHkAXAAiACwAIABcACIAQQBuAHkAXAAiACwAIABcACIAQQBuAHkAXAAiAFwAbgAgACAAIAAgACAAIAAgACAAfQAsACAAcgAsACAAYwApAFwAbgAgACAAIAAgACAAIAApAFwAbgAgACAAIAAgACkAXABuACAAIAApADsAXABuAFwAbgAgACAAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAE4AMgBPAF8AVgBhAHIAaQBhAHQAaQBvAG4AXABuACAAIAA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAATQBBAEsARQBBAFIAUgBBAFkAKAA1ACwAIAAxACwAIABcAG4AIAAgACAAIAAgACAATABBAE0AQgBEAEEAKAByACwAYwAsACAAXABuACAAIAAgACAAIAAgACAAIABJAE4ARABFAFgAKAB7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBWAEEAUgBJAEEAVABJAE8ATgAgAE8ARgAgAFMATwBVAFIAQwBFACAARABBAFQAQQA6AFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBSAGUAbQBvAHYAZQBkACAAZAB1AHAAbABpAGMAYQB0AGUAIAAnAEEAcQB1AGEAYwB1AGwAdAB1AHIAZQAnACAAcgBvAHcALgBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAUgBlAG0AbwB2AGUAZAAgAGEAcwB0AGUAcgBpAHMAawBzACAAdABvACAAYQBpAGQAIABsAG8AbwBrAHUAcAAuAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBBAGQAZABlAGQAIAAnAHAAcgBvAGQAdQBjAHQAaQBvAG4AIABzAHkAcwB0AGUAbQAgAG8AbgBsAHkAJwAsACAAJwByAGEAaQBuAGYAYQBsAGwAIAB6AG8AbgBlACcAIABhAG4AZAAgACcAaQByAHIAaQBnAGEAdABpAG8AbgAgAG0AZQB0AGgAbwBkACcAIABjAG8AbAB1AG0AbgBzACAAdABvACAAYQBpAGQAIABsAG8AbwBrAHUAcAAuAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBEAHUAcABsAGkAYwBhAHQAZQBkACAAJwBuAG8AbgAtAGkAcgByAGkAZwBhAHQAZQBkACAAcABhAHMAdAB1AHIAZQAnACAAcgBvAHcAIAB3AGkAdABoACAAcwBhAG0AZQAgAEUARgAgAGYAbwByACAAbABvAHcAIABhAG4AZAAgAGgAaQBnAGgAIAByAGEAaQBuAGYAYQBsAGwAIAB6AG8AbgBlAHMAIAB0AG8AIABhAGkAZAAgAGwAbwBvAGsAdQBwAC4AXAAiAFwAbgAgACAAIAAgACAAIAAgACAAfQAsACAAcgAsACAAYwApAFwAbgAgACAAIAAgACAAIAApAFwAbgAgACAAIAAgACkAXABuACAAIAApADsAXABuAFwAbgAvACoAIABcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAHIAYQBjAFcARQBUAEkAcgByAGkAZwBhAHQAaQBvAG4AXABuAFYARQBFAFIARwAgADIAMAAyADYAOgAgAEMAaABhAHAAdABlAHIAIAAxACwAIABzAGUAYwB0AGkAbwBuACAAMQAuADgALgAyACAATABlAGEAYwBoAGkAbgBnACwAIABjAGwAaQBtAGEAdABlACAAYQBuAGQAIAByAGEAaQBuAGYAYQBsAGwAIAB6AG8AbgBlAHMAXABuAEkAUABDAEMAOgAgAE4AMgBPACAARQBNAEkAUwBTAEkATwBOAFMAIABGAFIATwBNACAATQBBAE4AQQBHAEUARAAgAFMATwBJAEwAUwAsACAAQQBOAEQAIABDAE8AMgAgAEUATQBJAFMAUwBJAE8ATgBTACAARgBSAE8ATQAgAEwASQBNAEUAIABBAE4ARAAgAFUAUgBFAEEAIABBAFAAUABMAEkAQwBBAFQASQBPAE4AXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AKgAvAFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgByAGEAYwBXAEUAVABJAHIAcgBpAGcAYQB0AGkAbwBuAF8AVABpAHQAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBGAHIAYQBjAFcARQBUACAAZgBvAHIAIABpAHIAcgBpAGcAYQB0AGkAbwBuACAAdAB5AHAAZQBzAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAHIAYQBjAFcARQBUAEkAcgByAGkAZwBhAHQAaQBvAG4AXwBVAG4AaQB0AFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBkAGkAbQBlAG4AcwBpAG8AbgBsAGUAcwBzAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAHIAYQBjAFcARQBUAEkAcgByAGkAZwBhAHQAaQBvAG4AXwBTAG8AdQByAGMAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAVgBFAEUAUgBHACAAMgAwADIANgA6ACAAQwBoAGEAcAB0AGUAcgAgADEALAAgAHMAZQBjAHQAaQBvAG4AIAAxAC4AOAAuADIAIABMAGUAYQBjAGgAaQBuAGcALAAgAGMAbABpAG0AYQB0AGUAIABhAG4AZAAgAHIAYQBpAG4AZgBhAGwAbAAgAHoAbwBuAGUAcwBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgByAGEAYwBXAEUAVABJAHIAcgBpAGcAYQB0AGkAbwBuAF8ATgBJAFIAUgBlAGYAZQByAGUAbgBjAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAEkAUABDAEMAIAAyADAAMQA5ACAAUgBlAGYAaQBuAGUAbQBlAG4AdAAgAFYAbwBsAHUAbQBlACAANAA6ACAAQwBoAGEAcAB0AGUAcgAgADEAMQA6ACAATgAyAE8AIABFAG0AaQBzAHMAaQBvAG4AcwAgAGYAcgBvAG0AIABNAGEAbgBhAGcAZQBkACAAUwBvAGkAbABzACwAIABhAG4AZAAgAEMATwAyACAARQBtAGkAcwBzAGkAbwBuAHMAIABmAHIAbwBtACAATABpAG0AZQAgAGEAbgBkACAAVQByAGUAYQAgAEEAcABwAGwAaQBjAGEAdABpAG8AbgBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgByAGEAYwBXAEUAVABJAHIAcgBpAGcAYQB0AGkAbwBuAF8ARABhAHQAYQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABNAEEASwBFAEEAUgBSAEEAWQAoADYALAAgADIALAAgAFwAbgAgACAAIAAgACAAIABMAEEATQBCAEQAQQAoAHIALABjACwAIABcAG4AIAAgACAAIAAgACAAIAAgAEkATgBEAEUAWAAoAHsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEkAcgByAGkAZwBhAHQAaQBvAG4AIAB0AHkAcABlACAAaQByAFwAIgAsAFwAIgBGAHIAYQBjAFcARQBUAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBOAG8AdAAgAGkAcgByAGkAZwBhAHQAZQBkAFwAIgAsACAAMAA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBEAHIAaQBwACAAaQByAHIAaQBnAGEAdABpAG8AbgBcACIALAAgADAAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAUwBwAHIAaQBuAGsAbABlAHIAIABpAHIAcgBpAGcAYQB0AGkAbwBuAFwAIgAsACAAMQA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBTAHUAcgBmAGEAYwBlACAAaQByAHIAaQBnAGEAdABpAG8AbgBcACIALAAgADEAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIATwB0AGgAZQByACAAaQByAHIAaQBnAGEAdABpAG8AbgBcACIALAAgADEAXABuACAAIAAgACAAIAAgACAAIAB9ACwAIAByACwAIABjACkAXABuACAAIAAgACAAIAAgACkAXABuACAAIAAgACAAKQBcAG4AIAAgACkAOwBcAG4AXABuACAAIABDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAHIAYQBjAFcARQBUAEkAcgByAGkAZwBhAHQAaQBvAG4AXwBWAGEAcgBpAGEAdABpAG8AbgBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAVgBBAFIASQBBAFQASQBPAE4AIABGAFIATwBNACAAUwBPAFUAUgBDAEUAIABEAEEAVABBADoAIABUAGEAYgBsAGUAIABjAHIAZQBhAHQAZQBkACAAYgBhAHMAZQBkACAAbwBuACAAVgBFAEUAUgBHACAAdABlAHgAdAAgACcAQQByAGUAYQBzACAAYQByAGUAIABzAHUAYgBqAGUAYwB0ACAAdABvACAAbABlAGEAYwBoAGkAbgBnACAAKABpAC4AZQAuACwAIABpAG4AIAB0AGgAZQAgAGwAZQBhAGMAaABpAG4AZwAgAHoAbwBuAGUAKQAgAHcAaABlAG4ALgAuAC4AIAB0AGgAZQAgAGwAYQBuAGQAIABpAHMAIABpAHIAcgBpAGcAYQB0AGUAZAAgACgAZQB4AGMAZQBwAHQAIABkAHIAaQBwACAAaQByAHIAaQBnAGEAdABpAG8AbgApAC4AJwBcACIAKQA7AFwAbgBcAG4AXABuAC8AKgAgAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEUARgBQAGEAcwB0AHUAcgBlAFIAYQBuAGcAZQBBAG4AZABQAGEAZABkAG8AYwBrAFwAbgBUAGEAYgBsAGUAIABBAC4AMgAuADIALgAyADoAIABFAG0AaQBzAHMAaQBvAG4AIABmAGEAYwB0AG8AcgAgAGYAbwByACAAdQByAGkAbgBlACAAYQBuAGQAIABkAHUAbgBnACAAZABlAHAAbwBzAGkAdABlAGQAIABvAG4AIABwAGEAcwB0AHUAcgBlACwAIAByAGEAbgBnAGUAIABvAHIAIABwAGEAZABkAG8AYwBrACAAKABrAGcAIABOADIATwAtAE4ALwBrAGcAIABOACkAIAAoAEUARgBQAFIAUAApAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuACoALwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEUARgBQAGEAcwB0AHUAcgBlAFIAYQBuAGcAZQBBAG4AZABQAGEAZABkAG8AYwBrAF8AVABpAHQAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBFAG0AaQBzAHMAaQBvAG4AIABmAGEAYwB0AG8AcgAgAGYAbwByACAAdQByAGkAbgBlACAAYQBuAGQAIABkAHUAbgBnACAAZABlAHAAbwBzAGkAdABlAGQAIABvAG4AIABwAGEAcwB0AHUAcgBlACwAIAByAGEAbgBnAGUAIABvAHIAIABwAGEAZABkAG8AYwBrAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYAUABhAHMAdAB1AHIAZQBSAGEAbgBnAGUAQQBuAGQAUABhAGQAZABvAGMAawBfAFUAbgBpAHQAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAGsAZwAgAE4AMgBPACAALQAgAE4AIAAvACAAawBnACAATgBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAFAAYQBzAHQAdQByAGUAUgBhAG4AZwBlAEEAbgBkAFAAYQBkAGQAbwBjAGsAXwBTAG8AdQByAGMAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAVgBFAEUAUgBHACAAMgAwADIANgA6ACAAVABhAGIAbABlACAAQQAuADIALgAyAC4AMgBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAFAAYQBzAHQAdQByAGUAUgBhAG4AZwBlAEEAbgBkAFAAYQBkAGQAbwBjAGsAXwBOAEkAUgBSAGUAZgBlAHIAZQBuAGMAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEUARgBQAGEAcwB0AHUAcgBlAFIAYQBuAGcAZQBBAG4AZABQAGEAZABkAG8AYwBrAF8ARABhAHQAYQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABNAEEASwBFAEEAUgBSAEEAWQAoADMALAAgADIALAAgAFwAbgAgACAAIAAgACAAIABMAEEATQBCAEQAQQAoAHIALABjACwAIABcAG4AIAAgACAAIAAgACAAIAAgAEkATgBEAEUAWAAoAHsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEMAbABpAG0AYQB0AGUAIAB6AG8AbgBlAFwAIgAsACAAXAAiAEUARgBQAFIAUABcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVwBlAHQAIABjAGwAaQBtAGEAdABlACAAegBvAG4AZQBcACIALAAgADAALgAwADAANgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBEAHIAeQAgAGMAbABpAG0AYQB0AGUAIAB6AG8AbgBlAFwAIgAsACAAMAAuADAAMAAyAFwAbgAgACAAIAAgACAAIAAgACAAfQAsACAAcgAsACAAYwApAFwAbgAgACAAIAAgACAAIAApAFwAbgAgACAAIAAgACkAXABuACAAIAApADsAXABuAFwAbgAgACAAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAFAAYQBzAHQAdQByAGUAUgBhAG4AZwBlAEEAbgBkAFAAYQBkAGQAbwBjAGsAXwBWAGEAcgBpAGEAdABpAG8AbgBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAVgBBAFIASQBBAFQASQBPAE4AIABGAFIATwBNACAAUwBPAFUAUgBDAEUAIABEAEEAVABBADoAIABDAGgAYQBuAGcAZQBkACAAJwBEAHIAeQAgAGMAbABpAG0AYQB0AGUAIAB6AG8AbgBlAHMAJwAgAHQAbwAgAHMAaQBuAGcAdQBsAGEAcgAgACcARAByAHkAIABjAGwAaQBtAGEAdABlACAAegBvAG4AZQAnACAAdABvACAAYQBpAGQAIABsAG8AbwBrAHUAcAAuAFwAIgApADsAXABuAFwAbgBcAG4ALwAqACAAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ATQBvAG4AdABoAHMAVABvAFMAZQBhAHMAbwBuAHMAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AKgAvAFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ATQBvAG4AdABoAHMAVABvAFMAZQBhAHMAbwBuAHMAXwBUAGkAdABsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAE0AbwBuAHQAaABzACAAdABvACAAUwBlAGEAcwBvAG4AcwAgAE0AYQBwAHAAaQBuAGcAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAE0AbwBuAHQAaABzAFQAbwBTAGUAYQBzAG8AbgBzAF8AVQBuAGkAdABcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAE0AbwBuAHQAaABzAFQAbwBTAGUAYQBzAG8AbgBzAF8AUwBvAHUAcgBjAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBNAG8AbgB0AGgAcwBUAG8AUwBlAGEAcwBvAG4AcwBfAE4ASQBSAFIAZQBmAGUAcgBlAG4AYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ATQBvAG4AdABoAHMAVABvAFMAZQBhAHMAbwBuAHMAXwBEAGEAdABhAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAE0AQQBLAEUAQQBSAFIAQQBZACgAMQAzACwAIAAyACwAIABcAG4AIAAgACAAIAAgACAATABBAE0AQgBEAEEAKAByACwAYwAsACAAXABuACAAIAAgACAAIAAgACAAIABJAE4ARABFAFgAKAB7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBNAG8AbgB0AGgAXAAiACwAIABcACIAUwBlAGEAcwBvAG4AXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEoAYQBuAHUAYQByAHkAXAAiACwAIABcACIAUwB1AG0AbQBlAHIAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEYAZQBiAHIAdQBhAHIAeQBcACIALAAgAFwAIgBTAHUAbQBtAGUAcgBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIATQBhAHIAYwBoAFwAIgAsACAAXAAiAEEAdQB0AHUAbQBuAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBBAHAAcgBpAGwAXAAiACwAIABcACIAQQB1AHQAdQBtAG4AXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAE0AYQB5AFwAIgAsACAAXAAiAEEAdQB0AHUAbQBuAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBKAHUAbgBlAFwAIgAsACAAXAAiAFcAaQBuAHQAZQByAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBKAHUAbAB5AFwAIgAsACAAXAAiAFcAaQBuAHQAZQByAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBBAHUAZwB1AHMAdABcACIALAAgAFwAIgBXAGkAbgB0AGUAcgBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAUwBlAHAAdABlAG0AYgBlAHIAXAAiACwAIABcACIAUwBwAHIAaQBuAGcAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAE8AYwB0AG8AYgBlAHIAXAAiACwAIABcACIAUwBwAHIAaQBuAGcAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAE4AbwB2AGUAbQBiAGUAcgBcACIALAAgAFwAIgBTAHAAcgBpAG4AZwBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIARABlAGMAZQBtAGIAZQByAFwAIgAsACAAXAAiAFMAdQBtAG0AZQByAFwAIgBcAG4AIAAgACAAIAAgACAAIAAgAH0ALAAgAHIALAAgAGMAKQBcAG4AIAAgACAAIAAgACAAKQBcAG4AIAAgACAAIAApAFwAbgAgACAAKQA7AFwAbgBcAG4AIAAgAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAE0AbwBuAHQAaABzAFQAbwBTAGUAYQBzAG8AbgBzAF8AVgBhAHIAaQBhAHQAaQBvAG4AXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFwAIgApADsAXABuAFwAbgBcAG4AXABuAC8AKgAgAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAE0AQwBGAFQAZQBtAHAAZQByAGEAdAB1AHIAZQBaAG8AbgBlAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuACoALwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAE0AQwBGAFQAZQBtAHAAZQByAGEAdAB1AHIAZQBaAG8AbgBlAF8AVABpAHQAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBNAGEAbgB1AHIAZQAgAE0AYQBuAGEAZwBlAG0AZQBuAHQAIAATICAATQBlAHQAaABhAG4AZQAgAGMAbwBuAHYAZQByAHMAaQBvAG4AIABmAGEAYwB0AG8AcgAgAHAAZQByACAAdABlAG0AcABlAHIAYQB0AHUAcgBlACAAegBvAG4AZQAgACgAZgByAGEAYwB0AGkAbwBuACkAIAAoAE0AQwBGAGkAbQApAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBNAEMARgBUAGUAbQBwAGUAcgBhAHQAdQByAGUAWgBvAG4AZQBfAFUAbgBpAHQAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAGYAcgBhAGMAdABpAG8AbgBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ATQBDAEYAVABlAG0AcABlAHIAYQB0AHUAcgBlAFoAbwBuAGUAXwBTAG8AdQByAGMAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAVgBFAEUAUgBHACAAMgAwADIANgA6ACAAVABhAGIAbABlACAAQQAuADEALgA4AC4AMQBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ATQBDAEYAVABlAG0AcABlAHIAYQB0AHUAcgBlAFoAbwBuAGUAXwBEAGEAdABhAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAE0AQQBLAEUAQQBSAFIAQQBZACgAMgAyACwAIAAxADYALAAgAFwAbgAgACAAIAAgACAAIABMAEEATQBCAEQAQQAoAHIALABjACwAIABcAG4AIAAgACAAIAAgACAAIAAgAEkATgBEAEUAWAAoAHsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFQAZQBtAHAAZQByAGEAdAB1AHIAZQAgAHoAbwBuAGUAXAAiACwAIABcACIATQBBAFQAIAAoALoAQwApAFwAIgAsACAAXAAiAFUAbgBjAG8AdgBlAHIAZQBkACAAYQBuAGUAcgBvAGIAaQBjACAAbABhAGcAbwBvAG4AXAAiACwAIABcACIAQwBvAHYAZQByAGUAZAAgAGwAYQBnAG8AbwBuAFwAIgAsACAAXAAiAEwAaQBxAHUAaQBkACAAUwBsAHUAcgByAHkAIAAoAHcAaQB0AGgAbwB1AHQAIABuAGEAdAB1AHIAYQBsACAAYwByAHUAcwB0ACkAXAAiACwAIABcACIARABhAGkAbAB5ACAAcwBwAHIAZQBhAGQAIAAoAGIAKQBcACIALAAgAFwAIgBDAG8AbQBwAG8AcwB0AGkAbgBnACAAKABwAGEAcwBzAGkAdgBlACAAdwBpAG4AZAByAG8AdwApAFwAIgAsACAAXAAiAFMAbwBsAGkAZAAgAFMAdABvAHIAYQBnAGUAXAAiACwAIABcACIAUABpAHQAIABTAHQAbwByAGEAZwBlACAAPAAxACAAbQBvAG4AdABoAFwAIgAsACAAXAAiAEQAZQBlAHAAIABMAGkAdAB0AGUAcgBcACIALAAgAFwAIgBQAG8AdQBsAHQAcgB5ACAATQBhAG4AdQByAGUAIAAoAHcAaQB0AGgALwB3AGkAdABoAG8AdQB0ACAAbABpAHQAdABlAHIAKQBcACIALAAgAFwAIgBcACIALAAgAFwAIgBEAGkAcgBlAGMAdAAgAHAAcgBvAGMAZQBzAHMAaQBuAGcAIABpAG4AdABvACAAcABlAGwAbABlAHQAaQB6AGUAZAAgAGYAZQByAHQAaQBsAGkAcwBlAHIAXAAiACwAIABcACIARABpAHIAZQBjAHQAIABhAHAAcABsAGkAYwBhAHQAaQBvAG4AIAB0AG8AIABzAG8AaQBsAFwAIgAsACAAXAAiAFAAYQBzAHQAdQByAGUALAAgAFIAYQBuAGcAZQAgAGEAbgBkACAAUABhAGQAZABvAGMAawAgACgAYwApACgAZAApAFwAIgAsACAAXAAiAE0AQQBUACAAcgBhAHcAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEMAbwBvAGwAXAAiACwAIABcACIAZCIxADAAXAAiACwAIAAwAC4ANgA2ACwAIAAwAC4AMQAsACAAMAAuADEALAAgADAALgAwADAAMQAsACAAMAAuADAAMAA1ACwAIAAwAC4AMAAyACwAIAAwAC4AMAAzACwAIAAwAC4AMAA0ACwAIAAwAC4AMAAxADUALAAgADAALgAwADEANQAsACAAMAAsACAAMAAsACAAMAAuADAAMAA0ADcALAAgADEAMAA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBDAG8AbwBsAFwAIgAsACAAMQAxACwAIAAwAC4ANgA4ACwAIAAwAC4AMQAsACAAMAAuADEAMQAsACAAMAAuADAAMAAxACwAIAAwAC4AMAAwADUALAAgADAALgAwADIALAAgADAALgAwADMALAAgADAALgAwADQALAAgADAALgAwADEANQAsACAAMAAuADAAMQA1ACwAIAAwACwAIAAwACwAIAAwAC4AMAAwADQANwAsACAAMQAxADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEMAbwBvAGwAXAAiACwAIAAxADIALAAgADAALgA3ACwAIAAwAC4AMQAsACAAMAAuADEAMwAsACAAMAAuADAAMAAxACwAIAAwAC4AMAAwADUALAAgADAALgAwADIALAAgADAALgAwADMALAAgADAALgAwADQALAAgADAALgAwADEANQAsACAAMAAuADAAMQA1ACwAIAAwACwAIAAwACwAIAAwAC4AMAAwADQANwAsACAAMQAyADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEMAbwBvAGwAXAAiACwAIAAxADMALAAgADAALgA3ADEALAAgADAALgAxACwAIAAwAC4AMQA0ACwAIAAwAC4AMAAwADEALAAgADAALgAwADAANQAsACAAMAAuADAAMgAsACAAMAAuADAAMwAsACAAMAAuADAANAAsACAAMAAuADAAMQA1ACwAIAAwAC4AMAAxADUALAAgADAALAAgADAALAAgADAALgAwADAANAA3ACwAIAAxADMAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAQwBvAG8AbABcACIALAAgADEANAAsACAAMAAuADcAMwAsACAAMAAuADEALAAgADAALgAxADUALAAgADAALgAwADAAMQAsACAAMAAuADAAMAA1ACwAIAAwAC4AMAAyACwAIAAwAC4AMAAzACwAIAAwAC4AMAA0ACwAIAAwAC4AMAAxADUALAAgADAALgAwADEANQAsACAAMAAsACAAMAAsACAAMAAuADAAMAA0ADcALAAgADEANAA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBUAGUAbQBwAGUAcgBhAHQAZQBcACIALAAgADEANQAsACAAMAAuADcANAAsACAAMAAuADEALAAgADAALgAxADcALAAgADAALgAwADAANQAsACAAMAAuADAAMQAsACAAMAAuADAAMgAsACAAMAAuADAAMwAsACAAMAAuADAANAAsACAAMAAuADAAMQA1ACwAIAAwAC4AMAAxADUALAAgADAALAAgADAALAAgADAALgAwADAANAA3ACwAIAAxADUAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVABlAG0AcABlAHIAYQB0AGUAXAAiACwAIAAxADYALAAgADAALgA3ADUALAAgADAALgAxACwAIAAwAC4AMQA4ACwAIAAwAC4AMAAwADUALAAgADAALgAwADEALAAgADAALgAwADIALAAgADAALgAwADMALAAgADAALgAwADQALAAgADAALgAwADEANQAsACAAMAAuADAAMQA1ACwAIAAwACwAIAAwACwAIAAwAC4AMAAwADQANwAsACAAMQA2ADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFQAZQBtAHAAZQByAGEAdABlAFwAIgAsACAAMQA3ACwAIAAwAC4ANwA2ACwAIAAwAC4AMQAsACAAMAAuADIALAAgADAALgAwADAANQAsACAAMAAuADAAMQAsACAAMAAuADAAMgAsACAAMAAuADAAMwAsACAAMAAuADAANAAsACAAMAAuADAAMQA1ACwAIAAwAC4AMAAxADUALAAgADAALAAgADAALAAgADAALgAwADAANAA3ACwAIAAxADcAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVABlAG0AcABlAHIAYQB0AGUAXAAiACwAIAAxADgALAAgADAALgA3ADcALAAgADAALgAxACwAIAAwAC4AMgAyACwAIAAwAC4AMAAwADUALAAgADAALgAwADEALAAgADAALgAwADIALAAgADAALgAwADMALAAgADAALgAwADQALAAgADAALgAwADEANQAsACAAMAAuADAAMQA1ACwAIAAwACwAIAAwACwAIAAwAC4AMAAwADQANwAsACAAMQA4ADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFQAZQBtAHAAZQByAGEAdABlAFwAIgAsACAAMQA5ACwAIAAwAC4ANwA3ACwAIAAwAC4AMQAsACAAMAAuADIANAAsACAAMAAuADAAMAA1ACwAIAAwAC4AMAAxACwAIAAwAC4AMAAyACwAIAAwAC4AMAAzACwAIAAwAC4AMAA0ACwAIAAwAC4AMAAxADUALAAgADAALgAwADEANQAsACAAMAAsACAAMAAsACAAMAAuADAAMAA0ADcALAAgADEAOQA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBUAGUAbQBwAGUAcgBhAHQAZQBcACIALAAgADIAMAAsACAAMAAuADcAOAAsACAAMAAuADEALAAgADAALgAyADYALAAgADAALgAwADAANQAsACAAMAAuADAAMQAsACAAMAAuADAAMgAsACAAMAAuADAAMwAsACAAMAAuADAANAAsACAAMAAuADAAMQA1ACwAIAAwAC4AMAAxADUALAAgADAALAAgADAALAAgADAALgAwADAANAA3ACwAIAAyADAAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVABlAG0AcABlAHIAYQB0AGUAXAAiACwAIAAyADEALAAgADAALgA3ADgALAAgADAALgAxACwAIAAwAC4AMgA5ACwAIAAwAC4AMAAwADUALAAgADAALgAwADEALAAgADAALgAwADIALAAgADAALgAwADMALAAgADAALgAwADQALAAgADAALgAwADEANQAsACAAMAAuADAAMQA1ACwAIAAwACwAIAAwACwAIAAwAC4AMAAwADQANwAsACAAMgAxADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFQAZQBtAHAAZQByAGEAdABlAFwAIgAsACAAMgAyACwAIAAwAC4ANwA4ACwAIAAwAC4AMQAsACAAMAAuADMAMQAsACAAMAAuADAAMAA1ACwAIAAwAC4AMAAxACwAIAAwAC4AMAAyACwAIAAwAC4AMAAzACwAIAAwAC4AMAA0ACwAIAAwAC4AMAAxADUALAAgADAALgAwADEANQAsACAAMAAsACAAMAAsACAAMAAuADAAMAA0ADcALAAgADIAMgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBUAGUAbQBwAGUAcgBhAHQAZQBcACIALAAgADIAMwAsACAAMAAuADcAOQAsACAAMAAuADEALAAgADAALgAzADQALAAgADAALgAwADAANQAsACAAMAAuADAAMQAsACAAMAAuADAAMgAsACAAMAAuADAAMwAsACAAMAAuADAANAAsACAAMAAuADAAMQA1ACwAIAAwAC4AMAAxADUALAAgADAALAAgADAALAAgADAALgAwADAANAA3ACwAIAAyADMAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVABlAG0AcABlAHIAYQB0AGUAXAAiACwAIAAyADQALAAgADAALgA3ADkALAAgADAALgAxACwAIAAwAC4AMwA3ACwAIAAwAC4AMAAwADUALAAgADAALgAwADEALAAgADAALgAwADIALAAgADAALgAwADMALAAgADAALgAwADQALAAgADAALgAwADEANQAsACAAMAAuADAAMQA1ACwAIAAwACwAIAAwACwAIAAwAC4AMAAwADQANwAsACAAMgA0ADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFQAZQBtAHAAZQByAGEAdABlAFwAIgAsACAAMgA1ACwAIAAwAC4ANwA5ACwAIAAwAC4AMQAsACAAMAAuADQAMQAsACAAMAAuADAAMAA1ACwAIAAwAC4AMAAxACwAIAAwAC4AMAAyACwAIAAwAC4AMAAzACwAIAAwAC4AMAA0ACwAIAAwAC4AMAAxADUALAAgADAALgAwADEANQAsACAAMAAsACAAMAAsACAAMAAuADAAMAA0ADcALAAgADIANQA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBXAGEAcgBtAFwAIgAsACAAMgA2ACwAIAAwAC4ANwA5ACwAIAAwAC4AMQAsACAAMAAuADQANAAsACAAMAAuADAAMQAsACAAMAAuADAAMQA1ACwAIAAwAC4AMAAyACwAIAAwAC4AMAAzACwAIAAwAC4AMAA0ACwAIAAwAC4AMAAxADUALAAgADAALgAwADEANQAsACAAMAAsACAAMAAsACAAMAAuADAAMAA0ADcALAAgADIANgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBXAGEAcgBtAFwAIgAsACAAMgA3ACwAIAAwAC4AOAAsACAAMAAuADEALAAgADAALgA0ADgALAAgADAALgAwADEALAAgADAALgAwADEANQAsACAAMAAuADAAMgAsACAAMAAuADAAMwAsACAAMAAuADAANAAsACAAMAAuADAAMQA1ACwAIAAwAC4AMAAxADUALAAgADAALAAgADAALAAgADAALgAwADAANAA3ACwAIAAyADcAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVwBhAHIAbQBcACIALAAgAFwAIgBlIjIAOABcACIALAAgADAALgA4ACwAIAAwAC4AMQAsACAAMAAuADUALAAgADAALgAwADEALAAgADAALgAwADEANQAsACAAMAAuADAAMgAsACAAMAAuADAAMwAsACAAMAAuADAANAAsACAAMAAuADAAMQA1ACwAIAAwAC4AMAAxADUALAAgADAALAAgADAALAAgADAALgAwADAANAA3ACwAIAAyADgAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAXAAiACwAIABcACIAXAAiACwAIABcACIAQQBuAGEAZQByAG8AYgBpAGMAIABsAGEAZwBvAG8AbgBcACIALAAgAFwAIgBEAGkAZwBlAHMAdABlAHIAIAAvACAAYwBvAHYAZQByAGUAZAAgAGwAYQBnAG8AbwBuAHMAXAAiACwAIABcACIATABpAHEAdQBpAGQAIABzAHkAcwB0AGUAbQBzAFwAIgAsACAAXAAiAEQAYQBpAGwAeQAgAHMAcAByAGUAYQBkAFwAIgAsACAAXAAiAEMAbwBtAHAAbwBzAHQAaQBuAGcAIAAoAHAAYQBzAHMAaQB2AGUAIAB3AGkAbgBkAHIAbwB3ACkAXAAiACwAIABcACIAUwBvAGwAaQBkACAAcwB0AG8AcgBhAGcAZQBcACIALAAgAFwAIgBQAGkAdAAgAHMAdABvAHIAYQBnAGUAXAAiACwAIABcACIARABlAGUAcAAgAGwAaQB0AHQAZQByAFwAIgAsACAAXAAiAFAAbwB1AGwAdAByAHkAIABtAGEAbgB1AHIAZQAgAHcAaQB0AGgAIABiAGUAZABkAGkAbgBnAFwAIgAsACAAXAAiAFAAbwB1AGwAdAByAHkAIABtAGEAbgB1AHIAZQAgAHcAaQB0AGgAbwB1AHQAIABiAGUAZABkAGkAbgBnAFwAIgAsACAAXAAiAEQAaQByAGUAYwB0ACAAcAByAG8AYwBlAHMAcwBpAG4AZwBcACIALAAgAFwAIgBEAGkAcgBlAGMAdAAgAGEAcABwAGwAaQBjAGEAdABpAG8AbgBcACIALAAgAFwAIgBQAGEAcwB0AHUAcgBlACAAcgBhAG4AZwBlACAAYQBuAGQAIABwAGEAZABkAG8AYwBrAFwAIgAsACAAXAAiAE0AQQBUACAAcgBhAHcAXAAiACAAXABuACAAIAAgACAAIAAgACAAIAB9ACwAIAByACwAIABjACkAXABuACAAIAAgACAAIAAgACkAXABuACAAIAAgACAAKQBcAG4AIAAgACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAE0AQwBGAFQAZQBtAHAAZQByAGEAdAB1AHIAZQBaAG8AbgBlAF8AVgBhAHIAaQBhAHQAaQBvAG4AXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFYAQQBSAEkAQQBUAEkATwBOACAARgBSAE8ATQAgAFMATwBVAFIAQwBFADoAIABBAGQAZABlAGQAIAByAG8AdwAgAG8AZgAgAE4ASQBSACAATQBNAEEAIABkAGUAZgBpAG4AaQB0AGkAbwBuAHMAIAB0AG8AIABhAGkAZAAgAGwAbwBvAGsAdQBwAC4AIABEAHUAcABsAGkAYwBhAHQAZQBkACAAJwBQAG8AdQBsAHQAcgB5ACAAdwBpAHQAaAAgAGEAbgBkACAAdwBpAHQAaABvAHUAdAAgAGwAaQB0AHQAZQByACcAIABjAG8AbAB1AG0AbgAgAHcAaQB0AGgAIABzAGUAcABhAHIAYQB0AGUAIABOAEkAUgAgAGQAZQBmAGkAbgBpAHQAaQBvAG4AcwAgAHQAbwAgAGEAaQBkACAAbABvAG8AawB1AHAALgAgAEEAZABkAGUAZAAgACcATQBBAFQAIAByAGEAdwAnACAAYwBvAGwAdQBtAG4AIAB0AG8AIABhAGwAbABvAHcAIABsAG8AbwBrAHUAcAAgAG8AZgAgAG4AdQBtAGIAZQByAHMALgBcACIAKQA7AFwAbgBcAG4AXABuAFwAbgAvACoAIABcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYATwByAGcAYQBuAGkAYwBGAGUAcgB0AGkAbABpAHMAZQByAEEAbgBkAEMAcgBvAHAAUgBlAHMAaQBkAHUAZQBzAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuACoALwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEUARgBPAHIAZwBhAG4AaQBjAEYAZQByAHQAaQBsAGkAcwBlAHIAQQBuAGQAQwByAG8AcABSAGUAcwBpAGQAdQBlAHMAXwBUAGkAdABsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAEUAbQBpAHMAcwBpAG8AbgAgAGYAYQBjAHQAbwByACAAZgBvAHIAIABvAHIAZwBhAG4AaQBjACAAZgBlAHIAdABpAGwAaQBzAGUAcgAgAGEAbgBkACAAYwByAG8AcAAgAHIAZQBzAGkAZAB1AGUAcwAgAHIAZQB0AHUAcgBuAGUAZAAgAHQAbwAgAHQAaABlACAAcwBvAGkAbABcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAE8AcgBnAGEAbgBpAGMARgBlAHIAdABpAGwAaQBzAGUAcgBBAG4AZABDAHIAbwBwAFIAZQBzAGkAZAB1AGUAcwBfAFYAYQByAGkAYQBiAGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIARQBGAE4AaQAgACYAIABFAEYATgAyAE8AaQBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAE8AcgBnAGEAbgBpAGMARgBlAHIAdABpAGwAaQBzAGUAcgBBAG4AZABDAHIAbwBwAFIAZQBzAGkAZAB1AGUAcwBfAFUAbgBpAHQAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAGsAZwAgAE4AMgBPACAALQAgAE4AIAAvACAAawBnACAATgBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAE8AcgBnAGEAbgBpAGMARgBlAHIAdABpAGwAaQBzAGUAcgBBAG4AZABDAHIAbwBwAFIAZQBzAGkAZAB1AGUAcwBfAFMAbwB1AHIAYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBWAEUARQBSAEcAIAAyADAAMgA2ADoAIABUAGEAYgBsAGUAIABBAC4AMgAuADEALgA0AFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYATwByAGcAYQBuAGkAYwBGAGUAcgB0AGkAbABpAHMAZQByAEEAbgBkAEMAcgBvAHAAUgBlAHMAaQBkAHUAZQBzAF8ATgBJAFIAUgBlAGYAZQByAGUAbgBjAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYATwByAGcAYQBuAGkAYwBGAGUAcgB0AGkAbABpAHMAZQByAEEAbgBkAEMAcgBvAHAAUgBlAHMAaQBkAHUAZQBzAF8ARABhAHQAYQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABNAEEASwBFAEEAUgBSAEEAWQAoADMALAAgADIALAAgAFwAbgAgACAAIAAgACAAIABMAEEATQBCAEQAQQAoAHIALABjACwAIABcAG4AIAAgACAAIAAgACAAIAAgAEkATgBEAEUAWAAoAHsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEMAbABpAG0AYQB0AGUAIAB6AG8AbgBlAFwAIgAsACAAXAAiAEUARgBOAGkAIAAmACAARQBGAE4AMgBPAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBXAGUAdAAgAGMAbABpAG0AYQB0AGUAIAB6AG8AbgBlAFwAIgAsACAAMAAuADAAMAA2ADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEQAcgB5ACAAYwBsAGkAbQBhAHQAZQAgAHoAbwBuAGUAXAAiACwAIAAwAC4AMAAwADUAXABuACAAIAAgACAAIAAgACAAIAB9ACwAIAByACwAIABjACkAXABuACAAIAAgACAAIAAgACkAXABuACAAIAAgACAAKQBcAG4AIAAgACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEUARgBPAHIAZwBhAG4AaQBjAEYAZQByAHQAaQBsAGkAcwBlAHIAQQBuAGQAQwByAG8AcABSAGUAcwBpAGQAdQBlAHMAXwBWAGEAcgBpAGEAdABpAG8AbgBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAXAAiACkAOwBcAG4AXABuAFwAbgBcAG4AXABuAFwAbgBcAG4AXABuAFwAbgBcAG4AXABuAFwAbgBcAG4AXABuAFwAbgBcAG4AXABuACIAfQBdACwAIgBwAHIAbwBqAGUAYwB0AE4AYQBtAGUAcwAiADoAWwAiAEMAbwBtAG0AbwBuAF8ARQBxAHUAYQB0AGkAbwBuAHMALgBDAG8AbQBtAG8AbgBfAEMAbwBuAHYAZQByAHQATgAyAE8AVABvAEMATwAyAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBFAHEAdQBhAHQAaQBvAG4AcwAuAEMAbwBtAG0AbwBuAF8AQwBvAG4AdgBlAHIAdABOADIATwBUAG8AQwBPADIAZQBfAFQAaQB0AGwAZQAiACwAIgBDAG8AbQBtAG8AbgBfAEUAcQB1AGEAdABpAG8AbgBzAC4AQwBvAG0AbQBvAG4AXwBDAG8AbgB2AGUAcgB0AE4AMgBPAFQAbwBDAE8AMgBlAF8AVgBhAHIAaQBhAGIAbABlACIALAAiAEMAbwBtAG0AbwBuAF8ARQBxAHUAYQB0AGkAbwBuAHMALgBDAG8AbQBtAG8AbgBfAEMAbwBuAHYAZQByAHQATgAyAE8AVABvAEMATwAyAGUAXwBVAG4AaQB0ACIALAAiAEMAbwBtAG0AbwBuAF8ARQBxAHUAYQB0AGkAbwBuAHMALgBDAG8AbQBtAG8AbgBfAEMAbwBuAHYAZQByAHQATgAyAE8AVABvAEMATwAyAGUAXwBOAEkAUgBSAGUAZgBlAHIAZQBuAGMAZQAiACwAIgBDAG8AbQBtAG8AbgBfAEUAcQB1AGEAdABpAG8AbgBzAC4AQwBvAG0AbQBvAG4AXwBDAG8AbgB2AGUAcgB0AE4AMgBPAFQAbwBDAE8AMgBlAF8ATABhAHQAZQB4AEUAcQB1AGEAdABpAG8AbgAiACwAIgBDAG8AbQBtAG8AbgBfAEUAcQB1AGEAdABpAG8AbgBzAC4AQwBvAG0AbQBvAG4AXwBDAG8AbgB2AGUAcgB0AE4AMgBPAFQAbwBDAE8AMgBlAF8AQQByAGcAdQBtAGUAbgB0AHMAIgAsACIAQwBvAG0AbQBvAG4AXwBFAHEAdQBhAHQAaQBvAG4AcwAuAEMAbwBtAG0AbwBuAF8AQwBvAG4AdgBlAHIAdABDAEgANABUAG8AQwBPADIAZQAiACwAIgBDAG8AbQBtAG8AbgBfAEUAcQB1AGEAdABpAG8AbgBzAC4AQwBvAG0AbQBvAG4AXwBDAG8AbgB2AGUAcgB0AEMASAA0AFQAbwBDAE8AMgBlAF8AVABpAHQAbABlACIALAAiAEMAbwBtAG0AbwBuAF8ARQBxAHUAYQB0AGkAbwBuAHMALgBDAG8AbQBtAG8AbgBfAEMAbwBuAHYAZQByAHQAQwBIADQAVABvAEMATwAyAGUAXwBWAGEAcgBpAGEAYgBsAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBFAHEAdQBhAHQAaQBvAG4AcwAuAEMAbwBtAG0AbwBuAF8AQwBvAG4AdgBlAHIAdABDAEgANABUAG8AQwBPADIAZQBfAFUAbgBpAHQAIgAsACIAQwBvAG0AbQBvAG4AXwBFAHEAdQBhAHQAaQBvAG4AcwAuAEMAbwBtAG0AbwBuAF8AQwBvAG4AdgBlAHIAdABDAEgANABUAG8AQwBPADIAZQBfAE4ASQBSAFIAZQBmAGUAcgBlAG4AYwBlACIALAAiAEMAbwBtAG0AbwBuAF8ARQBxAHUAYQB0AGkAbwBuAHMALgBDAG8AbQBtAG8AbgBfAEMAbwBuAHYAZQByAHQAQwBIADQAVABvAEMATwAyAGUAXwBMAGEAdABlAHgARQBxAHUAYQB0AGkAbwBuACIALAAiAEMAbwBtAG0AbwBuAF8ARQBxAHUAYQB0AGkAbwBuAHMALgBDAG8AbQBtAG8AbgBfAEMAbwBuAHYAZQByAHQAQwBIADQAVABvAEMATwAyAGUAXwBBAHIAZwB1AG0AZQBuAHQAcwAiACwAIgBDAG8AbQBtAG8AbgBfAEkAbgBwAHUAdABGAHUAbgBjAHQAaQBvAG4AcwAuAFUAdABpAGwAaQB0AHkAXwBHAGUAdABBAHIAcgBhAHkAVABhAGIAbABlAFIAbwB3AFMAdABhAHIAdABOAHUAbQBiAGUAcgAiACwAIgBDAG8AbQBtAG8AbgBfAEkAbgBwAHUAdABGAHUAbgBjAHQAaQBvAG4AcwAuAFUAdABpAGwAaQB0AHkAXwBHAGUAdABBAHIAcgBhAHkAVABhAGIAbABlAEMAbwBsAHUAbQBuAFMAdABhAHIAdABOAHUAbQBiAGUAcgAiACwAIgBDAG8AbQBtAG8AbgBfAEkAbgBwAHUAdABGAHUAbgBjAHQAaQBvAG4AcwAuAFUAdABpAGwAaQB0AHkAXwBEAGkAcwBwAGwAYQB5AEEAcgByAGEAeQBJAG4AVABhAGIAbABlACIALAAiAEMAbwBtAG0AbwBuAF8ASQBuAHAAdQB0AEYAdQBuAGMAdABpAG8AbgBzAC4AVQB0AGkAbABpAHQAeQBfAEwAbwBvAGsAdQBwAFYAYQBsAHUAZQBJAG4AVABhAGIAbABlACIALAAiAEMAbwBtAG0AbwBuAF8ASQBuAHAAdQB0AEYAdQBuAGMAdABpAG8AbgBzAC4AVQB0AGkAbABpAHQAeQBfAEwAbwBvAGsAdQBwAFYAYQBsAHUAZQBJAG4AVABhAGIAbABlAE4AdQBtAGIAZQByACIALAAiAEMAbwBtAG0AbwBuAF8ASQBuAHAAdQB0AEYAdQBuAGMAdABpAG8AbgBzAC4AVQB0AGkAbABpAHQAeQBfAEwAbwBvAGsAdQBwAFYAYQBsAHUAZQBJAG4AVABhAGIAbABlAFQAdwBvAEMAbwBsAHUAbQBuAHMAIgAsACIAQwBvAG0AbQBvAG4AXwBJAG4AcAB1AHQARgB1AG4AYwB0AGkAbwBuAHMALgBVAHQAaQBsAGkAdAB5AF8ATABvAG8AawB1AHAAVgBhAGwAdQBlAEkAbgBUAGEAYgBsAGUATwBuAGUAQwBvAGwAdQBtAG4AQQBuAGQASABlAGEAZABlAHIAIgAsACIAQwBvAG0AbQBvAG4AXwBJAG4AcAB1AHQARgB1AG4AYwB0AGkAbwBuAHMALgBVAHQAaQBsAGkAdAB5AF8AUwBwAGwAaQB0AFMAdAByAGkAbgBnAEkAbgB0AG8AQQByAHIAYQB5ACIALAAiAEMAbwBtAG0AbwBuAF8ASQBuAHAAdQB0AEYAdQBuAGMAdABpAG8AbgBzAC4AVQB0AGkAbABpAHQAeQBfAEcAZQB0AEMAbABpAG0AYQB0AGUAWgBvAG4AZQAiACwAIgBDAG8AbQBtAG8AbgBfAEkAbgBwAHUAdABGAHUAbgBjAHQAaQBvAG4AcwAuAFUAdABpAGwAaQB0AHkAXwBMAG8AbwBrAHUAcABJAHQAZQBtAEYAcgBvAG0ATQBpAG4ATQBhAHgAIgAsACIAQwBvAG0AbQBvAG4AXwBJAG4AcAB1AHQARgB1AG4AYwB0AGkAbwBuAHMALgBVAHQAaQBsAGkAdAB5AF8AUwB1AG0AUQB1AGEAbgB0AGkAdAB5AEYAcgBvAG0AQwByAGkAdABlAHIAaQBhACIALAAiAEMAbwBtAG0AbwBuAF8ASQBuAHAAdQB0AEYAdQBuAGMAdABpAG8AbgBzAC4AZwBlAHQATwB2AGUAcgBsAGEAcABwAGkAbgBnAFIAZQBwAG8AcgB0AGkAbgBnAFAAZQByAGkAbwBkAHMAIgAsACIAQwBvAG0AbQBvAG4AXwBJAG4AcAB1AHQARgB1AG4AYwB0AGkAbwBuAHMALgBVAHQAaQBsAGkAdAB5AF8ARABpAHMAcABsAGEAeQBGAHUAbgBjAHQAaQBvAG4ATgBhAG0AZQAiACwAIgBDAG8AbQBtAG8AbgBfAEkAbgBwAHUAdABGAHUAbgBjAHQAaQBvAG4AcwAuAFUAdABpAGwAaQB0AHkAXwBMAG8AbwBrAHUAcABOADIATwBFAEYARgByAG8AbQBQAHIAbwBkAEkAcgByAGkAZwBhAHQAaQBvAG4AUgBhAGkAbgBmAGEAbABsACIALAAiAEMAbwBtAG0AbwBuAF8ASQBuAHAAdQB0AEYAdQBuAGMAdABpAG8AbgBzAC4AQwBvAG0AbQBvAG4AQwByAG8AcABwAGkAbgBnAF8ARwBlAHQARgByAGEAYwBXAEUAVAAiACwAIgBDAG8AbQBtAG8AbgBfAEkAbgBwAHUAdABGAHUAbgBjAHQAaQBvAG4AcwAuAFUAdABpAGwAaQB0AHkAXwBDAG8AbgB2AGUAcgB0AFMAdABhAHQAZQBDAG8AbQBtAG8AbgBOAGEAbQBlAFQAbwBBAGIAYgByAGUAdgBpAGEAdABpAG8AbgAiACwAIgBDAG8AbQBtAG8AbgBfAEkAbgBwAHUAdABGAHUAbgBjAHQAaQBvAG4AcwAuAFUAdABpAGwAaQB0AHkAXwBTAG8AdQByAGMAZQBIAHkAcABlAHIAbABpAG4AawBEAGkAZgBmAGUAcgBlAG4AdABTAGgAZQBlAHQAIgAsACIAQwBvAG0AbQBvAG4AXwBJAG4AcAB1AHQARgB1AG4AYwB0AGkAbwBuAHMALgBVAHQAaQBsAGkAdAB5AF8AUgBlAHMAdQBsAHQAcwBJAHQAZQBtAEYAcgBvAG0ARQBxAHUAYQB0AGkAbwBuAFQAaQB0AGwAZQBBAG4AZABTAG8AdQByAGMAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGUAbgBzAGkAdAB5AE8AZgBNAGUAdABoAGEAbgBlAF8AVABpAHQAbABlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEQAZQBuAHMAaQB0AHkATwBmAE0AZQB0AGgAYQBuAGUAXwBVAG4AaQB0ACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEQAZQBuAHMAaQB0AHkATwBmAE0AZQB0AGgAYQBuAGUAXwBTAG8AdQByAGMAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGUAbgBzAGkAdAB5AE8AZgBNAGUAdABoAGEAbgBlAF8ARABhAHQAYQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBDAG8AbgB2AGUAcgB0AE4AMgBvAEUAbABlAG0AZQBuAHQAYQBsAFQAbwBNAG8AbABlAGMAdQBsAGEAcgBDAGcAXwBUAGkAdABsAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQwBvAG4AdgBlAHIAdABOADIAbwBFAGwAZQBtAGUAbgB0AGEAbABUAG8ATQBvAGwAZQBjAHUAbABhAHIAQwBnAF8AVgBhAHIAaQBhAGIAbABlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEMAbwBuAHYAZQByAHQATgAyAG8ARQBsAGUAbQBlAG4AdABhAGwAVABvAE0AbwBsAGUAYwB1AGwAYQByAEMAZwBfAFUAbgBpAHQAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQwBvAG4AdgBlAHIAdABOADIAbwBFAGwAZQBtAGUAbgB0AGEAbABUAG8ATQBvAGwAZQBjAHUAbABhAHIAQwBnAF8AUwBvAHUAcgBjAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQwBvAG4AdgBlAHIAdABOADIAbwBFAGwAZQBtAGUAbgB0AGEAbABUAG8ATQBvAGwAZQBjAHUAbABhAHIAQwBnAF8ARABhAHQAYQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBDAG8AbgB2AGUAcgB0AEcAYQBzAEUAbABlAG0AZQBuAHQAYQBsAFQAbwBNAG8AbABlAGMAdQBsAGEAcgBfAFQAaQB0AGwAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBDAG8AbgB2AGUAcgB0AEcAYQBzAEUAbABlAG0AZQBuAHQAYQBsAFQAbwBNAG8AbABlAGMAdQBsAGEAcgBfAFYAYQByAGkAYQBiAGwAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBDAG8AbgB2AGUAcgB0AEcAYQBzAEUAbABlAG0AZQBuAHQAYQBsAFQAbwBNAG8AbABlAGMAdQBsAGEAcgBfAFUAbgBpAHQAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQwBvAG4AdgBlAHIAdABHAGEAcwBFAGwAZQBtAGUAbgB0AGEAbABUAG8ATQBvAGwAZQBjAHUAbABhAHIAXwBTAG8AdQByAGMAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBDAG8AbgB2AGUAcgB0AEcAYQBzAEUAbABlAG0AZQBuAHQAYQBsAFQAbwBNAG8AbABlAGMAdQBsAGEAcgBfAEQAYQB0AGEAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARwBXAFAAXwBUAGkAdABsAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARwBXAFAAXwBWAGEAcgBpAGEAYgBsAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARwBXAFAAXwBVAG4AaQB0ACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEcAVwBQAF8AUwBvAHUAcgBjAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARwBXAFAAXwBEAGEAdABhACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEEAdQBzAHQAcgBhAGwAaQBhAG4AUwB0AGEAdABlAHMAVABlAHIAcgBpAHQAbwByAGkAZQBzAF8AVABpAHQAbABlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEEAdQBzAHQAcgBhAGwAaQBhAG4AUwB0AGEAdABlAHMAVABlAHIAcgBpAHQAbwByAGkAZQBzAF8AVgBhAHIAaQBhAGIAbABlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEEAdQBzAHQAcgBhAGwAaQBhAG4AUwB0AGEAdABlAHMAVABlAHIAcgBpAHQAbwByAGkAZQBzAF8AVQBuAGkAdAAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBBAHUAcwB0AHIAYQBsAGkAYQBuAFMAdABhAHQAZQBzAFQAZQByAHIAaQB0AG8AcgBpAGUAcwBfAFMAbwB1AHIAYwBlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEEAdQBzAHQAcgBhAGwAaQBhAG4AUwB0AGEAdABlAHMAVABlAHIAcgBpAHQAbwByAGkAZQBzAF8ARABhAHQAYQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBXAEEAUwBBADQAQQByAGUAYQBzAF8AVABpAHQAbABlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFcAQQBTAEEANABBAHIAZQBhAHMAXwBWAGEAcgBpAGEAYgBsAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AVwBBAFMAQQA0AEEAcgBlAGEAcwBfAFUAbgBpAHQAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AVwBBAFMAQQA0AEEAcgBlAGEAcwBfAFMAbwB1AHIAYwBlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFcAQQBTAEEANABBAHIAZQBhAHMAXwBEAGEAdABhACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFcAZQB0AEEAbgBkAEQAcgB5AFoAbwBuAGUAcwBfAFQAaQB0AGwAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBXAGUAdABBAG4AZABEAHIAeQBaAG8AbgBlAHMAXwBWAGEAcgBpAGEAYgBsAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AVwBlAHQAQQBuAGQARAByAHkAWgBvAG4AZQBzAF8AVQBuAGkAdAAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBXAGUAdABBAG4AZABEAHIAeQBaAG8AbgBlAHMAXwBTAG8AdQByAGMAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBXAGUAdABBAG4AZABEAHIAeQBaAG8AbgBlAHMAXwBWAGEAcgBpAGEAdABpAG8AbgAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBXAGUAdABBAG4AZABEAHIAeQBaAG8AbgBlAHMAXwBEAGEAdABhACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEMAbABpAG0AYQB0AGUAWgBvAG4AZQBzAF8AVABpAHQAbABlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEMAbABpAG0AYQB0AGUAWgBvAG4AZQBzAF8AVgBhAHIAaQBhAGIAbABlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEMAbABpAG0AYQB0AGUAWgBvAG4AZQBzAF8AVQBuAGkAdAAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBDAGwAaQBtAGEAdABlAFoAbwBuAGUAcwBfAFMAbwB1AHIAYwBlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEMAbABpAG0AYQB0AGUAWgBvAG4AZQBzAF8AVgBhAHIAaQBhAHQAaQBvAG4AIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQwBsAGkAbQBhAHQAZQBaAG8AbgBlAHMAXwBEAGEAdABhACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEMAbABpAG0AYQB0AGUAWgBvAG4AZQBzAF8AQQBwAHAAZQBuAGQAaQBjAGUAcwAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBUAGUAbQBwAGUAcgBhAHQAdQByAGUAWgBvAG4AZQBzAF8AVABpAHQAbABlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFQAZQBtAHAAZQByAGEAdAB1AHIAZQBaAG8AbgBlAHMAXwBWAGEAcgBpAGEAYgBsAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AVABlAG0AcABlAHIAYQB0AHUAcgBlAFoAbwBuAGUAcwBfAFUAbgBpAHQAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AVABlAG0AcABlAHIAYQB0AHUAcgBlAFoAbwBuAGUAcwBfAFMAbwB1AHIAYwBlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFQAZQBtAHAAZQByAGEAdAB1AHIAZQBaAG8AbgBlAHMAXwBWAGEAcgBpAGEAdABpAG8AbgAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBUAGUAbQBwAGUAcgBhAHQAdQByAGUAWgBvAG4AZQBzAF8ARABhAHQAYQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBSAGEAaQBuAGYAYQBsAGwAWgBvAG4AZQBzAF8AVABpAHQAbABlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFIAYQBpAG4AZgBhAGwAbABaAG8AbgBlAHMAXwBWAGEAcgBpAGEAYgBsAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AUgBhAGkAbgBmAGEAbABsAFoAbwBuAGUAcwBfAFUAbgBpAHQAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AUgBhAGkAbgBmAGEAbABsAFoAbwBuAGUAcwBfAFMAbwB1AHIAYwBlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFIAYQBpAG4AZgBhAGwAbABaAG8AbgBlAHMAXwBWAGEAcgBpAGEAdABpAG8AbgAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBSAGEAaQBuAGYAYQBsAGwAWgBvAG4AZQBzAF8ARABhAHQAYQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBMAGUAYQBjAGgAaQBuAGcAWgBvAG4AZQBzAF8AVABpAHQAbABlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEwAZQBhAGMAaABpAG4AZwBaAG8AbgBlAHMAXwBWAGEAcgBpAGEAYgBsAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ATABlAGEAYwBoAGkAbgBnAFoAbwBuAGUAcwBfAFUAbgBpAHQAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ATABlAGEAYwBoAGkAbgBnAFoAbwBuAGUAcwBfAFMAbwB1AHIAYwBlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEwAZQBhAGMAaABpAG4AZwBaAG8AbgBlAHMAXwBWAGEAcgBpAGEAdABpAG8AbgAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBMAGUAYQBjAGgAaQBuAGcAWgBvAG4AZQBzAF8ARABhAHQAYQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAHIAYQBjAFcARQBUAF8AVABpAHQAbABlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAcgBhAGMAVwBFAFQAXwBVAG4AaQB0ACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAcgBhAGMAVwBFAFQAXwBTAG8AdQByAGMAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAHIAYQBjAFcARQBUAF8ATgBJAFIAUgBlAGYAZQByAGUAbgBjAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgByAGEAYwBXAEUAVABfAEQAYQB0AGEAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgByAGEAYwBXAEUAVABfAFYAYQByAGkAYQB0AGkAbwBuACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEQAYQB0AGEAUwBjAG8AcgBlAHMAXwBTAGMAbwBwAGUAMwBfAFQAaQB0AGwAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGEAdABhAFMAYwBvAHIAZQBzAF8AUwBjAG8AcABlADMAXwBWAGEAcgBpAGEAYgBsAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABhAHQAYQBTAGMAbwByAGUAcwBfAFMAYwBvAHAAZQAzAF8AVQBuAGkAdAAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGEAdABhAFMAYwBvAHIAZQBzAF8AUwBjAG8AcABlADMAXwBTAG8AdQByAGMAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGEAdABhAFMAYwBvAHIAZQBzAF8AUwBjAG8AcABlADMAXwBWAGEAcgBpAGEAdABpAG8AbgAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGEAdABhAFMAYwBvAHIAZQBzAF8AUwBjAG8AcABlADMAXwBEAGEAdABhACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAcgBhAGMATABFAEEAQwBIAF8AVABpAHQAbABlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAcgBhAGMATABFAEEAQwBIAF8AVQBuAGkAdAAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAHIAYQBjAEwARQBBAEMASABfAFMAbwB1AHIAYwBlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAcgBhAGMATABFAEEAQwBIAF8ATgBJAFIAUgBlAGYAZQByAGUAbgBjAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgByAGEAYwBMAEUAQQBDAEgAXwBEAGEAdABhACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAcgBhAGMATABFAEEAQwBIAF8AVgBhAHIAaQBhAHQAaQBvAG4AIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAGwAZQBhAGMAaABfAFQAaQB0AGwAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYAbABlAGEAYwBoAF8AVQBuAGkAdAAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYAbABlAGEAYwBoAF8AUwBvAHUAcgBjAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAGwAZQBhAGMAaABfAE4ASQBSAFIAZQBmAGUAcgBlAG4AYwBlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEUARgBsAGUAYQBjAGgAXwBEAGEAdABhACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEUARgBsAGUAYQBjAGgAXwBWAGEAcgBpAGEAdABpAG8AbgAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYATgAyAE8AXwBUAGkAdABsAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAE4AMgBPAF8AVQBuAGkAdAAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYATgAyAE8AXwBTAG8AdQByAGMAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYATgAyAE8AXwBOAEkAUgBSAGUAZgBlAHIAZQBuAGMAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYATgAyAE8AXwBEAGEAdABhACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEUARgBOADIATwBfAFYAYQByAGkAYQB0AGkAbwBuACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAcgBhAGMAVwBFAFQASQByAHIAaQBnAGEAdABpAG8AbgBfAFQAaQB0AGwAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAHIAYQBjAFcARQBUAEkAcgByAGkAZwBhAHQAaQBvAG4AXwBVAG4AaQB0ACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAcgBhAGMAVwBFAFQASQByAHIAaQBnAGEAdABpAG8AbgBfAFMAbwB1AHIAYwBlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAcgBhAGMAVwBFAFQASQByAHIAaQBnAGEAdABpAG8AbgBfAE4ASQBSAFIAZQBmAGUAcgBlAG4AYwBlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAcgBhAGMAVwBFAFQASQByAHIAaQBnAGEAdABpAG8AbgBfAEQAYQB0AGEAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgByAGEAYwBXAEUAVABJAHIAcgBpAGcAYQB0AGkAbwBuAF8AVgBhAHIAaQBhAHQAaQBvAG4AIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAFAAYQBzAHQAdQByAGUAUgBhAG4AZwBlAEEAbgBkAFAAYQBkAGQAbwBjAGsAXwBUAGkAdABsAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAFAAYQBzAHQAdQByAGUAUgBhAG4AZwBlAEEAbgBkAFAAYQBkAGQAbwBjAGsAXwBVAG4AaQB0ACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEUARgBQAGEAcwB0AHUAcgBlAFIAYQBuAGcAZQBBAG4AZABQAGEAZABkAG8AYwBrAF8AUwBvAHUAcgBjAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAFAAYQBzAHQAdQByAGUAUgBhAG4AZwBlAEEAbgBkAFAAYQBkAGQAbwBjAGsAXwBOAEkAUgBSAGUAZgBlAHIAZQBuAGMAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYAUABhAHMAdAB1AHIAZQBSAGEAbgBnAGUAQQBuAGQAUABhAGQAZABvAGMAawBfAEQAYQB0AGEAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAFAAYQBzAHQAdQByAGUAUgBhAG4AZwBlAEEAbgBkAFAAYQBkAGQAbwBjAGsAXwBWAGEAcgBpAGEAdABpAG8AbgAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBNAG8AbgB0AGgAcwBUAG8AUwBlAGEAcwBvAG4AcwBfAFQAaQB0AGwAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBNAG8AbgB0AGgAcwBUAG8AUwBlAGEAcwBvAG4AcwBfAFUAbgBpAHQAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ATQBvAG4AdABoAHMAVABvAFMAZQBhAHMAbwBuAHMAXwBTAG8AdQByAGMAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBNAG8AbgB0AGgAcwBUAG8AUwBlAGEAcwBvAG4AcwBfAE4ASQBSAFIAZQBmAGUAcgBlAG4AYwBlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAE0AbwBuAHQAaABzAFQAbwBTAGUAYQBzAG8AbgBzAF8ARABhAHQAYQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBNAG8AbgB0AGgAcwBUAG8AUwBlAGEAcwBvAG4AcwBfAFYAYQByAGkAYQB0AGkAbwBuACIAXQAsACIAbABvAGMAYQBsAGUAIgA6AHsAIgBsAGkAcwB0AFMAZQBwAGEAcgBhAHQAbwByACIAOgAiACwAIgAsACIAcgBvAHcAUwBlAHAAYQByAGEAdABvAHIAIgA6ACIAOwAiACwAIgBjAG8AbAB1AG0AbgBTAGUAcABhAHIAYQB0AG8AcgAiADoAIgAsACIALAAiAHQAaABvAHUAcwBhAG4AZABzAFMAZQBwAGEAcgBhAHQAbwByACIAOgAiACwAIgAsACIAdABoAG8AdQBzAGEAbgBkAHMAUABvAHMAaQB0AGkAbwBuAHMAIgA6AFsAMwBdACwAIgBkAGUAYwBpAG0AYQBsAFMAZQBwAGEAcgBhAHQAbwByACIAOgAiAC4AIgAsACIAZABhAHQAZQBPAHIAZABlAHIAIgA6ACIARABNAFkAIgAsACIAYwB1AHIAcgBlAG4AYwB5AFMAeQBtAGIAbwBsACIAOgAiACQAIgAsACIAaQBzAEMAdQByAHIAZQBuAGMAeQBTAHkAbQBiAG8AbABMAGUAYQBkACIAOgB0AHIAdQBlACwAIgBpAHMAQwB1AHIAcgBlAG4AYwB5AFMAZQBwAEIAeQBTAHAAYQBjAGUAIgA6AGYAYQBsAHMAZQAsACIAcgBvAHcATABlAHQAdABlAHIAIgA6ACIAUgAiACwAIgBjAG8AbAB1AG0AbgBMAGUAdAB0AGUAcgAiADoAIgBDACIALAAiAHIAYwBMAGUAZgB0AEIAcgBhAGMAawBlAHQAIgA6ACIAWwAiACwAIgByAGMAUgBpAGcAaAB0AEIAcgBhAGMAawBlAHQAIgA6ACIAXQAiACwAIgBzAHQAYQB0AGUAbQBlAG4AdABTAGUAcABhAHIAYQB0AG8AcgAiADoAIgA7ACIALAAiAGwAbwBjAGEAbABlAE4AYQBtAGUAIgA6ACIAZQBuAC0AdQBzACIAfQB9AA==</AFEJSONBlob>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <TaxCatchAll xmlns="09eef6d6-daa8-4301-8f9f-b1ec38079286" xsi:nil="true"/>
+    <lcf76f155ced4ddcb4097134ff3c332f xmlns="7291119c-fce9-4911-96ae-b800be5dccd8">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    </lcf76f155ced4ddcb4097134ff3c332f>
+  </documentManagement>
+</p:properties>
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -11623,12 +11518,9 @@
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{CD460F9D-420A-4723-B323-396E4D19EC9B}">
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{B6BE249C-20B1-4A62-BBCD-F2A46D88BCAB}">
   <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="09eef6d6-daa8-4301-8f9f-b1ec38079286"/>
-    <ds:schemaRef ds:uri="7291119c-fce9-4911-96ae-b800be5dccd8"/>
+    <ds:schemaRef ds:uri="http://schemas.advancedformulaenvironment.officeapps.live.com/afejsonblob/1.0"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>
@@ -11653,9 +11545,12 @@
 </file>
 
 <file path=customXml/itemProps4.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{B6BE249C-20B1-4A62-BBCD-F2A46D88BCAB}">
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{CD460F9D-420A-4723-B323-396E4D19EC9B}">
   <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.advancedformulaenvironment.officeapps.live.com/afejsonblob/1.0"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="09eef6d6-daa8-4301-8f9f-b1ec38079286"/>
+    <ds:schemaRef ds:uri="7291119c-fce9-4911-96ae-b800be5dccd8"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>
--- a/Excel/Enterprises/Enterprise_Dairy_Template_WIP_v01.xlsx
+++ b/Excel/Enterprises/Enterprise_Dairy_Template_WIP_v01.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\htdocs\zneagcrc\GAF-VEERG-Functions\Excel\Enterprises\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E0E4F344-6AEF-44BB-B4E3-D8BBE908E514}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BCAFCAC9-00CC-43FA-9BD7-A26133195CDE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="2085" yWindow="1065" windowWidth="36255" windowHeight="19140" activeTab="1" xr2:uid="{992023F3-CAB7-4E5B-A348-08D563A0EF40}"/>
+    <workbookView xWindow="1155" yWindow="465" windowWidth="36255" windowHeight="19140" activeTab="6" xr2:uid="{992023F3-CAB7-4E5B-A348-08D563A0EF40}"/>
   </bookViews>
   <sheets>
     <sheet name="Home" sheetId="71" r:id="rId1"/>
@@ -19,14 +19,19 @@
     <sheet name="Input - Enterprise" sheetId="72" r:id="rId4"/>
     <sheet name="Input - Livestock sales" sheetId="77" r:id="rId5"/>
     <sheet name="Input - Fert Prod System" sheetId="76" r:id="rId6"/>
-    <sheet name="Constants - Common" sheetId="74" r:id="rId7"/>
+    <sheet name="Input - Data quality" sheetId="78" r:id="rId7"/>
+    <sheet name="Constants - Common" sheetId="74" r:id="rId8"/>
   </sheets>
   <externalReferences>
-    <externalReference r:id="rId8"/>
+    <externalReference r:id="rId9"/>
+    <externalReference r:id="rId10"/>
+    <externalReference r:id="rId11"/>
   </externalReferences>
   <definedNames>
+    <definedName name="Common_Equations.Common_ConvertCH4ToCO2e" localSheetId="6">_xlfn.LAMBDA(_xlpm.E_CH4,_xlpm.GWP_CH4, _xlpm.E_CH4 * _xlpm.GWP_CH4)</definedName>
     <definedName name="Common_Equations.Common_ConvertCH4ToCO2e" localSheetId="4">_xlfn.LAMBDA(_xlpm.E_CH4,_xlpm.GWP_CH4, _xlpm.E_CH4 * _xlpm.GWP_CH4)</definedName>
     <definedName name="Common_Equations.Common_ConvertCH4ToCO2e">_xlfn.LAMBDA(_xlpm.E_CH4,_xlpm.GWP_CH4, _xlpm.E_CH4 * _xlpm.GWP_CH4)</definedName>
+    <definedName name="Common_Equations.Common_ConvertCH4ToCO2e_Arguments" localSheetId="6">_xlfn.LAMBDA(_xlfn.MAKEARRAY(2, 2, _xlfn.LAMBDA(_xlpm.r,_xlpm.c, INDEX({"ECH4","Methane emissions (t CH4)";"GWPCH4","Global warming potential for methane (t CO2-e / t CH4)"}, _xlpm.r, _xlpm.c))))</definedName>
     <definedName name="Common_Equations.Common_ConvertCH4ToCO2e_Arguments" localSheetId="4">_xlfn.LAMBDA(_xlfn.MAKEARRAY(2, 2, _xlfn.LAMBDA(_xlpm.r,_xlpm.c, INDEX({"ECH4","Methane emissions (t CH4)";"GWPCH4","Global warming potential for methane (t CO2-e / t CH4)"}, _xlpm.r, _xlpm.c))))</definedName>
     <definedName name="Common_Equations.Common_ConvertCH4ToCO2e_Arguments">_xlfn.LAMBDA(_xlfn.MAKEARRAY(2, 2, _xlfn.LAMBDA(_xlpm.r,_xlpm.c, INDEX({"ECH4","Methane emissions (t CH4)";"GWPCH4","Global warming potential for methane (t CO2-e / t CH4)"}, _xlpm.r, _xlpm.c))))</definedName>
     <definedName name="Common_Equations.Common_ConvertCH4ToCO2e_LatexEquation">_xlfn.LAMBDA("CO2_e = E_{CH4} \times GWP_{CH4}")</definedName>
@@ -34,8 +39,10 @@
     <definedName name="Common_Equations.Common_ConvertCH4ToCO2e_Title">_xlfn.LAMBDA("Convert methane emissions to carbon dioxide equivalent emissions")</definedName>
     <definedName name="Common_Equations.Common_ConvertCH4ToCO2e_Unit">_xlfn.LAMBDA("t CO2e")</definedName>
     <definedName name="Common_Equations.Common_ConvertCH4ToCO2e_Variable">_xlfn.LAMBDA("ECH4 CO2e")</definedName>
+    <definedName name="Common_Equations.Common_ConvertN2OToCO2e" localSheetId="6">_xlfn.LAMBDA(_xlpm.E_N2O,_xlpm.GWP_N2O, _xlpm.E_N2O * _xlpm.GWP_N2O)</definedName>
     <definedName name="Common_Equations.Common_ConvertN2OToCO2e" localSheetId="4">_xlfn.LAMBDA(_xlpm.E_N2O,_xlpm.GWP_N2O, _xlpm.E_N2O * _xlpm.GWP_N2O)</definedName>
     <definedName name="Common_Equations.Common_ConvertN2OToCO2e">_xlfn.LAMBDA(_xlpm.E_N2O,_xlpm.GWP_N2O, _xlpm.E_N2O * _xlpm.GWP_N2O)</definedName>
+    <definedName name="Common_Equations.Common_ConvertN2OToCO2e_Arguments" localSheetId="6">_xlfn.LAMBDA(_xlfn.MAKEARRAY(2, 2, _xlfn.LAMBDA(_xlpm.r,_xlpm.c, INDEX({"EN2O","Nitrous oxide emissions (t N2O)";"GWPN2O","Global warming potential for nitrous oxide (t CO2-e / t N2O)"}, _xlpm.r, _xlpm.c))))</definedName>
     <definedName name="Common_Equations.Common_ConvertN2OToCO2e_Arguments" localSheetId="4">_xlfn.LAMBDA(_xlfn.MAKEARRAY(2, 2, _xlfn.LAMBDA(_xlpm.r,_xlpm.c, INDEX({"EN2O","Nitrous oxide emissions (t N2O)";"GWPN2O","Global warming potential for nitrous oxide (t CO2-e / t N2O)"}, _xlpm.r, _xlpm.c))))</definedName>
     <definedName name="Common_Equations.Common_ConvertN2OToCO2e_Arguments">_xlfn.LAMBDA(_xlfn.MAKEARRAY(2, 2, _xlfn.LAMBDA(_xlpm.r,_xlpm.c, INDEX({"EN2O","Nitrous oxide emissions (t N2O)";"GWPN2O","Global warming potential for nitrous oxide (t CO2-e / t N2O)"}, _xlpm.r, _xlpm.c))))</definedName>
     <definedName name="Common_Equations.Common_ConvertN2OToCO2e_LatexEquation">_xlfn.LAMBDA("CO2_e = E_{N2O} \times GWP_{N2O}")</definedName>
@@ -43,68 +50,96 @@
     <definedName name="Common_Equations.Common_ConvertN2OToCO2e_Title">_xlfn.LAMBDA("Convert nitrous oxide emissions to carbon dioxide equivalent emissions")</definedName>
     <definedName name="Common_Equations.Common_ConvertN2OToCO2e_Unit">_xlfn.LAMBDA("t CO2e")</definedName>
     <definedName name="Common_Equations.Common_ConvertN2OToCO2e_Variable">_xlfn.LAMBDA("EN2O CO2e")</definedName>
+    <definedName name="Common_InputFunctions.Common_GetMCFTemperatureZone" localSheetId="6">_xlfn.LAMBDA(_xlpm.Temperature,_xlpm.MMS,_xlpm.TemperatureArray,_xlpm.MMSArray,_xlpm.ReturnArray, _xlfn.XLOOKUP(MEDIAN(_xlpm.Temperature, MIN(_xlpm.TemperatureArray), MAX(_xlpm.TemperatureArray)), _xlpm.TemperatureArray, _xlfn.XLOOKUP(_xlpm.MMS, _xlpm.MMSArray, _xlpm.ReturnArray)))</definedName>
     <definedName name="Common_InputFunctions.Common_GetMCFTemperatureZone" localSheetId="4">_xlfn.LAMBDA(_xlpm.Temperature,_xlpm.MMS,_xlpm.TemperatureArray,_xlpm.MMSArray,_xlpm.ReturnArray, _xlfn.XLOOKUP(MEDIAN(_xlpm.Temperature, MIN(_xlpm.TemperatureArray), MAX(_xlpm.TemperatureArray)), _xlpm.TemperatureArray, _xlfn.XLOOKUP(_xlpm.MMS, _xlpm.MMSArray, _xlpm.ReturnArray)))</definedName>
     <definedName name="Common_InputFunctions.Common_GetMCFTemperatureZone">_xlfn.LAMBDA(_xlpm.Temperature,_xlpm.MMS,_xlpm.TemperatureArray,_xlpm.MMSArray,_xlpm.ReturnArray, _xlfn.XLOOKUP(MEDIAN(_xlpm.Temperature, MIN(_xlpm.TemperatureArray), MAX(_xlpm.TemperatureArray)), _xlpm.TemperatureArray, _xlfn.XLOOKUP(_xlpm.MMS, _xlpm.MMSArray, _xlpm.ReturnArray)))</definedName>
+    <definedName name="Common_InputFunctions.CommonCropping_GetFracWET" localSheetId="6">_xlfn.LAMBDA(_xlpm.LeachingZone,_xlpm.ProductionSystem,_xlpm.LeachingZoneLookup,_xlpm.LeachingZoneFracWETLookup,_xlpm.ProductionSystemLookup,_xlpm.ProductionSystemFracWETLookup, _xlfn.LET(_xlpm.LeachingZoneFracWET, 'Input - Data quality'!Common_InputFunctions.Utility_LookupValueInTableNumber(_xlpm.LeachingZone, _xlpm.LeachingZoneLookup, _xlpm.LeachingZoneFracWETLookup), _xlpm.ProductionSystemFracWET, 'Input - Data quality'!Common_InputFunctions.Utility_LookupValueInTableNumber(_xlpm.ProductionSystem, _xlpm.ProductionSystemLookup, _xlpm.ProductionSystemFracWETLookup), IF(_xlpm.LeachingZoneFracWET + _xlpm.ProductionSystemFracWET &gt; 0, 1, 0)))</definedName>
     <definedName name="Common_InputFunctions.CommonCropping_GetFracWET" localSheetId="4">_xlfn.LAMBDA(_xlpm.LeachingZone,_xlpm.ProductionSystem,_xlpm.LeachingZoneLookup,_xlpm.LeachingZoneFracWETLookup,_xlpm.ProductionSystemLookup,_xlpm.ProductionSystemFracWETLookup, _xlfn.LET(_xlpm.LeachingZoneFracWET, 'Input - Livestock sales'!Common_InputFunctions.Utility_LookupValueInTableNumber(_xlpm.LeachingZone, _xlpm.LeachingZoneLookup, _xlpm.LeachingZoneFracWETLookup), _xlpm.ProductionSystemFracWET, 'Input - Livestock sales'!Common_InputFunctions.Utility_LookupValueInTableNumber(_xlpm.ProductionSystem, _xlpm.ProductionSystemLookup, _xlpm.ProductionSystemFracWETLookup), IF(_xlpm.LeachingZoneFracWET + _xlpm.ProductionSystemFracWET &gt; 0, 1, 0)))</definedName>
     <definedName name="Common_InputFunctions.CommonCropping_GetFracWET">_xlfn.LAMBDA(_xlpm.LeachingZone,_xlpm.ProductionSystem,_xlpm.LeachingZoneLookup,_xlpm.LeachingZoneFracWETLookup,_xlpm.ProductionSystemLookup,_xlpm.ProductionSystemFracWETLookup, _xlfn.LET(_xlpm.LeachingZoneFracWET, Common_InputFunctions.Utility_LookupValueInTableNumber(_xlpm.LeachingZone, _xlpm.LeachingZoneLookup, _xlpm.LeachingZoneFracWETLookup), _xlpm.ProductionSystemFracWET, Common_InputFunctions.Utility_LookupValueInTableNumber(_xlpm.ProductionSystem, _xlpm.ProductionSystemLookup, _xlpm.ProductionSystemFracWETLookup), IF(_xlpm.LeachingZoneFracWET + _xlpm.ProductionSystemFracWET &gt; 0, 1, 0)))</definedName>
+    <definedName name="Common_InputFunctions.getOverlappingReportingCycles" localSheetId="6">_xlfn.LAMBDA(_xlpm.ProductionCycleStart,_xlpm.ProductionCycleEnd,_xlpm.ReportingCycleStart, _xlfn.LET(_xlpm.S, _xlpm.ProductionCycleStart, _xlpm.E, _xlpm.ProductionCycleEnd, _xlpm.m, MONTH(_xlpm.ReportingCycleStart), _xlpm.d, DAY(_xlpm.ReportingCycleStart), _xlpm.PeriodEnd, _xlfn.LAMBDA(_xlpm.st, EDATE(_xlpm.st, 12) - 1), _xlpm.A, _xlpm.S - 365, _xlpm.ya, YEAR(_xlpm.A), _xlpm.yb, YEAR(_xlpm.E), _xlpm.firstYear, _xlpm.ya + (_xlpm.PeriodEnd(DATE(_xlpm.ya, _xlpm.m, _xlpm.d)) &lt; _xlpm.S), _xlpm.lastYear, _xlpm.yb - (DATE(_xlpm.yb, _xlpm.m, _xlpm.d) &gt; _xlpm.E), MAX(0, _xlpm.lastYear - _xlpm.firstYear + 1)))</definedName>
     <definedName name="Common_InputFunctions.getOverlappingReportingCycles" localSheetId="4">_xlfn.LAMBDA(_xlpm.ProductionCycleStart,_xlpm.ProductionCycleEnd,_xlpm.ReportingCycleStart, _xlfn.LET(_xlpm.S, _xlpm.ProductionCycleStart, _xlpm.E, _xlpm.ProductionCycleEnd, _xlpm.m, MONTH(_xlpm.ReportingCycleStart), _xlpm.d, DAY(_xlpm.ReportingCycleStart), _xlpm.PeriodEnd, _xlfn.LAMBDA(_xlpm.st, EDATE(_xlpm.st, 12) - 1), _xlpm.A, _xlpm.S - 365, _xlpm.ya, YEAR(_xlpm.A), _xlpm.yb, YEAR(_xlpm.E), _xlpm.firstYear, _xlpm.ya + (_xlpm.PeriodEnd(DATE(_xlpm.ya, _xlpm.m, _xlpm.d)) &lt; _xlpm.S), _xlpm.lastYear, _xlpm.yb - (DATE(_xlpm.yb, _xlpm.m, _xlpm.d) &gt; _xlpm.E), MAX(0, _xlpm.lastYear - _xlpm.firstYear + 1)))</definedName>
     <definedName name="Common_InputFunctions.getOverlappingReportingCycles">_xlfn.LAMBDA(_xlpm.ProductionCycleStart,_xlpm.ProductionCycleEnd,_xlpm.ReportingCycleStart, _xlfn.LET(_xlpm.S, _xlpm.ProductionCycleStart, _xlpm.E, _xlpm.ProductionCycleEnd, _xlpm.m, MONTH(_xlpm.ReportingCycleStart), _xlpm.d, DAY(_xlpm.ReportingCycleStart), _xlpm.PeriodEnd, _xlfn.LAMBDA(_xlpm.st, EDATE(_xlpm.st, 12) - 1), _xlpm.A, _xlpm.S - 365, _xlpm.ya, YEAR(_xlpm.A), _xlpm.yb, YEAR(_xlpm.E), _xlpm.firstYear, _xlpm.ya + (_xlpm.PeriodEnd(DATE(_xlpm.ya, _xlpm.m, _xlpm.d)) &lt; _xlpm.S), _xlpm.lastYear, _xlpm.yb - (DATE(_xlpm.yb, _xlpm.m, _xlpm.d) &gt; _xlpm.E), MAX(0, _xlpm.lastYear - _xlpm.firstYear + 1)))</definedName>
+    <definedName name="Common_InputFunctions.getOverlappingReportingPeriods" localSheetId="6">_xlfn.LAMBDA(_xlpm.ProductionCycleStart,_xlpm.ProductionCycleEnd,_xlpm.ReportingCycleStart, _xlfn.LET(_xlpm.S, _xlpm.ProductionCycleStart, _xlpm.E, _xlpm.ProductionCycleEnd, _xlpm.m, MONTH(_xlpm.ReportingCycleStart), _xlpm.d, DAY(_xlpm.ReportingCycleStart), _xlpm.PeriodEnd, _xlfn.LAMBDA(_xlpm.st, EDATE(_xlpm.st, 12) - 1), _xlpm.A, _xlpm.S - 365, _xlpm.ya, YEAR(_xlpm.A), _xlpm.yb, YEAR(_xlpm.E), _xlpm.firstYear, _xlpm.ya + (_xlpm.PeriodEnd(DATE(_xlpm.ya, _xlpm.m, _xlpm.d)) &lt; _xlpm.S), _xlpm.lastYear, _xlpm.yb - (DATE(_xlpm.yb, _xlpm.m, _xlpm.d) &gt; _xlpm.E), _xlpm.n, MAX(0, _xlpm.lastYear - _xlpm.firstYear + 1), _xlpm.yrs, _xlfn.SEQUENCE(_xlpm.n, 1, _xlpm.firstYear, 1), _xlpm.starts, DATE(_xlpm.yrs, _xlpm.m, _xlpm.d), _xlpm.ends, _xlfn.MAP(_xlpm.starts, _xlpm.PeriodEnd), _xlpm.tag, IF(_xlpm.starts = _xlpm.ReportingCycleStart, " (This reporting cycle)", ""), _xlpm.startsText, TEXT(_xlpm.starts, "dd mmm yyyy"), _xlpm.endsText, TEXT(_xlpm.ends, "dd mmm yyyy"), _xlpm.rows, IF(_xlpm.n = 0, "", _xlfn.HSTACK(_xlpm.startsText &amp; " to " &amp; _xlpm.endsText &amp; _xlpm.tag)), _xlpm.rows))</definedName>
     <definedName name="Common_InputFunctions.getOverlappingReportingPeriods" localSheetId="4">_xlfn.LAMBDA(_xlpm.ProductionCycleStart,_xlpm.ProductionCycleEnd,_xlpm.ReportingCycleStart, _xlfn.LET(_xlpm.S, _xlpm.ProductionCycleStart, _xlpm.E, _xlpm.ProductionCycleEnd, _xlpm.m, MONTH(_xlpm.ReportingCycleStart), _xlpm.d, DAY(_xlpm.ReportingCycleStart), _xlpm.PeriodEnd, _xlfn.LAMBDA(_xlpm.st, EDATE(_xlpm.st, 12) - 1), _xlpm.A, _xlpm.S - 365, _xlpm.ya, YEAR(_xlpm.A), _xlpm.yb, YEAR(_xlpm.E), _xlpm.firstYear, _xlpm.ya + (_xlpm.PeriodEnd(DATE(_xlpm.ya, _xlpm.m, _xlpm.d)) &lt; _xlpm.S), _xlpm.lastYear, _xlpm.yb - (DATE(_xlpm.yb, _xlpm.m, _xlpm.d) &gt; _xlpm.E), _xlpm.n, MAX(0, _xlpm.lastYear - _xlpm.firstYear + 1), _xlpm.yrs, _xlfn.SEQUENCE(_xlpm.n, 1, _xlpm.firstYear, 1), _xlpm.starts, DATE(_xlpm.yrs, _xlpm.m, _xlpm.d), _xlpm.ends, _xlfn.MAP(_xlpm.starts, _xlpm.PeriodEnd), _xlpm.tag, IF(_xlpm.starts = _xlpm.ReportingCycleStart, " (This reporting cycle)", ""), _xlpm.startsText, TEXT(_xlpm.starts, "dd mmm yyyy"), _xlpm.endsText, TEXT(_xlpm.ends, "dd mmm yyyy"), _xlpm.rows, IF(_xlpm.n = 0, "", _xlfn.HSTACK(_xlpm.startsText &amp; " to " &amp; _xlpm.endsText &amp; _xlpm.tag)), _xlpm.rows))</definedName>
     <definedName name="Common_InputFunctions.getOverlappingReportingPeriods">_xlfn.LAMBDA(_xlpm.ProductionCycleStart,_xlpm.ProductionCycleEnd,_xlpm.ReportingCycleStart, _xlfn.LET(_xlpm.S, _xlpm.ProductionCycleStart, _xlpm.E, _xlpm.ProductionCycleEnd, _xlpm.m, MONTH(_xlpm.ReportingCycleStart), _xlpm.d, DAY(_xlpm.ReportingCycleStart), _xlpm.PeriodEnd, _xlfn.LAMBDA(_xlpm.st, EDATE(_xlpm.st, 12) - 1), _xlpm.A, _xlpm.S - 365, _xlpm.ya, YEAR(_xlpm.A), _xlpm.yb, YEAR(_xlpm.E), _xlpm.firstYear, _xlpm.ya + (_xlpm.PeriodEnd(DATE(_xlpm.ya, _xlpm.m, _xlpm.d)) &lt; _xlpm.S), _xlpm.lastYear, _xlpm.yb - (DATE(_xlpm.yb, _xlpm.m, _xlpm.d) &gt; _xlpm.E), _xlpm.n, MAX(0, _xlpm.lastYear - _xlpm.firstYear + 1), _xlpm.yrs, _xlfn.SEQUENCE(_xlpm.n, 1, _xlpm.firstYear, 1), _xlpm.starts, DATE(_xlpm.yrs, _xlpm.m, _xlpm.d), _xlpm.ends, _xlfn.MAP(_xlpm.starts, _xlpm.PeriodEnd), _xlpm.tag, IF(_xlpm.starts = _xlpm.ReportingCycleStart, " (This reporting cycle)", ""), _xlpm.startsText, TEXT(_xlpm.starts, "dd mmm yyyy"), _xlpm.endsText, TEXT(_xlpm.ends, "dd mmm yyyy"), _xlpm.rows, IF(_xlpm.n = 0, "", _xlfn.HSTACK(_xlpm.startsText &amp; " to " &amp; _xlpm.endsText &amp; _xlpm.tag)), _xlpm.rows))</definedName>
+    <definedName name="Common_InputFunctions.Utility_ConvertStateCommonNameToAbbreviation" localSheetId="6">_xlfn.LAMBDA(_xlpm.StateCommonName,_xlpm.StateCommonNameArray,_xlpm.StateAbbreviationArray, _xlfn.XLOOKUP(_xlpm.StateCommonName, _xlpm.StateCommonNameArray, _xlpm.StateAbbreviationArray, ""))</definedName>
     <definedName name="Common_InputFunctions.Utility_ConvertStateCommonNameToAbbreviation" localSheetId="4">_xlfn.LAMBDA(_xlpm.StateCommonName,_xlpm.StateCommonNameArray,_xlpm.StateAbbreviationArray, _xlfn.XLOOKUP(_xlpm.StateCommonName, _xlpm.StateCommonNameArray, _xlpm.StateAbbreviationArray, ""))</definedName>
     <definedName name="Common_InputFunctions.Utility_ConvertStateCommonNameToAbbreviation">_xlfn.LAMBDA(_xlpm.StateCommonName,_xlpm.StateCommonNameArray,_xlpm.StateAbbreviationArray, _xlfn.XLOOKUP(_xlpm.StateCommonName, _xlpm.StateCommonNameArray, _xlpm.StateAbbreviationArray, ""))</definedName>
+    <definedName name="Common_InputFunctions.Utility_DisplayArguments_1_2" localSheetId="6">_xlfn.LAMBDA(_xlpm.ArgumentsArray, _xlfn.CHOOSECOLS(_xlpm.ArgumentsArray, 1, 2))</definedName>
     <definedName name="Common_InputFunctions.Utility_DisplayArguments_1_2" localSheetId="4">_xlfn.LAMBDA(_xlpm.ArgumentsArray, _xlfn.CHOOSECOLS(_xlpm.ArgumentsArray, 1, 2))</definedName>
     <definedName name="Common_InputFunctions.Utility_DisplayArguments_1_2">_xlfn.LAMBDA(_xlpm.ArgumentsArray, _xlfn.CHOOSECOLS(_xlpm.ArgumentsArray, 1, 2))</definedName>
+    <definedName name="Common_InputFunctions.Utility_DisplayArguments_3_4" localSheetId="6">_xlfn.LAMBDA(_xlpm.ArgumentsArray, _xlfn.CHOOSECOLS(_xlpm.ArgumentsArray, 3, 4))</definedName>
     <definedName name="Common_InputFunctions.Utility_DisplayArguments_3_4" localSheetId="4">_xlfn.LAMBDA(_xlpm.ArgumentsArray, _xlfn.CHOOSECOLS(_xlpm.ArgumentsArray, 3, 4))</definedName>
     <definedName name="Common_InputFunctions.Utility_DisplayArguments_3_4">_xlfn.LAMBDA(_xlpm.ArgumentsArray, _xlfn.CHOOSECOLS(_xlpm.ArgumentsArray, 3, 4))</definedName>
+    <definedName name="Common_InputFunctions.Utility_DisplayArrayInTable" localSheetId="6">_xlfn.LAMBDA(_xlpm.ArrayData,_xlpm.TableheaderCell,_xlpm.RowsBetweenHeaderandArray,_xlop.ColumnsBetweenHeaderAndArray, IFERROR(INDEX(_xlfn.UNIQUE(_xlpm.ArrayData), ROW() - 'Input - Data quality'!Common_InputFunctions.Utility_GetArrayTableRowStartNumber(_xlpm.TableheaderCell, _xlpm.RowsBetweenHeaderandArray), COLUMN() - 'Input - Data quality'!Common_InputFunctions.Utility_GetArrayTableColumnStartNumber(_xlpm.TableheaderCell) + IF(_xlfn.ISOMITTED(_xlpm.ColumnsBetweenHeaderAndArray), 1, _xlpm.ColumnsBetweenHeaderAndArray)), ""))</definedName>
     <definedName name="Common_InputFunctions.Utility_DisplayArrayInTable" localSheetId="4">_xlfn.LAMBDA(_xlpm.ArrayData,_xlpm.TableheaderCell,_xlpm.RowsBetweenHeaderandArray,_xlop.ColumnsBetweenHeaderAndArray, IFERROR(INDEX(_xlfn.UNIQUE(_xlpm.ArrayData), ROW() - 'Input - Livestock sales'!Common_InputFunctions.Utility_GetArrayTableRowStartNumber(_xlpm.TableheaderCell, _xlpm.RowsBetweenHeaderandArray), COLUMN() - 'Input - Livestock sales'!Common_InputFunctions.Utility_GetArrayTableColumnStartNumber(_xlpm.TableheaderCell) + IF(_xlfn.ISOMITTED(_xlpm.ColumnsBetweenHeaderAndArray), 1, _xlpm.ColumnsBetweenHeaderAndArray)), ""))</definedName>
     <definedName name="Common_InputFunctions.Utility_DisplayArrayInTable">_xlfn.LAMBDA(_xlpm.ArrayData,_xlpm.TableheaderCell,_xlpm.RowsBetweenHeaderandArray,_xlop.ColumnsBetweenHeaderAndArray, IFERROR(INDEX(_xlfn.UNIQUE(_xlpm.ArrayData), ROW() - Common_InputFunctions.Utility_GetArrayTableRowStartNumber(_xlpm.TableheaderCell, _xlpm.RowsBetweenHeaderandArray), COLUMN() - Common_InputFunctions.Utility_GetArrayTableColumnStartNumber(_xlpm.TableheaderCell) + IF(_xlfn.ISOMITTED(_xlpm.ColumnsBetweenHeaderAndArray), 1, _xlpm.ColumnsBetweenHeaderAndArray)), ""))</definedName>
+    <definedName name="Common_InputFunctions.Utility_DisplayFunctionName" localSheetId="6">_xlfn.LAMBDA(_xlpm.Function, _xlfn.TEXTBEFORE(_xlfn.FORMULATEXT(_xlpm.Function), "("))</definedName>
     <definedName name="Common_InputFunctions.Utility_DisplayFunctionName" localSheetId="4">_xlfn.LAMBDA(_xlpm.Function, _xlfn.TEXTBEFORE(_xlfn.FORMULATEXT(_xlpm.Function), "("))</definedName>
     <definedName name="Common_InputFunctions.Utility_DisplayFunctionName">_xlfn.LAMBDA(_xlpm.Function, _xlfn.TEXTBEFORE(_xlfn.FORMULATEXT(_xlpm.Function), "("))</definedName>
+    <definedName name="Common_InputFunctions.Utility_GetArrayTableColumnStartNumber" localSheetId="6">_xlfn.LAMBDA(_xlpm.TableHeaderCell, COLUMN(_xlpm.TableHeaderCell))</definedName>
     <definedName name="Common_InputFunctions.Utility_GetArrayTableColumnStartNumber" localSheetId="4">_xlfn.LAMBDA(_xlpm.TableHeaderCell, COLUMN(_xlpm.TableHeaderCell))</definedName>
     <definedName name="Common_InputFunctions.Utility_GetArrayTableColumnStartNumber">_xlfn.LAMBDA(_xlpm.TableHeaderCell, COLUMN(_xlpm.TableHeaderCell))</definedName>
+    <definedName name="Common_InputFunctions.Utility_GetArrayTableRowStartNumber" localSheetId="6">_xlfn.LAMBDA(_xlpm.TableheaderCell,_xlpm.RowsBetweenHeaderandArray, ROW(_xlpm.TableheaderCell) + _xlpm.RowsBetweenHeaderandArray - 1)</definedName>
     <definedName name="Common_InputFunctions.Utility_GetArrayTableRowStartNumber" localSheetId="4">_xlfn.LAMBDA(_xlpm.TableheaderCell,_xlpm.RowsBetweenHeaderandArray, ROW(_xlpm.TableheaderCell) + _xlpm.RowsBetweenHeaderandArray - 1)</definedName>
     <definedName name="Common_InputFunctions.Utility_GetArrayTableRowStartNumber">_xlfn.LAMBDA(_xlpm.TableheaderCell,_xlpm.RowsBetweenHeaderandArray, ROW(_xlpm.TableheaderCell) + _xlpm.RowsBetweenHeaderandArray - 1)</definedName>
+    <definedName name="Common_InputFunctions.Utility_GetClimateZone" localSheetId="6">_xlfn.LAMBDA(_xlpm.avgTemp,_xlpm.avgRain,_xlpm.frostDays,_xlpm.elev,_xlpm.map_pet,_xlpm.minTempArray,_xlpm.maxTempArray,_xlpm.minRainfallArray,_xlpm.maxRainfallArray,_xlpm.minFrostArray,_xlpm.maxFrostArray,_xlpm.minElevationArray,_xlpm.maxElevationArray,_xlpm.minPETArray,_xlpm.maxPETArray,_xlpm.climateZoneArray, _xlfn.LET(_xlpm.mask, (VALUE(_xlpm.minTempArray) &lt;= _xlpm.avgTemp) * (VALUE(_xlpm.maxTempArray) &gt;= _xlpm.avgTemp) * (VALUE(_xlpm.minRainfallArray) &lt;= _xlpm.avgRain) * (VALUE(_xlpm.maxRainfallArray) &gt;= _xlpm.avgRain) * (VALUE(_xlpm.minFrostArray) &lt;= _xlpm.frostDays) * (VALUE(_xlpm.maxFrostArray) &gt;= _xlpm.frostDays) * (VALUE(_xlpm.minElevationArray) &lt;= _xlpm.elev) * (VALUE(_xlpm.maxElevationArray) &gt;= _xlpm.elev) * (VALUE(_xlpm.minPETArray) &lt;= _xlpm.map_pet) * (VALUE(_xlpm.maxPETArray) &gt;= _xlpm.map_pet), _xlfn.TAKE(_xlfn._xlws.FILTER(_xlpm.climateZoneArray, _xlpm.mask, "No match"), 1)))</definedName>
     <definedName name="Common_InputFunctions.Utility_GetClimateZone" localSheetId="4">_xlfn.LAMBDA(_xlpm.avgTemp,_xlpm.avgRain,_xlpm.frostDays,_xlpm.elev,_xlpm.map_pet,_xlpm.minTempArray,_xlpm.maxTempArray,_xlpm.minRainfallArray,_xlpm.maxRainfallArray,_xlpm.minFrostArray,_xlpm.maxFrostArray,_xlpm.minElevationArray,_xlpm.maxElevationArray,_xlpm.minPETArray,_xlpm.maxPETArray,_xlpm.climateZoneArray, _xlfn.LET(_xlpm.mask, (VALUE(_xlpm.minTempArray) &lt;= _xlpm.avgTemp) * (VALUE(_xlpm.maxTempArray) &gt;= _xlpm.avgTemp) * (VALUE(_xlpm.minRainfallArray) &lt;= _xlpm.avgRain) * (VALUE(_xlpm.maxRainfallArray) &gt;= _xlpm.avgRain) * (VALUE(_xlpm.minFrostArray) &lt;= _xlpm.frostDays) * (VALUE(_xlpm.maxFrostArray) &gt;= _xlpm.frostDays) * (VALUE(_xlpm.minElevationArray) &lt;= _xlpm.elev) * (VALUE(_xlpm.maxElevationArray) &gt;= _xlpm.elev) * (VALUE(_xlpm.minPETArray) &lt;= _xlpm.map_pet) * (VALUE(_xlpm.maxPETArray) &gt;= _xlpm.map_pet), _xlfn.TAKE(_xlfn._xlws.FILTER(_xlpm.climateZoneArray, _xlpm.mask, "No match"), 1)))</definedName>
     <definedName name="Common_InputFunctions.Utility_GetClimateZone">_xlfn.LAMBDA(_xlpm.avgTemp,_xlpm.avgRain,_xlpm.frostDays,_xlpm.elev,_xlpm.map_pet,_xlpm.minTempArray,_xlpm.maxTempArray,_xlpm.minRainfallArray,_xlpm.maxRainfallArray,_xlpm.minFrostArray,_xlpm.maxFrostArray,_xlpm.minElevationArray,_xlpm.maxElevationArray,_xlpm.minPETArray,_xlpm.maxPETArray,_xlpm.climateZoneArray, _xlfn.LET(_xlpm.mask, (VALUE(_xlpm.minTempArray) &lt;= _xlpm.avgTemp) * (VALUE(_xlpm.maxTempArray) &gt;= _xlpm.avgTemp) * (VALUE(_xlpm.minRainfallArray) &lt;= _xlpm.avgRain) * (VALUE(_xlpm.maxRainfallArray) &gt;= _xlpm.avgRain) * (VALUE(_xlpm.minFrostArray) &lt;= _xlpm.frostDays) * (VALUE(_xlpm.maxFrostArray) &gt;= _xlpm.frostDays) * (VALUE(_xlpm.minElevationArray) &lt;= _xlpm.elev) * (VALUE(_xlpm.maxElevationArray) &gt;= _xlpm.elev) * (VALUE(_xlpm.minPETArray) &lt;= _xlpm.map_pet) * (VALUE(_xlpm.maxPETArray) &gt;= _xlpm.map_pet), _xlfn.TAKE(_xlfn._xlws.FILTER(_xlpm.climateZoneArray, _xlpm.mask, "No match"), 1)))</definedName>
+    <definedName name="Common_InputFunctions.Utility_LookupItemFromMinMax" localSheetId="6">_xlfn.LAMBDA(_xlpm.LookupValue,_xlpm.MinArray,_xlpm.MaxArray,_xlpm.ItemArray, _xlfn.LET(_xlpm.mask, (VALUE(_xlpm.MinArray) &lt;= _xlpm.LookupValue) * (VALUE(_xlpm.MaxArray) &gt;= _xlpm.LookupValue), _xlfn._xlws.FILTER(_xlpm.ItemArray, _xlpm.mask, "No match")))</definedName>
     <definedName name="Common_InputFunctions.Utility_LookupItemFromMinMax" localSheetId="4">_xlfn.LAMBDA(_xlpm.LookupValue,_xlpm.MinArray,_xlpm.MaxArray,_xlpm.ItemArray, _xlfn.LET(_xlpm.mask, (VALUE(_xlpm.MinArray) &lt;= _xlpm.LookupValue) * (VALUE(_xlpm.MaxArray) &gt;= _xlpm.LookupValue), _xlfn._xlws.FILTER(_xlpm.ItemArray, _xlpm.mask, "No match")))</definedName>
     <definedName name="Common_InputFunctions.Utility_LookupItemFromMinMax">_xlfn.LAMBDA(_xlpm.LookupValue,_xlpm.MinArray,_xlpm.MaxArray,_xlpm.ItemArray, _xlfn.LET(_xlpm.mask, (VALUE(_xlpm.MinArray) &lt;= _xlpm.LookupValue) * (VALUE(_xlpm.MaxArray) &gt;= _xlpm.LookupValue), _xlfn._xlws.FILTER(_xlpm.ItemArray, _xlpm.mask, "No match")))</definedName>
+    <definedName name="Common_InputFunctions.Utility_LookupN2OEFFromProdIrrigationRainfall" localSheetId="6">_xlfn.LAMBDA(_xlpm.ProductionSystem,_xlpm.IrrigationMethod,_xlpm.RainfallZone,_xlpm.ProductionSystemArray,_xlpm.IrrigationMethodArray,_xlpm.RainfallZoneArray,_xlpm.ReturnArray, _xlfn.LET(_xlpm.IrrigationMethod, IF(_xlpm.IrrigationMethod = "Not irrigated", "Not irrigated", "Any"), _xlpm.RainfallZone, IF(_xlpm.IrrigationMethod = "Not irrigated", _xlpm.RainfallZone, "Any"), _xlfn.XLOOKUP(1, (_xlpm.ProductionSystemArray = _xlpm.ProductionSystem) * (_xlpm.IrrigationMethodArray = _xlpm.IrrigationMethod) * (_xlpm.RainfallZoneArray = _xlpm.RainfallZone), _xlpm.ReturnArray)))</definedName>
     <definedName name="Common_InputFunctions.Utility_LookupN2OEFFromProdIrrigationRainfall" localSheetId="4">_xlfn.LAMBDA(_xlpm.ProductionSystem,_xlpm.IrrigationMethod,_xlpm.RainfallZone,_xlpm.ProductionSystemArray,_xlpm.IrrigationMethodArray,_xlpm.RainfallZoneArray,_xlpm.ReturnArray, _xlfn.LET(_xlpm.IrrigationMethod, IF(_xlpm.IrrigationMethod = "Not irrigated", "Not irrigated", "Any"), _xlpm.RainfallZone, IF(_xlpm.IrrigationMethod = "Not irrigated", _xlpm.RainfallZone, "Any"), _xlfn.XLOOKUP(1, (_xlpm.ProductionSystemArray = _xlpm.ProductionSystem) * (_xlpm.IrrigationMethodArray = _xlpm.IrrigationMethod) * (_xlpm.RainfallZoneArray = _xlpm.RainfallZone), _xlpm.ReturnArray)))</definedName>
     <definedName name="Common_InputFunctions.Utility_LookupN2OEFFromProdIrrigationRainfall">_xlfn.LAMBDA(_xlpm.ProductionSystem,_xlpm.IrrigationMethod,_xlpm.RainfallZone,_xlpm.ProductionSystemArray,_xlpm.IrrigationMethodArray,_xlpm.RainfallZoneArray,_xlpm.ReturnArray, _xlfn.LET(_xlpm.IrrigationMethod, IF(_xlpm.IrrigationMethod = "Not irrigated", "Not irrigated", "Any"), _xlpm.RainfallZone, IF(_xlpm.IrrigationMethod = "Not irrigated", _xlpm.RainfallZone, "Any"), _xlfn.XLOOKUP(1, (_xlpm.ProductionSystemArray = _xlpm.ProductionSystem) * (_xlpm.IrrigationMethodArray = _xlpm.IrrigationMethod) * (_xlpm.RainfallZoneArray = _xlpm.RainfallZone), _xlpm.ReturnArray)))</definedName>
+    <definedName name="Common_InputFunctions.Utility_LookupValueInTable" localSheetId="6">_xlfn.LAMBDA(_xlpm.LookupValue,_xlpm.LookupArray,_xlpm.ReturnArray, _xlfn.XLOOKUP(_xlpm.LookupValue, _xlpm.LookupArray, _xlpm.ReturnArray, ""))</definedName>
     <definedName name="Common_InputFunctions.Utility_LookupValueInTable" localSheetId="4">_xlfn.LAMBDA(_xlpm.LookupValue,_xlpm.LookupArray,_xlpm.ReturnArray, _xlfn.XLOOKUP(_xlpm.LookupValue, _xlpm.LookupArray, _xlpm.ReturnArray, ""))</definedName>
     <definedName name="Common_InputFunctions.Utility_LookupValueInTable">_xlfn.LAMBDA(_xlpm.LookupValue,_xlpm.LookupArray,_xlpm.ReturnArray, _xlfn.XLOOKUP(_xlpm.LookupValue, _xlpm.LookupArray, _xlpm.ReturnArray, ""))</definedName>
+    <definedName name="Common_InputFunctions.Utility_LookupValueInTableNumber" localSheetId="6">_xlfn.LAMBDA(_xlpm.LookupValue,_xlpm.LookupArray,_xlpm.ReturnArray, IF(ISNUMBER(_xlfn.XLOOKUP(_xlpm.LookupValue, _xlpm.LookupArray, _xlpm.ReturnArray, "")), _xlfn.XLOOKUP(_xlpm.LookupValue, _xlpm.LookupArray, _xlpm.ReturnArray, ""), 0))</definedName>
     <definedName name="Common_InputFunctions.Utility_LookupValueInTableNumber" localSheetId="4">_xlfn.LAMBDA(_xlpm.LookupValue,_xlpm.LookupArray,_xlpm.ReturnArray, IF(ISNUMBER(_xlfn.XLOOKUP(_xlpm.LookupValue, _xlpm.LookupArray, _xlpm.ReturnArray, "")), _xlfn.XLOOKUP(_xlpm.LookupValue, _xlpm.LookupArray, _xlpm.ReturnArray, ""), 0))</definedName>
     <definedName name="Common_InputFunctions.Utility_LookupValueInTableNumber">_xlfn.LAMBDA(_xlpm.LookupValue,_xlpm.LookupArray,_xlpm.ReturnArray, IF(ISNUMBER(_xlfn.XLOOKUP(_xlpm.LookupValue, _xlpm.LookupArray, _xlpm.ReturnArray, "")), _xlfn.XLOOKUP(_xlpm.LookupValue, _xlpm.LookupArray, _xlpm.ReturnArray, ""), 0))</definedName>
+    <definedName name="Common_InputFunctions.Utility_LookupValueInTableOneColumnAndHeader" localSheetId="6">_xlfn.LAMBDA(_xlpm.LookupValue1,_xlpm.LookupValue2,_xlpm.LookupArray1,_xlpm.LookupArray2,_xlpm.ReturnArray,_xlop.ValueIfFalse, IFERROR(_xlfn.XLOOKUP(_xlpm.LookupValue1, _xlpm.LookupArray1, _xlfn.XLOOKUP(_xlpm.LookupValue2, _xlpm.LookupArray2, _xlpm.ReturnArray)), IF(_xlfn.ISOMITTED(_xlpm.ValueIfFalse), "", _xlpm.ValueIfFalse)))</definedName>
     <definedName name="Common_InputFunctions.Utility_LookupValueInTableOneColumnAndHeader" localSheetId="4">_xlfn.LAMBDA(_xlpm.LookupValue1,_xlpm.LookupValue2,_xlpm.LookupArray1,_xlpm.LookupArray2,_xlpm.ReturnArray,_xlop.ValueIfFalse, IFERROR(_xlfn.XLOOKUP(_xlpm.LookupValue1, _xlpm.LookupArray1, _xlfn.XLOOKUP(_xlpm.LookupValue2, _xlpm.LookupArray2, _xlpm.ReturnArray)), IF(_xlfn.ISOMITTED(_xlpm.ValueIfFalse), "", _xlpm.ValueIfFalse)))</definedName>
     <definedName name="Common_InputFunctions.Utility_LookupValueInTableOneColumnAndHeader">_xlfn.LAMBDA(_xlpm.LookupValue1,_xlpm.LookupValue2,_xlpm.LookupArray1,_xlpm.LookupArray2,_xlpm.ReturnArray,_xlop.ValueIfFalse, IFERROR(_xlfn.XLOOKUP(_xlpm.LookupValue1, _xlpm.LookupArray1, _xlfn.XLOOKUP(_xlpm.LookupValue2, _xlpm.LookupArray2, _xlpm.ReturnArray)), IF(_xlfn.ISOMITTED(_xlpm.ValueIfFalse), "", _xlpm.ValueIfFalse)))</definedName>
+    <definedName name="Common_InputFunctions.Utility_LookupValueInTableTwoColumns" localSheetId="6">_xlfn.LAMBDA(_xlpm.LookupValue1,_xlpm.LookupValue2,_xlpm.LookupArray1,_xlpm.LookupArray2,_xlpm.ReturnArray,_xlop.ValueIFFalse, _xlfn.XLOOKUP(1, (_xlpm.LookupArray1 = _xlpm.LookupValue1) * (_xlpm.LookupArray2 = _xlpm.LookupValue2), _xlpm.ReturnArray, IF(_xlfn.ISOMITTED(_xlpm.ValueIFFalse), "", _xlpm.ValueIFFalse)))</definedName>
     <definedName name="Common_InputFunctions.Utility_LookupValueInTableTwoColumns" localSheetId="4">_xlfn.LAMBDA(_xlpm.LookupValue1,_xlpm.LookupValue2,_xlpm.LookupArray1,_xlpm.LookupArray2,_xlpm.ReturnArray,_xlop.ValueIFFalse, _xlfn.XLOOKUP(1, (_xlpm.LookupArray1 = _xlpm.LookupValue1) * (_xlpm.LookupArray2 = _xlpm.LookupValue2), _xlpm.ReturnArray, IF(_xlfn.ISOMITTED(_xlpm.ValueIFFalse), "", _xlpm.ValueIFFalse)))</definedName>
     <definedName name="Common_InputFunctions.Utility_LookupValueInTableTwoColumns">_xlfn.LAMBDA(_xlpm.LookupValue1,_xlpm.LookupValue2,_xlpm.LookupArray1,_xlpm.LookupArray2,_xlpm.ReturnArray,_xlop.ValueIFFalse, _xlfn.XLOOKUP(1, (_xlpm.LookupArray1 = _xlpm.LookupValue1) * (_xlpm.LookupArray2 = _xlpm.LookupValue2), _xlpm.ReturnArray, IF(_xlfn.ISOMITTED(_xlpm.ValueIFFalse), "", _xlpm.ValueIFFalse)))</definedName>
+    <definedName name="Common_InputFunctions.Utility_ResultsItemFromEquationTitleAndSource" localSheetId="6">_xlfn.LAMBDA(_xlpm.TitleCell,_xlpm.SourceCell, SUBSTITUTE(LEFT(_xlpm.SourceCell, FIND(",", _xlpm.SourceCell) - 1), "VEERG 2026: ", "") &amp; " " &amp; _xlpm.TitleCell)</definedName>
     <definedName name="Common_InputFunctions.Utility_ResultsItemFromEquationTitleAndSource" localSheetId="4">_xlfn.LAMBDA(_xlpm.TitleCell,_xlpm.SourceCell, SUBSTITUTE(LEFT(_xlpm.SourceCell, FIND(",", _xlpm.SourceCell) - 1), "VEERG 2026: ", "") &amp; " " &amp; _xlpm.TitleCell)</definedName>
     <definedName name="Common_InputFunctions.Utility_ResultsItemFromEquationTitleAndSource">_xlfn.LAMBDA(_xlpm.TitleCell,_xlpm.SourceCell, SUBSTITUTE(LEFT(_xlpm.SourceCell, FIND(",", _xlpm.SourceCell) - 1), "VEERG 2026: ", "") &amp; " " &amp; _xlpm.TitleCell)</definedName>
+    <definedName name="Common_InputFunctions.Utility_SourceHyperlink" localSheetId="6">_xlfn.LAMBDA(_xlpm.TargetCell, _xlfn.LET(_xlpm.sh, _xlfn.TEXTAFTER(CELL("filename", _xlpm.TargetCell), "]"), _xlpm.addr, CELL("address", _xlpm.TargetCell), "#'" &amp; _xlpm.sh &amp; "'!" &amp; _xlpm.addr))</definedName>
     <definedName name="Common_InputFunctions.Utility_SourceHyperlink" localSheetId="4">_xlfn.LAMBDA(_xlpm.TargetCell, _xlfn.LET(_xlpm.sh, _xlfn.TEXTAFTER(CELL("filename", _xlpm.TargetCell), "]"), _xlpm.addr, CELL("address", _xlpm.TargetCell), "#'" &amp; _xlpm.sh &amp; "'!" &amp; _xlpm.addr))</definedName>
     <definedName name="Common_InputFunctions.Utility_SourceHyperlink">_xlfn.LAMBDA(_xlpm.TargetCell, _xlfn.LET(_xlpm.sh, _xlfn.TEXTAFTER(CELL("filename", _xlpm.TargetCell), "]"), _xlpm.addr, CELL("address", _xlpm.TargetCell), "#'" &amp; _xlpm.sh &amp; "'!" &amp; _xlpm.addr))</definedName>
+    <definedName name="Common_InputFunctions.Utility_SourceHyperlinkDifferentSheet" localSheetId="6">_xlfn.LAMBDA(_xlpm.TargetCell, _xlfn.LET(_xlpm.sh, _xlfn.TEXTAFTER(CELL("filename", _xlpm.TargetCell), "]"), _xlpm.addr, CELL("address", _xlpm.TargetCell), "#" &amp; _xlpm.addr))</definedName>
     <definedName name="Common_InputFunctions.Utility_SourceHyperlinkDifferentSheet" localSheetId="4">_xlfn.LAMBDA(_xlpm.TargetCell, _xlfn.LET(_xlpm.sh, _xlfn.TEXTAFTER(CELL("filename", _xlpm.TargetCell), "]"), _xlpm.addr, CELL("address", _xlpm.TargetCell), "#" &amp; _xlpm.addr))</definedName>
     <definedName name="Common_InputFunctions.Utility_SourceHyperlinkDifferentSheet">_xlfn.LAMBDA(_xlpm.TargetCell, _xlfn.LET(_xlpm.sh, _xlfn.TEXTAFTER(CELL("filename", _xlpm.TargetCell), "]"), _xlpm.addr, CELL("address", _xlpm.TargetCell), "#" &amp; _xlpm.addr))</definedName>
+    <definedName name="Common_InputFunctions.Utility_SplitStringIntoArray" localSheetId="6">_xlfn.LAMBDA(_xlpm.Cell,_xlpm.Delimiter,_xlop.CharacterToRemove1,_xlop.CharacterToRemove2, _xlfn.FILTERXML("&lt;t&gt;&lt;s&gt;" &amp; SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(_xlpm.Cell, _xlpm.CharacterToRemove1, ""), _xlpm.CharacterToRemove2, ""), _xlpm.Delimiter, "&lt;/s&gt;&lt;s&gt;") &amp; "&lt;/s&gt;&lt;/t&gt;", "//s"))</definedName>
     <definedName name="Common_InputFunctions.Utility_SplitStringIntoArray" localSheetId="4">_xlfn.LAMBDA(_xlpm.Cell,_xlpm.Delimiter,_xlop.CharacterToRemove1,_xlop.CharacterToRemove2, _xlfn.FILTERXML("&lt;t&gt;&lt;s&gt;" &amp; SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(_xlpm.Cell, _xlpm.CharacterToRemove1, ""), _xlpm.CharacterToRemove2, ""), _xlpm.Delimiter, "&lt;/s&gt;&lt;s&gt;") &amp; "&lt;/s&gt;&lt;/t&gt;", "//s"))</definedName>
     <definedName name="Common_InputFunctions.Utility_SplitStringIntoArray">_xlfn.LAMBDA(_xlpm.Cell,_xlpm.Delimiter,_xlop.CharacterToRemove1,_xlop.CharacterToRemove2, _xlfn.FILTERXML("&lt;t&gt;&lt;s&gt;" &amp; SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(_xlpm.Cell, _xlpm.CharacterToRemove1, ""), _xlpm.CharacterToRemove2, ""), _xlpm.Delimiter, "&lt;/s&gt;&lt;s&gt;") &amp; "&lt;/s&gt;&lt;/t&gt;", "//s"))</definedName>
+    <definedName name="Common_InputFunctions.Utility_SumQuantityFromCriteria" localSheetId="6">_xlfn.LAMBDA(_xlpm.Criteria1,_xlpm.Criteria1TypeArray,_xlpm.Quantity,_xlop.Multiplier,_xlop.Criteria2,_xlop.Criteria2Array, _xlfn.LET(_xlpm.multiplier, IF(_xlfn.ISOMITTED(_xlpm.Multiplier), 1, _xlpm.Multiplier), _xlpm.quantity, _xlpm.Quantity * _xlpm.multiplier, _xlpm.criteria1, --(_xlpm.Criteria1TypeArray = _xlpm.Criteria1), _xlpm.criteria2, IF(_xlfn.ISOMITTED(_xlpm.Criteria2), 1, --(_xlpm.Criteria2Array = _xlpm.Criteria2)), SUMPRODUCT(_xlpm.criteria1 * _xlpm.criteria2 * _xlpm.quantity)))</definedName>
     <definedName name="Common_InputFunctions.Utility_SumQuantityFromCriteria" localSheetId="4">_xlfn.LAMBDA(_xlpm.Criteria1,_xlpm.Criteria1TypeArray,_xlpm.Quantity,_xlop.Multiplier,_xlop.Criteria2,_xlop.Criteria2Array, _xlfn.LET(_xlpm.multiplier, IF(_xlfn.ISOMITTED(_xlpm.Multiplier), 1, _xlpm.Multiplier), _xlpm.quantity, _xlpm.Quantity * _xlpm.multiplier, _xlpm.criteria1, --(_xlpm.Criteria1TypeArray = _xlpm.Criteria1), _xlpm.criteria2, IF(_xlfn.ISOMITTED(_xlpm.Criteria2), 1, --(_xlpm.Criteria2Array = _xlpm.Criteria2)), SUMPRODUCT(_xlpm.criteria1 * _xlpm.criteria2 * _xlpm.quantity)))</definedName>
     <definedName name="Common_InputFunctions.Utility_SumQuantityFromCriteria">_xlfn.LAMBDA(_xlpm.Criteria1,_xlpm.Criteria1TypeArray,_xlpm.Quantity,_xlop.Multiplier,_xlop.Criteria2,_xlop.Criteria2Array, _xlfn.LET(_xlpm.multiplier, IF(_xlfn.ISOMITTED(_xlpm.Multiplier), 1, _xlpm.Multiplier), _xlpm.quantity, _xlpm.Quantity * _xlpm.multiplier, _xlpm.criteria1, --(_xlpm.Criteria1TypeArray = _xlpm.Criteria1), _xlpm.criteria2, IF(_xlfn.ISOMITTED(_xlpm.Criteria2), 1, --(_xlpm.Criteria2Array = _xlpm.Criteria2)), SUMPRODUCT(_xlpm.criteria1 * _xlpm.criteria2 * _xlpm.quantity)))</definedName>
+    <definedName name="Common_SourceData.Common_SourceData_AustralianStatesTerritories_Data" localSheetId="6">_xlfn.LAMBDA(_xlfn.MAKEARRAY(9, 3, _xlfn.LAMBDA(_xlpm.r,_xlpm.c, INDEX({"State/Territory","Common Name","Abbreviation";"New South Wales","New South Wales","NSW";"Australian Capital Territory","ACT","ACT";"Victoria","Victoria","VIC";"Queensland","Queensland","QLD";"South Australia","South Australia","SA";"Western Australia","Western Australia","WA";"Tasmania","Tasmania","TAS";"Northern Territory","Northern Territory","NT"}, _xlpm.r, _xlpm.c))))</definedName>
     <definedName name="Common_SourceData.Common_SourceData_AustralianStatesTerritories_Data" localSheetId="4">_xlfn.LAMBDA(_xlfn.MAKEARRAY(9, 3, _xlfn.LAMBDA(_xlpm.r,_xlpm.c, INDEX({"State/Territory","Common Name","Abbreviation";"New South Wales","New South Wales","NSW";"Australian Capital Territory","ACT","ACT";"Victoria","Victoria","VIC";"Queensland","Queensland","QLD";"South Australia","South Australia","SA";"Western Australia","Western Australia","WA";"Tasmania","Tasmania","TAS";"Northern Territory","Northern Territory","NT"}, _xlpm.r, _xlpm.c))))</definedName>
     <definedName name="Common_SourceData.Common_SourceData_AustralianStatesTerritories_Data">_xlfn.LAMBDA(_xlfn.MAKEARRAY(9, 3, _xlfn.LAMBDA(_xlpm.r,_xlpm.c, INDEX({"State/Territory","Common Name","Abbreviation";"New South Wales","New South Wales","NSW";"Australian Capital Territory","ACT","ACT";"Victoria","Victoria","VIC";"Queensland","Queensland","QLD";"South Australia","South Australia","SA";"Western Australia","Western Australia","WA";"Tasmania","Tasmania","TAS";"Northern Territory","Northern Territory","NT"}, _xlpm.r, _xlpm.c))))</definedName>
     <definedName name="Common_SourceData.Common_SourceData_AustralianStatesTerritories_Source">_xlfn.LAMBDA("")</definedName>
     <definedName name="Common_SourceData.Common_SourceData_AustralianStatesTerritories_Title">_xlfn.LAMBDA("Australian states and territories")</definedName>
     <definedName name="Common_SourceData.Common_SourceData_AustralianStatesTerritories_Unit">_xlfn.LAMBDA("")</definedName>
     <definedName name="Common_SourceData.Common_SourceData_AustralianStatesTerritories_Variable">_xlfn.LAMBDA("")</definedName>
+    <definedName name="Common_SourceData.Common_SourceData_ClimateZones_Appendices" localSheetId="6">_xlfn.LAMBDA(_xlfn.MAKEARRAY(4, 1, _xlfn.LAMBDA(_xlpm.r,_xlpm.c, INDEX({"Note:";"MAT = mean annual temperature";"MAP = mean annual precipitation";"PET = potential evapotranspiration"}, _xlpm.r, _xlpm.c))))</definedName>
     <definedName name="Common_SourceData.Common_SourceData_ClimateZones_Appendices" localSheetId="4">_xlfn.LAMBDA(_xlfn.MAKEARRAY(4, 1, _xlfn.LAMBDA(_xlpm.r,_xlpm.c, INDEX({"Note:";"MAT = mean annual temperature";"MAP = mean annual precipitation";"PET = potential evapotranspiration"}, _xlpm.r, _xlpm.c))))</definedName>
     <definedName name="Common_SourceData.Common_SourceData_ClimateZones_Appendices">_xlfn.LAMBDA(_xlfn.MAKEARRAY(4, 1, _xlfn.LAMBDA(_xlpm.r,_xlpm.c, INDEX({"Note:";"MAT = mean annual temperature";"MAP = mean annual precipitation";"PET = potential evapotranspiration"}, _xlpm.r, _xlpm.c))))</definedName>
+    <definedName name="Common_SourceData.Common_SourceData_ClimateZones_Data" localSheetId="6">_xlfn.LAMBDA(_xlfn.MAKEARRAY(9, 16, _xlfn.LAMBDA(_xlpm.r,_xlpm.c, INDEX({"Climate Zone","MAT","MAP","Frost days per year","Elevation","MAP:PET","Min temp","Max temp","Min rainfall","Max rainfall","Min frost days","Max frost days","Min elevation","Max elevation","Min MAP:PET","Min MAP:PET";"Tropical montane","&gt; 18 C","Any","≤ 7","&gt; 1000 m","Any",18.001,999999,-999999,999999,-999999,7,1000,999999,-999999,999999;"Tropical wet","&gt; 18 C","&gt; 2000 mm","≤ 7","≤ 1000 m","Any",18.001,999999,2000.001,999999,-999999,7,-999999,999.999,-999999,999999;"Tropical moist","&gt; 18 C","&gt; 1000 mm - ≤ 2000 mm","≤ 7","≤ 1000 m","Any",18.001,999999,1000.001,2000,-999999,7,-999999,999.999,-999999,999999;"Tropical dry","&gt; 18 C","≤ 1000 mm","≤ 7","≤ 1000 m","Any",18.001,999999,-999999,1000,-999999,7,-999999,999.999,-999999,999999;"Warm temperate moist","&gt; 10 C","Any","Any","Any","&gt; 1",10.001,999999,-999999,999999,-999999,999999,-999999,999999,1.001,999999;"Warm temperate dry","&gt; 10 C","Any","Any","Any","≤ 1",10.001,999999,-999999,999999,-999999,999999,-999999,999999,-999999,1;"Cool temperate moist","&gt; 0 C - ≤ 10 C","Any","Any","Any","&gt; 1",-999999,10,-999999,999999,-999999,999999,-999999,999999,1.001,999999;"Cool temperate dry","&gt; 0 C - ≤ 10 C","Any","Any","Any","≤ 1",-999999,10,-999999,999999,-999999,999999,-999999,999999,-999999,1}, _xlpm.r, _xlpm.c))))</definedName>
     <definedName name="Common_SourceData.Common_SourceData_ClimateZones_Data" localSheetId="4">_xlfn.LAMBDA(_xlfn.MAKEARRAY(9, 16, _xlfn.LAMBDA(_xlpm.r,_xlpm.c, INDEX({"Climate Zone","MAT","MAP","Frost days per year","Elevation","MAP:PET","Min temp","Max temp","Min rainfall","Max rainfall","Min frost days","Max frost days","Min elevation","Max elevation","Min MAP:PET","Min MAP:PET";"Tropical montane","&gt; 18 C","Any","≤ 7","&gt; 1000 m","Any",18.001,999999,-999999,999999,-999999,7,1000,999999,-999999,999999;"Tropical wet","&gt; 18 C","&gt; 2000 mm","≤ 7","≤ 1000 m","Any",18.001,999999,2000.001,999999,-999999,7,-999999,999.999,-999999,999999;"Tropical moist","&gt; 18 C","&gt; 1000 mm - ≤ 2000 mm","≤ 7","≤ 1000 m","Any",18.001,999999,1000.001,2000,-999999,7,-999999,999.999,-999999,999999;"Tropical dry","&gt; 18 C","≤ 1000 mm","≤ 7","≤ 1000 m","Any",18.001,999999,-999999,1000,-999999,7,-999999,999.999,-999999,999999;"Warm temperate moist","&gt; 10 C","Any","Any","Any","&gt; 1",10.001,999999,-999999,999999,-999999,999999,-999999,999999,1.001,999999;"Warm temperate dry","&gt; 10 C","Any","Any","Any","≤ 1",10.001,999999,-999999,999999,-999999,999999,-999999,999999,-999999,1;"Cool temperate moist","&gt; 0 C - ≤ 10 C","Any","Any","Any","&gt; 1",-999999,10,-999999,999999,-999999,999999,-999999,999999,1.001,999999;"Cool temperate dry","&gt; 0 C - ≤ 10 C","Any","Any","Any","≤ 1",-999999,10,-999999,999999,-999999,999999,-999999,999999,-999999,1}, _xlpm.r, _xlpm.c))))</definedName>
     <definedName name="Common_SourceData.Common_SourceData_ClimateZones_Data">_xlfn.LAMBDA(_xlfn.MAKEARRAY(9, 16, _xlfn.LAMBDA(_xlpm.r,_xlpm.c, INDEX({"Climate Zone","MAT","MAP","Frost days per year","Elevation","MAP:PET","Min temp","Max temp","Min rainfall","Max rainfall","Min frost days","Max frost days","Min elevation","Max elevation","Min MAP:PET","Min MAP:PET";"Tropical montane","&gt; 18 C","Any","≤ 7","&gt; 1000 m","Any",18.001,999999,-999999,999999,-999999,7,1000,999999,-999999,999999;"Tropical wet","&gt; 18 C","&gt; 2000 mm","≤ 7","≤ 1000 m","Any",18.001,999999,2000.001,999999,-999999,7,-999999,999.999,-999999,999999;"Tropical moist","&gt; 18 C","&gt; 1000 mm - ≤ 2000 mm","≤ 7","≤ 1000 m","Any",18.001,999999,1000.001,2000,-999999,7,-999999,999.999,-999999,999999;"Tropical dry","&gt; 18 C","≤ 1000 mm","≤ 7","≤ 1000 m","Any",18.001,999999,-999999,1000,-999999,7,-999999,999.999,-999999,999999;"Warm temperate moist","&gt; 10 C","Any","Any","Any","&gt; 1",10.001,999999,-999999,999999,-999999,999999,-999999,999999,1.001,999999;"Warm temperate dry","&gt; 10 C","Any","Any","Any","≤ 1",10.001,999999,-999999,999999,-999999,999999,-999999,999999,-999999,1;"Cool temperate moist","&gt; 0 C - ≤ 10 C","Any","Any","Any","&gt; 1",-999999,10,-999999,999999,-999999,999999,-999999,999999,1.001,999999;"Cool temperate dry","&gt; 0 C - ≤ 10 C","Any","Any","Any","≤ 1",-999999,10,-999999,999999,-999999,999999,-999999,999999,-999999,1}, _xlpm.r, _xlpm.c))))</definedName>
     <definedName name="Common_SourceData.Common_SourceData_ClimateZones_Source">_xlfn.LAMBDA("VEERG 2026: Table 1.3: Climate and Rainfall zone classifications and definitions")</definedName>
     <definedName name="Common_SourceData.Common_SourceData_ClimateZones_Title">_xlfn.LAMBDA("VEERG Australian climate zones")</definedName>
     <definedName name="Common_SourceData.Common_SourceData_ClimateZones_Unit">_xlfn.LAMBDA("")</definedName>
     <definedName name="Common_SourceData.Common_SourceData_ClimateZones_Variable">_xlfn.LAMBDA("")</definedName>
+    <definedName name="Common_SourceData.Common_SourceData_ClimateZones_Variation" localSheetId="6">_xlfn.LAMBDA(_xlfn.MAKEARRAY(5, 1, _xlfn.LAMBDA(_xlpm.r,_xlpm.c, INDEX({"VARIATION OF SOURCE DATA:";"Added warm / cool temperate moist / dry - low frost and high temp classes to accommodate climate scenarios excluded by VEERG criteria.";"Fixed typo in MAT value for warm temperate dry - changed 10 to 11.";"Added min and max columns for MAT, MAP, frost days per year, elevation, MAP:PET to calculate zones from real climate data.";"GAF accepts rainfall as a proxy for precipitation."}, _xlpm.r, _xlpm.c))))</definedName>
     <definedName name="Common_SourceData.Common_SourceData_ClimateZones_Variation" localSheetId="4">_xlfn.LAMBDA(_xlfn.MAKEARRAY(5, 1, _xlfn.LAMBDA(_xlpm.r,_xlpm.c, INDEX({"VARIATION OF SOURCE DATA:";"Added warm / cool temperate moist / dry - low frost and high temp classes to accommodate climate scenarios excluded by VEERG criteria.";"Fixed typo in MAT value for warm temperate dry - changed 10 to 11.";"Added min and max columns for MAT, MAP, frost days per year, elevation, MAP:PET to calculate zones from real climate data.";"GAF accepts rainfall as a proxy for precipitation."}, _xlpm.r, _xlpm.c))))</definedName>
     <definedName name="Common_SourceData.Common_SourceData_ClimateZones_Variation">_xlfn.LAMBDA(_xlfn.MAKEARRAY(5, 1, _xlfn.LAMBDA(_xlpm.r,_xlpm.c, INDEX({"VARIATION OF SOURCE DATA:";"Added warm / cool temperate moist / dry - low frost and high temp classes to accommodate climate scenarios excluded by VEERG criteria.";"Fixed typo in MAT value for warm temperate dry - changed 10 to 11.";"Added min and max columns for MAT, MAP, frost days per year, elevation, MAP:PET to calculate zones from real climate data.";"GAF accepts rainfall as a proxy for precipitation."}, _xlpm.r, _xlpm.c))))</definedName>
+    <definedName name="Common_SourceData.Common_SourceData_ConvertGasElementalToMolecular_Data" localSheetId="6">_xlfn.LAMBDA(_xlfn.MAKEARRAY(8, 4, _xlfn.LAMBDA(_xlpm.r,_xlpm.c, INDEX({"Gas","Conversion factor","Conversion factor 1","Conversion factor 2";"CO2","44/12",44,12;"CH4","16/12",16,12;"N2O","44/28",44,28;"Nox","46/14",46,14;"CO","28/12",28,12;"CO2 Lime","44/12",44,12;"NMVOC","14/12",14,12}, _xlpm.r, _xlpm.c))))</definedName>
     <definedName name="Common_SourceData.Common_SourceData_ConvertGasElementalToMolecular_Data" localSheetId="4">_xlfn.LAMBDA(_xlfn.MAKEARRAY(8, 4, _xlfn.LAMBDA(_xlpm.r,_xlpm.c, INDEX({"Gas","Conversion factor","Conversion factor 1","Conversion factor 2";"CO2","44/12",44,12;"CH4","16/12",16,12;"N2O","44/28",44,28;"Nox","46/14",46,14;"CO","28/12",28,12;"CO2 Lime","44/12",44,12;"NMVOC","14/12",14,12}, _xlpm.r, _xlpm.c))))</definedName>
     <definedName name="Common_SourceData.Common_SourceData_ConvertGasElementalToMolecular_Data">_xlfn.LAMBDA(_xlfn.MAKEARRAY(8, 4, _xlfn.LAMBDA(_xlpm.r,_xlpm.c, INDEX({"Gas","Conversion factor","Conversion factor 1","Conversion factor 2";"CO2","44/12",44,12;"CH4","16/12",16,12;"N2O","44/28",44,28;"Nox","46/14",46,14;"CO","28/12",28,12;"CO2 Lime","44/12",44,12;"NMVOC","14/12",14,12}, _xlpm.r, _xlpm.c))))</definedName>
     <definedName name="Common_SourceData.Common_SourceData_ConvertGasElementalToMolecular_Source">_xlfn.LAMBDA("XXXXXXX")</definedName>
@@ -116,6 +151,7 @@
     <definedName name="Common_SourceData.Common_SourceData_ConvertN2oElementalToMolecularCg_Title">_xlfn.LAMBDA("Factor to convert elemental mass of N2O to molecular mass")</definedName>
     <definedName name="Common_SourceData.Common_SourceData_ConvertN2oElementalToMolecularCg_Unit">_xlfn.LAMBDA("factor")</definedName>
     <definedName name="Common_SourceData.Common_SourceData_ConvertN2oElementalToMolecularCg_Variable">_xlfn.LAMBDA("CgN2O")</definedName>
+    <definedName name="Common_SourceData.Common_SourceData_DataScores_Scope3_Data" localSheetId="6">_xlfn.LAMBDA(_xlfn.MAKEARRAY(6, 2, _xlfn.LAMBDA(_xlpm.r,_xlpm.c, INDEX({"Data source","Data score";"International scope 3 database",1;"Australian scope 3 database",2;"State or regional scope 3 database",3;"Emissions intensity calculated from approved method",4;"Verified credential matching ISO14067",5}, _xlpm.r, _xlpm.c))))</definedName>
     <definedName name="Common_SourceData.Common_SourceData_DataScores_Scope3_Data" localSheetId="4">_xlfn.LAMBDA(_xlfn.MAKEARRAY(6, 2, _xlfn.LAMBDA(_xlpm.r,_xlpm.c, INDEX({"Data source","Data score";"International scope 3 database",1;"Australian scope 3 database",2;"State or regional scope 3 database",3;"Emissions intensity calculated from approved method",4;"Verified credential matching ISO14067",5}, _xlpm.r, _xlpm.c))))</definedName>
     <definedName name="Common_SourceData.Common_SourceData_DataScores_Scope3_Data">_xlfn.LAMBDA(_xlfn.MAKEARRAY(6, 2, _xlfn.LAMBDA(_xlpm.r,_xlpm.c, INDEX({"Data source","Data score";"International scope 3 database",1;"Australian scope 3 database",2;"State or regional scope 3 database",3;"Emissions intensity calculated from approved method",4;"Verified credential matching ISO14067",5}, _xlpm.r, _xlpm.c))))</definedName>
     <definedName name="Common_SourceData.Common_SourceData_DataScores_Scope3_Source">_xlfn.LAMBDA("VEERG 2026: XXXXXXXX")</definedName>
@@ -127,6 +163,7 @@
     <definedName name="Common_SourceData.Common_SourceData_DensityOfMethane_Source">_xlfn.LAMBDA("National Inventory Report 2023 Volume 1: Equations 3.B.1a_2, 3.B.1c_2, 3.B.3_1, 3.B.4g_2")</definedName>
     <definedName name="Common_SourceData.Common_SourceData_DensityOfMethane_Title">_xlfn.LAMBDA("p = density of methane")</definedName>
     <definedName name="Common_SourceData.Common_SourceData_DensityOfMethane_Unit">_xlfn.LAMBDA("kg/m3")</definedName>
+    <definedName name="Common_SourceData.Common_SourceData_EFleach_Data" localSheetId="6">_xlfn.LAMBDA(_xlfn.MAKEARRAY(1, 2, _xlfn.LAMBDA(_xlpm.r,_xlpm.c, INDEX({"EFleach",0.011}, _xlpm.r, _xlpm.c))))</definedName>
     <definedName name="Common_SourceData.Common_SourceData_EFleach_Data" localSheetId="4">_xlfn.LAMBDA(_xlfn.MAKEARRAY(1, 2, _xlfn.LAMBDA(_xlpm.r,_xlpm.c, INDEX({"EFleach",0.011}, _xlpm.r, _xlpm.c))))</definedName>
     <definedName name="Common_SourceData.Common_SourceData_EFleach_Data">_xlfn.LAMBDA(_xlfn.MAKEARRAY(1, 2, _xlfn.LAMBDA(_xlpm.r,_xlpm.c, INDEX({"EFleach",0.011}, _xlpm.r, _xlpm.c))))</definedName>
     <definedName name="Common_SourceData.Common_SourceData_EFleach_NIRReference">_xlfn.LAMBDA("National Inventory Report Volume 1: Equation 3.D.B_10")</definedName>
@@ -134,14 +171,17 @@
     <definedName name="Common_SourceData.Common_SourceData_EFleach_Title">_xlfn.LAMBDA("Emission factor for nitrogen leaching and runoff")</definedName>
     <definedName name="Common_SourceData.Common_SourceData_EFleach_Unit">_xlfn.LAMBDA("(kg N2O-N / kg N")</definedName>
     <definedName name="Common_SourceData.Common_SourceData_EFleach_Variation">_xlfn.LAMBDA((""))</definedName>
+    <definedName name="Common_SourceData.Common_SourceData_EFN2O_Data" localSheetId="6">_xlfn.LAMBDA(_xlfn.MAKEARRAY(15, 5, _xlfn.LAMBDA(_xlpm.r,_xlpm.c, INDEX({"Production system j","EFN2O","Production system only","Irrigation method","Rainfall zone";"Irrigated pasture",0.0059,"Pasture","Any","Any";"Irrigated crop",0.007,"Crop","Any","Any";"Non-irrigated pasture",0.0018,"Pasture","Not irrigated","Low rainfall";"Non-irrigated pasture",0.0018,"Pasture","Not irrigated","High rainfall";"Non-irrigated crop (low rainfall)",0.0029,"Crop","Not irrigated","Low rainfall";"Non-irrigated crop (high rainfall)",0.008,"Crop","Not irrigated","High rainfall";"Sugar",0.0199,"Sugar","Any","Any";"Cotton",0.0053,"Cotton","Any","Any";"Horticultural crops",0.0064,"Horticultural crops","Any","Any";"Rice (continuous flooding)",0.003,"Rice","Continuous flooding","Any";"Rice (single and multiple drainage, or alternate wetting and drying)",0.005,"Rice","Single and multiple drainage, or alternate wetting and drying","Any";"Aquaculture",0.0026,"Aquaculture","Any","Any";"Forestry",0.0018,"Forestry","Any","Any"}, _xlpm.r, _xlpm.c))))</definedName>
     <definedName name="Common_SourceData.Common_SourceData_EFN2O_Data" localSheetId="4">_xlfn.LAMBDA(_xlfn.MAKEARRAY(15, 5, _xlfn.LAMBDA(_xlpm.r,_xlpm.c, INDEX({"Production system j","EFN2O","Production system only","Irrigation method","Rainfall zone";"Irrigated pasture",0.0059,"Pasture","Any","Any";"Irrigated crop",0.007,"Crop","Any","Any";"Non-irrigated pasture",0.0018,"Pasture","Not irrigated","Low rainfall";"Non-irrigated pasture",0.0018,"Pasture","Not irrigated","High rainfall";"Non-irrigated crop (low rainfall)",0.0029,"Crop","Not irrigated","Low rainfall";"Non-irrigated crop (high rainfall)",0.008,"Crop","Not irrigated","High rainfall";"Sugar",0.0199,"Sugar","Any","Any";"Cotton",0.0053,"Cotton","Any","Any";"Horticultural crops",0.0064,"Horticultural crops","Any","Any";"Rice (continuous flooding)",0.003,"Rice","Continuous flooding","Any";"Rice (single and multiple drainage, or alternate wetting and drying)",0.005,"Rice","Single and multiple drainage, or alternate wetting and drying","Any";"Aquaculture",0.0026,"Aquaculture","Any","Any";"Forestry",0.0018,"Forestry","Any","Any"}, _xlpm.r, _xlpm.c))))</definedName>
     <definedName name="Common_SourceData.Common_SourceData_EFN2O_Data">_xlfn.LAMBDA(_xlfn.MAKEARRAY(15, 5, _xlfn.LAMBDA(_xlpm.r,_xlpm.c, INDEX({"Production system j","EFN2O","Production system only","Irrigation method","Rainfall zone";"Irrigated pasture",0.0059,"Pasture","Any","Any";"Irrigated crop",0.007,"Crop","Any","Any";"Non-irrigated pasture",0.0018,"Pasture","Not irrigated","Low rainfall";"Non-irrigated pasture",0.0018,"Pasture","Not irrigated","High rainfall";"Non-irrigated crop (low rainfall)",0.0029,"Crop","Not irrigated","Low rainfall";"Non-irrigated crop (high rainfall)",0.008,"Crop","Not irrigated","High rainfall";"Sugar",0.0199,"Sugar","Any","Any";"Cotton",0.0053,"Cotton","Any","Any";"Horticultural crops",0.0064,"Horticultural crops","Any","Any";"Rice (continuous flooding)",0.003,"Rice","Continuous flooding","Any";"Rice (single and multiple drainage, or alternate wetting and drying)",0.005,"Rice","Single and multiple drainage, or alternate wetting and drying","Any";"Aquaculture",0.0026,"Aquaculture","Any","Any";"Forestry",0.0018,"Forestry","Any","Any"}, _xlpm.r, _xlpm.c))))</definedName>
     <definedName name="Common_SourceData.Common_SourceData_EFN2O_NIRReference">_xlfn.LAMBDA("")</definedName>
     <definedName name="Common_SourceData.Common_SourceData_EFN2O_Source">_xlfn.LAMBDA("VEERG 2026: Table A.2.2.1")</definedName>
     <definedName name="Common_SourceData.Common_SourceData_EFN2O_Title">_xlfn.LAMBDA("Nitrous oxide emission factors for inorganic fertiliser application")</definedName>
     <definedName name="Common_SourceData.Common_SourceData_EFN2O_Unit">_xlfn.LAMBDA("(kg N2O-N / kg N")</definedName>
+    <definedName name="Common_SourceData.Common_SourceData_EFN2O_Variation" localSheetId="6">_xlfn.LAMBDA(_xlfn.MAKEARRAY(5, 1, _xlfn.LAMBDA(_xlpm.r,_xlpm.c, INDEX({"VARIATION OF SOURCE DATA:";"Removed duplicate 'Aquaculture' row.";"Removed asterisks to aid lookup.";"Added 'production system only', 'rainfall zone' and 'irrigation method' columns to aid lookup.";"Duplicated 'non-irrigated pasture' row with same EF for low and high rainfall zones to aid lookup."}, _xlpm.r, _xlpm.c))))</definedName>
     <definedName name="Common_SourceData.Common_SourceData_EFN2O_Variation" localSheetId="4">_xlfn.LAMBDA(_xlfn.MAKEARRAY(5, 1, _xlfn.LAMBDA(_xlpm.r,_xlpm.c, INDEX({"VARIATION OF SOURCE DATA:";"Removed duplicate 'Aquaculture' row.";"Removed asterisks to aid lookup.";"Added 'production system only', 'rainfall zone' and 'irrigation method' columns to aid lookup.";"Duplicated 'non-irrigated pasture' row with same EF for low and high rainfall zones to aid lookup."}, _xlpm.r, _xlpm.c))))</definedName>
     <definedName name="Common_SourceData.Common_SourceData_EFN2O_Variation">_xlfn.LAMBDA(_xlfn.MAKEARRAY(5, 1, _xlfn.LAMBDA(_xlpm.r,_xlpm.c, INDEX({"VARIATION OF SOURCE DATA:";"Removed duplicate 'Aquaculture' row.";"Removed asterisks to aid lookup.";"Added 'production system only', 'rainfall zone' and 'irrigation method' columns to aid lookup.";"Duplicated 'non-irrigated pasture' row with same EF for low and high rainfall zones to aid lookup."}, _xlpm.r, _xlpm.c))))</definedName>
+    <definedName name="Common_SourceData.Common_SourceData_EFOrganicFertiliserAndCropResidues_Data" localSheetId="6">_xlfn.LAMBDA(_xlfn.MAKEARRAY(3, 2, _xlfn.LAMBDA(_xlpm.r,_xlpm.c, INDEX({"Climate zone","EFNi &amp; EFN2O";"Wet climate zone",0.006;"Dry climate zone",0.005}, _xlpm.r, _xlpm.c))))</definedName>
     <definedName name="Common_SourceData.Common_SourceData_EFOrganicFertiliserAndCropResidues_Data" localSheetId="4">_xlfn.LAMBDA(_xlfn.MAKEARRAY(3, 2, _xlfn.LAMBDA(_xlpm.r,_xlpm.c, INDEX({"Climate zone","EFNi &amp; EFN2O";"Wet climate zone",0.006;"Dry climate zone",0.005}, _xlpm.r, _xlpm.c))))</definedName>
     <definedName name="Common_SourceData.Common_SourceData_EFOrganicFertiliserAndCropResidues_Data">_xlfn.LAMBDA(_xlfn.MAKEARRAY(3, 2, _xlfn.LAMBDA(_xlpm.r,_xlpm.c, INDEX({"Climate zone","EFNi &amp; EFN2O";"Wet climate zone",0.006;"Dry climate zone",0.005}, _xlpm.r, _xlpm.c))))</definedName>
     <definedName name="Common_SourceData.Common_SourceData_EFOrganicFertiliserAndCropResidues_NIRReference">_xlfn.LAMBDA("")</definedName>
@@ -150,6 +190,7 @@
     <definedName name="Common_SourceData.Common_SourceData_EFOrganicFertiliserAndCropResidues_Unit">_xlfn.LAMBDA("kg N2O - N / kg N")</definedName>
     <definedName name="Common_SourceData.Common_SourceData_EFOrganicFertiliserAndCropResidues_Variable">_xlfn.LAMBDA("EFNi &amp; EFN2Oi")</definedName>
     <definedName name="Common_SourceData.Common_SourceData_EFOrganicFertiliserAndCropResidues_Variation">_xlfn.LAMBDA("")</definedName>
+    <definedName name="Common_SourceData.Common_SourceData_EFPastureRangeAndPaddock_Data" localSheetId="6">_xlfn.LAMBDA(_xlfn.MAKEARRAY(3, 2, _xlfn.LAMBDA(_xlpm.r,_xlpm.c, INDEX({"Climate zone","EFPRP";"Wet climate zone",0.006;"Dry climate zone",0.002}, _xlpm.r, _xlpm.c))))</definedName>
     <definedName name="Common_SourceData.Common_SourceData_EFPastureRangeAndPaddock_Data" localSheetId="4">_xlfn.LAMBDA(_xlfn.MAKEARRAY(3, 2, _xlfn.LAMBDA(_xlpm.r,_xlpm.c, INDEX({"Climate zone","EFPRP";"Wet climate zone",0.006;"Dry climate zone",0.002}, _xlpm.r, _xlpm.c))))</definedName>
     <definedName name="Common_SourceData.Common_SourceData_EFPastureRangeAndPaddock_Data">_xlfn.LAMBDA(_xlfn.MAKEARRAY(3, 2, _xlfn.LAMBDA(_xlpm.r,_xlpm.c, INDEX({"Climate zone","EFPRP";"Wet climate zone",0.006;"Dry climate zone",0.002}, _xlpm.r, _xlpm.c))))</definedName>
     <definedName name="Common_SourceData.Common_SourceData_EFPastureRangeAndPaddock_NIRReference">_xlfn.LAMBDA("")</definedName>
@@ -157,6 +198,7 @@
     <definedName name="Common_SourceData.Common_SourceData_EFPastureRangeAndPaddock_Title">_xlfn.LAMBDA("Emission factor for urine and dung deposited on pasture, range or paddock")</definedName>
     <definedName name="Common_SourceData.Common_SourceData_EFPastureRangeAndPaddock_Unit">_xlfn.LAMBDA("kg N2O - N / kg N")</definedName>
     <definedName name="Common_SourceData.Common_SourceData_EFPastureRangeAndPaddock_Variation">_xlfn.LAMBDA("VARIATION FROM SOURCE DATA: Changed 'Dry climate zones' to singular 'Dry climate zone' to aid lookup.")</definedName>
+    <definedName name="Common_SourceData.Common_SourceData_FracLEACH_Data" localSheetId="6">_xlfn.LAMBDA(_xlfn.MAKEARRAY(1, 2, _xlfn.LAMBDA(_xlpm.r,_xlpm.c, INDEX({"FracLEACH",0.24}, _xlpm.r, _xlpm.c))))</definedName>
     <definedName name="Common_SourceData.Common_SourceData_FracLEACH_Data" localSheetId="4">_xlfn.LAMBDA(_xlfn.MAKEARRAY(1, 2, _xlfn.LAMBDA(_xlpm.r,_xlpm.c, INDEX({"FracLEACH",0.24}, _xlpm.r, _xlpm.c))))</definedName>
     <definedName name="Common_SourceData.Common_SourceData_FracLEACH_Data">_xlfn.LAMBDA(_xlfn.MAKEARRAY(1, 2, _xlfn.LAMBDA(_xlpm.r,_xlpm.c, INDEX({"FracLEACH",0.24}, _xlpm.r, _xlpm.c))))</definedName>
     <definedName name="Common_SourceData.Common_SourceData_FracLEACH_NIRReference">_xlfn.LAMBDA("National Inventory Report Volume 1: Leaching and runoff (3.D.b.2)")</definedName>
@@ -164,6 +206,7 @@
     <definedName name="Common_SourceData.Common_SourceData_FracLEACH_Title">_xlfn.LAMBDA("Fraction of N that is available for leaching and runoff")</definedName>
     <definedName name="Common_SourceData.Common_SourceData_FracLEACH_Unit">_xlfn.LAMBDA("(Dimensionless")</definedName>
     <definedName name="Common_SourceData.Common_SourceData_FracLEACH_Variation">_xlfn.LAMBDA((""))</definedName>
+    <definedName name="Common_SourceData.Common_SourceData_FracWET_Data" localSheetId="6">_xlfn.LAMBDA(_xlfn.MAKEARRAY(3, 2, _xlfn.LAMBDA(_xlpm.r,_xlpm.c, INDEX({"Is in leaching zone","FracWET";"Yes - in leaching zone",1;"No - not in leaching zone",0}, _xlpm.r, _xlpm.c))))</definedName>
     <definedName name="Common_SourceData.Common_SourceData_FracWET_Data" localSheetId="4">_xlfn.LAMBDA(_xlfn.MAKEARRAY(3, 2, _xlfn.LAMBDA(_xlpm.r,_xlpm.c, INDEX({"Is in leaching zone","FracWET";"Yes - in leaching zone",1;"No - not in leaching zone",0}, _xlpm.r, _xlpm.c))))</definedName>
     <definedName name="Common_SourceData.Common_SourceData_FracWET_Data">_xlfn.LAMBDA(_xlfn.MAKEARRAY(3, 2, _xlfn.LAMBDA(_xlpm.r,_xlpm.c, INDEX({"Is in leaching zone","FracWET";"Yes - in leaching zone",1;"No - not in leaching zone",0}, _xlpm.r, _xlpm.c))))</definedName>
     <definedName name="Common_SourceData.Common_SourceData_FracWET_NIRReference">_xlfn.LAMBDA("")</definedName>
@@ -171,6 +214,7 @@
     <definedName name="Common_SourceData.Common_SourceData_FracWET_Title">_xlfn.LAMBDA("Fraction of N that is available for leaching and runoff")</definedName>
     <definedName name="Common_SourceData.Common_SourceData_FracWET_Unit">_xlfn.LAMBDA("(Dimensionless")</definedName>
     <definedName name="Common_SourceData.Common_SourceData_FracWET_Variation">_xlfn.LAMBDA((""))</definedName>
+    <definedName name="Common_SourceData.Common_SourceData_FracWETIrrigation_Data" localSheetId="6">_xlfn.LAMBDA(_xlfn.MAKEARRAY(6, 2, _xlfn.LAMBDA(_xlpm.r,_xlpm.c, INDEX({"Irrigation type ir","FracWET";"Not irrigated",0;"Drip irrigation",0;"Sprinkler irrigation",1;"Surface irrigation",1;"Other irrigation",1}, _xlpm.r, _xlpm.c))))</definedName>
     <definedName name="Common_SourceData.Common_SourceData_FracWETIrrigation_Data" localSheetId="4">_xlfn.LAMBDA(_xlfn.MAKEARRAY(6, 2, _xlfn.LAMBDA(_xlpm.r,_xlpm.c, INDEX({"Irrigation type ir","FracWET";"Not irrigated",0;"Drip irrigation",0;"Sprinkler irrigation",1;"Surface irrigation",1;"Other irrigation",1}, _xlpm.r, _xlpm.c))))</definedName>
     <definedName name="Common_SourceData.Common_SourceData_FracWETIrrigation_Data">_xlfn.LAMBDA(_xlfn.MAKEARRAY(6, 2, _xlfn.LAMBDA(_xlpm.r,_xlpm.c, INDEX({"Irrigation type ir","FracWET";"Not irrigated",0;"Drip irrigation",0;"Sprinkler irrigation",1;"Surface irrigation",1;"Other irrigation",1}, _xlpm.r, _xlpm.c))))</definedName>
     <definedName name="Common_SourceData.Common_SourceData_FracWETIrrigation_NIRReference">_xlfn.LAMBDA("IPCC 2019 Refinement Volume 4: Chapter 11: N2O Emissions from Managed Soils, and CO2 Emissions from Lime and Urea Application")</definedName>
@@ -178,12 +222,14 @@
     <definedName name="Common_SourceData.Common_SourceData_FracWETIrrigation_Title">_xlfn.LAMBDA("FracWET for irrigation types")</definedName>
     <definedName name="Common_SourceData.Common_SourceData_FracWETIrrigation_Unit">_xlfn.LAMBDA("dimensionless")</definedName>
     <definedName name="Common_SourceData.Common_SourceData_FracWETIrrigation_Variation">_xlfn.LAMBDA("VARIATION FROM SOURCE DATA: Table created based on VEERG text 'Areas are subject to leaching (i.e., in the leaching zone) when... the land is irrigated (except drip irrigation).'")</definedName>
+    <definedName name="Common_SourceData.Common_SourceData_GWP_Data" localSheetId="6">_xlfn.LAMBDA(_xlfn.MAKEARRAY(8, 2, _xlfn.LAMBDA(_xlpm.r,_xlpm.c, INDEX({"Gas","CO2-e factor";"CO2",1;"CH4",28;"N2O",265;"CF4",6630;"C2F6",12200;"SF6",22800;"NF3",17200}, _xlpm.r, _xlpm.c))))</definedName>
     <definedName name="Common_SourceData.Common_SourceData_GWP_Data" localSheetId="4">_xlfn.LAMBDA(_xlfn.MAKEARRAY(8, 2, _xlfn.LAMBDA(_xlpm.r,_xlpm.c, INDEX({"Gas","CO2-e factor";"CO2",1;"CH4",28;"N2O",265;"CF4",6630;"C2F6",12200;"SF6",22800;"NF3",17200}, _xlpm.r, _xlpm.c))))</definedName>
     <definedName name="Common_SourceData.Common_SourceData_GWP_Data">_xlfn.LAMBDA(_xlfn.MAKEARRAY(8, 2, _xlfn.LAMBDA(_xlpm.r,_xlpm.c, INDEX({"Gas","CO2-e factor";"CO2",1;"CH4",28;"N2O",265;"CF4",6630;"C2F6",12200;"SF6",22800;"NF3",17200}, _xlpm.r, _xlpm.c))))</definedName>
     <definedName name="Common_SourceData.Common_SourceData_GWP_Source">_xlfn.LAMBDA("XXXXXXX")</definedName>
     <definedName name="Common_SourceData.Common_SourceData_GWP_Title">_xlfn.LAMBDA("Global warming potential for greenhouse gases")</definedName>
     <definedName name="Common_SourceData.Common_SourceData_GWP_Unit">_xlfn.LAMBDA("factor")</definedName>
     <definedName name="Common_SourceData.Common_SourceData_GWP_Variable">_xlfn.LAMBDA("GWPN2O")</definedName>
+    <definedName name="Common_SourceData.Common_SourceData_LeachingZones_Data" localSheetId="6">_xlfn.LAMBDA(_xlfn.MAKEARRAY(4, 2, _xlfn.LAMBDA(_xlpm.r,_xlpm.c, INDEX({"Leaching Zone","Leaching criteria";"Leaching occurs","Σ(𝑟𝑎𝑖𝑛)&gt;Σ(𝐸𝑇0)+𝑠𝑜𝑖𝑙 𝑤𝑎𝑡𝑒𝑟 ℎ𝑜𝑙𝑑𝑖𝑛𝑔 𝑐𝑎𝑝𝑎𝑐𝑖𝑡𝑦";"Leaching does not occur","Σ(𝑟𝑎𝑖𝑛)≤Σ(𝐸𝑇0)+𝑠𝑜𝑖𝑙 𝑤𝑎𝑡𝑒𝑟 ℎ𝑜𝑙𝑑𝑖𝑛𝑔 𝑐𝑎𝑝𝑎𝑐𝑖𝑡𝑦"}, _xlpm.r, _xlpm.c))))</definedName>
     <definedName name="Common_SourceData.Common_SourceData_LeachingZones_Data" localSheetId="4">_xlfn.LAMBDA(_xlfn.MAKEARRAY(4, 2, _xlfn.LAMBDA(_xlpm.r,_xlpm.c, INDEX({"Leaching Zone","Leaching criteria";"Leaching occurs","Σ(𝑟𝑎𝑖𝑛)&gt;Σ(𝐸𝑇0)+𝑠𝑜𝑖𝑙 𝑤𝑎𝑡𝑒𝑟 ℎ𝑜𝑙𝑑𝑖𝑛𝑔 𝑐𝑎𝑝𝑎𝑐𝑖𝑡𝑦";"Leaching does not occur","Σ(𝑟𝑎𝑖𝑛)≤Σ(𝐸𝑇0)+𝑠𝑜𝑖𝑙 𝑤𝑎𝑡𝑒𝑟 ℎ𝑜𝑙𝑑𝑖𝑛𝑔 𝑐𝑎𝑝𝑎𝑐𝑖𝑡𝑦"}, _xlpm.r, _xlpm.c))))</definedName>
     <definedName name="Common_SourceData.Common_SourceData_LeachingZones_Data">_xlfn.LAMBDA(_xlfn.MAKEARRAY(4, 2, _xlfn.LAMBDA(_xlpm.r,_xlpm.c, INDEX({"Leaching Zone","Leaching criteria";"Leaching occurs","Σ(𝑟𝑎𝑖𝑛)&gt;Σ(𝐸𝑇0)+𝑠𝑜𝑖𝑙 𝑤𝑎𝑡𝑒𝑟 ℎ𝑜𝑙𝑑𝑖𝑛𝑔 𝑐𝑎𝑝𝑎𝑐𝑖𝑡𝑦";"Leaching does not occur","Σ(𝑟𝑎𝑖𝑛)≤Σ(𝐸𝑇0)+𝑠𝑜𝑖𝑙 𝑤𝑎𝑡𝑒𝑟 ℎ𝑜𝑙𝑑𝑖𝑛𝑔 𝑐𝑎𝑝𝑎𝑐𝑖𝑡𝑦"}, _xlpm.r, _xlpm.c))))</definedName>
     <definedName name="Common_SourceData.Common_SourceData_LeachingZones_Source">_xlfn.LAMBDA("VEERG 2026: Table 1.3: Climate and Rainfall zone classifications and definitions")</definedName>
@@ -191,12 +237,14 @@
     <definedName name="Common_SourceData.Common_SourceData_LeachingZones_Unit">_xlfn.LAMBDA("")</definedName>
     <definedName name="Common_SourceData.Common_SourceData_LeachingZones_Variable">_xlfn.LAMBDA("")</definedName>
     <definedName name="Common_SourceData.Common_SourceData_LeachingZones_Variation">_xlfn.LAMBDA("")</definedName>
+    <definedName name="Common_SourceData.Common_SourceData_MCFTemperatureZone_Data" localSheetId="6">_xlfn.LAMBDA(_xlfn.MAKEARRAY(22, 16, _xlfn.LAMBDA(_xlpm.r,_xlpm.c, INDEX({"Temperature zone","MAT (ºC)","Uncovered anerobic lagoon","Covered lagoon","Liquid Slurry (without natural crust)","Daily spread (b)","Composting (passive windrow)","Solid Storage","Pit Storage &lt;1 month","Deep Litter","Poultry Manure (with/without litter)","","Direct processing into pelletized fertiliser","Direct application to soil","Pasture, Range and Paddock (c)(d)","MAT raw";"Cool","≤10",0.66,0.1,0.1,0.001,0.005,0.02,0.03,0.04,0.015,0.015,0,0,0.0047,10;"Cool",11,0.68,0.1,0.11,0.001,0.005,0.02,0.03,0.04,0.015,0.015,0,0,0.0047,11;"Cool",12,0.7,0.1,0.13,0.001,0.005,0.02,0.03,0.04,0.015,0.015,0,0,0.0047,12;"Cool",13,0.71,0.1,0.14,0.001,0.005,0.02,0.03,0.04,0.015,0.015,0,0,0.0047,13;"Cool",14,0.73,0.1,0.15,0.001,0.005,0.02,0.03,0.04,0.015,0.015,0,0,0.0047,14;"Temperate",15,0.74,0.1,0.17,0.005,0.01,0.02,0.03,0.04,0.015,0.015,0,0,0.0047,15;"Temperate",16,0.75,0.1,0.18,0.005,0.01,0.02,0.03,0.04,0.015,0.015,0,0,0.0047,16;"Temperate",17,0.76,0.1,0.2,0.005,0.01,0.02,0.03,0.04,0.015,0.015,0,0,0.0047,17;"Temperate",18,0.77,0.1,0.22,0.005,0.01,0.02,0.03,0.04,0.015,0.015,0,0,0.0047,18;"Temperate",19,0.77,0.1,0.24,0.005,0.01,0.02,0.03,0.04,0.015,0.015,0,0,0.0047,19;"Temperate",20,0.78,0.1,0.26,0.005,0.01,0.02,0.03,0.04,0.015,0.015,0,0,0.0047,20;"Temperate",21,0.78,0.1,0.29,0.005,0.01,0.02,0.03,0.04,0.015,0.015,0,0,0.0047,21;"Temperate",22,0.78,0.1,0.31,0.005,0.01,0.02,0.03,0.04,0.015,0.015,0,0,0.0047,22;"Temperate",23,0.79,0.1,0.34,0.005,0.01,0.02,0.03,0.04,0.015,0.015,0,0,0.0047,23;"Temperate",24,0.79,0.1,0.37,0.005,0.01,0.02,0.03,0.04,0.015,0.015,0,0,0.0047,24;"Temperate",25,0.79,0.1,0.41,0.005,0.01,0.02,0.03,0.04,0.015,0.015,0,0,0.0047,25;"Warm",26,0.79,0.1,0.44,0.01,0.015,0.02,0.03,0.04,0.015,0.015,0,0,0.0047,26;"Warm",27,0.8,0.1,0.48,0.01,0.015,0.02,0.03,0.04,0.015,0.015,0,0,0.0047,27;"Warm","≥28",0.8,0.1,0.5,0.01,0.015,0.02,0.03,0.04,0.015,0.015,0,0,0.0047,28;"","","Anaerobic lagoon","Digester / covered lagoons","Liquid systems","Daily spread","Composting (passive windrow)","Solid storage","Pit storage","Deep litter","Poultry manure with bedding","Poultry manure without bedding","Direct processing","Direct application","Pasture range and paddock","MAT raw"}, _xlpm.r, _xlpm.c))))</definedName>
     <definedName name="Common_SourceData.Common_SourceData_MCFTemperatureZone_Data" localSheetId="4">_xlfn.LAMBDA(_xlfn.MAKEARRAY(22, 16, _xlfn.LAMBDA(_xlpm.r,_xlpm.c, INDEX({"Temperature zone","MAT (ºC)","Uncovered anerobic lagoon","Covered lagoon","Liquid Slurry (without natural crust)","Daily spread (b)","Composting (passive windrow)","Solid Storage","Pit Storage &lt;1 month","Deep Litter","Poultry Manure (with/without litter)","","Direct processing into pelletized fertiliser","Direct application to soil","Pasture, Range and Paddock (c)(d)","MAT raw";"Cool","≤10",0.66,0.1,0.1,0.001,0.005,0.02,0.03,0.04,0.015,0.015,0,0,0.0047,10;"Cool",11,0.68,0.1,0.11,0.001,0.005,0.02,0.03,0.04,0.015,0.015,0,0,0.0047,11;"Cool",12,0.7,0.1,0.13,0.001,0.005,0.02,0.03,0.04,0.015,0.015,0,0,0.0047,12;"Cool",13,0.71,0.1,0.14,0.001,0.005,0.02,0.03,0.04,0.015,0.015,0,0,0.0047,13;"Cool",14,0.73,0.1,0.15,0.001,0.005,0.02,0.03,0.04,0.015,0.015,0,0,0.0047,14;"Temperate",15,0.74,0.1,0.17,0.005,0.01,0.02,0.03,0.04,0.015,0.015,0,0,0.0047,15;"Temperate",16,0.75,0.1,0.18,0.005,0.01,0.02,0.03,0.04,0.015,0.015,0,0,0.0047,16;"Temperate",17,0.76,0.1,0.2,0.005,0.01,0.02,0.03,0.04,0.015,0.015,0,0,0.0047,17;"Temperate",18,0.77,0.1,0.22,0.005,0.01,0.02,0.03,0.04,0.015,0.015,0,0,0.0047,18;"Temperate",19,0.77,0.1,0.24,0.005,0.01,0.02,0.03,0.04,0.015,0.015,0,0,0.0047,19;"Temperate",20,0.78,0.1,0.26,0.005,0.01,0.02,0.03,0.04,0.015,0.015,0,0,0.0047,20;"Temperate",21,0.78,0.1,0.29,0.005,0.01,0.02,0.03,0.04,0.015,0.015,0,0,0.0047,21;"Temperate",22,0.78,0.1,0.31,0.005,0.01,0.02,0.03,0.04,0.015,0.015,0,0,0.0047,22;"Temperate",23,0.79,0.1,0.34,0.005,0.01,0.02,0.03,0.04,0.015,0.015,0,0,0.0047,23;"Temperate",24,0.79,0.1,0.37,0.005,0.01,0.02,0.03,0.04,0.015,0.015,0,0,0.0047,24;"Temperate",25,0.79,0.1,0.41,0.005,0.01,0.02,0.03,0.04,0.015,0.015,0,0,0.0047,25;"Warm",26,0.79,0.1,0.44,0.01,0.015,0.02,0.03,0.04,0.015,0.015,0,0,0.0047,26;"Warm",27,0.8,0.1,0.48,0.01,0.015,0.02,0.03,0.04,0.015,0.015,0,0,0.0047,27;"Warm","≥28",0.8,0.1,0.5,0.01,0.015,0.02,0.03,0.04,0.015,0.015,0,0,0.0047,28;"","","Anaerobic lagoon","Digester / covered lagoons","Liquid systems","Daily spread","Composting (passive windrow)","Solid storage","Pit storage","Deep litter","Poultry manure with bedding","Poultry manure without bedding","Direct processing","Direct application","Pasture range and paddock","MAT raw"}, _xlpm.r, _xlpm.c))))</definedName>
     <definedName name="Common_SourceData.Common_SourceData_MCFTemperatureZone_Data">_xlfn.LAMBDA(_xlfn.MAKEARRAY(22, 16, _xlfn.LAMBDA(_xlpm.r,_xlpm.c, INDEX({"Temperature zone","MAT (ºC)","Uncovered anerobic lagoon","Covered lagoon","Liquid Slurry (without natural crust)","Daily spread (b)","Composting (passive windrow)","Solid Storage","Pit Storage &lt;1 month","Deep Litter","Poultry Manure (with/without litter)","","Direct processing into pelletized fertiliser","Direct application to soil","Pasture, Range and Paddock (c)(d)","MAT raw";"Cool","≤10",0.66,0.1,0.1,0.001,0.005,0.02,0.03,0.04,0.015,0.015,0,0,0.0047,10;"Cool",11,0.68,0.1,0.11,0.001,0.005,0.02,0.03,0.04,0.015,0.015,0,0,0.0047,11;"Cool",12,0.7,0.1,0.13,0.001,0.005,0.02,0.03,0.04,0.015,0.015,0,0,0.0047,12;"Cool",13,0.71,0.1,0.14,0.001,0.005,0.02,0.03,0.04,0.015,0.015,0,0,0.0047,13;"Cool",14,0.73,0.1,0.15,0.001,0.005,0.02,0.03,0.04,0.015,0.015,0,0,0.0047,14;"Temperate",15,0.74,0.1,0.17,0.005,0.01,0.02,0.03,0.04,0.015,0.015,0,0,0.0047,15;"Temperate",16,0.75,0.1,0.18,0.005,0.01,0.02,0.03,0.04,0.015,0.015,0,0,0.0047,16;"Temperate",17,0.76,0.1,0.2,0.005,0.01,0.02,0.03,0.04,0.015,0.015,0,0,0.0047,17;"Temperate",18,0.77,0.1,0.22,0.005,0.01,0.02,0.03,0.04,0.015,0.015,0,0,0.0047,18;"Temperate",19,0.77,0.1,0.24,0.005,0.01,0.02,0.03,0.04,0.015,0.015,0,0,0.0047,19;"Temperate",20,0.78,0.1,0.26,0.005,0.01,0.02,0.03,0.04,0.015,0.015,0,0,0.0047,20;"Temperate",21,0.78,0.1,0.29,0.005,0.01,0.02,0.03,0.04,0.015,0.015,0,0,0.0047,21;"Temperate",22,0.78,0.1,0.31,0.005,0.01,0.02,0.03,0.04,0.015,0.015,0,0,0.0047,22;"Temperate",23,0.79,0.1,0.34,0.005,0.01,0.02,0.03,0.04,0.015,0.015,0,0,0.0047,23;"Temperate",24,0.79,0.1,0.37,0.005,0.01,0.02,0.03,0.04,0.015,0.015,0,0,0.0047,24;"Temperate",25,0.79,0.1,0.41,0.005,0.01,0.02,0.03,0.04,0.015,0.015,0,0,0.0047,25;"Warm",26,0.79,0.1,0.44,0.01,0.015,0.02,0.03,0.04,0.015,0.015,0,0,0.0047,26;"Warm",27,0.8,0.1,0.48,0.01,0.015,0.02,0.03,0.04,0.015,0.015,0,0,0.0047,27;"Warm","≥28",0.8,0.1,0.5,0.01,0.015,0.02,0.03,0.04,0.015,0.015,0,0,0.0047,28;"","","Anaerobic lagoon","Digester / covered lagoons","Liquid systems","Daily spread","Composting (passive windrow)","Solid storage","Pit storage","Deep litter","Poultry manure with bedding","Poultry manure without bedding","Direct processing","Direct application","Pasture range and paddock","MAT raw"}, _xlpm.r, _xlpm.c))))</definedName>
     <definedName name="Common_SourceData.Common_SourceData_MCFTemperatureZone_Source">_xlfn.LAMBDA("VEERG 2026: Table A.1.8.1")</definedName>
     <definedName name="Common_SourceData.Common_SourceData_MCFTemperatureZone_Title">_xlfn.LAMBDA("Manure Management – Methane conversion factor per temperature zone (fraction) (MCFim)")</definedName>
     <definedName name="Common_SourceData.Common_SourceData_MCFTemperatureZone_Unit">_xlfn.LAMBDA("fraction")</definedName>
     <definedName name="Common_SourceData.Common_SourceData_MCFTemperatureZone_Variation">_xlfn.LAMBDA("VARIATION FROM SOURCE: Added row of NIR MMA definitions to aid lookup. Duplicated 'Poultry with and without litter' column with separate NIR definitions to aid lookup. Added 'MAT raw' column to allow lookup of numbers.")</definedName>
+    <definedName name="Common_SourceData.Common_SourceData_MonthsToSeasons_Data" localSheetId="6">_xlfn.LAMBDA(_xlfn.MAKEARRAY(13, 2, _xlfn.LAMBDA(_xlpm.r,_xlpm.c, INDEX({"Month","Season";"January","Summer";"February","Summer";"March","Autumn";"April","Autumn";"May","Autumn";"June","Winter";"July","Winter";"August","Winter";"September","Spring";"October","Spring";"November","Spring";"December","Summer"}, _xlpm.r, _xlpm.c))))</definedName>
     <definedName name="Common_SourceData.Common_SourceData_MonthsToSeasons_Data" localSheetId="4">_xlfn.LAMBDA(_xlfn.MAKEARRAY(13, 2, _xlfn.LAMBDA(_xlpm.r,_xlpm.c, INDEX({"Month","Season";"January","Summer";"February","Summer";"March","Autumn";"April","Autumn";"May","Autumn";"June","Winter";"July","Winter";"August","Winter";"September","Spring";"October","Spring";"November","Spring";"December","Summer"}, _xlpm.r, _xlpm.c))))</definedName>
     <definedName name="Common_SourceData.Common_SourceData_MonthsToSeasons_Data">_xlfn.LAMBDA(_xlfn.MAKEARRAY(13, 2, _xlfn.LAMBDA(_xlpm.r,_xlpm.c, INDEX({"Month","Season";"January","Summer";"February","Summer";"March","Autumn";"April","Autumn";"May","Autumn";"June","Winter";"July","Winter";"August","Winter";"September","Spring";"October","Spring";"November","Spring";"December","Summer"}, _xlpm.r, _xlpm.c))))</definedName>
     <definedName name="Common_SourceData.Common_SourceData_MonthsToSeasons_NIRReference">_xlfn.LAMBDA("")</definedName>
@@ -204,6 +252,7 @@
     <definedName name="Common_SourceData.Common_SourceData_MonthsToSeasons_Title">_xlfn.LAMBDA("Months to Seasons Mapping")</definedName>
     <definedName name="Common_SourceData.Common_SourceData_MonthsToSeasons_Unit">_xlfn.LAMBDA("")</definedName>
     <definedName name="Common_SourceData.Common_SourceData_MonthsToSeasons_Variation">_xlfn.LAMBDA("")</definedName>
+    <definedName name="Common_SourceData.Common_SourceData_RainfallZones_Data" localSheetId="6">_xlfn.LAMBDA(_xlfn.MAKEARRAY(3, 4, _xlfn.LAMBDA(_xlpm.r,_xlpm.c, INDEX({"Rainfall Zone","Annual rainfall","Rainfall min","Rainfall max";"High rainfall","Annual rainfall &gt; 600mm",600.001,999999;"Low rainfall","Annual rainfall ≤ 600mm",-999999,600}, _xlpm.r, _xlpm.c))))</definedName>
     <definedName name="Common_SourceData.Common_SourceData_RainfallZones_Data" localSheetId="4">_xlfn.LAMBDA(_xlfn.MAKEARRAY(3, 4, _xlfn.LAMBDA(_xlpm.r,_xlpm.c, INDEX({"Rainfall Zone","Annual rainfall","Rainfall min","Rainfall max";"High rainfall","Annual rainfall &gt; 600mm",600.001,999999;"Low rainfall","Annual rainfall ≤ 600mm",-999999,600}, _xlpm.r, _xlpm.c))))</definedName>
     <definedName name="Common_SourceData.Common_SourceData_RainfallZones_Data">_xlfn.LAMBDA(_xlfn.MAKEARRAY(3, 4, _xlfn.LAMBDA(_xlpm.r,_xlpm.c, INDEX({"Rainfall Zone","Annual rainfall","Rainfall min","Rainfall max";"High rainfall","Annual rainfall &gt; 600mm",600.001,999999;"Low rainfall","Annual rainfall ≤ 600mm",-999999,600}, _xlpm.r, _xlpm.c))))</definedName>
     <definedName name="Common_SourceData.Common_SourceData_RainfallZones_Source">_xlfn.LAMBDA("VEERG 2026: Table 1.3: Climate and Rainfall zone classifications and definitions")</definedName>
@@ -211,6 +260,7 @@
     <definedName name="Common_SourceData.Common_SourceData_RainfallZones_Unit">_xlfn.LAMBDA("")</definedName>
     <definedName name="Common_SourceData.Common_SourceData_RainfallZones_Variable">_xlfn.LAMBDA("")</definedName>
     <definedName name="Common_SourceData.Common_SourceData_RainfallZones_Variation">_xlfn.LAMBDA("VARIATION OF SOURCE DATA: Added extra Rainfall min and Rainfall max columns to calculate zone from real rainfall data.")</definedName>
+    <definedName name="Common_SourceData.Common_SourceData_TemperatureZones_Data" localSheetId="6">_xlfn.LAMBDA(_xlfn.MAKEARRAY(4, 4, _xlfn.LAMBDA(_xlpm.r,_xlpm.c, INDEX({"Temperature Zone","Median Annual Temperature (MAT)","Min MAT","Max MAT";"Warm","≥ 26 C",26,999999;"Temperate","15 - 25 C",15,25.999;"Cool","≤ 14 C",-999999,14.999}, _xlpm.r, _xlpm.c))))</definedName>
     <definedName name="Common_SourceData.Common_SourceData_TemperatureZones_Data" localSheetId="4">_xlfn.LAMBDA(_xlfn.MAKEARRAY(4, 4, _xlfn.LAMBDA(_xlpm.r,_xlpm.c, INDEX({"Temperature Zone","Median Annual Temperature (MAT)","Min MAT","Max MAT";"Warm","≥ 26 C",26,999999;"Temperate","15 - 25 C",15,25.999;"Cool","≤ 14 C",-999999,14.999}, _xlpm.r, _xlpm.c))))</definedName>
     <definedName name="Common_SourceData.Common_SourceData_TemperatureZones_Data">_xlfn.LAMBDA(_xlfn.MAKEARRAY(4, 4, _xlfn.LAMBDA(_xlpm.r,_xlpm.c, INDEX({"Temperature Zone","Median Annual Temperature (MAT)","Min MAT","Max MAT";"Warm","≥ 26 C",26,999999;"Temperate","15 - 25 C",15,25.999;"Cool","≤ 14 C",-999999,14.999}, _xlpm.r, _xlpm.c))))</definedName>
     <definedName name="Common_SourceData.Common_SourceData_TemperatureZones_Source">_xlfn.LAMBDA("VEERG 2026: Table 1.3: Climate and Rainfall zone classifications and definitions")</definedName>
@@ -218,49 +268,89 @@
     <definedName name="Common_SourceData.Common_SourceData_TemperatureZones_Unit">_xlfn.LAMBDA("")</definedName>
     <definedName name="Common_SourceData.Common_SourceData_TemperatureZones_Variable">_xlfn.LAMBDA("")</definedName>
     <definedName name="Common_SourceData.Common_SourceData_TemperatureZones_Variation">_xlfn.LAMBDA("VARIATION OF SOURCE DATA: Added extra MAT min and MAT max columns to calculate zone from real temperature data.")</definedName>
+    <definedName name="Common_SourceData.Common_SourceData_WASA4Areas_Data" localSheetId="6">_xlfn.LAMBDA(_xlfn.MAKEARRAY(11, 1, _xlfn.LAMBDA(_xlpm.r,_xlpm.c, INDEX({"SA 4 Name";"Bunbury";"Mandurah";"Perth - Inner";"Perth - North East";"Perth - North West";"Perth - South East";"Perth - South West";"Western Australia - Wheat Belt";"Western Australia - Outback (North)";"Western Australia - Outback (South)"}, _xlpm.r, _xlpm.c))))</definedName>
     <definedName name="Common_SourceData.Common_SourceData_WASA4Areas_Data" localSheetId="4">_xlfn.LAMBDA(_xlfn.MAKEARRAY(11, 1, _xlfn.LAMBDA(_xlpm.r,_xlpm.c, INDEX({"SA 4 Name";"Bunbury";"Mandurah";"Perth - Inner";"Perth - North East";"Perth - North West";"Perth - South East";"Perth - South West";"Western Australia - Wheat Belt";"Western Australia - Outback (North)";"Western Australia - Outback (South)"}, _xlpm.r, _xlpm.c))))</definedName>
     <definedName name="Common_SourceData.Common_SourceData_WASA4Areas_Data">_xlfn.LAMBDA(_xlfn.MAKEARRAY(11, 1, _xlfn.LAMBDA(_xlpm.r,_xlpm.c, INDEX({"SA 4 Name";"Bunbury";"Mandurah";"Perth - Inner";"Perth - North East";"Perth - North West";"Perth - South East";"Perth - South West";"Western Australia - Wheat Belt";"Western Australia - Outback (North)";"Western Australia - Outback (South)"}, _xlpm.r, _xlpm.c))))</definedName>
     <definedName name="Common_SourceData.Common_SourceData_WASA4Areas_Source">_xlfn.LAMBDA("Australian Bureau of Statistics (ABS) - Statistical Areas Level 2 - 2021 - Shapefile")</definedName>
     <definedName name="Common_SourceData.Common_SourceData_WASA4Areas_Title">_xlfn.LAMBDA("ABS Statistcal Areas Level 4 - Western Australia")</definedName>
     <definedName name="Common_SourceData.Common_SourceData_WASA4Areas_Unit">_xlfn.LAMBDA("")</definedName>
     <definedName name="Common_SourceData.Common_SourceData_WASA4Areas_Variable">_xlfn.LAMBDA("")</definedName>
+    <definedName name="Common_SourceData.Common_SourceData_WetAndDryZones_Data" localSheetId="6">_xlfn.LAMBDA(_xlfn.MAKEARRAY(15, 2, _xlfn.LAMBDA(_xlpm.r,_xlpm.c, INDEX({"Climate Zone","Wet or Dry Zone";"Tropical montane","Wet climate zone";"Tropical wet","Wet climate zone";"Tropical moist","Wet climate zone";"Tropical dry","Dry climate zone";"Warm temperate moist","Wet climate zone";"Warm temperate dry","Dry climate zone";"Cool temperate moist","Wet climate zone";"Cool temperate dry","Dry climate zone";"Warm temperate moist - low frost","Wet climate zone";"Warm temperate dry - low frost","Dry climate zone";"Warm temperate moist - high temp","Wet climate zone";"Warm temperate dry - high temp","Dry climate zone";"Cool temperate moist - low frost","Wet climate zone";"Cool temperate dry - low frost","Dry climate zone"}, _xlpm.r, _xlpm.c))))</definedName>
     <definedName name="Common_SourceData.Common_SourceData_WetAndDryZones_Data" localSheetId="4">_xlfn.LAMBDA(_xlfn.MAKEARRAY(15, 2, _xlfn.LAMBDA(_xlpm.r,_xlpm.c, INDEX({"Climate Zone","Wet or Dry Zone";"Tropical montane","Wet climate zone";"Tropical wet","Wet climate zone";"Tropical moist","Wet climate zone";"Tropical dry","Dry climate zone";"Warm temperate moist","Wet climate zone";"Warm temperate dry","Dry climate zone";"Cool temperate moist","Wet climate zone";"Cool temperate dry","Dry climate zone";"Warm temperate moist - low frost","Wet climate zone";"Warm temperate dry - low frost","Dry climate zone";"Warm temperate moist - high temp","Wet climate zone";"Warm temperate dry - high temp","Dry climate zone";"Cool temperate moist - low frost","Wet climate zone";"Cool temperate dry - low frost","Dry climate zone"}, _xlpm.r, _xlpm.c))))</definedName>
     <definedName name="Common_SourceData.Common_SourceData_WetAndDryZones_Data">_xlfn.LAMBDA(_xlfn.MAKEARRAY(15, 2, _xlfn.LAMBDA(_xlpm.r,_xlpm.c, INDEX({"Climate Zone","Wet or Dry Zone";"Tropical montane","Wet climate zone";"Tropical wet","Wet climate zone";"Tropical moist","Wet climate zone";"Tropical dry","Dry climate zone";"Warm temperate moist","Wet climate zone";"Warm temperate dry","Dry climate zone";"Cool temperate moist","Wet climate zone";"Cool temperate dry","Dry climate zone";"Warm temperate moist - low frost","Wet climate zone";"Warm temperate dry - low frost","Dry climate zone";"Warm temperate moist - high temp","Wet climate zone";"Warm temperate dry - high temp","Dry climate zone";"Cool temperate moist - low frost","Wet climate zone";"Cool temperate dry - low frost","Dry climate zone"}, _xlpm.r, _xlpm.c))))</definedName>
     <definedName name="Common_SourceData.Common_SourceData_WetAndDryZones_Source">_xlfn.LAMBDA("VEERG 2026: Table 1.2: Translating climate zones to wet and dry zones")</definedName>
     <definedName name="Common_SourceData.Common_SourceData_WetAndDryZones_Title">_xlfn.LAMBDA("VEERG Australian wet and dry zones")</definedName>
     <definedName name="Common_SourceData.Common_SourceData_WetAndDryZones_Unit">_xlfn.LAMBDA("")</definedName>
     <definedName name="Common_SourceData.Common_SourceData_WetAndDryZones_Variable">_xlfn.LAMBDA("")</definedName>
+    <definedName name="Common_SourceData.Common_SourceData_WetAndDryZones_Variation" localSheetId="6">_xlfn.LAMBDA(_xlfn.MAKEARRAY(3, 1, _xlfn.LAMBDA(_xlpm.r,_xlpm.c, INDEX({"VARIATION OF SOURCE DATA:";"Added warm / cool temperate moist / dry - low frost and high temp classes to accommodate climate scenarios excluded by VEERG criteria.";"Fixed typo - Changed 'Fry' to 'Dry'."}, _xlpm.r, _xlpm.c))))</definedName>
     <definedName name="Common_SourceData.Common_SourceData_WetAndDryZones_Variation" localSheetId="4">_xlfn.LAMBDA(_xlfn.MAKEARRAY(3, 1, _xlfn.LAMBDA(_xlpm.r,_xlpm.c, INDEX({"VARIATION OF SOURCE DATA:";"Added warm / cool temperate moist / dry - low frost and high temp classes to accommodate climate scenarios excluded by VEERG criteria.";"Fixed typo - Changed 'Fry' to 'Dry'."}, _xlpm.r, _xlpm.c))))</definedName>
     <definedName name="Common_SourceData.Common_SourceData_WetAndDryZones_Variation">_xlfn.LAMBDA(_xlfn.MAKEARRAY(3, 1, _xlfn.LAMBDA(_xlpm.r,_xlpm.c, INDEX({"VARIATION OF SOURCE DATA:";"Added warm / cool temperate moist / dry - low frost and high temp classes to accommodate climate scenarios excluded by VEERG criteria.";"Fixed typo - Changed 'Fry' to 'Dry'."}, _xlpm.r, _xlpm.c))))</definedName>
+    <definedName name="CommonLivestock_InputFunctions.AverageLiveweightEndOfMonth">_xlfn.LAMBDA(_xlpm.Month,_xlpm.LivestockClass,_xlpm.HeadAtStart,_xlpm.LiveweightAtStart,_xlpm.LiveweightGain, [0]!CommonLivestock_InputFunctions.LivestockMovement_ProportionalAverageLiveweightAddedDuringMonth(_xlpm.Month, _xlpm.LivestockClass, _xlpm.HeadAtStart) + [0]!CommonLivestock_InputFunctions.LivestockMovement_ProportionalAverageLiveweightRemainingAtEndOfMonth(_xlpm.Month, _xlpm.LivestockClass, _xlpm.HeadAtStart, _xlpm.LiveweightAtStart, _xlpm.LiveweightGain))</definedName>
+    <definedName name="CommonLivestock_InputFunctions.LivestockMovement_AverageLiveweightAddedDuringMonth">_xlfn.LAMBDA(_xlpm.Month,_xlpm.LivestockClass, IFERROR([0]!CommonLivestock_InputFunctions.LivestockMovement_TotalLiveweightAddedDuringMonth(_xlpm.Month, _xlpm.LivestockClass) / [0]!CommonLivestock_InputFunctions.LivestockMovement_HeadAddedDuringMonth(_xlpm.Month, _xlpm.LivestockClass), 0))</definedName>
+    <definedName name="CommonLivestock_InputFunctions.LivestockMovement_GetMovementLiveweightGain">_xlfn.LAMBDA(_xlpm.LivestockClass,_xlpm.MovementDate, _xlfn.LET(_xlpm.ym, TEXT(_xlpm.MovementDate, "yyyymm"), IFERROR(INDEX(_xlfn._xlws.FILTER(#REF!, (TEXT(#REF!, "yyyymm") = _xlpm.ym) * (#REF! = _xlpm.LivestockClass)), 1), "")))</definedName>
+    <definedName name="CommonLivestock_InputFunctions.LivestockMovement_HeadAddedDuringMonth">_xlfn.LAMBDA(_xlpm.Month,_xlpm.LivestockClass, IFERROR(SUM(_xlfn._xlws.FILTER(#REF!, (#REF! &gt;= EOMONTH(_xlpm.Month, -1) + 1) * (#REF! &lt;= EOMONTH(_xlpm.Month, 0)) * (#REF! = _xlpm.LivestockClass))), 0))</definedName>
+    <definedName name="CommonLivestock_InputFunctions.LivestockMovement_HeadAtEndOfMonth">_xlfn.LAMBDA(_xlpm.HeadAtStart,_xlpm.Month,_xlpm.LivestockClass, _xlpm.HeadAtStart + [0]!CommonLivestock_InputFunctions.LivestockMovement_HeadAddedDuringMonth(_xlpm.Month, _xlpm.LivestockClass) - [0]!CommonLivestock_InputFunctions.LivestockMovement_HeadLostDuringMonth(_xlpm.Month, _xlpm.LivestockClass))</definedName>
+    <definedName name="CommonLivestock_InputFunctions.LivestockMovement_HeadLostDuringMonth">_xlfn.LAMBDA(_xlpm.Month,_xlpm.LivestockClass, IFERROR(SUM(_xlfn._xlws.FILTER(#REF!, (#REF! &gt;= EOMONTH(_xlpm.Month, -1) + 1) * (#REF! &lt;= EOMONTH(_xlpm.Month, 0)) * (#REF! = _xlpm.LivestockClass))), 0))</definedName>
+    <definedName name="CommonLivestock_InputFunctions.LivestockMovement_HeadRemainingAtMonthEnd">_xlfn.LAMBDA(_xlpm.Month,_xlpm.LivestockClass,_xlpm.HeadAtStartOfMonth, MAX(_xlpm.HeadAtStartOfMonth - [0]!CommonLivestock_InputFunctions.LivestockMovement_HeadLostDuringMonth(_xlpm.Month, _xlpm.LivestockClass), 0))</definedName>
+    <definedName name="CommonLivestock_InputFunctions.LivestockMovement_LiveweightAddedDuringMonth">_xlfn.LAMBDA(_xlpm.LivestockClass,_xlpm.MovementDate,_xlpm.WeightAtMovementDate,_xlpm.Head, IFERROR(_xlpm.Head * (_xlpm.WeightAtMovementDate + [0]!CommonLivestock_InputFunctions.LivestockMovement_LiveweightGrownDuringMonthPerHead(_xlpm.LivestockClass, _xlpm.MovementDate)), 0))</definedName>
+    <definedName name="CommonLivestock_InputFunctions.LivestockMovement_LiveweightGrownDuringMonthPerHead">_xlfn.LAMBDA(_xlpm.LivestockClass,_xlpm.MovementDate, IFERROR([0]!CommonLivestock_InputFunctions.LivestockMovement_GetMovementLiveweightGain(_xlpm.LivestockClass, _xlpm.MovementDate) * CommonLivestock_InputFunctions.LivestockMovement_DaysMovementToMonthEnd(_xlpm.MovementDate), 0))</definedName>
+    <definedName name="CommonLivestock_InputFunctions.LivestockMovement_LiveweightGrownFromMonthStartPerHead">_xlfn.LAMBDA(_xlpm.LivestockClass,_xlpm.Month, [0]!CommonLivestock_InputFunctions.LivestockMovement_LiveweightGrownDuringMonthPerHead(_xlpm.LivestockClass, EOMONTH(_xlpm.Month, -1) + 1))</definedName>
+    <definedName name="CommonLivestock_InputFunctions.LivestockMovement_LiveweightGrownFromMonthStartTotal">_xlfn.LAMBDA(_xlpm.LivestockClass,_xlpm.Month,_xlpm.HeadAtStartOfMonth, [0]!CommonLivestock_InputFunctions.LivestockMovement_HeadRemainingAtMonthEnd(_xlpm.Month, _xlpm.LivestockClass, _xlpm.HeadAtStartOfMonth) * [0]!CommonLivestock_InputFunctions.LivestockMovement_LiveweightGrownFromMonthStartPerHead(_xlpm.LivestockClass, _xlpm.Month))</definedName>
+    <definedName name="CommonLivestock_InputFunctions.LivestockMovement_LiveweightGrownFromMovementDateTotal">_xlfn.LAMBDA(_xlpm.LivestockClass,_xlpm.MovementDate,_xlpm.Head, [0]!CommonLivestock_InputFunctions.LivestockMovement_LiveweightGrownDuringMonthPerHead(_xlpm.LivestockClass, _xlpm.MovementDate) * _xlpm.Head)</definedName>
+    <definedName name="CommonLivestock_InputFunctions.LivestockMovement_ProportionalAverageLiveweightAddedDuringMonth">_xlfn.LAMBDA(_xlpm.Month,_xlpm.LivestockClass,_xlpm.HeadAtStart, [0]!CommonLivestock_InputFunctions.LivestockMovement_ProportionHeadAddedDuringMonth(_xlpm.Month, _xlpm.LivestockClass, _xlpm.HeadAtStart) * [0]!CommonLivestock_InputFunctions.LivestockMovement_AverageLiveweightAddedDuringMonth(_xlpm.Month, _xlpm.LivestockClass))</definedName>
+    <definedName name="CommonLivestock_InputFunctions.LivestockMovement_ProportionalAverageLiveweightRemainingAtEndOfMonth">_xlfn.LAMBDA(_xlpm.Month,_xlpm.LivestockClass,_xlpm.HeadAtStart,_xlpm.LiveweightAtStart,_xlpm.LiveweightGain, [0]!CommonLivestock_InputFunctions.LivestockMovement_ProportionHeadRemainingAtEndOfMonth(_xlpm.Month, _xlpm.LivestockClass, _xlpm.HeadAtStart) * CommonLivestock_InputFunctions.LivestockMovement_AverageLiveweightRemainingHead(_xlpm.Month, _xlpm.LiveweightAtStart, _xlpm.LiveweightGain))</definedName>
+    <definedName name="CommonLivestock_InputFunctions.LivestockMovement_ProportionHeadAddedDuringMonth">_xlfn.LAMBDA(_xlpm.Month,_xlpm.LivestockClass,_xlpm.HeadAtStart, IFERROR(MIN(1, [0]!CommonLivestock_InputFunctions.LivestockMovement_HeadAddedDuringMonth(_xlpm.Month, _xlpm.LivestockClass) / [0]!CommonLivestock_InputFunctions.LivestockMovement_HeadAtEndOfMonth(_xlpm.HeadAtStart, _xlpm.Month, _xlpm.LivestockClass)), 0))</definedName>
+    <definedName name="CommonLivestock_InputFunctions.LivestockMovement_ProportionHeadRemainingAtEndOfMonth">_xlfn.LAMBDA(_xlpm.Month,_xlpm.LivestockClass,_xlpm.HeadAtStart, IFERROR(MIN(1, [0]!CommonLivestock_InputFunctions.LivestockMovement_HeadRemainingAtMonthEnd(_xlpm.Month, _xlpm.LivestockClass, _xlpm.HeadAtStart) / [0]!CommonLivestock_InputFunctions.LivestockMovement_HeadAtEndOfMonth(_xlpm.HeadAtStart, _xlpm.Month, _xlpm.LivestockClass)), 0))</definedName>
+    <definedName name="CommonLivestock_InputFunctions.LivestockMovement_TotalLiveweightAddedDuringMonth">_xlfn.LAMBDA(_xlpm.Month,_xlpm.LivestockClass, IFERROR(SUM(_xlfn._xlws.FILTER(#REF!, (#REF! &gt;= EOMONTH(_xlpm.Month, -1) + 1) * (#REF! &lt;= EOMONTH(_xlpm.Month, 0)) * (#REF! = _xlpm.LivestockClass))), 0))</definedName>
+    <definedName name="CommonLivestock_InputFunctions.LivestockMovement_TotalLiveweightGrownDuringMonth">_xlfn.LAMBDA(_xlpm.Month,_xlpm.LivestockClass, IFERROR(SUM(_xlfn._xlws.FILTER(#REF!, (#REF! &gt;= EOMONTH(_xlpm.Month, -1) + 1) * (#REF! &lt;= EOMONTH(_xlpm.Month, 0)) * (#REF! = _xlpm.LivestockClass))), 0))</definedName>
+    <definedName name="CommonLivestock_InputFunctions.LivestockMovement_TotalLiveweightGrownDuringMonthAddedAndRemaining">_xlfn.LAMBDA(_xlpm.Month,_xlpm.LivestockClass,_xlpm.HeadAtStart, [0]!CommonLivestock_InputFunctions.LivestockMovement_LiveweightGrownFromMonthStartTotal(_xlpm.LivestockClass, _xlpm.Month, _xlpm.HeadAtStart) + [0]!CommonLivestock_InputFunctions.LivestockMovement_TotalLiveweightGrownDuringMonth(_xlpm.Month, _xlpm.LivestockClass))</definedName>
+    <definedName name="CommonLivestock_SourceData.SourceData_Livestock_Common_SymbolsMMS_Data">_xlfn.LAMBDA(_xlfn.MAKEARRAY(19, 3, _xlfn.LAMBDA(_xlpm.r,_xlpm.c, INDEX({"Symbol","Manure management system","";"1","Anaerobic lagoon","Anaerobic lagoon (m=1)";"2","Liquid systems","Liquid systems (m=2)";"3","Daily spread","Daily spread (m=3)";"3a","Sump and dispersal system","Sump and dispersal system (m=3a)";"3b","Drains to paddock","Drains to paddock (m=3b)";"4","Solid storage","Solid storage (m=4)";"5","Drylot (feed pad)","Drylot (feed pad) (m=5)";"6","Composting (passive windrow)","Composting (passive windrow) (m=6)";"7","Digester / covered lagoons","Digester / covered lagoons (m=7)";"8","Deep litter","Deep litter (m=8)";"9","Pit storage","Pit storage (m=9)";"10","Poultry manure with bedding","Poultry manure with bedding (m=10)";"11","Poultry manure without bedding","Poultry manure without bedding (m=11)";"11a","Belt manure removal","Belt manure removal (m=11a)";"11b","Manure stored in house","Manure stored in house (m=11b)";"12","Direct processing","Direct processing (m=12)";"13","Direct application","Direct application (m=13)";"14","Pasture range and paddock","Pasture range and paddock (m=14)"}, _xlpm.r, _xlpm.c))))</definedName>
+    <definedName name="Enterprise_PastureBeef_InputFunctions.multiplyCorrespondingCells" localSheetId="6">_xlfn.LAMBDA(_xlpm.range1,_xlpm.range2,_xlpm.range3, _xlfn.LET(_xlpm.numRows, ROWS(_xlpm.range1), _xlpm.numCols, COLUMNS(_xlpm.range1), _xlpm.result, _xlfn.MAKEARRAY(_xlpm.numRows, _xlpm.numCols, _xlfn.LAMBDA(_xlpm.r,_xlpm.c, IF(ISNUMBER(INDEX(_xlpm.range1, _xlpm.r, _xlpm.c)), INDEX(_xlpm.range1, _xlpm.r, _xlpm.c), 0) * IF(ISNUMBER(INDEX(_xlpm.range2, _xlpm.r, _xlpm.c)), INDEX(_xlpm.range2, _xlpm.r, _xlpm.c), 0) * IF(ISNUMBER(INDEX(_xlpm.range3, _xlpm.r, _xlpm.c)), INDEX(_xlpm.range3, _xlpm.r, _xlpm.c), 0))), _xlpm.result))</definedName>
     <definedName name="Enterprise_PastureBeef_InputFunctions.multiplyCorrespondingCells" localSheetId="4">_xlfn.LAMBDA(_xlpm.range1,_xlpm.range2,_xlpm.range3, _xlfn.LET(_xlpm.numRows, ROWS(_xlpm.range1), _xlpm.numCols, COLUMNS(_xlpm.range1), _xlpm.result, _xlfn.MAKEARRAY(_xlpm.numRows, _xlpm.numCols, _xlfn.LAMBDA(_xlpm.r,_xlpm.c, IF(ISNUMBER(INDEX(_xlpm.range1, _xlpm.r, _xlpm.c)), INDEX(_xlpm.range1, _xlpm.r, _xlpm.c), 0) * IF(ISNUMBER(INDEX(_xlpm.range2, _xlpm.r, _xlpm.c)), INDEX(_xlpm.range2, _xlpm.r, _xlpm.c), 0) * IF(ISNUMBER(INDEX(_xlpm.range3, _xlpm.r, _xlpm.c)), INDEX(_xlpm.range3, _xlpm.r, _xlpm.c), 0))), _xlpm.result))</definedName>
     <definedName name="Enterprise_PastureBeef_InputFunctions.multiplyCorrespondingCells">_xlfn.LAMBDA(_xlpm.range1,_xlpm.range2,_xlpm.range3, _xlfn.LET(_xlpm.numRows, ROWS(_xlpm.range1), _xlpm.numCols, COLUMNS(_xlpm.range1), _xlpm.result, _xlfn.MAKEARRAY(_xlpm.numRows, _xlpm.numCols, _xlfn.LAMBDA(_xlpm.r,_xlpm.c, IF(ISNUMBER(INDEX(_xlpm.range1, _xlpm.r, _xlpm.c)), INDEX(_xlpm.range1, _xlpm.r, _xlpm.c), 0) * IF(ISNUMBER(INDEX(_xlpm.range2, _xlpm.r, _xlpm.c)), INDEX(_xlpm.range2, _xlpm.r, _xlpm.c), 0) * IF(ISNUMBER(INDEX(_xlpm.range3, _xlpm.r, _xlpm.c)), INDEX(_xlpm.range3, _xlpm.r, _xlpm.c), 0))), _xlpm.result))</definedName>
+    <definedName name="getOverlappingReportingCycles" localSheetId="6">_xlfn.LAMBDA(_xlpm.ProductionCycleStart,_xlpm.ProductionCycleEnd,_xlpm.ReportingStartMonth,_xlpm.ReportingStartDay, _xlfn.LET(_xlpm.S, _xlpm.ProductionCycleStart, _xlpm.E, _xlpm.ProductionCycleEnd, _xlpm.m, _xlpm.ReportingStartMonth, _xlpm.d, _xlpm.ReportingStartDay, _xlpm.A, _xlpm.S - 364, _xlpm.ya, YEAR(_xlpm.A), _xlpm.yb, YEAR(_xlpm.E), _xlpm.firstYear, _xlpm.ya + (DATE(_xlpm.ya, _xlpm.m, _xlpm.d) &lt; _xlpm.A), _xlpm.lastYear, _xlpm.yb - (DATE(_xlpm.yb, _xlpm.m, _xlpm.d) &gt; _xlpm.E), MAX(0, _xlpm.lastYear - _xlpm.firstYear + 1)))</definedName>
     <definedName name="getOverlappingReportingCycles" localSheetId="4">_xlfn.LAMBDA(_xlpm.ProductionCycleStart,_xlpm.ProductionCycleEnd,_xlpm.ReportingStartMonth,_xlpm.ReportingStartDay, _xlfn.LET(_xlpm.S, _xlpm.ProductionCycleStart, _xlpm.E, _xlpm.ProductionCycleEnd, _xlpm.m, _xlpm.ReportingStartMonth, _xlpm.d, _xlpm.ReportingStartDay, _xlpm.A, _xlpm.S - 364, _xlpm.ya, YEAR(_xlpm.A), _xlpm.yb, YEAR(_xlpm.E), _xlpm.firstYear, _xlpm.ya + (DATE(_xlpm.ya, _xlpm.m, _xlpm.d) &lt; _xlpm.A), _xlpm.lastYear, _xlpm.yb - (DATE(_xlpm.yb, _xlpm.m, _xlpm.d) &gt; _xlpm.E), MAX(0, _xlpm.lastYear - _xlpm.firstYear + 1)))</definedName>
     <definedName name="getOverlappingReportingCycles">_xlfn.LAMBDA(_xlpm.ProductionCycleStart,_xlpm.ProductionCycleEnd,_xlpm.ReportingStartMonth,_xlpm.ReportingStartDay, _xlfn.LET(_xlpm.S, _xlpm.ProductionCycleStart, _xlpm.E, _xlpm.ProductionCycleEnd, _xlpm.m, _xlpm.ReportingStartMonth, _xlpm.d, _xlpm.ReportingStartDay, _xlpm.A, _xlpm.S - 364, _xlpm.ya, YEAR(_xlpm.A), _xlpm.yb, YEAR(_xlpm.E), _xlpm.firstYear, _xlpm.ya + (DATE(_xlpm.ya, _xlpm.m, _xlpm.d) &lt; _xlpm.A), _xlpm.lastYear, _xlpm.yb - (DATE(_xlpm.yb, _xlpm.m, _xlpm.d) &gt; _xlpm.E), MAX(0, _xlpm.lastYear - _xlpm.firstYear + 1)))</definedName>
+    <definedName name="InputFunctions_PastureBeef.ConvertMonthlyCalvingToSeason" localSheetId="6">_xlfn.LAMBDA(_xlpm.Season,_xlpm.SumArray,_xlpm.CalvingMonthArray,_xlpm.MonthArray,_xlpm.MonthToSeasonArray, _xlfn.LET(_xlpm.MonthText, TEXT(_xlpm.CalvingMonthArray, "mmmm"), _xlpm.SeasonPerRow, _xlfn.XLOOKUP(_xlpm.MonthText, _xlpm.MonthArray, _xlpm.MonthToSeasonArray, "", 0), SUM(_xlpm.SumArray * (_xlpm.SeasonPerRow = _xlpm.Season))))</definedName>
     <definedName name="InputFunctions_PastureBeef.ConvertMonthlyCalvingToSeason" localSheetId="4">_xlfn.LAMBDA(_xlpm.Season,_xlpm.SumArray,_xlpm.CalvingMonthArray,_xlpm.MonthArray,_xlpm.MonthToSeasonArray, _xlfn.LET(_xlpm.MonthText, TEXT(_xlpm.CalvingMonthArray, "mmmm"), _xlpm.SeasonPerRow, _xlfn.XLOOKUP(_xlpm.MonthText, _xlpm.MonthArray, _xlpm.MonthToSeasonArray, "", 0), SUM(_xlpm.SumArray * (_xlpm.SeasonPerRow = _xlpm.Season))))</definedName>
     <definedName name="InputFunctions_PastureBeef.ConvertMonthlyCalvingToSeason">_xlfn.LAMBDA(_xlpm.Season,_xlpm.SumArray,_xlpm.CalvingMonthArray,_xlpm.MonthArray,_xlpm.MonthToSeasonArray, _xlfn.LET(_xlpm.MonthText, TEXT(_xlpm.CalvingMonthArray, "mmmm"), _xlpm.SeasonPerRow, _xlfn.XLOOKUP(_xlpm.MonthText, _xlpm.MonthArray, _xlpm.MonthToSeasonArray, "", 0), SUM(_xlpm.SumArray * (_xlpm.SeasonPerRow = _xlpm.Season))))</definedName>
+    <definedName name="InputFunctions_PastureBeef.LookupLiveweightFromMonth" localSheetId="6">_xlfn.LAMBDA(_xlpm.State,_xlpm.Region,_xlpm.Month,_xlpm.LivestockClass,_xlpm.StateArray,_xlpm.RegionArray,_xlpm.SeasonArray,_xlpm.LivestockClassArray,_xlpm.ReturnArray,_xlpm.StateCommonNameArray,_xlpm.StateAbbreviationArray,_xlpm.MonthArray,_xlpm.MonthToSeasonArray, _xlfn.LET(_xlpm.Month, TEXT(_xlpm.Month, "mmmm"), _xlpm.State, _xlfn.XLOOKUP(_xlpm.State, _xlpm.StateCommonNameArray, _xlpm.StateAbbreviationArray), _xlpm.Season, _xlfn.XLOOKUP(_xlpm.Month, _xlpm.MonthArray, _xlpm.MonthToSeasonArray), _xlfn.XLOOKUP(1, (_xlpm.StateArray = _xlpm.State) * (_xlpm.RegionArray = _xlpm.Region) * (_xlpm.SeasonArray = _xlpm.Season), _xlfn.XLOOKUP(_xlpm.LivestockClass, _xlpm.LivestockClassArray, _xlpm.ReturnArray))))</definedName>
     <definedName name="InputFunctions_PastureBeef.LookupLiveweightFromMonth" localSheetId="4">_xlfn.LAMBDA(_xlpm.State,_xlpm.Region,_xlpm.Month,_xlpm.LivestockClass,_xlpm.StateArray,_xlpm.RegionArray,_xlpm.SeasonArray,_xlpm.LivestockClassArray,_xlpm.ReturnArray,_xlpm.StateCommonNameArray,_xlpm.StateAbbreviationArray,_xlpm.MonthArray,_xlpm.MonthToSeasonArray, _xlfn.LET(_xlpm.Month, TEXT(_xlpm.Month, "mmmm"), _xlpm.State, _xlfn.XLOOKUP(_xlpm.State, _xlpm.StateCommonNameArray, _xlpm.StateAbbreviationArray), _xlpm.Season, _xlfn.XLOOKUP(_xlpm.Month, _xlpm.MonthArray, _xlpm.MonthToSeasonArray), _xlfn.XLOOKUP(1, (_xlpm.StateArray = _xlpm.State) * (_xlpm.RegionArray = _xlpm.Region) * (_xlpm.SeasonArray = _xlpm.Season), _xlfn.XLOOKUP(_xlpm.LivestockClass, _xlpm.LivestockClassArray, _xlpm.ReturnArray))))</definedName>
     <definedName name="InputFunctions_PastureBeef.LookupLiveweightFromMonth">_xlfn.LAMBDA(_xlpm.State,_xlpm.Region,_xlpm.Month,_xlpm.LivestockClass,_xlpm.StateArray,_xlpm.RegionArray,_xlpm.SeasonArray,_xlpm.LivestockClassArray,_xlpm.ReturnArray,_xlpm.StateCommonNameArray,_xlpm.StateAbbreviationArray,_xlpm.MonthArray,_xlpm.MonthToSeasonArray, _xlfn.LET(_xlpm.Month, TEXT(_xlpm.Month, "mmmm"), _xlpm.State, _xlfn.XLOOKUP(_xlpm.State, _xlpm.StateCommonNameArray, _xlpm.StateAbbreviationArray), _xlpm.Season, _xlfn.XLOOKUP(_xlpm.Month, _xlpm.MonthArray, _xlpm.MonthToSeasonArray), _xlfn.XLOOKUP(1, (_xlpm.StateArray = _xlpm.State) * (_xlpm.RegionArray = _xlpm.Region) * (_xlpm.SeasonArray = _xlpm.Season), _xlfn.XLOOKUP(_xlpm.LivestockClass, _xlpm.LivestockClassArray, _xlpm.ReturnArray))))</definedName>
+    <definedName name="InputFunctions_PastureBeef.LookupLiveweightFromSeason" localSheetId="6">_xlfn.LAMBDA(_xlpm.State,_xlpm.Region,_xlpm.Season,_xlpm.LivestockClass,_xlpm.StateArray,_xlpm.RegionArray,_xlpm.SeasonArray,_xlpm.LivestockClassArray,_xlpm.ReturnArray,_xlpm.StateCommonNameArray,_xlpm.StateAbbreviationArray, _xlfn.LET(_xlpm.State, _xlfn.XLOOKUP(_xlpm.State, _xlpm.StateCommonNameArray, _xlpm.StateAbbreviationArray), _xlfn.XLOOKUP(1, (_xlpm.StateArray = _xlpm.State) * (_xlpm.RegionArray = _xlpm.Region) * (_xlpm.SeasonArray = _xlpm.Season), _xlfn.XLOOKUP(_xlpm.LivestockClass, _xlpm.LivestockClassArray, _xlpm.ReturnArray))))</definedName>
     <definedName name="InputFunctions_PastureBeef.LookupLiveweightFromSeason" localSheetId="4">_xlfn.LAMBDA(_xlpm.State,_xlpm.Region,_xlpm.Season,_xlpm.LivestockClass,_xlpm.StateArray,_xlpm.RegionArray,_xlpm.SeasonArray,_xlpm.LivestockClassArray,_xlpm.ReturnArray,_xlpm.StateCommonNameArray,_xlpm.StateAbbreviationArray, _xlfn.LET(_xlpm.State, _xlfn.XLOOKUP(_xlpm.State, _xlpm.StateCommonNameArray, _xlpm.StateAbbreviationArray), _xlfn.XLOOKUP(1, (_xlpm.StateArray = _xlpm.State) * (_xlpm.RegionArray = _xlpm.Region) * (_xlpm.SeasonArray = _xlpm.Season), _xlfn.XLOOKUP(_xlpm.LivestockClass, _xlpm.LivestockClassArray, _xlpm.ReturnArray))))</definedName>
     <definedName name="InputFunctions_PastureBeef.LookupLiveweightFromSeason">_xlfn.LAMBDA(_xlpm.State,_xlpm.Region,_xlpm.Season,_xlpm.LivestockClass,_xlpm.StateArray,_xlpm.RegionArray,_xlpm.SeasonArray,_xlpm.LivestockClassArray,_xlpm.ReturnArray,_xlpm.StateCommonNameArray,_xlpm.StateAbbreviationArray, _xlfn.LET(_xlpm.State, _xlfn.XLOOKUP(_xlpm.State, _xlpm.StateCommonNameArray, _xlpm.StateAbbreviationArray), _xlfn.XLOOKUP(1, (_xlpm.StateArray = _xlpm.State) * (_xlpm.RegionArray = _xlpm.Region) * (_xlpm.SeasonArray = _xlpm.Season), _xlfn.XLOOKUP(_xlpm.LivestockClass, _xlpm.LivestockClassArray, _xlpm.ReturnArray))))</definedName>
+    <definedName name="InputFunctions_PastureBeef.LookupValueFromStateRegionMonth" localSheetId="6">_xlfn.LAMBDA(_xlpm.State,_xlpm.Region,_xlpm.Month,_xlpm.StateArray,_xlpm.RegionArray,_xlpm.SeasonArray,_xlpm.ReturnArray,_xlpm.StateCommonNameArray,_xlpm.StateAbbreviationArray,_xlpm.MonthArray,_xlpm.MonthToSeasonArray, _xlfn.LET(_xlpm.State, _xlfn.XLOOKUP(_xlpm.State, _xlpm.StateCommonNameArray, _xlpm.StateAbbreviationArray), _xlpm.Season, _xlfn.XLOOKUP(TEXT(_xlpm.Month, "mmmm"), _xlpm.MonthArray, _xlpm.MonthToSeasonArray), _xlfn.XLOOKUP(1, (_xlpm.StateArray = _xlpm.State) * (_xlpm.RegionArray = _xlpm.Region), _xlfn.XLOOKUP(_xlpm.Season, _xlpm.SeasonArray, _xlpm.ReturnArray))))</definedName>
     <definedName name="InputFunctions_PastureBeef.LookupValueFromStateRegionMonth" localSheetId="4">_xlfn.LAMBDA(_xlpm.State,_xlpm.Region,_xlpm.Month,_xlpm.StateArray,_xlpm.RegionArray,_xlpm.SeasonArray,_xlpm.ReturnArray,_xlpm.StateCommonNameArray,_xlpm.StateAbbreviationArray,_xlpm.MonthArray,_xlpm.MonthToSeasonArray, _xlfn.LET(_xlpm.State, _xlfn.XLOOKUP(_xlpm.State, _xlpm.StateCommonNameArray, _xlpm.StateAbbreviationArray), _xlpm.Season, _xlfn.XLOOKUP(TEXT(_xlpm.Month, "mmmm"), _xlpm.MonthArray, _xlpm.MonthToSeasonArray), _xlfn.XLOOKUP(1, (_xlpm.StateArray = _xlpm.State) * (_xlpm.RegionArray = _xlpm.Region), _xlfn.XLOOKUP(_xlpm.Season, _xlpm.SeasonArray, _xlpm.ReturnArray))))</definedName>
     <definedName name="InputFunctions_PastureBeef.LookupValueFromStateRegionMonth">_xlfn.LAMBDA(_xlpm.State,_xlpm.Region,_xlpm.Month,_xlpm.StateArray,_xlpm.RegionArray,_xlpm.SeasonArray,_xlpm.ReturnArray,_xlpm.StateCommonNameArray,_xlpm.StateAbbreviationArray,_xlpm.MonthArray,_xlpm.MonthToSeasonArray, _xlfn.LET(_xlpm.State, _xlfn.XLOOKUP(_xlpm.State, _xlpm.StateCommonNameArray, _xlpm.StateAbbreviationArray), _xlpm.Season, _xlfn.XLOOKUP(TEXT(_xlpm.Month, "mmmm"), _xlpm.MonthArray, _xlpm.MonthToSeasonArray), _xlfn.XLOOKUP(1, (_xlpm.StateArray = _xlpm.State) * (_xlpm.RegionArray = _xlpm.Region), _xlfn.XLOOKUP(_xlpm.Season, _xlpm.SeasonArray, _xlpm.ReturnArray))))</definedName>
+    <definedName name="InputFunctions_PastureBeef.LookupValueFromStateRegionSeason" localSheetId="6">_xlfn.LAMBDA(_xlpm.State,_xlpm.Region,_xlpm.Season,_xlpm.StateArray,_xlpm.RegionArray,_xlpm.SeasonArray,_xlpm.ReturnArray,_xlpm.StateCommonNameArray,_xlpm.StateAbbreviationArray, _xlfn.LET(_xlpm.State, _xlfn.XLOOKUP(_xlpm.State, _xlpm.StateCommonNameArray, _xlpm.StateAbbreviationArray), _xlfn.XLOOKUP(1, (_xlpm.StateArray = _xlpm.State) * (_xlpm.RegionArray = _xlpm.Region), _xlfn.XLOOKUP(_xlpm.Season, _xlpm.SeasonArray, _xlpm.ReturnArray))))</definedName>
     <definedName name="InputFunctions_PastureBeef.LookupValueFromStateRegionSeason" localSheetId="4">_xlfn.LAMBDA(_xlpm.State,_xlpm.Region,_xlpm.Season,_xlpm.StateArray,_xlpm.RegionArray,_xlpm.SeasonArray,_xlpm.ReturnArray,_xlpm.StateCommonNameArray,_xlpm.StateAbbreviationArray, _xlfn.LET(_xlpm.State, _xlfn.XLOOKUP(_xlpm.State, _xlpm.StateCommonNameArray, _xlpm.StateAbbreviationArray), _xlfn.XLOOKUP(1, (_xlpm.StateArray = _xlpm.State) * (_xlpm.RegionArray = _xlpm.Region), _xlfn.XLOOKUP(_xlpm.Season, _xlpm.SeasonArray, _xlpm.ReturnArray))))</definedName>
     <definedName name="InputFunctions_PastureBeef.LookupValueFromStateRegionSeason">_xlfn.LAMBDA(_xlpm.State,_xlpm.Region,_xlpm.Season,_xlpm.StateArray,_xlpm.RegionArray,_xlpm.SeasonArray,_xlpm.ReturnArray,_xlpm.StateCommonNameArray,_xlpm.StateAbbreviationArray, _xlfn.LET(_xlpm.State, _xlfn.XLOOKUP(_xlpm.State, _xlpm.StateCommonNameArray, _xlpm.StateAbbreviationArray), _xlfn.XLOOKUP(1, (_xlpm.StateArray = _xlpm.State) * (_xlpm.RegionArray = _xlpm.Region), _xlfn.XLOOKUP(_xlpm.Season, _xlpm.SeasonArray, _xlpm.ReturnArray))))</definedName>
+    <definedName name="Result_CarbonRemovalsFromPlantings" localSheetId="6">[3]Results!$E$50</definedName>
     <definedName name="Result_CarbonRemovalsFromPlantings">Results!$E$56</definedName>
+    <definedName name="Result_EmissionsForWholeProductionCycle_Method1" localSheetId="6">[3]Results!$E$39</definedName>
     <definedName name="Result_EmissionsForWholeProductionCycle_Method1" localSheetId="4">[1]Results!$E$42</definedName>
     <definedName name="Result_EmissionsForWholeProductionCycle_Method1">Results!$E$45</definedName>
+    <definedName name="Result_EmissionsForWholeProductionCycle_Method2" localSheetId="6">[3]Results!$F$39</definedName>
     <definedName name="Result_EmissionsForWholeProductionCycle_Method2" localSheetId="4">[1]Results!$F$42</definedName>
     <definedName name="Result_EmissionsForWholeProductionCycle_Method2">Results!$F$45</definedName>
+    <definedName name="Result_Enterprise_Method1" localSheetId="6">[3]Results!$H$25</definedName>
     <definedName name="Result_Enterprise_Method1" localSheetId="4">[1]Results!$H$28</definedName>
     <definedName name="Result_Enterprise_Method1">Results!$H$31</definedName>
+    <definedName name="Result_Enterprise_Method2" localSheetId="6">[3]Results!$I$25</definedName>
     <definedName name="Result_Enterprise_Method2" localSheetId="4">[1]Results!$I$28</definedName>
     <definedName name="Result_Enterprise_Method2">Results!$I$31</definedName>
+    <definedName name="Result_NetEmissions_Method1" localSheetId="6">[3]Results!$E$56</definedName>
     <definedName name="Result_NetEmissions_Method1" localSheetId="4">[1]Results!$E$59</definedName>
     <definedName name="Result_NetEmissions_Method1">Results!$E$62</definedName>
+    <definedName name="Result_NetEmissions_Method2" localSheetId="6">[3]Results!$F$56</definedName>
     <definedName name="Result_NetEmissions_Method2" localSheetId="4">[1]Results!$F$59</definedName>
     <definedName name="Result_NetEmissions_Method2">Results!$F$62</definedName>
+    <definedName name="X_Cell_Enterprise_PercentIncomeFromGrain">'[3]Input - Enterprise'!$E$32</definedName>
+    <definedName name="X_Cell_Enterprise_ProductionTimeframeEnd" localSheetId="6">'[3]Input - Enterprise'!$E$19</definedName>
     <definedName name="X_Cell_Enterprise_ProductionTimeframeEnd" localSheetId="4">'[1]Input - Enterprise'!$E$19</definedName>
     <definedName name="X_Cell_Enterprise_ProductionTimeframeEnd">'Input - Enterprise'!$E$19</definedName>
+    <definedName name="X_Cell_Enterprise_ProductionTimeframeStart" localSheetId="6">'[3]Input - Enterprise'!$E$18</definedName>
     <definedName name="X_Cell_Enterprise_ProductionTimeframeStart" localSheetId="4">'[1]Input - Enterprise'!$E$18</definedName>
     <definedName name="X_Cell_Enterprise_ProductionTimeframeStart">'Input - Enterprise'!$E$18</definedName>
     <definedName name="X_Cell_Fertiliser_AreaUnderCropping">'Input - Fert Prod System'!$E$10</definedName>
@@ -279,6 +369,7 @@
     <definedName name="X_Cell_Site_RainfallZone">'Input - Site'!$E$19</definedName>
     <definedName name="X_Cell_Site_Region">'Input - Site'!$E$11</definedName>
     <definedName name="X_Cell_Site_ReportingEntityName">'Input - Enterprise'!$E$8</definedName>
+    <definedName name="X_Cell_Site_StartDate" localSheetId="6">'[3]Input - Enterprise'!$E$12</definedName>
     <definedName name="X_Cell_Site_StartDate" localSheetId="4">'[1]Input - Enterprise'!$E$12</definedName>
     <definedName name="X_Cell_Site_StartDate">'Input - Enterprise'!$E$12</definedName>
     <definedName name="X_Cell_Site_State">'Input - Site'!$E$10</definedName>
@@ -346,7 +437,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="312" uniqueCount="198">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="324" uniqueCount="210">
   <si>
     <t>Home</t>
   </si>
@@ -994,6 +1085,42 @@
   </si>
   <si>
     <t>t co2e/t milk solids</t>
+  </si>
+  <si>
+    <t>Input - Data quality</t>
+  </si>
+  <si>
+    <t>Input</t>
+  </si>
+  <si>
+    <t>Temporal representativeness</t>
+  </si>
+  <si>
+    <t>Spatial resolution</t>
+  </si>
+  <si>
+    <t>Sample size</t>
+  </si>
+  <si>
+    <t>Notes</t>
+  </si>
+  <si>
+    <t>Evidence files</t>
+  </si>
+  <si>
+    <t>Score</t>
+  </si>
+  <si>
+    <t>Input name</t>
+  </si>
+  <si>
+    <t>TR4</t>
+  </si>
+  <si>
+    <t>SR5</t>
+  </si>
+  <si>
+    <t>SS3</t>
   </si>
 </sst>
 </file>
@@ -1837,7 +1964,7 @@
     <xf numFmtId="43" fontId="9" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="9" fontId="9" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="95">
+  <cellXfs count="97">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="29" fillId="4" borderId="0" xfId="8">
       <alignment horizontal="left" vertical="center"/>
@@ -2091,6 +2218,13 @@
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="0" fontId="12" fillId="6" borderId="0" xfId="29">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="14" applyFont="1" applyBorder="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="69">
     <cellStyle name="Alert" xfId="59" xr:uid="{34EFE908-8095-4010-8F93-8CFE88055637}"/>
@@ -3344,6 +3478,108 @@
 </externalLink>
 </file>
 
+<file path=xl/externalLinks/externalLink2.xml><?xml version="1.0" encoding="utf-8"?>
+<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
+  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
+    <xxl21:alternateUrls>
+      <xxl21:absoluteUrl r:id="rId2"/>
+      <xxl21:relativeUrl r:id="rId3"/>
+    </xxl21:alternateUrls>
+    <sheetNames>
+      <sheetName val="Home"/>
+      <sheetName val="Input - Data quality"/>
+      <sheetName val="Constants - Common"/>
+      <sheetName val="Acknowledgements"/>
+    </sheetNames>
+    <sheetDataSet>
+      <sheetData sheetId="0"/>
+      <sheetData sheetId="1"/>
+      <sheetData sheetId="2"/>
+      <sheetData sheetId="3"/>
+    </sheetDataSet>
+  </externalBook>
+</externalLink>
+</file>
+
+<file path=xl/externalLinks/externalLink3.xml><?xml version="1.0" encoding="utf-8"?>
+<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
+  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
+    <xxl21:alternateUrls>
+      <xxl21:absoluteUrl r:id="rId2"/>
+    </xxl21:alternateUrls>
+    <sheetNames>
+      <sheetName val="Home"/>
+      <sheetName val="Results"/>
+      <sheetName val="Input - Site"/>
+      <sheetName val="Input - Enterprise"/>
+      <sheetName val="Input - Fert Prod System"/>
+      <sheetName val="Input - Data quality"/>
+      <sheetName val="Constants - Common"/>
+    </sheetNames>
+    <sheetDataSet>
+      <sheetData sheetId="0"/>
+      <sheetData sheetId="1">
+        <row r="25">
+          <cell r="H25" t="e">
+            <v>#NAME?</v>
+          </cell>
+          <cell r="I25" t="e">
+            <v>#NAME?</v>
+          </cell>
+        </row>
+        <row r="39">
+          <cell r="E39" t="e">
+            <v>#NAME?</v>
+          </cell>
+          <cell r="F39" t="e">
+            <v>#NAME?</v>
+          </cell>
+        </row>
+        <row r="50">
+          <cell r="E50">
+            <v>0</v>
+          </cell>
+        </row>
+        <row r="56">
+          <cell r="E56" t="e">
+            <v>#NAME?</v>
+          </cell>
+          <cell r="F56" t="e">
+            <v>#NAME?</v>
+          </cell>
+        </row>
+      </sheetData>
+      <sheetData sheetId="2"/>
+      <sheetData sheetId="3">
+        <row r="12">
+          <cell r="E12">
+            <v>45658</v>
+          </cell>
+        </row>
+        <row r="18">
+          <cell r="E18">
+            <v>45962</v>
+          </cell>
+        </row>
+        <row r="19">
+          <cell r="E19">
+            <v>46112</v>
+          </cell>
+        </row>
+        <row r="32">
+          <cell r="E32">
+            <v>0.8</v>
+          </cell>
+        </row>
+      </sheetData>
+      <sheetData sheetId="4"/>
+      <sheetData sheetId="5"/>
+      <sheetData sheetId="6"/>
+    </sheetDataSet>
+  </externalBook>
+</externalLink>
+</file>
+
 <file path=xl/richData/rdRichValueTypes.xml><?xml version="1.0" encoding="utf-8"?>
 <rvTypesInfo xmlns="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" mc:Ignorable="x">
   <global>
@@ -3433,6 +3669,32 @@
 </file>
 
 <file path=xl/tables/table10.xml><?xml version="1.0" encoding="utf-8"?>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="10" xr:uid="{AA9D31FA-C10A-401A-A990-FD7418530E07}" name="Table_SourceData_RainfallZones" displayName="Table_SourceData_RainfallZones" ref="D119:G121" totalsRowShown="0">
+  <autoFilter ref="D119:G121" xr:uid="{E08772F3-2E8C-40A8-B755-08A5BBDF4130}">
+    <filterColumn colId="0" hiddenButton="1"/>
+    <filterColumn colId="1" hiddenButton="1"/>
+    <filterColumn colId="2" hiddenButton="1"/>
+    <filterColumn colId="3" hiddenButton="1"/>
+  </autoFilter>
+  <tableColumns count="4">
+    <tableColumn id="1" xr3:uid="{A1896C80-5B23-4971-85DF-908C9411D636}" name="Rainfall Zone">
+      <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_RainfallZones_Data(),Table_SourceData_RainfallZones[[#Headers],[Rainfall Zone]],0)</calculatedColumnFormula>
+    </tableColumn>
+    <tableColumn id="2" xr3:uid="{776A729E-62FB-471E-9D55-F5C0C49DAFB1}" name="Annual rainfall">
+      <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_RainfallZones_Data(),Table_SourceData_RainfallZones[[#Headers],[Rainfall Zone]],0)</calculatedColumnFormula>
+    </tableColumn>
+    <tableColumn id="3" xr3:uid="{5C488583-1093-4920-BAEF-A4BD862E3623}" name="Min rainfall">
+      <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_RainfallZones_Data(),Table_SourceData_RainfallZones[[#Headers],[Rainfall Zone]],0)</calculatedColumnFormula>
+    </tableColumn>
+    <tableColumn id="4" xr3:uid="{EDCA589F-5D6E-4F25-A934-864B94D632CD}" name="Max rainfall">
+      <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_RainfallZones_Data(),Table_SourceData_RainfallZones[[#Headers],[Rainfall Zone]],0)</calculatedColumnFormula>
+    </tableColumn>
+  </tableColumns>
+  <tableStyleInfo name="Equation table" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
+</table>
+</file>
+
+<file path=xl/tables/table11.xml><?xml version="1.0" encoding="utf-8"?>
 <table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="11" xr:uid="{EC0B98FF-3B1A-4F33-9028-A6B26A7E6CE4}" name="Table_SourceData_LeachingZones" displayName="Table_SourceData_LeachingZones" ref="D127:E129" totalsRowShown="0">
   <autoFilter ref="D127:E129" xr:uid="{A159E140-02ED-4547-B6E1-6695D8B16A11}">
     <filterColumn colId="0" hiddenButton="1"/>
@@ -3450,7 +3712,7 @@
 </table>
 </file>
 
-<file path=xl/tables/table11.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/tables/table12.xml><?xml version="1.0" encoding="utf-8"?>
 <table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="12" xr:uid="{C1B321B1-DD2B-4EC5-AE20-D47C87F02BBF}" name="Table_SourceData_DataScores_Scope3" displayName="Table_SourceData_DataScores_Scope3" ref="D153:E158" totalsRowShown="0">
   <autoFilter ref="D153:E158" xr:uid="{133D42B0-F6D2-470A-858A-37E6A7F5EC2B}">
     <filterColumn colId="0" hiddenButton="1"/>
@@ -3468,7 +3730,7 @@
 </table>
 </file>
 
-<file path=xl/tables/table12.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/tables/table13.xml><?xml version="1.0" encoding="utf-8"?>
 <table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="13" xr:uid="{14C890C4-4A77-40EC-A6C1-19C0895BD309}" name="Table_SourceData_FracWET" displayName="Table_SourceData_FracWET" ref="D134:E136" totalsRowShown="0">
   <autoFilter ref="D134:E136" xr:uid="{308E99BE-FE1F-47A4-B2CA-97217277C4E9}">
     <filterColumn colId="0" hiddenButton="1"/>
@@ -3486,7 +3748,7 @@
 </table>
 </file>
 
-<file path=xl/tables/table13.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/tables/table14.xml><?xml version="1.0" encoding="utf-8"?>
 <table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="14" xr:uid="{6BB36C9A-81C9-4008-9621-02E7765F4217}" name="Table_SourceData_Common_EFN2O" displayName="Table_SourceData_Common_EFN2O" ref="D186:H199" totalsRowShown="0">
   <autoFilter ref="D186:H199" xr:uid="{D41FBEA4-8379-4DF7-A068-BF94D364F1A2}">
     <filterColumn colId="0" hiddenButton="1"/>
@@ -3516,7 +3778,7 @@
 </table>
 </file>
 
-<file path=xl/tables/table14.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/tables/table15.xml><?xml version="1.0" encoding="utf-8"?>
 <table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="15" xr:uid="{81046769-5E78-4435-8902-BE2F7ED271E9}" name="Table_SourceData_FracWETIrrigation" displayName="Table_SourceData_FracWETIrrigation" ref="D142:E147" totalsRowShown="0">
   <autoFilter ref="D142:E147" xr:uid="{1F48CA34-50DE-46D5-B32A-BB3A1E818E37}">
     <filterColumn colId="0" hiddenButton="1"/>
@@ -3534,7 +3796,7 @@
 </table>
 </file>
 
-<file path=xl/tables/table15.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/tables/table16.xml><?xml version="1.0" encoding="utf-8"?>
 <table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="16" xr:uid="{0D2D24A9-44B5-40A8-9D93-5D127038E490}" name="Table_SourceData_EFPastureRangeAndPaddock" displayName="Table_SourceData_EFPastureRangeAndPaddock" ref="D206:E208" totalsRowShown="0">
   <autoFilter ref="D206:E208" xr:uid="{D5BE3F89-D70E-4C53-A71C-E756622DEF38}">
     <filterColumn colId="0" hiddenButton="1"/>
@@ -3552,7 +3814,7 @@
 </table>
 </file>
 
-<file path=xl/tables/table16.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/tables/table17.xml><?xml version="1.0" encoding="utf-8"?>
 <table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="17" xr:uid="{E20A54E0-06E3-423D-998B-2E4A7C9A48F2}" name="Table_SourceData_Common_MonthToSeason" displayName="Table_SourceData_Common_MonthToSeason" ref="D212:E224" totalsRowShown="0">
   <autoFilter ref="D212:E224" xr:uid="{97796C3A-D95E-4077-AA20-A8FE4145DAAD}">
     <filterColumn colId="0" hiddenButton="1"/>
@@ -3570,7 +3832,7 @@
 </table>
 </file>
 
-<file path=xl/tables/table17.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/tables/table18.xml><?xml version="1.0" encoding="utf-8"?>
 <table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="18" xr:uid="{06A63BFC-1602-47C1-AF55-49AA6B4633CD}" name="Table_SourceData_Common_MCFTemperatureZone" displayName="Table_SourceData_Common_MCFTemperatureZone" ref="D231:S250" totalsRowShown="0">
   <autoFilter ref="D231:S250" xr:uid="{1D72DD9B-C8FA-48F4-9A11-20231FF87B5A}">
     <filterColumn colId="0" hiddenButton="1"/>
@@ -3644,7 +3906,7 @@
 </table>
 </file>
 
-<file path=xl/tables/table18.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/tables/table19.xml><?xml version="1.0" encoding="utf-8"?>
 <table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="19" xr:uid="{949FFD0F-1699-4700-8323-CF2162C2663F}" name="Table_SourceData_Common_EFOrganicFertCropResidues" displayName="Table_SourceData_Common_EFOrganicFertCropResidues" ref="D257:E259" totalsRowShown="0">
   <autoFilter ref="D257:E259" xr:uid="{56E01C14-1BB8-4015-9158-4CEB4D3B605C}">
     <filterColumn colId="0" hiddenButton="1"/>
@@ -3663,6 +3925,32 @@
 </file>
 
 <file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{3CA0A1CD-8E5B-46C1-9B1B-A6414BB18D09}" name="Table_Input_DataQuality" displayName="Table_Input_DataQuality" ref="D6:J7" totalsRowShown="0" headerRowCellStyle="Input table column header">
+  <autoFilter ref="D6:J7" xr:uid="{13023411-FAD9-40B6-9366-7826422CBF8A}">
+    <filterColumn colId="0" hiddenButton="1"/>
+    <filterColumn colId="1" hiddenButton="1"/>
+    <filterColumn colId="2" hiddenButton="1"/>
+    <filterColumn colId="3" hiddenButton="1"/>
+    <filterColumn colId="4" hiddenButton="1"/>
+    <filterColumn colId="5" hiddenButton="1"/>
+    <filterColumn colId="6" hiddenButton="1"/>
+  </autoFilter>
+  <tableColumns count="7">
+    <tableColumn id="1" xr3:uid="{62D91677-2A2D-42DA-8119-4ECEF8794C8C}" name="Input"/>
+    <tableColumn id="2" xr3:uid="{D0F60017-C58D-42ED-9BF1-8D01902E8D4D}" name="Temporal representativeness" dataCellStyle="Input select"/>
+    <tableColumn id="3" xr3:uid="{08DBDF97-0155-4B2F-8291-54B61FF408BD}" name="Spatial resolution" dataCellStyle="Input select"/>
+    <tableColumn id="4" xr3:uid="{022C6E4C-4A1B-4829-929A-D1AA689758A2}" name="Sample size" dataCellStyle="Input select"/>
+    <tableColumn id="5" xr3:uid="{28F01E09-BECE-484C-81F3-93DFF53DC900}" name="Notes"/>
+    <tableColumn id="6" xr3:uid="{DDF62FEF-8F18-4588-8C64-94585E6BFF74}" name="Evidence files"/>
+    <tableColumn id="7" xr3:uid="{05442818-31FF-4B7D-911F-5A30BA48670D}" name="Score" dataCellStyle="Input number general calculated">
+      <calculatedColumnFormula>_xlfn.XLOOKUP(Table_Input_DataQuality[[#This Row],[Temporal representativeness]],[2]!Table_SourceData_DataQuality_TemporalRepresentativeness[ID],[2]!Table_SourceData_DataQuality_TemporalRepresentativeness[Score])+_xlfn.XLOOKUP(Table_Input_DataQuality[[#This Row],[Spatial resolution]],[2]!Table_SourceData_DataQuality_SpatialRepresentativeness[ID],[2]!Table_SourceData_DataQuality_SpatialRepresentativeness[Score])+_xlfn.XLOOKUP(Table_Input_DataQuality[[#This Row],[Sample size]],[2]!Table_SourceData_DataQuality_SampleSize[ID],[2]!Table_SourceData_DataQuality_SampleSize[Score])</calculatedColumnFormula>
+    </tableColumn>
+  </tableColumns>
+  <tableStyleInfo name="Editable table" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
+</table>
+</file>
+
+<file path=xl/tables/table3.xml><?xml version="1.0" encoding="utf-8"?>
 <table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="3" xr:uid="{2BFA511D-1E33-4FA7-9E53-155741FDE40A}" name="Table_AustralianStates" displayName="Table_AustralianStates" ref="D6:F14" totalsRowShown="0">
   <autoFilter ref="D6:F14" xr:uid="{E0906749-7FC7-47DE-82F6-F796C4463018}">
     <filterColumn colId="0" hiddenButton="1"/>
@@ -3684,7 +3972,7 @@
 </table>
 </file>
 
-<file path=xl/tables/table3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/tables/table4.xml><?xml version="1.0" encoding="utf-8"?>
 <table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="4" xr:uid="{A251EF82-BC21-4875-B405-6D0F230C2B8D}" name="Table_WASA4Areas" displayName="Table_WASA4Areas" ref="D20:D30" totalsRowShown="0">
   <autoFilter ref="D20:D30" xr:uid="{5FA81339-C6C8-4D36-BEEA-6C4AEDD9E676}">
     <filterColumn colId="0" hiddenButton="1"/>
@@ -3698,7 +3986,7 @@
 </table>
 </file>
 
-<file path=xl/tables/table4.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/tables/table5.xml><?xml version="1.0" encoding="utf-8"?>
 <table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="5" xr:uid="{3F15B4B0-BD4E-4903-9096-ED3FE0A9167C}" name="Table_GWPData" displayName="Table_GWPData" ref="D36:E43" totalsRowShown="0">
   <autoFilter ref="D36:E43" xr:uid="{B8E87A66-3E41-4AD3-925D-01EE21B43D7A}">
     <filterColumn colId="0" hiddenButton="1"/>
@@ -3716,7 +4004,7 @@
 </table>
 </file>
 
-<file path=xl/tables/table5.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/tables/table6.xml><?xml version="1.0" encoding="utf-8"?>
 <table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="6" xr:uid="{66C67C36-18E1-4B8A-BFF1-35CF3DC4AC81}" name="Table_GasToMolecularConversionFactor" displayName="Table_GasToMolecularConversionFactor" ref="D47:H54" totalsRowShown="0">
   <autoFilter ref="D47:H54" xr:uid="{C1F562BB-DAA6-45BB-951A-7BAFA5B64B45}">
     <filterColumn colId="0" hiddenButton="1"/>
@@ -3746,7 +4034,7 @@
 </table>
 </file>
 
-<file path=xl/tables/table6.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/tables/table7.xml><?xml version="1.0" encoding="utf-8"?>
 <table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="7" xr:uid="{1D6C8105-982C-4B9F-A603-F884FE56E1B4}" name="Table_SourceData_ClimateZones" displayName="Table_SourceData_ClimateZones" ref="D89:S97" totalsRowShown="0">
   <autoFilter ref="D89:S97" xr:uid="{5A437AE9-7724-4CF2-ACCF-291078682FB9}">
     <filterColumn colId="0" hiddenButton="1"/>
@@ -3820,7 +4108,7 @@
 </table>
 </file>
 
-<file path=xl/tables/table7.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/tables/table8.xml><?xml version="1.0" encoding="utf-8"?>
 <table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="8" xr:uid="{D228FD2E-DAAA-4D4F-BEFF-0E68A1F33AA0}" name="Table_SourceData_WetDryZones" displayName="Table_SourceData_WetDryZones" ref="D63:E77" totalsRowShown="0">
   <autoFilter ref="D63:E77" xr:uid="{3597E019-B21E-4B76-BCC8-D02D497BCFA9}">
     <filterColumn colId="0" hiddenButton="1"/>
@@ -3838,7 +4126,7 @@
 </table>
 </file>
 
-<file path=xl/tables/table8.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/tables/table9.xml><?xml version="1.0" encoding="utf-8"?>
 <table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="9" xr:uid="{E436A27C-11D9-4092-B110-DE3B0C7D7A9C}" name="Table_SourceData_TemperatureZones" displayName="Table_SourceData_TemperatureZones" ref="D109:G112" totalsRowShown="0">
   <autoFilter ref="D109:G112" xr:uid="{AB16FEAB-AB03-45E1-BBD4-66D29CD412DF}">
     <filterColumn colId="0" hiddenButton="1"/>
@@ -3858,32 +4146,6 @@
     </tableColumn>
     <tableColumn id="4" xr3:uid="{4C8D6B45-65E8-4A84-9B64-B4D1E990BE71}" name="Max MAT">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_TemperatureZones_Data(),Table_SourceData_TemperatureZones[[#Headers],[Temperature Zone]],0)</calculatedColumnFormula>
-    </tableColumn>
-  </tableColumns>
-  <tableStyleInfo name="Equation table" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
-</table>
-</file>
-
-<file path=xl/tables/table9.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="10" xr:uid="{AA9D31FA-C10A-401A-A990-FD7418530E07}" name="Table_SourceData_RainfallZones" displayName="Table_SourceData_RainfallZones" ref="D119:G121" totalsRowShown="0">
-  <autoFilter ref="D119:G121" xr:uid="{E08772F3-2E8C-40A8-B755-08A5BBDF4130}">
-    <filterColumn colId="0" hiddenButton="1"/>
-    <filterColumn colId="1" hiddenButton="1"/>
-    <filterColumn colId="2" hiddenButton="1"/>
-    <filterColumn colId="3" hiddenButton="1"/>
-  </autoFilter>
-  <tableColumns count="4">
-    <tableColumn id="1" xr3:uid="{A1896C80-5B23-4971-85DF-908C9411D636}" name="Rainfall Zone">
-      <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_RainfallZones_Data(),Table_SourceData_RainfallZones[[#Headers],[Rainfall Zone]],0)</calculatedColumnFormula>
-    </tableColumn>
-    <tableColumn id="2" xr3:uid="{776A729E-62FB-471E-9D55-F5C0C49DAFB1}" name="Annual rainfall">
-      <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_RainfallZones_Data(),Table_SourceData_RainfallZones[[#Headers],[Rainfall Zone]],0)</calculatedColumnFormula>
-    </tableColumn>
-    <tableColumn id="3" xr3:uid="{5C488583-1093-4920-BAEF-A4BD862E3623}" name="Min rainfall">
-      <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_RainfallZones_Data(),Table_SourceData_RainfallZones[[#Headers],[Rainfall Zone]],0)</calculatedColumnFormula>
-    </tableColumn>
-    <tableColumn id="4" xr3:uid="{EDCA589F-5D6E-4F25-A934-864B94D632CD}" name="Max rainfall">
-      <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_RainfallZones_Data(),Table_SourceData_RainfallZones[[#Headers],[Rainfall Zone]],0)</calculatedColumnFormula>
     </tableColumn>
   </tableColumns>
   <tableStyleInfo name="Equation table" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
@@ -7296,6 +7558,106 @@
 </file>
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5097532C-8540-44E5-8090-E452C3E8BF20}">
+  <sheetPr>
+    <tabColor rgb="FFCC6600"/>
+  </sheetPr>
+  <dimension ref="C1:M7"/>
+  <sheetFormatPr defaultRowHeight="15.75" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="30.7109375" customWidth="1"/>
+    <col min="2" max="2" width="4.7109375" customWidth="1"/>
+    <col min="3" max="3" width="4.7109375" style="1" customWidth="1"/>
+    <col min="4" max="4" width="49" style="1" customWidth="1"/>
+    <col min="5" max="7" width="30.7109375" style="1" customWidth="1"/>
+    <col min="8" max="8" width="101.28515625" style="1" customWidth="1"/>
+    <col min="9" max="9" width="74.5703125" style="1" customWidth="1"/>
+    <col min="10" max="13" width="30.7109375" style="1" customWidth="1"/>
+    <col min="14" max="14" width="30.7109375" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="3:13" s="17" customFormat="1" ht="25.5" x14ac:dyDescent="0.35">
+      <c r="C1" s="17" t="s">
+        <v>198</v>
+      </c>
+    </row>
+    <row r="2" spans="3:13" s="3" customFormat="1" x14ac:dyDescent="0.25"/>
+    <row r="3" spans="3:13" ht="20.25" x14ac:dyDescent="0.25">
+      <c r="C3" s="39"/>
+      <c r="D3" s="39"/>
+      <c r="E3" s="39"/>
+      <c r="F3" s="39"/>
+      <c r="G3" s="39"/>
+      <c r="H3" s="39"/>
+      <c r="I3" s="39"/>
+      <c r="J3" s="39"/>
+      <c r="K3" s="39"/>
+      <c r="L3" s="39"/>
+      <c r="M3" s="39"/>
+    </row>
+    <row r="6" spans="3:13" x14ac:dyDescent="0.25">
+      <c r="D6" s="95" t="s">
+        <v>199</v>
+      </c>
+      <c r="E6" s="95" t="s">
+        <v>200</v>
+      </c>
+      <c r="F6" s="95" t="s">
+        <v>201</v>
+      </c>
+      <c r="G6" s="95" t="s">
+        <v>202</v>
+      </c>
+      <c r="H6" s="95" t="s">
+        <v>203</v>
+      </c>
+      <c r="I6" s="95" t="s">
+        <v>204</v>
+      </c>
+      <c r="J6" s="95" t="s">
+        <v>205</v>
+      </c>
+    </row>
+    <row r="7" spans="3:13" x14ac:dyDescent="0.25">
+      <c r="D7" s="96" t="s">
+        <v>206</v>
+      </c>
+      <c r="E7" s="24" t="s">
+        <v>207</v>
+      </c>
+      <c r="F7" s="24" t="s">
+        <v>208</v>
+      </c>
+      <c r="G7" s="24" t="s">
+        <v>209</v>
+      </c>
+      <c r="H7" s="96"/>
+      <c r="I7" s="96"/>
+      <c r="J7" s="26">
+        <f>_xlfn.XLOOKUP(Table_Input_DataQuality[[#This Row],[Temporal representativeness]],[2]!Table_SourceData_DataQuality_TemporalRepresentativeness[ID],[2]!Table_SourceData_DataQuality_TemporalRepresentativeness[Score])+_xlfn.XLOOKUP(Table_Input_DataQuality[[#This Row],[Spatial resolution]],[2]!Table_SourceData_DataQuality_SpatialRepresentativeness[ID],[2]!Table_SourceData_DataQuality_SpatialRepresentativeness[Score])+_xlfn.XLOOKUP(Table_Input_DataQuality[[#This Row],[Sample size]],[2]!Table_SourceData_DataQuality_SampleSize[ID],[2]!Table_SourceData_DataQuality_SampleSize[Score])</f>
+        <v>12</v>
+      </c>
+    </row>
+  </sheetData>
+  <dataValidations count="3">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="G7" xr:uid="{023991CC-ACAB-4CCA-BF6E-5B4983A34A68}">
+      <formula1>INDIRECT("Table_SourceData_DataQuality_SampleSize[ID]")</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="F7" xr:uid="{D85C1557-4D18-4B87-9B82-D7755813B359}">
+      <formula1>INDIRECT("Table_SourceData_DataQuality_SpatialRepresentativeness[ID]")</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="E7" xr:uid="{D7C04A1D-8792-4527-94D7-0D838FC14D35}">
+      <formula1>INDIRECT("Table_SourceData_DataQuality_TemporalRepresentativeness[ID]")</formula1>
+    </dataValidation>
+  </dataValidations>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <tableParts count="1">
+    <tablePart r:id="rId1"/>
+  </tableParts>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{FD7772F5-D62F-448B-BE59-D05AA2138B09}">
   <sheetPr>
     <tabColor theme="2" tint="-0.499984740745262"/>
@@ -11291,6 +11653,10 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<AFEJSONBlob xmlns="http://schemas.advancedformulaenvironment.officeapps.live.com/afejsonblob/1.0">ewAiAHMAYwBoAGUAbQBhACIAOgAiAGgAdAB0AHAAOgAvAC8AcwBjAGgAZQBtAGEAcwAuAGEAZAB2AGEAbgBjAGUAZABmAG8AcgBtAHUAbABhAGUAbgB2AGkAcgBvAG4AbQBlAG4AdAAuAG8AZgBmAGkAYwBlAGEAcABwAHMALgBsAGkAdgBlAC4AYwBvAG0ALwBhAGYAZQBwAHIAbwBqAGUAYwB0AHMALwAwAC4AMgAiACwAIgBmAGkAbABlAHMAIgA6AFsAewAiAHAAYQB0AGgAIgA6ACIALwBwAHIAbwBqAGUAYwB0AHMALwBXAG8AcgBrAGIAbwBvAGsAIgAsACIAdABlAHgAdAAiADoAIgAvAC8AIAAtAC0ALQAgAFcAbwByAGsAYgBvAG8AawAgAG0AbwBkAHUAbABlACAALQAtAC0AXABuAC8ALwAgAEEAIABmAGkAbABlACAAbwBmACAAbgBhAG0AZQAgAGQAZQBmAGkAbgBpAHQAaQBvAG4AcwAgAG8AZgAgAHQAaABlACAAZgBvAHIAbQA6AFwAbgAvAC8AIAAgACAAIABuAGEAbQBlACAAPQAgAGQAZQBmAGkAbgBpAHQAaQBvAG4AOwBcAG4AIgB9ACwAewAiAHAAYQB0AGgAIgA6ACIALwBwAHIAbwBqAGUAYwB0AHMALwBDAG8AbQBtAG8AbgBfAEUAcQB1AGEAdABpAG8AbgBzACIALAAiAHQAZQB4AHQAIgA6ACIAXABuAC8AKgAgAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuAEMAbwBtAG0AbwBuAF8AQwBvAG4AdgBlAHIAdABOADIATwBUAG8AQwBPADIAZQBcAG4AQwBvAG4AdgBlAHIAdAAgAG4AaQB0AHIAbwB1AHMAIABvAHgAaQBkAGUAIABlAG0AaQBzAHMAaQBvAG4AcwAgAHQAbwAgAGMAYQByAGIAbwBuACAAZABpAG8AeABpAGQAZQAgAGUAcQB1AGkAdgBhAGwAZQBuAHQAIABlAG0AaQBzAHMAaQBvAG4AcwBcAG4ARQBOADIATwAgAEMATwAyAGUAXABuAHQAIABDAE8AMgBlAFwAbgBFAE4AMgBPADoAIABuAGkAdAByAG8AdQBzACAAbwB4AGkAZABlACAAZQBtAGkAcwBzAGkAbwBuAHMAIAAoAHQAIABOADIATwApAFwAbgBHAFcAUABOADIATwA6ACAAZwBsAG8AYgBhAGwAIAB3AGEAcgBtAGkAbgBnACAAcABvAHQAZQBuAHQAaQBhAGwAIABmAG8AcgAgAG4AaQB0AHIAbwB1AHMAIABvAHgAaQBkAGUAIAAoAHQAIABDAE8AMgAtAGUAIAAvACAAdAAgAE4AMgBPACkAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AKgAvAFwAbgBcAG4AXABuAEMAbwBtAG0AbwBuAF8AQwBvAG4AdgBlAHIAdABOADIATwBUAG8AQwBPADIAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABFAF8ATgAyAE8ALAAgAEcAVwBQAF8ATgAyAE8ALABcAG4AIAAgACAAIABFAF8ATgAyAE8AIAAqACAARwBXAFAAXwBOADIATwBcAG4AIAAgACkAXABuADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAEMAbwBuAHYAZQByAHQATgAyAE8AVABvAEMATwAyAGUAXwBUAGkAdABsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAEMAbwBuAHYAZQByAHQAIABuAGkAdAByAG8AdQBzACAAbwB4AGkAZABlACAAZQBtAGkAcwBzAGkAbwBuAHMAIAB0AG8AIABjAGEAcgBiAG8AbgAgAGQAaQBvAHgAaQBkAGUAIABlAHEAdQBpAHYAYQBsAGUAbgB0ACAAZQBtAGkAcwBzAGkAbwBuAHMAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AQwBvAG4AdgBlAHIAdABOADIATwBUAG8AQwBPADIAZQBfAFYAYQByAGkAYQBiAGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIARQBOADIATwAgAEMATwAyAGUAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AQwBvAG4AdgBlAHIAdABOADIATwBUAG8AQwBPADIAZQBfAFUAbgBpAHQAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAHQAIABDAE8AMgBlAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAEMAbwBuAHYAZQByAHQATgAyAE8AVABvAEMATwAyAGUAXwBOAEkAUgBSAGUAZgBlAHIAZQBuAGMAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AQwBvAG4AdgBlAHIAdABOADIATwBUAG8AQwBPADIAZQBfAEwAYQB0AGUAeABFAHEAdQBhAHQAaQBvAG4AXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAEMATwAyAF8AZQAgAD0AIABFAF8AewBOADIATwB9ACAAXABcAHQAaQBtAGUAcwAgAEcAVwBQAF8AewBOADIATwB9AFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAEMAbwBuAHYAZQByAHQATgAyAE8AVABvAEMATwAyAGUAXwBBAHIAZwB1AG0AZQBuAHQAcwBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABNAEEASwBFAEEAUgBSAEEAWQAoADIALAAgADIALAAgAFwAbgAgACAAIAAgACAAIABMAEEATQBCAEQAQQAoAHIALABjACwAIABcAG4AIAAgACAAIAAgACAAIAAgAEkATgBEAEUAWAAoAHsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEUATgAyAE8AXAAiACwAXAAiAE4AaQB0AHIAbwB1AHMAIABvAHgAaQBkAGUAIABlAG0AaQBzAHMAaQBvAG4AcwAgACgAdAAgAE4AMgBPACkAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEcAVwBQAE4AMgBPAFwAIgAsAFwAIgBHAGwAbwBiAGEAbAAgAHcAYQByAG0AaQBuAGcAIABwAG8AdABlAG4AdABpAGEAbAAgAGYAbwByACAAbgBpAHQAcgBvAHUAcwAgAG8AeABpAGQAZQAgACgAdAAgAEMATwAyAC0AZQAgAC8AIAB0ACAATgAyAE8AKQBcACIAXABuACAAIAAgACAAIAAgACAAIAB9ACwAIAByACwAIABjACkAXABuACAAIAAgACAAIAAgACkAXABuACAAIAAgACAAKQBcAG4AIAAgACkAOwBcAG4AXABuAC8AKgAgAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuAEMAbwBtAG0AbwBuAF8AQwBvAG4AdgBlAHIAdABDAEgANABUAG8AQwBPADIAZQBcAG4AQwBvAG4AdgBlAHIAdAAgAG0AZQB0AGgAYQBuAGUAIABlAG0AaQBzAHMAaQBvAG4AcwAgAHQAbwAgAGMAYQByAGIAbwBuACAAZABpAG8AeABpAGQAZQAgAGUAcQB1AGkAdgBhAGwAZQBuAHQAIABlAG0AaQBzAHMAaQBvAG4AcwBcAG4ARQBDAEgANAAgAEMATwAyAGUAXABuAHQAIABDAE8AMgBlAFwAbgBFAEMASAA0ADoAIABtAGUAdABoAGEAbgBlACAAZQBtAGkAcwBzAGkAbwBuAHMAIAAoAHQAIABDAEgANAApAFwAbgBHAFcAUABDAEgANAA6ACAAZwBsAG8AYgBhAGwAIAB3AGEAcgBtAGkAbgBnACAAcABvAHQAZQBuAHQAaQBhAGwAIABmAG8AcgAgAG0AZQB0AGgAYQBuAGUAIAAoAHQAIABDAE8AMgAtAGUAIAAvACAAdAAgAEMASAA0ACkAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AKgAvAFwAbgBcAG4AXABuAEMAbwBtAG0AbwBuAF8AQwBvAG4AdgBlAHIAdABDAEgANABUAG8AQwBPADIAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABFAF8AQwBIADQALAAgAEcAVwBQAF8AQwBIADQALABcAG4AIAAgACAAIABFAF8AQwBIADQAIAAqACAARwBXAFAAXwBDAEgANABcAG4AIAAgACkAXABuADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAEMAbwBuAHYAZQByAHQAQwBIADQAVABvAEMATwAyAGUAXwBUAGkAdABsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAEMAbwBuAHYAZQByAHQAIABtAGUAdABoAGEAbgBlACAAZQBtAGkAcwBzAGkAbwBuAHMAIAB0AG8AIABjAGEAcgBiAG8AbgAgAGQAaQBvAHgAaQBkAGUAIABlAHEAdQBpAHYAYQBsAGUAbgB0ACAAZQBtAGkAcwBzAGkAbwBuAHMAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AQwBvAG4AdgBlAHIAdABDAEgANABUAG8AQwBPADIAZQBfAFYAYQByAGkAYQBiAGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIARQBDAEgANAAgAEMATwAyAGUAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AQwBvAG4AdgBlAHIAdABDAEgANABUAG8AQwBPADIAZQBfAFUAbgBpAHQAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAHQAIABDAE8AMgBlAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAEMAbwBuAHYAZQByAHQAQwBIADQAVABvAEMATwAyAGUAXwBOAEkAUgBSAGUAZgBlAHIAZQBuAGMAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AQwBvAG4AdgBlAHIAdABDAEgANABUAG8AQwBPADIAZQBfAEwAYQB0AGUAeABFAHEAdQBhAHQAaQBvAG4AXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAEMATwAyAF8AZQAgAD0AIABFAF8AewBDAEgANAB9ACAAXABcAHQAaQBtAGUAcwAgAEcAVwBQAF8AewBDAEgANAB9AFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAEMAbwBuAHYAZQByAHQAQwBIADQAVABvAEMATwAyAGUAXwBBAHIAZwB1AG0AZQBuAHQAcwBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABNAEEASwBFAEEAUgBSAEEAWQAoADIALAAgADIALAAgAFwAbgAgACAAIAAgACAAIABMAEEATQBCAEQAQQAoAHIALABjACwAIABcAG4AIAAgACAAIAAgACAAIAAgAEkATgBEAEUAWAAoAHsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEUAQwBIADQAXAAiACwAXAAiAE0AZQB0AGgAYQBuAGUAIABlAG0AaQBzAHMAaQBvAG4AcwAgACgAdAAgAEMASAA0ACkAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEcAVwBQAEMASAA0AFwAIgAsAFwAIgBHAGwAbwBiAGEAbAAgAHcAYQByAG0AaQBuAGcAIABwAG8AdABlAG4AdABpAGEAbAAgAGYAbwByACAAbQBlAHQAaABhAG4AZQAgACgAdAAgAEMATwAyAC0AZQAgAC8AIAB0ACAAQwBIADQAKQBcACIAXABuACAAIAAgACAAIAAgACAAIAB9ACwAIAByACwAIABjACkAXABuACAAIAAgACAAIAAgACkAXABuACAAIAAgACAAKQBcAG4AIAAgACkAOwAiAH0ALAB7ACIAcABhAHQAaAAiADoAIgAvAHAAcgBvAGoAZQBjAHQAcwAvAEMAbwBtAG0AbwBuAF8ASQBuAHAAdQB0AEYAdQBuAGMAdABpAG8AbgBzACIALAAiAHQAZQB4AHQAIgA6ACIAVQB0AGkAbABpAHQAeQBfAEcAZQB0AEEAcgByAGEAeQBUAGEAYgBsAGUAUgBvAHcAUwB0AGEAcgB0AE4AdQBtAGIAZQByAFwAbgA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAAVABhAGIAbABlAGgAZQBhAGQAZQByAEMAZQBsAGwALABSAG8AdwBzAEIAZQB0AHcAZQBlAG4ASABlAGEAZABlAHIAYQBuAGQAQQByAHIAYQB5ACwAXABuACAAIAAgACAAUgBPAFcAKABUAGEAYgBsAGUAaABlAGEAZABlAHIAQwBlAGwAbAApACAAKwAgAFIAbwB3AHMAQgBlAHQAdwBlAGUAbgBIAGUAYQBkAGUAcgBhAG4AZABBAHIAcgBhAHkAIAAtACAAMQBcAG4AKQA7AFwAbgBcAG4AVQB0AGkAbABpAHQAeQBfAEcAZQB0AEEAcgByAGEAeQBUAGEAYgBsAGUAQwBvAGwAdQBtAG4AUwB0AGEAcgB0AE4AdQBtAGIAZQByAFwAbgA9AEwAQQBNAEIARABBACgAXABuACAAIABUAGEAYgBsAGUASABlAGEAZABlAHIAQwBlAGwAbAAsAFwAbgAgACAAQwBPAEwAVQBNAE4AKABUAGEAYgBsAGUASABlAGEAZABlAHIAQwBlAGwAbAApAFwAbgApADsAXABuAFwAbgBVAHQAaQBsAGkAdAB5AF8ARABpAHMAcABsAGEAeQBBAHIAcgBhAHkASQBuAFQAYQBiAGwAZQBcAG4APQBMAEEATQBCAEQAQQAoAFwAbgAgAEEAcgByAGEAeQBEAGEAdABhACwAIABUAGEAYgBsAGUAaABlAGEAZABlAHIAQwBlAGwAbAAsACAAUgBvAHcAcwBCAGUAdAB3AGUAZQBuAEgAZQBhAGQAZQByAGEAbgBkAEEAcgByAGEAeQAsACAAWwBDAG8AbAB1AG0AbgBzAEIAZQB0AHcAZQBlAG4ASABlAGEAZABlAHIAQQBuAGQAQQByAHIAYQB5AF0ALABcAG4AIABJAEYARQBSAFIATwBSACgAXABuACAAIAAgACAAIABJAE4ARABFAFgAKABcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAVQBOAEkAUQBVAEUAKABBAHIAcgBhAHkARABhAHQAYQApACwAIABcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAUgBPAFcAKAApAC0AVQB0AGkAbABpAHQAeQBfAEcAZQB0AEEAcgByAGEAeQBUAGEAYgBsAGUAUgBvAHcAUwB0AGEAcgB0AE4AdQBtAGIAZQByACgAVABhAGIAbABlAGgAZQBhAGQAZQByAEMAZQBsAGwALAAgAFIAbwB3AHMAQgBlAHQAdwBlAGUAbgBIAGUAYQBkAGUAcgBhAG4AZABBAHIAcgBhAHkAKQAsACAAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgAEMATwBMAFUATQBOACgAKQAtAFUAdABpAGwAaQB0AHkAXwBHAGUAdABBAHIAcgBhAHkAVABhAGIAbABlAEMAbwBsAHUAbQBuAFMAdABhAHIAdABOAHUAbQBiAGUAcgAoAFQAYQBiAGwAZQBoAGUAYQBkAGUAcgBDAGUAbABsACkAIAArAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIABJAEYAKABJAFMATwBNAEkAVABUAEUARAAoAEMAbwBsAHUAbQBuAHMAQgBlAHQAdwBlAGUAbgBIAGUAYQBkAGUAcgBBAG4AZABBAHIAcgBhAHkAKQAsACAAMQAsACAAQwBvAGwAdQBtAG4AcwBCAGUAdAB3AGUAZQBuAEgAZQBhAGQAZQByAEEAbgBkAEEAcgByAGEAeQApAFwAbgAgACAAIAAgACAAIAAgACAAKQAsACAAXAAiAFwAIgBcAG4AIAAgACAAIAApAFwAbgApADsAXABuAFwAbgBVAHQAaQBsAGkAdAB5AF8ATABvAG8AawB1AHAAVgBhAGwAdQBlAEkAbgBUAGEAYgBsAGUAXABuAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABMAG8AbwBrAHUAcABWAGEAbAB1AGUALAAgAEwAbwBvAGsAdQBwAEEAcgByAGEAeQAsACAAUgBlAHQAdQByAG4AQQByAHIAYQB5ACwAXABuACAAIAAgACAAWABMAE8ATwBLAFUAUAAoAEwAbwBvAGsAdQBwAFYAYQBsAHUAZQAsACAATABvAG8AawB1AHAAQQByAHIAYQB5ACwAIABSAGUAdAB1AHIAbgBBAHIAcgBhAHkALAAgAFwAIgBcACIAKQBcAG4AKQA7AFwAbgBcAG4AVQB0AGkAbABpAHQAeQBfAEwAbwBvAGsAdQBwAFYAYQBsAHUAZQBJAG4AVABhAGIAbABlAE4AdQBtAGIAZQByAFwAbgA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAATABvAG8AawB1AHAAVgBhAGwAdQBlACwAIABMAG8AbwBrAHUAcABBAHIAcgBhAHkALAAgAFIAZQB0AHUAcgBuAEEAcgByAGEAeQAsAFwAbgAgACAAIAAgAEkARgAoAEkAUwBOAFUATQBCAEUAUgAoAFwAbgAgACAAIAAgACAAIAAgACAAWABMAE8ATwBLAFUAUAAoAEwAbwBvAGsAdQBwAFYAYQBsAHUAZQAsACAATABvAG8AawB1AHAAQQByAHIAYQB5ACwAIABSAGUAdAB1AHIAbgBBAHIAcgBhAHkALAAgAFwAIgBcACIAKQBcAG4AIAAgACAAIAApACwAIABYAEwATwBPAEsAVQBQACgATABvAG8AawB1AHAAVgBhAGwAdQBlACwAIABMAG8AbwBrAHUAcABBAHIAcgBhAHkALAAgAFIAZQB0AHUAcgBuAEEAcgByAGEAeQAsACAAXAAiAFwAIgApACwAIAAwACkAXABuACkAOwBcAG4AXABuAFUAdABpAGwAaQB0AHkAXwBMAG8AbwBrAHUAcABWAGEAbAB1AGUASQBuAFQAYQBiAGwAZQBUAHcAbwBDAG8AbAB1AG0AbgBzAFwAbgA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAATABvAG8AawB1AHAAVgBhAGwAdQBlADEALAAgAEwAbwBvAGsAdQBwAFYAYQBsAHUAZQAyACwAIABMAG8AbwBrAHUAcABBAHIAcgBhAHkAMQAsACAATABvAG8AawB1AHAAQQByAHIAYQB5ADIALAAgAFIAZQB0AHUAcgBuAEEAcgByAGEAeQAsACAAWwBWAGEAbAB1AGUASQBGAEYAYQBsAHMAZQBdACwAXABuACAAIAAgACAAWABMAE8ATwBLAFUAUAAoADEALAAgACgATABvAG8AawB1AHAAQQByAHIAYQB5ADEAPQBMAG8AbwBrAHUAcABWAGEAbAB1AGUAMQApACoAKABMAG8AbwBrAHUAcABBAHIAcgBhAHkAMgA9AEwAbwBvAGsAdQBwAFYAYQBsAHUAZQAyACkALAAgAFIAZQB0AHUAcgBuAEEAcgByAGEAeQAsACAASQBGACgASQBTAE8ATQBJAFQAVABFAEQAKABWAGEAbAB1AGUASQBGAEYAYQBsAHMAZQApACwAIABcACIAXAAiACwAIABWAGEAbAB1AGUASQBGAEYAYQBsAHMAZQApACkAXABuACkAOwBcAG4AXABuAFUAdABpAGwAaQB0AHkAXwBMAG8AbwBrAHUAcABWAGEAbAB1AGUASQBuAFQAYQBiAGwAZQBPAG4AZQBDAG8AbAB1AG0AbgBBAG4AZABIAGUAYQBkAGUAcgBcAG4APQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAEwAbwBvAGsAdQBwAFYAYQBsAHUAZQAxACwAIABMAG8AbwBrAHUAcABWAGEAbAB1AGUAMgAsACAATABvAG8AawB1AHAAQQByAHIAYQB5ADEALAAgAEwAbwBvAGsAdQBwAEEAcgByAGEAeQAyACwAIABSAGUAdAB1AHIAbgBBAHIAcgBhAHkALAAgAFsAVgBhAGwAdQBlAEkAZgBGAGEAbABzAGUAXQAsAFwAbgAgACAAIAAgAEkARgBFAFIAUgBPAFIAKABcAG4AIAAgACAAIAAgACAAIAAgAFgATABPAE8ASwBVAFAAKABMAG8AbwBrAHUAcABWAGEAbAB1AGUAMQAsACAATABvAG8AawB1AHAAQQByAHIAYQB5ADEALABcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAWABMAE8ATwBLAFUAUAAoAEwAbwBvAGsAdQBwAFYAYQBsAHUAZQAyACwAIABMAG8AbwBrAHUAcABBAHIAcgBhAHkAMgAsACAAUgBlAHQAdQByAG4AQQByAHIAYQB5ACkAXABuACAAIAAgACAAIAAgACAAIAApACwAXABuACAAIAAgACAAIAAgACAAIABJAEYAKABJAFMATwBNAEkAVABUAEUARAAoAFYAYQBsAHUAZQBJAGYARgBhAGwAcwBlACkALAAgAFwAIgBcACIALAAgAFYAYQBsAHUAZQBJAGYARgBhAGwAcwBlACkAXABuACAAIAAgACAAKQBcAG4AKQA7AFwAbgBcAG4AVQB0AGkAbABpAHQAeQBfAFMAcABsAGkAdABTAHQAcgBpAG4AZwBJAG4AdABvAEEAcgByAGEAeQBcAG4APQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAEMAZQBsAGwALAAgAEQAZQBsAGkAbQBpAHQAZQByACwAIABbAEMAaABhAHIAYQBjAHQAZQByAFQAbwBSAGUAbQBvAHYAZQAxAF0ALAAgAFsAQwBoAGEAcgBhAGMAdABlAHIAVABvAFIAZQBtAG8AdgBlADIAXQAsAFwAbgAgACAAIAAgACAAIAAgACAARgBJAEwAVABFAFIAWABNAEwAKABcAG4AIAAgACAAIAAgACAAIAAgAFwAIgA8AHQAPgA8AHMAPgBcACIAIAAmAFwAbgAgACAAIAAgACAAIAAgACAAUwBVAEIAUwBUAEkAVABVAFQARQAoAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIABTAFUAQgBTAFQASQBUAFUAVABFACgAUwBVAEIAUwBUAEkAVABVAFQARQAoAEMAZQBsAGwALABDAGgAYQByAGEAYwB0AGUAcgBUAG8AUgBlAG0AbwB2AGUAMQAsAFwAIgBcACIAKQAsAEMAaABhAHIAYQBjAHQAZQByAFQAbwBSAGUAbQBvAHYAZQAyACwAXAAiAFwAIgApACwAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgAEQAZQBsAGkAbQBpAHQAZQByACwAXAAiADwALwBzAD4APABzAD4AXAAiAFwAbgAgACAAIAAgACAAIAAgACAAKQAgACYAXABuACAAIAAgACAAIAAgACAAIABcACIAPAAvAHMAPgA8AC8AdAA+AFwAIgAsAFwAbgAgACAAIAAgACAAIAAgACAAXAAiAC8ALwBzAFwAIgBcAG4AIAAgACAAIAApAFwAbgApADsAXABuAFwAbgBVAHQAaQBsAGkAdAB5AF8ARwBlAHQAQwBsAGkAbQBhAHQAZQBaAG8AbgBlAFwAbgA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAAYQB2AGcAVABlAG0AcAAsAGEAdgBnAFIAYQBpAG4ALABmAHIAbwBzAHQARABhAHkAcwAsAGUAbABlAHYALABtAGEAcABfAHAAZQB0ACwAXABuACAAIAAgACAAbQBpAG4AVABlAG0AcABBAHIAcgBhAHkALABtAGEAeABUAGUAbQBwAEEAcgByAGEAeQAsAFwAbgAgACAAIAAgAG0AaQBuAFIAYQBpAG4AZgBhAGwAbABBAHIAcgBhAHkALABtAGEAeABSAGEAaQBuAGYAYQBsAGwAQQByAHIAYQB5ACwAXABuACAAIAAgACAAbQBpAG4ARgByAG8AcwB0AEEAcgByAGEAeQAsAG0AYQB4AEYAcgBvAHMAdABBAHIAcgBhAHkALABcAG4AIAAgACAAIABtAGkAbgBFAGwAZQB2AGEAdABpAG8AbgBBAHIAcgBhAHkALABtAGEAeABFAGwAZQB2AGEAdABpAG8AbgBBAHIAcgBhAHkALABcAG4AIAAgACAAIABtAGkAbgBQAEUAVABBAHIAcgBhAHkALABtAGEAeABQAEUAVABBAHIAcgBhAHkALABcAG4AIAAgACAAIABjAGwAaQBtAGEAdABlAFoAbwBuAGUAQQByAHIAYQB5ACwAXABuACAAIAAgACAATABFAFQAKABcAG4AIAAgACAAIAAgACAAIAAgAG0AYQBzAGsALABcAG4AIAAgACAAIAAgACAAIAAgACgAVgBBAEwAVQBFACgAbQBpAG4AVABlAG0AcABBAHIAcgBhAHkAKQA8AD0AYQB2AGcAVABlAG0AcAApACoAXABuACAAIAAgACAAIAAgACAAIAAoAFYAQQBMAFUARQAoAG0AYQB4AFQAZQBtAHAAQQByAHIAYQB5ACkAPgA9AGEAdgBnAFQAZQBtAHAAKQAqAFwAbgAgACAAIAAgACAAIAAgACAAKABWAEEATABVAEUAKABtAGkAbgBSAGEAaQBuAGYAYQBsAGwAQQByAHIAYQB5ACkAPAA9AGEAdgBnAFIAYQBpAG4AKQAqAFwAbgAgACAAIAAgACAAIAAgACAAKABWAEEATABVAEUAKABtAGEAeABSAGEAaQBuAGYAYQBsAGwAQQByAHIAYQB5ACkAPgA9AGEAdgBnAFIAYQBpAG4AKQAqAFwAbgAgACAAIAAgACAAIAAgACAAKABWAEEATABVAEUAKABtAGkAbgBGAHIAbwBzAHQAQQByAHIAYQB5ACkAPAA9AGYAcgBvAHMAdABEAGEAeQBzACkAKgBcAG4AIAAgACAAIAAgACAAIAAgACgAVgBBAEwAVQBFACgAbQBhAHgARgByAG8AcwB0AEEAcgByAGEAeQApAD4APQBmAHIAbwBzAHQARABhAHkAcwApACoAXABuACAAIAAgACAAIAAgACAAIAAoAFYAQQBMAFUARQAoAG0AaQBuAEUAbABlAHYAYQB0AGkAbwBuAEEAcgByAGEAeQApADwAPQBlAGwAZQB2ACkAKgBcAG4AIAAgACAAIAAgACAAIAAgACgAVgBBAEwAVQBFACgAbQBhAHgARQBsAGUAdgBhAHQAaQBvAG4AQQByAHIAYQB5ACkAPgA9AGUAbABlAHYAKQAqAFwAbgAgACAAIAAgACAAIAAgACAAKABWAEEATABVAEUAKABtAGkAbgBQAEUAVABBAHIAcgBhAHkAKQA8AD0AbQBhAHAAXwBwAGUAdAApACoAXABuACAAIAAgACAAIAAgACAAIAAoAFYAQQBMAFUARQAoAG0AYQB4AFAARQBUAEEAcgByAGEAeQApAD4APQBtAGEAcABfAHAAZQB0ACkALABcAG4AIAAgACAAIAAgACAAIAAgAFQAQQBLAEUAKABcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAARgBJAEwAVABFAFIAKABjAGwAaQBtAGEAdABlAFoAbwBuAGUAQQByAHIAYQB5ACwAbQBhAHMAawAsACAAXAAiAE4AbwAgAG0AYQB0AGMAaABcACIAKQAsAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIAAxAFwAbgAgACAAIAAgACAAIAAgACAAKQBcAG4AIAAgACAAIAApAFwAbgApADsAXABuAFwAbgBVAHQAaQBsAGkAdAB5AF8ATABvAG8AawB1AHAASQB0AGUAbQBGAHIAbwBtAE0AaQBuAE0AYQB4AFwAbgA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAATABvAG8AawB1AHAAVgBhAGwAdQBlACwAIABNAGkAbgBBAHIAcgBhAHkALAAgAE0AYQB4AEEAcgByAGEAeQAsACAASQB0AGUAbQBBAHIAcgBhAHkALABcAG4AIAAgACAAIABMAEUAVAAoAFwAbgAgACAAIAAgACAAIAAgACAAbQBhAHMAawAsAFwAbgAgACAAIAAgACAAIAAgACAAKABWAEEATABVAEUAKABNAGkAbgBBAHIAcgBhAHkAKQA8AD0ATABvAG8AawB1AHAAVgBhAGwAdQBlACkAKgBcAG4AIAAgACAAIAAgACAAIAAgACgAVgBBAEwAVQBFACgATQBhAHgAQQByAHIAYQB5ACkAPgA9AEwAbwBvAGsAdQBwAFYAYQBsAHUAZQApACwAXABuACAAIAAgACAAIAAgACAAIABGAEkATABUAEUAUgAoAEkAdABlAG0AQQByAHIAYQB5ACwAIABtAGEAcwBrACwAIABcACIATgBvACAAbQBhAHQAYwBoAFwAIgApAFwAbgAgACAAIAAgACkAXABuACkAOwBcAG4AXABuAFwAbgBVAHQAaQBsAGkAdAB5AF8AUwB1AG0AUQB1AGEAbgB0AGkAdAB5AEYAcgBvAG0AQwByAGkAdABlAHIAaQBhAFwAbgA9AEwAQQBNAEIARABBACgAXABuACAAIABDAHIAaQB0AGUAcgBpAGEAMQAsACAAQwByAGkAdABlAHIAaQBhADEAVAB5AHAAZQBBAHIAcgBhAHkALAAgAFEAdQBhAG4AdABpAHQAeQAsACAAWwBNAHUAbAB0AGkAcABsAGkAZQByAF0ALAAgAFsAQwByAGkAdABlAHIAaQBhADIAXQAsAFsAQwByAGkAdABlAHIAaQBhADIAQQByAHIAYQB5AF0ALABcAG4AIAAgAEwARQBUACgAXABuACAAIAAgACAAbQB1AGwAdABpAHAAbABpAGUAcgAsACAASQBGACgASQBTAE8ATQBJAFQAVABFAEQAKABNAHUAbAB0AGkAcABsAGkAZQByACkALAAxACwATQB1AGwAdABpAHAAbABpAGUAcgApACwAXABuACAAIAAgACAAcQB1AGEAbgB0AGkAdAB5ACwAIABRAHUAYQBuAHQAaQB0AHkAKgBNAHUAbAB0AGkAcABsAGkAZQByACwAXABuACAAIAAgACAAYwByAGkAdABlAHIAaQBhADEALAAtAC0AKABDAHIAaQB0AGUAcgBpAGEAMQBUAHkAcABlAEEAcgByAGEAeQA9AEMAcgBpAHQAZQByAGkAYQAxACkALABcAG4AIAAgACAAIABjAHIAaQB0AGUAcgBpAGEAMgAsAEkARgAoAEkAUwBPAE0ASQBUAFQARQBEACgAQwByAGkAdABlAHIAaQBhADIAKQAsADEALAAtAC0AKABDAHIAaQB0AGUAcgBpAGEAMgBBAHIAcgBhAHkAPQBDAHIAaQB0AGUAcgBpAGEAMgApACkALABcAG4AIAAgACAAIABTAFUATQBQAFIATwBEAFUAQwBUACgAYwByAGkAdABlAHIAaQBhADEAKgBjAHIAaQB0AGUAcgBpAGEAMgAqAHEAdQBhAG4AdABpAHQAeQApAFwAbgAgACAAKQBcAG4AKQA7AFwAbgBcAG4AZwBlAHQATwB2AGUAcgBsAGEAcABwAGkAbgBnAFIAZQBwAG8AcgB0AGkAbgBnAEMAeQBjAGwAZQBzAFwAbgA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAAUAByAG8AZAB1AGMAdABpAG8AbgBDAHkAYwBsAGUAUwB0AGEAcgB0ACwAUAByAG8AZAB1AGMAdABpAG8AbgBDAHkAYwBsAGUARQBuAGQALABSAGUAcABvAHIAdABpAG4AZwBDAHkAYwBsAGUAUwB0AGEAcgB0ACwAXABuACAAIAAgACAATABFAFQAKABcAG4AIAAgACAAIAAgACAAIAAgAFMALABQAHIAbwBkAHUAYwB0AGkAbwBuAEMAeQBjAGwAZQBTAHQAYQByAHQALABcAG4AIAAgACAAIAAgACAAIAAgAEUALABQAHIAbwBkAHUAYwB0AGkAbwBuAEMAeQBjAGwAZQBFAG4AZAAsAFwAbgAgACAAIAAgACAAIAAgACAAbQAsAE0ATwBOAFQASAAoAFIAZQBwAG8AcgB0AGkAbgBnAEMAeQBjAGwAZQBTAHQAYQByAHQAKQAsAFwAbgAgACAAIAAgACAAIAAgACAAZAAsAEQAQQBZACgAUgBlAHAAbwByAHQAaQBuAGcAQwB5AGMAbABlAFMAdABhAHIAdAApACwAXABuACAAIAAgACAAIAAgACAAIABQAGUAcgBpAG8AZABFAG4AZAAsAEwAQQBNAEIARABBACgAcwB0ACwARQBEAEEAVABFACgAcwB0ACwAMQAyACkALQAxACkALABcAG4AIAAgACAAIAAgACAAIAAgAEEALABTAC0AMwA2ADUALABcAG4AIAAgACAAIAAgACAAIAAgAHkAYQAsAFkARQBBAFIAKABBACkALABcAG4AIAAgACAAIAAgACAAIAAgAHkAYgAsAFkARQBBAFIAKABFACkALABcAG4AIAAgACAAIAAgACAAIAAgAGYAaQByAHMAdABZAGUAYQByACwAeQBhACsAKABQAGUAcgBpAG8AZABFAG4AZAAoAEQAQQBUAEUAKAB5AGEALABtACwAZAApACkAPAAgAFMAKQAsAFwAbgAgACAAIAAgACAAIAAgACAAbABhAHMAdABZAGUAYQByACwAeQBiAC0AKABEAEEAVABFACgAeQBiACwAbQAsAGQAKQA+ACAARQApACwAXABuACAAIAAgACAAIAAgACAAIABNAEEAWAAoADAALABsAGEAcwB0AFkAZQBhAHIALQBmAGkAcgBzAHQAWQBlAGEAcgArADEAKQBcAG4AIAAgACAAIAApAFwAbgApADsAXABuAFwAbgBnAGUAdABPAHYAZQByAGwAYQBwAHAAaQBuAGcAUgBlAHAAbwByAHQAaQBuAGcAUABlAHIAaQBvAGQAcwBcAG4APQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAFAAcgBvAGQAdQBjAHQAaQBvAG4AQwB5AGMAbABlAFMAdABhAHIAdAAsAFAAcgBvAGQAdQBjAHQAaQBvAG4AQwB5AGMAbABlAEUAbgBkACwAUgBlAHAAbwByAHQAaQBuAGcAQwB5AGMAbABlAFMAdABhAHIAdAAsAFwAbgAgACAAIAAgAEwARQBUACgAXABuACAAIAAgACAAIAAgACAAIABTACwAUAByAG8AZAB1AGMAdABpAG8AbgBDAHkAYwBsAGUAUwB0AGEAcgB0ACwAXABuACAAIAAgACAAIAAgACAAIABFACwAUAByAG8AZAB1AGMAdABpAG8AbgBDAHkAYwBsAGUARQBuAGQALABcAG4AIAAgACAAIAAgACAAIAAgAG0ALABNAE8ATgBUAEgAKABSAGUAcABvAHIAdABpAG4AZwBDAHkAYwBsAGUAUwB0AGEAcgB0ACkALABcAG4AIAAgACAAIAAgACAAIAAgAGQALABEAEEAWQAoAFIAZQBwAG8AcgB0AGkAbgBnAEMAeQBjAGwAZQBTAHQAYQByAHQAKQAsACAALwAqAGgAZQBsAHAAZQByADoAIABlAG4AZAAgAGQAYQB0AGUAIABmAG8AcgAgAGEAIAByAGUAcABvAHIAdABpAG4AZwAgAHAAZQByAGkAbwBkACAAcwB0AGEAcgB0AGkAbgBnACAAYQB0ACAAYQAgAGcAaQB2AGUAbgAgAGQAYQB0AGUAKgAvAFwAbgAgACAAIAAgACAAIAAgACAAUABlAHIAaQBvAGQARQBuAGQALABMAEEATQBCAEQAQQAoAHMAdAAsAEUARABBAFQARQAoAHMAdAAsADEAMgApAC0AMQApACwAIAAvACoAbwBuAGwAeQAgAG4AZQBlAGQAIAB0AG8AIABsAG8AbwBrACAAYgBhAGMAawAgADMANgA1ACAAZABhAHkAcwAoAG0AYQB4ACAAbwB2AGUAcgBsAGEAcAAgAHcAaQBuAGQAbwB3ACkAKgAvAFwAbgAgACAAIAAgACAAIAAgACAAQQAsAFMALQAzADYANQAsAFwAbgAgACAAIAAgACAAIAAgACAAeQBhACwAWQBFAEEAUgAoAEEAKQAsAFwAbgAgACAAIAAgACAAIAAgACAAeQBiACwAWQBFAEEAUgAoAEUAKQAsACAALwAqAGkAZgAgAHQAaABlACAAYQBuAGMAaABvAHIAIABmAG8AcgAgAHkAYQAgAGUAbgBkAHMAIABiAGUAZgBvAHIAZQAgAFMALABpAHQAIABjAGEAbgAnAHQAIABvAHYAZQByAGwAYQBwADsAIABtAG8AdgBlACAAdABvACAAbgBlAHgAdAAgAHkAZQBhAHIAKgAvAFwAbgAgACAAIAAgACAAIAAgACAAZgBpAHIAcwB0AFkAZQBhAHIALAB5AGEAKwAoAFAAZQByAGkAbwBkAEUAbgBkACgARABBAFQARQAoAHkAYQAsAG0ALABkACkAKQA8AFMAKQAsACAALwAqAGkAZgAgAHQAaABlACAAYQBuAGMAaABvAHIAIABmAG8AcgAgAHkAYgAgAHMAdABhAHIAdABzACAAYQBmAHQAZQByACAARQAsAGkAdAAgAGMAYQBuACcAdAAgAG8AdgBlAHIAbABhAHAAOwAgAG0AbwB2AGUAIAB0AG8AIABwAHIAZQB2AGkAbwB1AHMAIAB5AGUAYQByACoALwBcAG4AIAAgACAAIAAgACAAIAAgAGwAYQBzAHQAWQBlAGEAcgAsAHkAYgAtACgARABBAFQARQAoAHkAYgAsAG0ALABkACkAPgBFACkALABcAG4AIAAgACAAIAAgACAAIAAgAG4ALABNAEEAWAAoADAALABsAGEAcwB0AFkAZQBhAHIALQBmAGkAcgBzAHQAWQBlAGEAcgArADEAKQAsAFwAbgAgACAAIAAgACAAIAAgACAAeQByAHMALABTAEUAUQBVAEUATgBDAEUAKABuACwAMQAsAGYAaQByAHMAdABZAGUAYQByACwAMQApACwAXABuACAAIAAgACAAIAAgACAAIABzAHQAYQByAHQAcwAsAEQAQQBUAEUAKAB5AHIAcwAsAG0ALABkACkALABcAG4AIAAgACAAIAAgACAAIAAgAGUAbgBkAHMALABNAEEAUAAoAHMAdABhAHIAdABzACwAUABlAHIAaQBvAGQARQBuAGQAKQAsAFwAbgAgACAAIAAgACAAIAAgACAAdABhAGcALABJAEYAKABzAHQAYQByAHQAcwA9AFIAZQBwAG8AcgB0AGkAbgBnAEMAeQBjAGwAZQBTAHQAYQByAHQALABcACIAIAAoAFQAaABpAHMAIAByAGUAcABvAHIAdABpAG4AZwAgAGMAeQBjAGwAZQApAFwAIgAsAFwAIgBcACIAKQAsAFwAbgAgACAAIAAgACAAIAAgACAAcwB0AGEAcgB0AHMAVABlAHgAdAAsAFQARQBYAFQAKABzAHQAYQByAHQAcwAsAFwAIgBkAGQAIABtAG0AbQAgAHkAeQB5AHkAXAAiACkALABcAG4AIAAgACAAIAAgACAAIAAgAGUAbgBkAHMAVABlAHgAdAAsAFQARQBYAFQAKABlAG4AZABzACwAXAAiAGQAZAAgAG0AbQBtACAAeQB5AHkAeQBcACIAKQAsAFwAbgAgACAAIAAgACAAIAAgACAAcgBvAHcAcwAsAEkARgAoAG4APQAwACwAXAAiAFwAIgAsAEgAUwBUAEEAQwBLACgAcwB0AGEAcgB0AHMAVABlAHgAdAAgACYAIABcACIAIAB0AG8AIABcACIAIAAmACAAZQBuAGQAcwBUAGUAeAB0ACAAJgAgAHQAYQBnACkAKQAsAFwAbgAgACAAIAAgACAAIAAgACAAcgBvAHcAcwBcAG4AIAAgACAAIAApAFwAbgApADsAXABuAFwAbgBcAG4AVQB0AGkAbABpAHQAeQBfAEQAaQBzAHAAbABhAHkARgB1AG4AYwB0AGkAbwBuAE4AYQBtAGUAXABuAD0ATABBAE0AQgBEAEEAKABGAHUAbgBjAHQAaQBvAG4ALAAgAFQARQBYAFQAQgBFAEYATwBSAEUAKABGAE8AUgBNAFUATABBAFQARQBYAFQAKABGAHUAbgBjAHQAaQBvAG4AKQAsACAAXAAiACgAXAAiACkAKQA7AFwAbgBcAG4AVQB0AGkAbABpAHQAeQBfAEwAbwBvAGsAdQBwAE4AMgBPAEUARgBGAHIAbwBtAFAAcgBvAGQASQByAHIAaQBnAGEAdABpAG8AbgBSAGEAaQBuAGYAYQBsAGwAXABuAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABQAHIAbwBkAHUAYwB0AGkAbwBuAFMAeQBzAHQAZQBtACwAIABJAHIAcgBpAGcAYQB0AGkAbwBuAE0AZQB0AGgAbwBkACwAIABSAGEAaQBuAGYAYQBsAGwAWgBvAG4AZQAsAFwAbgAgACAAIAAgAFAAcgBvAGQAdQBjAHQAaQBvAG4AUwB5AHMAdABlAG0AQQByAHIAYQB5ACwAIABJAHIAcgBpAGcAYQB0AGkAbwBuAE0AZQB0AGgAbwBkAEEAcgByAGEAeQAsACAAUgBhAGkAbgBmAGEAbABsAFoAbwBuAGUAQQByAHIAYQB5ACwAUgBlAHQAdQByAG4AQQByAHIAYQB5ACwAXABuACAAIAAgACAATABFAFQAKABcAG4AIAAgACAAIAAgACAAIAAgAEkAcgByAGkAZwBhAHQAaQBvAG4ATQBlAHQAaABvAGQALAAgAEkARgAoAEkAcgByAGkAZwBhAHQAaQBvAG4ATQBlAHQAaABvAGQAPQBcACIATgBvAHQAIABpAHIAcgBpAGcAYQB0AGUAZABcACIALAAgAFwAIgBOAG8AdAAgAGkAcgByAGkAZwBhAHQAZQBkAFwAIgAsACAAXAAiAEEAbgB5AFwAIgApACwAXABuACAAIAAgACAAIAAgACAAIABSAGEAaQBuAGYAYQBsAGwAWgBvAG4AZQAsACAASQBGACgASQByAHIAaQBnAGEAdABpAG8AbgBNAGUAdABoAG8AZAAgAD0AIABcACIATgBvAHQAIABpAHIAcgBpAGcAYQB0AGUAZABcACIALAAgAFIAYQBpAG4AZgBhAGwAbABaAG8AbgBlACwAIABcACIAQQBuAHkAXAAiACkALABcAG4AIAAgACAAIAAgACAAIAAgAFgATABPAE8ASwBVAFAAKAAxACwAIABcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAKABQAHIAbwBkAHUAYwB0AGkAbwBuAFMAeQBzAHQAZQBtAEEAcgByAGEAeQA9AFAAcgBvAGQAdQBjAHQAaQBvAG4AUwB5AHMAdABlAG0AKQAqAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIAAoAEkAcgByAGkAZwBhAHQAaQBvAG4ATQBlAHQAaABvAGQAQQByAHIAYQB5AD0ASQByAHIAaQBnAGEAdABpAG8AbgBNAGUAdABoAG8AZAApACoAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgACgAUgBhAGkAbgBmAGEAbABsAFoAbwBuAGUAQQByAHIAYQB5AD0AUgBhAGkAbgBmAGEAbABsAFoAbwBuAGUAKQAsACAAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgAFIAZQB0AHUAcgBuAEEAcgByAGEAeQApAFwAbgAgACAAIAAgACkAXABuACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAEMAcgBvAHAAcABpAG4AZwBfAEcAZQB0AEYAcgBhAGMAVwBFAFQAXABuAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABMAGUAYQBjAGgAaQBuAGcAWgBvAG4AZQAsAFwAbgAgACAAIAAgAFAAcgBvAGQAdQBjAHQAaQBvAG4AUwB5AHMAdABlAG0ALABcAG4AIAAgACAAIABMAGUAYQBjAGgAaQBuAGcAWgBvAG4AZQBMAG8AbwBrAHUAcAAsAFwAbgAgACAAIAAgAEwAZQBhAGMAaABpAG4AZwBaAG8AbgBlAEYAcgBhAGMAVwBFAFQATABvAG8AawB1AHAALABcAG4AIAAgACAAIABQAHIAbwBkAHUAYwB0AGkAbwBuAFMAeQBzAHQAZQBtAEwAbwBvAGsAdQBwACwAXABuACAAIAAgACAAUAByAG8AZAB1AGMAdABpAG8AbgBTAHkAcwB0AGUAbQBGAHIAYQBjAFcARQBUAEwAbwBvAGsAdQBwACwAXABuACAAIAAgACAATABFAFQAKABcAG4AIAAgACAAIAAgACAAIAAgAEwAZQBhAGMAaABpAG4AZwBaAG8AbgBlAEYAcgBhAGMAVwBFAFQALAAgAFwAbgAgACAAIAAgACAAIAAgACAAQwBvAG0AbQBvAG4AXwBJAG4AcAB1AHQARgB1AG4AYwB0AGkAbwBuAHMALgBVAHQAaQBsAGkAdAB5AF8ATABvAG8AawB1AHAAVgBhAGwAdQBlAEkAbgBUAGEAYgBsAGUATgB1AG0AYgBlAHIAKABcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAATABlAGEAYwBoAGkAbgBnAFoAbwBuAGUALABMAGUAYQBjAGgAaQBuAGcAWgBvAG4AZQBMAG8AbwBrAHUAcAAsAEwAZQBhAGMAaABpAG4AZwBaAG8AbgBlAEYAcgBhAGMAVwBFAFQATABvAG8AawB1AHAAXABuACAAIAAgACAAIAAgACAAIAApACwAXABuACAAIAAgACAAIAAgACAAIABQAHIAbwBkAHUAYwB0AGkAbwBuAFMAeQBzAHQAZQBtAEYAcgBhAGMAVwBFAFQALAAgAFwAbgAgACAAIAAgACAAIAAgACAAQwBvAG0AbQBvAG4AXwBJAG4AcAB1AHQARgB1AG4AYwB0AGkAbwBuAHMALgBVAHQAaQBsAGkAdAB5AF8ATABvAG8AawB1AHAAVgBhAGwAdQBlAEkAbgBUAGEAYgBsAGUATgB1AG0AYgBlAHIAKABcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAUAByAG8AZAB1AGMAdABpAG8AbgBTAHkAcwB0AGUAbQAsAFAAcgBvAGQAdQBjAHQAaQBvAG4AUwB5AHMAdABlAG0ATABvAG8AawB1AHAALABQAHIAbwBkAHUAYwB0AGkAbwBuAFMAeQBzAHQAZQBtAEYAcgBhAGMAVwBFAFQATABvAG8AawB1AHAAXABuACAAIAAgACAAIAAgACAAIAApACwAXABuACAAIAAgACAAIAAgACAAIABJAEYAKABMAGUAYQBjAGgAaQBuAGcAWgBvAG4AZQBGAHIAYQBjAFcARQBUACAAKwAgAFAAcgBvAGQAdQBjAHQAaQBvAG4AUwB5AHMAdABlAG0ARgByAGEAYwBXAEUAVAA+ADAALAAgADEALAAgADAAKQBcAG4AIAAgACAAIAApACkAOwBcAG4AXABuAFwAbgBVAHQAaQBsAGkAdAB5AF8AQwBvAG4AdgBlAHIAdABTAHQAYQB0AGUAQwBvAG0AbQBvAG4ATgBhAG0AZQBUAG8AQQBiAGIAcgBlAHYAaQBhAHQAaQBvAG4AXABuAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABTAHQAYQB0AGUAQwBvAG0AbQBvAG4ATgBhAG0AZQAsAFwAbgAgACAAIAAgAFMAdABhAHQAZQBDAG8AbQBtAG8AbgBOAGEAbQBlAEEAcgByAGEAeQAsACAAUwB0AGEAdABlAEEAYgBiAHIAZQB2AGkAYQB0AGkAbwBuAEEAcgByAGEAeQAsAFwAbgAgACAAIAAgAFgATABPAE8ASwBVAFAAKABTAHQAYQB0AGUAQwBvAG0AbQBvAG4ATgBhAG0AZQAsACAAUwB0AGEAdABlAEMAbwBtAG0AbwBuAE4AYQBtAGUAQQByAHIAYQB5ACwAIABTAHQAYQB0AGUAQQBiAGIAcgBlAHYAaQBhAHQAaQBvAG4AQQByAHIAYQB5ACwAIABcACIAXAAiACkAXABuACkAOwBcAG4AXABuAFUAdABpAGwAaQB0AHkAXwBTAG8AdQByAGMAZQBIAHkAcABlAHIAbABpAG4AawBcAG4APQBMAEEATQBCAEQAQQAoAFQAYQByAGcAZQB0AEMAZQBsAGwALABcAG4AIAAgAEwARQBUACgAXABuACAAIAAgACAAcwBoACwAIABUAEUAWABUAEEARgBUAEUAUgAoAEMARQBMAEwAKABcACIAZgBpAGwAZQBuAGEAbQBlAFwAIgAsACAAVABhAHIAZwBlAHQAQwBlAGwAbAApACwAIABcACIAXQBcACIAKQAsAFwAbgAgACAAIAAgAGEAZABkAHIALAAgAEMARQBMAEwAKABcACIAYQBkAGQAcgBlAHMAcwBcACIALAAgAFQAYQByAGcAZQB0AEMAZQBsAGwAKQAsAFwAbgAgACAAIAAgAFwAIgAjACcAXAAiACAAJgAgAHMAaAAgACYAIABcACIAJwAhAFwAIgAgACYAIABhAGQAZAByAFwAbgAgACAAKQBcAG4AKQA7AFwAbgBcAG4AVQB0AGkAbABpAHQAeQBfAFMAbwB1AHIAYwBlAEgAeQBwAGUAcgBsAGkAbgBrAEQAaQBmAGYAZQByAGUAbgB0AFMAaABlAGUAdABcAG4APQBMAEEATQBCAEQAQQAoAFQAYQByAGcAZQB0AEMAZQBsAGwALABcAG4AIAAgAEwARQBUACgAXABuACAAIAAgACAAcwBoACwAIABUAEUAWABUAEEARgBUAEUAUgAoAEMARQBMAEwAKABcACIAZgBpAGwAZQBuAGEAbQBlAFwAIgAsACAAVABhAHIAZwBlAHQAQwBlAGwAbAApACwAIABcACIAXQBcACIAKQAsAFwAbgAgACAAIAAgAGEAZABkAHIALAAgAEMARQBMAEwAKABcACIAYQBkAGQAcgBlAHMAcwBcACIALAAgAFQAYQByAGcAZQB0AEMAZQBsAGwAKQAsAFwAbgAgACAAIAAgAFwAIgAjAFwAIgAgACYAIABhAGQAZAByAFwAbgAgACAAKQBcAG4AKQA7AFwAbgBcAG4AVQB0AGkAbABpAHQAeQBfAEQAaQBzAHAAbABhAHkAQQByAGcAdQBtAGUAbgB0AHMAXwAxAF8AMgBcAG4APQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAEEAcgBnAHUAbQBlAG4AdABzAEEAcgByAGEAeQAsAFwAbgAgACAAIAAgAEMASABPAE8AUwBFAEMATwBMAFMAKABBAHIAZwB1AG0AZQBuAHQAcwBBAHIAcgBhAHkALAAgADEALAAgADIAKQBcAG4AKQA7AFwAbgBcAG4AVQB0AGkAbABpAHQAeQBfAEQAaQBzAHAAbABhAHkAQQByAGcAdQBtAGUAbgB0AHMAXwAzAF8ANABcAG4APQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAEEAcgBnAHUAbQBlAG4AdABzAEEAcgByAGEAeQAsAFwAbgAgACAAIAAgAEMASABPAE8AUwBFAEMATwBMAFMAKABBAHIAZwB1AG0AZQBuAHQAcwBBAHIAcgBhAHkALAAgADMALAAgADQAKQBcAG4AKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBHAGUAdABNAEMARgBUAGUAbQBwAGUAcgBhAHQAdQByAGUAWgBvAG4AZQBcAG4APQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAFQAZQBtAHAAZQByAGEAdAB1AHIAZQAsACAATQBNAFMALAAgAFQAZQBtAHAAZQByAGEAdAB1AHIAZQBBAHIAcgBhAHkALAAgAE0ATQBTAEEAcgByAGEAeQAsACAAUgBlAHQAdQByAG4AQQByAHIAYQB5ACwAXABuACAAIAAgACAAWABMAE8ATwBLAFUAUAAoAFwAbgAgACAAIAAgACAAIAAgACAATQBFAEQASQBBAE4AKABcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAVABlAG0AcABlAHIAYQB0AHUAcgBlACwAIABcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAATQBJAE4AKABUAGUAbQBwAGUAcgBhAHQAdQByAGUAQQByAHIAYQB5ACkALAAgAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIABNAEEAWAAoAFQAZQBtAHAAZQByAGEAdAB1AHIAZQBBAHIAcgBhAHkAKQBcAG4AIAAgACAAIAAgACAAIAAgACkALABcAG4AIAAgACAAIAAgACAAIAAgAFQAZQBtAHAAZQByAGEAdAB1AHIAZQBBAHIAcgBhAHkALABcAG4AIAAgACAAIAAgACAAIAAgAFgATABPAE8ASwBVAFAAKABNAE0AUwAsACAATQBNAFMAQQByAHIAYQB5ACwAIABSAGUAdAB1AHIAbgBBAHIAcgBhAHkAKQBcAG4AIAAgACAAIAApAFwAbgApADsAXABuAFwAbgBcAG4AVQB0AGkAbABpAHQAeQBfAFIAZQBzAHUAbAB0AHMASQB0AGUAbQBGAHIAbwBtAEUAcQB1AGEAdABpAG8AbgBUAGkAdABsAGUAQQBuAGQAUwBvAHUAcgBjAGUAXABuAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABUAGkAdABsAGUAQwBlAGwAbAAsACAAUwBvAHUAcgBjAGUAQwBlAGwAbAAsAFwAbgAgACAAIAAgAFMAVQBCAFMAVABJAFQAVQBUAEUAKABMAEUARgBUACgAUwBvAHUAcgBjAGUAQwBlAGwAbAAsACAARgBJAE4ARAAoAFwAIgAsAFwAIgAsACAAUwBvAHUAcgBjAGUAQwBlAGwAbAApACAALQAxACkALAAgAFwAIgBWAEUARQBSAEcAIAAyADAAMgA2ADoAIABcACIALAAgAFwAIgBcACIAKQAgACYAIABcACIAIABcACIAIAAmACAAVABpAHQAbABlAEMAZQBsAGwAXABuACkAOwAiAH0ALAB7ACIAcABhAHQAaAAiADoAIgAvAHAAcgBvAGoAZQBjAHQAcwAvAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAiACwAIgB0AGUAeAB0ACIAOgAiAC8AKgBcAG4APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQBcAG4APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQBcAG4AUwBvAHUAcgBjAGUAIABkAGEAdABhACAAdABoAGEAdAAgAGkAcwAgAGMAbwBtAG0AbwBuACAAYQBjAHIAbwBzAHMAIABhAGwAbAAgAGUAbgB0AGUAcgBwAHIAaQBzAGUAIAB0AHkAcABlAHMAXABuAEUAeABjAGUAbAAgAG0AbwBkAHUAbABlACAAbgBhAG0AZQA6ACAAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAFwAbgA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AFwAbgA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AFwAbgAqAC8AXABuAFwAbgAvACoAXABuAD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQBcAG4APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AFwAbgBTAG8AdQByAGMAZQA6ACAATgBhAHQAaQBvAG4AYQBsACAASQBuAHYAZQBuAHQAbwByAHkAIABSAGUAcABvAHIAdAAgADIAMAAyADMAIABWAG8AbAB1AG0AZQAgADEAXABuAE4ASQBSAF8AMgAwADIAMwBfAFYAbwBsADEAXABuAD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQBcAG4APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AFwAbgAqAC8AXABuAFwAbgAvACoAIABcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGUAbgBzAGkAdAB5AE8AZgBNAGUAdABoAGEAbgBlAFwAbgBwACAAPQAgAGQAZQBuAHMAaQB0AHkAIABvAGYAIABtAGUAdABoAGEAbgBlACAAKAAwAC4ANgA3ADgANAAgAGsAZwAvAG0AMwApAFwAbgBUAGEAawBlAG4AIABmAHIAbwBtACAAdABoAGUAIABOAGEAdABpAG8AbgBhAGwAIABHAHIAZQBlAG4AaABvAHUAcwBlACAAYQBuAGQAIABFAG4AZQByAGcAeQAgAFIAZQBwAG8AcgB0AGkAbgBnACAAXABuACgATQBlAGEAcwB1AHIAZQBtAGUAbgB0ACkAIABEAGUAdABlAHIAbQBpAG4AYQB0AGkAbwBuACAAMgAwADAAOABcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgAqAC8AXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGUAbgBzAGkAdAB5AE8AZgBNAGUAdABoAGEAbgBlAF8AVABpAHQAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBwACAAPQAgAGQAZQBuAHMAaQB0AHkAIABvAGYAIABtAGUAdABoAGEAbgBlAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGUAbgBzAGkAdAB5AE8AZgBNAGUAdABoAGEAbgBlAF8AVQBuAGkAdABcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAawBnAC8AbQAzAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGUAbgBzAGkAdAB5AE8AZgBNAGUAdABoAGEAbgBlAF8AUwBvAHUAcgBjAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAE4AYQB0AGkAbwBuAGEAbAAgAEkAbgB2AGUAbgB0AG8AcgB5ACAAUgBlAHAAbwByAHQAIAAyADAAMgAzACAAVgBvAGwAdQBtAGUAIAAxADoAIABFAHEAdQBhAHQAaQBvAG4AcwAgADMALgBCAC4AMQBhAF8AMgAsACAAMwAuAEIALgAxAGMAXwAyACwAIAAzAC4AQgAuADMAXwAxACwAIAAzAC4AQgAuADQAZwBfADIAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEQAZQBuAHMAaQB0AHkATwBmAE0AZQB0AGgAYQBuAGUAXwBEAGEAdABhAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoADAALgA2ADcAOAA0ACkAOwBcAG4AXABuAC8AKgAgAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEMAbwBuAHYAZQByAHQATgAyAG8ARQBsAGUAbQBlAG4AdABhAGwAVABvAE0AbwBsAGUAYwB1AGwAYQByAEMAZwBcAG4AQwBnACAAPQAgADQANAAvADIAOAAgAGYAYQBjAHQAbwByACAAdABvACAAYwBvAG4AdgBlAHIAdAAgAGUAbABlAG0AZQBuAHQAYQBsACAAbQBhAHMAcwAgAG8AZgAgAE4AMgBPACAAdABvACAAbQBvAGwAZQBjAHUAbABhAHIAIABtAGEAcwBzAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuACoALwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEMAbwBuAHYAZQByAHQATgAyAG8ARQBsAGUAbQBlAG4AdABhAGwAVABvAE0AbwBsAGUAYwB1AGwAYQByAEMAZwBfAFQAaQB0AGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIARgBhAGMAdABvAHIAIAB0AG8AIABjAG8AbgB2AGUAcgB0ACAAZQBsAGUAbQBlAG4AdABhAGwAIABtAGEAcwBzACAAbwBmACAATgAyAE8AIAB0AG8AIABtAG8AbABlAGMAdQBsAGEAcgAgAG0AYQBzAHMAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEMAbwBuAHYAZQByAHQATgAyAG8ARQBsAGUAbQBlAG4AdABhAGwAVABvAE0AbwBsAGUAYwB1AGwAYQByAEMAZwBfAFYAYQByAGkAYQBiAGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAQwBnAE4AMgBPAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBDAG8AbgB2AGUAcgB0AE4AMgBvAEUAbABlAG0AZQBuAHQAYQBsAFQAbwBNAG8AbABlAGMAdQBsAGEAcgBDAGcAXwBVAG4AaQB0AFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBmAGEAYwB0AG8AcgBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQwBvAG4AdgBlAHIAdABOADIAbwBFAGwAZQBtAGUAbgB0AGEAbABUAG8ATQBvAGwAZQBjAHUAbABhAHIAQwBnAF8AUwBvAHUAcgBjAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAE4AYQB0AGkAbwBuAGEAbAAgAEkAbgB2AGUAbgB0AG8AcgB5ACAAUgBlAHAAbwByAHQAIAAyADAAMgAzACAAVgBvAGwAdQBtAGUAIAAxAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBDAG8AbgB2AGUAcgB0AE4AMgBvAEUAbABlAG0AZQBuAHQAYQBsAFQAbwBNAG8AbABlAGMAdQBsAGEAcgBDAGcAXwBEAGEAdABhAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoADQANAAvADIAOAApADsAXABuAFwAbgAvACoAIABcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBDAG8AbgB2AGUAcgB0AEcAYQBzAEUAbABlAG0AZQBuAHQAYQBsAFQAbwBNAG8AbABlAGMAdQBsAGEAcgBcAG4ARgBhAGMAdABvAHIAIAB0AG8AIABjAG8AbgB2AGUAcgB0ACAAZQBsAGUAbQBlAG4AdABhAGwAIABtAGEAcwBzACAAbwBmACAAZwBhAHMAIAB0AG8AIABtAG8AbABlAGMAdQBsAGEAcgAgAG0AYQBzAHMAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AKgAvAFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQwBvAG4AdgBlAHIAdABHAGEAcwBFAGwAZQBtAGUAbgB0AGEAbABUAG8ATQBvAGwAZQBjAHUAbABhAHIAXwBUAGkAdABsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAEYAYQBjAHQAbwByACAAdABvACAAYwBvAG4AdgBlAHIAdAAgAGUAbABlAG0AZQBuAHQAYQBsACAAbQBhAHMAcwAgAG8AZgAgAGcAYQBzACAAdABvACAAbQBvAGwAZQBjAHUAbABhAHIAIABtAGEAcwBzAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBDAG8AbgB2AGUAcgB0AEcAYQBzAEUAbABlAG0AZQBuAHQAYQBsAFQAbwBNAG8AbABlAGMAdQBsAGEAcgBfAFYAYQByAGkAYQBiAGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAQwBnAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBDAG8AbgB2AGUAcgB0AEcAYQBzAEUAbABlAG0AZQBuAHQAYQBsAFQAbwBNAG8AbABlAGMAdQBsAGEAcgBfAFUAbgBpAHQAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAGYAYQBjAHQAbwByAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBDAG8AbgB2AGUAcgB0AEcAYQBzAEUAbABlAG0AZQBuAHQAYQBsAFQAbwBNAG8AbABlAGMAdQBsAGEAcgBfAFMAbwB1AHIAYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBYAFgAWABYAFgAWABYAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBDAG8AbgB2AGUAcgB0AEcAYQBzAEUAbABlAG0AZQBuAHQAYQBsAFQAbwBNAG8AbABlAGMAdQBsAGEAcgBfAEQAYQB0AGEAXABuACAAIAA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAATQBBAEsARQBBAFIAUgBBAFkAKAA4ACwAIAA0ACwAIABcAG4AIAAgACAAIAAgACAATABBAE0AQgBEAEEAKAByACwAYwAsACAAXABuACAAIAAgACAAIAAgACAAIABJAE4ARABFAFgAKAB7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBHAGEAcwBcACIALAAgAFwAIgBDAG8AbgB2AGUAcgBzAGkAbwBuACAAZgBhAGMAdABvAHIAXAAiACwAIABcACIAQwBvAG4AdgBlAHIAcwBpAG8AbgAgAGYAYQBjAHQAbwByACAAMQBcACIALAAgAFwAIgBDAG8AbgB2AGUAcgBzAGkAbwBuACAAZgBhAGMAdABvAHIAIAAyAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBDAE8AMgBcACIALAAgAFwAIgA0ADQALwAxADIAXAAiACwAIAA0ADQALAAgADEAMgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBDAEgANABcACIALAAgAFwAIgAxADYALwAxADIAXAAiACwAIAAxADYALAAgADEAMgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBOADIATwBcACIALAAgAFwAIgA0ADQALwAyADgAXAAiACwAIAA0ADQALAAgADIAOAA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBOAG8AeABcACIALAAgAFwAIgA0ADYALwAxADQAXAAiACwAIAA0ADYALAAgADEANAA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBDAE8AXAAiACwAIABcACIAMgA4AC8AMQAyAFwAIgAsACAAMgA4ACwAIAAxADIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAQwBPADIAIABMAGkAbQBlAFwAIgAsACAAXAAiADQANAAvADEAMgBcACIALAAgADQANAAsACAAMQAyADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAE4ATQBWAE8AQwBcACIALAAgAFwAIgAxADQALwAxADIAXAAiACwAIAAxADQALAAgADEAMgBcAG4AIAAgACAAIAAgACAAIAAgAH0ALAAgAHIALAAgAGMAKQBcAG4AIAAgACAAIAAgACAAKQBcAG4AIAAgACAAIAApAFwAbgAgACAAKQA7AFwAbgBcAG4ALwAqACAAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARwBXAFAATgAyAE8AXABuAEcAbABvAGIAYQBsACAAdwBhAHIAbQBpAG4AZwAgAHAAbwB0AGUAbgB0AGkAYQBsACAAZgBvAHIAIABnAHIAZQBlAG4AaABvAHUAcwBlACAAZwBhAHMAZQBzAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuACoALwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEcAVwBQAF8AVABpAHQAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBHAGwAbwBiAGEAbAAgAHcAYQByAG0AaQBuAGcAIABwAG8AdABlAG4AdABpAGEAbAAgAGYAbwByACAAZwByAGUAZQBuAGgAbwB1AHMAZQAgAGcAYQBzAGUAcwBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARwBXAFAAXwBWAGEAcgBpAGEAYgBsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAEcAVwBQAE4AMgBPAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBHAFcAUABfAFUAbgBpAHQAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAGYAYQBjAHQAbwByAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBHAFcAUABfAFMAbwB1AHIAYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBYAFgAWABYAFgAWABYAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBHAFcAUABfAEQAYQB0AGEAXABuACAAIAA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAATQBBAEsARQBBAFIAUgBBAFkAKAA4ACwAIAAyACwAIABcAG4AIAAgACAAIAAgACAATABBAE0AQgBEAEEAKAByACwAYwAsACAAXABuACAAIAAgACAAIAAgACAAIABJAE4ARABFAFgAKAB7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBHAGEAcwBcACIALAAgAFwAIgBDAE8AMgAtAGUAIABmAGEAYwB0AG8AcgBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAQwBPADIAXAAiACwAIAAxADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEMASAA0AFwAIgAsACAAMgA4ADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAE4AMgBPAFwAIgAsACAAMgA2ADUAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAQwBGADQAXAAiACwAIAA2ADYAMwAwADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEMAMgBGADYAXAAiACwAIAAxADIAMgAwADAAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAUwBGADYAXAAiACwAIAAyADIAOAAwADAAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIATgBGADMAXAAiACwAIAAxADcAMgAwADAAXABuACAAIAAgACAAIAAgACAAIAB9ACwAIAByACwAIABjACkAXABuACAAIAAgACAAIAAgACkAXABuACAAIAAgACAAKQBcAG4AIAAgACkAOwBcAG4AXABuAFwAbgAvACoAIABcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBBAHUAcwB0AHIAYQBsAGkAYQBuAFMAdABhAHQAZQBzAFQAZQByAHIAaQB0AG8AcgBpAGUAcwBcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgAqAC8AXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBBAHUAcwB0AHIAYQBsAGkAYQBuAFMAdABhAHQAZQBzAFQAZQByAHIAaQB0AG8AcgBpAGUAcwBfAFQAaQB0AGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAQQB1AHMAdAByAGEAbABpAGEAbgAgAHMAdABhAHQAZQBzACAAYQBuAGQAIAB0AGUAcgByAGkAdABvAHIAaQBlAHMAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEEAdQBzAHQAcgBhAGwAaQBhAG4AUwB0AGEAdABlAHMAVABlAHIAcgBpAHQAbwByAGkAZQBzAF8AVgBhAHIAaQBhAGIAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQQB1AHMAdAByAGEAbABpAGEAbgBTAHQAYQB0AGUAcwBUAGUAcgByAGkAdABvAHIAaQBlAHMAXwBVAG4AaQB0AFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQQB1AHMAdAByAGEAbABpAGEAbgBTAHQAYQB0AGUAcwBUAGUAcgByAGkAdABvAHIAaQBlAHMAXwBTAG8AdQByAGMAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEEAdQBzAHQAcgBhAGwAaQBhAG4AUwB0AGEAdABlAHMAVABlAHIAcgBpAHQAbwByAGkAZQBzAF8ARABhAHQAYQBcAG4AIAAgACAAPQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAE0AQQBLAEUAQQBSAFIAQQBZACgAOQAsACAAMwAsACAAXABuACAAIAAgACAAIAAgAEwAQQBNAEIARABBACgAcgAsAGMALAAgAFwAbgAgACAAIAAgACAAIAAgACAASQBOAEQARQBYACgAewBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAUwB0AGEAdABlAC8AVABlAHIAcgBpAHQAbwByAHkAXAAiACwAIABcACIAQwBvAG0AbQBvAG4AIABOAGEAbQBlAFwAIgAsACAAXAAiAEEAYgBiAHIAZQB2AGkAYQB0AGkAbwBuAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBOAGUAdwAgAFMAbwB1AHQAaAAgAFcAYQBsAGUAcwBcACIALAAgAFwAIgBOAGUAdwAgAFMAbwB1AHQAaAAgAFcAYQBsAGUAcwBcACIALAAgAFwAIgBOAFMAVwBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAQQB1AHMAdAByAGEAbABpAGEAbgAgAEMAYQBwAGkAdABhAGwAIABUAGUAcgByAGkAdABvAHIAeQBcACIALAAgAFwAIgBBAEMAVABcACIALAAgAFwAIgBBAEMAVABcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVgBpAGMAdABvAHIAaQBhAFwAIgAsACAAXAAiAFYAaQBjAHQAbwByAGkAYQBcACIALAAgAFwAIgBWAEkAQwBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAUQB1AGUAZQBuAHMAbABhAG4AZABcACIALAAgAFwAIgBRAHUAZQBlAG4AcwBsAGEAbgBkAFwAIgAsACAAXAAiAFEATABEAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBTAG8AdQB0AGgAIABBAHUAcwB0AHIAYQBsAGkAYQBcACIALAAgAFwAIgBTAG8AdQB0AGgAIABBAHUAcwB0AHIAYQBsAGkAYQBcACIALAAgAFwAIgBTAEEAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFcAZQBzAHQAZQByAG4AIABBAHUAcwB0AHIAYQBsAGkAYQBcACIALAAgAFwAIgBXAGUAcwB0AGUAcgBuACAAQQB1AHMAdAByAGEAbABpAGEAXAAiACwAIABcACIAVwBBAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBUAGEAcwBtAGEAbgBpAGEAXAAiACwAIABcACIAVABhAHMAbQBhAG4AaQBhAFwAIgAsACAAXAAiAFQAQQBTAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBOAG8AcgB0AGgAZQByAG4AIABUAGUAcgByAGkAdABvAHIAeQBcACIALAAgAFwAIgBOAG8AcgB0AGgAZQByAG4AIABUAGUAcgByAGkAdABvAHIAeQBcACIALAAgAFwAIgBOAFQAXAAiAFwAbgAgACAAIAAgACAAIAAgACAAfQAsACAAcgAsACAAYwApAFwAbgAgACAAIAAgACAAIAApAFwAbgAgACAAIAAgACkAXABuACAAIAApADsAXABuAFwAbgAvACoAIABcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBXAEEAUwBBADQAQQByAGUAYQBzAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuACoALwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFcAQQBTAEEANABBAHIAZQBhAHMAXwBUAGkAdABsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAEEAQgBTACAAUwB0AGEAdABpAHMAdABjAGEAbAAgAEEAcgBlAGEAcwAgAEwAZQB2AGUAbAAgADQAIAAtACAAVwBlAHMAdABlAHIAbgAgAEEAdQBzAHQAcgBhAGwAaQBhAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBXAEEAUwBBADQAQQByAGUAYQBzAF8AVgBhAHIAaQBhAGIAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AVwBBAFMAQQA0AEEAcgBlAGEAcwBfAFUAbgBpAHQAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBXAEEAUwBBADQAQQByAGUAYQBzAF8AUwBvAHUAcgBjAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAEEAdQBzAHQAcgBhAGwAaQBhAG4AIABCAHUAcgBlAGEAdQAgAG8AZgAgAFMAdABhAHQAaQBzAHQAaQBjAHMAIAAoAEEAQgBTACkAIAAtACAAUwB0AGEAdABpAHMAdABpAGMAYQBsACAAQQByAGUAYQBzACAATABlAHYAZQBsACAAMgAgAC0AIAAyADAAMgAxACAALQAgAFMAaABhAHAAZQBmAGkAbABlAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBXAEEAUwBBADQAQQByAGUAYQBzAF8ARABhAHQAYQBcAG4AIAAgACAAPQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAE0AQQBLAEUAQQBSAFIAQQBZACgAMQAxACwAIAAxACwAIABcAG4AIAAgACAAIAAgACAATABBAE0AQgBEAEEAKAByACwAYwAsACAAXABuACAAIAAgACAAIAAgACAAIABJAE4ARABFAFgAKAB7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBTAEEAIAA0ACAATgBhAG0AZQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAQgB1AG4AYgB1AHIAeQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIATQBhAG4AZAB1AHIAYQBoAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBQAGUAcgB0AGgAIAAtACAASQBuAG4AZQByAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBQAGUAcgB0AGgAIAAtACAATgBvAHIAdABoACAARQBhAHMAdABcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAUABlAHIAdABoACAALQAgAE4AbwByAHQAaAAgAFcAZQBzAHQAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFAAZQByAHQAaAAgAC0AIABTAG8AdQB0AGgAIABFAGEAcwB0AFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBQAGUAcgB0AGgAIAAtACAAUwBvAHUAdABoACAAVwBlAHMAdABcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVwBlAHMAdABlAHIAbgAgAEEAdQBzAHQAcgBhAGwAaQBhACAALQAgAFcAaABlAGEAdAAgAEIAZQBsAHQAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFcAZQBzAHQAZQByAG4AIABBAHUAcwB0AHIAYQBsAGkAYQAgAC0AIABPAHUAdABiAGEAYwBrACAAKABOAG8AcgB0AGgAKQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVwBlAHMAdABlAHIAbgAgAEEAdQBzAHQAcgBhAGwAaQBhACAALQAgAE8AdQB0AGIAYQBjAGsAIAAoAFMAbwB1AHQAaAApAFwAIgBcAG4AIAAgACAAIAAgACAAIAAgAH0ALAAgAHIALAAgAGMAKQBcAG4AIAAgACAAIAAgACAAKQBcAG4AIAAgACAAIAApAFwAbgAgACAAKQA7AFwAbgBcAG4ALwAqACAAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AVwBlAHQAQQBuAGQARAByAHkAWgBvAG4AZQBzAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuACoALwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFcAZQB0AEEAbgBkAEQAcgB5AFoAbwBuAGUAcwBfAFQAaQB0AGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAVgBFAEUAUgBHACAAQQB1AHMAdAByAGEAbABpAGEAbgAgAHcAZQB0ACAAYQBuAGQAIABkAHIAeQAgAHoAbwBuAGUAcwBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AVwBlAHQAQQBuAGQARAByAHkAWgBvAG4AZQBzAF8AVgBhAHIAaQBhAGIAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AVwBlAHQAQQBuAGQARAByAHkAWgBvAG4AZQBzAF8AVQBuAGkAdABcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFcAZQB0AEEAbgBkAEQAcgB5AFoAbwBuAGUAcwBfAFMAbwB1AHIAYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBWAEUARQBSAEcAIAAyADAAMgA2ADoAIABUAGEAYgBsAGUAIAAxAC4AMgA6ACAAVAByAGEAbgBzAGwAYQB0AGkAbgBnACAAYwBsAGkAbQBhAHQAZQAgAHoAbwBuAGUAcwAgAHQAbwAgAHcAZQB0ACAAYQBuAGQAIABkAHIAeQAgAHoAbwBuAGUAcwBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AVwBlAHQAQQBuAGQARAByAHkAWgBvAG4AZQBzAF8AVgBhAHIAaQBhAHQAaQBvAG4AXABuACAAIAAgAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABNAEEASwBFAEEAUgBSAEEAWQAoADMALAAgADEALAAgAFwAbgAgACAAIAAgACAAIABMAEEATQBCAEQAQQAoAHIALABjACwAIABcAG4AIAAgACAAIAAgACAAIAAgAEkATgBEAEUAWAAoAHsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFYAQQBSAEkAQQBUAEkATwBOACAATwBGACAAUwBPAFUAUgBDAEUAIABEAEEAVABBADoAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEEAZABkAGUAZAAgAHcAYQByAG0AIAAvACAAYwBvAG8AbAAgAHQAZQBtAHAAZQByAGEAdABlACAAbQBvAGkAcwB0ACAALwAgAGQAcgB5ACAALQAgAGwAbwB3ACAAZgByAG8AcwB0ACAAYQBuAGQAIABoAGkAZwBoACAAdABlAG0AcAAgAGMAbABhAHMAcwBlAHMAIAB0AG8AIABhAGMAYwBvAG0AbQBvAGQAYQB0AGUAIABjAGwAaQBtAGEAdABlACAAcwBjAGUAbgBhAHIAaQBvAHMAIABlAHgAYwBsAHUAZABlAGQAIABiAHkAIABWAEUARQBSAEcAIABjAHIAaQB0AGUAcgBpAGEALgBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIARgBpAHgAZQBkACAAdAB5AHAAbwAgAC0AIABDAGgAYQBuAGcAZQBkACAAJwBGAHIAeQAnACAAdABvACAAJwBEAHIAeQAnAC4AXAAiAFwAbgAgACAAIAAgACAAIAAgACAAfQAsACAAcgAsACAAYwApAFwAbgAgACAAIAAgACAAIAApAFwAbgAgACAAIAAgACkAXABuACAAIAApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBXAGUAdABBAG4AZABEAHIAeQBaAG8AbgBlAHMAXwBEAGEAdABhAFwAbgAgACAAIAA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAATQBBAEsARQBBAFIAUgBBAFkAKAAxADUALAAgADIALAAgAFwAbgAgACAAIAAgACAAIABMAEEATQBCAEQAQQAoAHIALABjACwAIABcAG4AIAAgACAAIAAgACAAIAAgAEkATgBEAEUAWAAoAHsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEMAbABpAG0AYQB0AGUAIABaAG8AbgBlAFwAIgAsACAAXAAiAFcAZQB0ACAAbwByACAARAByAHkAIABaAG8AbgBlAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBUAHIAbwBwAGkAYwBhAGwAIABtAG8AbgB0AGEAbgBlAFwAIgAsACAAXAAiAFcAZQB0ACAAYwBsAGkAbQBhAHQAZQAgAHoAbwBuAGUAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFQAcgBvAHAAaQBjAGEAbAAgAHcAZQB0AFwAIgAsACAAXAAiAFcAZQB0ACAAYwBsAGkAbQBhAHQAZQAgAHoAbwBuAGUAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFQAcgBvAHAAaQBjAGEAbAAgAG0AbwBpAHMAdABcACIALAAgAFwAIgBXAGUAdAAgAGMAbABpAG0AYQB0AGUAIAB6AG8AbgBlAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBUAHIAbwBwAGkAYwBhAGwAIABkAHIAeQBcACIALAAgAFwAIgBEAHIAeQAgAGMAbABpAG0AYQB0AGUAIAB6AG8AbgBlAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBXAGEAcgBtACAAdABlAG0AcABlAHIAYQB0AGUAIABtAG8AaQBzAHQAXAAiACwAIABcACIAVwBlAHQAIABjAGwAaQBtAGEAdABlACAAegBvAG4AZQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVwBhAHIAbQAgAHQAZQBtAHAAZQByAGEAdABlACAAZAByAHkAXAAiACwAIABcACIARAByAHkAIABjAGwAaQBtAGEAdABlACAAegBvAG4AZQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAQwBvAG8AbAAgAHQAZQBtAHAAZQByAGEAdABlACAAbQBvAGkAcwB0AFwAIgAsACAAXAAiAFcAZQB0ACAAYwBsAGkAbQBhAHQAZQAgAHoAbwBuAGUAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEMAbwBvAGwAIAB0AGUAbQBwAGUAcgBhAHQAZQAgAGQAcgB5AFwAIgAsACAAXAAiAEQAcgB5ACAAYwBsAGkAbQBhAHQAZQAgAHoAbwBuAGUAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFcAYQByAG0AIAB0AGUAbQBwAGUAcgBhAHQAZQAgAG0AbwBpAHMAdAAgAC0AIABsAG8AdwAgAGYAcgBvAHMAdABcACIALAAgAFwAIgBXAGUAdAAgAGMAbABpAG0AYQB0AGUAIAB6AG8AbgBlAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBXAGEAcgBtACAAdABlAG0AcABlAHIAYQB0AGUAIABkAHIAeQAgAC0AIABsAG8AdwAgAGYAcgBvAHMAdABcACIALAAgAFwAIgBEAHIAeQAgAGMAbABpAG0AYQB0AGUAIAB6AG8AbgBlAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBXAGEAcgBtACAAdABlAG0AcABlAHIAYQB0AGUAIABtAG8AaQBzAHQAIAAtACAAaABpAGcAaAAgAHQAZQBtAHAAXAAiACwAIABcACIAVwBlAHQAIABjAGwAaQBtAGEAdABlACAAegBvAG4AZQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVwBhAHIAbQAgAHQAZQBtAHAAZQByAGEAdABlACAAZAByAHkAIAAtACAAaABpAGcAaAAgAHQAZQBtAHAAXAAiACwAIABcACIARAByAHkAIABjAGwAaQBtAGEAdABlACAAegBvAG4AZQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAQwBvAG8AbAAgAHQAZQBtAHAAZQByAGEAdABlACAAbQBvAGkAcwB0ACAALQAgAGwAbwB3ACAAZgByAG8AcwB0AFwAIgAsACAAXAAiAFcAZQB0ACAAYwBsAGkAbQBhAHQAZQAgAHoAbwBuAGUAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEMAbwBvAGwAIAB0AGUAbQBwAGUAcgBhAHQAZQAgAGQAcgB5ACAALQAgAGwAbwB3ACAAZgByAG8AcwB0AFwAIgAsACAAXAAiAEQAcgB5ACAAYwBsAGkAbQBhAHQAZQAgAHoAbwBuAGUAXAAiAFwAbgAgACAAIAAgACAAIAAgACAAfQAsACAAcgAsACAAYwApAFwAbgAgACAAIAAgACAAIAApAFwAbgAgACAAIAAgACkAXABuACAAIAApADsAXABuAFwAbgAvACoAIABcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBDAGwAaQBtAGEAdABlAFoAbwBuAGUAcwBcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgAqAC8AXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBDAGwAaQBtAGEAdABlAFoAbwBuAGUAcwBfAFQAaQB0AGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAVgBFAEUAUgBHACAAQQB1AHMAdAByAGEAbABpAGEAbgAgAGMAbABpAG0AYQB0AGUAIAB6AG8AbgBlAHMAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEMAbABpAG0AYQB0AGUAWgBvAG4AZQBzAF8AVgBhAHIAaQBhAGIAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQwBsAGkAbQBhAHQAZQBaAG8AbgBlAHMAXwBVAG4AaQB0AFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQwBsAGkAbQBhAHQAZQBaAG8AbgBlAHMAXwBTAG8AdQByAGMAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAVgBFAEUAUgBHACAAMgAwADIANgA6ACAAVABhAGIAbABlACAAMQAuADMAOgAgAEMAbABpAG0AYQB0AGUAIABhAG4AZAAgAFIAYQBpAG4AZgBhAGwAbAAgAHoAbwBuAGUAIABjAGwAYQBzAHMAaQBmAGkAYwBhAHQAaQBvAG4AcwAgAGEAbgBkACAAZABlAGYAaQBuAGkAdABpAG8AbgBzAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBDAGwAaQBtAGEAdABlAFoAbwBuAGUAcwBfAFYAYQByAGkAYQB0AGkAbwBuAFwAbgAgACAAIAA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAATQBBAEsARQBBAFIAUgBBAFkAKAA1ACwAIAAxACwAIABcAG4AIAAgACAAIAAgACAATABBAE0AQgBEAEEAKAByACwAYwAsACAAXABuACAAIAAgACAAIAAgACAAIABJAE4ARABFAFgAKAB7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBWAEEAUgBJAEEAVABJAE8ATgAgAE8ARgAgAFMATwBVAFIAQwBFACAARABBAFQAQQA6AFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBBAGQAZABlAGQAIAB3AGEAcgBtACAALwAgAGMAbwBvAGwAIAB0AGUAbQBwAGUAcgBhAHQAZQAgAG0AbwBpAHMAdAAgAC8AIABkAHIAeQAgAC0AIABsAG8AdwAgAGYAcgBvAHMAdAAgAGEAbgBkACAAaABpAGcAaAAgAHQAZQBtAHAAIABjAGwAYQBzAHMAZQBzACAAdABvACAAYQBjAGMAbwBtAG0AbwBkAGEAdABlACAAYwBsAGkAbQBhAHQAZQAgAHMAYwBlAG4AYQByAGkAbwBzACAAZQB4AGMAbAB1AGQAZQBkACAAYgB5ACAAVgBFAEUAUgBHACAAYwByAGkAdABlAHIAaQBhAC4AXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEYAaQB4AGUAZAAgAHQAeQBwAG8AIABpAG4AIABNAEEAVAAgAHYAYQBsAHUAZQAgAGYAbwByACAAdwBhAHIAbQAgAHQAZQBtAHAAZQByAGEAdABlACAAZAByAHkAIAAtACAAYwBoAGEAbgBnAGUAZAAgADEAMAAgAHQAbwAgADEAMQAuAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBBAGQAZABlAGQAIABtAGkAbgAgAGEAbgBkACAAbQBhAHgAIABjAG8AbAB1AG0AbgBzACAAZgBvAHIAIABNAEEAVAAsACAATQBBAFAALAAgAGYAcgBvAHMAdAAgAGQAYQB5AHMAIABwAGUAcgAgAHkAZQBhAHIALAAgAGUAbABlAHYAYQB0AGkAbwBuACwAIABNAEEAUAA6AFAARQBUACAAdABvACAAYwBhAGwAYwB1AGwAYQB0AGUAIAB6AG8AbgBlAHMAIABmAHIAbwBtACAAcgBlAGEAbAAgAGMAbABpAG0AYQB0AGUAIABkAGEAdABhAC4AXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEcAQQBGACAAYQBjAGMAZQBwAHQAcwAgAHIAYQBpAG4AZgBhAGwAbAAgAGEAcwAgAGEAIABwAHIAbwB4AHkAIABmAG8AcgAgAHAAcgBlAGMAaQBwAGkAdABhAHQAaQBvAG4ALgBcACIAXABuACAAIAAgACAAIAAgACAAIAB9ACwAIAByACwAIABjACkAXABuACAAIAAgACAAIAAgACkAXABuACAAIAAgACAAKQBcAG4AIAAgACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEMAbABpAG0AYQB0AGUAWgBvAG4AZQBzAF8ARABhAHQAYQBcAG4AIAAgACAAPQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAE0AQQBLAEUAQQBSAFIAQQBZACgAOQAsACAAMQA2ACwAIABcAG4AIAAgACAAIAAgACAATABBAE0AQgBEAEEAKAByACwAYwAsACAAXABuACAAIAAgACAAIAAgACAAIABJAE4ARABFAFgAKAB7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBDAGwAaQBtAGEAdABlACAAWgBvAG4AZQBcACIALAAgAFwAIgBNAEEAVABcACIALAAgAFwAIgBNAEEAUABcACIALAAgAFwAIgBGAHIAbwBzAHQAIABkAGEAeQBzACAAcABlAHIAIAB5AGUAYQByAFwAIgAsACAAXAAiAEUAbABlAHYAYQB0AGkAbwBuAFwAIgAsACAAXAAiAE0AQQBQADoAUABFAFQAXAAiACwAIABcACIATQBpAG4AIAB0AGUAbQBwAFwAIgAsACAAXAAiAE0AYQB4ACAAdABlAG0AcABcACIALAAgAFwAIgBNAGkAbgAgAHIAYQBpAG4AZgBhAGwAbABcACIALAAgAFwAIgBNAGEAeAAgAHIAYQBpAG4AZgBhAGwAbABcACIALAAgAFwAIgBNAGkAbgAgAGYAcgBvAHMAdAAgAGQAYQB5AHMAXAAiACwAIABcACIATQBhAHgAIABmAHIAbwBzAHQAIABkAGEAeQBzAFwAIgAsACAAXAAiAE0AaQBuACAAZQBsAGUAdgBhAHQAaQBvAG4AXAAiACwAIABcACIATQBhAHgAIABlAGwAZQB2AGEAdABpAG8AbgBcACIALAAgAFwAIgBNAGkAbgAgAE0AQQBQADoAUABFAFQAXAAiACwAIABcACIATQBpAG4AIABNAEEAUAA6AFAARQBUAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBUAHIAbwBwAGkAYwBhAGwAIABtAG8AbgB0AGEAbgBlAFwAIgAsACAAXAAiAD4AIAAxADgAIABDAFwAIgAsACAAXAAiAEEAbgB5AFwAIgAsACAAXAAiAGQiIAA3AFwAIgAsACAAXAAiAD4AIAAxADAAMAAwACAAbQBcACIALAAgAFwAIgBBAG4AeQBcACIALAAgADEAOAAuADAAMAAxACwAIAA5ADkAOQA5ADkAOQAsACAALQA5ADkAOQA5ADkAOQAsACAAOQA5ADkAOQA5ADkALAAgAC0AOQA5ADkAOQA5ADkALAAgADcALAAgADEAMAAwADAALAAgADkAOQA5ADkAOQA5ACwAIAAtADkAOQA5ADkAOQA5ACwAIAA5ADkAOQA5ADkAOQA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBUAHIAbwBwAGkAYwBhAGwAIAB3AGUAdABcACIALAAgAFwAIgA+ACAAMQA4ACAAQwBcACIALAAgAFwAIgA+ACAAMgAwADAAMAAgAG0AbQBcACIALAAgAFwAIgBkIiAANwBcACIALAAgAFwAIgBkIiAAMQAwADAAMAAgAG0AXAAiACwAIABcACIAQQBuAHkAXAAiACwAIAAxADgALgAwADAAMQAsACAAOQA5ADkAOQA5ADkALAAgADIAMAAwADAALgAwADAAMQAsACAAOQA5ADkAOQA5ADkALAAgAC0AOQA5ADkAOQA5ADkALAAgADcALAAgAC0AOQA5ADkAOQA5ADkALAAgADkAOQA5AC4AOQA5ADkALAAgACAALQA5ADkAOQA5ADkAOQAsACAAOQA5ADkAOQA5ADkAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVAByAG8AcABpAGMAYQBsACAAbQBvAGkAcwB0AFwAIgAsACAAXAAiAD4AIAAxADgAIABDAFwAIgAsACAAXAAiAD4AIAAxADAAMAAwACAAbQBtACAALQAgAGQiIAAyADAAMAAwACAAbQBtAFwAIgAsACAAXAAiAGQiIAA3AFwAIgAsACAAXAAiAGQiIAAxADAAMAAwACAAbQBcACIALAAgAFwAIgBBAG4AeQBcACIALAAgADEAOAAuADAAMAAxACwAIAA5ADkAOQA5ADkAOQAsACAAMQAwADAAMAAuADAAMAAxACwAIAAyADAAMAAwACwAIAAtADkAOQA5ADkAOQA5ACwAIAA3ACwAIAAtADkAOQA5ADkAOQA5ACwAIAA5ADkAOQAuADkAOQA5ACwAIAAgAC0AOQA5ADkAOQA5ADkALAAgADkAOQA5ADkAOQA5ADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFQAcgBvAHAAaQBjAGEAbAAgAGQAcgB5AFwAIgAsACAAXAAiAD4AIAAxADgAIABDAFwAIgAsACAAXAAiAGQiIAAxADAAMAAwACAAbQBtAFwAIgAsACAAXAAiAGQiIAA3AFwAIgAsACAAXAAiAGQiIAAxADAAMAAwACAAbQBcACIALAAgAFwAIgBBAG4AeQBcACIALAAgADEAOAAuADAAMAAxACwAIAA5ADkAOQA5ADkAOQAsACAALQA5ADkAOQA5ADkAOQAsACAAMQAwADAAMAAsACAALQA5ADkAOQA5ADkAOQAsACAANwAsACAALQA5ADkAOQA5ADkAOQAsACAAOQA5ADkALgA5ADkAOQAsACAAIAAtADkAOQA5ADkAOQA5ACwAIAA5ADkAOQA5ADkAOQA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBXAGEAcgBtACAAdABlAG0AcABlAHIAYQB0AGUAIABtAG8AaQBzAHQAXAAiACwAIABcACIAPgAgADEAMAAgAEMAXAAiACwAIABcACIAQQBuAHkAXAAiACwAIABcACIAQQBuAHkAXAAiACwAIABcACIAQQBuAHkAXAAiACwAIABcACIAPgAgADEAXAAiACwAIAAxADAALgAwADAAMQAsACAAOQA5ADkAOQA5ADkALAAgAC0AOQA5ADkAOQA5ADkALAAgADkAOQA5ADkAOQA5ACwAIAAtADkAOQA5ADkAOQA5ACwAIAA5ADkAOQA5ADkAOQAsACAALQA5ADkAOQA5ADkAOQAsACAAOQA5ADkAOQA5ADkALAAgADEALgAwADAAMQAsACAAOQA5ADkAOQA5ADkAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVwBhAHIAbQAgAHQAZQBtAHAAZQByAGEAdABlACAAZAByAHkAXAAiACwAIABcACIAPgAgADEAMAAgAEMAXAAiACwAIABcACIAQQBuAHkAXAAiACwAIABcACIAQQBuAHkAXAAiACwAIABcACIAQQBuAHkAXAAiACwAIABcACIAZCIgADEAXAAiACwAIAAxADAALgAwADAAMQAsACAAOQA5ADkAOQA5ADkALAAgAC0AOQA5ADkAOQA5ADkALAAgADkAOQA5ADkAOQA5ACwAIAAtADkAOQA5ADkAOQA5ACwAIAA5ADkAOQA5ADkAOQAsACAALQA5ADkAOQA5ADkAOQAsACAAOQA5ADkAOQA5ADkALAAgACAALQA5ADkAOQA5ADkAOQAsACAAMQA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBDAG8AbwBsACAAdABlAG0AcABlAHIAYQB0AGUAIABtAG8AaQBzAHQAXAAiACwAIABcACIAPgAgADAAIABDACAALQAgAGQiIAAxADAAIABDAFwAIgAsACAAXAAiAEEAbgB5AFwAIgAsACAAXAAiAEEAbgB5AFwAIgAsACAAXAAiAEEAbgB5AFwAIgAsACAAXAAiAD4AIAAxAFwAIgAsACAALQA5ADkAOQA5ADkAOQAsACAAMQAwACwAIAAtADkAOQA5ADkAOQA5ACwAIAA5ADkAOQA5ADkAOQAsACAALQA5ADkAOQA5ADkAOQAsACAAOQA5ADkAOQA5ADkALAAgAC0AOQA5ADkAOQA5ADkALAAgADkAOQA5ADkAOQA5ACwAIAAxAC4AMAAwADEALAAgADkAOQA5ADkAOQA5ADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEMAbwBvAGwAIAB0AGUAbQBwAGUAcgBhAHQAZQAgAGQAcgB5AFwAIgAsACAAXAAiAD4AIAAwACAAQwAgAC0AIABkIiAAMQAwACAAQwBcACIALAAgAFwAIgBBAG4AeQBcACIALAAgAFwAIgBBAG4AeQBcACIALAAgAFwAIgBBAG4AeQBcACIALAAgAFwAIgBkIiAAMQBcACIALAAgAC0AOQA5ADkAOQA5ADkALAAgADEAMAAsACAALQA5ADkAOQA5ADkAOQAsACAAOQA5ADkAOQA5ADkALAAgAC0AOQA5ADkAOQA5ADkALAAgADkAOQA5ADkAOQA5ACwAIAAtADkAOQA5ADkAOQA5ACwAIAA5ADkAOQA5ADkAOQAsACAAIAAtADkAOQA5ADkAOQA5ACwAIAAxAFwAbgAgACAAIAAgACAAIAAgACAAfQAsACAAcgAsACAAYwApAFwAbgAgACAAIAAgACAAIAApAFwAbgAgACAAIAAgACkAXABuACAAIAApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBDAGwAaQBtAGEAdABlAFoAbwBuAGUAcwBfAEEAcABwAGUAbgBkAGkAYwBlAHMAXABuACAAIAAgAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABNAEEASwBFAEEAUgBSAEEAWQAoADQALAAgADEALAAgAFwAbgAgACAAIAAgACAAIABMAEEATQBCAEQAQQAoAHIALABjACwAIABcAG4AIAAgACAAIAAgACAAIAAgAEkATgBEAEUAWAAoAHsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAE4AbwB0AGUAOgBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIATQBBAFQAIAA9ACAAbQBlAGEAbgAgAGEAbgBuAHUAYQBsACAAdABlAG0AcABlAHIAYQB0AHUAcgBlAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBNAEEAUAAgAD0AIABtAGUAYQBuACAAYQBuAG4AdQBhAGwAIABwAHIAZQBjAGkAcABpAHQAYQB0AGkAbwBuAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBQAEUAVAAgAD0AIABwAG8AdABlAG4AdABpAGEAbAAgAGUAdgBhAHAAbwB0AHIAYQBuAHMAcABpAHIAYQB0AGkAbwBuAFwAIgBcAG4AIAAgACAAIAAgACAAIAAgAH0ALAAgAHIALAAgAGMAKQBcAG4AIAAgACAAIAAgACAAKQBcAG4AIAAgACAAIAApAFwAbgAgACAAKQA7AFwAbgBcAG4AXABuAC8AKgAgAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFQAZQBtAHAAZQByAGEAdAB1AHIAZQBaAG8AbgBlAHMAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AKgAvAFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AVABlAG0AcABlAHIAYQB0AHUAcgBlAFoAbwBuAGUAcwBfAFQAaQB0AGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAVgBFAEUAUgBHACAAQQB1AHMAdAByAGEAbABpAGEAbgAgAHQAZQBtAHAAZQByAGEAdAB1AHIAZQAgAHoAbwBuAGUAcwBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AVABlAG0AcABlAHIAYQB0AHUAcgBlAFoAbwBuAGUAcwBfAFYAYQByAGkAYQBiAGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFQAZQBtAHAAZQByAGEAdAB1AHIAZQBaAG8AbgBlAHMAXwBVAG4AaQB0AFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AVABlAG0AcABlAHIAYQB0AHUAcgBlAFoAbwBuAGUAcwBfAFMAbwB1AHIAYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBWAEUARQBSAEcAIAAyADAAMgA2ADoAIABUAGEAYgBsAGUAIAAxAC4AMwA6ACAAQwBsAGkAbQBhAHQAZQAgAGEAbgBkACAAUgBhAGkAbgBmAGEAbABsACAAegBvAG4AZQAgAGMAbABhAHMAcwBpAGYAaQBjAGEAdABpAG8AbgBzACAAYQBuAGQAIABkAGUAZgBpAG4AaQB0AGkAbwBuAHMAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFQAZQBtAHAAZQByAGEAdAB1AHIAZQBaAG8AbgBlAHMAXwBWAGEAcgBpAGEAdABpAG8AbgBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAVgBBAFIASQBBAFQASQBPAE4AIABPAEYAIABTAE8AVQBSAEMARQAgAEQAQQBUAEEAOgAgAEEAZABkAGUAZAAgAGUAeAB0AHIAYQAgAE0AQQBUACAAbQBpAG4AIABhAG4AZAAgAE0AQQBUACAAbQBhAHgAIABjAG8AbAB1AG0AbgBzACAAdABvACAAYwBhAGwAYwB1AGwAYQB0AGUAIAB6AG8AbgBlACAAZgByAG8AbQAgAHIAZQBhAGwAIAB0AGUAbQBwAGUAcgBhAHQAdQByAGUAIABkAGEAdABhAC4AXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFQAZQBtAHAAZQByAGEAdAB1AHIAZQBaAG8AbgBlAHMAXwBEAGEAdABhAFwAbgAgACAAIAA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAATQBBAEsARQBBAFIAUgBBAFkAKAA0ACwAIAA0ACwAIABcAG4AIAAgACAAIAAgACAATABBAE0AQgBEAEEAKAByACwAYwAsACAAXABuACAAIAAgACAAIAAgACAAIABJAE4ARABFAFgAKAB7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBUAGUAbQBwAGUAcgBhAHQAdQByAGUAIABaAG8AbgBlAFwAIgAsACAAXAAiAE0AZQBkAGkAYQBuACAAQQBuAG4AdQBhAGwAIABUAGUAbQBwAGUAcgBhAHQAdQByAGUAIAAoAE0AQQBUACkAXAAiACwAIABcACIATQBpAG4AIABNAEEAVABcACIALAAgAFwAIgBNAGEAeAAgAE0AQQBUAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBXAGEAcgBtAFwAIgAsACAAXAAiAGUiIAAyADYAIABDAFwAIgAsACAAMgA2ACwAIAA5ADkAOQA5ADkAOQA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBUAGUAbQBwAGUAcgBhAHQAZQBcACIALAAgAFwAIgAxADUAIAAtACAAMgA1ACAAQwBcACIALAAgADEANQAsACAAMgA1AC4AOQA5ADkAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAQwBvAG8AbABcACIALAAgAFwAIgBkIiAAMQA0ACAAQwBcACIALAAgAC0AOQA5ADkAOQA5ADkALAAgADEANAAuADkAOQA5AFwAbgAgACAAIAAgACAAIAAgACAAfQAsACAAcgAsACAAYwApAFwAbgAgACAAIAAgACAAIAApAFwAbgAgACAAIAAgACkAXABuACAAIAApADsAXABuAFwAbgAvACoAIABcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBSAGEAaQBuAGYAYQBsAGwAWgBvAG4AZQBzAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuACoALwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFIAYQBpAG4AZgBhAGwAbABaAG8AbgBlAHMAXwBUAGkAdABsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFYARQBFAFIARwAgAEEAdQBzAHQAcgBhAGwAaQBhAG4AIAByAGEAaQBuAGYAYQBsAGwAIAB6AG8AbgBlAHMAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFIAYQBpAG4AZgBhAGwAbABaAG8AbgBlAHMAXwBWAGEAcgBpAGEAYgBsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBSAGEAaQBuAGYAYQBsAGwAWgBvAG4AZQBzAF8AVQBuAGkAdABcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFIAYQBpAG4AZgBhAGwAbABaAG8AbgBlAHMAXwBTAG8AdQByAGMAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAVgBFAEUAUgBHACAAMgAwADIANgA6ACAAVABhAGIAbABlACAAMQAuADMAOgAgAEMAbABpAG0AYQB0AGUAIABhAG4AZAAgAFIAYQBpAG4AZgBhAGwAbAAgAHoAbwBuAGUAIABjAGwAYQBzAHMAaQBmAGkAYwBhAHQAaQBvAG4AcwAgAGEAbgBkACAAZABlAGYAaQBuAGkAdABpAG8AbgBzAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBSAGEAaQBuAGYAYQBsAGwAWgBvAG4AZQBzAF8AVgBhAHIAaQBhAHQAaQBvAG4AXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFYAQQBSAEkAQQBUAEkATwBOACAATwBGACAAUwBPAFUAUgBDAEUAIABEAEEAVABBADoAIABBAGQAZABlAGQAIABlAHgAdAByAGEAIABSAGEAaQBuAGYAYQBsAGwAIABtAGkAbgAgAGEAbgBkACAAUgBhAGkAbgBmAGEAbABsACAAbQBhAHgAIABjAG8AbAB1AG0AbgBzACAAdABvACAAYwBhAGwAYwB1AGwAYQB0AGUAIAB6AG8AbgBlACAAZgByAG8AbQAgAHIAZQBhAGwAIAByAGEAaQBuAGYAYQBsAGwAIABkAGEAdABhAC4AXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFIAYQBpAG4AZgBhAGwAbABaAG8AbgBlAHMAXwBEAGEAdABhAFwAbgAgACAAIAA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAATQBBAEsARQBBAFIAUgBBAFkAKAAzACwAIAA0ACwAIABcAG4AIAAgACAAIAAgACAATABBAE0AQgBEAEEAKAByACwAYwAsACAAXABuACAAIAAgACAAIAAgACAAIABJAE4ARABFAFgAKAB7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBSAGEAaQBuAGYAYQBsAGwAIABaAG8AbgBlAFwAIgAsACAAXAAiAEEAbgBuAHUAYQBsACAAcgBhAGkAbgBmAGEAbABsAFwAIgAsACAAXAAiAFIAYQBpAG4AZgBhAGwAbAAgAG0AaQBuAFwAIgAsACAAXAAiAFIAYQBpAG4AZgBhAGwAbAAgAG0AYQB4AFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBIAGkAZwBoACAAcgBhAGkAbgBmAGEAbABsAFwAIgAsACAAXAAiAEEAbgBuAHUAYQBsACAAcgBhAGkAbgBmAGEAbABsACAAPgAgADYAMAAwAG0AbQBcACIALAAgADYAMAAwAC4AMAAwADEALAAgADkAOQA5ADkAOQA5ADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEwAbwB3ACAAcgBhAGkAbgBmAGEAbABsAFwAIgAsACAAXAAiAEEAbgBuAHUAYQBsACAAcgBhAGkAbgBmAGEAbABsACAAZCIgADYAMAAwAG0AbQBcACIALAAgAC0AOQA5ADkAOQA5ADkALAAgADYAMAAwAFwAbgAgACAAIAAgACAAIAAgACAAfQAsACAAcgAsACAAYwApAFwAbgAgACAAIAAgACAAIAApAFwAbgAgACAAIAAgACkAXABuACAAIAApADsAXABuAFwAbgAvACoAIABcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBMAGUAYQBjAGgAaQBuAGcAWgBvAG4AZQBzAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuACoALwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEwAZQBhAGMAaABpAG4AZwBaAG8AbgBlAHMAXwBUAGkAdABsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFYARQBFAFIARwAgAEEAdQBzAHQAcgBhAGwAaQBhAG4AIABsAGUAYQBjAGgAaQBuAGcAIAB6AG8AbgBlAHMAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEwAZQBhAGMAaABpAG4AZwBaAG8AbgBlAHMAXwBWAGEAcgBpAGEAYgBsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBMAGUAYQBjAGgAaQBuAGcAWgBvAG4AZQBzAF8AVQBuAGkAdABcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEwAZQBhAGMAaABpAG4AZwBaAG8AbgBlAHMAXwBTAG8AdQByAGMAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAVgBFAEUAUgBHACAAMgAwADIANgA6ACAAVABhAGIAbABlACAAMQAuADMAOgAgAEMAbABpAG0AYQB0AGUAIABhAG4AZAAgAFIAYQBpAG4AZgBhAGwAbAAgAHoAbwBuAGUAIABjAGwAYQBzAHMAaQBmAGkAYwBhAHQAaQBvAG4AcwAgAGEAbgBkACAAZABlAGYAaQBuAGkAdABpAG8AbgBzAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBMAGUAYQBjAGgAaQBuAGcAWgBvAG4AZQBzAF8AVgBhAHIAaQBhAHQAaQBvAG4AXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBMAGUAYQBjAGgAaQBuAGcAWgBvAG4AZQBzAF8ARABhAHQAYQBcAG4AIAAgACAAPQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAE0AQQBLAEUAQQBSAFIAQQBZACgANAAsACAAMgAsACAAXABuACAAIAAgACAAIAAgAEwAQQBNAEIARABBACgAcgAsAGMALAAgAFwAbgAgACAAIAAgACAAIAAgACAASQBOAEQARQBYACgAewBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIATABlAGEAYwBoAGkAbgBnACAAWgBvAG4AZQBcACIALAAgAFwAIgBMAGUAYQBjAGgAaQBuAGcAIABjAHIAaQB0AGUAcgBpAGEAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEwAZQBhAGMAaABpAG4AZwAgAG8AYwBjAHUAcgBzAFwAIgAsACAAXAAiAKMDKAA12F/cNdhO3DXYVtw12FvcKQA+AKMDKAA12DjcNdhH3DAAKQArADXYYNw12FzcNdhW3DXYWdwgADXYZNw12E7cNdhh3DXYUtw12F/cIAAOITXYXNw12FncNdhR3DXYVtw12FvcNdhU3CAANdhQ3DXYTtw12F3cNdhO3DXYUNw12FbcNdhh3DXYZtxcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIATABlAGEAYwBoAGkAbgBnACAAZABvAGUAcwAgAG4AbwB0ACAAbwBjAGMAdQByAFwAIgAsACAAXAAiAKMDKAA12F/cNdhO3DXYVtw12FvcKQBkIqMDKAA12DjcNdhH3DAAKQArADXYYNw12FzcNdhW3DXYWdwgADXYZNw12E7cNdhh3DXYUtw12F/cIAAOITXYXNw12FncNdhR3DXYVtw12FvcNdhU3CAANdhQ3DXYTtw12F3cNdhO3DXYUNw12FbcNdhh3DXYZtxcACIAXABuACAAIAAgACAAIAAgACAAIAB9ACwAIAByACwAIABjACkAXABuACAAIAAgACAAIAAgACkAXABuACAAIAAgACAAKQBcAG4AIAAgACkAOwBcAG4AXABuAC8AKgAgAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAcgBhAGMAVwBFAFQAXABuADUALgA1AC4AMgAuADMAIABDAG8AbgBzAHQAYQBuAHQAIABQAGEAcgBhAG0AZQB0AGUAcgBzAFwAbgBGAHIAYQBjAHQAaQBvAG4AIABvAGYAIABOACAAdABoAGEAdAAgAGkAcwAgAGEAdgBhAGkAbABhAGIAbABlACAAZgBvAHIAIABsAGUAYQBjAGgAaQBuAGcAIABhAG4AZAAgAHIAdQBuAG8AZgBmAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuACoALwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAcgBhAGMAVwBFAFQAXwBUAGkAdABsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAEYAcgBhAGMAdABpAG8AbgAgAG8AZgAgAE4AIAB0AGgAYQB0ACAAaQBzACAAYQB2AGEAaQBsAGEAYgBsAGUAIABmAG8AcgAgAGwAZQBhAGMAaABpAG4AZwAgAGEAbgBkACAAcgB1AG4AbwBmAGYAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAcgBhAGMAVwBFAFQAXwBVAG4AaQB0AFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgAoAEQAaQBtAGUAbgBzAGkAbwBuAGwAZQBzAHMAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAcgBhAGMAVwBFAFQAXwBTAG8AdQByAGMAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAVgBFAEUAUgBHACAAMgAwADIANgA6ADUALgA1AC4AMgAuADMAIABDAG8AbgBzAHQAYQBuAHQAIABQAGEAcgBhAG0AZQB0AGUAcgBzAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAHIAYQBjAFcARQBUAF8ATgBJAFIAUgBlAGYAZQByAGUAbgBjAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAHIAYQBjAFcARQBUAF8ARABhAHQAYQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABNAEEASwBFAEEAUgBSAEEAWQAoADMALAAgADIALAAgAFwAbgAgACAAIAAgACAAIABMAEEATQBCAEQAQQAoAHIALABjACwAIABcAG4AIAAgACAAIAAgACAAIAAgAEkATgBEAEUAWAAoAHsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEkAcwAgAGkAbgAgAGwAZQBhAGMAaABpAG4AZwAgAHoAbwBuAGUAXAAiACwAXAAiAEYAcgBhAGMAVwBFAFQAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFkAZQBzACAALQAgAGkAbgAgAGwAZQBhAGMAaABpAG4AZwAgAHoAbwBuAGUAXAAiACwAIAAxADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAE4AbwAgAC0AIABuAG8AdAAgAGkAbgAgAGwAZQBhAGMAaABpAG4AZwAgAHoAbwBuAGUAXAAiACwAIAAwAFwAbgAgACAAIAAgACAAIAAgACAAfQAsACAAcgAsACAAYwApAFwAbgAgACAAIAAgACAAIAApAFwAbgAgACAAIAAgACkAXABuACAAIAApADsAXABuAFwAbgAgACAAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgByAGEAYwBXAEUAVABfAFYAYQByAGkAYQB0AGkAbwBuAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoACgAXAAiAFwAIgApACkAOwBcAG4AXABuAFwAbgBcAG4ALwAqACAAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABhAHQAYQBTAGMAbwByAGUAcwBfAFMAYwBvAHAAZQAzAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuACoALwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEQAYQB0AGEAUwBjAG8AcgBlAHMAXwBTAGMAbwBwAGUAMwBfAFQAaQB0AGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAQQB1AHMAdAByAGEAbABpAGEAbgAgAGQAYQB0AGEAIABzAGMAbwByAGUAcwAgAGYAbwByACAAcwBjAG8AcABlACAAMwBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABhAHQAYQBTAGMAbwByAGUAcwBfAFMAYwBvAHAAZQAzAF8AVgBhAHIAaQBhAGIAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABhAHQAYQBTAGMAbwByAGUAcwBfAFMAYwBvAHAAZQAzAF8AVQBuAGkAdABcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEQAYQB0AGEAUwBjAG8AcgBlAHMAXwBTAGMAbwBwAGUAMwBfAFMAbwB1AHIAYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBWAEUARQBSAEcAIAAyADAAMgA2ADoAIABYAFgAWABYAFgAWABYAFgAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEQAYQB0AGEAUwBjAG8AcgBlAHMAXwBTAGMAbwBwAGUAMwBfAFYAYQByAGkAYQB0AGkAbwBuAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABhAHQAYQBTAGMAbwByAGUAcwBfAFMAYwBvAHAAZQAzAF8ARABhAHQAYQBcAG4AIAAgACAAPQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAE0AQQBLAEUAQQBSAFIAQQBZACgANgAsACAAMgAsACAAXABuACAAIAAgACAAIAAgAEwAQQBNAEIARABBACgAcgAsAGMALAAgAFwAbgAgACAAIAAgACAAIAAgACAASQBOAEQARQBYACgAewBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIARABhAHQAYQAgAHMAbwB1AHIAYwBlAFwAIgAsACAAXAAiAEQAYQB0AGEAIABzAGMAbwByAGUAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEkAbgB0AGUAcgBuAGEAdABpAG8AbgBhAGwAIABzAGMAbwBwAGUAIAAzACAAZABhAHQAYQBiAGEAcwBlAFwAIgAsACAAMQA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBBAHUAcwB0AHIAYQBsAGkAYQBuACAAcwBjAG8AcABlACAAMwAgAGQAYQB0AGEAYgBhAHMAZQBcACIALAAgADIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAUwB0AGEAdABlACAAbwByACAAcgBlAGcAaQBvAG4AYQBsACAAcwBjAG8AcABlACAAMwAgAGQAYQB0AGEAYgBhAHMAZQBcACIALAAgADMAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIARQBtAGkAcwBzAGkAbwBuAHMAIABpAG4AdABlAG4AcwBpAHQAeQAgAGMAYQBsAGMAdQBsAGEAdABlAGQAIABmAHIAbwBtACAAYQBwAHAAcgBvAHYAZQBkACAAbQBlAHQAaABvAGQAXAAiACwAIAA0ADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFYAZQByAGkAZgBpAGUAZAAgAGMAcgBlAGQAZQBuAHQAaQBhAGwAIABtAGEAdABjAGgAaQBuAGcAIABJAFMATwAxADQAMAA2ADcAXAAiACwAIAA1AFwAbgAgACAAIAAgACAAIAAgACAAfQAsACAAcgAsACAAYwApAFwAbgAgACAAIAAgACAAIAApAFwAbgAgACAAIAAgACkAXABuACAAIAApADsAXABuAFwAbgBcAG4ALwAqACAAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgByAGEAYwBMAEUAQQBDAEgAXABuADUALgA1AC4AMgAuADMAIABDAG8AbgBzAHQAYQBuAHQAIABQAGEAcgBhAG0AZQB0AGUAcgBzAFwAbgBGAHIAYQBjAHQAaQBvAG4AIABvAGYAIABOACAAdABoAGEAdAAgAGkAcwAgAGEAdgBhAGkAbABhAGIAbABlACAAZgBvAHIAIABsAGUAYQBjAGgAaQBuAGcAIABhAG4AZAAgAHIAdQBuAG8AZgBmAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuACoALwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAcgBhAGMATABFAEEAQwBIAF8AVABpAHQAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBGAHIAYQBjAHQAaQBvAG4AIABvAGYAIABOACAAdABoAGEAdAAgAGkAcwAgAGEAdgBhAGkAbABhAGIAbABlACAAZgBvAHIAIABsAGUAYQBjAGgAaQBuAGcAIABhAG4AZAAgAHIAdQBuAG8AZgBmAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAHIAYQBjAEwARQBBAEMASABfAFUAbgBpAHQAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiACgARABpAG0AZQBuAHMAaQBvAG4AbABlAHMAcwBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgByAGEAYwBMAEUAQQBDAEgAXwBTAG8AdQByAGMAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAVgBFAEUAUgBHACAAMgAwADIANgA6ADUALgA1AC4AMgAuADMAIABDAG8AbgBzAHQAYQBuAHQAIABQAGEAcgBhAG0AZQB0AGUAcgBzAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAHIAYQBjAEwARQBBAEMASABfAE4ASQBSAFIAZQBmAGUAcgBlAG4AYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBOAGEAdABpAG8AbgBhAGwAIABJAG4AdgBlAG4AdABvAHIAeQAgAFIAZQBwAG8AcgB0ACAAVgBvAGwAdQBtAGUAIAAxADoAIABMAGUAYQBjAGgAaQBuAGcAIABhAG4AZAAgAHIAdQBuAG8AZgBmACAAKAAzAC4ARAAuAGIALgAyACkAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAcgBhAGMATABFAEEAQwBIAF8ARABhAHQAYQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABNAEEASwBFAEEAUgBSAEEAWQAoADEALAAgADIALAAgAFwAbgAgACAAIAAgACAAIABMAEEATQBCAEQAQQAoAHIALABjACwAIABcAG4AIAAgACAAIAAgACAAIAAgAEkATgBEAEUAWAAoAHsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEYAcgBhAGMATABFAEEAQwBIAFwAIgAsADAALgAyADQAXABuACAAIAAgACAAIAAgACAAIAB9ACwAIAByACwAIABjACkAXABuACAAIAAgACAAIAAgACkAXABuACAAIAAgACAAKQBcAG4AIAAgACkAOwBcAG4AXABuACAAIABDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAHIAYQBjAEwARQBBAEMASABfAFYAYQByAGkAYQB0AGkAbwBuAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoACgAXAAiAFwAIgApACkAOwBcAG4AXABuAFwAbgBcAG4ALwAqACAAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAGwAZQBhAGMAaABcAG4ANQAuADUALgAyAC4AMwAgAEMAbwBuAHMAdABhAG4AdAAgAFAAYQByAGEAbQBlAHQAZQByAHMAXABuAEUAbQBpAHMAcwBpAG8AbgAgAGYAYQBjAHQAbwByACAAZgBvAHIAIABuAGkAdAByAG8AZwBlAG4AIABsAGUAYQBjAGgAaQBuAGcAIABhAG4AZAAgAHIAdQBuAG8AZgBmAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuACoALwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEUARgBsAGUAYQBjAGgAXwBUAGkAdABsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAEUAbQBpAHMAcwBpAG8AbgAgAGYAYQBjAHQAbwByACAAZgBvAHIAIABuAGkAdAByAG8AZwBlAG4AIABsAGUAYQBjAGgAaQBuAGcAIABhAG4AZAAgAHIAdQBuAG8AZgBmAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYAbABlAGEAYwBoAF8AVQBuAGkAdABcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAKABrAGcAIABOADIATwAtAE4AIAAvACAAawBnACAATgBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAGwAZQBhAGMAaABfAFMAbwB1AHIAYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBWAEUARQBSAEcAIAAyADAAMgA2ADoANQAuADUALgAyAC4AMwAgAEMAbwBuAHMAdABhAG4AdAAgAFAAYQByAGEAbQBlAHQAZQByAHMAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEUARgBsAGUAYQBjAGgAXwBOAEkAUgBSAGUAZgBlAHIAZQBuAGMAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIATgBhAHQAaQBvAG4AYQBsACAASQBuAHYAZQBuAHQAbwByAHkAIABSAGUAcABvAHIAdAAgAFYAbwBsAHUAbQBlACAAMQA6ACAARQBxAHUAYQB0AGkAbwBuACAAMwAuAEQALgBCAF8AMQAwAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYAbABlAGEAYwBoAF8ARABhAHQAYQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABNAEEASwBFAEEAUgBSAEEAWQAoADEALAAgADIALAAgAFwAbgAgACAAIAAgACAAIABMAEEATQBCAEQAQQAoAHIALABjACwAIABcAG4AIAAgACAAIAAgACAAIAAgAEkATgBEAEUAWAAoAHsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEUARgBsAGUAYQBjAGgAXAAiACwAMAAuADAAMQAxAFwAbgAgACAAIAAgACAAIAAgACAAfQAsACAAcgAsACAAYwApAFwAbgAgACAAIAAgACAAIAApAFwAbgAgACAAIAAgACkAXABuACAAIAApADsAXABuAFwAbgAgACAAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAGwAZQBhAGMAaABfAFYAYQByAGkAYQB0AGkAbwBuAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoACgAXAAiAFwAIgApACkAOwBcAG4AXABuAFwAbgAvACoAIABcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYATgAyAE8AXABuAFQAYQBiAGwAZQAgAEEALgAyAC4AMgAuADEAXABuAE4AaQB0AHIAbwB1AHMAIABvAHgAaQBkAGUAIABlAG0AaQBzAHMAaQBvAG4AIABmAGEAYwB0AG8AcgBzACAAZgBvAHIAIABpAG4AbwByAGcAYQBuAGkAYwAgAGYAZQByAHQAaQBsAGkAcwBlAHIAIABhAHAAcABsAGkAYwBhAHQAaQBvAG4AIAAoAGsAZwAgAE4AMgBPAC0ATgAvAGsAZwAgAE4AKQAgACgARQBGAE4AMgBPACkAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AKgAvAFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAE4AMgBPAF8AVABpAHQAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBOAGkAdAByAG8AdQBzACAAbwB4AGkAZABlACAAZQBtAGkAcwBzAGkAbwBuACAAZgBhAGMAdABvAHIAcwAgAGYAbwByACAAaQBuAG8AcgBnAGEAbgBpAGMAIABmAGUAcgB0AGkAbABpAHMAZQByACAAYQBwAHAAbABpAGMAYQB0AGkAbwBuAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYATgAyAE8AXwBVAG4AaQB0AFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgAoAGsAZwAgAE4AMgBPAC0ATgAgAC8AIABrAGcAIABOAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYATgAyAE8AXwBTAG8AdQByAGMAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAVgBFAEUAUgBHACAAMgAwADIANgA6ACAAVABhAGIAbABlACAAQQAuADIALgAyAC4AMQBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAE4AMgBPAF8ATgBJAFIAUgBlAGYAZQByAGUAbgBjAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYATgAyAE8AXwBEAGEAdABhAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAE0AQQBLAEUAQQBSAFIAQQBZACgAMQA1ACwAIAA1ACwAIABcAG4AIAAgACAAIAAgACAATABBAE0AQgBEAEEAKAByACwAYwAsACAAXABuACAAIAAgACAAIAAgACAAIABJAE4ARABFAFgAKAB7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBQAHIAbwBkAHUAYwB0AGkAbwBuACAAcwB5AHMAdABlAG0AIABqAFwAIgAsAFwAIgBFAEYATgAyAE8AXAAiACwAIABcACIAUAByAG8AZAB1AGMAdABpAG8AbgAgAHMAeQBzAHQAZQBtACAAbwBuAGwAeQBcACIALAAgAFwAIgBJAHIAcgBpAGcAYQB0AGkAbwBuACAAbQBlAHQAaABvAGQAXAAiACwAIABcACIAUgBhAGkAbgBmAGEAbABsACAAegBvAG4AZQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIASQByAHIAaQBnAGEAdABlAGQAIABwAGEAcwB0AHUAcgBlAFwAIgAsADAALgAwADAANQA5ACwAIABcACIAUABhAHMAdAB1AHIAZQBcACIALAAgAFwAIgBBAG4AeQBcACIALAAgAFwAIgBBAG4AeQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIASQByAHIAaQBnAGEAdABlAGQAIABjAHIAbwBwAFwAIgAsADAALgAwADAANwAsACAAXAAiAEMAcgBvAHAAXAAiACwAIABcACIAQQBuAHkAXAAiACwAIABcACIAQQBuAHkAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAE4AbwBuAC0AaQByAHIAaQBnAGEAdABlAGQAIABwAGEAcwB0AHUAcgBlAFwAIgAsADAALgAwADAAMQA4ACwAIABcACIAUABhAHMAdAB1AHIAZQBcACIALAAgAFwAIgBOAG8AdAAgAGkAcgByAGkAZwBhAHQAZQBkAFwAIgAsACAAXAAiAEwAbwB3ACAAcgBhAGkAbgBmAGEAbABsAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBOAG8AbgAtAGkAcgByAGkAZwBhAHQAZQBkACAAcABhAHMAdAB1AHIAZQBcACIALAAwAC4AMAAwADEAOAAsACAAXAAiAFAAYQBzAHQAdQByAGUAXAAiACwAIABcACIATgBvAHQAIABpAHIAcgBpAGcAYQB0AGUAZABcACIALAAgAFwAIgBIAGkAZwBoACAAcgBhAGkAbgBmAGEAbABsAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBOAG8AbgAtAGkAcgByAGkAZwBhAHQAZQBkACAAYwByAG8AcAAgACgAbABvAHcAIAByAGEAaQBuAGYAYQBsAGwAKQBcACIALAAwAC4AMAAwADIAOQAsACAAXAAiAEMAcgBvAHAAXAAiACwAIABcACIATgBvAHQAIABpAHIAcgBpAGcAYQB0AGUAZABcACIALAAgAFwAIgBMAG8AdwAgAHIAYQBpAG4AZgBhAGwAbABcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIATgBvAG4ALQBpAHIAcgBpAGcAYQB0AGUAZAAgAGMAcgBvAHAAIAAoAGgAaQBnAGgAIAByAGEAaQBuAGYAYQBsAGwAKQBcACIALAAwAC4AMAAwADgALAAgAFwAIgBDAHIAbwBwAFwAIgAsACAAXAAiAE4AbwB0ACAAaQByAHIAaQBnAGEAdABlAGQAXAAiACwAIABcACIASABpAGcAaAAgAHIAYQBpAG4AZgBhAGwAbABcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAUwB1AGcAYQByAFwAIgAsADAALgAwADEAOQA5ACwAIABcACIAUwB1AGcAYQByAFwAIgAsACAAXAAiAEEAbgB5AFwAIgAsACAAXAAiAEEAbgB5AFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBDAG8AdAB0AG8AbgBcACIALAAwAC4AMAAwADUAMwAsACAAXAAiAEMAbwB0AHQAbwBuAFwAIgAsACAAXAAiAEEAbgB5AFwAIgAsACAAXAAiAEEAbgB5AFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBIAG8AcgB0AGkAYwB1AGwAdAB1AHIAYQBsACAAYwByAG8AcABzAFwAIgAsADAALgAwADAANgA0ACwAIABcACIASABvAHIAdABpAGMAdQBsAHQAdQByAGEAbAAgAGMAcgBvAHAAcwBcACIALAAgAFwAIgBBAG4AeQBcACIALAAgAFwAIgBBAG4AeQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAUgBpAGMAZQAgACgAYwBvAG4AdABpAG4AdQBvAHUAcwAgAGYAbABvAG8AZABpAG4AZwApAFwAIgAsADAALgAwADAAMwAsACAAXAAiAFIAaQBjAGUAXAAiACwAIABcACIAQwBvAG4AdABpAG4AdQBvAHUAcwAgAGYAbABvAG8AZABpAG4AZwBcACIALAAgAFwAIgBBAG4AeQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAUgBpAGMAZQAgACgAcwBpAG4AZwBsAGUAIABhAG4AZAAgAG0AdQBsAHQAaQBwAGwAZQAgAGQAcgBhAGkAbgBhAGcAZQAsACAAbwByACAAYQBsAHQAZQByAG4AYQB0AGUAIAB3AGUAdAB0AGkAbgBnACAAYQBuAGQAIABkAHIAeQBpAG4AZwApAFwAIgAsADAALgAwADAANQAsACAAXAAiAFIAaQBjAGUAXAAiACwAIABcACIAUwBpAG4AZwBsAGUAIABhAG4AZAAgAG0AdQBsAHQAaQBwAGwAZQAgAGQAcgBhAGkAbgBhAGcAZQAsACAAbwByACAAYQBsAHQAZQByAG4AYQB0AGUAIAB3AGUAdAB0AGkAbgBnACAAYQBuAGQAIABkAHIAeQBpAG4AZwBcACIALAAgAFwAIgBBAG4AeQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAQQBxAHUAYQBjAHUAbAB0AHUAcgBlAFwAIgAsADAALgAwADAAMgA2ACwAIABcACIAQQBxAHUAYQBjAHUAbAB0AHUAcgBlAFwAIgAsACAAXAAiAEEAbgB5AFwAIgAsACAAXAAiAEEAbgB5AFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBGAG8AcgBlAHMAdAByAHkAXAAiACwAMAAuADAAMAAxADgALAAgAFwAIgBGAG8AcgBlAHMAdAByAHkAXAAiACwAIABcACIAQQBuAHkAXAAiACwAIABcACIAQQBuAHkAXAAiAFwAbgAgACAAIAAgACAAIAAgACAAfQAsACAAcgAsACAAYwApAFwAbgAgACAAIAAgACAAIAApAFwAbgAgACAAIAAgACkAXABuACAAIAApADsAXABuAFwAbgAgACAAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAE4AMgBPAF8AVgBhAHIAaQBhAHQAaQBvAG4AXABuACAAIAA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAATQBBAEsARQBBAFIAUgBBAFkAKAA1ACwAIAAxACwAIABcAG4AIAAgACAAIAAgACAATABBAE0AQgBEAEEAKAByACwAYwAsACAAXABuACAAIAAgACAAIAAgACAAIABJAE4ARABFAFgAKAB7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBWAEEAUgBJAEEAVABJAE8ATgAgAE8ARgAgAFMATwBVAFIAQwBFACAARABBAFQAQQA6AFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBSAGUAbQBvAHYAZQBkACAAZAB1AHAAbABpAGMAYQB0AGUAIAAnAEEAcQB1AGEAYwB1AGwAdAB1AHIAZQAnACAAcgBvAHcALgBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAUgBlAG0AbwB2AGUAZAAgAGEAcwB0AGUAcgBpAHMAawBzACAAdABvACAAYQBpAGQAIABsAG8AbwBrAHUAcAAuAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBBAGQAZABlAGQAIAAnAHAAcgBvAGQAdQBjAHQAaQBvAG4AIABzAHkAcwB0AGUAbQAgAG8AbgBsAHkAJwAsACAAJwByAGEAaQBuAGYAYQBsAGwAIAB6AG8AbgBlACcAIABhAG4AZAAgACcAaQByAHIAaQBnAGEAdABpAG8AbgAgAG0AZQB0AGgAbwBkACcAIABjAG8AbAB1AG0AbgBzACAAdABvACAAYQBpAGQAIABsAG8AbwBrAHUAcAAuAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBEAHUAcABsAGkAYwBhAHQAZQBkACAAJwBuAG8AbgAtAGkAcgByAGkAZwBhAHQAZQBkACAAcABhAHMAdAB1AHIAZQAnACAAcgBvAHcAIAB3AGkAdABoACAAcwBhAG0AZQAgAEUARgAgAGYAbwByACAAbABvAHcAIABhAG4AZAAgAGgAaQBnAGgAIAByAGEAaQBuAGYAYQBsAGwAIAB6AG8AbgBlAHMAIAB0AG8AIABhAGkAZAAgAGwAbwBvAGsAdQBwAC4AXAAiAFwAbgAgACAAIAAgACAAIAAgACAAfQAsACAAcgAsACAAYwApAFwAbgAgACAAIAAgACAAIAApAFwAbgAgACAAIAAgACkAXABuACAAIAApADsAXABuAFwAbgAvACoAIABcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAHIAYQBjAFcARQBUAEkAcgByAGkAZwBhAHQAaQBvAG4AXABuAFYARQBFAFIARwAgADIAMAAyADYAOgAgAEMAaABhAHAAdABlAHIAIAAxACwAIABzAGUAYwB0AGkAbwBuACAAMQAuADgALgAyACAATABlAGEAYwBoAGkAbgBnACwAIABjAGwAaQBtAGEAdABlACAAYQBuAGQAIAByAGEAaQBuAGYAYQBsAGwAIAB6AG8AbgBlAHMAXABuAEkAUABDAEMAOgAgAE4AMgBPACAARQBNAEkAUwBTAEkATwBOAFMAIABGAFIATwBNACAATQBBAE4AQQBHAEUARAAgAFMATwBJAEwAUwAsACAAQQBOAEQAIABDAE8AMgAgAEUATQBJAFMAUwBJAE8ATgBTACAARgBSAE8ATQAgAEwASQBNAEUAIABBAE4ARAAgAFUAUgBFAEEAIABBAFAAUABMAEkAQwBBAFQASQBPAE4AXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AKgAvAFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgByAGEAYwBXAEUAVABJAHIAcgBpAGcAYQB0AGkAbwBuAF8AVABpAHQAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBGAHIAYQBjAFcARQBUACAAZgBvAHIAIABpAHIAcgBpAGcAYQB0AGkAbwBuACAAdAB5AHAAZQBzAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAHIAYQBjAFcARQBUAEkAcgByAGkAZwBhAHQAaQBvAG4AXwBVAG4AaQB0AFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBkAGkAbQBlAG4AcwBpAG8AbgBsAGUAcwBzAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAHIAYQBjAFcARQBUAEkAcgByAGkAZwBhAHQAaQBvAG4AXwBTAG8AdQByAGMAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAVgBFAEUAUgBHACAAMgAwADIANgA6ACAAQwBoAGEAcAB0AGUAcgAgADEALAAgAHMAZQBjAHQAaQBvAG4AIAAxAC4AOAAuADIAIABMAGUAYQBjAGgAaQBuAGcALAAgAGMAbABpAG0AYQB0AGUAIABhAG4AZAAgAHIAYQBpAG4AZgBhAGwAbAAgAHoAbwBuAGUAcwBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgByAGEAYwBXAEUAVABJAHIAcgBpAGcAYQB0AGkAbwBuAF8ATgBJAFIAUgBlAGYAZQByAGUAbgBjAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAEkAUABDAEMAIAAyADAAMQA5ACAAUgBlAGYAaQBuAGUAbQBlAG4AdAAgAFYAbwBsAHUAbQBlACAANAA6ACAAQwBoAGEAcAB0AGUAcgAgADEAMQA6ACAATgAyAE8AIABFAG0AaQBzAHMAaQBvAG4AcwAgAGYAcgBvAG0AIABNAGEAbgBhAGcAZQBkACAAUwBvAGkAbABzACwAIABhAG4AZAAgAEMATwAyACAARQBtAGkAcwBzAGkAbwBuAHMAIABmAHIAbwBtACAATABpAG0AZQAgAGEAbgBkACAAVQByAGUAYQAgAEEAcABwAGwAaQBjAGEAdABpAG8AbgBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgByAGEAYwBXAEUAVABJAHIAcgBpAGcAYQB0AGkAbwBuAF8ARABhAHQAYQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABNAEEASwBFAEEAUgBSAEEAWQAoADYALAAgADIALAAgAFwAbgAgACAAIAAgACAAIABMAEEATQBCAEQAQQAoAHIALABjACwAIABcAG4AIAAgACAAIAAgACAAIAAgAEkATgBEAEUAWAAoAHsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEkAcgByAGkAZwBhAHQAaQBvAG4AIAB0AHkAcABlACAAaQByAFwAIgAsAFwAIgBGAHIAYQBjAFcARQBUAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBOAG8AdAAgAGkAcgByAGkAZwBhAHQAZQBkAFwAIgAsACAAMAA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBEAHIAaQBwACAAaQByAHIAaQBnAGEAdABpAG8AbgBcACIALAAgADAAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAUwBwAHIAaQBuAGsAbABlAHIAIABpAHIAcgBpAGcAYQB0AGkAbwBuAFwAIgAsACAAMQA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBTAHUAcgBmAGEAYwBlACAAaQByAHIAaQBnAGEAdABpAG8AbgBcACIALAAgADEAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIATwB0AGgAZQByACAAaQByAHIAaQBnAGEAdABpAG8AbgBcACIALAAgADEAXABuACAAIAAgACAAIAAgACAAIAB9ACwAIAByACwAIABjACkAXABuACAAIAAgACAAIAAgACkAXABuACAAIAAgACAAKQBcAG4AIAAgACkAOwBcAG4AXABuACAAIABDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAHIAYQBjAFcARQBUAEkAcgByAGkAZwBhAHQAaQBvAG4AXwBWAGEAcgBpAGEAdABpAG8AbgBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAVgBBAFIASQBBAFQASQBPAE4AIABGAFIATwBNACAAUwBPAFUAUgBDAEUAIABEAEEAVABBADoAIABUAGEAYgBsAGUAIABjAHIAZQBhAHQAZQBkACAAYgBhAHMAZQBkACAAbwBuACAAVgBFAEUAUgBHACAAdABlAHgAdAAgACcAQQByAGUAYQBzACAAYQByAGUAIABzAHUAYgBqAGUAYwB0ACAAdABvACAAbABlAGEAYwBoAGkAbgBnACAAKABpAC4AZQAuACwAIABpAG4AIAB0AGgAZQAgAGwAZQBhAGMAaABpAG4AZwAgAHoAbwBuAGUAKQAgAHcAaABlAG4ALgAuAC4AIAB0AGgAZQAgAGwAYQBuAGQAIABpAHMAIABpAHIAcgBpAGcAYQB0AGUAZAAgACgAZQB4AGMAZQBwAHQAIABkAHIAaQBwACAAaQByAHIAaQBnAGEAdABpAG8AbgApAC4AJwBcACIAKQA7AFwAbgBcAG4AXABuAC8AKgAgAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEUARgBQAGEAcwB0AHUAcgBlAFIAYQBuAGcAZQBBAG4AZABQAGEAZABkAG8AYwBrAFwAbgBUAGEAYgBsAGUAIABBAC4AMgAuADIALgAyADoAIABFAG0AaQBzAHMAaQBvAG4AIABmAGEAYwB0AG8AcgAgAGYAbwByACAAdQByAGkAbgBlACAAYQBuAGQAIABkAHUAbgBnACAAZABlAHAAbwBzAGkAdABlAGQAIABvAG4AIABwAGEAcwB0AHUAcgBlACwAIAByAGEAbgBnAGUAIABvAHIAIABwAGEAZABkAG8AYwBrACAAKABrAGcAIABOADIATwAtAE4ALwBrAGcAIABOACkAIAAoAEUARgBQAFIAUAApAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuACoALwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEUARgBQAGEAcwB0AHUAcgBlAFIAYQBuAGcAZQBBAG4AZABQAGEAZABkAG8AYwBrAF8AVABpAHQAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBFAG0AaQBzAHMAaQBvAG4AIABmAGEAYwB0AG8AcgAgAGYAbwByACAAdQByAGkAbgBlACAAYQBuAGQAIABkAHUAbgBnACAAZABlAHAAbwBzAGkAdABlAGQAIABvAG4AIABwAGEAcwB0AHUAcgBlACwAIAByAGEAbgBnAGUAIABvAHIAIABwAGEAZABkAG8AYwBrAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYAUABhAHMAdAB1AHIAZQBSAGEAbgBnAGUAQQBuAGQAUABhAGQAZABvAGMAawBfAFUAbgBpAHQAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAGsAZwAgAE4AMgBPACAALQAgAE4AIAAvACAAawBnACAATgBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAFAAYQBzAHQAdQByAGUAUgBhAG4AZwBlAEEAbgBkAFAAYQBkAGQAbwBjAGsAXwBTAG8AdQByAGMAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAVgBFAEUAUgBHACAAMgAwADIANgA6ACAAVABhAGIAbABlACAAQQAuADIALgAyAC4AMgBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAFAAYQBzAHQAdQByAGUAUgBhAG4AZwBlAEEAbgBkAFAAYQBkAGQAbwBjAGsAXwBOAEkAUgBSAGUAZgBlAHIAZQBuAGMAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEUARgBQAGEAcwB0AHUAcgBlAFIAYQBuAGcAZQBBAG4AZABQAGEAZABkAG8AYwBrAF8ARABhAHQAYQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABNAEEASwBFAEEAUgBSAEEAWQAoADMALAAgADIALAAgAFwAbgAgACAAIAAgACAAIABMAEEATQBCAEQAQQAoAHIALABjACwAIABcAG4AIAAgACAAIAAgACAAIAAgAEkATgBEAEUAWAAoAHsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEMAbABpAG0AYQB0AGUAIAB6AG8AbgBlAFwAIgAsACAAXAAiAEUARgBQAFIAUABcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVwBlAHQAIABjAGwAaQBtAGEAdABlACAAegBvAG4AZQBcACIALAAgADAALgAwADAANgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBEAHIAeQAgAGMAbABpAG0AYQB0AGUAIAB6AG8AbgBlAFwAIgAsACAAMAAuADAAMAAyAFwAbgAgACAAIAAgACAAIAAgACAAfQAsACAAcgAsACAAYwApAFwAbgAgACAAIAAgACAAIAApAFwAbgAgACAAIAAgACkAXABuACAAIAApADsAXABuAFwAbgAgACAAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAFAAYQBzAHQAdQByAGUAUgBhAG4AZwBlAEEAbgBkAFAAYQBkAGQAbwBjAGsAXwBWAGEAcgBpAGEAdABpAG8AbgBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAVgBBAFIASQBBAFQASQBPAE4AIABGAFIATwBNACAAUwBPAFUAUgBDAEUAIABEAEEAVABBADoAIABDAGgAYQBuAGcAZQBkACAAJwBEAHIAeQAgAGMAbABpAG0AYQB0AGUAIAB6AG8AbgBlAHMAJwAgAHQAbwAgAHMAaQBuAGcAdQBsAGEAcgAgACcARAByAHkAIABjAGwAaQBtAGEAdABlACAAegBvAG4AZQAnACAAdABvACAAYQBpAGQAIABsAG8AbwBrAHUAcAAuAFwAIgApADsAXABuAFwAbgBcAG4ALwAqACAAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ATQBvAG4AdABoAHMAVABvAFMAZQBhAHMAbwBuAHMAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AKgAvAFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ATQBvAG4AdABoAHMAVABvAFMAZQBhAHMAbwBuAHMAXwBUAGkAdABsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAE0AbwBuAHQAaABzACAAdABvACAAUwBlAGEAcwBvAG4AcwAgAE0AYQBwAHAAaQBuAGcAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAE0AbwBuAHQAaABzAFQAbwBTAGUAYQBzAG8AbgBzAF8AVQBuAGkAdABcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAE0AbwBuAHQAaABzAFQAbwBTAGUAYQBzAG8AbgBzAF8AUwBvAHUAcgBjAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBNAG8AbgB0AGgAcwBUAG8AUwBlAGEAcwBvAG4AcwBfAE4ASQBSAFIAZQBmAGUAcgBlAG4AYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ATQBvAG4AdABoAHMAVABvAFMAZQBhAHMAbwBuAHMAXwBEAGEAdABhAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAE0AQQBLAEUAQQBSAFIAQQBZACgAMQAzACwAIAAyACwAIABcAG4AIAAgACAAIAAgACAATABBAE0AQgBEAEEAKAByACwAYwAsACAAXABuACAAIAAgACAAIAAgACAAIABJAE4ARABFAFgAKAB7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBNAG8AbgB0AGgAXAAiACwAIABcACIAUwBlAGEAcwBvAG4AXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEoAYQBuAHUAYQByAHkAXAAiACwAIABcACIAUwB1AG0AbQBlAHIAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEYAZQBiAHIAdQBhAHIAeQBcACIALAAgAFwAIgBTAHUAbQBtAGUAcgBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIATQBhAHIAYwBoAFwAIgAsACAAXAAiAEEAdQB0AHUAbQBuAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBBAHAAcgBpAGwAXAAiACwAIABcACIAQQB1AHQAdQBtAG4AXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAE0AYQB5AFwAIgAsACAAXAAiAEEAdQB0AHUAbQBuAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBKAHUAbgBlAFwAIgAsACAAXAAiAFcAaQBuAHQAZQByAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBKAHUAbAB5AFwAIgAsACAAXAAiAFcAaQBuAHQAZQByAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBBAHUAZwB1AHMAdABcACIALAAgAFwAIgBXAGkAbgB0AGUAcgBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAUwBlAHAAdABlAG0AYgBlAHIAXAAiACwAIABcACIAUwBwAHIAaQBuAGcAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAE8AYwB0AG8AYgBlAHIAXAAiACwAIABcACIAUwBwAHIAaQBuAGcAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAE4AbwB2AGUAbQBiAGUAcgBcACIALAAgAFwAIgBTAHAAcgBpAG4AZwBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIARABlAGMAZQBtAGIAZQByAFwAIgAsACAAXAAiAFMAdQBtAG0AZQByAFwAIgBcAG4AIAAgACAAIAAgACAAIAAgAH0ALAAgAHIALAAgAGMAKQBcAG4AIAAgACAAIAAgACAAKQBcAG4AIAAgACAAIAApAFwAbgAgACAAKQA7AFwAbgBcAG4AIAAgAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAE0AbwBuAHQAaABzAFQAbwBTAGUAYQBzAG8AbgBzAF8AVgBhAHIAaQBhAHQAaQBvAG4AXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFwAIgApADsAXABuAFwAbgBcAG4AXABuAC8AKgAgAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAE0AQwBGAFQAZQBtAHAAZQByAGEAdAB1AHIAZQBaAG8AbgBlAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuACoALwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAE0AQwBGAFQAZQBtAHAAZQByAGEAdAB1AHIAZQBaAG8AbgBlAF8AVABpAHQAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBNAGEAbgB1AHIAZQAgAE0AYQBuAGEAZwBlAG0AZQBuAHQAIAATICAATQBlAHQAaABhAG4AZQAgAGMAbwBuAHYAZQByAHMAaQBvAG4AIABmAGEAYwB0AG8AcgAgAHAAZQByACAAdABlAG0AcABlAHIAYQB0AHUAcgBlACAAegBvAG4AZQAgACgAZgByAGEAYwB0AGkAbwBuACkAIAAoAE0AQwBGAGkAbQApAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBNAEMARgBUAGUAbQBwAGUAcgBhAHQAdQByAGUAWgBvAG4AZQBfAFUAbgBpAHQAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAGYAcgBhAGMAdABpAG8AbgBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ATQBDAEYAVABlAG0AcABlAHIAYQB0AHUAcgBlAFoAbwBuAGUAXwBTAG8AdQByAGMAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAVgBFAEUAUgBHACAAMgAwADIANgA6ACAAVABhAGIAbABlACAAQQAuADEALgA4AC4AMQBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ATQBDAEYAVABlAG0AcABlAHIAYQB0AHUAcgBlAFoAbwBuAGUAXwBEAGEAdABhAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAE0AQQBLAEUAQQBSAFIAQQBZACgAMgAyACwAIAAxADYALAAgAFwAbgAgACAAIAAgACAAIABMAEEATQBCAEQAQQAoAHIALABjACwAIABcAG4AIAAgACAAIAAgACAAIAAgAEkATgBEAEUAWAAoAHsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFQAZQBtAHAAZQByAGEAdAB1AHIAZQAgAHoAbwBuAGUAXAAiACwAIABcACIATQBBAFQAIAAoALoAQwApAFwAIgAsACAAXAAiAFUAbgBjAG8AdgBlAHIAZQBkACAAYQBuAGUAcgBvAGIAaQBjACAAbABhAGcAbwBvAG4AXAAiACwAIABcACIAQwBvAHYAZQByAGUAZAAgAGwAYQBnAG8AbwBuAFwAIgAsACAAXAAiAEwAaQBxAHUAaQBkACAAUwBsAHUAcgByAHkAIAAoAHcAaQB0AGgAbwB1AHQAIABuAGEAdAB1AHIAYQBsACAAYwByAHUAcwB0ACkAXAAiACwAIABcACIARABhAGkAbAB5ACAAcwBwAHIAZQBhAGQAIAAoAGIAKQBcACIALAAgAFwAIgBDAG8AbQBwAG8AcwB0AGkAbgBnACAAKABwAGEAcwBzAGkAdgBlACAAdwBpAG4AZAByAG8AdwApAFwAIgAsACAAXAAiAFMAbwBsAGkAZAAgAFMAdABvAHIAYQBnAGUAXAAiACwAIABcACIAUABpAHQAIABTAHQAbwByAGEAZwBlACAAPAAxACAAbQBvAG4AdABoAFwAIgAsACAAXAAiAEQAZQBlAHAAIABMAGkAdAB0AGUAcgBcACIALAAgAFwAIgBQAG8AdQBsAHQAcgB5ACAATQBhAG4AdQByAGUAIAAoAHcAaQB0AGgALwB3AGkAdABoAG8AdQB0ACAAbABpAHQAdABlAHIAKQBcACIALAAgAFwAIgBcACIALAAgAFwAIgBEAGkAcgBlAGMAdAAgAHAAcgBvAGMAZQBzAHMAaQBuAGcAIABpAG4AdABvACAAcABlAGwAbABlAHQAaQB6AGUAZAAgAGYAZQByAHQAaQBsAGkAcwBlAHIAXAAiACwAIABcACIARABpAHIAZQBjAHQAIABhAHAAcABsAGkAYwBhAHQAaQBvAG4AIAB0AG8AIABzAG8AaQBsAFwAIgAsACAAXAAiAFAAYQBzAHQAdQByAGUALAAgAFIAYQBuAGcAZQAgAGEAbgBkACAAUABhAGQAZABvAGMAawAgACgAYwApACgAZAApAFwAIgAsACAAXAAiAE0AQQBUACAAcgBhAHcAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEMAbwBvAGwAXAAiACwAIABcACIAZCIxADAAXAAiACwAIAAwAC4ANgA2ACwAIAAwAC4AMQAsACAAMAAuADEALAAgADAALgAwADAAMQAsACAAMAAuADAAMAA1ACwAIAAwAC4AMAAyACwAIAAwAC4AMAAzACwAIAAwAC4AMAA0ACwAIAAwAC4AMAAxADUALAAgADAALgAwADEANQAsACAAMAAsACAAMAAsACAAMAAuADAAMAA0ADcALAAgADEAMAA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBDAG8AbwBsAFwAIgAsACAAMQAxACwAIAAwAC4ANgA4ACwAIAAwAC4AMQAsACAAMAAuADEAMQAsACAAMAAuADAAMAAxACwAIAAwAC4AMAAwADUALAAgADAALgAwADIALAAgADAALgAwADMALAAgADAALgAwADQALAAgADAALgAwADEANQAsACAAMAAuADAAMQA1ACwAIAAwACwAIAAwACwAIAAwAC4AMAAwADQANwAsACAAMQAxADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEMAbwBvAGwAXAAiACwAIAAxADIALAAgADAALgA3ACwAIAAwAC4AMQAsACAAMAAuADEAMwAsACAAMAAuADAAMAAxACwAIAAwAC4AMAAwADUALAAgADAALgAwADIALAAgADAALgAwADMALAAgADAALgAwADQALAAgADAALgAwADEANQAsACAAMAAuADAAMQA1ACwAIAAwACwAIAAwACwAIAAwAC4AMAAwADQANwAsACAAMQAyADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEMAbwBvAGwAXAAiACwAIAAxADMALAAgADAALgA3ADEALAAgADAALgAxACwAIAAwAC4AMQA0ACwAIAAwAC4AMAAwADEALAAgADAALgAwADAANQAsACAAMAAuADAAMgAsACAAMAAuADAAMwAsACAAMAAuADAANAAsACAAMAAuADAAMQA1ACwAIAAwAC4AMAAxADUALAAgADAALAAgADAALAAgADAALgAwADAANAA3ACwAIAAxADMAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAQwBvAG8AbABcACIALAAgADEANAAsACAAMAAuADcAMwAsACAAMAAuADEALAAgADAALgAxADUALAAgADAALgAwADAAMQAsACAAMAAuADAAMAA1ACwAIAAwAC4AMAAyACwAIAAwAC4AMAAzACwAIAAwAC4AMAA0ACwAIAAwAC4AMAAxADUALAAgADAALgAwADEANQAsACAAMAAsACAAMAAsACAAMAAuADAAMAA0ADcALAAgADEANAA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBUAGUAbQBwAGUAcgBhAHQAZQBcACIALAAgADEANQAsACAAMAAuADcANAAsACAAMAAuADEALAAgADAALgAxADcALAAgADAALgAwADAANQAsACAAMAAuADAAMQAsACAAMAAuADAAMgAsACAAMAAuADAAMwAsACAAMAAuADAANAAsACAAMAAuADAAMQA1ACwAIAAwAC4AMAAxADUALAAgADAALAAgADAALAAgADAALgAwADAANAA3ACwAIAAxADUAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVABlAG0AcABlAHIAYQB0AGUAXAAiACwAIAAxADYALAAgADAALgA3ADUALAAgADAALgAxACwAIAAwAC4AMQA4ACwAIAAwAC4AMAAwADUALAAgADAALgAwADEALAAgADAALgAwADIALAAgADAALgAwADMALAAgADAALgAwADQALAAgADAALgAwADEANQAsACAAMAAuADAAMQA1ACwAIAAwACwAIAAwACwAIAAwAC4AMAAwADQANwAsACAAMQA2ADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFQAZQBtAHAAZQByAGEAdABlAFwAIgAsACAAMQA3ACwAIAAwAC4ANwA2ACwAIAAwAC4AMQAsACAAMAAuADIALAAgADAALgAwADAANQAsACAAMAAuADAAMQAsACAAMAAuADAAMgAsACAAMAAuADAAMwAsACAAMAAuADAANAAsACAAMAAuADAAMQA1ACwAIAAwAC4AMAAxADUALAAgADAALAAgADAALAAgADAALgAwADAANAA3ACwAIAAxADcAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVABlAG0AcABlAHIAYQB0AGUAXAAiACwAIAAxADgALAAgADAALgA3ADcALAAgADAALgAxACwAIAAwAC4AMgAyACwAIAAwAC4AMAAwADUALAAgADAALgAwADEALAAgADAALgAwADIALAAgADAALgAwADMALAAgADAALgAwADQALAAgADAALgAwADEANQAsACAAMAAuADAAMQA1ACwAIAAwACwAIAAwACwAIAAwAC4AMAAwADQANwAsACAAMQA4ADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFQAZQBtAHAAZQByAGEAdABlAFwAIgAsACAAMQA5ACwAIAAwAC4ANwA3ACwAIAAwAC4AMQAsACAAMAAuADIANAAsACAAMAAuADAAMAA1ACwAIAAwAC4AMAAxACwAIAAwAC4AMAAyACwAIAAwAC4AMAAzACwAIAAwAC4AMAA0ACwAIAAwAC4AMAAxADUALAAgADAALgAwADEANQAsACAAMAAsACAAMAAsACAAMAAuADAAMAA0ADcALAAgADEAOQA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBUAGUAbQBwAGUAcgBhAHQAZQBcACIALAAgADIAMAAsACAAMAAuADcAOAAsACAAMAAuADEALAAgADAALgAyADYALAAgADAALgAwADAANQAsACAAMAAuADAAMQAsACAAMAAuADAAMgAsACAAMAAuADAAMwAsACAAMAAuADAANAAsACAAMAAuADAAMQA1ACwAIAAwAC4AMAAxADUALAAgADAALAAgADAALAAgADAALgAwADAANAA3ACwAIAAyADAAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVABlAG0AcABlAHIAYQB0AGUAXAAiACwAIAAyADEALAAgADAALgA3ADgALAAgADAALgAxACwAIAAwAC4AMgA5ACwAIAAwAC4AMAAwADUALAAgADAALgAwADEALAAgADAALgAwADIALAAgADAALgAwADMALAAgADAALgAwADQALAAgADAALgAwADEANQAsACAAMAAuADAAMQA1ACwAIAAwACwAIAAwACwAIAAwAC4AMAAwADQANwAsACAAMgAxADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFQAZQBtAHAAZQByAGEAdABlAFwAIgAsACAAMgAyACwAIAAwAC4ANwA4ACwAIAAwAC4AMQAsACAAMAAuADMAMQAsACAAMAAuADAAMAA1ACwAIAAwAC4AMAAxACwAIAAwAC4AMAAyACwAIAAwAC4AMAAzACwAIAAwAC4AMAA0ACwAIAAwAC4AMAAxADUALAAgADAALgAwADEANQAsACAAMAAsACAAMAAsACAAMAAuADAAMAA0ADcALAAgADIAMgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBUAGUAbQBwAGUAcgBhAHQAZQBcACIALAAgADIAMwAsACAAMAAuADcAOQAsACAAMAAuADEALAAgADAALgAzADQALAAgADAALgAwADAANQAsACAAMAAuADAAMQAsACAAMAAuADAAMgAsACAAMAAuADAAMwAsACAAMAAuADAANAAsACAAMAAuADAAMQA1ACwAIAAwAC4AMAAxADUALAAgADAALAAgADAALAAgADAALgAwADAANAA3ACwAIAAyADMAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVABlAG0AcABlAHIAYQB0AGUAXAAiACwAIAAyADQALAAgADAALgA3ADkALAAgADAALgAxACwAIAAwAC4AMwA3ACwAIAAwAC4AMAAwADUALAAgADAALgAwADEALAAgADAALgAwADIALAAgADAALgAwADMALAAgADAALgAwADQALAAgADAALgAwADEANQAsACAAMAAuADAAMQA1ACwAIAAwACwAIAAwACwAIAAwAC4AMAAwADQANwAsACAAMgA0ADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFQAZQBtAHAAZQByAGEAdABlAFwAIgAsACAAMgA1ACwAIAAwAC4ANwA5ACwAIAAwAC4AMQAsACAAMAAuADQAMQAsACAAMAAuADAAMAA1ACwAIAAwAC4AMAAxACwAIAAwAC4AMAAyACwAIAAwAC4AMAAzACwAIAAwAC4AMAA0ACwAIAAwAC4AMAAxADUALAAgADAALgAwADEANQAsACAAMAAsACAAMAAsACAAMAAuADAAMAA0ADcALAAgADIANQA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBXAGEAcgBtAFwAIgAsACAAMgA2ACwAIAAwAC4ANwA5ACwAIAAwAC4AMQAsACAAMAAuADQANAAsACAAMAAuADAAMQAsACAAMAAuADAAMQA1ACwAIAAwAC4AMAAyACwAIAAwAC4AMAAzACwAIAAwAC4AMAA0ACwAIAAwAC4AMAAxADUALAAgADAALgAwADEANQAsACAAMAAsACAAMAAsACAAMAAuADAAMAA0ADcALAAgADIANgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBXAGEAcgBtAFwAIgAsACAAMgA3ACwAIAAwAC4AOAAsACAAMAAuADEALAAgADAALgA0ADgALAAgADAALgAwADEALAAgADAALgAwADEANQAsACAAMAAuADAAMgAsACAAMAAuADAAMwAsACAAMAAuADAANAAsACAAMAAuADAAMQA1ACwAIAAwAC4AMAAxADUALAAgADAALAAgADAALAAgADAALgAwADAANAA3ACwAIAAyADcAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVwBhAHIAbQBcACIALAAgAFwAIgBlIjIAOABcACIALAAgADAALgA4ACwAIAAwAC4AMQAsACAAMAAuADUALAAgADAALgAwADEALAAgADAALgAwADEANQAsACAAMAAuADAAMgAsACAAMAAuADAAMwAsACAAMAAuADAANAAsACAAMAAuADAAMQA1ACwAIAAwAC4AMAAxADUALAAgADAALAAgADAALAAgADAALgAwADAANAA3ACwAIAAyADgAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAXAAiACwAIABcACIAXAAiACwAIABcACIAQQBuAGEAZQByAG8AYgBpAGMAIABsAGEAZwBvAG8AbgBcACIALAAgAFwAIgBEAGkAZwBlAHMAdABlAHIAIAAvACAAYwBvAHYAZQByAGUAZAAgAGwAYQBnAG8AbwBuAHMAXAAiACwAIABcACIATABpAHEAdQBpAGQAIABzAHkAcwB0AGUAbQBzAFwAIgAsACAAXAAiAEQAYQBpAGwAeQAgAHMAcAByAGUAYQBkAFwAIgAsACAAXAAiAEMAbwBtAHAAbwBzAHQAaQBuAGcAIAAoAHAAYQBzAHMAaQB2AGUAIAB3AGkAbgBkAHIAbwB3ACkAXAAiACwAIABcACIAUwBvAGwAaQBkACAAcwB0AG8AcgBhAGcAZQBcACIALAAgAFwAIgBQAGkAdAAgAHMAdABvAHIAYQBnAGUAXAAiACwAIABcACIARABlAGUAcAAgAGwAaQB0AHQAZQByAFwAIgAsACAAXAAiAFAAbwB1AGwAdAByAHkAIABtAGEAbgB1AHIAZQAgAHcAaQB0AGgAIABiAGUAZABkAGkAbgBnAFwAIgAsACAAXAAiAFAAbwB1AGwAdAByAHkAIABtAGEAbgB1AHIAZQAgAHcAaQB0AGgAbwB1AHQAIABiAGUAZABkAGkAbgBnAFwAIgAsACAAXAAiAEQAaQByAGUAYwB0ACAAcAByAG8AYwBlAHMAcwBpAG4AZwBcACIALAAgAFwAIgBEAGkAcgBlAGMAdAAgAGEAcABwAGwAaQBjAGEAdABpAG8AbgBcACIALAAgAFwAIgBQAGEAcwB0AHUAcgBlACAAcgBhAG4AZwBlACAAYQBuAGQAIABwAGEAZABkAG8AYwBrAFwAIgAsACAAXAAiAE0AQQBUACAAcgBhAHcAXAAiACAAXABuACAAIAAgACAAIAAgACAAIAB9ACwAIAByACwAIABjACkAXABuACAAIAAgACAAIAAgACkAXABuACAAIAAgACAAKQBcAG4AIAAgACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAE0AQwBGAFQAZQBtAHAAZQByAGEAdAB1AHIAZQBaAG8AbgBlAF8AVgBhAHIAaQBhAHQAaQBvAG4AXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFYAQQBSAEkAQQBUAEkATwBOACAARgBSAE8ATQAgAFMATwBVAFIAQwBFADoAIABBAGQAZABlAGQAIAByAG8AdwAgAG8AZgAgAE4ASQBSACAATQBNAEEAIABkAGUAZgBpAG4AaQB0AGkAbwBuAHMAIAB0AG8AIABhAGkAZAAgAGwAbwBvAGsAdQBwAC4AIABEAHUAcABsAGkAYwBhAHQAZQBkACAAJwBQAG8AdQBsAHQAcgB5ACAAdwBpAHQAaAAgAGEAbgBkACAAdwBpAHQAaABvAHUAdAAgAGwAaQB0AHQAZQByACcAIABjAG8AbAB1AG0AbgAgAHcAaQB0AGgAIABzAGUAcABhAHIAYQB0AGUAIABOAEkAUgAgAGQAZQBmAGkAbgBpAHQAaQBvAG4AcwAgAHQAbwAgAGEAaQBkACAAbABvAG8AawB1AHAALgAgAEEAZABkAGUAZAAgACcATQBBAFQAIAByAGEAdwAnACAAYwBvAGwAdQBtAG4AIAB0AG8AIABhAGwAbABvAHcAIABsAG8AbwBrAHUAcAAgAG8AZgAgAG4AdQBtAGIAZQByAHMALgBcACIAKQA7AFwAbgBcAG4AXABuAFwAbgAvACoAIABcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYATwByAGcAYQBuAGkAYwBGAGUAcgB0AGkAbABpAHMAZQByAEEAbgBkAEMAcgBvAHAAUgBlAHMAaQBkAHUAZQBzAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuACoALwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEUARgBPAHIAZwBhAG4AaQBjAEYAZQByAHQAaQBsAGkAcwBlAHIAQQBuAGQAQwByAG8AcABSAGUAcwBpAGQAdQBlAHMAXwBUAGkAdABsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAEUAbQBpAHMAcwBpAG8AbgAgAGYAYQBjAHQAbwByACAAZgBvAHIAIABvAHIAZwBhAG4AaQBjACAAZgBlAHIAdABpAGwAaQBzAGUAcgAgAGEAbgBkACAAYwByAG8AcAAgAHIAZQBzAGkAZAB1AGUAcwAgAHIAZQB0AHUAcgBuAGUAZAAgAHQAbwAgAHQAaABlACAAcwBvAGkAbABcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAE8AcgBnAGEAbgBpAGMARgBlAHIAdABpAGwAaQBzAGUAcgBBAG4AZABDAHIAbwBwAFIAZQBzAGkAZAB1AGUAcwBfAFYAYQByAGkAYQBiAGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIARQBGAE4AaQAgACYAIABFAEYATgAyAE8AaQBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAE8AcgBnAGEAbgBpAGMARgBlAHIAdABpAGwAaQBzAGUAcgBBAG4AZABDAHIAbwBwAFIAZQBzAGkAZAB1AGUAcwBfAFUAbgBpAHQAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAGsAZwAgAE4AMgBPACAALQAgAE4AIAAvACAAawBnACAATgBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAE8AcgBnAGEAbgBpAGMARgBlAHIAdABpAGwAaQBzAGUAcgBBAG4AZABDAHIAbwBwAFIAZQBzAGkAZAB1AGUAcwBfAFMAbwB1AHIAYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBWAEUARQBSAEcAIAAyADAAMgA2ADoAIABUAGEAYgBsAGUAIABBAC4AMgAuADEALgA0AFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYATwByAGcAYQBuAGkAYwBGAGUAcgB0AGkAbABpAHMAZQByAEEAbgBkAEMAcgBvAHAAUgBlAHMAaQBkAHUAZQBzAF8ATgBJAFIAUgBlAGYAZQByAGUAbgBjAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYATwByAGcAYQBuAGkAYwBGAGUAcgB0AGkAbABpAHMAZQByAEEAbgBkAEMAcgBvAHAAUgBlAHMAaQBkAHUAZQBzAF8ARABhAHQAYQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABNAEEASwBFAEEAUgBSAEEAWQAoADMALAAgADIALAAgAFwAbgAgACAAIAAgACAAIABMAEEATQBCAEQAQQAoAHIALABjACwAIABcAG4AIAAgACAAIAAgACAAIAAgAEkATgBEAEUAWAAoAHsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEMAbABpAG0AYQB0AGUAIAB6AG8AbgBlAFwAIgAsACAAXAAiAEUARgBOAGkAIAAmACAARQBGAE4AMgBPAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBXAGUAdAAgAGMAbABpAG0AYQB0AGUAIAB6AG8AbgBlAFwAIgAsACAAMAAuADAAMAA2ADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEQAcgB5ACAAYwBsAGkAbQBhAHQAZQAgAHoAbwBuAGUAXAAiACwAIAAwAC4AMAAwADUAXABuACAAIAAgACAAIAAgACAAIAB9ACwAIAByACwAIABjACkAXABuACAAIAAgACAAIAAgACkAXABuACAAIAAgACAAKQBcAG4AIAAgACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEUARgBPAHIAZwBhAG4AaQBjAEYAZQByAHQAaQBsAGkAcwBlAHIAQQBuAGQAQwByAG8AcABSAGUAcwBpAGQAdQBlAHMAXwBWAGEAcgBpAGEAdABpAG8AbgBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAXAAiACkAOwBcAG4AXABuAFwAbgBcAG4AXABuAFwAbgBcAG4AXABuAFwAbgBcAG4AXABuAFwAbgBcAG4AXABuAFwAbgBcAG4AXABuACIAfQBdACwAIgBwAHIAbwBqAGUAYwB0AE4AYQBtAGUAcwAiADoAWwAiAEMAbwBtAG0AbwBuAF8ARQBxAHUAYQB0AGkAbwBuAHMALgBDAG8AbQBtAG8AbgBfAEMAbwBuAHYAZQByAHQATgAyAE8AVABvAEMATwAyAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBFAHEAdQBhAHQAaQBvAG4AcwAuAEMAbwBtAG0AbwBuAF8AQwBvAG4AdgBlAHIAdABOADIATwBUAG8AQwBPADIAZQBfAFQAaQB0AGwAZQAiACwAIgBDAG8AbQBtAG8AbgBfAEUAcQB1AGEAdABpAG8AbgBzAC4AQwBvAG0AbQBvAG4AXwBDAG8AbgB2AGUAcgB0AE4AMgBPAFQAbwBDAE8AMgBlAF8AVgBhAHIAaQBhAGIAbABlACIALAAiAEMAbwBtAG0AbwBuAF8ARQBxAHUAYQB0AGkAbwBuAHMALgBDAG8AbQBtAG8AbgBfAEMAbwBuAHYAZQByAHQATgAyAE8AVABvAEMATwAyAGUAXwBVAG4AaQB0ACIALAAiAEMAbwBtAG0AbwBuAF8ARQBxAHUAYQB0AGkAbwBuAHMALgBDAG8AbQBtAG8AbgBfAEMAbwBuAHYAZQByAHQATgAyAE8AVABvAEMATwAyAGUAXwBOAEkAUgBSAGUAZgBlAHIAZQBuAGMAZQAiACwAIgBDAG8AbQBtAG8AbgBfAEUAcQB1AGEAdABpAG8AbgBzAC4AQwBvAG0AbQBvAG4AXwBDAG8AbgB2AGUAcgB0AE4AMgBPAFQAbwBDAE8AMgBlAF8ATABhAHQAZQB4AEUAcQB1AGEAdABpAG8AbgAiACwAIgBDAG8AbQBtAG8AbgBfAEUAcQB1AGEAdABpAG8AbgBzAC4AQwBvAG0AbQBvAG4AXwBDAG8AbgB2AGUAcgB0AE4AMgBPAFQAbwBDAE8AMgBlAF8AQQByAGcAdQBtAGUAbgB0AHMAIgAsACIAQwBvAG0AbQBvAG4AXwBFAHEAdQBhAHQAaQBvAG4AcwAuAEMAbwBtAG0AbwBuAF8AQwBvAG4AdgBlAHIAdABDAEgANABUAG8AQwBPADIAZQAiACwAIgBDAG8AbQBtAG8AbgBfAEUAcQB1AGEAdABpAG8AbgBzAC4AQwBvAG0AbQBvAG4AXwBDAG8AbgB2AGUAcgB0AEMASAA0AFQAbwBDAE8AMgBlAF8AVABpAHQAbABlACIALAAiAEMAbwBtAG0AbwBuAF8ARQBxAHUAYQB0AGkAbwBuAHMALgBDAG8AbQBtAG8AbgBfAEMAbwBuAHYAZQByAHQAQwBIADQAVABvAEMATwAyAGUAXwBWAGEAcgBpAGEAYgBsAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBFAHEAdQBhAHQAaQBvAG4AcwAuAEMAbwBtAG0AbwBuAF8AQwBvAG4AdgBlAHIAdABDAEgANABUAG8AQwBPADIAZQBfAFUAbgBpAHQAIgAsACIAQwBvAG0AbQBvAG4AXwBFAHEAdQBhAHQAaQBvAG4AcwAuAEMAbwBtAG0AbwBuAF8AQwBvAG4AdgBlAHIAdABDAEgANABUAG8AQwBPADIAZQBfAE4ASQBSAFIAZQBmAGUAcgBlAG4AYwBlACIALAAiAEMAbwBtAG0AbwBuAF8ARQBxAHUAYQB0AGkAbwBuAHMALgBDAG8AbQBtAG8AbgBfAEMAbwBuAHYAZQByAHQAQwBIADQAVABvAEMATwAyAGUAXwBMAGEAdABlAHgARQBxAHUAYQB0AGkAbwBuACIALAAiAEMAbwBtAG0AbwBuAF8ARQBxAHUAYQB0AGkAbwBuAHMALgBDAG8AbQBtAG8AbgBfAEMAbwBuAHYAZQByAHQAQwBIADQAVABvAEMATwAyAGUAXwBBAHIAZwB1AG0AZQBuAHQAcwAiACwAIgBDAG8AbQBtAG8AbgBfAEkAbgBwAHUAdABGAHUAbgBjAHQAaQBvAG4AcwAuAFUAdABpAGwAaQB0AHkAXwBHAGUAdABBAHIAcgBhAHkAVABhAGIAbABlAFIAbwB3AFMAdABhAHIAdABOAHUAbQBiAGUAcgAiACwAIgBDAG8AbQBtAG8AbgBfAEkAbgBwAHUAdABGAHUAbgBjAHQAaQBvAG4AcwAuAFUAdABpAGwAaQB0AHkAXwBHAGUAdABBAHIAcgBhAHkAVABhAGIAbABlAEMAbwBsAHUAbQBuAFMAdABhAHIAdABOAHUAbQBiAGUAcgAiACwAIgBDAG8AbQBtAG8AbgBfAEkAbgBwAHUAdABGAHUAbgBjAHQAaQBvAG4AcwAuAFUAdABpAGwAaQB0AHkAXwBEAGkAcwBwAGwAYQB5AEEAcgByAGEAeQBJAG4AVABhAGIAbABlACIALAAiAEMAbwBtAG0AbwBuAF8ASQBuAHAAdQB0AEYAdQBuAGMAdABpAG8AbgBzAC4AVQB0AGkAbABpAHQAeQBfAEwAbwBvAGsAdQBwAFYAYQBsAHUAZQBJAG4AVABhAGIAbABlACIALAAiAEMAbwBtAG0AbwBuAF8ASQBuAHAAdQB0AEYAdQBuAGMAdABpAG8AbgBzAC4AVQB0AGkAbABpAHQAeQBfAEwAbwBvAGsAdQBwAFYAYQBsAHUAZQBJAG4AVABhAGIAbABlAE4AdQBtAGIAZQByACIALAAiAEMAbwBtAG0AbwBuAF8ASQBuAHAAdQB0AEYAdQBuAGMAdABpAG8AbgBzAC4AVQB0AGkAbABpAHQAeQBfAEwAbwBvAGsAdQBwAFYAYQBsAHUAZQBJAG4AVABhAGIAbABlAFQAdwBvAEMAbwBsAHUAbQBuAHMAIgAsACIAQwBvAG0AbQBvAG4AXwBJAG4AcAB1AHQARgB1AG4AYwB0AGkAbwBuAHMALgBVAHQAaQBsAGkAdAB5AF8ATABvAG8AawB1AHAAVgBhAGwAdQBlAEkAbgBUAGEAYgBsAGUATwBuAGUAQwBvAGwAdQBtAG4AQQBuAGQASABlAGEAZABlAHIAIgAsACIAQwBvAG0AbQBvAG4AXwBJAG4AcAB1AHQARgB1AG4AYwB0AGkAbwBuAHMALgBVAHQAaQBsAGkAdAB5AF8AUwBwAGwAaQB0AFMAdAByAGkAbgBnAEkAbgB0AG8AQQByAHIAYQB5ACIALAAiAEMAbwBtAG0AbwBuAF8ASQBuAHAAdQB0AEYAdQBuAGMAdABpAG8AbgBzAC4AVQB0AGkAbABpAHQAeQBfAEcAZQB0AEMAbABpAG0AYQB0AGUAWgBvAG4AZQAiACwAIgBDAG8AbQBtAG8AbgBfAEkAbgBwAHUAdABGAHUAbgBjAHQAaQBvAG4AcwAuAFUAdABpAGwAaQB0AHkAXwBMAG8AbwBrAHUAcABJAHQAZQBtAEYAcgBvAG0ATQBpAG4ATQBhAHgAIgAsACIAQwBvAG0AbQBvAG4AXwBJAG4AcAB1AHQARgB1AG4AYwB0AGkAbwBuAHMALgBVAHQAaQBsAGkAdAB5AF8AUwB1AG0AUQB1AGEAbgB0AGkAdAB5AEYAcgBvAG0AQwByAGkAdABlAHIAaQBhACIALAAiAEMAbwBtAG0AbwBuAF8ASQBuAHAAdQB0AEYAdQBuAGMAdABpAG8AbgBzAC4AZwBlAHQATwB2AGUAcgBsAGEAcABwAGkAbgBnAFIAZQBwAG8AcgB0AGkAbgBnAFAAZQByAGkAbwBkAHMAIgAsACIAQwBvAG0AbQBvAG4AXwBJAG4AcAB1AHQARgB1AG4AYwB0AGkAbwBuAHMALgBVAHQAaQBsAGkAdAB5AF8ARABpAHMAcABsAGEAeQBGAHUAbgBjAHQAaQBvAG4ATgBhAG0AZQAiACwAIgBDAG8AbQBtAG8AbgBfAEkAbgBwAHUAdABGAHUAbgBjAHQAaQBvAG4AcwAuAFUAdABpAGwAaQB0AHkAXwBMAG8AbwBrAHUAcABOADIATwBFAEYARgByAG8AbQBQAHIAbwBkAEkAcgByAGkAZwBhAHQAaQBvAG4AUgBhAGkAbgBmAGEAbABsACIALAAiAEMAbwBtAG0AbwBuAF8ASQBuAHAAdQB0AEYAdQBuAGMAdABpAG8AbgBzAC4AQwBvAG0AbQBvAG4AQwByAG8AcABwAGkAbgBnAF8ARwBlAHQARgByAGEAYwBXAEUAVAAiACwAIgBDAG8AbQBtAG8AbgBfAEkAbgBwAHUAdABGAHUAbgBjAHQAaQBvAG4AcwAuAFUAdABpAGwAaQB0AHkAXwBDAG8AbgB2AGUAcgB0AFMAdABhAHQAZQBDAG8AbQBtAG8AbgBOAGEAbQBlAFQAbwBBAGIAYgByAGUAdgBpAGEAdABpAG8AbgAiACwAIgBDAG8AbQBtAG8AbgBfAEkAbgBwAHUAdABGAHUAbgBjAHQAaQBvAG4AcwAuAFUAdABpAGwAaQB0AHkAXwBTAG8AdQByAGMAZQBIAHkAcABlAHIAbABpAG4AawBEAGkAZgBmAGUAcgBlAG4AdABTAGgAZQBlAHQAIgAsACIAQwBvAG0AbQBvAG4AXwBJAG4AcAB1AHQARgB1AG4AYwB0AGkAbwBuAHMALgBVAHQAaQBsAGkAdAB5AF8AUgBlAHMAdQBsAHQAcwBJAHQAZQBtAEYAcgBvAG0ARQBxAHUAYQB0AGkAbwBuAFQAaQB0AGwAZQBBAG4AZABTAG8AdQByAGMAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGUAbgBzAGkAdAB5AE8AZgBNAGUAdABoAGEAbgBlAF8AVABpAHQAbABlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEQAZQBuAHMAaQB0AHkATwBmAE0AZQB0AGgAYQBuAGUAXwBVAG4AaQB0ACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEQAZQBuAHMAaQB0AHkATwBmAE0AZQB0AGgAYQBuAGUAXwBTAG8AdQByAGMAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGUAbgBzAGkAdAB5AE8AZgBNAGUAdABoAGEAbgBlAF8ARABhAHQAYQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBDAG8AbgB2AGUAcgB0AE4AMgBvAEUAbABlAG0AZQBuAHQAYQBsAFQAbwBNAG8AbABlAGMAdQBsAGEAcgBDAGcAXwBUAGkAdABsAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQwBvAG4AdgBlAHIAdABOADIAbwBFAGwAZQBtAGUAbgB0AGEAbABUAG8ATQBvAGwAZQBjAHUAbABhAHIAQwBnAF8AVgBhAHIAaQBhAGIAbABlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEMAbwBuAHYAZQByAHQATgAyAG8ARQBsAGUAbQBlAG4AdABhAGwAVABvAE0AbwBsAGUAYwB1AGwAYQByAEMAZwBfAFUAbgBpAHQAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQwBvAG4AdgBlAHIAdABOADIAbwBFAGwAZQBtAGUAbgB0AGEAbABUAG8ATQBvAGwAZQBjAHUAbABhAHIAQwBnAF8AUwBvAHUAcgBjAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQwBvAG4AdgBlAHIAdABOADIAbwBFAGwAZQBtAGUAbgB0AGEAbABUAG8ATQBvAGwAZQBjAHUAbABhAHIAQwBnAF8ARABhAHQAYQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBDAG8AbgB2AGUAcgB0AEcAYQBzAEUAbABlAG0AZQBuAHQAYQBsAFQAbwBNAG8AbABlAGMAdQBsAGEAcgBfAFQAaQB0AGwAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBDAG8AbgB2AGUAcgB0AEcAYQBzAEUAbABlAG0AZQBuAHQAYQBsAFQAbwBNAG8AbABlAGMAdQBsAGEAcgBfAFYAYQByAGkAYQBiAGwAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBDAG8AbgB2AGUAcgB0AEcAYQBzAEUAbABlAG0AZQBuAHQAYQBsAFQAbwBNAG8AbABlAGMAdQBsAGEAcgBfAFUAbgBpAHQAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQwBvAG4AdgBlAHIAdABHAGEAcwBFAGwAZQBtAGUAbgB0AGEAbABUAG8ATQBvAGwAZQBjAHUAbABhAHIAXwBTAG8AdQByAGMAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBDAG8AbgB2AGUAcgB0AEcAYQBzAEUAbABlAG0AZQBuAHQAYQBsAFQAbwBNAG8AbABlAGMAdQBsAGEAcgBfAEQAYQB0AGEAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARwBXAFAAXwBUAGkAdABsAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARwBXAFAAXwBWAGEAcgBpAGEAYgBsAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARwBXAFAAXwBVAG4AaQB0ACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEcAVwBQAF8AUwBvAHUAcgBjAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARwBXAFAAXwBEAGEAdABhACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEEAdQBzAHQAcgBhAGwAaQBhAG4AUwB0AGEAdABlAHMAVABlAHIAcgBpAHQAbwByAGkAZQBzAF8AVABpAHQAbABlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEEAdQBzAHQAcgBhAGwAaQBhAG4AUwB0AGEAdABlAHMAVABlAHIAcgBpAHQAbwByAGkAZQBzAF8AVgBhAHIAaQBhAGIAbABlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEEAdQBzAHQAcgBhAGwAaQBhAG4AUwB0AGEAdABlAHMAVABlAHIAcgBpAHQAbwByAGkAZQBzAF8AVQBuAGkAdAAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBBAHUAcwB0AHIAYQBsAGkAYQBuAFMAdABhAHQAZQBzAFQAZQByAHIAaQB0AG8AcgBpAGUAcwBfAFMAbwB1AHIAYwBlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEEAdQBzAHQAcgBhAGwAaQBhAG4AUwB0AGEAdABlAHMAVABlAHIAcgBpAHQAbwByAGkAZQBzAF8ARABhAHQAYQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBXAEEAUwBBADQAQQByAGUAYQBzAF8AVABpAHQAbABlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFcAQQBTAEEANABBAHIAZQBhAHMAXwBWAGEAcgBpAGEAYgBsAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AVwBBAFMAQQA0AEEAcgBlAGEAcwBfAFUAbgBpAHQAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AVwBBAFMAQQA0AEEAcgBlAGEAcwBfAFMAbwB1AHIAYwBlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFcAQQBTAEEANABBAHIAZQBhAHMAXwBEAGEAdABhACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFcAZQB0AEEAbgBkAEQAcgB5AFoAbwBuAGUAcwBfAFQAaQB0AGwAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBXAGUAdABBAG4AZABEAHIAeQBaAG8AbgBlAHMAXwBWAGEAcgBpAGEAYgBsAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AVwBlAHQAQQBuAGQARAByAHkAWgBvAG4AZQBzAF8AVQBuAGkAdAAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBXAGUAdABBAG4AZABEAHIAeQBaAG8AbgBlAHMAXwBTAG8AdQByAGMAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBXAGUAdABBAG4AZABEAHIAeQBaAG8AbgBlAHMAXwBWAGEAcgBpAGEAdABpAG8AbgAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBXAGUAdABBAG4AZABEAHIAeQBaAG8AbgBlAHMAXwBEAGEAdABhACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEMAbABpAG0AYQB0AGUAWgBvAG4AZQBzAF8AVABpAHQAbABlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEMAbABpAG0AYQB0AGUAWgBvAG4AZQBzAF8AVgBhAHIAaQBhAGIAbABlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEMAbABpAG0AYQB0AGUAWgBvAG4AZQBzAF8AVQBuAGkAdAAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBDAGwAaQBtAGEAdABlAFoAbwBuAGUAcwBfAFMAbwB1AHIAYwBlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEMAbABpAG0AYQB0AGUAWgBvAG4AZQBzAF8AVgBhAHIAaQBhAHQAaQBvAG4AIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQwBsAGkAbQBhAHQAZQBaAG8AbgBlAHMAXwBEAGEAdABhACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEMAbABpAG0AYQB0AGUAWgBvAG4AZQBzAF8AQQBwAHAAZQBuAGQAaQBjAGUAcwAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBUAGUAbQBwAGUAcgBhAHQAdQByAGUAWgBvAG4AZQBzAF8AVABpAHQAbABlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFQAZQBtAHAAZQByAGEAdAB1AHIAZQBaAG8AbgBlAHMAXwBWAGEAcgBpAGEAYgBsAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AVABlAG0AcABlAHIAYQB0AHUAcgBlAFoAbwBuAGUAcwBfAFUAbgBpAHQAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AVABlAG0AcABlAHIAYQB0AHUAcgBlAFoAbwBuAGUAcwBfAFMAbwB1AHIAYwBlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFQAZQBtAHAAZQByAGEAdAB1AHIAZQBaAG8AbgBlAHMAXwBWAGEAcgBpAGEAdABpAG8AbgAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBUAGUAbQBwAGUAcgBhAHQAdQByAGUAWgBvAG4AZQBzAF8ARABhAHQAYQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBSAGEAaQBuAGYAYQBsAGwAWgBvAG4AZQBzAF8AVABpAHQAbABlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFIAYQBpAG4AZgBhAGwAbABaAG8AbgBlAHMAXwBWAGEAcgBpAGEAYgBsAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AUgBhAGkAbgBmAGEAbABsAFoAbwBuAGUAcwBfAFUAbgBpAHQAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AUgBhAGkAbgBmAGEAbABsAFoAbwBuAGUAcwBfAFMAbwB1AHIAYwBlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFIAYQBpAG4AZgBhAGwAbABaAG8AbgBlAHMAXwBWAGEAcgBpAGEAdABpAG8AbgAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBSAGEAaQBuAGYAYQBsAGwAWgBvAG4AZQBzAF8ARABhAHQAYQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBMAGUAYQBjAGgAaQBuAGcAWgBvAG4AZQBzAF8AVABpAHQAbABlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEwAZQBhAGMAaABpAG4AZwBaAG8AbgBlAHMAXwBWAGEAcgBpAGEAYgBsAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ATABlAGEAYwBoAGkAbgBnAFoAbwBuAGUAcwBfAFUAbgBpAHQAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ATABlAGEAYwBoAGkAbgBnAFoAbwBuAGUAcwBfAFMAbwB1AHIAYwBlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEwAZQBhAGMAaABpAG4AZwBaAG8AbgBlAHMAXwBWAGEAcgBpAGEAdABpAG8AbgAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBMAGUAYQBjAGgAaQBuAGcAWgBvAG4AZQBzAF8ARABhAHQAYQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAHIAYQBjAFcARQBUAF8AVABpAHQAbABlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAcgBhAGMAVwBFAFQAXwBVAG4AaQB0ACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAcgBhAGMAVwBFAFQAXwBTAG8AdQByAGMAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAHIAYQBjAFcARQBUAF8ATgBJAFIAUgBlAGYAZQByAGUAbgBjAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgByAGEAYwBXAEUAVABfAEQAYQB0AGEAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgByAGEAYwBXAEUAVABfAFYAYQByAGkAYQB0AGkAbwBuACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEQAYQB0AGEAUwBjAG8AcgBlAHMAXwBTAGMAbwBwAGUAMwBfAFQAaQB0AGwAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGEAdABhAFMAYwBvAHIAZQBzAF8AUwBjAG8AcABlADMAXwBWAGEAcgBpAGEAYgBsAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABhAHQAYQBTAGMAbwByAGUAcwBfAFMAYwBvAHAAZQAzAF8AVQBuAGkAdAAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGEAdABhAFMAYwBvAHIAZQBzAF8AUwBjAG8AcABlADMAXwBTAG8AdQByAGMAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGEAdABhAFMAYwBvAHIAZQBzAF8AUwBjAG8AcABlADMAXwBWAGEAcgBpAGEAdABpAG8AbgAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGEAdABhAFMAYwBvAHIAZQBzAF8AUwBjAG8AcABlADMAXwBEAGEAdABhACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAcgBhAGMATABFAEEAQwBIAF8AVABpAHQAbABlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAcgBhAGMATABFAEEAQwBIAF8AVQBuAGkAdAAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAHIAYQBjAEwARQBBAEMASABfAFMAbwB1AHIAYwBlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAcgBhAGMATABFAEEAQwBIAF8ATgBJAFIAUgBlAGYAZQByAGUAbgBjAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgByAGEAYwBMAEUAQQBDAEgAXwBEAGEAdABhACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAcgBhAGMATABFAEEAQwBIAF8AVgBhAHIAaQBhAHQAaQBvAG4AIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAGwAZQBhAGMAaABfAFQAaQB0AGwAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYAbABlAGEAYwBoAF8AVQBuAGkAdAAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYAbABlAGEAYwBoAF8AUwBvAHUAcgBjAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAGwAZQBhAGMAaABfAE4ASQBSAFIAZQBmAGUAcgBlAG4AYwBlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEUARgBsAGUAYQBjAGgAXwBEAGEAdABhACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEUARgBsAGUAYQBjAGgAXwBWAGEAcgBpAGEAdABpAG8AbgAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYATgAyAE8AXwBUAGkAdABsAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAE4AMgBPAF8AVQBuAGkAdAAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYATgAyAE8AXwBTAG8AdQByAGMAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYATgAyAE8AXwBOAEkAUgBSAGUAZgBlAHIAZQBuAGMAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYATgAyAE8AXwBEAGEAdABhACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEUARgBOADIATwBfAFYAYQByAGkAYQB0AGkAbwBuACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAcgBhAGMAVwBFAFQASQByAHIAaQBnAGEAdABpAG8AbgBfAFQAaQB0AGwAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAHIAYQBjAFcARQBUAEkAcgByAGkAZwBhAHQAaQBvAG4AXwBVAG4AaQB0ACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAcgBhAGMAVwBFAFQASQByAHIAaQBnAGEAdABpAG8AbgBfAFMAbwB1AHIAYwBlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAcgBhAGMAVwBFAFQASQByAHIAaQBnAGEAdABpAG8AbgBfAE4ASQBSAFIAZQBmAGUAcgBlAG4AYwBlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAcgBhAGMAVwBFAFQASQByAHIAaQBnAGEAdABpAG8AbgBfAEQAYQB0AGEAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgByAGEAYwBXAEUAVABJAHIAcgBpAGcAYQB0AGkAbwBuAF8AVgBhAHIAaQBhAHQAaQBvAG4AIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAFAAYQBzAHQAdQByAGUAUgBhAG4AZwBlAEEAbgBkAFAAYQBkAGQAbwBjAGsAXwBUAGkAdABsAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAFAAYQBzAHQAdQByAGUAUgBhAG4AZwBlAEEAbgBkAFAAYQBkAGQAbwBjAGsAXwBVAG4AaQB0ACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEUARgBQAGEAcwB0AHUAcgBlAFIAYQBuAGcAZQBBAG4AZABQAGEAZABkAG8AYwBrAF8AUwBvAHUAcgBjAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAFAAYQBzAHQAdQByAGUAUgBhAG4AZwBlAEEAbgBkAFAAYQBkAGQAbwBjAGsAXwBOAEkAUgBSAGUAZgBlAHIAZQBuAGMAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYAUABhAHMAdAB1AHIAZQBSAGEAbgBnAGUAQQBuAGQAUABhAGQAZABvAGMAawBfAEQAYQB0AGEAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAFAAYQBzAHQAdQByAGUAUgBhAG4AZwBlAEEAbgBkAFAAYQBkAGQAbwBjAGsAXwBWAGEAcgBpAGEAdABpAG8AbgAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBNAG8AbgB0AGgAcwBUAG8AUwBlAGEAcwBvAG4AcwBfAFQAaQB0AGwAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBNAG8AbgB0AGgAcwBUAG8AUwBlAGEAcwBvAG4AcwBfAFUAbgBpAHQAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ATQBvAG4AdABoAHMAVABvAFMAZQBhAHMAbwBuAHMAXwBTAG8AdQByAGMAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBNAG8AbgB0AGgAcwBUAG8AUwBlAGEAcwBvAG4AcwBfAE4ASQBSAFIAZQBmAGUAcgBlAG4AYwBlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAE0AbwBuAHQAaABzAFQAbwBTAGUAYQBzAG8AbgBzAF8ARABhAHQAYQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBNAG8AbgB0AGgAcwBUAG8AUwBlAGEAcwBvAG4AcwBfAFYAYQByAGkAYQB0AGkAbwBuACIAXQAsACIAbABvAGMAYQBsAGUAIgA6AHsAIgBsAGkAcwB0AFMAZQBwAGEAcgBhAHQAbwByACIAOgAiACwAIgAsACIAcgBvAHcAUwBlAHAAYQByAGEAdABvAHIAIgA6ACIAOwAiACwAIgBjAG8AbAB1AG0AbgBTAGUAcABhAHIAYQB0AG8AcgAiADoAIgAsACIALAAiAHQAaABvAHUAcwBhAG4AZABzAFMAZQBwAGEAcgBhAHQAbwByACIAOgAiACwAIgAsACIAdABoAG8AdQBzAGEAbgBkAHMAUABvAHMAaQB0AGkAbwBuAHMAIgA6AFsAMwBdACwAIgBkAGUAYwBpAG0AYQBsAFMAZQBwAGEAcgBhAHQAbwByACIAOgAiAC4AIgAsACIAZABhAHQAZQBPAHIAZABlAHIAIgA6ACIARABNAFkAIgAsACIAYwB1AHIAcgBlAG4AYwB5AFMAeQBtAGIAbwBsACIAOgAiACQAIgAsACIAaQBzAEMAdQByAHIAZQBuAGMAeQBTAHkAbQBiAG8AbABMAGUAYQBkACIAOgB0AHIAdQBlACwAIgBpAHMAQwB1AHIAcgBlAG4AYwB5AFMAZQBwAEIAeQBTAHAAYQBjAGUAIgA6AGYAYQBsAHMAZQAsACIAcgBvAHcATABlAHQAdABlAHIAIgA6ACIAUgAiACwAIgBjAG8AbAB1AG0AbgBMAGUAdAB0AGUAcgAiADoAIgBDACIALAAiAHIAYwBMAGUAZgB0AEIAcgBhAGMAawBlAHQAIgA6ACIAWwAiACwAIgByAGMAUgBpAGcAaAB0AEIAcgBhAGMAawBlAHQAIgA6ACIAXQAiACwAIgBzAHQAYQB0AGUAbQBlAG4AdABTAGUAcABhAHIAYQB0AG8AcgAiADoAIgA7ACIALAAiAGwAbwBjAGEAbABlAE4AYQBtAGUAIgA6ACIAZQBuAC0AdQBzACIAfQB9AA==</AFEJSONBlob>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
 <?mso-contentType ?>
 <FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
   <Display>DocumentLibraryForm</Display>
@@ -11299,11 +11665,18 @@
 </FormTemplates>
 </file>
 
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<AFEJSONBlob xmlns="http://schemas.advancedformulaenvironment.officeapps.live.com/afejsonblob/1.0">ewAiAHMAYwBoAGUAbQBhACIAOgAiAGgAdAB0AHAAOgAvAC8AcwBjAGgAZQBtAGEAcwAuAGEAZAB2AGEAbgBjAGUAZABmAG8AcgBtAHUAbABhAGUAbgB2AGkAcgBvAG4AbQBlAG4AdAAuAG8AZgBmAGkAYwBlAGEAcABwAHMALgBsAGkAdgBlAC4AYwBvAG0ALwBhAGYAZQBwAHIAbwBqAGUAYwB0AHMALwAwAC4AMgAiACwAIgBmAGkAbABlAHMAIgA6AFsAewAiAHAAYQB0AGgAIgA6ACIALwBwAHIAbwBqAGUAYwB0AHMALwBXAG8AcgBrAGIAbwBvAGsAIgAsACIAdABlAHgAdAAiADoAIgAvAC8AIAAtAC0ALQAgAFcAbwByAGsAYgBvAG8AawAgAG0AbwBkAHUAbABlACAALQAtAC0AXABuAC8ALwAgAEEAIABmAGkAbABlACAAbwBmACAAbgBhAG0AZQAgAGQAZQBmAGkAbgBpAHQAaQBvAG4AcwAgAG8AZgAgAHQAaABlACAAZgBvAHIAbQA6AFwAbgAvAC8AIAAgACAAIABuAGEAbQBlACAAPQAgAGQAZQBmAGkAbgBpAHQAaQBvAG4AOwBcAG4AIgB9ACwAewAiAHAAYQB0AGgAIgA6ACIALwBwAHIAbwBqAGUAYwB0AHMALwBDAG8AbQBtAG8AbgBfAEUAcQB1AGEAdABpAG8AbgBzACIALAAiAHQAZQB4AHQAIgA6ACIAXABuAC8AKgAgAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuAEMAbwBtAG0AbwBuAF8AQwBvAG4AdgBlAHIAdABOADIATwBUAG8AQwBPADIAZQBcAG4AQwBvAG4AdgBlAHIAdAAgAG4AaQB0AHIAbwB1AHMAIABvAHgAaQBkAGUAIABlAG0AaQBzAHMAaQBvAG4AcwAgAHQAbwAgAGMAYQByAGIAbwBuACAAZABpAG8AeABpAGQAZQAgAGUAcQB1AGkAdgBhAGwAZQBuAHQAIABlAG0AaQBzAHMAaQBvAG4AcwBcAG4ARQBOADIATwAgAEMATwAyAGUAXABuAHQAIABDAE8AMgBlAFwAbgBFAE4AMgBPADoAIABuAGkAdAByAG8AdQBzACAAbwB4AGkAZABlACAAZQBtAGkAcwBzAGkAbwBuAHMAIAAoAHQAIABOADIATwApAFwAbgBHAFcAUABOADIATwA6ACAAZwBsAG8AYgBhAGwAIAB3AGEAcgBtAGkAbgBnACAAcABvAHQAZQBuAHQAaQBhAGwAIABmAG8AcgAgAG4AaQB0AHIAbwB1AHMAIABvAHgAaQBkAGUAIAAoAHQAIABDAE8AMgAtAGUAIAAvACAAdAAgAE4AMgBPACkAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AKgAvAFwAbgBcAG4AXABuAEMAbwBtAG0AbwBuAF8AQwBvAG4AdgBlAHIAdABOADIATwBUAG8AQwBPADIAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABFAF8ATgAyAE8ALAAgAEcAVwBQAF8ATgAyAE8ALABcAG4AIAAgACAAIABFAF8ATgAyAE8AIAAqACAARwBXAFAAXwBOADIATwBcAG4AIAAgACkAXABuADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAEMAbwBuAHYAZQByAHQATgAyAE8AVABvAEMATwAyAGUAXwBUAGkAdABsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAEMAbwBuAHYAZQByAHQAIABuAGkAdAByAG8AdQBzACAAbwB4AGkAZABlACAAZQBtAGkAcwBzAGkAbwBuAHMAIAB0AG8AIABjAGEAcgBiAG8AbgAgAGQAaQBvAHgAaQBkAGUAIABlAHEAdQBpAHYAYQBsAGUAbgB0ACAAZQBtAGkAcwBzAGkAbwBuAHMAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AQwBvAG4AdgBlAHIAdABOADIATwBUAG8AQwBPADIAZQBfAFYAYQByAGkAYQBiAGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIARQBOADIATwAgAEMATwAyAGUAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AQwBvAG4AdgBlAHIAdABOADIATwBUAG8AQwBPADIAZQBfAFUAbgBpAHQAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAHQAIABDAE8AMgBlAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAEMAbwBuAHYAZQByAHQATgAyAE8AVABvAEMATwAyAGUAXwBOAEkAUgBSAGUAZgBlAHIAZQBuAGMAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AQwBvAG4AdgBlAHIAdABOADIATwBUAG8AQwBPADIAZQBfAEwAYQB0AGUAeABFAHEAdQBhAHQAaQBvAG4AXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAEMATwAyAF8AZQAgAD0AIABFAF8AewBOADIATwB9ACAAXABcAHQAaQBtAGUAcwAgAEcAVwBQAF8AewBOADIATwB9AFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAEMAbwBuAHYAZQByAHQATgAyAE8AVABvAEMATwAyAGUAXwBBAHIAZwB1AG0AZQBuAHQAcwBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABNAEEASwBFAEEAUgBSAEEAWQAoADIALAAgADIALAAgAFwAbgAgACAAIAAgACAAIABMAEEATQBCAEQAQQAoAHIALABjACwAIABcAG4AIAAgACAAIAAgACAAIAAgAEkATgBEAEUAWAAoAHsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEUATgAyAE8AXAAiACwAXAAiAE4AaQB0AHIAbwB1AHMAIABvAHgAaQBkAGUAIABlAG0AaQBzAHMAaQBvAG4AcwAgACgAdAAgAE4AMgBPACkAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEcAVwBQAE4AMgBPAFwAIgAsAFwAIgBHAGwAbwBiAGEAbAAgAHcAYQByAG0AaQBuAGcAIABwAG8AdABlAG4AdABpAGEAbAAgAGYAbwByACAAbgBpAHQAcgBvAHUAcwAgAG8AeABpAGQAZQAgACgAdAAgAEMATwAyAC0AZQAgAC8AIAB0ACAATgAyAE8AKQBcACIAXABuACAAIAAgACAAIAAgACAAIAB9ACwAIAByACwAIABjACkAXABuACAAIAAgACAAIAAgACkAXABuACAAIAAgACAAKQBcAG4AIAAgACkAOwBcAG4AXABuAC8AKgAgAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuAEMAbwBtAG0AbwBuAF8AQwBvAG4AdgBlAHIAdABDAEgANABUAG8AQwBPADIAZQBcAG4AQwBvAG4AdgBlAHIAdAAgAG0AZQB0AGgAYQBuAGUAIABlAG0AaQBzAHMAaQBvAG4AcwAgAHQAbwAgAGMAYQByAGIAbwBuACAAZABpAG8AeABpAGQAZQAgAGUAcQB1AGkAdgBhAGwAZQBuAHQAIABlAG0AaQBzAHMAaQBvAG4AcwBcAG4ARQBDAEgANAAgAEMATwAyAGUAXABuAHQAIABDAE8AMgBlAFwAbgBFAEMASAA0ADoAIABtAGUAdABoAGEAbgBlACAAZQBtAGkAcwBzAGkAbwBuAHMAIAAoAHQAIABDAEgANAApAFwAbgBHAFcAUABDAEgANAA6ACAAZwBsAG8AYgBhAGwAIAB3AGEAcgBtAGkAbgBnACAAcABvAHQAZQBuAHQAaQBhAGwAIABmAG8AcgAgAG0AZQB0AGgAYQBuAGUAIAAoAHQAIABDAE8AMgAtAGUAIAAvACAAdAAgAEMASAA0ACkAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AKgAvAFwAbgBcAG4AXABuAEMAbwBtAG0AbwBuAF8AQwBvAG4AdgBlAHIAdABDAEgANABUAG8AQwBPADIAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABFAF8AQwBIADQALAAgAEcAVwBQAF8AQwBIADQALABcAG4AIAAgACAAIABFAF8AQwBIADQAIAAqACAARwBXAFAAXwBDAEgANABcAG4AIAAgACkAXABuADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAEMAbwBuAHYAZQByAHQAQwBIADQAVABvAEMATwAyAGUAXwBUAGkAdABsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAEMAbwBuAHYAZQByAHQAIABtAGUAdABoAGEAbgBlACAAZQBtAGkAcwBzAGkAbwBuAHMAIAB0AG8AIABjAGEAcgBiAG8AbgAgAGQAaQBvAHgAaQBkAGUAIABlAHEAdQBpAHYAYQBsAGUAbgB0ACAAZQBtAGkAcwBzAGkAbwBuAHMAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AQwBvAG4AdgBlAHIAdABDAEgANABUAG8AQwBPADIAZQBfAFYAYQByAGkAYQBiAGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIARQBDAEgANAAgAEMATwAyAGUAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AQwBvAG4AdgBlAHIAdABDAEgANABUAG8AQwBPADIAZQBfAFUAbgBpAHQAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAHQAIABDAE8AMgBlAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAEMAbwBuAHYAZQByAHQAQwBIADQAVABvAEMATwAyAGUAXwBOAEkAUgBSAGUAZgBlAHIAZQBuAGMAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AQwBvAG4AdgBlAHIAdABDAEgANABUAG8AQwBPADIAZQBfAEwAYQB0AGUAeABFAHEAdQBhAHQAaQBvAG4AXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAEMATwAyAF8AZQAgAD0AIABFAF8AewBDAEgANAB9ACAAXABcAHQAaQBtAGUAcwAgAEcAVwBQAF8AewBDAEgANAB9AFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAEMAbwBuAHYAZQByAHQAQwBIADQAVABvAEMATwAyAGUAXwBBAHIAZwB1AG0AZQBuAHQAcwBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABNAEEASwBFAEEAUgBSAEEAWQAoADIALAAgADIALAAgAFwAbgAgACAAIAAgACAAIABMAEEATQBCAEQAQQAoAHIALABjACwAIABcAG4AIAAgACAAIAAgACAAIAAgAEkATgBEAEUAWAAoAHsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEUAQwBIADQAXAAiACwAXAAiAE0AZQB0AGgAYQBuAGUAIABlAG0AaQBzAHMAaQBvAG4AcwAgACgAdAAgAEMASAA0ACkAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEcAVwBQAEMASAA0AFwAIgAsAFwAIgBHAGwAbwBiAGEAbAAgAHcAYQByAG0AaQBuAGcAIABwAG8AdABlAG4AdABpAGEAbAAgAGYAbwByACAAbQBlAHQAaABhAG4AZQAgACgAdAAgAEMATwAyAC0AZQAgAC8AIAB0ACAAQwBIADQAKQBcACIAXABuACAAIAAgACAAIAAgACAAIAB9ACwAIAByACwAIABjACkAXABuACAAIAAgACAAIAAgACkAXABuACAAIAAgACAAKQBcAG4AIAAgACkAOwAiAH0ALAB7ACIAcABhAHQAaAAiADoAIgAvAHAAcgBvAGoAZQBjAHQAcwAvAEMAbwBtAG0AbwBuAF8ASQBuAHAAdQB0AEYAdQBuAGMAdABpAG8AbgBzACIALAAiAHQAZQB4AHQAIgA6ACIAVQB0AGkAbABpAHQAeQBfAEcAZQB0AEEAcgByAGEAeQBUAGEAYgBsAGUAUgBvAHcAUwB0AGEAcgB0AE4AdQBtAGIAZQByAFwAbgA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAAVABhAGIAbABlAGgAZQBhAGQAZQByAEMAZQBsAGwALABSAG8AdwBzAEIAZQB0AHcAZQBlAG4ASABlAGEAZABlAHIAYQBuAGQAQQByAHIAYQB5ACwAXABuACAAIAAgACAAUgBPAFcAKABUAGEAYgBsAGUAaABlAGEAZABlAHIAQwBlAGwAbAApACAAKwAgAFIAbwB3AHMAQgBlAHQAdwBlAGUAbgBIAGUAYQBkAGUAcgBhAG4AZABBAHIAcgBhAHkAIAAtACAAMQBcAG4AKQA7AFwAbgBcAG4AVQB0AGkAbABpAHQAeQBfAEcAZQB0AEEAcgByAGEAeQBUAGEAYgBsAGUAQwBvAGwAdQBtAG4AUwB0AGEAcgB0AE4AdQBtAGIAZQByAFwAbgA9AEwAQQBNAEIARABBACgAXABuACAAIABUAGEAYgBsAGUASABlAGEAZABlAHIAQwBlAGwAbAAsAFwAbgAgACAAQwBPAEwAVQBNAE4AKABUAGEAYgBsAGUASABlAGEAZABlAHIAQwBlAGwAbAApAFwAbgApADsAXABuAFwAbgBVAHQAaQBsAGkAdAB5AF8ARABpAHMAcABsAGEAeQBBAHIAcgBhAHkASQBuAFQAYQBiAGwAZQBcAG4APQBMAEEATQBCAEQAQQAoAFwAbgAgAEEAcgByAGEAeQBEAGEAdABhACwAIABUAGEAYgBsAGUAaABlAGEAZABlAHIAQwBlAGwAbAAsACAAUgBvAHcAcwBCAGUAdAB3AGUAZQBuAEgAZQBhAGQAZQByAGEAbgBkAEEAcgByAGEAeQAsACAAWwBDAG8AbAB1AG0AbgBzAEIAZQB0AHcAZQBlAG4ASABlAGEAZABlAHIAQQBuAGQAQQByAHIAYQB5AF0ALABcAG4AIABJAEYARQBSAFIATwBSACgAXABuACAAIAAgACAAIABJAE4ARABFAFgAKABcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAVQBOAEkAUQBVAEUAKABBAHIAcgBhAHkARABhAHQAYQApACwAIABcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAUgBPAFcAKAApAC0AVQB0AGkAbABpAHQAeQBfAEcAZQB0AEEAcgByAGEAeQBUAGEAYgBsAGUAUgBvAHcAUwB0AGEAcgB0AE4AdQBtAGIAZQByACgAVABhAGIAbABlAGgAZQBhAGQAZQByAEMAZQBsAGwALAAgAFIAbwB3AHMAQgBlAHQAdwBlAGUAbgBIAGUAYQBkAGUAcgBhAG4AZABBAHIAcgBhAHkAKQAsACAAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgAEMATwBMAFUATQBOACgAKQAtAFUAdABpAGwAaQB0AHkAXwBHAGUAdABBAHIAcgBhAHkAVABhAGIAbABlAEMAbwBsAHUAbQBuAFMAdABhAHIAdABOAHUAbQBiAGUAcgAoAFQAYQBiAGwAZQBoAGUAYQBkAGUAcgBDAGUAbABsACkAIAArAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIABJAEYAKABJAFMATwBNAEkAVABUAEUARAAoAEMAbwBsAHUAbQBuAHMAQgBlAHQAdwBlAGUAbgBIAGUAYQBkAGUAcgBBAG4AZABBAHIAcgBhAHkAKQAsACAAMQAsACAAQwBvAGwAdQBtAG4AcwBCAGUAdAB3AGUAZQBuAEgAZQBhAGQAZQByAEEAbgBkAEEAcgByAGEAeQApAFwAbgAgACAAIAAgACAAIAAgACAAKQAsACAAXAAiAFwAIgBcAG4AIAAgACAAIAApAFwAbgApADsAXABuAFwAbgBVAHQAaQBsAGkAdAB5AF8ATABvAG8AawB1AHAAVgBhAGwAdQBlAEkAbgBUAGEAYgBsAGUAXABuAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABMAG8AbwBrAHUAcABWAGEAbAB1AGUALAAgAEwAbwBvAGsAdQBwAEEAcgByAGEAeQAsACAAUgBlAHQAdQByAG4AQQByAHIAYQB5ACwAXABuACAAIAAgACAAWABMAE8ATwBLAFUAUAAoAEwAbwBvAGsAdQBwAFYAYQBsAHUAZQAsACAATABvAG8AawB1AHAAQQByAHIAYQB5ACwAIABSAGUAdAB1AHIAbgBBAHIAcgBhAHkALAAgAFwAIgBcACIAKQBcAG4AKQA7AFwAbgBcAG4AVQB0AGkAbABpAHQAeQBfAEwAbwBvAGsAdQBwAFYAYQBsAHUAZQBJAG4AVABhAGIAbABlAE4AdQBtAGIAZQByAFwAbgA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAATABvAG8AawB1AHAAVgBhAGwAdQBlACwAIABMAG8AbwBrAHUAcABBAHIAcgBhAHkALAAgAFIAZQB0AHUAcgBuAEEAcgByAGEAeQAsAFwAbgAgACAAIAAgAEkARgAoAEkAUwBOAFUATQBCAEUAUgAoAFwAbgAgACAAIAAgACAAIAAgACAAWABMAE8ATwBLAFUAUAAoAEwAbwBvAGsAdQBwAFYAYQBsAHUAZQAsACAATABvAG8AawB1AHAAQQByAHIAYQB5ACwAIABSAGUAdAB1AHIAbgBBAHIAcgBhAHkALAAgAFwAIgBcACIAKQBcAG4AIAAgACAAIAApACwAIABYAEwATwBPAEsAVQBQACgATABvAG8AawB1AHAAVgBhAGwAdQBlACwAIABMAG8AbwBrAHUAcABBAHIAcgBhAHkALAAgAFIAZQB0AHUAcgBuAEEAcgByAGEAeQAsACAAXAAiAFwAIgApACwAIAAwACkAXABuACkAOwBcAG4AXABuAFUAdABpAGwAaQB0AHkAXwBMAG8AbwBrAHUAcABWAGEAbAB1AGUASQBuAFQAYQBiAGwAZQBUAHcAbwBDAG8AbAB1AG0AbgBzAFwAbgA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAATABvAG8AawB1AHAAVgBhAGwAdQBlADEALAAgAEwAbwBvAGsAdQBwAFYAYQBsAHUAZQAyACwAIABMAG8AbwBrAHUAcABBAHIAcgBhAHkAMQAsACAATABvAG8AawB1AHAAQQByAHIAYQB5ADIALAAgAFIAZQB0AHUAcgBuAEEAcgByAGEAeQAsACAAWwBWAGEAbAB1AGUASQBGAEYAYQBsAHMAZQBdACwAXABuACAAIAAgACAAWABMAE8ATwBLAFUAUAAoADEALAAgACgATABvAG8AawB1AHAAQQByAHIAYQB5ADEAPQBMAG8AbwBrAHUAcABWAGEAbAB1AGUAMQApACoAKABMAG8AbwBrAHUAcABBAHIAcgBhAHkAMgA9AEwAbwBvAGsAdQBwAFYAYQBsAHUAZQAyACkALAAgAFIAZQB0AHUAcgBuAEEAcgByAGEAeQAsACAASQBGACgASQBTAE8ATQBJAFQAVABFAEQAKABWAGEAbAB1AGUASQBGAEYAYQBsAHMAZQApACwAIABcACIAXAAiACwAIABWAGEAbAB1AGUASQBGAEYAYQBsAHMAZQApACkAXABuACkAOwBcAG4AXABuAFUAdABpAGwAaQB0AHkAXwBMAG8AbwBrAHUAcABWAGEAbAB1AGUASQBuAFQAYQBiAGwAZQBPAG4AZQBDAG8AbAB1AG0AbgBBAG4AZABIAGUAYQBkAGUAcgBcAG4APQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAEwAbwBvAGsAdQBwAFYAYQBsAHUAZQAxACwAIABMAG8AbwBrAHUAcABWAGEAbAB1AGUAMgAsACAATABvAG8AawB1AHAAQQByAHIAYQB5ADEALAAgAEwAbwBvAGsAdQBwAEEAcgByAGEAeQAyACwAIABSAGUAdAB1AHIAbgBBAHIAcgBhAHkALAAgAFsAVgBhAGwAdQBlAEkAZgBGAGEAbABzAGUAXQAsAFwAbgAgACAAIAAgAEkARgBFAFIAUgBPAFIAKABcAG4AIAAgACAAIAAgACAAIAAgAFgATABPAE8ASwBVAFAAKABMAG8AbwBrAHUAcABWAGEAbAB1AGUAMQAsACAATABvAG8AawB1AHAAQQByAHIAYQB5ADEALABcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAWABMAE8ATwBLAFUAUAAoAEwAbwBvAGsAdQBwAFYAYQBsAHUAZQAyACwAIABMAG8AbwBrAHUAcABBAHIAcgBhAHkAMgAsACAAUgBlAHQAdQByAG4AQQByAHIAYQB5ACkAXABuACAAIAAgACAAIAAgACAAIAApACwAXABuACAAIAAgACAAIAAgACAAIABJAEYAKABJAFMATwBNAEkAVABUAEUARAAoAFYAYQBsAHUAZQBJAGYARgBhAGwAcwBlACkALAAgAFwAIgBcACIALAAgAFYAYQBsAHUAZQBJAGYARgBhAGwAcwBlACkAXABuACAAIAAgACAAKQBcAG4AKQA7AFwAbgBcAG4AVQB0AGkAbABpAHQAeQBfAFMAcABsAGkAdABTAHQAcgBpAG4AZwBJAG4AdABvAEEAcgByAGEAeQBcAG4APQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAEMAZQBsAGwALAAgAEQAZQBsAGkAbQBpAHQAZQByACwAIABbAEMAaABhAHIAYQBjAHQAZQByAFQAbwBSAGUAbQBvAHYAZQAxAF0ALAAgAFsAQwBoAGEAcgBhAGMAdABlAHIAVABvAFIAZQBtAG8AdgBlADIAXQAsAFwAbgAgACAAIAAgACAAIAAgACAARgBJAEwAVABFAFIAWABNAEwAKABcAG4AIAAgACAAIAAgACAAIAAgAFwAIgA8AHQAPgA8AHMAPgBcACIAIAAmAFwAbgAgACAAIAAgACAAIAAgACAAUwBVAEIAUwBUAEkAVABVAFQARQAoAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIABTAFUAQgBTAFQASQBUAFUAVABFACgAUwBVAEIAUwBUAEkAVABVAFQARQAoAEMAZQBsAGwALABDAGgAYQByAGEAYwB0AGUAcgBUAG8AUgBlAG0AbwB2AGUAMQAsAFwAIgBcACIAKQAsAEMAaABhAHIAYQBjAHQAZQByAFQAbwBSAGUAbQBvAHYAZQAyACwAXAAiAFwAIgApACwAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgAEQAZQBsAGkAbQBpAHQAZQByACwAXAAiADwALwBzAD4APABzAD4AXAAiAFwAbgAgACAAIAAgACAAIAAgACAAKQAgACYAXABuACAAIAAgACAAIAAgACAAIABcACIAPAAvAHMAPgA8AC8AdAA+AFwAIgAsAFwAbgAgACAAIAAgACAAIAAgACAAXAAiAC8ALwBzAFwAIgBcAG4AIAAgACAAIAApAFwAbgApADsAXABuAFwAbgBVAHQAaQBsAGkAdAB5AF8ARwBlAHQAQwBsAGkAbQBhAHQAZQBaAG8AbgBlAFwAbgA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAAYQB2AGcAVABlAG0AcAAsAGEAdgBnAFIAYQBpAG4ALABmAHIAbwBzAHQARABhAHkAcwAsAGUAbABlAHYALABtAGEAcABfAHAAZQB0ACwAXABuACAAIAAgACAAbQBpAG4AVABlAG0AcABBAHIAcgBhAHkALABtAGEAeABUAGUAbQBwAEEAcgByAGEAeQAsAFwAbgAgACAAIAAgAG0AaQBuAFIAYQBpAG4AZgBhAGwAbABBAHIAcgBhAHkALABtAGEAeABSAGEAaQBuAGYAYQBsAGwAQQByAHIAYQB5ACwAXABuACAAIAAgACAAbQBpAG4ARgByAG8AcwB0AEEAcgByAGEAeQAsAG0AYQB4AEYAcgBvAHMAdABBAHIAcgBhAHkALABcAG4AIAAgACAAIABtAGkAbgBFAGwAZQB2AGEAdABpAG8AbgBBAHIAcgBhAHkALABtAGEAeABFAGwAZQB2AGEAdABpAG8AbgBBAHIAcgBhAHkALABcAG4AIAAgACAAIABtAGkAbgBQAEUAVABBAHIAcgBhAHkALABtAGEAeABQAEUAVABBAHIAcgBhAHkALABcAG4AIAAgACAAIABjAGwAaQBtAGEAdABlAFoAbwBuAGUAQQByAHIAYQB5ACwAXABuACAAIAAgACAATABFAFQAKABcAG4AIAAgACAAIAAgACAAIAAgAG0AYQBzAGsALABcAG4AIAAgACAAIAAgACAAIAAgACgAVgBBAEwAVQBFACgAbQBpAG4AVABlAG0AcABBAHIAcgBhAHkAKQA8AD0AYQB2AGcAVABlAG0AcAApACoAXABuACAAIAAgACAAIAAgACAAIAAoAFYAQQBMAFUARQAoAG0AYQB4AFQAZQBtAHAAQQByAHIAYQB5ACkAPgA9AGEAdgBnAFQAZQBtAHAAKQAqAFwAbgAgACAAIAAgACAAIAAgACAAKABWAEEATABVAEUAKABtAGkAbgBSAGEAaQBuAGYAYQBsAGwAQQByAHIAYQB5ACkAPAA9AGEAdgBnAFIAYQBpAG4AKQAqAFwAbgAgACAAIAAgACAAIAAgACAAKABWAEEATABVAEUAKABtAGEAeABSAGEAaQBuAGYAYQBsAGwAQQByAHIAYQB5ACkAPgA9AGEAdgBnAFIAYQBpAG4AKQAqAFwAbgAgACAAIAAgACAAIAAgACAAKABWAEEATABVAEUAKABtAGkAbgBGAHIAbwBzAHQAQQByAHIAYQB5ACkAPAA9AGYAcgBvAHMAdABEAGEAeQBzACkAKgBcAG4AIAAgACAAIAAgACAAIAAgACgAVgBBAEwAVQBFACgAbQBhAHgARgByAG8AcwB0AEEAcgByAGEAeQApAD4APQBmAHIAbwBzAHQARABhAHkAcwApACoAXABuACAAIAAgACAAIAAgACAAIAAoAFYAQQBMAFUARQAoAG0AaQBuAEUAbABlAHYAYQB0AGkAbwBuAEEAcgByAGEAeQApADwAPQBlAGwAZQB2ACkAKgBcAG4AIAAgACAAIAAgACAAIAAgACgAVgBBAEwAVQBFACgAbQBhAHgARQBsAGUAdgBhAHQAaQBvAG4AQQByAHIAYQB5ACkAPgA9AGUAbABlAHYAKQAqAFwAbgAgACAAIAAgACAAIAAgACAAKABWAEEATABVAEUAKABtAGkAbgBQAEUAVABBAHIAcgBhAHkAKQA8AD0AbQBhAHAAXwBwAGUAdAApACoAXABuACAAIAAgACAAIAAgACAAIAAoAFYAQQBMAFUARQAoAG0AYQB4AFAARQBUAEEAcgByAGEAeQApAD4APQBtAGEAcABfAHAAZQB0ACkALABcAG4AIAAgACAAIAAgACAAIAAgAFQAQQBLAEUAKABcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAARgBJAEwAVABFAFIAKABjAGwAaQBtAGEAdABlAFoAbwBuAGUAQQByAHIAYQB5ACwAbQBhAHMAawAsACAAXAAiAE4AbwAgAG0AYQB0AGMAaABcACIAKQAsAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIAAxAFwAbgAgACAAIAAgACAAIAAgACAAKQBcAG4AIAAgACAAIAApAFwAbgApADsAXABuAFwAbgBVAHQAaQBsAGkAdAB5AF8ATABvAG8AawB1AHAASQB0AGUAbQBGAHIAbwBtAE0AaQBuAE0AYQB4AFwAbgA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAATABvAG8AawB1AHAAVgBhAGwAdQBlACwAIABNAGkAbgBBAHIAcgBhAHkALAAgAE0AYQB4AEEAcgByAGEAeQAsACAASQB0AGUAbQBBAHIAcgBhAHkALABcAG4AIAAgACAAIABMAEUAVAAoAFwAbgAgACAAIAAgACAAIAAgACAAbQBhAHMAawAsAFwAbgAgACAAIAAgACAAIAAgACAAKABWAEEATABVAEUAKABNAGkAbgBBAHIAcgBhAHkAKQA8AD0ATABvAG8AawB1AHAAVgBhAGwAdQBlACkAKgBcAG4AIAAgACAAIAAgACAAIAAgACgAVgBBAEwAVQBFACgATQBhAHgAQQByAHIAYQB5ACkAPgA9AEwAbwBvAGsAdQBwAFYAYQBsAHUAZQApACwAXABuACAAIAAgACAAIAAgACAAIABGAEkATABUAEUAUgAoAEkAdABlAG0AQQByAHIAYQB5ACwAIABtAGEAcwBrACwAIABcACIATgBvACAAbQBhAHQAYwBoAFwAIgApAFwAbgAgACAAIAAgACkAXABuACkAOwBcAG4AXABuAFwAbgBVAHQAaQBsAGkAdAB5AF8AUwB1AG0AUQB1AGEAbgB0AGkAdAB5AEYAcgBvAG0AQwByAGkAdABlAHIAaQBhAFwAbgA9AEwAQQBNAEIARABBACgAXABuACAAIABDAHIAaQB0AGUAcgBpAGEAMQAsACAAQwByAGkAdABlAHIAaQBhADEAVAB5AHAAZQBBAHIAcgBhAHkALAAgAFEAdQBhAG4AdABpAHQAeQAsACAAWwBNAHUAbAB0AGkAcABsAGkAZQByAF0ALAAgAFsAQwByAGkAdABlAHIAaQBhADIAXQAsAFsAQwByAGkAdABlAHIAaQBhADIAQQByAHIAYQB5AF0ALABcAG4AIAAgAEwARQBUACgAXABuACAAIAAgACAAbQB1AGwAdABpAHAAbABpAGUAcgAsACAASQBGACgASQBTAE8ATQBJAFQAVABFAEQAKABNAHUAbAB0AGkAcABsAGkAZQByACkALAAxACwATQB1AGwAdABpAHAAbABpAGUAcgApACwAXABuACAAIAAgACAAcQB1AGEAbgB0AGkAdAB5ACwAIABRAHUAYQBuAHQAaQB0AHkAKgBNAHUAbAB0AGkAcABsAGkAZQByACwAXABuACAAIAAgACAAYwByAGkAdABlAHIAaQBhADEALAAtAC0AKABDAHIAaQB0AGUAcgBpAGEAMQBUAHkAcABlAEEAcgByAGEAeQA9AEMAcgBpAHQAZQByAGkAYQAxACkALABcAG4AIAAgACAAIABjAHIAaQB0AGUAcgBpAGEAMgAsAEkARgAoAEkAUwBPAE0ASQBUAFQARQBEACgAQwByAGkAdABlAHIAaQBhADIAKQAsADEALAAtAC0AKABDAHIAaQB0AGUAcgBpAGEAMgBBAHIAcgBhAHkAPQBDAHIAaQB0AGUAcgBpAGEAMgApACkALABcAG4AIAAgACAAIABTAFUATQBQAFIATwBEAFUAQwBUACgAYwByAGkAdABlAHIAaQBhADEAKgBjAHIAaQB0AGUAcgBpAGEAMgAqAHEAdQBhAG4AdABpAHQAeQApAFwAbgAgACAAKQBcAG4AKQA7AFwAbgBcAG4AZwBlAHQATwB2AGUAcgBsAGEAcABwAGkAbgBnAFIAZQBwAG8AcgB0AGkAbgBnAEMAeQBjAGwAZQBzAFwAbgA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAAUAByAG8AZAB1AGMAdABpAG8AbgBDAHkAYwBsAGUAUwB0AGEAcgB0ACwAUAByAG8AZAB1AGMAdABpAG8AbgBDAHkAYwBsAGUARQBuAGQALABSAGUAcABvAHIAdABpAG4AZwBDAHkAYwBsAGUAUwB0AGEAcgB0ACwAXABuACAAIAAgACAATABFAFQAKABcAG4AIAAgACAAIAAgACAAIAAgAFMALABQAHIAbwBkAHUAYwB0AGkAbwBuAEMAeQBjAGwAZQBTAHQAYQByAHQALABcAG4AIAAgACAAIAAgACAAIAAgAEUALABQAHIAbwBkAHUAYwB0AGkAbwBuAEMAeQBjAGwAZQBFAG4AZAAsAFwAbgAgACAAIAAgACAAIAAgACAAbQAsAE0ATwBOAFQASAAoAFIAZQBwAG8AcgB0AGkAbgBnAEMAeQBjAGwAZQBTAHQAYQByAHQAKQAsAFwAbgAgACAAIAAgACAAIAAgACAAZAAsAEQAQQBZACgAUgBlAHAAbwByAHQAaQBuAGcAQwB5AGMAbABlAFMAdABhAHIAdAApACwAXABuACAAIAAgACAAIAAgACAAIABQAGUAcgBpAG8AZABFAG4AZAAsAEwAQQBNAEIARABBACgAcwB0ACwARQBEAEEAVABFACgAcwB0ACwAMQAyACkALQAxACkALABcAG4AIAAgACAAIAAgACAAIAAgAEEALABTAC0AMwA2ADUALABcAG4AIAAgACAAIAAgACAAIAAgAHkAYQAsAFkARQBBAFIAKABBACkALABcAG4AIAAgACAAIAAgACAAIAAgAHkAYgAsAFkARQBBAFIAKABFACkALABcAG4AIAAgACAAIAAgACAAIAAgAGYAaQByAHMAdABZAGUAYQByACwAeQBhACsAKABQAGUAcgBpAG8AZABFAG4AZAAoAEQAQQBUAEUAKAB5AGEALABtACwAZAApACkAPAAgAFMAKQAsAFwAbgAgACAAIAAgACAAIAAgACAAbABhAHMAdABZAGUAYQByACwAeQBiAC0AKABEAEEAVABFACgAeQBiACwAbQAsAGQAKQA+ACAARQApACwAXABuACAAIAAgACAAIAAgACAAIABNAEEAWAAoADAALABsAGEAcwB0AFkAZQBhAHIALQBmAGkAcgBzAHQAWQBlAGEAcgArADEAKQBcAG4AIAAgACAAIAApAFwAbgApADsAXABuAFwAbgBnAGUAdABPAHYAZQByAGwAYQBwAHAAaQBuAGcAUgBlAHAAbwByAHQAaQBuAGcAUABlAHIAaQBvAGQAcwBcAG4APQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAFAAcgBvAGQAdQBjAHQAaQBvAG4AQwB5AGMAbABlAFMAdABhAHIAdAAsAFAAcgBvAGQAdQBjAHQAaQBvAG4AQwB5AGMAbABlAEUAbgBkACwAUgBlAHAAbwByAHQAaQBuAGcAQwB5AGMAbABlAFMAdABhAHIAdAAsAFwAbgAgACAAIAAgAEwARQBUACgAXABuACAAIAAgACAAIAAgACAAIABTACwAUAByAG8AZAB1AGMAdABpAG8AbgBDAHkAYwBsAGUAUwB0AGEAcgB0ACwAXABuACAAIAAgACAAIAAgACAAIABFACwAUAByAG8AZAB1AGMAdABpAG8AbgBDAHkAYwBsAGUARQBuAGQALABcAG4AIAAgACAAIAAgACAAIAAgAG0ALABNAE8ATgBUAEgAKABSAGUAcABvAHIAdABpAG4AZwBDAHkAYwBsAGUAUwB0AGEAcgB0ACkALABcAG4AIAAgACAAIAAgACAAIAAgAGQALABEAEEAWQAoAFIAZQBwAG8AcgB0AGkAbgBnAEMAeQBjAGwAZQBTAHQAYQByAHQAKQAsACAALwAqAGgAZQBsAHAAZQByADoAIABlAG4AZAAgAGQAYQB0AGUAIABmAG8AcgAgAGEAIAByAGUAcABvAHIAdABpAG4AZwAgAHAAZQByAGkAbwBkACAAcwB0AGEAcgB0AGkAbgBnACAAYQB0ACAAYQAgAGcAaQB2AGUAbgAgAGQAYQB0AGUAKgAvAFwAbgAgACAAIAAgACAAIAAgACAAUABlAHIAaQBvAGQARQBuAGQALABMAEEATQBCAEQAQQAoAHMAdAAsAEUARABBAFQARQAoAHMAdAAsADEAMgApAC0AMQApACwAIAAvACoAbwBuAGwAeQAgAG4AZQBlAGQAIAB0AG8AIABsAG8AbwBrACAAYgBhAGMAawAgADMANgA1ACAAZABhAHkAcwAoAG0AYQB4ACAAbwB2AGUAcgBsAGEAcAAgAHcAaQBuAGQAbwB3ACkAKgAvAFwAbgAgACAAIAAgACAAIAAgACAAQQAsAFMALQAzADYANQAsAFwAbgAgACAAIAAgACAAIAAgACAAeQBhACwAWQBFAEEAUgAoAEEAKQAsAFwAbgAgACAAIAAgACAAIAAgACAAeQBiACwAWQBFAEEAUgAoAEUAKQAsACAALwAqAGkAZgAgAHQAaABlACAAYQBuAGMAaABvAHIAIABmAG8AcgAgAHkAYQAgAGUAbgBkAHMAIABiAGUAZgBvAHIAZQAgAFMALABpAHQAIABjAGEAbgAnAHQAIABvAHYAZQByAGwAYQBwADsAIABtAG8AdgBlACAAdABvACAAbgBlAHgAdAAgAHkAZQBhAHIAKgAvAFwAbgAgACAAIAAgACAAIAAgACAAZgBpAHIAcwB0AFkAZQBhAHIALAB5AGEAKwAoAFAAZQByAGkAbwBkAEUAbgBkACgARABBAFQARQAoAHkAYQAsAG0ALABkACkAKQA8AFMAKQAsACAALwAqAGkAZgAgAHQAaABlACAAYQBuAGMAaABvAHIAIABmAG8AcgAgAHkAYgAgAHMAdABhAHIAdABzACAAYQBmAHQAZQByACAARQAsAGkAdAAgAGMAYQBuACcAdAAgAG8AdgBlAHIAbABhAHAAOwAgAG0AbwB2AGUAIAB0AG8AIABwAHIAZQB2AGkAbwB1AHMAIAB5AGUAYQByACoALwBcAG4AIAAgACAAIAAgACAAIAAgAGwAYQBzAHQAWQBlAGEAcgAsAHkAYgAtACgARABBAFQARQAoAHkAYgAsAG0ALABkACkAPgBFACkALABcAG4AIAAgACAAIAAgACAAIAAgAG4ALABNAEEAWAAoADAALABsAGEAcwB0AFkAZQBhAHIALQBmAGkAcgBzAHQAWQBlAGEAcgArADEAKQAsAFwAbgAgACAAIAAgACAAIAAgACAAeQByAHMALABTAEUAUQBVAEUATgBDAEUAKABuACwAMQAsAGYAaQByAHMAdABZAGUAYQByACwAMQApACwAXABuACAAIAAgACAAIAAgACAAIABzAHQAYQByAHQAcwAsAEQAQQBUAEUAKAB5AHIAcwAsAG0ALABkACkALABcAG4AIAAgACAAIAAgACAAIAAgAGUAbgBkAHMALABNAEEAUAAoAHMAdABhAHIAdABzACwAUABlAHIAaQBvAGQARQBuAGQAKQAsAFwAbgAgACAAIAAgACAAIAAgACAAdABhAGcALABJAEYAKABzAHQAYQByAHQAcwA9AFIAZQBwAG8AcgB0AGkAbgBnAEMAeQBjAGwAZQBTAHQAYQByAHQALABcACIAIAAoAFQAaABpAHMAIAByAGUAcABvAHIAdABpAG4AZwAgAGMAeQBjAGwAZQApAFwAIgAsAFwAIgBcACIAKQAsAFwAbgAgACAAIAAgACAAIAAgACAAcwB0AGEAcgB0AHMAVABlAHgAdAAsAFQARQBYAFQAKABzAHQAYQByAHQAcwAsAFwAIgBkAGQAIABtAG0AbQAgAHkAeQB5AHkAXAAiACkALABcAG4AIAAgACAAIAAgACAAIAAgAGUAbgBkAHMAVABlAHgAdAAsAFQARQBYAFQAKABlAG4AZABzACwAXAAiAGQAZAAgAG0AbQBtACAAeQB5AHkAeQBcACIAKQAsAFwAbgAgACAAIAAgACAAIAAgACAAcgBvAHcAcwAsAEkARgAoAG4APQAwACwAXAAiAFwAIgAsAEgAUwBUAEEAQwBLACgAcwB0AGEAcgB0AHMAVABlAHgAdAAgACYAIABcACIAIAB0AG8AIABcACIAIAAmACAAZQBuAGQAcwBUAGUAeAB0ACAAJgAgAHQAYQBnACkAKQAsAFwAbgAgACAAIAAgACAAIAAgACAAcgBvAHcAcwBcAG4AIAAgACAAIAApAFwAbgApADsAXABuAFwAbgBcAG4AVQB0AGkAbABpAHQAeQBfAEQAaQBzAHAAbABhAHkARgB1AG4AYwB0AGkAbwBuAE4AYQBtAGUAXABuAD0ATABBAE0AQgBEAEEAKABGAHUAbgBjAHQAaQBvAG4ALAAgAFQARQBYAFQAQgBFAEYATwBSAEUAKABGAE8AUgBNAFUATABBAFQARQBYAFQAKABGAHUAbgBjAHQAaQBvAG4AKQAsACAAXAAiACgAXAAiACkAKQA7AFwAbgBcAG4AVQB0AGkAbABpAHQAeQBfAEwAbwBvAGsAdQBwAE4AMgBPAEUARgBGAHIAbwBtAFAAcgBvAGQASQByAHIAaQBnAGEAdABpAG8AbgBSAGEAaQBuAGYAYQBsAGwAXABuAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABQAHIAbwBkAHUAYwB0AGkAbwBuAFMAeQBzAHQAZQBtACwAIABJAHIAcgBpAGcAYQB0AGkAbwBuAE0AZQB0AGgAbwBkACwAIABSAGEAaQBuAGYAYQBsAGwAWgBvAG4AZQAsAFwAbgAgACAAIAAgAFAAcgBvAGQAdQBjAHQAaQBvAG4AUwB5AHMAdABlAG0AQQByAHIAYQB5ACwAIABJAHIAcgBpAGcAYQB0AGkAbwBuAE0AZQB0AGgAbwBkAEEAcgByAGEAeQAsACAAUgBhAGkAbgBmAGEAbABsAFoAbwBuAGUAQQByAHIAYQB5ACwAUgBlAHQAdQByAG4AQQByAHIAYQB5ACwAXABuACAAIAAgACAATABFAFQAKABcAG4AIAAgACAAIAAgACAAIAAgAEkAcgByAGkAZwBhAHQAaQBvAG4ATQBlAHQAaABvAGQALAAgAEkARgAoAEkAcgByAGkAZwBhAHQAaQBvAG4ATQBlAHQAaABvAGQAPQBcACIATgBvAHQAIABpAHIAcgBpAGcAYQB0AGUAZABcACIALAAgAFwAIgBOAG8AdAAgAGkAcgByAGkAZwBhAHQAZQBkAFwAIgAsACAAXAAiAEEAbgB5AFwAIgApACwAXABuACAAIAAgACAAIAAgACAAIABSAGEAaQBuAGYAYQBsAGwAWgBvAG4AZQAsACAASQBGACgASQByAHIAaQBnAGEAdABpAG8AbgBNAGUAdABoAG8AZAAgAD0AIABcACIATgBvAHQAIABpAHIAcgBpAGcAYQB0AGUAZABcACIALAAgAFIAYQBpAG4AZgBhAGwAbABaAG8AbgBlACwAIABcACIAQQBuAHkAXAAiACkALABcAG4AIAAgACAAIAAgACAAIAAgAFgATABPAE8ASwBVAFAAKAAxACwAIABcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAKABQAHIAbwBkAHUAYwB0AGkAbwBuAFMAeQBzAHQAZQBtAEEAcgByAGEAeQA9AFAAcgBvAGQAdQBjAHQAaQBvAG4AUwB5AHMAdABlAG0AKQAqAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIAAoAEkAcgByAGkAZwBhAHQAaQBvAG4ATQBlAHQAaABvAGQAQQByAHIAYQB5AD0ASQByAHIAaQBnAGEAdABpAG8AbgBNAGUAdABoAG8AZAApACoAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgACgAUgBhAGkAbgBmAGEAbABsAFoAbwBuAGUAQQByAHIAYQB5AD0AUgBhAGkAbgBmAGEAbABsAFoAbwBuAGUAKQAsACAAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgAFIAZQB0AHUAcgBuAEEAcgByAGEAeQApAFwAbgAgACAAIAAgACkAXABuACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAEMAcgBvAHAAcABpAG4AZwBfAEcAZQB0AEYAcgBhAGMAVwBFAFQAXABuAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABMAGUAYQBjAGgAaQBuAGcAWgBvAG4AZQAsAFwAbgAgACAAIAAgAFAAcgBvAGQAdQBjAHQAaQBvAG4AUwB5AHMAdABlAG0ALABcAG4AIAAgACAAIABMAGUAYQBjAGgAaQBuAGcAWgBvAG4AZQBMAG8AbwBrAHUAcAAsAFwAbgAgACAAIAAgAEwAZQBhAGMAaABpAG4AZwBaAG8AbgBlAEYAcgBhAGMAVwBFAFQATABvAG8AawB1AHAALABcAG4AIAAgACAAIABQAHIAbwBkAHUAYwB0AGkAbwBuAFMAeQBzAHQAZQBtAEwAbwBvAGsAdQBwACwAXABuACAAIAAgACAAUAByAG8AZAB1AGMAdABpAG8AbgBTAHkAcwB0AGUAbQBGAHIAYQBjAFcARQBUAEwAbwBvAGsAdQBwACwAXABuACAAIAAgACAATABFAFQAKABcAG4AIAAgACAAIAAgACAAIAAgAEwAZQBhAGMAaABpAG4AZwBaAG8AbgBlAEYAcgBhAGMAVwBFAFQALAAgAFwAbgAgACAAIAAgACAAIAAgACAAQwBvAG0AbQBvAG4AXwBJAG4AcAB1AHQARgB1AG4AYwB0AGkAbwBuAHMALgBVAHQAaQBsAGkAdAB5AF8ATABvAG8AawB1AHAAVgBhAGwAdQBlAEkAbgBUAGEAYgBsAGUATgB1AG0AYgBlAHIAKABcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAATABlAGEAYwBoAGkAbgBnAFoAbwBuAGUALABMAGUAYQBjAGgAaQBuAGcAWgBvAG4AZQBMAG8AbwBrAHUAcAAsAEwAZQBhAGMAaABpAG4AZwBaAG8AbgBlAEYAcgBhAGMAVwBFAFQATABvAG8AawB1AHAAXABuACAAIAAgACAAIAAgACAAIAApACwAXABuACAAIAAgACAAIAAgACAAIABQAHIAbwBkAHUAYwB0AGkAbwBuAFMAeQBzAHQAZQBtAEYAcgBhAGMAVwBFAFQALAAgAFwAbgAgACAAIAAgACAAIAAgACAAQwBvAG0AbQBvAG4AXwBJAG4AcAB1AHQARgB1AG4AYwB0AGkAbwBuAHMALgBVAHQAaQBsAGkAdAB5AF8ATABvAG8AawB1AHAAVgBhAGwAdQBlAEkAbgBUAGEAYgBsAGUATgB1AG0AYgBlAHIAKABcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAUAByAG8AZAB1AGMAdABpAG8AbgBTAHkAcwB0AGUAbQAsAFAAcgBvAGQAdQBjAHQAaQBvAG4AUwB5AHMAdABlAG0ATABvAG8AawB1AHAALABQAHIAbwBkAHUAYwB0AGkAbwBuAFMAeQBzAHQAZQBtAEYAcgBhAGMAVwBFAFQATABvAG8AawB1AHAAXABuACAAIAAgACAAIAAgACAAIAApACwAXABuACAAIAAgACAAIAAgACAAIABJAEYAKABMAGUAYQBjAGgAaQBuAGcAWgBvAG4AZQBGAHIAYQBjAFcARQBUACAAKwAgAFAAcgBvAGQAdQBjAHQAaQBvAG4AUwB5AHMAdABlAG0ARgByAGEAYwBXAEUAVAA+ADAALAAgADEALAAgADAAKQBcAG4AIAAgACAAIAApACkAOwBcAG4AXABuAFwAbgBVAHQAaQBsAGkAdAB5AF8AQwBvAG4AdgBlAHIAdABTAHQAYQB0AGUAQwBvAG0AbQBvAG4ATgBhAG0AZQBUAG8AQQBiAGIAcgBlAHYAaQBhAHQAaQBvAG4AXABuAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABTAHQAYQB0AGUAQwBvAG0AbQBvAG4ATgBhAG0AZQAsAFwAbgAgACAAIAAgAFMAdABhAHQAZQBDAG8AbQBtAG8AbgBOAGEAbQBlAEEAcgByAGEAeQAsACAAUwB0AGEAdABlAEEAYgBiAHIAZQB2AGkAYQB0AGkAbwBuAEEAcgByAGEAeQAsAFwAbgAgACAAIAAgAFgATABPAE8ASwBVAFAAKABTAHQAYQB0AGUAQwBvAG0AbQBvAG4ATgBhAG0AZQAsACAAUwB0AGEAdABlAEMAbwBtAG0AbwBuAE4AYQBtAGUAQQByAHIAYQB5ACwAIABTAHQAYQB0AGUAQQBiAGIAcgBlAHYAaQBhAHQAaQBvAG4AQQByAHIAYQB5ACwAIABcACIAXAAiACkAXABuACkAOwBcAG4AXABuAFUAdABpAGwAaQB0AHkAXwBTAG8AdQByAGMAZQBIAHkAcABlAHIAbABpAG4AawBcAG4APQBMAEEATQBCAEQAQQAoAFQAYQByAGcAZQB0AEMAZQBsAGwALABcAG4AIAAgAEwARQBUACgAXABuACAAIAAgACAAcwBoACwAIABUAEUAWABUAEEARgBUAEUAUgAoAEMARQBMAEwAKABcACIAZgBpAGwAZQBuAGEAbQBlAFwAIgAsACAAVABhAHIAZwBlAHQAQwBlAGwAbAApACwAIABcACIAXQBcACIAKQAsAFwAbgAgACAAIAAgAGEAZABkAHIALAAgAEMARQBMAEwAKABcACIAYQBkAGQAcgBlAHMAcwBcACIALAAgAFQAYQByAGcAZQB0AEMAZQBsAGwAKQAsAFwAbgAgACAAIAAgAFwAIgAjACcAXAAiACAAJgAgAHMAaAAgACYAIABcACIAJwAhAFwAIgAgACYAIABhAGQAZAByAFwAbgAgACAAKQBcAG4AKQA7AFwAbgBcAG4AVQB0AGkAbABpAHQAeQBfAFMAbwB1AHIAYwBlAEgAeQBwAGUAcgBsAGkAbgBrAEQAaQBmAGYAZQByAGUAbgB0AFMAaABlAGUAdABcAG4APQBMAEEATQBCAEQAQQAoAFQAYQByAGcAZQB0AEMAZQBsAGwALABcAG4AIAAgAEwARQBUACgAXABuACAAIAAgACAAcwBoACwAIABUAEUAWABUAEEARgBUAEUAUgAoAEMARQBMAEwAKABcACIAZgBpAGwAZQBuAGEAbQBlAFwAIgAsACAAVABhAHIAZwBlAHQAQwBlAGwAbAApACwAIABcACIAXQBcACIAKQAsAFwAbgAgACAAIAAgAGEAZABkAHIALAAgAEMARQBMAEwAKABcACIAYQBkAGQAcgBlAHMAcwBcACIALAAgAFQAYQByAGcAZQB0AEMAZQBsAGwAKQAsAFwAbgAgACAAIAAgAFwAIgAjAFwAIgAgACYAIABhAGQAZAByAFwAbgAgACAAKQBcAG4AKQA7AFwAbgBcAG4AVQB0AGkAbABpAHQAeQBfAEQAaQBzAHAAbABhAHkAQQByAGcAdQBtAGUAbgB0AHMAXwAxAF8AMgBcAG4APQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAEEAcgBnAHUAbQBlAG4AdABzAEEAcgByAGEAeQAsAFwAbgAgACAAIAAgAEMASABPAE8AUwBFAEMATwBMAFMAKABBAHIAZwB1AG0AZQBuAHQAcwBBAHIAcgBhAHkALAAgADEALAAgADIAKQBcAG4AKQA7AFwAbgBcAG4AVQB0AGkAbABpAHQAeQBfAEQAaQBzAHAAbABhAHkAQQByAGcAdQBtAGUAbgB0AHMAXwAzAF8ANABcAG4APQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAEEAcgBnAHUAbQBlAG4AdABzAEEAcgByAGEAeQAsAFwAbgAgACAAIAAgAEMASABPAE8AUwBFAEMATwBMAFMAKABBAHIAZwB1AG0AZQBuAHQAcwBBAHIAcgBhAHkALAAgADMALAAgADQAKQBcAG4AKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBHAGUAdABNAEMARgBUAGUAbQBwAGUAcgBhAHQAdQByAGUAWgBvAG4AZQBcAG4APQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAFQAZQBtAHAAZQByAGEAdAB1AHIAZQAsACAATQBNAFMALAAgAFQAZQBtAHAAZQByAGEAdAB1AHIAZQBBAHIAcgBhAHkALAAgAE0ATQBTAEEAcgByAGEAeQAsACAAUgBlAHQAdQByAG4AQQByAHIAYQB5ACwAXABuACAAIAAgACAAWABMAE8ATwBLAFUAUAAoAFwAbgAgACAAIAAgACAAIAAgACAATQBFAEQASQBBAE4AKABcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAVABlAG0AcABlAHIAYQB0AHUAcgBlACwAIABcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAATQBJAE4AKABUAGUAbQBwAGUAcgBhAHQAdQByAGUAQQByAHIAYQB5ACkALAAgAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIABNAEEAWAAoAFQAZQBtAHAAZQByAGEAdAB1AHIAZQBBAHIAcgBhAHkAKQBcAG4AIAAgACAAIAAgACAAIAAgACkALABcAG4AIAAgACAAIAAgACAAIAAgAFQAZQBtAHAAZQByAGEAdAB1AHIAZQBBAHIAcgBhAHkALABcAG4AIAAgACAAIAAgACAAIAAgAFgATABPAE8ASwBVAFAAKABNAE0AUwAsACAATQBNAFMAQQByAHIAYQB5ACwAIABSAGUAdAB1AHIAbgBBAHIAcgBhAHkAKQBcAG4AIAAgACAAIAApAFwAbgApADsAXABuAFwAbgBcAG4AVQB0AGkAbABpAHQAeQBfAFIAZQBzAHUAbAB0AHMASQB0AGUAbQBGAHIAbwBtAEUAcQB1AGEAdABpAG8AbgBUAGkAdABsAGUAQQBuAGQAUwBvAHUAcgBjAGUAXABuAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABUAGkAdABsAGUAQwBlAGwAbAAsACAAUwBvAHUAcgBjAGUAQwBlAGwAbAAsAFwAbgAgACAAIAAgAFMAVQBCAFMAVABJAFQAVQBUAEUAKABMAEUARgBUACgAUwBvAHUAcgBjAGUAQwBlAGwAbAAsACAARgBJAE4ARAAoAFwAIgAsAFwAIgAsACAAUwBvAHUAcgBjAGUAQwBlAGwAbAApACAALQAxACkALAAgAFwAIgBWAEUARQBSAEcAIAAyADAAMgA2ADoAIABcACIALAAgAFwAIgBcACIAKQAgACYAIABcACIAIABcACIAIAAmACAAVABpAHQAbABlAEMAZQBsAGwAXABuACkAOwAiAH0ALAB7ACIAcABhAHQAaAAiADoAIgAvAHAAcgBvAGoAZQBjAHQAcwAvAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAiACwAIgB0AGUAeAB0ACIAOgAiAC8AKgBcAG4APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQBcAG4APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQBcAG4AUwBvAHUAcgBjAGUAIABkAGEAdABhACAAdABoAGEAdAAgAGkAcwAgAGMAbwBtAG0AbwBuACAAYQBjAHIAbwBzAHMAIABhAGwAbAAgAGUAbgB0AGUAcgBwAHIAaQBzAGUAIAB0AHkAcABlAHMAXABuAEUAeABjAGUAbAAgAG0AbwBkAHUAbABlACAAbgBhAG0AZQA6ACAAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAFwAbgA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AFwAbgA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AFwAbgAqAC8AXABuAFwAbgAvACoAXABuAD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQBcAG4APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AFwAbgBTAG8AdQByAGMAZQA6ACAATgBhAHQAaQBvAG4AYQBsACAASQBuAHYAZQBuAHQAbwByAHkAIABSAGUAcABvAHIAdAAgADIAMAAyADMAIABWAG8AbAB1AG0AZQAgADEAXABuAE4ASQBSAF8AMgAwADIAMwBfAFYAbwBsADEAXABuAD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQBcAG4APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AFwAbgAqAC8AXABuAFwAbgAvACoAIABcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGUAbgBzAGkAdAB5AE8AZgBNAGUAdABoAGEAbgBlAFwAbgBwACAAPQAgAGQAZQBuAHMAaQB0AHkAIABvAGYAIABtAGUAdABoAGEAbgBlACAAKAAwAC4ANgA3ADgANAAgAGsAZwAvAG0AMwApAFwAbgBUAGEAawBlAG4AIABmAHIAbwBtACAAdABoAGUAIABOAGEAdABpAG8AbgBhAGwAIABHAHIAZQBlAG4AaABvAHUAcwBlACAAYQBuAGQAIABFAG4AZQByAGcAeQAgAFIAZQBwAG8AcgB0AGkAbgBnACAAXABuACgATQBlAGEAcwB1AHIAZQBtAGUAbgB0ACkAIABEAGUAdABlAHIAbQBpAG4AYQB0AGkAbwBuACAAMgAwADAAOABcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgAqAC8AXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGUAbgBzAGkAdAB5AE8AZgBNAGUAdABoAGEAbgBlAF8AVABpAHQAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBwACAAPQAgAGQAZQBuAHMAaQB0AHkAIABvAGYAIABtAGUAdABoAGEAbgBlAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGUAbgBzAGkAdAB5AE8AZgBNAGUAdABoAGEAbgBlAF8AVQBuAGkAdABcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAawBnAC8AbQAzAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGUAbgBzAGkAdAB5AE8AZgBNAGUAdABoAGEAbgBlAF8AUwBvAHUAcgBjAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAE4AYQB0AGkAbwBuAGEAbAAgAEkAbgB2AGUAbgB0AG8AcgB5ACAAUgBlAHAAbwByAHQAIAAyADAAMgAzACAAVgBvAGwAdQBtAGUAIAAxADoAIABFAHEAdQBhAHQAaQBvAG4AcwAgADMALgBCAC4AMQBhAF8AMgAsACAAMwAuAEIALgAxAGMAXwAyACwAIAAzAC4AQgAuADMAXwAxACwAIAAzAC4AQgAuADQAZwBfADIAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEQAZQBuAHMAaQB0AHkATwBmAE0AZQB0AGgAYQBuAGUAXwBEAGEAdABhAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoADAALgA2ADcAOAA0ACkAOwBcAG4AXABuAC8AKgAgAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEMAbwBuAHYAZQByAHQATgAyAG8ARQBsAGUAbQBlAG4AdABhAGwAVABvAE0AbwBsAGUAYwB1AGwAYQByAEMAZwBcAG4AQwBnACAAPQAgADQANAAvADIAOAAgAGYAYQBjAHQAbwByACAAdABvACAAYwBvAG4AdgBlAHIAdAAgAGUAbABlAG0AZQBuAHQAYQBsACAAbQBhAHMAcwAgAG8AZgAgAE4AMgBPACAAdABvACAAbQBvAGwAZQBjAHUAbABhAHIAIABtAGEAcwBzAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuACoALwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEMAbwBuAHYAZQByAHQATgAyAG8ARQBsAGUAbQBlAG4AdABhAGwAVABvAE0AbwBsAGUAYwB1AGwAYQByAEMAZwBfAFQAaQB0AGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIARgBhAGMAdABvAHIAIAB0AG8AIABjAG8AbgB2AGUAcgB0ACAAZQBsAGUAbQBlAG4AdABhAGwAIABtAGEAcwBzACAAbwBmACAATgAyAE8AIAB0AG8AIABtAG8AbABlAGMAdQBsAGEAcgAgAG0AYQBzAHMAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEMAbwBuAHYAZQByAHQATgAyAG8ARQBsAGUAbQBlAG4AdABhAGwAVABvAE0AbwBsAGUAYwB1AGwAYQByAEMAZwBfAFYAYQByAGkAYQBiAGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAQwBnAE4AMgBPAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBDAG8AbgB2AGUAcgB0AE4AMgBvAEUAbABlAG0AZQBuAHQAYQBsAFQAbwBNAG8AbABlAGMAdQBsAGEAcgBDAGcAXwBVAG4AaQB0AFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBmAGEAYwB0AG8AcgBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQwBvAG4AdgBlAHIAdABOADIAbwBFAGwAZQBtAGUAbgB0AGEAbABUAG8ATQBvAGwAZQBjAHUAbABhAHIAQwBnAF8AUwBvAHUAcgBjAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAE4AYQB0AGkAbwBuAGEAbAAgAEkAbgB2AGUAbgB0AG8AcgB5ACAAUgBlAHAAbwByAHQAIAAyADAAMgAzACAAVgBvAGwAdQBtAGUAIAAxAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBDAG8AbgB2AGUAcgB0AE4AMgBvAEUAbABlAG0AZQBuAHQAYQBsAFQAbwBNAG8AbABlAGMAdQBsAGEAcgBDAGcAXwBEAGEAdABhAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoADQANAAvADIAOAApADsAXABuAFwAbgAvACoAIABcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBDAG8AbgB2AGUAcgB0AEcAYQBzAEUAbABlAG0AZQBuAHQAYQBsAFQAbwBNAG8AbABlAGMAdQBsAGEAcgBcAG4ARgBhAGMAdABvAHIAIAB0AG8AIABjAG8AbgB2AGUAcgB0ACAAZQBsAGUAbQBlAG4AdABhAGwAIABtAGEAcwBzACAAbwBmACAAZwBhAHMAIAB0AG8AIABtAG8AbABlAGMAdQBsAGEAcgAgAG0AYQBzAHMAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AKgAvAFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQwBvAG4AdgBlAHIAdABHAGEAcwBFAGwAZQBtAGUAbgB0AGEAbABUAG8ATQBvAGwAZQBjAHUAbABhAHIAXwBUAGkAdABsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAEYAYQBjAHQAbwByACAAdABvACAAYwBvAG4AdgBlAHIAdAAgAGUAbABlAG0AZQBuAHQAYQBsACAAbQBhAHMAcwAgAG8AZgAgAGcAYQBzACAAdABvACAAbQBvAGwAZQBjAHUAbABhAHIAIABtAGEAcwBzAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBDAG8AbgB2AGUAcgB0AEcAYQBzAEUAbABlAG0AZQBuAHQAYQBsAFQAbwBNAG8AbABlAGMAdQBsAGEAcgBfAFYAYQByAGkAYQBiAGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAQwBnAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBDAG8AbgB2AGUAcgB0AEcAYQBzAEUAbABlAG0AZQBuAHQAYQBsAFQAbwBNAG8AbABlAGMAdQBsAGEAcgBfAFUAbgBpAHQAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAGYAYQBjAHQAbwByAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBDAG8AbgB2AGUAcgB0AEcAYQBzAEUAbABlAG0AZQBuAHQAYQBsAFQAbwBNAG8AbABlAGMAdQBsAGEAcgBfAFMAbwB1AHIAYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBYAFgAWABYAFgAWABYAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBDAG8AbgB2AGUAcgB0AEcAYQBzAEUAbABlAG0AZQBuAHQAYQBsAFQAbwBNAG8AbABlAGMAdQBsAGEAcgBfAEQAYQB0AGEAXABuACAAIAA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAATQBBAEsARQBBAFIAUgBBAFkAKAA4ACwAIAA0ACwAIABcAG4AIAAgACAAIAAgACAATABBAE0AQgBEAEEAKAByACwAYwAsACAAXABuACAAIAAgACAAIAAgACAAIABJAE4ARABFAFgAKAB7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBHAGEAcwBcACIALAAgAFwAIgBDAG8AbgB2AGUAcgBzAGkAbwBuACAAZgBhAGMAdABvAHIAXAAiACwAIABcACIAQwBvAG4AdgBlAHIAcwBpAG8AbgAgAGYAYQBjAHQAbwByACAAMQBcACIALAAgAFwAIgBDAG8AbgB2AGUAcgBzAGkAbwBuACAAZgBhAGMAdABvAHIAIAAyAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBDAE8AMgBcACIALAAgAFwAIgA0ADQALwAxADIAXAAiACwAIAA0ADQALAAgADEAMgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBDAEgANABcACIALAAgAFwAIgAxADYALwAxADIAXAAiACwAIAAxADYALAAgADEAMgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBOADIATwBcACIALAAgAFwAIgA0ADQALwAyADgAXAAiACwAIAA0ADQALAAgADIAOAA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBOAG8AeABcACIALAAgAFwAIgA0ADYALwAxADQAXAAiACwAIAA0ADYALAAgADEANAA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBDAE8AXAAiACwAIABcACIAMgA4AC8AMQAyAFwAIgAsACAAMgA4ACwAIAAxADIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAQwBPADIAIABMAGkAbQBlAFwAIgAsACAAXAAiADQANAAvADEAMgBcACIALAAgADQANAAsACAAMQAyADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAE4ATQBWAE8AQwBcACIALAAgAFwAIgAxADQALwAxADIAXAAiACwAIAAxADQALAAgADEAMgBcAG4AIAAgACAAIAAgACAAIAAgAH0ALAAgAHIALAAgAGMAKQBcAG4AIAAgACAAIAAgACAAKQBcAG4AIAAgACAAIAApAFwAbgAgACAAKQA7AFwAbgBcAG4ALwAqACAAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARwBXAFAATgAyAE8AXABuAEcAbABvAGIAYQBsACAAdwBhAHIAbQBpAG4AZwAgAHAAbwB0AGUAbgB0AGkAYQBsACAAZgBvAHIAIABnAHIAZQBlAG4AaABvAHUAcwBlACAAZwBhAHMAZQBzAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuACoALwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEcAVwBQAF8AVABpAHQAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBHAGwAbwBiAGEAbAAgAHcAYQByAG0AaQBuAGcAIABwAG8AdABlAG4AdABpAGEAbAAgAGYAbwByACAAZwByAGUAZQBuAGgAbwB1AHMAZQAgAGcAYQBzAGUAcwBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARwBXAFAAXwBWAGEAcgBpAGEAYgBsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAEcAVwBQAE4AMgBPAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBHAFcAUABfAFUAbgBpAHQAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAGYAYQBjAHQAbwByAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBHAFcAUABfAFMAbwB1AHIAYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBYAFgAWABYAFgAWABYAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBHAFcAUABfAEQAYQB0AGEAXABuACAAIAA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAATQBBAEsARQBBAFIAUgBBAFkAKAA4ACwAIAAyACwAIABcAG4AIAAgACAAIAAgACAATABBAE0AQgBEAEEAKAByACwAYwAsACAAXABuACAAIAAgACAAIAAgACAAIABJAE4ARABFAFgAKAB7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBHAGEAcwBcACIALAAgAFwAIgBDAE8AMgAtAGUAIABmAGEAYwB0AG8AcgBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAQwBPADIAXAAiACwAIAAxADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEMASAA0AFwAIgAsACAAMgA4ADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAE4AMgBPAFwAIgAsACAAMgA2ADUAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAQwBGADQAXAAiACwAIAA2ADYAMwAwADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEMAMgBGADYAXAAiACwAIAAxADIAMgAwADAAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAUwBGADYAXAAiACwAIAAyADIAOAAwADAAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIATgBGADMAXAAiACwAIAAxADcAMgAwADAAXABuACAAIAAgACAAIAAgACAAIAB9ACwAIAByACwAIABjACkAXABuACAAIAAgACAAIAAgACkAXABuACAAIAAgACAAKQBcAG4AIAAgACkAOwBcAG4AXABuAFwAbgAvACoAIABcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBBAHUAcwB0AHIAYQBsAGkAYQBuAFMAdABhAHQAZQBzAFQAZQByAHIAaQB0AG8AcgBpAGUAcwBcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgAqAC8AXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBBAHUAcwB0AHIAYQBsAGkAYQBuAFMAdABhAHQAZQBzAFQAZQByAHIAaQB0AG8AcgBpAGUAcwBfAFQAaQB0AGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAQQB1AHMAdAByAGEAbABpAGEAbgAgAHMAdABhAHQAZQBzACAAYQBuAGQAIAB0AGUAcgByAGkAdABvAHIAaQBlAHMAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEEAdQBzAHQAcgBhAGwAaQBhAG4AUwB0AGEAdABlAHMAVABlAHIAcgBpAHQAbwByAGkAZQBzAF8AVgBhAHIAaQBhAGIAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQQB1AHMAdAByAGEAbABpAGEAbgBTAHQAYQB0AGUAcwBUAGUAcgByAGkAdABvAHIAaQBlAHMAXwBVAG4AaQB0AFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQQB1AHMAdAByAGEAbABpAGEAbgBTAHQAYQB0AGUAcwBUAGUAcgByAGkAdABvAHIAaQBlAHMAXwBTAG8AdQByAGMAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEEAdQBzAHQAcgBhAGwAaQBhAG4AUwB0AGEAdABlAHMAVABlAHIAcgBpAHQAbwByAGkAZQBzAF8ARABhAHQAYQBcAG4AIAAgACAAPQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAE0AQQBLAEUAQQBSAFIAQQBZACgAOQAsACAAMwAsACAAXABuACAAIAAgACAAIAAgAEwAQQBNAEIARABBACgAcgAsAGMALAAgAFwAbgAgACAAIAAgACAAIAAgACAASQBOAEQARQBYACgAewBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAUwB0AGEAdABlAC8AVABlAHIAcgBpAHQAbwByAHkAXAAiACwAIABcACIAQwBvAG0AbQBvAG4AIABOAGEAbQBlAFwAIgAsACAAXAAiAEEAYgBiAHIAZQB2AGkAYQB0AGkAbwBuAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBOAGUAdwAgAFMAbwB1AHQAaAAgAFcAYQBsAGUAcwBcACIALAAgAFwAIgBOAGUAdwAgAFMAbwB1AHQAaAAgAFcAYQBsAGUAcwBcACIALAAgAFwAIgBOAFMAVwBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAQQB1AHMAdAByAGEAbABpAGEAbgAgAEMAYQBwAGkAdABhAGwAIABUAGUAcgByAGkAdABvAHIAeQBcACIALAAgAFwAIgBBAEMAVABcACIALAAgAFwAIgBBAEMAVABcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVgBpAGMAdABvAHIAaQBhAFwAIgAsACAAXAAiAFYAaQBjAHQAbwByAGkAYQBcACIALAAgAFwAIgBWAEkAQwBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAUQB1AGUAZQBuAHMAbABhAG4AZABcACIALAAgAFwAIgBRAHUAZQBlAG4AcwBsAGEAbgBkAFwAIgAsACAAXAAiAFEATABEAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBTAG8AdQB0AGgAIABBAHUAcwB0AHIAYQBsAGkAYQBcACIALAAgAFwAIgBTAG8AdQB0AGgAIABBAHUAcwB0AHIAYQBsAGkAYQBcACIALAAgAFwAIgBTAEEAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFcAZQBzAHQAZQByAG4AIABBAHUAcwB0AHIAYQBsAGkAYQBcACIALAAgAFwAIgBXAGUAcwB0AGUAcgBuACAAQQB1AHMAdAByAGEAbABpAGEAXAAiACwAIABcACIAVwBBAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBUAGEAcwBtAGEAbgBpAGEAXAAiACwAIABcACIAVABhAHMAbQBhAG4AaQBhAFwAIgAsACAAXAAiAFQAQQBTAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBOAG8AcgB0AGgAZQByAG4AIABUAGUAcgByAGkAdABvAHIAeQBcACIALAAgAFwAIgBOAG8AcgB0AGgAZQByAG4AIABUAGUAcgByAGkAdABvAHIAeQBcACIALAAgAFwAIgBOAFQAXAAiAFwAbgAgACAAIAAgACAAIAAgACAAfQAsACAAcgAsACAAYwApAFwAbgAgACAAIAAgACAAIAApAFwAbgAgACAAIAAgACkAXABuACAAIAApADsAXABuAFwAbgAvACoAIABcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBXAEEAUwBBADQAQQByAGUAYQBzAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuACoALwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFcAQQBTAEEANABBAHIAZQBhAHMAXwBUAGkAdABsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAEEAQgBTACAAUwB0AGEAdABpAHMAdABjAGEAbAAgAEEAcgBlAGEAcwAgAEwAZQB2AGUAbAAgADQAIAAtACAAVwBlAHMAdABlAHIAbgAgAEEAdQBzAHQAcgBhAGwAaQBhAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBXAEEAUwBBADQAQQByAGUAYQBzAF8AVgBhAHIAaQBhAGIAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AVwBBAFMAQQA0AEEAcgBlAGEAcwBfAFUAbgBpAHQAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBXAEEAUwBBADQAQQByAGUAYQBzAF8AUwBvAHUAcgBjAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAEEAdQBzAHQAcgBhAGwAaQBhAG4AIABCAHUAcgBlAGEAdQAgAG8AZgAgAFMAdABhAHQAaQBzAHQAaQBjAHMAIAAoAEEAQgBTACkAIAAtACAAUwB0AGEAdABpAHMAdABpAGMAYQBsACAAQQByAGUAYQBzACAATABlAHYAZQBsACAAMgAgAC0AIAAyADAAMgAxACAALQAgAFMAaABhAHAAZQBmAGkAbABlAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBXAEEAUwBBADQAQQByAGUAYQBzAF8ARABhAHQAYQBcAG4AIAAgACAAPQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAE0AQQBLAEUAQQBSAFIAQQBZACgAMQAxACwAIAAxACwAIABcAG4AIAAgACAAIAAgACAATABBAE0AQgBEAEEAKAByACwAYwAsACAAXABuACAAIAAgACAAIAAgACAAIABJAE4ARABFAFgAKAB7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBTAEEAIAA0ACAATgBhAG0AZQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAQgB1AG4AYgB1AHIAeQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIATQBhAG4AZAB1AHIAYQBoAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBQAGUAcgB0AGgAIAAtACAASQBuAG4AZQByAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBQAGUAcgB0AGgAIAAtACAATgBvAHIAdABoACAARQBhAHMAdABcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAUABlAHIAdABoACAALQAgAE4AbwByAHQAaAAgAFcAZQBzAHQAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFAAZQByAHQAaAAgAC0AIABTAG8AdQB0AGgAIABFAGEAcwB0AFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBQAGUAcgB0AGgAIAAtACAAUwBvAHUAdABoACAAVwBlAHMAdABcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVwBlAHMAdABlAHIAbgAgAEEAdQBzAHQAcgBhAGwAaQBhACAALQAgAFcAaABlAGEAdAAgAEIAZQBsAHQAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFcAZQBzAHQAZQByAG4AIABBAHUAcwB0AHIAYQBsAGkAYQAgAC0AIABPAHUAdABiAGEAYwBrACAAKABOAG8AcgB0AGgAKQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVwBlAHMAdABlAHIAbgAgAEEAdQBzAHQAcgBhAGwAaQBhACAALQAgAE8AdQB0AGIAYQBjAGsAIAAoAFMAbwB1AHQAaAApAFwAIgBcAG4AIAAgACAAIAAgACAAIAAgAH0ALAAgAHIALAAgAGMAKQBcAG4AIAAgACAAIAAgACAAKQBcAG4AIAAgACAAIAApAFwAbgAgACAAKQA7AFwAbgBcAG4ALwAqACAAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AVwBlAHQAQQBuAGQARAByAHkAWgBvAG4AZQBzAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuACoALwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFcAZQB0AEEAbgBkAEQAcgB5AFoAbwBuAGUAcwBfAFQAaQB0AGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAVgBFAEUAUgBHACAAQQB1AHMAdAByAGEAbABpAGEAbgAgAHcAZQB0ACAAYQBuAGQAIABkAHIAeQAgAHoAbwBuAGUAcwBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AVwBlAHQAQQBuAGQARAByAHkAWgBvAG4AZQBzAF8AVgBhAHIAaQBhAGIAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AVwBlAHQAQQBuAGQARAByAHkAWgBvAG4AZQBzAF8AVQBuAGkAdABcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFcAZQB0AEEAbgBkAEQAcgB5AFoAbwBuAGUAcwBfAFMAbwB1AHIAYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBWAEUARQBSAEcAIAAyADAAMgA2ADoAIABUAGEAYgBsAGUAIAAxAC4AMgA6ACAAVAByAGEAbgBzAGwAYQB0AGkAbgBnACAAYwBsAGkAbQBhAHQAZQAgAHoAbwBuAGUAcwAgAHQAbwAgAHcAZQB0ACAAYQBuAGQAIABkAHIAeQAgAHoAbwBuAGUAcwBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AVwBlAHQAQQBuAGQARAByAHkAWgBvAG4AZQBzAF8AVgBhAHIAaQBhAHQAaQBvAG4AXABuACAAIAAgAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABNAEEASwBFAEEAUgBSAEEAWQAoADMALAAgADEALAAgAFwAbgAgACAAIAAgACAAIABMAEEATQBCAEQAQQAoAHIALABjACwAIABcAG4AIAAgACAAIAAgACAAIAAgAEkATgBEAEUAWAAoAHsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFYAQQBSAEkAQQBUAEkATwBOACAATwBGACAAUwBPAFUAUgBDAEUAIABEAEEAVABBADoAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEEAZABkAGUAZAAgAHcAYQByAG0AIAAvACAAYwBvAG8AbAAgAHQAZQBtAHAAZQByAGEAdABlACAAbQBvAGkAcwB0ACAALwAgAGQAcgB5ACAALQAgAGwAbwB3ACAAZgByAG8AcwB0ACAAYQBuAGQAIABoAGkAZwBoACAAdABlAG0AcAAgAGMAbABhAHMAcwBlAHMAIAB0AG8AIABhAGMAYwBvAG0AbQBvAGQAYQB0AGUAIABjAGwAaQBtAGEAdABlACAAcwBjAGUAbgBhAHIAaQBvAHMAIABlAHgAYwBsAHUAZABlAGQAIABiAHkAIABWAEUARQBSAEcAIABjAHIAaQB0AGUAcgBpAGEALgBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIARgBpAHgAZQBkACAAdAB5AHAAbwAgAC0AIABDAGgAYQBuAGcAZQBkACAAJwBGAHIAeQAnACAAdABvACAAJwBEAHIAeQAnAC4AXAAiAFwAbgAgACAAIAAgACAAIAAgACAAfQAsACAAcgAsACAAYwApAFwAbgAgACAAIAAgACAAIAApAFwAbgAgACAAIAAgACkAXABuACAAIAApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBXAGUAdABBAG4AZABEAHIAeQBaAG8AbgBlAHMAXwBEAGEAdABhAFwAbgAgACAAIAA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAATQBBAEsARQBBAFIAUgBBAFkAKAAxADUALAAgADIALAAgAFwAbgAgACAAIAAgACAAIABMAEEATQBCAEQAQQAoAHIALABjACwAIABcAG4AIAAgACAAIAAgACAAIAAgAEkATgBEAEUAWAAoAHsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEMAbABpAG0AYQB0AGUAIABaAG8AbgBlAFwAIgAsACAAXAAiAFcAZQB0ACAAbwByACAARAByAHkAIABaAG8AbgBlAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBUAHIAbwBwAGkAYwBhAGwAIABtAG8AbgB0AGEAbgBlAFwAIgAsACAAXAAiAFcAZQB0ACAAYwBsAGkAbQBhAHQAZQAgAHoAbwBuAGUAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFQAcgBvAHAAaQBjAGEAbAAgAHcAZQB0AFwAIgAsACAAXAAiAFcAZQB0ACAAYwBsAGkAbQBhAHQAZQAgAHoAbwBuAGUAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFQAcgBvAHAAaQBjAGEAbAAgAG0AbwBpAHMAdABcACIALAAgAFwAIgBXAGUAdAAgAGMAbABpAG0AYQB0AGUAIAB6AG8AbgBlAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBUAHIAbwBwAGkAYwBhAGwAIABkAHIAeQBcACIALAAgAFwAIgBEAHIAeQAgAGMAbABpAG0AYQB0AGUAIAB6AG8AbgBlAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBXAGEAcgBtACAAdABlAG0AcABlAHIAYQB0AGUAIABtAG8AaQBzAHQAXAAiACwAIABcACIAVwBlAHQAIABjAGwAaQBtAGEAdABlACAAegBvAG4AZQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVwBhAHIAbQAgAHQAZQBtAHAAZQByAGEAdABlACAAZAByAHkAXAAiACwAIABcACIARAByAHkAIABjAGwAaQBtAGEAdABlACAAegBvAG4AZQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAQwBvAG8AbAAgAHQAZQBtAHAAZQByAGEAdABlACAAbQBvAGkAcwB0AFwAIgAsACAAXAAiAFcAZQB0ACAAYwBsAGkAbQBhAHQAZQAgAHoAbwBuAGUAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEMAbwBvAGwAIAB0AGUAbQBwAGUAcgBhAHQAZQAgAGQAcgB5AFwAIgAsACAAXAAiAEQAcgB5ACAAYwBsAGkAbQBhAHQAZQAgAHoAbwBuAGUAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFcAYQByAG0AIAB0AGUAbQBwAGUAcgBhAHQAZQAgAG0AbwBpAHMAdAAgAC0AIABsAG8AdwAgAGYAcgBvAHMAdABcACIALAAgAFwAIgBXAGUAdAAgAGMAbABpAG0AYQB0AGUAIAB6AG8AbgBlAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBXAGEAcgBtACAAdABlAG0AcABlAHIAYQB0AGUAIABkAHIAeQAgAC0AIABsAG8AdwAgAGYAcgBvAHMAdABcACIALAAgAFwAIgBEAHIAeQAgAGMAbABpAG0AYQB0AGUAIAB6AG8AbgBlAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBXAGEAcgBtACAAdABlAG0AcABlAHIAYQB0AGUAIABtAG8AaQBzAHQAIAAtACAAaABpAGcAaAAgAHQAZQBtAHAAXAAiACwAIABcACIAVwBlAHQAIABjAGwAaQBtAGEAdABlACAAegBvAG4AZQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVwBhAHIAbQAgAHQAZQBtAHAAZQByAGEAdABlACAAZAByAHkAIAAtACAAaABpAGcAaAAgAHQAZQBtAHAAXAAiACwAIABcACIARAByAHkAIABjAGwAaQBtAGEAdABlACAAegBvAG4AZQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAQwBvAG8AbAAgAHQAZQBtAHAAZQByAGEAdABlACAAbQBvAGkAcwB0ACAALQAgAGwAbwB3ACAAZgByAG8AcwB0AFwAIgAsACAAXAAiAFcAZQB0ACAAYwBsAGkAbQBhAHQAZQAgAHoAbwBuAGUAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEMAbwBvAGwAIAB0AGUAbQBwAGUAcgBhAHQAZQAgAGQAcgB5ACAALQAgAGwAbwB3ACAAZgByAG8AcwB0AFwAIgAsACAAXAAiAEQAcgB5ACAAYwBsAGkAbQBhAHQAZQAgAHoAbwBuAGUAXAAiAFwAbgAgACAAIAAgACAAIAAgACAAfQAsACAAcgAsACAAYwApAFwAbgAgACAAIAAgACAAIAApAFwAbgAgACAAIAAgACkAXABuACAAIAApADsAXABuAFwAbgAvACoAIABcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBDAGwAaQBtAGEAdABlAFoAbwBuAGUAcwBcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgAqAC8AXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBDAGwAaQBtAGEAdABlAFoAbwBuAGUAcwBfAFQAaQB0AGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAVgBFAEUAUgBHACAAQQB1AHMAdAByAGEAbABpAGEAbgAgAGMAbABpAG0AYQB0AGUAIAB6AG8AbgBlAHMAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEMAbABpAG0AYQB0AGUAWgBvAG4AZQBzAF8AVgBhAHIAaQBhAGIAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQwBsAGkAbQBhAHQAZQBaAG8AbgBlAHMAXwBVAG4AaQB0AFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQwBsAGkAbQBhAHQAZQBaAG8AbgBlAHMAXwBTAG8AdQByAGMAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAVgBFAEUAUgBHACAAMgAwADIANgA6ACAAVABhAGIAbABlACAAMQAuADMAOgAgAEMAbABpAG0AYQB0AGUAIABhAG4AZAAgAFIAYQBpAG4AZgBhAGwAbAAgAHoAbwBuAGUAIABjAGwAYQBzAHMAaQBmAGkAYwBhAHQAaQBvAG4AcwAgAGEAbgBkACAAZABlAGYAaQBuAGkAdABpAG8AbgBzAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBDAGwAaQBtAGEAdABlAFoAbwBuAGUAcwBfAFYAYQByAGkAYQB0AGkAbwBuAFwAbgAgACAAIAA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAATQBBAEsARQBBAFIAUgBBAFkAKAA1ACwAIAAxACwAIABcAG4AIAAgACAAIAAgACAATABBAE0AQgBEAEEAKAByACwAYwAsACAAXABuACAAIAAgACAAIAAgACAAIABJAE4ARABFAFgAKAB7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBWAEEAUgBJAEEAVABJAE8ATgAgAE8ARgAgAFMATwBVAFIAQwBFACAARABBAFQAQQA6AFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBBAGQAZABlAGQAIAB3AGEAcgBtACAALwAgAGMAbwBvAGwAIAB0AGUAbQBwAGUAcgBhAHQAZQAgAG0AbwBpAHMAdAAgAC8AIABkAHIAeQAgAC0AIABsAG8AdwAgAGYAcgBvAHMAdAAgAGEAbgBkACAAaABpAGcAaAAgAHQAZQBtAHAAIABjAGwAYQBzAHMAZQBzACAAdABvACAAYQBjAGMAbwBtAG0AbwBkAGEAdABlACAAYwBsAGkAbQBhAHQAZQAgAHMAYwBlAG4AYQByAGkAbwBzACAAZQB4AGMAbAB1AGQAZQBkACAAYgB5ACAAVgBFAEUAUgBHACAAYwByAGkAdABlAHIAaQBhAC4AXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEYAaQB4AGUAZAAgAHQAeQBwAG8AIABpAG4AIABNAEEAVAAgAHYAYQBsAHUAZQAgAGYAbwByACAAdwBhAHIAbQAgAHQAZQBtAHAAZQByAGEAdABlACAAZAByAHkAIAAtACAAYwBoAGEAbgBnAGUAZAAgADEAMAAgAHQAbwAgADEAMQAuAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBBAGQAZABlAGQAIABtAGkAbgAgAGEAbgBkACAAbQBhAHgAIABjAG8AbAB1AG0AbgBzACAAZgBvAHIAIABNAEEAVAAsACAATQBBAFAALAAgAGYAcgBvAHMAdAAgAGQAYQB5AHMAIABwAGUAcgAgAHkAZQBhAHIALAAgAGUAbABlAHYAYQB0AGkAbwBuACwAIABNAEEAUAA6AFAARQBUACAAdABvACAAYwBhAGwAYwB1AGwAYQB0AGUAIAB6AG8AbgBlAHMAIABmAHIAbwBtACAAcgBlAGEAbAAgAGMAbABpAG0AYQB0AGUAIABkAGEAdABhAC4AXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEcAQQBGACAAYQBjAGMAZQBwAHQAcwAgAHIAYQBpAG4AZgBhAGwAbAAgAGEAcwAgAGEAIABwAHIAbwB4AHkAIABmAG8AcgAgAHAAcgBlAGMAaQBwAGkAdABhAHQAaQBvAG4ALgBcACIAXABuACAAIAAgACAAIAAgACAAIAB9ACwAIAByACwAIABjACkAXABuACAAIAAgACAAIAAgACkAXABuACAAIAAgACAAKQBcAG4AIAAgACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEMAbABpAG0AYQB0AGUAWgBvAG4AZQBzAF8ARABhAHQAYQBcAG4AIAAgACAAPQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAE0AQQBLAEUAQQBSAFIAQQBZACgAOQAsACAAMQA2ACwAIABcAG4AIAAgACAAIAAgACAATABBAE0AQgBEAEEAKAByACwAYwAsACAAXABuACAAIAAgACAAIAAgACAAIABJAE4ARABFAFgAKAB7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBDAGwAaQBtAGEAdABlACAAWgBvAG4AZQBcACIALAAgAFwAIgBNAEEAVABcACIALAAgAFwAIgBNAEEAUABcACIALAAgAFwAIgBGAHIAbwBzAHQAIABkAGEAeQBzACAAcABlAHIAIAB5AGUAYQByAFwAIgAsACAAXAAiAEUAbABlAHYAYQB0AGkAbwBuAFwAIgAsACAAXAAiAE0AQQBQADoAUABFAFQAXAAiACwAIABcACIATQBpAG4AIAB0AGUAbQBwAFwAIgAsACAAXAAiAE0AYQB4ACAAdABlAG0AcABcACIALAAgAFwAIgBNAGkAbgAgAHIAYQBpAG4AZgBhAGwAbABcACIALAAgAFwAIgBNAGEAeAAgAHIAYQBpAG4AZgBhAGwAbABcACIALAAgAFwAIgBNAGkAbgAgAGYAcgBvAHMAdAAgAGQAYQB5AHMAXAAiACwAIABcACIATQBhAHgAIABmAHIAbwBzAHQAIABkAGEAeQBzAFwAIgAsACAAXAAiAE0AaQBuACAAZQBsAGUAdgBhAHQAaQBvAG4AXAAiACwAIABcACIATQBhAHgAIABlAGwAZQB2AGEAdABpAG8AbgBcACIALAAgAFwAIgBNAGkAbgAgAE0AQQBQADoAUABFAFQAXAAiACwAIABcACIATQBpAG4AIABNAEEAUAA6AFAARQBUAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBUAHIAbwBwAGkAYwBhAGwAIABtAG8AbgB0AGEAbgBlAFwAIgAsACAAXAAiAD4AIAAxADgAIABDAFwAIgAsACAAXAAiAEEAbgB5AFwAIgAsACAAXAAiAGQiIAA3AFwAIgAsACAAXAAiAD4AIAAxADAAMAAwACAAbQBcACIALAAgAFwAIgBBAG4AeQBcACIALAAgADEAOAAuADAAMAAxACwAIAA5ADkAOQA5ADkAOQAsACAALQA5ADkAOQA5ADkAOQAsACAAOQA5ADkAOQA5ADkALAAgAC0AOQA5ADkAOQA5ADkALAAgADcALAAgADEAMAAwADAALAAgADkAOQA5ADkAOQA5ACwAIAAtADkAOQA5ADkAOQA5ACwAIAA5ADkAOQA5ADkAOQA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBUAHIAbwBwAGkAYwBhAGwAIAB3AGUAdABcACIALAAgAFwAIgA+ACAAMQA4ACAAQwBcACIALAAgAFwAIgA+ACAAMgAwADAAMAAgAG0AbQBcACIALAAgAFwAIgBkIiAANwBcACIALAAgAFwAIgBkIiAAMQAwADAAMAAgAG0AXAAiACwAIABcACIAQQBuAHkAXAAiACwAIAAxADgALgAwADAAMQAsACAAOQA5ADkAOQA5ADkALAAgADIAMAAwADAALgAwADAAMQAsACAAOQA5ADkAOQA5ADkALAAgAC0AOQA5ADkAOQA5ADkALAAgADcALAAgAC0AOQA5ADkAOQA5ADkALAAgADkAOQA5AC4AOQA5ADkALAAgACAALQA5ADkAOQA5ADkAOQAsACAAOQA5ADkAOQA5ADkAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVAByAG8AcABpAGMAYQBsACAAbQBvAGkAcwB0AFwAIgAsACAAXAAiAD4AIAAxADgAIABDAFwAIgAsACAAXAAiAD4AIAAxADAAMAAwACAAbQBtACAALQAgAGQiIAAyADAAMAAwACAAbQBtAFwAIgAsACAAXAAiAGQiIAA3AFwAIgAsACAAXAAiAGQiIAAxADAAMAAwACAAbQBcACIALAAgAFwAIgBBAG4AeQBcACIALAAgADEAOAAuADAAMAAxACwAIAA5ADkAOQA5ADkAOQAsACAAMQAwADAAMAAuADAAMAAxACwAIAAyADAAMAAwACwAIAAtADkAOQA5ADkAOQA5ACwAIAA3ACwAIAAtADkAOQA5ADkAOQA5ACwAIAA5ADkAOQAuADkAOQA5ACwAIAAgAC0AOQA5ADkAOQA5ADkALAAgADkAOQA5ADkAOQA5ADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFQAcgBvAHAAaQBjAGEAbAAgAGQAcgB5AFwAIgAsACAAXAAiAD4AIAAxADgAIABDAFwAIgAsACAAXAAiAGQiIAAxADAAMAAwACAAbQBtAFwAIgAsACAAXAAiAGQiIAA3AFwAIgAsACAAXAAiAGQiIAAxADAAMAAwACAAbQBcACIALAAgAFwAIgBBAG4AeQBcACIALAAgADEAOAAuADAAMAAxACwAIAA5ADkAOQA5ADkAOQAsACAALQA5ADkAOQA5ADkAOQAsACAAMQAwADAAMAAsACAALQA5ADkAOQA5ADkAOQAsACAANwAsACAALQA5ADkAOQA5ADkAOQAsACAAOQA5ADkALgA5ADkAOQAsACAAIAAtADkAOQA5ADkAOQA5ACwAIAA5ADkAOQA5ADkAOQA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBXAGEAcgBtACAAdABlAG0AcABlAHIAYQB0AGUAIABtAG8AaQBzAHQAXAAiACwAIABcACIAPgAgADEAMAAgAEMAXAAiACwAIABcACIAQQBuAHkAXAAiACwAIABcACIAQQBuAHkAXAAiACwAIABcACIAQQBuAHkAXAAiACwAIABcACIAPgAgADEAXAAiACwAIAAxADAALgAwADAAMQAsACAAOQA5ADkAOQA5ADkALAAgAC0AOQA5ADkAOQA5ADkALAAgADkAOQA5ADkAOQA5ACwAIAAtADkAOQA5ADkAOQA5ACwAIAA5ADkAOQA5ADkAOQAsACAALQA5ADkAOQA5ADkAOQAsACAAOQA5ADkAOQA5ADkALAAgADEALgAwADAAMQAsACAAOQA5ADkAOQA5ADkAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVwBhAHIAbQAgAHQAZQBtAHAAZQByAGEAdABlACAAZAByAHkAXAAiACwAIABcACIAPgAgADEAMAAgAEMAXAAiACwAIABcACIAQQBuAHkAXAAiACwAIABcACIAQQBuAHkAXAAiACwAIABcACIAQQBuAHkAXAAiACwAIABcACIAZCIgADEAXAAiACwAIAAxADAALgAwADAAMQAsACAAOQA5ADkAOQA5ADkALAAgAC0AOQA5ADkAOQA5ADkALAAgADkAOQA5ADkAOQA5ACwAIAAtADkAOQA5ADkAOQA5ACwAIAA5ADkAOQA5ADkAOQAsACAALQA5ADkAOQA5ADkAOQAsACAAOQA5ADkAOQA5ADkALAAgACAALQA5ADkAOQA5ADkAOQAsACAAMQA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBDAG8AbwBsACAAdABlAG0AcABlAHIAYQB0AGUAIABtAG8AaQBzAHQAXAAiACwAIABcACIAPgAgADAAIABDACAALQAgAGQiIAAxADAAIABDAFwAIgAsACAAXAAiAEEAbgB5AFwAIgAsACAAXAAiAEEAbgB5AFwAIgAsACAAXAAiAEEAbgB5AFwAIgAsACAAXAAiAD4AIAAxAFwAIgAsACAALQA5ADkAOQA5ADkAOQAsACAAMQAwACwAIAAtADkAOQA5ADkAOQA5ACwAIAA5ADkAOQA5ADkAOQAsACAALQA5ADkAOQA5ADkAOQAsACAAOQA5ADkAOQA5ADkALAAgAC0AOQA5ADkAOQA5ADkALAAgADkAOQA5ADkAOQA5ACwAIAAxAC4AMAAwADEALAAgADkAOQA5ADkAOQA5ADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEMAbwBvAGwAIAB0AGUAbQBwAGUAcgBhAHQAZQAgAGQAcgB5AFwAIgAsACAAXAAiAD4AIAAwACAAQwAgAC0AIABkIiAAMQAwACAAQwBcACIALAAgAFwAIgBBAG4AeQBcACIALAAgAFwAIgBBAG4AeQBcACIALAAgAFwAIgBBAG4AeQBcACIALAAgAFwAIgBkIiAAMQBcACIALAAgAC0AOQA5ADkAOQA5ADkALAAgADEAMAAsACAALQA5ADkAOQA5ADkAOQAsACAAOQA5ADkAOQA5ADkALAAgAC0AOQA5ADkAOQA5ADkALAAgADkAOQA5ADkAOQA5ACwAIAAtADkAOQA5ADkAOQA5ACwAIAA5ADkAOQA5ADkAOQAsACAAIAAtADkAOQA5ADkAOQA5ACwAIAAxAFwAbgAgACAAIAAgACAAIAAgACAAfQAsACAAcgAsACAAYwApAFwAbgAgACAAIAAgACAAIAApAFwAbgAgACAAIAAgACkAXABuACAAIAApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBDAGwAaQBtAGEAdABlAFoAbwBuAGUAcwBfAEEAcABwAGUAbgBkAGkAYwBlAHMAXABuACAAIAAgAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABNAEEASwBFAEEAUgBSAEEAWQAoADQALAAgADEALAAgAFwAbgAgACAAIAAgACAAIABMAEEATQBCAEQAQQAoAHIALABjACwAIABcAG4AIAAgACAAIAAgACAAIAAgAEkATgBEAEUAWAAoAHsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAE4AbwB0AGUAOgBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIATQBBAFQAIAA9ACAAbQBlAGEAbgAgAGEAbgBuAHUAYQBsACAAdABlAG0AcABlAHIAYQB0AHUAcgBlAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBNAEEAUAAgAD0AIABtAGUAYQBuACAAYQBuAG4AdQBhAGwAIABwAHIAZQBjAGkAcABpAHQAYQB0AGkAbwBuAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBQAEUAVAAgAD0AIABwAG8AdABlAG4AdABpAGEAbAAgAGUAdgBhAHAAbwB0AHIAYQBuAHMAcABpAHIAYQB0AGkAbwBuAFwAIgBcAG4AIAAgACAAIAAgACAAIAAgAH0ALAAgAHIALAAgAGMAKQBcAG4AIAAgACAAIAAgACAAKQBcAG4AIAAgACAAIAApAFwAbgAgACAAKQA7AFwAbgBcAG4AXABuAC8AKgAgAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFQAZQBtAHAAZQByAGEAdAB1AHIAZQBaAG8AbgBlAHMAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AKgAvAFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AVABlAG0AcABlAHIAYQB0AHUAcgBlAFoAbwBuAGUAcwBfAFQAaQB0AGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAVgBFAEUAUgBHACAAQQB1AHMAdAByAGEAbABpAGEAbgAgAHQAZQBtAHAAZQByAGEAdAB1AHIAZQAgAHoAbwBuAGUAcwBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AVABlAG0AcABlAHIAYQB0AHUAcgBlAFoAbwBuAGUAcwBfAFYAYQByAGkAYQBiAGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFQAZQBtAHAAZQByAGEAdAB1AHIAZQBaAG8AbgBlAHMAXwBVAG4AaQB0AFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AVABlAG0AcABlAHIAYQB0AHUAcgBlAFoAbwBuAGUAcwBfAFMAbwB1AHIAYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBWAEUARQBSAEcAIAAyADAAMgA2ADoAIABUAGEAYgBsAGUAIAAxAC4AMwA6ACAAQwBsAGkAbQBhAHQAZQAgAGEAbgBkACAAUgBhAGkAbgBmAGEAbABsACAAegBvAG4AZQAgAGMAbABhAHMAcwBpAGYAaQBjAGEAdABpAG8AbgBzACAAYQBuAGQAIABkAGUAZgBpAG4AaQB0AGkAbwBuAHMAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFQAZQBtAHAAZQByAGEAdAB1AHIAZQBaAG8AbgBlAHMAXwBWAGEAcgBpAGEAdABpAG8AbgBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAVgBBAFIASQBBAFQASQBPAE4AIABPAEYAIABTAE8AVQBSAEMARQAgAEQAQQBUAEEAOgAgAEEAZABkAGUAZAAgAGUAeAB0AHIAYQAgAE0AQQBUACAAbQBpAG4AIABhAG4AZAAgAE0AQQBUACAAbQBhAHgAIABjAG8AbAB1AG0AbgBzACAAdABvACAAYwBhAGwAYwB1AGwAYQB0AGUAIAB6AG8AbgBlACAAZgByAG8AbQAgAHIAZQBhAGwAIAB0AGUAbQBwAGUAcgBhAHQAdQByAGUAIABkAGEAdABhAC4AXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFQAZQBtAHAAZQByAGEAdAB1AHIAZQBaAG8AbgBlAHMAXwBEAGEAdABhAFwAbgAgACAAIAA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAATQBBAEsARQBBAFIAUgBBAFkAKAA0ACwAIAA0ACwAIABcAG4AIAAgACAAIAAgACAATABBAE0AQgBEAEEAKAByACwAYwAsACAAXABuACAAIAAgACAAIAAgACAAIABJAE4ARABFAFgAKAB7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBUAGUAbQBwAGUAcgBhAHQAdQByAGUAIABaAG8AbgBlAFwAIgAsACAAXAAiAE0AZQBkAGkAYQBuACAAQQBuAG4AdQBhAGwAIABUAGUAbQBwAGUAcgBhAHQAdQByAGUAIAAoAE0AQQBUACkAXAAiACwAIABcACIATQBpAG4AIABNAEEAVABcACIALAAgAFwAIgBNAGEAeAAgAE0AQQBUAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBXAGEAcgBtAFwAIgAsACAAXAAiAGUiIAAyADYAIABDAFwAIgAsACAAMgA2ACwAIAA5ADkAOQA5ADkAOQA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBUAGUAbQBwAGUAcgBhAHQAZQBcACIALAAgAFwAIgAxADUAIAAtACAAMgA1ACAAQwBcACIALAAgADEANQAsACAAMgA1AC4AOQA5ADkAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAQwBvAG8AbABcACIALAAgAFwAIgBkIiAAMQA0ACAAQwBcACIALAAgAC0AOQA5ADkAOQA5ADkALAAgADEANAAuADkAOQA5AFwAbgAgACAAIAAgACAAIAAgACAAfQAsACAAcgAsACAAYwApAFwAbgAgACAAIAAgACAAIAApAFwAbgAgACAAIAAgACkAXABuACAAIAApADsAXABuAFwAbgAvACoAIABcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBSAGEAaQBuAGYAYQBsAGwAWgBvAG4AZQBzAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuACoALwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFIAYQBpAG4AZgBhAGwAbABaAG8AbgBlAHMAXwBUAGkAdABsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFYARQBFAFIARwAgAEEAdQBzAHQAcgBhAGwAaQBhAG4AIAByAGEAaQBuAGYAYQBsAGwAIAB6AG8AbgBlAHMAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFIAYQBpAG4AZgBhAGwAbABaAG8AbgBlAHMAXwBWAGEAcgBpAGEAYgBsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBSAGEAaQBuAGYAYQBsAGwAWgBvAG4AZQBzAF8AVQBuAGkAdABcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFIAYQBpAG4AZgBhAGwAbABaAG8AbgBlAHMAXwBTAG8AdQByAGMAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAVgBFAEUAUgBHACAAMgAwADIANgA6ACAAVABhAGIAbABlACAAMQAuADMAOgAgAEMAbABpAG0AYQB0AGUAIABhAG4AZAAgAFIAYQBpAG4AZgBhAGwAbAAgAHoAbwBuAGUAIABjAGwAYQBzAHMAaQBmAGkAYwBhAHQAaQBvAG4AcwAgAGEAbgBkACAAZABlAGYAaQBuAGkAdABpAG8AbgBzAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBSAGEAaQBuAGYAYQBsAGwAWgBvAG4AZQBzAF8AVgBhAHIAaQBhAHQAaQBvAG4AXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFYAQQBSAEkAQQBUAEkATwBOACAATwBGACAAUwBPAFUAUgBDAEUAIABEAEEAVABBADoAIABBAGQAZABlAGQAIABlAHgAdAByAGEAIABSAGEAaQBuAGYAYQBsAGwAIABtAGkAbgAgAGEAbgBkACAAUgBhAGkAbgBmAGEAbABsACAAbQBhAHgAIABjAG8AbAB1AG0AbgBzACAAdABvACAAYwBhAGwAYwB1AGwAYQB0AGUAIAB6AG8AbgBlACAAZgByAG8AbQAgAHIAZQBhAGwAIAByAGEAaQBuAGYAYQBsAGwAIABkAGEAdABhAC4AXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFIAYQBpAG4AZgBhAGwAbABaAG8AbgBlAHMAXwBEAGEAdABhAFwAbgAgACAAIAA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAATQBBAEsARQBBAFIAUgBBAFkAKAAzACwAIAA0ACwAIABcAG4AIAAgACAAIAAgACAATABBAE0AQgBEAEEAKAByACwAYwAsACAAXABuACAAIAAgACAAIAAgACAAIABJAE4ARABFAFgAKAB7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBSAGEAaQBuAGYAYQBsAGwAIABaAG8AbgBlAFwAIgAsACAAXAAiAEEAbgBuAHUAYQBsACAAcgBhAGkAbgBmAGEAbABsAFwAIgAsACAAXAAiAFIAYQBpAG4AZgBhAGwAbAAgAG0AaQBuAFwAIgAsACAAXAAiAFIAYQBpAG4AZgBhAGwAbAAgAG0AYQB4AFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBIAGkAZwBoACAAcgBhAGkAbgBmAGEAbABsAFwAIgAsACAAXAAiAEEAbgBuAHUAYQBsACAAcgBhAGkAbgBmAGEAbABsACAAPgAgADYAMAAwAG0AbQBcACIALAAgADYAMAAwAC4AMAAwADEALAAgADkAOQA5ADkAOQA5ADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEwAbwB3ACAAcgBhAGkAbgBmAGEAbABsAFwAIgAsACAAXAAiAEEAbgBuAHUAYQBsACAAcgBhAGkAbgBmAGEAbABsACAAZCIgADYAMAAwAG0AbQBcACIALAAgAC0AOQA5ADkAOQA5ADkALAAgADYAMAAwAFwAbgAgACAAIAAgACAAIAAgACAAfQAsACAAcgAsACAAYwApAFwAbgAgACAAIAAgACAAIAApAFwAbgAgACAAIAAgACkAXABuACAAIAApADsAXABuAFwAbgAvACoAIABcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBMAGUAYQBjAGgAaQBuAGcAWgBvAG4AZQBzAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuACoALwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEwAZQBhAGMAaABpAG4AZwBaAG8AbgBlAHMAXwBUAGkAdABsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFYARQBFAFIARwAgAEEAdQBzAHQAcgBhAGwAaQBhAG4AIABsAGUAYQBjAGgAaQBuAGcAIAB6AG8AbgBlAHMAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEwAZQBhAGMAaABpAG4AZwBaAG8AbgBlAHMAXwBWAGEAcgBpAGEAYgBsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBMAGUAYQBjAGgAaQBuAGcAWgBvAG4AZQBzAF8AVQBuAGkAdABcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEwAZQBhAGMAaABpAG4AZwBaAG8AbgBlAHMAXwBTAG8AdQByAGMAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAVgBFAEUAUgBHACAAMgAwADIANgA6ACAAVABhAGIAbABlACAAMQAuADMAOgAgAEMAbABpAG0AYQB0AGUAIABhAG4AZAAgAFIAYQBpAG4AZgBhAGwAbAAgAHoAbwBuAGUAIABjAGwAYQBzAHMAaQBmAGkAYwBhAHQAaQBvAG4AcwAgAGEAbgBkACAAZABlAGYAaQBuAGkAdABpAG8AbgBzAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBMAGUAYQBjAGgAaQBuAGcAWgBvAG4AZQBzAF8AVgBhAHIAaQBhAHQAaQBvAG4AXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBMAGUAYQBjAGgAaQBuAGcAWgBvAG4AZQBzAF8ARABhAHQAYQBcAG4AIAAgACAAPQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAE0AQQBLAEUAQQBSAFIAQQBZACgANAAsACAAMgAsACAAXABuACAAIAAgACAAIAAgAEwAQQBNAEIARABBACgAcgAsAGMALAAgAFwAbgAgACAAIAAgACAAIAAgACAASQBOAEQARQBYACgAewBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIATABlAGEAYwBoAGkAbgBnACAAWgBvAG4AZQBcACIALAAgAFwAIgBMAGUAYQBjAGgAaQBuAGcAIABjAHIAaQB0AGUAcgBpAGEAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEwAZQBhAGMAaABpAG4AZwAgAG8AYwBjAHUAcgBzAFwAIgAsACAAXAAiAKMDKAA12F/cNdhO3DXYVtw12FvcKQA+AKMDKAA12DjcNdhH3DAAKQArADXYYNw12FzcNdhW3DXYWdwgADXYZNw12E7cNdhh3DXYUtw12F/cIAAOITXYXNw12FncNdhR3DXYVtw12FvcNdhU3CAANdhQ3DXYTtw12F3cNdhO3DXYUNw12FbcNdhh3DXYZtxcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIATABlAGEAYwBoAGkAbgBnACAAZABvAGUAcwAgAG4AbwB0ACAAbwBjAGMAdQByAFwAIgAsACAAXAAiAKMDKAA12F/cNdhO3DXYVtw12FvcKQBkIqMDKAA12DjcNdhH3DAAKQArADXYYNw12FzcNdhW3DXYWdwgADXYZNw12E7cNdhh3DXYUtw12F/cIAAOITXYXNw12FncNdhR3DXYVtw12FvcNdhU3CAANdhQ3DXYTtw12F3cNdhO3DXYUNw12FbcNdhh3DXYZtxcACIAXABuACAAIAAgACAAIAAgACAAIAB9ACwAIAByACwAIABjACkAXABuACAAIAAgACAAIAAgACkAXABuACAAIAAgACAAKQBcAG4AIAAgACkAOwBcAG4AXABuAC8AKgAgAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAcgBhAGMAVwBFAFQAXABuADUALgA1AC4AMgAuADMAIABDAG8AbgBzAHQAYQBuAHQAIABQAGEAcgBhAG0AZQB0AGUAcgBzAFwAbgBGAHIAYQBjAHQAaQBvAG4AIABvAGYAIABOACAAdABoAGEAdAAgAGkAcwAgAGEAdgBhAGkAbABhAGIAbABlACAAZgBvAHIAIABsAGUAYQBjAGgAaQBuAGcAIABhAG4AZAAgAHIAdQBuAG8AZgBmAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuACoALwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAcgBhAGMAVwBFAFQAXwBUAGkAdABsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAEYAcgBhAGMAdABpAG8AbgAgAG8AZgAgAE4AIAB0AGgAYQB0ACAAaQBzACAAYQB2AGEAaQBsAGEAYgBsAGUAIABmAG8AcgAgAGwAZQBhAGMAaABpAG4AZwAgAGEAbgBkACAAcgB1AG4AbwBmAGYAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAcgBhAGMAVwBFAFQAXwBVAG4AaQB0AFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgAoAEQAaQBtAGUAbgBzAGkAbwBuAGwAZQBzAHMAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAcgBhAGMAVwBFAFQAXwBTAG8AdQByAGMAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAVgBFAEUAUgBHACAAMgAwADIANgA6ADUALgA1AC4AMgAuADMAIABDAG8AbgBzAHQAYQBuAHQAIABQAGEAcgBhAG0AZQB0AGUAcgBzAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAHIAYQBjAFcARQBUAF8ATgBJAFIAUgBlAGYAZQByAGUAbgBjAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAHIAYQBjAFcARQBUAF8ARABhAHQAYQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABNAEEASwBFAEEAUgBSAEEAWQAoADMALAAgADIALAAgAFwAbgAgACAAIAAgACAAIABMAEEATQBCAEQAQQAoAHIALABjACwAIABcAG4AIAAgACAAIAAgACAAIAAgAEkATgBEAEUAWAAoAHsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEkAcwAgAGkAbgAgAGwAZQBhAGMAaABpAG4AZwAgAHoAbwBuAGUAXAAiACwAXAAiAEYAcgBhAGMAVwBFAFQAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFkAZQBzACAALQAgAGkAbgAgAGwAZQBhAGMAaABpAG4AZwAgAHoAbwBuAGUAXAAiACwAIAAxADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAE4AbwAgAC0AIABuAG8AdAAgAGkAbgAgAGwAZQBhAGMAaABpAG4AZwAgAHoAbwBuAGUAXAAiACwAIAAwAFwAbgAgACAAIAAgACAAIAAgACAAfQAsACAAcgAsACAAYwApAFwAbgAgACAAIAAgACAAIAApAFwAbgAgACAAIAAgACkAXABuACAAIAApADsAXABuAFwAbgAgACAAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgByAGEAYwBXAEUAVABfAFYAYQByAGkAYQB0AGkAbwBuAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoACgAXAAiAFwAIgApACkAOwBcAG4AXABuAFwAbgBcAG4ALwAqACAAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABhAHQAYQBTAGMAbwByAGUAcwBfAFMAYwBvAHAAZQAzAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuACoALwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEQAYQB0AGEAUwBjAG8AcgBlAHMAXwBTAGMAbwBwAGUAMwBfAFQAaQB0AGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAQQB1AHMAdAByAGEAbABpAGEAbgAgAGQAYQB0AGEAIABzAGMAbwByAGUAcwAgAGYAbwByACAAcwBjAG8AcABlACAAMwBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABhAHQAYQBTAGMAbwByAGUAcwBfAFMAYwBvAHAAZQAzAF8AVgBhAHIAaQBhAGIAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABhAHQAYQBTAGMAbwByAGUAcwBfAFMAYwBvAHAAZQAzAF8AVQBuAGkAdABcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEQAYQB0AGEAUwBjAG8AcgBlAHMAXwBTAGMAbwBwAGUAMwBfAFMAbwB1AHIAYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBWAEUARQBSAEcAIAAyADAAMgA2ADoAIABYAFgAWABYAFgAWABYAFgAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEQAYQB0AGEAUwBjAG8AcgBlAHMAXwBTAGMAbwBwAGUAMwBfAFYAYQByAGkAYQB0AGkAbwBuAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABhAHQAYQBTAGMAbwByAGUAcwBfAFMAYwBvAHAAZQAzAF8ARABhAHQAYQBcAG4AIAAgACAAPQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAE0AQQBLAEUAQQBSAFIAQQBZACgANgAsACAAMgAsACAAXABuACAAIAAgACAAIAAgAEwAQQBNAEIARABBACgAcgAsAGMALAAgAFwAbgAgACAAIAAgACAAIAAgACAASQBOAEQARQBYACgAewBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIARABhAHQAYQAgAHMAbwB1AHIAYwBlAFwAIgAsACAAXAAiAEQAYQB0AGEAIABzAGMAbwByAGUAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEkAbgB0AGUAcgBuAGEAdABpAG8AbgBhAGwAIABzAGMAbwBwAGUAIAAzACAAZABhAHQAYQBiAGEAcwBlAFwAIgAsACAAMQA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBBAHUAcwB0AHIAYQBsAGkAYQBuACAAcwBjAG8AcABlACAAMwAgAGQAYQB0AGEAYgBhAHMAZQBcACIALAAgADIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAUwB0AGEAdABlACAAbwByACAAcgBlAGcAaQBvAG4AYQBsACAAcwBjAG8AcABlACAAMwAgAGQAYQB0AGEAYgBhAHMAZQBcACIALAAgADMAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIARQBtAGkAcwBzAGkAbwBuAHMAIABpAG4AdABlAG4AcwBpAHQAeQAgAGMAYQBsAGMAdQBsAGEAdABlAGQAIABmAHIAbwBtACAAYQBwAHAAcgBvAHYAZQBkACAAbQBlAHQAaABvAGQAXAAiACwAIAA0ADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFYAZQByAGkAZgBpAGUAZAAgAGMAcgBlAGQAZQBuAHQAaQBhAGwAIABtAGEAdABjAGgAaQBuAGcAIABJAFMATwAxADQAMAA2ADcAXAAiACwAIAA1AFwAbgAgACAAIAAgACAAIAAgACAAfQAsACAAcgAsACAAYwApAFwAbgAgACAAIAAgACAAIAApAFwAbgAgACAAIAAgACkAXABuACAAIAApADsAXABuAFwAbgBcAG4ALwAqACAAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgByAGEAYwBMAEUAQQBDAEgAXABuADUALgA1AC4AMgAuADMAIABDAG8AbgBzAHQAYQBuAHQAIABQAGEAcgBhAG0AZQB0AGUAcgBzAFwAbgBGAHIAYQBjAHQAaQBvAG4AIABvAGYAIABOACAAdABoAGEAdAAgAGkAcwAgAGEAdgBhAGkAbABhAGIAbABlACAAZgBvAHIAIABsAGUAYQBjAGgAaQBuAGcAIABhAG4AZAAgAHIAdQBuAG8AZgBmAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuACoALwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAcgBhAGMATABFAEEAQwBIAF8AVABpAHQAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBGAHIAYQBjAHQAaQBvAG4AIABvAGYAIABOACAAdABoAGEAdAAgAGkAcwAgAGEAdgBhAGkAbABhAGIAbABlACAAZgBvAHIAIABsAGUAYQBjAGgAaQBuAGcAIABhAG4AZAAgAHIAdQBuAG8AZgBmAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAHIAYQBjAEwARQBBAEMASABfAFUAbgBpAHQAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiACgARABpAG0AZQBuAHMAaQBvAG4AbABlAHMAcwBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgByAGEAYwBMAEUAQQBDAEgAXwBTAG8AdQByAGMAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAVgBFAEUAUgBHACAAMgAwADIANgA6ADUALgA1AC4AMgAuADMAIABDAG8AbgBzAHQAYQBuAHQAIABQAGEAcgBhAG0AZQB0AGUAcgBzAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAHIAYQBjAEwARQBBAEMASABfAE4ASQBSAFIAZQBmAGUAcgBlAG4AYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBOAGEAdABpAG8AbgBhAGwAIABJAG4AdgBlAG4AdABvAHIAeQAgAFIAZQBwAG8AcgB0ACAAVgBvAGwAdQBtAGUAIAAxADoAIABMAGUAYQBjAGgAaQBuAGcAIABhAG4AZAAgAHIAdQBuAG8AZgBmACAAKAAzAC4ARAAuAGIALgAyACkAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAcgBhAGMATABFAEEAQwBIAF8ARABhAHQAYQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABNAEEASwBFAEEAUgBSAEEAWQAoADEALAAgADIALAAgAFwAbgAgACAAIAAgACAAIABMAEEATQBCAEQAQQAoAHIALABjACwAIABcAG4AIAAgACAAIAAgACAAIAAgAEkATgBEAEUAWAAoAHsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEYAcgBhAGMATABFAEEAQwBIAFwAIgAsADAALgAyADQAXABuACAAIAAgACAAIAAgACAAIAB9ACwAIAByACwAIABjACkAXABuACAAIAAgACAAIAAgACkAXABuACAAIAAgACAAKQBcAG4AIAAgACkAOwBcAG4AXABuACAAIABDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAHIAYQBjAEwARQBBAEMASABfAFYAYQByAGkAYQB0AGkAbwBuAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoACgAXAAiAFwAIgApACkAOwBcAG4AXABuAFwAbgBcAG4ALwAqACAAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAGwAZQBhAGMAaABcAG4ANQAuADUALgAyAC4AMwAgAEMAbwBuAHMAdABhAG4AdAAgAFAAYQByAGEAbQBlAHQAZQByAHMAXABuAEUAbQBpAHMAcwBpAG8AbgAgAGYAYQBjAHQAbwByACAAZgBvAHIAIABuAGkAdAByAG8AZwBlAG4AIABsAGUAYQBjAGgAaQBuAGcAIABhAG4AZAAgAHIAdQBuAG8AZgBmAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuACoALwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEUARgBsAGUAYQBjAGgAXwBUAGkAdABsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAEUAbQBpAHMAcwBpAG8AbgAgAGYAYQBjAHQAbwByACAAZgBvAHIAIABuAGkAdAByAG8AZwBlAG4AIABsAGUAYQBjAGgAaQBuAGcAIABhAG4AZAAgAHIAdQBuAG8AZgBmAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYAbABlAGEAYwBoAF8AVQBuAGkAdABcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAKABrAGcAIABOADIATwAtAE4AIAAvACAAawBnACAATgBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAGwAZQBhAGMAaABfAFMAbwB1AHIAYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBWAEUARQBSAEcAIAAyADAAMgA2ADoANQAuADUALgAyAC4AMwAgAEMAbwBuAHMAdABhAG4AdAAgAFAAYQByAGEAbQBlAHQAZQByAHMAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEUARgBsAGUAYQBjAGgAXwBOAEkAUgBSAGUAZgBlAHIAZQBuAGMAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIATgBhAHQAaQBvAG4AYQBsACAASQBuAHYAZQBuAHQAbwByAHkAIABSAGUAcABvAHIAdAAgAFYAbwBsAHUAbQBlACAAMQA6ACAARQBxAHUAYQB0AGkAbwBuACAAMwAuAEQALgBCAF8AMQAwAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYAbABlAGEAYwBoAF8ARABhAHQAYQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABNAEEASwBFAEEAUgBSAEEAWQAoADEALAAgADIALAAgAFwAbgAgACAAIAAgACAAIABMAEEATQBCAEQAQQAoAHIALABjACwAIABcAG4AIAAgACAAIAAgACAAIAAgAEkATgBEAEUAWAAoAHsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEUARgBsAGUAYQBjAGgAXAAiACwAMAAuADAAMQAxAFwAbgAgACAAIAAgACAAIAAgACAAfQAsACAAcgAsACAAYwApAFwAbgAgACAAIAAgACAAIAApAFwAbgAgACAAIAAgACkAXABuACAAIAApADsAXABuAFwAbgAgACAAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAGwAZQBhAGMAaABfAFYAYQByAGkAYQB0AGkAbwBuAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoACgAXAAiAFwAIgApACkAOwBcAG4AXABuAFwAbgAvACoAIABcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYATgAyAE8AXABuAFQAYQBiAGwAZQAgAEEALgAyAC4AMgAuADEAXABuAE4AaQB0AHIAbwB1AHMAIABvAHgAaQBkAGUAIABlAG0AaQBzAHMAaQBvAG4AIABmAGEAYwB0AG8AcgBzACAAZgBvAHIAIABpAG4AbwByAGcAYQBuAGkAYwAgAGYAZQByAHQAaQBsAGkAcwBlAHIAIABhAHAAcABsAGkAYwBhAHQAaQBvAG4AIAAoAGsAZwAgAE4AMgBPAC0ATgAvAGsAZwAgAE4AKQAgACgARQBGAE4AMgBPACkAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AKgAvAFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAE4AMgBPAF8AVABpAHQAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBOAGkAdAByAG8AdQBzACAAbwB4AGkAZABlACAAZQBtAGkAcwBzAGkAbwBuACAAZgBhAGMAdABvAHIAcwAgAGYAbwByACAAaQBuAG8AcgBnAGEAbgBpAGMAIABmAGUAcgB0AGkAbABpAHMAZQByACAAYQBwAHAAbABpAGMAYQB0AGkAbwBuAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYATgAyAE8AXwBVAG4AaQB0AFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgAoAGsAZwAgAE4AMgBPAC0ATgAgAC8AIABrAGcAIABOAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYATgAyAE8AXwBTAG8AdQByAGMAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAVgBFAEUAUgBHACAAMgAwADIANgA6ACAAVABhAGIAbABlACAAQQAuADIALgAyAC4AMQBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAE4AMgBPAF8ATgBJAFIAUgBlAGYAZQByAGUAbgBjAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYATgAyAE8AXwBEAGEAdABhAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAE0AQQBLAEUAQQBSAFIAQQBZACgAMQA1ACwAIAA1ACwAIABcAG4AIAAgACAAIAAgACAATABBAE0AQgBEAEEAKAByACwAYwAsACAAXABuACAAIAAgACAAIAAgACAAIABJAE4ARABFAFgAKAB7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBQAHIAbwBkAHUAYwB0AGkAbwBuACAAcwB5AHMAdABlAG0AIABqAFwAIgAsAFwAIgBFAEYATgAyAE8AXAAiACwAIABcACIAUAByAG8AZAB1AGMAdABpAG8AbgAgAHMAeQBzAHQAZQBtACAAbwBuAGwAeQBcACIALAAgAFwAIgBJAHIAcgBpAGcAYQB0AGkAbwBuACAAbQBlAHQAaABvAGQAXAAiACwAIABcACIAUgBhAGkAbgBmAGEAbABsACAAegBvAG4AZQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIASQByAHIAaQBnAGEAdABlAGQAIABwAGEAcwB0AHUAcgBlAFwAIgAsADAALgAwADAANQA5ACwAIABcACIAUABhAHMAdAB1AHIAZQBcACIALAAgAFwAIgBBAG4AeQBcACIALAAgAFwAIgBBAG4AeQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIASQByAHIAaQBnAGEAdABlAGQAIABjAHIAbwBwAFwAIgAsADAALgAwADAANwAsACAAXAAiAEMAcgBvAHAAXAAiACwAIABcACIAQQBuAHkAXAAiACwAIABcACIAQQBuAHkAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAE4AbwBuAC0AaQByAHIAaQBnAGEAdABlAGQAIABwAGEAcwB0AHUAcgBlAFwAIgAsADAALgAwADAAMQA4ACwAIABcACIAUABhAHMAdAB1AHIAZQBcACIALAAgAFwAIgBOAG8AdAAgAGkAcgByAGkAZwBhAHQAZQBkAFwAIgAsACAAXAAiAEwAbwB3ACAAcgBhAGkAbgBmAGEAbABsAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBOAG8AbgAtAGkAcgByAGkAZwBhAHQAZQBkACAAcABhAHMAdAB1AHIAZQBcACIALAAwAC4AMAAwADEAOAAsACAAXAAiAFAAYQBzAHQAdQByAGUAXAAiACwAIABcACIATgBvAHQAIABpAHIAcgBpAGcAYQB0AGUAZABcACIALAAgAFwAIgBIAGkAZwBoACAAcgBhAGkAbgBmAGEAbABsAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBOAG8AbgAtAGkAcgByAGkAZwBhAHQAZQBkACAAYwByAG8AcAAgACgAbABvAHcAIAByAGEAaQBuAGYAYQBsAGwAKQBcACIALAAwAC4AMAAwADIAOQAsACAAXAAiAEMAcgBvAHAAXAAiACwAIABcACIATgBvAHQAIABpAHIAcgBpAGcAYQB0AGUAZABcACIALAAgAFwAIgBMAG8AdwAgAHIAYQBpAG4AZgBhAGwAbABcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIATgBvAG4ALQBpAHIAcgBpAGcAYQB0AGUAZAAgAGMAcgBvAHAAIAAoAGgAaQBnAGgAIAByAGEAaQBuAGYAYQBsAGwAKQBcACIALAAwAC4AMAAwADgALAAgAFwAIgBDAHIAbwBwAFwAIgAsACAAXAAiAE4AbwB0ACAAaQByAHIAaQBnAGEAdABlAGQAXAAiACwAIABcACIASABpAGcAaAAgAHIAYQBpAG4AZgBhAGwAbABcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAUwB1AGcAYQByAFwAIgAsADAALgAwADEAOQA5ACwAIABcACIAUwB1AGcAYQByAFwAIgAsACAAXAAiAEEAbgB5AFwAIgAsACAAXAAiAEEAbgB5AFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBDAG8AdAB0AG8AbgBcACIALAAwAC4AMAAwADUAMwAsACAAXAAiAEMAbwB0AHQAbwBuAFwAIgAsACAAXAAiAEEAbgB5AFwAIgAsACAAXAAiAEEAbgB5AFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBIAG8AcgB0AGkAYwB1AGwAdAB1AHIAYQBsACAAYwByAG8AcABzAFwAIgAsADAALgAwADAANgA0ACwAIABcACIASABvAHIAdABpAGMAdQBsAHQAdQByAGEAbAAgAGMAcgBvAHAAcwBcACIALAAgAFwAIgBBAG4AeQBcACIALAAgAFwAIgBBAG4AeQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAUgBpAGMAZQAgACgAYwBvAG4AdABpAG4AdQBvAHUAcwAgAGYAbABvAG8AZABpAG4AZwApAFwAIgAsADAALgAwADAAMwAsACAAXAAiAFIAaQBjAGUAXAAiACwAIABcACIAQwBvAG4AdABpAG4AdQBvAHUAcwAgAGYAbABvAG8AZABpAG4AZwBcACIALAAgAFwAIgBBAG4AeQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAUgBpAGMAZQAgACgAcwBpAG4AZwBsAGUAIABhAG4AZAAgAG0AdQBsAHQAaQBwAGwAZQAgAGQAcgBhAGkAbgBhAGcAZQAsACAAbwByACAAYQBsAHQAZQByAG4AYQB0AGUAIAB3AGUAdAB0AGkAbgBnACAAYQBuAGQAIABkAHIAeQBpAG4AZwApAFwAIgAsADAALgAwADAANQAsACAAXAAiAFIAaQBjAGUAXAAiACwAIABcACIAUwBpAG4AZwBsAGUAIABhAG4AZAAgAG0AdQBsAHQAaQBwAGwAZQAgAGQAcgBhAGkAbgBhAGcAZQAsACAAbwByACAAYQBsAHQAZQByAG4AYQB0AGUAIAB3AGUAdAB0AGkAbgBnACAAYQBuAGQAIABkAHIAeQBpAG4AZwBcACIALAAgAFwAIgBBAG4AeQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAQQBxAHUAYQBjAHUAbAB0AHUAcgBlAFwAIgAsADAALgAwADAAMgA2ACwAIABcACIAQQBxAHUAYQBjAHUAbAB0AHUAcgBlAFwAIgAsACAAXAAiAEEAbgB5AFwAIgAsACAAXAAiAEEAbgB5AFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBGAG8AcgBlAHMAdAByAHkAXAAiACwAMAAuADAAMAAxADgALAAgAFwAIgBGAG8AcgBlAHMAdAByAHkAXAAiACwAIABcACIAQQBuAHkAXAAiACwAIABcACIAQQBuAHkAXAAiAFwAbgAgACAAIAAgACAAIAAgACAAfQAsACAAcgAsACAAYwApAFwAbgAgACAAIAAgACAAIAApAFwAbgAgACAAIAAgACkAXABuACAAIAApADsAXABuAFwAbgAgACAAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAE4AMgBPAF8AVgBhAHIAaQBhAHQAaQBvAG4AXABuACAAIAA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAATQBBAEsARQBBAFIAUgBBAFkAKAA1ACwAIAAxACwAIABcAG4AIAAgACAAIAAgACAATABBAE0AQgBEAEEAKAByACwAYwAsACAAXABuACAAIAAgACAAIAAgACAAIABJAE4ARABFAFgAKAB7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBWAEEAUgBJAEEAVABJAE8ATgAgAE8ARgAgAFMATwBVAFIAQwBFACAARABBAFQAQQA6AFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBSAGUAbQBvAHYAZQBkACAAZAB1AHAAbABpAGMAYQB0AGUAIAAnAEEAcQB1AGEAYwB1AGwAdAB1AHIAZQAnACAAcgBvAHcALgBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAUgBlAG0AbwB2AGUAZAAgAGEAcwB0AGUAcgBpAHMAawBzACAAdABvACAAYQBpAGQAIABsAG8AbwBrAHUAcAAuAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBBAGQAZABlAGQAIAAnAHAAcgBvAGQAdQBjAHQAaQBvAG4AIABzAHkAcwB0AGUAbQAgAG8AbgBsAHkAJwAsACAAJwByAGEAaQBuAGYAYQBsAGwAIAB6AG8AbgBlACcAIABhAG4AZAAgACcAaQByAHIAaQBnAGEAdABpAG8AbgAgAG0AZQB0AGgAbwBkACcAIABjAG8AbAB1AG0AbgBzACAAdABvACAAYQBpAGQAIABsAG8AbwBrAHUAcAAuAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBEAHUAcABsAGkAYwBhAHQAZQBkACAAJwBuAG8AbgAtAGkAcgByAGkAZwBhAHQAZQBkACAAcABhAHMAdAB1AHIAZQAnACAAcgBvAHcAIAB3AGkAdABoACAAcwBhAG0AZQAgAEUARgAgAGYAbwByACAAbABvAHcAIABhAG4AZAAgAGgAaQBnAGgAIAByAGEAaQBuAGYAYQBsAGwAIAB6AG8AbgBlAHMAIAB0AG8AIABhAGkAZAAgAGwAbwBvAGsAdQBwAC4AXAAiAFwAbgAgACAAIAAgACAAIAAgACAAfQAsACAAcgAsACAAYwApAFwAbgAgACAAIAAgACAAIAApAFwAbgAgACAAIAAgACkAXABuACAAIAApADsAXABuAFwAbgAvACoAIABcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAHIAYQBjAFcARQBUAEkAcgByAGkAZwBhAHQAaQBvAG4AXABuAFYARQBFAFIARwAgADIAMAAyADYAOgAgAEMAaABhAHAAdABlAHIAIAAxACwAIABzAGUAYwB0AGkAbwBuACAAMQAuADgALgAyACAATABlAGEAYwBoAGkAbgBnACwAIABjAGwAaQBtAGEAdABlACAAYQBuAGQAIAByAGEAaQBuAGYAYQBsAGwAIAB6AG8AbgBlAHMAXABuAEkAUABDAEMAOgAgAE4AMgBPACAARQBNAEkAUwBTAEkATwBOAFMAIABGAFIATwBNACAATQBBAE4AQQBHAEUARAAgAFMATwBJAEwAUwAsACAAQQBOAEQAIABDAE8AMgAgAEUATQBJAFMAUwBJAE8ATgBTACAARgBSAE8ATQAgAEwASQBNAEUAIABBAE4ARAAgAFUAUgBFAEEAIABBAFAAUABMAEkAQwBBAFQASQBPAE4AXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AKgAvAFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgByAGEAYwBXAEUAVABJAHIAcgBpAGcAYQB0AGkAbwBuAF8AVABpAHQAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBGAHIAYQBjAFcARQBUACAAZgBvAHIAIABpAHIAcgBpAGcAYQB0AGkAbwBuACAAdAB5AHAAZQBzAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAHIAYQBjAFcARQBUAEkAcgByAGkAZwBhAHQAaQBvAG4AXwBVAG4AaQB0AFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBkAGkAbQBlAG4AcwBpAG8AbgBsAGUAcwBzAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAHIAYQBjAFcARQBUAEkAcgByAGkAZwBhAHQAaQBvAG4AXwBTAG8AdQByAGMAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAVgBFAEUAUgBHACAAMgAwADIANgA6ACAAQwBoAGEAcAB0AGUAcgAgADEALAAgAHMAZQBjAHQAaQBvAG4AIAAxAC4AOAAuADIAIABMAGUAYQBjAGgAaQBuAGcALAAgAGMAbABpAG0AYQB0AGUAIABhAG4AZAAgAHIAYQBpAG4AZgBhAGwAbAAgAHoAbwBuAGUAcwBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgByAGEAYwBXAEUAVABJAHIAcgBpAGcAYQB0AGkAbwBuAF8ATgBJAFIAUgBlAGYAZQByAGUAbgBjAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAEkAUABDAEMAIAAyADAAMQA5ACAAUgBlAGYAaQBuAGUAbQBlAG4AdAAgAFYAbwBsAHUAbQBlACAANAA6ACAAQwBoAGEAcAB0AGUAcgAgADEAMQA6ACAATgAyAE8AIABFAG0AaQBzAHMAaQBvAG4AcwAgAGYAcgBvAG0AIABNAGEAbgBhAGcAZQBkACAAUwBvAGkAbABzACwAIABhAG4AZAAgAEMATwAyACAARQBtAGkAcwBzAGkAbwBuAHMAIABmAHIAbwBtACAATABpAG0AZQAgAGEAbgBkACAAVQByAGUAYQAgAEEAcABwAGwAaQBjAGEAdABpAG8AbgBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgByAGEAYwBXAEUAVABJAHIAcgBpAGcAYQB0AGkAbwBuAF8ARABhAHQAYQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABNAEEASwBFAEEAUgBSAEEAWQAoADYALAAgADIALAAgAFwAbgAgACAAIAAgACAAIABMAEEATQBCAEQAQQAoAHIALABjACwAIABcAG4AIAAgACAAIAAgACAAIAAgAEkATgBEAEUAWAAoAHsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEkAcgByAGkAZwBhAHQAaQBvAG4AIAB0AHkAcABlACAAaQByAFwAIgAsAFwAIgBGAHIAYQBjAFcARQBUAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBOAG8AdAAgAGkAcgByAGkAZwBhAHQAZQBkAFwAIgAsACAAMAA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBEAHIAaQBwACAAaQByAHIAaQBnAGEAdABpAG8AbgBcACIALAAgADAAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAUwBwAHIAaQBuAGsAbABlAHIAIABpAHIAcgBpAGcAYQB0AGkAbwBuAFwAIgAsACAAMQA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBTAHUAcgBmAGEAYwBlACAAaQByAHIAaQBnAGEAdABpAG8AbgBcACIALAAgADEAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIATwB0AGgAZQByACAAaQByAHIAaQBnAGEAdABpAG8AbgBcACIALAAgADEAXABuACAAIAAgACAAIAAgACAAIAB9ACwAIAByACwAIABjACkAXABuACAAIAAgACAAIAAgACkAXABuACAAIAAgACAAKQBcAG4AIAAgACkAOwBcAG4AXABuACAAIABDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAHIAYQBjAFcARQBUAEkAcgByAGkAZwBhAHQAaQBvAG4AXwBWAGEAcgBpAGEAdABpAG8AbgBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAVgBBAFIASQBBAFQASQBPAE4AIABGAFIATwBNACAAUwBPAFUAUgBDAEUAIABEAEEAVABBADoAIABUAGEAYgBsAGUAIABjAHIAZQBhAHQAZQBkACAAYgBhAHMAZQBkACAAbwBuACAAVgBFAEUAUgBHACAAdABlAHgAdAAgACcAQQByAGUAYQBzACAAYQByAGUAIABzAHUAYgBqAGUAYwB0ACAAdABvACAAbABlAGEAYwBoAGkAbgBnACAAKABpAC4AZQAuACwAIABpAG4AIAB0AGgAZQAgAGwAZQBhAGMAaABpAG4AZwAgAHoAbwBuAGUAKQAgAHcAaABlAG4ALgAuAC4AIAB0AGgAZQAgAGwAYQBuAGQAIABpAHMAIABpAHIAcgBpAGcAYQB0AGUAZAAgACgAZQB4AGMAZQBwAHQAIABkAHIAaQBwACAAaQByAHIAaQBnAGEAdABpAG8AbgApAC4AJwBcACIAKQA7AFwAbgBcAG4AXABuAC8AKgAgAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEUARgBQAGEAcwB0AHUAcgBlAFIAYQBuAGcAZQBBAG4AZABQAGEAZABkAG8AYwBrAFwAbgBUAGEAYgBsAGUAIABBAC4AMgAuADIALgAyADoAIABFAG0AaQBzAHMAaQBvAG4AIABmAGEAYwB0AG8AcgAgAGYAbwByACAAdQByAGkAbgBlACAAYQBuAGQAIABkAHUAbgBnACAAZABlAHAAbwBzAGkAdABlAGQAIABvAG4AIABwAGEAcwB0AHUAcgBlACwAIAByAGEAbgBnAGUAIABvAHIAIABwAGEAZABkAG8AYwBrACAAKABrAGcAIABOADIATwAtAE4ALwBrAGcAIABOACkAIAAoAEUARgBQAFIAUAApAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuACoALwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEUARgBQAGEAcwB0AHUAcgBlAFIAYQBuAGcAZQBBAG4AZABQAGEAZABkAG8AYwBrAF8AVABpAHQAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBFAG0AaQBzAHMAaQBvAG4AIABmAGEAYwB0AG8AcgAgAGYAbwByACAAdQByAGkAbgBlACAAYQBuAGQAIABkAHUAbgBnACAAZABlAHAAbwBzAGkAdABlAGQAIABvAG4AIABwAGEAcwB0AHUAcgBlACwAIAByAGEAbgBnAGUAIABvAHIAIABwAGEAZABkAG8AYwBrAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYAUABhAHMAdAB1AHIAZQBSAGEAbgBnAGUAQQBuAGQAUABhAGQAZABvAGMAawBfAFUAbgBpAHQAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAGsAZwAgAE4AMgBPACAALQAgAE4AIAAvACAAawBnACAATgBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAFAAYQBzAHQAdQByAGUAUgBhAG4AZwBlAEEAbgBkAFAAYQBkAGQAbwBjAGsAXwBTAG8AdQByAGMAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAVgBFAEUAUgBHACAAMgAwADIANgA6ACAAVABhAGIAbABlACAAQQAuADIALgAyAC4AMgBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAFAAYQBzAHQAdQByAGUAUgBhAG4AZwBlAEEAbgBkAFAAYQBkAGQAbwBjAGsAXwBOAEkAUgBSAGUAZgBlAHIAZQBuAGMAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEUARgBQAGEAcwB0AHUAcgBlAFIAYQBuAGcAZQBBAG4AZABQAGEAZABkAG8AYwBrAF8ARABhAHQAYQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABNAEEASwBFAEEAUgBSAEEAWQAoADMALAAgADIALAAgAFwAbgAgACAAIAAgACAAIABMAEEATQBCAEQAQQAoAHIALABjACwAIABcAG4AIAAgACAAIAAgACAAIAAgAEkATgBEAEUAWAAoAHsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEMAbABpAG0AYQB0AGUAIAB6AG8AbgBlAFwAIgAsACAAXAAiAEUARgBQAFIAUABcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVwBlAHQAIABjAGwAaQBtAGEAdABlACAAegBvAG4AZQBcACIALAAgADAALgAwADAANgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBEAHIAeQAgAGMAbABpAG0AYQB0AGUAIAB6AG8AbgBlAFwAIgAsACAAMAAuADAAMAAyAFwAbgAgACAAIAAgACAAIAAgACAAfQAsACAAcgAsACAAYwApAFwAbgAgACAAIAAgACAAIAApAFwAbgAgACAAIAAgACkAXABuACAAIAApADsAXABuAFwAbgAgACAAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAFAAYQBzAHQAdQByAGUAUgBhAG4AZwBlAEEAbgBkAFAAYQBkAGQAbwBjAGsAXwBWAGEAcgBpAGEAdABpAG8AbgBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAVgBBAFIASQBBAFQASQBPAE4AIABGAFIATwBNACAAUwBPAFUAUgBDAEUAIABEAEEAVABBADoAIABDAGgAYQBuAGcAZQBkACAAJwBEAHIAeQAgAGMAbABpAG0AYQB0AGUAIAB6AG8AbgBlAHMAJwAgAHQAbwAgAHMAaQBuAGcAdQBsAGEAcgAgACcARAByAHkAIABjAGwAaQBtAGEAdABlACAAegBvAG4AZQAnACAAdABvACAAYQBpAGQAIABsAG8AbwBrAHUAcAAuAFwAIgApADsAXABuAFwAbgBcAG4ALwAqACAAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ATQBvAG4AdABoAHMAVABvAFMAZQBhAHMAbwBuAHMAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AKgAvAFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ATQBvAG4AdABoAHMAVABvAFMAZQBhAHMAbwBuAHMAXwBUAGkAdABsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAE0AbwBuAHQAaABzACAAdABvACAAUwBlAGEAcwBvAG4AcwAgAE0AYQBwAHAAaQBuAGcAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAE0AbwBuAHQAaABzAFQAbwBTAGUAYQBzAG8AbgBzAF8AVQBuAGkAdABcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAE0AbwBuAHQAaABzAFQAbwBTAGUAYQBzAG8AbgBzAF8AUwBvAHUAcgBjAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBNAG8AbgB0AGgAcwBUAG8AUwBlAGEAcwBvAG4AcwBfAE4ASQBSAFIAZQBmAGUAcgBlAG4AYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ATQBvAG4AdABoAHMAVABvAFMAZQBhAHMAbwBuAHMAXwBEAGEAdABhAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAE0AQQBLAEUAQQBSAFIAQQBZACgAMQAzACwAIAAyACwAIABcAG4AIAAgACAAIAAgACAATABBAE0AQgBEAEEAKAByACwAYwAsACAAXABuACAAIAAgACAAIAAgACAAIABJAE4ARABFAFgAKAB7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBNAG8AbgB0AGgAXAAiACwAIABcACIAUwBlAGEAcwBvAG4AXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEoAYQBuAHUAYQByAHkAXAAiACwAIABcACIAUwB1AG0AbQBlAHIAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEYAZQBiAHIAdQBhAHIAeQBcACIALAAgAFwAIgBTAHUAbQBtAGUAcgBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIATQBhAHIAYwBoAFwAIgAsACAAXAAiAEEAdQB0AHUAbQBuAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBBAHAAcgBpAGwAXAAiACwAIABcACIAQQB1AHQAdQBtAG4AXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAE0AYQB5AFwAIgAsACAAXAAiAEEAdQB0AHUAbQBuAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBKAHUAbgBlAFwAIgAsACAAXAAiAFcAaQBuAHQAZQByAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBKAHUAbAB5AFwAIgAsACAAXAAiAFcAaQBuAHQAZQByAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBBAHUAZwB1AHMAdABcACIALAAgAFwAIgBXAGkAbgB0AGUAcgBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAUwBlAHAAdABlAG0AYgBlAHIAXAAiACwAIABcACIAUwBwAHIAaQBuAGcAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAE8AYwB0AG8AYgBlAHIAXAAiACwAIABcACIAUwBwAHIAaQBuAGcAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAE4AbwB2AGUAbQBiAGUAcgBcACIALAAgAFwAIgBTAHAAcgBpAG4AZwBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIARABlAGMAZQBtAGIAZQByAFwAIgAsACAAXAAiAFMAdQBtAG0AZQByAFwAIgBcAG4AIAAgACAAIAAgACAAIAAgAH0ALAAgAHIALAAgAGMAKQBcAG4AIAAgACAAIAAgACAAKQBcAG4AIAAgACAAIAApAFwAbgAgACAAKQA7AFwAbgBcAG4AIAAgAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAE0AbwBuAHQAaABzAFQAbwBTAGUAYQBzAG8AbgBzAF8AVgBhAHIAaQBhAHQAaQBvAG4AXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFwAIgApADsAXABuAFwAbgBcAG4AXABuAC8AKgAgAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAE0AQwBGAFQAZQBtAHAAZQByAGEAdAB1AHIAZQBaAG8AbgBlAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuACoALwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAE0AQwBGAFQAZQBtAHAAZQByAGEAdAB1AHIAZQBaAG8AbgBlAF8AVABpAHQAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBNAGEAbgB1AHIAZQAgAE0AYQBuAGEAZwBlAG0AZQBuAHQAIAATICAATQBlAHQAaABhAG4AZQAgAGMAbwBuAHYAZQByAHMAaQBvAG4AIABmAGEAYwB0AG8AcgAgAHAAZQByACAAdABlAG0AcABlAHIAYQB0AHUAcgBlACAAegBvAG4AZQAgACgAZgByAGEAYwB0AGkAbwBuACkAIAAoAE0AQwBGAGkAbQApAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBNAEMARgBUAGUAbQBwAGUAcgBhAHQAdQByAGUAWgBvAG4AZQBfAFUAbgBpAHQAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAGYAcgBhAGMAdABpAG8AbgBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ATQBDAEYAVABlAG0AcABlAHIAYQB0AHUAcgBlAFoAbwBuAGUAXwBTAG8AdQByAGMAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAVgBFAEUAUgBHACAAMgAwADIANgA6ACAAVABhAGIAbABlACAAQQAuADEALgA4AC4AMQBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ATQBDAEYAVABlAG0AcABlAHIAYQB0AHUAcgBlAFoAbwBuAGUAXwBEAGEAdABhAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAE0AQQBLAEUAQQBSAFIAQQBZACgAMgAyACwAIAAxADYALAAgAFwAbgAgACAAIAAgACAAIABMAEEATQBCAEQAQQAoAHIALABjACwAIABcAG4AIAAgACAAIAAgACAAIAAgAEkATgBEAEUAWAAoAHsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFQAZQBtAHAAZQByAGEAdAB1AHIAZQAgAHoAbwBuAGUAXAAiACwAIABcACIATQBBAFQAIAAoALoAQwApAFwAIgAsACAAXAAiAFUAbgBjAG8AdgBlAHIAZQBkACAAYQBuAGUAcgBvAGIAaQBjACAAbABhAGcAbwBvAG4AXAAiACwAIABcACIAQwBvAHYAZQByAGUAZAAgAGwAYQBnAG8AbwBuAFwAIgAsACAAXAAiAEwAaQBxAHUAaQBkACAAUwBsAHUAcgByAHkAIAAoAHcAaQB0AGgAbwB1AHQAIABuAGEAdAB1AHIAYQBsACAAYwByAHUAcwB0ACkAXAAiACwAIABcACIARABhAGkAbAB5ACAAcwBwAHIAZQBhAGQAIAAoAGIAKQBcACIALAAgAFwAIgBDAG8AbQBwAG8AcwB0AGkAbgBnACAAKABwAGEAcwBzAGkAdgBlACAAdwBpAG4AZAByAG8AdwApAFwAIgAsACAAXAAiAFMAbwBsAGkAZAAgAFMAdABvAHIAYQBnAGUAXAAiACwAIABcACIAUABpAHQAIABTAHQAbwByAGEAZwBlACAAPAAxACAAbQBvAG4AdABoAFwAIgAsACAAXAAiAEQAZQBlAHAAIABMAGkAdAB0AGUAcgBcACIALAAgAFwAIgBQAG8AdQBsAHQAcgB5ACAATQBhAG4AdQByAGUAIAAoAHcAaQB0AGgALwB3AGkAdABoAG8AdQB0ACAAbABpAHQAdABlAHIAKQBcACIALAAgAFwAIgBcACIALAAgAFwAIgBEAGkAcgBlAGMAdAAgAHAAcgBvAGMAZQBzAHMAaQBuAGcAIABpAG4AdABvACAAcABlAGwAbABlAHQAaQB6AGUAZAAgAGYAZQByAHQAaQBsAGkAcwBlAHIAXAAiACwAIABcACIARABpAHIAZQBjAHQAIABhAHAAcABsAGkAYwBhAHQAaQBvAG4AIAB0AG8AIABzAG8AaQBsAFwAIgAsACAAXAAiAFAAYQBzAHQAdQByAGUALAAgAFIAYQBuAGcAZQAgAGEAbgBkACAAUABhAGQAZABvAGMAawAgACgAYwApACgAZAApAFwAIgAsACAAXAAiAE0AQQBUACAAcgBhAHcAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEMAbwBvAGwAXAAiACwAIABcACIAZCIxADAAXAAiACwAIAAwAC4ANgA2ACwAIAAwAC4AMQAsACAAMAAuADEALAAgADAALgAwADAAMQAsACAAMAAuADAAMAA1ACwAIAAwAC4AMAAyACwAIAAwAC4AMAAzACwAIAAwAC4AMAA0ACwAIAAwAC4AMAAxADUALAAgADAALgAwADEANQAsACAAMAAsACAAMAAsACAAMAAuADAAMAA0ADcALAAgADEAMAA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBDAG8AbwBsAFwAIgAsACAAMQAxACwAIAAwAC4ANgA4ACwAIAAwAC4AMQAsACAAMAAuADEAMQAsACAAMAAuADAAMAAxACwAIAAwAC4AMAAwADUALAAgADAALgAwADIALAAgADAALgAwADMALAAgADAALgAwADQALAAgADAALgAwADEANQAsACAAMAAuADAAMQA1ACwAIAAwACwAIAAwACwAIAAwAC4AMAAwADQANwAsACAAMQAxADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEMAbwBvAGwAXAAiACwAIAAxADIALAAgADAALgA3ACwAIAAwAC4AMQAsACAAMAAuADEAMwAsACAAMAAuADAAMAAxACwAIAAwAC4AMAAwADUALAAgADAALgAwADIALAAgADAALgAwADMALAAgADAALgAwADQALAAgADAALgAwADEANQAsACAAMAAuADAAMQA1ACwAIAAwACwAIAAwACwAIAAwAC4AMAAwADQANwAsACAAMQAyADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEMAbwBvAGwAXAAiACwAIAAxADMALAAgADAALgA3ADEALAAgADAALgAxACwAIAAwAC4AMQA0ACwAIAAwAC4AMAAwADEALAAgADAALgAwADAANQAsACAAMAAuADAAMgAsACAAMAAuADAAMwAsACAAMAAuADAANAAsACAAMAAuADAAMQA1ACwAIAAwAC4AMAAxADUALAAgADAALAAgADAALAAgADAALgAwADAANAA3ACwAIAAxADMAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAQwBvAG8AbABcACIALAAgADEANAAsACAAMAAuADcAMwAsACAAMAAuADEALAAgADAALgAxADUALAAgADAALgAwADAAMQAsACAAMAAuADAAMAA1ACwAIAAwAC4AMAAyACwAIAAwAC4AMAAzACwAIAAwAC4AMAA0ACwAIAAwAC4AMAAxADUALAAgADAALgAwADEANQAsACAAMAAsACAAMAAsACAAMAAuADAAMAA0ADcALAAgADEANAA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBUAGUAbQBwAGUAcgBhAHQAZQBcACIALAAgADEANQAsACAAMAAuADcANAAsACAAMAAuADEALAAgADAALgAxADcALAAgADAALgAwADAANQAsACAAMAAuADAAMQAsACAAMAAuADAAMgAsACAAMAAuADAAMwAsACAAMAAuADAANAAsACAAMAAuADAAMQA1ACwAIAAwAC4AMAAxADUALAAgADAALAAgADAALAAgADAALgAwADAANAA3ACwAIAAxADUAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVABlAG0AcABlAHIAYQB0AGUAXAAiACwAIAAxADYALAAgADAALgA3ADUALAAgADAALgAxACwAIAAwAC4AMQA4ACwAIAAwAC4AMAAwADUALAAgADAALgAwADEALAAgADAALgAwADIALAAgADAALgAwADMALAAgADAALgAwADQALAAgADAALgAwADEANQAsACAAMAAuADAAMQA1ACwAIAAwACwAIAAwACwAIAAwAC4AMAAwADQANwAsACAAMQA2ADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFQAZQBtAHAAZQByAGEAdABlAFwAIgAsACAAMQA3ACwAIAAwAC4ANwA2ACwAIAAwAC4AMQAsACAAMAAuADIALAAgADAALgAwADAANQAsACAAMAAuADAAMQAsACAAMAAuADAAMgAsACAAMAAuADAAMwAsACAAMAAuADAANAAsACAAMAAuADAAMQA1ACwAIAAwAC4AMAAxADUALAAgADAALAAgADAALAAgADAALgAwADAANAA3ACwAIAAxADcAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVABlAG0AcABlAHIAYQB0AGUAXAAiACwAIAAxADgALAAgADAALgA3ADcALAAgADAALgAxACwAIAAwAC4AMgAyACwAIAAwAC4AMAAwADUALAAgADAALgAwADEALAAgADAALgAwADIALAAgADAALgAwADMALAAgADAALgAwADQALAAgADAALgAwADEANQAsACAAMAAuADAAMQA1ACwAIAAwACwAIAAwACwAIAAwAC4AMAAwADQANwAsACAAMQA4ADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFQAZQBtAHAAZQByAGEAdABlAFwAIgAsACAAMQA5ACwAIAAwAC4ANwA3ACwAIAAwAC4AMQAsACAAMAAuADIANAAsACAAMAAuADAAMAA1ACwAIAAwAC4AMAAxACwAIAAwAC4AMAAyACwAIAAwAC4AMAAzACwAIAAwAC4AMAA0ACwAIAAwAC4AMAAxADUALAAgADAALgAwADEANQAsACAAMAAsACAAMAAsACAAMAAuADAAMAA0ADcALAAgADEAOQA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBUAGUAbQBwAGUAcgBhAHQAZQBcACIALAAgADIAMAAsACAAMAAuADcAOAAsACAAMAAuADEALAAgADAALgAyADYALAAgADAALgAwADAANQAsACAAMAAuADAAMQAsACAAMAAuADAAMgAsACAAMAAuADAAMwAsACAAMAAuADAANAAsACAAMAAuADAAMQA1ACwAIAAwAC4AMAAxADUALAAgADAALAAgADAALAAgADAALgAwADAANAA3ACwAIAAyADAAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVABlAG0AcABlAHIAYQB0AGUAXAAiACwAIAAyADEALAAgADAALgA3ADgALAAgADAALgAxACwAIAAwAC4AMgA5ACwAIAAwAC4AMAAwADUALAAgADAALgAwADEALAAgADAALgAwADIALAAgADAALgAwADMALAAgADAALgAwADQALAAgADAALgAwADEANQAsACAAMAAuADAAMQA1ACwAIAAwACwAIAAwACwAIAAwAC4AMAAwADQANwAsACAAMgAxADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFQAZQBtAHAAZQByAGEAdABlAFwAIgAsACAAMgAyACwAIAAwAC4ANwA4ACwAIAAwAC4AMQAsACAAMAAuADMAMQAsACAAMAAuADAAMAA1ACwAIAAwAC4AMAAxACwAIAAwAC4AMAAyACwAIAAwAC4AMAAzACwAIAAwAC4AMAA0ACwAIAAwAC4AMAAxADUALAAgADAALgAwADEANQAsACAAMAAsACAAMAAsACAAMAAuADAAMAA0ADcALAAgADIAMgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBUAGUAbQBwAGUAcgBhAHQAZQBcACIALAAgADIAMwAsACAAMAAuADcAOQAsACAAMAAuADEALAAgADAALgAzADQALAAgADAALgAwADAANQAsACAAMAAuADAAMQAsACAAMAAuADAAMgAsACAAMAAuADAAMwAsACAAMAAuADAANAAsACAAMAAuADAAMQA1ACwAIAAwAC4AMAAxADUALAAgADAALAAgADAALAAgADAALgAwADAANAA3ACwAIAAyADMAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVABlAG0AcABlAHIAYQB0AGUAXAAiACwAIAAyADQALAAgADAALgA3ADkALAAgADAALgAxACwAIAAwAC4AMwA3ACwAIAAwAC4AMAAwADUALAAgADAALgAwADEALAAgADAALgAwADIALAAgADAALgAwADMALAAgADAALgAwADQALAAgADAALgAwADEANQAsACAAMAAuADAAMQA1ACwAIAAwACwAIAAwACwAIAAwAC4AMAAwADQANwAsACAAMgA0ADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFQAZQBtAHAAZQByAGEAdABlAFwAIgAsACAAMgA1ACwAIAAwAC4ANwA5ACwAIAAwAC4AMQAsACAAMAAuADQAMQAsACAAMAAuADAAMAA1ACwAIAAwAC4AMAAxACwAIAAwAC4AMAAyACwAIAAwAC4AMAAzACwAIAAwAC4AMAA0ACwAIAAwAC4AMAAxADUALAAgADAALgAwADEANQAsACAAMAAsACAAMAAsACAAMAAuADAAMAA0ADcALAAgADIANQA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBXAGEAcgBtAFwAIgAsACAAMgA2ACwAIAAwAC4ANwA5ACwAIAAwAC4AMQAsACAAMAAuADQANAAsACAAMAAuADAAMQAsACAAMAAuADAAMQA1ACwAIAAwAC4AMAAyACwAIAAwAC4AMAAzACwAIAAwAC4AMAA0ACwAIAAwAC4AMAAxADUALAAgADAALgAwADEANQAsACAAMAAsACAAMAAsACAAMAAuADAAMAA0ADcALAAgADIANgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBXAGEAcgBtAFwAIgAsACAAMgA3ACwAIAAwAC4AOAAsACAAMAAuADEALAAgADAALgA0ADgALAAgADAALgAwADEALAAgADAALgAwADEANQAsACAAMAAuADAAMgAsACAAMAAuADAAMwAsACAAMAAuADAANAAsACAAMAAuADAAMQA1ACwAIAAwAC4AMAAxADUALAAgADAALAAgADAALAAgADAALgAwADAANAA3ACwAIAAyADcAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVwBhAHIAbQBcACIALAAgAFwAIgBlIjIAOABcACIALAAgADAALgA4ACwAIAAwAC4AMQAsACAAMAAuADUALAAgADAALgAwADEALAAgADAALgAwADEANQAsACAAMAAuADAAMgAsACAAMAAuADAAMwAsACAAMAAuADAANAAsACAAMAAuADAAMQA1ACwAIAAwAC4AMAAxADUALAAgADAALAAgADAALAAgADAALgAwADAANAA3ACwAIAAyADgAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAXAAiACwAIABcACIAXAAiACwAIABcACIAQQBuAGEAZQByAG8AYgBpAGMAIABsAGEAZwBvAG8AbgBcACIALAAgAFwAIgBEAGkAZwBlAHMAdABlAHIAIAAvACAAYwBvAHYAZQByAGUAZAAgAGwAYQBnAG8AbwBuAHMAXAAiACwAIABcACIATABpAHEAdQBpAGQAIABzAHkAcwB0AGUAbQBzAFwAIgAsACAAXAAiAEQAYQBpAGwAeQAgAHMAcAByAGUAYQBkAFwAIgAsACAAXAAiAEMAbwBtAHAAbwBzAHQAaQBuAGcAIAAoAHAAYQBzAHMAaQB2AGUAIAB3AGkAbgBkAHIAbwB3ACkAXAAiACwAIABcACIAUwBvAGwAaQBkACAAcwB0AG8AcgBhAGcAZQBcACIALAAgAFwAIgBQAGkAdAAgAHMAdABvAHIAYQBnAGUAXAAiACwAIABcACIARABlAGUAcAAgAGwAaQB0AHQAZQByAFwAIgAsACAAXAAiAFAAbwB1AGwAdAByAHkAIABtAGEAbgB1AHIAZQAgAHcAaQB0AGgAIABiAGUAZABkAGkAbgBnAFwAIgAsACAAXAAiAFAAbwB1AGwAdAByAHkAIABtAGEAbgB1AHIAZQAgAHcAaQB0AGgAbwB1AHQAIABiAGUAZABkAGkAbgBnAFwAIgAsACAAXAAiAEQAaQByAGUAYwB0ACAAcAByAG8AYwBlAHMAcwBpAG4AZwBcACIALAAgAFwAIgBEAGkAcgBlAGMAdAAgAGEAcABwAGwAaQBjAGEAdABpAG8AbgBcACIALAAgAFwAIgBQAGEAcwB0AHUAcgBlACAAcgBhAG4AZwBlACAAYQBuAGQAIABwAGEAZABkAG8AYwBrAFwAIgAsACAAXAAiAE0AQQBUACAAcgBhAHcAXAAiACAAXABuACAAIAAgACAAIAAgACAAIAB9ACwAIAByACwAIABjACkAXABuACAAIAAgACAAIAAgACkAXABuACAAIAAgACAAKQBcAG4AIAAgACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAE0AQwBGAFQAZQBtAHAAZQByAGEAdAB1AHIAZQBaAG8AbgBlAF8AVgBhAHIAaQBhAHQAaQBvAG4AXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFYAQQBSAEkAQQBUAEkATwBOACAARgBSAE8ATQAgAFMATwBVAFIAQwBFADoAIABBAGQAZABlAGQAIAByAG8AdwAgAG8AZgAgAE4ASQBSACAATQBNAEEAIABkAGUAZgBpAG4AaQB0AGkAbwBuAHMAIAB0AG8AIABhAGkAZAAgAGwAbwBvAGsAdQBwAC4AIABEAHUAcABsAGkAYwBhAHQAZQBkACAAJwBQAG8AdQBsAHQAcgB5ACAAdwBpAHQAaAAgAGEAbgBkACAAdwBpAHQAaABvAHUAdAAgAGwAaQB0AHQAZQByACcAIABjAG8AbAB1AG0AbgAgAHcAaQB0AGgAIABzAGUAcABhAHIAYQB0AGUAIABOAEkAUgAgAGQAZQBmAGkAbgBpAHQAaQBvAG4AcwAgAHQAbwAgAGEAaQBkACAAbABvAG8AawB1AHAALgAgAEEAZABkAGUAZAAgACcATQBBAFQAIAByAGEAdwAnACAAYwBvAGwAdQBtAG4AIAB0AG8AIABhAGwAbABvAHcAIABsAG8AbwBrAHUAcAAgAG8AZgAgAG4AdQBtAGIAZQByAHMALgBcACIAKQA7AFwAbgBcAG4AXABuAFwAbgAvACoAIABcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYATwByAGcAYQBuAGkAYwBGAGUAcgB0AGkAbABpAHMAZQByAEEAbgBkAEMAcgBvAHAAUgBlAHMAaQBkAHUAZQBzAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuACoALwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEUARgBPAHIAZwBhAG4AaQBjAEYAZQByAHQAaQBsAGkAcwBlAHIAQQBuAGQAQwByAG8AcABSAGUAcwBpAGQAdQBlAHMAXwBUAGkAdABsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAEUAbQBpAHMAcwBpAG8AbgAgAGYAYQBjAHQAbwByACAAZgBvAHIAIABvAHIAZwBhAG4AaQBjACAAZgBlAHIAdABpAGwAaQBzAGUAcgAgAGEAbgBkACAAYwByAG8AcAAgAHIAZQBzAGkAZAB1AGUAcwAgAHIAZQB0AHUAcgBuAGUAZAAgAHQAbwAgAHQAaABlACAAcwBvAGkAbABcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAE8AcgBnAGEAbgBpAGMARgBlAHIAdABpAGwAaQBzAGUAcgBBAG4AZABDAHIAbwBwAFIAZQBzAGkAZAB1AGUAcwBfAFYAYQByAGkAYQBiAGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIARQBGAE4AaQAgACYAIABFAEYATgAyAE8AaQBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAE8AcgBnAGEAbgBpAGMARgBlAHIAdABpAGwAaQBzAGUAcgBBAG4AZABDAHIAbwBwAFIAZQBzAGkAZAB1AGUAcwBfAFUAbgBpAHQAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAGsAZwAgAE4AMgBPACAALQAgAE4AIAAvACAAawBnACAATgBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAE8AcgBnAGEAbgBpAGMARgBlAHIAdABpAGwAaQBzAGUAcgBBAG4AZABDAHIAbwBwAFIAZQBzAGkAZAB1AGUAcwBfAFMAbwB1AHIAYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBWAEUARQBSAEcAIAAyADAAMgA2ADoAIABUAGEAYgBsAGUAIABBAC4AMgAuADEALgA0AFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYATwByAGcAYQBuAGkAYwBGAGUAcgB0AGkAbABpAHMAZQByAEEAbgBkAEMAcgBvAHAAUgBlAHMAaQBkAHUAZQBzAF8ATgBJAFIAUgBlAGYAZQByAGUAbgBjAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYATwByAGcAYQBuAGkAYwBGAGUAcgB0AGkAbABpAHMAZQByAEEAbgBkAEMAcgBvAHAAUgBlAHMAaQBkAHUAZQBzAF8ARABhAHQAYQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABNAEEASwBFAEEAUgBSAEEAWQAoADMALAAgADIALAAgAFwAbgAgACAAIAAgACAAIABMAEEATQBCAEQAQQAoAHIALABjACwAIABcAG4AIAAgACAAIAAgACAAIAAgAEkATgBEAEUAWAAoAHsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEMAbABpAG0AYQB0AGUAIAB6AG8AbgBlAFwAIgAsACAAXAAiAEUARgBOAGkAIAAmACAARQBGAE4AMgBPAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBXAGUAdAAgAGMAbABpAG0AYQB0AGUAIAB6AG8AbgBlAFwAIgAsACAAMAAuADAAMAA2ADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEQAcgB5ACAAYwBsAGkAbQBhAHQAZQAgAHoAbwBuAGUAXAAiACwAIAAwAC4AMAAwADUAXABuACAAIAAgACAAIAAgACAAIAB9ACwAIAByACwAIABjACkAXABuACAAIAAgACAAIAAgACkAXABuACAAIAAgACAAKQBcAG4AIAAgACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEUARgBPAHIAZwBhAG4AaQBjAEYAZQByAHQAaQBsAGkAcwBlAHIAQQBuAGQAQwByAG8AcABSAGUAcwBpAGQAdQBlAHMAXwBWAGEAcgBpAGEAdABpAG8AbgBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAXAAiACkAOwBcAG4AXABuAFwAbgBcAG4AXABuAFwAbgBcAG4AXABuAFwAbgBcAG4AXABuAFwAbgBcAG4AXABuAFwAbgBcAG4AXABuACIAfQBdACwAIgBwAHIAbwBqAGUAYwB0AE4AYQBtAGUAcwAiADoAWwAiAEMAbwBtAG0AbwBuAF8ARQBxAHUAYQB0AGkAbwBuAHMALgBDAG8AbQBtAG8AbgBfAEMAbwBuAHYAZQByAHQATgAyAE8AVABvAEMATwAyAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBFAHEAdQBhAHQAaQBvAG4AcwAuAEMAbwBtAG0AbwBuAF8AQwBvAG4AdgBlAHIAdABOADIATwBUAG8AQwBPADIAZQBfAFQAaQB0AGwAZQAiACwAIgBDAG8AbQBtAG8AbgBfAEUAcQB1AGEAdABpAG8AbgBzAC4AQwBvAG0AbQBvAG4AXwBDAG8AbgB2AGUAcgB0AE4AMgBPAFQAbwBDAE8AMgBlAF8AVgBhAHIAaQBhAGIAbABlACIALAAiAEMAbwBtAG0AbwBuAF8ARQBxAHUAYQB0AGkAbwBuAHMALgBDAG8AbQBtAG8AbgBfAEMAbwBuAHYAZQByAHQATgAyAE8AVABvAEMATwAyAGUAXwBVAG4AaQB0ACIALAAiAEMAbwBtAG0AbwBuAF8ARQBxAHUAYQB0AGkAbwBuAHMALgBDAG8AbQBtAG8AbgBfAEMAbwBuAHYAZQByAHQATgAyAE8AVABvAEMATwAyAGUAXwBOAEkAUgBSAGUAZgBlAHIAZQBuAGMAZQAiACwAIgBDAG8AbQBtAG8AbgBfAEUAcQB1AGEAdABpAG8AbgBzAC4AQwBvAG0AbQBvAG4AXwBDAG8AbgB2AGUAcgB0AE4AMgBPAFQAbwBDAE8AMgBlAF8ATABhAHQAZQB4AEUAcQB1AGEAdABpAG8AbgAiACwAIgBDAG8AbQBtAG8AbgBfAEUAcQB1AGEAdABpAG8AbgBzAC4AQwBvAG0AbQBvAG4AXwBDAG8AbgB2AGUAcgB0AE4AMgBPAFQAbwBDAE8AMgBlAF8AQQByAGcAdQBtAGUAbgB0AHMAIgAsACIAQwBvAG0AbQBvAG4AXwBFAHEAdQBhAHQAaQBvAG4AcwAuAEMAbwBtAG0AbwBuAF8AQwBvAG4AdgBlAHIAdABDAEgANABUAG8AQwBPADIAZQAiACwAIgBDAG8AbQBtAG8AbgBfAEUAcQB1AGEAdABpAG8AbgBzAC4AQwBvAG0AbQBvAG4AXwBDAG8AbgB2AGUAcgB0AEMASAA0AFQAbwBDAE8AMgBlAF8AVABpAHQAbABlACIALAAiAEMAbwBtAG0AbwBuAF8ARQBxAHUAYQB0AGkAbwBuAHMALgBDAG8AbQBtAG8AbgBfAEMAbwBuAHYAZQByAHQAQwBIADQAVABvAEMATwAyAGUAXwBWAGEAcgBpAGEAYgBsAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBFAHEAdQBhAHQAaQBvAG4AcwAuAEMAbwBtAG0AbwBuAF8AQwBvAG4AdgBlAHIAdABDAEgANABUAG8AQwBPADIAZQBfAFUAbgBpAHQAIgAsACIAQwBvAG0AbQBvAG4AXwBFAHEAdQBhAHQAaQBvAG4AcwAuAEMAbwBtAG0AbwBuAF8AQwBvAG4AdgBlAHIAdABDAEgANABUAG8AQwBPADIAZQBfAE4ASQBSAFIAZQBmAGUAcgBlAG4AYwBlACIALAAiAEMAbwBtAG0AbwBuAF8ARQBxAHUAYQB0AGkAbwBuAHMALgBDAG8AbQBtAG8AbgBfAEMAbwBuAHYAZQByAHQAQwBIADQAVABvAEMATwAyAGUAXwBMAGEAdABlAHgARQBxAHUAYQB0AGkAbwBuACIALAAiAEMAbwBtAG0AbwBuAF8ARQBxAHUAYQB0AGkAbwBuAHMALgBDAG8AbQBtAG8AbgBfAEMAbwBuAHYAZQByAHQAQwBIADQAVABvAEMATwAyAGUAXwBBAHIAZwB1AG0AZQBuAHQAcwAiACwAIgBDAG8AbQBtAG8AbgBfAEkAbgBwAHUAdABGAHUAbgBjAHQAaQBvAG4AcwAuAFUAdABpAGwAaQB0AHkAXwBHAGUAdABBAHIAcgBhAHkAVABhAGIAbABlAFIAbwB3AFMAdABhAHIAdABOAHUAbQBiAGUAcgAiACwAIgBDAG8AbQBtAG8AbgBfAEkAbgBwAHUAdABGAHUAbgBjAHQAaQBvAG4AcwAuAFUAdABpAGwAaQB0AHkAXwBHAGUAdABBAHIAcgBhAHkAVABhAGIAbABlAEMAbwBsAHUAbQBuAFMAdABhAHIAdABOAHUAbQBiAGUAcgAiACwAIgBDAG8AbQBtAG8AbgBfAEkAbgBwAHUAdABGAHUAbgBjAHQAaQBvAG4AcwAuAFUAdABpAGwAaQB0AHkAXwBEAGkAcwBwAGwAYQB5AEEAcgByAGEAeQBJAG4AVABhAGIAbABlACIALAAiAEMAbwBtAG0AbwBuAF8ASQBuAHAAdQB0AEYAdQBuAGMAdABpAG8AbgBzAC4AVQB0AGkAbABpAHQAeQBfAEwAbwBvAGsAdQBwAFYAYQBsAHUAZQBJAG4AVABhAGIAbABlACIALAAiAEMAbwBtAG0AbwBuAF8ASQBuAHAAdQB0AEYAdQBuAGMAdABpAG8AbgBzAC4AVQB0AGkAbABpAHQAeQBfAEwAbwBvAGsAdQBwAFYAYQBsAHUAZQBJAG4AVABhAGIAbABlAE4AdQBtAGIAZQByACIALAAiAEMAbwBtAG0AbwBuAF8ASQBuAHAAdQB0AEYAdQBuAGMAdABpAG8AbgBzAC4AVQB0AGkAbABpAHQAeQBfAEwAbwBvAGsAdQBwAFYAYQBsAHUAZQBJAG4AVABhAGIAbABlAFQAdwBvAEMAbwBsAHUAbQBuAHMAIgAsACIAQwBvAG0AbQBvAG4AXwBJAG4AcAB1AHQARgB1AG4AYwB0AGkAbwBuAHMALgBVAHQAaQBsAGkAdAB5AF8ATABvAG8AawB1AHAAVgBhAGwAdQBlAEkAbgBUAGEAYgBsAGUATwBuAGUAQwBvAGwAdQBtAG4AQQBuAGQASABlAGEAZABlAHIAIgAsACIAQwBvAG0AbQBvAG4AXwBJAG4AcAB1AHQARgB1AG4AYwB0AGkAbwBuAHMALgBVAHQAaQBsAGkAdAB5AF8AUwBwAGwAaQB0AFMAdAByAGkAbgBnAEkAbgB0AG8AQQByAHIAYQB5ACIALAAiAEMAbwBtAG0AbwBuAF8ASQBuAHAAdQB0AEYAdQBuAGMAdABpAG8AbgBzAC4AVQB0AGkAbABpAHQAeQBfAEcAZQB0AEMAbABpAG0AYQB0AGUAWgBvAG4AZQAiACwAIgBDAG8AbQBtAG8AbgBfAEkAbgBwAHUAdABGAHUAbgBjAHQAaQBvAG4AcwAuAFUAdABpAGwAaQB0AHkAXwBMAG8AbwBrAHUAcABJAHQAZQBtAEYAcgBvAG0ATQBpAG4ATQBhAHgAIgAsACIAQwBvAG0AbQBvAG4AXwBJAG4AcAB1AHQARgB1AG4AYwB0AGkAbwBuAHMALgBVAHQAaQBsAGkAdAB5AF8AUwB1AG0AUQB1AGEAbgB0AGkAdAB5AEYAcgBvAG0AQwByAGkAdABlAHIAaQBhACIALAAiAEMAbwBtAG0AbwBuAF8ASQBuAHAAdQB0AEYAdQBuAGMAdABpAG8AbgBzAC4AZwBlAHQATwB2AGUAcgBsAGEAcABwAGkAbgBnAFIAZQBwAG8AcgB0AGkAbgBnAFAAZQByAGkAbwBkAHMAIgAsACIAQwBvAG0AbQBvAG4AXwBJAG4AcAB1AHQARgB1AG4AYwB0AGkAbwBuAHMALgBVAHQAaQBsAGkAdAB5AF8ARABpAHMAcABsAGEAeQBGAHUAbgBjAHQAaQBvAG4ATgBhAG0AZQAiACwAIgBDAG8AbQBtAG8AbgBfAEkAbgBwAHUAdABGAHUAbgBjAHQAaQBvAG4AcwAuAFUAdABpAGwAaQB0AHkAXwBMAG8AbwBrAHUAcABOADIATwBFAEYARgByAG8AbQBQAHIAbwBkAEkAcgByAGkAZwBhAHQAaQBvAG4AUgBhAGkAbgBmAGEAbABsACIALAAiAEMAbwBtAG0AbwBuAF8ASQBuAHAAdQB0AEYAdQBuAGMAdABpAG8AbgBzAC4AQwBvAG0AbQBvAG4AQwByAG8AcABwAGkAbgBnAF8ARwBlAHQARgByAGEAYwBXAEUAVAAiACwAIgBDAG8AbQBtAG8AbgBfAEkAbgBwAHUAdABGAHUAbgBjAHQAaQBvAG4AcwAuAFUAdABpAGwAaQB0AHkAXwBDAG8AbgB2AGUAcgB0AFMAdABhAHQAZQBDAG8AbQBtAG8AbgBOAGEAbQBlAFQAbwBBAGIAYgByAGUAdgBpAGEAdABpAG8AbgAiACwAIgBDAG8AbQBtAG8AbgBfAEkAbgBwAHUAdABGAHUAbgBjAHQAaQBvAG4AcwAuAFUAdABpAGwAaQB0AHkAXwBTAG8AdQByAGMAZQBIAHkAcABlAHIAbABpAG4AawBEAGkAZgBmAGUAcgBlAG4AdABTAGgAZQBlAHQAIgAsACIAQwBvAG0AbQBvAG4AXwBJAG4AcAB1AHQARgB1AG4AYwB0AGkAbwBuAHMALgBVAHQAaQBsAGkAdAB5AF8AUgBlAHMAdQBsAHQAcwBJAHQAZQBtAEYAcgBvAG0ARQBxAHUAYQB0AGkAbwBuAFQAaQB0AGwAZQBBAG4AZABTAG8AdQByAGMAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGUAbgBzAGkAdAB5AE8AZgBNAGUAdABoAGEAbgBlAF8AVABpAHQAbABlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEQAZQBuAHMAaQB0AHkATwBmAE0AZQB0AGgAYQBuAGUAXwBVAG4AaQB0ACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEQAZQBuAHMAaQB0AHkATwBmAE0AZQB0AGgAYQBuAGUAXwBTAG8AdQByAGMAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGUAbgBzAGkAdAB5AE8AZgBNAGUAdABoAGEAbgBlAF8ARABhAHQAYQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBDAG8AbgB2AGUAcgB0AE4AMgBvAEUAbABlAG0AZQBuAHQAYQBsAFQAbwBNAG8AbABlAGMAdQBsAGEAcgBDAGcAXwBUAGkAdABsAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQwBvAG4AdgBlAHIAdABOADIAbwBFAGwAZQBtAGUAbgB0AGEAbABUAG8ATQBvAGwAZQBjAHUAbABhAHIAQwBnAF8AVgBhAHIAaQBhAGIAbABlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEMAbwBuAHYAZQByAHQATgAyAG8ARQBsAGUAbQBlAG4AdABhAGwAVABvAE0AbwBsAGUAYwB1AGwAYQByAEMAZwBfAFUAbgBpAHQAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQwBvAG4AdgBlAHIAdABOADIAbwBFAGwAZQBtAGUAbgB0AGEAbABUAG8ATQBvAGwAZQBjAHUAbABhAHIAQwBnAF8AUwBvAHUAcgBjAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQwBvAG4AdgBlAHIAdABOADIAbwBFAGwAZQBtAGUAbgB0AGEAbABUAG8ATQBvAGwAZQBjAHUAbABhAHIAQwBnAF8ARABhAHQAYQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBDAG8AbgB2AGUAcgB0AEcAYQBzAEUAbABlAG0AZQBuAHQAYQBsAFQAbwBNAG8AbABlAGMAdQBsAGEAcgBfAFQAaQB0AGwAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBDAG8AbgB2AGUAcgB0AEcAYQBzAEUAbABlAG0AZQBuAHQAYQBsAFQAbwBNAG8AbABlAGMAdQBsAGEAcgBfAFYAYQByAGkAYQBiAGwAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBDAG8AbgB2AGUAcgB0AEcAYQBzAEUAbABlAG0AZQBuAHQAYQBsAFQAbwBNAG8AbABlAGMAdQBsAGEAcgBfAFUAbgBpAHQAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQwBvAG4AdgBlAHIAdABHAGEAcwBFAGwAZQBtAGUAbgB0AGEAbABUAG8ATQBvAGwAZQBjAHUAbABhAHIAXwBTAG8AdQByAGMAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBDAG8AbgB2AGUAcgB0AEcAYQBzAEUAbABlAG0AZQBuAHQAYQBsAFQAbwBNAG8AbABlAGMAdQBsAGEAcgBfAEQAYQB0AGEAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARwBXAFAAXwBUAGkAdABsAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARwBXAFAAXwBWAGEAcgBpAGEAYgBsAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARwBXAFAAXwBVAG4AaQB0ACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEcAVwBQAF8AUwBvAHUAcgBjAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARwBXAFAAXwBEAGEAdABhACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEEAdQBzAHQAcgBhAGwAaQBhAG4AUwB0AGEAdABlAHMAVABlAHIAcgBpAHQAbwByAGkAZQBzAF8AVABpAHQAbABlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEEAdQBzAHQAcgBhAGwAaQBhAG4AUwB0AGEAdABlAHMAVABlAHIAcgBpAHQAbwByAGkAZQBzAF8AVgBhAHIAaQBhAGIAbABlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEEAdQBzAHQAcgBhAGwAaQBhAG4AUwB0AGEAdABlAHMAVABlAHIAcgBpAHQAbwByAGkAZQBzAF8AVQBuAGkAdAAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBBAHUAcwB0AHIAYQBsAGkAYQBuAFMAdABhAHQAZQBzAFQAZQByAHIAaQB0AG8AcgBpAGUAcwBfAFMAbwB1AHIAYwBlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEEAdQBzAHQAcgBhAGwAaQBhAG4AUwB0AGEAdABlAHMAVABlAHIAcgBpAHQAbwByAGkAZQBzAF8ARABhAHQAYQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBXAEEAUwBBADQAQQByAGUAYQBzAF8AVABpAHQAbABlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFcAQQBTAEEANABBAHIAZQBhAHMAXwBWAGEAcgBpAGEAYgBsAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AVwBBAFMAQQA0AEEAcgBlAGEAcwBfAFUAbgBpAHQAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AVwBBAFMAQQA0AEEAcgBlAGEAcwBfAFMAbwB1AHIAYwBlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFcAQQBTAEEANABBAHIAZQBhAHMAXwBEAGEAdABhACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFcAZQB0AEEAbgBkAEQAcgB5AFoAbwBuAGUAcwBfAFQAaQB0AGwAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBXAGUAdABBAG4AZABEAHIAeQBaAG8AbgBlAHMAXwBWAGEAcgBpAGEAYgBsAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AVwBlAHQAQQBuAGQARAByAHkAWgBvAG4AZQBzAF8AVQBuAGkAdAAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBXAGUAdABBAG4AZABEAHIAeQBaAG8AbgBlAHMAXwBTAG8AdQByAGMAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBXAGUAdABBAG4AZABEAHIAeQBaAG8AbgBlAHMAXwBWAGEAcgBpAGEAdABpAG8AbgAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBXAGUAdABBAG4AZABEAHIAeQBaAG8AbgBlAHMAXwBEAGEAdABhACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEMAbABpAG0AYQB0AGUAWgBvAG4AZQBzAF8AVABpAHQAbABlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEMAbABpAG0AYQB0AGUAWgBvAG4AZQBzAF8AVgBhAHIAaQBhAGIAbABlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEMAbABpAG0AYQB0AGUAWgBvAG4AZQBzAF8AVQBuAGkAdAAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBDAGwAaQBtAGEAdABlAFoAbwBuAGUAcwBfAFMAbwB1AHIAYwBlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEMAbABpAG0AYQB0AGUAWgBvAG4AZQBzAF8AVgBhAHIAaQBhAHQAaQBvAG4AIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQwBsAGkAbQBhAHQAZQBaAG8AbgBlAHMAXwBEAGEAdABhACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEMAbABpAG0AYQB0AGUAWgBvAG4AZQBzAF8AQQBwAHAAZQBuAGQAaQBjAGUAcwAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBUAGUAbQBwAGUAcgBhAHQAdQByAGUAWgBvAG4AZQBzAF8AVABpAHQAbABlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFQAZQBtAHAAZQByAGEAdAB1AHIAZQBaAG8AbgBlAHMAXwBWAGEAcgBpAGEAYgBsAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AVABlAG0AcABlAHIAYQB0AHUAcgBlAFoAbwBuAGUAcwBfAFUAbgBpAHQAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AVABlAG0AcABlAHIAYQB0AHUAcgBlAFoAbwBuAGUAcwBfAFMAbwB1AHIAYwBlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFQAZQBtAHAAZQByAGEAdAB1AHIAZQBaAG8AbgBlAHMAXwBWAGEAcgBpAGEAdABpAG8AbgAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBUAGUAbQBwAGUAcgBhAHQAdQByAGUAWgBvAG4AZQBzAF8ARABhAHQAYQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBSAGEAaQBuAGYAYQBsAGwAWgBvAG4AZQBzAF8AVABpAHQAbABlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFIAYQBpAG4AZgBhAGwAbABaAG8AbgBlAHMAXwBWAGEAcgBpAGEAYgBsAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AUgBhAGkAbgBmAGEAbABsAFoAbwBuAGUAcwBfAFUAbgBpAHQAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AUgBhAGkAbgBmAGEAbABsAFoAbwBuAGUAcwBfAFMAbwB1AHIAYwBlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFIAYQBpAG4AZgBhAGwAbABaAG8AbgBlAHMAXwBWAGEAcgBpAGEAdABpAG8AbgAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBSAGEAaQBuAGYAYQBsAGwAWgBvAG4AZQBzAF8ARABhAHQAYQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBMAGUAYQBjAGgAaQBuAGcAWgBvAG4AZQBzAF8AVABpAHQAbABlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEwAZQBhAGMAaABpAG4AZwBaAG8AbgBlAHMAXwBWAGEAcgBpAGEAYgBsAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ATABlAGEAYwBoAGkAbgBnAFoAbwBuAGUAcwBfAFUAbgBpAHQAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ATABlAGEAYwBoAGkAbgBnAFoAbwBuAGUAcwBfAFMAbwB1AHIAYwBlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEwAZQBhAGMAaABpAG4AZwBaAG8AbgBlAHMAXwBWAGEAcgBpAGEAdABpAG8AbgAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBMAGUAYQBjAGgAaQBuAGcAWgBvAG4AZQBzAF8ARABhAHQAYQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAHIAYQBjAFcARQBUAF8AVABpAHQAbABlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAcgBhAGMAVwBFAFQAXwBVAG4AaQB0ACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAcgBhAGMAVwBFAFQAXwBTAG8AdQByAGMAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAHIAYQBjAFcARQBUAF8ATgBJAFIAUgBlAGYAZQByAGUAbgBjAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgByAGEAYwBXAEUAVABfAEQAYQB0AGEAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgByAGEAYwBXAEUAVABfAFYAYQByAGkAYQB0AGkAbwBuACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEQAYQB0AGEAUwBjAG8AcgBlAHMAXwBTAGMAbwBwAGUAMwBfAFQAaQB0AGwAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGEAdABhAFMAYwBvAHIAZQBzAF8AUwBjAG8AcABlADMAXwBWAGEAcgBpAGEAYgBsAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABhAHQAYQBTAGMAbwByAGUAcwBfAFMAYwBvAHAAZQAzAF8AVQBuAGkAdAAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGEAdABhAFMAYwBvAHIAZQBzAF8AUwBjAG8AcABlADMAXwBTAG8AdQByAGMAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGEAdABhAFMAYwBvAHIAZQBzAF8AUwBjAG8AcABlADMAXwBWAGEAcgBpAGEAdABpAG8AbgAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGEAdABhAFMAYwBvAHIAZQBzAF8AUwBjAG8AcABlADMAXwBEAGEAdABhACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAcgBhAGMATABFAEEAQwBIAF8AVABpAHQAbABlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAcgBhAGMATABFAEEAQwBIAF8AVQBuAGkAdAAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAHIAYQBjAEwARQBBAEMASABfAFMAbwB1AHIAYwBlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAcgBhAGMATABFAEEAQwBIAF8ATgBJAFIAUgBlAGYAZQByAGUAbgBjAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgByAGEAYwBMAEUAQQBDAEgAXwBEAGEAdABhACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAcgBhAGMATABFAEEAQwBIAF8AVgBhAHIAaQBhAHQAaQBvAG4AIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAGwAZQBhAGMAaABfAFQAaQB0AGwAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYAbABlAGEAYwBoAF8AVQBuAGkAdAAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYAbABlAGEAYwBoAF8AUwBvAHUAcgBjAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAGwAZQBhAGMAaABfAE4ASQBSAFIAZQBmAGUAcgBlAG4AYwBlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEUARgBsAGUAYQBjAGgAXwBEAGEAdABhACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEUARgBsAGUAYQBjAGgAXwBWAGEAcgBpAGEAdABpAG8AbgAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYATgAyAE8AXwBUAGkAdABsAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAE4AMgBPAF8AVQBuAGkAdAAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYATgAyAE8AXwBTAG8AdQByAGMAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYATgAyAE8AXwBOAEkAUgBSAGUAZgBlAHIAZQBuAGMAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYATgAyAE8AXwBEAGEAdABhACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEUARgBOADIATwBfAFYAYQByAGkAYQB0AGkAbwBuACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAcgBhAGMAVwBFAFQASQByAHIAaQBnAGEAdABpAG8AbgBfAFQAaQB0AGwAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAHIAYQBjAFcARQBUAEkAcgByAGkAZwBhAHQAaQBvAG4AXwBVAG4AaQB0ACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAcgBhAGMAVwBFAFQASQByAHIAaQBnAGEAdABpAG8AbgBfAFMAbwB1AHIAYwBlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAcgBhAGMAVwBFAFQASQByAHIAaQBnAGEAdABpAG8AbgBfAE4ASQBSAFIAZQBmAGUAcgBlAG4AYwBlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAcgBhAGMAVwBFAFQASQByAHIAaQBnAGEAdABpAG8AbgBfAEQAYQB0AGEAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgByAGEAYwBXAEUAVABJAHIAcgBpAGcAYQB0AGkAbwBuAF8AVgBhAHIAaQBhAHQAaQBvAG4AIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAFAAYQBzAHQAdQByAGUAUgBhAG4AZwBlAEEAbgBkAFAAYQBkAGQAbwBjAGsAXwBUAGkAdABsAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAFAAYQBzAHQAdQByAGUAUgBhAG4AZwBlAEEAbgBkAFAAYQBkAGQAbwBjAGsAXwBVAG4AaQB0ACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEUARgBQAGEAcwB0AHUAcgBlAFIAYQBuAGcAZQBBAG4AZABQAGEAZABkAG8AYwBrAF8AUwBvAHUAcgBjAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAFAAYQBzAHQAdQByAGUAUgBhAG4AZwBlAEEAbgBkAFAAYQBkAGQAbwBjAGsAXwBOAEkAUgBSAGUAZgBlAHIAZQBuAGMAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYAUABhAHMAdAB1AHIAZQBSAGEAbgBnAGUAQQBuAGQAUABhAGQAZABvAGMAawBfAEQAYQB0AGEAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAFAAYQBzAHQAdQByAGUAUgBhAG4AZwBlAEEAbgBkAFAAYQBkAGQAbwBjAGsAXwBWAGEAcgBpAGEAdABpAG8AbgAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBNAG8AbgB0AGgAcwBUAG8AUwBlAGEAcwBvAG4AcwBfAFQAaQB0AGwAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBNAG8AbgB0AGgAcwBUAG8AUwBlAGEAcwBvAG4AcwBfAFUAbgBpAHQAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ATQBvAG4AdABoAHMAVABvAFMAZQBhAHMAbwBuAHMAXwBTAG8AdQByAGMAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBNAG8AbgB0AGgAcwBUAG8AUwBlAGEAcwBvAG4AcwBfAE4ASQBSAFIAZQBmAGUAcgBlAG4AYwBlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAE0AbwBuAHQAaABzAFQAbwBTAGUAYQBzAG8AbgBzAF8ARABhAHQAYQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBNAG8AbgB0AGgAcwBUAG8AUwBlAGEAcwBvAG4AcwBfAFYAYQByAGkAYQB0AGkAbwBuACIAXQAsACIAbABvAGMAYQBsAGUAIgA6AHsAIgBsAGkAcwB0AFMAZQBwAGEAcgBhAHQAbwByACIAOgAiACwAIgAsACIAcgBvAHcAUwBlAHAAYQByAGEAdABvAHIAIgA6ACIAOwAiACwAIgBjAG8AbAB1AG0AbgBTAGUAcABhAHIAYQB0AG8AcgAiADoAIgAsACIALAAiAHQAaABvAHUAcwBhAG4AZABzAFMAZQBwAGEAcgBhAHQAbwByACIAOgAiACwAIgAsACIAdABoAG8AdQBzAGEAbgBkAHMAUABvAHMAaQB0AGkAbwBuAHMAIgA6AFsAMwBdACwAIgBkAGUAYwBpAG0AYQBsAFMAZQBwAGEAcgBhAHQAbwByACIAOgAiAC4AIgAsACIAZABhAHQAZQBPAHIAZABlAHIAIgA6ACIARABNAFkAIgAsACIAYwB1AHIAcgBlAG4AYwB5AFMAeQBtAGIAbwBsACIAOgAiACQAIgAsACIAaQBzAEMAdQByAHIAZQBuAGMAeQBTAHkAbQBiAG8AbABMAGUAYQBkACIAOgB0AHIAdQBlACwAIgBpAHMAQwB1AHIAcgBlAG4AYwB5AFMAZQBwAEIAeQBTAHAAYQBjAGUAIgA6AGYAYQBsAHMAZQAsACIAcgBvAHcATABlAHQAdABlAHIAIgA6ACIAUgAiACwAIgBjAG8AbAB1AG0AbgBMAGUAdAB0AGUAcgAiADoAIgBDACIALAAiAHIAYwBMAGUAZgB0AEIAcgBhAGMAawBlAHQAIgA6ACIAWwAiACwAIgByAGMAUgBpAGcAaAB0AEIAcgBhAGMAawBlAHQAIgA6ACIAXQAiACwAIgBzAHQAYQB0AGUAbQBlAG4AdABTAGUAcABhAHIAYQB0AG8AcgAiADoAIgA7ACIALAAiAGwAbwBjAGEAbABlAE4AYQBtAGUAIgA6ACIAZQBuAC0AdQBzACIAfQB9AA==</AFEJSONBlob>
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <TaxCatchAll xmlns="09eef6d6-daa8-4301-8f9f-b1ec38079286" xsi:nil="true"/>
+    <lcf76f155ced4ddcb4097134ff3c332f xmlns="7291119c-fce9-4911-96ae-b800be5dccd8">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    </lcf76f155ced4ddcb4097134ff3c332f>
+  </documentManagement>
+</p:properties>
 </file>
 
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/item4.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x010100ACB660BB23738846A00119B5826AC974" ma:contentTypeVersion="11" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="3e3613359d4ae7f6bda6c57be713f101">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="7291119c-fce9-4911-96ae-b800be5dccd8" xmlns:ns3="09eef6d6-daa8-4301-8f9f-b1ec38079286" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="87491bfad7f11426ad96486e70428b3e" ns2:_="" ns3:_="">
     <xsd:import namespace="7291119c-fce9-4911-96ae-b800be5dccd8"/>
@@ -11498,18 +11871,15 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/item4.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <TaxCatchAll xmlns="09eef6d6-daa8-4301-8f9f-b1ec38079286" xsi:nil="true"/>
-    <lcf76f155ced4ddcb4097134ff3c332f xmlns="7291119c-fce9-4911-96ae-b800be5dccd8">
-      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    </lcf76f155ced4ddcb4097134ff3c332f>
-  </documentManagement>
-</p:properties>
+<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{B6BE249C-20B1-4A62-BBCD-F2A46D88BCAB}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.advancedformulaenvironment.officeapps.live.com/afejsonblob/1.0"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
 
-<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{9A9CF321-0D35-4044-BC72-33748FE2B865}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
@@ -11517,15 +11887,18 @@
 </ds:datastoreItem>
 </file>
 
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{B6BE249C-20B1-4A62-BBCD-F2A46D88BCAB}">
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{CD460F9D-420A-4723-B323-396E4D19EC9B}">
   <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.advancedformulaenvironment.officeapps.live.com/afejsonblob/1.0"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="09eef6d6-daa8-4301-8f9f-b1ec38079286"/>
+    <ds:schemaRef ds:uri="7291119c-fce9-4911-96ae-b800be5dccd8"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>
 
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/itemProps4.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{809E3D44-A88D-4EBF-A307-6B8CE77A3361}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -11542,15 +11915,4 @@
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps4.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{CD460F9D-420A-4723-B323-396E4D19EC9B}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="09eef6d6-daa8-4301-8f9f-b1ec38079286"/>
-    <ds:schemaRef ds:uri="7291119c-fce9-4911-96ae-b800be5dccd8"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
 </file>
--- a/Excel/Enterprises/Enterprise_Dairy_Template_WIP_v01.xlsx
+++ b/Excel/Enterprises/Enterprise_Dairy_Template_WIP_v01.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\htdocs\zneagcrc\GAF-VEERG-Functions\Excel\Enterprises\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BCAFCAC9-00CC-43FA-9BD7-A26133195CDE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8F38A7C5-5CCB-49C0-8FFF-2EA2DD7AADB6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1155" yWindow="465" windowWidth="36255" windowHeight="19140" activeTab="6" xr2:uid="{992023F3-CAB7-4E5B-A348-08D563A0EF40}"/>
+    <workbookView xWindow="615" yWindow="2460" windowWidth="37785" windowHeight="19140" activeTab="1" xr2:uid="{992023F3-CAB7-4E5B-A348-08D563A0EF40}"/>
   </bookViews>
   <sheets>
     <sheet name="Home" sheetId="71" r:id="rId1"/>
@@ -326,32 +326,32 @@
     <definedName name="InputFunctions_PastureBeef.LookupValueFromStateRegionSeason" localSheetId="6">_xlfn.LAMBDA(_xlpm.State,_xlpm.Region,_xlpm.Season,_xlpm.StateArray,_xlpm.RegionArray,_xlpm.SeasonArray,_xlpm.ReturnArray,_xlpm.StateCommonNameArray,_xlpm.StateAbbreviationArray, _xlfn.LET(_xlpm.State, _xlfn.XLOOKUP(_xlpm.State, _xlpm.StateCommonNameArray, _xlpm.StateAbbreviationArray), _xlfn.XLOOKUP(1, (_xlpm.StateArray = _xlpm.State) * (_xlpm.RegionArray = _xlpm.Region), _xlfn.XLOOKUP(_xlpm.Season, _xlpm.SeasonArray, _xlpm.ReturnArray))))</definedName>
     <definedName name="InputFunctions_PastureBeef.LookupValueFromStateRegionSeason" localSheetId="4">_xlfn.LAMBDA(_xlpm.State,_xlpm.Region,_xlpm.Season,_xlpm.StateArray,_xlpm.RegionArray,_xlpm.SeasonArray,_xlpm.ReturnArray,_xlpm.StateCommonNameArray,_xlpm.StateAbbreviationArray, _xlfn.LET(_xlpm.State, _xlfn.XLOOKUP(_xlpm.State, _xlpm.StateCommonNameArray, _xlpm.StateAbbreviationArray), _xlfn.XLOOKUP(1, (_xlpm.StateArray = _xlpm.State) * (_xlpm.RegionArray = _xlpm.Region), _xlfn.XLOOKUP(_xlpm.Season, _xlpm.SeasonArray, _xlpm.ReturnArray))))</definedName>
     <definedName name="InputFunctions_PastureBeef.LookupValueFromStateRegionSeason">_xlfn.LAMBDA(_xlpm.State,_xlpm.Region,_xlpm.Season,_xlpm.StateArray,_xlpm.RegionArray,_xlpm.SeasonArray,_xlpm.ReturnArray,_xlpm.StateCommonNameArray,_xlpm.StateAbbreviationArray, _xlfn.LET(_xlpm.State, _xlfn.XLOOKUP(_xlpm.State, _xlpm.StateCommonNameArray, _xlpm.StateAbbreviationArray), _xlfn.XLOOKUP(1, (_xlpm.StateArray = _xlpm.State) * (_xlpm.RegionArray = _xlpm.Region), _xlfn.XLOOKUP(_xlpm.Season, _xlpm.SeasonArray, _xlpm.ReturnArray))))</definedName>
-    <definedName name="Result_CarbonRemovalsFromPlantings" localSheetId="6">[3]Results!$E$50</definedName>
+    <definedName name="Result_CarbonRemovalsFromPlantings" localSheetId="6">[1]Results!$E$50</definedName>
     <definedName name="Result_CarbonRemovalsFromPlantings">Results!$E$56</definedName>
-    <definedName name="Result_EmissionsForWholeProductionCycle_Method1" localSheetId="6">[3]Results!$E$39</definedName>
-    <definedName name="Result_EmissionsForWholeProductionCycle_Method1" localSheetId="4">[1]Results!$E$42</definedName>
+    <definedName name="Result_EmissionsForWholeProductionCycle_Method1" localSheetId="6">[1]Results!$E$39</definedName>
+    <definedName name="Result_EmissionsForWholeProductionCycle_Method1" localSheetId="4">[2]Results!$E$42</definedName>
     <definedName name="Result_EmissionsForWholeProductionCycle_Method1">Results!$E$45</definedName>
-    <definedName name="Result_EmissionsForWholeProductionCycle_Method2" localSheetId="6">[3]Results!$F$39</definedName>
-    <definedName name="Result_EmissionsForWholeProductionCycle_Method2" localSheetId="4">[1]Results!$F$42</definedName>
+    <definedName name="Result_EmissionsForWholeProductionCycle_Method2" localSheetId="6">[1]Results!$F$39</definedName>
+    <definedName name="Result_EmissionsForWholeProductionCycle_Method2" localSheetId="4">[2]Results!$F$42</definedName>
     <definedName name="Result_EmissionsForWholeProductionCycle_Method2">Results!$F$45</definedName>
-    <definedName name="Result_Enterprise_Method1" localSheetId="6">[3]Results!$H$25</definedName>
-    <definedName name="Result_Enterprise_Method1" localSheetId="4">[1]Results!$H$28</definedName>
+    <definedName name="Result_Enterprise_Method1" localSheetId="6">[1]Results!$H$25</definedName>
+    <definedName name="Result_Enterprise_Method1" localSheetId="4">[2]Results!$H$28</definedName>
     <definedName name="Result_Enterprise_Method1">Results!$H$31</definedName>
-    <definedName name="Result_Enterprise_Method2" localSheetId="6">[3]Results!$I$25</definedName>
-    <definedName name="Result_Enterprise_Method2" localSheetId="4">[1]Results!$I$28</definedName>
+    <definedName name="Result_Enterprise_Method2" localSheetId="6">[1]Results!$I$25</definedName>
+    <definedName name="Result_Enterprise_Method2" localSheetId="4">[2]Results!$I$28</definedName>
     <definedName name="Result_Enterprise_Method2">Results!$I$31</definedName>
-    <definedName name="Result_NetEmissions_Method1" localSheetId="6">[3]Results!$E$56</definedName>
-    <definedName name="Result_NetEmissions_Method1" localSheetId="4">[1]Results!$E$59</definedName>
+    <definedName name="Result_NetEmissions_Method1" localSheetId="6">[1]Results!$E$56</definedName>
+    <definedName name="Result_NetEmissions_Method1" localSheetId="4">[2]Results!$E$59</definedName>
     <definedName name="Result_NetEmissions_Method1">Results!$E$62</definedName>
-    <definedName name="Result_NetEmissions_Method2" localSheetId="6">[3]Results!$F$56</definedName>
-    <definedName name="Result_NetEmissions_Method2" localSheetId="4">[1]Results!$F$59</definedName>
+    <definedName name="Result_NetEmissions_Method2" localSheetId="6">[1]Results!$F$56</definedName>
+    <definedName name="Result_NetEmissions_Method2" localSheetId="4">[2]Results!$F$59</definedName>
     <definedName name="Result_NetEmissions_Method2">Results!$F$62</definedName>
-    <definedName name="X_Cell_Enterprise_PercentIncomeFromGrain">'[3]Input - Enterprise'!$E$32</definedName>
-    <definedName name="X_Cell_Enterprise_ProductionTimeframeEnd" localSheetId="6">'[3]Input - Enterprise'!$E$19</definedName>
-    <definedName name="X_Cell_Enterprise_ProductionTimeframeEnd" localSheetId="4">'[1]Input - Enterprise'!$E$19</definedName>
+    <definedName name="X_Cell_Enterprise_PercentIncomeFromGrain">'[1]Input - Enterprise'!$E$32</definedName>
+    <definedName name="X_Cell_Enterprise_ProductionTimeframeEnd" localSheetId="6">'[1]Input - Enterprise'!$E$19</definedName>
+    <definedName name="X_Cell_Enterprise_ProductionTimeframeEnd" localSheetId="4">'[2]Input - Enterprise'!$E$19</definedName>
     <definedName name="X_Cell_Enterprise_ProductionTimeframeEnd">'Input - Enterprise'!$E$19</definedName>
-    <definedName name="X_Cell_Enterprise_ProductionTimeframeStart" localSheetId="6">'[3]Input - Enterprise'!$E$18</definedName>
-    <definedName name="X_Cell_Enterprise_ProductionTimeframeStart" localSheetId="4">'[1]Input - Enterprise'!$E$18</definedName>
+    <definedName name="X_Cell_Enterprise_ProductionTimeframeStart" localSheetId="6">'[1]Input - Enterprise'!$E$18</definedName>
+    <definedName name="X_Cell_Enterprise_ProductionTimeframeStart" localSheetId="4">'[2]Input - Enterprise'!$E$18</definedName>
     <definedName name="X_Cell_Enterprise_ProductionTimeframeStart">'Input - Enterprise'!$E$18</definedName>
     <definedName name="X_Cell_Fertiliser_AreaUnderCropping">'Input - Fert Prod System'!$E$10</definedName>
     <definedName name="X_Cell_Fertiliser_CropType">'Input - Fert Prod System'!$E$8</definedName>
@@ -369,8 +369,8 @@
     <definedName name="X_Cell_Site_RainfallZone">'Input - Site'!$E$19</definedName>
     <definedName name="X_Cell_Site_Region">'Input - Site'!$E$11</definedName>
     <definedName name="X_Cell_Site_ReportingEntityName">'Input - Enterprise'!$E$8</definedName>
-    <definedName name="X_Cell_Site_StartDate" localSheetId="6">'[3]Input - Enterprise'!$E$12</definedName>
-    <definedName name="X_Cell_Site_StartDate" localSheetId="4">'[1]Input - Enterprise'!$E$12</definedName>
+    <definedName name="X_Cell_Site_StartDate" localSheetId="6">'[1]Input - Enterprise'!$E$12</definedName>
+    <definedName name="X_Cell_Site_StartDate" localSheetId="4">'[2]Input - Enterprise'!$E$12</definedName>
     <definedName name="X_Cell_Site_StartDate">'Input - Enterprise'!$E$12</definedName>
     <definedName name="X_Cell_Site_State">'Input - Site'!$E$10</definedName>
     <definedName name="X_Cell_Site_TemperatureZone">'Input - Site'!$E$22</definedName>
@@ -3421,98 +3421,6 @@
       <sheetName val="Input - Site"/>
       <sheetName val="Input - Enterprise"/>
       <sheetName val="Input - Fert Prod System"/>
-      <sheetName val="Input - Livestock sales"/>
-      <sheetName val="Constants - Common"/>
-    </sheetNames>
-    <sheetDataSet>
-      <sheetData sheetId="0"/>
-      <sheetData sheetId="1">
-        <row r="28">
-          <cell r="H28" t="e">
-            <v>#NAME?</v>
-          </cell>
-          <cell r="I28" t="e">
-            <v>#NAME?</v>
-          </cell>
-        </row>
-        <row r="42">
-          <cell r="E42" t="e">
-            <v>#NAME?</v>
-          </cell>
-          <cell r="F42" t="e">
-            <v>#NAME?</v>
-          </cell>
-        </row>
-        <row r="59">
-          <cell r="E59" t="e">
-            <v>#NAME?</v>
-          </cell>
-          <cell r="F59" t="e">
-            <v>#NAME?</v>
-          </cell>
-        </row>
-      </sheetData>
-      <sheetData sheetId="2"/>
-      <sheetData sheetId="3">
-        <row r="12">
-          <cell r="E12">
-            <v>45292</v>
-          </cell>
-        </row>
-        <row r="18">
-          <cell r="E18">
-            <v>45231</v>
-          </cell>
-        </row>
-        <row r="19">
-          <cell r="E19">
-            <v>45747</v>
-          </cell>
-        </row>
-      </sheetData>
-      <sheetData sheetId="4"/>
-      <sheetData sheetId="5"/>
-      <sheetData sheetId="6"/>
-    </sheetDataSet>
-  </externalBook>
-</externalLink>
-</file>
-
-<file path=xl/externalLinks/externalLink2.xml><?xml version="1.0" encoding="utf-8"?>
-<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
-  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
-    <xxl21:alternateUrls>
-      <xxl21:absoluteUrl r:id="rId2"/>
-      <xxl21:relativeUrl r:id="rId3"/>
-    </xxl21:alternateUrls>
-    <sheetNames>
-      <sheetName val="Home"/>
-      <sheetName val="Input - Data quality"/>
-      <sheetName val="Constants - Common"/>
-      <sheetName val="Acknowledgements"/>
-    </sheetNames>
-    <sheetDataSet>
-      <sheetData sheetId="0"/>
-      <sheetData sheetId="1"/>
-      <sheetData sheetId="2"/>
-      <sheetData sheetId="3"/>
-    </sheetDataSet>
-  </externalBook>
-</externalLink>
-</file>
-
-<file path=xl/externalLinks/externalLink3.xml><?xml version="1.0" encoding="utf-8"?>
-<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
-  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
-    <xxl21:alternateUrls>
-      <xxl21:absoluteUrl r:id="rId2"/>
-    </xxl21:alternateUrls>
-    <sheetNames>
-      <sheetName val="Home"/>
-      <sheetName val="Results"/>
-      <sheetName val="Input - Site"/>
-      <sheetName val="Input - Enterprise"/>
-      <sheetName val="Input - Fert Prod System"/>
       <sheetName val="Input - Data quality"/>
       <sheetName val="Constants - Common"/>
     </sheetNames>
@@ -3575,6 +3483,98 @@
       <sheetData sheetId="4"/>
       <sheetData sheetId="5"/>
       <sheetData sheetId="6"/>
+    </sheetDataSet>
+  </externalBook>
+</externalLink>
+</file>
+
+<file path=xl/externalLinks/externalLink2.xml><?xml version="1.0" encoding="utf-8"?>
+<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
+  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
+    <xxl21:alternateUrls>
+      <xxl21:absoluteUrl r:id="rId2"/>
+    </xxl21:alternateUrls>
+    <sheetNames>
+      <sheetName val="Home"/>
+      <sheetName val="Results"/>
+      <sheetName val="Input - Site"/>
+      <sheetName val="Input - Enterprise"/>
+      <sheetName val="Input - Fert Prod System"/>
+      <sheetName val="Input - Livestock sales"/>
+      <sheetName val="Constants - Common"/>
+    </sheetNames>
+    <sheetDataSet>
+      <sheetData sheetId="0"/>
+      <sheetData sheetId="1">
+        <row r="28">
+          <cell r="H28" t="e">
+            <v>#NAME?</v>
+          </cell>
+          <cell r="I28" t="e">
+            <v>#NAME?</v>
+          </cell>
+        </row>
+        <row r="42">
+          <cell r="E42" t="e">
+            <v>#NAME?</v>
+          </cell>
+          <cell r="F42" t="e">
+            <v>#NAME?</v>
+          </cell>
+        </row>
+        <row r="59">
+          <cell r="E59" t="e">
+            <v>#NAME?</v>
+          </cell>
+          <cell r="F59" t="e">
+            <v>#NAME?</v>
+          </cell>
+        </row>
+      </sheetData>
+      <sheetData sheetId="2"/>
+      <sheetData sheetId="3">
+        <row r="12">
+          <cell r="E12">
+            <v>45292</v>
+          </cell>
+        </row>
+        <row r="18">
+          <cell r="E18">
+            <v>45231</v>
+          </cell>
+        </row>
+        <row r="19">
+          <cell r="E19">
+            <v>45747</v>
+          </cell>
+        </row>
+      </sheetData>
+      <sheetData sheetId="4"/>
+      <sheetData sheetId="5"/>
+      <sheetData sheetId="6"/>
+    </sheetDataSet>
+  </externalBook>
+</externalLink>
+</file>
+
+<file path=xl/externalLinks/externalLink3.xml><?xml version="1.0" encoding="utf-8"?>
+<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
+  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
+    <xxl21:alternateUrls>
+      <xxl21:absoluteUrl r:id="rId2"/>
+      <xxl21:relativeUrl r:id="rId3"/>
+    </xxl21:alternateUrls>
+    <sheetNames>
+      <sheetName val="Home"/>
+      <sheetName val="Input - Data quality"/>
+      <sheetName val="Constants - Common"/>
+      <sheetName val="Acknowledgements"/>
+    </sheetNames>
+    <sheetDataSet>
+      <sheetData sheetId="0"/>
+      <sheetData sheetId="1"/>
+      <sheetData sheetId="2"/>
+      <sheetData sheetId="3"/>
     </sheetDataSet>
   </externalBook>
 </externalLink>
@@ -3943,7 +3943,7 @@
     <tableColumn id="5" xr3:uid="{28F01E09-BECE-484C-81F3-93DFF53DC900}" name="Notes"/>
     <tableColumn id="6" xr3:uid="{DDF62FEF-8F18-4588-8C64-94585E6BFF74}" name="Evidence files"/>
     <tableColumn id="7" xr3:uid="{05442818-31FF-4B7D-911F-5A30BA48670D}" name="Score" dataCellStyle="Input number general calculated">
-      <calculatedColumnFormula>_xlfn.XLOOKUP(Table_Input_DataQuality[[#This Row],[Temporal representativeness]],[2]!Table_SourceData_DataQuality_TemporalRepresentativeness[ID],[2]!Table_SourceData_DataQuality_TemporalRepresentativeness[Score])+_xlfn.XLOOKUP(Table_Input_DataQuality[[#This Row],[Spatial resolution]],[2]!Table_SourceData_DataQuality_SpatialRepresentativeness[ID],[2]!Table_SourceData_DataQuality_SpatialRepresentativeness[Score])+_xlfn.XLOOKUP(Table_Input_DataQuality[[#This Row],[Sample size]],[2]!Table_SourceData_DataQuality_SampleSize[ID],[2]!Table_SourceData_DataQuality_SampleSize[Score])</calculatedColumnFormula>
+      <calculatedColumnFormula>_xlfn.XLOOKUP(Table_Input_DataQuality[[#This Row],[Temporal representativeness]],[3]!Table_SourceData_DataQuality_TemporalRepresentativeness[ID],[3]!Table_SourceData_DataQuality_TemporalRepresentativeness[Score])+_xlfn.XLOOKUP(Table_Input_DataQuality[[#This Row],[Spatial resolution]],[3]!Table_SourceData_DataQuality_SpatialRepresentativeness[ID],[3]!Table_SourceData_DataQuality_SpatialRepresentativeness[Score])+_xlfn.XLOOKUP(Table_Input_DataQuality[[#This Row],[Sample size]],[3]!Table_SourceData_DataQuality_SampleSize[ID],[3]!Table_SourceData_DataQuality_SampleSize[Score])</calculatedColumnFormula>
     </tableColumn>
   </tableColumns>
   <tableStyleInfo name="Editable table" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
@@ -5399,11 +5399,11 @@
         <v>01 Jan 2023 to 31 Dec 2023</v>
       </c>
       <c r="E40" s="86" t="str">
-        <f>IF(ISBLANK($D40), "", IF(ISNUMBER(SEARCH("reporting", $D40)), Result_Enterprise_Method1, "Enter value"))</f>
+        <f>IF(ISBLANK($D40), 0, IF(ISNUMBER(SEARCH("reporting", $D40)), Result_Enterprise_Method1, "Enter value"))</f>
         <v>Enter value</v>
       </c>
       <c r="F40" s="86" t="str">
-        <f>IF(ISBLANK($D40), "", IF(ISNUMBER(SEARCH("reporting", $D40)), Result_Enterprise_Method2, "Enter value"))</f>
+        <f>IF(ISBLANK($D40), 0, IF(ISNUMBER(SEARCH("reporting", $D40)), Result_Enterprise_Method2, "Enter value"))</f>
         <v>Enter value</v>
       </c>
       <c r="G40" s="16" t="s">
@@ -5420,11 +5420,11 @@
         <v>01 Jan 2024 to 31 Dec 2024 (This reporting cycle)</v>
       </c>
       <c r="E41" s="86" t="e">
-        <f>IF(ISBLANK($D41), "", IF(ISNUMBER(SEARCH("reporting", $D41)), Result_Enterprise_Method1, "Enter value"))</f>
+        <f>IF(ISBLANK($D41), 0, IF(ISNUMBER(SEARCH("reporting", $D41)), Result_Enterprise_Method1, "Enter value"))</f>
         <v>#NAME?</v>
       </c>
       <c r="F41" s="86" t="e">
-        <f>IF(ISBLANK($D41), "", IF(ISNUMBER(SEARCH("reporting", $D41)), Result_Enterprise_Method2, "Enter value"))</f>
+        <f>IF(ISBLANK($D41), 0, IF(ISNUMBER(SEARCH("reporting", $D41)), Result_Enterprise_Method2, "Enter value"))</f>
         <v>#NAME?</v>
       </c>
       <c r="G41" s="16" t="s">
@@ -5441,11 +5441,11 @@
         <v>01 Jan 2025 to 31 Dec 2025</v>
       </c>
       <c r="E42" s="86" t="str">
-        <f>IF(ISBLANK($D42), "", IF(ISNUMBER(SEARCH("reporting", $D42)), Result_Enterprise_Method1, "Enter value"))</f>
+        <f>IF(ISBLANK($D42), 0, IF(ISNUMBER(SEARCH("reporting", $D42)), Result_Enterprise_Method1, "Enter value"))</f>
         <v>Enter value</v>
       </c>
       <c r="F42" s="86" t="str">
-        <f>IF(ISBLANK($D42), "", IF(ISNUMBER(SEARCH("reporting", $D42)), Result_Enterprise_Method2, "Enter value"))</f>
+        <f>IF(ISBLANK($D42), 0, IF(ISNUMBER(SEARCH("reporting", $D42)), Result_Enterprise_Method2, "Enter value"))</f>
         <v>Enter value</v>
       </c>
       <c r="G42" s="16" t="s">
@@ -5459,13 +5459,13 @@
     <row r="43" spans="3:11" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C43" s="9"/>
       <c r="D43" s="1"/>
-      <c r="E43" s="86" t="str">
-        <f>IF(ISBLANK($D43), "", IF(ISNUMBER(SEARCH("reporting", $D43)), Result_Enterprise_Method1, "Enter value"))</f>
-        <v/>
-      </c>
-      <c r="F43" s="86" t="str">
-        <f>IF(ISBLANK($D43), "", IF(ISNUMBER(SEARCH("reporting", $D43)), Result_Enterprise_Method2, "Enter value"))</f>
-        <v/>
+      <c r="E43" s="86">
+        <f>IF(ISBLANK($D43), 0, IF(ISNUMBER(SEARCH("reporting", $D43)), Result_Enterprise_Method1, "Enter value"))</f>
+        <v>0</v>
+      </c>
+      <c r="F43" s="86">
+        <f>IF(ISBLANK($D43), 0, IF(ISNUMBER(SEARCH("reporting", $D43)), Result_Enterprise_Method2, "Enter value"))</f>
+        <v>0</v>
       </c>
       <c r="G43" s="16" t="s">
         <v>8</v>
@@ -5478,13 +5478,13 @@
     <row r="44" spans="3:11" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C44" s="9"/>
       <c r="D44" s="88"/>
-      <c r="E44" s="86" t="str">
-        <f>IF(ISBLANK($D44), "", IF(ISNUMBER(SEARCH("reporting", $D44)), Result_Enterprise_Method1, "Enter value"))</f>
-        <v/>
-      </c>
-      <c r="F44" s="86" t="str">
-        <f>IF(ISBLANK($D44), "", IF(ISNUMBER(SEARCH("reporting", $D44)), Result_Enterprise_Method2, "Enter value"))</f>
-        <v/>
+      <c r="E44" s="86">
+        <f>IF(ISBLANK($D44), 0, IF(ISNUMBER(SEARCH("reporting", $D44)), Result_Enterprise_Method1, "Enter value"))</f>
+        <v>0</v>
+      </c>
+      <c r="F44" s="86">
+        <f>IF(ISBLANK($D44), 0, IF(ISNUMBER(SEARCH("reporting", $D44)), Result_Enterprise_Method2, "Enter value"))</f>
+        <v>0</v>
       </c>
       <c r="G44" s="16" t="s">
         <v>8</v>
@@ -5581,7 +5581,7 @@
         <v>01 Jan 2023 to 31 Dec 2023</v>
       </c>
       <c r="E51" s="86" t="str">
-        <f>IF(ISBLANK(D51), "", "Enter value")</f>
+        <f>IF(ISBLANK(D51), 0, "Enter value")</f>
         <v>Enter value</v>
       </c>
       <c r="F51" s="16" t="s">
@@ -5599,7 +5599,7 @@
         <v>01 Jan 2024 to 31 Dec 2024 (This reporting cycle)</v>
       </c>
       <c r="E52" s="86" t="str">
-        <f t="shared" ref="E52:E55" si="1">IF(ISBLANK(D52), "", "Enter value")</f>
+        <f t="shared" ref="E52:E55" si="1">IF(ISBLANK(D52), 0, "Enter value")</f>
         <v>Enter value</v>
       </c>
       <c r="F52" s="16" t="s">
@@ -5632,9 +5632,9 @@
     <row r="54" spans="3:11" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C54" s="9"/>
       <c r="D54" s="1"/>
-      <c r="E54" s="86" t="str">
+      <c r="E54" s="86">
         <f t="shared" si="1"/>
-        <v/>
+        <v>0</v>
       </c>
       <c r="F54" s="16" t="s">
         <v>133</v>
@@ -5648,9 +5648,9 @@
     <row r="55" spans="3:11" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C55" s="9"/>
       <c r="D55" s="1"/>
-      <c r="E55" s="86" t="str">
+      <c r="E55" s="86">
         <f t="shared" si="1"/>
-        <v/>
+        <v>0</v>
       </c>
       <c r="F55" s="16" t="s">
         <v>133</v>
@@ -5667,7 +5667,7 @@
         <v>135</v>
       </c>
       <c r="E56" s="20">
-        <f>SUM(E51:E54)</f>
+        <f>SUM(E51:E55)</f>
         <v>0</v>
       </c>
       <c r="F56" s="1"/>
@@ -7634,7 +7634,7 @@
       <c r="H7" s="96"/>
       <c r="I7" s="96"/>
       <c r="J7" s="26">
-        <f>_xlfn.XLOOKUP(Table_Input_DataQuality[[#This Row],[Temporal representativeness]],[2]!Table_SourceData_DataQuality_TemporalRepresentativeness[ID],[2]!Table_SourceData_DataQuality_TemporalRepresentativeness[Score])+_xlfn.XLOOKUP(Table_Input_DataQuality[[#This Row],[Spatial resolution]],[2]!Table_SourceData_DataQuality_SpatialRepresentativeness[ID],[2]!Table_SourceData_DataQuality_SpatialRepresentativeness[Score])+_xlfn.XLOOKUP(Table_Input_DataQuality[[#This Row],[Sample size]],[2]!Table_SourceData_DataQuality_SampleSize[ID],[2]!Table_SourceData_DataQuality_SampleSize[Score])</f>
+        <f>_xlfn.XLOOKUP(Table_Input_DataQuality[[#This Row],[Temporal representativeness]],[3]!Table_SourceData_DataQuality_TemporalRepresentativeness[ID],[3]!Table_SourceData_DataQuality_TemporalRepresentativeness[Score])+_xlfn.XLOOKUP(Table_Input_DataQuality[[#This Row],[Spatial resolution]],[3]!Table_SourceData_DataQuality_SpatialRepresentativeness[ID],[3]!Table_SourceData_DataQuality_SpatialRepresentativeness[Score])+_xlfn.XLOOKUP(Table_Input_DataQuality[[#This Row],[Sample size]],[3]!Table_SourceData_DataQuality_SampleSize[ID],[3]!Table_SourceData_DataQuality_SampleSize[Score])</f>
         <v>12</v>
       </c>
     </row>
@@ -11653,30 +11653,6 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<AFEJSONBlob xmlns="http://schemas.advancedformulaenvironment.officeapps.live.com/afejsonblob/1.0">ewAiAHMAYwBoAGUAbQBhACIAOgAiAGgAdAB0AHAAOgAvAC8AcwBjAGgAZQBtAGEAcwAuAGEAZAB2AGEAbgBjAGUAZABmAG8AcgBtAHUAbABhAGUAbgB2AGkAcgBvAG4AbQBlAG4AdAAuAG8AZgBmAGkAYwBlAGEAcABwAHMALgBsAGkAdgBlAC4AYwBvAG0ALwBhAGYAZQBwAHIAbwBqAGUAYwB0AHMALwAwAC4AMgAiACwAIgBmAGkAbABlAHMAIgA6AFsAewAiAHAAYQB0AGgAIgA6ACIALwBwAHIAbwBqAGUAYwB0AHMALwBXAG8AcgBrAGIAbwBvAGsAIgAsACIAdABlAHgAdAAiADoAIgAvAC8AIAAtAC0ALQAgAFcAbwByAGsAYgBvAG8AawAgAG0AbwBkAHUAbABlACAALQAtAC0AXABuAC8ALwAgAEEAIABmAGkAbABlACAAbwBmACAAbgBhAG0AZQAgAGQAZQBmAGkAbgBpAHQAaQBvAG4AcwAgAG8AZgAgAHQAaABlACAAZgBvAHIAbQA6AFwAbgAvAC8AIAAgACAAIABuAGEAbQBlACAAPQAgAGQAZQBmAGkAbgBpAHQAaQBvAG4AOwBcAG4AIgB9ACwAewAiAHAAYQB0AGgAIgA6ACIALwBwAHIAbwBqAGUAYwB0AHMALwBDAG8AbQBtAG8AbgBfAEUAcQB1AGEAdABpAG8AbgBzACIALAAiAHQAZQB4AHQAIgA6ACIAXABuAC8AKgAgAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuAEMAbwBtAG0AbwBuAF8AQwBvAG4AdgBlAHIAdABOADIATwBUAG8AQwBPADIAZQBcAG4AQwBvAG4AdgBlAHIAdAAgAG4AaQB0AHIAbwB1AHMAIABvAHgAaQBkAGUAIABlAG0AaQBzAHMAaQBvAG4AcwAgAHQAbwAgAGMAYQByAGIAbwBuACAAZABpAG8AeABpAGQAZQAgAGUAcQB1AGkAdgBhAGwAZQBuAHQAIABlAG0AaQBzAHMAaQBvAG4AcwBcAG4ARQBOADIATwAgAEMATwAyAGUAXABuAHQAIABDAE8AMgBlAFwAbgBFAE4AMgBPADoAIABuAGkAdAByAG8AdQBzACAAbwB4AGkAZABlACAAZQBtAGkAcwBzAGkAbwBuAHMAIAAoAHQAIABOADIATwApAFwAbgBHAFcAUABOADIATwA6ACAAZwBsAG8AYgBhAGwAIAB3AGEAcgBtAGkAbgBnACAAcABvAHQAZQBuAHQAaQBhAGwAIABmAG8AcgAgAG4AaQB0AHIAbwB1AHMAIABvAHgAaQBkAGUAIAAoAHQAIABDAE8AMgAtAGUAIAAvACAAdAAgAE4AMgBPACkAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AKgAvAFwAbgBcAG4AXABuAEMAbwBtAG0AbwBuAF8AQwBvAG4AdgBlAHIAdABOADIATwBUAG8AQwBPADIAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABFAF8ATgAyAE8ALAAgAEcAVwBQAF8ATgAyAE8ALABcAG4AIAAgACAAIABFAF8ATgAyAE8AIAAqACAARwBXAFAAXwBOADIATwBcAG4AIAAgACkAXABuADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAEMAbwBuAHYAZQByAHQATgAyAE8AVABvAEMATwAyAGUAXwBUAGkAdABsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAEMAbwBuAHYAZQByAHQAIABuAGkAdAByAG8AdQBzACAAbwB4AGkAZABlACAAZQBtAGkAcwBzAGkAbwBuAHMAIAB0AG8AIABjAGEAcgBiAG8AbgAgAGQAaQBvAHgAaQBkAGUAIABlAHEAdQBpAHYAYQBsAGUAbgB0ACAAZQBtAGkAcwBzAGkAbwBuAHMAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AQwBvAG4AdgBlAHIAdABOADIATwBUAG8AQwBPADIAZQBfAFYAYQByAGkAYQBiAGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIARQBOADIATwAgAEMATwAyAGUAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AQwBvAG4AdgBlAHIAdABOADIATwBUAG8AQwBPADIAZQBfAFUAbgBpAHQAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAHQAIABDAE8AMgBlAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAEMAbwBuAHYAZQByAHQATgAyAE8AVABvAEMATwAyAGUAXwBOAEkAUgBSAGUAZgBlAHIAZQBuAGMAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AQwBvAG4AdgBlAHIAdABOADIATwBUAG8AQwBPADIAZQBfAEwAYQB0AGUAeABFAHEAdQBhAHQAaQBvAG4AXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAEMATwAyAF8AZQAgAD0AIABFAF8AewBOADIATwB9ACAAXABcAHQAaQBtAGUAcwAgAEcAVwBQAF8AewBOADIATwB9AFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAEMAbwBuAHYAZQByAHQATgAyAE8AVABvAEMATwAyAGUAXwBBAHIAZwB1AG0AZQBuAHQAcwBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABNAEEASwBFAEEAUgBSAEEAWQAoADIALAAgADIALAAgAFwAbgAgACAAIAAgACAAIABMAEEATQBCAEQAQQAoAHIALABjACwAIABcAG4AIAAgACAAIAAgACAAIAAgAEkATgBEAEUAWAAoAHsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEUATgAyAE8AXAAiACwAXAAiAE4AaQB0AHIAbwB1AHMAIABvAHgAaQBkAGUAIABlAG0AaQBzAHMAaQBvAG4AcwAgACgAdAAgAE4AMgBPACkAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEcAVwBQAE4AMgBPAFwAIgAsAFwAIgBHAGwAbwBiAGEAbAAgAHcAYQByAG0AaQBuAGcAIABwAG8AdABlAG4AdABpAGEAbAAgAGYAbwByACAAbgBpAHQAcgBvAHUAcwAgAG8AeABpAGQAZQAgACgAdAAgAEMATwAyAC0AZQAgAC8AIAB0ACAATgAyAE8AKQBcACIAXABuACAAIAAgACAAIAAgACAAIAB9ACwAIAByACwAIABjACkAXABuACAAIAAgACAAIAAgACkAXABuACAAIAAgACAAKQBcAG4AIAAgACkAOwBcAG4AXABuAC8AKgAgAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuAEMAbwBtAG0AbwBuAF8AQwBvAG4AdgBlAHIAdABDAEgANABUAG8AQwBPADIAZQBcAG4AQwBvAG4AdgBlAHIAdAAgAG0AZQB0AGgAYQBuAGUAIABlAG0AaQBzAHMAaQBvAG4AcwAgAHQAbwAgAGMAYQByAGIAbwBuACAAZABpAG8AeABpAGQAZQAgAGUAcQB1AGkAdgBhAGwAZQBuAHQAIABlAG0AaQBzAHMAaQBvAG4AcwBcAG4ARQBDAEgANAAgAEMATwAyAGUAXABuAHQAIABDAE8AMgBlAFwAbgBFAEMASAA0ADoAIABtAGUAdABoAGEAbgBlACAAZQBtAGkAcwBzAGkAbwBuAHMAIAAoAHQAIABDAEgANAApAFwAbgBHAFcAUABDAEgANAA6ACAAZwBsAG8AYgBhAGwAIAB3AGEAcgBtAGkAbgBnACAAcABvAHQAZQBuAHQAaQBhAGwAIABmAG8AcgAgAG0AZQB0AGgAYQBuAGUAIAAoAHQAIABDAE8AMgAtAGUAIAAvACAAdAAgAEMASAA0ACkAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AKgAvAFwAbgBcAG4AXABuAEMAbwBtAG0AbwBuAF8AQwBvAG4AdgBlAHIAdABDAEgANABUAG8AQwBPADIAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABFAF8AQwBIADQALAAgAEcAVwBQAF8AQwBIADQALABcAG4AIAAgACAAIABFAF8AQwBIADQAIAAqACAARwBXAFAAXwBDAEgANABcAG4AIAAgACkAXABuADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAEMAbwBuAHYAZQByAHQAQwBIADQAVABvAEMATwAyAGUAXwBUAGkAdABsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAEMAbwBuAHYAZQByAHQAIABtAGUAdABoAGEAbgBlACAAZQBtAGkAcwBzAGkAbwBuAHMAIAB0AG8AIABjAGEAcgBiAG8AbgAgAGQAaQBvAHgAaQBkAGUAIABlAHEAdQBpAHYAYQBsAGUAbgB0ACAAZQBtAGkAcwBzAGkAbwBuAHMAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AQwBvAG4AdgBlAHIAdABDAEgANABUAG8AQwBPADIAZQBfAFYAYQByAGkAYQBiAGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIARQBDAEgANAAgAEMATwAyAGUAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AQwBvAG4AdgBlAHIAdABDAEgANABUAG8AQwBPADIAZQBfAFUAbgBpAHQAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAHQAIABDAE8AMgBlAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAEMAbwBuAHYAZQByAHQAQwBIADQAVABvAEMATwAyAGUAXwBOAEkAUgBSAGUAZgBlAHIAZQBuAGMAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AQwBvAG4AdgBlAHIAdABDAEgANABUAG8AQwBPADIAZQBfAEwAYQB0AGUAeABFAHEAdQBhAHQAaQBvAG4AXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAEMATwAyAF8AZQAgAD0AIABFAF8AewBDAEgANAB9ACAAXABcAHQAaQBtAGUAcwAgAEcAVwBQAF8AewBDAEgANAB9AFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAEMAbwBuAHYAZQByAHQAQwBIADQAVABvAEMATwAyAGUAXwBBAHIAZwB1AG0AZQBuAHQAcwBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABNAEEASwBFAEEAUgBSAEEAWQAoADIALAAgADIALAAgAFwAbgAgACAAIAAgACAAIABMAEEATQBCAEQAQQAoAHIALABjACwAIABcAG4AIAAgACAAIAAgACAAIAAgAEkATgBEAEUAWAAoAHsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEUAQwBIADQAXAAiACwAXAAiAE0AZQB0AGgAYQBuAGUAIABlAG0AaQBzAHMAaQBvAG4AcwAgACgAdAAgAEMASAA0ACkAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEcAVwBQAEMASAA0AFwAIgAsAFwAIgBHAGwAbwBiAGEAbAAgAHcAYQByAG0AaQBuAGcAIABwAG8AdABlAG4AdABpAGEAbAAgAGYAbwByACAAbQBlAHQAaABhAG4AZQAgACgAdAAgAEMATwAyAC0AZQAgAC8AIAB0ACAAQwBIADQAKQBcACIAXABuACAAIAAgACAAIAAgACAAIAB9ACwAIAByACwAIABjACkAXABuACAAIAAgACAAIAAgACkAXABuACAAIAAgACAAKQBcAG4AIAAgACkAOwAiAH0ALAB7ACIAcABhAHQAaAAiADoAIgAvAHAAcgBvAGoAZQBjAHQAcwAvAEMAbwBtAG0AbwBuAF8ASQBuAHAAdQB0AEYAdQBuAGMAdABpAG8AbgBzACIALAAiAHQAZQB4AHQAIgA6ACIAVQB0AGkAbABpAHQAeQBfAEcAZQB0AEEAcgByAGEAeQBUAGEAYgBsAGUAUgBvAHcAUwB0AGEAcgB0AE4AdQBtAGIAZQByAFwAbgA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAAVABhAGIAbABlAGgAZQBhAGQAZQByAEMAZQBsAGwALABSAG8AdwBzAEIAZQB0AHcAZQBlAG4ASABlAGEAZABlAHIAYQBuAGQAQQByAHIAYQB5ACwAXABuACAAIAAgACAAUgBPAFcAKABUAGEAYgBsAGUAaABlAGEAZABlAHIAQwBlAGwAbAApACAAKwAgAFIAbwB3AHMAQgBlAHQAdwBlAGUAbgBIAGUAYQBkAGUAcgBhAG4AZABBAHIAcgBhAHkAIAAtACAAMQBcAG4AKQA7AFwAbgBcAG4AVQB0AGkAbABpAHQAeQBfAEcAZQB0AEEAcgByAGEAeQBUAGEAYgBsAGUAQwBvAGwAdQBtAG4AUwB0AGEAcgB0AE4AdQBtAGIAZQByAFwAbgA9AEwAQQBNAEIARABBACgAXABuACAAIABUAGEAYgBsAGUASABlAGEAZABlAHIAQwBlAGwAbAAsAFwAbgAgACAAQwBPAEwAVQBNAE4AKABUAGEAYgBsAGUASABlAGEAZABlAHIAQwBlAGwAbAApAFwAbgApADsAXABuAFwAbgBVAHQAaQBsAGkAdAB5AF8ARABpAHMAcABsAGEAeQBBAHIAcgBhAHkASQBuAFQAYQBiAGwAZQBcAG4APQBMAEEATQBCAEQAQQAoAFwAbgAgAEEAcgByAGEAeQBEAGEAdABhACwAIABUAGEAYgBsAGUAaABlAGEAZABlAHIAQwBlAGwAbAAsACAAUgBvAHcAcwBCAGUAdAB3AGUAZQBuAEgAZQBhAGQAZQByAGEAbgBkAEEAcgByAGEAeQAsACAAWwBDAG8AbAB1AG0AbgBzAEIAZQB0AHcAZQBlAG4ASABlAGEAZABlAHIAQQBuAGQAQQByAHIAYQB5AF0ALABcAG4AIABJAEYARQBSAFIATwBSACgAXABuACAAIAAgACAAIABJAE4ARABFAFgAKABcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAVQBOAEkAUQBVAEUAKABBAHIAcgBhAHkARABhAHQAYQApACwAIABcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAUgBPAFcAKAApAC0AVQB0AGkAbABpAHQAeQBfAEcAZQB0AEEAcgByAGEAeQBUAGEAYgBsAGUAUgBvAHcAUwB0AGEAcgB0AE4AdQBtAGIAZQByACgAVABhAGIAbABlAGgAZQBhAGQAZQByAEMAZQBsAGwALAAgAFIAbwB3AHMAQgBlAHQAdwBlAGUAbgBIAGUAYQBkAGUAcgBhAG4AZABBAHIAcgBhAHkAKQAsACAAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgAEMATwBMAFUATQBOACgAKQAtAFUAdABpAGwAaQB0AHkAXwBHAGUAdABBAHIAcgBhAHkAVABhAGIAbABlAEMAbwBsAHUAbQBuAFMAdABhAHIAdABOAHUAbQBiAGUAcgAoAFQAYQBiAGwAZQBoAGUAYQBkAGUAcgBDAGUAbABsACkAIAArAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIABJAEYAKABJAFMATwBNAEkAVABUAEUARAAoAEMAbwBsAHUAbQBuAHMAQgBlAHQAdwBlAGUAbgBIAGUAYQBkAGUAcgBBAG4AZABBAHIAcgBhAHkAKQAsACAAMQAsACAAQwBvAGwAdQBtAG4AcwBCAGUAdAB3AGUAZQBuAEgAZQBhAGQAZQByAEEAbgBkAEEAcgByAGEAeQApAFwAbgAgACAAIAAgACAAIAAgACAAKQAsACAAXAAiAFwAIgBcAG4AIAAgACAAIAApAFwAbgApADsAXABuAFwAbgBVAHQAaQBsAGkAdAB5AF8ATABvAG8AawB1AHAAVgBhAGwAdQBlAEkAbgBUAGEAYgBsAGUAXABuAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABMAG8AbwBrAHUAcABWAGEAbAB1AGUALAAgAEwAbwBvAGsAdQBwAEEAcgByAGEAeQAsACAAUgBlAHQAdQByAG4AQQByAHIAYQB5ACwAXABuACAAIAAgACAAWABMAE8ATwBLAFUAUAAoAEwAbwBvAGsAdQBwAFYAYQBsAHUAZQAsACAATABvAG8AawB1AHAAQQByAHIAYQB5ACwAIABSAGUAdAB1AHIAbgBBAHIAcgBhAHkALAAgAFwAIgBcACIAKQBcAG4AKQA7AFwAbgBcAG4AVQB0AGkAbABpAHQAeQBfAEwAbwBvAGsAdQBwAFYAYQBsAHUAZQBJAG4AVABhAGIAbABlAE4AdQBtAGIAZQByAFwAbgA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAATABvAG8AawB1AHAAVgBhAGwAdQBlACwAIABMAG8AbwBrAHUAcABBAHIAcgBhAHkALAAgAFIAZQB0AHUAcgBuAEEAcgByAGEAeQAsAFwAbgAgACAAIAAgAEkARgAoAEkAUwBOAFUATQBCAEUAUgAoAFwAbgAgACAAIAAgACAAIAAgACAAWABMAE8ATwBLAFUAUAAoAEwAbwBvAGsAdQBwAFYAYQBsAHUAZQAsACAATABvAG8AawB1AHAAQQByAHIAYQB5ACwAIABSAGUAdAB1AHIAbgBBAHIAcgBhAHkALAAgAFwAIgBcACIAKQBcAG4AIAAgACAAIAApACwAIABYAEwATwBPAEsAVQBQACgATABvAG8AawB1AHAAVgBhAGwAdQBlACwAIABMAG8AbwBrAHUAcABBAHIAcgBhAHkALAAgAFIAZQB0AHUAcgBuAEEAcgByAGEAeQAsACAAXAAiAFwAIgApACwAIAAwACkAXABuACkAOwBcAG4AXABuAFUAdABpAGwAaQB0AHkAXwBMAG8AbwBrAHUAcABWAGEAbAB1AGUASQBuAFQAYQBiAGwAZQBUAHcAbwBDAG8AbAB1AG0AbgBzAFwAbgA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAATABvAG8AawB1AHAAVgBhAGwAdQBlADEALAAgAEwAbwBvAGsAdQBwAFYAYQBsAHUAZQAyACwAIABMAG8AbwBrAHUAcABBAHIAcgBhAHkAMQAsACAATABvAG8AawB1AHAAQQByAHIAYQB5ADIALAAgAFIAZQB0AHUAcgBuAEEAcgByAGEAeQAsACAAWwBWAGEAbAB1AGUASQBGAEYAYQBsAHMAZQBdACwAXABuACAAIAAgACAAWABMAE8ATwBLAFUAUAAoADEALAAgACgATABvAG8AawB1AHAAQQByAHIAYQB5ADEAPQBMAG8AbwBrAHUAcABWAGEAbAB1AGUAMQApACoAKABMAG8AbwBrAHUAcABBAHIAcgBhAHkAMgA9AEwAbwBvAGsAdQBwAFYAYQBsAHUAZQAyACkALAAgAFIAZQB0AHUAcgBuAEEAcgByAGEAeQAsACAASQBGACgASQBTAE8ATQBJAFQAVABFAEQAKABWAGEAbAB1AGUASQBGAEYAYQBsAHMAZQApACwAIABcACIAXAAiACwAIABWAGEAbAB1AGUASQBGAEYAYQBsAHMAZQApACkAXABuACkAOwBcAG4AXABuAFUAdABpAGwAaQB0AHkAXwBMAG8AbwBrAHUAcABWAGEAbAB1AGUASQBuAFQAYQBiAGwAZQBPAG4AZQBDAG8AbAB1AG0AbgBBAG4AZABIAGUAYQBkAGUAcgBcAG4APQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAEwAbwBvAGsAdQBwAFYAYQBsAHUAZQAxACwAIABMAG8AbwBrAHUAcABWAGEAbAB1AGUAMgAsACAATABvAG8AawB1AHAAQQByAHIAYQB5ADEALAAgAEwAbwBvAGsAdQBwAEEAcgByAGEAeQAyACwAIABSAGUAdAB1AHIAbgBBAHIAcgBhAHkALAAgAFsAVgBhAGwAdQBlAEkAZgBGAGEAbABzAGUAXQAsAFwAbgAgACAAIAAgAEkARgBFAFIAUgBPAFIAKABcAG4AIAAgACAAIAAgACAAIAAgAFgATABPAE8ASwBVAFAAKABMAG8AbwBrAHUAcABWAGEAbAB1AGUAMQAsACAATABvAG8AawB1AHAAQQByAHIAYQB5ADEALABcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAWABMAE8ATwBLAFUAUAAoAEwAbwBvAGsAdQBwAFYAYQBsAHUAZQAyACwAIABMAG8AbwBrAHUAcABBAHIAcgBhAHkAMgAsACAAUgBlAHQAdQByAG4AQQByAHIAYQB5ACkAXABuACAAIAAgACAAIAAgACAAIAApACwAXABuACAAIAAgACAAIAAgACAAIABJAEYAKABJAFMATwBNAEkAVABUAEUARAAoAFYAYQBsAHUAZQBJAGYARgBhAGwAcwBlACkALAAgAFwAIgBcACIALAAgAFYAYQBsAHUAZQBJAGYARgBhAGwAcwBlACkAXABuACAAIAAgACAAKQBcAG4AKQA7AFwAbgBcAG4AVQB0AGkAbABpAHQAeQBfAFMAcABsAGkAdABTAHQAcgBpAG4AZwBJAG4AdABvAEEAcgByAGEAeQBcAG4APQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAEMAZQBsAGwALAAgAEQAZQBsAGkAbQBpAHQAZQByACwAIABbAEMAaABhAHIAYQBjAHQAZQByAFQAbwBSAGUAbQBvAHYAZQAxAF0ALAAgAFsAQwBoAGEAcgBhAGMAdABlAHIAVABvAFIAZQBtAG8AdgBlADIAXQAsAFwAbgAgACAAIAAgACAAIAAgACAARgBJAEwAVABFAFIAWABNAEwAKABcAG4AIAAgACAAIAAgACAAIAAgAFwAIgA8AHQAPgA8AHMAPgBcACIAIAAmAFwAbgAgACAAIAAgACAAIAAgACAAUwBVAEIAUwBUAEkAVABVAFQARQAoAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIABTAFUAQgBTAFQASQBUAFUAVABFACgAUwBVAEIAUwBUAEkAVABVAFQARQAoAEMAZQBsAGwALABDAGgAYQByAGEAYwB0AGUAcgBUAG8AUgBlAG0AbwB2AGUAMQAsAFwAIgBcACIAKQAsAEMAaABhAHIAYQBjAHQAZQByAFQAbwBSAGUAbQBvAHYAZQAyACwAXAAiAFwAIgApACwAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgAEQAZQBsAGkAbQBpAHQAZQByACwAXAAiADwALwBzAD4APABzAD4AXAAiAFwAbgAgACAAIAAgACAAIAAgACAAKQAgACYAXABuACAAIAAgACAAIAAgACAAIABcACIAPAAvAHMAPgA8AC8AdAA+AFwAIgAsAFwAbgAgACAAIAAgACAAIAAgACAAXAAiAC8ALwBzAFwAIgBcAG4AIAAgACAAIAApAFwAbgApADsAXABuAFwAbgBVAHQAaQBsAGkAdAB5AF8ARwBlAHQAQwBsAGkAbQBhAHQAZQBaAG8AbgBlAFwAbgA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAAYQB2AGcAVABlAG0AcAAsAGEAdgBnAFIAYQBpAG4ALABmAHIAbwBzAHQARABhAHkAcwAsAGUAbABlAHYALABtAGEAcABfAHAAZQB0ACwAXABuACAAIAAgACAAbQBpAG4AVABlAG0AcABBAHIAcgBhAHkALABtAGEAeABUAGUAbQBwAEEAcgByAGEAeQAsAFwAbgAgACAAIAAgAG0AaQBuAFIAYQBpAG4AZgBhAGwAbABBAHIAcgBhAHkALABtAGEAeABSAGEAaQBuAGYAYQBsAGwAQQByAHIAYQB5ACwAXABuACAAIAAgACAAbQBpAG4ARgByAG8AcwB0AEEAcgByAGEAeQAsAG0AYQB4AEYAcgBvAHMAdABBAHIAcgBhAHkALABcAG4AIAAgACAAIABtAGkAbgBFAGwAZQB2AGEAdABpAG8AbgBBAHIAcgBhAHkALABtAGEAeABFAGwAZQB2AGEAdABpAG8AbgBBAHIAcgBhAHkALABcAG4AIAAgACAAIABtAGkAbgBQAEUAVABBAHIAcgBhAHkALABtAGEAeABQAEUAVABBAHIAcgBhAHkALABcAG4AIAAgACAAIABjAGwAaQBtAGEAdABlAFoAbwBuAGUAQQByAHIAYQB5ACwAXABuACAAIAAgACAATABFAFQAKABcAG4AIAAgACAAIAAgACAAIAAgAG0AYQBzAGsALABcAG4AIAAgACAAIAAgACAAIAAgACgAVgBBAEwAVQBFACgAbQBpAG4AVABlAG0AcABBAHIAcgBhAHkAKQA8AD0AYQB2AGcAVABlAG0AcAApACoAXABuACAAIAAgACAAIAAgACAAIAAoAFYAQQBMAFUARQAoAG0AYQB4AFQAZQBtAHAAQQByAHIAYQB5ACkAPgA9AGEAdgBnAFQAZQBtAHAAKQAqAFwAbgAgACAAIAAgACAAIAAgACAAKABWAEEATABVAEUAKABtAGkAbgBSAGEAaQBuAGYAYQBsAGwAQQByAHIAYQB5ACkAPAA9AGEAdgBnAFIAYQBpAG4AKQAqAFwAbgAgACAAIAAgACAAIAAgACAAKABWAEEATABVAEUAKABtAGEAeABSAGEAaQBuAGYAYQBsAGwAQQByAHIAYQB5ACkAPgA9AGEAdgBnAFIAYQBpAG4AKQAqAFwAbgAgACAAIAAgACAAIAAgACAAKABWAEEATABVAEUAKABtAGkAbgBGAHIAbwBzAHQAQQByAHIAYQB5ACkAPAA9AGYAcgBvAHMAdABEAGEAeQBzACkAKgBcAG4AIAAgACAAIAAgACAAIAAgACgAVgBBAEwAVQBFACgAbQBhAHgARgByAG8AcwB0AEEAcgByAGEAeQApAD4APQBmAHIAbwBzAHQARABhAHkAcwApACoAXABuACAAIAAgACAAIAAgACAAIAAoAFYAQQBMAFUARQAoAG0AaQBuAEUAbABlAHYAYQB0AGkAbwBuAEEAcgByAGEAeQApADwAPQBlAGwAZQB2ACkAKgBcAG4AIAAgACAAIAAgACAAIAAgACgAVgBBAEwAVQBFACgAbQBhAHgARQBsAGUAdgBhAHQAaQBvAG4AQQByAHIAYQB5ACkAPgA9AGUAbABlAHYAKQAqAFwAbgAgACAAIAAgACAAIAAgACAAKABWAEEATABVAEUAKABtAGkAbgBQAEUAVABBAHIAcgBhAHkAKQA8AD0AbQBhAHAAXwBwAGUAdAApACoAXABuACAAIAAgACAAIAAgACAAIAAoAFYAQQBMAFUARQAoAG0AYQB4AFAARQBUAEEAcgByAGEAeQApAD4APQBtAGEAcABfAHAAZQB0ACkALABcAG4AIAAgACAAIAAgACAAIAAgAFQAQQBLAEUAKABcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAARgBJAEwAVABFAFIAKABjAGwAaQBtAGEAdABlAFoAbwBuAGUAQQByAHIAYQB5ACwAbQBhAHMAawAsACAAXAAiAE4AbwAgAG0AYQB0AGMAaABcACIAKQAsAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIAAxAFwAbgAgACAAIAAgACAAIAAgACAAKQBcAG4AIAAgACAAIAApAFwAbgApADsAXABuAFwAbgBVAHQAaQBsAGkAdAB5AF8ATABvAG8AawB1AHAASQB0AGUAbQBGAHIAbwBtAE0AaQBuAE0AYQB4AFwAbgA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAATABvAG8AawB1AHAAVgBhAGwAdQBlACwAIABNAGkAbgBBAHIAcgBhAHkALAAgAE0AYQB4AEEAcgByAGEAeQAsACAASQB0AGUAbQBBAHIAcgBhAHkALABcAG4AIAAgACAAIABMAEUAVAAoAFwAbgAgACAAIAAgACAAIAAgACAAbQBhAHMAawAsAFwAbgAgACAAIAAgACAAIAAgACAAKABWAEEATABVAEUAKABNAGkAbgBBAHIAcgBhAHkAKQA8AD0ATABvAG8AawB1AHAAVgBhAGwAdQBlACkAKgBcAG4AIAAgACAAIAAgACAAIAAgACgAVgBBAEwAVQBFACgATQBhAHgAQQByAHIAYQB5ACkAPgA9AEwAbwBvAGsAdQBwAFYAYQBsAHUAZQApACwAXABuACAAIAAgACAAIAAgACAAIABGAEkATABUAEUAUgAoAEkAdABlAG0AQQByAHIAYQB5ACwAIABtAGEAcwBrACwAIABcACIATgBvACAAbQBhAHQAYwBoAFwAIgApAFwAbgAgACAAIAAgACkAXABuACkAOwBcAG4AXABuAFwAbgBVAHQAaQBsAGkAdAB5AF8AUwB1AG0AUQB1AGEAbgB0AGkAdAB5AEYAcgBvAG0AQwByAGkAdABlAHIAaQBhAFwAbgA9AEwAQQBNAEIARABBACgAXABuACAAIABDAHIAaQB0AGUAcgBpAGEAMQAsACAAQwByAGkAdABlAHIAaQBhADEAVAB5AHAAZQBBAHIAcgBhAHkALAAgAFEAdQBhAG4AdABpAHQAeQAsACAAWwBNAHUAbAB0AGkAcABsAGkAZQByAF0ALAAgAFsAQwByAGkAdABlAHIAaQBhADIAXQAsAFsAQwByAGkAdABlAHIAaQBhADIAQQByAHIAYQB5AF0ALABcAG4AIAAgAEwARQBUACgAXABuACAAIAAgACAAbQB1AGwAdABpAHAAbABpAGUAcgAsACAASQBGACgASQBTAE8ATQBJAFQAVABFAEQAKABNAHUAbAB0AGkAcABsAGkAZQByACkALAAxACwATQB1AGwAdABpAHAAbABpAGUAcgApACwAXABuACAAIAAgACAAcQB1AGEAbgB0AGkAdAB5ACwAIABRAHUAYQBuAHQAaQB0AHkAKgBNAHUAbAB0AGkAcABsAGkAZQByACwAXABuACAAIAAgACAAYwByAGkAdABlAHIAaQBhADEALAAtAC0AKABDAHIAaQB0AGUAcgBpAGEAMQBUAHkAcABlAEEAcgByAGEAeQA9AEMAcgBpAHQAZQByAGkAYQAxACkALABcAG4AIAAgACAAIABjAHIAaQB0AGUAcgBpAGEAMgAsAEkARgAoAEkAUwBPAE0ASQBUAFQARQBEACgAQwByAGkAdABlAHIAaQBhADIAKQAsADEALAAtAC0AKABDAHIAaQB0AGUAcgBpAGEAMgBBAHIAcgBhAHkAPQBDAHIAaQB0AGUAcgBpAGEAMgApACkALABcAG4AIAAgACAAIABTAFUATQBQAFIATwBEAFUAQwBUACgAYwByAGkAdABlAHIAaQBhADEAKgBjAHIAaQB0AGUAcgBpAGEAMgAqAHEAdQBhAG4AdABpAHQAeQApAFwAbgAgACAAKQBcAG4AKQA7AFwAbgBcAG4AZwBlAHQATwB2AGUAcgBsAGEAcABwAGkAbgBnAFIAZQBwAG8AcgB0AGkAbgBnAEMAeQBjAGwAZQBzAFwAbgA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAAUAByAG8AZAB1AGMAdABpAG8AbgBDAHkAYwBsAGUAUwB0AGEAcgB0ACwAUAByAG8AZAB1AGMAdABpAG8AbgBDAHkAYwBsAGUARQBuAGQALABSAGUAcABvAHIAdABpAG4AZwBDAHkAYwBsAGUAUwB0AGEAcgB0ACwAXABuACAAIAAgACAATABFAFQAKABcAG4AIAAgACAAIAAgACAAIAAgAFMALABQAHIAbwBkAHUAYwB0AGkAbwBuAEMAeQBjAGwAZQBTAHQAYQByAHQALABcAG4AIAAgACAAIAAgACAAIAAgAEUALABQAHIAbwBkAHUAYwB0AGkAbwBuAEMAeQBjAGwAZQBFAG4AZAAsAFwAbgAgACAAIAAgACAAIAAgACAAbQAsAE0ATwBOAFQASAAoAFIAZQBwAG8AcgB0AGkAbgBnAEMAeQBjAGwAZQBTAHQAYQByAHQAKQAsAFwAbgAgACAAIAAgACAAIAAgACAAZAAsAEQAQQBZACgAUgBlAHAAbwByAHQAaQBuAGcAQwB5AGMAbABlAFMAdABhAHIAdAApACwAXABuACAAIAAgACAAIAAgACAAIABQAGUAcgBpAG8AZABFAG4AZAAsAEwAQQBNAEIARABBACgAcwB0ACwARQBEAEEAVABFACgAcwB0ACwAMQAyACkALQAxACkALABcAG4AIAAgACAAIAAgACAAIAAgAEEALABTAC0AMwA2ADUALABcAG4AIAAgACAAIAAgACAAIAAgAHkAYQAsAFkARQBBAFIAKABBACkALABcAG4AIAAgACAAIAAgACAAIAAgAHkAYgAsAFkARQBBAFIAKABFACkALABcAG4AIAAgACAAIAAgACAAIAAgAGYAaQByAHMAdABZAGUAYQByACwAeQBhACsAKABQAGUAcgBpAG8AZABFAG4AZAAoAEQAQQBUAEUAKAB5AGEALABtACwAZAApACkAPAAgAFMAKQAsAFwAbgAgACAAIAAgACAAIAAgACAAbABhAHMAdABZAGUAYQByACwAeQBiAC0AKABEAEEAVABFACgAeQBiACwAbQAsAGQAKQA+ACAARQApACwAXABuACAAIAAgACAAIAAgACAAIABNAEEAWAAoADAALABsAGEAcwB0AFkAZQBhAHIALQBmAGkAcgBzAHQAWQBlAGEAcgArADEAKQBcAG4AIAAgACAAIAApAFwAbgApADsAXABuAFwAbgBnAGUAdABPAHYAZQByAGwAYQBwAHAAaQBuAGcAUgBlAHAAbwByAHQAaQBuAGcAUABlAHIAaQBvAGQAcwBcAG4APQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAFAAcgBvAGQAdQBjAHQAaQBvAG4AQwB5AGMAbABlAFMAdABhAHIAdAAsAFAAcgBvAGQAdQBjAHQAaQBvAG4AQwB5AGMAbABlAEUAbgBkACwAUgBlAHAAbwByAHQAaQBuAGcAQwB5AGMAbABlAFMAdABhAHIAdAAsAFwAbgAgACAAIAAgAEwARQBUACgAXABuACAAIAAgACAAIAAgACAAIABTACwAUAByAG8AZAB1AGMAdABpAG8AbgBDAHkAYwBsAGUAUwB0AGEAcgB0ACwAXABuACAAIAAgACAAIAAgACAAIABFACwAUAByAG8AZAB1AGMAdABpAG8AbgBDAHkAYwBsAGUARQBuAGQALABcAG4AIAAgACAAIAAgACAAIAAgAG0ALABNAE8ATgBUAEgAKABSAGUAcABvAHIAdABpAG4AZwBDAHkAYwBsAGUAUwB0AGEAcgB0ACkALABcAG4AIAAgACAAIAAgACAAIAAgAGQALABEAEEAWQAoAFIAZQBwAG8AcgB0AGkAbgBnAEMAeQBjAGwAZQBTAHQAYQByAHQAKQAsACAALwAqAGgAZQBsAHAAZQByADoAIABlAG4AZAAgAGQAYQB0AGUAIABmAG8AcgAgAGEAIAByAGUAcABvAHIAdABpAG4AZwAgAHAAZQByAGkAbwBkACAAcwB0AGEAcgB0AGkAbgBnACAAYQB0ACAAYQAgAGcAaQB2AGUAbgAgAGQAYQB0AGUAKgAvAFwAbgAgACAAIAAgACAAIAAgACAAUABlAHIAaQBvAGQARQBuAGQALABMAEEATQBCAEQAQQAoAHMAdAAsAEUARABBAFQARQAoAHMAdAAsADEAMgApAC0AMQApACwAIAAvACoAbwBuAGwAeQAgAG4AZQBlAGQAIAB0AG8AIABsAG8AbwBrACAAYgBhAGMAawAgADMANgA1ACAAZABhAHkAcwAoAG0AYQB4ACAAbwB2AGUAcgBsAGEAcAAgAHcAaQBuAGQAbwB3ACkAKgAvAFwAbgAgACAAIAAgACAAIAAgACAAQQAsAFMALQAzADYANQAsAFwAbgAgACAAIAAgACAAIAAgACAAeQBhACwAWQBFAEEAUgAoAEEAKQAsAFwAbgAgACAAIAAgACAAIAAgACAAeQBiACwAWQBFAEEAUgAoAEUAKQAsACAALwAqAGkAZgAgAHQAaABlACAAYQBuAGMAaABvAHIAIABmAG8AcgAgAHkAYQAgAGUAbgBkAHMAIABiAGUAZgBvAHIAZQAgAFMALABpAHQAIABjAGEAbgAnAHQAIABvAHYAZQByAGwAYQBwADsAIABtAG8AdgBlACAAdABvACAAbgBlAHgAdAAgAHkAZQBhAHIAKgAvAFwAbgAgACAAIAAgACAAIAAgACAAZgBpAHIAcwB0AFkAZQBhAHIALAB5AGEAKwAoAFAAZQByAGkAbwBkAEUAbgBkACgARABBAFQARQAoAHkAYQAsAG0ALABkACkAKQA8AFMAKQAsACAALwAqAGkAZgAgAHQAaABlACAAYQBuAGMAaABvAHIAIABmAG8AcgAgAHkAYgAgAHMAdABhAHIAdABzACAAYQBmAHQAZQByACAARQAsAGkAdAAgAGMAYQBuACcAdAAgAG8AdgBlAHIAbABhAHAAOwAgAG0AbwB2AGUAIAB0AG8AIABwAHIAZQB2AGkAbwB1AHMAIAB5AGUAYQByACoALwBcAG4AIAAgACAAIAAgACAAIAAgAGwAYQBzAHQAWQBlAGEAcgAsAHkAYgAtACgARABBAFQARQAoAHkAYgAsAG0ALABkACkAPgBFACkALABcAG4AIAAgACAAIAAgACAAIAAgAG4ALABNAEEAWAAoADAALABsAGEAcwB0AFkAZQBhAHIALQBmAGkAcgBzAHQAWQBlAGEAcgArADEAKQAsAFwAbgAgACAAIAAgACAAIAAgACAAeQByAHMALABTAEUAUQBVAEUATgBDAEUAKABuACwAMQAsAGYAaQByAHMAdABZAGUAYQByACwAMQApACwAXABuACAAIAAgACAAIAAgACAAIABzAHQAYQByAHQAcwAsAEQAQQBUAEUAKAB5AHIAcwAsAG0ALABkACkALABcAG4AIAAgACAAIAAgACAAIAAgAGUAbgBkAHMALABNAEEAUAAoAHMAdABhAHIAdABzACwAUABlAHIAaQBvAGQARQBuAGQAKQAsAFwAbgAgACAAIAAgACAAIAAgACAAdABhAGcALABJAEYAKABzAHQAYQByAHQAcwA9AFIAZQBwAG8AcgB0AGkAbgBnAEMAeQBjAGwAZQBTAHQAYQByAHQALABcACIAIAAoAFQAaABpAHMAIAByAGUAcABvAHIAdABpAG4AZwAgAGMAeQBjAGwAZQApAFwAIgAsAFwAIgBcACIAKQAsAFwAbgAgACAAIAAgACAAIAAgACAAcwB0AGEAcgB0AHMAVABlAHgAdAAsAFQARQBYAFQAKABzAHQAYQByAHQAcwAsAFwAIgBkAGQAIABtAG0AbQAgAHkAeQB5AHkAXAAiACkALABcAG4AIAAgACAAIAAgACAAIAAgAGUAbgBkAHMAVABlAHgAdAAsAFQARQBYAFQAKABlAG4AZABzACwAXAAiAGQAZAAgAG0AbQBtACAAeQB5AHkAeQBcACIAKQAsAFwAbgAgACAAIAAgACAAIAAgACAAcgBvAHcAcwAsAEkARgAoAG4APQAwACwAXAAiAFwAIgAsAEgAUwBUAEEAQwBLACgAcwB0AGEAcgB0AHMAVABlAHgAdAAgACYAIABcACIAIAB0AG8AIABcACIAIAAmACAAZQBuAGQAcwBUAGUAeAB0ACAAJgAgAHQAYQBnACkAKQAsAFwAbgAgACAAIAAgACAAIAAgACAAcgBvAHcAcwBcAG4AIAAgACAAIAApAFwAbgApADsAXABuAFwAbgBcAG4AVQB0AGkAbABpAHQAeQBfAEQAaQBzAHAAbABhAHkARgB1AG4AYwB0AGkAbwBuAE4AYQBtAGUAXABuAD0ATABBAE0AQgBEAEEAKABGAHUAbgBjAHQAaQBvAG4ALAAgAFQARQBYAFQAQgBFAEYATwBSAEUAKABGAE8AUgBNAFUATABBAFQARQBYAFQAKABGAHUAbgBjAHQAaQBvAG4AKQAsACAAXAAiACgAXAAiACkAKQA7AFwAbgBcAG4AVQB0AGkAbABpAHQAeQBfAEwAbwBvAGsAdQBwAE4AMgBPAEUARgBGAHIAbwBtAFAAcgBvAGQASQByAHIAaQBnAGEAdABpAG8AbgBSAGEAaQBuAGYAYQBsAGwAXABuAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABQAHIAbwBkAHUAYwB0AGkAbwBuAFMAeQBzAHQAZQBtACwAIABJAHIAcgBpAGcAYQB0AGkAbwBuAE0AZQB0AGgAbwBkACwAIABSAGEAaQBuAGYAYQBsAGwAWgBvAG4AZQAsAFwAbgAgACAAIAAgAFAAcgBvAGQAdQBjAHQAaQBvAG4AUwB5AHMAdABlAG0AQQByAHIAYQB5ACwAIABJAHIAcgBpAGcAYQB0AGkAbwBuAE0AZQB0AGgAbwBkAEEAcgByAGEAeQAsACAAUgBhAGkAbgBmAGEAbABsAFoAbwBuAGUAQQByAHIAYQB5ACwAUgBlAHQAdQByAG4AQQByAHIAYQB5ACwAXABuACAAIAAgACAATABFAFQAKABcAG4AIAAgACAAIAAgACAAIAAgAEkAcgByAGkAZwBhAHQAaQBvAG4ATQBlAHQAaABvAGQALAAgAEkARgAoAEkAcgByAGkAZwBhAHQAaQBvAG4ATQBlAHQAaABvAGQAPQBcACIATgBvAHQAIABpAHIAcgBpAGcAYQB0AGUAZABcACIALAAgAFwAIgBOAG8AdAAgAGkAcgByAGkAZwBhAHQAZQBkAFwAIgAsACAAXAAiAEEAbgB5AFwAIgApACwAXABuACAAIAAgACAAIAAgACAAIABSAGEAaQBuAGYAYQBsAGwAWgBvAG4AZQAsACAASQBGACgASQByAHIAaQBnAGEAdABpAG8AbgBNAGUAdABoAG8AZAAgAD0AIABcACIATgBvAHQAIABpAHIAcgBpAGcAYQB0AGUAZABcACIALAAgAFIAYQBpAG4AZgBhAGwAbABaAG8AbgBlACwAIABcACIAQQBuAHkAXAAiACkALABcAG4AIAAgACAAIAAgACAAIAAgAFgATABPAE8ASwBVAFAAKAAxACwAIABcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAKABQAHIAbwBkAHUAYwB0AGkAbwBuAFMAeQBzAHQAZQBtAEEAcgByAGEAeQA9AFAAcgBvAGQAdQBjAHQAaQBvAG4AUwB5AHMAdABlAG0AKQAqAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIAAoAEkAcgByAGkAZwBhAHQAaQBvAG4ATQBlAHQAaABvAGQAQQByAHIAYQB5AD0ASQByAHIAaQBnAGEAdABpAG8AbgBNAGUAdABoAG8AZAApACoAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgACgAUgBhAGkAbgBmAGEAbABsAFoAbwBuAGUAQQByAHIAYQB5AD0AUgBhAGkAbgBmAGEAbABsAFoAbwBuAGUAKQAsACAAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgAFIAZQB0AHUAcgBuAEEAcgByAGEAeQApAFwAbgAgACAAIAAgACkAXABuACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAEMAcgBvAHAAcABpAG4AZwBfAEcAZQB0AEYAcgBhAGMAVwBFAFQAXABuAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABMAGUAYQBjAGgAaQBuAGcAWgBvAG4AZQAsAFwAbgAgACAAIAAgAFAAcgBvAGQAdQBjAHQAaQBvAG4AUwB5AHMAdABlAG0ALABcAG4AIAAgACAAIABMAGUAYQBjAGgAaQBuAGcAWgBvAG4AZQBMAG8AbwBrAHUAcAAsAFwAbgAgACAAIAAgAEwAZQBhAGMAaABpAG4AZwBaAG8AbgBlAEYAcgBhAGMAVwBFAFQATABvAG8AawB1AHAALABcAG4AIAAgACAAIABQAHIAbwBkAHUAYwB0AGkAbwBuAFMAeQBzAHQAZQBtAEwAbwBvAGsAdQBwACwAXABuACAAIAAgACAAUAByAG8AZAB1AGMAdABpAG8AbgBTAHkAcwB0AGUAbQBGAHIAYQBjAFcARQBUAEwAbwBvAGsAdQBwACwAXABuACAAIAAgACAATABFAFQAKABcAG4AIAAgACAAIAAgACAAIAAgAEwAZQBhAGMAaABpAG4AZwBaAG8AbgBlAEYAcgBhAGMAVwBFAFQALAAgAFwAbgAgACAAIAAgACAAIAAgACAAQwBvAG0AbQBvAG4AXwBJAG4AcAB1AHQARgB1AG4AYwB0AGkAbwBuAHMALgBVAHQAaQBsAGkAdAB5AF8ATABvAG8AawB1AHAAVgBhAGwAdQBlAEkAbgBUAGEAYgBsAGUATgB1AG0AYgBlAHIAKABcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAATABlAGEAYwBoAGkAbgBnAFoAbwBuAGUALABMAGUAYQBjAGgAaQBuAGcAWgBvAG4AZQBMAG8AbwBrAHUAcAAsAEwAZQBhAGMAaABpAG4AZwBaAG8AbgBlAEYAcgBhAGMAVwBFAFQATABvAG8AawB1AHAAXABuACAAIAAgACAAIAAgACAAIAApACwAXABuACAAIAAgACAAIAAgACAAIABQAHIAbwBkAHUAYwB0AGkAbwBuAFMAeQBzAHQAZQBtAEYAcgBhAGMAVwBFAFQALAAgAFwAbgAgACAAIAAgACAAIAAgACAAQwBvAG0AbQBvAG4AXwBJAG4AcAB1AHQARgB1AG4AYwB0AGkAbwBuAHMALgBVAHQAaQBsAGkAdAB5AF8ATABvAG8AawB1AHAAVgBhAGwAdQBlAEkAbgBUAGEAYgBsAGUATgB1AG0AYgBlAHIAKABcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAUAByAG8AZAB1AGMAdABpAG8AbgBTAHkAcwB0AGUAbQAsAFAAcgBvAGQAdQBjAHQAaQBvAG4AUwB5AHMAdABlAG0ATABvAG8AawB1AHAALABQAHIAbwBkAHUAYwB0AGkAbwBuAFMAeQBzAHQAZQBtAEYAcgBhAGMAVwBFAFQATABvAG8AawB1AHAAXABuACAAIAAgACAAIAAgACAAIAApACwAXABuACAAIAAgACAAIAAgACAAIABJAEYAKABMAGUAYQBjAGgAaQBuAGcAWgBvAG4AZQBGAHIAYQBjAFcARQBUACAAKwAgAFAAcgBvAGQAdQBjAHQAaQBvAG4AUwB5AHMAdABlAG0ARgByAGEAYwBXAEUAVAA+ADAALAAgADEALAAgADAAKQBcAG4AIAAgACAAIAApACkAOwBcAG4AXABuAFwAbgBVAHQAaQBsAGkAdAB5AF8AQwBvAG4AdgBlAHIAdABTAHQAYQB0AGUAQwBvAG0AbQBvAG4ATgBhAG0AZQBUAG8AQQBiAGIAcgBlAHYAaQBhAHQAaQBvAG4AXABuAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABTAHQAYQB0AGUAQwBvAG0AbQBvAG4ATgBhAG0AZQAsAFwAbgAgACAAIAAgAFMAdABhAHQAZQBDAG8AbQBtAG8AbgBOAGEAbQBlAEEAcgByAGEAeQAsACAAUwB0AGEAdABlAEEAYgBiAHIAZQB2AGkAYQB0AGkAbwBuAEEAcgByAGEAeQAsAFwAbgAgACAAIAAgAFgATABPAE8ASwBVAFAAKABTAHQAYQB0AGUAQwBvAG0AbQBvAG4ATgBhAG0AZQAsACAAUwB0AGEAdABlAEMAbwBtAG0AbwBuAE4AYQBtAGUAQQByAHIAYQB5ACwAIABTAHQAYQB0AGUAQQBiAGIAcgBlAHYAaQBhAHQAaQBvAG4AQQByAHIAYQB5ACwAIABcACIAXAAiACkAXABuACkAOwBcAG4AXABuAFUAdABpAGwAaQB0AHkAXwBTAG8AdQByAGMAZQBIAHkAcABlAHIAbABpAG4AawBcAG4APQBMAEEATQBCAEQAQQAoAFQAYQByAGcAZQB0AEMAZQBsAGwALABcAG4AIAAgAEwARQBUACgAXABuACAAIAAgACAAcwBoACwAIABUAEUAWABUAEEARgBUAEUAUgAoAEMARQBMAEwAKABcACIAZgBpAGwAZQBuAGEAbQBlAFwAIgAsACAAVABhAHIAZwBlAHQAQwBlAGwAbAApACwAIABcACIAXQBcACIAKQAsAFwAbgAgACAAIAAgAGEAZABkAHIALAAgAEMARQBMAEwAKABcACIAYQBkAGQAcgBlAHMAcwBcACIALAAgAFQAYQByAGcAZQB0AEMAZQBsAGwAKQAsAFwAbgAgACAAIAAgAFwAIgAjACcAXAAiACAAJgAgAHMAaAAgACYAIABcACIAJwAhAFwAIgAgACYAIABhAGQAZAByAFwAbgAgACAAKQBcAG4AKQA7AFwAbgBcAG4AVQB0AGkAbABpAHQAeQBfAFMAbwB1AHIAYwBlAEgAeQBwAGUAcgBsAGkAbgBrAEQAaQBmAGYAZQByAGUAbgB0AFMAaABlAGUAdABcAG4APQBMAEEATQBCAEQAQQAoAFQAYQByAGcAZQB0AEMAZQBsAGwALABcAG4AIAAgAEwARQBUACgAXABuACAAIAAgACAAcwBoACwAIABUAEUAWABUAEEARgBUAEUAUgAoAEMARQBMAEwAKABcACIAZgBpAGwAZQBuAGEAbQBlAFwAIgAsACAAVABhAHIAZwBlAHQAQwBlAGwAbAApACwAIABcACIAXQBcACIAKQAsAFwAbgAgACAAIAAgAGEAZABkAHIALAAgAEMARQBMAEwAKABcACIAYQBkAGQAcgBlAHMAcwBcACIALAAgAFQAYQByAGcAZQB0AEMAZQBsAGwAKQAsAFwAbgAgACAAIAAgAFwAIgAjAFwAIgAgACYAIABhAGQAZAByAFwAbgAgACAAKQBcAG4AKQA7AFwAbgBcAG4AVQB0AGkAbABpAHQAeQBfAEQAaQBzAHAAbABhAHkAQQByAGcAdQBtAGUAbgB0AHMAXwAxAF8AMgBcAG4APQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAEEAcgBnAHUAbQBlAG4AdABzAEEAcgByAGEAeQAsAFwAbgAgACAAIAAgAEMASABPAE8AUwBFAEMATwBMAFMAKABBAHIAZwB1AG0AZQBuAHQAcwBBAHIAcgBhAHkALAAgADEALAAgADIAKQBcAG4AKQA7AFwAbgBcAG4AVQB0AGkAbABpAHQAeQBfAEQAaQBzAHAAbABhAHkAQQByAGcAdQBtAGUAbgB0AHMAXwAzAF8ANABcAG4APQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAEEAcgBnAHUAbQBlAG4AdABzAEEAcgByAGEAeQAsAFwAbgAgACAAIAAgAEMASABPAE8AUwBFAEMATwBMAFMAKABBAHIAZwB1AG0AZQBuAHQAcwBBAHIAcgBhAHkALAAgADMALAAgADQAKQBcAG4AKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBHAGUAdABNAEMARgBUAGUAbQBwAGUAcgBhAHQAdQByAGUAWgBvAG4AZQBcAG4APQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAFQAZQBtAHAAZQByAGEAdAB1AHIAZQAsACAATQBNAFMALAAgAFQAZQBtAHAAZQByAGEAdAB1AHIAZQBBAHIAcgBhAHkALAAgAE0ATQBTAEEAcgByAGEAeQAsACAAUgBlAHQAdQByAG4AQQByAHIAYQB5ACwAXABuACAAIAAgACAAWABMAE8ATwBLAFUAUAAoAFwAbgAgACAAIAAgACAAIAAgACAATQBFAEQASQBBAE4AKABcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAVABlAG0AcABlAHIAYQB0AHUAcgBlACwAIABcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAATQBJAE4AKABUAGUAbQBwAGUAcgBhAHQAdQByAGUAQQByAHIAYQB5ACkALAAgAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIABNAEEAWAAoAFQAZQBtAHAAZQByAGEAdAB1AHIAZQBBAHIAcgBhAHkAKQBcAG4AIAAgACAAIAAgACAAIAAgACkALABcAG4AIAAgACAAIAAgACAAIAAgAFQAZQBtAHAAZQByAGEAdAB1AHIAZQBBAHIAcgBhAHkALABcAG4AIAAgACAAIAAgACAAIAAgAFgATABPAE8ASwBVAFAAKABNAE0AUwAsACAATQBNAFMAQQByAHIAYQB5ACwAIABSAGUAdAB1AHIAbgBBAHIAcgBhAHkAKQBcAG4AIAAgACAAIAApAFwAbgApADsAXABuAFwAbgBcAG4AVQB0AGkAbABpAHQAeQBfAFIAZQBzAHUAbAB0AHMASQB0AGUAbQBGAHIAbwBtAEUAcQB1AGEAdABpAG8AbgBUAGkAdABsAGUAQQBuAGQAUwBvAHUAcgBjAGUAXABuAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABUAGkAdABsAGUAQwBlAGwAbAAsACAAUwBvAHUAcgBjAGUAQwBlAGwAbAAsAFwAbgAgACAAIAAgAFMAVQBCAFMAVABJAFQAVQBUAEUAKABMAEUARgBUACgAUwBvAHUAcgBjAGUAQwBlAGwAbAAsACAARgBJAE4ARAAoAFwAIgAsAFwAIgAsACAAUwBvAHUAcgBjAGUAQwBlAGwAbAApACAALQAxACkALAAgAFwAIgBWAEUARQBSAEcAIAAyADAAMgA2ADoAIABcACIALAAgAFwAIgBcACIAKQAgACYAIABcACIAIABcACIAIAAmACAAVABpAHQAbABlAEMAZQBsAGwAXABuACkAOwAiAH0ALAB7ACIAcABhAHQAaAAiADoAIgAvAHAAcgBvAGoAZQBjAHQAcwAvAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAiACwAIgB0AGUAeAB0ACIAOgAiAC8AKgBcAG4APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQBcAG4APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQBcAG4AUwBvAHUAcgBjAGUAIABkAGEAdABhACAAdABoAGEAdAAgAGkAcwAgAGMAbwBtAG0AbwBuACAAYQBjAHIAbwBzAHMAIABhAGwAbAAgAGUAbgB0AGUAcgBwAHIAaQBzAGUAIAB0AHkAcABlAHMAXABuAEUAeABjAGUAbAAgAG0AbwBkAHUAbABlACAAbgBhAG0AZQA6ACAAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAFwAbgA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AFwAbgA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AFwAbgAqAC8AXABuAFwAbgAvACoAXABuAD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQBcAG4APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AFwAbgBTAG8AdQByAGMAZQA6ACAATgBhAHQAaQBvAG4AYQBsACAASQBuAHYAZQBuAHQAbwByAHkAIABSAGUAcABvAHIAdAAgADIAMAAyADMAIABWAG8AbAB1AG0AZQAgADEAXABuAE4ASQBSAF8AMgAwADIAMwBfAFYAbwBsADEAXABuAD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQBcAG4APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AFwAbgAqAC8AXABuAFwAbgAvACoAIABcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGUAbgBzAGkAdAB5AE8AZgBNAGUAdABoAGEAbgBlAFwAbgBwACAAPQAgAGQAZQBuAHMAaQB0AHkAIABvAGYAIABtAGUAdABoAGEAbgBlACAAKAAwAC4ANgA3ADgANAAgAGsAZwAvAG0AMwApAFwAbgBUAGEAawBlAG4AIABmAHIAbwBtACAAdABoAGUAIABOAGEAdABpAG8AbgBhAGwAIABHAHIAZQBlAG4AaABvAHUAcwBlACAAYQBuAGQAIABFAG4AZQByAGcAeQAgAFIAZQBwAG8AcgB0AGkAbgBnACAAXABuACgATQBlAGEAcwB1AHIAZQBtAGUAbgB0ACkAIABEAGUAdABlAHIAbQBpAG4AYQB0AGkAbwBuACAAMgAwADAAOABcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgAqAC8AXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGUAbgBzAGkAdAB5AE8AZgBNAGUAdABoAGEAbgBlAF8AVABpAHQAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBwACAAPQAgAGQAZQBuAHMAaQB0AHkAIABvAGYAIABtAGUAdABoAGEAbgBlAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGUAbgBzAGkAdAB5AE8AZgBNAGUAdABoAGEAbgBlAF8AVQBuAGkAdABcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAawBnAC8AbQAzAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGUAbgBzAGkAdAB5AE8AZgBNAGUAdABoAGEAbgBlAF8AUwBvAHUAcgBjAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAE4AYQB0AGkAbwBuAGEAbAAgAEkAbgB2AGUAbgB0AG8AcgB5ACAAUgBlAHAAbwByAHQAIAAyADAAMgAzACAAVgBvAGwAdQBtAGUAIAAxADoAIABFAHEAdQBhAHQAaQBvAG4AcwAgADMALgBCAC4AMQBhAF8AMgAsACAAMwAuAEIALgAxAGMAXwAyACwAIAAzAC4AQgAuADMAXwAxACwAIAAzAC4AQgAuADQAZwBfADIAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEQAZQBuAHMAaQB0AHkATwBmAE0AZQB0AGgAYQBuAGUAXwBEAGEAdABhAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoADAALgA2ADcAOAA0ACkAOwBcAG4AXABuAC8AKgAgAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEMAbwBuAHYAZQByAHQATgAyAG8ARQBsAGUAbQBlAG4AdABhAGwAVABvAE0AbwBsAGUAYwB1AGwAYQByAEMAZwBcAG4AQwBnACAAPQAgADQANAAvADIAOAAgAGYAYQBjAHQAbwByACAAdABvACAAYwBvAG4AdgBlAHIAdAAgAGUAbABlAG0AZQBuAHQAYQBsACAAbQBhAHMAcwAgAG8AZgAgAE4AMgBPACAAdABvACAAbQBvAGwAZQBjAHUAbABhAHIAIABtAGEAcwBzAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuACoALwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEMAbwBuAHYAZQByAHQATgAyAG8ARQBsAGUAbQBlAG4AdABhAGwAVABvAE0AbwBsAGUAYwB1AGwAYQByAEMAZwBfAFQAaQB0AGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIARgBhAGMAdABvAHIAIAB0AG8AIABjAG8AbgB2AGUAcgB0ACAAZQBsAGUAbQBlAG4AdABhAGwAIABtAGEAcwBzACAAbwBmACAATgAyAE8AIAB0AG8AIABtAG8AbABlAGMAdQBsAGEAcgAgAG0AYQBzAHMAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEMAbwBuAHYAZQByAHQATgAyAG8ARQBsAGUAbQBlAG4AdABhAGwAVABvAE0AbwBsAGUAYwB1AGwAYQByAEMAZwBfAFYAYQByAGkAYQBiAGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAQwBnAE4AMgBPAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBDAG8AbgB2AGUAcgB0AE4AMgBvAEUAbABlAG0AZQBuAHQAYQBsAFQAbwBNAG8AbABlAGMAdQBsAGEAcgBDAGcAXwBVAG4AaQB0AFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBmAGEAYwB0AG8AcgBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQwBvAG4AdgBlAHIAdABOADIAbwBFAGwAZQBtAGUAbgB0AGEAbABUAG8ATQBvAGwAZQBjAHUAbABhAHIAQwBnAF8AUwBvAHUAcgBjAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAE4AYQB0AGkAbwBuAGEAbAAgAEkAbgB2AGUAbgB0AG8AcgB5ACAAUgBlAHAAbwByAHQAIAAyADAAMgAzACAAVgBvAGwAdQBtAGUAIAAxAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBDAG8AbgB2AGUAcgB0AE4AMgBvAEUAbABlAG0AZQBuAHQAYQBsAFQAbwBNAG8AbABlAGMAdQBsAGEAcgBDAGcAXwBEAGEAdABhAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoADQANAAvADIAOAApADsAXABuAFwAbgAvACoAIABcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBDAG8AbgB2AGUAcgB0AEcAYQBzAEUAbABlAG0AZQBuAHQAYQBsAFQAbwBNAG8AbABlAGMAdQBsAGEAcgBcAG4ARgBhAGMAdABvAHIAIAB0AG8AIABjAG8AbgB2AGUAcgB0ACAAZQBsAGUAbQBlAG4AdABhAGwAIABtAGEAcwBzACAAbwBmACAAZwBhAHMAIAB0AG8AIABtAG8AbABlAGMAdQBsAGEAcgAgAG0AYQBzAHMAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AKgAvAFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQwBvAG4AdgBlAHIAdABHAGEAcwBFAGwAZQBtAGUAbgB0AGEAbABUAG8ATQBvAGwAZQBjAHUAbABhAHIAXwBUAGkAdABsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAEYAYQBjAHQAbwByACAAdABvACAAYwBvAG4AdgBlAHIAdAAgAGUAbABlAG0AZQBuAHQAYQBsACAAbQBhAHMAcwAgAG8AZgAgAGcAYQBzACAAdABvACAAbQBvAGwAZQBjAHUAbABhAHIAIABtAGEAcwBzAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBDAG8AbgB2AGUAcgB0AEcAYQBzAEUAbABlAG0AZQBuAHQAYQBsAFQAbwBNAG8AbABlAGMAdQBsAGEAcgBfAFYAYQByAGkAYQBiAGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAQwBnAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBDAG8AbgB2AGUAcgB0AEcAYQBzAEUAbABlAG0AZQBuAHQAYQBsAFQAbwBNAG8AbABlAGMAdQBsAGEAcgBfAFUAbgBpAHQAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAGYAYQBjAHQAbwByAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBDAG8AbgB2AGUAcgB0AEcAYQBzAEUAbABlAG0AZQBuAHQAYQBsAFQAbwBNAG8AbABlAGMAdQBsAGEAcgBfAFMAbwB1AHIAYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBYAFgAWABYAFgAWABYAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBDAG8AbgB2AGUAcgB0AEcAYQBzAEUAbABlAG0AZQBuAHQAYQBsAFQAbwBNAG8AbABlAGMAdQBsAGEAcgBfAEQAYQB0AGEAXABuACAAIAA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAATQBBAEsARQBBAFIAUgBBAFkAKAA4ACwAIAA0ACwAIABcAG4AIAAgACAAIAAgACAATABBAE0AQgBEAEEAKAByACwAYwAsACAAXABuACAAIAAgACAAIAAgACAAIABJAE4ARABFAFgAKAB7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBHAGEAcwBcACIALAAgAFwAIgBDAG8AbgB2AGUAcgBzAGkAbwBuACAAZgBhAGMAdABvAHIAXAAiACwAIABcACIAQwBvAG4AdgBlAHIAcwBpAG8AbgAgAGYAYQBjAHQAbwByACAAMQBcACIALAAgAFwAIgBDAG8AbgB2AGUAcgBzAGkAbwBuACAAZgBhAGMAdABvAHIAIAAyAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBDAE8AMgBcACIALAAgAFwAIgA0ADQALwAxADIAXAAiACwAIAA0ADQALAAgADEAMgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBDAEgANABcACIALAAgAFwAIgAxADYALwAxADIAXAAiACwAIAAxADYALAAgADEAMgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBOADIATwBcACIALAAgAFwAIgA0ADQALwAyADgAXAAiACwAIAA0ADQALAAgADIAOAA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBOAG8AeABcACIALAAgAFwAIgA0ADYALwAxADQAXAAiACwAIAA0ADYALAAgADEANAA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBDAE8AXAAiACwAIABcACIAMgA4AC8AMQAyAFwAIgAsACAAMgA4ACwAIAAxADIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAQwBPADIAIABMAGkAbQBlAFwAIgAsACAAXAAiADQANAAvADEAMgBcACIALAAgADQANAAsACAAMQAyADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAE4ATQBWAE8AQwBcACIALAAgAFwAIgAxADQALwAxADIAXAAiACwAIAAxADQALAAgADEAMgBcAG4AIAAgACAAIAAgACAAIAAgAH0ALAAgAHIALAAgAGMAKQBcAG4AIAAgACAAIAAgACAAKQBcAG4AIAAgACAAIAApAFwAbgAgACAAKQA7AFwAbgBcAG4ALwAqACAAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARwBXAFAATgAyAE8AXABuAEcAbABvAGIAYQBsACAAdwBhAHIAbQBpAG4AZwAgAHAAbwB0AGUAbgB0AGkAYQBsACAAZgBvAHIAIABnAHIAZQBlAG4AaABvAHUAcwBlACAAZwBhAHMAZQBzAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuACoALwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEcAVwBQAF8AVABpAHQAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBHAGwAbwBiAGEAbAAgAHcAYQByAG0AaQBuAGcAIABwAG8AdABlAG4AdABpAGEAbAAgAGYAbwByACAAZwByAGUAZQBuAGgAbwB1AHMAZQAgAGcAYQBzAGUAcwBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARwBXAFAAXwBWAGEAcgBpAGEAYgBsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAEcAVwBQAE4AMgBPAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBHAFcAUABfAFUAbgBpAHQAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAGYAYQBjAHQAbwByAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBHAFcAUABfAFMAbwB1AHIAYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBYAFgAWABYAFgAWABYAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBHAFcAUABfAEQAYQB0AGEAXABuACAAIAA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAATQBBAEsARQBBAFIAUgBBAFkAKAA4ACwAIAAyACwAIABcAG4AIAAgACAAIAAgACAATABBAE0AQgBEAEEAKAByACwAYwAsACAAXABuACAAIAAgACAAIAAgACAAIABJAE4ARABFAFgAKAB7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBHAGEAcwBcACIALAAgAFwAIgBDAE8AMgAtAGUAIABmAGEAYwB0AG8AcgBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAQwBPADIAXAAiACwAIAAxADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEMASAA0AFwAIgAsACAAMgA4ADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAE4AMgBPAFwAIgAsACAAMgA2ADUAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAQwBGADQAXAAiACwAIAA2ADYAMwAwADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEMAMgBGADYAXAAiACwAIAAxADIAMgAwADAAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAUwBGADYAXAAiACwAIAAyADIAOAAwADAAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIATgBGADMAXAAiACwAIAAxADcAMgAwADAAXABuACAAIAAgACAAIAAgACAAIAB9ACwAIAByACwAIABjACkAXABuACAAIAAgACAAIAAgACkAXABuACAAIAAgACAAKQBcAG4AIAAgACkAOwBcAG4AXABuAFwAbgAvACoAIABcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBBAHUAcwB0AHIAYQBsAGkAYQBuAFMAdABhAHQAZQBzAFQAZQByAHIAaQB0AG8AcgBpAGUAcwBcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgAqAC8AXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBBAHUAcwB0AHIAYQBsAGkAYQBuAFMAdABhAHQAZQBzAFQAZQByAHIAaQB0AG8AcgBpAGUAcwBfAFQAaQB0AGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAQQB1AHMAdAByAGEAbABpAGEAbgAgAHMAdABhAHQAZQBzACAAYQBuAGQAIAB0AGUAcgByAGkAdABvAHIAaQBlAHMAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEEAdQBzAHQAcgBhAGwAaQBhAG4AUwB0AGEAdABlAHMAVABlAHIAcgBpAHQAbwByAGkAZQBzAF8AVgBhAHIAaQBhAGIAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQQB1AHMAdAByAGEAbABpAGEAbgBTAHQAYQB0AGUAcwBUAGUAcgByAGkAdABvAHIAaQBlAHMAXwBVAG4AaQB0AFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQQB1AHMAdAByAGEAbABpAGEAbgBTAHQAYQB0AGUAcwBUAGUAcgByAGkAdABvAHIAaQBlAHMAXwBTAG8AdQByAGMAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEEAdQBzAHQAcgBhAGwAaQBhAG4AUwB0AGEAdABlAHMAVABlAHIAcgBpAHQAbwByAGkAZQBzAF8ARABhAHQAYQBcAG4AIAAgACAAPQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAE0AQQBLAEUAQQBSAFIAQQBZACgAOQAsACAAMwAsACAAXABuACAAIAAgACAAIAAgAEwAQQBNAEIARABBACgAcgAsAGMALAAgAFwAbgAgACAAIAAgACAAIAAgACAASQBOAEQARQBYACgAewBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAUwB0AGEAdABlAC8AVABlAHIAcgBpAHQAbwByAHkAXAAiACwAIABcACIAQwBvAG0AbQBvAG4AIABOAGEAbQBlAFwAIgAsACAAXAAiAEEAYgBiAHIAZQB2AGkAYQB0AGkAbwBuAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBOAGUAdwAgAFMAbwB1AHQAaAAgAFcAYQBsAGUAcwBcACIALAAgAFwAIgBOAGUAdwAgAFMAbwB1AHQAaAAgAFcAYQBsAGUAcwBcACIALAAgAFwAIgBOAFMAVwBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAQQB1AHMAdAByAGEAbABpAGEAbgAgAEMAYQBwAGkAdABhAGwAIABUAGUAcgByAGkAdABvAHIAeQBcACIALAAgAFwAIgBBAEMAVABcACIALAAgAFwAIgBBAEMAVABcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVgBpAGMAdABvAHIAaQBhAFwAIgAsACAAXAAiAFYAaQBjAHQAbwByAGkAYQBcACIALAAgAFwAIgBWAEkAQwBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAUQB1AGUAZQBuAHMAbABhAG4AZABcACIALAAgAFwAIgBRAHUAZQBlAG4AcwBsAGEAbgBkAFwAIgAsACAAXAAiAFEATABEAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBTAG8AdQB0AGgAIABBAHUAcwB0AHIAYQBsAGkAYQBcACIALAAgAFwAIgBTAG8AdQB0AGgAIABBAHUAcwB0AHIAYQBsAGkAYQBcACIALAAgAFwAIgBTAEEAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFcAZQBzAHQAZQByAG4AIABBAHUAcwB0AHIAYQBsAGkAYQBcACIALAAgAFwAIgBXAGUAcwB0AGUAcgBuACAAQQB1AHMAdAByAGEAbABpAGEAXAAiACwAIABcACIAVwBBAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBUAGEAcwBtAGEAbgBpAGEAXAAiACwAIABcACIAVABhAHMAbQBhAG4AaQBhAFwAIgAsACAAXAAiAFQAQQBTAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBOAG8AcgB0AGgAZQByAG4AIABUAGUAcgByAGkAdABvAHIAeQBcACIALAAgAFwAIgBOAG8AcgB0AGgAZQByAG4AIABUAGUAcgByAGkAdABvAHIAeQBcACIALAAgAFwAIgBOAFQAXAAiAFwAbgAgACAAIAAgACAAIAAgACAAfQAsACAAcgAsACAAYwApAFwAbgAgACAAIAAgACAAIAApAFwAbgAgACAAIAAgACkAXABuACAAIAApADsAXABuAFwAbgAvACoAIABcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBXAEEAUwBBADQAQQByAGUAYQBzAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuACoALwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFcAQQBTAEEANABBAHIAZQBhAHMAXwBUAGkAdABsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAEEAQgBTACAAUwB0AGEAdABpAHMAdABjAGEAbAAgAEEAcgBlAGEAcwAgAEwAZQB2AGUAbAAgADQAIAAtACAAVwBlAHMAdABlAHIAbgAgAEEAdQBzAHQAcgBhAGwAaQBhAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBXAEEAUwBBADQAQQByAGUAYQBzAF8AVgBhAHIAaQBhAGIAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AVwBBAFMAQQA0AEEAcgBlAGEAcwBfAFUAbgBpAHQAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBXAEEAUwBBADQAQQByAGUAYQBzAF8AUwBvAHUAcgBjAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAEEAdQBzAHQAcgBhAGwAaQBhAG4AIABCAHUAcgBlAGEAdQAgAG8AZgAgAFMAdABhAHQAaQBzAHQAaQBjAHMAIAAoAEEAQgBTACkAIAAtACAAUwB0AGEAdABpAHMAdABpAGMAYQBsACAAQQByAGUAYQBzACAATABlAHYAZQBsACAAMgAgAC0AIAAyADAAMgAxACAALQAgAFMAaABhAHAAZQBmAGkAbABlAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBXAEEAUwBBADQAQQByAGUAYQBzAF8ARABhAHQAYQBcAG4AIAAgACAAPQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAE0AQQBLAEUAQQBSAFIAQQBZACgAMQAxACwAIAAxACwAIABcAG4AIAAgACAAIAAgACAATABBAE0AQgBEAEEAKAByACwAYwAsACAAXABuACAAIAAgACAAIAAgACAAIABJAE4ARABFAFgAKAB7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBTAEEAIAA0ACAATgBhAG0AZQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAQgB1AG4AYgB1AHIAeQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIATQBhAG4AZAB1AHIAYQBoAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBQAGUAcgB0AGgAIAAtACAASQBuAG4AZQByAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBQAGUAcgB0AGgAIAAtACAATgBvAHIAdABoACAARQBhAHMAdABcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAUABlAHIAdABoACAALQAgAE4AbwByAHQAaAAgAFcAZQBzAHQAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFAAZQByAHQAaAAgAC0AIABTAG8AdQB0AGgAIABFAGEAcwB0AFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBQAGUAcgB0AGgAIAAtACAAUwBvAHUAdABoACAAVwBlAHMAdABcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVwBlAHMAdABlAHIAbgAgAEEAdQBzAHQAcgBhAGwAaQBhACAALQAgAFcAaABlAGEAdAAgAEIAZQBsAHQAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFcAZQBzAHQAZQByAG4AIABBAHUAcwB0AHIAYQBsAGkAYQAgAC0AIABPAHUAdABiAGEAYwBrACAAKABOAG8AcgB0AGgAKQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVwBlAHMAdABlAHIAbgAgAEEAdQBzAHQAcgBhAGwAaQBhACAALQAgAE8AdQB0AGIAYQBjAGsAIAAoAFMAbwB1AHQAaAApAFwAIgBcAG4AIAAgACAAIAAgACAAIAAgAH0ALAAgAHIALAAgAGMAKQBcAG4AIAAgACAAIAAgACAAKQBcAG4AIAAgACAAIAApAFwAbgAgACAAKQA7AFwAbgBcAG4ALwAqACAAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AVwBlAHQAQQBuAGQARAByAHkAWgBvAG4AZQBzAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuACoALwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFcAZQB0AEEAbgBkAEQAcgB5AFoAbwBuAGUAcwBfAFQAaQB0AGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAVgBFAEUAUgBHACAAQQB1AHMAdAByAGEAbABpAGEAbgAgAHcAZQB0ACAAYQBuAGQAIABkAHIAeQAgAHoAbwBuAGUAcwBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AVwBlAHQAQQBuAGQARAByAHkAWgBvAG4AZQBzAF8AVgBhAHIAaQBhAGIAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AVwBlAHQAQQBuAGQARAByAHkAWgBvAG4AZQBzAF8AVQBuAGkAdABcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFcAZQB0AEEAbgBkAEQAcgB5AFoAbwBuAGUAcwBfAFMAbwB1AHIAYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBWAEUARQBSAEcAIAAyADAAMgA2ADoAIABUAGEAYgBsAGUAIAAxAC4AMgA6ACAAVAByAGEAbgBzAGwAYQB0AGkAbgBnACAAYwBsAGkAbQBhAHQAZQAgAHoAbwBuAGUAcwAgAHQAbwAgAHcAZQB0ACAAYQBuAGQAIABkAHIAeQAgAHoAbwBuAGUAcwBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AVwBlAHQAQQBuAGQARAByAHkAWgBvAG4AZQBzAF8AVgBhAHIAaQBhAHQAaQBvAG4AXABuACAAIAAgAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABNAEEASwBFAEEAUgBSAEEAWQAoADMALAAgADEALAAgAFwAbgAgACAAIAAgACAAIABMAEEATQBCAEQAQQAoAHIALABjACwAIABcAG4AIAAgACAAIAAgACAAIAAgAEkATgBEAEUAWAAoAHsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFYAQQBSAEkAQQBUAEkATwBOACAATwBGACAAUwBPAFUAUgBDAEUAIABEAEEAVABBADoAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEEAZABkAGUAZAAgAHcAYQByAG0AIAAvACAAYwBvAG8AbAAgAHQAZQBtAHAAZQByAGEAdABlACAAbQBvAGkAcwB0ACAALwAgAGQAcgB5ACAALQAgAGwAbwB3ACAAZgByAG8AcwB0ACAAYQBuAGQAIABoAGkAZwBoACAAdABlAG0AcAAgAGMAbABhAHMAcwBlAHMAIAB0AG8AIABhAGMAYwBvAG0AbQBvAGQAYQB0AGUAIABjAGwAaQBtAGEAdABlACAAcwBjAGUAbgBhAHIAaQBvAHMAIABlAHgAYwBsAHUAZABlAGQAIABiAHkAIABWAEUARQBSAEcAIABjAHIAaQB0AGUAcgBpAGEALgBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIARgBpAHgAZQBkACAAdAB5AHAAbwAgAC0AIABDAGgAYQBuAGcAZQBkACAAJwBGAHIAeQAnACAAdABvACAAJwBEAHIAeQAnAC4AXAAiAFwAbgAgACAAIAAgACAAIAAgACAAfQAsACAAcgAsACAAYwApAFwAbgAgACAAIAAgACAAIAApAFwAbgAgACAAIAAgACkAXABuACAAIAApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBXAGUAdABBAG4AZABEAHIAeQBaAG8AbgBlAHMAXwBEAGEAdABhAFwAbgAgACAAIAA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAATQBBAEsARQBBAFIAUgBBAFkAKAAxADUALAAgADIALAAgAFwAbgAgACAAIAAgACAAIABMAEEATQBCAEQAQQAoAHIALABjACwAIABcAG4AIAAgACAAIAAgACAAIAAgAEkATgBEAEUAWAAoAHsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEMAbABpAG0AYQB0AGUAIABaAG8AbgBlAFwAIgAsACAAXAAiAFcAZQB0ACAAbwByACAARAByAHkAIABaAG8AbgBlAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBUAHIAbwBwAGkAYwBhAGwAIABtAG8AbgB0AGEAbgBlAFwAIgAsACAAXAAiAFcAZQB0ACAAYwBsAGkAbQBhAHQAZQAgAHoAbwBuAGUAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFQAcgBvAHAAaQBjAGEAbAAgAHcAZQB0AFwAIgAsACAAXAAiAFcAZQB0ACAAYwBsAGkAbQBhAHQAZQAgAHoAbwBuAGUAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFQAcgBvAHAAaQBjAGEAbAAgAG0AbwBpAHMAdABcACIALAAgAFwAIgBXAGUAdAAgAGMAbABpAG0AYQB0AGUAIAB6AG8AbgBlAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBUAHIAbwBwAGkAYwBhAGwAIABkAHIAeQBcACIALAAgAFwAIgBEAHIAeQAgAGMAbABpAG0AYQB0AGUAIAB6AG8AbgBlAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBXAGEAcgBtACAAdABlAG0AcABlAHIAYQB0AGUAIABtAG8AaQBzAHQAXAAiACwAIABcACIAVwBlAHQAIABjAGwAaQBtAGEAdABlACAAegBvAG4AZQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVwBhAHIAbQAgAHQAZQBtAHAAZQByAGEAdABlACAAZAByAHkAXAAiACwAIABcACIARAByAHkAIABjAGwAaQBtAGEAdABlACAAegBvAG4AZQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAQwBvAG8AbAAgAHQAZQBtAHAAZQByAGEAdABlACAAbQBvAGkAcwB0AFwAIgAsACAAXAAiAFcAZQB0ACAAYwBsAGkAbQBhAHQAZQAgAHoAbwBuAGUAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEMAbwBvAGwAIAB0AGUAbQBwAGUAcgBhAHQAZQAgAGQAcgB5AFwAIgAsACAAXAAiAEQAcgB5ACAAYwBsAGkAbQBhAHQAZQAgAHoAbwBuAGUAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFcAYQByAG0AIAB0AGUAbQBwAGUAcgBhAHQAZQAgAG0AbwBpAHMAdAAgAC0AIABsAG8AdwAgAGYAcgBvAHMAdABcACIALAAgAFwAIgBXAGUAdAAgAGMAbABpAG0AYQB0AGUAIAB6AG8AbgBlAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBXAGEAcgBtACAAdABlAG0AcABlAHIAYQB0AGUAIABkAHIAeQAgAC0AIABsAG8AdwAgAGYAcgBvAHMAdABcACIALAAgAFwAIgBEAHIAeQAgAGMAbABpAG0AYQB0AGUAIAB6AG8AbgBlAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBXAGEAcgBtACAAdABlAG0AcABlAHIAYQB0AGUAIABtAG8AaQBzAHQAIAAtACAAaABpAGcAaAAgAHQAZQBtAHAAXAAiACwAIABcACIAVwBlAHQAIABjAGwAaQBtAGEAdABlACAAegBvAG4AZQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVwBhAHIAbQAgAHQAZQBtAHAAZQByAGEAdABlACAAZAByAHkAIAAtACAAaABpAGcAaAAgAHQAZQBtAHAAXAAiACwAIABcACIARAByAHkAIABjAGwAaQBtAGEAdABlACAAegBvAG4AZQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAQwBvAG8AbAAgAHQAZQBtAHAAZQByAGEAdABlACAAbQBvAGkAcwB0ACAALQAgAGwAbwB3ACAAZgByAG8AcwB0AFwAIgAsACAAXAAiAFcAZQB0ACAAYwBsAGkAbQBhAHQAZQAgAHoAbwBuAGUAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEMAbwBvAGwAIAB0AGUAbQBwAGUAcgBhAHQAZQAgAGQAcgB5ACAALQAgAGwAbwB3ACAAZgByAG8AcwB0AFwAIgAsACAAXAAiAEQAcgB5ACAAYwBsAGkAbQBhAHQAZQAgAHoAbwBuAGUAXAAiAFwAbgAgACAAIAAgACAAIAAgACAAfQAsACAAcgAsACAAYwApAFwAbgAgACAAIAAgACAAIAApAFwAbgAgACAAIAAgACkAXABuACAAIAApADsAXABuAFwAbgAvACoAIABcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBDAGwAaQBtAGEAdABlAFoAbwBuAGUAcwBcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgAqAC8AXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBDAGwAaQBtAGEAdABlAFoAbwBuAGUAcwBfAFQAaQB0AGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAVgBFAEUAUgBHACAAQQB1AHMAdAByAGEAbABpAGEAbgAgAGMAbABpAG0AYQB0AGUAIAB6AG8AbgBlAHMAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEMAbABpAG0AYQB0AGUAWgBvAG4AZQBzAF8AVgBhAHIAaQBhAGIAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQwBsAGkAbQBhAHQAZQBaAG8AbgBlAHMAXwBVAG4AaQB0AFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQwBsAGkAbQBhAHQAZQBaAG8AbgBlAHMAXwBTAG8AdQByAGMAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAVgBFAEUAUgBHACAAMgAwADIANgA6ACAAVABhAGIAbABlACAAMQAuADMAOgAgAEMAbABpAG0AYQB0AGUAIABhAG4AZAAgAFIAYQBpAG4AZgBhAGwAbAAgAHoAbwBuAGUAIABjAGwAYQBzAHMAaQBmAGkAYwBhAHQAaQBvAG4AcwAgAGEAbgBkACAAZABlAGYAaQBuAGkAdABpAG8AbgBzAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBDAGwAaQBtAGEAdABlAFoAbwBuAGUAcwBfAFYAYQByAGkAYQB0AGkAbwBuAFwAbgAgACAAIAA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAATQBBAEsARQBBAFIAUgBBAFkAKAA1ACwAIAAxACwAIABcAG4AIAAgACAAIAAgACAATABBAE0AQgBEAEEAKAByACwAYwAsACAAXABuACAAIAAgACAAIAAgACAAIABJAE4ARABFAFgAKAB7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBWAEEAUgBJAEEAVABJAE8ATgAgAE8ARgAgAFMATwBVAFIAQwBFACAARABBAFQAQQA6AFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBBAGQAZABlAGQAIAB3AGEAcgBtACAALwAgAGMAbwBvAGwAIAB0AGUAbQBwAGUAcgBhAHQAZQAgAG0AbwBpAHMAdAAgAC8AIABkAHIAeQAgAC0AIABsAG8AdwAgAGYAcgBvAHMAdAAgAGEAbgBkACAAaABpAGcAaAAgAHQAZQBtAHAAIABjAGwAYQBzAHMAZQBzACAAdABvACAAYQBjAGMAbwBtAG0AbwBkAGEAdABlACAAYwBsAGkAbQBhAHQAZQAgAHMAYwBlAG4AYQByAGkAbwBzACAAZQB4AGMAbAB1AGQAZQBkACAAYgB5ACAAVgBFAEUAUgBHACAAYwByAGkAdABlAHIAaQBhAC4AXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEYAaQB4AGUAZAAgAHQAeQBwAG8AIABpAG4AIABNAEEAVAAgAHYAYQBsAHUAZQAgAGYAbwByACAAdwBhAHIAbQAgAHQAZQBtAHAAZQByAGEAdABlACAAZAByAHkAIAAtACAAYwBoAGEAbgBnAGUAZAAgADEAMAAgAHQAbwAgADEAMQAuAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBBAGQAZABlAGQAIABtAGkAbgAgAGEAbgBkACAAbQBhAHgAIABjAG8AbAB1AG0AbgBzACAAZgBvAHIAIABNAEEAVAAsACAATQBBAFAALAAgAGYAcgBvAHMAdAAgAGQAYQB5AHMAIABwAGUAcgAgAHkAZQBhAHIALAAgAGUAbABlAHYAYQB0AGkAbwBuACwAIABNAEEAUAA6AFAARQBUACAAdABvACAAYwBhAGwAYwB1AGwAYQB0AGUAIAB6AG8AbgBlAHMAIABmAHIAbwBtACAAcgBlAGEAbAAgAGMAbABpAG0AYQB0AGUAIABkAGEAdABhAC4AXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEcAQQBGACAAYQBjAGMAZQBwAHQAcwAgAHIAYQBpAG4AZgBhAGwAbAAgAGEAcwAgAGEAIABwAHIAbwB4AHkAIABmAG8AcgAgAHAAcgBlAGMAaQBwAGkAdABhAHQAaQBvAG4ALgBcACIAXABuACAAIAAgACAAIAAgACAAIAB9ACwAIAByACwAIABjACkAXABuACAAIAAgACAAIAAgACkAXABuACAAIAAgACAAKQBcAG4AIAAgACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEMAbABpAG0AYQB0AGUAWgBvAG4AZQBzAF8ARABhAHQAYQBcAG4AIAAgACAAPQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAE0AQQBLAEUAQQBSAFIAQQBZACgAOQAsACAAMQA2ACwAIABcAG4AIAAgACAAIAAgACAATABBAE0AQgBEAEEAKAByACwAYwAsACAAXABuACAAIAAgACAAIAAgACAAIABJAE4ARABFAFgAKAB7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBDAGwAaQBtAGEAdABlACAAWgBvAG4AZQBcACIALAAgAFwAIgBNAEEAVABcACIALAAgAFwAIgBNAEEAUABcACIALAAgAFwAIgBGAHIAbwBzAHQAIABkAGEAeQBzACAAcABlAHIAIAB5AGUAYQByAFwAIgAsACAAXAAiAEUAbABlAHYAYQB0AGkAbwBuAFwAIgAsACAAXAAiAE0AQQBQADoAUABFAFQAXAAiACwAIABcACIATQBpAG4AIAB0AGUAbQBwAFwAIgAsACAAXAAiAE0AYQB4ACAAdABlAG0AcABcACIALAAgAFwAIgBNAGkAbgAgAHIAYQBpAG4AZgBhAGwAbABcACIALAAgAFwAIgBNAGEAeAAgAHIAYQBpAG4AZgBhAGwAbABcACIALAAgAFwAIgBNAGkAbgAgAGYAcgBvAHMAdAAgAGQAYQB5AHMAXAAiACwAIABcACIATQBhAHgAIABmAHIAbwBzAHQAIABkAGEAeQBzAFwAIgAsACAAXAAiAE0AaQBuACAAZQBsAGUAdgBhAHQAaQBvAG4AXAAiACwAIABcACIATQBhAHgAIABlAGwAZQB2AGEAdABpAG8AbgBcACIALAAgAFwAIgBNAGkAbgAgAE0AQQBQADoAUABFAFQAXAAiACwAIABcACIATQBpAG4AIABNAEEAUAA6AFAARQBUAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBUAHIAbwBwAGkAYwBhAGwAIABtAG8AbgB0AGEAbgBlAFwAIgAsACAAXAAiAD4AIAAxADgAIABDAFwAIgAsACAAXAAiAEEAbgB5AFwAIgAsACAAXAAiAGQiIAA3AFwAIgAsACAAXAAiAD4AIAAxADAAMAAwACAAbQBcACIALAAgAFwAIgBBAG4AeQBcACIALAAgADEAOAAuADAAMAAxACwAIAA5ADkAOQA5ADkAOQAsACAALQA5ADkAOQA5ADkAOQAsACAAOQA5ADkAOQA5ADkALAAgAC0AOQA5ADkAOQA5ADkALAAgADcALAAgADEAMAAwADAALAAgADkAOQA5ADkAOQA5ACwAIAAtADkAOQA5ADkAOQA5ACwAIAA5ADkAOQA5ADkAOQA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBUAHIAbwBwAGkAYwBhAGwAIAB3AGUAdABcACIALAAgAFwAIgA+ACAAMQA4ACAAQwBcACIALAAgAFwAIgA+ACAAMgAwADAAMAAgAG0AbQBcACIALAAgAFwAIgBkIiAANwBcACIALAAgAFwAIgBkIiAAMQAwADAAMAAgAG0AXAAiACwAIABcACIAQQBuAHkAXAAiACwAIAAxADgALgAwADAAMQAsACAAOQA5ADkAOQA5ADkALAAgADIAMAAwADAALgAwADAAMQAsACAAOQA5ADkAOQA5ADkALAAgAC0AOQA5ADkAOQA5ADkALAAgADcALAAgAC0AOQA5ADkAOQA5ADkALAAgADkAOQA5AC4AOQA5ADkALAAgACAALQA5ADkAOQA5ADkAOQAsACAAOQA5ADkAOQA5ADkAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVAByAG8AcABpAGMAYQBsACAAbQBvAGkAcwB0AFwAIgAsACAAXAAiAD4AIAAxADgAIABDAFwAIgAsACAAXAAiAD4AIAAxADAAMAAwACAAbQBtACAALQAgAGQiIAAyADAAMAAwACAAbQBtAFwAIgAsACAAXAAiAGQiIAA3AFwAIgAsACAAXAAiAGQiIAAxADAAMAAwACAAbQBcACIALAAgAFwAIgBBAG4AeQBcACIALAAgADEAOAAuADAAMAAxACwAIAA5ADkAOQA5ADkAOQAsACAAMQAwADAAMAAuADAAMAAxACwAIAAyADAAMAAwACwAIAAtADkAOQA5ADkAOQA5ACwAIAA3ACwAIAAtADkAOQA5ADkAOQA5ACwAIAA5ADkAOQAuADkAOQA5ACwAIAAgAC0AOQA5ADkAOQA5ADkALAAgADkAOQA5ADkAOQA5ADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFQAcgBvAHAAaQBjAGEAbAAgAGQAcgB5AFwAIgAsACAAXAAiAD4AIAAxADgAIABDAFwAIgAsACAAXAAiAGQiIAAxADAAMAAwACAAbQBtAFwAIgAsACAAXAAiAGQiIAA3AFwAIgAsACAAXAAiAGQiIAAxADAAMAAwACAAbQBcACIALAAgAFwAIgBBAG4AeQBcACIALAAgADEAOAAuADAAMAAxACwAIAA5ADkAOQA5ADkAOQAsACAALQA5ADkAOQA5ADkAOQAsACAAMQAwADAAMAAsACAALQA5ADkAOQA5ADkAOQAsACAANwAsACAALQA5ADkAOQA5ADkAOQAsACAAOQA5ADkALgA5ADkAOQAsACAAIAAtADkAOQA5ADkAOQA5ACwAIAA5ADkAOQA5ADkAOQA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBXAGEAcgBtACAAdABlAG0AcABlAHIAYQB0AGUAIABtAG8AaQBzAHQAXAAiACwAIABcACIAPgAgADEAMAAgAEMAXAAiACwAIABcACIAQQBuAHkAXAAiACwAIABcACIAQQBuAHkAXAAiACwAIABcACIAQQBuAHkAXAAiACwAIABcACIAPgAgADEAXAAiACwAIAAxADAALgAwADAAMQAsACAAOQA5ADkAOQA5ADkALAAgAC0AOQA5ADkAOQA5ADkALAAgADkAOQA5ADkAOQA5ACwAIAAtADkAOQA5ADkAOQA5ACwAIAA5ADkAOQA5ADkAOQAsACAALQA5ADkAOQA5ADkAOQAsACAAOQA5ADkAOQA5ADkALAAgADEALgAwADAAMQAsACAAOQA5ADkAOQA5ADkAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVwBhAHIAbQAgAHQAZQBtAHAAZQByAGEAdABlACAAZAByAHkAXAAiACwAIABcACIAPgAgADEAMAAgAEMAXAAiACwAIABcACIAQQBuAHkAXAAiACwAIABcACIAQQBuAHkAXAAiACwAIABcACIAQQBuAHkAXAAiACwAIABcACIAZCIgADEAXAAiACwAIAAxADAALgAwADAAMQAsACAAOQA5ADkAOQA5ADkALAAgAC0AOQA5ADkAOQA5ADkALAAgADkAOQA5ADkAOQA5ACwAIAAtADkAOQA5ADkAOQA5ACwAIAA5ADkAOQA5ADkAOQAsACAALQA5ADkAOQA5ADkAOQAsACAAOQA5ADkAOQA5ADkALAAgACAALQA5ADkAOQA5ADkAOQAsACAAMQA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBDAG8AbwBsACAAdABlAG0AcABlAHIAYQB0AGUAIABtAG8AaQBzAHQAXAAiACwAIABcACIAPgAgADAAIABDACAALQAgAGQiIAAxADAAIABDAFwAIgAsACAAXAAiAEEAbgB5AFwAIgAsACAAXAAiAEEAbgB5AFwAIgAsACAAXAAiAEEAbgB5AFwAIgAsACAAXAAiAD4AIAAxAFwAIgAsACAALQA5ADkAOQA5ADkAOQAsACAAMQAwACwAIAAtADkAOQA5ADkAOQA5ACwAIAA5ADkAOQA5ADkAOQAsACAALQA5ADkAOQA5ADkAOQAsACAAOQA5ADkAOQA5ADkALAAgAC0AOQA5ADkAOQA5ADkALAAgADkAOQA5ADkAOQA5ACwAIAAxAC4AMAAwADEALAAgADkAOQA5ADkAOQA5ADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEMAbwBvAGwAIAB0AGUAbQBwAGUAcgBhAHQAZQAgAGQAcgB5AFwAIgAsACAAXAAiAD4AIAAwACAAQwAgAC0AIABkIiAAMQAwACAAQwBcACIALAAgAFwAIgBBAG4AeQBcACIALAAgAFwAIgBBAG4AeQBcACIALAAgAFwAIgBBAG4AeQBcACIALAAgAFwAIgBkIiAAMQBcACIALAAgAC0AOQA5ADkAOQA5ADkALAAgADEAMAAsACAALQA5ADkAOQA5ADkAOQAsACAAOQA5ADkAOQA5ADkALAAgAC0AOQA5ADkAOQA5ADkALAAgADkAOQA5ADkAOQA5ACwAIAAtADkAOQA5ADkAOQA5ACwAIAA5ADkAOQA5ADkAOQAsACAAIAAtADkAOQA5ADkAOQA5ACwAIAAxAFwAbgAgACAAIAAgACAAIAAgACAAfQAsACAAcgAsACAAYwApAFwAbgAgACAAIAAgACAAIAApAFwAbgAgACAAIAAgACkAXABuACAAIAApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBDAGwAaQBtAGEAdABlAFoAbwBuAGUAcwBfAEEAcABwAGUAbgBkAGkAYwBlAHMAXABuACAAIAAgAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABNAEEASwBFAEEAUgBSAEEAWQAoADQALAAgADEALAAgAFwAbgAgACAAIAAgACAAIABMAEEATQBCAEQAQQAoAHIALABjACwAIABcAG4AIAAgACAAIAAgACAAIAAgAEkATgBEAEUAWAAoAHsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAE4AbwB0AGUAOgBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIATQBBAFQAIAA9ACAAbQBlAGEAbgAgAGEAbgBuAHUAYQBsACAAdABlAG0AcABlAHIAYQB0AHUAcgBlAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBNAEEAUAAgAD0AIABtAGUAYQBuACAAYQBuAG4AdQBhAGwAIABwAHIAZQBjAGkAcABpAHQAYQB0AGkAbwBuAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBQAEUAVAAgAD0AIABwAG8AdABlAG4AdABpAGEAbAAgAGUAdgBhAHAAbwB0AHIAYQBuAHMAcABpAHIAYQB0AGkAbwBuAFwAIgBcAG4AIAAgACAAIAAgACAAIAAgAH0ALAAgAHIALAAgAGMAKQBcAG4AIAAgACAAIAAgACAAKQBcAG4AIAAgACAAIAApAFwAbgAgACAAKQA7AFwAbgBcAG4AXABuAC8AKgAgAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFQAZQBtAHAAZQByAGEAdAB1AHIAZQBaAG8AbgBlAHMAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AKgAvAFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AVABlAG0AcABlAHIAYQB0AHUAcgBlAFoAbwBuAGUAcwBfAFQAaQB0AGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAVgBFAEUAUgBHACAAQQB1AHMAdAByAGEAbABpAGEAbgAgAHQAZQBtAHAAZQByAGEAdAB1AHIAZQAgAHoAbwBuAGUAcwBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AVABlAG0AcABlAHIAYQB0AHUAcgBlAFoAbwBuAGUAcwBfAFYAYQByAGkAYQBiAGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFQAZQBtAHAAZQByAGEAdAB1AHIAZQBaAG8AbgBlAHMAXwBVAG4AaQB0AFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AVABlAG0AcABlAHIAYQB0AHUAcgBlAFoAbwBuAGUAcwBfAFMAbwB1AHIAYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBWAEUARQBSAEcAIAAyADAAMgA2ADoAIABUAGEAYgBsAGUAIAAxAC4AMwA6ACAAQwBsAGkAbQBhAHQAZQAgAGEAbgBkACAAUgBhAGkAbgBmAGEAbABsACAAegBvAG4AZQAgAGMAbABhAHMAcwBpAGYAaQBjAGEAdABpAG8AbgBzACAAYQBuAGQAIABkAGUAZgBpAG4AaQB0AGkAbwBuAHMAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFQAZQBtAHAAZQByAGEAdAB1AHIAZQBaAG8AbgBlAHMAXwBWAGEAcgBpAGEAdABpAG8AbgBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAVgBBAFIASQBBAFQASQBPAE4AIABPAEYAIABTAE8AVQBSAEMARQAgAEQAQQBUAEEAOgAgAEEAZABkAGUAZAAgAGUAeAB0AHIAYQAgAE0AQQBUACAAbQBpAG4AIABhAG4AZAAgAE0AQQBUACAAbQBhAHgAIABjAG8AbAB1AG0AbgBzACAAdABvACAAYwBhAGwAYwB1AGwAYQB0AGUAIAB6AG8AbgBlACAAZgByAG8AbQAgAHIAZQBhAGwAIAB0AGUAbQBwAGUAcgBhAHQAdQByAGUAIABkAGEAdABhAC4AXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFQAZQBtAHAAZQByAGEAdAB1AHIAZQBaAG8AbgBlAHMAXwBEAGEAdABhAFwAbgAgACAAIAA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAATQBBAEsARQBBAFIAUgBBAFkAKAA0ACwAIAA0ACwAIABcAG4AIAAgACAAIAAgACAATABBAE0AQgBEAEEAKAByACwAYwAsACAAXABuACAAIAAgACAAIAAgACAAIABJAE4ARABFAFgAKAB7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBUAGUAbQBwAGUAcgBhAHQAdQByAGUAIABaAG8AbgBlAFwAIgAsACAAXAAiAE0AZQBkAGkAYQBuACAAQQBuAG4AdQBhAGwAIABUAGUAbQBwAGUAcgBhAHQAdQByAGUAIAAoAE0AQQBUACkAXAAiACwAIABcACIATQBpAG4AIABNAEEAVABcACIALAAgAFwAIgBNAGEAeAAgAE0AQQBUAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBXAGEAcgBtAFwAIgAsACAAXAAiAGUiIAAyADYAIABDAFwAIgAsACAAMgA2ACwAIAA5ADkAOQA5ADkAOQA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBUAGUAbQBwAGUAcgBhAHQAZQBcACIALAAgAFwAIgAxADUAIAAtACAAMgA1ACAAQwBcACIALAAgADEANQAsACAAMgA1AC4AOQA5ADkAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAQwBvAG8AbABcACIALAAgAFwAIgBkIiAAMQA0ACAAQwBcACIALAAgAC0AOQA5ADkAOQA5ADkALAAgADEANAAuADkAOQA5AFwAbgAgACAAIAAgACAAIAAgACAAfQAsACAAcgAsACAAYwApAFwAbgAgACAAIAAgACAAIAApAFwAbgAgACAAIAAgACkAXABuACAAIAApADsAXABuAFwAbgAvACoAIABcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBSAGEAaQBuAGYAYQBsAGwAWgBvAG4AZQBzAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuACoALwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFIAYQBpAG4AZgBhAGwAbABaAG8AbgBlAHMAXwBUAGkAdABsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFYARQBFAFIARwAgAEEAdQBzAHQAcgBhAGwAaQBhAG4AIAByAGEAaQBuAGYAYQBsAGwAIAB6AG8AbgBlAHMAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFIAYQBpAG4AZgBhAGwAbABaAG8AbgBlAHMAXwBWAGEAcgBpAGEAYgBsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBSAGEAaQBuAGYAYQBsAGwAWgBvAG4AZQBzAF8AVQBuAGkAdABcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFIAYQBpAG4AZgBhAGwAbABaAG8AbgBlAHMAXwBTAG8AdQByAGMAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAVgBFAEUAUgBHACAAMgAwADIANgA6ACAAVABhAGIAbABlACAAMQAuADMAOgAgAEMAbABpAG0AYQB0AGUAIABhAG4AZAAgAFIAYQBpAG4AZgBhAGwAbAAgAHoAbwBuAGUAIABjAGwAYQBzAHMAaQBmAGkAYwBhAHQAaQBvAG4AcwAgAGEAbgBkACAAZABlAGYAaQBuAGkAdABpAG8AbgBzAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBSAGEAaQBuAGYAYQBsAGwAWgBvAG4AZQBzAF8AVgBhAHIAaQBhAHQAaQBvAG4AXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFYAQQBSAEkAQQBUAEkATwBOACAATwBGACAAUwBPAFUAUgBDAEUAIABEAEEAVABBADoAIABBAGQAZABlAGQAIABlAHgAdAByAGEAIABSAGEAaQBuAGYAYQBsAGwAIABtAGkAbgAgAGEAbgBkACAAUgBhAGkAbgBmAGEAbABsACAAbQBhAHgAIABjAG8AbAB1AG0AbgBzACAAdABvACAAYwBhAGwAYwB1AGwAYQB0AGUAIAB6AG8AbgBlACAAZgByAG8AbQAgAHIAZQBhAGwAIAByAGEAaQBuAGYAYQBsAGwAIABkAGEAdABhAC4AXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFIAYQBpAG4AZgBhAGwAbABaAG8AbgBlAHMAXwBEAGEAdABhAFwAbgAgACAAIAA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAATQBBAEsARQBBAFIAUgBBAFkAKAAzACwAIAA0ACwAIABcAG4AIAAgACAAIAAgACAATABBAE0AQgBEAEEAKAByACwAYwAsACAAXABuACAAIAAgACAAIAAgACAAIABJAE4ARABFAFgAKAB7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBSAGEAaQBuAGYAYQBsAGwAIABaAG8AbgBlAFwAIgAsACAAXAAiAEEAbgBuAHUAYQBsACAAcgBhAGkAbgBmAGEAbABsAFwAIgAsACAAXAAiAFIAYQBpAG4AZgBhAGwAbAAgAG0AaQBuAFwAIgAsACAAXAAiAFIAYQBpAG4AZgBhAGwAbAAgAG0AYQB4AFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBIAGkAZwBoACAAcgBhAGkAbgBmAGEAbABsAFwAIgAsACAAXAAiAEEAbgBuAHUAYQBsACAAcgBhAGkAbgBmAGEAbABsACAAPgAgADYAMAAwAG0AbQBcACIALAAgADYAMAAwAC4AMAAwADEALAAgADkAOQA5ADkAOQA5ADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEwAbwB3ACAAcgBhAGkAbgBmAGEAbABsAFwAIgAsACAAXAAiAEEAbgBuAHUAYQBsACAAcgBhAGkAbgBmAGEAbABsACAAZCIgADYAMAAwAG0AbQBcACIALAAgAC0AOQA5ADkAOQA5ADkALAAgADYAMAAwAFwAbgAgACAAIAAgACAAIAAgACAAfQAsACAAcgAsACAAYwApAFwAbgAgACAAIAAgACAAIAApAFwAbgAgACAAIAAgACkAXABuACAAIAApADsAXABuAFwAbgAvACoAIABcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBMAGUAYQBjAGgAaQBuAGcAWgBvAG4AZQBzAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuACoALwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEwAZQBhAGMAaABpAG4AZwBaAG8AbgBlAHMAXwBUAGkAdABsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFYARQBFAFIARwAgAEEAdQBzAHQAcgBhAGwAaQBhAG4AIABsAGUAYQBjAGgAaQBuAGcAIAB6AG8AbgBlAHMAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEwAZQBhAGMAaABpAG4AZwBaAG8AbgBlAHMAXwBWAGEAcgBpAGEAYgBsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBMAGUAYQBjAGgAaQBuAGcAWgBvAG4AZQBzAF8AVQBuAGkAdABcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEwAZQBhAGMAaABpAG4AZwBaAG8AbgBlAHMAXwBTAG8AdQByAGMAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAVgBFAEUAUgBHACAAMgAwADIANgA6ACAAVABhAGIAbABlACAAMQAuADMAOgAgAEMAbABpAG0AYQB0AGUAIABhAG4AZAAgAFIAYQBpAG4AZgBhAGwAbAAgAHoAbwBuAGUAIABjAGwAYQBzAHMAaQBmAGkAYwBhAHQAaQBvAG4AcwAgAGEAbgBkACAAZABlAGYAaQBuAGkAdABpAG8AbgBzAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBMAGUAYQBjAGgAaQBuAGcAWgBvAG4AZQBzAF8AVgBhAHIAaQBhAHQAaQBvAG4AXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBMAGUAYQBjAGgAaQBuAGcAWgBvAG4AZQBzAF8ARABhAHQAYQBcAG4AIAAgACAAPQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAE0AQQBLAEUAQQBSAFIAQQBZACgANAAsACAAMgAsACAAXABuACAAIAAgACAAIAAgAEwAQQBNAEIARABBACgAcgAsAGMALAAgAFwAbgAgACAAIAAgACAAIAAgACAASQBOAEQARQBYACgAewBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIATABlAGEAYwBoAGkAbgBnACAAWgBvAG4AZQBcACIALAAgAFwAIgBMAGUAYQBjAGgAaQBuAGcAIABjAHIAaQB0AGUAcgBpAGEAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEwAZQBhAGMAaABpAG4AZwAgAG8AYwBjAHUAcgBzAFwAIgAsACAAXAAiAKMDKAA12F/cNdhO3DXYVtw12FvcKQA+AKMDKAA12DjcNdhH3DAAKQArADXYYNw12FzcNdhW3DXYWdwgADXYZNw12E7cNdhh3DXYUtw12F/cIAAOITXYXNw12FncNdhR3DXYVtw12FvcNdhU3CAANdhQ3DXYTtw12F3cNdhO3DXYUNw12FbcNdhh3DXYZtxcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIATABlAGEAYwBoAGkAbgBnACAAZABvAGUAcwAgAG4AbwB0ACAAbwBjAGMAdQByAFwAIgAsACAAXAAiAKMDKAA12F/cNdhO3DXYVtw12FvcKQBkIqMDKAA12DjcNdhH3DAAKQArADXYYNw12FzcNdhW3DXYWdwgADXYZNw12E7cNdhh3DXYUtw12F/cIAAOITXYXNw12FncNdhR3DXYVtw12FvcNdhU3CAANdhQ3DXYTtw12F3cNdhO3DXYUNw12FbcNdhh3DXYZtxcACIAXABuACAAIAAgACAAIAAgACAAIAB9ACwAIAByACwAIABjACkAXABuACAAIAAgACAAIAAgACkAXABuACAAIAAgACAAKQBcAG4AIAAgACkAOwBcAG4AXABuAC8AKgAgAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAcgBhAGMAVwBFAFQAXABuADUALgA1AC4AMgAuADMAIABDAG8AbgBzAHQAYQBuAHQAIABQAGEAcgBhAG0AZQB0AGUAcgBzAFwAbgBGAHIAYQBjAHQAaQBvAG4AIABvAGYAIABOACAAdABoAGEAdAAgAGkAcwAgAGEAdgBhAGkAbABhAGIAbABlACAAZgBvAHIAIABsAGUAYQBjAGgAaQBuAGcAIABhAG4AZAAgAHIAdQBuAG8AZgBmAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuACoALwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAcgBhAGMAVwBFAFQAXwBUAGkAdABsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAEYAcgBhAGMAdABpAG8AbgAgAG8AZgAgAE4AIAB0AGgAYQB0ACAAaQBzACAAYQB2AGEAaQBsAGEAYgBsAGUAIABmAG8AcgAgAGwAZQBhAGMAaABpAG4AZwAgAGEAbgBkACAAcgB1AG4AbwBmAGYAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAcgBhAGMAVwBFAFQAXwBVAG4AaQB0AFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgAoAEQAaQBtAGUAbgBzAGkAbwBuAGwAZQBzAHMAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAcgBhAGMAVwBFAFQAXwBTAG8AdQByAGMAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAVgBFAEUAUgBHACAAMgAwADIANgA6ADUALgA1AC4AMgAuADMAIABDAG8AbgBzAHQAYQBuAHQAIABQAGEAcgBhAG0AZQB0AGUAcgBzAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAHIAYQBjAFcARQBUAF8ATgBJAFIAUgBlAGYAZQByAGUAbgBjAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAHIAYQBjAFcARQBUAF8ARABhAHQAYQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABNAEEASwBFAEEAUgBSAEEAWQAoADMALAAgADIALAAgAFwAbgAgACAAIAAgACAAIABMAEEATQBCAEQAQQAoAHIALABjACwAIABcAG4AIAAgACAAIAAgACAAIAAgAEkATgBEAEUAWAAoAHsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEkAcwAgAGkAbgAgAGwAZQBhAGMAaABpAG4AZwAgAHoAbwBuAGUAXAAiACwAXAAiAEYAcgBhAGMAVwBFAFQAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFkAZQBzACAALQAgAGkAbgAgAGwAZQBhAGMAaABpAG4AZwAgAHoAbwBuAGUAXAAiACwAIAAxADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAE4AbwAgAC0AIABuAG8AdAAgAGkAbgAgAGwAZQBhAGMAaABpAG4AZwAgAHoAbwBuAGUAXAAiACwAIAAwAFwAbgAgACAAIAAgACAAIAAgACAAfQAsACAAcgAsACAAYwApAFwAbgAgACAAIAAgACAAIAApAFwAbgAgACAAIAAgACkAXABuACAAIAApADsAXABuAFwAbgAgACAAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgByAGEAYwBXAEUAVABfAFYAYQByAGkAYQB0AGkAbwBuAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoACgAXAAiAFwAIgApACkAOwBcAG4AXABuAFwAbgBcAG4ALwAqACAAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABhAHQAYQBTAGMAbwByAGUAcwBfAFMAYwBvAHAAZQAzAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuACoALwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEQAYQB0AGEAUwBjAG8AcgBlAHMAXwBTAGMAbwBwAGUAMwBfAFQAaQB0AGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAQQB1AHMAdAByAGEAbABpAGEAbgAgAGQAYQB0AGEAIABzAGMAbwByAGUAcwAgAGYAbwByACAAcwBjAG8AcABlACAAMwBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABhAHQAYQBTAGMAbwByAGUAcwBfAFMAYwBvAHAAZQAzAF8AVgBhAHIAaQBhAGIAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABhAHQAYQBTAGMAbwByAGUAcwBfAFMAYwBvAHAAZQAzAF8AVQBuAGkAdABcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEQAYQB0AGEAUwBjAG8AcgBlAHMAXwBTAGMAbwBwAGUAMwBfAFMAbwB1AHIAYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBWAEUARQBSAEcAIAAyADAAMgA2ADoAIABYAFgAWABYAFgAWABYAFgAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEQAYQB0AGEAUwBjAG8AcgBlAHMAXwBTAGMAbwBwAGUAMwBfAFYAYQByAGkAYQB0AGkAbwBuAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABhAHQAYQBTAGMAbwByAGUAcwBfAFMAYwBvAHAAZQAzAF8ARABhAHQAYQBcAG4AIAAgACAAPQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAE0AQQBLAEUAQQBSAFIAQQBZACgANgAsACAAMgAsACAAXABuACAAIAAgACAAIAAgAEwAQQBNAEIARABBACgAcgAsAGMALAAgAFwAbgAgACAAIAAgACAAIAAgACAASQBOAEQARQBYACgAewBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIARABhAHQAYQAgAHMAbwB1AHIAYwBlAFwAIgAsACAAXAAiAEQAYQB0AGEAIABzAGMAbwByAGUAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEkAbgB0AGUAcgBuAGEAdABpAG8AbgBhAGwAIABzAGMAbwBwAGUAIAAzACAAZABhAHQAYQBiAGEAcwBlAFwAIgAsACAAMQA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBBAHUAcwB0AHIAYQBsAGkAYQBuACAAcwBjAG8AcABlACAAMwAgAGQAYQB0AGEAYgBhAHMAZQBcACIALAAgADIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAUwB0AGEAdABlACAAbwByACAAcgBlAGcAaQBvAG4AYQBsACAAcwBjAG8AcABlACAAMwAgAGQAYQB0AGEAYgBhAHMAZQBcACIALAAgADMAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIARQBtAGkAcwBzAGkAbwBuAHMAIABpAG4AdABlAG4AcwBpAHQAeQAgAGMAYQBsAGMAdQBsAGEAdABlAGQAIABmAHIAbwBtACAAYQBwAHAAcgBvAHYAZQBkACAAbQBlAHQAaABvAGQAXAAiACwAIAA0ADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFYAZQByAGkAZgBpAGUAZAAgAGMAcgBlAGQAZQBuAHQAaQBhAGwAIABtAGEAdABjAGgAaQBuAGcAIABJAFMATwAxADQAMAA2ADcAXAAiACwAIAA1AFwAbgAgACAAIAAgACAAIAAgACAAfQAsACAAcgAsACAAYwApAFwAbgAgACAAIAAgACAAIAApAFwAbgAgACAAIAAgACkAXABuACAAIAApADsAXABuAFwAbgBcAG4ALwAqACAAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgByAGEAYwBMAEUAQQBDAEgAXABuADUALgA1AC4AMgAuADMAIABDAG8AbgBzAHQAYQBuAHQAIABQAGEAcgBhAG0AZQB0AGUAcgBzAFwAbgBGAHIAYQBjAHQAaQBvAG4AIABvAGYAIABOACAAdABoAGEAdAAgAGkAcwAgAGEAdgBhAGkAbABhAGIAbABlACAAZgBvAHIAIABsAGUAYQBjAGgAaQBuAGcAIABhAG4AZAAgAHIAdQBuAG8AZgBmAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuACoALwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAcgBhAGMATABFAEEAQwBIAF8AVABpAHQAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBGAHIAYQBjAHQAaQBvAG4AIABvAGYAIABOACAAdABoAGEAdAAgAGkAcwAgAGEAdgBhAGkAbABhAGIAbABlACAAZgBvAHIAIABsAGUAYQBjAGgAaQBuAGcAIABhAG4AZAAgAHIAdQBuAG8AZgBmAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAHIAYQBjAEwARQBBAEMASABfAFUAbgBpAHQAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiACgARABpAG0AZQBuAHMAaQBvAG4AbABlAHMAcwBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgByAGEAYwBMAEUAQQBDAEgAXwBTAG8AdQByAGMAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAVgBFAEUAUgBHACAAMgAwADIANgA6ADUALgA1AC4AMgAuADMAIABDAG8AbgBzAHQAYQBuAHQAIABQAGEAcgBhAG0AZQB0AGUAcgBzAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAHIAYQBjAEwARQBBAEMASABfAE4ASQBSAFIAZQBmAGUAcgBlAG4AYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBOAGEAdABpAG8AbgBhAGwAIABJAG4AdgBlAG4AdABvAHIAeQAgAFIAZQBwAG8AcgB0ACAAVgBvAGwAdQBtAGUAIAAxADoAIABMAGUAYQBjAGgAaQBuAGcAIABhAG4AZAAgAHIAdQBuAG8AZgBmACAAKAAzAC4ARAAuAGIALgAyACkAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAcgBhAGMATABFAEEAQwBIAF8ARABhAHQAYQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABNAEEASwBFAEEAUgBSAEEAWQAoADEALAAgADIALAAgAFwAbgAgACAAIAAgACAAIABMAEEATQBCAEQAQQAoAHIALABjACwAIABcAG4AIAAgACAAIAAgACAAIAAgAEkATgBEAEUAWAAoAHsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEYAcgBhAGMATABFAEEAQwBIAFwAIgAsADAALgAyADQAXABuACAAIAAgACAAIAAgACAAIAB9ACwAIAByACwAIABjACkAXABuACAAIAAgACAAIAAgACkAXABuACAAIAAgACAAKQBcAG4AIAAgACkAOwBcAG4AXABuACAAIABDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAHIAYQBjAEwARQBBAEMASABfAFYAYQByAGkAYQB0AGkAbwBuAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoACgAXAAiAFwAIgApACkAOwBcAG4AXABuAFwAbgBcAG4ALwAqACAAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAGwAZQBhAGMAaABcAG4ANQAuADUALgAyAC4AMwAgAEMAbwBuAHMAdABhAG4AdAAgAFAAYQByAGEAbQBlAHQAZQByAHMAXABuAEUAbQBpAHMAcwBpAG8AbgAgAGYAYQBjAHQAbwByACAAZgBvAHIAIABuAGkAdAByAG8AZwBlAG4AIABsAGUAYQBjAGgAaQBuAGcAIABhAG4AZAAgAHIAdQBuAG8AZgBmAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuACoALwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEUARgBsAGUAYQBjAGgAXwBUAGkAdABsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAEUAbQBpAHMAcwBpAG8AbgAgAGYAYQBjAHQAbwByACAAZgBvAHIAIABuAGkAdAByAG8AZwBlAG4AIABsAGUAYQBjAGgAaQBuAGcAIABhAG4AZAAgAHIAdQBuAG8AZgBmAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYAbABlAGEAYwBoAF8AVQBuAGkAdABcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAKABrAGcAIABOADIATwAtAE4AIAAvACAAawBnACAATgBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAGwAZQBhAGMAaABfAFMAbwB1AHIAYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBWAEUARQBSAEcAIAAyADAAMgA2ADoANQAuADUALgAyAC4AMwAgAEMAbwBuAHMAdABhAG4AdAAgAFAAYQByAGEAbQBlAHQAZQByAHMAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEUARgBsAGUAYQBjAGgAXwBOAEkAUgBSAGUAZgBlAHIAZQBuAGMAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIATgBhAHQAaQBvAG4AYQBsACAASQBuAHYAZQBuAHQAbwByAHkAIABSAGUAcABvAHIAdAAgAFYAbwBsAHUAbQBlACAAMQA6ACAARQBxAHUAYQB0AGkAbwBuACAAMwAuAEQALgBCAF8AMQAwAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYAbABlAGEAYwBoAF8ARABhAHQAYQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABNAEEASwBFAEEAUgBSAEEAWQAoADEALAAgADIALAAgAFwAbgAgACAAIAAgACAAIABMAEEATQBCAEQAQQAoAHIALABjACwAIABcAG4AIAAgACAAIAAgACAAIAAgAEkATgBEAEUAWAAoAHsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEUARgBsAGUAYQBjAGgAXAAiACwAMAAuADAAMQAxAFwAbgAgACAAIAAgACAAIAAgACAAfQAsACAAcgAsACAAYwApAFwAbgAgACAAIAAgACAAIAApAFwAbgAgACAAIAAgACkAXABuACAAIAApADsAXABuAFwAbgAgACAAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAGwAZQBhAGMAaABfAFYAYQByAGkAYQB0AGkAbwBuAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoACgAXAAiAFwAIgApACkAOwBcAG4AXABuAFwAbgAvACoAIABcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYATgAyAE8AXABuAFQAYQBiAGwAZQAgAEEALgAyAC4AMgAuADEAXABuAE4AaQB0AHIAbwB1AHMAIABvAHgAaQBkAGUAIABlAG0AaQBzAHMAaQBvAG4AIABmAGEAYwB0AG8AcgBzACAAZgBvAHIAIABpAG4AbwByAGcAYQBuAGkAYwAgAGYAZQByAHQAaQBsAGkAcwBlAHIAIABhAHAAcABsAGkAYwBhAHQAaQBvAG4AIAAoAGsAZwAgAE4AMgBPAC0ATgAvAGsAZwAgAE4AKQAgACgARQBGAE4AMgBPACkAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AKgAvAFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAE4AMgBPAF8AVABpAHQAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBOAGkAdAByAG8AdQBzACAAbwB4AGkAZABlACAAZQBtAGkAcwBzAGkAbwBuACAAZgBhAGMAdABvAHIAcwAgAGYAbwByACAAaQBuAG8AcgBnAGEAbgBpAGMAIABmAGUAcgB0AGkAbABpAHMAZQByACAAYQBwAHAAbABpAGMAYQB0AGkAbwBuAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYATgAyAE8AXwBVAG4AaQB0AFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgAoAGsAZwAgAE4AMgBPAC0ATgAgAC8AIABrAGcAIABOAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYATgAyAE8AXwBTAG8AdQByAGMAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAVgBFAEUAUgBHACAAMgAwADIANgA6ACAAVABhAGIAbABlACAAQQAuADIALgAyAC4AMQBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAE4AMgBPAF8ATgBJAFIAUgBlAGYAZQByAGUAbgBjAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYATgAyAE8AXwBEAGEAdABhAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAE0AQQBLAEUAQQBSAFIAQQBZACgAMQA1ACwAIAA1ACwAIABcAG4AIAAgACAAIAAgACAATABBAE0AQgBEAEEAKAByACwAYwAsACAAXABuACAAIAAgACAAIAAgACAAIABJAE4ARABFAFgAKAB7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBQAHIAbwBkAHUAYwB0AGkAbwBuACAAcwB5AHMAdABlAG0AIABqAFwAIgAsAFwAIgBFAEYATgAyAE8AXAAiACwAIABcACIAUAByAG8AZAB1AGMAdABpAG8AbgAgAHMAeQBzAHQAZQBtACAAbwBuAGwAeQBcACIALAAgAFwAIgBJAHIAcgBpAGcAYQB0AGkAbwBuACAAbQBlAHQAaABvAGQAXAAiACwAIABcACIAUgBhAGkAbgBmAGEAbABsACAAegBvAG4AZQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIASQByAHIAaQBnAGEAdABlAGQAIABwAGEAcwB0AHUAcgBlAFwAIgAsADAALgAwADAANQA5ACwAIABcACIAUABhAHMAdAB1AHIAZQBcACIALAAgAFwAIgBBAG4AeQBcACIALAAgAFwAIgBBAG4AeQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIASQByAHIAaQBnAGEAdABlAGQAIABjAHIAbwBwAFwAIgAsADAALgAwADAANwAsACAAXAAiAEMAcgBvAHAAXAAiACwAIABcACIAQQBuAHkAXAAiACwAIABcACIAQQBuAHkAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAE4AbwBuAC0AaQByAHIAaQBnAGEAdABlAGQAIABwAGEAcwB0AHUAcgBlAFwAIgAsADAALgAwADAAMQA4ACwAIABcACIAUABhAHMAdAB1AHIAZQBcACIALAAgAFwAIgBOAG8AdAAgAGkAcgByAGkAZwBhAHQAZQBkAFwAIgAsACAAXAAiAEwAbwB3ACAAcgBhAGkAbgBmAGEAbABsAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBOAG8AbgAtAGkAcgByAGkAZwBhAHQAZQBkACAAcABhAHMAdAB1AHIAZQBcACIALAAwAC4AMAAwADEAOAAsACAAXAAiAFAAYQBzAHQAdQByAGUAXAAiACwAIABcACIATgBvAHQAIABpAHIAcgBpAGcAYQB0AGUAZABcACIALAAgAFwAIgBIAGkAZwBoACAAcgBhAGkAbgBmAGEAbABsAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBOAG8AbgAtAGkAcgByAGkAZwBhAHQAZQBkACAAYwByAG8AcAAgACgAbABvAHcAIAByAGEAaQBuAGYAYQBsAGwAKQBcACIALAAwAC4AMAAwADIAOQAsACAAXAAiAEMAcgBvAHAAXAAiACwAIABcACIATgBvAHQAIABpAHIAcgBpAGcAYQB0AGUAZABcACIALAAgAFwAIgBMAG8AdwAgAHIAYQBpAG4AZgBhAGwAbABcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIATgBvAG4ALQBpAHIAcgBpAGcAYQB0AGUAZAAgAGMAcgBvAHAAIAAoAGgAaQBnAGgAIAByAGEAaQBuAGYAYQBsAGwAKQBcACIALAAwAC4AMAAwADgALAAgAFwAIgBDAHIAbwBwAFwAIgAsACAAXAAiAE4AbwB0ACAAaQByAHIAaQBnAGEAdABlAGQAXAAiACwAIABcACIASABpAGcAaAAgAHIAYQBpAG4AZgBhAGwAbABcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAUwB1AGcAYQByAFwAIgAsADAALgAwADEAOQA5ACwAIABcACIAUwB1AGcAYQByAFwAIgAsACAAXAAiAEEAbgB5AFwAIgAsACAAXAAiAEEAbgB5AFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBDAG8AdAB0AG8AbgBcACIALAAwAC4AMAAwADUAMwAsACAAXAAiAEMAbwB0AHQAbwBuAFwAIgAsACAAXAAiAEEAbgB5AFwAIgAsACAAXAAiAEEAbgB5AFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBIAG8AcgB0AGkAYwB1AGwAdAB1AHIAYQBsACAAYwByAG8AcABzAFwAIgAsADAALgAwADAANgA0ACwAIABcACIASABvAHIAdABpAGMAdQBsAHQAdQByAGEAbAAgAGMAcgBvAHAAcwBcACIALAAgAFwAIgBBAG4AeQBcACIALAAgAFwAIgBBAG4AeQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAUgBpAGMAZQAgACgAYwBvAG4AdABpAG4AdQBvAHUAcwAgAGYAbABvAG8AZABpAG4AZwApAFwAIgAsADAALgAwADAAMwAsACAAXAAiAFIAaQBjAGUAXAAiACwAIABcACIAQwBvAG4AdABpAG4AdQBvAHUAcwAgAGYAbABvAG8AZABpAG4AZwBcACIALAAgAFwAIgBBAG4AeQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAUgBpAGMAZQAgACgAcwBpAG4AZwBsAGUAIABhAG4AZAAgAG0AdQBsAHQAaQBwAGwAZQAgAGQAcgBhAGkAbgBhAGcAZQAsACAAbwByACAAYQBsAHQAZQByAG4AYQB0AGUAIAB3AGUAdAB0AGkAbgBnACAAYQBuAGQAIABkAHIAeQBpAG4AZwApAFwAIgAsADAALgAwADAANQAsACAAXAAiAFIAaQBjAGUAXAAiACwAIABcACIAUwBpAG4AZwBsAGUAIABhAG4AZAAgAG0AdQBsAHQAaQBwAGwAZQAgAGQAcgBhAGkAbgBhAGcAZQAsACAAbwByACAAYQBsAHQAZQByAG4AYQB0AGUAIAB3AGUAdAB0AGkAbgBnACAAYQBuAGQAIABkAHIAeQBpAG4AZwBcACIALAAgAFwAIgBBAG4AeQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAQQBxAHUAYQBjAHUAbAB0AHUAcgBlAFwAIgAsADAALgAwADAAMgA2ACwAIABcACIAQQBxAHUAYQBjAHUAbAB0AHUAcgBlAFwAIgAsACAAXAAiAEEAbgB5AFwAIgAsACAAXAAiAEEAbgB5AFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBGAG8AcgBlAHMAdAByAHkAXAAiACwAMAAuADAAMAAxADgALAAgAFwAIgBGAG8AcgBlAHMAdAByAHkAXAAiACwAIABcACIAQQBuAHkAXAAiACwAIABcACIAQQBuAHkAXAAiAFwAbgAgACAAIAAgACAAIAAgACAAfQAsACAAcgAsACAAYwApAFwAbgAgACAAIAAgACAAIAApAFwAbgAgACAAIAAgACkAXABuACAAIAApADsAXABuAFwAbgAgACAAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAE4AMgBPAF8AVgBhAHIAaQBhAHQAaQBvAG4AXABuACAAIAA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAATQBBAEsARQBBAFIAUgBBAFkAKAA1ACwAIAAxACwAIABcAG4AIAAgACAAIAAgACAATABBAE0AQgBEAEEAKAByACwAYwAsACAAXABuACAAIAAgACAAIAAgACAAIABJAE4ARABFAFgAKAB7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBWAEEAUgBJAEEAVABJAE8ATgAgAE8ARgAgAFMATwBVAFIAQwBFACAARABBAFQAQQA6AFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBSAGUAbQBvAHYAZQBkACAAZAB1AHAAbABpAGMAYQB0AGUAIAAnAEEAcQB1AGEAYwB1AGwAdAB1AHIAZQAnACAAcgBvAHcALgBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAUgBlAG0AbwB2AGUAZAAgAGEAcwB0AGUAcgBpAHMAawBzACAAdABvACAAYQBpAGQAIABsAG8AbwBrAHUAcAAuAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBBAGQAZABlAGQAIAAnAHAAcgBvAGQAdQBjAHQAaQBvAG4AIABzAHkAcwB0AGUAbQAgAG8AbgBsAHkAJwAsACAAJwByAGEAaQBuAGYAYQBsAGwAIAB6AG8AbgBlACcAIABhAG4AZAAgACcAaQByAHIAaQBnAGEAdABpAG8AbgAgAG0AZQB0AGgAbwBkACcAIABjAG8AbAB1AG0AbgBzACAAdABvACAAYQBpAGQAIABsAG8AbwBrAHUAcAAuAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBEAHUAcABsAGkAYwBhAHQAZQBkACAAJwBuAG8AbgAtAGkAcgByAGkAZwBhAHQAZQBkACAAcABhAHMAdAB1AHIAZQAnACAAcgBvAHcAIAB3AGkAdABoACAAcwBhAG0AZQAgAEUARgAgAGYAbwByACAAbABvAHcAIABhAG4AZAAgAGgAaQBnAGgAIAByAGEAaQBuAGYAYQBsAGwAIAB6AG8AbgBlAHMAIAB0AG8AIABhAGkAZAAgAGwAbwBvAGsAdQBwAC4AXAAiAFwAbgAgACAAIAAgACAAIAAgACAAfQAsACAAcgAsACAAYwApAFwAbgAgACAAIAAgACAAIAApAFwAbgAgACAAIAAgACkAXABuACAAIAApADsAXABuAFwAbgAvACoAIABcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAHIAYQBjAFcARQBUAEkAcgByAGkAZwBhAHQAaQBvAG4AXABuAFYARQBFAFIARwAgADIAMAAyADYAOgAgAEMAaABhAHAAdABlAHIAIAAxACwAIABzAGUAYwB0AGkAbwBuACAAMQAuADgALgAyACAATABlAGEAYwBoAGkAbgBnACwAIABjAGwAaQBtAGEAdABlACAAYQBuAGQAIAByAGEAaQBuAGYAYQBsAGwAIAB6AG8AbgBlAHMAXABuAEkAUABDAEMAOgAgAE4AMgBPACAARQBNAEkAUwBTAEkATwBOAFMAIABGAFIATwBNACAATQBBAE4AQQBHAEUARAAgAFMATwBJAEwAUwAsACAAQQBOAEQAIABDAE8AMgAgAEUATQBJAFMAUwBJAE8ATgBTACAARgBSAE8ATQAgAEwASQBNAEUAIABBAE4ARAAgAFUAUgBFAEEAIABBAFAAUABMAEkAQwBBAFQASQBPAE4AXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AKgAvAFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgByAGEAYwBXAEUAVABJAHIAcgBpAGcAYQB0AGkAbwBuAF8AVABpAHQAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBGAHIAYQBjAFcARQBUACAAZgBvAHIAIABpAHIAcgBpAGcAYQB0AGkAbwBuACAAdAB5AHAAZQBzAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAHIAYQBjAFcARQBUAEkAcgByAGkAZwBhAHQAaQBvAG4AXwBVAG4AaQB0AFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBkAGkAbQBlAG4AcwBpAG8AbgBsAGUAcwBzAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAHIAYQBjAFcARQBUAEkAcgByAGkAZwBhAHQAaQBvAG4AXwBTAG8AdQByAGMAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAVgBFAEUAUgBHACAAMgAwADIANgA6ACAAQwBoAGEAcAB0AGUAcgAgADEALAAgAHMAZQBjAHQAaQBvAG4AIAAxAC4AOAAuADIAIABMAGUAYQBjAGgAaQBuAGcALAAgAGMAbABpAG0AYQB0AGUAIABhAG4AZAAgAHIAYQBpAG4AZgBhAGwAbAAgAHoAbwBuAGUAcwBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgByAGEAYwBXAEUAVABJAHIAcgBpAGcAYQB0AGkAbwBuAF8ATgBJAFIAUgBlAGYAZQByAGUAbgBjAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAEkAUABDAEMAIAAyADAAMQA5ACAAUgBlAGYAaQBuAGUAbQBlAG4AdAAgAFYAbwBsAHUAbQBlACAANAA6ACAAQwBoAGEAcAB0AGUAcgAgADEAMQA6ACAATgAyAE8AIABFAG0AaQBzAHMAaQBvAG4AcwAgAGYAcgBvAG0AIABNAGEAbgBhAGcAZQBkACAAUwBvAGkAbABzACwAIABhAG4AZAAgAEMATwAyACAARQBtAGkAcwBzAGkAbwBuAHMAIABmAHIAbwBtACAATABpAG0AZQAgAGEAbgBkACAAVQByAGUAYQAgAEEAcABwAGwAaQBjAGEAdABpAG8AbgBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgByAGEAYwBXAEUAVABJAHIAcgBpAGcAYQB0AGkAbwBuAF8ARABhAHQAYQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABNAEEASwBFAEEAUgBSAEEAWQAoADYALAAgADIALAAgAFwAbgAgACAAIAAgACAAIABMAEEATQBCAEQAQQAoAHIALABjACwAIABcAG4AIAAgACAAIAAgACAAIAAgAEkATgBEAEUAWAAoAHsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEkAcgByAGkAZwBhAHQAaQBvAG4AIAB0AHkAcABlACAAaQByAFwAIgAsAFwAIgBGAHIAYQBjAFcARQBUAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBOAG8AdAAgAGkAcgByAGkAZwBhAHQAZQBkAFwAIgAsACAAMAA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBEAHIAaQBwACAAaQByAHIAaQBnAGEAdABpAG8AbgBcACIALAAgADAAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAUwBwAHIAaQBuAGsAbABlAHIAIABpAHIAcgBpAGcAYQB0AGkAbwBuAFwAIgAsACAAMQA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBTAHUAcgBmAGEAYwBlACAAaQByAHIAaQBnAGEAdABpAG8AbgBcACIALAAgADEAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIATwB0AGgAZQByACAAaQByAHIAaQBnAGEAdABpAG8AbgBcACIALAAgADEAXABuACAAIAAgACAAIAAgACAAIAB9ACwAIAByACwAIABjACkAXABuACAAIAAgACAAIAAgACkAXABuACAAIAAgACAAKQBcAG4AIAAgACkAOwBcAG4AXABuACAAIABDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAHIAYQBjAFcARQBUAEkAcgByAGkAZwBhAHQAaQBvAG4AXwBWAGEAcgBpAGEAdABpAG8AbgBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAVgBBAFIASQBBAFQASQBPAE4AIABGAFIATwBNACAAUwBPAFUAUgBDAEUAIABEAEEAVABBADoAIABUAGEAYgBsAGUAIABjAHIAZQBhAHQAZQBkACAAYgBhAHMAZQBkACAAbwBuACAAVgBFAEUAUgBHACAAdABlAHgAdAAgACcAQQByAGUAYQBzACAAYQByAGUAIABzAHUAYgBqAGUAYwB0ACAAdABvACAAbABlAGEAYwBoAGkAbgBnACAAKABpAC4AZQAuACwAIABpAG4AIAB0AGgAZQAgAGwAZQBhAGMAaABpAG4AZwAgAHoAbwBuAGUAKQAgAHcAaABlAG4ALgAuAC4AIAB0AGgAZQAgAGwAYQBuAGQAIABpAHMAIABpAHIAcgBpAGcAYQB0AGUAZAAgACgAZQB4AGMAZQBwAHQAIABkAHIAaQBwACAAaQByAHIAaQBnAGEAdABpAG8AbgApAC4AJwBcACIAKQA7AFwAbgBcAG4AXABuAC8AKgAgAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEUARgBQAGEAcwB0AHUAcgBlAFIAYQBuAGcAZQBBAG4AZABQAGEAZABkAG8AYwBrAFwAbgBUAGEAYgBsAGUAIABBAC4AMgAuADIALgAyADoAIABFAG0AaQBzAHMAaQBvAG4AIABmAGEAYwB0AG8AcgAgAGYAbwByACAAdQByAGkAbgBlACAAYQBuAGQAIABkAHUAbgBnACAAZABlAHAAbwBzAGkAdABlAGQAIABvAG4AIABwAGEAcwB0AHUAcgBlACwAIAByAGEAbgBnAGUAIABvAHIAIABwAGEAZABkAG8AYwBrACAAKABrAGcAIABOADIATwAtAE4ALwBrAGcAIABOACkAIAAoAEUARgBQAFIAUAApAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuACoALwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEUARgBQAGEAcwB0AHUAcgBlAFIAYQBuAGcAZQBBAG4AZABQAGEAZABkAG8AYwBrAF8AVABpAHQAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBFAG0AaQBzAHMAaQBvAG4AIABmAGEAYwB0AG8AcgAgAGYAbwByACAAdQByAGkAbgBlACAAYQBuAGQAIABkAHUAbgBnACAAZABlAHAAbwBzAGkAdABlAGQAIABvAG4AIABwAGEAcwB0AHUAcgBlACwAIAByAGEAbgBnAGUAIABvAHIAIABwAGEAZABkAG8AYwBrAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYAUABhAHMAdAB1AHIAZQBSAGEAbgBnAGUAQQBuAGQAUABhAGQAZABvAGMAawBfAFUAbgBpAHQAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAGsAZwAgAE4AMgBPACAALQAgAE4AIAAvACAAawBnACAATgBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAFAAYQBzAHQAdQByAGUAUgBhAG4AZwBlAEEAbgBkAFAAYQBkAGQAbwBjAGsAXwBTAG8AdQByAGMAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAVgBFAEUAUgBHACAAMgAwADIANgA6ACAAVABhAGIAbABlACAAQQAuADIALgAyAC4AMgBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAFAAYQBzAHQAdQByAGUAUgBhAG4AZwBlAEEAbgBkAFAAYQBkAGQAbwBjAGsAXwBOAEkAUgBSAGUAZgBlAHIAZQBuAGMAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEUARgBQAGEAcwB0AHUAcgBlAFIAYQBuAGcAZQBBAG4AZABQAGEAZABkAG8AYwBrAF8ARABhAHQAYQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABNAEEASwBFAEEAUgBSAEEAWQAoADMALAAgADIALAAgAFwAbgAgACAAIAAgACAAIABMAEEATQBCAEQAQQAoAHIALABjACwAIABcAG4AIAAgACAAIAAgACAAIAAgAEkATgBEAEUAWAAoAHsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEMAbABpAG0AYQB0AGUAIAB6AG8AbgBlAFwAIgAsACAAXAAiAEUARgBQAFIAUABcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVwBlAHQAIABjAGwAaQBtAGEAdABlACAAegBvAG4AZQBcACIALAAgADAALgAwADAANgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBEAHIAeQAgAGMAbABpAG0AYQB0AGUAIAB6AG8AbgBlAFwAIgAsACAAMAAuADAAMAAyAFwAbgAgACAAIAAgACAAIAAgACAAfQAsACAAcgAsACAAYwApAFwAbgAgACAAIAAgACAAIAApAFwAbgAgACAAIAAgACkAXABuACAAIAApADsAXABuAFwAbgAgACAAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAFAAYQBzAHQAdQByAGUAUgBhAG4AZwBlAEEAbgBkAFAAYQBkAGQAbwBjAGsAXwBWAGEAcgBpAGEAdABpAG8AbgBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAVgBBAFIASQBBAFQASQBPAE4AIABGAFIATwBNACAAUwBPAFUAUgBDAEUAIABEAEEAVABBADoAIABDAGgAYQBuAGcAZQBkACAAJwBEAHIAeQAgAGMAbABpAG0AYQB0AGUAIAB6AG8AbgBlAHMAJwAgAHQAbwAgAHMAaQBuAGcAdQBsAGEAcgAgACcARAByAHkAIABjAGwAaQBtAGEAdABlACAAegBvAG4AZQAnACAAdABvACAAYQBpAGQAIABsAG8AbwBrAHUAcAAuAFwAIgApADsAXABuAFwAbgBcAG4ALwAqACAAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ATQBvAG4AdABoAHMAVABvAFMAZQBhAHMAbwBuAHMAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AKgAvAFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ATQBvAG4AdABoAHMAVABvAFMAZQBhAHMAbwBuAHMAXwBUAGkAdABsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAE0AbwBuAHQAaABzACAAdABvACAAUwBlAGEAcwBvAG4AcwAgAE0AYQBwAHAAaQBuAGcAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAE0AbwBuAHQAaABzAFQAbwBTAGUAYQBzAG8AbgBzAF8AVQBuAGkAdABcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAE0AbwBuAHQAaABzAFQAbwBTAGUAYQBzAG8AbgBzAF8AUwBvAHUAcgBjAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBNAG8AbgB0AGgAcwBUAG8AUwBlAGEAcwBvAG4AcwBfAE4ASQBSAFIAZQBmAGUAcgBlAG4AYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ATQBvAG4AdABoAHMAVABvAFMAZQBhAHMAbwBuAHMAXwBEAGEAdABhAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAE0AQQBLAEUAQQBSAFIAQQBZACgAMQAzACwAIAAyACwAIABcAG4AIAAgACAAIAAgACAATABBAE0AQgBEAEEAKAByACwAYwAsACAAXABuACAAIAAgACAAIAAgACAAIABJAE4ARABFAFgAKAB7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBNAG8AbgB0AGgAXAAiACwAIABcACIAUwBlAGEAcwBvAG4AXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEoAYQBuAHUAYQByAHkAXAAiACwAIABcACIAUwB1AG0AbQBlAHIAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEYAZQBiAHIAdQBhAHIAeQBcACIALAAgAFwAIgBTAHUAbQBtAGUAcgBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIATQBhAHIAYwBoAFwAIgAsACAAXAAiAEEAdQB0AHUAbQBuAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBBAHAAcgBpAGwAXAAiACwAIABcACIAQQB1AHQAdQBtAG4AXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAE0AYQB5AFwAIgAsACAAXAAiAEEAdQB0AHUAbQBuAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBKAHUAbgBlAFwAIgAsACAAXAAiAFcAaQBuAHQAZQByAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBKAHUAbAB5AFwAIgAsACAAXAAiAFcAaQBuAHQAZQByAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBBAHUAZwB1AHMAdABcACIALAAgAFwAIgBXAGkAbgB0AGUAcgBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAUwBlAHAAdABlAG0AYgBlAHIAXAAiACwAIABcACIAUwBwAHIAaQBuAGcAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAE8AYwB0AG8AYgBlAHIAXAAiACwAIABcACIAUwBwAHIAaQBuAGcAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAE4AbwB2AGUAbQBiAGUAcgBcACIALAAgAFwAIgBTAHAAcgBpAG4AZwBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIARABlAGMAZQBtAGIAZQByAFwAIgAsACAAXAAiAFMAdQBtAG0AZQByAFwAIgBcAG4AIAAgACAAIAAgACAAIAAgAH0ALAAgAHIALAAgAGMAKQBcAG4AIAAgACAAIAAgACAAKQBcAG4AIAAgACAAIAApAFwAbgAgACAAKQA7AFwAbgBcAG4AIAAgAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAE0AbwBuAHQAaABzAFQAbwBTAGUAYQBzAG8AbgBzAF8AVgBhAHIAaQBhAHQAaQBvAG4AXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFwAIgApADsAXABuAFwAbgBcAG4AXABuAC8AKgAgAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAE0AQwBGAFQAZQBtAHAAZQByAGEAdAB1AHIAZQBaAG8AbgBlAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuACoALwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAE0AQwBGAFQAZQBtAHAAZQByAGEAdAB1AHIAZQBaAG8AbgBlAF8AVABpAHQAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBNAGEAbgB1AHIAZQAgAE0AYQBuAGEAZwBlAG0AZQBuAHQAIAATICAATQBlAHQAaABhAG4AZQAgAGMAbwBuAHYAZQByAHMAaQBvAG4AIABmAGEAYwB0AG8AcgAgAHAAZQByACAAdABlAG0AcABlAHIAYQB0AHUAcgBlACAAegBvAG4AZQAgACgAZgByAGEAYwB0AGkAbwBuACkAIAAoAE0AQwBGAGkAbQApAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBNAEMARgBUAGUAbQBwAGUAcgBhAHQAdQByAGUAWgBvAG4AZQBfAFUAbgBpAHQAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAGYAcgBhAGMAdABpAG8AbgBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ATQBDAEYAVABlAG0AcABlAHIAYQB0AHUAcgBlAFoAbwBuAGUAXwBTAG8AdQByAGMAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAVgBFAEUAUgBHACAAMgAwADIANgA6ACAAVABhAGIAbABlACAAQQAuADEALgA4AC4AMQBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ATQBDAEYAVABlAG0AcABlAHIAYQB0AHUAcgBlAFoAbwBuAGUAXwBEAGEAdABhAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAE0AQQBLAEUAQQBSAFIAQQBZACgAMgAyACwAIAAxADYALAAgAFwAbgAgACAAIAAgACAAIABMAEEATQBCAEQAQQAoAHIALABjACwAIABcAG4AIAAgACAAIAAgACAAIAAgAEkATgBEAEUAWAAoAHsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFQAZQBtAHAAZQByAGEAdAB1AHIAZQAgAHoAbwBuAGUAXAAiACwAIABcACIATQBBAFQAIAAoALoAQwApAFwAIgAsACAAXAAiAFUAbgBjAG8AdgBlAHIAZQBkACAAYQBuAGUAcgBvAGIAaQBjACAAbABhAGcAbwBvAG4AXAAiACwAIABcACIAQwBvAHYAZQByAGUAZAAgAGwAYQBnAG8AbwBuAFwAIgAsACAAXAAiAEwAaQBxAHUAaQBkACAAUwBsAHUAcgByAHkAIAAoAHcAaQB0AGgAbwB1AHQAIABuAGEAdAB1AHIAYQBsACAAYwByAHUAcwB0ACkAXAAiACwAIABcACIARABhAGkAbAB5ACAAcwBwAHIAZQBhAGQAIAAoAGIAKQBcACIALAAgAFwAIgBDAG8AbQBwAG8AcwB0AGkAbgBnACAAKABwAGEAcwBzAGkAdgBlACAAdwBpAG4AZAByAG8AdwApAFwAIgAsACAAXAAiAFMAbwBsAGkAZAAgAFMAdABvAHIAYQBnAGUAXAAiACwAIABcACIAUABpAHQAIABTAHQAbwByAGEAZwBlACAAPAAxACAAbQBvAG4AdABoAFwAIgAsACAAXAAiAEQAZQBlAHAAIABMAGkAdAB0AGUAcgBcACIALAAgAFwAIgBQAG8AdQBsAHQAcgB5ACAATQBhAG4AdQByAGUAIAAoAHcAaQB0AGgALwB3AGkAdABoAG8AdQB0ACAAbABpAHQAdABlAHIAKQBcACIALAAgAFwAIgBcACIALAAgAFwAIgBEAGkAcgBlAGMAdAAgAHAAcgBvAGMAZQBzAHMAaQBuAGcAIABpAG4AdABvACAAcABlAGwAbABlAHQAaQB6AGUAZAAgAGYAZQByAHQAaQBsAGkAcwBlAHIAXAAiACwAIABcACIARABpAHIAZQBjAHQAIABhAHAAcABsAGkAYwBhAHQAaQBvAG4AIAB0AG8AIABzAG8AaQBsAFwAIgAsACAAXAAiAFAAYQBzAHQAdQByAGUALAAgAFIAYQBuAGcAZQAgAGEAbgBkACAAUABhAGQAZABvAGMAawAgACgAYwApACgAZAApAFwAIgAsACAAXAAiAE0AQQBUACAAcgBhAHcAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEMAbwBvAGwAXAAiACwAIABcACIAZCIxADAAXAAiACwAIAAwAC4ANgA2ACwAIAAwAC4AMQAsACAAMAAuADEALAAgADAALgAwADAAMQAsACAAMAAuADAAMAA1ACwAIAAwAC4AMAAyACwAIAAwAC4AMAAzACwAIAAwAC4AMAA0ACwAIAAwAC4AMAAxADUALAAgADAALgAwADEANQAsACAAMAAsACAAMAAsACAAMAAuADAAMAA0ADcALAAgADEAMAA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBDAG8AbwBsAFwAIgAsACAAMQAxACwAIAAwAC4ANgA4ACwAIAAwAC4AMQAsACAAMAAuADEAMQAsACAAMAAuADAAMAAxACwAIAAwAC4AMAAwADUALAAgADAALgAwADIALAAgADAALgAwADMALAAgADAALgAwADQALAAgADAALgAwADEANQAsACAAMAAuADAAMQA1ACwAIAAwACwAIAAwACwAIAAwAC4AMAAwADQANwAsACAAMQAxADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEMAbwBvAGwAXAAiACwAIAAxADIALAAgADAALgA3ACwAIAAwAC4AMQAsACAAMAAuADEAMwAsACAAMAAuADAAMAAxACwAIAAwAC4AMAAwADUALAAgADAALgAwADIALAAgADAALgAwADMALAAgADAALgAwADQALAAgADAALgAwADEANQAsACAAMAAuADAAMQA1ACwAIAAwACwAIAAwACwAIAAwAC4AMAAwADQANwAsACAAMQAyADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEMAbwBvAGwAXAAiACwAIAAxADMALAAgADAALgA3ADEALAAgADAALgAxACwAIAAwAC4AMQA0ACwAIAAwAC4AMAAwADEALAAgADAALgAwADAANQAsACAAMAAuADAAMgAsACAAMAAuADAAMwAsACAAMAAuADAANAAsACAAMAAuADAAMQA1ACwAIAAwAC4AMAAxADUALAAgADAALAAgADAALAAgADAALgAwADAANAA3ACwAIAAxADMAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAQwBvAG8AbABcACIALAAgADEANAAsACAAMAAuADcAMwAsACAAMAAuADEALAAgADAALgAxADUALAAgADAALgAwADAAMQAsACAAMAAuADAAMAA1ACwAIAAwAC4AMAAyACwAIAAwAC4AMAAzACwAIAAwAC4AMAA0ACwAIAAwAC4AMAAxADUALAAgADAALgAwADEANQAsACAAMAAsACAAMAAsACAAMAAuADAAMAA0ADcALAAgADEANAA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBUAGUAbQBwAGUAcgBhAHQAZQBcACIALAAgADEANQAsACAAMAAuADcANAAsACAAMAAuADEALAAgADAALgAxADcALAAgADAALgAwADAANQAsACAAMAAuADAAMQAsACAAMAAuADAAMgAsACAAMAAuADAAMwAsACAAMAAuADAANAAsACAAMAAuADAAMQA1ACwAIAAwAC4AMAAxADUALAAgADAALAAgADAALAAgADAALgAwADAANAA3ACwAIAAxADUAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVABlAG0AcABlAHIAYQB0AGUAXAAiACwAIAAxADYALAAgADAALgA3ADUALAAgADAALgAxACwAIAAwAC4AMQA4ACwAIAAwAC4AMAAwADUALAAgADAALgAwADEALAAgADAALgAwADIALAAgADAALgAwADMALAAgADAALgAwADQALAAgADAALgAwADEANQAsACAAMAAuADAAMQA1ACwAIAAwACwAIAAwACwAIAAwAC4AMAAwADQANwAsACAAMQA2ADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFQAZQBtAHAAZQByAGEAdABlAFwAIgAsACAAMQA3ACwAIAAwAC4ANwA2ACwAIAAwAC4AMQAsACAAMAAuADIALAAgADAALgAwADAANQAsACAAMAAuADAAMQAsACAAMAAuADAAMgAsACAAMAAuADAAMwAsACAAMAAuADAANAAsACAAMAAuADAAMQA1ACwAIAAwAC4AMAAxADUALAAgADAALAAgADAALAAgADAALgAwADAANAA3ACwAIAAxADcAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVABlAG0AcABlAHIAYQB0AGUAXAAiACwAIAAxADgALAAgADAALgA3ADcALAAgADAALgAxACwAIAAwAC4AMgAyACwAIAAwAC4AMAAwADUALAAgADAALgAwADEALAAgADAALgAwADIALAAgADAALgAwADMALAAgADAALgAwADQALAAgADAALgAwADEANQAsACAAMAAuADAAMQA1ACwAIAAwACwAIAAwACwAIAAwAC4AMAAwADQANwAsACAAMQA4ADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFQAZQBtAHAAZQByAGEAdABlAFwAIgAsACAAMQA5ACwAIAAwAC4ANwA3ACwAIAAwAC4AMQAsACAAMAAuADIANAAsACAAMAAuADAAMAA1ACwAIAAwAC4AMAAxACwAIAAwAC4AMAAyACwAIAAwAC4AMAAzACwAIAAwAC4AMAA0ACwAIAAwAC4AMAAxADUALAAgADAALgAwADEANQAsACAAMAAsACAAMAAsACAAMAAuADAAMAA0ADcALAAgADEAOQA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBUAGUAbQBwAGUAcgBhAHQAZQBcACIALAAgADIAMAAsACAAMAAuADcAOAAsACAAMAAuADEALAAgADAALgAyADYALAAgADAALgAwADAANQAsACAAMAAuADAAMQAsACAAMAAuADAAMgAsACAAMAAuADAAMwAsACAAMAAuADAANAAsACAAMAAuADAAMQA1ACwAIAAwAC4AMAAxADUALAAgADAALAAgADAALAAgADAALgAwADAANAA3ACwAIAAyADAAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVABlAG0AcABlAHIAYQB0AGUAXAAiACwAIAAyADEALAAgADAALgA3ADgALAAgADAALgAxACwAIAAwAC4AMgA5ACwAIAAwAC4AMAAwADUALAAgADAALgAwADEALAAgADAALgAwADIALAAgADAALgAwADMALAAgADAALgAwADQALAAgADAALgAwADEANQAsACAAMAAuADAAMQA1ACwAIAAwACwAIAAwACwAIAAwAC4AMAAwADQANwAsACAAMgAxADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFQAZQBtAHAAZQByAGEAdABlAFwAIgAsACAAMgAyACwAIAAwAC4ANwA4ACwAIAAwAC4AMQAsACAAMAAuADMAMQAsACAAMAAuADAAMAA1ACwAIAAwAC4AMAAxACwAIAAwAC4AMAAyACwAIAAwAC4AMAAzACwAIAAwAC4AMAA0ACwAIAAwAC4AMAAxADUALAAgADAALgAwADEANQAsACAAMAAsACAAMAAsACAAMAAuADAAMAA0ADcALAAgADIAMgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBUAGUAbQBwAGUAcgBhAHQAZQBcACIALAAgADIAMwAsACAAMAAuADcAOQAsACAAMAAuADEALAAgADAALgAzADQALAAgADAALgAwADAANQAsACAAMAAuADAAMQAsACAAMAAuADAAMgAsACAAMAAuADAAMwAsACAAMAAuADAANAAsACAAMAAuADAAMQA1ACwAIAAwAC4AMAAxADUALAAgADAALAAgADAALAAgADAALgAwADAANAA3ACwAIAAyADMAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVABlAG0AcABlAHIAYQB0AGUAXAAiACwAIAAyADQALAAgADAALgA3ADkALAAgADAALgAxACwAIAAwAC4AMwA3ACwAIAAwAC4AMAAwADUALAAgADAALgAwADEALAAgADAALgAwADIALAAgADAALgAwADMALAAgADAALgAwADQALAAgADAALgAwADEANQAsACAAMAAuADAAMQA1ACwAIAAwACwAIAAwACwAIAAwAC4AMAAwADQANwAsACAAMgA0ADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFQAZQBtAHAAZQByAGEAdABlAFwAIgAsACAAMgA1ACwAIAAwAC4ANwA5ACwAIAAwAC4AMQAsACAAMAAuADQAMQAsACAAMAAuADAAMAA1ACwAIAAwAC4AMAAxACwAIAAwAC4AMAAyACwAIAAwAC4AMAAzACwAIAAwAC4AMAA0ACwAIAAwAC4AMAAxADUALAAgADAALgAwADEANQAsACAAMAAsACAAMAAsACAAMAAuADAAMAA0ADcALAAgADIANQA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBXAGEAcgBtAFwAIgAsACAAMgA2ACwAIAAwAC4ANwA5ACwAIAAwAC4AMQAsACAAMAAuADQANAAsACAAMAAuADAAMQAsACAAMAAuADAAMQA1ACwAIAAwAC4AMAAyACwAIAAwAC4AMAAzACwAIAAwAC4AMAA0ACwAIAAwAC4AMAAxADUALAAgADAALgAwADEANQAsACAAMAAsACAAMAAsACAAMAAuADAAMAA0ADcALAAgADIANgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBXAGEAcgBtAFwAIgAsACAAMgA3ACwAIAAwAC4AOAAsACAAMAAuADEALAAgADAALgA0ADgALAAgADAALgAwADEALAAgADAALgAwADEANQAsACAAMAAuADAAMgAsACAAMAAuADAAMwAsACAAMAAuADAANAAsACAAMAAuADAAMQA1ACwAIAAwAC4AMAAxADUALAAgADAALAAgADAALAAgADAALgAwADAANAA3ACwAIAAyADcAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVwBhAHIAbQBcACIALAAgAFwAIgBlIjIAOABcACIALAAgADAALgA4ACwAIAAwAC4AMQAsACAAMAAuADUALAAgADAALgAwADEALAAgADAALgAwADEANQAsACAAMAAuADAAMgAsACAAMAAuADAAMwAsACAAMAAuADAANAAsACAAMAAuADAAMQA1ACwAIAAwAC4AMAAxADUALAAgADAALAAgADAALAAgADAALgAwADAANAA3ACwAIAAyADgAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAXAAiACwAIABcACIAXAAiACwAIABcACIAQQBuAGEAZQByAG8AYgBpAGMAIABsAGEAZwBvAG8AbgBcACIALAAgAFwAIgBEAGkAZwBlAHMAdABlAHIAIAAvACAAYwBvAHYAZQByAGUAZAAgAGwAYQBnAG8AbwBuAHMAXAAiACwAIABcACIATABpAHEAdQBpAGQAIABzAHkAcwB0AGUAbQBzAFwAIgAsACAAXAAiAEQAYQBpAGwAeQAgAHMAcAByAGUAYQBkAFwAIgAsACAAXAAiAEMAbwBtAHAAbwBzAHQAaQBuAGcAIAAoAHAAYQBzAHMAaQB2AGUAIAB3AGkAbgBkAHIAbwB3ACkAXAAiACwAIABcACIAUwBvAGwAaQBkACAAcwB0AG8AcgBhAGcAZQBcACIALAAgAFwAIgBQAGkAdAAgAHMAdABvAHIAYQBnAGUAXAAiACwAIABcACIARABlAGUAcAAgAGwAaQB0AHQAZQByAFwAIgAsACAAXAAiAFAAbwB1AGwAdAByAHkAIABtAGEAbgB1AHIAZQAgAHcAaQB0AGgAIABiAGUAZABkAGkAbgBnAFwAIgAsACAAXAAiAFAAbwB1AGwAdAByAHkAIABtAGEAbgB1AHIAZQAgAHcAaQB0AGgAbwB1AHQAIABiAGUAZABkAGkAbgBnAFwAIgAsACAAXAAiAEQAaQByAGUAYwB0ACAAcAByAG8AYwBlAHMAcwBpAG4AZwBcACIALAAgAFwAIgBEAGkAcgBlAGMAdAAgAGEAcABwAGwAaQBjAGEAdABpAG8AbgBcACIALAAgAFwAIgBQAGEAcwB0AHUAcgBlACAAcgBhAG4AZwBlACAAYQBuAGQAIABwAGEAZABkAG8AYwBrAFwAIgAsACAAXAAiAE0AQQBUACAAcgBhAHcAXAAiACAAXABuACAAIAAgACAAIAAgACAAIAB9ACwAIAByACwAIABjACkAXABuACAAIAAgACAAIAAgACkAXABuACAAIAAgACAAKQBcAG4AIAAgACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAE0AQwBGAFQAZQBtAHAAZQByAGEAdAB1AHIAZQBaAG8AbgBlAF8AVgBhAHIAaQBhAHQAaQBvAG4AXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFYAQQBSAEkAQQBUAEkATwBOACAARgBSAE8ATQAgAFMATwBVAFIAQwBFADoAIABBAGQAZABlAGQAIAByAG8AdwAgAG8AZgAgAE4ASQBSACAATQBNAEEAIABkAGUAZgBpAG4AaQB0AGkAbwBuAHMAIAB0AG8AIABhAGkAZAAgAGwAbwBvAGsAdQBwAC4AIABEAHUAcABsAGkAYwBhAHQAZQBkACAAJwBQAG8AdQBsAHQAcgB5ACAAdwBpAHQAaAAgAGEAbgBkACAAdwBpAHQAaABvAHUAdAAgAGwAaQB0AHQAZQByACcAIABjAG8AbAB1AG0AbgAgAHcAaQB0AGgAIABzAGUAcABhAHIAYQB0AGUAIABOAEkAUgAgAGQAZQBmAGkAbgBpAHQAaQBvAG4AcwAgAHQAbwAgAGEAaQBkACAAbABvAG8AawB1AHAALgAgAEEAZABkAGUAZAAgACcATQBBAFQAIAByAGEAdwAnACAAYwBvAGwAdQBtAG4AIAB0AG8AIABhAGwAbABvAHcAIABsAG8AbwBrAHUAcAAgAG8AZgAgAG4AdQBtAGIAZQByAHMALgBcACIAKQA7AFwAbgBcAG4AXABuAFwAbgAvACoAIABcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYATwByAGcAYQBuAGkAYwBGAGUAcgB0AGkAbABpAHMAZQByAEEAbgBkAEMAcgBvAHAAUgBlAHMAaQBkAHUAZQBzAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuACoALwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEUARgBPAHIAZwBhAG4AaQBjAEYAZQByAHQAaQBsAGkAcwBlAHIAQQBuAGQAQwByAG8AcABSAGUAcwBpAGQAdQBlAHMAXwBUAGkAdABsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAEUAbQBpAHMAcwBpAG8AbgAgAGYAYQBjAHQAbwByACAAZgBvAHIAIABvAHIAZwBhAG4AaQBjACAAZgBlAHIAdABpAGwAaQBzAGUAcgAgAGEAbgBkACAAYwByAG8AcAAgAHIAZQBzAGkAZAB1AGUAcwAgAHIAZQB0AHUAcgBuAGUAZAAgAHQAbwAgAHQAaABlACAAcwBvAGkAbABcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAE8AcgBnAGEAbgBpAGMARgBlAHIAdABpAGwAaQBzAGUAcgBBAG4AZABDAHIAbwBwAFIAZQBzAGkAZAB1AGUAcwBfAFYAYQByAGkAYQBiAGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIARQBGAE4AaQAgACYAIABFAEYATgAyAE8AaQBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAE8AcgBnAGEAbgBpAGMARgBlAHIAdABpAGwAaQBzAGUAcgBBAG4AZABDAHIAbwBwAFIAZQBzAGkAZAB1AGUAcwBfAFUAbgBpAHQAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAGsAZwAgAE4AMgBPACAALQAgAE4AIAAvACAAawBnACAATgBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAE8AcgBnAGEAbgBpAGMARgBlAHIAdABpAGwAaQBzAGUAcgBBAG4AZABDAHIAbwBwAFIAZQBzAGkAZAB1AGUAcwBfAFMAbwB1AHIAYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBWAEUARQBSAEcAIAAyADAAMgA2ADoAIABUAGEAYgBsAGUAIABBAC4AMgAuADEALgA0AFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYATwByAGcAYQBuAGkAYwBGAGUAcgB0AGkAbABpAHMAZQByAEEAbgBkAEMAcgBvAHAAUgBlAHMAaQBkAHUAZQBzAF8ATgBJAFIAUgBlAGYAZQByAGUAbgBjAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYATwByAGcAYQBuAGkAYwBGAGUAcgB0AGkAbABpAHMAZQByAEEAbgBkAEMAcgBvAHAAUgBlAHMAaQBkAHUAZQBzAF8ARABhAHQAYQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABNAEEASwBFAEEAUgBSAEEAWQAoADMALAAgADIALAAgAFwAbgAgACAAIAAgACAAIABMAEEATQBCAEQAQQAoAHIALABjACwAIABcAG4AIAAgACAAIAAgACAAIAAgAEkATgBEAEUAWAAoAHsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEMAbABpAG0AYQB0AGUAIAB6AG8AbgBlAFwAIgAsACAAXAAiAEUARgBOAGkAIAAmACAARQBGAE4AMgBPAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBXAGUAdAAgAGMAbABpAG0AYQB0AGUAIAB6AG8AbgBlAFwAIgAsACAAMAAuADAAMAA2ADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEQAcgB5ACAAYwBsAGkAbQBhAHQAZQAgAHoAbwBuAGUAXAAiACwAIAAwAC4AMAAwADUAXABuACAAIAAgACAAIAAgACAAIAB9ACwAIAByACwAIABjACkAXABuACAAIAAgACAAIAAgACkAXABuACAAIAAgACAAKQBcAG4AIAAgACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEUARgBPAHIAZwBhAG4AaQBjAEYAZQByAHQAaQBsAGkAcwBlAHIAQQBuAGQAQwByAG8AcABSAGUAcwBpAGQAdQBlAHMAXwBWAGEAcgBpAGEAdABpAG8AbgBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAXAAiACkAOwBcAG4AXABuAFwAbgBcAG4AXABuAFwAbgBcAG4AXABuAFwAbgBcAG4AXABuAFwAbgBcAG4AXABuAFwAbgBcAG4AXABuACIAfQBdACwAIgBwAHIAbwBqAGUAYwB0AE4AYQBtAGUAcwAiADoAWwAiAEMAbwBtAG0AbwBuAF8ARQBxAHUAYQB0AGkAbwBuAHMALgBDAG8AbQBtAG8AbgBfAEMAbwBuAHYAZQByAHQATgAyAE8AVABvAEMATwAyAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBFAHEAdQBhAHQAaQBvAG4AcwAuAEMAbwBtAG0AbwBuAF8AQwBvAG4AdgBlAHIAdABOADIATwBUAG8AQwBPADIAZQBfAFQAaQB0AGwAZQAiACwAIgBDAG8AbQBtAG8AbgBfAEUAcQB1AGEAdABpAG8AbgBzAC4AQwBvAG0AbQBvAG4AXwBDAG8AbgB2AGUAcgB0AE4AMgBPAFQAbwBDAE8AMgBlAF8AVgBhAHIAaQBhAGIAbABlACIALAAiAEMAbwBtAG0AbwBuAF8ARQBxAHUAYQB0AGkAbwBuAHMALgBDAG8AbQBtAG8AbgBfAEMAbwBuAHYAZQByAHQATgAyAE8AVABvAEMATwAyAGUAXwBVAG4AaQB0ACIALAAiAEMAbwBtAG0AbwBuAF8ARQBxAHUAYQB0AGkAbwBuAHMALgBDAG8AbQBtAG8AbgBfAEMAbwBuAHYAZQByAHQATgAyAE8AVABvAEMATwAyAGUAXwBOAEkAUgBSAGUAZgBlAHIAZQBuAGMAZQAiACwAIgBDAG8AbQBtAG8AbgBfAEUAcQB1AGEAdABpAG8AbgBzAC4AQwBvAG0AbQBvAG4AXwBDAG8AbgB2AGUAcgB0AE4AMgBPAFQAbwBDAE8AMgBlAF8ATABhAHQAZQB4AEUAcQB1AGEAdABpAG8AbgAiACwAIgBDAG8AbQBtAG8AbgBfAEUAcQB1AGEAdABpAG8AbgBzAC4AQwBvAG0AbQBvAG4AXwBDAG8AbgB2AGUAcgB0AE4AMgBPAFQAbwBDAE8AMgBlAF8AQQByAGcAdQBtAGUAbgB0AHMAIgAsACIAQwBvAG0AbQBvAG4AXwBFAHEAdQBhAHQAaQBvAG4AcwAuAEMAbwBtAG0AbwBuAF8AQwBvAG4AdgBlAHIAdABDAEgANABUAG8AQwBPADIAZQAiACwAIgBDAG8AbQBtAG8AbgBfAEUAcQB1AGEAdABpAG8AbgBzAC4AQwBvAG0AbQBvAG4AXwBDAG8AbgB2AGUAcgB0AEMASAA0AFQAbwBDAE8AMgBlAF8AVABpAHQAbABlACIALAAiAEMAbwBtAG0AbwBuAF8ARQBxAHUAYQB0AGkAbwBuAHMALgBDAG8AbQBtAG8AbgBfAEMAbwBuAHYAZQByAHQAQwBIADQAVABvAEMATwAyAGUAXwBWAGEAcgBpAGEAYgBsAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBFAHEAdQBhAHQAaQBvAG4AcwAuAEMAbwBtAG0AbwBuAF8AQwBvAG4AdgBlAHIAdABDAEgANABUAG8AQwBPADIAZQBfAFUAbgBpAHQAIgAsACIAQwBvAG0AbQBvAG4AXwBFAHEAdQBhAHQAaQBvAG4AcwAuAEMAbwBtAG0AbwBuAF8AQwBvAG4AdgBlAHIAdABDAEgANABUAG8AQwBPADIAZQBfAE4ASQBSAFIAZQBmAGUAcgBlAG4AYwBlACIALAAiAEMAbwBtAG0AbwBuAF8ARQBxAHUAYQB0AGkAbwBuAHMALgBDAG8AbQBtAG8AbgBfAEMAbwBuAHYAZQByAHQAQwBIADQAVABvAEMATwAyAGUAXwBMAGEAdABlAHgARQBxAHUAYQB0AGkAbwBuACIALAAiAEMAbwBtAG0AbwBuAF8ARQBxAHUAYQB0AGkAbwBuAHMALgBDAG8AbQBtAG8AbgBfAEMAbwBuAHYAZQByAHQAQwBIADQAVABvAEMATwAyAGUAXwBBAHIAZwB1AG0AZQBuAHQAcwAiACwAIgBDAG8AbQBtAG8AbgBfAEkAbgBwAHUAdABGAHUAbgBjAHQAaQBvAG4AcwAuAFUAdABpAGwAaQB0AHkAXwBHAGUAdABBAHIAcgBhAHkAVABhAGIAbABlAFIAbwB3AFMAdABhAHIAdABOAHUAbQBiAGUAcgAiACwAIgBDAG8AbQBtAG8AbgBfAEkAbgBwAHUAdABGAHUAbgBjAHQAaQBvAG4AcwAuAFUAdABpAGwAaQB0AHkAXwBHAGUAdABBAHIAcgBhAHkAVABhAGIAbABlAEMAbwBsAHUAbQBuAFMAdABhAHIAdABOAHUAbQBiAGUAcgAiACwAIgBDAG8AbQBtAG8AbgBfAEkAbgBwAHUAdABGAHUAbgBjAHQAaQBvAG4AcwAuAFUAdABpAGwAaQB0AHkAXwBEAGkAcwBwAGwAYQB5AEEAcgByAGEAeQBJAG4AVABhAGIAbABlACIALAAiAEMAbwBtAG0AbwBuAF8ASQBuAHAAdQB0AEYAdQBuAGMAdABpAG8AbgBzAC4AVQB0AGkAbABpAHQAeQBfAEwAbwBvAGsAdQBwAFYAYQBsAHUAZQBJAG4AVABhAGIAbABlACIALAAiAEMAbwBtAG0AbwBuAF8ASQBuAHAAdQB0AEYAdQBuAGMAdABpAG8AbgBzAC4AVQB0AGkAbABpAHQAeQBfAEwAbwBvAGsAdQBwAFYAYQBsAHUAZQBJAG4AVABhAGIAbABlAE4AdQBtAGIAZQByACIALAAiAEMAbwBtAG0AbwBuAF8ASQBuAHAAdQB0AEYAdQBuAGMAdABpAG8AbgBzAC4AVQB0AGkAbABpAHQAeQBfAEwAbwBvAGsAdQBwAFYAYQBsAHUAZQBJAG4AVABhAGIAbABlAFQAdwBvAEMAbwBsAHUAbQBuAHMAIgAsACIAQwBvAG0AbQBvAG4AXwBJAG4AcAB1AHQARgB1AG4AYwB0AGkAbwBuAHMALgBVAHQAaQBsAGkAdAB5AF8ATABvAG8AawB1AHAAVgBhAGwAdQBlAEkAbgBUAGEAYgBsAGUATwBuAGUAQwBvAGwAdQBtAG4AQQBuAGQASABlAGEAZABlAHIAIgAsACIAQwBvAG0AbQBvAG4AXwBJAG4AcAB1AHQARgB1AG4AYwB0AGkAbwBuAHMALgBVAHQAaQBsAGkAdAB5AF8AUwBwAGwAaQB0AFMAdAByAGkAbgBnAEkAbgB0AG8AQQByAHIAYQB5ACIALAAiAEMAbwBtAG0AbwBuAF8ASQBuAHAAdQB0AEYAdQBuAGMAdABpAG8AbgBzAC4AVQB0AGkAbABpAHQAeQBfAEcAZQB0AEMAbABpAG0AYQB0AGUAWgBvAG4AZQAiACwAIgBDAG8AbQBtAG8AbgBfAEkAbgBwAHUAdABGAHUAbgBjAHQAaQBvAG4AcwAuAFUAdABpAGwAaQB0AHkAXwBMAG8AbwBrAHUAcABJAHQAZQBtAEYAcgBvAG0ATQBpAG4ATQBhAHgAIgAsACIAQwBvAG0AbQBvAG4AXwBJAG4AcAB1AHQARgB1AG4AYwB0AGkAbwBuAHMALgBVAHQAaQBsAGkAdAB5AF8AUwB1AG0AUQB1AGEAbgB0AGkAdAB5AEYAcgBvAG0AQwByAGkAdABlAHIAaQBhACIALAAiAEMAbwBtAG0AbwBuAF8ASQBuAHAAdQB0AEYAdQBuAGMAdABpAG8AbgBzAC4AZwBlAHQATwB2AGUAcgBsAGEAcABwAGkAbgBnAFIAZQBwAG8AcgB0AGkAbgBnAFAAZQByAGkAbwBkAHMAIgAsACIAQwBvAG0AbQBvAG4AXwBJAG4AcAB1AHQARgB1AG4AYwB0AGkAbwBuAHMALgBVAHQAaQBsAGkAdAB5AF8ARABpAHMAcABsAGEAeQBGAHUAbgBjAHQAaQBvAG4ATgBhAG0AZQAiACwAIgBDAG8AbQBtAG8AbgBfAEkAbgBwAHUAdABGAHUAbgBjAHQAaQBvAG4AcwAuAFUAdABpAGwAaQB0AHkAXwBMAG8AbwBrAHUAcABOADIATwBFAEYARgByAG8AbQBQAHIAbwBkAEkAcgByAGkAZwBhAHQAaQBvAG4AUgBhAGkAbgBmAGEAbABsACIALAAiAEMAbwBtAG0AbwBuAF8ASQBuAHAAdQB0AEYAdQBuAGMAdABpAG8AbgBzAC4AQwBvAG0AbQBvAG4AQwByAG8AcABwAGkAbgBnAF8ARwBlAHQARgByAGEAYwBXAEUAVAAiACwAIgBDAG8AbQBtAG8AbgBfAEkAbgBwAHUAdABGAHUAbgBjAHQAaQBvAG4AcwAuAFUAdABpAGwAaQB0AHkAXwBDAG8AbgB2AGUAcgB0AFMAdABhAHQAZQBDAG8AbQBtAG8AbgBOAGEAbQBlAFQAbwBBAGIAYgByAGUAdgBpAGEAdABpAG8AbgAiACwAIgBDAG8AbQBtAG8AbgBfAEkAbgBwAHUAdABGAHUAbgBjAHQAaQBvAG4AcwAuAFUAdABpAGwAaQB0AHkAXwBTAG8AdQByAGMAZQBIAHkAcABlAHIAbABpAG4AawBEAGkAZgBmAGUAcgBlAG4AdABTAGgAZQBlAHQAIgAsACIAQwBvAG0AbQBvAG4AXwBJAG4AcAB1AHQARgB1AG4AYwB0AGkAbwBuAHMALgBVAHQAaQBsAGkAdAB5AF8AUgBlAHMAdQBsAHQAcwBJAHQAZQBtAEYAcgBvAG0ARQBxAHUAYQB0AGkAbwBuAFQAaQB0AGwAZQBBAG4AZABTAG8AdQByAGMAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGUAbgBzAGkAdAB5AE8AZgBNAGUAdABoAGEAbgBlAF8AVABpAHQAbABlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEQAZQBuAHMAaQB0AHkATwBmAE0AZQB0AGgAYQBuAGUAXwBVAG4AaQB0ACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEQAZQBuAHMAaQB0AHkATwBmAE0AZQB0AGgAYQBuAGUAXwBTAG8AdQByAGMAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGUAbgBzAGkAdAB5AE8AZgBNAGUAdABoAGEAbgBlAF8ARABhAHQAYQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBDAG8AbgB2AGUAcgB0AE4AMgBvAEUAbABlAG0AZQBuAHQAYQBsAFQAbwBNAG8AbABlAGMAdQBsAGEAcgBDAGcAXwBUAGkAdABsAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQwBvAG4AdgBlAHIAdABOADIAbwBFAGwAZQBtAGUAbgB0AGEAbABUAG8ATQBvAGwAZQBjAHUAbABhAHIAQwBnAF8AVgBhAHIAaQBhAGIAbABlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEMAbwBuAHYAZQByAHQATgAyAG8ARQBsAGUAbQBlAG4AdABhAGwAVABvAE0AbwBsAGUAYwB1AGwAYQByAEMAZwBfAFUAbgBpAHQAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQwBvAG4AdgBlAHIAdABOADIAbwBFAGwAZQBtAGUAbgB0AGEAbABUAG8ATQBvAGwAZQBjAHUAbABhAHIAQwBnAF8AUwBvAHUAcgBjAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQwBvAG4AdgBlAHIAdABOADIAbwBFAGwAZQBtAGUAbgB0AGEAbABUAG8ATQBvAGwAZQBjAHUAbABhAHIAQwBnAF8ARABhAHQAYQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBDAG8AbgB2AGUAcgB0AEcAYQBzAEUAbABlAG0AZQBuAHQAYQBsAFQAbwBNAG8AbABlAGMAdQBsAGEAcgBfAFQAaQB0AGwAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBDAG8AbgB2AGUAcgB0AEcAYQBzAEUAbABlAG0AZQBuAHQAYQBsAFQAbwBNAG8AbABlAGMAdQBsAGEAcgBfAFYAYQByAGkAYQBiAGwAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBDAG8AbgB2AGUAcgB0AEcAYQBzAEUAbABlAG0AZQBuAHQAYQBsAFQAbwBNAG8AbABlAGMAdQBsAGEAcgBfAFUAbgBpAHQAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQwBvAG4AdgBlAHIAdABHAGEAcwBFAGwAZQBtAGUAbgB0AGEAbABUAG8ATQBvAGwAZQBjAHUAbABhAHIAXwBTAG8AdQByAGMAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBDAG8AbgB2AGUAcgB0AEcAYQBzAEUAbABlAG0AZQBuAHQAYQBsAFQAbwBNAG8AbABlAGMAdQBsAGEAcgBfAEQAYQB0AGEAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARwBXAFAAXwBUAGkAdABsAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARwBXAFAAXwBWAGEAcgBpAGEAYgBsAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARwBXAFAAXwBVAG4AaQB0ACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEcAVwBQAF8AUwBvAHUAcgBjAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARwBXAFAAXwBEAGEAdABhACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEEAdQBzAHQAcgBhAGwAaQBhAG4AUwB0AGEAdABlAHMAVABlAHIAcgBpAHQAbwByAGkAZQBzAF8AVABpAHQAbABlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEEAdQBzAHQAcgBhAGwAaQBhAG4AUwB0AGEAdABlAHMAVABlAHIAcgBpAHQAbwByAGkAZQBzAF8AVgBhAHIAaQBhAGIAbABlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEEAdQBzAHQAcgBhAGwAaQBhAG4AUwB0AGEAdABlAHMAVABlAHIAcgBpAHQAbwByAGkAZQBzAF8AVQBuAGkAdAAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBBAHUAcwB0AHIAYQBsAGkAYQBuAFMAdABhAHQAZQBzAFQAZQByAHIAaQB0AG8AcgBpAGUAcwBfAFMAbwB1AHIAYwBlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEEAdQBzAHQAcgBhAGwAaQBhAG4AUwB0AGEAdABlAHMAVABlAHIAcgBpAHQAbwByAGkAZQBzAF8ARABhAHQAYQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBXAEEAUwBBADQAQQByAGUAYQBzAF8AVABpAHQAbABlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFcAQQBTAEEANABBAHIAZQBhAHMAXwBWAGEAcgBpAGEAYgBsAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AVwBBAFMAQQA0AEEAcgBlAGEAcwBfAFUAbgBpAHQAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AVwBBAFMAQQA0AEEAcgBlAGEAcwBfAFMAbwB1AHIAYwBlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFcAQQBTAEEANABBAHIAZQBhAHMAXwBEAGEAdABhACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFcAZQB0AEEAbgBkAEQAcgB5AFoAbwBuAGUAcwBfAFQAaQB0AGwAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBXAGUAdABBAG4AZABEAHIAeQBaAG8AbgBlAHMAXwBWAGEAcgBpAGEAYgBsAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AVwBlAHQAQQBuAGQARAByAHkAWgBvAG4AZQBzAF8AVQBuAGkAdAAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBXAGUAdABBAG4AZABEAHIAeQBaAG8AbgBlAHMAXwBTAG8AdQByAGMAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBXAGUAdABBAG4AZABEAHIAeQBaAG8AbgBlAHMAXwBWAGEAcgBpAGEAdABpAG8AbgAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBXAGUAdABBAG4AZABEAHIAeQBaAG8AbgBlAHMAXwBEAGEAdABhACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEMAbABpAG0AYQB0AGUAWgBvAG4AZQBzAF8AVABpAHQAbABlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEMAbABpAG0AYQB0AGUAWgBvAG4AZQBzAF8AVgBhAHIAaQBhAGIAbABlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEMAbABpAG0AYQB0AGUAWgBvAG4AZQBzAF8AVQBuAGkAdAAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBDAGwAaQBtAGEAdABlAFoAbwBuAGUAcwBfAFMAbwB1AHIAYwBlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEMAbABpAG0AYQB0AGUAWgBvAG4AZQBzAF8AVgBhAHIAaQBhAHQAaQBvAG4AIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQwBsAGkAbQBhAHQAZQBaAG8AbgBlAHMAXwBEAGEAdABhACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEMAbABpAG0AYQB0AGUAWgBvAG4AZQBzAF8AQQBwAHAAZQBuAGQAaQBjAGUAcwAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBUAGUAbQBwAGUAcgBhAHQAdQByAGUAWgBvAG4AZQBzAF8AVABpAHQAbABlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFQAZQBtAHAAZQByAGEAdAB1AHIAZQBaAG8AbgBlAHMAXwBWAGEAcgBpAGEAYgBsAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AVABlAG0AcABlAHIAYQB0AHUAcgBlAFoAbwBuAGUAcwBfAFUAbgBpAHQAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AVABlAG0AcABlAHIAYQB0AHUAcgBlAFoAbwBuAGUAcwBfAFMAbwB1AHIAYwBlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFQAZQBtAHAAZQByAGEAdAB1AHIAZQBaAG8AbgBlAHMAXwBWAGEAcgBpAGEAdABpAG8AbgAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBUAGUAbQBwAGUAcgBhAHQAdQByAGUAWgBvAG4AZQBzAF8ARABhAHQAYQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBSAGEAaQBuAGYAYQBsAGwAWgBvAG4AZQBzAF8AVABpAHQAbABlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFIAYQBpAG4AZgBhAGwAbABaAG8AbgBlAHMAXwBWAGEAcgBpAGEAYgBsAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AUgBhAGkAbgBmAGEAbABsAFoAbwBuAGUAcwBfAFUAbgBpAHQAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AUgBhAGkAbgBmAGEAbABsAFoAbwBuAGUAcwBfAFMAbwB1AHIAYwBlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFIAYQBpAG4AZgBhAGwAbABaAG8AbgBlAHMAXwBWAGEAcgBpAGEAdABpAG8AbgAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBSAGEAaQBuAGYAYQBsAGwAWgBvAG4AZQBzAF8ARABhAHQAYQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBMAGUAYQBjAGgAaQBuAGcAWgBvAG4AZQBzAF8AVABpAHQAbABlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEwAZQBhAGMAaABpAG4AZwBaAG8AbgBlAHMAXwBWAGEAcgBpAGEAYgBsAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ATABlAGEAYwBoAGkAbgBnAFoAbwBuAGUAcwBfAFUAbgBpAHQAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ATABlAGEAYwBoAGkAbgBnAFoAbwBuAGUAcwBfAFMAbwB1AHIAYwBlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEwAZQBhAGMAaABpAG4AZwBaAG8AbgBlAHMAXwBWAGEAcgBpAGEAdABpAG8AbgAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBMAGUAYQBjAGgAaQBuAGcAWgBvAG4AZQBzAF8ARABhAHQAYQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAHIAYQBjAFcARQBUAF8AVABpAHQAbABlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAcgBhAGMAVwBFAFQAXwBVAG4AaQB0ACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAcgBhAGMAVwBFAFQAXwBTAG8AdQByAGMAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAHIAYQBjAFcARQBUAF8ATgBJAFIAUgBlAGYAZQByAGUAbgBjAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgByAGEAYwBXAEUAVABfAEQAYQB0AGEAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgByAGEAYwBXAEUAVABfAFYAYQByAGkAYQB0AGkAbwBuACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEQAYQB0AGEAUwBjAG8AcgBlAHMAXwBTAGMAbwBwAGUAMwBfAFQAaQB0AGwAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGEAdABhAFMAYwBvAHIAZQBzAF8AUwBjAG8AcABlADMAXwBWAGEAcgBpAGEAYgBsAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABhAHQAYQBTAGMAbwByAGUAcwBfAFMAYwBvAHAAZQAzAF8AVQBuAGkAdAAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGEAdABhAFMAYwBvAHIAZQBzAF8AUwBjAG8AcABlADMAXwBTAG8AdQByAGMAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGEAdABhAFMAYwBvAHIAZQBzAF8AUwBjAG8AcABlADMAXwBWAGEAcgBpAGEAdABpAG8AbgAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGEAdABhAFMAYwBvAHIAZQBzAF8AUwBjAG8AcABlADMAXwBEAGEAdABhACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAcgBhAGMATABFAEEAQwBIAF8AVABpAHQAbABlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAcgBhAGMATABFAEEAQwBIAF8AVQBuAGkAdAAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAHIAYQBjAEwARQBBAEMASABfAFMAbwB1AHIAYwBlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAcgBhAGMATABFAEEAQwBIAF8ATgBJAFIAUgBlAGYAZQByAGUAbgBjAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgByAGEAYwBMAEUAQQBDAEgAXwBEAGEAdABhACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAcgBhAGMATABFAEEAQwBIAF8AVgBhAHIAaQBhAHQAaQBvAG4AIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAGwAZQBhAGMAaABfAFQAaQB0AGwAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYAbABlAGEAYwBoAF8AVQBuAGkAdAAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYAbABlAGEAYwBoAF8AUwBvAHUAcgBjAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAGwAZQBhAGMAaABfAE4ASQBSAFIAZQBmAGUAcgBlAG4AYwBlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEUARgBsAGUAYQBjAGgAXwBEAGEAdABhACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEUARgBsAGUAYQBjAGgAXwBWAGEAcgBpAGEAdABpAG8AbgAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYATgAyAE8AXwBUAGkAdABsAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAE4AMgBPAF8AVQBuAGkAdAAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYATgAyAE8AXwBTAG8AdQByAGMAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYATgAyAE8AXwBOAEkAUgBSAGUAZgBlAHIAZQBuAGMAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYATgAyAE8AXwBEAGEAdABhACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEUARgBOADIATwBfAFYAYQByAGkAYQB0AGkAbwBuACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAcgBhAGMAVwBFAFQASQByAHIAaQBnAGEAdABpAG8AbgBfAFQAaQB0AGwAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAHIAYQBjAFcARQBUAEkAcgByAGkAZwBhAHQAaQBvAG4AXwBVAG4AaQB0ACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAcgBhAGMAVwBFAFQASQByAHIAaQBnAGEAdABpAG8AbgBfAFMAbwB1AHIAYwBlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAcgBhAGMAVwBFAFQASQByAHIAaQBnAGEAdABpAG8AbgBfAE4ASQBSAFIAZQBmAGUAcgBlAG4AYwBlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAcgBhAGMAVwBFAFQASQByAHIAaQBnAGEAdABpAG8AbgBfAEQAYQB0AGEAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgByAGEAYwBXAEUAVABJAHIAcgBpAGcAYQB0AGkAbwBuAF8AVgBhAHIAaQBhAHQAaQBvAG4AIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAFAAYQBzAHQAdQByAGUAUgBhAG4AZwBlAEEAbgBkAFAAYQBkAGQAbwBjAGsAXwBUAGkAdABsAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAFAAYQBzAHQAdQByAGUAUgBhAG4AZwBlAEEAbgBkAFAAYQBkAGQAbwBjAGsAXwBVAG4AaQB0ACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEUARgBQAGEAcwB0AHUAcgBlAFIAYQBuAGcAZQBBAG4AZABQAGEAZABkAG8AYwBrAF8AUwBvAHUAcgBjAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAFAAYQBzAHQAdQByAGUAUgBhAG4AZwBlAEEAbgBkAFAAYQBkAGQAbwBjAGsAXwBOAEkAUgBSAGUAZgBlAHIAZQBuAGMAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYAUABhAHMAdAB1AHIAZQBSAGEAbgBnAGUAQQBuAGQAUABhAGQAZABvAGMAawBfAEQAYQB0AGEAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAFAAYQBzAHQAdQByAGUAUgBhAG4AZwBlAEEAbgBkAFAAYQBkAGQAbwBjAGsAXwBWAGEAcgBpAGEAdABpAG8AbgAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBNAG8AbgB0AGgAcwBUAG8AUwBlAGEAcwBvAG4AcwBfAFQAaQB0AGwAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBNAG8AbgB0AGgAcwBUAG8AUwBlAGEAcwBvAG4AcwBfAFUAbgBpAHQAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ATQBvAG4AdABoAHMAVABvAFMAZQBhAHMAbwBuAHMAXwBTAG8AdQByAGMAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBNAG8AbgB0AGgAcwBUAG8AUwBlAGEAcwBvAG4AcwBfAE4ASQBSAFIAZQBmAGUAcgBlAG4AYwBlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAE0AbwBuAHQAaABzAFQAbwBTAGUAYQBzAG8AbgBzAF8ARABhAHQAYQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBNAG8AbgB0AGgAcwBUAG8AUwBlAGEAcwBvAG4AcwBfAFYAYQByAGkAYQB0AGkAbwBuACIAXQAsACIAbABvAGMAYQBsAGUAIgA6AHsAIgBsAGkAcwB0AFMAZQBwAGEAcgBhAHQAbwByACIAOgAiACwAIgAsACIAcgBvAHcAUwBlAHAAYQByAGEAdABvAHIAIgA6ACIAOwAiACwAIgBjAG8AbAB1AG0AbgBTAGUAcABhAHIAYQB0AG8AcgAiADoAIgAsACIALAAiAHQAaABvAHUAcwBhAG4AZABzAFMAZQBwAGEAcgBhAHQAbwByACIAOgAiACwAIgAsACIAdABoAG8AdQBzAGEAbgBkAHMAUABvAHMAaQB0AGkAbwBuAHMAIgA6AFsAMwBdACwAIgBkAGUAYwBpAG0AYQBsAFMAZQBwAGEAcgBhAHQAbwByACIAOgAiAC4AIgAsACIAZABhAHQAZQBPAHIAZABlAHIAIgA6ACIARABNAFkAIgAsACIAYwB1AHIAcgBlAG4AYwB5AFMAeQBtAGIAbwBsACIAOgAiACQAIgAsACIAaQBzAEMAdQByAHIAZQBuAGMAeQBTAHkAbQBiAG8AbABMAGUAYQBkACIAOgB0AHIAdQBlACwAIgBpAHMAQwB1AHIAcgBlAG4AYwB5AFMAZQBwAEIAeQBTAHAAYQBjAGUAIgA6AGYAYQBsAHMAZQAsACIAcgBvAHcATABlAHQAdABlAHIAIgA6ACIAUgAiACwAIgBjAG8AbAB1AG0AbgBMAGUAdAB0AGUAcgAiADoAIgBDACIALAAiAHIAYwBMAGUAZgB0AEIAcgBhAGMAawBlAHQAIgA6ACIAWwAiACwAIgByAGMAUgBpAGcAaAB0AEIAcgBhAGMAawBlAHQAIgA6ACIAXQAiACwAIgBzAHQAYQB0AGUAbQBlAG4AdABTAGUAcABhAHIAYQB0AG8AcgAiADoAIgA7ACIALAAiAGwAbwBjAGEAbABlAE4AYQBtAGUAIgA6ACIAZQBuAC0AdQBzACIAfQB9AA==</AFEJSONBlob>
-</file>
-
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <TaxCatchAll xmlns="09eef6d6-daa8-4301-8f9f-b1ec38079286" xsi:nil="true"/>
-    <lcf76f155ced4ddcb4097134ff3c332f xmlns="7291119c-fce9-4911-96ae-b800be5dccd8">
-      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    </lcf76f155ced4ddcb4097134ff3c332f>
-  </documentManagement>
-</p:properties>
-</file>
-
-<file path=customXml/item4.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x010100ACB660BB23738846A00119B5826AC974" ma:contentTypeVersion="11" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="3e3613359d4ae7f6bda6c57be713f101">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="7291119c-fce9-4911-96ae-b800be5dccd8" xmlns:ns3="09eef6d6-daa8-4301-8f9f-b1ec38079286" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="87491bfad7f11426ad96486e70428b3e" ns2:_="" ns3:_="">
     <xsd:import namespace="7291119c-fce9-4911-96ae-b800be5dccd8"/>
@@ -11871,34 +11847,31 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{B6BE249C-20B1-4A62-BBCD-F2A46D88BCAB}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.advancedformulaenvironment.officeapps.live.com/afejsonblob/1.0"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<AFEJSONBlob xmlns="http://schemas.advancedformulaenvironment.officeapps.live.com/afejsonblob/1.0">ewAiAHMAYwBoAGUAbQBhACIAOgAiAGgAdAB0AHAAOgAvAC8AcwBjAGgAZQBtAGEAcwAuAGEAZAB2AGEAbgBjAGUAZABmAG8AcgBtAHUAbABhAGUAbgB2AGkAcgBvAG4AbQBlAG4AdAAuAG8AZgBmAGkAYwBlAGEAcABwAHMALgBsAGkAdgBlAC4AYwBvAG0ALwBhAGYAZQBwAHIAbwBqAGUAYwB0AHMALwAwAC4AMgAiACwAIgBmAGkAbABlAHMAIgA6AFsAewAiAHAAYQB0AGgAIgA6ACIALwBwAHIAbwBqAGUAYwB0AHMALwBXAG8AcgBrAGIAbwBvAGsAIgAsACIAdABlAHgAdAAiADoAIgAvAC8AIAAtAC0ALQAgAFcAbwByAGsAYgBvAG8AawAgAG0AbwBkAHUAbABlACAALQAtAC0AXABuAC8ALwAgAEEAIABmAGkAbABlACAAbwBmACAAbgBhAG0AZQAgAGQAZQBmAGkAbgBpAHQAaQBvAG4AcwAgAG8AZgAgAHQAaABlACAAZgBvAHIAbQA6AFwAbgAvAC8AIAAgACAAIABuAGEAbQBlACAAPQAgAGQAZQBmAGkAbgBpAHQAaQBvAG4AOwBcAG4AIgB9ACwAewAiAHAAYQB0AGgAIgA6ACIALwBwAHIAbwBqAGUAYwB0AHMALwBDAG8AbQBtAG8AbgBfAEUAcQB1AGEAdABpAG8AbgBzACIALAAiAHQAZQB4AHQAIgA6ACIAXABuAC8AKgAgAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuAEMAbwBtAG0AbwBuAF8AQwBvAG4AdgBlAHIAdABOADIATwBUAG8AQwBPADIAZQBcAG4AQwBvAG4AdgBlAHIAdAAgAG4AaQB0AHIAbwB1AHMAIABvAHgAaQBkAGUAIABlAG0AaQBzAHMAaQBvAG4AcwAgAHQAbwAgAGMAYQByAGIAbwBuACAAZABpAG8AeABpAGQAZQAgAGUAcQB1AGkAdgBhAGwAZQBuAHQAIABlAG0AaQBzAHMAaQBvAG4AcwBcAG4ARQBOADIATwAgAEMATwAyAGUAXABuAHQAIABDAE8AMgBlAFwAbgBFAE4AMgBPADoAIABuAGkAdAByAG8AdQBzACAAbwB4AGkAZABlACAAZQBtAGkAcwBzAGkAbwBuAHMAIAAoAHQAIABOADIATwApAFwAbgBHAFcAUABOADIATwA6ACAAZwBsAG8AYgBhAGwAIAB3AGEAcgBtAGkAbgBnACAAcABvAHQAZQBuAHQAaQBhAGwAIABmAG8AcgAgAG4AaQB0AHIAbwB1AHMAIABvAHgAaQBkAGUAIAAoAHQAIABDAE8AMgAtAGUAIAAvACAAdAAgAE4AMgBPACkAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AKgAvAFwAbgBcAG4AXABuAEMAbwBtAG0AbwBuAF8AQwBvAG4AdgBlAHIAdABOADIATwBUAG8AQwBPADIAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABFAF8ATgAyAE8ALAAgAEcAVwBQAF8ATgAyAE8ALABcAG4AIAAgACAAIABFAF8ATgAyAE8AIAAqACAARwBXAFAAXwBOADIATwBcAG4AIAAgACkAXABuADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAEMAbwBuAHYAZQByAHQATgAyAE8AVABvAEMATwAyAGUAXwBUAGkAdABsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAEMAbwBuAHYAZQByAHQAIABuAGkAdAByAG8AdQBzACAAbwB4AGkAZABlACAAZQBtAGkAcwBzAGkAbwBuAHMAIAB0AG8AIABjAGEAcgBiAG8AbgAgAGQAaQBvAHgAaQBkAGUAIABlAHEAdQBpAHYAYQBsAGUAbgB0ACAAZQBtAGkAcwBzAGkAbwBuAHMAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AQwBvAG4AdgBlAHIAdABOADIATwBUAG8AQwBPADIAZQBfAFYAYQByAGkAYQBiAGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIARQBOADIATwAgAEMATwAyAGUAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AQwBvAG4AdgBlAHIAdABOADIATwBUAG8AQwBPADIAZQBfAFUAbgBpAHQAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAHQAIABDAE8AMgBlAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAEMAbwBuAHYAZQByAHQATgAyAE8AVABvAEMATwAyAGUAXwBOAEkAUgBSAGUAZgBlAHIAZQBuAGMAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AQwBvAG4AdgBlAHIAdABOADIATwBUAG8AQwBPADIAZQBfAEwAYQB0AGUAeABFAHEAdQBhAHQAaQBvAG4AXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAEMATwAyAF8AZQAgAD0AIABFAF8AewBOADIATwB9ACAAXABcAHQAaQBtAGUAcwAgAEcAVwBQAF8AewBOADIATwB9AFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAEMAbwBuAHYAZQByAHQATgAyAE8AVABvAEMATwAyAGUAXwBBAHIAZwB1AG0AZQBuAHQAcwBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABNAEEASwBFAEEAUgBSAEEAWQAoADIALAAgADIALAAgAFwAbgAgACAAIAAgACAAIABMAEEATQBCAEQAQQAoAHIALABjACwAIABcAG4AIAAgACAAIAAgACAAIAAgAEkATgBEAEUAWAAoAHsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEUATgAyAE8AXAAiACwAXAAiAE4AaQB0AHIAbwB1AHMAIABvAHgAaQBkAGUAIABlAG0AaQBzAHMAaQBvAG4AcwAgACgAdAAgAE4AMgBPACkAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEcAVwBQAE4AMgBPAFwAIgAsAFwAIgBHAGwAbwBiAGEAbAAgAHcAYQByAG0AaQBuAGcAIABwAG8AdABlAG4AdABpAGEAbAAgAGYAbwByACAAbgBpAHQAcgBvAHUAcwAgAG8AeABpAGQAZQAgACgAdAAgAEMATwAyAC0AZQAgAC8AIAB0ACAATgAyAE8AKQBcACIAXABuACAAIAAgACAAIAAgACAAIAB9ACwAIAByACwAIABjACkAXABuACAAIAAgACAAIAAgACkAXABuACAAIAAgACAAKQBcAG4AIAAgACkAOwBcAG4AXABuAC8AKgAgAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuAEMAbwBtAG0AbwBuAF8AQwBvAG4AdgBlAHIAdABDAEgANABUAG8AQwBPADIAZQBcAG4AQwBvAG4AdgBlAHIAdAAgAG0AZQB0AGgAYQBuAGUAIABlAG0AaQBzAHMAaQBvAG4AcwAgAHQAbwAgAGMAYQByAGIAbwBuACAAZABpAG8AeABpAGQAZQAgAGUAcQB1AGkAdgBhAGwAZQBuAHQAIABlAG0AaQBzAHMAaQBvAG4AcwBcAG4ARQBDAEgANAAgAEMATwAyAGUAXABuAHQAIABDAE8AMgBlAFwAbgBFAEMASAA0ADoAIABtAGUAdABoAGEAbgBlACAAZQBtAGkAcwBzAGkAbwBuAHMAIAAoAHQAIABDAEgANAApAFwAbgBHAFcAUABDAEgANAA6ACAAZwBsAG8AYgBhAGwAIAB3AGEAcgBtAGkAbgBnACAAcABvAHQAZQBuAHQAaQBhAGwAIABmAG8AcgAgAG0AZQB0AGgAYQBuAGUAIAAoAHQAIABDAE8AMgAtAGUAIAAvACAAdAAgAEMASAA0ACkAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AKgAvAFwAbgBcAG4AXABuAEMAbwBtAG0AbwBuAF8AQwBvAG4AdgBlAHIAdABDAEgANABUAG8AQwBPADIAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABFAF8AQwBIADQALAAgAEcAVwBQAF8AQwBIADQALABcAG4AIAAgACAAIABFAF8AQwBIADQAIAAqACAARwBXAFAAXwBDAEgANABcAG4AIAAgACkAXABuADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAEMAbwBuAHYAZQByAHQAQwBIADQAVABvAEMATwAyAGUAXwBUAGkAdABsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAEMAbwBuAHYAZQByAHQAIABtAGUAdABoAGEAbgBlACAAZQBtAGkAcwBzAGkAbwBuAHMAIAB0AG8AIABjAGEAcgBiAG8AbgAgAGQAaQBvAHgAaQBkAGUAIABlAHEAdQBpAHYAYQBsAGUAbgB0ACAAZQBtAGkAcwBzAGkAbwBuAHMAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AQwBvAG4AdgBlAHIAdABDAEgANABUAG8AQwBPADIAZQBfAFYAYQByAGkAYQBiAGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIARQBDAEgANAAgAEMATwAyAGUAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AQwBvAG4AdgBlAHIAdABDAEgANABUAG8AQwBPADIAZQBfAFUAbgBpAHQAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAHQAIABDAE8AMgBlAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAEMAbwBuAHYAZQByAHQAQwBIADQAVABvAEMATwAyAGUAXwBOAEkAUgBSAGUAZgBlAHIAZQBuAGMAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AQwBvAG4AdgBlAHIAdABDAEgANABUAG8AQwBPADIAZQBfAEwAYQB0AGUAeABFAHEAdQBhAHQAaQBvAG4AXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAEMATwAyAF8AZQAgAD0AIABFAF8AewBDAEgANAB9ACAAXABcAHQAaQBtAGUAcwAgAEcAVwBQAF8AewBDAEgANAB9AFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAEMAbwBuAHYAZQByAHQAQwBIADQAVABvAEMATwAyAGUAXwBBAHIAZwB1AG0AZQBuAHQAcwBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABNAEEASwBFAEEAUgBSAEEAWQAoADIALAAgADIALAAgAFwAbgAgACAAIAAgACAAIABMAEEATQBCAEQAQQAoAHIALABjACwAIABcAG4AIAAgACAAIAAgACAAIAAgAEkATgBEAEUAWAAoAHsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEUAQwBIADQAXAAiACwAXAAiAE0AZQB0AGgAYQBuAGUAIABlAG0AaQBzAHMAaQBvAG4AcwAgACgAdAAgAEMASAA0ACkAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEcAVwBQAEMASAA0AFwAIgAsAFwAIgBHAGwAbwBiAGEAbAAgAHcAYQByAG0AaQBuAGcAIABwAG8AdABlAG4AdABpAGEAbAAgAGYAbwByACAAbQBlAHQAaABhAG4AZQAgACgAdAAgAEMATwAyAC0AZQAgAC8AIAB0ACAAQwBIADQAKQBcACIAXABuACAAIAAgACAAIAAgACAAIAB9ACwAIAByACwAIABjACkAXABuACAAIAAgACAAIAAgACkAXABuACAAIAAgACAAKQBcAG4AIAAgACkAOwAiAH0ALAB7ACIAcABhAHQAaAAiADoAIgAvAHAAcgBvAGoAZQBjAHQAcwAvAEMAbwBtAG0AbwBuAF8ASQBuAHAAdQB0AEYAdQBuAGMAdABpAG8AbgBzACIALAAiAHQAZQB4AHQAIgA6ACIAVQB0AGkAbABpAHQAeQBfAEcAZQB0AEEAcgByAGEAeQBUAGEAYgBsAGUAUgBvAHcAUwB0AGEAcgB0AE4AdQBtAGIAZQByAFwAbgA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAAVABhAGIAbABlAGgAZQBhAGQAZQByAEMAZQBsAGwALABSAG8AdwBzAEIAZQB0AHcAZQBlAG4ASABlAGEAZABlAHIAYQBuAGQAQQByAHIAYQB5ACwAXABuACAAIAAgACAAUgBPAFcAKABUAGEAYgBsAGUAaABlAGEAZABlAHIAQwBlAGwAbAApACAAKwAgAFIAbwB3AHMAQgBlAHQAdwBlAGUAbgBIAGUAYQBkAGUAcgBhAG4AZABBAHIAcgBhAHkAIAAtACAAMQBcAG4AKQA7AFwAbgBcAG4AVQB0AGkAbABpAHQAeQBfAEcAZQB0AEEAcgByAGEAeQBUAGEAYgBsAGUAQwBvAGwAdQBtAG4AUwB0AGEAcgB0AE4AdQBtAGIAZQByAFwAbgA9AEwAQQBNAEIARABBACgAXABuACAAIABUAGEAYgBsAGUASABlAGEAZABlAHIAQwBlAGwAbAAsAFwAbgAgACAAQwBPAEwAVQBNAE4AKABUAGEAYgBsAGUASABlAGEAZABlAHIAQwBlAGwAbAApAFwAbgApADsAXABuAFwAbgBVAHQAaQBsAGkAdAB5AF8ARABpAHMAcABsAGEAeQBBAHIAcgBhAHkASQBuAFQAYQBiAGwAZQBcAG4APQBMAEEATQBCAEQAQQAoAFwAbgAgAEEAcgByAGEAeQBEAGEAdABhACwAIABUAGEAYgBsAGUAaABlAGEAZABlAHIAQwBlAGwAbAAsACAAUgBvAHcAcwBCAGUAdAB3AGUAZQBuAEgAZQBhAGQAZQByAGEAbgBkAEEAcgByAGEAeQAsACAAWwBDAG8AbAB1AG0AbgBzAEIAZQB0AHcAZQBlAG4ASABlAGEAZABlAHIAQQBuAGQAQQByAHIAYQB5AF0ALABcAG4AIABJAEYARQBSAFIATwBSACgAXABuACAAIAAgACAAIABJAE4ARABFAFgAKABcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAVQBOAEkAUQBVAEUAKABBAHIAcgBhAHkARABhAHQAYQApACwAIABcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAUgBPAFcAKAApAC0AVQB0AGkAbABpAHQAeQBfAEcAZQB0AEEAcgByAGEAeQBUAGEAYgBsAGUAUgBvAHcAUwB0AGEAcgB0AE4AdQBtAGIAZQByACgAVABhAGIAbABlAGgAZQBhAGQAZQByAEMAZQBsAGwALAAgAFIAbwB3AHMAQgBlAHQAdwBlAGUAbgBIAGUAYQBkAGUAcgBhAG4AZABBAHIAcgBhAHkAKQAsACAAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgAEMATwBMAFUATQBOACgAKQAtAFUAdABpAGwAaQB0AHkAXwBHAGUAdABBAHIAcgBhAHkAVABhAGIAbABlAEMAbwBsAHUAbQBuAFMAdABhAHIAdABOAHUAbQBiAGUAcgAoAFQAYQBiAGwAZQBoAGUAYQBkAGUAcgBDAGUAbABsACkAIAArAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIABJAEYAKABJAFMATwBNAEkAVABUAEUARAAoAEMAbwBsAHUAbQBuAHMAQgBlAHQAdwBlAGUAbgBIAGUAYQBkAGUAcgBBAG4AZABBAHIAcgBhAHkAKQAsACAAMQAsACAAQwBvAGwAdQBtAG4AcwBCAGUAdAB3AGUAZQBuAEgAZQBhAGQAZQByAEEAbgBkAEEAcgByAGEAeQApAFwAbgAgACAAIAAgACAAIAAgACAAKQAsACAAXAAiAFwAIgBcAG4AIAAgACAAIAApAFwAbgApADsAXABuAFwAbgBVAHQAaQBsAGkAdAB5AF8ATABvAG8AawB1AHAAVgBhAGwAdQBlAEkAbgBUAGEAYgBsAGUAXABuAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABMAG8AbwBrAHUAcABWAGEAbAB1AGUALAAgAEwAbwBvAGsAdQBwAEEAcgByAGEAeQAsACAAUgBlAHQAdQByAG4AQQByAHIAYQB5ACwAXABuACAAIAAgACAAWABMAE8ATwBLAFUAUAAoAEwAbwBvAGsAdQBwAFYAYQBsAHUAZQAsACAATABvAG8AawB1AHAAQQByAHIAYQB5ACwAIABSAGUAdAB1AHIAbgBBAHIAcgBhAHkALAAgAFwAIgBcACIAKQBcAG4AKQA7AFwAbgBcAG4AVQB0AGkAbABpAHQAeQBfAEwAbwBvAGsAdQBwAFYAYQBsAHUAZQBJAG4AVABhAGIAbABlAE4AdQBtAGIAZQByAFwAbgA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAATABvAG8AawB1AHAAVgBhAGwAdQBlACwAIABMAG8AbwBrAHUAcABBAHIAcgBhAHkALAAgAFIAZQB0AHUAcgBuAEEAcgByAGEAeQAsAFwAbgAgACAAIAAgAEkARgAoAEkAUwBOAFUATQBCAEUAUgAoAFwAbgAgACAAIAAgACAAIAAgACAAWABMAE8ATwBLAFUAUAAoAEwAbwBvAGsAdQBwAFYAYQBsAHUAZQAsACAATABvAG8AawB1AHAAQQByAHIAYQB5ACwAIABSAGUAdAB1AHIAbgBBAHIAcgBhAHkALAAgAFwAIgBcACIAKQBcAG4AIAAgACAAIAApACwAIABYAEwATwBPAEsAVQBQACgATABvAG8AawB1AHAAVgBhAGwAdQBlACwAIABMAG8AbwBrAHUAcABBAHIAcgBhAHkALAAgAFIAZQB0AHUAcgBuAEEAcgByAGEAeQAsACAAXAAiAFwAIgApACwAIAAwACkAXABuACkAOwBcAG4AXABuAFUAdABpAGwAaQB0AHkAXwBMAG8AbwBrAHUAcABWAGEAbAB1AGUASQBuAFQAYQBiAGwAZQBUAHcAbwBDAG8AbAB1AG0AbgBzAFwAbgA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAATABvAG8AawB1AHAAVgBhAGwAdQBlADEALAAgAEwAbwBvAGsAdQBwAFYAYQBsAHUAZQAyACwAIABMAG8AbwBrAHUAcABBAHIAcgBhAHkAMQAsACAATABvAG8AawB1AHAAQQByAHIAYQB5ADIALAAgAFIAZQB0AHUAcgBuAEEAcgByAGEAeQAsACAAWwBWAGEAbAB1AGUASQBGAEYAYQBsAHMAZQBdACwAXABuACAAIAAgACAAWABMAE8ATwBLAFUAUAAoADEALAAgACgATABvAG8AawB1AHAAQQByAHIAYQB5ADEAPQBMAG8AbwBrAHUAcABWAGEAbAB1AGUAMQApACoAKABMAG8AbwBrAHUAcABBAHIAcgBhAHkAMgA9AEwAbwBvAGsAdQBwAFYAYQBsAHUAZQAyACkALAAgAFIAZQB0AHUAcgBuAEEAcgByAGEAeQAsACAASQBGACgASQBTAE8ATQBJAFQAVABFAEQAKABWAGEAbAB1AGUASQBGAEYAYQBsAHMAZQApACwAIABcACIAXAAiACwAIABWAGEAbAB1AGUASQBGAEYAYQBsAHMAZQApACkAXABuACkAOwBcAG4AXABuAFUAdABpAGwAaQB0AHkAXwBMAG8AbwBrAHUAcABWAGEAbAB1AGUASQBuAFQAYQBiAGwAZQBPAG4AZQBDAG8AbAB1AG0AbgBBAG4AZABIAGUAYQBkAGUAcgBcAG4APQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAEwAbwBvAGsAdQBwAFYAYQBsAHUAZQAxACwAIABMAG8AbwBrAHUAcABWAGEAbAB1AGUAMgAsACAATABvAG8AawB1AHAAQQByAHIAYQB5ADEALAAgAEwAbwBvAGsAdQBwAEEAcgByAGEAeQAyACwAIABSAGUAdAB1AHIAbgBBAHIAcgBhAHkALAAgAFsAVgBhAGwAdQBlAEkAZgBGAGEAbABzAGUAXQAsAFwAbgAgACAAIAAgAEkARgBFAFIAUgBPAFIAKABcAG4AIAAgACAAIAAgACAAIAAgAFgATABPAE8ASwBVAFAAKABMAG8AbwBrAHUAcABWAGEAbAB1AGUAMQAsACAATABvAG8AawB1AHAAQQByAHIAYQB5ADEALABcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAWABMAE8ATwBLAFUAUAAoAEwAbwBvAGsAdQBwAFYAYQBsAHUAZQAyACwAIABMAG8AbwBrAHUAcABBAHIAcgBhAHkAMgAsACAAUgBlAHQAdQByAG4AQQByAHIAYQB5ACkAXABuACAAIAAgACAAIAAgACAAIAApACwAXABuACAAIAAgACAAIAAgACAAIABJAEYAKABJAFMATwBNAEkAVABUAEUARAAoAFYAYQBsAHUAZQBJAGYARgBhAGwAcwBlACkALAAgAFwAIgBcACIALAAgAFYAYQBsAHUAZQBJAGYARgBhAGwAcwBlACkAXABuACAAIAAgACAAKQBcAG4AKQA7AFwAbgBcAG4AVQB0AGkAbABpAHQAeQBfAFMAcABsAGkAdABTAHQAcgBpAG4AZwBJAG4AdABvAEEAcgByAGEAeQBcAG4APQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAEMAZQBsAGwALAAgAEQAZQBsAGkAbQBpAHQAZQByACwAIABbAEMAaABhAHIAYQBjAHQAZQByAFQAbwBSAGUAbQBvAHYAZQAxAF0ALAAgAFsAQwBoAGEAcgBhAGMAdABlAHIAVABvAFIAZQBtAG8AdgBlADIAXQAsAFwAbgAgACAAIAAgACAAIAAgACAARgBJAEwAVABFAFIAWABNAEwAKABcAG4AIAAgACAAIAAgACAAIAAgAFwAIgA8AHQAPgA8AHMAPgBcACIAIAAmAFwAbgAgACAAIAAgACAAIAAgACAAUwBVAEIAUwBUAEkAVABVAFQARQAoAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIABTAFUAQgBTAFQASQBUAFUAVABFACgAUwBVAEIAUwBUAEkAVABVAFQARQAoAEMAZQBsAGwALABDAGgAYQByAGEAYwB0AGUAcgBUAG8AUgBlAG0AbwB2AGUAMQAsAFwAIgBcACIAKQAsAEMAaABhAHIAYQBjAHQAZQByAFQAbwBSAGUAbQBvAHYAZQAyACwAXAAiAFwAIgApACwAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgAEQAZQBsAGkAbQBpAHQAZQByACwAXAAiADwALwBzAD4APABzAD4AXAAiAFwAbgAgACAAIAAgACAAIAAgACAAKQAgACYAXABuACAAIAAgACAAIAAgACAAIABcACIAPAAvAHMAPgA8AC8AdAA+AFwAIgAsAFwAbgAgACAAIAAgACAAIAAgACAAXAAiAC8ALwBzAFwAIgBcAG4AIAAgACAAIAApAFwAbgApADsAXABuAFwAbgBVAHQAaQBsAGkAdAB5AF8ARwBlAHQAQwBsAGkAbQBhAHQAZQBaAG8AbgBlAFwAbgA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAAYQB2AGcAVABlAG0AcAAsAGEAdgBnAFIAYQBpAG4ALABmAHIAbwBzAHQARABhAHkAcwAsAGUAbABlAHYALABtAGEAcABfAHAAZQB0ACwAXABuACAAIAAgACAAbQBpAG4AVABlAG0AcABBAHIAcgBhAHkALABtAGEAeABUAGUAbQBwAEEAcgByAGEAeQAsAFwAbgAgACAAIAAgAG0AaQBuAFIAYQBpAG4AZgBhAGwAbABBAHIAcgBhAHkALABtAGEAeABSAGEAaQBuAGYAYQBsAGwAQQByAHIAYQB5ACwAXABuACAAIAAgACAAbQBpAG4ARgByAG8AcwB0AEEAcgByAGEAeQAsAG0AYQB4AEYAcgBvAHMAdABBAHIAcgBhAHkALABcAG4AIAAgACAAIABtAGkAbgBFAGwAZQB2AGEAdABpAG8AbgBBAHIAcgBhAHkALABtAGEAeABFAGwAZQB2AGEAdABpAG8AbgBBAHIAcgBhAHkALABcAG4AIAAgACAAIABtAGkAbgBQAEUAVABBAHIAcgBhAHkALABtAGEAeABQAEUAVABBAHIAcgBhAHkALABcAG4AIAAgACAAIABjAGwAaQBtAGEAdABlAFoAbwBuAGUAQQByAHIAYQB5ACwAXABuACAAIAAgACAATABFAFQAKABcAG4AIAAgACAAIAAgACAAIAAgAG0AYQBzAGsALABcAG4AIAAgACAAIAAgACAAIAAgACgAVgBBAEwAVQBFACgAbQBpAG4AVABlAG0AcABBAHIAcgBhAHkAKQA8AD0AYQB2AGcAVABlAG0AcAApACoAXABuACAAIAAgACAAIAAgACAAIAAoAFYAQQBMAFUARQAoAG0AYQB4AFQAZQBtAHAAQQByAHIAYQB5ACkAPgA9AGEAdgBnAFQAZQBtAHAAKQAqAFwAbgAgACAAIAAgACAAIAAgACAAKABWAEEATABVAEUAKABtAGkAbgBSAGEAaQBuAGYAYQBsAGwAQQByAHIAYQB5ACkAPAA9AGEAdgBnAFIAYQBpAG4AKQAqAFwAbgAgACAAIAAgACAAIAAgACAAKABWAEEATABVAEUAKABtAGEAeABSAGEAaQBuAGYAYQBsAGwAQQByAHIAYQB5ACkAPgA9AGEAdgBnAFIAYQBpAG4AKQAqAFwAbgAgACAAIAAgACAAIAAgACAAKABWAEEATABVAEUAKABtAGkAbgBGAHIAbwBzAHQAQQByAHIAYQB5ACkAPAA9AGYAcgBvAHMAdABEAGEAeQBzACkAKgBcAG4AIAAgACAAIAAgACAAIAAgACgAVgBBAEwAVQBFACgAbQBhAHgARgByAG8AcwB0AEEAcgByAGEAeQApAD4APQBmAHIAbwBzAHQARABhAHkAcwApACoAXABuACAAIAAgACAAIAAgACAAIAAoAFYAQQBMAFUARQAoAG0AaQBuAEUAbABlAHYAYQB0AGkAbwBuAEEAcgByAGEAeQApADwAPQBlAGwAZQB2ACkAKgBcAG4AIAAgACAAIAAgACAAIAAgACgAVgBBAEwAVQBFACgAbQBhAHgARQBsAGUAdgBhAHQAaQBvAG4AQQByAHIAYQB5ACkAPgA9AGUAbABlAHYAKQAqAFwAbgAgACAAIAAgACAAIAAgACAAKABWAEEATABVAEUAKABtAGkAbgBQAEUAVABBAHIAcgBhAHkAKQA8AD0AbQBhAHAAXwBwAGUAdAApACoAXABuACAAIAAgACAAIAAgACAAIAAoAFYAQQBMAFUARQAoAG0AYQB4AFAARQBUAEEAcgByAGEAeQApAD4APQBtAGEAcABfAHAAZQB0ACkALABcAG4AIAAgACAAIAAgACAAIAAgAFQAQQBLAEUAKABcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAARgBJAEwAVABFAFIAKABjAGwAaQBtAGEAdABlAFoAbwBuAGUAQQByAHIAYQB5ACwAbQBhAHMAawAsACAAXAAiAE4AbwAgAG0AYQB0AGMAaABcACIAKQAsAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIAAxAFwAbgAgACAAIAAgACAAIAAgACAAKQBcAG4AIAAgACAAIAApAFwAbgApADsAXABuAFwAbgBVAHQAaQBsAGkAdAB5AF8ATABvAG8AawB1AHAASQB0AGUAbQBGAHIAbwBtAE0AaQBuAE0AYQB4AFwAbgA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAATABvAG8AawB1AHAAVgBhAGwAdQBlACwAIABNAGkAbgBBAHIAcgBhAHkALAAgAE0AYQB4AEEAcgByAGEAeQAsACAASQB0AGUAbQBBAHIAcgBhAHkALABcAG4AIAAgACAAIABMAEUAVAAoAFwAbgAgACAAIAAgACAAIAAgACAAbQBhAHMAawAsAFwAbgAgACAAIAAgACAAIAAgACAAKABWAEEATABVAEUAKABNAGkAbgBBAHIAcgBhAHkAKQA8AD0ATABvAG8AawB1AHAAVgBhAGwAdQBlACkAKgBcAG4AIAAgACAAIAAgACAAIAAgACgAVgBBAEwAVQBFACgATQBhAHgAQQByAHIAYQB5ACkAPgA9AEwAbwBvAGsAdQBwAFYAYQBsAHUAZQApACwAXABuACAAIAAgACAAIAAgACAAIABGAEkATABUAEUAUgAoAEkAdABlAG0AQQByAHIAYQB5ACwAIABtAGEAcwBrACwAIABcACIATgBvACAAbQBhAHQAYwBoAFwAIgApAFwAbgAgACAAIAAgACkAXABuACkAOwBcAG4AXABuAFwAbgBVAHQAaQBsAGkAdAB5AF8AUwB1AG0AUQB1AGEAbgB0AGkAdAB5AEYAcgBvAG0AQwByAGkAdABlAHIAaQBhAFwAbgA9AEwAQQBNAEIARABBACgAXABuACAAIABDAHIAaQB0AGUAcgBpAGEAMQAsACAAQwByAGkAdABlAHIAaQBhADEAVAB5AHAAZQBBAHIAcgBhAHkALAAgAFEAdQBhAG4AdABpAHQAeQAsACAAWwBNAHUAbAB0AGkAcABsAGkAZQByAF0ALAAgAFsAQwByAGkAdABlAHIAaQBhADIAXQAsAFsAQwByAGkAdABlAHIAaQBhADIAQQByAHIAYQB5AF0ALABcAG4AIAAgAEwARQBUACgAXABuACAAIAAgACAAbQB1AGwAdABpAHAAbABpAGUAcgAsACAASQBGACgASQBTAE8ATQBJAFQAVABFAEQAKABNAHUAbAB0AGkAcABsAGkAZQByACkALAAxACwATQB1AGwAdABpAHAAbABpAGUAcgApACwAXABuACAAIAAgACAAcQB1AGEAbgB0AGkAdAB5ACwAIABRAHUAYQBuAHQAaQB0AHkAKgBNAHUAbAB0AGkAcABsAGkAZQByACwAXABuACAAIAAgACAAYwByAGkAdABlAHIAaQBhADEALAAtAC0AKABDAHIAaQB0AGUAcgBpAGEAMQBUAHkAcABlAEEAcgByAGEAeQA9AEMAcgBpAHQAZQByAGkAYQAxACkALABcAG4AIAAgACAAIABjAHIAaQB0AGUAcgBpAGEAMgAsAEkARgAoAEkAUwBPAE0ASQBUAFQARQBEACgAQwByAGkAdABlAHIAaQBhADIAKQAsADEALAAtAC0AKABDAHIAaQB0AGUAcgBpAGEAMgBBAHIAcgBhAHkAPQBDAHIAaQB0AGUAcgBpAGEAMgApACkALABcAG4AIAAgACAAIABTAFUATQBQAFIATwBEAFUAQwBUACgAYwByAGkAdABlAHIAaQBhADEAKgBjAHIAaQB0AGUAcgBpAGEAMgAqAHEAdQBhAG4AdABpAHQAeQApAFwAbgAgACAAKQBcAG4AKQA7AFwAbgBcAG4AZwBlAHQATwB2AGUAcgBsAGEAcABwAGkAbgBnAFIAZQBwAG8AcgB0AGkAbgBnAEMAeQBjAGwAZQBzAFwAbgA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAAUAByAG8AZAB1AGMAdABpAG8AbgBDAHkAYwBsAGUAUwB0AGEAcgB0ACwAUAByAG8AZAB1AGMAdABpAG8AbgBDAHkAYwBsAGUARQBuAGQALABSAGUAcABvAHIAdABpAG4AZwBDAHkAYwBsAGUAUwB0AGEAcgB0ACwAXABuACAAIAAgACAATABFAFQAKABcAG4AIAAgACAAIAAgACAAIAAgAFMALABQAHIAbwBkAHUAYwB0AGkAbwBuAEMAeQBjAGwAZQBTAHQAYQByAHQALABcAG4AIAAgACAAIAAgACAAIAAgAEUALABQAHIAbwBkAHUAYwB0AGkAbwBuAEMAeQBjAGwAZQBFAG4AZAAsAFwAbgAgACAAIAAgACAAIAAgACAAbQAsAE0ATwBOAFQASAAoAFIAZQBwAG8AcgB0AGkAbgBnAEMAeQBjAGwAZQBTAHQAYQByAHQAKQAsAFwAbgAgACAAIAAgACAAIAAgACAAZAAsAEQAQQBZACgAUgBlAHAAbwByAHQAaQBuAGcAQwB5AGMAbABlAFMAdABhAHIAdAApACwAXABuACAAIAAgACAAIAAgACAAIABQAGUAcgBpAG8AZABFAG4AZAAsAEwAQQBNAEIARABBACgAcwB0ACwARQBEAEEAVABFACgAcwB0ACwAMQAyACkALQAxACkALABcAG4AIAAgACAAIAAgACAAIAAgAEEALABTAC0AMwA2ADUALABcAG4AIAAgACAAIAAgACAAIAAgAHkAYQAsAFkARQBBAFIAKABBACkALABcAG4AIAAgACAAIAAgACAAIAAgAHkAYgAsAFkARQBBAFIAKABFACkALABcAG4AIAAgACAAIAAgACAAIAAgAGYAaQByAHMAdABZAGUAYQByACwAeQBhACsAKABQAGUAcgBpAG8AZABFAG4AZAAoAEQAQQBUAEUAKAB5AGEALABtACwAZAApACkAPAAgAFMAKQAsAFwAbgAgACAAIAAgACAAIAAgACAAbABhAHMAdABZAGUAYQByACwAeQBiAC0AKABEAEEAVABFACgAeQBiACwAbQAsAGQAKQA+ACAARQApACwAXABuACAAIAAgACAAIAAgACAAIABNAEEAWAAoADAALABsAGEAcwB0AFkAZQBhAHIALQBmAGkAcgBzAHQAWQBlAGEAcgArADEAKQBcAG4AIAAgACAAIAApAFwAbgApADsAXABuAFwAbgBnAGUAdABPAHYAZQByAGwAYQBwAHAAaQBuAGcAUgBlAHAAbwByAHQAaQBuAGcAUABlAHIAaQBvAGQAcwBcAG4APQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAFAAcgBvAGQAdQBjAHQAaQBvAG4AQwB5AGMAbABlAFMAdABhAHIAdAAsAFAAcgBvAGQAdQBjAHQAaQBvAG4AQwB5AGMAbABlAEUAbgBkACwAUgBlAHAAbwByAHQAaQBuAGcAQwB5AGMAbABlAFMAdABhAHIAdAAsAFwAbgAgACAAIAAgAEwARQBUACgAXABuACAAIAAgACAAIAAgACAAIABTACwAUAByAG8AZAB1AGMAdABpAG8AbgBDAHkAYwBsAGUAUwB0AGEAcgB0ACwAXABuACAAIAAgACAAIAAgACAAIABFACwAUAByAG8AZAB1AGMAdABpAG8AbgBDAHkAYwBsAGUARQBuAGQALABcAG4AIAAgACAAIAAgACAAIAAgAG0ALABNAE8ATgBUAEgAKABSAGUAcABvAHIAdABpAG4AZwBDAHkAYwBsAGUAUwB0AGEAcgB0ACkALABcAG4AIAAgACAAIAAgACAAIAAgAGQALABEAEEAWQAoAFIAZQBwAG8AcgB0AGkAbgBnAEMAeQBjAGwAZQBTAHQAYQByAHQAKQAsACAALwAqAGgAZQBsAHAAZQByADoAIABlAG4AZAAgAGQAYQB0AGUAIABmAG8AcgAgAGEAIAByAGUAcABvAHIAdABpAG4AZwAgAHAAZQByAGkAbwBkACAAcwB0AGEAcgB0AGkAbgBnACAAYQB0ACAAYQAgAGcAaQB2AGUAbgAgAGQAYQB0AGUAKgAvAFwAbgAgACAAIAAgACAAIAAgACAAUABlAHIAaQBvAGQARQBuAGQALABMAEEATQBCAEQAQQAoAHMAdAAsAEUARABBAFQARQAoAHMAdAAsADEAMgApAC0AMQApACwAIAAvACoAbwBuAGwAeQAgAG4AZQBlAGQAIAB0AG8AIABsAG8AbwBrACAAYgBhAGMAawAgADMANgA1ACAAZABhAHkAcwAoAG0AYQB4ACAAbwB2AGUAcgBsAGEAcAAgAHcAaQBuAGQAbwB3ACkAKgAvAFwAbgAgACAAIAAgACAAIAAgACAAQQAsAFMALQAzADYANQAsAFwAbgAgACAAIAAgACAAIAAgACAAeQBhACwAWQBFAEEAUgAoAEEAKQAsAFwAbgAgACAAIAAgACAAIAAgACAAeQBiACwAWQBFAEEAUgAoAEUAKQAsACAALwAqAGkAZgAgAHQAaABlACAAYQBuAGMAaABvAHIAIABmAG8AcgAgAHkAYQAgAGUAbgBkAHMAIABiAGUAZgBvAHIAZQAgAFMALABpAHQAIABjAGEAbgAnAHQAIABvAHYAZQByAGwAYQBwADsAIABtAG8AdgBlACAAdABvACAAbgBlAHgAdAAgAHkAZQBhAHIAKgAvAFwAbgAgACAAIAAgACAAIAAgACAAZgBpAHIAcwB0AFkAZQBhAHIALAB5AGEAKwAoAFAAZQByAGkAbwBkAEUAbgBkACgARABBAFQARQAoAHkAYQAsAG0ALABkACkAKQA8AFMAKQAsACAALwAqAGkAZgAgAHQAaABlACAAYQBuAGMAaABvAHIAIABmAG8AcgAgAHkAYgAgAHMAdABhAHIAdABzACAAYQBmAHQAZQByACAARQAsAGkAdAAgAGMAYQBuACcAdAAgAG8AdgBlAHIAbABhAHAAOwAgAG0AbwB2AGUAIAB0AG8AIABwAHIAZQB2AGkAbwB1AHMAIAB5AGUAYQByACoALwBcAG4AIAAgACAAIAAgACAAIAAgAGwAYQBzAHQAWQBlAGEAcgAsAHkAYgAtACgARABBAFQARQAoAHkAYgAsAG0ALABkACkAPgBFACkALABcAG4AIAAgACAAIAAgACAAIAAgAG4ALABNAEEAWAAoADAALABsAGEAcwB0AFkAZQBhAHIALQBmAGkAcgBzAHQAWQBlAGEAcgArADEAKQAsAFwAbgAgACAAIAAgACAAIAAgACAAeQByAHMALABTAEUAUQBVAEUATgBDAEUAKABuACwAMQAsAGYAaQByAHMAdABZAGUAYQByACwAMQApACwAXABuACAAIAAgACAAIAAgACAAIABzAHQAYQByAHQAcwAsAEQAQQBUAEUAKAB5AHIAcwAsAG0ALABkACkALABcAG4AIAAgACAAIAAgACAAIAAgAGUAbgBkAHMALABNAEEAUAAoAHMAdABhAHIAdABzACwAUABlAHIAaQBvAGQARQBuAGQAKQAsAFwAbgAgACAAIAAgACAAIAAgACAAdABhAGcALABJAEYAKABzAHQAYQByAHQAcwA9AFIAZQBwAG8AcgB0AGkAbgBnAEMAeQBjAGwAZQBTAHQAYQByAHQALABcACIAIAAoAFQAaABpAHMAIAByAGUAcABvAHIAdABpAG4AZwAgAGMAeQBjAGwAZQApAFwAIgAsAFwAIgBcACIAKQAsAFwAbgAgACAAIAAgACAAIAAgACAAcwB0AGEAcgB0AHMAVABlAHgAdAAsAFQARQBYAFQAKABzAHQAYQByAHQAcwAsAFwAIgBkAGQAIABtAG0AbQAgAHkAeQB5AHkAXAAiACkALABcAG4AIAAgACAAIAAgACAAIAAgAGUAbgBkAHMAVABlAHgAdAAsAFQARQBYAFQAKABlAG4AZABzACwAXAAiAGQAZAAgAG0AbQBtACAAeQB5AHkAeQBcACIAKQAsAFwAbgAgACAAIAAgACAAIAAgACAAcgBvAHcAcwAsAEkARgAoAG4APQAwACwAXAAiAFwAIgAsAEgAUwBUAEEAQwBLACgAcwB0AGEAcgB0AHMAVABlAHgAdAAgACYAIABcACIAIAB0AG8AIABcACIAIAAmACAAZQBuAGQAcwBUAGUAeAB0ACAAJgAgAHQAYQBnACkAKQAsAFwAbgAgACAAIAAgACAAIAAgACAAcgBvAHcAcwBcAG4AIAAgACAAIAApAFwAbgApADsAXABuAFwAbgBcAG4AVQB0AGkAbABpAHQAeQBfAEQAaQBzAHAAbABhAHkARgB1AG4AYwB0AGkAbwBuAE4AYQBtAGUAXABuAD0ATABBAE0AQgBEAEEAKABGAHUAbgBjAHQAaQBvAG4ALAAgAFQARQBYAFQAQgBFAEYATwBSAEUAKABGAE8AUgBNAFUATABBAFQARQBYAFQAKABGAHUAbgBjAHQAaQBvAG4AKQAsACAAXAAiACgAXAAiACkAKQA7AFwAbgBcAG4AVQB0AGkAbABpAHQAeQBfAEwAbwBvAGsAdQBwAE4AMgBPAEUARgBGAHIAbwBtAFAAcgBvAGQASQByAHIAaQBnAGEAdABpAG8AbgBSAGEAaQBuAGYAYQBsAGwAXABuAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABQAHIAbwBkAHUAYwB0AGkAbwBuAFMAeQBzAHQAZQBtACwAIABJAHIAcgBpAGcAYQB0AGkAbwBuAE0AZQB0AGgAbwBkACwAIABSAGEAaQBuAGYAYQBsAGwAWgBvAG4AZQAsAFwAbgAgACAAIAAgAFAAcgBvAGQAdQBjAHQAaQBvAG4AUwB5AHMAdABlAG0AQQByAHIAYQB5ACwAIABJAHIAcgBpAGcAYQB0AGkAbwBuAE0AZQB0AGgAbwBkAEEAcgByAGEAeQAsACAAUgBhAGkAbgBmAGEAbABsAFoAbwBuAGUAQQByAHIAYQB5ACwAUgBlAHQAdQByAG4AQQByAHIAYQB5ACwAXABuACAAIAAgACAATABFAFQAKABcAG4AIAAgACAAIAAgACAAIAAgAEkAcgByAGkAZwBhAHQAaQBvAG4ATQBlAHQAaABvAGQALAAgAEkARgAoAEkAcgByAGkAZwBhAHQAaQBvAG4ATQBlAHQAaABvAGQAPQBcACIATgBvAHQAIABpAHIAcgBpAGcAYQB0AGUAZABcACIALAAgAFwAIgBOAG8AdAAgAGkAcgByAGkAZwBhAHQAZQBkAFwAIgAsACAAXAAiAEEAbgB5AFwAIgApACwAXABuACAAIAAgACAAIAAgACAAIABSAGEAaQBuAGYAYQBsAGwAWgBvAG4AZQAsACAASQBGACgASQByAHIAaQBnAGEAdABpAG8AbgBNAGUAdABoAG8AZAAgAD0AIABcACIATgBvAHQAIABpAHIAcgBpAGcAYQB0AGUAZABcACIALAAgAFIAYQBpAG4AZgBhAGwAbABaAG8AbgBlACwAIABcACIAQQBuAHkAXAAiACkALABcAG4AIAAgACAAIAAgACAAIAAgAFgATABPAE8ASwBVAFAAKAAxACwAIABcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAKABQAHIAbwBkAHUAYwB0AGkAbwBuAFMAeQBzAHQAZQBtAEEAcgByAGEAeQA9AFAAcgBvAGQAdQBjAHQAaQBvAG4AUwB5AHMAdABlAG0AKQAqAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIAAoAEkAcgByAGkAZwBhAHQAaQBvAG4ATQBlAHQAaABvAGQAQQByAHIAYQB5AD0ASQByAHIAaQBnAGEAdABpAG8AbgBNAGUAdABoAG8AZAApACoAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgACgAUgBhAGkAbgBmAGEAbABsAFoAbwBuAGUAQQByAHIAYQB5AD0AUgBhAGkAbgBmAGEAbABsAFoAbwBuAGUAKQAsACAAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgAFIAZQB0AHUAcgBuAEEAcgByAGEAeQApAFwAbgAgACAAIAAgACkAXABuACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAEMAcgBvAHAAcABpAG4AZwBfAEcAZQB0AEYAcgBhAGMAVwBFAFQAXABuAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABMAGUAYQBjAGgAaQBuAGcAWgBvAG4AZQAsAFwAbgAgACAAIAAgAFAAcgBvAGQAdQBjAHQAaQBvAG4AUwB5AHMAdABlAG0ALABcAG4AIAAgACAAIABMAGUAYQBjAGgAaQBuAGcAWgBvAG4AZQBMAG8AbwBrAHUAcAAsAFwAbgAgACAAIAAgAEwAZQBhAGMAaABpAG4AZwBaAG8AbgBlAEYAcgBhAGMAVwBFAFQATABvAG8AawB1AHAALABcAG4AIAAgACAAIABQAHIAbwBkAHUAYwB0AGkAbwBuAFMAeQBzAHQAZQBtAEwAbwBvAGsAdQBwACwAXABuACAAIAAgACAAUAByAG8AZAB1AGMAdABpAG8AbgBTAHkAcwB0AGUAbQBGAHIAYQBjAFcARQBUAEwAbwBvAGsAdQBwACwAXABuACAAIAAgACAATABFAFQAKABcAG4AIAAgACAAIAAgACAAIAAgAEwAZQBhAGMAaABpAG4AZwBaAG8AbgBlAEYAcgBhAGMAVwBFAFQALAAgAFwAbgAgACAAIAAgACAAIAAgACAAQwBvAG0AbQBvAG4AXwBJAG4AcAB1AHQARgB1AG4AYwB0AGkAbwBuAHMALgBVAHQAaQBsAGkAdAB5AF8ATABvAG8AawB1AHAAVgBhAGwAdQBlAEkAbgBUAGEAYgBsAGUATgB1AG0AYgBlAHIAKABcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAATABlAGEAYwBoAGkAbgBnAFoAbwBuAGUALABMAGUAYQBjAGgAaQBuAGcAWgBvAG4AZQBMAG8AbwBrAHUAcAAsAEwAZQBhAGMAaABpAG4AZwBaAG8AbgBlAEYAcgBhAGMAVwBFAFQATABvAG8AawB1AHAAXABuACAAIAAgACAAIAAgACAAIAApACwAXABuACAAIAAgACAAIAAgACAAIABQAHIAbwBkAHUAYwB0AGkAbwBuAFMAeQBzAHQAZQBtAEYAcgBhAGMAVwBFAFQALAAgAFwAbgAgACAAIAAgACAAIAAgACAAQwBvAG0AbQBvAG4AXwBJAG4AcAB1AHQARgB1AG4AYwB0AGkAbwBuAHMALgBVAHQAaQBsAGkAdAB5AF8ATABvAG8AawB1AHAAVgBhAGwAdQBlAEkAbgBUAGEAYgBsAGUATgB1AG0AYgBlAHIAKABcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAUAByAG8AZAB1AGMAdABpAG8AbgBTAHkAcwB0AGUAbQAsAFAAcgBvAGQAdQBjAHQAaQBvAG4AUwB5AHMAdABlAG0ATABvAG8AawB1AHAALABQAHIAbwBkAHUAYwB0AGkAbwBuAFMAeQBzAHQAZQBtAEYAcgBhAGMAVwBFAFQATABvAG8AawB1AHAAXABuACAAIAAgACAAIAAgACAAIAApACwAXABuACAAIAAgACAAIAAgACAAIABJAEYAKABMAGUAYQBjAGgAaQBuAGcAWgBvAG4AZQBGAHIAYQBjAFcARQBUACAAKwAgAFAAcgBvAGQAdQBjAHQAaQBvAG4AUwB5AHMAdABlAG0ARgByAGEAYwBXAEUAVAA+ADAALAAgADEALAAgADAAKQBcAG4AIAAgACAAIAApACkAOwBcAG4AXABuAFwAbgBVAHQAaQBsAGkAdAB5AF8AQwBvAG4AdgBlAHIAdABTAHQAYQB0AGUAQwBvAG0AbQBvAG4ATgBhAG0AZQBUAG8AQQBiAGIAcgBlAHYAaQBhAHQAaQBvAG4AXABuAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABTAHQAYQB0AGUAQwBvAG0AbQBvAG4ATgBhAG0AZQAsAFwAbgAgACAAIAAgAFMAdABhAHQAZQBDAG8AbQBtAG8AbgBOAGEAbQBlAEEAcgByAGEAeQAsACAAUwB0AGEAdABlAEEAYgBiAHIAZQB2AGkAYQB0AGkAbwBuAEEAcgByAGEAeQAsAFwAbgAgACAAIAAgAFgATABPAE8ASwBVAFAAKABTAHQAYQB0AGUAQwBvAG0AbQBvAG4ATgBhAG0AZQAsACAAUwB0AGEAdABlAEMAbwBtAG0AbwBuAE4AYQBtAGUAQQByAHIAYQB5ACwAIABTAHQAYQB0AGUAQQBiAGIAcgBlAHYAaQBhAHQAaQBvAG4AQQByAHIAYQB5ACwAIABcACIAXAAiACkAXABuACkAOwBcAG4AXABuAFUAdABpAGwAaQB0AHkAXwBTAG8AdQByAGMAZQBIAHkAcABlAHIAbABpAG4AawBcAG4APQBMAEEATQBCAEQAQQAoAFQAYQByAGcAZQB0AEMAZQBsAGwALABcAG4AIAAgAEwARQBUACgAXABuACAAIAAgACAAcwBoACwAIABUAEUAWABUAEEARgBUAEUAUgAoAEMARQBMAEwAKABcACIAZgBpAGwAZQBuAGEAbQBlAFwAIgAsACAAVABhAHIAZwBlAHQAQwBlAGwAbAApACwAIABcACIAXQBcACIAKQAsAFwAbgAgACAAIAAgAGEAZABkAHIALAAgAEMARQBMAEwAKABcACIAYQBkAGQAcgBlAHMAcwBcACIALAAgAFQAYQByAGcAZQB0AEMAZQBsAGwAKQAsAFwAbgAgACAAIAAgAFwAIgAjACcAXAAiACAAJgAgAHMAaAAgACYAIABcACIAJwAhAFwAIgAgACYAIABhAGQAZAByAFwAbgAgACAAKQBcAG4AKQA7AFwAbgBcAG4AVQB0AGkAbABpAHQAeQBfAFMAbwB1AHIAYwBlAEgAeQBwAGUAcgBsAGkAbgBrAEQAaQBmAGYAZQByAGUAbgB0AFMAaABlAGUAdABcAG4APQBMAEEATQBCAEQAQQAoAFQAYQByAGcAZQB0AEMAZQBsAGwALABcAG4AIAAgAEwARQBUACgAXABuACAAIAAgACAAcwBoACwAIABUAEUAWABUAEEARgBUAEUAUgAoAEMARQBMAEwAKABcACIAZgBpAGwAZQBuAGEAbQBlAFwAIgAsACAAVABhAHIAZwBlAHQAQwBlAGwAbAApACwAIABcACIAXQBcACIAKQAsAFwAbgAgACAAIAAgAGEAZABkAHIALAAgAEMARQBMAEwAKABcACIAYQBkAGQAcgBlAHMAcwBcACIALAAgAFQAYQByAGcAZQB0AEMAZQBsAGwAKQAsAFwAbgAgACAAIAAgAFwAIgAjAFwAIgAgACYAIABhAGQAZAByAFwAbgAgACAAKQBcAG4AKQA7AFwAbgBcAG4AVQB0AGkAbABpAHQAeQBfAEQAaQBzAHAAbABhAHkAQQByAGcAdQBtAGUAbgB0AHMAXwAxAF8AMgBcAG4APQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAEEAcgBnAHUAbQBlAG4AdABzAEEAcgByAGEAeQAsAFwAbgAgACAAIAAgAEMASABPAE8AUwBFAEMATwBMAFMAKABBAHIAZwB1AG0AZQBuAHQAcwBBAHIAcgBhAHkALAAgADEALAAgADIAKQBcAG4AKQA7AFwAbgBcAG4AVQB0AGkAbABpAHQAeQBfAEQAaQBzAHAAbABhAHkAQQByAGcAdQBtAGUAbgB0AHMAXwAzAF8ANABcAG4APQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAEEAcgBnAHUAbQBlAG4AdABzAEEAcgByAGEAeQAsAFwAbgAgACAAIAAgAEMASABPAE8AUwBFAEMATwBMAFMAKABBAHIAZwB1AG0AZQBuAHQAcwBBAHIAcgBhAHkALAAgADMALAAgADQAKQBcAG4AKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBHAGUAdABNAEMARgBUAGUAbQBwAGUAcgBhAHQAdQByAGUAWgBvAG4AZQBcAG4APQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAFQAZQBtAHAAZQByAGEAdAB1AHIAZQAsACAATQBNAFMALAAgAFQAZQBtAHAAZQByAGEAdAB1AHIAZQBBAHIAcgBhAHkALAAgAE0ATQBTAEEAcgByAGEAeQAsACAAUgBlAHQAdQByAG4AQQByAHIAYQB5ACwAXABuACAAIAAgACAAWABMAE8ATwBLAFUAUAAoAFwAbgAgACAAIAAgACAAIAAgACAATQBFAEQASQBBAE4AKABcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAVABlAG0AcABlAHIAYQB0AHUAcgBlACwAIABcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAATQBJAE4AKABUAGUAbQBwAGUAcgBhAHQAdQByAGUAQQByAHIAYQB5ACkALAAgAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIABNAEEAWAAoAFQAZQBtAHAAZQByAGEAdAB1AHIAZQBBAHIAcgBhAHkAKQBcAG4AIAAgACAAIAAgACAAIAAgACkALABcAG4AIAAgACAAIAAgACAAIAAgAFQAZQBtAHAAZQByAGEAdAB1AHIAZQBBAHIAcgBhAHkALABcAG4AIAAgACAAIAAgACAAIAAgAFgATABPAE8ASwBVAFAAKABNAE0AUwAsACAATQBNAFMAQQByAHIAYQB5ACwAIABSAGUAdAB1AHIAbgBBAHIAcgBhAHkAKQBcAG4AIAAgACAAIAApAFwAbgApADsAXABuAFwAbgBcAG4AVQB0AGkAbABpAHQAeQBfAFIAZQBzAHUAbAB0AHMASQB0AGUAbQBGAHIAbwBtAEUAcQB1AGEAdABpAG8AbgBUAGkAdABsAGUAQQBuAGQAUwBvAHUAcgBjAGUAXABuAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABUAGkAdABsAGUAQwBlAGwAbAAsACAAUwBvAHUAcgBjAGUAQwBlAGwAbAAsAFwAbgAgACAAIAAgAFMAVQBCAFMAVABJAFQAVQBUAEUAKABMAEUARgBUACgAUwBvAHUAcgBjAGUAQwBlAGwAbAAsACAARgBJAE4ARAAoAFwAIgAsAFwAIgAsACAAUwBvAHUAcgBjAGUAQwBlAGwAbAApACAALQAxACkALAAgAFwAIgBWAEUARQBSAEcAIAAyADAAMgA2ADoAIABcACIALAAgAFwAIgBcACIAKQAgACYAIABcACIAIABcACIAIAAmACAAVABpAHQAbABlAEMAZQBsAGwAXABuACkAOwAiAH0ALAB7ACIAcABhAHQAaAAiADoAIgAvAHAAcgBvAGoAZQBjAHQAcwAvAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAiACwAIgB0AGUAeAB0ACIAOgAiAC8AKgBcAG4APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQBcAG4APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQBcAG4AUwBvAHUAcgBjAGUAIABkAGEAdABhACAAdABoAGEAdAAgAGkAcwAgAGMAbwBtAG0AbwBuACAAYQBjAHIAbwBzAHMAIABhAGwAbAAgAGUAbgB0AGUAcgBwAHIAaQBzAGUAIAB0AHkAcABlAHMAXABuAEUAeABjAGUAbAAgAG0AbwBkAHUAbABlACAAbgBhAG0AZQA6ACAAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAFwAbgA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AFwAbgA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AFwAbgAqAC8AXABuAFwAbgAvACoAXABuAD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQBcAG4APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AFwAbgBTAG8AdQByAGMAZQA6ACAATgBhAHQAaQBvAG4AYQBsACAASQBuAHYAZQBuAHQAbwByAHkAIABSAGUAcABvAHIAdAAgADIAMAAyADMAIABWAG8AbAB1AG0AZQAgADEAXABuAE4ASQBSAF8AMgAwADIAMwBfAFYAbwBsADEAXABuAD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQBcAG4APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AFwAbgAqAC8AXABuAFwAbgAvACoAIABcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGUAbgBzAGkAdAB5AE8AZgBNAGUAdABoAGEAbgBlAFwAbgBwACAAPQAgAGQAZQBuAHMAaQB0AHkAIABvAGYAIABtAGUAdABoAGEAbgBlACAAKAAwAC4ANgA3ADgANAAgAGsAZwAvAG0AMwApAFwAbgBUAGEAawBlAG4AIABmAHIAbwBtACAAdABoAGUAIABOAGEAdABpAG8AbgBhAGwAIABHAHIAZQBlAG4AaABvAHUAcwBlACAAYQBuAGQAIABFAG4AZQByAGcAeQAgAFIAZQBwAG8AcgB0AGkAbgBnACAAXABuACgATQBlAGEAcwB1AHIAZQBtAGUAbgB0ACkAIABEAGUAdABlAHIAbQBpAG4AYQB0AGkAbwBuACAAMgAwADAAOABcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgAqAC8AXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGUAbgBzAGkAdAB5AE8AZgBNAGUAdABoAGEAbgBlAF8AVABpAHQAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBwACAAPQAgAGQAZQBuAHMAaQB0AHkAIABvAGYAIABtAGUAdABoAGEAbgBlAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGUAbgBzAGkAdAB5AE8AZgBNAGUAdABoAGEAbgBlAF8AVQBuAGkAdABcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAawBnAC8AbQAzAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGUAbgBzAGkAdAB5AE8AZgBNAGUAdABoAGEAbgBlAF8AUwBvAHUAcgBjAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAE4AYQB0AGkAbwBuAGEAbAAgAEkAbgB2AGUAbgB0AG8AcgB5ACAAUgBlAHAAbwByAHQAIAAyADAAMgAzACAAVgBvAGwAdQBtAGUAIAAxADoAIABFAHEAdQBhAHQAaQBvAG4AcwAgADMALgBCAC4AMQBhAF8AMgAsACAAMwAuAEIALgAxAGMAXwAyACwAIAAzAC4AQgAuADMAXwAxACwAIAAzAC4AQgAuADQAZwBfADIAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEQAZQBuAHMAaQB0AHkATwBmAE0AZQB0AGgAYQBuAGUAXwBEAGEAdABhAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoADAALgA2ADcAOAA0ACkAOwBcAG4AXABuAC8AKgAgAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEMAbwBuAHYAZQByAHQATgAyAG8ARQBsAGUAbQBlAG4AdABhAGwAVABvAE0AbwBsAGUAYwB1AGwAYQByAEMAZwBcAG4AQwBnACAAPQAgADQANAAvADIAOAAgAGYAYQBjAHQAbwByACAAdABvACAAYwBvAG4AdgBlAHIAdAAgAGUAbABlAG0AZQBuAHQAYQBsACAAbQBhAHMAcwAgAG8AZgAgAE4AMgBPACAAdABvACAAbQBvAGwAZQBjAHUAbABhAHIAIABtAGEAcwBzAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuACoALwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEMAbwBuAHYAZQByAHQATgAyAG8ARQBsAGUAbQBlAG4AdABhAGwAVABvAE0AbwBsAGUAYwB1AGwAYQByAEMAZwBfAFQAaQB0AGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIARgBhAGMAdABvAHIAIAB0AG8AIABjAG8AbgB2AGUAcgB0ACAAZQBsAGUAbQBlAG4AdABhAGwAIABtAGEAcwBzACAAbwBmACAATgAyAE8AIAB0AG8AIABtAG8AbABlAGMAdQBsAGEAcgAgAG0AYQBzAHMAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEMAbwBuAHYAZQByAHQATgAyAG8ARQBsAGUAbQBlAG4AdABhAGwAVABvAE0AbwBsAGUAYwB1AGwAYQByAEMAZwBfAFYAYQByAGkAYQBiAGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAQwBnAE4AMgBPAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBDAG8AbgB2AGUAcgB0AE4AMgBvAEUAbABlAG0AZQBuAHQAYQBsAFQAbwBNAG8AbABlAGMAdQBsAGEAcgBDAGcAXwBVAG4AaQB0AFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBmAGEAYwB0AG8AcgBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQwBvAG4AdgBlAHIAdABOADIAbwBFAGwAZQBtAGUAbgB0AGEAbABUAG8ATQBvAGwAZQBjAHUAbABhAHIAQwBnAF8AUwBvAHUAcgBjAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAE4AYQB0AGkAbwBuAGEAbAAgAEkAbgB2AGUAbgB0AG8AcgB5ACAAUgBlAHAAbwByAHQAIAAyADAAMgAzACAAVgBvAGwAdQBtAGUAIAAxAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBDAG8AbgB2AGUAcgB0AE4AMgBvAEUAbABlAG0AZQBuAHQAYQBsAFQAbwBNAG8AbABlAGMAdQBsAGEAcgBDAGcAXwBEAGEAdABhAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoADQANAAvADIAOAApADsAXABuAFwAbgAvACoAIABcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBDAG8AbgB2AGUAcgB0AEcAYQBzAEUAbABlAG0AZQBuAHQAYQBsAFQAbwBNAG8AbABlAGMAdQBsAGEAcgBcAG4ARgBhAGMAdABvAHIAIAB0AG8AIABjAG8AbgB2AGUAcgB0ACAAZQBsAGUAbQBlAG4AdABhAGwAIABtAGEAcwBzACAAbwBmACAAZwBhAHMAIAB0AG8AIABtAG8AbABlAGMAdQBsAGEAcgAgAG0AYQBzAHMAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AKgAvAFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQwBvAG4AdgBlAHIAdABHAGEAcwBFAGwAZQBtAGUAbgB0AGEAbABUAG8ATQBvAGwAZQBjAHUAbABhAHIAXwBUAGkAdABsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAEYAYQBjAHQAbwByACAAdABvACAAYwBvAG4AdgBlAHIAdAAgAGUAbABlAG0AZQBuAHQAYQBsACAAbQBhAHMAcwAgAG8AZgAgAGcAYQBzACAAdABvACAAbQBvAGwAZQBjAHUAbABhAHIAIABtAGEAcwBzAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBDAG8AbgB2AGUAcgB0AEcAYQBzAEUAbABlAG0AZQBuAHQAYQBsAFQAbwBNAG8AbABlAGMAdQBsAGEAcgBfAFYAYQByAGkAYQBiAGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAQwBnAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBDAG8AbgB2AGUAcgB0AEcAYQBzAEUAbABlAG0AZQBuAHQAYQBsAFQAbwBNAG8AbABlAGMAdQBsAGEAcgBfAFUAbgBpAHQAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAGYAYQBjAHQAbwByAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBDAG8AbgB2AGUAcgB0AEcAYQBzAEUAbABlAG0AZQBuAHQAYQBsAFQAbwBNAG8AbABlAGMAdQBsAGEAcgBfAFMAbwB1AHIAYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBYAFgAWABYAFgAWABYAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBDAG8AbgB2AGUAcgB0AEcAYQBzAEUAbABlAG0AZQBuAHQAYQBsAFQAbwBNAG8AbABlAGMAdQBsAGEAcgBfAEQAYQB0AGEAXABuACAAIAA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAATQBBAEsARQBBAFIAUgBBAFkAKAA4ACwAIAA0ACwAIABcAG4AIAAgACAAIAAgACAATABBAE0AQgBEAEEAKAByACwAYwAsACAAXABuACAAIAAgACAAIAAgACAAIABJAE4ARABFAFgAKAB7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBHAGEAcwBcACIALAAgAFwAIgBDAG8AbgB2AGUAcgBzAGkAbwBuACAAZgBhAGMAdABvAHIAXAAiACwAIABcACIAQwBvAG4AdgBlAHIAcwBpAG8AbgAgAGYAYQBjAHQAbwByACAAMQBcACIALAAgAFwAIgBDAG8AbgB2AGUAcgBzAGkAbwBuACAAZgBhAGMAdABvAHIAIAAyAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBDAE8AMgBcACIALAAgAFwAIgA0ADQALwAxADIAXAAiACwAIAA0ADQALAAgADEAMgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBDAEgANABcACIALAAgAFwAIgAxADYALwAxADIAXAAiACwAIAAxADYALAAgADEAMgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBOADIATwBcACIALAAgAFwAIgA0ADQALwAyADgAXAAiACwAIAA0ADQALAAgADIAOAA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBOAG8AeABcACIALAAgAFwAIgA0ADYALwAxADQAXAAiACwAIAA0ADYALAAgADEANAA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBDAE8AXAAiACwAIABcACIAMgA4AC8AMQAyAFwAIgAsACAAMgA4ACwAIAAxADIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAQwBPADIAIABMAGkAbQBlAFwAIgAsACAAXAAiADQANAAvADEAMgBcACIALAAgADQANAAsACAAMQAyADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAE4ATQBWAE8AQwBcACIALAAgAFwAIgAxADQALwAxADIAXAAiACwAIAAxADQALAAgADEAMgBcAG4AIAAgACAAIAAgACAAIAAgAH0ALAAgAHIALAAgAGMAKQBcAG4AIAAgACAAIAAgACAAKQBcAG4AIAAgACAAIAApAFwAbgAgACAAKQA7AFwAbgBcAG4ALwAqACAAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARwBXAFAATgAyAE8AXABuAEcAbABvAGIAYQBsACAAdwBhAHIAbQBpAG4AZwAgAHAAbwB0AGUAbgB0AGkAYQBsACAAZgBvAHIAIABnAHIAZQBlAG4AaABvAHUAcwBlACAAZwBhAHMAZQBzAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuACoALwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEcAVwBQAF8AVABpAHQAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBHAGwAbwBiAGEAbAAgAHcAYQByAG0AaQBuAGcAIABwAG8AdABlAG4AdABpAGEAbAAgAGYAbwByACAAZwByAGUAZQBuAGgAbwB1AHMAZQAgAGcAYQBzAGUAcwBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARwBXAFAAXwBWAGEAcgBpAGEAYgBsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAEcAVwBQAE4AMgBPAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBHAFcAUABfAFUAbgBpAHQAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAGYAYQBjAHQAbwByAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBHAFcAUABfAFMAbwB1AHIAYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBYAFgAWABYAFgAWABYAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBHAFcAUABfAEQAYQB0AGEAXABuACAAIAA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAATQBBAEsARQBBAFIAUgBBAFkAKAA4ACwAIAAyACwAIABcAG4AIAAgACAAIAAgACAATABBAE0AQgBEAEEAKAByACwAYwAsACAAXABuACAAIAAgACAAIAAgACAAIABJAE4ARABFAFgAKAB7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBHAGEAcwBcACIALAAgAFwAIgBDAE8AMgAtAGUAIABmAGEAYwB0AG8AcgBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAQwBPADIAXAAiACwAIAAxADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEMASAA0AFwAIgAsACAAMgA4ADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAE4AMgBPAFwAIgAsACAAMgA2ADUAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAQwBGADQAXAAiACwAIAA2ADYAMwAwADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEMAMgBGADYAXAAiACwAIAAxADIAMgAwADAAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAUwBGADYAXAAiACwAIAAyADIAOAAwADAAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIATgBGADMAXAAiACwAIAAxADcAMgAwADAAXABuACAAIAAgACAAIAAgACAAIAB9ACwAIAByACwAIABjACkAXABuACAAIAAgACAAIAAgACkAXABuACAAIAAgACAAKQBcAG4AIAAgACkAOwBcAG4AXABuAFwAbgAvACoAIABcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBBAHUAcwB0AHIAYQBsAGkAYQBuAFMAdABhAHQAZQBzAFQAZQByAHIAaQB0AG8AcgBpAGUAcwBcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgAqAC8AXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBBAHUAcwB0AHIAYQBsAGkAYQBuAFMAdABhAHQAZQBzAFQAZQByAHIAaQB0AG8AcgBpAGUAcwBfAFQAaQB0AGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAQQB1AHMAdAByAGEAbABpAGEAbgAgAHMAdABhAHQAZQBzACAAYQBuAGQAIAB0AGUAcgByAGkAdABvAHIAaQBlAHMAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEEAdQBzAHQAcgBhAGwAaQBhAG4AUwB0AGEAdABlAHMAVABlAHIAcgBpAHQAbwByAGkAZQBzAF8AVgBhAHIAaQBhAGIAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQQB1AHMAdAByAGEAbABpAGEAbgBTAHQAYQB0AGUAcwBUAGUAcgByAGkAdABvAHIAaQBlAHMAXwBVAG4AaQB0AFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQQB1AHMAdAByAGEAbABpAGEAbgBTAHQAYQB0AGUAcwBUAGUAcgByAGkAdABvAHIAaQBlAHMAXwBTAG8AdQByAGMAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEEAdQBzAHQAcgBhAGwAaQBhAG4AUwB0AGEAdABlAHMAVABlAHIAcgBpAHQAbwByAGkAZQBzAF8ARABhAHQAYQBcAG4AIAAgACAAPQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAE0AQQBLAEUAQQBSAFIAQQBZACgAOQAsACAAMwAsACAAXABuACAAIAAgACAAIAAgAEwAQQBNAEIARABBACgAcgAsAGMALAAgAFwAbgAgACAAIAAgACAAIAAgACAASQBOAEQARQBYACgAewBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAUwB0AGEAdABlAC8AVABlAHIAcgBpAHQAbwByAHkAXAAiACwAIABcACIAQwBvAG0AbQBvAG4AIABOAGEAbQBlAFwAIgAsACAAXAAiAEEAYgBiAHIAZQB2AGkAYQB0AGkAbwBuAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBOAGUAdwAgAFMAbwB1AHQAaAAgAFcAYQBsAGUAcwBcACIALAAgAFwAIgBOAGUAdwAgAFMAbwB1AHQAaAAgAFcAYQBsAGUAcwBcACIALAAgAFwAIgBOAFMAVwBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAQQB1AHMAdAByAGEAbABpAGEAbgAgAEMAYQBwAGkAdABhAGwAIABUAGUAcgByAGkAdABvAHIAeQBcACIALAAgAFwAIgBBAEMAVABcACIALAAgAFwAIgBBAEMAVABcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVgBpAGMAdABvAHIAaQBhAFwAIgAsACAAXAAiAFYAaQBjAHQAbwByAGkAYQBcACIALAAgAFwAIgBWAEkAQwBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAUQB1AGUAZQBuAHMAbABhAG4AZABcACIALAAgAFwAIgBRAHUAZQBlAG4AcwBsAGEAbgBkAFwAIgAsACAAXAAiAFEATABEAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBTAG8AdQB0AGgAIABBAHUAcwB0AHIAYQBsAGkAYQBcACIALAAgAFwAIgBTAG8AdQB0AGgAIABBAHUAcwB0AHIAYQBsAGkAYQBcACIALAAgAFwAIgBTAEEAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFcAZQBzAHQAZQByAG4AIABBAHUAcwB0AHIAYQBsAGkAYQBcACIALAAgAFwAIgBXAGUAcwB0AGUAcgBuACAAQQB1AHMAdAByAGEAbABpAGEAXAAiACwAIABcACIAVwBBAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBUAGEAcwBtAGEAbgBpAGEAXAAiACwAIABcACIAVABhAHMAbQBhAG4AaQBhAFwAIgAsACAAXAAiAFQAQQBTAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBOAG8AcgB0AGgAZQByAG4AIABUAGUAcgByAGkAdABvAHIAeQBcACIALAAgAFwAIgBOAG8AcgB0AGgAZQByAG4AIABUAGUAcgByAGkAdABvAHIAeQBcACIALAAgAFwAIgBOAFQAXAAiAFwAbgAgACAAIAAgACAAIAAgACAAfQAsACAAcgAsACAAYwApAFwAbgAgACAAIAAgACAAIAApAFwAbgAgACAAIAAgACkAXABuACAAIAApADsAXABuAFwAbgAvACoAIABcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBXAEEAUwBBADQAQQByAGUAYQBzAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuACoALwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFcAQQBTAEEANABBAHIAZQBhAHMAXwBUAGkAdABsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAEEAQgBTACAAUwB0AGEAdABpAHMAdABjAGEAbAAgAEEAcgBlAGEAcwAgAEwAZQB2AGUAbAAgADQAIAAtACAAVwBlAHMAdABlAHIAbgAgAEEAdQBzAHQAcgBhAGwAaQBhAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBXAEEAUwBBADQAQQByAGUAYQBzAF8AVgBhAHIAaQBhAGIAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AVwBBAFMAQQA0AEEAcgBlAGEAcwBfAFUAbgBpAHQAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBXAEEAUwBBADQAQQByAGUAYQBzAF8AUwBvAHUAcgBjAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAEEAdQBzAHQAcgBhAGwAaQBhAG4AIABCAHUAcgBlAGEAdQAgAG8AZgAgAFMAdABhAHQAaQBzAHQAaQBjAHMAIAAoAEEAQgBTACkAIAAtACAAUwB0AGEAdABpAHMAdABpAGMAYQBsACAAQQByAGUAYQBzACAATABlAHYAZQBsACAAMgAgAC0AIAAyADAAMgAxACAALQAgAFMAaABhAHAAZQBmAGkAbABlAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBXAEEAUwBBADQAQQByAGUAYQBzAF8ARABhAHQAYQBcAG4AIAAgACAAPQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAE0AQQBLAEUAQQBSAFIAQQBZACgAMQAxACwAIAAxACwAIABcAG4AIAAgACAAIAAgACAATABBAE0AQgBEAEEAKAByACwAYwAsACAAXABuACAAIAAgACAAIAAgACAAIABJAE4ARABFAFgAKAB7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBTAEEAIAA0ACAATgBhAG0AZQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAQgB1AG4AYgB1AHIAeQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIATQBhAG4AZAB1AHIAYQBoAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBQAGUAcgB0AGgAIAAtACAASQBuAG4AZQByAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBQAGUAcgB0AGgAIAAtACAATgBvAHIAdABoACAARQBhAHMAdABcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAUABlAHIAdABoACAALQAgAE4AbwByAHQAaAAgAFcAZQBzAHQAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFAAZQByAHQAaAAgAC0AIABTAG8AdQB0AGgAIABFAGEAcwB0AFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBQAGUAcgB0AGgAIAAtACAAUwBvAHUAdABoACAAVwBlAHMAdABcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVwBlAHMAdABlAHIAbgAgAEEAdQBzAHQAcgBhAGwAaQBhACAALQAgAFcAaABlAGEAdAAgAEIAZQBsAHQAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFcAZQBzAHQAZQByAG4AIABBAHUAcwB0AHIAYQBsAGkAYQAgAC0AIABPAHUAdABiAGEAYwBrACAAKABOAG8AcgB0AGgAKQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVwBlAHMAdABlAHIAbgAgAEEAdQBzAHQAcgBhAGwAaQBhACAALQAgAE8AdQB0AGIAYQBjAGsAIAAoAFMAbwB1AHQAaAApAFwAIgBcAG4AIAAgACAAIAAgACAAIAAgAH0ALAAgAHIALAAgAGMAKQBcAG4AIAAgACAAIAAgACAAKQBcAG4AIAAgACAAIAApAFwAbgAgACAAKQA7AFwAbgBcAG4ALwAqACAAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AVwBlAHQAQQBuAGQARAByAHkAWgBvAG4AZQBzAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuACoALwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFcAZQB0AEEAbgBkAEQAcgB5AFoAbwBuAGUAcwBfAFQAaQB0AGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAVgBFAEUAUgBHACAAQQB1AHMAdAByAGEAbABpAGEAbgAgAHcAZQB0ACAAYQBuAGQAIABkAHIAeQAgAHoAbwBuAGUAcwBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AVwBlAHQAQQBuAGQARAByAHkAWgBvAG4AZQBzAF8AVgBhAHIAaQBhAGIAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AVwBlAHQAQQBuAGQARAByAHkAWgBvAG4AZQBzAF8AVQBuAGkAdABcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFcAZQB0AEEAbgBkAEQAcgB5AFoAbwBuAGUAcwBfAFMAbwB1AHIAYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBWAEUARQBSAEcAIAAyADAAMgA2ADoAIABUAGEAYgBsAGUAIAAxAC4AMgA6ACAAVAByAGEAbgBzAGwAYQB0AGkAbgBnACAAYwBsAGkAbQBhAHQAZQAgAHoAbwBuAGUAcwAgAHQAbwAgAHcAZQB0ACAAYQBuAGQAIABkAHIAeQAgAHoAbwBuAGUAcwBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AVwBlAHQAQQBuAGQARAByAHkAWgBvAG4AZQBzAF8AVgBhAHIAaQBhAHQAaQBvAG4AXABuACAAIAAgAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABNAEEASwBFAEEAUgBSAEEAWQAoADMALAAgADEALAAgAFwAbgAgACAAIAAgACAAIABMAEEATQBCAEQAQQAoAHIALABjACwAIABcAG4AIAAgACAAIAAgACAAIAAgAEkATgBEAEUAWAAoAHsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFYAQQBSAEkAQQBUAEkATwBOACAATwBGACAAUwBPAFUAUgBDAEUAIABEAEEAVABBADoAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEEAZABkAGUAZAAgAHcAYQByAG0AIAAvACAAYwBvAG8AbAAgAHQAZQBtAHAAZQByAGEAdABlACAAbQBvAGkAcwB0ACAALwAgAGQAcgB5ACAALQAgAGwAbwB3ACAAZgByAG8AcwB0ACAAYQBuAGQAIABoAGkAZwBoACAAdABlAG0AcAAgAGMAbABhAHMAcwBlAHMAIAB0AG8AIABhAGMAYwBvAG0AbQBvAGQAYQB0AGUAIABjAGwAaQBtAGEAdABlACAAcwBjAGUAbgBhAHIAaQBvAHMAIABlAHgAYwBsAHUAZABlAGQAIABiAHkAIABWAEUARQBSAEcAIABjAHIAaQB0AGUAcgBpAGEALgBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIARgBpAHgAZQBkACAAdAB5AHAAbwAgAC0AIABDAGgAYQBuAGcAZQBkACAAJwBGAHIAeQAnACAAdABvACAAJwBEAHIAeQAnAC4AXAAiAFwAbgAgACAAIAAgACAAIAAgACAAfQAsACAAcgAsACAAYwApAFwAbgAgACAAIAAgACAAIAApAFwAbgAgACAAIAAgACkAXABuACAAIAApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBXAGUAdABBAG4AZABEAHIAeQBaAG8AbgBlAHMAXwBEAGEAdABhAFwAbgAgACAAIAA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAATQBBAEsARQBBAFIAUgBBAFkAKAAxADUALAAgADIALAAgAFwAbgAgACAAIAAgACAAIABMAEEATQBCAEQAQQAoAHIALABjACwAIABcAG4AIAAgACAAIAAgACAAIAAgAEkATgBEAEUAWAAoAHsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEMAbABpAG0AYQB0AGUAIABaAG8AbgBlAFwAIgAsACAAXAAiAFcAZQB0ACAAbwByACAARAByAHkAIABaAG8AbgBlAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBUAHIAbwBwAGkAYwBhAGwAIABtAG8AbgB0AGEAbgBlAFwAIgAsACAAXAAiAFcAZQB0ACAAYwBsAGkAbQBhAHQAZQAgAHoAbwBuAGUAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFQAcgBvAHAAaQBjAGEAbAAgAHcAZQB0AFwAIgAsACAAXAAiAFcAZQB0ACAAYwBsAGkAbQBhAHQAZQAgAHoAbwBuAGUAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFQAcgBvAHAAaQBjAGEAbAAgAG0AbwBpAHMAdABcACIALAAgAFwAIgBXAGUAdAAgAGMAbABpAG0AYQB0AGUAIAB6AG8AbgBlAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBUAHIAbwBwAGkAYwBhAGwAIABkAHIAeQBcACIALAAgAFwAIgBEAHIAeQAgAGMAbABpAG0AYQB0AGUAIAB6AG8AbgBlAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBXAGEAcgBtACAAdABlAG0AcABlAHIAYQB0AGUAIABtAG8AaQBzAHQAXAAiACwAIABcACIAVwBlAHQAIABjAGwAaQBtAGEAdABlACAAegBvAG4AZQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVwBhAHIAbQAgAHQAZQBtAHAAZQByAGEAdABlACAAZAByAHkAXAAiACwAIABcACIARAByAHkAIABjAGwAaQBtAGEAdABlACAAegBvAG4AZQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAQwBvAG8AbAAgAHQAZQBtAHAAZQByAGEAdABlACAAbQBvAGkAcwB0AFwAIgAsACAAXAAiAFcAZQB0ACAAYwBsAGkAbQBhAHQAZQAgAHoAbwBuAGUAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEMAbwBvAGwAIAB0AGUAbQBwAGUAcgBhAHQAZQAgAGQAcgB5AFwAIgAsACAAXAAiAEQAcgB5ACAAYwBsAGkAbQBhAHQAZQAgAHoAbwBuAGUAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFcAYQByAG0AIAB0AGUAbQBwAGUAcgBhAHQAZQAgAG0AbwBpAHMAdAAgAC0AIABsAG8AdwAgAGYAcgBvAHMAdABcACIALAAgAFwAIgBXAGUAdAAgAGMAbABpAG0AYQB0AGUAIAB6AG8AbgBlAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBXAGEAcgBtACAAdABlAG0AcABlAHIAYQB0AGUAIABkAHIAeQAgAC0AIABsAG8AdwAgAGYAcgBvAHMAdABcACIALAAgAFwAIgBEAHIAeQAgAGMAbABpAG0AYQB0AGUAIAB6AG8AbgBlAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBXAGEAcgBtACAAdABlAG0AcABlAHIAYQB0AGUAIABtAG8AaQBzAHQAIAAtACAAaABpAGcAaAAgAHQAZQBtAHAAXAAiACwAIABcACIAVwBlAHQAIABjAGwAaQBtAGEAdABlACAAegBvAG4AZQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVwBhAHIAbQAgAHQAZQBtAHAAZQByAGEAdABlACAAZAByAHkAIAAtACAAaABpAGcAaAAgAHQAZQBtAHAAXAAiACwAIABcACIARAByAHkAIABjAGwAaQBtAGEAdABlACAAegBvAG4AZQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAQwBvAG8AbAAgAHQAZQBtAHAAZQByAGEAdABlACAAbQBvAGkAcwB0ACAALQAgAGwAbwB3ACAAZgByAG8AcwB0AFwAIgAsACAAXAAiAFcAZQB0ACAAYwBsAGkAbQBhAHQAZQAgAHoAbwBuAGUAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEMAbwBvAGwAIAB0AGUAbQBwAGUAcgBhAHQAZQAgAGQAcgB5ACAALQAgAGwAbwB3ACAAZgByAG8AcwB0AFwAIgAsACAAXAAiAEQAcgB5ACAAYwBsAGkAbQBhAHQAZQAgAHoAbwBuAGUAXAAiAFwAbgAgACAAIAAgACAAIAAgACAAfQAsACAAcgAsACAAYwApAFwAbgAgACAAIAAgACAAIAApAFwAbgAgACAAIAAgACkAXABuACAAIAApADsAXABuAFwAbgAvACoAIABcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBDAGwAaQBtAGEAdABlAFoAbwBuAGUAcwBcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgAqAC8AXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBDAGwAaQBtAGEAdABlAFoAbwBuAGUAcwBfAFQAaQB0AGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAVgBFAEUAUgBHACAAQQB1AHMAdAByAGEAbABpAGEAbgAgAGMAbABpAG0AYQB0AGUAIAB6AG8AbgBlAHMAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEMAbABpAG0AYQB0AGUAWgBvAG4AZQBzAF8AVgBhAHIAaQBhAGIAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQwBsAGkAbQBhAHQAZQBaAG8AbgBlAHMAXwBVAG4AaQB0AFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQwBsAGkAbQBhAHQAZQBaAG8AbgBlAHMAXwBTAG8AdQByAGMAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAVgBFAEUAUgBHACAAMgAwADIANgA6ACAAVABhAGIAbABlACAAMQAuADMAOgAgAEMAbABpAG0AYQB0AGUAIABhAG4AZAAgAFIAYQBpAG4AZgBhAGwAbAAgAHoAbwBuAGUAIABjAGwAYQBzAHMAaQBmAGkAYwBhAHQAaQBvAG4AcwAgAGEAbgBkACAAZABlAGYAaQBuAGkAdABpAG8AbgBzAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBDAGwAaQBtAGEAdABlAFoAbwBuAGUAcwBfAFYAYQByAGkAYQB0AGkAbwBuAFwAbgAgACAAIAA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAATQBBAEsARQBBAFIAUgBBAFkAKAA1ACwAIAAxACwAIABcAG4AIAAgACAAIAAgACAATABBAE0AQgBEAEEAKAByACwAYwAsACAAXABuACAAIAAgACAAIAAgACAAIABJAE4ARABFAFgAKAB7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBWAEEAUgBJAEEAVABJAE8ATgAgAE8ARgAgAFMATwBVAFIAQwBFACAARABBAFQAQQA6AFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBBAGQAZABlAGQAIAB3AGEAcgBtACAALwAgAGMAbwBvAGwAIAB0AGUAbQBwAGUAcgBhAHQAZQAgAG0AbwBpAHMAdAAgAC8AIABkAHIAeQAgAC0AIABsAG8AdwAgAGYAcgBvAHMAdAAgAGEAbgBkACAAaABpAGcAaAAgAHQAZQBtAHAAIABjAGwAYQBzAHMAZQBzACAAdABvACAAYQBjAGMAbwBtAG0AbwBkAGEAdABlACAAYwBsAGkAbQBhAHQAZQAgAHMAYwBlAG4AYQByAGkAbwBzACAAZQB4AGMAbAB1AGQAZQBkACAAYgB5ACAAVgBFAEUAUgBHACAAYwByAGkAdABlAHIAaQBhAC4AXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEYAaQB4AGUAZAAgAHQAeQBwAG8AIABpAG4AIABNAEEAVAAgAHYAYQBsAHUAZQAgAGYAbwByACAAdwBhAHIAbQAgAHQAZQBtAHAAZQByAGEAdABlACAAZAByAHkAIAAtACAAYwBoAGEAbgBnAGUAZAAgADEAMAAgAHQAbwAgADEAMQAuAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBBAGQAZABlAGQAIABtAGkAbgAgAGEAbgBkACAAbQBhAHgAIABjAG8AbAB1AG0AbgBzACAAZgBvAHIAIABNAEEAVAAsACAATQBBAFAALAAgAGYAcgBvAHMAdAAgAGQAYQB5AHMAIABwAGUAcgAgAHkAZQBhAHIALAAgAGUAbABlAHYAYQB0AGkAbwBuACwAIABNAEEAUAA6AFAARQBUACAAdABvACAAYwBhAGwAYwB1AGwAYQB0AGUAIAB6AG8AbgBlAHMAIABmAHIAbwBtACAAcgBlAGEAbAAgAGMAbABpAG0AYQB0AGUAIABkAGEAdABhAC4AXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEcAQQBGACAAYQBjAGMAZQBwAHQAcwAgAHIAYQBpAG4AZgBhAGwAbAAgAGEAcwAgAGEAIABwAHIAbwB4AHkAIABmAG8AcgAgAHAAcgBlAGMAaQBwAGkAdABhAHQAaQBvAG4ALgBcACIAXABuACAAIAAgACAAIAAgACAAIAB9ACwAIAByACwAIABjACkAXABuACAAIAAgACAAIAAgACkAXABuACAAIAAgACAAKQBcAG4AIAAgACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEMAbABpAG0AYQB0AGUAWgBvAG4AZQBzAF8ARABhAHQAYQBcAG4AIAAgACAAPQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAE0AQQBLAEUAQQBSAFIAQQBZACgAOQAsACAAMQA2ACwAIABcAG4AIAAgACAAIAAgACAATABBAE0AQgBEAEEAKAByACwAYwAsACAAXABuACAAIAAgACAAIAAgACAAIABJAE4ARABFAFgAKAB7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBDAGwAaQBtAGEAdABlACAAWgBvAG4AZQBcACIALAAgAFwAIgBNAEEAVABcACIALAAgAFwAIgBNAEEAUABcACIALAAgAFwAIgBGAHIAbwBzAHQAIABkAGEAeQBzACAAcABlAHIAIAB5AGUAYQByAFwAIgAsACAAXAAiAEUAbABlAHYAYQB0AGkAbwBuAFwAIgAsACAAXAAiAE0AQQBQADoAUABFAFQAXAAiACwAIABcACIATQBpAG4AIAB0AGUAbQBwAFwAIgAsACAAXAAiAE0AYQB4ACAAdABlAG0AcABcACIALAAgAFwAIgBNAGkAbgAgAHIAYQBpAG4AZgBhAGwAbABcACIALAAgAFwAIgBNAGEAeAAgAHIAYQBpAG4AZgBhAGwAbABcACIALAAgAFwAIgBNAGkAbgAgAGYAcgBvAHMAdAAgAGQAYQB5AHMAXAAiACwAIABcACIATQBhAHgAIABmAHIAbwBzAHQAIABkAGEAeQBzAFwAIgAsACAAXAAiAE0AaQBuACAAZQBsAGUAdgBhAHQAaQBvAG4AXAAiACwAIABcACIATQBhAHgAIABlAGwAZQB2AGEAdABpAG8AbgBcACIALAAgAFwAIgBNAGkAbgAgAE0AQQBQADoAUABFAFQAXAAiACwAIABcACIATQBpAG4AIABNAEEAUAA6AFAARQBUAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBUAHIAbwBwAGkAYwBhAGwAIABtAG8AbgB0AGEAbgBlAFwAIgAsACAAXAAiAD4AIAAxADgAIABDAFwAIgAsACAAXAAiAEEAbgB5AFwAIgAsACAAXAAiAGQiIAA3AFwAIgAsACAAXAAiAD4AIAAxADAAMAAwACAAbQBcACIALAAgAFwAIgBBAG4AeQBcACIALAAgADEAOAAuADAAMAAxACwAIAA5ADkAOQA5ADkAOQAsACAALQA5ADkAOQA5ADkAOQAsACAAOQA5ADkAOQA5ADkALAAgAC0AOQA5ADkAOQA5ADkALAAgADcALAAgADEAMAAwADAALAAgADkAOQA5ADkAOQA5ACwAIAAtADkAOQA5ADkAOQA5ACwAIAA5ADkAOQA5ADkAOQA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBUAHIAbwBwAGkAYwBhAGwAIAB3AGUAdABcACIALAAgAFwAIgA+ACAAMQA4ACAAQwBcACIALAAgAFwAIgA+ACAAMgAwADAAMAAgAG0AbQBcACIALAAgAFwAIgBkIiAANwBcACIALAAgAFwAIgBkIiAAMQAwADAAMAAgAG0AXAAiACwAIABcACIAQQBuAHkAXAAiACwAIAAxADgALgAwADAAMQAsACAAOQA5ADkAOQA5ADkALAAgADIAMAAwADAALgAwADAAMQAsACAAOQA5ADkAOQA5ADkALAAgAC0AOQA5ADkAOQA5ADkALAAgADcALAAgAC0AOQA5ADkAOQA5ADkALAAgADkAOQA5AC4AOQA5ADkALAAgACAALQA5ADkAOQA5ADkAOQAsACAAOQA5ADkAOQA5ADkAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVAByAG8AcABpAGMAYQBsACAAbQBvAGkAcwB0AFwAIgAsACAAXAAiAD4AIAAxADgAIABDAFwAIgAsACAAXAAiAD4AIAAxADAAMAAwACAAbQBtACAALQAgAGQiIAAyADAAMAAwACAAbQBtAFwAIgAsACAAXAAiAGQiIAA3AFwAIgAsACAAXAAiAGQiIAAxADAAMAAwACAAbQBcACIALAAgAFwAIgBBAG4AeQBcACIALAAgADEAOAAuADAAMAAxACwAIAA5ADkAOQA5ADkAOQAsACAAMQAwADAAMAAuADAAMAAxACwAIAAyADAAMAAwACwAIAAtADkAOQA5ADkAOQA5ACwAIAA3ACwAIAAtADkAOQA5ADkAOQA5ACwAIAA5ADkAOQAuADkAOQA5ACwAIAAgAC0AOQA5ADkAOQA5ADkALAAgADkAOQA5ADkAOQA5ADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFQAcgBvAHAAaQBjAGEAbAAgAGQAcgB5AFwAIgAsACAAXAAiAD4AIAAxADgAIABDAFwAIgAsACAAXAAiAGQiIAAxADAAMAAwACAAbQBtAFwAIgAsACAAXAAiAGQiIAA3AFwAIgAsACAAXAAiAGQiIAAxADAAMAAwACAAbQBcACIALAAgAFwAIgBBAG4AeQBcACIALAAgADEAOAAuADAAMAAxACwAIAA5ADkAOQA5ADkAOQAsACAALQA5ADkAOQA5ADkAOQAsACAAMQAwADAAMAAsACAALQA5ADkAOQA5ADkAOQAsACAANwAsACAALQA5ADkAOQA5ADkAOQAsACAAOQA5ADkALgA5ADkAOQAsACAAIAAtADkAOQA5ADkAOQA5ACwAIAA5ADkAOQA5ADkAOQA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBXAGEAcgBtACAAdABlAG0AcABlAHIAYQB0AGUAIABtAG8AaQBzAHQAXAAiACwAIABcACIAPgAgADEAMAAgAEMAXAAiACwAIABcACIAQQBuAHkAXAAiACwAIABcACIAQQBuAHkAXAAiACwAIABcACIAQQBuAHkAXAAiACwAIABcACIAPgAgADEAXAAiACwAIAAxADAALgAwADAAMQAsACAAOQA5ADkAOQA5ADkALAAgAC0AOQA5ADkAOQA5ADkALAAgADkAOQA5ADkAOQA5ACwAIAAtADkAOQA5ADkAOQA5ACwAIAA5ADkAOQA5ADkAOQAsACAALQA5ADkAOQA5ADkAOQAsACAAOQA5ADkAOQA5ADkALAAgADEALgAwADAAMQAsACAAOQA5ADkAOQA5ADkAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVwBhAHIAbQAgAHQAZQBtAHAAZQByAGEAdABlACAAZAByAHkAXAAiACwAIABcACIAPgAgADEAMAAgAEMAXAAiACwAIABcACIAQQBuAHkAXAAiACwAIABcACIAQQBuAHkAXAAiACwAIABcACIAQQBuAHkAXAAiACwAIABcACIAZCIgADEAXAAiACwAIAAxADAALgAwADAAMQAsACAAOQA5ADkAOQA5ADkALAAgAC0AOQA5ADkAOQA5ADkALAAgADkAOQA5ADkAOQA5ACwAIAAtADkAOQA5ADkAOQA5ACwAIAA5ADkAOQA5ADkAOQAsACAALQA5ADkAOQA5ADkAOQAsACAAOQA5ADkAOQA5ADkALAAgACAALQA5ADkAOQA5ADkAOQAsACAAMQA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBDAG8AbwBsACAAdABlAG0AcABlAHIAYQB0AGUAIABtAG8AaQBzAHQAXAAiACwAIABcACIAPgAgADAAIABDACAALQAgAGQiIAAxADAAIABDAFwAIgAsACAAXAAiAEEAbgB5AFwAIgAsACAAXAAiAEEAbgB5AFwAIgAsACAAXAAiAEEAbgB5AFwAIgAsACAAXAAiAD4AIAAxAFwAIgAsACAALQA5ADkAOQA5ADkAOQAsACAAMQAwACwAIAAtADkAOQA5ADkAOQA5ACwAIAA5ADkAOQA5ADkAOQAsACAALQA5ADkAOQA5ADkAOQAsACAAOQA5ADkAOQA5ADkALAAgAC0AOQA5ADkAOQA5ADkALAAgADkAOQA5ADkAOQA5ACwAIAAxAC4AMAAwADEALAAgADkAOQA5ADkAOQA5ADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEMAbwBvAGwAIAB0AGUAbQBwAGUAcgBhAHQAZQAgAGQAcgB5AFwAIgAsACAAXAAiAD4AIAAwACAAQwAgAC0AIABkIiAAMQAwACAAQwBcACIALAAgAFwAIgBBAG4AeQBcACIALAAgAFwAIgBBAG4AeQBcACIALAAgAFwAIgBBAG4AeQBcACIALAAgAFwAIgBkIiAAMQBcACIALAAgAC0AOQA5ADkAOQA5ADkALAAgADEAMAAsACAALQA5ADkAOQA5ADkAOQAsACAAOQA5ADkAOQA5ADkALAAgAC0AOQA5ADkAOQA5ADkALAAgADkAOQA5ADkAOQA5ACwAIAAtADkAOQA5ADkAOQA5ACwAIAA5ADkAOQA5ADkAOQAsACAAIAAtADkAOQA5ADkAOQA5ACwAIAAxAFwAbgAgACAAIAAgACAAIAAgACAAfQAsACAAcgAsACAAYwApAFwAbgAgACAAIAAgACAAIAApAFwAbgAgACAAIAAgACkAXABuACAAIAApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBDAGwAaQBtAGEAdABlAFoAbwBuAGUAcwBfAEEAcABwAGUAbgBkAGkAYwBlAHMAXABuACAAIAAgAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABNAEEASwBFAEEAUgBSAEEAWQAoADQALAAgADEALAAgAFwAbgAgACAAIAAgACAAIABMAEEATQBCAEQAQQAoAHIALABjACwAIABcAG4AIAAgACAAIAAgACAAIAAgAEkATgBEAEUAWAAoAHsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAE4AbwB0AGUAOgBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIATQBBAFQAIAA9ACAAbQBlAGEAbgAgAGEAbgBuAHUAYQBsACAAdABlAG0AcABlAHIAYQB0AHUAcgBlAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBNAEEAUAAgAD0AIABtAGUAYQBuACAAYQBuAG4AdQBhAGwAIABwAHIAZQBjAGkAcABpAHQAYQB0AGkAbwBuAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBQAEUAVAAgAD0AIABwAG8AdABlAG4AdABpAGEAbAAgAGUAdgBhAHAAbwB0AHIAYQBuAHMAcABpAHIAYQB0AGkAbwBuAFwAIgBcAG4AIAAgACAAIAAgACAAIAAgAH0ALAAgAHIALAAgAGMAKQBcAG4AIAAgACAAIAAgACAAKQBcAG4AIAAgACAAIAApAFwAbgAgACAAKQA7AFwAbgBcAG4AXABuAC8AKgAgAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFQAZQBtAHAAZQByAGEAdAB1AHIAZQBaAG8AbgBlAHMAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AKgAvAFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AVABlAG0AcABlAHIAYQB0AHUAcgBlAFoAbwBuAGUAcwBfAFQAaQB0AGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAVgBFAEUAUgBHACAAQQB1AHMAdAByAGEAbABpAGEAbgAgAHQAZQBtAHAAZQByAGEAdAB1AHIAZQAgAHoAbwBuAGUAcwBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AVABlAG0AcABlAHIAYQB0AHUAcgBlAFoAbwBuAGUAcwBfAFYAYQByAGkAYQBiAGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFQAZQBtAHAAZQByAGEAdAB1AHIAZQBaAG8AbgBlAHMAXwBVAG4AaQB0AFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AVABlAG0AcABlAHIAYQB0AHUAcgBlAFoAbwBuAGUAcwBfAFMAbwB1AHIAYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBWAEUARQBSAEcAIAAyADAAMgA2ADoAIABUAGEAYgBsAGUAIAAxAC4AMwA6ACAAQwBsAGkAbQBhAHQAZQAgAGEAbgBkACAAUgBhAGkAbgBmAGEAbABsACAAegBvAG4AZQAgAGMAbABhAHMAcwBpAGYAaQBjAGEAdABpAG8AbgBzACAAYQBuAGQAIABkAGUAZgBpAG4AaQB0AGkAbwBuAHMAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFQAZQBtAHAAZQByAGEAdAB1AHIAZQBaAG8AbgBlAHMAXwBWAGEAcgBpAGEAdABpAG8AbgBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAVgBBAFIASQBBAFQASQBPAE4AIABPAEYAIABTAE8AVQBSAEMARQAgAEQAQQBUAEEAOgAgAEEAZABkAGUAZAAgAGUAeAB0AHIAYQAgAE0AQQBUACAAbQBpAG4AIABhAG4AZAAgAE0AQQBUACAAbQBhAHgAIABjAG8AbAB1AG0AbgBzACAAdABvACAAYwBhAGwAYwB1AGwAYQB0AGUAIAB6AG8AbgBlACAAZgByAG8AbQAgAHIAZQBhAGwAIAB0AGUAbQBwAGUAcgBhAHQAdQByAGUAIABkAGEAdABhAC4AXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFQAZQBtAHAAZQByAGEAdAB1AHIAZQBaAG8AbgBlAHMAXwBEAGEAdABhAFwAbgAgACAAIAA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAATQBBAEsARQBBAFIAUgBBAFkAKAA0ACwAIAA0ACwAIABcAG4AIAAgACAAIAAgACAATABBAE0AQgBEAEEAKAByACwAYwAsACAAXABuACAAIAAgACAAIAAgACAAIABJAE4ARABFAFgAKAB7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBUAGUAbQBwAGUAcgBhAHQAdQByAGUAIABaAG8AbgBlAFwAIgAsACAAXAAiAE0AZQBkAGkAYQBuACAAQQBuAG4AdQBhAGwAIABUAGUAbQBwAGUAcgBhAHQAdQByAGUAIAAoAE0AQQBUACkAXAAiACwAIABcACIATQBpAG4AIABNAEEAVABcACIALAAgAFwAIgBNAGEAeAAgAE0AQQBUAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBXAGEAcgBtAFwAIgAsACAAXAAiAGUiIAAyADYAIABDAFwAIgAsACAAMgA2ACwAIAA5ADkAOQA5ADkAOQA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBUAGUAbQBwAGUAcgBhAHQAZQBcACIALAAgAFwAIgAxADUAIAAtACAAMgA1ACAAQwBcACIALAAgADEANQAsACAAMgA1AC4AOQA5ADkAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAQwBvAG8AbABcACIALAAgAFwAIgBkIiAAMQA0ACAAQwBcACIALAAgAC0AOQA5ADkAOQA5ADkALAAgADEANAAuADkAOQA5AFwAbgAgACAAIAAgACAAIAAgACAAfQAsACAAcgAsACAAYwApAFwAbgAgACAAIAAgACAAIAApAFwAbgAgACAAIAAgACkAXABuACAAIAApADsAXABuAFwAbgAvACoAIABcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBSAGEAaQBuAGYAYQBsAGwAWgBvAG4AZQBzAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuACoALwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFIAYQBpAG4AZgBhAGwAbABaAG8AbgBlAHMAXwBUAGkAdABsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFYARQBFAFIARwAgAEEAdQBzAHQAcgBhAGwAaQBhAG4AIAByAGEAaQBuAGYAYQBsAGwAIAB6AG8AbgBlAHMAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFIAYQBpAG4AZgBhAGwAbABaAG8AbgBlAHMAXwBWAGEAcgBpAGEAYgBsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBSAGEAaQBuAGYAYQBsAGwAWgBvAG4AZQBzAF8AVQBuAGkAdABcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFIAYQBpAG4AZgBhAGwAbABaAG8AbgBlAHMAXwBTAG8AdQByAGMAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAVgBFAEUAUgBHACAAMgAwADIANgA6ACAAVABhAGIAbABlACAAMQAuADMAOgAgAEMAbABpAG0AYQB0AGUAIABhAG4AZAAgAFIAYQBpAG4AZgBhAGwAbAAgAHoAbwBuAGUAIABjAGwAYQBzAHMAaQBmAGkAYwBhAHQAaQBvAG4AcwAgAGEAbgBkACAAZABlAGYAaQBuAGkAdABpAG8AbgBzAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBSAGEAaQBuAGYAYQBsAGwAWgBvAG4AZQBzAF8AVgBhAHIAaQBhAHQAaQBvAG4AXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFYAQQBSAEkAQQBUAEkATwBOACAATwBGACAAUwBPAFUAUgBDAEUAIABEAEEAVABBADoAIABBAGQAZABlAGQAIABlAHgAdAByAGEAIABSAGEAaQBuAGYAYQBsAGwAIABtAGkAbgAgAGEAbgBkACAAUgBhAGkAbgBmAGEAbABsACAAbQBhAHgAIABjAG8AbAB1AG0AbgBzACAAdABvACAAYwBhAGwAYwB1AGwAYQB0AGUAIAB6AG8AbgBlACAAZgByAG8AbQAgAHIAZQBhAGwAIAByAGEAaQBuAGYAYQBsAGwAIABkAGEAdABhAC4AXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFIAYQBpAG4AZgBhAGwAbABaAG8AbgBlAHMAXwBEAGEAdABhAFwAbgAgACAAIAA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAATQBBAEsARQBBAFIAUgBBAFkAKAAzACwAIAA0ACwAIABcAG4AIAAgACAAIAAgACAATABBAE0AQgBEAEEAKAByACwAYwAsACAAXABuACAAIAAgACAAIAAgACAAIABJAE4ARABFAFgAKAB7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBSAGEAaQBuAGYAYQBsAGwAIABaAG8AbgBlAFwAIgAsACAAXAAiAEEAbgBuAHUAYQBsACAAcgBhAGkAbgBmAGEAbABsAFwAIgAsACAAXAAiAFIAYQBpAG4AZgBhAGwAbAAgAG0AaQBuAFwAIgAsACAAXAAiAFIAYQBpAG4AZgBhAGwAbAAgAG0AYQB4AFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBIAGkAZwBoACAAcgBhAGkAbgBmAGEAbABsAFwAIgAsACAAXAAiAEEAbgBuAHUAYQBsACAAcgBhAGkAbgBmAGEAbABsACAAPgAgADYAMAAwAG0AbQBcACIALAAgADYAMAAwAC4AMAAwADEALAAgADkAOQA5ADkAOQA5ADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEwAbwB3ACAAcgBhAGkAbgBmAGEAbABsAFwAIgAsACAAXAAiAEEAbgBuAHUAYQBsACAAcgBhAGkAbgBmAGEAbABsACAAZCIgADYAMAAwAG0AbQBcACIALAAgAC0AOQA5ADkAOQA5ADkALAAgADYAMAAwAFwAbgAgACAAIAAgACAAIAAgACAAfQAsACAAcgAsACAAYwApAFwAbgAgACAAIAAgACAAIAApAFwAbgAgACAAIAAgACkAXABuACAAIAApADsAXABuAFwAbgAvACoAIABcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBMAGUAYQBjAGgAaQBuAGcAWgBvAG4AZQBzAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuACoALwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEwAZQBhAGMAaABpAG4AZwBaAG8AbgBlAHMAXwBUAGkAdABsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFYARQBFAFIARwAgAEEAdQBzAHQAcgBhAGwAaQBhAG4AIABsAGUAYQBjAGgAaQBuAGcAIAB6AG8AbgBlAHMAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEwAZQBhAGMAaABpAG4AZwBaAG8AbgBlAHMAXwBWAGEAcgBpAGEAYgBsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBMAGUAYQBjAGgAaQBuAGcAWgBvAG4AZQBzAF8AVQBuAGkAdABcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEwAZQBhAGMAaABpAG4AZwBaAG8AbgBlAHMAXwBTAG8AdQByAGMAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAVgBFAEUAUgBHACAAMgAwADIANgA6ACAAVABhAGIAbABlACAAMQAuADMAOgAgAEMAbABpAG0AYQB0AGUAIABhAG4AZAAgAFIAYQBpAG4AZgBhAGwAbAAgAHoAbwBuAGUAIABjAGwAYQBzAHMAaQBmAGkAYwBhAHQAaQBvAG4AcwAgAGEAbgBkACAAZABlAGYAaQBuAGkAdABpAG8AbgBzAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBMAGUAYQBjAGgAaQBuAGcAWgBvAG4AZQBzAF8AVgBhAHIAaQBhAHQAaQBvAG4AXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBMAGUAYQBjAGgAaQBuAGcAWgBvAG4AZQBzAF8ARABhAHQAYQBcAG4AIAAgACAAPQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAE0AQQBLAEUAQQBSAFIAQQBZACgANAAsACAAMgAsACAAXABuACAAIAAgACAAIAAgAEwAQQBNAEIARABBACgAcgAsAGMALAAgAFwAbgAgACAAIAAgACAAIAAgACAASQBOAEQARQBYACgAewBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIATABlAGEAYwBoAGkAbgBnACAAWgBvAG4AZQBcACIALAAgAFwAIgBMAGUAYQBjAGgAaQBuAGcAIABjAHIAaQB0AGUAcgBpAGEAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEwAZQBhAGMAaABpAG4AZwAgAG8AYwBjAHUAcgBzAFwAIgAsACAAXAAiAKMDKAA12F/cNdhO3DXYVtw12FvcKQA+AKMDKAA12DjcNdhH3DAAKQArADXYYNw12FzcNdhW3DXYWdwgADXYZNw12E7cNdhh3DXYUtw12F/cIAAOITXYXNw12FncNdhR3DXYVtw12FvcNdhU3CAANdhQ3DXYTtw12F3cNdhO3DXYUNw12FbcNdhh3DXYZtxcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIATABlAGEAYwBoAGkAbgBnACAAZABvAGUAcwAgAG4AbwB0ACAAbwBjAGMAdQByAFwAIgAsACAAXAAiAKMDKAA12F/cNdhO3DXYVtw12FvcKQBkIqMDKAA12DjcNdhH3DAAKQArADXYYNw12FzcNdhW3DXYWdwgADXYZNw12E7cNdhh3DXYUtw12F/cIAAOITXYXNw12FncNdhR3DXYVtw12FvcNdhU3CAANdhQ3DXYTtw12F3cNdhO3DXYUNw12FbcNdhh3DXYZtxcACIAXABuACAAIAAgACAAIAAgACAAIAB9ACwAIAByACwAIABjACkAXABuACAAIAAgACAAIAAgACkAXABuACAAIAAgACAAKQBcAG4AIAAgACkAOwBcAG4AXABuAC8AKgAgAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAcgBhAGMAVwBFAFQAXABuADUALgA1AC4AMgAuADMAIABDAG8AbgBzAHQAYQBuAHQAIABQAGEAcgBhAG0AZQB0AGUAcgBzAFwAbgBGAHIAYQBjAHQAaQBvAG4AIABvAGYAIABOACAAdABoAGEAdAAgAGkAcwAgAGEAdgBhAGkAbABhAGIAbABlACAAZgBvAHIAIABsAGUAYQBjAGgAaQBuAGcAIABhAG4AZAAgAHIAdQBuAG8AZgBmAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuACoALwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAcgBhAGMAVwBFAFQAXwBUAGkAdABsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAEYAcgBhAGMAdABpAG8AbgAgAG8AZgAgAE4AIAB0AGgAYQB0ACAAaQBzACAAYQB2AGEAaQBsAGEAYgBsAGUAIABmAG8AcgAgAGwAZQBhAGMAaABpAG4AZwAgAGEAbgBkACAAcgB1AG4AbwBmAGYAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAcgBhAGMAVwBFAFQAXwBVAG4AaQB0AFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgAoAEQAaQBtAGUAbgBzAGkAbwBuAGwAZQBzAHMAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAcgBhAGMAVwBFAFQAXwBTAG8AdQByAGMAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAVgBFAEUAUgBHACAAMgAwADIANgA6ADUALgA1AC4AMgAuADMAIABDAG8AbgBzAHQAYQBuAHQAIABQAGEAcgBhAG0AZQB0AGUAcgBzAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAHIAYQBjAFcARQBUAF8ATgBJAFIAUgBlAGYAZQByAGUAbgBjAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAHIAYQBjAFcARQBUAF8ARABhAHQAYQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABNAEEASwBFAEEAUgBSAEEAWQAoADMALAAgADIALAAgAFwAbgAgACAAIAAgACAAIABMAEEATQBCAEQAQQAoAHIALABjACwAIABcAG4AIAAgACAAIAAgACAAIAAgAEkATgBEAEUAWAAoAHsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEkAcwAgAGkAbgAgAGwAZQBhAGMAaABpAG4AZwAgAHoAbwBuAGUAXAAiACwAXAAiAEYAcgBhAGMAVwBFAFQAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFkAZQBzACAALQAgAGkAbgAgAGwAZQBhAGMAaABpAG4AZwAgAHoAbwBuAGUAXAAiACwAIAAxADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAE4AbwAgAC0AIABuAG8AdAAgAGkAbgAgAGwAZQBhAGMAaABpAG4AZwAgAHoAbwBuAGUAXAAiACwAIAAwAFwAbgAgACAAIAAgACAAIAAgACAAfQAsACAAcgAsACAAYwApAFwAbgAgACAAIAAgACAAIAApAFwAbgAgACAAIAAgACkAXABuACAAIAApADsAXABuAFwAbgAgACAAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgByAGEAYwBXAEUAVABfAFYAYQByAGkAYQB0AGkAbwBuAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoACgAXAAiAFwAIgApACkAOwBcAG4AXABuAFwAbgBcAG4ALwAqACAAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABhAHQAYQBTAGMAbwByAGUAcwBfAFMAYwBvAHAAZQAzAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuACoALwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEQAYQB0AGEAUwBjAG8AcgBlAHMAXwBTAGMAbwBwAGUAMwBfAFQAaQB0AGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAQQB1AHMAdAByAGEAbABpAGEAbgAgAGQAYQB0AGEAIABzAGMAbwByAGUAcwAgAGYAbwByACAAcwBjAG8AcABlACAAMwBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABhAHQAYQBTAGMAbwByAGUAcwBfAFMAYwBvAHAAZQAzAF8AVgBhAHIAaQBhAGIAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABhAHQAYQBTAGMAbwByAGUAcwBfAFMAYwBvAHAAZQAzAF8AVQBuAGkAdABcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEQAYQB0AGEAUwBjAG8AcgBlAHMAXwBTAGMAbwBwAGUAMwBfAFMAbwB1AHIAYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBWAEUARQBSAEcAIAAyADAAMgA2ADoAIABYAFgAWABYAFgAWABYAFgAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEQAYQB0AGEAUwBjAG8AcgBlAHMAXwBTAGMAbwBwAGUAMwBfAFYAYQByAGkAYQB0AGkAbwBuAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABhAHQAYQBTAGMAbwByAGUAcwBfAFMAYwBvAHAAZQAzAF8ARABhAHQAYQBcAG4AIAAgACAAPQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAE0AQQBLAEUAQQBSAFIAQQBZACgANgAsACAAMgAsACAAXABuACAAIAAgACAAIAAgAEwAQQBNAEIARABBACgAcgAsAGMALAAgAFwAbgAgACAAIAAgACAAIAAgACAASQBOAEQARQBYACgAewBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIARABhAHQAYQAgAHMAbwB1AHIAYwBlAFwAIgAsACAAXAAiAEQAYQB0AGEAIABzAGMAbwByAGUAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEkAbgB0AGUAcgBuAGEAdABpAG8AbgBhAGwAIABzAGMAbwBwAGUAIAAzACAAZABhAHQAYQBiAGEAcwBlAFwAIgAsACAAMQA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBBAHUAcwB0AHIAYQBsAGkAYQBuACAAcwBjAG8AcABlACAAMwAgAGQAYQB0AGEAYgBhAHMAZQBcACIALAAgADIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAUwB0AGEAdABlACAAbwByACAAcgBlAGcAaQBvAG4AYQBsACAAcwBjAG8AcABlACAAMwAgAGQAYQB0AGEAYgBhAHMAZQBcACIALAAgADMAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIARQBtAGkAcwBzAGkAbwBuAHMAIABpAG4AdABlAG4AcwBpAHQAeQAgAGMAYQBsAGMAdQBsAGEAdABlAGQAIABmAHIAbwBtACAAYQBwAHAAcgBvAHYAZQBkACAAbQBlAHQAaABvAGQAXAAiACwAIAA0ADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFYAZQByAGkAZgBpAGUAZAAgAGMAcgBlAGQAZQBuAHQAaQBhAGwAIABtAGEAdABjAGgAaQBuAGcAIABJAFMATwAxADQAMAA2ADcAXAAiACwAIAA1AFwAbgAgACAAIAAgACAAIAAgACAAfQAsACAAcgAsACAAYwApAFwAbgAgACAAIAAgACAAIAApAFwAbgAgACAAIAAgACkAXABuACAAIAApADsAXABuAFwAbgBcAG4ALwAqACAAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgByAGEAYwBMAEUAQQBDAEgAXABuADUALgA1AC4AMgAuADMAIABDAG8AbgBzAHQAYQBuAHQAIABQAGEAcgBhAG0AZQB0AGUAcgBzAFwAbgBGAHIAYQBjAHQAaQBvAG4AIABvAGYAIABOACAAdABoAGEAdAAgAGkAcwAgAGEAdgBhAGkAbABhAGIAbABlACAAZgBvAHIAIABsAGUAYQBjAGgAaQBuAGcAIABhAG4AZAAgAHIAdQBuAG8AZgBmAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuACoALwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAcgBhAGMATABFAEEAQwBIAF8AVABpAHQAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBGAHIAYQBjAHQAaQBvAG4AIABvAGYAIABOACAAdABoAGEAdAAgAGkAcwAgAGEAdgBhAGkAbABhAGIAbABlACAAZgBvAHIAIABsAGUAYQBjAGgAaQBuAGcAIABhAG4AZAAgAHIAdQBuAG8AZgBmAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAHIAYQBjAEwARQBBAEMASABfAFUAbgBpAHQAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiACgARABpAG0AZQBuAHMAaQBvAG4AbABlAHMAcwBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgByAGEAYwBMAEUAQQBDAEgAXwBTAG8AdQByAGMAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAVgBFAEUAUgBHACAAMgAwADIANgA6ADUALgA1AC4AMgAuADMAIABDAG8AbgBzAHQAYQBuAHQAIABQAGEAcgBhAG0AZQB0AGUAcgBzAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAHIAYQBjAEwARQBBAEMASABfAE4ASQBSAFIAZQBmAGUAcgBlAG4AYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBOAGEAdABpAG8AbgBhAGwAIABJAG4AdgBlAG4AdABvAHIAeQAgAFIAZQBwAG8AcgB0ACAAVgBvAGwAdQBtAGUAIAAxADoAIABMAGUAYQBjAGgAaQBuAGcAIABhAG4AZAAgAHIAdQBuAG8AZgBmACAAKAAzAC4ARAAuAGIALgAyACkAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAcgBhAGMATABFAEEAQwBIAF8ARABhAHQAYQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABNAEEASwBFAEEAUgBSAEEAWQAoADEALAAgADIALAAgAFwAbgAgACAAIAAgACAAIABMAEEATQBCAEQAQQAoAHIALABjACwAIABcAG4AIAAgACAAIAAgACAAIAAgAEkATgBEAEUAWAAoAHsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEYAcgBhAGMATABFAEEAQwBIAFwAIgAsADAALgAyADQAXABuACAAIAAgACAAIAAgACAAIAB9ACwAIAByACwAIABjACkAXABuACAAIAAgACAAIAAgACkAXABuACAAIAAgACAAKQBcAG4AIAAgACkAOwBcAG4AXABuACAAIABDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAHIAYQBjAEwARQBBAEMASABfAFYAYQByAGkAYQB0AGkAbwBuAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoACgAXAAiAFwAIgApACkAOwBcAG4AXABuAFwAbgBcAG4ALwAqACAAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAGwAZQBhAGMAaABcAG4ANQAuADUALgAyAC4AMwAgAEMAbwBuAHMAdABhAG4AdAAgAFAAYQByAGEAbQBlAHQAZQByAHMAXABuAEUAbQBpAHMAcwBpAG8AbgAgAGYAYQBjAHQAbwByACAAZgBvAHIAIABuAGkAdAByAG8AZwBlAG4AIABsAGUAYQBjAGgAaQBuAGcAIABhAG4AZAAgAHIAdQBuAG8AZgBmAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuACoALwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEUARgBsAGUAYQBjAGgAXwBUAGkAdABsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAEUAbQBpAHMAcwBpAG8AbgAgAGYAYQBjAHQAbwByACAAZgBvAHIAIABuAGkAdAByAG8AZwBlAG4AIABsAGUAYQBjAGgAaQBuAGcAIABhAG4AZAAgAHIAdQBuAG8AZgBmAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYAbABlAGEAYwBoAF8AVQBuAGkAdABcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAKABrAGcAIABOADIATwAtAE4AIAAvACAAawBnACAATgBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAGwAZQBhAGMAaABfAFMAbwB1AHIAYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBWAEUARQBSAEcAIAAyADAAMgA2ADoANQAuADUALgAyAC4AMwAgAEMAbwBuAHMAdABhAG4AdAAgAFAAYQByAGEAbQBlAHQAZQByAHMAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEUARgBsAGUAYQBjAGgAXwBOAEkAUgBSAGUAZgBlAHIAZQBuAGMAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIATgBhAHQAaQBvAG4AYQBsACAASQBuAHYAZQBuAHQAbwByAHkAIABSAGUAcABvAHIAdAAgAFYAbwBsAHUAbQBlACAAMQA6ACAARQBxAHUAYQB0AGkAbwBuACAAMwAuAEQALgBCAF8AMQAwAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYAbABlAGEAYwBoAF8ARABhAHQAYQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABNAEEASwBFAEEAUgBSAEEAWQAoADEALAAgADIALAAgAFwAbgAgACAAIAAgACAAIABMAEEATQBCAEQAQQAoAHIALABjACwAIABcAG4AIAAgACAAIAAgACAAIAAgAEkATgBEAEUAWAAoAHsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEUARgBsAGUAYQBjAGgAXAAiACwAMAAuADAAMQAxAFwAbgAgACAAIAAgACAAIAAgACAAfQAsACAAcgAsACAAYwApAFwAbgAgACAAIAAgACAAIAApAFwAbgAgACAAIAAgACkAXABuACAAIAApADsAXABuAFwAbgAgACAAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAGwAZQBhAGMAaABfAFYAYQByAGkAYQB0AGkAbwBuAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoACgAXAAiAFwAIgApACkAOwBcAG4AXABuAFwAbgAvACoAIABcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYATgAyAE8AXABuAFQAYQBiAGwAZQAgAEEALgAyAC4AMgAuADEAXABuAE4AaQB0AHIAbwB1AHMAIABvAHgAaQBkAGUAIABlAG0AaQBzAHMAaQBvAG4AIABmAGEAYwB0AG8AcgBzACAAZgBvAHIAIABpAG4AbwByAGcAYQBuAGkAYwAgAGYAZQByAHQAaQBsAGkAcwBlAHIAIABhAHAAcABsAGkAYwBhAHQAaQBvAG4AIAAoAGsAZwAgAE4AMgBPAC0ATgAvAGsAZwAgAE4AKQAgACgARQBGAE4AMgBPACkAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AKgAvAFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAE4AMgBPAF8AVABpAHQAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBOAGkAdAByAG8AdQBzACAAbwB4AGkAZABlACAAZQBtAGkAcwBzAGkAbwBuACAAZgBhAGMAdABvAHIAcwAgAGYAbwByACAAaQBuAG8AcgBnAGEAbgBpAGMAIABmAGUAcgB0AGkAbABpAHMAZQByACAAYQBwAHAAbABpAGMAYQB0AGkAbwBuAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYATgAyAE8AXwBVAG4AaQB0AFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgAoAGsAZwAgAE4AMgBPAC0ATgAgAC8AIABrAGcAIABOAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYATgAyAE8AXwBTAG8AdQByAGMAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAVgBFAEUAUgBHACAAMgAwADIANgA6ACAAVABhAGIAbABlACAAQQAuADIALgAyAC4AMQBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAE4AMgBPAF8ATgBJAFIAUgBlAGYAZQByAGUAbgBjAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYATgAyAE8AXwBEAGEAdABhAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAE0AQQBLAEUAQQBSAFIAQQBZACgAMQA1ACwAIAA1ACwAIABcAG4AIAAgACAAIAAgACAATABBAE0AQgBEAEEAKAByACwAYwAsACAAXABuACAAIAAgACAAIAAgACAAIABJAE4ARABFAFgAKAB7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBQAHIAbwBkAHUAYwB0AGkAbwBuACAAcwB5AHMAdABlAG0AIABqAFwAIgAsAFwAIgBFAEYATgAyAE8AXAAiACwAIABcACIAUAByAG8AZAB1AGMAdABpAG8AbgAgAHMAeQBzAHQAZQBtACAAbwBuAGwAeQBcACIALAAgAFwAIgBJAHIAcgBpAGcAYQB0AGkAbwBuACAAbQBlAHQAaABvAGQAXAAiACwAIABcACIAUgBhAGkAbgBmAGEAbABsACAAegBvAG4AZQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIASQByAHIAaQBnAGEAdABlAGQAIABwAGEAcwB0AHUAcgBlAFwAIgAsADAALgAwADAANQA5ACwAIABcACIAUABhAHMAdAB1AHIAZQBcACIALAAgAFwAIgBBAG4AeQBcACIALAAgAFwAIgBBAG4AeQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIASQByAHIAaQBnAGEAdABlAGQAIABjAHIAbwBwAFwAIgAsADAALgAwADAANwAsACAAXAAiAEMAcgBvAHAAXAAiACwAIABcACIAQQBuAHkAXAAiACwAIABcACIAQQBuAHkAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAE4AbwBuAC0AaQByAHIAaQBnAGEAdABlAGQAIABwAGEAcwB0AHUAcgBlAFwAIgAsADAALgAwADAAMQA4ACwAIABcACIAUABhAHMAdAB1AHIAZQBcACIALAAgAFwAIgBOAG8AdAAgAGkAcgByAGkAZwBhAHQAZQBkAFwAIgAsACAAXAAiAEwAbwB3ACAAcgBhAGkAbgBmAGEAbABsAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBOAG8AbgAtAGkAcgByAGkAZwBhAHQAZQBkACAAcABhAHMAdAB1AHIAZQBcACIALAAwAC4AMAAwADEAOAAsACAAXAAiAFAAYQBzAHQAdQByAGUAXAAiACwAIABcACIATgBvAHQAIABpAHIAcgBpAGcAYQB0AGUAZABcACIALAAgAFwAIgBIAGkAZwBoACAAcgBhAGkAbgBmAGEAbABsAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBOAG8AbgAtAGkAcgByAGkAZwBhAHQAZQBkACAAYwByAG8AcAAgACgAbABvAHcAIAByAGEAaQBuAGYAYQBsAGwAKQBcACIALAAwAC4AMAAwADIAOQAsACAAXAAiAEMAcgBvAHAAXAAiACwAIABcACIATgBvAHQAIABpAHIAcgBpAGcAYQB0AGUAZABcACIALAAgAFwAIgBMAG8AdwAgAHIAYQBpAG4AZgBhAGwAbABcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIATgBvAG4ALQBpAHIAcgBpAGcAYQB0AGUAZAAgAGMAcgBvAHAAIAAoAGgAaQBnAGgAIAByAGEAaQBuAGYAYQBsAGwAKQBcACIALAAwAC4AMAAwADgALAAgAFwAIgBDAHIAbwBwAFwAIgAsACAAXAAiAE4AbwB0ACAAaQByAHIAaQBnAGEAdABlAGQAXAAiACwAIABcACIASABpAGcAaAAgAHIAYQBpAG4AZgBhAGwAbABcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAUwB1AGcAYQByAFwAIgAsADAALgAwADEAOQA5ACwAIABcACIAUwB1AGcAYQByAFwAIgAsACAAXAAiAEEAbgB5AFwAIgAsACAAXAAiAEEAbgB5AFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBDAG8AdAB0AG8AbgBcACIALAAwAC4AMAAwADUAMwAsACAAXAAiAEMAbwB0AHQAbwBuAFwAIgAsACAAXAAiAEEAbgB5AFwAIgAsACAAXAAiAEEAbgB5AFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBIAG8AcgB0AGkAYwB1AGwAdAB1AHIAYQBsACAAYwByAG8AcABzAFwAIgAsADAALgAwADAANgA0ACwAIABcACIASABvAHIAdABpAGMAdQBsAHQAdQByAGEAbAAgAGMAcgBvAHAAcwBcACIALAAgAFwAIgBBAG4AeQBcACIALAAgAFwAIgBBAG4AeQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAUgBpAGMAZQAgACgAYwBvAG4AdABpAG4AdQBvAHUAcwAgAGYAbABvAG8AZABpAG4AZwApAFwAIgAsADAALgAwADAAMwAsACAAXAAiAFIAaQBjAGUAXAAiACwAIABcACIAQwBvAG4AdABpAG4AdQBvAHUAcwAgAGYAbABvAG8AZABpAG4AZwBcACIALAAgAFwAIgBBAG4AeQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAUgBpAGMAZQAgACgAcwBpAG4AZwBsAGUAIABhAG4AZAAgAG0AdQBsAHQAaQBwAGwAZQAgAGQAcgBhAGkAbgBhAGcAZQAsACAAbwByACAAYQBsAHQAZQByAG4AYQB0AGUAIAB3AGUAdAB0AGkAbgBnACAAYQBuAGQAIABkAHIAeQBpAG4AZwApAFwAIgAsADAALgAwADAANQAsACAAXAAiAFIAaQBjAGUAXAAiACwAIABcACIAUwBpAG4AZwBsAGUAIABhAG4AZAAgAG0AdQBsAHQAaQBwAGwAZQAgAGQAcgBhAGkAbgBhAGcAZQAsACAAbwByACAAYQBsAHQAZQByAG4AYQB0AGUAIAB3AGUAdAB0AGkAbgBnACAAYQBuAGQAIABkAHIAeQBpAG4AZwBcACIALAAgAFwAIgBBAG4AeQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAQQBxAHUAYQBjAHUAbAB0AHUAcgBlAFwAIgAsADAALgAwADAAMgA2ACwAIABcACIAQQBxAHUAYQBjAHUAbAB0AHUAcgBlAFwAIgAsACAAXAAiAEEAbgB5AFwAIgAsACAAXAAiAEEAbgB5AFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBGAG8AcgBlAHMAdAByAHkAXAAiACwAMAAuADAAMAAxADgALAAgAFwAIgBGAG8AcgBlAHMAdAByAHkAXAAiACwAIABcACIAQQBuAHkAXAAiACwAIABcACIAQQBuAHkAXAAiAFwAbgAgACAAIAAgACAAIAAgACAAfQAsACAAcgAsACAAYwApAFwAbgAgACAAIAAgACAAIAApAFwAbgAgACAAIAAgACkAXABuACAAIAApADsAXABuAFwAbgAgACAAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAE4AMgBPAF8AVgBhAHIAaQBhAHQAaQBvAG4AXABuACAAIAA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAATQBBAEsARQBBAFIAUgBBAFkAKAA1ACwAIAAxACwAIABcAG4AIAAgACAAIAAgACAATABBAE0AQgBEAEEAKAByACwAYwAsACAAXABuACAAIAAgACAAIAAgACAAIABJAE4ARABFAFgAKAB7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBWAEEAUgBJAEEAVABJAE8ATgAgAE8ARgAgAFMATwBVAFIAQwBFACAARABBAFQAQQA6AFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBSAGUAbQBvAHYAZQBkACAAZAB1AHAAbABpAGMAYQB0AGUAIAAnAEEAcQB1AGEAYwB1AGwAdAB1AHIAZQAnACAAcgBvAHcALgBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAUgBlAG0AbwB2AGUAZAAgAGEAcwB0AGUAcgBpAHMAawBzACAAdABvACAAYQBpAGQAIABsAG8AbwBrAHUAcAAuAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBBAGQAZABlAGQAIAAnAHAAcgBvAGQAdQBjAHQAaQBvAG4AIABzAHkAcwB0AGUAbQAgAG8AbgBsAHkAJwAsACAAJwByAGEAaQBuAGYAYQBsAGwAIAB6AG8AbgBlACcAIABhAG4AZAAgACcAaQByAHIAaQBnAGEAdABpAG8AbgAgAG0AZQB0AGgAbwBkACcAIABjAG8AbAB1AG0AbgBzACAAdABvACAAYQBpAGQAIABsAG8AbwBrAHUAcAAuAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBEAHUAcABsAGkAYwBhAHQAZQBkACAAJwBuAG8AbgAtAGkAcgByAGkAZwBhAHQAZQBkACAAcABhAHMAdAB1AHIAZQAnACAAcgBvAHcAIAB3AGkAdABoACAAcwBhAG0AZQAgAEUARgAgAGYAbwByACAAbABvAHcAIABhAG4AZAAgAGgAaQBnAGgAIAByAGEAaQBuAGYAYQBsAGwAIAB6AG8AbgBlAHMAIAB0AG8AIABhAGkAZAAgAGwAbwBvAGsAdQBwAC4AXAAiAFwAbgAgACAAIAAgACAAIAAgACAAfQAsACAAcgAsACAAYwApAFwAbgAgACAAIAAgACAAIAApAFwAbgAgACAAIAAgACkAXABuACAAIAApADsAXABuAFwAbgAvACoAIABcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAHIAYQBjAFcARQBUAEkAcgByAGkAZwBhAHQAaQBvAG4AXABuAFYARQBFAFIARwAgADIAMAAyADYAOgAgAEMAaABhAHAAdABlAHIAIAAxACwAIABzAGUAYwB0AGkAbwBuACAAMQAuADgALgAyACAATABlAGEAYwBoAGkAbgBnACwAIABjAGwAaQBtAGEAdABlACAAYQBuAGQAIAByAGEAaQBuAGYAYQBsAGwAIAB6AG8AbgBlAHMAXABuAEkAUABDAEMAOgAgAE4AMgBPACAARQBNAEkAUwBTAEkATwBOAFMAIABGAFIATwBNACAATQBBAE4AQQBHAEUARAAgAFMATwBJAEwAUwAsACAAQQBOAEQAIABDAE8AMgAgAEUATQBJAFMAUwBJAE8ATgBTACAARgBSAE8ATQAgAEwASQBNAEUAIABBAE4ARAAgAFUAUgBFAEEAIABBAFAAUABMAEkAQwBBAFQASQBPAE4AXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AKgAvAFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgByAGEAYwBXAEUAVABJAHIAcgBpAGcAYQB0AGkAbwBuAF8AVABpAHQAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBGAHIAYQBjAFcARQBUACAAZgBvAHIAIABpAHIAcgBpAGcAYQB0AGkAbwBuACAAdAB5AHAAZQBzAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAHIAYQBjAFcARQBUAEkAcgByAGkAZwBhAHQAaQBvAG4AXwBVAG4AaQB0AFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBkAGkAbQBlAG4AcwBpAG8AbgBsAGUAcwBzAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAHIAYQBjAFcARQBUAEkAcgByAGkAZwBhAHQAaQBvAG4AXwBTAG8AdQByAGMAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAVgBFAEUAUgBHACAAMgAwADIANgA6ACAAQwBoAGEAcAB0AGUAcgAgADEALAAgAHMAZQBjAHQAaQBvAG4AIAAxAC4AOAAuADIAIABMAGUAYQBjAGgAaQBuAGcALAAgAGMAbABpAG0AYQB0AGUAIABhAG4AZAAgAHIAYQBpAG4AZgBhAGwAbAAgAHoAbwBuAGUAcwBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgByAGEAYwBXAEUAVABJAHIAcgBpAGcAYQB0AGkAbwBuAF8ATgBJAFIAUgBlAGYAZQByAGUAbgBjAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAEkAUABDAEMAIAAyADAAMQA5ACAAUgBlAGYAaQBuAGUAbQBlAG4AdAAgAFYAbwBsAHUAbQBlACAANAA6ACAAQwBoAGEAcAB0AGUAcgAgADEAMQA6ACAATgAyAE8AIABFAG0AaQBzAHMAaQBvAG4AcwAgAGYAcgBvAG0AIABNAGEAbgBhAGcAZQBkACAAUwBvAGkAbABzACwAIABhAG4AZAAgAEMATwAyACAARQBtAGkAcwBzAGkAbwBuAHMAIABmAHIAbwBtACAATABpAG0AZQAgAGEAbgBkACAAVQByAGUAYQAgAEEAcABwAGwAaQBjAGEAdABpAG8AbgBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgByAGEAYwBXAEUAVABJAHIAcgBpAGcAYQB0AGkAbwBuAF8ARABhAHQAYQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABNAEEASwBFAEEAUgBSAEEAWQAoADYALAAgADIALAAgAFwAbgAgACAAIAAgACAAIABMAEEATQBCAEQAQQAoAHIALABjACwAIABcAG4AIAAgACAAIAAgACAAIAAgAEkATgBEAEUAWAAoAHsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEkAcgByAGkAZwBhAHQAaQBvAG4AIAB0AHkAcABlACAAaQByAFwAIgAsAFwAIgBGAHIAYQBjAFcARQBUAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBOAG8AdAAgAGkAcgByAGkAZwBhAHQAZQBkAFwAIgAsACAAMAA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBEAHIAaQBwACAAaQByAHIAaQBnAGEAdABpAG8AbgBcACIALAAgADAAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAUwBwAHIAaQBuAGsAbABlAHIAIABpAHIAcgBpAGcAYQB0AGkAbwBuAFwAIgAsACAAMQA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBTAHUAcgBmAGEAYwBlACAAaQByAHIAaQBnAGEAdABpAG8AbgBcACIALAAgADEAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIATwB0AGgAZQByACAAaQByAHIAaQBnAGEAdABpAG8AbgBcACIALAAgADEAXABuACAAIAAgACAAIAAgACAAIAB9ACwAIAByACwAIABjACkAXABuACAAIAAgACAAIAAgACkAXABuACAAIAAgACAAKQBcAG4AIAAgACkAOwBcAG4AXABuACAAIABDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAHIAYQBjAFcARQBUAEkAcgByAGkAZwBhAHQAaQBvAG4AXwBWAGEAcgBpAGEAdABpAG8AbgBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAVgBBAFIASQBBAFQASQBPAE4AIABGAFIATwBNACAAUwBPAFUAUgBDAEUAIABEAEEAVABBADoAIABUAGEAYgBsAGUAIABjAHIAZQBhAHQAZQBkACAAYgBhAHMAZQBkACAAbwBuACAAVgBFAEUAUgBHACAAdABlAHgAdAAgACcAQQByAGUAYQBzACAAYQByAGUAIABzAHUAYgBqAGUAYwB0ACAAdABvACAAbABlAGEAYwBoAGkAbgBnACAAKABpAC4AZQAuACwAIABpAG4AIAB0AGgAZQAgAGwAZQBhAGMAaABpAG4AZwAgAHoAbwBuAGUAKQAgAHcAaABlAG4ALgAuAC4AIAB0AGgAZQAgAGwAYQBuAGQAIABpAHMAIABpAHIAcgBpAGcAYQB0AGUAZAAgACgAZQB4AGMAZQBwAHQAIABkAHIAaQBwACAAaQByAHIAaQBnAGEAdABpAG8AbgApAC4AJwBcACIAKQA7AFwAbgBcAG4AXABuAC8AKgAgAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEUARgBQAGEAcwB0AHUAcgBlAFIAYQBuAGcAZQBBAG4AZABQAGEAZABkAG8AYwBrAFwAbgBUAGEAYgBsAGUAIABBAC4AMgAuADIALgAyADoAIABFAG0AaQBzAHMAaQBvAG4AIABmAGEAYwB0AG8AcgAgAGYAbwByACAAdQByAGkAbgBlACAAYQBuAGQAIABkAHUAbgBnACAAZABlAHAAbwBzAGkAdABlAGQAIABvAG4AIABwAGEAcwB0AHUAcgBlACwAIAByAGEAbgBnAGUAIABvAHIAIABwAGEAZABkAG8AYwBrACAAKABrAGcAIABOADIATwAtAE4ALwBrAGcAIABOACkAIAAoAEUARgBQAFIAUAApAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuACoALwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEUARgBQAGEAcwB0AHUAcgBlAFIAYQBuAGcAZQBBAG4AZABQAGEAZABkAG8AYwBrAF8AVABpAHQAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBFAG0AaQBzAHMAaQBvAG4AIABmAGEAYwB0AG8AcgAgAGYAbwByACAAdQByAGkAbgBlACAAYQBuAGQAIABkAHUAbgBnACAAZABlAHAAbwBzAGkAdABlAGQAIABvAG4AIABwAGEAcwB0AHUAcgBlACwAIAByAGEAbgBnAGUAIABvAHIAIABwAGEAZABkAG8AYwBrAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYAUABhAHMAdAB1AHIAZQBSAGEAbgBnAGUAQQBuAGQAUABhAGQAZABvAGMAawBfAFUAbgBpAHQAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAGsAZwAgAE4AMgBPACAALQAgAE4AIAAvACAAawBnACAATgBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAFAAYQBzAHQAdQByAGUAUgBhAG4AZwBlAEEAbgBkAFAAYQBkAGQAbwBjAGsAXwBTAG8AdQByAGMAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAVgBFAEUAUgBHACAAMgAwADIANgA6ACAAVABhAGIAbABlACAAQQAuADIALgAyAC4AMgBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAFAAYQBzAHQAdQByAGUAUgBhAG4AZwBlAEEAbgBkAFAAYQBkAGQAbwBjAGsAXwBOAEkAUgBSAGUAZgBlAHIAZQBuAGMAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEUARgBQAGEAcwB0AHUAcgBlAFIAYQBuAGcAZQBBAG4AZABQAGEAZABkAG8AYwBrAF8ARABhAHQAYQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABNAEEASwBFAEEAUgBSAEEAWQAoADMALAAgADIALAAgAFwAbgAgACAAIAAgACAAIABMAEEATQBCAEQAQQAoAHIALABjACwAIABcAG4AIAAgACAAIAAgACAAIAAgAEkATgBEAEUAWAAoAHsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEMAbABpAG0AYQB0AGUAIAB6AG8AbgBlAFwAIgAsACAAXAAiAEUARgBQAFIAUABcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVwBlAHQAIABjAGwAaQBtAGEAdABlACAAegBvAG4AZQBcACIALAAgADAALgAwADAANgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBEAHIAeQAgAGMAbABpAG0AYQB0AGUAIAB6AG8AbgBlAFwAIgAsACAAMAAuADAAMAAyAFwAbgAgACAAIAAgACAAIAAgACAAfQAsACAAcgAsACAAYwApAFwAbgAgACAAIAAgACAAIAApAFwAbgAgACAAIAAgACkAXABuACAAIAApADsAXABuAFwAbgAgACAAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAFAAYQBzAHQAdQByAGUAUgBhAG4AZwBlAEEAbgBkAFAAYQBkAGQAbwBjAGsAXwBWAGEAcgBpAGEAdABpAG8AbgBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAVgBBAFIASQBBAFQASQBPAE4AIABGAFIATwBNACAAUwBPAFUAUgBDAEUAIABEAEEAVABBADoAIABDAGgAYQBuAGcAZQBkACAAJwBEAHIAeQAgAGMAbABpAG0AYQB0AGUAIAB6AG8AbgBlAHMAJwAgAHQAbwAgAHMAaQBuAGcAdQBsAGEAcgAgACcARAByAHkAIABjAGwAaQBtAGEAdABlACAAegBvAG4AZQAnACAAdABvACAAYQBpAGQAIABsAG8AbwBrAHUAcAAuAFwAIgApADsAXABuAFwAbgBcAG4ALwAqACAAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ATQBvAG4AdABoAHMAVABvAFMAZQBhAHMAbwBuAHMAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AKgAvAFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ATQBvAG4AdABoAHMAVABvAFMAZQBhAHMAbwBuAHMAXwBUAGkAdABsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAE0AbwBuAHQAaABzACAAdABvACAAUwBlAGEAcwBvAG4AcwAgAE0AYQBwAHAAaQBuAGcAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAE0AbwBuAHQAaABzAFQAbwBTAGUAYQBzAG8AbgBzAF8AVQBuAGkAdABcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAE0AbwBuAHQAaABzAFQAbwBTAGUAYQBzAG8AbgBzAF8AUwBvAHUAcgBjAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBNAG8AbgB0AGgAcwBUAG8AUwBlAGEAcwBvAG4AcwBfAE4ASQBSAFIAZQBmAGUAcgBlAG4AYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ATQBvAG4AdABoAHMAVABvAFMAZQBhAHMAbwBuAHMAXwBEAGEAdABhAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAE0AQQBLAEUAQQBSAFIAQQBZACgAMQAzACwAIAAyACwAIABcAG4AIAAgACAAIAAgACAATABBAE0AQgBEAEEAKAByACwAYwAsACAAXABuACAAIAAgACAAIAAgACAAIABJAE4ARABFAFgAKAB7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBNAG8AbgB0AGgAXAAiACwAIABcACIAUwBlAGEAcwBvAG4AXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEoAYQBuAHUAYQByAHkAXAAiACwAIABcACIAUwB1AG0AbQBlAHIAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEYAZQBiAHIAdQBhAHIAeQBcACIALAAgAFwAIgBTAHUAbQBtAGUAcgBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIATQBhAHIAYwBoAFwAIgAsACAAXAAiAEEAdQB0AHUAbQBuAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBBAHAAcgBpAGwAXAAiACwAIABcACIAQQB1AHQAdQBtAG4AXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAE0AYQB5AFwAIgAsACAAXAAiAEEAdQB0AHUAbQBuAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBKAHUAbgBlAFwAIgAsACAAXAAiAFcAaQBuAHQAZQByAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBKAHUAbAB5AFwAIgAsACAAXAAiAFcAaQBuAHQAZQByAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBBAHUAZwB1AHMAdABcACIALAAgAFwAIgBXAGkAbgB0AGUAcgBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAUwBlAHAAdABlAG0AYgBlAHIAXAAiACwAIABcACIAUwBwAHIAaQBuAGcAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAE8AYwB0AG8AYgBlAHIAXAAiACwAIABcACIAUwBwAHIAaQBuAGcAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAE4AbwB2AGUAbQBiAGUAcgBcACIALAAgAFwAIgBTAHAAcgBpAG4AZwBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIARABlAGMAZQBtAGIAZQByAFwAIgAsACAAXAAiAFMAdQBtAG0AZQByAFwAIgBcAG4AIAAgACAAIAAgACAAIAAgAH0ALAAgAHIALAAgAGMAKQBcAG4AIAAgACAAIAAgACAAKQBcAG4AIAAgACAAIAApAFwAbgAgACAAKQA7AFwAbgBcAG4AIAAgAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAE0AbwBuAHQAaABzAFQAbwBTAGUAYQBzAG8AbgBzAF8AVgBhAHIAaQBhAHQAaQBvAG4AXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFwAIgApADsAXABuAFwAbgBcAG4AXABuAC8AKgAgAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAE0AQwBGAFQAZQBtAHAAZQByAGEAdAB1AHIAZQBaAG8AbgBlAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuACoALwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAE0AQwBGAFQAZQBtAHAAZQByAGEAdAB1AHIAZQBaAG8AbgBlAF8AVABpAHQAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBNAGEAbgB1AHIAZQAgAE0AYQBuAGEAZwBlAG0AZQBuAHQAIAATICAATQBlAHQAaABhAG4AZQAgAGMAbwBuAHYAZQByAHMAaQBvAG4AIABmAGEAYwB0AG8AcgAgAHAAZQByACAAdABlAG0AcABlAHIAYQB0AHUAcgBlACAAegBvAG4AZQAgACgAZgByAGEAYwB0AGkAbwBuACkAIAAoAE0AQwBGAGkAbQApAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBNAEMARgBUAGUAbQBwAGUAcgBhAHQAdQByAGUAWgBvAG4AZQBfAFUAbgBpAHQAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAGYAcgBhAGMAdABpAG8AbgBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ATQBDAEYAVABlAG0AcABlAHIAYQB0AHUAcgBlAFoAbwBuAGUAXwBTAG8AdQByAGMAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAVgBFAEUAUgBHACAAMgAwADIANgA6ACAAVABhAGIAbABlACAAQQAuADEALgA4AC4AMQBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ATQBDAEYAVABlAG0AcABlAHIAYQB0AHUAcgBlAFoAbwBuAGUAXwBEAGEAdABhAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAE0AQQBLAEUAQQBSAFIAQQBZACgAMgAyACwAIAAxADYALAAgAFwAbgAgACAAIAAgACAAIABMAEEATQBCAEQAQQAoAHIALABjACwAIABcAG4AIAAgACAAIAAgACAAIAAgAEkATgBEAEUAWAAoAHsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFQAZQBtAHAAZQByAGEAdAB1AHIAZQAgAHoAbwBuAGUAXAAiACwAIABcACIATQBBAFQAIAAoALoAQwApAFwAIgAsACAAXAAiAFUAbgBjAG8AdgBlAHIAZQBkACAAYQBuAGUAcgBvAGIAaQBjACAAbABhAGcAbwBvAG4AXAAiACwAIABcACIAQwBvAHYAZQByAGUAZAAgAGwAYQBnAG8AbwBuAFwAIgAsACAAXAAiAEwAaQBxAHUAaQBkACAAUwBsAHUAcgByAHkAIAAoAHcAaQB0AGgAbwB1AHQAIABuAGEAdAB1AHIAYQBsACAAYwByAHUAcwB0ACkAXAAiACwAIABcACIARABhAGkAbAB5ACAAcwBwAHIAZQBhAGQAIAAoAGIAKQBcACIALAAgAFwAIgBDAG8AbQBwAG8AcwB0AGkAbgBnACAAKABwAGEAcwBzAGkAdgBlACAAdwBpAG4AZAByAG8AdwApAFwAIgAsACAAXAAiAFMAbwBsAGkAZAAgAFMAdABvAHIAYQBnAGUAXAAiACwAIABcACIAUABpAHQAIABTAHQAbwByAGEAZwBlACAAPAAxACAAbQBvAG4AdABoAFwAIgAsACAAXAAiAEQAZQBlAHAAIABMAGkAdAB0AGUAcgBcACIALAAgAFwAIgBQAG8AdQBsAHQAcgB5ACAATQBhAG4AdQByAGUAIAAoAHcAaQB0AGgALwB3AGkAdABoAG8AdQB0ACAAbABpAHQAdABlAHIAKQBcACIALAAgAFwAIgBcACIALAAgAFwAIgBEAGkAcgBlAGMAdAAgAHAAcgBvAGMAZQBzAHMAaQBuAGcAIABpAG4AdABvACAAcABlAGwAbABlAHQAaQB6AGUAZAAgAGYAZQByAHQAaQBsAGkAcwBlAHIAXAAiACwAIABcACIARABpAHIAZQBjAHQAIABhAHAAcABsAGkAYwBhAHQAaQBvAG4AIAB0AG8AIABzAG8AaQBsAFwAIgAsACAAXAAiAFAAYQBzAHQAdQByAGUALAAgAFIAYQBuAGcAZQAgAGEAbgBkACAAUABhAGQAZABvAGMAawAgACgAYwApACgAZAApAFwAIgAsACAAXAAiAE0AQQBUACAAcgBhAHcAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEMAbwBvAGwAXAAiACwAIABcACIAZCIxADAAXAAiACwAIAAwAC4ANgA2ACwAIAAwAC4AMQAsACAAMAAuADEALAAgADAALgAwADAAMQAsACAAMAAuADAAMAA1ACwAIAAwAC4AMAAyACwAIAAwAC4AMAAzACwAIAAwAC4AMAA0ACwAIAAwAC4AMAAxADUALAAgADAALgAwADEANQAsACAAMAAsACAAMAAsACAAMAAuADAAMAA0ADcALAAgADEAMAA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBDAG8AbwBsAFwAIgAsACAAMQAxACwAIAAwAC4ANgA4ACwAIAAwAC4AMQAsACAAMAAuADEAMQAsACAAMAAuADAAMAAxACwAIAAwAC4AMAAwADUALAAgADAALgAwADIALAAgADAALgAwADMALAAgADAALgAwADQALAAgADAALgAwADEANQAsACAAMAAuADAAMQA1ACwAIAAwACwAIAAwACwAIAAwAC4AMAAwADQANwAsACAAMQAxADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEMAbwBvAGwAXAAiACwAIAAxADIALAAgADAALgA3ACwAIAAwAC4AMQAsACAAMAAuADEAMwAsACAAMAAuADAAMAAxACwAIAAwAC4AMAAwADUALAAgADAALgAwADIALAAgADAALgAwADMALAAgADAALgAwADQALAAgADAALgAwADEANQAsACAAMAAuADAAMQA1ACwAIAAwACwAIAAwACwAIAAwAC4AMAAwADQANwAsACAAMQAyADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEMAbwBvAGwAXAAiACwAIAAxADMALAAgADAALgA3ADEALAAgADAALgAxACwAIAAwAC4AMQA0ACwAIAAwAC4AMAAwADEALAAgADAALgAwADAANQAsACAAMAAuADAAMgAsACAAMAAuADAAMwAsACAAMAAuADAANAAsACAAMAAuADAAMQA1ACwAIAAwAC4AMAAxADUALAAgADAALAAgADAALAAgADAALgAwADAANAA3ACwAIAAxADMAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAQwBvAG8AbABcACIALAAgADEANAAsACAAMAAuADcAMwAsACAAMAAuADEALAAgADAALgAxADUALAAgADAALgAwADAAMQAsACAAMAAuADAAMAA1ACwAIAAwAC4AMAAyACwAIAAwAC4AMAAzACwAIAAwAC4AMAA0ACwAIAAwAC4AMAAxADUALAAgADAALgAwADEANQAsACAAMAAsACAAMAAsACAAMAAuADAAMAA0ADcALAAgADEANAA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBUAGUAbQBwAGUAcgBhAHQAZQBcACIALAAgADEANQAsACAAMAAuADcANAAsACAAMAAuADEALAAgADAALgAxADcALAAgADAALgAwADAANQAsACAAMAAuADAAMQAsACAAMAAuADAAMgAsACAAMAAuADAAMwAsACAAMAAuADAANAAsACAAMAAuADAAMQA1ACwAIAAwAC4AMAAxADUALAAgADAALAAgADAALAAgADAALgAwADAANAA3ACwAIAAxADUAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVABlAG0AcABlAHIAYQB0AGUAXAAiACwAIAAxADYALAAgADAALgA3ADUALAAgADAALgAxACwAIAAwAC4AMQA4ACwAIAAwAC4AMAAwADUALAAgADAALgAwADEALAAgADAALgAwADIALAAgADAALgAwADMALAAgADAALgAwADQALAAgADAALgAwADEANQAsACAAMAAuADAAMQA1ACwAIAAwACwAIAAwACwAIAAwAC4AMAAwADQANwAsACAAMQA2ADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFQAZQBtAHAAZQByAGEAdABlAFwAIgAsACAAMQA3ACwAIAAwAC4ANwA2ACwAIAAwAC4AMQAsACAAMAAuADIALAAgADAALgAwADAANQAsACAAMAAuADAAMQAsACAAMAAuADAAMgAsACAAMAAuADAAMwAsACAAMAAuADAANAAsACAAMAAuADAAMQA1ACwAIAAwAC4AMAAxADUALAAgADAALAAgADAALAAgADAALgAwADAANAA3ACwAIAAxADcAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVABlAG0AcABlAHIAYQB0AGUAXAAiACwAIAAxADgALAAgADAALgA3ADcALAAgADAALgAxACwAIAAwAC4AMgAyACwAIAAwAC4AMAAwADUALAAgADAALgAwADEALAAgADAALgAwADIALAAgADAALgAwADMALAAgADAALgAwADQALAAgADAALgAwADEANQAsACAAMAAuADAAMQA1ACwAIAAwACwAIAAwACwAIAAwAC4AMAAwADQANwAsACAAMQA4ADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFQAZQBtAHAAZQByAGEAdABlAFwAIgAsACAAMQA5ACwAIAAwAC4ANwA3ACwAIAAwAC4AMQAsACAAMAAuADIANAAsACAAMAAuADAAMAA1ACwAIAAwAC4AMAAxACwAIAAwAC4AMAAyACwAIAAwAC4AMAAzACwAIAAwAC4AMAA0ACwAIAAwAC4AMAAxADUALAAgADAALgAwADEANQAsACAAMAAsACAAMAAsACAAMAAuADAAMAA0ADcALAAgADEAOQA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBUAGUAbQBwAGUAcgBhAHQAZQBcACIALAAgADIAMAAsACAAMAAuADcAOAAsACAAMAAuADEALAAgADAALgAyADYALAAgADAALgAwADAANQAsACAAMAAuADAAMQAsACAAMAAuADAAMgAsACAAMAAuADAAMwAsACAAMAAuADAANAAsACAAMAAuADAAMQA1ACwAIAAwAC4AMAAxADUALAAgADAALAAgADAALAAgADAALgAwADAANAA3ACwAIAAyADAAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVABlAG0AcABlAHIAYQB0AGUAXAAiACwAIAAyADEALAAgADAALgA3ADgALAAgADAALgAxACwAIAAwAC4AMgA5ACwAIAAwAC4AMAAwADUALAAgADAALgAwADEALAAgADAALgAwADIALAAgADAALgAwADMALAAgADAALgAwADQALAAgADAALgAwADEANQAsACAAMAAuADAAMQA1ACwAIAAwACwAIAAwACwAIAAwAC4AMAAwADQANwAsACAAMgAxADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFQAZQBtAHAAZQByAGEAdABlAFwAIgAsACAAMgAyACwAIAAwAC4ANwA4ACwAIAAwAC4AMQAsACAAMAAuADMAMQAsACAAMAAuADAAMAA1ACwAIAAwAC4AMAAxACwAIAAwAC4AMAAyACwAIAAwAC4AMAAzACwAIAAwAC4AMAA0ACwAIAAwAC4AMAAxADUALAAgADAALgAwADEANQAsACAAMAAsACAAMAAsACAAMAAuADAAMAA0ADcALAAgADIAMgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBUAGUAbQBwAGUAcgBhAHQAZQBcACIALAAgADIAMwAsACAAMAAuADcAOQAsACAAMAAuADEALAAgADAALgAzADQALAAgADAALgAwADAANQAsACAAMAAuADAAMQAsACAAMAAuADAAMgAsACAAMAAuADAAMwAsACAAMAAuADAANAAsACAAMAAuADAAMQA1ACwAIAAwAC4AMAAxADUALAAgADAALAAgADAALAAgADAALgAwADAANAA3ACwAIAAyADMAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVABlAG0AcABlAHIAYQB0AGUAXAAiACwAIAAyADQALAAgADAALgA3ADkALAAgADAALgAxACwAIAAwAC4AMwA3ACwAIAAwAC4AMAAwADUALAAgADAALgAwADEALAAgADAALgAwADIALAAgADAALgAwADMALAAgADAALgAwADQALAAgADAALgAwADEANQAsACAAMAAuADAAMQA1ACwAIAAwACwAIAAwACwAIAAwAC4AMAAwADQANwAsACAAMgA0ADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFQAZQBtAHAAZQByAGEAdABlAFwAIgAsACAAMgA1ACwAIAAwAC4ANwA5ACwAIAAwAC4AMQAsACAAMAAuADQAMQAsACAAMAAuADAAMAA1ACwAIAAwAC4AMAAxACwAIAAwAC4AMAAyACwAIAAwAC4AMAAzACwAIAAwAC4AMAA0ACwAIAAwAC4AMAAxADUALAAgADAALgAwADEANQAsACAAMAAsACAAMAAsACAAMAAuADAAMAA0ADcALAAgADIANQA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBXAGEAcgBtAFwAIgAsACAAMgA2ACwAIAAwAC4ANwA5ACwAIAAwAC4AMQAsACAAMAAuADQANAAsACAAMAAuADAAMQAsACAAMAAuADAAMQA1ACwAIAAwAC4AMAAyACwAIAAwAC4AMAAzACwAIAAwAC4AMAA0ACwAIAAwAC4AMAAxADUALAAgADAALgAwADEANQAsACAAMAAsACAAMAAsACAAMAAuADAAMAA0ADcALAAgADIANgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBXAGEAcgBtAFwAIgAsACAAMgA3ACwAIAAwAC4AOAAsACAAMAAuADEALAAgADAALgA0ADgALAAgADAALgAwADEALAAgADAALgAwADEANQAsACAAMAAuADAAMgAsACAAMAAuADAAMwAsACAAMAAuADAANAAsACAAMAAuADAAMQA1ACwAIAAwAC4AMAAxADUALAAgADAALAAgADAALAAgADAALgAwADAANAA3ACwAIAAyADcAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVwBhAHIAbQBcACIALAAgAFwAIgBlIjIAOABcACIALAAgADAALgA4ACwAIAAwAC4AMQAsACAAMAAuADUALAAgADAALgAwADEALAAgADAALgAwADEANQAsACAAMAAuADAAMgAsACAAMAAuADAAMwAsACAAMAAuADAANAAsACAAMAAuADAAMQA1ACwAIAAwAC4AMAAxADUALAAgADAALAAgADAALAAgADAALgAwADAANAA3ACwAIAAyADgAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAXAAiACwAIABcACIAXAAiACwAIABcACIAQQBuAGEAZQByAG8AYgBpAGMAIABsAGEAZwBvAG8AbgBcACIALAAgAFwAIgBEAGkAZwBlAHMAdABlAHIAIAAvACAAYwBvAHYAZQByAGUAZAAgAGwAYQBnAG8AbwBuAHMAXAAiACwAIABcACIATABpAHEAdQBpAGQAIABzAHkAcwB0AGUAbQBzAFwAIgAsACAAXAAiAEQAYQBpAGwAeQAgAHMAcAByAGUAYQBkAFwAIgAsACAAXAAiAEMAbwBtAHAAbwBzAHQAaQBuAGcAIAAoAHAAYQBzAHMAaQB2AGUAIAB3AGkAbgBkAHIAbwB3ACkAXAAiACwAIABcACIAUwBvAGwAaQBkACAAcwB0AG8AcgBhAGcAZQBcACIALAAgAFwAIgBQAGkAdAAgAHMAdABvAHIAYQBnAGUAXAAiACwAIABcACIARABlAGUAcAAgAGwAaQB0AHQAZQByAFwAIgAsACAAXAAiAFAAbwB1AGwAdAByAHkAIABtAGEAbgB1AHIAZQAgAHcAaQB0AGgAIABiAGUAZABkAGkAbgBnAFwAIgAsACAAXAAiAFAAbwB1AGwAdAByAHkAIABtAGEAbgB1AHIAZQAgAHcAaQB0AGgAbwB1AHQAIABiAGUAZABkAGkAbgBnAFwAIgAsACAAXAAiAEQAaQByAGUAYwB0ACAAcAByAG8AYwBlAHMAcwBpAG4AZwBcACIALAAgAFwAIgBEAGkAcgBlAGMAdAAgAGEAcABwAGwAaQBjAGEAdABpAG8AbgBcACIALAAgAFwAIgBQAGEAcwB0AHUAcgBlACAAcgBhAG4AZwBlACAAYQBuAGQAIABwAGEAZABkAG8AYwBrAFwAIgAsACAAXAAiAE0AQQBUACAAcgBhAHcAXAAiACAAXABuACAAIAAgACAAIAAgACAAIAB9ACwAIAByACwAIABjACkAXABuACAAIAAgACAAIAAgACkAXABuACAAIAAgACAAKQBcAG4AIAAgACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAE0AQwBGAFQAZQBtAHAAZQByAGEAdAB1AHIAZQBaAG8AbgBlAF8AVgBhAHIAaQBhAHQAaQBvAG4AXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFYAQQBSAEkAQQBUAEkATwBOACAARgBSAE8ATQAgAFMATwBVAFIAQwBFADoAIABBAGQAZABlAGQAIAByAG8AdwAgAG8AZgAgAE4ASQBSACAATQBNAEEAIABkAGUAZgBpAG4AaQB0AGkAbwBuAHMAIAB0AG8AIABhAGkAZAAgAGwAbwBvAGsAdQBwAC4AIABEAHUAcABsAGkAYwBhAHQAZQBkACAAJwBQAG8AdQBsAHQAcgB5ACAAdwBpAHQAaAAgAGEAbgBkACAAdwBpAHQAaABvAHUAdAAgAGwAaQB0AHQAZQByACcAIABjAG8AbAB1AG0AbgAgAHcAaQB0AGgAIABzAGUAcABhAHIAYQB0AGUAIABOAEkAUgAgAGQAZQBmAGkAbgBpAHQAaQBvAG4AcwAgAHQAbwAgAGEAaQBkACAAbABvAG8AawB1AHAALgAgAEEAZABkAGUAZAAgACcATQBBAFQAIAByAGEAdwAnACAAYwBvAGwAdQBtAG4AIAB0AG8AIABhAGwAbABvAHcAIABsAG8AbwBrAHUAcAAgAG8AZgAgAG4AdQBtAGIAZQByAHMALgBcACIAKQA7AFwAbgBcAG4AXABuAFwAbgAvACoAIABcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYATwByAGcAYQBuAGkAYwBGAGUAcgB0AGkAbABpAHMAZQByAEEAbgBkAEMAcgBvAHAAUgBlAHMAaQBkAHUAZQBzAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuACoALwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEUARgBPAHIAZwBhAG4AaQBjAEYAZQByAHQAaQBsAGkAcwBlAHIAQQBuAGQAQwByAG8AcABSAGUAcwBpAGQAdQBlAHMAXwBUAGkAdABsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAEUAbQBpAHMAcwBpAG8AbgAgAGYAYQBjAHQAbwByACAAZgBvAHIAIABvAHIAZwBhAG4AaQBjACAAZgBlAHIAdABpAGwAaQBzAGUAcgAgAGEAbgBkACAAYwByAG8AcAAgAHIAZQBzAGkAZAB1AGUAcwAgAHIAZQB0AHUAcgBuAGUAZAAgAHQAbwAgAHQAaABlACAAcwBvAGkAbABcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAE8AcgBnAGEAbgBpAGMARgBlAHIAdABpAGwAaQBzAGUAcgBBAG4AZABDAHIAbwBwAFIAZQBzAGkAZAB1AGUAcwBfAFYAYQByAGkAYQBiAGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIARQBGAE4AaQAgACYAIABFAEYATgAyAE8AaQBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAE8AcgBnAGEAbgBpAGMARgBlAHIAdABpAGwAaQBzAGUAcgBBAG4AZABDAHIAbwBwAFIAZQBzAGkAZAB1AGUAcwBfAFUAbgBpAHQAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAGsAZwAgAE4AMgBPACAALQAgAE4AIAAvACAAawBnACAATgBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAE8AcgBnAGEAbgBpAGMARgBlAHIAdABpAGwAaQBzAGUAcgBBAG4AZABDAHIAbwBwAFIAZQBzAGkAZAB1AGUAcwBfAFMAbwB1AHIAYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBWAEUARQBSAEcAIAAyADAAMgA2ADoAIABUAGEAYgBsAGUAIABBAC4AMgAuADEALgA0AFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYATwByAGcAYQBuAGkAYwBGAGUAcgB0AGkAbABpAHMAZQByAEEAbgBkAEMAcgBvAHAAUgBlAHMAaQBkAHUAZQBzAF8ATgBJAFIAUgBlAGYAZQByAGUAbgBjAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYATwByAGcAYQBuAGkAYwBGAGUAcgB0AGkAbABpAHMAZQByAEEAbgBkAEMAcgBvAHAAUgBlAHMAaQBkAHUAZQBzAF8ARABhAHQAYQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABNAEEASwBFAEEAUgBSAEEAWQAoADMALAAgADIALAAgAFwAbgAgACAAIAAgACAAIABMAEEATQBCAEQAQQAoAHIALABjACwAIABcAG4AIAAgACAAIAAgACAAIAAgAEkATgBEAEUAWAAoAHsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEMAbABpAG0AYQB0AGUAIAB6AG8AbgBlAFwAIgAsACAAXAAiAEUARgBOAGkAIAAmACAARQBGAE4AMgBPAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBXAGUAdAAgAGMAbABpAG0AYQB0AGUAIAB6AG8AbgBlAFwAIgAsACAAMAAuADAAMAA2ADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEQAcgB5ACAAYwBsAGkAbQBhAHQAZQAgAHoAbwBuAGUAXAAiACwAIAAwAC4AMAAwADUAXABuACAAIAAgACAAIAAgACAAIAB9ACwAIAByACwAIABjACkAXABuACAAIAAgACAAIAAgACkAXABuACAAIAAgACAAKQBcAG4AIAAgACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEUARgBPAHIAZwBhAG4AaQBjAEYAZQByAHQAaQBsAGkAcwBlAHIAQQBuAGQAQwByAG8AcABSAGUAcwBpAGQAdQBlAHMAXwBWAGEAcgBpAGEAdABpAG8AbgBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAXAAiACkAOwBcAG4AXABuAFwAbgBcAG4AXABuAFwAbgBcAG4AXABuAFwAbgBcAG4AXABuAFwAbgBcAG4AXABuAFwAbgBcAG4AXABuACIAfQBdACwAIgBwAHIAbwBqAGUAYwB0AE4AYQBtAGUAcwAiADoAWwAiAEMAbwBtAG0AbwBuAF8ARQBxAHUAYQB0AGkAbwBuAHMALgBDAG8AbQBtAG8AbgBfAEMAbwBuAHYAZQByAHQATgAyAE8AVABvAEMATwAyAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBFAHEAdQBhAHQAaQBvAG4AcwAuAEMAbwBtAG0AbwBuAF8AQwBvAG4AdgBlAHIAdABOADIATwBUAG8AQwBPADIAZQBfAFQAaQB0AGwAZQAiACwAIgBDAG8AbQBtAG8AbgBfAEUAcQB1AGEAdABpAG8AbgBzAC4AQwBvAG0AbQBvAG4AXwBDAG8AbgB2AGUAcgB0AE4AMgBPAFQAbwBDAE8AMgBlAF8AVgBhAHIAaQBhAGIAbABlACIALAAiAEMAbwBtAG0AbwBuAF8ARQBxAHUAYQB0AGkAbwBuAHMALgBDAG8AbQBtAG8AbgBfAEMAbwBuAHYAZQByAHQATgAyAE8AVABvAEMATwAyAGUAXwBVAG4AaQB0ACIALAAiAEMAbwBtAG0AbwBuAF8ARQBxAHUAYQB0AGkAbwBuAHMALgBDAG8AbQBtAG8AbgBfAEMAbwBuAHYAZQByAHQATgAyAE8AVABvAEMATwAyAGUAXwBOAEkAUgBSAGUAZgBlAHIAZQBuAGMAZQAiACwAIgBDAG8AbQBtAG8AbgBfAEUAcQB1AGEAdABpAG8AbgBzAC4AQwBvAG0AbQBvAG4AXwBDAG8AbgB2AGUAcgB0AE4AMgBPAFQAbwBDAE8AMgBlAF8ATABhAHQAZQB4AEUAcQB1AGEAdABpAG8AbgAiACwAIgBDAG8AbQBtAG8AbgBfAEUAcQB1AGEAdABpAG8AbgBzAC4AQwBvAG0AbQBvAG4AXwBDAG8AbgB2AGUAcgB0AE4AMgBPAFQAbwBDAE8AMgBlAF8AQQByAGcAdQBtAGUAbgB0AHMAIgAsACIAQwBvAG0AbQBvAG4AXwBFAHEAdQBhAHQAaQBvAG4AcwAuAEMAbwBtAG0AbwBuAF8AQwBvAG4AdgBlAHIAdABDAEgANABUAG8AQwBPADIAZQAiACwAIgBDAG8AbQBtAG8AbgBfAEUAcQB1AGEAdABpAG8AbgBzAC4AQwBvAG0AbQBvAG4AXwBDAG8AbgB2AGUAcgB0AEMASAA0AFQAbwBDAE8AMgBlAF8AVABpAHQAbABlACIALAAiAEMAbwBtAG0AbwBuAF8ARQBxAHUAYQB0AGkAbwBuAHMALgBDAG8AbQBtAG8AbgBfAEMAbwBuAHYAZQByAHQAQwBIADQAVABvAEMATwAyAGUAXwBWAGEAcgBpAGEAYgBsAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBFAHEAdQBhAHQAaQBvAG4AcwAuAEMAbwBtAG0AbwBuAF8AQwBvAG4AdgBlAHIAdABDAEgANABUAG8AQwBPADIAZQBfAFUAbgBpAHQAIgAsACIAQwBvAG0AbQBvAG4AXwBFAHEAdQBhAHQAaQBvAG4AcwAuAEMAbwBtAG0AbwBuAF8AQwBvAG4AdgBlAHIAdABDAEgANABUAG8AQwBPADIAZQBfAE4ASQBSAFIAZQBmAGUAcgBlAG4AYwBlACIALAAiAEMAbwBtAG0AbwBuAF8ARQBxAHUAYQB0AGkAbwBuAHMALgBDAG8AbQBtAG8AbgBfAEMAbwBuAHYAZQByAHQAQwBIADQAVABvAEMATwAyAGUAXwBMAGEAdABlAHgARQBxAHUAYQB0AGkAbwBuACIALAAiAEMAbwBtAG0AbwBuAF8ARQBxAHUAYQB0AGkAbwBuAHMALgBDAG8AbQBtAG8AbgBfAEMAbwBuAHYAZQByAHQAQwBIADQAVABvAEMATwAyAGUAXwBBAHIAZwB1AG0AZQBuAHQAcwAiACwAIgBDAG8AbQBtAG8AbgBfAEkAbgBwAHUAdABGAHUAbgBjAHQAaQBvAG4AcwAuAFUAdABpAGwAaQB0AHkAXwBHAGUAdABBAHIAcgBhAHkAVABhAGIAbABlAFIAbwB3AFMAdABhAHIAdABOAHUAbQBiAGUAcgAiACwAIgBDAG8AbQBtAG8AbgBfAEkAbgBwAHUAdABGAHUAbgBjAHQAaQBvAG4AcwAuAFUAdABpAGwAaQB0AHkAXwBHAGUAdABBAHIAcgBhAHkAVABhAGIAbABlAEMAbwBsAHUAbQBuAFMAdABhAHIAdABOAHUAbQBiAGUAcgAiACwAIgBDAG8AbQBtAG8AbgBfAEkAbgBwAHUAdABGAHUAbgBjAHQAaQBvAG4AcwAuAFUAdABpAGwAaQB0AHkAXwBEAGkAcwBwAGwAYQB5AEEAcgByAGEAeQBJAG4AVABhAGIAbABlACIALAAiAEMAbwBtAG0AbwBuAF8ASQBuAHAAdQB0AEYAdQBuAGMAdABpAG8AbgBzAC4AVQB0AGkAbABpAHQAeQBfAEwAbwBvAGsAdQBwAFYAYQBsAHUAZQBJAG4AVABhAGIAbABlACIALAAiAEMAbwBtAG0AbwBuAF8ASQBuAHAAdQB0AEYAdQBuAGMAdABpAG8AbgBzAC4AVQB0AGkAbABpAHQAeQBfAEwAbwBvAGsAdQBwAFYAYQBsAHUAZQBJAG4AVABhAGIAbABlAE4AdQBtAGIAZQByACIALAAiAEMAbwBtAG0AbwBuAF8ASQBuAHAAdQB0AEYAdQBuAGMAdABpAG8AbgBzAC4AVQB0AGkAbABpAHQAeQBfAEwAbwBvAGsAdQBwAFYAYQBsAHUAZQBJAG4AVABhAGIAbABlAFQAdwBvAEMAbwBsAHUAbQBuAHMAIgAsACIAQwBvAG0AbQBvAG4AXwBJAG4AcAB1AHQARgB1AG4AYwB0AGkAbwBuAHMALgBVAHQAaQBsAGkAdAB5AF8ATABvAG8AawB1AHAAVgBhAGwAdQBlAEkAbgBUAGEAYgBsAGUATwBuAGUAQwBvAGwAdQBtAG4AQQBuAGQASABlAGEAZABlAHIAIgAsACIAQwBvAG0AbQBvAG4AXwBJAG4AcAB1AHQARgB1AG4AYwB0AGkAbwBuAHMALgBVAHQAaQBsAGkAdAB5AF8AUwBwAGwAaQB0AFMAdAByAGkAbgBnAEkAbgB0AG8AQQByAHIAYQB5ACIALAAiAEMAbwBtAG0AbwBuAF8ASQBuAHAAdQB0AEYAdQBuAGMAdABpAG8AbgBzAC4AVQB0AGkAbABpAHQAeQBfAEcAZQB0AEMAbABpAG0AYQB0AGUAWgBvAG4AZQAiACwAIgBDAG8AbQBtAG8AbgBfAEkAbgBwAHUAdABGAHUAbgBjAHQAaQBvAG4AcwAuAFUAdABpAGwAaQB0AHkAXwBMAG8AbwBrAHUAcABJAHQAZQBtAEYAcgBvAG0ATQBpAG4ATQBhAHgAIgAsACIAQwBvAG0AbQBvAG4AXwBJAG4AcAB1AHQARgB1AG4AYwB0AGkAbwBuAHMALgBVAHQAaQBsAGkAdAB5AF8AUwB1AG0AUQB1AGEAbgB0AGkAdAB5AEYAcgBvAG0AQwByAGkAdABlAHIAaQBhACIALAAiAEMAbwBtAG0AbwBuAF8ASQBuAHAAdQB0AEYAdQBuAGMAdABpAG8AbgBzAC4AZwBlAHQATwB2AGUAcgBsAGEAcABwAGkAbgBnAFIAZQBwAG8AcgB0AGkAbgBnAFAAZQByAGkAbwBkAHMAIgAsACIAQwBvAG0AbQBvAG4AXwBJAG4AcAB1AHQARgB1AG4AYwB0AGkAbwBuAHMALgBVAHQAaQBsAGkAdAB5AF8ARABpAHMAcABsAGEAeQBGAHUAbgBjAHQAaQBvAG4ATgBhAG0AZQAiACwAIgBDAG8AbQBtAG8AbgBfAEkAbgBwAHUAdABGAHUAbgBjAHQAaQBvAG4AcwAuAFUAdABpAGwAaQB0AHkAXwBMAG8AbwBrAHUAcABOADIATwBFAEYARgByAG8AbQBQAHIAbwBkAEkAcgByAGkAZwBhAHQAaQBvAG4AUgBhAGkAbgBmAGEAbABsACIALAAiAEMAbwBtAG0AbwBuAF8ASQBuAHAAdQB0AEYAdQBuAGMAdABpAG8AbgBzAC4AQwBvAG0AbQBvAG4AQwByAG8AcABwAGkAbgBnAF8ARwBlAHQARgByAGEAYwBXAEUAVAAiACwAIgBDAG8AbQBtAG8AbgBfAEkAbgBwAHUAdABGAHUAbgBjAHQAaQBvAG4AcwAuAFUAdABpAGwAaQB0AHkAXwBDAG8AbgB2AGUAcgB0AFMAdABhAHQAZQBDAG8AbQBtAG8AbgBOAGEAbQBlAFQAbwBBAGIAYgByAGUAdgBpAGEAdABpAG8AbgAiACwAIgBDAG8AbQBtAG8AbgBfAEkAbgBwAHUAdABGAHUAbgBjAHQAaQBvAG4AcwAuAFUAdABpAGwAaQB0AHkAXwBTAG8AdQByAGMAZQBIAHkAcABlAHIAbABpAG4AawBEAGkAZgBmAGUAcgBlAG4AdABTAGgAZQBlAHQAIgAsACIAQwBvAG0AbQBvAG4AXwBJAG4AcAB1AHQARgB1AG4AYwB0AGkAbwBuAHMALgBVAHQAaQBsAGkAdAB5AF8AUgBlAHMAdQBsAHQAcwBJAHQAZQBtAEYAcgBvAG0ARQBxAHUAYQB0AGkAbwBuAFQAaQB0AGwAZQBBAG4AZABTAG8AdQByAGMAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGUAbgBzAGkAdAB5AE8AZgBNAGUAdABoAGEAbgBlAF8AVABpAHQAbABlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEQAZQBuAHMAaQB0AHkATwBmAE0AZQB0AGgAYQBuAGUAXwBVAG4AaQB0ACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEQAZQBuAHMAaQB0AHkATwBmAE0AZQB0AGgAYQBuAGUAXwBTAG8AdQByAGMAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGUAbgBzAGkAdAB5AE8AZgBNAGUAdABoAGEAbgBlAF8ARABhAHQAYQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBDAG8AbgB2AGUAcgB0AE4AMgBvAEUAbABlAG0AZQBuAHQAYQBsAFQAbwBNAG8AbABlAGMAdQBsAGEAcgBDAGcAXwBUAGkAdABsAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQwBvAG4AdgBlAHIAdABOADIAbwBFAGwAZQBtAGUAbgB0AGEAbABUAG8ATQBvAGwAZQBjAHUAbABhAHIAQwBnAF8AVgBhAHIAaQBhAGIAbABlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEMAbwBuAHYAZQByAHQATgAyAG8ARQBsAGUAbQBlAG4AdABhAGwAVABvAE0AbwBsAGUAYwB1AGwAYQByAEMAZwBfAFUAbgBpAHQAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQwBvAG4AdgBlAHIAdABOADIAbwBFAGwAZQBtAGUAbgB0AGEAbABUAG8ATQBvAGwAZQBjAHUAbABhAHIAQwBnAF8AUwBvAHUAcgBjAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQwBvAG4AdgBlAHIAdABOADIAbwBFAGwAZQBtAGUAbgB0AGEAbABUAG8ATQBvAGwAZQBjAHUAbABhAHIAQwBnAF8ARABhAHQAYQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBDAG8AbgB2AGUAcgB0AEcAYQBzAEUAbABlAG0AZQBuAHQAYQBsAFQAbwBNAG8AbABlAGMAdQBsAGEAcgBfAFQAaQB0AGwAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBDAG8AbgB2AGUAcgB0AEcAYQBzAEUAbABlAG0AZQBuAHQAYQBsAFQAbwBNAG8AbABlAGMAdQBsAGEAcgBfAFYAYQByAGkAYQBiAGwAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBDAG8AbgB2AGUAcgB0AEcAYQBzAEUAbABlAG0AZQBuAHQAYQBsAFQAbwBNAG8AbABlAGMAdQBsAGEAcgBfAFUAbgBpAHQAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQwBvAG4AdgBlAHIAdABHAGEAcwBFAGwAZQBtAGUAbgB0AGEAbABUAG8ATQBvAGwAZQBjAHUAbABhAHIAXwBTAG8AdQByAGMAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBDAG8AbgB2AGUAcgB0AEcAYQBzAEUAbABlAG0AZQBuAHQAYQBsAFQAbwBNAG8AbABlAGMAdQBsAGEAcgBfAEQAYQB0AGEAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARwBXAFAAXwBUAGkAdABsAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARwBXAFAAXwBWAGEAcgBpAGEAYgBsAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARwBXAFAAXwBVAG4AaQB0ACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEcAVwBQAF8AUwBvAHUAcgBjAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARwBXAFAAXwBEAGEAdABhACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEEAdQBzAHQAcgBhAGwAaQBhAG4AUwB0AGEAdABlAHMAVABlAHIAcgBpAHQAbwByAGkAZQBzAF8AVABpAHQAbABlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEEAdQBzAHQAcgBhAGwAaQBhAG4AUwB0AGEAdABlAHMAVABlAHIAcgBpAHQAbwByAGkAZQBzAF8AVgBhAHIAaQBhAGIAbABlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEEAdQBzAHQAcgBhAGwAaQBhAG4AUwB0AGEAdABlAHMAVABlAHIAcgBpAHQAbwByAGkAZQBzAF8AVQBuAGkAdAAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBBAHUAcwB0AHIAYQBsAGkAYQBuAFMAdABhAHQAZQBzAFQAZQByAHIAaQB0AG8AcgBpAGUAcwBfAFMAbwB1AHIAYwBlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEEAdQBzAHQAcgBhAGwAaQBhAG4AUwB0AGEAdABlAHMAVABlAHIAcgBpAHQAbwByAGkAZQBzAF8ARABhAHQAYQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBXAEEAUwBBADQAQQByAGUAYQBzAF8AVABpAHQAbABlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFcAQQBTAEEANABBAHIAZQBhAHMAXwBWAGEAcgBpAGEAYgBsAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AVwBBAFMAQQA0AEEAcgBlAGEAcwBfAFUAbgBpAHQAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AVwBBAFMAQQA0AEEAcgBlAGEAcwBfAFMAbwB1AHIAYwBlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFcAQQBTAEEANABBAHIAZQBhAHMAXwBEAGEAdABhACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFcAZQB0AEEAbgBkAEQAcgB5AFoAbwBuAGUAcwBfAFQAaQB0AGwAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBXAGUAdABBAG4AZABEAHIAeQBaAG8AbgBlAHMAXwBWAGEAcgBpAGEAYgBsAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AVwBlAHQAQQBuAGQARAByAHkAWgBvAG4AZQBzAF8AVQBuAGkAdAAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBXAGUAdABBAG4AZABEAHIAeQBaAG8AbgBlAHMAXwBTAG8AdQByAGMAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBXAGUAdABBAG4AZABEAHIAeQBaAG8AbgBlAHMAXwBWAGEAcgBpAGEAdABpAG8AbgAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBXAGUAdABBAG4AZABEAHIAeQBaAG8AbgBlAHMAXwBEAGEAdABhACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEMAbABpAG0AYQB0AGUAWgBvAG4AZQBzAF8AVABpAHQAbABlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEMAbABpAG0AYQB0AGUAWgBvAG4AZQBzAF8AVgBhAHIAaQBhAGIAbABlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEMAbABpAG0AYQB0AGUAWgBvAG4AZQBzAF8AVQBuAGkAdAAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBDAGwAaQBtAGEAdABlAFoAbwBuAGUAcwBfAFMAbwB1AHIAYwBlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEMAbABpAG0AYQB0AGUAWgBvAG4AZQBzAF8AVgBhAHIAaQBhAHQAaQBvAG4AIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQwBsAGkAbQBhAHQAZQBaAG8AbgBlAHMAXwBEAGEAdABhACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEMAbABpAG0AYQB0AGUAWgBvAG4AZQBzAF8AQQBwAHAAZQBuAGQAaQBjAGUAcwAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBUAGUAbQBwAGUAcgBhAHQAdQByAGUAWgBvAG4AZQBzAF8AVABpAHQAbABlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFQAZQBtAHAAZQByAGEAdAB1AHIAZQBaAG8AbgBlAHMAXwBWAGEAcgBpAGEAYgBsAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AVABlAG0AcABlAHIAYQB0AHUAcgBlAFoAbwBuAGUAcwBfAFUAbgBpAHQAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AVABlAG0AcABlAHIAYQB0AHUAcgBlAFoAbwBuAGUAcwBfAFMAbwB1AHIAYwBlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFQAZQBtAHAAZQByAGEAdAB1AHIAZQBaAG8AbgBlAHMAXwBWAGEAcgBpAGEAdABpAG8AbgAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBUAGUAbQBwAGUAcgBhAHQAdQByAGUAWgBvAG4AZQBzAF8ARABhAHQAYQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBSAGEAaQBuAGYAYQBsAGwAWgBvAG4AZQBzAF8AVABpAHQAbABlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFIAYQBpAG4AZgBhAGwAbABaAG8AbgBlAHMAXwBWAGEAcgBpAGEAYgBsAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AUgBhAGkAbgBmAGEAbABsAFoAbwBuAGUAcwBfAFUAbgBpAHQAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AUgBhAGkAbgBmAGEAbABsAFoAbwBuAGUAcwBfAFMAbwB1AHIAYwBlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFIAYQBpAG4AZgBhAGwAbABaAG8AbgBlAHMAXwBWAGEAcgBpAGEAdABpAG8AbgAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBSAGEAaQBuAGYAYQBsAGwAWgBvAG4AZQBzAF8ARABhAHQAYQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBMAGUAYQBjAGgAaQBuAGcAWgBvAG4AZQBzAF8AVABpAHQAbABlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEwAZQBhAGMAaABpAG4AZwBaAG8AbgBlAHMAXwBWAGEAcgBpAGEAYgBsAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ATABlAGEAYwBoAGkAbgBnAFoAbwBuAGUAcwBfAFUAbgBpAHQAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ATABlAGEAYwBoAGkAbgBnAFoAbwBuAGUAcwBfAFMAbwB1AHIAYwBlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEwAZQBhAGMAaABpAG4AZwBaAG8AbgBlAHMAXwBWAGEAcgBpAGEAdABpAG8AbgAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBMAGUAYQBjAGgAaQBuAGcAWgBvAG4AZQBzAF8ARABhAHQAYQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAHIAYQBjAFcARQBUAF8AVABpAHQAbABlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAcgBhAGMAVwBFAFQAXwBVAG4AaQB0ACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAcgBhAGMAVwBFAFQAXwBTAG8AdQByAGMAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAHIAYQBjAFcARQBUAF8ATgBJAFIAUgBlAGYAZQByAGUAbgBjAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgByAGEAYwBXAEUAVABfAEQAYQB0AGEAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgByAGEAYwBXAEUAVABfAFYAYQByAGkAYQB0AGkAbwBuACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEQAYQB0AGEAUwBjAG8AcgBlAHMAXwBTAGMAbwBwAGUAMwBfAFQAaQB0AGwAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGEAdABhAFMAYwBvAHIAZQBzAF8AUwBjAG8AcABlADMAXwBWAGEAcgBpAGEAYgBsAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABhAHQAYQBTAGMAbwByAGUAcwBfAFMAYwBvAHAAZQAzAF8AVQBuAGkAdAAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGEAdABhAFMAYwBvAHIAZQBzAF8AUwBjAG8AcABlADMAXwBTAG8AdQByAGMAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGEAdABhAFMAYwBvAHIAZQBzAF8AUwBjAG8AcABlADMAXwBWAGEAcgBpAGEAdABpAG8AbgAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGEAdABhAFMAYwBvAHIAZQBzAF8AUwBjAG8AcABlADMAXwBEAGEAdABhACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAcgBhAGMATABFAEEAQwBIAF8AVABpAHQAbABlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAcgBhAGMATABFAEEAQwBIAF8AVQBuAGkAdAAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAHIAYQBjAEwARQBBAEMASABfAFMAbwB1AHIAYwBlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAcgBhAGMATABFAEEAQwBIAF8ATgBJAFIAUgBlAGYAZQByAGUAbgBjAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgByAGEAYwBMAEUAQQBDAEgAXwBEAGEAdABhACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAcgBhAGMATABFAEEAQwBIAF8AVgBhAHIAaQBhAHQAaQBvAG4AIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAGwAZQBhAGMAaABfAFQAaQB0AGwAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYAbABlAGEAYwBoAF8AVQBuAGkAdAAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYAbABlAGEAYwBoAF8AUwBvAHUAcgBjAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAGwAZQBhAGMAaABfAE4ASQBSAFIAZQBmAGUAcgBlAG4AYwBlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEUARgBsAGUAYQBjAGgAXwBEAGEAdABhACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEUARgBsAGUAYQBjAGgAXwBWAGEAcgBpAGEAdABpAG8AbgAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYATgAyAE8AXwBUAGkAdABsAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAE4AMgBPAF8AVQBuAGkAdAAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYATgAyAE8AXwBTAG8AdQByAGMAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYATgAyAE8AXwBOAEkAUgBSAGUAZgBlAHIAZQBuAGMAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYATgAyAE8AXwBEAGEAdABhACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEUARgBOADIATwBfAFYAYQByAGkAYQB0AGkAbwBuACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAcgBhAGMAVwBFAFQASQByAHIAaQBnAGEAdABpAG8AbgBfAFQAaQB0AGwAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAHIAYQBjAFcARQBUAEkAcgByAGkAZwBhAHQAaQBvAG4AXwBVAG4AaQB0ACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAcgBhAGMAVwBFAFQASQByAHIAaQBnAGEAdABpAG8AbgBfAFMAbwB1AHIAYwBlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAcgBhAGMAVwBFAFQASQByAHIAaQBnAGEAdABpAG8AbgBfAE4ASQBSAFIAZQBmAGUAcgBlAG4AYwBlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAcgBhAGMAVwBFAFQASQByAHIAaQBnAGEAdABpAG8AbgBfAEQAYQB0AGEAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgByAGEAYwBXAEUAVABJAHIAcgBpAGcAYQB0AGkAbwBuAF8AVgBhAHIAaQBhAHQAaQBvAG4AIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAFAAYQBzAHQAdQByAGUAUgBhAG4AZwBlAEEAbgBkAFAAYQBkAGQAbwBjAGsAXwBUAGkAdABsAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAFAAYQBzAHQAdQByAGUAUgBhAG4AZwBlAEEAbgBkAFAAYQBkAGQAbwBjAGsAXwBVAG4AaQB0ACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEUARgBQAGEAcwB0AHUAcgBlAFIAYQBuAGcAZQBBAG4AZABQAGEAZABkAG8AYwBrAF8AUwBvAHUAcgBjAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAFAAYQBzAHQAdQByAGUAUgBhAG4AZwBlAEEAbgBkAFAAYQBkAGQAbwBjAGsAXwBOAEkAUgBSAGUAZgBlAHIAZQBuAGMAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYAUABhAHMAdAB1AHIAZQBSAGEAbgBnAGUAQQBuAGQAUABhAGQAZABvAGMAawBfAEQAYQB0AGEAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAFAAYQBzAHQAdQByAGUAUgBhAG4AZwBlAEEAbgBkAFAAYQBkAGQAbwBjAGsAXwBWAGEAcgBpAGEAdABpAG8AbgAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBNAG8AbgB0AGgAcwBUAG8AUwBlAGEAcwBvAG4AcwBfAFQAaQB0AGwAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBNAG8AbgB0AGgAcwBUAG8AUwBlAGEAcwBvAG4AcwBfAFUAbgBpAHQAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ATQBvAG4AdABoAHMAVABvAFMAZQBhAHMAbwBuAHMAXwBTAG8AdQByAGMAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBNAG8AbgB0AGgAcwBUAG8AUwBlAGEAcwBvAG4AcwBfAE4ASQBSAFIAZQBmAGUAcgBlAG4AYwBlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAE0AbwBuAHQAaABzAFQAbwBTAGUAYQBzAG8AbgBzAF8ARABhAHQAYQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBNAG8AbgB0AGgAcwBUAG8AUwBlAGEAcwBvAG4AcwBfAFYAYQByAGkAYQB0AGkAbwBuACIAXQAsACIAbABvAGMAYQBsAGUAIgA6AHsAIgBsAGkAcwB0AFMAZQBwAGEAcgBhAHQAbwByACIAOgAiACwAIgAsACIAcgBvAHcAUwBlAHAAYQByAGEAdABvAHIAIgA6ACIAOwAiACwAIgBjAG8AbAB1AG0AbgBTAGUAcABhAHIAYQB0AG8AcgAiADoAIgAsACIALAAiAHQAaABvAHUAcwBhAG4AZABzAFMAZQBwAGEAcgBhAHQAbwByACIAOgAiACwAIgAsACIAdABoAG8AdQBzAGEAbgBkAHMAUABvAHMAaQB0AGkAbwBuAHMAIgA6AFsAMwBdACwAIgBkAGUAYwBpAG0AYQBsAFMAZQBwAGEAcgBhAHQAbwByACIAOgAiAC4AIgAsACIAZABhAHQAZQBPAHIAZABlAHIAIgA6ACIARABNAFkAIgAsACIAYwB1AHIAcgBlAG4AYwB5AFMAeQBtAGIAbwBsACIAOgAiACQAIgAsACIAaQBzAEMAdQByAHIAZQBuAGMAeQBTAHkAbQBiAG8AbABMAGUAYQBkACIAOgB0AHIAdQBlACwAIgBpAHMAQwB1AHIAcgBlAG4AYwB5AFMAZQBwAEIAeQBTAHAAYQBjAGUAIgA6AGYAYQBsAHMAZQAsACIAcgBvAHcATABlAHQAdABlAHIAIgA6ACIAUgAiACwAIgBjAG8AbAB1AG0AbgBMAGUAdAB0AGUAcgAiADoAIgBDACIALAAiAHIAYwBMAGUAZgB0AEIAcgBhAGMAawBlAHQAIgA6ACIAWwAiACwAIgByAGMAUgBpAGcAaAB0AEIAcgBhAGMAawBlAHQAIgA6ACIAXQAiACwAIgBzAHQAYQB0AGUAbQBlAG4AdABTAGUAcABhAHIAYQB0AG8AcgAiADoAIgA7ACIALAAiAGwAbwBjAGEAbABlAE4AYQBtAGUAIgA6ACIAZQBuAC0AdQBzACIAfQB9AA==</AFEJSONBlob>
 </file>
 
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{9A9CF321-0D35-4044-BC72-33748FE2B865}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
 </file>
 
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{CD460F9D-420A-4723-B323-396E4D19EC9B}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="09eef6d6-daa8-4301-8f9f-b1ec38079286"/>
-    <ds:schemaRef ds:uri="7291119c-fce9-4911-96ae-b800be5dccd8"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
+<file path=customXml/item4.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <TaxCatchAll xmlns="09eef6d6-daa8-4301-8f9f-b1ec38079286" xsi:nil="true"/>
+    <lcf76f155ced4ddcb4097134ff3c332f xmlns="7291119c-fce9-4911-96ae-b800be5dccd8">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    </lcf76f155ced4ddcb4097134ff3c332f>
+  </documentManagement>
+</p:properties>
 </file>
 
-<file path=customXml/itemProps4.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{809E3D44-A88D-4EBF-A307-6B8CE77A3361}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -11915,4 +11888,31 @@
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{B6BE249C-20B1-4A62-BBCD-F2A46D88BCAB}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.advancedformulaenvironment.officeapps.live.com/afejsonblob/1.0"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{9A9CF321-0D35-4044-BC72-33748FE2B865}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps4.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{CD460F9D-420A-4723-B323-396E4D19EC9B}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="09eef6d6-daa8-4301-8f9f-b1ec38079286"/>
+    <ds:schemaRef ds:uri="7291119c-fce9-4911-96ae-b800be5dccd8"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
--- a/Excel/Enterprises/Enterprise_Dairy_Template_WIP_v01.xlsx
+++ b/Excel/Enterprises/Enterprise_Dairy_Template_WIP_v01.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\htdocs\zneagcrc\GAF-VEERG-Functions\Excel\Enterprises\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8F38A7C5-5CCB-49C0-8FFF-2EA2DD7AADB6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F8F02752-60BE-45FA-9AB5-93865184AC5D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="615" yWindow="2460" windowWidth="37785" windowHeight="19140" activeTab="1" xr2:uid="{992023F3-CAB7-4E5B-A348-08D563A0EF40}"/>
+    <workbookView xWindow="390" yWindow="390" windowWidth="28800" windowHeight="15345" firstSheet="4" activeTab="7" xr2:uid="{992023F3-CAB7-4E5B-A348-08D563A0EF40}"/>
   </bookViews>
   <sheets>
     <sheet name="Home" sheetId="71" r:id="rId1"/>
@@ -20,7 +20,7 @@
     <sheet name="Input - Livestock sales" sheetId="77" r:id="rId5"/>
     <sheet name="Input - Fert Prod System" sheetId="76" r:id="rId6"/>
     <sheet name="Input - Data quality" sheetId="78" r:id="rId7"/>
-    <sheet name="Constants - Common" sheetId="74" r:id="rId8"/>
+    <sheet name="Constants - Common" sheetId="79" r:id="rId8"/>
   </sheets>
   <externalReferences>
     <externalReference r:id="rId9"/>
@@ -28,119 +28,55 @@
     <externalReference r:id="rId11"/>
   </externalReferences>
   <definedNames>
-    <definedName name="Common_Equations.Common_ConvertCH4ToCO2e" localSheetId="6">_xlfn.LAMBDA(_xlpm.E_CH4,_xlpm.GWP_CH4, _xlpm.E_CH4 * _xlpm.GWP_CH4)</definedName>
-    <definedName name="Common_Equations.Common_ConvertCH4ToCO2e" localSheetId="4">_xlfn.LAMBDA(_xlpm.E_CH4,_xlpm.GWP_CH4, _xlpm.E_CH4 * _xlpm.GWP_CH4)</definedName>
     <definedName name="Common_Equations.Common_ConvertCH4ToCO2e">_xlfn.LAMBDA(_xlpm.E_CH4,_xlpm.GWP_CH4, _xlpm.E_CH4 * _xlpm.GWP_CH4)</definedName>
-    <definedName name="Common_Equations.Common_ConvertCH4ToCO2e_Arguments" localSheetId="6">_xlfn.LAMBDA(_xlfn.MAKEARRAY(2, 2, _xlfn.LAMBDA(_xlpm.r,_xlpm.c, INDEX({"ECH4","Methane emissions (t CH4)";"GWPCH4","Global warming potential for methane (t CO2-e / t CH4)"}, _xlpm.r, _xlpm.c))))</definedName>
-    <definedName name="Common_Equations.Common_ConvertCH4ToCO2e_Arguments" localSheetId="4">_xlfn.LAMBDA(_xlfn.MAKEARRAY(2, 2, _xlfn.LAMBDA(_xlpm.r,_xlpm.c, INDEX({"ECH4","Methane emissions (t CH4)";"GWPCH4","Global warming potential for methane (t CO2-e / t CH4)"}, _xlpm.r, _xlpm.c))))</definedName>
     <definedName name="Common_Equations.Common_ConvertCH4ToCO2e_Arguments">_xlfn.LAMBDA(_xlfn.MAKEARRAY(2, 2, _xlfn.LAMBDA(_xlpm.r,_xlpm.c, INDEX({"ECH4","Methane emissions (t CH4)";"GWPCH4","Global warming potential for methane (t CO2-e / t CH4)"}, _xlpm.r, _xlpm.c))))</definedName>
     <definedName name="Common_Equations.Common_ConvertCH4ToCO2e_LatexEquation">_xlfn.LAMBDA("CO2_e = E_{CH4} \times GWP_{CH4}")</definedName>
     <definedName name="Common_Equations.Common_ConvertCH4ToCO2e_NIRReference">_xlfn.LAMBDA("")</definedName>
     <definedName name="Common_Equations.Common_ConvertCH4ToCO2e_Title">_xlfn.LAMBDA("Convert methane emissions to carbon dioxide equivalent emissions")</definedName>
     <definedName name="Common_Equations.Common_ConvertCH4ToCO2e_Unit">_xlfn.LAMBDA("t CO2e")</definedName>
     <definedName name="Common_Equations.Common_ConvertCH4ToCO2e_Variable">_xlfn.LAMBDA("ECH4 CO2e")</definedName>
-    <definedName name="Common_Equations.Common_ConvertN2OToCO2e" localSheetId="6">_xlfn.LAMBDA(_xlpm.E_N2O,_xlpm.GWP_N2O, _xlpm.E_N2O * _xlpm.GWP_N2O)</definedName>
-    <definedName name="Common_Equations.Common_ConvertN2OToCO2e" localSheetId="4">_xlfn.LAMBDA(_xlpm.E_N2O,_xlpm.GWP_N2O, _xlpm.E_N2O * _xlpm.GWP_N2O)</definedName>
     <definedName name="Common_Equations.Common_ConvertN2OToCO2e">_xlfn.LAMBDA(_xlpm.E_N2O,_xlpm.GWP_N2O, _xlpm.E_N2O * _xlpm.GWP_N2O)</definedName>
-    <definedName name="Common_Equations.Common_ConvertN2OToCO2e_Arguments" localSheetId="6">_xlfn.LAMBDA(_xlfn.MAKEARRAY(2, 2, _xlfn.LAMBDA(_xlpm.r,_xlpm.c, INDEX({"EN2O","Nitrous oxide emissions (t N2O)";"GWPN2O","Global warming potential for nitrous oxide (t CO2-e / t N2O)"}, _xlpm.r, _xlpm.c))))</definedName>
-    <definedName name="Common_Equations.Common_ConvertN2OToCO2e_Arguments" localSheetId="4">_xlfn.LAMBDA(_xlfn.MAKEARRAY(2, 2, _xlfn.LAMBDA(_xlpm.r,_xlpm.c, INDEX({"EN2O","Nitrous oxide emissions (t N2O)";"GWPN2O","Global warming potential for nitrous oxide (t CO2-e / t N2O)"}, _xlpm.r, _xlpm.c))))</definedName>
     <definedName name="Common_Equations.Common_ConvertN2OToCO2e_Arguments">_xlfn.LAMBDA(_xlfn.MAKEARRAY(2, 2, _xlfn.LAMBDA(_xlpm.r,_xlpm.c, INDEX({"EN2O","Nitrous oxide emissions (t N2O)";"GWPN2O","Global warming potential for nitrous oxide (t CO2-e / t N2O)"}, _xlpm.r, _xlpm.c))))</definedName>
     <definedName name="Common_Equations.Common_ConvertN2OToCO2e_LatexEquation">_xlfn.LAMBDA("CO2_e = E_{N2O} \times GWP_{N2O}")</definedName>
     <definedName name="Common_Equations.Common_ConvertN2OToCO2e_NIRReference">_xlfn.LAMBDA("")</definedName>
     <definedName name="Common_Equations.Common_ConvertN2OToCO2e_Title">_xlfn.LAMBDA("Convert nitrous oxide emissions to carbon dioxide equivalent emissions")</definedName>
     <definedName name="Common_Equations.Common_ConvertN2OToCO2e_Unit">_xlfn.LAMBDA("t CO2e")</definedName>
     <definedName name="Common_Equations.Common_ConvertN2OToCO2e_Variable">_xlfn.LAMBDA("EN2O CO2e")</definedName>
-    <definedName name="Common_InputFunctions.Common_GetMCFTemperatureZone" localSheetId="6">_xlfn.LAMBDA(_xlpm.Temperature,_xlpm.MMS,_xlpm.TemperatureArray,_xlpm.MMSArray,_xlpm.ReturnArray, _xlfn.XLOOKUP(MEDIAN(_xlpm.Temperature, MIN(_xlpm.TemperatureArray), MAX(_xlpm.TemperatureArray)), _xlpm.TemperatureArray, _xlfn.XLOOKUP(_xlpm.MMS, _xlpm.MMSArray, _xlpm.ReturnArray)))</definedName>
-    <definedName name="Common_InputFunctions.Common_GetMCFTemperatureZone" localSheetId="4">_xlfn.LAMBDA(_xlpm.Temperature,_xlpm.MMS,_xlpm.TemperatureArray,_xlpm.MMSArray,_xlpm.ReturnArray, _xlfn.XLOOKUP(MEDIAN(_xlpm.Temperature, MIN(_xlpm.TemperatureArray), MAX(_xlpm.TemperatureArray)), _xlpm.TemperatureArray, _xlfn.XLOOKUP(_xlpm.MMS, _xlpm.MMSArray, _xlpm.ReturnArray)))</definedName>
     <definedName name="Common_InputFunctions.Common_GetMCFTemperatureZone">_xlfn.LAMBDA(_xlpm.Temperature,_xlpm.MMS,_xlpm.TemperatureArray,_xlpm.MMSArray,_xlpm.ReturnArray, _xlfn.XLOOKUP(MEDIAN(_xlpm.Temperature, MIN(_xlpm.TemperatureArray), MAX(_xlpm.TemperatureArray)), _xlpm.TemperatureArray, _xlfn.XLOOKUP(_xlpm.MMS, _xlpm.MMSArray, _xlpm.ReturnArray)))</definedName>
-    <definedName name="Common_InputFunctions.CommonCropping_GetFracWET" localSheetId="6">_xlfn.LAMBDA(_xlpm.LeachingZone,_xlpm.ProductionSystem,_xlpm.LeachingZoneLookup,_xlpm.LeachingZoneFracWETLookup,_xlpm.ProductionSystemLookup,_xlpm.ProductionSystemFracWETLookup, _xlfn.LET(_xlpm.LeachingZoneFracWET, 'Input - Data quality'!Common_InputFunctions.Utility_LookupValueInTableNumber(_xlpm.LeachingZone, _xlpm.LeachingZoneLookup, _xlpm.LeachingZoneFracWETLookup), _xlpm.ProductionSystemFracWET, 'Input - Data quality'!Common_InputFunctions.Utility_LookupValueInTableNumber(_xlpm.ProductionSystem, _xlpm.ProductionSystemLookup, _xlpm.ProductionSystemFracWETLookup), IF(_xlpm.LeachingZoneFracWET + _xlpm.ProductionSystemFracWET &gt; 0, 1, 0)))</definedName>
-    <definedName name="Common_InputFunctions.CommonCropping_GetFracWET" localSheetId="4">_xlfn.LAMBDA(_xlpm.LeachingZone,_xlpm.ProductionSystem,_xlpm.LeachingZoneLookup,_xlpm.LeachingZoneFracWETLookup,_xlpm.ProductionSystemLookup,_xlpm.ProductionSystemFracWETLookup, _xlfn.LET(_xlpm.LeachingZoneFracWET, 'Input - Livestock sales'!Common_InputFunctions.Utility_LookupValueInTableNumber(_xlpm.LeachingZone, _xlpm.LeachingZoneLookup, _xlpm.LeachingZoneFracWETLookup), _xlpm.ProductionSystemFracWET, 'Input - Livestock sales'!Common_InputFunctions.Utility_LookupValueInTableNumber(_xlpm.ProductionSystem, _xlpm.ProductionSystemLookup, _xlpm.ProductionSystemFracWETLookup), IF(_xlpm.LeachingZoneFracWET + _xlpm.ProductionSystemFracWET &gt; 0, 1, 0)))</definedName>
-    <definedName name="Common_InputFunctions.CommonCropping_GetFracWET">_xlfn.LAMBDA(_xlpm.LeachingZone,_xlpm.ProductionSystem,_xlpm.LeachingZoneLookup,_xlpm.LeachingZoneFracWETLookup,_xlpm.ProductionSystemLookup,_xlpm.ProductionSystemFracWETLookup, _xlfn.LET(_xlpm.LeachingZoneFracWET, Common_InputFunctions.Utility_LookupValueInTableNumber(_xlpm.LeachingZone, _xlpm.LeachingZoneLookup, _xlpm.LeachingZoneFracWETLookup), _xlpm.ProductionSystemFracWET, Common_InputFunctions.Utility_LookupValueInTableNumber(_xlpm.ProductionSystem, _xlpm.ProductionSystemLookup, _xlpm.ProductionSystemFracWETLookup), IF(_xlpm.LeachingZoneFracWET + _xlpm.ProductionSystemFracWET &gt; 0, 1, 0)))</definedName>
-    <definedName name="Common_InputFunctions.getOverlappingReportingCycles" localSheetId="6">_xlfn.LAMBDA(_xlpm.ProductionCycleStart,_xlpm.ProductionCycleEnd,_xlpm.ReportingCycleStart, _xlfn.LET(_xlpm.S, _xlpm.ProductionCycleStart, _xlpm.E, _xlpm.ProductionCycleEnd, _xlpm.m, MONTH(_xlpm.ReportingCycleStart), _xlpm.d, DAY(_xlpm.ReportingCycleStart), _xlpm.PeriodEnd, _xlfn.LAMBDA(_xlpm.st, EDATE(_xlpm.st, 12) - 1), _xlpm.A, _xlpm.S - 365, _xlpm.ya, YEAR(_xlpm.A), _xlpm.yb, YEAR(_xlpm.E), _xlpm.firstYear, _xlpm.ya + (_xlpm.PeriodEnd(DATE(_xlpm.ya, _xlpm.m, _xlpm.d)) &lt; _xlpm.S), _xlpm.lastYear, _xlpm.yb - (DATE(_xlpm.yb, _xlpm.m, _xlpm.d) &gt; _xlpm.E), MAX(0, _xlpm.lastYear - _xlpm.firstYear + 1)))</definedName>
-    <definedName name="Common_InputFunctions.getOverlappingReportingCycles" localSheetId="4">_xlfn.LAMBDA(_xlpm.ProductionCycleStart,_xlpm.ProductionCycleEnd,_xlpm.ReportingCycleStart, _xlfn.LET(_xlpm.S, _xlpm.ProductionCycleStart, _xlpm.E, _xlpm.ProductionCycleEnd, _xlpm.m, MONTH(_xlpm.ReportingCycleStart), _xlpm.d, DAY(_xlpm.ReportingCycleStart), _xlpm.PeriodEnd, _xlfn.LAMBDA(_xlpm.st, EDATE(_xlpm.st, 12) - 1), _xlpm.A, _xlpm.S - 365, _xlpm.ya, YEAR(_xlpm.A), _xlpm.yb, YEAR(_xlpm.E), _xlpm.firstYear, _xlpm.ya + (_xlpm.PeriodEnd(DATE(_xlpm.ya, _xlpm.m, _xlpm.d)) &lt; _xlpm.S), _xlpm.lastYear, _xlpm.yb - (DATE(_xlpm.yb, _xlpm.m, _xlpm.d) &gt; _xlpm.E), MAX(0, _xlpm.lastYear - _xlpm.firstYear + 1)))</definedName>
+    <definedName name="Common_InputFunctions.CommonCropping_GetFracWET">_xlfn.LAMBDA(_xlpm.LeachingZone,_xlpm.ProductionSystem,_xlpm.LeachingZoneLookup,_xlpm.LeachingZoneFracWETLookup,_xlpm.ProductionSystemLookup,_xlpm.ProductionSystemFracWETLookup, _xlfn.LET(_xlpm.LeachingZoneFracWET, 'Input - Data quality'!Common_InputFunctions.Utility_LookupValueInTableNumber(_xlpm.LeachingZone, _xlpm.LeachingZoneLookup, _xlpm.LeachingZoneFracWETLookup), _xlpm.ProductionSystemFracWET, 'Input - Data quality'!Common_InputFunctions.Utility_LookupValueInTableNumber(_xlpm.ProductionSystem, _xlpm.ProductionSystemLookup, _xlpm.ProductionSystemFracWETLookup), IF(_xlpm.LeachingZoneFracWET + _xlpm.ProductionSystemFracWET &gt; 0, 1, 0)))</definedName>
     <definedName name="Common_InputFunctions.getOverlappingReportingCycles">_xlfn.LAMBDA(_xlpm.ProductionCycleStart,_xlpm.ProductionCycleEnd,_xlpm.ReportingCycleStart, _xlfn.LET(_xlpm.S, _xlpm.ProductionCycleStart, _xlpm.E, _xlpm.ProductionCycleEnd, _xlpm.m, MONTH(_xlpm.ReportingCycleStart), _xlpm.d, DAY(_xlpm.ReportingCycleStart), _xlpm.PeriodEnd, _xlfn.LAMBDA(_xlpm.st, EDATE(_xlpm.st, 12) - 1), _xlpm.A, _xlpm.S - 365, _xlpm.ya, YEAR(_xlpm.A), _xlpm.yb, YEAR(_xlpm.E), _xlpm.firstYear, _xlpm.ya + (_xlpm.PeriodEnd(DATE(_xlpm.ya, _xlpm.m, _xlpm.d)) &lt; _xlpm.S), _xlpm.lastYear, _xlpm.yb - (DATE(_xlpm.yb, _xlpm.m, _xlpm.d) &gt; _xlpm.E), MAX(0, _xlpm.lastYear - _xlpm.firstYear + 1)))</definedName>
-    <definedName name="Common_InputFunctions.getOverlappingReportingPeriods" localSheetId="6">_xlfn.LAMBDA(_xlpm.ProductionCycleStart,_xlpm.ProductionCycleEnd,_xlpm.ReportingCycleStart, _xlfn.LET(_xlpm.S, _xlpm.ProductionCycleStart, _xlpm.E, _xlpm.ProductionCycleEnd, _xlpm.m, MONTH(_xlpm.ReportingCycleStart), _xlpm.d, DAY(_xlpm.ReportingCycleStart), _xlpm.PeriodEnd, _xlfn.LAMBDA(_xlpm.st, EDATE(_xlpm.st, 12) - 1), _xlpm.A, _xlpm.S - 365, _xlpm.ya, YEAR(_xlpm.A), _xlpm.yb, YEAR(_xlpm.E), _xlpm.firstYear, _xlpm.ya + (_xlpm.PeriodEnd(DATE(_xlpm.ya, _xlpm.m, _xlpm.d)) &lt; _xlpm.S), _xlpm.lastYear, _xlpm.yb - (DATE(_xlpm.yb, _xlpm.m, _xlpm.d) &gt; _xlpm.E), _xlpm.n, MAX(0, _xlpm.lastYear - _xlpm.firstYear + 1), _xlpm.yrs, _xlfn.SEQUENCE(_xlpm.n, 1, _xlpm.firstYear, 1), _xlpm.starts, DATE(_xlpm.yrs, _xlpm.m, _xlpm.d), _xlpm.ends, _xlfn.MAP(_xlpm.starts, _xlpm.PeriodEnd), _xlpm.tag, IF(_xlpm.starts = _xlpm.ReportingCycleStart, " (This reporting cycle)", ""), _xlpm.startsText, TEXT(_xlpm.starts, "dd mmm yyyy"), _xlpm.endsText, TEXT(_xlpm.ends, "dd mmm yyyy"), _xlpm.rows, IF(_xlpm.n = 0, "", _xlfn.HSTACK(_xlpm.startsText &amp; " to " &amp; _xlpm.endsText &amp; _xlpm.tag)), _xlpm.rows))</definedName>
-    <definedName name="Common_InputFunctions.getOverlappingReportingPeriods" localSheetId="4">_xlfn.LAMBDA(_xlpm.ProductionCycleStart,_xlpm.ProductionCycleEnd,_xlpm.ReportingCycleStart, _xlfn.LET(_xlpm.S, _xlpm.ProductionCycleStart, _xlpm.E, _xlpm.ProductionCycleEnd, _xlpm.m, MONTH(_xlpm.ReportingCycleStart), _xlpm.d, DAY(_xlpm.ReportingCycleStart), _xlpm.PeriodEnd, _xlfn.LAMBDA(_xlpm.st, EDATE(_xlpm.st, 12) - 1), _xlpm.A, _xlpm.S - 365, _xlpm.ya, YEAR(_xlpm.A), _xlpm.yb, YEAR(_xlpm.E), _xlpm.firstYear, _xlpm.ya + (_xlpm.PeriodEnd(DATE(_xlpm.ya, _xlpm.m, _xlpm.d)) &lt; _xlpm.S), _xlpm.lastYear, _xlpm.yb - (DATE(_xlpm.yb, _xlpm.m, _xlpm.d) &gt; _xlpm.E), _xlpm.n, MAX(0, _xlpm.lastYear - _xlpm.firstYear + 1), _xlpm.yrs, _xlfn.SEQUENCE(_xlpm.n, 1, _xlpm.firstYear, 1), _xlpm.starts, DATE(_xlpm.yrs, _xlpm.m, _xlpm.d), _xlpm.ends, _xlfn.MAP(_xlpm.starts, _xlpm.PeriodEnd), _xlpm.tag, IF(_xlpm.starts = _xlpm.ReportingCycleStart, " (This reporting cycle)", ""), _xlpm.startsText, TEXT(_xlpm.starts, "dd mmm yyyy"), _xlpm.endsText, TEXT(_xlpm.ends, "dd mmm yyyy"), _xlpm.rows, IF(_xlpm.n = 0, "", _xlfn.HSTACK(_xlpm.startsText &amp; " to " &amp; _xlpm.endsText &amp; _xlpm.tag)), _xlpm.rows))</definedName>
     <definedName name="Common_InputFunctions.getOverlappingReportingPeriods">_xlfn.LAMBDA(_xlpm.ProductionCycleStart,_xlpm.ProductionCycleEnd,_xlpm.ReportingCycleStart, _xlfn.LET(_xlpm.S, _xlpm.ProductionCycleStart, _xlpm.E, _xlpm.ProductionCycleEnd, _xlpm.m, MONTH(_xlpm.ReportingCycleStart), _xlpm.d, DAY(_xlpm.ReportingCycleStart), _xlpm.PeriodEnd, _xlfn.LAMBDA(_xlpm.st, EDATE(_xlpm.st, 12) - 1), _xlpm.A, _xlpm.S - 365, _xlpm.ya, YEAR(_xlpm.A), _xlpm.yb, YEAR(_xlpm.E), _xlpm.firstYear, _xlpm.ya + (_xlpm.PeriodEnd(DATE(_xlpm.ya, _xlpm.m, _xlpm.d)) &lt; _xlpm.S), _xlpm.lastYear, _xlpm.yb - (DATE(_xlpm.yb, _xlpm.m, _xlpm.d) &gt; _xlpm.E), _xlpm.n, MAX(0, _xlpm.lastYear - _xlpm.firstYear + 1), _xlpm.yrs, _xlfn.SEQUENCE(_xlpm.n, 1, _xlpm.firstYear, 1), _xlpm.starts, DATE(_xlpm.yrs, _xlpm.m, _xlpm.d), _xlpm.ends, _xlfn.MAP(_xlpm.starts, _xlpm.PeriodEnd), _xlpm.tag, IF(_xlpm.starts = _xlpm.ReportingCycleStart, " (This reporting cycle)", ""), _xlpm.startsText, TEXT(_xlpm.starts, "dd mmm yyyy"), _xlpm.endsText, TEXT(_xlpm.ends, "dd mmm yyyy"), _xlpm.rows, IF(_xlpm.n = 0, "", _xlfn.HSTACK(_xlpm.startsText &amp; " to " &amp; _xlpm.endsText &amp; _xlpm.tag)), _xlpm.rows))</definedName>
-    <definedName name="Common_InputFunctions.Utility_ConvertStateCommonNameToAbbreviation" localSheetId="6">_xlfn.LAMBDA(_xlpm.StateCommonName,_xlpm.StateCommonNameArray,_xlpm.StateAbbreviationArray, _xlfn.XLOOKUP(_xlpm.StateCommonName, _xlpm.StateCommonNameArray, _xlpm.StateAbbreviationArray, ""))</definedName>
-    <definedName name="Common_InputFunctions.Utility_ConvertStateCommonNameToAbbreviation" localSheetId="4">_xlfn.LAMBDA(_xlpm.StateCommonName,_xlpm.StateCommonNameArray,_xlpm.StateAbbreviationArray, _xlfn.XLOOKUP(_xlpm.StateCommonName, _xlpm.StateCommonNameArray, _xlpm.StateAbbreviationArray, ""))</definedName>
     <definedName name="Common_InputFunctions.Utility_ConvertStateCommonNameToAbbreviation">_xlfn.LAMBDA(_xlpm.StateCommonName,_xlpm.StateCommonNameArray,_xlpm.StateAbbreviationArray, _xlfn.XLOOKUP(_xlpm.StateCommonName, _xlpm.StateCommonNameArray, _xlpm.StateAbbreviationArray, ""))</definedName>
-    <definedName name="Common_InputFunctions.Utility_DisplayArguments_1_2" localSheetId="6">_xlfn.LAMBDA(_xlpm.ArgumentsArray, _xlfn.CHOOSECOLS(_xlpm.ArgumentsArray, 1, 2))</definedName>
-    <definedName name="Common_InputFunctions.Utility_DisplayArguments_1_2" localSheetId="4">_xlfn.LAMBDA(_xlpm.ArgumentsArray, _xlfn.CHOOSECOLS(_xlpm.ArgumentsArray, 1, 2))</definedName>
     <definedName name="Common_InputFunctions.Utility_DisplayArguments_1_2">_xlfn.LAMBDA(_xlpm.ArgumentsArray, _xlfn.CHOOSECOLS(_xlpm.ArgumentsArray, 1, 2))</definedName>
-    <definedName name="Common_InputFunctions.Utility_DisplayArguments_3_4" localSheetId="6">_xlfn.LAMBDA(_xlpm.ArgumentsArray, _xlfn.CHOOSECOLS(_xlpm.ArgumentsArray, 3, 4))</definedName>
-    <definedName name="Common_InputFunctions.Utility_DisplayArguments_3_4" localSheetId="4">_xlfn.LAMBDA(_xlpm.ArgumentsArray, _xlfn.CHOOSECOLS(_xlpm.ArgumentsArray, 3, 4))</definedName>
     <definedName name="Common_InputFunctions.Utility_DisplayArguments_3_4">_xlfn.LAMBDA(_xlpm.ArgumentsArray, _xlfn.CHOOSECOLS(_xlpm.ArgumentsArray, 3, 4))</definedName>
-    <definedName name="Common_InputFunctions.Utility_DisplayArrayInTable" localSheetId="6">_xlfn.LAMBDA(_xlpm.ArrayData,_xlpm.TableheaderCell,_xlpm.RowsBetweenHeaderandArray,_xlop.ColumnsBetweenHeaderAndArray, IFERROR(INDEX(_xlfn.UNIQUE(_xlpm.ArrayData), ROW() - 'Input - Data quality'!Common_InputFunctions.Utility_GetArrayTableRowStartNumber(_xlpm.TableheaderCell, _xlpm.RowsBetweenHeaderandArray), COLUMN() - 'Input - Data quality'!Common_InputFunctions.Utility_GetArrayTableColumnStartNumber(_xlpm.TableheaderCell) + IF(_xlfn.ISOMITTED(_xlpm.ColumnsBetweenHeaderAndArray), 1, _xlpm.ColumnsBetweenHeaderAndArray)), ""))</definedName>
-    <definedName name="Common_InputFunctions.Utility_DisplayArrayInTable" localSheetId="4">_xlfn.LAMBDA(_xlpm.ArrayData,_xlpm.TableheaderCell,_xlpm.RowsBetweenHeaderandArray,_xlop.ColumnsBetweenHeaderAndArray, IFERROR(INDEX(_xlfn.UNIQUE(_xlpm.ArrayData), ROW() - 'Input - Livestock sales'!Common_InputFunctions.Utility_GetArrayTableRowStartNumber(_xlpm.TableheaderCell, _xlpm.RowsBetweenHeaderandArray), COLUMN() - 'Input - Livestock sales'!Common_InputFunctions.Utility_GetArrayTableColumnStartNumber(_xlpm.TableheaderCell) + IF(_xlfn.ISOMITTED(_xlpm.ColumnsBetweenHeaderAndArray), 1, _xlpm.ColumnsBetweenHeaderAndArray)), ""))</definedName>
-    <definedName name="Common_InputFunctions.Utility_DisplayArrayInTable">_xlfn.LAMBDA(_xlpm.ArrayData,_xlpm.TableheaderCell,_xlpm.RowsBetweenHeaderandArray,_xlop.ColumnsBetweenHeaderAndArray, IFERROR(INDEX(_xlfn.UNIQUE(_xlpm.ArrayData), ROW() - Common_InputFunctions.Utility_GetArrayTableRowStartNumber(_xlpm.TableheaderCell, _xlpm.RowsBetweenHeaderandArray), COLUMN() - Common_InputFunctions.Utility_GetArrayTableColumnStartNumber(_xlpm.TableheaderCell) + IF(_xlfn.ISOMITTED(_xlpm.ColumnsBetweenHeaderAndArray), 1, _xlpm.ColumnsBetweenHeaderAndArray)), ""))</definedName>
-    <definedName name="Common_InputFunctions.Utility_DisplayFunctionName" localSheetId="6">_xlfn.LAMBDA(_xlpm.Function, _xlfn.TEXTBEFORE(_xlfn.FORMULATEXT(_xlpm.Function), "("))</definedName>
-    <definedName name="Common_InputFunctions.Utility_DisplayFunctionName" localSheetId="4">_xlfn.LAMBDA(_xlpm.Function, _xlfn.TEXTBEFORE(_xlfn.FORMULATEXT(_xlpm.Function), "("))</definedName>
+    <definedName name="Common_InputFunctions.Utility_DisplayArrayInTable">_xlfn.LAMBDA(_xlpm.ArrayData,_xlpm.TableheaderCell,_xlpm.RowsBetweenHeaderandArray,_xlop.ColumnsBetweenHeaderAndArray, IFERROR(INDEX(_xlfn.UNIQUE(_xlpm.ArrayData), ROW() - 'Input - Data quality'!Common_InputFunctions.Utility_GetArrayTableRowStartNumber(_xlpm.TableheaderCell, _xlpm.RowsBetweenHeaderandArray), COLUMN() - 'Input - Data quality'!Common_InputFunctions.Utility_GetArrayTableColumnStartNumber(_xlpm.TableheaderCell) + IF(_xlfn.ISOMITTED(_xlpm.ColumnsBetweenHeaderAndArray), 1, _xlpm.ColumnsBetweenHeaderAndArray)), ""))</definedName>
     <definedName name="Common_InputFunctions.Utility_DisplayFunctionName">_xlfn.LAMBDA(_xlpm.Function, _xlfn.TEXTBEFORE(_xlfn.FORMULATEXT(_xlpm.Function), "("))</definedName>
-    <definedName name="Common_InputFunctions.Utility_GetArrayTableColumnStartNumber" localSheetId="6">_xlfn.LAMBDA(_xlpm.TableHeaderCell, COLUMN(_xlpm.TableHeaderCell))</definedName>
-    <definedName name="Common_InputFunctions.Utility_GetArrayTableColumnStartNumber" localSheetId="4">_xlfn.LAMBDA(_xlpm.TableHeaderCell, COLUMN(_xlpm.TableHeaderCell))</definedName>
     <definedName name="Common_InputFunctions.Utility_GetArrayTableColumnStartNumber">_xlfn.LAMBDA(_xlpm.TableHeaderCell, COLUMN(_xlpm.TableHeaderCell))</definedName>
-    <definedName name="Common_InputFunctions.Utility_GetArrayTableRowStartNumber" localSheetId="6">_xlfn.LAMBDA(_xlpm.TableheaderCell,_xlpm.RowsBetweenHeaderandArray, ROW(_xlpm.TableheaderCell) + _xlpm.RowsBetweenHeaderandArray - 1)</definedName>
-    <definedName name="Common_InputFunctions.Utility_GetArrayTableRowStartNumber" localSheetId="4">_xlfn.LAMBDA(_xlpm.TableheaderCell,_xlpm.RowsBetweenHeaderandArray, ROW(_xlpm.TableheaderCell) + _xlpm.RowsBetweenHeaderandArray - 1)</definedName>
     <definedName name="Common_InputFunctions.Utility_GetArrayTableRowStartNumber">_xlfn.LAMBDA(_xlpm.TableheaderCell,_xlpm.RowsBetweenHeaderandArray, ROW(_xlpm.TableheaderCell) + _xlpm.RowsBetweenHeaderandArray - 1)</definedName>
-    <definedName name="Common_InputFunctions.Utility_GetClimateZone" localSheetId="6">_xlfn.LAMBDA(_xlpm.avgTemp,_xlpm.avgRain,_xlpm.frostDays,_xlpm.elev,_xlpm.map_pet,_xlpm.minTempArray,_xlpm.maxTempArray,_xlpm.minRainfallArray,_xlpm.maxRainfallArray,_xlpm.minFrostArray,_xlpm.maxFrostArray,_xlpm.minElevationArray,_xlpm.maxElevationArray,_xlpm.minPETArray,_xlpm.maxPETArray,_xlpm.climateZoneArray, _xlfn.LET(_xlpm.mask, (VALUE(_xlpm.minTempArray) &lt;= _xlpm.avgTemp) * (VALUE(_xlpm.maxTempArray) &gt;= _xlpm.avgTemp) * (VALUE(_xlpm.minRainfallArray) &lt;= _xlpm.avgRain) * (VALUE(_xlpm.maxRainfallArray) &gt;= _xlpm.avgRain) * (VALUE(_xlpm.minFrostArray) &lt;= _xlpm.frostDays) * (VALUE(_xlpm.maxFrostArray) &gt;= _xlpm.frostDays) * (VALUE(_xlpm.minElevationArray) &lt;= _xlpm.elev) * (VALUE(_xlpm.maxElevationArray) &gt;= _xlpm.elev) * (VALUE(_xlpm.minPETArray) &lt;= _xlpm.map_pet) * (VALUE(_xlpm.maxPETArray) &gt;= _xlpm.map_pet), _xlfn.TAKE(_xlfn._xlws.FILTER(_xlpm.climateZoneArray, _xlpm.mask, "No match"), 1)))</definedName>
-    <definedName name="Common_InputFunctions.Utility_GetClimateZone" localSheetId="4">_xlfn.LAMBDA(_xlpm.avgTemp,_xlpm.avgRain,_xlpm.frostDays,_xlpm.elev,_xlpm.map_pet,_xlpm.minTempArray,_xlpm.maxTempArray,_xlpm.minRainfallArray,_xlpm.maxRainfallArray,_xlpm.minFrostArray,_xlpm.maxFrostArray,_xlpm.minElevationArray,_xlpm.maxElevationArray,_xlpm.minPETArray,_xlpm.maxPETArray,_xlpm.climateZoneArray, _xlfn.LET(_xlpm.mask, (VALUE(_xlpm.minTempArray) &lt;= _xlpm.avgTemp) * (VALUE(_xlpm.maxTempArray) &gt;= _xlpm.avgTemp) * (VALUE(_xlpm.minRainfallArray) &lt;= _xlpm.avgRain) * (VALUE(_xlpm.maxRainfallArray) &gt;= _xlpm.avgRain) * (VALUE(_xlpm.minFrostArray) &lt;= _xlpm.frostDays) * (VALUE(_xlpm.maxFrostArray) &gt;= _xlpm.frostDays) * (VALUE(_xlpm.minElevationArray) &lt;= _xlpm.elev) * (VALUE(_xlpm.maxElevationArray) &gt;= _xlpm.elev) * (VALUE(_xlpm.minPETArray) &lt;= _xlpm.map_pet) * (VALUE(_xlpm.maxPETArray) &gt;= _xlpm.map_pet), _xlfn.TAKE(_xlfn._xlws.FILTER(_xlpm.climateZoneArray, _xlpm.mask, "No match"), 1)))</definedName>
     <definedName name="Common_InputFunctions.Utility_GetClimateZone">_xlfn.LAMBDA(_xlpm.avgTemp,_xlpm.avgRain,_xlpm.frostDays,_xlpm.elev,_xlpm.map_pet,_xlpm.minTempArray,_xlpm.maxTempArray,_xlpm.minRainfallArray,_xlpm.maxRainfallArray,_xlpm.minFrostArray,_xlpm.maxFrostArray,_xlpm.minElevationArray,_xlpm.maxElevationArray,_xlpm.minPETArray,_xlpm.maxPETArray,_xlpm.climateZoneArray, _xlfn.LET(_xlpm.mask, (VALUE(_xlpm.minTempArray) &lt;= _xlpm.avgTemp) * (VALUE(_xlpm.maxTempArray) &gt;= _xlpm.avgTemp) * (VALUE(_xlpm.minRainfallArray) &lt;= _xlpm.avgRain) * (VALUE(_xlpm.maxRainfallArray) &gt;= _xlpm.avgRain) * (VALUE(_xlpm.minFrostArray) &lt;= _xlpm.frostDays) * (VALUE(_xlpm.maxFrostArray) &gt;= _xlpm.frostDays) * (VALUE(_xlpm.minElevationArray) &lt;= _xlpm.elev) * (VALUE(_xlpm.maxElevationArray) &gt;= _xlpm.elev) * (VALUE(_xlpm.minPETArray) &lt;= _xlpm.map_pet) * (VALUE(_xlpm.maxPETArray) &gt;= _xlpm.map_pet), _xlfn.TAKE(_xlfn._xlws.FILTER(_xlpm.climateZoneArray, _xlpm.mask, "No match"), 1)))</definedName>
-    <definedName name="Common_InputFunctions.Utility_LookupItemFromMinMax" localSheetId="6">_xlfn.LAMBDA(_xlpm.LookupValue,_xlpm.MinArray,_xlpm.MaxArray,_xlpm.ItemArray, _xlfn.LET(_xlpm.mask, (VALUE(_xlpm.MinArray) &lt;= _xlpm.LookupValue) * (VALUE(_xlpm.MaxArray) &gt;= _xlpm.LookupValue), _xlfn._xlws.FILTER(_xlpm.ItemArray, _xlpm.mask, "No match")))</definedName>
-    <definedName name="Common_InputFunctions.Utility_LookupItemFromMinMax" localSheetId="4">_xlfn.LAMBDA(_xlpm.LookupValue,_xlpm.MinArray,_xlpm.MaxArray,_xlpm.ItemArray, _xlfn.LET(_xlpm.mask, (VALUE(_xlpm.MinArray) &lt;= _xlpm.LookupValue) * (VALUE(_xlpm.MaxArray) &gt;= _xlpm.LookupValue), _xlfn._xlws.FILTER(_xlpm.ItemArray, _xlpm.mask, "No match")))</definedName>
     <definedName name="Common_InputFunctions.Utility_LookupItemFromMinMax">_xlfn.LAMBDA(_xlpm.LookupValue,_xlpm.MinArray,_xlpm.MaxArray,_xlpm.ItemArray, _xlfn.LET(_xlpm.mask, (VALUE(_xlpm.MinArray) &lt;= _xlpm.LookupValue) * (VALUE(_xlpm.MaxArray) &gt;= _xlpm.LookupValue), _xlfn._xlws.FILTER(_xlpm.ItemArray, _xlpm.mask, "No match")))</definedName>
-    <definedName name="Common_InputFunctions.Utility_LookupN2OEFFromProdIrrigationRainfall" localSheetId="6">_xlfn.LAMBDA(_xlpm.ProductionSystem,_xlpm.IrrigationMethod,_xlpm.RainfallZone,_xlpm.ProductionSystemArray,_xlpm.IrrigationMethodArray,_xlpm.RainfallZoneArray,_xlpm.ReturnArray, _xlfn.LET(_xlpm.IrrigationMethod, IF(_xlpm.IrrigationMethod = "Not irrigated", "Not irrigated", "Any"), _xlpm.RainfallZone, IF(_xlpm.IrrigationMethod = "Not irrigated", _xlpm.RainfallZone, "Any"), _xlfn.XLOOKUP(1, (_xlpm.ProductionSystemArray = _xlpm.ProductionSystem) * (_xlpm.IrrigationMethodArray = _xlpm.IrrigationMethod) * (_xlpm.RainfallZoneArray = _xlpm.RainfallZone), _xlpm.ReturnArray)))</definedName>
-    <definedName name="Common_InputFunctions.Utility_LookupN2OEFFromProdIrrigationRainfall" localSheetId="4">_xlfn.LAMBDA(_xlpm.ProductionSystem,_xlpm.IrrigationMethod,_xlpm.RainfallZone,_xlpm.ProductionSystemArray,_xlpm.IrrigationMethodArray,_xlpm.RainfallZoneArray,_xlpm.ReturnArray, _xlfn.LET(_xlpm.IrrigationMethod, IF(_xlpm.IrrigationMethod = "Not irrigated", "Not irrigated", "Any"), _xlpm.RainfallZone, IF(_xlpm.IrrigationMethod = "Not irrigated", _xlpm.RainfallZone, "Any"), _xlfn.XLOOKUP(1, (_xlpm.ProductionSystemArray = _xlpm.ProductionSystem) * (_xlpm.IrrigationMethodArray = _xlpm.IrrigationMethod) * (_xlpm.RainfallZoneArray = _xlpm.RainfallZone), _xlpm.ReturnArray)))</definedName>
     <definedName name="Common_InputFunctions.Utility_LookupN2OEFFromProdIrrigationRainfall">_xlfn.LAMBDA(_xlpm.ProductionSystem,_xlpm.IrrigationMethod,_xlpm.RainfallZone,_xlpm.ProductionSystemArray,_xlpm.IrrigationMethodArray,_xlpm.RainfallZoneArray,_xlpm.ReturnArray, _xlfn.LET(_xlpm.IrrigationMethod, IF(_xlpm.IrrigationMethod = "Not irrigated", "Not irrigated", "Any"), _xlpm.RainfallZone, IF(_xlpm.IrrigationMethod = "Not irrigated", _xlpm.RainfallZone, "Any"), _xlfn.XLOOKUP(1, (_xlpm.ProductionSystemArray = _xlpm.ProductionSystem) * (_xlpm.IrrigationMethodArray = _xlpm.IrrigationMethod) * (_xlpm.RainfallZoneArray = _xlpm.RainfallZone), _xlpm.ReturnArray)))</definedName>
-    <definedName name="Common_InputFunctions.Utility_LookupValueInTable" localSheetId="6">_xlfn.LAMBDA(_xlpm.LookupValue,_xlpm.LookupArray,_xlpm.ReturnArray, _xlfn.XLOOKUP(_xlpm.LookupValue, _xlpm.LookupArray, _xlpm.ReturnArray, ""))</definedName>
-    <definedName name="Common_InputFunctions.Utility_LookupValueInTable" localSheetId="4">_xlfn.LAMBDA(_xlpm.LookupValue,_xlpm.LookupArray,_xlpm.ReturnArray, _xlfn.XLOOKUP(_xlpm.LookupValue, _xlpm.LookupArray, _xlpm.ReturnArray, ""))</definedName>
     <definedName name="Common_InputFunctions.Utility_LookupValueInTable">_xlfn.LAMBDA(_xlpm.LookupValue,_xlpm.LookupArray,_xlpm.ReturnArray, _xlfn.XLOOKUP(_xlpm.LookupValue, _xlpm.LookupArray, _xlpm.ReturnArray, ""))</definedName>
-    <definedName name="Common_InputFunctions.Utility_LookupValueInTableNumber" localSheetId="6">_xlfn.LAMBDA(_xlpm.LookupValue,_xlpm.LookupArray,_xlpm.ReturnArray, IF(ISNUMBER(_xlfn.XLOOKUP(_xlpm.LookupValue, _xlpm.LookupArray, _xlpm.ReturnArray, "")), _xlfn.XLOOKUP(_xlpm.LookupValue, _xlpm.LookupArray, _xlpm.ReturnArray, ""), 0))</definedName>
-    <definedName name="Common_InputFunctions.Utility_LookupValueInTableNumber" localSheetId="4">_xlfn.LAMBDA(_xlpm.LookupValue,_xlpm.LookupArray,_xlpm.ReturnArray, IF(ISNUMBER(_xlfn.XLOOKUP(_xlpm.LookupValue, _xlpm.LookupArray, _xlpm.ReturnArray, "")), _xlfn.XLOOKUP(_xlpm.LookupValue, _xlpm.LookupArray, _xlpm.ReturnArray, ""), 0))</definedName>
     <definedName name="Common_InputFunctions.Utility_LookupValueInTableNumber">_xlfn.LAMBDA(_xlpm.LookupValue,_xlpm.LookupArray,_xlpm.ReturnArray, IF(ISNUMBER(_xlfn.XLOOKUP(_xlpm.LookupValue, _xlpm.LookupArray, _xlpm.ReturnArray, "")), _xlfn.XLOOKUP(_xlpm.LookupValue, _xlpm.LookupArray, _xlpm.ReturnArray, ""), 0))</definedName>
-    <definedName name="Common_InputFunctions.Utility_LookupValueInTableOneColumnAndHeader" localSheetId="6">_xlfn.LAMBDA(_xlpm.LookupValue1,_xlpm.LookupValue2,_xlpm.LookupArray1,_xlpm.LookupArray2,_xlpm.ReturnArray,_xlop.ValueIfFalse, IFERROR(_xlfn.XLOOKUP(_xlpm.LookupValue1, _xlpm.LookupArray1, _xlfn.XLOOKUP(_xlpm.LookupValue2, _xlpm.LookupArray2, _xlpm.ReturnArray)), IF(_xlfn.ISOMITTED(_xlpm.ValueIfFalse), "", _xlpm.ValueIfFalse)))</definedName>
-    <definedName name="Common_InputFunctions.Utility_LookupValueInTableOneColumnAndHeader" localSheetId="4">_xlfn.LAMBDA(_xlpm.LookupValue1,_xlpm.LookupValue2,_xlpm.LookupArray1,_xlpm.LookupArray2,_xlpm.ReturnArray,_xlop.ValueIfFalse, IFERROR(_xlfn.XLOOKUP(_xlpm.LookupValue1, _xlpm.LookupArray1, _xlfn.XLOOKUP(_xlpm.LookupValue2, _xlpm.LookupArray2, _xlpm.ReturnArray)), IF(_xlfn.ISOMITTED(_xlpm.ValueIfFalse), "", _xlpm.ValueIfFalse)))</definedName>
     <definedName name="Common_InputFunctions.Utility_LookupValueInTableOneColumnAndHeader">_xlfn.LAMBDA(_xlpm.LookupValue1,_xlpm.LookupValue2,_xlpm.LookupArray1,_xlpm.LookupArray2,_xlpm.ReturnArray,_xlop.ValueIfFalse, IFERROR(_xlfn.XLOOKUP(_xlpm.LookupValue1, _xlpm.LookupArray1, _xlfn.XLOOKUP(_xlpm.LookupValue2, _xlpm.LookupArray2, _xlpm.ReturnArray)), IF(_xlfn.ISOMITTED(_xlpm.ValueIfFalse), "", _xlpm.ValueIfFalse)))</definedName>
-    <definedName name="Common_InputFunctions.Utility_LookupValueInTableTwoColumns" localSheetId="6">_xlfn.LAMBDA(_xlpm.LookupValue1,_xlpm.LookupValue2,_xlpm.LookupArray1,_xlpm.LookupArray2,_xlpm.ReturnArray,_xlop.ValueIFFalse, _xlfn.XLOOKUP(1, (_xlpm.LookupArray1 = _xlpm.LookupValue1) * (_xlpm.LookupArray2 = _xlpm.LookupValue2), _xlpm.ReturnArray, IF(_xlfn.ISOMITTED(_xlpm.ValueIFFalse), "", _xlpm.ValueIFFalse)))</definedName>
-    <definedName name="Common_InputFunctions.Utility_LookupValueInTableTwoColumns" localSheetId="4">_xlfn.LAMBDA(_xlpm.LookupValue1,_xlpm.LookupValue2,_xlpm.LookupArray1,_xlpm.LookupArray2,_xlpm.ReturnArray,_xlop.ValueIFFalse, _xlfn.XLOOKUP(1, (_xlpm.LookupArray1 = _xlpm.LookupValue1) * (_xlpm.LookupArray2 = _xlpm.LookupValue2), _xlpm.ReturnArray, IF(_xlfn.ISOMITTED(_xlpm.ValueIFFalse), "", _xlpm.ValueIFFalse)))</definedName>
     <definedName name="Common_InputFunctions.Utility_LookupValueInTableTwoColumns">_xlfn.LAMBDA(_xlpm.LookupValue1,_xlpm.LookupValue2,_xlpm.LookupArray1,_xlpm.LookupArray2,_xlpm.ReturnArray,_xlop.ValueIFFalse, _xlfn.XLOOKUP(1, (_xlpm.LookupArray1 = _xlpm.LookupValue1) * (_xlpm.LookupArray2 = _xlpm.LookupValue2), _xlpm.ReturnArray, IF(_xlfn.ISOMITTED(_xlpm.ValueIFFalse), "", _xlpm.ValueIFFalse)))</definedName>
-    <definedName name="Common_InputFunctions.Utility_ResultsItemFromEquationTitleAndSource" localSheetId="6">_xlfn.LAMBDA(_xlpm.TitleCell,_xlpm.SourceCell, SUBSTITUTE(LEFT(_xlpm.SourceCell, FIND(",", _xlpm.SourceCell) - 1), "VEERG 2026: ", "") &amp; " " &amp; _xlpm.TitleCell)</definedName>
-    <definedName name="Common_InputFunctions.Utility_ResultsItemFromEquationTitleAndSource" localSheetId="4">_xlfn.LAMBDA(_xlpm.TitleCell,_xlpm.SourceCell, SUBSTITUTE(LEFT(_xlpm.SourceCell, FIND(",", _xlpm.SourceCell) - 1), "VEERG 2026: ", "") &amp; " " &amp; _xlpm.TitleCell)</definedName>
     <definedName name="Common_InputFunctions.Utility_ResultsItemFromEquationTitleAndSource">_xlfn.LAMBDA(_xlpm.TitleCell,_xlpm.SourceCell, SUBSTITUTE(LEFT(_xlpm.SourceCell, FIND(",", _xlpm.SourceCell) - 1), "VEERG 2026: ", "") &amp; " " &amp; _xlpm.TitleCell)</definedName>
-    <definedName name="Common_InputFunctions.Utility_SourceHyperlink" localSheetId="6">_xlfn.LAMBDA(_xlpm.TargetCell, _xlfn.LET(_xlpm.sh, _xlfn.TEXTAFTER(CELL("filename", _xlpm.TargetCell), "]"), _xlpm.addr, CELL("address", _xlpm.TargetCell), "#'" &amp; _xlpm.sh &amp; "'!" &amp; _xlpm.addr))</definedName>
-    <definedName name="Common_InputFunctions.Utility_SourceHyperlink" localSheetId="4">_xlfn.LAMBDA(_xlpm.TargetCell, _xlfn.LET(_xlpm.sh, _xlfn.TEXTAFTER(CELL("filename", _xlpm.TargetCell), "]"), _xlpm.addr, CELL("address", _xlpm.TargetCell), "#'" &amp; _xlpm.sh &amp; "'!" &amp; _xlpm.addr))</definedName>
     <definedName name="Common_InputFunctions.Utility_SourceHyperlink">_xlfn.LAMBDA(_xlpm.TargetCell, _xlfn.LET(_xlpm.sh, _xlfn.TEXTAFTER(CELL("filename", _xlpm.TargetCell), "]"), _xlpm.addr, CELL("address", _xlpm.TargetCell), "#'" &amp; _xlpm.sh &amp; "'!" &amp; _xlpm.addr))</definedName>
-    <definedName name="Common_InputFunctions.Utility_SourceHyperlinkDifferentSheet" localSheetId="6">_xlfn.LAMBDA(_xlpm.TargetCell, _xlfn.LET(_xlpm.sh, _xlfn.TEXTAFTER(CELL("filename", _xlpm.TargetCell), "]"), _xlpm.addr, CELL("address", _xlpm.TargetCell), "#" &amp; _xlpm.addr))</definedName>
-    <definedName name="Common_InputFunctions.Utility_SourceHyperlinkDifferentSheet" localSheetId="4">_xlfn.LAMBDA(_xlpm.TargetCell, _xlfn.LET(_xlpm.sh, _xlfn.TEXTAFTER(CELL("filename", _xlpm.TargetCell), "]"), _xlpm.addr, CELL("address", _xlpm.TargetCell), "#" &amp; _xlpm.addr))</definedName>
     <definedName name="Common_InputFunctions.Utility_SourceHyperlinkDifferentSheet">_xlfn.LAMBDA(_xlpm.TargetCell, _xlfn.LET(_xlpm.sh, _xlfn.TEXTAFTER(CELL("filename", _xlpm.TargetCell), "]"), _xlpm.addr, CELL("address", _xlpm.TargetCell), "#" &amp; _xlpm.addr))</definedName>
-    <definedName name="Common_InputFunctions.Utility_SplitStringIntoArray" localSheetId="6">_xlfn.LAMBDA(_xlpm.Cell,_xlpm.Delimiter,_xlop.CharacterToRemove1,_xlop.CharacterToRemove2, _xlfn.FILTERXML("&lt;t&gt;&lt;s&gt;" &amp; SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(_xlpm.Cell, _xlpm.CharacterToRemove1, ""), _xlpm.CharacterToRemove2, ""), _xlpm.Delimiter, "&lt;/s&gt;&lt;s&gt;") &amp; "&lt;/s&gt;&lt;/t&gt;", "//s"))</definedName>
-    <definedName name="Common_InputFunctions.Utility_SplitStringIntoArray" localSheetId="4">_xlfn.LAMBDA(_xlpm.Cell,_xlpm.Delimiter,_xlop.CharacterToRemove1,_xlop.CharacterToRemove2, _xlfn.FILTERXML("&lt;t&gt;&lt;s&gt;" &amp; SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(_xlpm.Cell, _xlpm.CharacterToRemove1, ""), _xlpm.CharacterToRemove2, ""), _xlpm.Delimiter, "&lt;/s&gt;&lt;s&gt;") &amp; "&lt;/s&gt;&lt;/t&gt;", "//s"))</definedName>
     <definedName name="Common_InputFunctions.Utility_SplitStringIntoArray">_xlfn.LAMBDA(_xlpm.Cell,_xlpm.Delimiter,_xlop.CharacterToRemove1,_xlop.CharacterToRemove2, _xlfn.FILTERXML("&lt;t&gt;&lt;s&gt;" &amp; SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(_xlpm.Cell, _xlpm.CharacterToRemove1, ""), _xlpm.CharacterToRemove2, ""), _xlpm.Delimiter, "&lt;/s&gt;&lt;s&gt;") &amp; "&lt;/s&gt;&lt;/t&gt;", "//s"))</definedName>
-    <definedName name="Common_InputFunctions.Utility_SumQuantityFromCriteria" localSheetId="6">_xlfn.LAMBDA(_xlpm.Criteria1,_xlpm.Criteria1TypeArray,_xlpm.Quantity,_xlop.Multiplier,_xlop.Criteria2,_xlop.Criteria2Array, _xlfn.LET(_xlpm.multiplier, IF(_xlfn.ISOMITTED(_xlpm.Multiplier), 1, _xlpm.Multiplier), _xlpm.quantity, _xlpm.Quantity * _xlpm.multiplier, _xlpm.criteria1, --(_xlpm.Criteria1TypeArray = _xlpm.Criteria1), _xlpm.criteria2, IF(_xlfn.ISOMITTED(_xlpm.Criteria2), 1, --(_xlpm.Criteria2Array = _xlpm.Criteria2)), SUMPRODUCT(_xlpm.criteria1 * _xlpm.criteria2 * _xlpm.quantity)))</definedName>
-    <definedName name="Common_InputFunctions.Utility_SumQuantityFromCriteria" localSheetId="4">_xlfn.LAMBDA(_xlpm.Criteria1,_xlpm.Criteria1TypeArray,_xlpm.Quantity,_xlop.Multiplier,_xlop.Criteria2,_xlop.Criteria2Array, _xlfn.LET(_xlpm.multiplier, IF(_xlfn.ISOMITTED(_xlpm.Multiplier), 1, _xlpm.Multiplier), _xlpm.quantity, _xlpm.Quantity * _xlpm.multiplier, _xlpm.criteria1, --(_xlpm.Criteria1TypeArray = _xlpm.Criteria1), _xlpm.criteria2, IF(_xlfn.ISOMITTED(_xlpm.Criteria2), 1, --(_xlpm.Criteria2Array = _xlpm.Criteria2)), SUMPRODUCT(_xlpm.criteria1 * _xlpm.criteria2 * _xlpm.quantity)))</definedName>
     <definedName name="Common_InputFunctions.Utility_SumQuantityFromCriteria">_xlfn.LAMBDA(_xlpm.Criteria1,_xlpm.Criteria1TypeArray,_xlpm.Quantity,_xlop.Multiplier,_xlop.Criteria2,_xlop.Criteria2Array, _xlfn.LET(_xlpm.multiplier, IF(_xlfn.ISOMITTED(_xlpm.Multiplier), 1, _xlpm.Multiplier), _xlpm.quantity, _xlpm.Quantity * _xlpm.multiplier, _xlpm.criteria1, --(_xlpm.Criteria1TypeArray = _xlpm.Criteria1), _xlpm.criteria2, IF(_xlfn.ISOMITTED(_xlpm.Criteria2), 1, --(_xlpm.Criteria2Array = _xlpm.Criteria2)), SUMPRODUCT(_xlpm.criteria1 * _xlpm.criteria2 * _xlpm.quantity)))</definedName>
-    <definedName name="Common_SourceData.Common_SourceData_AustralianStatesTerritories_Data" localSheetId="6">_xlfn.LAMBDA(_xlfn.MAKEARRAY(9, 3, _xlfn.LAMBDA(_xlpm.r,_xlpm.c, INDEX({"State/Territory","Common Name","Abbreviation";"New South Wales","New South Wales","NSW";"Australian Capital Territory","ACT","ACT";"Victoria","Victoria","VIC";"Queensland","Queensland","QLD";"South Australia","South Australia","SA";"Western Australia","Western Australia","WA";"Tasmania","Tasmania","TAS";"Northern Territory","Northern Territory","NT"}, _xlpm.r, _xlpm.c))))</definedName>
-    <definedName name="Common_SourceData.Common_SourceData_AustralianStatesTerritories_Data" localSheetId="4">_xlfn.LAMBDA(_xlfn.MAKEARRAY(9, 3, _xlfn.LAMBDA(_xlpm.r,_xlpm.c, INDEX({"State/Territory","Common Name","Abbreviation";"New South Wales","New South Wales","NSW";"Australian Capital Territory","ACT","ACT";"Victoria","Victoria","VIC";"Queensland","Queensland","QLD";"South Australia","South Australia","SA";"Western Australia","Western Australia","WA";"Tasmania","Tasmania","TAS";"Northern Territory","Northern Territory","NT"}, _xlpm.r, _xlpm.c))))</definedName>
     <definedName name="Common_SourceData.Common_SourceData_AustralianStatesTerritories_Data">_xlfn.LAMBDA(_xlfn.MAKEARRAY(9, 3, _xlfn.LAMBDA(_xlpm.r,_xlpm.c, INDEX({"State/Territory","Common Name","Abbreviation";"New South Wales","New South Wales","NSW";"Australian Capital Territory","ACT","ACT";"Victoria","Victoria","VIC";"Queensland","Queensland","QLD";"South Australia","South Australia","SA";"Western Australia","Western Australia","WA";"Tasmania","Tasmania","TAS";"Northern Territory","Northern Territory","NT"}, _xlpm.r, _xlpm.c))))</definedName>
     <definedName name="Common_SourceData.Common_SourceData_AustralianStatesTerritories_Source">_xlfn.LAMBDA("")</definedName>
     <definedName name="Common_SourceData.Common_SourceData_AustralianStatesTerritories_Title">_xlfn.LAMBDA("Australian states and territories")</definedName>
     <definedName name="Common_SourceData.Common_SourceData_AustralianStatesTerritories_Unit">_xlfn.LAMBDA("")</definedName>
     <definedName name="Common_SourceData.Common_SourceData_AustralianStatesTerritories_Variable">_xlfn.LAMBDA("")</definedName>
-    <definedName name="Common_SourceData.Common_SourceData_ClimateZones_Appendices" localSheetId="6">_xlfn.LAMBDA(_xlfn.MAKEARRAY(4, 1, _xlfn.LAMBDA(_xlpm.r,_xlpm.c, INDEX({"Note:";"MAT = mean annual temperature";"MAP = mean annual precipitation";"PET = potential evapotranspiration"}, _xlpm.r, _xlpm.c))))</definedName>
-    <definedName name="Common_SourceData.Common_SourceData_ClimateZones_Appendices" localSheetId="4">_xlfn.LAMBDA(_xlfn.MAKEARRAY(4, 1, _xlfn.LAMBDA(_xlpm.r,_xlpm.c, INDEX({"Note:";"MAT = mean annual temperature";"MAP = mean annual precipitation";"PET = potential evapotranspiration"}, _xlpm.r, _xlpm.c))))</definedName>
     <definedName name="Common_SourceData.Common_SourceData_ClimateZones_Appendices">_xlfn.LAMBDA(_xlfn.MAKEARRAY(4, 1, _xlfn.LAMBDA(_xlpm.r,_xlpm.c, INDEX({"Note:";"MAT = mean annual temperature";"MAP = mean annual precipitation";"PET = potential evapotranspiration"}, _xlpm.r, _xlpm.c))))</definedName>
-    <definedName name="Common_SourceData.Common_SourceData_ClimateZones_Data" localSheetId="6">_xlfn.LAMBDA(_xlfn.MAKEARRAY(9, 16, _xlfn.LAMBDA(_xlpm.r,_xlpm.c, INDEX({"Climate Zone","MAT","MAP","Frost days per year","Elevation","MAP:PET","Min temp","Max temp","Min rainfall","Max rainfall","Min frost days","Max frost days","Min elevation","Max elevation","Min MAP:PET","Min MAP:PET";"Tropical montane","&gt; 18 C","Any","≤ 7","&gt; 1000 m","Any",18.001,999999,-999999,999999,-999999,7,1000,999999,-999999,999999;"Tropical wet","&gt; 18 C","&gt; 2000 mm","≤ 7","≤ 1000 m","Any",18.001,999999,2000.001,999999,-999999,7,-999999,999.999,-999999,999999;"Tropical moist","&gt; 18 C","&gt; 1000 mm - ≤ 2000 mm","≤ 7","≤ 1000 m","Any",18.001,999999,1000.001,2000,-999999,7,-999999,999.999,-999999,999999;"Tropical dry","&gt; 18 C","≤ 1000 mm","≤ 7","≤ 1000 m","Any",18.001,999999,-999999,1000,-999999,7,-999999,999.999,-999999,999999;"Warm temperate moist","&gt; 10 C","Any","Any","Any","&gt; 1",10.001,999999,-999999,999999,-999999,999999,-999999,999999,1.001,999999;"Warm temperate dry","&gt; 10 C","Any","Any","Any","≤ 1",10.001,999999,-999999,999999,-999999,999999,-999999,999999,-999999,1;"Cool temperate moist","&gt; 0 C - ≤ 10 C","Any","Any","Any","&gt; 1",-999999,10,-999999,999999,-999999,999999,-999999,999999,1.001,999999;"Cool temperate dry","&gt; 0 C - ≤ 10 C","Any","Any","Any","≤ 1",-999999,10,-999999,999999,-999999,999999,-999999,999999,-999999,1}, _xlpm.r, _xlpm.c))))</definedName>
-    <definedName name="Common_SourceData.Common_SourceData_ClimateZones_Data" localSheetId="4">_xlfn.LAMBDA(_xlfn.MAKEARRAY(9, 16, _xlfn.LAMBDA(_xlpm.r,_xlpm.c, INDEX({"Climate Zone","MAT","MAP","Frost days per year","Elevation","MAP:PET","Min temp","Max temp","Min rainfall","Max rainfall","Min frost days","Max frost days","Min elevation","Max elevation","Min MAP:PET","Min MAP:PET";"Tropical montane","&gt; 18 C","Any","≤ 7","&gt; 1000 m","Any",18.001,999999,-999999,999999,-999999,7,1000,999999,-999999,999999;"Tropical wet","&gt; 18 C","&gt; 2000 mm","≤ 7","≤ 1000 m","Any",18.001,999999,2000.001,999999,-999999,7,-999999,999.999,-999999,999999;"Tropical moist","&gt; 18 C","&gt; 1000 mm - ≤ 2000 mm","≤ 7","≤ 1000 m","Any",18.001,999999,1000.001,2000,-999999,7,-999999,999.999,-999999,999999;"Tropical dry","&gt; 18 C","≤ 1000 mm","≤ 7","≤ 1000 m","Any",18.001,999999,-999999,1000,-999999,7,-999999,999.999,-999999,999999;"Warm temperate moist","&gt; 10 C","Any","Any","Any","&gt; 1",10.001,999999,-999999,999999,-999999,999999,-999999,999999,1.001,999999;"Warm temperate dry","&gt; 10 C","Any","Any","Any","≤ 1",10.001,999999,-999999,999999,-999999,999999,-999999,999999,-999999,1;"Cool temperate moist","&gt; 0 C - ≤ 10 C","Any","Any","Any","&gt; 1",-999999,10,-999999,999999,-999999,999999,-999999,999999,1.001,999999;"Cool temperate dry","&gt; 0 C - ≤ 10 C","Any","Any","Any","≤ 1",-999999,10,-999999,999999,-999999,999999,-999999,999999,-999999,1}, _xlpm.r, _xlpm.c))))</definedName>
     <definedName name="Common_SourceData.Common_SourceData_ClimateZones_Data">_xlfn.LAMBDA(_xlfn.MAKEARRAY(9, 16, _xlfn.LAMBDA(_xlpm.r,_xlpm.c, INDEX({"Climate Zone","MAT","MAP","Frost days per year","Elevation","MAP:PET","Min temp","Max temp","Min rainfall","Max rainfall","Min frost days","Max frost days","Min elevation","Max elevation","Min MAP:PET","Min MAP:PET";"Tropical montane","&gt; 18 C","Any","≤ 7","&gt; 1000 m","Any",18.001,999999,-999999,999999,-999999,7,1000,999999,-999999,999999;"Tropical wet","&gt; 18 C","&gt; 2000 mm","≤ 7","≤ 1000 m","Any",18.001,999999,2000.001,999999,-999999,7,-999999,999.999,-999999,999999;"Tropical moist","&gt; 18 C","&gt; 1000 mm - ≤ 2000 mm","≤ 7","≤ 1000 m","Any",18.001,999999,1000.001,2000,-999999,7,-999999,999.999,-999999,999999;"Tropical dry","&gt; 18 C","≤ 1000 mm","≤ 7","≤ 1000 m","Any",18.001,999999,-999999,1000,-999999,7,-999999,999.999,-999999,999999;"Warm temperate moist","&gt; 10 C","Any","Any","Any","&gt; 1",10.001,999999,-999999,999999,-999999,999999,-999999,999999,1.001,999999;"Warm temperate dry","&gt; 10 C","Any","Any","Any","≤ 1",10.001,999999,-999999,999999,-999999,999999,-999999,999999,-999999,1;"Cool temperate moist","&gt; 0 C - ≤ 10 C","Any","Any","Any","&gt; 1",-999999,10,-999999,999999,-999999,999999,-999999,999999,1.001,999999;"Cool temperate dry","&gt; 0 C - ≤ 10 C","Any","Any","Any","≤ 1",-999999,10,-999999,999999,-999999,999999,-999999,999999,-999999,1}, _xlpm.r, _xlpm.c))))</definedName>
     <definedName name="Common_SourceData.Common_SourceData_ClimateZones_Source">_xlfn.LAMBDA("VEERG 2026: Table 1.3: Climate and Rainfall zone classifications and definitions")</definedName>
     <definedName name="Common_SourceData.Common_SourceData_ClimateZones_Title">_xlfn.LAMBDA("VEERG Australian climate zones")</definedName>
     <definedName name="Common_SourceData.Common_SourceData_ClimateZones_Unit">_xlfn.LAMBDA("")</definedName>
     <definedName name="Common_SourceData.Common_SourceData_ClimateZones_Variable">_xlfn.LAMBDA("")</definedName>
-    <definedName name="Common_SourceData.Common_SourceData_ClimateZones_Variation" localSheetId="6">_xlfn.LAMBDA(_xlfn.MAKEARRAY(5, 1, _xlfn.LAMBDA(_xlpm.r,_xlpm.c, INDEX({"VARIATION OF SOURCE DATA:";"Added warm / cool temperate moist / dry - low frost and high temp classes to accommodate climate scenarios excluded by VEERG criteria.";"Fixed typo in MAT value for warm temperate dry - changed 10 to 11.";"Added min and max columns for MAT, MAP, frost days per year, elevation, MAP:PET to calculate zones from real climate data.";"GAF accepts rainfall as a proxy for precipitation."}, _xlpm.r, _xlpm.c))))</definedName>
-    <definedName name="Common_SourceData.Common_SourceData_ClimateZones_Variation" localSheetId="4">_xlfn.LAMBDA(_xlfn.MAKEARRAY(5, 1, _xlfn.LAMBDA(_xlpm.r,_xlpm.c, INDEX({"VARIATION OF SOURCE DATA:";"Added warm / cool temperate moist / dry - low frost and high temp classes to accommodate climate scenarios excluded by VEERG criteria.";"Fixed typo in MAT value for warm temperate dry - changed 10 to 11.";"Added min and max columns for MAT, MAP, frost days per year, elevation, MAP:PET to calculate zones from real climate data.";"GAF accepts rainfall as a proxy for precipitation."}, _xlpm.r, _xlpm.c))))</definedName>
     <definedName name="Common_SourceData.Common_SourceData_ClimateZones_Variation">_xlfn.LAMBDA(_xlfn.MAKEARRAY(5, 1, _xlfn.LAMBDA(_xlpm.r,_xlpm.c, INDEX({"VARIATION OF SOURCE DATA:";"Added warm / cool temperate moist / dry - low frost and high temp classes to accommodate climate scenarios excluded by VEERG criteria.";"Fixed typo in MAT value for warm temperate dry - changed 10 to 11.";"Added min and max columns for MAT, MAP, frost days per year, elevation, MAP:PET to calculate zones from real climate data.";"GAF accepts rainfall as a proxy for precipitation."}, _xlpm.r, _xlpm.c))))</definedName>
-    <definedName name="Common_SourceData.Common_SourceData_ConvertGasElementalToMolecular_Data" localSheetId="6">_xlfn.LAMBDA(_xlfn.MAKEARRAY(8, 4, _xlfn.LAMBDA(_xlpm.r,_xlpm.c, INDEX({"Gas","Conversion factor","Conversion factor 1","Conversion factor 2";"CO2","44/12",44,12;"CH4","16/12",16,12;"N2O","44/28",44,28;"Nox","46/14",46,14;"CO","28/12",28,12;"CO2 Lime","44/12",44,12;"NMVOC","14/12",14,12}, _xlpm.r, _xlpm.c))))</definedName>
-    <definedName name="Common_SourceData.Common_SourceData_ConvertGasElementalToMolecular_Data" localSheetId="4">_xlfn.LAMBDA(_xlfn.MAKEARRAY(8, 4, _xlfn.LAMBDA(_xlpm.r,_xlpm.c, INDEX({"Gas","Conversion factor","Conversion factor 1","Conversion factor 2";"CO2","44/12",44,12;"CH4","16/12",16,12;"N2O","44/28",44,28;"Nox","46/14",46,14;"CO","28/12",28,12;"CO2 Lime","44/12",44,12;"NMVOC","14/12",14,12}, _xlpm.r, _xlpm.c))))</definedName>
     <definedName name="Common_SourceData.Common_SourceData_ConvertGasElementalToMolecular_Data">_xlfn.LAMBDA(_xlfn.MAKEARRAY(8, 4, _xlfn.LAMBDA(_xlpm.r,_xlpm.c, INDEX({"Gas","Conversion factor","Conversion factor 1","Conversion factor 2";"CO2","44/12",44,12;"CH4","16/12",16,12;"N2O","44/28",44,28;"Nox","46/14",46,14;"CO","28/12",28,12;"CO2 Lime","44/12",44,12;"NMVOC","14/12",14,12}, _xlpm.r, _xlpm.c))))</definedName>
     <definedName name="Common_SourceData.Common_SourceData_ConvertGasElementalToMolecular_Source">_xlfn.LAMBDA("XXXXXXX")</definedName>
     <definedName name="Common_SourceData.Common_SourceData_ConvertGasElementalToMolecular_Title">_xlfn.LAMBDA("Factor to convert elemental mass of gas to molecular mass")</definedName>
@@ -151,8 +87,6 @@
     <definedName name="Common_SourceData.Common_SourceData_ConvertN2oElementalToMolecularCg_Title">_xlfn.LAMBDA("Factor to convert elemental mass of N2O to molecular mass")</definedName>
     <definedName name="Common_SourceData.Common_SourceData_ConvertN2oElementalToMolecularCg_Unit">_xlfn.LAMBDA("factor")</definedName>
     <definedName name="Common_SourceData.Common_SourceData_ConvertN2oElementalToMolecularCg_Variable">_xlfn.LAMBDA("CgN2O")</definedName>
-    <definedName name="Common_SourceData.Common_SourceData_DataScores_Scope3_Data" localSheetId="6">_xlfn.LAMBDA(_xlfn.MAKEARRAY(6, 2, _xlfn.LAMBDA(_xlpm.r,_xlpm.c, INDEX({"Data source","Data score";"International scope 3 database",1;"Australian scope 3 database",2;"State or regional scope 3 database",3;"Emissions intensity calculated from approved method",4;"Verified credential matching ISO14067",5}, _xlpm.r, _xlpm.c))))</definedName>
-    <definedName name="Common_SourceData.Common_SourceData_DataScores_Scope3_Data" localSheetId="4">_xlfn.LAMBDA(_xlfn.MAKEARRAY(6, 2, _xlfn.LAMBDA(_xlpm.r,_xlpm.c, INDEX({"Data source","Data score";"International scope 3 database",1;"Australian scope 3 database",2;"State or regional scope 3 database",3;"Emissions intensity calculated from approved method",4;"Verified credential matching ISO14067",5}, _xlpm.r, _xlpm.c))))</definedName>
     <definedName name="Common_SourceData.Common_SourceData_DataScores_Scope3_Data">_xlfn.LAMBDA(_xlfn.MAKEARRAY(6, 2, _xlfn.LAMBDA(_xlpm.r,_xlpm.c, INDEX({"Data source","Data score";"International scope 3 database",1;"Australian scope 3 database",2;"State or regional scope 3 database",3;"Emissions intensity calculated from approved method",4;"Verified credential matching ISO14067",5}, _xlpm.r, _xlpm.c))))</definedName>
     <definedName name="Common_SourceData.Common_SourceData_DataScores_Scope3_Source">_xlfn.LAMBDA("VEERG 2026: XXXXXXXX")</definedName>
     <definedName name="Common_SourceData.Common_SourceData_DataScores_Scope3_Title">_xlfn.LAMBDA("Australian data scores for scope 3")</definedName>
@@ -163,26 +97,18 @@
     <definedName name="Common_SourceData.Common_SourceData_DensityOfMethane_Source">_xlfn.LAMBDA("National Inventory Report 2023 Volume 1: Equations 3.B.1a_2, 3.B.1c_2, 3.B.3_1, 3.B.4g_2")</definedName>
     <definedName name="Common_SourceData.Common_SourceData_DensityOfMethane_Title">_xlfn.LAMBDA("p = density of methane")</definedName>
     <definedName name="Common_SourceData.Common_SourceData_DensityOfMethane_Unit">_xlfn.LAMBDA("kg/m3")</definedName>
-    <definedName name="Common_SourceData.Common_SourceData_EFleach_Data" localSheetId="6">_xlfn.LAMBDA(_xlfn.MAKEARRAY(1, 2, _xlfn.LAMBDA(_xlpm.r,_xlpm.c, INDEX({"EFleach",0.011}, _xlpm.r, _xlpm.c))))</definedName>
-    <definedName name="Common_SourceData.Common_SourceData_EFleach_Data" localSheetId="4">_xlfn.LAMBDA(_xlfn.MAKEARRAY(1, 2, _xlfn.LAMBDA(_xlpm.r,_xlpm.c, INDEX({"EFleach",0.011}, _xlpm.r, _xlpm.c))))</definedName>
     <definedName name="Common_SourceData.Common_SourceData_EFleach_Data">_xlfn.LAMBDA(_xlfn.MAKEARRAY(1, 2, _xlfn.LAMBDA(_xlpm.r,_xlpm.c, INDEX({"EFleach",0.011}, _xlpm.r, _xlpm.c))))</definedName>
     <definedName name="Common_SourceData.Common_SourceData_EFleach_NIRReference">_xlfn.LAMBDA("National Inventory Report Volume 1: Equation 3.D.B_10")</definedName>
     <definedName name="Common_SourceData.Common_SourceData_EFleach_Source">_xlfn.LAMBDA("VEERG 2026:5.5.2.3 Constant Parameters")</definedName>
     <definedName name="Common_SourceData.Common_SourceData_EFleach_Title">_xlfn.LAMBDA("Emission factor for nitrogen leaching and runoff")</definedName>
     <definedName name="Common_SourceData.Common_SourceData_EFleach_Unit">_xlfn.LAMBDA("(kg N2O-N / kg N")</definedName>
     <definedName name="Common_SourceData.Common_SourceData_EFleach_Variation">_xlfn.LAMBDA((""))</definedName>
-    <definedName name="Common_SourceData.Common_SourceData_EFN2O_Data" localSheetId="6">_xlfn.LAMBDA(_xlfn.MAKEARRAY(15, 5, _xlfn.LAMBDA(_xlpm.r,_xlpm.c, INDEX({"Production system j","EFN2O","Production system only","Irrigation method","Rainfall zone";"Irrigated pasture",0.0059,"Pasture","Any","Any";"Irrigated crop",0.007,"Crop","Any","Any";"Non-irrigated pasture",0.0018,"Pasture","Not irrigated","Low rainfall";"Non-irrigated pasture",0.0018,"Pasture","Not irrigated","High rainfall";"Non-irrigated crop (low rainfall)",0.0029,"Crop","Not irrigated","Low rainfall";"Non-irrigated crop (high rainfall)",0.008,"Crop","Not irrigated","High rainfall";"Sugar",0.0199,"Sugar","Any","Any";"Cotton",0.0053,"Cotton","Any","Any";"Horticultural crops",0.0064,"Horticultural crops","Any","Any";"Rice (continuous flooding)",0.003,"Rice","Continuous flooding","Any";"Rice (single and multiple drainage, or alternate wetting and drying)",0.005,"Rice","Single and multiple drainage, or alternate wetting and drying","Any";"Aquaculture",0.0026,"Aquaculture","Any","Any";"Forestry",0.0018,"Forestry","Any","Any"}, _xlpm.r, _xlpm.c))))</definedName>
-    <definedName name="Common_SourceData.Common_SourceData_EFN2O_Data" localSheetId="4">_xlfn.LAMBDA(_xlfn.MAKEARRAY(15, 5, _xlfn.LAMBDA(_xlpm.r,_xlpm.c, INDEX({"Production system j","EFN2O","Production system only","Irrigation method","Rainfall zone";"Irrigated pasture",0.0059,"Pasture","Any","Any";"Irrigated crop",0.007,"Crop","Any","Any";"Non-irrigated pasture",0.0018,"Pasture","Not irrigated","Low rainfall";"Non-irrigated pasture",0.0018,"Pasture","Not irrigated","High rainfall";"Non-irrigated crop (low rainfall)",0.0029,"Crop","Not irrigated","Low rainfall";"Non-irrigated crop (high rainfall)",0.008,"Crop","Not irrigated","High rainfall";"Sugar",0.0199,"Sugar","Any","Any";"Cotton",0.0053,"Cotton","Any","Any";"Horticultural crops",0.0064,"Horticultural crops","Any","Any";"Rice (continuous flooding)",0.003,"Rice","Continuous flooding","Any";"Rice (single and multiple drainage, or alternate wetting and drying)",0.005,"Rice","Single and multiple drainage, or alternate wetting and drying","Any";"Aquaculture",0.0026,"Aquaculture","Any","Any";"Forestry",0.0018,"Forestry","Any","Any"}, _xlpm.r, _xlpm.c))))</definedName>
     <definedName name="Common_SourceData.Common_SourceData_EFN2O_Data">_xlfn.LAMBDA(_xlfn.MAKEARRAY(15, 5, _xlfn.LAMBDA(_xlpm.r,_xlpm.c, INDEX({"Production system j","EFN2O","Production system only","Irrigation method","Rainfall zone";"Irrigated pasture",0.0059,"Pasture","Any","Any";"Irrigated crop",0.007,"Crop","Any","Any";"Non-irrigated pasture",0.0018,"Pasture","Not irrigated","Low rainfall";"Non-irrigated pasture",0.0018,"Pasture","Not irrigated","High rainfall";"Non-irrigated crop (low rainfall)",0.0029,"Crop","Not irrigated","Low rainfall";"Non-irrigated crop (high rainfall)",0.008,"Crop","Not irrigated","High rainfall";"Sugar",0.0199,"Sugar","Any","Any";"Cotton",0.0053,"Cotton","Any","Any";"Horticultural crops",0.0064,"Horticultural crops","Any","Any";"Rice (continuous flooding)",0.003,"Rice","Continuous flooding","Any";"Rice (single and multiple drainage, or alternate wetting and drying)",0.005,"Rice","Single and multiple drainage, or alternate wetting and drying","Any";"Aquaculture",0.0026,"Aquaculture","Any","Any";"Forestry",0.0018,"Forestry","Any","Any"}, _xlpm.r, _xlpm.c))))</definedName>
     <definedName name="Common_SourceData.Common_SourceData_EFN2O_NIRReference">_xlfn.LAMBDA("")</definedName>
     <definedName name="Common_SourceData.Common_SourceData_EFN2O_Source">_xlfn.LAMBDA("VEERG 2026: Table A.2.2.1")</definedName>
     <definedName name="Common_SourceData.Common_SourceData_EFN2O_Title">_xlfn.LAMBDA("Nitrous oxide emission factors for inorganic fertiliser application")</definedName>
     <definedName name="Common_SourceData.Common_SourceData_EFN2O_Unit">_xlfn.LAMBDA("(kg N2O-N / kg N")</definedName>
-    <definedName name="Common_SourceData.Common_SourceData_EFN2O_Variation" localSheetId="6">_xlfn.LAMBDA(_xlfn.MAKEARRAY(5, 1, _xlfn.LAMBDA(_xlpm.r,_xlpm.c, INDEX({"VARIATION OF SOURCE DATA:";"Removed duplicate 'Aquaculture' row.";"Removed asterisks to aid lookup.";"Added 'production system only', 'rainfall zone' and 'irrigation method' columns to aid lookup.";"Duplicated 'non-irrigated pasture' row with same EF for low and high rainfall zones to aid lookup."}, _xlpm.r, _xlpm.c))))</definedName>
-    <definedName name="Common_SourceData.Common_SourceData_EFN2O_Variation" localSheetId="4">_xlfn.LAMBDA(_xlfn.MAKEARRAY(5, 1, _xlfn.LAMBDA(_xlpm.r,_xlpm.c, INDEX({"VARIATION OF SOURCE DATA:";"Removed duplicate 'Aquaculture' row.";"Removed asterisks to aid lookup.";"Added 'production system only', 'rainfall zone' and 'irrigation method' columns to aid lookup.";"Duplicated 'non-irrigated pasture' row with same EF for low and high rainfall zones to aid lookup."}, _xlpm.r, _xlpm.c))))</definedName>
     <definedName name="Common_SourceData.Common_SourceData_EFN2O_Variation">_xlfn.LAMBDA(_xlfn.MAKEARRAY(5, 1, _xlfn.LAMBDA(_xlpm.r,_xlpm.c, INDEX({"VARIATION OF SOURCE DATA:";"Removed duplicate 'Aquaculture' row.";"Removed asterisks to aid lookup.";"Added 'production system only', 'rainfall zone' and 'irrigation method' columns to aid lookup.";"Duplicated 'non-irrigated pasture' row with same EF for low and high rainfall zones to aid lookup."}, _xlpm.r, _xlpm.c))))</definedName>
-    <definedName name="Common_SourceData.Common_SourceData_EFOrganicFertiliserAndCropResidues_Data" localSheetId="6">_xlfn.LAMBDA(_xlfn.MAKEARRAY(3, 2, _xlfn.LAMBDA(_xlpm.r,_xlpm.c, INDEX({"Climate zone","EFNi &amp; EFN2O";"Wet climate zone",0.006;"Dry climate zone",0.005}, _xlpm.r, _xlpm.c))))</definedName>
-    <definedName name="Common_SourceData.Common_SourceData_EFOrganicFertiliserAndCropResidues_Data" localSheetId="4">_xlfn.LAMBDA(_xlfn.MAKEARRAY(3, 2, _xlfn.LAMBDA(_xlpm.r,_xlpm.c, INDEX({"Climate zone","EFNi &amp; EFN2O";"Wet climate zone",0.006;"Dry climate zone",0.005}, _xlpm.r, _xlpm.c))))</definedName>
     <definedName name="Common_SourceData.Common_SourceData_EFOrganicFertiliserAndCropResidues_Data">_xlfn.LAMBDA(_xlfn.MAKEARRAY(3, 2, _xlfn.LAMBDA(_xlpm.r,_xlpm.c, INDEX({"Climate zone","EFNi &amp; EFN2O";"Wet climate zone",0.006;"Dry climate zone",0.005}, _xlpm.r, _xlpm.c))))</definedName>
     <definedName name="Common_SourceData.Common_SourceData_EFOrganicFertiliserAndCropResidues_NIRReference">_xlfn.LAMBDA("")</definedName>
     <definedName name="Common_SourceData.Common_SourceData_EFOrganicFertiliserAndCropResidues_Source">_xlfn.LAMBDA("VEERG 2026: Table A.2.1.4")</definedName>
@@ -190,106 +116,84 @@
     <definedName name="Common_SourceData.Common_SourceData_EFOrganicFertiliserAndCropResidues_Unit">_xlfn.LAMBDA("kg N2O - N / kg N")</definedName>
     <definedName name="Common_SourceData.Common_SourceData_EFOrganicFertiliserAndCropResidues_Variable">_xlfn.LAMBDA("EFNi &amp; EFN2Oi")</definedName>
     <definedName name="Common_SourceData.Common_SourceData_EFOrganicFertiliserAndCropResidues_Variation">_xlfn.LAMBDA("")</definedName>
-    <definedName name="Common_SourceData.Common_SourceData_EFPastureRangeAndPaddock_Data" localSheetId="6">_xlfn.LAMBDA(_xlfn.MAKEARRAY(3, 2, _xlfn.LAMBDA(_xlpm.r,_xlpm.c, INDEX({"Climate zone","EFPRP";"Wet climate zone",0.006;"Dry climate zone",0.002}, _xlpm.r, _xlpm.c))))</definedName>
-    <definedName name="Common_SourceData.Common_SourceData_EFPastureRangeAndPaddock_Data" localSheetId="4">_xlfn.LAMBDA(_xlfn.MAKEARRAY(3, 2, _xlfn.LAMBDA(_xlpm.r,_xlpm.c, INDEX({"Climate zone","EFPRP";"Wet climate zone",0.006;"Dry climate zone",0.002}, _xlpm.r, _xlpm.c))))</definedName>
     <definedName name="Common_SourceData.Common_SourceData_EFPastureRangeAndPaddock_Data">_xlfn.LAMBDA(_xlfn.MAKEARRAY(3, 2, _xlfn.LAMBDA(_xlpm.r,_xlpm.c, INDEX({"Climate zone","EFPRP";"Wet climate zone",0.006;"Dry climate zone",0.002}, _xlpm.r, _xlpm.c))))</definedName>
     <definedName name="Common_SourceData.Common_SourceData_EFPastureRangeAndPaddock_NIRReference">_xlfn.LAMBDA("")</definedName>
     <definedName name="Common_SourceData.Common_SourceData_EFPastureRangeAndPaddock_Source">_xlfn.LAMBDA("VEERG 2026: Table A.2.2.2")</definedName>
     <definedName name="Common_SourceData.Common_SourceData_EFPastureRangeAndPaddock_Title">_xlfn.LAMBDA("Emission factor for urine and dung deposited on pasture, range or paddock")</definedName>
     <definedName name="Common_SourceData.Common_SourceData_EFPastureRangeAndPaddock_Unit">_xlfn.LAMBDA("kg N2O - N / kg N")</definedName>
     <definedName name="Common_SourceData.Common_SourceData_EFPastureRangeAndPaddock_Variation">_xlfn.LAMBDA("VARIATION FROM SOURCE DATA: Changed 'Dry climate zones' to singular 'Dry climate zone' to aid lookup.")</definedName>
-    <definedName name="Common_SourceData.Common_SourceData_FracLEACH_Data" localSheetId="6">_xlfn.LAMBDA(_xlfn.MAKEARRAY(1, 2, _xlfn.LAMBDA(_xlpm.r,_xlpm.c, INDEX({"FracLEACH",0.24}, _xlpm.r, _xlpm.c))))</definedName>
-    <definedName name="Common_SourceData.Common_SourceData_FracLEACH_Data" localSheetId="4">_xlfn.LAMBDA(_xlfn.MAKEARRAY(1, 2, _xlfn.LAMBDA(_xlpm.r,_xlpm.c, INDEX({"FracLEACH",0.24}, _xlpm.r, _xlpm.c))))</definedName>
     <definedName name="Common_SourceData.Common_SourceData_FracLEACH_Data">_xlfn.LAMBDA(_xlfn.MAKEARRAY(1, 2, _xlfn.LAMBDA(_xlpm.r,_xlpm.c, INDEX({"FracLEACH",0.24}, _xlpm.r, _xlpm.c))))</definedName>
     <definedName name="Common_SourceData.Common_SourceData_FracLEACH_NIRReference">_xlfn.LAMBDA("National Inventory Report Volume 1: Leaching and runoff (3.D.b.2)")</definedName>
     <definedName name="Common_SourceData.Common_SourceData_FracLEACH_Source">_xlfn.LAMBDA("VEERG 2026:5.5.2.3 Constant Parameters")</definedName>
     <definedName name="Common_SourceData.Common_SourceData_FracLEACH_Title">_xlfn.LAMBDA("Fraction of N that is available for leaching and runoff")</definedName>
     <definedName name="Common_SourceData.Common_SourceData_FracLEACH_Unit">_xlfn.LAMBDA("(Dimensionless")</definedName>
     <definedName name="Common_SourceData.Common_SourceData_FracLEACH_Variation">_xlfn.LAMBDA((""))</definedName>
-    <definedName name="Common_SourceData.Common_SourceData_FracWET_Data" localSheetId="6">_xlfn.LAMBDA(_xlfn.MAKEARRAY(3, 2, _xlfn.LAMBDA(_xlpm.r,_xlpm.c, INDEX({"Is in leaching zone","FracWET";"Yes - in leaching zone",1;"No - not in leaching zone",0}, _xlpm.r, _xlpm.c))))</definedName>
-    <definedName name="Common_SourceData.Common_SourceData_FracWET_Data" localSheetId="4">_xlfn.LAMBDA(_xlfn.MAKEARRAY(3, 2, _xlfn.LAMBDA(_xlpm.r,_xlpm.c, INDEX({"Is in leaching zone","FracWET";"Yes - in leaching zone",1;"No - not in leaching zone",0}, _xlpm.r, _xlpm.c))))</definedName>
     <definedName name="Common_SourceData.Common_SourceData_FracWET_Data">_xlfn.LAMBDA(_xlfn.MAKEARRAY(3, 2, _xlfn.LAMBDA(_xlpm.r,_xlpm.c, INDEX({"Is in leaching zone","FracWET";"Yes - in leaching zone",1;"No - not in leaching zone",0}, _xlpm.r, _xlpm.c))))</definedName>
     <definedName name="Common_SourceData.Common_SourceData_FracWET_NIRReference">_xlfn.LAMBDA("")</definedName>
     <definedName name="Common_SourceData.Common_SourceData_FracWET_Source">_xlfn.LAMBDA("VEERG 2026:5.5.2.3 Constant Parameters")</definedName>
     <definedName name="Common_SourceData.Common_SourceData_FracWET_Title">_xlfn.LAMBDA("Fraction of N that is available for leaching and runoff")</definedName>
     <definedName name="Common_SourceData.Common_SourceData_FracWET_Unit">_xlfn.LAMBDA("(Dimensionless")</definedName>
     <definedName name="Common_SourceData.Common_SourceData_FracWET_Variation">_xlfn.LAMBDA((""))</definedName>
-    <definedName name="Common_SourceData.Common_SourceData_FracWETIrrigation_Data" localSheetId="6">_xlfn.LAMBDA(_xlfn.MAKEARRAY(6, 2, _xlfn.LAMBDA(_xlpm.r,_xlpm.c, INDEX({"Irrigation type ir","FracWET";"Not irrigated",0;"Drip irrigation",0;"Sprinkler irrigation",1;"Surface irrigation",1;"Other irrigation",1}, _xlpm.r, _xlpm.c))))</definedName>
-    <definedName name="Common_SourceData.Common_SourceData_FracWETIrrigation_Data" localSheetId="4">_xlfn.LAMBDA(_xlfn.MAKEARRAY(6, 2, _xlfn.LAMBDA(_xlpm.r,_xlpm.c, INDEX({"Irrigation type ir","FracWET";"Not irrigated",0;"Drip irrigation",0;"Sprinkler irrigation",1;"Surface irrigation",1;"Other irrigation",1}, _xlpm.r, _xlpm.c))))</definedName>
     <definedName name="Common_SourceData.Common_SourceData_FracWETIrrigation_Data">_xlfn.LAMBDA(_xlfn.MAKEARRAY(6, 2, _xlfn.LAMBDA(_xlpm.r,_xlpm.c, INDEX({"Irrigation type ir","FracWET";"Not irrigated",0;"Drip irrigation",0;"Sprinkler irrigation",1;"Surface irrigation",1;"Other irrigation",1}, _xlpm.r, _xlpm.c))))</definedName>
     <definedName name="Common_SourceData.Common_SourceData_FracWETIrrigation_NIRReference">_xlfn.LAMBDA("IPCC 2019 Refinement Volume 4: Chapter 11: N2O Emissions from Managed Soils, and CO2 Emissions from Lime and Urea Application")</definedName>
     <definedName name="Common_SourceData.Common_SourceData_FracWETIrrigation_Source">_xlfn.LAMBDA("VEERG 2026: Chapter 1, section 1.8.2 Leaching, climate and rainfall zones")</definedName>
     <definedName name="Common_SourceData.Common_SourceData_FracWETIrrigation_Title">_xlfn.LAMBDA("FracWET for irrigation types")</definedName>
     <definedName name="Common_SourceData.Common_SourceData_FracWETIrrigation_Unit">_xlfn.LAMBDA("dimensionless")</definedName>
     <definedName name="Common_SourceData.Common_SourceData_FracWETIrrigation_Variation">_xlfn.LAMBDA("VARIATION FROM SOURCE DATA: Table created based on VEERG text 'Areas are subject to leaching (i.e., in the leaching zone) when... the land is irrigated (except drip irrigation).'")</definedName>
-    <definedName name="Common_SourceData.Common_SourceData_GWP_Data" localSheetId="6">_xlfn.LAMBDA(_xlfn.MAKEARRAY(8, 2, _xlfn.LAMBDA(_xlpm.r,_xlpm.c, INDEX({"Gas","CO2-e factor";"CO2",1;"CH4",28;"N2O",265;"CF4",6630;"C2F6",12200;"SF6",22800;"NF3",17200}, _xlpm.r, _xlpm.c))))</definedName>
-    <definedName name="Common_SourceData.Common_SourceData_GWP_Data" localSheetId="4">_xlfn.LAMBDA(_xlfn.MAKEARRAY(8, 2, _xlfn.LAMBDA(_xlpm.r,_xlpm.c, INDEX({"Gas","CO2-e factor";"CO2",1;"CH4",28;"N2O",265;"CF4",6630;"C2F6",12200;"SF6",22800;"NF3",17200}, _xlpm.r, _xlpm.c))))</definedName>
     <definedName name="Common_SourceData.Common_SourceData_GWP_Data">_xlfn.LAMBDA(_xlfn.MAKEARRAY(8, 2, _xlfn.LAMBDA(_xlpm.r,_xlpm.c, INDEX({"Gas","CO2-e factor";"CO2",1;"CH4",28;"N2O",265;"CF4",6630;"C2F6",12200;"SF6",22800;"NF3",17200}, _xlpm.r, _xlpm.c))))</definedName>
     <definedName name="Common_SourceData.Common_SourceData_GWP_Source">_xlfn.LAMBDA("XXXXXXX")</definedName>
     <definedName name="Common_SourceData.Common_SourceData_GWP_Title">_xlfn.LAMBDA("Global warming potential for greenhouse gases")</definedName>
     <definedName name="Common_SourceData.Common_SourceData_GWP_Unit">_xlfn.LAMBDA("factor")</definedName>
     <definedName name="Common_SourceData.Common_SourceData_GWP_Variable">_xlfn.LAMBDA("GWPN2O")</definedName>
-    <definedName name="Common_SourceData.Common_SourceData_LeachingZones_Data" localSheetId="6">_xlfn.LAMBDA(_xlfn.MAKEARRAY(4, 2, _xlfn.LAMBDA(_xlpm.r,_xlpm.c, INDEX({"Leaching Zone","Leaching criteria";"Leaching occurs","Σ(𝑟𝑎𝑖𝑛)&gt;Σ(𝐸𝑇0)+𝑠𝑜𝑖𝑙 𝑤𝑎𝑡𝑒𝑟 ℎ𝑜𝑙𝑑𝑖𝑛𝑔 𝑐𝑎𝑝𝑎𝑐𝑖𝑡𝑦";"Leaching does not occur","Σ(𝑟𝑎𝑖𝑛)≤Σ(𝐸𝑇0)+𝑠𝑜𝑖𝑙 𝑤𝑎𝑡𝑒𝑟 ℎ𝑜𝑙𝑑𝑖𝑛𝑔 𝑐𝑎𝑝𝑎𝑐𝑖𝑡𝑦"}, _xlpm.r, _xlpm.c))))</definedName>
-    <definedName name="Common_SourceData.Common_SourceData_LeachingZones_Data" localSheetId="4">_xlfn.LAMBDA(_xlfn.MAKEARRAY(4, 2, _xlfn.LAMBDA(_xlpm.r,_xlpm.c, INDEX({"Leaching Zone","Leaching criteria";"Leaching occurs","Σ(𝑟𝑎𝑖𝑛)&gt;Σ(𝐸𝑇0)+𝑠𝑜𝑖𝑙 𝑤𝑎𝑡𝑒𝑟 ℎ𝑜𝑙𝑑𝑖𝑛𝑔 𝑐𝑎𝑝𝑎𝑐𝑖𝑡𝑦";"Leaching does not occur","Σ(𝑟𝑎𝑖𝑛)≤Σ(𝐸𝑇0)+𝑠𝑜𝑖𝑙 𝑤𝑎𝑡𝑒𝑟 ℎ𝑜𝑙𝑑𝑖𝑛𝑔 𝑐𝑎𝑝𝑎𝑐𝑖𝑡𝑦"}, _xlpm.r, _xlpm.c))))</definedName>
     <definedName name="Common_SourceData.Common_SourceData_LeachingZones_Data">_xlfn.LAMBDA(_xlfn.MAKEARRAY(4, 2, _xlfn.LAMBDA(_xlpm.r,_xlpm.c, INDEX({"Leaching Zone","Leaching criteria";"Leaching occurs","Σ(𝑟𝑎𝑖𝑛)&gt;Σ(𝐸𝑇0)+𝑠𝑜𝑖𝑙 𝑤𝑎𝑡𝑒𝑟 ℎ𝑜𝑙𝑑𝑖𝑛𝑔 𝑐𝑎𝑝𝑎𝑐𝑖𝑡𝑦";"Leaching does not occur","Σ(𝑟𝑎𝑖𝑛)≤Σ(𝐸𝑇0)+𝑠𝑜𝑖𝑙 𝑤𝑎𝑡𝑒𝑟 ℎ𝑜𝑙𝑑𝑖𝑛𝑔 𝑐𝑎𝑝𝑎𝑐𝑖𝑡𝑦"}, _xlpm.r, _xlpm.c))))</definedName>
     <definedName name="Common_SourceData.Common_SourceData_LeachingZones_Source">_xlfn.LAMBDA("VEERG 2026: Table 1.3: Climate and Rainfall zone classifications and definitions")</definedName>
     <definedName name="Common_SourceData.Common_SourceData_LeachingZones_Title">_xlfn.LAMBDA("VEERG Australian leaching zones")</definedName>
     <definedName name="Common_SourceData.Common_SourceData_LeachingZones_Unit">_xlfn.LAMBDA("")</definedName>
     <definedName name="Common_SourceData.Common_SourceData_LeachingZones_Variable">_xlfn.LAMBDA("")</definedName>
     <definedName name="Common_SourceData.Common_SourceData_LeachingZones_Variation">_xlfn.LAMBDA("")</definedName>
-    <definedName name="Common_SourceData.Common_SourceData_MCFTemperatureZone_Data" localSheetId="6">_xlfn.LAMBDA(_xlfn.MAKEARRAY(22, 16, _xlfn.LAMBDA(_xlpm.r,_xlpm.c, INDEX({"Temperature zone","MAT (ºC)","Uncovered anerobic lagoon","Covered lagoon","Liquid Slurry (without natural crust)","Daily spread (b)","Composting (passive windrow)","Solid Storage","Pit Storage &lt;1 month","Deep Litter","Poultry Manure (with/without litter)","","Direct processing into pelletized fertiliser","Direct application to soil","Pasture, Range and Paddock (c)(d)","MAT raw";"Cool","≤10",0.66,0.1,0.1,0.001,0.005,0.02,0.03,0.04,0.015,0.015,0,0,0.0047,10;"Cool",11,0.68,0.1,0.11,0.001,0.005,0.02,0.03,0.04,0.015,0.015,0,0,0.0047,11;"Cool",12,0.7,0.1,0.13,0.001,0.005,0.02,0.03,0.04,0.015,0.015,0,0,0.0047,12;"Cool",13,0.71,0.1,0.14,0.001,0.005,0.02,0.03,0.04,0.015,0.015,0,0,0.0047,13;"Cool",14,0.73,0.1,0.15,0.001,0.005,0.02,0.03,0.04,0.015,0.015,0,0,0.0047,14;"Temperate",15,0.74,0.1,0.17,0.005,0.01,0.02,0.03,0.04,0.015,0.015,0,0,0.0047,15;"Temperate",16,0.75,0.1,0.18,0.005,0.01,0.02,0.03,0.04,0.015,0.015,0,0,0.0047,16;"Temperate",17,0.76,0.1,0.2,0.005,0.01,0.02,0.03,0.04,0.015,0.015,0,0,0.0047,17;"Temperate",18,0.77,0.1,0.22,0.005,0.01,0.02,0.03,0.04,0.015,0.015,0,0,0.0047,18;"Temperate",19,0.77,0.1,0.24,0.005,0.01,0.02,0.03,0.04,0.015,0.015,0,0,0.0047,19;"Temperate",20,0.78,0.1,0.26,0.005,0.01,0.02,0.03,0.04,0.015,0.015,0,0,0.0047,20;"Temperate",21,0.78,0.1,0.29,0.005,0.01,0.02,0.03,0.04,0.015,0.015,0,0,0.0047,21;"Temperate",22,0.78,0.1,0.31,0.005,0.01,0.02,0.03,0.04,0.015,0.015,0,0,0.0047,22;"Temperate",23,0.79,0.1,0.34,0.005,0.01,0.02,0.03,0.04,0.015,0.015,0,0,0.0047,23;"Temperate",24,0.79,0.1,0.37,0.005,0.01,0.02,0.03,0.04,0.015,0.015,0,0,0.0047,24;"Temperate",25,0.79,0.1,0.41,0.005,0.01,0.02,0.03,0.04,0.015,0.015,0,0,0.0047,25;"Warm",26,0.79,0.1,0.44,0.01,0.015,0.02,0.03,0.04,0.015,0.015,0,0,0.0047,26;"Warm",27,0.8,0.1,0.48,0.01,0.015,0.02,0.03,0.04,0.015,0.015,0,0,0.0047,27;"Warm","≥28",0.8,0.1,0.5,0.01,0.015,0.02,0.03,0.04,0.015,0.015,0,0,0.0047,28;"","","Anaerobic lagoon","Digester / covered lagoons","Liquid systems","Daily spread","Composting (passive windrow)","Solid storage","Pit storage","Deep litter","Poultry manure with bedding","Poultry manure without bedding","Direct processing","Direct application","Pasture range and paddock","MAT raw"}, _xlpm.r, _xlpm.c))))</definedName>
-    <definedName name="Common_SourceData.Common_SourceData_MCFTemperatureZone_Data" localSheetId="4">_xlfn.LAMBDA(_xlfn.MAKEARRAY(22, 16, _xlfn.LAMBDA(_xlpm.r,_xlpm.c, INDEX({"Temperature zone","MAT (ºC)","Uncovered anerobic lagoon","Covered lagoon","Liquid Slurry (without natural crust)","Daily spread (b)","Composting (passive windrow)","Solid Storage","Pit Storage &lt;1 month","Deep Litter","Poultry Manure (with/without litter)","","Direct processing into pelletized fertiliser","Direct application to soil","Pasture, Range and Paddock (c)(d)","MAT raw";"Cool","≤10",0.66,0.1,0.1,0.001,0.005,0.02,0.03,0.04,0.015,0.015,0,0,0.0047,10;"Cool",11,0.68,0.1,0.11,0.001,0.005,0.02,0.03,0.04,0.015,0.015,0,0,0.0047,11;"Cool",12,0.7,0.1,0.13,0.001,0.005,0.02,0.03,0.04,0.015,0.015,0,0,0.0047,12;"Cool",13,0.71,0.1,0.14,0.001,0.005,0.02,0.03,0.04,0.015,0.015,0,0,0.0047,13;"Cool",14,0.73,0.1,0.15,0.001,0.005,0.02,0.03,0.04,0.015,0.015,0,0,0.0047,14;"Temperate",15,0.74,0.1,0.17,0.005,0.01,0.02,0.03,0.04,0.015,0.015,0,0,0.0047,15;"Temperate",16,0.75,0.1,0.18,0.005,0.01,0.02,0.03,0.04,0.015,0.015,0,0,0.0047,16;"Temperate",17,0.76,0.1,0.2,0.005,0.01,0.02,0.03,0.04,0.015,0.015,0,0,0.0047,17;"Temperate",18,0.77,0.1,0.22,0.005,0.01,0.02,0.03,0.04,0.015,0.015,0,0,0.0047,18;"Temperate",19,0.77,0.1,0.24,0.005,0.01,0.02,0.03,0.04,0.015,0.015,0,0,0.0047,19;"Temperate",20,0.78,0.1,0.26,0.005,0.01,0.02,0.03,0.04,0.015,0.015,0,0,0.0047,20;"Temperate",21,0.78,0.1,0.29,0.005,0.01,0.02,0.03,0.04,0.015,0.015,0,0,0.0047,21;"Temperate",22,0.78,0.1,0.31,0.005,0.01,0.02,0.03,0.04,0.015,0.015,0,0,0.0047,22;"Temperate",23,0.79,0.1,0.34,0.005,0.01,0.02,0.03,0.04,0.015,0.015,0,0,0.0047,23;"Temperate",24,0.79,0.1,0.37,0.005,0.01,0.02,0.03,0.04,0.015,0.015,0,0,0.0047,24;"Temperate",25,0.79,0.1,0.41,0.005,0.01,0.02,0.03,0.04,0.015,0.015,0,0,0.0047,25;"Warm",26,0.79,0.1,0.44,0.01,0.015,0.02,0.03,0.04,0.015,0.015,0,0,0.0047,26;"Warm",27,0.8,0.1,0.48,0.01,0.015,0.02,0.03,0.04,0.015,0.015,0,0,0.0047,27;"Warm","≥28",0.8,0.1,0.5,0.01,0.015,0.02,0.03,0.04,0.015,0.015,0,0,0.0047,28;"","","Anaerobic lagoon","Digester / covered lagoons","Liquid systems","Daily spread","Composting (passive windrow)","Solid storage","Pit storage","Deep litter","Poultry manure with bedding","Poultry manure without bedding","Direct processing","Direct application","Pasture range and paddock","MAT raw"}, _xlpm.r, _xlpm.c))))</definedName>
     <definedName name="Common_SourceData.Common_SourceData_MCFTemperatureZone_Data">_xlfn.LAMBDA(_xlfn.MAKEARRAY(22, 16, _xlfn.LAMBDA(_xlpm.r,_xlpm.c, INDEX({"Temperature zone","MAT (ºC)","Uncovered anerobic lagoon","Covered lagoon","Liquid Slurry (without natural crust)","Daily spread (b)","Composting (passive windrow)","Solid Storage","Pit Storage &lt;1 month","Deep Litter","Poultry Manure (with/without litter)","","Direct processing into pelletized fertiliser","Direct application to soil","Pasture, Range and Paddock (c)(d)","MAT raw";"Cool","≤10",0.66,0.1,0.1,0.001,0.005,0.02,0.03,0.04,0.015,0.015,0,0,0.0047,10;"Cool",11,0.68,0.1,0.11,0.001,0.005,0.02,0.03,0.04,0.015,0.015,0,0,0.0047,11;"Cool",12,0.7,0.1,0.13,0.001,0.005,0.02,0.03,0.04,0.015,0.015,0,0,0.0047,12;"Cool",13,0.71,0.1,0.14,0.001,0.005,0.02,0.03,0.04,0.015,0.015,0,0,0.0047,13;"Cool",14,0.73,0.1,0.15,0.001,0.005,0.02,0.03,0.04,0.015,0.015,0,0,0.0047,14;"Temperate",15,0.74,0.1,0.17,0.005,0.01,0.02,0.03,0.04,0.015,0.015,0,0,0.0047,15;"Temperate",16,0.75,0.1,0.18,0.005,0.01,0.02,0.03,0.04,0.015,0.015,0,0,0.0047,16;"Temperate",17,0.76,0.1,0.2,0.005,0.01,0.02,0.03,0.04,0.015,0.015,0,0,0.0047,17;"Temperate",18,0.77,0.1,0.22,0.005,0.01,0.02,0.03,0.04,0.015,0.015,0,0,0.0047,18;"Temperate",19,0.77,0.1,0.24,0.005,0.01,0.02,0.03,0.04,0.015,0.015,0,0,0.0047,19;"Temperate",20,0.78,0.1,0.26,0.005,0.01,0.02,0.03,0.04,0.015,0.015,0,0,0.0047,20;"Temperate",21,0.78,0.1,0.29,0.005,0.01,0.02,0.03,0.04,0.015,0.015,0,0,0.0047,21;"Temperate",22,0.78,0.1,0.31,0.005,0.01,0.02,0.03,0.04,0.015,0.015,0,0,0.0047,22;"Temperate",23,0.79,0.1,0.34,0.005,0.01,0.02,0.03,0.04,0.015,0.015,0,0,0.0047,23;"Temperate",24,0.79,0.1,0.37,0.005,0.01,0.02,0.03,0.04,0.015,0.015,0,0,0.0047,24;"Temperate",25,0.79,0.1,0.41,0.005,0.01,0.02,0.03,0.04,0.015,0.015,0,0,0.0047,25;"Warm",26,0.79,0.1,0.44,0.01,0.015,0.02,0.03,0.04,0.015,0.015,0,0,0.0047,26;"Warm",27,0.8,0.1,0.48,0.01,0.015,0.02,0.03,0.04,0.015,0.015,0,0,0.0047,27;"Warm","≥28",0.8,0.1,0.5,0.01,0.015,0.02,0.03,0.04,0.015,0.015,0,0,0.0047,28;"","","Anaerobic lagoon","Digester / covered lagoons","Liquid systems","Daily spread","Composting (passive windrow)","Solid storage","Pit storage","Deep litter","Poultry manure with bedding","Poultry manure without bedding","Direct processing","Direct application","Pasture range and paddock","MAT raw"}, _xlpm.r, _xlpm.c))))</definedName>
     <definedName name="Common_SourceData.Common_SourceData_MCFTemperatureZone_Source">_xlfn.LAMBDA("VEERG 2026: Table A.1.8.1")</definedName>
     <definedName name="Common_SourceData.Common_SourceData_MCFTemperatureZone_Title">_xlfn.LAMBDA("Manure Management – Methane conversion factor per temperature zone (fraction) (MCFim)")</definedName>
     <definedName name="Common_SourceData.Common_SourceData_MCFTemperatureZone_Unit">_xlfn.LAMBDA("fraction")</definedName>
     <definedName name="Common_SourceData.Common_SourceData_MCFTemperatureZone_Variation">_xlfn.LAMBDA("VARIATION FROM SOURCE: Added row of NIR MMA definitions to aid lookup. Duplicated 'Poultry with and without litter' column with separate NIR definitions to aid lookup. Added 'MAT raw' column to allow lookup of numbers.")</definedName>
-    <definedName name="Common_SourceData.Common_SourceData_MonthsToSeasons_Data" localSheetId="6">_xlfn.LAMBDA(_xlfn.MAKEARRAY(13, 2, _xlfn.LAMBDA(_xlpm.r,_xlpm.c, INDEX({"Month","Season";"January","Summer";"February","Summer";"March","Autumn";"April","Autumn";"May","Autumn";"June","Winter";"July","Winter";"August","Winter";"September","Spring";"October","Spring";"November","Spring";"December","Summer"}, _xlpm.r, _xlpm.c))))</definedName>
-    <definedName name="Common_SourceData.Common_SourceData_MonthsToSeasons_Data" localSheetId="4">_xlfn.LAMBDA(_xlfn.MAKEARRAY(13, 2, _xlfn.LAMBDA(_xlpm.r,_xlpm.c, INDEX({"Month","Season";"January","Summer";"February","Summer";"March","Autumn";"April","Autumn";"May","Autumn";"June","Winter";"July","Winter";"August","Winter";"September","Spring";"October","Spring";"November","Spring";"December","Summer"}, _xlpm.r, _xlpm.c))))</definedName>
     <definedName name="Common_SourceData.Common_SourceData_MonthsToSeasons_Data">_xlfn.LAMBDA(_xlfn.MAKEARRAY(13, 2, _xlfn.LAMBDA(_xlpm.r,_xlpm.c, INDEX({"Month","Season";"January","Summer";"February","Summer";"March","Autumn";"April","Autumn";"May","Autumn";"June","Winter";"July","Winter";"August","Winter";"September","Spring";"October","Spring";"November","Spring";"December","Summer"}, _xlpm.r, _xlpm.c))))</definedName>
     <definedName name="Common_SourceData.Common_SourceData_MonthsToSeasons_NIRReference">_xlfn.LAMBDA("")</definedName>
     <definedName name="Common_SourceData.Common_SourceData_MonthsToSeasons_Source">_xlfn.LAMBDA("")</definedName>
     <definedName name="Common_SourceData.Common_SourceData_MonthsToSeasons_Title">_xlfn.LAMBDA("Months to Seasons Mapping")</definedName>
     <definedName name="Common_SourceData.Common_SourceData_MonthsToSeasons_Unit">_xlfn.LAMBDA("")</definedName>
     <definedName name="Common_SourceData.Common_SourceData_MonthsToSeasons_Variation">_xlfn.LAMBDA("")</definedName>
-    <definedName name="Common_SourceData.Common_SourceData_RainfallZones_Data" localSheetId="6">_xlfn.LAMBDA(_xlfn.MAKEARRAY(3, 4, _xlfn.LAMBDA(_xlpm.r,_xlpm.c, INDEX({"Rainfall Zone","Annual rainfall","Rainfall min","Rainfall max";"High rainfall","Annual rainfall &gt; 600mm",600.001,999999;"Low rainfall","Annual rainfall ≤ 600mm",-999999,600}, _xlpm.r, _xlpm.c))))</definedName>
-    <definedName name="Common_SourceData.Common_SourceData_RainfallZones_Data" localSheetId="4">_xlfn.LAMBDA(_xlfn.MAKEARRAY(3, 4, _xlfn.LAMBDA(_xlpm.r,_xlpm.c, INDEX({"Rainfall Zone","Annual rainfall","Rainfall min","Rainfall max";"High rainfall","Annual rainfall &gt; 600mm",600.001,999999;"Low rainfall","Annual rainfall ≤ 600mm",-999999,600}, _xlpm.r, _xlpm.c))))</definedName>
     <definedName name="Common_SourceData.Common_SourceData_RainfallZones_Data">_xlfn.LAMBDA(_xlfn.MAKEARRAY(3, 4, _xlfn.LAMBDA(_xlpm.r,_xlpm.c, INDEX({"Rainfall Zone","Annual rainfall","Rainfall min","Rainfall max";"High rainfall","Annual rainfall &gt; 600mm",600.001,999999;"Low rainfall","Annual rainfall ≤ 600mm",-999999,600}, _xlpm.r, _xlpm.c))))</definedName>
     <definedName name="Common_SourceData.Common_SourceData_RainfallZones_Source">_xlfn.LAMBDA("VEERG 2026: Table 1.3: Climate and Rainfall zone classifications and definitions")</definedName>
     <definedName name="Common_SourceData.Common_SourceData_RainfallZones_Title">_xlfn.LAMBDA("VEERG Australian rainfall zones")</definedName>
     <definedName name="Common_SourceData.Common_SourceData_RainfallZones_Unit">_xlfn.LAMBDA("")</definedName>
     <definedName name="Common_SourceData.Common_SourceData_RainfallZones_Variable">_xlfn.LAMBDA("")</definedName>
     <definedName name="Common_SourceData.Common_SourceData_RainfallZones_Variation">_xlfn.LAMBDA("VARIATION OF SOURCE DATA: Added extra Rainfall min and Rainfall max columns to calculate zone from real rainfall data.")</definedName>
-    <definedName name="Common_SourceData.Common_SourceData_TemperatureZones_Data" localSheetId="6">_xlfn.LAMBDA(_xlfn.MAKEARRAY(4, 4, _xlfn.LAMBDA(_xlpm.r,_xlpm.c, INDEX({"Temperature Zone","Median Annual Temperature (MAT)","Min MAT","Max MAT";"Warm","≥ 26 C",26,999999;"Temperate","15 - 25 C",15,25.999;"Cool","≤ 14 C",-999999,14.999}, _xlpm.r, _xlpm.c))))</definedName>
-    <definedName name="Common_SourceData.Common_SourceData_TemperatureZones_Data" localSheetId="4">_xlfn.LAMBDA(_xlfn.MAKEARRAY(4, 4, _xlfn.LAMBDA(_xlpm.r,_xlpm.c, INDEX({"Temperature Zone","Median Annual Temperature (MAT)","Min MAT","Max MAT";"Warm","≥ 26 C",26,999999;"Temperate","15 - 25 C",15,25.999;"Cool","≤ 14 C",-999999,14.999}, _xlpm.r, _xlpm.c))))</definedName>
     <definedName name="Common_SourceData.Common_SourceData_TemperatureZones_Data">_xlfn.LAMBDA(_xlfn.MAKEARRAY(4, 4, _xlfn.LAMBDA(_xlpm.r,_xlpm.c, INDEX({"Temperature Zone","Median Annual Temperature (MAT)","Min MAT","Max MAT";"Warm","≥ 26 C",26,999999;"Temperate","15 - 25 C",15,25.999;"Cool","≤ 14 C",-999999,14.999}, _xlpm.r, _xlpm.c))))</definedName>
     <definedName name="Common_SourceData.Common_SourceData_TemperatureZones_Source">_xlfn.LAMBDA("VEERG 2026: Table 1.3: Climate and Rainfall zone classifications and definitions")</definedName>
     <definedName name="Common_SourceData.Common_SourceData_TemperatureZones_Title">_xlfn.LAMBDA("VEERG Australian temperature zones")</definedName>
     <definedName name="Common_SourceData.Common_SourceData_TemperatureZones_Unit">_xlfn.LAMBDA("")</definedName>
     <definedName name="Common_SourceData.Common_SourceData_TemperatureZones_Variable">_xlfn.LAMBDA("")</definedName>
     <definedName name="Common_SourceData.Common_SourceData_TemperatureZones_Variation">_xlfn.LAMBDA("VARIATION OF SOURCE DATA: Added extra MAT min and MAT max columns to calculate zone from real temperature data.")</definedName>
-    <definedName name="Common_SourceData.Common_SourceData_WASA4Areas_Data" localSheetId="6">_xlfn.LAMBDA(_xlfn.MAKEARRAY(11, 1, _xlfn.LAMBDA(_xlpm.r,_xlpm.c, INDEX({"SA 4 Name";"Bunbury";"Mandurah";"Perth - Inner";"Perth - North East";"Perth - North West";"Perth - South East";"Perth - South West";"Western Australia - Wheat Belt";"Western Australia - Outback (North)";"Western Australia - Outback (South)"}, _xlpm.r, _xlpm.c))))</definedName>
-    <definedName name="Common_SourceData.Common_SourceData_WASA4Areas_Data" localSheetId="4">_xlfn.LAMBDA(_xlfn.MAKEARRAY(11, 1, _xlfn.LAMBDA(_xlpm.r,_xlpm.c, INDEX({"SA 4 Name";"Bunbury";"Mandurah";"Perth - Inner";"Perth - North East";"Perth - North West";"Perth - South East";"Perth - South West";"Western Australia - Wheat Belt";"Western Australia - Outback (North)";"Western Australia - Outback (South)"}, _xlpm.r, _xlpm.c))))</definedName>
     <definedName name="Common_SourceData.Common_SourceData_WASA4Areas_Data">_xlfn.LAMBDA(_xlfn.MAKEARRAY(11, 1, _xlfn.LAMBDA(_xlpm.r,_xlpm.c, INDEX({"SA 4 Name";"Bunbury";"Mandurah";"Perth - Inner";"Perth - North East";"Perth - North West";"Perth - South East";"Perth - South West";"Western Australia - Wheat Belt";"Western Australia - Outback (North)";"Western Australia - Outback (South)"}, _xlpm.r, _xlpm.c))))</definedName>
     <definedName name="Common_SourceData.Common_SourceData_WASA4Areas_Source">_xlfn.LAMBDA("Australian Bureau of Statistics (ABS) - Statistical Areas Level 2 - 2021 - Shapefile")</definedName>
     <definedName name="Common_SourceData.Common_SourceData_WASA4Areas_Title">_xlfn.LAMBDA("ABS Statistcal Areas Level 4 - Western Australia")</definedName>
     <definedName name="Common_SourceData.Common_SourceData_WASA4Areas_Unit">_xlfn.LAMBDA("")</definedName>
     <definedName name="Common_SourceData.Common_SourceData_WASA4Areas_Variable">_xlfn.LAMBDA("")</definedName>
-    <definedName name="Common_SourceData.Common_SourceData_WetAndDryZones_Data" localSheetId="6">_xlfn.LAMBDA(_xlfn.MAKEARRAY(15, 2, _xlfn.LAMBDA(_xlpm.r,_xlpm.c, INDEX({"Climate Zone","Wet or Dry Zone";"Tropical montane","Wet climate zone";"Tropical wet","Wet climate zone";"Tropical moist","Wet climate zone";"Tropical dry","Dry climate zone";"Warm temperate moist","Wet climate zone";"Warm temperate dry","Dry climate zone";"Cool temperate moist","Wet climate zone";"Cool temperate dry","Dry climate zone";"Warm temperate moist - low frost","Wet climate zone";"Warm temperate dry - low frost","Dry climate zone";"Warm temperate moist - high temp","Wet climate zone";"Warm temperate dry - high temp","Dry climate zone";"Cool temperate moist - low frost","Wet climate zone";"Cool temperate dry - low frost","Dry climate zone"}, _xlpm.r, _xlpm.c))))</definedName>
-    <definedName name="Common_SourceData.Common_SourceData_WetAndDryZones_Data" localSheetId="4">_xlfn.LAMBDA(_xlfn.MAKEARRAY(15, 2, _xlfn.LAMBDA(_xlpm.r,_xlpm.c, INDEX({"Climate Zone","Wet or Dry Zone";"Tropical montane","Wet climate zone";"Tropical wet","Wet climate zone";"Tropical moist","Wet climate zone";"Tropical dry","Dry climate zone";"Warm temperate moist","Wet climate zone";"Warm temperate dry","Dry climate zone";"Cool temperate moist","Wet climate zone";"Cool temperate dry","Dry climate zone";"Warm temperate moist - low frost","Wet climate zone";"Warm temperate dry - low frost","Dry climate zone";"Warm temperate moist - high temp","Wet climate zone";"Warm temperate dry - high temp","Dry climate zone";"Cool temperate moist - low frost","Wet climate zone";"Cool temperate dry - low frost","Dry climate zone"}, _xlpm.r, _xlpm.c))))</definedName>
     <definedName name="Common_SourceData.Common_SourceData_WetAndDryZones_Data">_xlfn.LAMBDA(_xlfn.MAKEARRAY(15, 2, _xlfn.LAMBDA(_xlpm.r,_xlpm.c, INDEX({"Climate Zone","Wet or Dry Zone";"Tropical montane","Wet climate zone";"Tropical wet","Wet climate zone";"Tropical moist","Wet climate zone";"Tropical dry","Dry climate zone";"Warm temperate moist","Wet climate zone";"Warm temperate dry","Dry climate zone";"Cool temperate moist","Wet climate zone";"Cool temperate dry","Dry climate zone";"Warm temperate moist - low frost","Wet climate zone";"Warm temperate dry - low frost","Dry climate zone";"Warm temperate moist - high temp","Wet climate zone";"Warm temperate dry - high temp","Dry climate zone";"Cool temperate moist - low frost","Wet climate zone";"Cool temperate dry - low frost","Dry climate zone"}, _xlpm.r, _xlpm.c))))</definedName>
     <definedName name="Common_SourceData.Common_SourceData_WetAndDryZones_Source">_xlfn.LAMBDA("VEERG 2026: Table 1.2: Translating climate zones to wet and dry zones")</definedName>
     <definedName name="Common_SourceData.Common_SourceData_WetAndDryZones_Title">_xlfn.LAMBDA("VEERG Australian wet and dry zones")</definedName>
     <definedName name="Common_SourceData.Common_SourceData_WetAndDryZones_Unit">_xlfn.LAMBDA("")</definedName>
     <definedName name="Common_SourceData.Common_SourceData_WetAndDryZones_Variable">_xlfn.LAMBDA("")</definedName>
-    <definedName name="Common_SourceData.Common_SourceData_WetAndDryZones_Variation" localSheetId="6">_xlfn.LAMBDA(_xlfn.MAKEARRAY(3, 1, _xlfn.LAMBDA(_xlpm.r,_xlpm.c, INDEX({"VARIATION OF SOURCE DATA:";"Added warm / cool temperate moist / dry - low frost and high temp classes to accommodate climate scenarios excluded by VEERG criteria.";"Fixed typo - Changed 'Fry' to 'Dry'."}, _xlpm.r, _xlpm.c))))</definedName>
-    <definedName name="Common_SourceData.Common_SourceData_WetAndDryZones_Variation" localSheetId="4">_xlfn.LAMBDA(_xlfn.MAKEARRAY(3, 1, _xlfn.LAMBDA(_xlpm.r,_xlpm.c, INDEX({"VARIATION OF SOURCE DATA:";"Added warm / cool temperate moist / dry - low frost and high temp classes to accommodate climate scenarios excluded by VEERG criteria.";"Fixed typo - Changed 'Fry' to 'Dry'."}, _xlpm.r, _xlpm.c))))</definedName>
     <definedName name="Common_SourceData.Common_SourceData_WetAndDryZones_Variation">_xlfn.LAMBDA(_xlfn.MAKEARRAY(3, 1, _xlfn.LAMBDA(_xlpm.r,_xlpm.c, INDEX({"VARIATION OF SOURCE DATA:";"Added warm / cool temperate moist / dry - low frost and high temp classes to accommodate climate scenarios excluded by VEERG criteria.";"Fixed typo - Changed 'Fry' to 'Dry'."}, _xlpm.r, _xlpm.c))))</definedName>
+    <definedName name="Common_SourceData_DensityOfMethane_Data">'Constants - Common'!$D$175</definedName>
     <definedName name="CommonLivestock_InputFunctions.AverageLiveweightEndOfMonth">_xlfn.LAMBDA(_xlpm.Month,_xlpm.LivestockClass,_xlpm.HeadAtStart,_xlpm.LiveweightAtStart,_xlpm.LiveweightGain, [0]!CommonLivestock_InputFunctions.LivestockMovement_ProportionalAverageLiveweightAddedDuringMonth(_xlpm.Month, _xlpm.LivestockClass, _xlpm.HeadAtStart) + [0]!CommonLivestock_InputFunctions.LivestockMovement_ProportionalAverageLiveweightRemainingAtEndOfMonth(_xlpm.Month, _xlpm.LivestockClass, _xlpm.HeadAtStart, _xlpm.LiveweightAtStart, _xlpm.LiveweightGain))</definedName>
     <definedName name="CommonLivestock_InputFunctions.LivestockMovement_AverageLiveweightAddedDuringMonth">_xlfn.LAMBDA(_xlpm.Month,_xlpm.LivestockClass, IFERROR([0]!CommonLivestock_InputFunctions.LivestockMovement_TotalLiveweightAddedDuringMonth(_xlpm.Month, _xlpm.LivestockClass) / [0]!CommonLivestock_InputFunctions.LivestockMovement_HeadAddedDuringMonth(_xlpm.Month, _xlpm.LivestockClass), 0))</definedName>
+    <definedName name="CommonLivestock_InputFunctions.LivestockMovement_GetMovementLiveweightGain" localSheetId="7">_xlfn.LAMBDA(_xlpm.LivestockClass,_xlpm.MovementDate, _xlfn.LET(_xlpm.ym, TEXT(_xlpm.MovementDate, "yyyymm"), IFERROR(INDEX(_xlfn._xlws.FILTER(#REF!, (TEXT(#REF!, "yyyymm") = _xlpm.ym) * (#REF! = _xlpm.LivestockClass)), 1), "")))</definedName>
     <definedName name="CommonLivestock_InputFunctions.LivestockMovement_GetMovementLiveweightGain">_xlfn.LAMBDA(_xlpm.LivestockClass,_xlpm.MovementDate, _xlfn.LET(_xlpm.ym, TEXT(_xlpm.MovementDate, "yyyymm"), IFERROR(INDEX(_xlfn._xlws.FILTER(#REF!, (TEXT(#REF!, "yyyymm") = _xlpm.ym) * (#REF! = _xlpm.LivestockClass)), 1), "")))</definedName>
+    <definedName name="CommonLivestock_InputFunctions.LivestockMovement_HeadAddedDuringMonth" localSheetId="7">_xlfn.LAMBDA(_xlpm.Month,_xlpm.LivestockClass, IFERROR(SUM(_xlfn._xlws.FILTER(#REF!, (#REF! &gt;= EOMONTH(_xlpm.Month, -1) + 1) * (#REF! &lt;= EOMONTH(_xlpm.Month, 0)) * (#REF! = _xlpm.LivestockClass))), 0))</definedName>
     <definedName name="CommonLivestock_InputFunctions.LivestockMovement_HeadAddedDuringMonth">_xlfn.LAMBDA(_xlpm.Month,_xlpm.LivestockClass, IFERROR(SUM(_xlfn._xlws.FILTER(#REF!, (#REF! &gt;= EOMONTH(_xlpm.Month, -1) + 1) * (#REF! &lt;= EOMONTH(_xlpm.Month, 0)) * (#REF! = _xlpm.LivestockClass))), 0))</definedName>
     <definedName name="CommonLivestock_InputFunctions.LivestockMovement_HeadAtEndOfMonth">_xlfn.LAMBDA(_xlpm.HeadAtStart,_xlpm.Month,_xlpm.LivestockClass, _xlpm.HeadAtStart + [0]!CommonLivestock_InputFunctions.LivestockMovement_HeadAddedDuringMonth(_xlpm.Month, _xlpm.LivestockClass) - [0]!CommonLivestock_InputFunctions.LivestockMovement_HeadLostDuringMonth(_xlpm.Month, _xlpm.LivestockClass))</definedName>
+    <definedName name="CommonLivestock_InputFunctions.LivestockMovement_HeadLostDuringMonth" localSheetId="7">_xlfn.LAMBDA(_xlpm.Month,_xlpm.LivestockClass, IFERROR(SUM(_xlfn._xlws.FILTER(#REF!, (#REF! &gt;= EOMONTH(_xlpm.Month, -1) + 1) * (#REF! &lt;= EOMONTH(_xlpm.Month, 0)) * (#REF! = _xlpm.LivestockClass))), 0))</definedName>
     <definedName name="CommonLivestock_InputFunctions.LivestockMovement_HeadLostDuringMonth">_xlfn.LAMBDA(_xlpm.Month,_xlpm.LivestockClass, IFERROR(SUM(_xlfn._xlws.FILTER(#REF!, (#REF! &gt;= EOMONTH(_xlpm.Month, -1) + 1) * (#REF! &lt;= EOMONTH(_xlpm.Month, 0)) * (#REF! = _xlpm.LivestockClass))), 0))</definedName>
     <definedName name="CommonLivestock_InputFunctions.LivestockMovement_HeadRemainingAtMonthEnd">_xlfn.LAMBDA(_xlpm.Month,_xlpm.LivestockClass,_xlpm.HeadAtStartOfMonth, MAX(_xlpm.HeadAtStartOfMonth - [0]!CommonLivestock_InputFunctions.LivestockMovement_HeadLostDuringMonth(_xlpm.Month, _xlpm.LivestockClass), 0))</definedName>
     <definedName name="CommonLivestock_InputFunctions.LivestockMovement_LiveweightAddedDuringMonth">_xlfn.LAMBDA(_xlpm.LivestockClass,_xlpm.MovementDate,_xlpm.WeightAtMovementDate,_xlpm.Head, IFERROR(_xlpm.Head * (_xlpm.WeightAtMovementDate + [0]!CommonLivestock_InputFunctions.LivestockMovement_LiveweightGrownDuringMonthPerHead(_xlpm.LivestockClass, _xlpm.MovementDate)), 0))</definedName>
@@ -301,30 +205,18 @@
     <definedName name="CommonLivestock_InputFunctions.LivestockMovement_ProportionalAverageLiveweightRemainingAtEndOfMonth">_xlfn.LAMBDA(_xlpm.Month,_xlpm.LivestockClass,_xlpm.HeadAtStart,_xlpm.LiveweightAtStart,_xlpm.LiveweightGain, [0]!CommonLivestock_InputFunctions.LivestockMovement_ProportionHeadRemainingAtEndOfMonth(_xlpm.Month, _xlpm.LivestockClass, _xlpm.HeadAtStart) * CommonLivestock_InputFunctions.LivestockMovement_AverageLiveweightRemainingHead(_xlpm.Month, _xlpm.LiveweightAtStart, _xlpm.LiveweightGain))</definedName>
     <definedName name="CommonLivestock_InputFunctions.LivestockMovement_ProportionHeadAddedDuringMonth">_xlfn.LAMBDA(_xlpm.Month,_xlpm.LivestockClass,_xlpm.HeadAtStart, IFERROR(MIN(1, [0]!CommonLivestock_InputFunctions.LivestockMovement_HeadAddedDuringMonth(_xlpm.Month, _xlpm.LivestockClass) / [0]!CommonLivestock_InputFunctions.LivestockMovement_HeadAtEndOfMonth(_xlpm.HeadAtStart, _xlpm.Month, _xlpm.LivestockClass)), 0))</definedName>
     <definedName name="CommonLivestock_InputFunctions.LivestockMovement_ProportionHeadRemainingAtEndOfMonth">_xlfn.LAMBDA(_xlpm.Month,_xlpm.LivestockClass,_xlpm.HeadAtStart, IFERROR(MIN(1, [0]!CommonLivestock_InputFunctions.LivestockMovement_HeadRemainingAtMonthEnd(_xlpm.Month, _xlpm.LivestockClass, _xlpm.HeadAtStart) / [0]!CommonLivestock_InputFunctions.LivestockMovement_HeadAtEndOfMonth(_xlpm.HeadAtStart, _xlpm.Month, _xlpm.LivestockClass)), 0))</definedName>
+    <definedName name="CommonLivestock_InputFunctions.LivestockMovement_TotalLiveweightAddedDuringMonth" localSheetId="7">_xlfn.LAMBDA(_xlpm.Month,_xlpm.LivestockClass, IFERROR(SUM(_xlfn._xlws.FILTER(#REF!, (#REF! &gt;= EOMONTH(_xlpm.Month, -1) + 1) * (#REF! &lt;= EOMONTH(_xlpm.Month, 0)) * (#REF! = _xlpm.LivestockClass))), 0))</definedName>
     <definedName name="CommonLivestock_InputFunctions.LivestockMovement_TotalLiveweightAddedDuringMonth">_xlfn.LAMBDA(_xlpm.Month,_xlpm.LivestockClass, IFERROR(SUM(_xlfn._xlws.FILTER(#REF!, (#REF! &gt;= EOMONTH(_xlpm.Month, -1) + 1) * (#REF! &lt;= EOMONTH(_xlpm.Month, 0)) * (#REF! = _xlpm.LivestockClass))), 0))</definedName>
+    <definedName name="CommonLivestock_InputFunctions.LivestockMovement_TotalLiveweightGrownDuringMonth" localSheetId="7">_xlfn.LAMBDA(_xlpm.Month,_xlpm.LivestockClass, IFERROR(SUM(_xlfn._xlws.FILTER(#REF!, (#REF! &gt;= EOMONTH(_xlpm.Month, -1) + 1) * (#REF! &lt;= EOMONTH(_xlpm.Month, 0)) * (#REF! = _xlpm.LivestockClass))), 0))</definedName>
     <definedName name="CommonLivestock_InputFunctions.LivestockMovement_TotalLiveweightGrownDuringMonth">_xlfn.LAMBDA(_xlpm.Month,_xlpm.LivestockClass, IFERROR(SUM(_xlfn._xlws.FILTER(#REF!, (#REF! &gt;= EOMONTH(_xlpm.Month, -1) + 1) * (#REF! &lt;= EOMONTH(_xlpm.Month, 0)) * (#REF! = _xlpm.LivestockClass))), 0))</definedName>
     <definedName name="CommonLivestock_InputFunctions.LivestockMovement_TotalLiveweightGrownDuringMonthAddedAndRemaining">_xlfn.LAMBDA(_xlpm.Month,_xlpm.LivestockClass,_xlpm.HeadAtStart, [0]!CommonLivestock_InputFunctions.LivestockMovement_LiveweightGrownFromMonthStartTotal(_xlpm.LivestockClass, _xlpm.Month, _xlpm.HeadAtStart) + [0]!CommonLivestock_InputFunctions.LivestockMovement_TotalLiveweightGrownDuringMonth(_xlpm.Month, _xlpm.LivestockClass))</definedName>
     <definedName name="CommonLivestock_SourceData.SourceData_Livestock_Common_SymbolsMMS_Data">_xlfn.LAMBDA(_xlfn.MAKEARRAY(19, 3, _xlfn.LAMBDA(_xlpm.r,_xlpm.c, INDEX({"Symbol","Manure management system","";"1","Anaerobic lagoon","Anaerobic lagoon (m=1)";"2","Liquid systems","Liquid systems (m=2)";"3","Daily spread","Daily spread (m=3)";"3a","Sump and dispersal system","Sump and dispersal system (m=3a)";"3b","Drains to paddock","Drains to paddock (m=3b)";"4","Solid storage","Solid storage (m=4)";"5","Drylot (feed pad)","Drylot (feed pad) (m=5)";"6","Composting (passive windrow)","Composting (passive windrow) (m=6)";"7","Digester / covered lagoons","Digester / covered lagoons (m=7)";"8","Deep litter","Deep litter (m=8)";"9","Pit storage","Pit storage (m=9)";"10","Poultry manure with bedding","Poultry manure with bedding (m=10)";"11","Poultry manure without bedding","Poultry manure without bedding (m=11)";"11a","Belt manure removal","Belt manure removal (m=11a)";"11b","Manure stored in house","Manure stored in house (m=11b)";"12","Direct processing","Direct processing (m=12)";"13","Direct application","Direct application (m=13)";"14","Pasture range and paddock","Pasture range and paddock (m=14)"}, _xlpm.r, _xlpm.c))))</definedName>
-    <definedName name="Enterprise_PastureBeef_InputFunctions.multiplyCorrespondingCells" localSheetId="6">_xlfn.LAMBDA(_xlpm.range1,_xlpm.range2,_xlpm.range3, _xlfn.LET(_xlpm.numRows, ROWS(_xlpm.range1), _xlpm.numCols, COLUMNS(_xlpm.range1), _xlpm.result, _xlfn.MAKEARRAY(_xlpm.numRows, _xlpm.numCols, _xlfn.LAMBDA(_xlpm.r,_xlpm.c, IF(ISNUMBER(INDEX(_xlpm.range1, _xlpm.r, _xlpm.c)), INDEX(_xlpm.range1, _xlpm.r, _xlpm.c), 0) * IF(ISNUMBER(INDEX(_xlpm.range2, _xlpm.r, _xlpm.c)), INDEX(_xlpm.range2, _xlpm.r, _xlpm.c), 0) * IF(ISNUMBER(INDEX(_xlpm.range3, _xlpm.r, _xlpm.c)), INDEX(_xlpm.range3, _xlpm.r, _xlpm.c), 0))), _xlpm.result))</definedName>
-    <definedName name="Enterprise_PastureBeef_InputFunctions.multiplyCorrespondingCells" localSheetId="4">_xlfn.LAMBDA(_xlpm.range1,_xlpm.range2,_xlpm.range3, _xlfn.LET(_xlpm.numRows, ROWS(_xlpm.range1), _xlpm.numCols, COLUMNS(_xlpm.range1), _xlpm.result, _xlfn.MAKEARRAY(_xlpm.numRows, _xlpm.numCols, _xlfn.LAMBDA(_xlpm.r,_xlpm.c, IF(ISNUMBER(INDEX(_xlpm.range1, _xlpm.r, _xlpm.c)), INDEX(_xlpm.range1, _xlpm.r, _xlpm.c), 0) * IF(ISNUMBER(INDEX(_xlpm.range2, _xlpm.r, _xlpm.c)), INDEX(_xlpm.range2, _xlpm.r, _xlpm.c), 0) * IF(ISNUMBER(INDEX(_xlpm.range3, _xlpm.r, _xlpm.c)), INDEX(_xlpm.range3, _xlpm.r, _xlpm.c), 0))), _xlpm.result))</definedName>
     <definedName name="Enterprise_PastureBeef_InputFunctions.multiplyCorrespondingCells">_xlfn.LAMBDA(_xlpm.range1,_xlpm.range2,_xlpm.range3, _xlfn.LET(_xlpm.numRows, ROWS(_xlpm.range1), _xlpm.numCols, COLUMNS(_xlpm.range1), _xlpm.result, _xlfn.MAKEARRAY(_xlpm.numRows, _xlpm.numCols, _xlfn.LAMBDA(_xlpm.r,_xlpm.c, IF(ISNUMBER(INDEX(_xlpm.range1, _xlpm.r, _xlpm.c)), INDEX(_xlpm.range1, _xlpm.r, _xlpm.c), 0) * IF(ISNUMBER(INDEX(_xlpm.range2, _xlpm.r, _xlpm.c)), INDEX(_xlpm.range2, _xlpm.r, _xlpm.c), 0) * IF(ISNUMBER(INDEX(_xlpm.range3, _xlpm.r, _xlpm.c)), INDEX(_xlpm.range3, _xlpm.r, _xlpm.c), 0))), _xlpm.result))</definedName>
-    <definedName name="getOverlappingReportingCycles" localSheetId="6">_xlfn.LAMBDA(_xlpm.ProductionCycleStart,_xlpm.ProductionCycleEnd,_xlpm.ReportingStartMonth,_xlpm.ReportingStartDay, _xlfn.LET(_xlpm.S, _xlpm.ProductionCycleStart, _xlpm.E, _xlpm.ProductionCycleEnd, _xlpm.m, _xlpm.ReportingStartMonth, _xlpm.d, _xlpm.ReportingStartDay, _xlpm.A, _xlpm.S - 364, _xlpm.ya, YEAR(_xlpm.A), _xlpm.yb, YEAR(_xlpm.E), _xlpm.firstYear, _xlpm.ya + (DATE(_xlpm.ya, _xlpm.m, _xlpm.d) &lt; _xlpm.A), _xlpm.lastYear, _xlpm.yb - (DATE(_xlpm.yb, _xlpm.m, _xlpm.d) &gt; _xlpm.E), MAX(0, _xlpm.lastYear - _xlpm.firstYear + 1)))</definedName>
-    <definedName name="getOverlappingReportingCycles" localSheetId="4">_xlfn.LAMBDA(_xlpm.ProductionCycleStart,_xlpm.ProductionCycleEnd,_xlpm.ReportingStartMonth,_xlpm.ReportingStartDay, _xlfn.LET(_xlpm.S, _xlpm.ProductionCycleStart, _xlpm.E, _xlpm.ProductionCycleEnd, _xlpm.m, _xlpm.ReportingStartMonth, _xlpm.d, _xlpm.ReportingStartDay, _xlpm.A, _xlpm.S - 364, _xlpm.ya, YEAR(_xlpm.A), _xlpm.yb, YEAR(_xlpm.E), _xlpm.firstYear, _xlpm.ya + (DATE(_xlpm.ya, _xlpm.m, _xlpm.d) &lt; _xlpm.A), _xlpm.lastYear, _xlpm.yb - (DATE(_xlpm.yb, _xlpm.m, _xlpm.d) &gt; _xlpm.E), MAX(0, _xlpm.lastYear - _xlpm.firstYear + 1)))</definedName>
     <definedName name="getOverlappingReportingCycles">_xlfn.LAMBDA(_xlpm.ProductionCycleStart,_xlpm.ProductionCycleEnd,_xlpm.ReportingStartMonth,_xlpm.ReportingStartDay, _xlfn.LET(_xlpm.S, _xlpm.ProductionCycleStart, _xlpm.E, _xlpm.ProductionCycleEnd, _xlpm.m, _xlpm.ReportingStartMonth, _xlpm.d, _xlpm.ReportingStartDay, _xlpm.A, _xlpm.S - 364, _xlpm.ya, YEAR(_xlpm.A), _xlpm.yb, YEAR(_xlpm.E), _xlpm.firstYear, _xlpm.ya + (DATE(_xlpm.ya, _xlpm.m, _xlpm.d) &lt; _xlpm.A), _xlpm.lastYear, _xlpm.yb - (DATE(_xlpm.yb, _xlpm.m, _xlpm.d) &gt; _xlpm.E), MAX(0, _xlpm.lastYear - _xlpm.firstYear + 1)))</definedName>
-    <definedName name="InputFunctions_PastureBeef.ConvertMonthlyCalvingToSeason" localSheetId="6">_xlfn.LAMBDA(_xlpm.Season,_xlpm.SumArray,_xlpm.CalvingMonthArray,_xlpm.MonthArray,_xlpm.MonthToSeasonArray, _xlfn.LET(_xlpm.MonthText, TEXT(_xlpm.CalvingMonthArray, "mmmm"), _xlpm.SeasonPerRow, _xlfn.XLOOKUP(_xlpm.MonthText, _xlpm.MonthArray, _xlpm.MonthToSeasonArray, "", 0), SUM(_xlpm.SumArray * (_xlpm.SeasonPerRow = _xlpm.Season))))</definedName>
-    <definedName name="InputFunctions_PastureBeef.ConvertMonthlyCalvingToSeason" localSheetId="4">_xlfn.LAMBDA(_xlpm.Season,_xlpm.SumArray,_xlpm.CalvingMonthArray,_xlpm.MonthArray,_xlpm.MonthToSeasonArray, _xlfn.LET(_xlpm.MonthText, TEXT(_xlpm.CalvingMonthArray, "mmmm"), _xlpm.SeasonPerRow, _xlfn.XLOOKUP(_xlpm.MonthText, _xlpm.MonthArray, _xlpm.MonthToSeasonArray, "", 0), SUM(_xlpm.SumArray * (_xlpm.SeasonPerRow = _xlpm.Season))))</definedName>
     <definedName name="InputFunctions_PastureBeef.ConvertMonthlyCalvingToSeason">_xlfn.LAMBDA(_xlpm.Season,_xlpm.SumArray,_xlpm.CalvingMonthArray,_xlpm.MonthArray,_xlpm.MonthToSeasonArray, _xlfn.LET(_xlpm.MonthText, TEXT(_xlpm.CalvingMonthArray, "mmmm"), _xlpm.SeasonPerRow, _xlfn.XLOOKUP(_xlpm.MonthText, _xlpm.MonthArray, _xlpm.MonthToSeasonArray, "", 0), SUM(_xlpm.SumArray * (_xlpm.SeasonPerRow = _xlpm.Season))))</definedName>
-    <definedName name="InputFunctions_PastureBeef.LookupLiveweightFromMonth" localSheetId="6">_xlfn.LAMBDA(_xlpm.State,_xlpm.Region,_xlpm.Month,_xlpm.LivestockClass,_xlpm.StateArray,_xlpm.RegionArray,_xlpm.SeasonArray,_xlpm.LivestockClassArray,_xlpm.ReturnArray,_xlpm.StateCommonNameArray,_xlpm.StateAbbreviationArray,_xlpm.MonthArray,_xlpm.MonthToSeasonArray, _xlfn.LET(_xlpm.Month, TEXT(_xlpm.Month, "mmmm"), _xlpm.State, _xlfn.XLOOKUP(_xlpm.State, _xlpm.StateCommonNameArray, _xlpm.StateAbbreviationArray), _xlpm.Season, _xlfn.XLOOKUP(_xlpm.Month, _xlpm.MonthArray, _xlpm.MonthToSeasonArray), _xlfn.XLOOKUP(1, (_xlpm.StateArray = _xlpm.State) * (_xlpm.RegionArray = _xlpm.Region) * (_xlpm.SeasonArray = _xlpm.Season), _xlfn.XLOOKUP(_xlpm.LivestockClass, _xlpm.LivestockClassArray, _xlpm.ReturnArray))))</definedName>
-    <definedName name="InputFunctions_PastureBeef.LookupLiveweightFromMonth" localSheetId="4">_xlfn.LAMBDA(_xlpm.State,_xlpm.Region,_xlpm.Month,_xlpm.LivestockClass,_xlpm.StateArray,_xlpm.RegionArray,_xlpm.SeasonArray,_xlpm.LivestockClassArray,_xlpm.ReturnArray,_xlpm.StateCommonNameArray,_xlpm.StateAbbreviationArray,_xlpm.MonthArray,_xlpm.MonthToSeasonArray, _xlfn.LET(_xlpm.Month, TEXT(_xlpm.Month, "mmmm"), _xlpm.State, _xlfn.XLOOKUP(_xlpm.State, _xlpm.StateCommonNameArray, _xlpm.StateAbbreviationArray), _xlpm.Season, _xlfn.XLOOKUP(_xlpm.Month, _xlpm.MonthArray, _xlpm.MonthToSeasonArray), _xlfn.XLOOKUP(1, (_xlpm.StateArray = _xlpm.State) * (_xlpm.RegionArray = _xlpm.Region) * (_xlpm.SeasonArray = _xlpm.Season), _xlfn.XLOOKUP(_xlpm.LivestockClass, _xlpm.LivestockClassArray, _xlpm.ReturnArray))))</definedName>
     <definedName name="InputFunctions_PastureBeef.LookupLiveweightFromMonth">_xlfn.LAMBDA(_xlpm.State,_xlpm.Region,_xlpm.Month,_xlpm.LivestockClass,_xlpm.StateArray,_xlpm.RegionArray,_xlpm.SeasonArray,_xlpm.LivestockClassArray,_xlpm.ReturnArray,_xlpm.StateCommonNameArray,_xlpm.StateAbbreviationArray,_xlpm.MonthArray,_xlpm.MonthToSeasonArray, _xlfn.LET(_xlpm.Month, TEXT(_xlpm.Month, "mmmm"), _xlpm.State, _xlfn.XLOOKUP(_xlpm.State, _xlpm.StateCommonNameArray, _xlpm.StateAbbreviationArray), _xlpm.Season, _xlfn.XLOOKUP(_xlpm.Month, _xlpm.MonthArray, _xlpm.MonthToSeasonArray), _xlfn.XLOOKUP(1, (_xlpm.StateArray = _xlpm.State) * (_xlpm.RegionArray = _xlpm.Region) * (_xlpm.SeasonArray = _xlpm.Season), _xlfn.XLOOKUP(_xlpm.LivestockClass, _xlpm.LivestockClassArray, _xlpm.ReturnArray))))</definedName>
-    <definedName name="InputFunctions_PastureBeef.LookupLiveweightFromSeason" localSheetId="6">_xlfn.LAMBDA(_xlpm.State,_xlpm.Region,_xlpm.Season,_xlpm.LivestockClass,_xlpm.StateArray,_xlpm.RegionArray,_xlpm.SeasonArray,_xlpm.LivestockClassArray,_xlpm.ReturnArray,_xlpm.StateCommonNameArray,_xlpm.StateAbbreviationArray, _xlfn.LET(_xlpm.State, _xlfn.XLOOKUP(_xlpm.State, _xlpm.StateCommonNameArray, _xlpm.StateAbbreviationArray), _xlfn.XLOOKUP(1, (_xlpm.StateArray = _xlpm.State) * (_xlpm.RegionArray = _xlpm.Region) * (_xlpm.SeasonArray = _xlpm.Season), _xlfn.XLOOKUP(_xlpm.LivestockClass, _xlpm.LivestockClassArray, _xlpm.ReturnArray))))</definedName>
-    <definedName name="InputFunctions_PastureBeef.LookupLiveweightFromSeason" localSheetId="4">_xlfn.LAMBDA(_xlpm.State,_xlpm.Region,_xlpm.Season,_xlpm.LivestockClass,_xlpm.StateArray,_xlpm.RegionArray,_xlpm.SeasonArray,_xlpm.LivestockClassArray,_xlpm.ReturnArray,_xlpm.StateCommonNameArray,_xlpm.StateAbbreviationArray, _xlfn.LET(_xlpm.State, _xlfn.XLOOKUP(_xlpm.State, _xlpm.StateCommonNameArray, _xlpm.StateAbbreviationArray), _xlfn.XLOOKUP(1, (_xlpm.StateArray = _xlpm.State) * (_xlpm.RegionArray = _xlpm.Region) * (_xlpm.SeasonArray = _xlpm.Season), _xlfn.XLOOKUP(_xlpm.LivestockClass, _xlpm.LivestockClassArray, _xlpm.ReturnArray))))</definedName>
     <definedName name="InputFunctions_PastureBeef.LookupLiveweightFromSeason">_xlfn.LAMBDA(_xlpm.State,_xlpm.Region,_xlpm.Season,_xlpm.LivestockClass,_xlpm.StateArray,_xlpm.RegionArray,_xlpm.SeasonArray,_xlpm.LivestockClassArray,_xlpm.ReturnArray,_xlpm.StateCommonNameArray,_xlpm.StateAbbreviationArray, _xlfn.LET(_xlpm.State, _xlfn.XLOOKUP(_xlpm.State, _xlpm.StateCommonNameArray, _xlpm.StateAbbreviationArray), _xlfn.XLOOKUP(1, (_xlpm.StateArray = _xlpm.State) * (_xlpm.RegionArray = _xlpm.Region) * (_xlpm.SeasonArray = _xlpm.Season), _xlfn.XLOOKUP(_xlpm.LivestockClass, _xlpm.LivestockClassArray, _xlpm.ReturnArray))))</definedName>
-    <definedName name="InputFunctions_PastureBeef.LookupValueFromStateRegionMonth" localSheetId="6">_xlfn.LAMBDA(_xlpm.State,_xlpm.Region,_xlpm.Month,_xlpm.StateArray,_xlpm.RegionArray,_xlpm.SeasonArray,_xlpm.ReturnArray,_xlpm.StateCommonNameArray,_xlpm.StateAbbreviationArray,_xlpm.MonthArray,_xlpm.MonthToSeasonArray, _xlfn.LET(_xlpm.State, _xlfn.XLOOKUP(_xlpm.State, _xlpm.StateCommonNameArray, _xlpm.StateAbbreviationArray), _xlpm.Season, _xlfn.XLOOKUP(TEXT(_xlpm.Month, "mmmm"), _xlpm.MonthArray, _xlpm.MonthToSeasonArray), _xlfn.XLOOKUP(1, (_xlpm.StateArray = _xlpm.State) * (_xlpm.RegionArray = _xlpm.Region), _xlfn.XLOOKUP(_xlpm.Season, _xlpm.SeasonArray, _xlpm.ReturnArray))))</definedName>
-    <definedName name="InputFunctions_PastureBeef.LookupValueFromStateRegionMonth" localSheetId="4">_xlfn.LAMBDA(_xlpm.State,_xlpm.Region,_xlpm.Month,_xlpm.StateArray,_xlpm.RegionArray,_xlpm.SeasonArray,_xlpm.ReturnArray,_xlpm.StateCommonNameArray,_xlpm.StateAbbreviationArray,_xlpm.MonthArray,_xlpm.MonthToSeasonArray, _xlfn.LET(_xlpm.State, _xlfn.XLOOKUP(_xlpm.State, _xlpm.StateCommonNameArray, _xlpm.StateAbbreviationArray), _xlpm.Season, _xlfn.XLOOKUP(TEXT(_xlpm.Month, "mmmm"), _xlpm.MonthArray, _xlpm.MonthToSeasonArray), _xlfn.XLOOKUP(1, (_xlpm.StateArray = _xlpm.State) * (_xlpm.RegionArray = _xlpm.Region), _xlfn.XLOOKUP(_xlpm.Season, _xlpm.SeasonArray, _xlpm.ReturnArray))))</definedName>
     <definedName name="InputFunctions_PastureBeef.LookupValueFromStateRegionMonth">_xlfn.LAMBDA(_xlpm.State,_xlpm.Region,_xlpm.Month,_xlpm.StateArray,_xlpm.RegionArray,_xlpm.SeasonArray,_xlpm.ReturnArray,_xlpm.StateCommonNameArray,_xlpm.StateAbbreviationArray,_xlpm.MonthArray,_xlpm.MonthToSeasonArray, _xlfn.LET(_xlpm.State, _xlfn.XLOOKUP(_xlpm.State, _xlpm.StateCommonNameArray, _xlpm.StateAbbreviationArray), _xlpm.Season, _xlfn.XLOOKUP(TEXT(_xlpm.Month, "mmmm"), _xlpm.MonthArray, _xlpm.MonthToSeasonArray), _xlfn.XLOOKUP(1, (_xlpm.StateArray = _xlpm.State) * (_xlpm.RegionArray = _xlpm.Region), _xlfn.XLOOKUP(_xlpm.Season, _xlpm.SeasonArray, _xlpm.ReturnArray))))</definedName>
-    <definedName name="InputFunctions_PastureBeef.LookupValueFromStateRegionSeason" localSheetId="6">_xlfn.LAMBDA(_xlpm.State,_xlpm.Region,_xlpm.Season,_xlpm.StateArray,_xlpm.RegionArray,_xlpm.SeasonArray,_xlpm.ReturnArray,_xlpm.StateCommonNameArray,_xlpm.StateAbbreviationArray, _xlfn.LET(_xlpm.State, _xlfn.XLOOKUP(_xlpm.State, _xlpm.StateCommonNameArray, _xlpm.StateAbbreviationArray), _xlfn.XLOOKUP(1, (_xlpm.StateArray = _xlpm.State) * (_xlpm.RegionArray = _xlpm.Region), _xlfn.XLOOKUP(_xlpm.Season, _xlpm.SeasonArray, _xlpm.ReturnArray))))</definedName>
-    <definedName name="InputFunctions_PastureBeef.LookupValueFromStateRegionSeason" localSheetId="4">_xlfn.LAMBDA(_xlpm.State,_xlpm.Region,_xlpm.Season,_xlpm.StateArray,_xlpm.RegionArray,_xlpm.SeasonArray,_xlpm.ReturnArray,_xlpm.StateCommonNameArray,_xlpm.StateAbbreviationArray, _xlfn.LET(_xlpm.State, _xlfn.XLOOKUP(_xlpm.State, _xlpm.StateCommonNameArray, _xlpm.StateAbbreviationArray), _xlfn.XLOOKUP(1, (_xlpm.StateArray = _xlpm.State) * (_xlpm.RegionArray = _xlpm.Region), _xlfn.XLOOKUP(_xlpm.Season, _xlpm.SeasonArray, _xlpm.ReturnArray))))</definedName>
     <definedName name="InputFunctions_PastureBeef.LookupValueFromStateRegionSeason">_xlfn.LAMBDA(_xlpm.State,_xlpm.Region,_xlpm.Season,_xlpm.StateArray,_xlpm.RegionArray,_xlpm.SeasonArray,_xlpm.ReturnArray,_xlpm.StateCommonNameArray,_xlpm.StateAbbreviationArray, _xlfn.LET(_xlpm.State, _xlfn.XLOOKUP(_xlpm.State, _xlpm.StateCommonNameArray, _xlpm.StateAbbreviationArray), _xlfn.XLOOKUP(1, (_xlpm.StateArray = _xlpm.State) * (_xlpm.RegionArray = _xlpm.Region), _xlfn.XLOOKUP(_xlpm.Season, _xlpm.SeasonArray, _xlpm.ReturnArray))))</definedName>
     <definedName name="Result_CarbonRemovalsFromPlantings" localSheetId="6">[1]Results!$E$50</definedName>
     <definedName name="Result_CarbonRemovalsFromPlantings">Results!$E$56</definedName>
@@ -437,7 +329,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="324" uniqueCount="210">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="383" uniqueCount="254">
   <si>
     <t>Home</t>
   </si>
@@ -1122,6 +1014,138 @@
   <si>
     <t>SS3</t>
   </si>
+  <si>
+    <t>Data quality scoring</t>
+  </si>
+  <si>
+    <t>Table_SourceData_DataQuality_TemporalRepresentativeness</t>
+  </si>
+  <si>
+    <t>Description</t>
+  </si>
+  <si>
+    <t>ID</t>
+  </si>
+  <si>
+    <t>Data collected covers the time-period for which emissions are being estimated  </t>
+  </si>
+  <si>
+    <t>TR5</t>
+  </si>
+  <si>
+    <t>Data collected represents activities that occurred within 2 years of the time-period being assessed  </t>
+  </si>
+  <si>
+    <t>Data collected represents activities that occurred within 3 years of to the time-period being assessed  </t>
+  </si>
+  <si>
+    <t>TR3</t>
+  </si>
+  <si>
+    <t>Data collected represents activities that occurred within 4 years of the time-period being assessed  </t>
+  </si>
+  <si>
+    <t>TR2</t>
+  </si>
+  <si>
+    <t>Age of data unknown or data more than 4 years older than the time-period being reported  </t>
+  </si>
+  <si>
+    <t>TR1</t>
+  </si>
+  <si>
+    <t>Table_SourceData_DataQuality_SpatialRepresentativeness</t>
+  </si>
+  <si>
+    <t>Data covers specific entity location(s) with spatial partitioning or using stratified sampling within property </t>
+  </si>
+  <si>
+    <t>Data covers specific entity location(s) without spatial partitioning within property  </t>
+  </si>
+  <si>
+    <t>SR4</t>
+  </si>
+  <si>
+    <t>Data based on regional data from a government or industry database or survey </t>
+  </si>
+  <si>
+    <t>SR3</t>
+  </si>
+  <si>
+    <t>Data based on state data from a government or industry database or survey </t>
+  </si>
+  <si>
+    <t>SR2</t>
+  </si>
+  <si>
+    <t>Data based on national data from a government or industry database or survey </t>
+  </si>
+  <si>
+    <t>SR1</t>
+  </si>
+  <si>
+    <t>Table_SourceData_DataQuality_SampleSize</t>
+  </si>
+  <si>
+    <t>Data based on sample size of &gt;90% (e.g. total annual fuel purchases) </t>
+  </si>
+  <si>
+    <t>SS5</t>
+  </si>
+  <si>
+    <t>Data based on sample size of 51-90%  </t>
+  </si>
+  <si>
+    <t>SS4</t>
+  </si>
+  <si>
+    <t>Data based on sample size of 21-50%  </t>
+  </si>
+  <si>
+    <t>Data based on sample size of &lt;20% (e.g. liveweight measured for 10% of herd) </t>
+  </si>
+  <si>
+    <t>SS2</t>
+  </si>
+  <si>
+    <t>Unknown (e.g. data based on national/state/regional data source) </t>
+  </si>
+  <si>
+    <t>SS1</t>
+  </si>
+  <si>
+    <t>Table_SourceData_DataQuality_Scope3</t>
+  </si>
+  <si>
+    <t>Verified data provided by supplier consistent with ISO14067:2018 or GHG Protocol Product Lifecycle Accounting and Reporting Standard </t>
+  </si>
+  <si>
+    <t>S35</t>
+  </si>
+  <si>
+    <t>Unverified supplier data, consistent with ISO14067:2018 or GHG Protocol Product Lifecycle Accounting and Reporting Standard, or consistent with these Guidelines (where appropriate)</t>
+  </si>
+  <si>
+    <t>S34</t>
+  </si>
+  <si>
+    <t>Regionally relevant product specific value from database developed using international best practice </t>
+  </si>
+  <si>
+    <t>S33</t>
+  </si>
+  <si>
+    <t>Nationally relevant product specific value from database developed using international best practice   </t>
+  </si>
+  <si>
+    <t>S32</t>
+  </si>
+  <si>
+    <t>Geographically generic product specific value from database developed using international best practice </t>
+  </si>
+  <si>
+    <t>S31</t>
+  </si>
 </sst>
 </file>
 
@@ -1137,7 +1161,7 @@
     <numFmt numFmtId="169" formatCode="_-* #,##0_-;\-* #,##0_-;_-* &quot;-&quot;??_-;_-@_-"/>
     <numFmt numFmtId="170" formatCode="[$-F800]dddd\,\ mmmm\ dd\,\ yyyy"/>
   </numFmts>
-  <fonts count="53" x14ac:knownFonts="1">
+  <fonts count="54" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -1491,6 +1515,12 @@
       <name val="Consolas"/>
       <family val="3"/>
     </font>
+    <font>
+      <sz val="9"/>
+      <color rgb="FF404040"/>
+      <name val="Times New Roman"/>
+      <family val="1"/>
+    </font>
   </fonts>
   <fills count="16">
     <fill>
@@ -1964,7 +1994,7 @@
     <xf numFmtId="43" fontId="9" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="9" fontId="9" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="97">
+  <cellXfs count="100">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="29" fillId="4" borderId="0" xfId="8">
       <alignment horizontal="left" vertical="center"/>
@@ -2224,6 +2254,13 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="14" applyFont="1" applyBorder="1">
       <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="42" fillId="0" borderId="0" xfId="66"/>
+    <xf numFmtId="0" fontId="53" fillId="9" borderId="4" xfId="34" applyFont="1">
+      <alignment horizontal="left" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="10" borderId="0" xfId="35">
+      <alignment horizontal="left" vertical="center" indent="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="69">
@@ -2297,7 +2334,31 @@
     <cellStyle name="Variable type input" xfId="65" xr:uid="{69904D21-1566-4CAB-9A42-C86AC6535120}"/>
     <cellStyle name="Variable type other" xfId="64" xr:uid="{105BD9DE-B567-4DA0-87E6-C60A0ECC1C65}"/>
   </cellStyles>
-  <dxfs count="49">
+  <dxfs count="50">
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <name val="Times New Roman"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <fill>
+        <patternFill patternType="none">
+          <fgColor indexed="64"/>
+          <bgColor indexed="65"/>
+        </patternFill>
+      </fill>
+    </dxf>
     <dxf>
       <font>
         <b val="0"/>
@@ -3367,20 +3428,20 @@
   </dxfs>
   <tableStyles count="3" defaultTableStyle="Equation table" defaultPivotStyle="PivotStyleLight16">
     <tableStyle name="Editable table" pivot="0" count="6" xr9:uid="{8C498A1C-5864-4BF8-8739-A3055FE117E0}">
-      <tableStyleElement type="wholeTable" dxfId="48"/>
-      <tableStyleElement type="headerRow" dxfId="47"/>
-      <tableStyleElement type="totalRow" dxfId="46"/>
-      <tableStyleElement type="firstColumn" dxfId="45"/>
-      <tableStyleElement type="firstRowStripe" dxfId="44"/>
-      <tableStyleElement type="secondRowStripe" dxfId="43"/>
+      <tableStyleElement type="wholeTable" dxfId="49"/>
+      <tableStyleElement type="headerRow" dxfId="48"/>
+      <tableStyleElement type="totalRow" dxfId="47"/>
+      <tableStyleElement type="firstColumn" dxfId="46"/>
+      <tableStyleElement type="firstRowStripe" dxfId="45"/>
+      <tableStyleElement type="secondRowStripe" dxfId="44"/>
     </tableStyle>
     <tableStyle name="Equation table" pivot="0" count="6" xr9:uid="{B247698E-E41D-4CCD-AA0A-C14817E9DE65}">
-      <tableStyleElement type="wholeTable" dxfId="42"/>
-      <tableStyleElement type="headerRow" dxfId="41"/>
-      <tableStyleElement type="totalRow" dxfId="40"/>
-      <tableStyleElement type="firstColumn" dxfId="39"/>
-      <tableStyleElement type="firstRowStripe" dxfId="38"/>
-      <tableStyleElement type="secondRowStripe" dxfId="37"/>
+      <tableStyleElement type="wholeTable" dxfId="43"/>
+      <tableStyleElement type="headerRow" dxfId="42"/>
+      <tableStyleElement type="totalRow" dxfId="41"/>
+      <tableStyleElement type="firstColumn" dxfId="40"/>
+      <tableStyleElement type="firstRowStripe" dxfId="39"/>
+      <tableStyleElement type="secondRowStripe" dxfId="38"/>
     </tableStyle>
     <tableStyle name="Table Style 1" pivot="0" count="0" xr9:uid="{97B370DB-5463-4A31-9160-5A96BD6A559D}"/>
   </tableStyles>
@@ -3566,7 +3627,6 @@
     </xxl21:alternateUrls>
     <sheetNames>
       <sheetName val="Home"/>
-      <sheetName val="Input - Data quality"/>
       <sheetName val="Constants - Common"/>
       <sheetName val="Acknowledgements"/>
     </sheetNames>
@@ -3574,7 +3634,6 @@
       <sheetData sheetId="0"/>
       <sheetData sheetId="1"/>
       <sheetData sheetId="2"/>
-      <sheetData sheetId="3"/>
     </sheetDataSet>
   </externalBook>
 </externalLink>
@@ -3657,7 +3716,7 @@
   <tableColumns count="6">
     <tableColumn id="6" xr3:uid="{84D8E3C0-97CA-4CF1-A63F-3CF6AAE07330}" name="Transaction name" dataCellStyle="Input text"/>
     <tableColumn id="1" xr3:uid="{E41B3FA3-55C1-4BBF-A477-D8EDBC89025E}" name="Class (select)" dataCellStyle="Input select"/>
-    <tableColumn id="2" xr3:uid="{3F9F09B6-E6B3-4323-AB6A-249C77DAFA51}" name="Sale date" dataDxfId="36"/>
+    <tableColumn id="2" xr3:uid="{3F9F09B6-E6B3-4323-AB6A-249C77DAFA51}" name="Sale date" dataDxfId="37"/>
     <tableColumn id="3" xr3:uid="{48DB24D2-2F89-4EEB-911F-2F24089C3918}" name="Head sold"/>
     <tableColumn id="4" xr3:uid="{879FC871-5C62-44BF-952F-ACBA1C3B6AE4}" name="Average weight per head (kg)"/>
     <tableColumn id="5" xr3:uid="{B8588D76-BACA-4516-8963-B7E8E5A87B93}" name="Total liveweight sold" dataCellStyle="Input number general calculated">
@@ -3669,7 +3728,7 @@
 </file>
 
 <file path=xl/tables/table10.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="10" xr:uid="{AA9D31FA-C10A-401A-A990-FD7418530E07}" name="Table_SourceData_RainfallZones" displayName="Table_SourceData_RainfallZones" ref="D119:G121" totalsRowShown="0">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="27" xr:uid="{F04C603B-B6F6-4EF5-BD98-BFD203645EBE}" name="Table_SourceData_RainfallZones" displayName="Table_SourceData_RainfallZones" ref="D119:G121" totalsRowShown="0">
   <autoFilter ref="D119:G121" xr:uid="{E08772F3-2E8C-40A8-B755-08A5BBDF4130}">
     <filterColumn colId="0" hiddenButton="1"/>
     <filterColumn colId="1" hiddenButton="1"/>
@@ -3677,16 +3736,16 @@
     <filterColumn colId="3" hiddenButton="1"/>
   </autoFilter>
   <tableColumns count="4">
-    <tableColumn id="1" xr3:uid="{A1896C80-5B23-4971-85DF-908C9411D636}" name="Rainfall Zone">
+    <tableColumn id="1" xr3:uid="{2ADDB08F-80D5-4814-A2A0-D98870369EC7}" name="Rainfall Zone">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_RainfallZones_Data(),Table_SourceData_RainfallZones[[#Headers],[Rainfall Zone]],0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="2" xr3:uid="{776A729E-62FB-471E-9D55-F5C0C49DAFB1}" name="Annual rainfall">
+    <tableColumn id="2" xr3:uid="{E0DE79E3-5186-40AE-AFE3-FF55A6EEA374}" name="Annual rainfall">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_RainfallZones_Data(),Table_SourceData_RainfallZones[[#Headers],[Rainfall Zone]],0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="3" xr3:uid="{5C488583-1093-4920-BAEF-A4BD862E3623}" name="Min rainfall">
+    <tableColumn id="3" xr3:uid="{31804A76-4AC7-4705-A77D-2CCE1E9337BE}" name="Min rainfall">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_RainfallZones_Data(),Table_SourceData_RainfallZones[[#Headers],[Rainfall Zone]],0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="4" xr3:uid="{EDCA589F-5D6E-4F25-A934-864B94D632CD}" name="Max rainfall">
+    <tableColumn id="4" xr3:uid="{D9EF56B1-0415-4006-AE4F-4DB80FEDB329}" name="Max rainfall">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_RainfallZones_Data(),Table_SourceData_RainfallZones[[#Headers],[Rainfall Zone]],0)</calculatedColumnFormula>
     </tableColumn>
   </tableColumns>
@@ -3695,16 +3754,16 @@
 </file>
 
 <file path=xl/tables/table11.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="11" xr:uid="{EC0B98FF-3B1A-4F33-9028-A6B26A7E6CE4}" name="Table_SourceData_LeachingZones" displayName="Table_SourceData_LeachingZones" ref="D127:E129" totalsRowShown="0">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="28" xr:uid="{7AA4CFA5-F9FD-4055-8934-17ECCA2F6C85}" name="Table_SourceData_LeachingZones" displayName="Table_SourceData_LeachingZones" ref="D127:E129" totalsRowShown="0">
   <autoFilter ref="D127:E129" xr:uid="{A159E140-02ED-4547-B6E1-6695D8B16A11}">
     <filterColumn colId="0" hiddenButton="1"/>
     <filterColumn colId="1" hiddenButton="1"/>
   </autoFilter>
   <tableColumns count="2">
-    <tableColumn id="1" xr3:uid="{BBC50AC7-FEC1-431E-AD41-7CB9E130FE72}" name="Leaching Zone">
+    <tableColumn id="1" xr3:uid="{81F7D022-6B55-4D8B-932F-227988594410}" name="Leaching Zone">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_LeachingZones_Data(), Table_SourceData_LeachingZones[[#Headers],[Leaching Zone]], 0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="2" xr3:uid="{ED997B4B-69AA-458D-AD94-F4C79A1B94D0}" name="Leaching criteria">
+    <tableColumn id="2" xr3:uid="{2F08230F-DF28-4379-B8D2-B1FBE7194F94}" name="Leaching criteria">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_LeachingZones_Data(), Table_SourceData_LeachingZones[[#Headers],[Leaching Zone]], 0)</calculatedColumnFormula>
     </tableColumn>
   </tableColumns>
@@ -3713,16 +3772,16 @@
 </file>
 
 <file path=xl/tables/table12.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="12" xr:uid="{C1B321B1-DD2B-4EC5-AE20-D47C87F02BBF}" name="Table_SourceData_DataScores_Scope3" displayName="Table_SourceData_DataScores_Scope3" ref="D153:E158" totalsRowShown="0">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="29" xr:uid="{231C3C94-FBA2-41C7-A91E-9959E5819B6D}" name="Table_SourceData_DataScores_Scope3" displayName="Table_SourceData_DataScores_Scope3" ref="D153:E158" totalsRowShown="0">
   <autoFilter ref="D153:E158" xr:uid="{133D42B0-F6D2-470A-858A-37E6A7F5EC2B}">
     <filterColumn colId="0" hiddenButton="1"/>
     <filterColumn colId="1" hiddenButton="1"/>
   </autoFilter>
   <tableColumns count="2">
-    <tableColumn id="1" xr3:uid="{18CA1470-758E-4475-BE8B-25D35A86BE01}" name="Data source">
+    <tableColumn id="1" xr3:uid="{3A7BCDD8-83C0-455D-9496-7FEF773FF5E2}" name="Data source">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_DataScores_Scope3_Data(), Table_SourceData_DataScores_Scope3[[#Headers],[Data source]], 0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="2" xr3:uid="{1F17B60B-4C21-4D79-B503-2BB5C2CDDBDF}" name="Data score">
+    <tableColumn id="2" xr3:uid="{E2BCFC54-9252-41C2-9D03-980F90A46BF2}" name="Data score">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_DataScores_Scope3_Data(), Table_SourceData_DataScores_Scope3[[#Headers],[Data source]], 0)</calculatedColumnFormula>
     </tableColumn>
   </tableColumns>
@@ -3731,16 +3790,16 @@
 </file>
 
 <file path=xl/tables/table13.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="13" xr:uid="{14C890C4-4A77-40EC-A6C1-19C0895BD309}" name="Table_SourceData_FracWET" displayName="Table_SourceData_FracWET" ref="D134:E136" totalsRowShown="0">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="30" xr:uid="{2280D15C-3F73-4E88-9643-0E3B7226C575}" name="Table_SourceData_FracWET" displayName="Table_SourceData_FracWET" ref="D134:E136" totalsRowShown="0">
   <autoFilter ref="D134:E136" xr:uid="{308E99BE-FE1F-47A4-B2CA-97217277C4E9}">
     <filterColumn colId="0" hiddenButton="1"/>
     <filterColumn colId="1" hiddenButton="1"/>
   </autoFilter>
   <tableColumns count="2">
-    <tableColumn id="1" xr3:uid="{AEB37CE8-5689-4CCA-AF1D-E45E37F37CC1}" name="Is in leaching zone">
+    <tableColumn id="1" xr3:uid="{52D54B98-3F5C-4DAD-91D8-47209B1CBF0F}" name="Is in leaching zone">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_FracWET_Data(),Table_SourceData_FracWET[[#Headers],[Is in leaching zone]],0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="2" xr3:uid="{8ABB6BDF-FE17-4B3B-BDE2-B9AAF30FF3BD}" name="FracWET" dataDxfId="19">
+    <tableColumn id="2" xr3:uid="{9A57EC7B-E1C2-4105-B13E-4EB510230417}" name="FracWET" dataDxfId="20">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_FracWET_Data(),Table_SourceData_FracWET[[#Headers],[Is in leaching zone]],0)</calculatedColumnFormula>
     </tableColumn>
   </tableColumns>
@@ -3749,7 +3808,7 @@
 </file>
 
 <file path=xl/tables/table14.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="14" xr:uid="{6BB36C9A-81C9-4008-9621-02E7765F4217}" name="Table_SourceData_Common_EFN2O" displayName="Table_SourceData_Common_EFN2O" ref="D186:H199" totalsRowShown="0">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="31" xr:uid="{17F96F76-16B5-4D2C-B2C0-0677F9A62AAD}" name="Table_SourceData_Common_EFN2O" displayName="Table_SourceData_Common_EFN2O" ref="D186:H199" totalsRowShown="0">
   <autoFilter ref="D186:H199" xr:uid="{D41FBEA4-8379-4DF7-A068-BF94D364F1A2}">
     <filterColumn colId="0" hiddenButton="1"/>
     <filterColumn colId="1" hiddenButton="1"/>
@@ -3758,19 +3817,19 @@
     <filterColumn colId="4" hiddenButton="1"/>
   </autoFilter>
   <tableColumns count="5">
-    <tableColumn id="1" xr3:uid="{7F8F31AC-00F6-4249-87C9-3FC6FE61BBC6}" name="Production system j">
+    <tableColumn id="1" xr3:uid="{877D4AE1-5BBD-45EF-BFCD-46D4274DEA0D}" name="Production system j">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_EFN2O_Data(), Table_SourceData_Common_EFN2O[[#Headers],[Production system j]], 0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="2" xr3:uid="{C297EA64-FE6E-4A07-A69E-528AF5291D69}" name="EFN2O">
+    <tableColumn id="2" xr3:uid="{C6CCA8D0-AB73-4541-AA09-167B095E7B82}" name="EFN2O">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_EFN2O_Data(), Table_SourceData_Common_EFN2O[[#Headers],[Production system j]], 0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="3" xr3:uid="{6AF2FB50-AEC5-4A97-85DD-5BA28FE67661}" name="Production system only">
+    <tableColumn id="3" xr3:uid="{204083C8-C399-4D6B-B0B2-8991D4E5A8F7}" name="Production system only">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_EFN2O_Data(), Table_SourceData_Common_EFN2O[[#Headers],[Production system j]], 0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="4" xr3:uid="{86FFBCC3-0C43-4C00-A2EE-6BE3F2E4BF06}" name="Irrigation method">
+    <tableColumn id="4" xr3:uid="{973DD926-23DF-46A2-AD58-D64F34F24EFA}" name="Irrigation method">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_EFN2O_Data(), Table_SourceData_Common_EFN2O[[#Headers],[Production system j]], 0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="5" xr3:uid="{149802D4-7D06-4288-AFC4-EA24F6C8F48E}" name="Rainfall zone">
+    <tableColumn id="5" xr3:uid="{E046B314-7010-4676-A5EB-F80F38D4F3A9}" name="Rainfall zone">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_EFN2O_Data(), Table_SourceData_Common_EFN2O[[#Headers],[Production system j]], 0)</calculatedColumnFormula>
     </tableColumn>
   </tableColumns>
@@ -3779,16 +3838,16 @@
 </file>
 
 <file path=xl/tables/table15.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="15" xr:uid="{81046769-5E78-4435-8902-BE2F7ED271E9}" name="Table_SourceData_FracWETIrrigation" displayName="Table_SourceData_FracWETIrrigation" ref="D142:E147" totalsRowShown="0">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="32" xr:uid="{4EBC22D0-6B32-4611-AF7D-E42A8F1055F4}" name="Table_SourceData_FracWETIrrigation" displayName="Table_SourceData_FracWETIrrigation" ref="D142:E147" totalsRowShown="0">
   <autoFilter ref="D142:E147" xr:uid="{1F48CA34-50DE-46D5-B32A-BB3A1E818E37}">
     <filterColumn colId="0" hiddenButton="1"/>
     <filterColumn colId="1" hiddenButton="1"/>
   </autoFilter>
   <tableColumns count="2">
-    <tableColumn id="1" xr3:uid="{1EE4C9C2-CE36-41D3-A67F-CC85678D8B80}" name="Irrigation type i">
+    <tableColumn id="1" xr3:uid="{7C001083-286C-4E7A-AD5C-B894196CEE00}" name="Irrigation type i">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_FracWETIrrigation_Data(), Table_SourceData_FracWETIrrigation[[#Headers],[Irrigation type i]], 0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="2" xr3:uid="{DD5CBEE2-8756-4D0C-9A90-6E931CF609D0}" name="FracWET" dataDxfId="18" dataCellStyle="Content normal">
+    <tableColumn id="2" xr3:uid="{DE1A60AE-C5D5-49AC-95C8-8D0AAEB02582}" name="FracWET" dataDxfId="19" dataCellStyle="Content normal">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_FracWETIrrigation_Data(), Table_SourceData_FracWETIrrigation[[#Headers],[Irrigation type i]], 0)</calculatedColumnFormula>
     </tableColumn>
   </tableColumns>
@@ -3797,16 +3856,16 @@
 </file>
 
 <file path=xl/tables/table16.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="16" xr:uid="{0D2D24A9-44B5-40A8-9D93-5D127038E490}" name="Table_SourceData_EFPastureRangeAndPaddock" displayName="Table_SourceData_EFPastureRangeAndPaddock" ref="D206:E208" totalsRowShown="0">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="33" xr:uid="{5BD8BBAD-D110-4F14-9BA3-022B7AA72A94}" name="Table_SourceData_EFPastureRangeAndPaddock" displayName="Table_SourceData_EFPastureRangeAndPaddock" ref="D206:E208" totalsRowShown="0">
   <autoFilter ref="D206:E208" xr:uid="{D5BE3F89-D70E-4C53-A71C-E756622DEF38}">
     <filterColumn colId="0" hiddenButton="1"/>
     <filterColumn colId="1" hiddenButton="1"/>
   </autoFilter>
   <tableColumns count="2">
-    <tableColumn id="1" xr3:uid="{76483A9E-91D3-4695-AB70-E830E24596D9}" name="Climate zone">
+    <tableColumn id="1" xr3:uid="{A9596886-0825-40AB-8B15-2DDEA3CCEB30}" name="Climate zone">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_EFPastureRangeAndPaddock_Data(), Table_SourceData_EFPastureRangeAndPaddock[[#Headers],[Climate zone]], 0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="2" xr3:uid="{1127A673-CAEF-41F9-A48A-D438D3FFF619}" name="EFPRP" dataDxfId="17" dataCellStyle="Content normal">
+    <tableColumn id="2" xr3:uid="{7A08677F-AAE3-40D4-BEDE-23058A375EDA}" name="EFPRP" dataDxfId="18" dataCellStyle="Content normal">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_EFPastureRangeAndPaddock_Data(), Table_SourceData_EFPastureRangeAndPaddock[[#Headers],[Climate zone]], 0)</calculatedColumnFormula>
     </tableColumn>
   </tableColumns>
@@ -3815,16 +3874,16 @@
 </file>
 
 <file path=xl/tables/table17.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="17" xr:uid="{E20A54E0-06E3-423D-998B-2E4A7C9A48F2}" name="Table_SourceData_Common_MonthToSeason" displayName="Table_SourceData_Common_MonthToSeason" ref="D212:E224" totalsRowShown="0">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="34" xr:uid="{C362327E-5357-47F6-8F2F-705B458BCC4B}" name="Table_SourceData_Common_MonthToSeason" displayName="Table_SourceData_Common_MonthToSeason" ref="D212:E224" totalsRowShown="0">
   <autoFilter ref="D212:E224" xr:uid="{97796C3A-D95E-4077-AA20-A8FE4145DAAD}">
     <filterColumn colId="0" hiddenButton="1"/>
     <filterColumn colId="1" hiddenButton="1"/>
   </autoFilter>
   <tableColumns count="2">
-    <tableColumn id="1" xr3:uid="{A2A66992-064C-4170-856F-B81D835CEE21}" name="Month">
+    <tableColumn id="1" xr3:uid="{57C75E7A-19E3-47ED-8896-2766A83C634A}" name="Month">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MonthsToSeasons_Data(), Table_SourceData_Common_MonthToSeason[[#Headers],[Month]], 0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="2" xr3:uid="{48B6FC8D-6503-4BB2-B07D-00597C808CB0}" name="Season" dataDxfId="16" dataCellStyle="Content normal">
+    <tableColumn id="2" xr3:uid="{812BD67D-F33D-41B3-8A9B-8A4DB75F9B83}" name="Season" dataDxfId="17" dataCellStyle="Content normal">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MonthsToSeasons_Data(), Table_SourceData_Common_MonthToSeason[[#Headers],[Month]], 0)</calculatedColumnFormula>
     </tableColumn>
   </tableColumns>
@@ -3833,7 +3892,7 @@
 </file>
 
 <file path=xl/tables/table18.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="18" xr:uid="{06A63BFC-1602-47C1-AF55-49AA6B4633CD}" name="Table_SourceData_Common_MCFTemperatureZone" displayName="Table_SourceData_Common_MCFTemperatureZone" ref="D231:S250" totalsRowShown="0">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="35" xr:uid="{A1C8652F-8FA0-4F1A-AD28-C3BA994322F5}" name="Table_SourceData_Common_MCFTemperatureZone" displayName="Table_SourceData_Common_MCFTemperatureZone" ref="D231:S250" totalsRowShown="0">
   <autoFilter ref="D231:S250" xr:uid="{1D72DD9B-C8FA-48F4-9A11-20231FF87B5A}">
     <filterColumn colId="0" hiddenButton="1"/>
     <filterColumn colId="1" hiddenButton="1"/>
@@ -3853,52 +3912,52 @@
     <filterColumn colId="15" hiddenButton="1"/>
   </autoFilter>
   <tableColumns count="16">
-    <tableColumn id="1" xr3:uid="{D344A8E3-CBAD-4F7E-B0CA-85C4550A31FF}" name="Temperature zone">
+    <tableColumn id="1" xr3:uid="{04C72E13-EE2E-41C7-BA47-EFB29BF9831F}" name="Temperature zone">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="2" xr3:uid="{4C26B9B4-F509-4ACF-A306-F52C2D83B94C}" name="MAT (ºC)" dataDxfId="15" dataCellStyle="Content normal">
+    <tableColumn id="2" xr3:uid="{2CDB234B-55CD-4F04-ABCC-7C1B9BE9C5EA}" name="MAT (ºC)" dataDxfId="16" dataCellStyle="Content normal">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="3" xr3:uid="{06D3FCFB-672E-43AB-BAD6-C5F3A36DC255}" name="Anaerobic lagoon" dataDxfId="14" dataCellStyle="Content normal">
+    <tableColumn id="3" xr3:uid="{31FC9592-470C-4745-BE0C-801EDB73B364}" name="Anaerobic lagoon" dataDxfId="15" dataCellStyle="Content normal">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="4" xr3:uid="{286B0E39-9F46-4519-A952-1FCC90F0A23E}" name="Digester / covered lagoons" dataDxfId="13" dataCellStyle="Content normal">
+    <tableColumn id="4" xr3:uid="{0BBADFC2-AD9E-45A1-A477-BCBE2A443483}" name="Digester / covered lagoons" dataDxfId="14" dataCellStyle="Content normal">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="5" xr3:uid="{CAB3566B-B894-433E-9D4A-4CA76B82C3BD}" name="Liquid systems" dataDxfId="12" dataCellStyle="Content normal">
+    <tableColumn id="5" xr3:uid="{91489AD5-67B7-4E73-8CF6-B6524734B20F}" name="Liquid systems" dataDxfId="13" dataCellStyle="Content normal">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="6" xr3:uid="{6D655DEC-7C3C-4046-9046-7ABE03AF26CA}" name="Daily spread" dataDxfId="11" dataCellStyle="Content normal">
+    <tableColumn id="6" xr3:uid="{C11525F1-D92E-45C7-9BF8-3E33E56C8730}" name="Daily spread" dataDxfId="12" dataCellStyle="Content normal">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="7" xr3:uid="{DC01C908-9F78-404B-A8A9-081231B6DBAF}" name="Composting (passive windrow)" dataDxfId="10" dataCellStyle="Content normal">
+    <tableColumn id="7" xr3:uid="{A24CB689-3CDB-4700-9377-C73EB2656DE1}" name="Composting (passive windrow)" dataDxfId="11" dataCellStyle="Content normal">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="8" xr3:uid="{016BC200-DE2E-4607-9A3A-E48F6A72FB0F}" name="Solid storage" dataDxfId="9" dataCellStyle="Content normal">
+    <tableColumn id="8" xr3:uid="{90D646B5-9BD0-4389-90A1-3149EF4602EE}" name="Solid storage" dataDxfId="10" dataCellStyle="Content normal">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="9" xr3:uid="{3D073AF2-25E0-49BE-825D-D38FD86B34D8}" name="Pit storage" dataDxfId="8" dataCellStyle="Content normal">
+    <tableColumn id="9" xr3:uid="{253D8404-CF61-4D43-BB93-FA9A02F1F766}" name="Pit storage" dataDxfId="9" dataCellStyle="Content normal">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="10" xr3:uid="{2C00D039-8FF7-4CF7-B97D-987BAE97BA35}" name="Deep litter" dataDxfId="7" dataCellStyle="Content normal">
+    <tableColumn id="10" xr3:uid="{9A04ED5B-4BC1-4A37-9DD3-B2528AAD7D05}" name="Deep litter" dataDxfId="8" dataCellStyle="Content normal">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="11" xr3:uid="{C3FD2E13-24D5-402A-8C77-E324B6925825}" name="Poultry manure with bedding" dataDxfId="6" dataCellStyle="Content normal">
+    <tableColumn id="11" xr3:uid="{BAA791DA-F3A0-4954-BB53-8C5671397221}" name="Poultry manure with bedding" dataDxfId="7" dataCellStyle="Content normal">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="12" xr3:uid="{6CCAA4CD-85BD-481B-A987-0719DD47798C}" name="Poultry manure without bedding" dataDxfId="5" dataCellStyle="Content normal">
+    <tableColumn id="12" xr3:uid="{0CE6F09E-7C27-49A4-B2A7-6B3A0CF05769}" name="Poultry manure without bedding" dataDxfId="6" dataCellStyle="Content normal">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="13" xr3:uid="{12540CA2-E51E-45F0-A036-45D45913194C}" name="Direct processing" dataDxfId="4" dataCellStyle="Content normal">
+    <tableColumn id="13" xr3:uid="{02162768-ACCE-48D5-8771-DFE30DA7454E}" name="Direct processing" dataDxfId="5" dataCellStyle="Content normal">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="14" xr3:uid="{393A0B3F-42CD-412F-B1E5-79CF90491213}" name="Direct application" dataDxfId="3" dataCellStyle="Content normal">
+    <tableColumn id="14" xr3:uid="{D0F00B85-C8DF-42B4-9E3D-CEE67B91738F}" name="Direct application" dataDxfId="4" dataCellStyle="Content normal">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="15" xr3:uid="{44E9918F-2DF8-4DE9-AD76-C61362285599}" name="Pasture range and paddock" dataDxfId="2" dataCellStyle="Content normal">
+    <tableColumn id="15" xr3:uid="{69065A74-641E-40D6-BB3B-C46C0998BA8B}" name="Pasture range and paddock" dataDxfId="3" dataCellStyle="Content normal">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="16" xr3:uid="{FE671AF8-F8E0-4322-B78A-1B6A3A96A4E0}" name="MAT raw" dataDxfId="1" dataCellStyle="Content normal">
+    <tableColumn id="16" xr3:uid="{E8697876-07FA-45DD-A420-6BD64684FC66}" name="MAT raw" dataDxfId="2" dataCellStyle="Content normal">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</calculatedColumnFormula>
     </tableColumn>
   </tableColumns>
@@ -3907,16 +3966,16 @@
 </file>
 
 <file path=xl/tables/table19.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="19" xr:uid="{949FFD0F-1699-4700-8323-CF2162C2663F}" name="Table_SourceData_Common_EFOrganicFertCropResidues" displayName="Table_SourceData_Common_EFOrganicFertCropResidues" ref="D257:E259" totalsRowShown="0">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="36" xr:uid="{94AA6F70-552D-46BB-96AE-FD3E2133B44B}" name="Table_SourceData_Common_EFOrganicFertCropResidues" displayName="Table_SourceData_Common_EFOrganicFertCropResidues" ref="D257:E259" totalsRowShown="0">
   <autoFilter ref="D257:E259" xr:uid="{56E01C14-1BB8-4015-9158-4CEB4D3B605C}">
     <filterColumn colId="0" hiddenButton="1"/>
     <filterColumn colId="1" hiddenButton="1"/>
   </autoFilter>
   <tableColumns count="2">
-    <tableColumn id="1" xr3:uid="{82DE88A1-FD3E-429F-81D0-81A0580D58D8}" name="Climate Zone">
+    <tableColumn id="1" xr3:uid="{FAA3D460-A09A-40D0-9FC4-A7902DA21DBF}" name="Climate Zone">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_EFOrganicFertiliserAndCropResidues_Data(), Table_SourceData_Common_EFOrganicFertCropResidues[[#Headers],[Climate Zone]], 0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="2" xr3:uid="{3505652E-76CD-41ED-BC1F-830404A5E233}" name="EFNi &amp; EFN2Oi" dataDxfId="0" dataCellStyle="Content normal">
+    <tableColumn id="2" xr3:uid="{396FB2E9-CFF3-46A0-BF64-8B8E1F7DF6B8}" name="EFNi &amp; EFN2Oi" dataDxfId="1" dataCellStyle="Content normal">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_EFOrganicFertiliserAndCropResidues_Data(), Table_SourceData_Common_EFOrganicFertCropResidues[[#Headers],[Climate Zone]], 0)</calculatedColumnFormula>
     </tableColumn>
   </tableColumns>
@@ -3950,21 +4009,85 @@
 </table>
 </file>
 
+<file path=xl/tables/table20.xml><?xml version="1.0" encoding="utf-8"?>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="37" xr:uid="{042CC366-20A9-444B-A561-C804E2F99D16}" name="Table_SourceData_DataQuality_TemporalRepresentativeness" displayName="Table_SourceData_DataQuality_TemporalRepresentativeness" ref="D265:F270" totalsRowShown="0">
+  <autoFilter ref="D265:F270" xr:uid="{9AD44602-D2F2-4D97-923C-A32E98F8C17A}">
+    <filterColumn colId="0" hiddenButton="1"/>
+    <filterColumn colId="1" hiddenButton="1"/>
+    <filterColumn colId="2" hiddenButton="1"/>
+  </autoFilter>
+  <tableColumns count="3">
+    <tableColumn id="2" xr3:uid="{7148520C-28F0-4874-9F7C-976B826B4A88}" name="Description" dataDxfId="0" dataCellStyle="Content normal"/>
+    <tableColumn id="1" xr3:uid="{4E13974D-F616-49F2-8E9F-954EDBFEB1DF}" name="ID"/>
+    <tableColumn id="3" xr3:uid="{D4828A0E-47E2-4749-9825-94EC16B5A930}" name="Score"/>
+  </tableColumns>
+  <tableStyleInfo name="Equation table" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
+</table>
+</file>
+
+<file path=xl/tables/table21.xml><?xml version="1.0" encoding="utf-8"?>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="38" xr:uid="{3AA6D4A1-4ED8-4C02-AA02-CEDDB7739BB5}" name="Table_SourceData_DataQuality_SpatialRepresentativeness" displayName="Table_SourceData_DataQuality_SpatialRepresentativeness" ref="D274:F279" totalsRowShown="0">
+  <autoFilter ref="D274:F279" xr:uid="{95094D65-3E0E-45CE-A3F4-F41E74C11901}">
+    <filterColumn colId="0" hiddenButton="1"/>
+    <filterColumn colId="1" hiddenButton="1"/>
+    <filterColumn colId="2" hiddenButton="1"/>
+  </autoFilter>
+  <tableColumns count="3">
+    <tableColumn id="1" xr3:uid="{5314C418-FE67-4ED2-AFCE-B99D3B3384BF}" name="Description"/>
+    <tableColumn id="2" xr3:uid="{C480E577-2F78-4D53-BB14-47F2D4CB7F6B}" name="ID"/>
+    <tableColumn id="3" xr3:uid="{27AA2D04-9437-4C31-9825-9D3DEF675DE3}" name="Score"/>
+  </tableColumns>
+  <tableStyleInfo name="Equation table" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
+</table>
+</file>
+
+<file path=xl/tables/table22.xml><?xml version="1.0" encoding="utf-8"?>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="39" xr:uid="{EE7EF91D-C903-4E93-8374-8181D0B54E94}" name="Table_SourceData_DataQuality_SampleSize" displayName="Table_SourceData_DataQuality_SampleSize" ref="D283:F288" totalsRowShown="0">
+  <autoFilter ref="D283:F288" xr:uid="{DE8F748C-E65A-4AA2-81BB-D28A432CF334}">
+    <filterColumn colId="0" hiddenButton="1"/>
+    <filterColumn colId="1" hiddenButton="1"/>
+    <filterColumn colId="2" hiddenButton="1"/>
+  </autoFilter>
+  <tableColumns count="3">
+    <tableColumn id="1" xr3:uid="{855C20E7-2F1D-46E4-BCBB-B0560AC9FFBE}" name="Description"/>
+    <tableColumn id="2" xr3:uid="{63747E18-1861-4B36-BC18-2372100BAEB5}" name="ID"/>
+    <tableColumn id="3" xr3:uid="{60790537-9A08-4B5B-8242-4A2FBE180FEA}" name="Score"/>
+  </tableColumns>
+  <tableStyleInfo name="Equation table" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
+</table>
+</file>
+
+<file path=xl/tables/table23.xml><?xml version="1.0" encoding="utf-8"?>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="40" xr:uid="{FC3C5FC3-6328-4E26-A1B1-2FF540B251A3}" name="Table_SourceData_DataQuality_Scope3" displayName="Table_SourceData_DataQuality_Scope3" ref="D292:F297" totalsRowShown="0">
+  <autoFilter ref="D292:F297" xr:uid="{43A1C4DA-75D1-45DF-BA9A-1798C2CC5A4B}">
+    <filterColumn colId="0" hiddenButton="1"/>
+    <filterColumn colId="1" hiddenButton="1"/>
+    <filterColumn colId="2" hiddenButton="1"/>
+  </autoFilter>
+  <tableColumns count="3">
+    <tableColumn id="1" xr3:uid="{1E03ECF4-A79D-42E7-943F-CF1494573C20}" name="Description"/>
+    <tableColumn id="2" xr3:uid="{001CA177-D95B-4CDB-8087-179AE22145B9}" name="ID"/>
+    <tableColumn id="3" xr3:uid="{4F4BC539-FCC4-4BE3-BF64-C433A1418A06}" name="Score"/>
+  </tableColumns>
+  <tableStyleInfo name="Equation table" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
+</table>
+</file>
+
 <file path=xl/tables/table3.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="3" xr:uid="{2BFA511D-1E33-4FA7-9E53-155741FDE40A}" name="Table_AustralianStates" displayName="Table_AustralianStates" ref="D6:F14" totalsRowShown="0">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="20" xr:uid="{4C478747-1F5D-47EE-BF4A-E425947C11C0}" name="Table_AustralianStates" displayName="Table_AustralianStates" ref="D6:F14" totalsRowShown="0">
   <autoFilter ref="D6:F14" xr:uid="{E0906749-7FC7-47DE-82F6-F796C4463018}">
     <filterColumn colId="0" hiddenButton="1"/>
     <filterColumn colId="1" hiddenButton="1"/>
     <filterColumn colId="2" hiddenButton="1"/>
   </autoFilter>
   <tableColumns count="3">
-    <tableColumn id="1" xr3:uid="{A7717A66-4BDA-43C0-BFCD-4A6F29AEE8A3}" name="State/Territory">
+    <tableColumn id="1" xr3:uid="{8A287FA3-800B-4A3C-B890-EE3EB2C92498}" name="State/Territory">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_AustralianStatesTerritories_Data(),Table_AustralianStates[[#Headers],[State/Territory]],0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="2" xr3:uid="{D6D2A619-26C3-4096-9C5E-261DB4783E3F}" name="Common Name">
+    <tableColumn id="2" xr3:uid="{96370351-02C0-481B-ABA4-01406FE3BD55}" name="Common Name">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_AustralianStatesTerritories_Data(),Table_AustralianStates[[#Headers],[State/Territory]],0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="3" xr3:uid="{8F8F275A-708B-458E-9ABF-5295B622DDF7}" name="Abbreviation">
+    <tableColumn id="3" xr3:uid="{842546B1-B984-44F3-AC64-198425448805}" name="Abbreviation">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_AustralianStatesTerritories_Data(),Table_AustralianStates[[#Headers],[State/Territory]],0)</calculatedColumnFormula>
     </tableColumn>
   </tableColumns>
@@ -3973,12 +4096,12 @@
 </file>
 
 <file path=xl/tables/table4.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="4" xr:uid="{A251EF82-BC21-4875-B405-6D0F230C2B8D}" name="Table_WASA4Areas" displayName="Table_WASA4Areas" ref="D20:D30" totalsRowShown="0">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="21" xr:uid="{739DC0B0-B96D-42DE-A74F-9666165298BB}" name="Table_WASA4Areas" displayName="Table_WASA4Areas" ref="D20:D30" totalsRowShown="0">
   <autoFilter ref="D20:D30" xr:uid="{5FA81339-C6C8-4D36-BEEA-6C4AEDD9E676}">
     <filterColumn colId="0" hiddenButton="1"/>
   </autoFilter>
   <tableColumns count="1">
-    <tableColumn id="1" xr3:uid="{0A16A557-CD1A-4230-A0E4-670FBDA4CD09}" name="SA 4 Name">
+    <tableColumn id="1" xr3:uid="{CEB26DE3-6D08-4488-BCC5-CAF66DA0743D}" name="SA 4 Name">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_WASA4Areas_Data(), Table_WASA4Areas[[#Headers],[SA 4 Name]], 0)</calculatedColumnFormula>
     </tableColumn>
   </tableColumns>
@@ -3987,16 +4110,16 @@
 </file>
 
 <file path=xl/tables/table5.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="5" xr:uid="{3F15B4B0-BD4E-4903-9096-ED3FE0A9167C}" name="Table_GWPData" displayName="Table_GWPData" ref="D36:E43" totalsRowShown="0">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="22" xr:uid="{B088AC4D-D2BB-4119-86D0-5C4ECEF277E6}" name="Table_GWPData" displayName="Table_GWPData" ref="D36:E43" totalsRowShown="0">
   <autoFilter ref="D36:E43" xr:uid="{B8E87A66-3E41-4AD3-925D-01EE21B43D7A}">
     <filterColumn colId="0" hiddenButton="1"/>
     <filterColumn colId="1" hiddenButton="1"/>
   </autoFilter>
   <tableColumns count="2">
-    <tableColumn id="1" xr3:uid="{9BFA3AA7-7549-47B7-8147-49CC22B23598}" name="Gas">
+    <tableColumn id="1" xr3:uid="{8B79CC01-3ECE-4E13-BCFA-D269536A7BCE}" name="Gas">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_GWP_Data(), Table_GWPData[[#Headers],[Gas]], 0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="2" xr3:uid="{56BBDB36-E3BB-4678-8824-A909AEED8E49}" name="CO2-e factor">
+    <tableColumn id="2" xr3:uid="{1429926F-63F9-41B0-922F-6ECBEB0F51C9}" name="CO2-e factor">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_GWP_Data(), Table_GWPData[[#Headers],[Gas]], 0)</calculatedColumnFormula>
     </tableColumn>
   </tableColumns>
@@ -4005,7 +4128,7 @@
 </file>
 
 <file path=xl/tables/table6.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="6" xr:uid="{66C67C36-18E1-4B8A-BFF1-35CF3DC4AC81}" name="Table_GasToMolecularConversionFactor" displayName="Table_GasToMolecularConversionFactor" ref="D47:H54" totalsRowShown="0">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="23" xr:uid="{7082FF7C-D65B-40DD-A145-3895A8DB7C1F}" name="Table_GasToMolecularConversionFactor" displayName="Table_GasToMolecularConversionFactor" ref="D47:H54" totalsRowShown="0">
   <autoFilter ref="D47:H54" xr:uid="{C1F562BB-DAA6-45BB-951A-7BAFA5B64B45}">
     <filterColumn colId="0" hiddenButton="1"/>
     <filterColumn colId="1" hiddenButton="1"/>
@@ -4014,19 +4137,19 @@
     <filterColumn colId="4" hiddenButton="1"/>
   </autoFilter>
   <tableColumns count="5">
-    <tableColumn id="1" xr3:uid="{BCBBB9D5-7AA2-41EA-B99D-63DD8E7116D6}" name="Gas">
+    <tableColumn id="1" xr3:uid="{4DBA2455-78CB-4D98-AA3F-09E76468921A}" name="Gas">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ConvertGasElementalToMolecular_Data(),Table_GasToMolecularConversionFactor[[#Headers],[Gas]], 0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="5" xr3:uid="{1F10E85A-E8E7-4403-B922-7CD822BDAAAC}" name="Conversion factor">
+    <tableColumn id="5" xr3:uid="{847F9075-C0C3-424A-89AD-B0E0C46CC2B7}" name="Conversion factor">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ConvertGasElementalToMolecular_Data(),Table_GasToMolecularConversionFactor[[#Headers],[Gas]], 0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="2" xr3:uid="{A186BBCE-16ED-4C60-8611-6582C90E465F}" name="Conversion factor 1">
+    <tableColumn id="2" xr3:uid="{B3F423E7-5422-4AB0-8E9F-FE964D1AB28C}" name="Conversion factor 1">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ConvertGasElementalToMolecular_Data(),Table_GasToMolecularConversionFactor[[#Headers],[Gas]], 0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="3" xr3:uid="{E1D6C7D2-A210-4091-8447-15F9317092F9}" name="Conversion factor 2">
+    <tableColumn id="3" xr3:uid="{70878C27-AF09-4C3E-AA84-4643A115F4B8}" name="Conversion factor 2">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ConvertGasElementalToMolecular_Data(),Table_GasToMolecularConversionFactor[[#Headers],[Gas]], 0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="4" xr3:uid="{7B5653AF-5CD0-44F6-827E-4F17D013B028}" name="Conversion factor combined">
+    <tableColumn id="4" xr3:uid="{5AA59925-0E1E-4C81-A2FE-508039861BCA}" name="Conversion factor combined">
       <calculatedColumnFormula>Table_GasToMolecularConversionFactor[[#This Row],[Conversion factor 1]]/Table_GasToMolecularConversionFactor[[#This Row],[Conversion factor 2]]</calculatedColumnFormula>
     </tableColumn>
   </tableColumns>
@@ -4035,7 +4158,7 @@
 </file>
 
 <file path=xl/tables/table7.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="7" xr:uid="{1D6C8105-982C-4B9F-A603-F884FE56E1B4}" name="Table_SourceData_ClimateZones" displayName="Table_SourceData_ClimateZones" ref="D89:S97" totalsRowShown="0">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="24" xr:uid="{D0CB345A-1C1C-4903-883E-95B118EE9D5B}" name="Table_SourceData_ClimateZones" displayName="Table_SourceData_ClimateZones" ref="D89:S97" totalsRowShown="0">
   <autoFilter ref="D89:S97" xr:uid="{5A437AE9-7724-4CF2-ACCF-291078682FB9}">
     <filterColumn colId="0" hiddenButton="1"/>
     <filterColumn colId="1" hiddenButton="1"/>
@@ -4055,52 +4178,52 @@
     <filterColumn colId="15" hiddenButton="1"/>
   </autoFilter>
   <tableColumns count="16">
-    <tableColumn id="1" xr3:uid="{ED61DF3B-A431-4956-B923-158AD5BF4554}" name="Climate zone" totalsRowCellStyle="Content bold">
+    <tableColumn id="1" xr3:uid="{622A5368-2115-4AFA-9E1B-55763DE89670}" name="Climate zone" totalsRowCellStyle="Content bold">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ClimateZones_Data(), Table_SourceData_ClimateZones[[#Headers],[Climate zone]], 0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="2" xr3:uid="{277D098C-8B59-4F56-B373-2BF7AAA9A607}" name="MAT" totalsRowDxfId="35" totalsRowCellStyle="Content bold">
+    <tableColumn id="2" xr3:uid="{85395033-5600-477B-B2A8-F9DD6340CCA7}" name="MAT" totalsRowDxfId="36" totalsRowCellStyle="Content bold">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ClimateZones_Data(), Table_SourceData_ClimateZones[[#Headers],[Climate zone]], 0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="3" xr3:uid="{827CC720-B781-4728-ABFA-68C972B57850}" name="MAP" totalsRowDxfId="34" totalsRowCellStyle="Content bold">
+    <tableColumn id="3" xr3:uid="{CFC93F08-2BC7-4BBC-A029-A0CEEFC4A386}" name="MAP" totalsRowDxfId="35" totalsRowCellStyle="Content bold">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ClimateZones_Data(), Table_SourceData_ClimateZones[[#Headers],[Climate zone]], 0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="4" xr3:uid="{38653B97-E186-444A-AFBD-15CE44DEBED7}" name="Frost days per year" totalsRowDxfId="33" totalsRowCellStyle="Content bold">
+    <tableColumn id="4" xr3:uid="{7EEE0652-905E-4C60-9EA8-BB1B972258D1}" name="Frost days per year" totalsRowDxfId="34" totalsRowCellStyle="Content bold">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ClimateZones_Data(), Table_SourceData_ClimateZones[[#Headers],[Climate zone]], 0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="5" xr3:uid="{735BA31E-1D4B-45A4-B9FF-7F8ED5243D20}" name="Elevation" totalsRowDxfId="32" totalsRowCellStyle="Content bold">
+    <tableColumn id="5" xr3:uid="{097C0B4C-AE79-4AEF-9D0C-8729F8FD7AE7}" name="Elevation" totalsRowDxfId="33" totalsRowCellStyle="Content bold">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ClimateZones_Data(), Table_SourceData_ClimateZones[[#Headers],[Climate zone]], 0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="6" xr3:uid="{370BE1BB-C3DF-4E43-B8DD-B18D69884A4B}" name="MAP:PET" totalsRowDxfId="31" totalsRowCellStyle="Content bold">
+    <tableColumn id="6" xr3:uid="{FEB741F7-AC5C-4AEE-9552-9D4B6ECAE991}" name="MAP:PET" totalsRowDxfId="32" totalsRowCellStyle="Content bold">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ClimateZones_Data(), Table_SourceData_ClimateZones[[#Headers],[Climate zone]], 0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="7" xr3:uid="{37A53713-47F8-4F27-9505-8BED300E0222}" name="Min temp" totalsRowDxfId="30" totalsRowCellStyle="Content bold">
+    <tableColumn id="7" xr3:uid="{D5410FE5-B548-4931-A6AC-14C2144A60DA}" name="Min temp" totalsRowDxfId="31" totalsRowCellStyle="Content bold">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ClimateZones_Data(), Table_SourceData_ClimateZones[[#Headers],[Climate zone]], 0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="8" xr3:uid="{D9399681-9FC5-41A0-A367-D4D41BBB28CA}" name="Max temp" totalsRowDxfId="29" totalsRowCellStyle="Content bold">
+    <tableColumn id="8" xr3:uid="{5A1A3BF3-FC1C-49D4-864A-417D756978EB}" name="Max temp" totalsRowDxfId="30" totalsRowCellStyle="Content bold">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ClimateZones_Data(), Table_SourceData_ClimateZones[[#Headers],[Climate zone]], 0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="9" xr3:uid="{65211A71-1ABE-4E6D-843C-B0028543D400}" name="Min rainfall" totalsRowDxfId="28" totalsRowCellStyle="Content bold">
+    <tableColumn id="9" xr3:uid="{2C3E4891-FDD2-45D8-9E12-D7E20AB2C942}" name="Min rainfall" totalsRowDxfId="29" totalsRowCellStyle="Content bold">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ClimateZones_Data(), Table_SourceData_ClimateZones[[#Headers],[Climate zone]], 0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="10" xr3:uid="{8ED03576-B413-4D12-B37A-5F11E15AA54D}" name="Max rainfall" totalsRowDxfId="27" totalsRowCellStyle="Content bold">
+    <tableColumn id="10" xr3:uid="{5C2EEE10-BE60-43AB-BD46-3D5857E233F0}" name="Max rainfall" totalsRowDxfId="28" totalsRowCellStyle="Content bold">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ClimateZones_Data(), Table_SourceData_ClimateZones[[#Headers],[Climate zone]], 0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="11" xr3:uid="{E749576A-EB5F-4709-BD15-9BD4E87548D5}" name="Min frost days" totalsRowDxfId="26" totalsRowCellStyle="Content bold">
+    <tableColumn id="11" xr3:uid="{B8D4FB2A-E41F-41E4-A1B0-B50B6F4B8222}" name="Min frost days" totalsRowDxfId="27" totalsRowCellStyle="Content bold">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ClimateZones_Data(), Table_SourceData_ClimateZones[[#Headers],[Climate zone]], 0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="15" xr3:uid="{61CC0B40-56FD-487C-A589-45456757E8A1}" name="Max frost days" totalsRowDxfId="25" totalsRowCellStyle="Content bold">
+    <tableColumn id="15" xr3:uid="{D1F195A5-29D3-4872-B840-5C2B982B31D3}" name="Max frost days" totalsRowDxfId="26" totalsRowCellStyle="Content bold">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ClimateZones_Data(), Table_SourceData_ClimateZones[[#Headers],[Climate zone]], 0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="12" xr3:uid="{32B52E24-5576-47A4-A024-CDC090D88746}" name="Min elevation" totalsRowDxfId="24" totalsRowCellStyle="Content bold">
+    <tableColumn id="12" xr3:uid="{D7C29537-FEDC-4D4C-ACE3-42DDEEA677B7}" name="Min elevation" totalsRowDxfId="25" totalsRowCellStyle="Content bold">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ClimateZones_Data(), Table_SourceData_ClimateZones[[#Headers],[Climate zone]], 0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="16" xr3:uid="{B4341912-AB7E-4E58-9B4D-9791D45FB352}" name="Max elevation" totalsRowDxfId="23" totalsRowCellStyle="Content bold">
+    <tableColumn id="16" xr3:uid="{958174B2-155C-4F21-8FC1-CAED3FC453D2}" name="Max elevation" totalsRowDxfId="24" totalsRowCellStyle="Content bold">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ClimateZones_Data(), Table_SourceData_ClimateZones[[#Headers],[Climate zone]], 0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="13" xr3:uid="{67418986-6C11-45D0-A4DC-D7861BD61C09}" name="Min MAP:PET" totalsRowDxfId="22" totalsRowCellStyle="Content bold">
+    <tableColumn id="13" xr3:uid="{17E613AB-F9F0-404A-8CFE-A6BE09D2A63F}" name="Min MAP:PET" totalsRowDxfId="23" totalsRowCellStyle="Content bold">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ClimateZones_Data(), Table_SourceData_ClimateZones[[#Headers],[Climate zone]], 0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="17" xr3:uid="{90614980-AE79-4306-A6ED-229525821D94}" name="Max MAP:PET" totalsRowDxfId="21" totalsRowCellStyle="Content bold">
+    <tableColumn id="17" xr3:uid="{1E04DA75-1873-41D6-92F5-FFC40E85975A}" name="Max MAP:PET" totalsRowDxfId="22" totalsRowCellStyle="Content bold">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ClimateZones_Data(), Table_SourceData_ClimateZones[[#Headers],[Climate zone]], 0)</calculatedColumnFormula>
     </tableColumn>
   </tableColumns>
@@ -4109,16 +4232,16 @@
 </file>
 
 <file path=xl/tables/table8.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="8" xr:uid="{D228FD2E-DAAA-4D4F-BEFF-0E68A1F33AA0}" name="Table_SourceData_WetDryZones" displayName="Table_SourceData_WetDryZones" ref="D63:E77" totalsRowShown="0">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="25" xr:uid="{78EA0F00-70EE-4353-B983-2572CEB0F042}" name="Table_SourceData_WetDryZones" displayName="Table_SourceData_WetDryZones" ref="D63:E77" totalsRowShown="0">
   <autoFilter ref="D63:E77" xr:uid="{3597E019-B21E-4B76-BCC8-D02D497BCFA9}">
     <filterColumn colId="0" hiddenButton="1"/>
     <filterColumn colId="1" hiddenButton="1"/>
   </autoFilter>
   <tableColumns count="2">
-    <tableColumn id="1" xr3:uid="{FEB61CA1-B375-461F-AD5A-5B01A03F7A14}" name="Climate zone" totalsRowCellStyle="Content bold">
+    <tableColumn id="1" xr3:uid="{18F355FA-9E18-4624-B96F-3F7C85E0C75C}" name="Climate zone" totalsRowCellStyle="Content bold">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_WetAndDryZones_Data(), Table_SourceData_WetDryZones[[#Headers],[Climate zone]], 0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="2" xr3:uid="{EE3C7A00-6DDA-427C-9573-7908B05111FB}" name="Wet or Dry Zone" totalsRowDxfId="20" totalsRowCellStyle="Content bold">
+    <tableColumn id="2" xr3:uid="{1E23F64E-887D-4EF9-9FE8-07F603CE353D}" name="Wet or Dry Zone" totalsRowDxfId="21" totalsRowCellStyle="Content bold">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_WetAndDryZones_Data(), Table_SourceData_WetDryZones[[#Headers],[Climate zone]], 0)</calculatedColumnFormula>
     </tableColumn>
   </tableColumns>
@@ -4127,7 +4250,7 @@
 </file>
 
 <file path=xl/tables/table9.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="9" xr:uid="{E436A27C-11D9-4092-B110-DE3B0C7D7A9C}" name="Table_SourceData_TemperatureZones" displayName="Table_SourceData_TemperatureZones" ref="D109:G112" totalsRowShown="0">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="26" xr:uid="{C3AFA370-8738-4E34-8DE5-34791278D8CA}" name="Table_SourceData_TemperatureZones" displayName="Table_SourceData_TemperatureZones" ref="D109:G112" totalsRowShown="0">
   <autoFilter ref="D109:G112" xr:uid="{AB16FEAB-AB03-45E1-BBD4-66D29CD412DF}">
     <filterColumn colId="0" hiddenButton="1"/>
     <filterColumn colId="1" hiddenButton="1"/>
@@ -4135,16 +4258,16 @@
     <filterColumn colId="3" hiddenButton="1"/>
   </autoFilter>
   <tableColumns count="4">
-    <tableColumn id="1" xr3:uid="{3E477FC1-0E60-467C-87C8-DC619003DA7D}" name="Temperature Zone">
+    <tableColumn id="1" xr3:uid="{D028E416-FD0D-4083-A9D9-9CDCBCBAB5EC}" name="Temperature Zone">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_TemperatureZones_Data(),Table_SourceData_TemperatureZones[[#Headers],[Temperature Zone]],0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="2" xr3:uid="{CD029E58-AF67-4858-BEF6-937BB536E757}" name="MAT">
+    <tableColumn id="2" xr3:uid="{3213D349-5EBF-4936-AAA8-D15F4B964FB1}" name="MAT">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_TemperatureZones_Data(),Table_SourceData_TemperatureZones[[#Headers],[Temperature Zone]],0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="3" xr3:uid="{5195427E-32DD-4977-88C7-473D17A15EDE}" name="Min MAT">
+    <tableColumn id="3" xr3:uid="{E0EBBFC7-A140-40A8-8E12-520D0626130C}" name="Min MAT">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_TemperatureZones_Data(),Table_SourceData_TemperatureZones[[#Headers],[Temperature Zone]],0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="4" xr3:uid="{4C8D6B45-65E8-4A84-9B64-B4D1E990BE71}" name="Max MAT">
+    <tableColumn id="4" xr3:uid="{D697D416-FDA5-4372-8BBC-3176E3922018}" name="Max MAT">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_TemperatureZones_Data(),Table_SourceData_TemperatureZones[[#Headers],[Temperature Zone]],0)</calculatedColumnFormula>
     </tableColumn>
   </tableColumns>
@@ -4410,12 +4533,35 @@
   <sheetPr>
     <tabColor rgb="FF0C769E"/>
   </sheetPr>
-  <dimension ref="A1"/>
+  <dimension ref="A1:A8"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
     <row r="1" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>0</v>
+      </c>
+    </row>
+    <row r="3" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A3" s="97" t="str">
+        <f>HYPERLINK("#'Home'!A1", "Home")</f>
+        <v>Home</v>
+      </c>
+    </row>
+    <row r="6" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A6" s="98" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="7" spans="1:1" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A7" s="5" t="str">
+        <f>HYPERLINK("#'Constants - Common'!A1", "Constants - Common")</f>
+        <v>Constants - Common</v>
+      </c>
+    </row>
+    <row r="8" spans="1:1" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A8" s="5" t="str">
+        <f>HYPERLINK("#'Acknowledgements'!A1", "Acknowledgements")</f>
+        <v>Acknowledgements</v>
       </c>
     </row>
   </sheetData>
@@ -4544,11 +4690,11 @@
         <v>7</v>
       </c>
       <c r="H7" s="19" t="e" cm="1">
-        <f t="array" ref="H7">Common_Equations.Common_ConvertCH4ToCO2e(E7,_xlfn.XLOOKUP("CH4", Table_GWPData[Gas],Table_GWPData[CO2-e factor]))</f>
+        <f t="array" aca="1" ref="H7" ca="1">Common_Equations.Common_ConvertCH4ToCO2e(E7,_xlfn.XLOOKUP("CH4", Table_GWPData[Gas],Table_GWPData[CO2-e factor]))</f>
         <v>#NAME?</v>
       </c>
       <c r="I7" s="19" t="e" cm="1">
-        <f t="array" ref="I7">Common_Equations.Common_ConvertCH4ToCO2e(F7,_xlfn.XLOOKUP("CH4", Table_GWPData[Gas],Table_GWPData[CO2-e factor]))</f>
+        <f t="array" aca="1" ref="I7" ca="1">Common_Equations.Common_ConvertCH4ToCO2e(F7,_xlfn.XLOOKUP("CH4", Table_GWPData[Gas],Table_GWPData[CO2-e factor]))</f>
         <v>#NAME?</v>
       </c>
       <c r="J7" s="16" t="s">
@@ -4577,11 +4723,11 @@
         <v>7</v>
       </c>
       <c r="H8" s="19" t="e" cm="1">
-        <f t="array" ref="H8">Common_Equations.Common_ConvertCH4ToCO2e(E8,_xlfn.XLOOKUP("CH4", Table_GWPData[Gas],Table_GWPData[CO2-e factor]))</f>
+        <f t="array" aca="1" ref="H8" ca="1">Common_Equations.Common_ConvertCH4ToCO2e(E8,_xlfn.XLOOKUP("CH4", Table_GWPData[Gas],Table_GWPData[CO2-e factor]))</f>
         <v>#NAME?</v>
       </c>
       <c r="I8" s="19" t="e" cm="1">
-        <f t="array" ref="I8">Common_Equations.Common_ConvertCH4ToCO2e(F8,_xlfn.XLOOKUP("CH4", Table_GWPData[Gas],Table_GWPData[CO2-e factor]))</f>
+        <f t="array" aca="1" ref="I8" ca="1">Common_Equations.Common_ConvertCH4ToCO2e(F8,_xlfn.XLOOKUP("CH4", Table_GWPData[Gas],Table_GWPData[CO2-e factor]))</f>
         <v>#NAME?</v>
       </c>
       <c r="J8" s="16" t="s">
@@ -4607,11 +4753,11 @@
         <v>13</v>
       </c>
       <c r="H9" s="19" t="e" cm="1">
-        <f t="array" ref="H9">Common_Equations.Common_ConvertN2OToCO2e(E9,_xlfn.XLOOKUP("N2O", Table_GWPData[Gas],Table_GWPData[CO2-e factor]))</f>
+        <f t="array" aca="1" ref="H9" ca="1">Common_Equations.Common_ConvertN2OToCO2e(E9,_xlfn.XLOOKUP("N2O", Table_GWPData[Gas],Table_GWPData[CO2-e factor]))</f>
         <v>#NAME?</v>
       </c>
       <c r="I9" s="19" t="e" cm="1">
-        <f t="array" ref="I9">Common_Equations.Common_ConvertN2OToCO2e(F9,_xlfn.XLOOKUP("N2O", Table_GWPData[Gas],Table_GWPData[CO2-e factor]))</f>
+        <f t="array" aca="1" ref="I9" ca="1">Common_Equations.Common_ConvertN2OToCO2e(F9,_xlfn.XLOOKUP("N2O", Table_GWPData[Gas],Table_GWPData[CO2-e factor]))</f>
         <v>#NAME?</v>
       </c>
       <c r="J9" s="16" t="s">
@@ -4639,11 +4785,11 @@
         <v>13</v>
       </c>
       <c r="H10" s="19" t="e" cm="1">
-        <f t="array" ref="H10">Common_Equations.Common_ConvertN2OToCO2e(E10,_xlfn.XLOOKUP("N2O", Table_GWPData[Gas],Table_GWPData[CO2-e factor]))</f>
+        <f t="array" aca="1" ref="H10" ca="1">Common_Equations.Common_ConvertN2OToCO2e(E10,_xlfn.XLOOKUP("N2O", Table_GWPData[Gas],Table_GWPData[CO2-e factor]))</f>
         <v>#NAME?</v>
       </c>
       <c r="I10" s="19" t="e" cm="1">
-        <f t="array" ref="I10">Common_Equations.Common_ConvertN2OToCO2e(F10,_xlfn.XLOOKUP("N2O", Table_GWPData[Gas],Table_GWPData[CO2-e factor]))</f>
+        <f t="array" aca="1" ref="I10" ca="1">Common_Equations.Common_ConvertN2OToCO2e(F10,_xlfn.XLOOKUP("N2O", Table_GWPData[Gas],Table_GWPData[CO2-e factor]))</f>
         <v>#NAME?</v>
       </c>
       <c r="J10" s="16" t="s">
@@ -4672,11 +4818,11 @@
         <v>13</v>
       </c>
       <c r="H11" s="19" t="e" cm="1">
-        <f t="array" ref="H11">Common_Equations.Common_ConvertN2OToCO2e(E11,_xlfn.XLOOKUP("N2O", Table_GWPData[Gas],Table_GWPData[CO2-e factor]))</f>
+        <f t="array" aca="1" ref="H11" ca="1">Common_Equations.Common_ConvertN2OToCO2e(E11,_xlfn.XLOOKUP("N2O", Table_GWPData[Gas],Table_GWPData[CO2-e factor]))</f>
         <v>#NAME?</v>
       </c>
       <c r="I11" s="19" t="e" cm="1">
-        <f t="array" ref="I11">Common_Equations.Common_ConvertN2OToCO2e(F11,_xlfn.XLOOKUP("N2O", Table_GWPData[Gas],Table_GWPData[CO2-e factor]))</f>
+        <f t="array" aca="1" ref="I11" ca="1">Common_Equations.Common_ConvertN2OToCO2e(F11,_xlfn.XLOOKUP("N2O", Table_GWPData[Gas],Table_GWPData[CO2-e factor]))</f>
         <v>#NAME?</v>
       </c>
       <c r="J11" s="16" t="s">
@@ -4705,11 +4851,11 @@
         <v>13</v>
       </c>
       <c r="H12" s="19" t="e" cm="1">
-        <f t="array" ref="H12">Common_Equations.Common_ConvertN2OToCO2e(E12,_xlfn.XLOOKUP("N2O", Table_GWPData[Gas],Table_GWPData[CO2-e factor]))</f>
+        <f t="array" aca="1" ref="H12" ca="1">Common_Equations.Common_ConvertN2OToCO2e(E12,_xlfn.XLOOKUP("N2O", Table_GWPData[Gas],Table_GWPData[CO2-e factor]))</f>
         <v>#NAME?</v>
       </c>
       <c r="I12" s="19" t="e" cm="1">
-        <f t="array" ref="I12">Common_Equations.Common_ConvertN2OToCO2e(F12,_xlfn.XLOOKUP("N2O", Table_GWPData[Gas],Table_GWPData[CO2-e factor]))</f>
+        <f t="array" aca="1" ref="I12" ca="1">Common_Equations.Common_ConvertN2OToCO2e(F12,_xlfn.XLOOKUP("N2O", Table_GWPData[Gas],Table_GWPData[CO2-e factor]))</f>
         <v>#NAME?</v>
       </c>
       <c r="J12" s="16" t="s">
@@ -4738,11 +4884,11 @@
         <v>13</v>
       </c>
       <c r="H13" s="19" t="e" cm="1">
-        <f t="array" ref="H13">Common_Equations.Common_ConvertN2OToCO2e(E13,_xlfn.XLOOKUP("N2O", Table_GWPData[Gas],Table_GWPData[CO2-e factor]))</f>
+        <f t="array" aca="1" ref="H13" ca="1">Common_Equations.Common_ConvertN2OToCO2e(E13,_xlfn.XLOOKUP("N2O", Table_GWPData[Gas],Table_GWPData[CO2-e factor]))</f>
         <v>#NAME?</v>
       </c>
       <c r="I13" s="19" t="e" cm="1">
-        <f t="array" ref="I13">Common_Equations.Common_ConvertN2OToCO2e(F13,_xlfn.XLOOKUP("N2O", Table_GWPData[Gas],Table_GWPData[CO2-e factor]))</f>
+        <f t="array" aca="1" ref="I13" ca="1">Common_Equations.Common_ConvertN2OToCO2e(F13,_xlfn.XLOOKUP("N2O", Table_GWPData[Gas],Table_GWPData[CO2-e factor]))</f>
         <v>#NAME?</v>
       </c>
       <c r="J13" s="16" t="s">
@@ -4771,11 +4917,11 @@
         <v>13</v>
       </c>
       <c r="H14" s="19" t="e" cm="1">
-        <f t="array" ref="H14">Common_Equations.Common_ConvertN2OToCO2e(E14,_xlfn.XLOOKUP("N2O", Table_GWPData[Gas],Table_GWPData[CO2-e factor]))</f>
+        <f t="array" aca="1" ref="H14" ca="1">Common_Equations.Common_ConvertN2OToCO2e(E14,_xlfn.XLOOKUP("N2O", Table_GWPData[Gas],Table_GWPData[CO2-e factor]))</f>
         <v>#NAME?</v>
       </c>
       <c r="I14" s="19" t="e" cm="1">
-        <f t="array" ref="I14">Common_Equations.Common_ConvertN2OToCO2e(F14,_xlfn.XLOOKUP("N2O", Table_GWPData[Gas],Table_GWPData[CO2-e factor]))</f>
+        <f t="array" aca="1" ref="I14" ca="1">Common_Equations.Common_ConvertN2OToCO2e(F14,_xlfn.XLOOKUP("N2O", Table_GWPData[Gas],Table_GWPData[CO2-e factor]))</f>
         <v>#NAME?</v>
       </c>
       <c r="J14" s="16" t="s">
@@ -4801,11 +4947,11 @@
         <v>13</v>
       </c>
       <c r="H15" s="19" t="e" cm="1">
-        <f t="array" ref="H15">Common_Equations.Common_ConvertN2OToCO2e(E15,_xlfn.XLOOKUP("N2O", Table_GWPData[Gas],Table_GWPData[CO2-e factor]))</f>
+        <f t="array" aca="1" ref="H15" ca="1">Common_Equations.Common_ConvertN2OToCO2e(E15,_xlfn.XLOOKUP("N2O", Table_GWPData[Gas],Table_GWPData[CO2-e factor]))</f>
         <v>#NAME?</v>
       </c>
       <c r="I15" s="19" t="e" cm="1">
-        <f t="array" ref="I15">Common_Equations.Common_ConvertN2OToCO2e(F15,_xlfn.XLOOKUP("N2O", Table_GWPData[Gas],Table_GWPData[CO2-e factor]))</f>
+        <f t="array" aca="1" ref="I15" ca="1">Common_Equations.Common_ConvertN2OToCO2e(F15,_xlfn.XLOOKUP("N2O", Table_GWPData[Gas],Table_GWPData[CO2-e factor]))</f>
         <v>#NAME?</v>
       </c>
       <c r="J15" s="16" t="s">
@@ -4866,11 +5012,11 @@
         <v>13</v>
       </c>
       <c r="H17" s="19" t="e" cm="1">
-        <f t="array" ref="H17">Common_Equations.Common_ConvertN2OToCO2e(E17,_xlfn.XLOOKUP("N2O", Table_GWPData[Gas],Table_GWPData[CO2-e factor]))</f>
+        <f t="array" aca="1" ref="H17" ca="1">Common_Equations.Common_ConvertN2OToCO2e(E17,_xlfn.XLOOKUP("N2O", Table_GWPData[Gas],Table_GWPData[CO2-e factor]))</f>
         <v>#NAME?</v>
       </c>
       <c r="I17" s="19" t="e" cm="1">
-        <f t="array" ref="I17">Common_Equations.Common_ConvertN2OToCO2e(F17,_xlfn.XLOOKUP("N2O", Table_GWPData[Gas],Table_GWPData[CO2-e factor]))</f>
+        <f t="array" aca="1" ref="I17" ca="1">Common_Equations.Common_ConvertN2OToCO2e(F17,_xlfn.XLOOKUP("N2O", Table_GWPData[Gas],Table_GWPData[CO2-e factor]))</f>
         <v>#NAME?</v>
       </c>
       <c r="J17" s="16" t="s">
@@ -4932,11 +5078,11 @@
         <v>13</v>
       </c>
       <c r="H19" s="19" t="e" cm="1">
-        <f t="array" ref="H19">Common_Equations.Common_ConvertN2OToCO2e(E19,_xlfn.XLOOKUP("N2O", Table_GWPData[Gas],Table_GWPData[CO2-e factor]))</f>
+        <f t="array" aca="1" ref="H19" ca="1">Common_Equations.Common_ConvertN2OToCO2e(E19,_xlfn.XLOOKUP("N2O", Table_GWPData[Gas],Table_GWPData[CO2-e factor]))</f>
         <v>#NAME?</v>
       </c>
       <c r="I19" s="19" t="e" cm="1">
-        <f t="array" ref="I19">Common_Equations.Common_ConvertN2OToCO2e(F19,_xlfn.XLOOKUP("N2O", Table_GWPData[Gas],Table_GWPData[CO2-e factor]))</f>
+        <f t="array" aca="1" ref="I19" ca="1">Common_Equations.Common_ConvertN2OToCO2e(F19,_xlfn.XLOOKUP("N2O", Table_GWPData[Gas],Table_GWPData[CO2-e factor]))</f>
         <v>#NAME?</v>
       </c>
       <c r="J19" s="16" t="s">
@@ -4965,11 +5111,11 @@
         <v>13</v>
       </c>
       <c r="H20" s="19" t="e" cm="1">
-        <f t="array" ref="H20">Common_Equations.Common_ConvertN2OToCO2e(E20,_xlfn.XLOOKUP("N2O", Table_GWPData[Gas],Table_GWPData[CO2-e factor]))</f>
+        <f t="array" aca="1" ref="H20" ca="1">Common_Equations.Common_ConvertN2OToCO2e(E20,_xlfn.XLOOKUP("N2O", Table_GWPData[Gas],Table_GWPData[CO2-e factor]))</f>
         <v>#NAME?</v>
       </c>
       <c r="I20" s="19" t="e" cm="1">
-        <f t="array" ref="I20">Common_Equations.Common_ConvertN2OToCO2e(F20,_xlfn.XLOOKUP("N2O", Table_GWPData[Gas],Table_GWPData[CO2-e factor]))</f>
+        <f t="array" aca="1" ref="I20" ca="1">Common_Equations.Common_ConvertN2OToCO2e(F20,_xlfn.XLOOKUP("N2O", Table_GWPData[Gas],Table_GWPData[CO2-e factor]))</f>
         <v>#NAME?</v>
       </c>
       <c r="J20" s="16" t="s">
@@ -4994,11 +5140,11 @@
         <v>13</v>
       </c>
       <c r="H21" s="19" t="e" cm="1">
-        <f t="array" ref="H21">Common_Equations.Common_ConvertN2OToCO2e(E21,_xlfn.XLOOKUP("N2O", Table_GWPData[Gas],Table_GWPData[CO2-e factor]))</f>
+        <f t="array" aca="1" ref="H21" ca="1">Common_Equations.Common_ConvertN2OToCO2e(E21,_xlfn.XLOOKUP("N2O", Table_GWPData[Gas],Table_GWPData[CO2-e factor]))</f>
         <v>#NAME?</v>
       </c>
       <c r="I21" s="19" t="e" cm="1">
-        <f t="array" ref="I21">Common_Equations.Common_ConvertN2OToCO2e(F21,_xlfn.XLOOKUP("N2O", Table_GWPData[Gas],Table_GWPData[CO2-e factor]))</f>
+        <f t="array" aca="1" ref="I21" ca="1">Common_Equations.Common_ConvertN2OToCO2e(F21,_xlfn.XLOOKUP("N2O", Table_GWPData[Gas],Table_GWPData[CO2-e factor]))</f>
         <v>#NAME?</v>
       </c>
       <c r="J21" s="16" t="s">
@@ -5024,11 +5170,11 @@
         <v>13</v>
       </c>
       <c r="H22" s="19" t="e" cm="1">
-        <f t="array" ref="H22">Common_Equations.Common_ConvertN2OToCO2e(E22,_xlfn.XLOOKUP("N2O", Table_GWPData[Gas],Table_GWPData[CO2-e factor]))</f>
+        <f t="array" aca="1" ref="H22" ca="1">Common_Equations.Common_ConvertN2OToCO2e(E22,_xlfn.XLOOKUP("N2O", Table_GWPData[Gas],Table_GWPData[CO2-e factor]))</f>
         <v>#NAME?</v>
       </c>
       <c r="I22" s="19" t="e" cm="1">
-        <f t="array" ref="I22">Common_Equations.Common_ConvertN2OToCO2e(F22,_xlfn.XLOOKUP("N2O", Table_GWPData[Gas],Table_GWPData[CO2-e factor]))</f>
+        <f t="array" aca="1" ref="I22" ca="1">Common_Equations.Common_ConvertN2OToCO2e(F22,_xlfn.XLOOKUP("N2O", Table_GWPData[Gas],Table_GWPData[CO2-e factor]))</f>
         <v>#NAME?</v>
       </c>
       <c r="J22" s="16" t="s">
@@ -5084,11 +5230,11 @@
         <v>7</v>
       </c>
       <c r="H24" s="19" t="e" cm="1">
-        <f t="array" ref="H24">Common_Equations.Common_ConvertCH4ToCO2e(E24,_xlfn.XLOOKUP("CH4", Table_GWPData[Gas],Table_GWPData[CO2-e factor]))</f>
+        <f t="array" aca="1" ref="H24" ca="1">Common_Equations.Common_ConvertCH4ToCO2e(E24,_xlfn.XLOOKUP("CH4", Table_GWPData[Gas],Table_GWPData[CO2-e factor]))</f>
         <v>#NAME?</v>
       </c>
       <c r="I24" s="19" t="e" cm="1">
-        <f t="array" ref="I24">Common_Equations.Common_ConvertCH4ToCO2e(F24,_xlfn.XLOOKUP("CH4", Table_GWPData[Gas],Table_GWPData[CO2-e factor]))</f>
+        <f t="array" aca="1" ref="I24" ca="1">Common_Equations.Common_ConvertCH4ToCO2e(F24,_xlfn.XLOOKUP("CH4", Table_GWPData[Gas],Table_GWPData[CO2-e factor]))</f>
         <v>#NAME?</v>
       </c>
       <c r="J24" s="16" t="s">
@@ -5113,11 +5259,11 @@
         <v>13</v>
       </c>
       <c r="H25" s="19" t="e" cm="1">
-        <f t="array" ref="H25">Common_Equations.Common_ConvertN2OToCO2e(E25,_xlfn.XLOOKUP("N2O", Table_GWPData[Gas],Table_GWPData[CO2-e factor]))</f>
+        <f t="array" aca="1" ref="H25" ca="1">Common_Equations.Common_ConvertN2OToCO2e(E25,_xlfn.XLOOKUP("N2O", Table_GWPData[Gas],Table_GWPData[CO2-e factor]))</f>
         <v>#NAME?</v>
       </c>
       <c r="I25" s="19" t="e" cm="1">
-        <f t="array" ref="I25">Common_Equations.Common_ConvertN2OToCO2e(F25,_xlfn.XLOOKUP("N2O", Table_GWPData[Gas],Table_GWPData[CO2-e factor]))</f>
+        <f t="array" aca="1" ref="I25" ca="1">Common_Equations.Common_ConvertN2OToCO2e(F25,_xlfn.XLOOKUP("N2O", Table_GWPData[Gas],Table_GWPData[CO2-e factor]))</f>
         <v>#NAME?</v>
       </c>
       <c r="J25" s="16" t="s">
@@ -5171,11 +5317,11 @@
         <v>7</v>
       </c>
       <c r="H27" s="19" t="e" cm="1">
-        <f t="array" ref="H27">Common_Equations.Common_ConvertCH4ToCO2e(E27,_xlfn.XLOOKUP("CH4", Table_GWPData[Gas],Table_GWPData[CO2-e factor]))</f>
+        <f t="array" aca="1" ref="H27" ca="1">Common_Equations.Common_ConvertCH4ToCO2e(E27,_xlfn.XLOOKUP("CH4", Table_GWPData[Gas],Table_GWPData[CO2-e factor]))</f>
         <v>#NAME?</v>
       </c>
       <c r="I27" s="19" t="e" cm="1">
-        <f t="array" ref="I27">Common_Equations.Common_ConvertCH4ToCO2e(F27,_xlfn.XLOOKUP("CH4", Table_GWPData[Gas],Table_GWPData[CO2-e factor]))</f>
+        <f t="array" aca="1" ref="I27" ca="1">Common_Equations.Common_ConvertCH4ToCO2e(F27,_xlfn.XLOOKUP("CH4", Table_GWPData[Gas],Table_GWPData[CO2-e factor]))</f>
         <v>#NAME?</v>
       </c>
       <c r="J27" s="16" t="s">
@@ -5200,11 +5346,11 @@
         <v>13</v>
       </c>
       <c r="H28" s="19" t="e" cm="1">
-        <f t="array" ref="H28">Common_Equations.Common_ConvertN2OToCO2e(E28,_xlfn.XLOOKUP("N2O", Table_GWPData[Gas],Table_GWPData[CO2-e factor]))</f>
+        <f t="array" aca="1" ref="H28" ca="1">Common_Equations.Common_ConvertN2OToCO2e(E28,_xlfn.XLOOKUP("N2O", Table_GWPData[Gas],Table_GWPData[CO2-e factor]))</f>
         <v>#NAME?</v>
       </c>
       <c r="I28" s="19" t="e" cm="1">
-        <f t="array" ref="I28">Common_Equations.Common_ConvertN2OToCO2e(F28,_xlfn.XLOOKUP("N2O", Table_GWPData[Gas],Table_GWPData[CO2-e factor]))</f>
+        <f t="array" aca="1" ref="I28" ca="1">Common_Equations.Common_ConvertN2OToCO2e(F28,_xlfn.XLOOKUP("N2O", Table_GWPData[Gas],Table_GWPData[CO2-e factor]))</f>
         <v>#NAME?</v>
       </c>
       <c r="J28" s="16" t="s">
@@ -5279,11 +5425,11 @@
       <c r="F31" s="10"/>
       <c r="G31" s="15"/>
       <c r="H31" s="20" t="e">
-        <f>SUM(H7:H30)</f>
+        <f ca="1">SUM(H7:H30)</f>
         <v>#NAME?</v>
       </c>
       <c r="I31" s="20" t="e">
-        <f>SUM(I7:I30)</f>
+        <f ca="1">SUM(I7:I30)</f>
         <v>#NAME?</v>
       </c>
       <c r="J31" s="16" t="s">
@@ -5420,11 +5566,11 @@
         <v>01 Jan 2024 to 31 Dec 2024 (This reporting cycle)</v>
       </c>
       <c r="E41" s="86" t="e">
-        <f>IF(ISBLANK($D41), 0, IF(ISNUMBER(SEARCH("reporting", $D41)), Result_Enterprise_Method1, "Enter value"))</f>
+        <f ca="1">IF(ISBLANK($D41), 0, IF(ISNUMBER(SEARCH("reporting", $D41)), Result_Enterprise_Method1, "Enter value"))</f>
         <v>#NAME?</v>
       </c>
       <c r="F41" s="86" t="e">
-        <f>IF(ISBLANK($D41), 0, IF(ISNUMBER(SEARCH("reporting", $D41)), Result_Enterprise_Method2, "Enter value"))</f>
+        <f ca="1">IF(ISBLANK($D41), 0, IF(ISNUMBER(SEARCH("reporting", $D41)), Result_Enterprise_Method2, "Enter value"))</f>
         <v>#NAME?</v>
       </c>
       <c r="G41" s="16" t="s">
@@ -5500,11 +5646,11 @@
         <v>134</v>
       </c>
       <c r="E45" s="20" t="e">
-        <f>SUM(E40:E44)</f>
+        <f ca="1">SUM(E40:E44)</f>
         <v>#NAME?</v>
       </c>
       <c r="F45" s="20" t="e">
-        <f>SUM(F40:F44)</f>
+        <f ca="1">SUM(F40:F44)</f>
         <v>#NAME?</v>
       </c>
       <c r="G45" s="1"/>
@@ -5744,11 +5890,11 @@
         <v>136</v>
       </c>
       <c r="E62" s="87" t="e">
-        <f>E45-E56</f>
+        <f ca="1">E45-E56</f>
         <v>#NAME?</v>
       </c>
       <c r="F62" s="87" t="e">
-        <f>F45-E56</f>
+        <f ca="1">F45-E56</f>
         <v>#NAME?</v>
       </c>
       <c r="G62" s="1"/>
@@ -5834,11 +5980,11 @@
         <v>#NAME?</v>
       </c>
       <c r="H67" s="19" t="e">
-        <f>(Result_EmissionsForWholeProductionCycle_Method1/F67)*G67</f>
+        <f ca="1">(Result_EmissionsForWholeProductionCycle_Method1/F67)*G67</f>
         <v>#NAME?</v>
       </c>
       <c r="I67" s="19" t="e">
-        <f>(Result_EmissionsForWholeProductionCycle_Method2/F67)*G67</f>
+        <f ca="1">(Result_EmissionsForWholeProductionCycle_Method2/F67)*G67</f>
         <v>#NAME?</v>
       </c>
       <c r="J67" s="16" t="s">
@@ -5863,11 +6009,11 @@
         <v>#NAME?</v>
       </c>
       <c r="H68" s="19" t="e">
-        <f>(Result_NetEmissions_Method1/F68)*G68</f>
+        <f ca="1">(Result_NetEmissions_Method1/F68)*G68</f>
         <v>#NAME?</v>
       </c>
       <c r="I68" s="19" t="e">
-        <f>(Result_NetEmissions_Method2/F68)*G68</f>
+        <f ca="1">(Result_NetEmissions_Method2/F68)*G68</f>
         <v>#NAME?</v>
       </c>
       <c r="J68" s="16" t="s">
@@ -5892,11 +6038,11 @@
         <v>#NAME?</v>
       </c>
       <c r="H69" s="19" t="e">
-        <f>(Result_EmissionsForWholeProductionCycle_Method1/F69)*G69</f>
+        <f ca="1">(Result_EmissionsForWholeProductionCycle_Method1/F69)*G69</f>
         <v>#NAME?</v>
       </c>
       <c r="I69" s="19" t="e">
-        <f>(Result_EmissionsForWholeProductionCycle_Method2/F69)*G69</f>
+        <f ca="1">(Result_EmissionsForWholeProductionCycle_Method2/F69)*G69</f>
         <v>#NAME?</v>
       </c>
       <c r="J69" s="16" t="s">
@@ -5921,11 +6067,11 @@
         <v>#NAME?</v>
       </c>
       <c r="H70" s="19" t="e">
-        <f>(Result_NetEmissions_Method1/F70)*G70</f>
+        <f ca="1">(Result_NetEmissions_Method1/F70)*G70</f>
         <v>#NAME?</v>
       </c>
       <c r="I70" s="19" t="e">
-        <f>(Result_NetEmissions_Method2/F70)*G70</f>
+        <f ca="1">(Result_NetEmissions_Method2/F70)*G70</f>
         <v>#NAME?</v>
       </c>
       <c r="J70" s="16" t="s">
@@ -5950,11 +6096,11 @@
         <v>#NAME?</v>
       </c>
       <c r="H71" s="19" t="e">
-        <f>(Result_EmissionsForWholeProductionCycle_Method1/F71)*G71</f>
+        <f ca="1">(Result_EmissionsForWholeProductionCycle_Method1/F71)*G71</f>
         <v>#NAME?</v>
       </c>
       <c r="I71" s="19" t="e">
-        <f>(Result_EmissionsForWholeProductionCycle_Method2/F71)*G71</f>
+        <f ca="1">(Result_EmissionsForWholeProductionCycle_Method2/F71)*G71</f>
         <v>#NAME?</v>
       </c>
       <c r="J71" s="16" t="s">
@@ -5979,11 +6125,11 @@
         <v>#NAME?</v>
       </c>
       <c r="H72" s="19" t="e">
-        <f>(Result_NetEmissions_Method1/F72)*G72</f>
+        <f ca="1">(Result_NetEmissions_Method1/F72)*G72</f>
         <v>#NAME?</v>
       </c>
       <c r="I72" s="19" t="e">
-        <f>(Result_NetEmissions_Method2/F72)*G72</f>
+        <f ca="1">(Result_NetEmissions_Method2/F72)*G72</f>
         <v>#NAME?</v>
       </c>
       <c r="J72" s="16" t="s">
@@ -6068,11 +6214,11 @@
         <v>0.8</v>
       </c>
       <c r="H77" s="19" t="e">
-        <f>(Result_EmissionsForWholeProductionCycle_Method1/F77)*G77</f>
+        <f ca="1">(Result_EmissionsForWholeProductionCycle_Method1/F77)*G77</f>
         <v>#NAME?</v>
       </c>
       <c r="I77" s="19" t="e">
-        <f>(Result_EmissionsForWholeProductionCycle_Method2/F77)*G77</f>
+        <f ca="1">(Result_EmissionsForWholeProductionCycle_Method2/F77)*G77</f>
         <v>#NAME?</v>
       </c>
       <c r="J77" s="16" t="s">
@@ -6097,11 +6243,11 @@
         <v>0.8</v>
       </c>
       <c r="H78" s="19" t="e">
-        <f>(Result_NetEmissions_Method1/F78)*G78</f>
+        <f ca="1">(Result_NetEmissions_Method1/F78)*G78</f>
         <v>#NAME?</v>
       </c>
       <c r="I78" s="19" t="e">
-        <f>(Result_NetEmissions_Method2/F78)*G78</f>
+        <f ca="1">(Result_NetEmissions_Method2/F78)*G78</f>
         <v>#NAME?</v>
       </c>
       <c r="J78" s="16" t="s">
@@ -6126,11 +6272,11 @@
         <v>0.15</v>
       </c>
       <c r="H79" s="19" t="e">
-        <f>(Result_EmissionsForWholeProductionCycle_Method1/F79)*G79</f>
+        <f ca="1">(Result_EmissionsForWholeProductionCycle_Method1/F79)*G79</f>
         <v>#NAME?</v>
       </c>
       <c r="I79" s="19" t="e">
-        <f>(Result_EmissionsForWholeProductionCycle_Method2/F79)*G79</f>
+        <f ca="1">(Result_EmissionsForWholeProductionCycle_Method2/F79)*G79</f>
         <v>#NAME?</v>
       </c>
       <c r="J79" s="16" t="s">
@@ -6155,11 +6301,11 @@
         <v>0.15</v>
       </c>
       <c r="H80" s="19" t="e">
-        <f>(Result_NetEmissions_Method1/F80)*G80</f>
+        <f ca="1">(Result_NetEmissions_Method1/F80)*G80</f>
         <v>#NAME?</v>
       </c>
       <c r="I80" s="19" t="e">
-        <f>(Result_NetEmissions_Method2/F80)*G80</f>
+        <f ca="1">(Result_NetEmissions_Method2/F80)*G80</f>
         <v>#NAME?</v>
       </c>
       <c r="J80" s="16" t="s">
@@ -6184,11 +6330,11 @@
         <v>0.05</v>
       </c>
       <c r="H81" s="19" t="e">
-        <f>(Result_EmissionsForWholeProductionCycle_Method1/F81)*G81</f>
+        <f ca="1">(Result_EmissionsForWholeProductionCycle_Method1/F81)*G81</f>
         <v>#NAME?</v>
       </c>
       <c r="I81" s="19" t="e">
-        <f>(Result_EmissionsForWholeProductionCycle_Method2/F81)*G81</f>
+        <f ca="1">(Result_EmissionsForWholeProductionCycle_Method2/F81)*G81</f>
         <v>#NAME?</v>
       </c>
       <c r="J81" s="16" t="s">
@@ -6213,11 +6359,11 @@
         <v>0.05</v>
       </c>
       <c r="H82" s="19" t="e">
-        <f>(Result_NetEmissions_Method1/F82)*G82</f>
+        <f ca="1">(Result_NetEmissions_Method1/F82)*G82</f>
         <v>#NAME?</v>
       </c>
       <c r="I82" s="19" t="e">
-        <f>(Result_NetEmissions_Method2/F82)*G82</f>
+        <f ca="1">(Result_NetEmissions_Method2/F82)*G82</f>
         <v>#NAME?</v>
       </c>
       <c r="J82" s="16" t="s">
@@ -6525,9 +6671,9 @@
       <c r="D19" s="23" t="s">
         <v>66</v>
       </c>
-      <c r="E19" s="26" t="str">
-        <f>Common_InputFunctions.Utility_LookupItemFromMinMax(E15,Table_SourceData_RainfallZones[Min rainfall],Table_SourceData_RainfallZones[Max rainfall],Table_SourceData_RainfallZones[Rainfall Zone])</f>
-        <v>High rainfall</v>
+      <c r="E19" s="26" t="e">
+        <f ca="1">Common_InputFunctions.Utility_LookupItemFromMinMax(E15,Table_SourceData_RainfallZones[Min rainfall],Table_SourceData_RainfallZones[Max rainfall],Table_SourceData_RainfallZones[Rainfall Zone])</f>
+        <v>#VALUE!</v>
       </c>
       <c r="G19" s="60"/>
       <c r="N19" s="41"/>
@@ -6540,9 +6686,9 @@
       <c r="D20" s="1" t="s">
         <v>33</v>
       </c>
-      <c r="E20" s="26" t="str">
-        <f>Common_InputFunctions.Utility_GetClimateZone(E14,E15,E17,E13,E18,Table_SourceData_ClimateZones[Min temp],Table_SourceData_ClimateZones[Max temp],Table_SourceData_ClimateZones[Min rainfall],Table_SourceData_ClimateZones[Max rainfall],Table_SourceData_ClimateZones[Min frost days],Table_SourceData_ClimateZones[Max frost days],Table_SourceData_ClimateZones[Min elevation],Table_SourceData_ClimateZones[Max elevation],Table_SourceData_ClimateZones[Min MAP:PET],Table_SourceData_ClimateZones[Max MAP:PET],Table_SourceData_ClimateZones[Climate zone])</f>
-        <v>Warm temperate dry</v>
+      <c r="E20" s="26" t="e">
+        <f ca="1">Common_InputFunctions.Utility_GetClimateZone(E14,E15,E17,E13,E18,Table_SourceData_ClimateZones[Min temp],Table_SourceData_ClimateZones[Max temp],Table_SourceData_ClimateZones[Min rainfall],Table_SourceData_ClimateZones[Max rainfall],Table_SourceData_ClimateZones[Min frost days],Table_SourceData_ClimateZones[Max frost days],Table_SourceData_ClimateZones[Min elevation],Table_SourceData_ClimateZones[Max elevation],Table_SourceData_ClimateZones[Min MAP:PET],Table_SourceData_ClimateZones[Max MAP:PET],Table_SourceData_ClimateZones[Climate zone])</f>
+        <v>#VALUE!</v>
       </c>
       <c r="F20" s="1"/>
       <c r="G20" s="59"/>
@@ -6553,9 +6699,9 @@
       <c r="D21" s="1" t="s">
         <v>116</v>
       </c>
-      <c r="E21" s="26" t="str">
-        <f>Common_InputFunctions.Utility_LookupValueInTable($E$20,Table_SourceData_WetDryZones[Climate zone],Table_SourceData_WetDryZones[Wet or Dry Zone])</f>
-        <v>Dry climate zone</v>
+      <c r="E21" s="26" t="e">
+        <f ca="1">Common_InputFunctions.Utility_LookupValueInTable($E$20,Table_SourceData_WetDryZones[Climate zone],Table_SourceData_WetDryZones[Wet or Dry Zone])</f>
+        <v>#VALUE!</v>
       </c>
       <c r="F21" s="1"/>
       <c r="G21" s="59"/>
@@ -6565,9 +6711,9 @@
       <c r="D22" s="1" t="s">
         <v>70</v>
       </c>
-      <c r="E22" s="26" t="str">
-        <f>Common_InputFunctions.Utility_LookupItemFromMinMax(E14,Table_SourceData_TemperatureZones[Min MAT],Table_SourceData_TemperatureZones[Max MAT],Table_SourceData_TemperatureZones[Temperature Zone])</f>
-        <v>Temperate</v>
+      <c r="E22" s="26" t="e">
+        <f ca="1">Common_InputFunctions.Utility_LookupItemFromMinMax(E14,Table_SourceData_TemperatureZones[Min MAT],Table_SourceData_TemperatureZones[Max MAT],Table_SourceData_TemperatureZones[Temperature Zone])</f>
+        <v>#VALUE!</v>
       </c>
       <c r="G22" s="63"/>
     </row>
@@ -7658,11 +7804,11 @@
 </file>
 
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{FD7772F5-D62F-448B-BE59-D05AA2138B09}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7D8BCD3A-3A3D-4316-924F-18DA0DDB7C4E}">
   <sheetPr>
     <tabColor theme="2" tint="-0.499984740745262"/>
   </sheetPr>
-  <dimension ref="A1:BY259"/>
+  <dimension ref="A1:BY297"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15.75" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="30.7109375" style="32" customWidth="1"/>
@@ -7696,9 +7842,14 @@
         <v>22</v>
       </c>
     </row>
-    <row r="2" spans="1:65" s="3" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="2" spans="1:65" s="3" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A2"/>
+    </row>
     <row r="3" spans="1:65" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A3"/>
+      <c r="A3" s="5" t="str">
+        <f>HYPERLINK("#'Home'!A1", "Home")</f>
+        <v>Home</v>
+      </c>
       <c r="C3" s="33"/>
       <c r="D3" s="33"/>
       <c r="E3" s="33"/>
@@ -7734,7 +7885,9 @@
       <c r="BM5" s="35"/>
     </row>
     <row r="6" spans="1:65" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A6"/>
+      <c r="A6" s="98" t="s">
+        <v>2</v>
+      </c>
       <c r="D6" s="30" t="s">
         <v>23</v>
       </c>
@@ -7746,125 +7899,131 @@
       </c>
     </row>
     <row r="7" spans="1:65" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A7"/>
+      <c r="A7" s="99" t="str">
+        <f>HYPERLINK("#'Constants - Common'!A1", "Constants - Common")</f>
+        <v>Constants - Common</v>
+      </c>
       <c r="D7" s="30" t="str" cm="1">
-        <f t="array" ref="D7">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_AustralianStatesTerritories_Data(),Table_AustralianStates[[#Headers],[State/Territory]],0)</f>
-        <v>New South Wales</v>
+        <f t="array" aca="1" ref="D7" ca="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_AustralianStatesTerritories_Data(),Table_AustralianStates[[#Headers],[State/Territory]],0)</f>
+        <v/>
       </c>
       <c r="E7" s="30" t="str" cm="1">
-        <f t="array" ref="E7">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_AustralianStatesTerritories_Data(),Table_AustralianStates[[#Headers],[State/Territory]],0)</f>
-        <v>New South Wales</v>
+        <f t="array" aca="1" ref="E7" ca="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_AustralianStatesTerritories_Data(),Table_AustralianStates[[#Headers],[State/Territory]],0)</f>
+        <v/>
       </c>
       <c r="F7" s="30" t="str" cm="1">
-        <f t="array" ref="F7">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_AustralianStatesTerritories_Data(),Table_AustralianStates[[#Headers],[State/Territory]],0)</f>
-        <v>NSW</v>
+        <f t="array" aca="1" ref="F7" ca="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_AustralianStatesTerritories_Data(),Table_AustralianStates[[#Headers],[State/Territory]],0)</f>
+        <v/>
       </c>
     </row>
     <row r="8" spans="1:65" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A8"/>
+      <c r="A8" s="5" t="str">
+        <f>HYPERLINK("#'Acknowledgements'!A1", "Acknowledgements")</f>
+        <v>Acknowledgements</v>
+      </c>
       <c r="D8" s="30" t="str" cm="1">
-        <f t="array" ref="D8">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_AustralianStatesTerritories_Data(),Table_AustralianStates[[#Headers],[State/Territory]],0)</f>
-        <v>Australian Capital Territory</v>
+        <f t="array" aca="1" ref="D8" ca="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_AustralianStatesTerritories_Data(),Table_AustralianStates[[#Headers],[State/Territory]],0)</f>
+        <v/>
       </c>
       <c r="E8" s="30" t="str" cm="1">
-        <f t="array" ref="E8">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_AustralianStatesTerritories_Data(),Table_AustralianStates[[#Headers],[State/Territory]],0)</f>
-        <v>ACT</v>
+        <f t="array" aca="1" ref="E8" ca="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_AustralianStatesTerritories_Data(),Table_AustralianStates[[#Headers],[State/Territory]],0)</f>
+        <v/>
       </c>
       <c r="F8" s="30" t="str" cm="1">
-        <f t="array" ref="F8">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_AustralianStatesTerritories_Data(),Table_AustralianStates[[#Headers],[State/Territory]],0)</f>
-        <v>ACT</v>
+        <f t="array" aca="1" ref="F8" ca="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_AustralianStatesTerritories_Data(),Table_AustralianStates[[#Headers],[State/Territory]],0)</f>
+        <v/>
       </c>
     </row>
     <row r="9" spans="1:65" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A9"/>
       <c r="D9" s="30" t="str" cm="1">
-        <f t="array" ref="D9">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_AustralianStatesTerritories_Data(),Table_AustralianStates[[#Headers],[State/Territory]],0)</f>
-        <v>Victoria</v>
+        <f t="array" aca="1" ref="D9" ca="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_AustralianStatesTerritories_Data(),Table_AustralianStates[[#Headers],[State/Territory]],0)</f>
+        <v/>
       </c>
       <c r="E9" s="30" t="str" cm="1">
-        <f t="array" ref="E9">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_AustralianStatesTerritories_Data(),Table_AustralianStates[[#Headers],[State/Territory]],0)</f>
-        <v>Victoria</v>
+        <f t="array" aca="1" ref="E9" ca="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_AustralianStatesTerritories_Data(),Table_AustralianStates[[#Headers],[State/Territory]],0)</f>
+        <v/>
       </c>
       <c r="F9" s="30" t="str" cm="1">
-        <f t="array" ref="F9">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_AustralianStatesTerritories_Data(),Table_AustralianStates[[#Headers],[State/Territory]],0)</f>
-        <v>VIC</v>
+        <f t="array" aca="1" ref="F9" ca="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_AustralianStatesTerritories_Data(),Table_AustralianStates[[#Headers],[State/Territory]],0)</f>
+        <v/>
       </c>
     </row>
     <row r="10" spans="1:65" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A10"/>
       <c r="D10" s="30" t="str" cm="1">
-        <f t="array" ref="D10">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_AustralianStatesTerritories_Data(),Table_AustralianStates[[#Headers],[State/Territory]],0)</f>
-        <v>Queensland</v>
+        <f t="array" aca="1" ref="D10" ca="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_AustralianStatesTerritories_Data(),Table_AustralianStates[[#Headers],[State/Territory]],0)</f>
+        <v/>
       </c>
       <c r="E10" s="30" t="str" cm="1">
-        <f t="array" ref="E10">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_AustralianStatesTerritories_Data(),Table_AustralianStates[[#Headers],[State/Territory]],0)</f>
-        <v>Queensland</v>
+        <f t="array" aca="1" ref="E10" ca="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_AustralianStatesTerritories_Data(),Table_AustralianStates[[#Headers],[State/Territory]],0)</f>
+        <v/>
       </c>
       <c r="F10" s="30" t="str" cm="1">
-        <f t="array" ref="F10">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_AustralianStatesTerritories_Data(),Table_AustralianStates[[#Headers],[State/Territory]],0)</f>
-        <v>QLD</v>
+        <f t="array" aca="1" ref="F10" ca="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_AustralianStatesTerritories_Data(),Table_AustralianStates[[#Headers],[State/Territory]],0)</f>
+        <v/>
       </c>
     </row>
     <row r="11" spans="1:65" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A11"/>
       <c r="D11" s="30" t="str" cm="1">
-        <f t="array" ref="D11">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_AustralianStatesTerritories_Data(),Table_AustralianStates[[#Headers],[State/Territory]],0)</f>
-        <v>South Australia</v>
+        <f t="array" aca="1" ref="D11" ca="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_AustralianStatesTerritories_Data(),Table_AustralianStates[[#Headers],[State/Territory]],0)</f>
+        <v/>
       </c>
       <c r="E11" s="30" t="str" cm="1">
-        <f t="array" ref="E11">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_AustralianStatesTerritories_Data(),Table_AustralianStates[[#Headers],[State/Territory]],0)</f>
-        <v>South Australia</v>
+        <f t="array" aca="1" ref="E11" ca="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_AustralianStatesTerritories_Data(),Table_AustralianStates[[#Headers],[State/Territory]],0)</f>
+        <v/>
       </c>
       <c r="F11" s="30" t="str" cm="1">
-        <f t="array" ref="F11">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_AustralianStatesTerritories_Data(),Table_AustralianStates[[#Headers],[State/Territory]],0)</f>
-        <v>SA</v>
+        <f t="array" aca="1" ref="F11" ca="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_AustralianStatesTerritories_Data(),Table_AustralianStates[[#Headers],[State/Territory]],0)</f>
+        <v/>
       </c>
       <c r="BM11" s="35"/>
     </row>
     <row r="12" spans="1:65" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A12"/>
       <c r="D12" s="30" t="str" cm="1">
-        <f t="array" ref="D12">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_AustralianStatesTerritories_Data(),Table_AustralianStates[[#Headers],[State/Territory]],0)</f>
-        <v>Western Australia</v>
+        <f t="array" aca="1" ref="D12" ca="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_AustralianStatesTerritories_Data(),Table_AustralianStates[[#Headers],[State/Territory]],0)</f>
+        <v/>
       </c>
       <c r="E12" s="30" t="str" cm="1">
-        <f t="array" ref="E12">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_AustralianStatesTerritories_Data(),Table_AustralianStates[[#Headers],[State/Territory]],0)</f>
-        <v>Western Australia</v>
+        <f t="array" aca="1" ref="E12" ca="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_AustralianStatesTerritories_Data(),Table_AustralianStates[[#Headers],[State/Territory]],0)</f>
+        <v/>
       </c>
       <c r="F12" s="30" t="str" cm="1">
-        <f t="array" ref="F12">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_AustralianStatesTerritories_Data(),Table_AustralianStates[[#Headers],[State/Territory]],0)</f>
-        <v>WA</v>
+        <f t="array" aca="1" ref="F12" ca="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_AustralianStatesTerritories_Data(),Table_AustralianStates[[#Headers],[State/Territory]],0)</f>
+        <v/>
       </c>
       <c r="BM12" s="35"/>
     </row>
     <row r="13" spans="1:65" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A13"/>
       <c r="D13" s="30" t="str" cm="1">
-        <f t="array" ref="D13">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_AustralianStatesTerritories_Data(),Table_AustralianStates[[#Headers],[State/Territory]],0)</f>
-        <v>Tasmania</v>
+        <f t="array" aca="1" ref="D13" ca="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_AustralianStatesTerritories_Data(),Table_AustralianStates[[#Headers],[State/Territory]],0)</f>
+        <v/>
       </c>
       <c r="E13" s="30" t="str" cm="1">
-        <f t="array" ref="E13">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_AustralianStatesTerritories_Data(),Table_AustralianStates[[#Headers],[State/Territory]],0)</f>
-        <v>Tasmania</v>
+        <f t="array" aca="1" ref="E13" ca="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_AustralianStatesTerritories_Data(),Table_AustralianStates[[#Headers],[State/Territory]],0)</f>
+        <v/>
       </c>
       <c r="F13" s="30" t="str" cm="1">
-        <f t="array" ref="F13">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_AustralianStatesTerritories_Data(),Table_AustralianStates[[#Headers],[State/Territory]],0)</f>
-        <v>TAS</v>
+        <f t="array" aca="1" ref="F13" ca="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_AustralianStatesTerritories_Data(),Table_AustralianStates[[#Headers],[State/Territory]],0)</f>
+        <v/>
       </c>
     </row>
     <row r="14" spans="1:65" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A14"/>
       <c r="D14" s="30" t="str" cm="1">
-        <f t="array" ref="D14">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_AustralianStatesTerritories_Data(),Table_AustralianStates[[#Headers],[State/Territory]],0)</f>
-        <v>Northern Territory</v>
+        <f t="array" aca="1" ref="D14" ca="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_AustralianStatesTerritories_Data(),Table_AustralianStates[[#Headers],[State/Territory]],0)</f>
+        <v/>
       </c>
       <c r="E14" s="30" t="str" cm="1">
-        <f t="array" ref="E14">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_AustralianStatesTerritories_Data(),Table_AustralianStates[[#Headers],[State/Territory]],0)</f>
-        <v>Northern Territory</v>
+        <f t="array" aca="1" ref="E14" ca="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_AustralianStatesTerritories_Data(),Table_AustralianStates[[#Headers],[State/Territory]],0)</f>
+        <v/>
       </c>
       <c r="F14" s="30" t="str" cm="1">
-        <f t="array" ref="F14">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_AustralianStatesTerritories_Data(),Table_AustralianStates[[#Headers],[State/Territory]],0)</f>
-        <v>NT</v>
+        <f t="array" aca="1" ref="F14" ca="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_AustralianStatesTerritories_Data(),Table_AustralianStates[[#Headers],[State/Territory]],0)</f>
+        <v/>
       </c>
     </row>
     <row r="15" spans="1:65" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
@@ -7899,71 +8058,71 @@
     <row r="21" spans="1:4" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A21"/>
       <c r="D21" s="30" t="str" cm="1">
-        <f t="array" ref="D21">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_WASA4Areas_Data(), Table_WASA4Areas[[#Headers],[SA 4 Name]], 0)</f>
-        <v>Bunbury</v>
+        <f t="array" aca="1" ref="D21" ca="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_WASA4Areas_Data(), Table_WASA4Areas[[#Headers],[SA 4 Name]], 0)</f>
+        <v/>
       </c>
     </row>
     <row r="22" spans="1:4" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A22"/>
       <c r="D22" s="30" t="str" cm="1">
-        <f t="array" ref="D22">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_WASA4Areas_Data(), Table_WASA4Areas[[#Headers],[SA 4 Name]], 0)</f>
-        <v>Mandurah</v>
+        <f t="array" aca="1" ref="D22" ca="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_WASA4Areas_Data(), Table_WASA4Areas[[#Headers],[SA 4 Name]], 0)</f>
+        <v/>
       </c>
     </row>
     <row r="23" spans="1:4" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A23"/>
       <c r="D23" s="30" t="str" cm="1">
-        <f t="array" ref="D23">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_WASA4Areas_Data(), Table_WASA4Areas[[#Headers],[SA 4 Name]], 0)</f>
-        <v>Perth - Inner</v>
+        <f t="array" aca="1" ref="D23" ca="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_WASA4Areas_Data(), Table_WASA4Areas[[#Headers],[SA 4 Name]], 0)</f>
+        <v/>
       </c>
     </row>
     <row r="24" spans="1:4" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A24"/>
       <c r="D24" s="30" t="str" cm="1">
-        <f t="array" ref="D24">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_WASA4Areas_Data(), Table_WASA4Areas[[#Headers],[SA 4 Name]], 0)</f>
-        <v>Perth - North East</v>
+        <f t="array" aca="1" ref="D24" ca="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_WASA4Areas_Data(), Table_WASA4Areas[[#Headers],[SA 4 Name]], 0)</f>
+        <v/>
       </c>
     </row>
     <row r="25" spans="1:4" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A25"/>
       <c r="D25" s="30" t="str" cm="1">
-        <f t="array" ref="D25">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_WASA4Areas_Data(), Table_WASA4Areas[[#Headers],[SA 4 Name]], 0)</f>
-        <v>Perth - North West</v>
+        <f t="array" aca="1" ref="D25" ca="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_WASA4Areas_Data(), Table_WASA4Areas[[#Headers],[SA 4 Name]], 0)</f>
+        <v/>
       </c>
     </row>
     <row r="26" spans="1:4" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A26"/>
       <c r="D26" s="30" t="str" cm="1">
-        <f t="array" ref="D26">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_WASA4Areas_Data(), Table_WASA4Areas[[#Headers],[SA 4 Name]], 0)</f>
-        <v>Perth - South East</v>
+        <f t="array" aca="1" ref="D26" ca="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_WASA4Areas_Data(), Table_WASA4Areas[[#Headers],[SA 4 Name]], 0)</f>
+        <v/>
       </c>
     </row>
     <row r="27" spans="1:4" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A27"/>
       <c r="D27" s="30" t="str" cm="1">
-        <f t="array" ref="D27">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_WASA4Areas_Data(), Table_WASA4Areas[[#Headers],[SA 4 Name]], 0)</f>
-        <v>Perth - South West</v>
+        <f t="array" aca="1" ref="D27" ca="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_WASA4Areas_Data(), Table_WASA4Areas[[#Headers],[SA 4 Name]], 0)</f>
+        <v/>
       </c>
     </row>
     <row r="28" spans="1:4" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A28"/>
       <c r="D28" s="30" t="str" cm="1">
-        <f t="array" ref="D28">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_WASA4Areas_Data(), Table_WASA4Areas[[#Headers],[SA 4 Name]], 0)</f>
-        <v>Western Australia - Wheat Belt</v>
+        <f t="array" aca="1" ref="D28" ca="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_WASA4Areas_Data(), Table_WASA4Areas[[#Headers],[SA 4 Name]], 0)</f>
+        <v/>
       </c>
     </row>
     <row r="29" spans="1:4" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A29"/>
       <c r="D29" s="30" t="str" cm="1">
-        <f t="array" ref="D29">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_WASA4Areas_Data(), Table_WASA4Areas[[#Headers],[SA 4 Name]], 0)</f>
-        <v>Western Australia - Outback (North)</v>
+        <f t="array" aca="1" ref="D29" ca="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_WASA4Areas_Data(), Table_WASA4Areas[[#Headers],[SA 4 Name]], 0)</f>
+        <v/>
       </c>
     </row>
     <row r="30" spans="1:4" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A30"/>
       <c r="D30" s="30" t="str" cm="1">
-        <f t="array" ref="D30">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_WASA4Areas_Data(), Table_WASA4Areas[[#Headers],[SA 4 Name]], 0)</f>
-        <v>Western Australia - Outback (South)</v>
+        <f t="array" aca="1" ref="D30" ca="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_WASA4Areas_Data(), Table_WASA4Areas[[#Headers],[SA 4 Name]], 0)</f>
+        <v/>
       </c>
     </row>
     <row r="31" spans="1:4" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
@@ -8001,92 +8160,99 @@
     <row r="37" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A37"/>
       <c r="D37" s="30" t="str" cm="1">
-        <f t="array" ref="D37">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_GWP_Data(), Table_GWPData[[#Headers],[Gas]], 0)</f>
-        <v>CO2</v>
-      </c>
-      <c r="E37" s="30" cm="1">
-        <f t="array" ref="E37">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_GWP_Data(), Table_GWPData[[#Headers],[Gas]], 0)</f>
-        <v>1</v>
+        <f t="array" aca="1" ref="D37" ca="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_GWP_Data(), Table_GWPData[[#Headers],[Gas]], 0)</f>
+        <v/>
+      </c>
+      <c r="E37" s="30" t="str" cm="1">
+        <f t="array" aca="1" ref="E37" ca="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_GWP_Data(), Table_GWPData[[#Headers],[Gas]], 0)</f>
+        <v/>
       </c>
     </row>
     <row r="38" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A38"/>
       <c r="D38" s="30" t="str" cm="1">
-        <f t="array" ref="D38">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_GWP_Data(), Table_GWPData[[#Headers],[Gas]], 0)</f>
-        <v>CH4</v>
-      </c>
-      <c r="E38" s="30" cm="1">
-        <f t="array" ref="E38">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_GWP_Data(), Table_GWPData[[#Headers],[Gas]], 0)</f>
-        <v>28</v>
+        <f t="array" aca="1" ref="D38" ca="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_GWP_Data(), Table_GWPData[[#Headers],[Gas]], 0)</f>
+        <v/>
+      </c>
+      <c r="E38" s="30" t="str" cm="1">
+        <f t="array" aca="1" ref="E38" ca="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_GWP_Data(), Table_GWPData[[#Headers],[Gas]], 0)</f>
+        <v/>
       </c>
     </row>
     <row r="39" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A39"/>
       <c r="D39" s="30" t="str" cm="1">
-        <f t="array" ref="D39">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_GWP_Data(), Table_GWPData[[#Headers],[Gas]], 0)</f>
-        <v>N2O</v>
-      </c>
-      <c r="E39" s="30" cm="1">
-        <f t="array" ref="E39">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_GWP_Data(), Table_GWPData[[#Headers],[Gas]], 0)</f>
-        <v>265</v>
+        <f t="array" aca="1" ref="D39" ca="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_GWP_Data(), Table_GWPData[[#Headers],[Gas]], 0)</f>
+        <v/>
+      </c>
+      <c r="E39" s="30" t="str" cm="1">
+        <f t="array" aca="1" ref="E39" ca="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_GWP_Data(), Table_GWPData[[#Headers],[Gas]], 0)</f>
+        <v/>
       </c>
     </row>
     <row r="40" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A40"/>
       <c r="D40" s="30" t="str" cm="1">
-        <f t="array" ref="D40">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_GWP_Data(), Table_GWPData[[#Headers],[Gas]], 0)</f>
-        <v>CF4</v>
-      </c>
-      <c r="E40" s="30" cm="1">
-        <f t="array" ref="E40">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_GWP_Data(), Table_GWPData[[#Headers],[Gas]], 0)</f>
-        <v>6630</v>
+        <f t="array" aca="1" ref="D40" ca="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_GWP_Data(), Table_GWPData[[#Headers],[Gas]], 0)</f>
+        <v/>
+      </c>
+      <c r="E40" s="30" t="str" cm="1">
+        <f t="array" aca="1" ref="E40" ca="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_GWP_Data(), Table_GWPData[[#Headers],[Gas]], 0)</f>
+        <v/>
       </c>
     </row>
     <row r="41" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A41"/>
       <c r="D41" s="30" t="str" cm="1">
-        <f t="array" ref="D41">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_GWP_Data(), Table_GWPData[[#Headers],[Gas]], 0)</f>
-        <v>C2F6</v>
-      </c>
-      <c r="E41" s="30" cm="1">
-        <f t="array" ref="E41">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_GWP_Data(), Table_GWPData[[#Headers],[Gas]], 0)</f>
-        <v>12200</v>
+        <f t="array" aca="1" ref="D41" ca="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_GWP_Data(), Table_GWPData[[#Headers],[Gas]], 0)</f>
+        <v/>
+      </c>
+      <c r="E41" s="30" t="str" cm="1">
+        <f t="array" aca="1" ref="E41" ca="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_GWP_Data(), Table_GWPData[[#Headers],[Gas]], 0)</f>
+        <v/>
       </c>
     </row>
     <row r="42" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A42"/>
       <c r="D42" s="30" t="str" cm="1">
-        <f t="array" ref="D42">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_GWP_Data(), Table_GWPData[[#Headers],[Gas]], 0)</f>
-        <v>SF6</v>
-      </c>
-      <c r="E42" s="30" cm="1">
-        <f t="array" ref="E42">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_GWP_Data(), Table_GWPData[[#Headers],[Gas]], 0)</f>
-        <v>22800</v>
+        <f t="array" aca="1" ref="D42" ca="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_GWP_Data(), Table_GWPData[[#Headers],[Gas]], 0)</f>
+        <v/>
+      </c>
+      <c r="E42" s="30" t="str" cm="1">
+        <f t="array" aca="1" ref="E42" ca="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_GWP_Data(), Table_GWPData[[#Headers],[Gas]], 0)</f>
+        <v/>
       </c>
     </row>
     <row r="43" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A43"/>
       <c r="D43" s="30" t="str" cm="1">
-        <f t="array" ref="D43">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_GWP_Data(), Table_GWPData[[#Headers],[Gas]], 0)</f>
-        <v>NF3</v>
-      </c>
-      <c r="E43" s="30" cm="1">
-        <f t="array" ref="E43">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_GWP_Data(), Table_GWPData[[#Headers],[Gas]], 0)</f>
-        <v>17200</v>
-      </c>
-    </row>
-    <row r="44" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
+        <f t="array" aca="1" ref="D43" ca="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_GWP_Data(), Table_GWPData[[#Headers],[Gas]], 0)</f>
+        <v/>
+      </c>
+      <c r="E43" s="30" t="str" cm="1">
+        <f t="array" aca="1" ref="E43" ca="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_GWP_Data(), Table_GWPData[[#Headers],[Gas]], 0)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="44" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A44"/>
+    </row>
     <row r="45" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A45"/>
       <c r="D45" s="2" t="str" cm="1">
         <f t="array" ref="D45">Common_SourceData.Common_SourceData_ConvertGasElementalToMolecular_Title()</f>
         <v>Factor to convert elemental mass of gas to molecular mass</v>
       </c>
     </row>
     <row r="46" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A46"/>
       <c r="D46" s="28" t="str" cm="1">
         <f t="array" ref="D46">Common_SourceData.Common_SourceData_ConvertGasElementalToMolecular_Source()</f>
         <v>XXXXXXX</v>
       </c>
     </row>
     <row r="47" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A47"/>
       <c r="D47" s="30" t="s">
         <v>27</v>
       </c>
@@ -8104,191 +8270,210 @@
       </c>
     </row>
     <row r="48" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A48"/>
       <c r="D48" s="30" t="str" cm="1">
-        <f t="array" ref="D48">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ConvertGasElementalToMolecular_Data(),Table_GasToMolecularConversionFactor[[#Headers],[Gas]], 0)</f>
-        <v>CO2</v>
+        <f t="array" aca="1" ref="D48" ca="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ConvertGasElementalToMolecular_Data(),Table_GasToMolecularConversionFactor[[#Headers],[Gas]], 0)</f>
+        <v/>
       </c>
       <c r="E48" s="30" t="str" cm="1">
-        <f t="array" ref="E48">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ConvertGasElementalToMolecular_Data(),Table_GasToMolecularConversionFactor[[#Headers],[Gas]], 0)</f>
-        <v>44/12</v>
-      </c>
-      <c r="F48" s="30" cm="1">
-        <f t="array" ref="F48">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ConvertGasElementalToMolecular_Data(),Table_GasToMolecularConversionFactor[[#Headers],[Gas]], 0)</f>
-        <v>44</v>
-      </c>
-      <c r="G48" s="30" cm="1">
-        <f t="array" ref="G48">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ConvertGasElementalToMolecular_Data(),Table_GasToMolecularConversionFactor[[#Headers],[Gas]], 0)</f>
-        <v>12</v>
-      </c>
-      <c r="H48" s="30">
-        <f>Table_GasToMolecularConversionFactor[[#This Row],[Conversion factor 1]]/Table_GasToMolecularConversionFactor[[#This Row],[Conversion factor 2]]</f>
-        <v>3.6666666666666665</v>
-      </c>
-    </row>
-    <row r="49" spans="4:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+        <f t="array" aca="1" ref="E48" ca="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ConvertGasElementalToMolecular_Data(),Table_GasToMolecularConversionFactor[[#Headers],[Gas]], 0)</f>
+        <v/>
+      </c>
+      <c r="F48" s="30" t="str" cm="1">
+        <f t="array" aca="1" ref="F48" ca="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ConvertGasElementalToMolecular_Data(),Table_GasToMolecularConversionFactor[[#Headers],[Gas]], 0)</f>
+        <v/>
+      </c>
+      <c r="G48" s="30" t="str" cm="1">
+        <f t="array" aca="1" ref="G48" ca="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ConvertGasElementalToMolecular_Data(),Table_GasToMolecularConversionFactor[[#Headers],[Gas]], 0)</f>
+        <v/>
+      </c>
+      <c r="H48" s="30" t="e">
+        <f ca="1">Table_GasToMolecularConversionFactor[[#This Row],[Conversion factor 1]]/Table_GasToMolecularConversionFactor[[#This Row],[Conversion factor 2]]</f>
+        <v>#VALUE!</v>
+      </c>
+    </row>
+    <row r="49" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A49"/>
       <c r="D49" s="30" t="str" cm="1">
-        <f t="array" ref="D49">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ConvertGasElementalToMolecular_Data(),Table_GasToMolecularConversionFactor[[#Headers],[Gas]], 0)</f>
-        <v>CH4</v>
+        <f t="array" aca="1" ref="D49" ca="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ConvertGasElementalToMolecular_Data(),Table_GasToMolecularConversionFactor[[#Headers],[Gas]], 0)</f>
+        <v/>
       </c>
       <c r="E49" s="30" t="str" cm="1">
-        <f t="array" ref="E49">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ConvertGasElementalToMolecular_Data(),Table_GasToMolecularConversionFactor[[#Headers],[Gas]], 0)</f>
-        <v>16/12</v>
-      </c>
-      <c r="F49" s="30" cm="1">
-        <f t="array" ref="F49">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ConvertGasElementalToMolecular_Data(),Table_GasToMolecularConversionFactor[[#Headers],[Gas]], 0)</f>
-        <v>16</v>
-      </c>
-      <c r="G49" s="30" cm="1">
-        <f t="array" ref="G49">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ConvertGasElementalToMolecular_Data(),Table_GasToMolecularConversionFactor[[#Headers],[Gas]], 0)</f>
-        <v>12</v>
-      </c>
-      <c r="H49" s="30">
-        <f>Table_GasToMolecularConversionFactor[[#This Row],[Conversion factor 1]]/Table_GasToMolecularConversionFactor[[#This Row],[Conversion factor 2]]</f>
-        <v>1.3333333333333333</v>
-      </c>
-    </row>
-    <row r="50" spans="4:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+        <f t="array" aca="1" ref="E49" ca="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ConvertGasElementalToMolecular_Data(),Table_GasToMolecularConversionFactor[[#Headers],[Gas]], 0)</f>
+        <v/>
+      </c>
+      <c r="F49" s="30" t="str" cm="1">
+        <f t="array" aca="1" ref="F49" ca="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ConvertGasElementalToMolecular_Data(),Table_GasToMolecularConversionFactor[[#Headers],[Gas]], 0)</f>
+        <v/>
+      </c>
+      <c r="G49" s="30" t="str" cm="1">
+        <f t="array" aca="1" ref="G49" ca="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ConvertGasElementalToMolecular_Data(),Table_GasToMolecularConversionFactor[[#Headers],[Gas]], 0)</f>
+        <v/>
+      </c>
+      <c r="H49" s="30" t="e">
+        <f ca="1">Table_GasToMolecularConversionFactor[[#This Row],[Conversion factor 1]]/Table_GasToMolecularConversionFactor[[#This Row],[Conversion factor 2]]</f>
+        <v>#VALUE!</v>
+      </c>
+    </row>
+    <row r="50" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A50"/>
       <c r="D50" s="30" t="str" cm="1">
-        <f t="array" ref="D50">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ConvertGasElementalToMolecular_Data(),Table_GasToMolecularConversionFactor[[#Headers],[Gas]], 0)</f>
-        <v>N2O</v>
+        <f t="array" aca="1" ref="D50" ca="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ConvertGasElementalToMolecular_Data(),Table_GasToMolecularConversionFactor[[#Headers],[Gas]], 0)</f>
+        <v/>
       </c>
       <c r="E50" s="30" t="str" cm="1">
-        <f t="array" ref="E50">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ConvertGasElementalToMolecular_Data(),Table_GasToMolecularConversionFactor[[#Headers],[Gas]], 0)</f>
-        <v>44/28</v>
-      </c>
-      <c r="F50" s="30" cm="1">
-        <f t="array" ref="F50">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ConvertGasElementalToMolecular_Data(),Table_GasToMolecularConversionFactor[[#Headers],[Gas]], 0)</f>
-        <v>44</v>
-      </c>
-      <c r="G50" s="30" cm="1">
-        <f t="array" ref="G50">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ConvertGasElementalToMolecular_Data(),Table_GasToMolecularConversionFactor[[#Headers],[Gas]], 0)</f>
-        <v>28</v>
-      </c>
-      <c r="H50" s="30">
-        <f>Table_GasToMolecularConversionFactor[[#This Row],[Conversion factor 1]]/Table_GasToMolecularConversionFactor[[#This Row],[Conversion factor 2]]</f>
-        <v>1.5714285714285714</v>
-      </c>
-    </row>
-    <row r="51" spans="4:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+        <f t="array" aca="1" ref="E50" ca="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ConvertGasElementalToMolecular_Data(),Table_GasToMolecularConversionFactor[[#Headers],[Gas]], 0)</f>
+        <v/>
+      </c>
+      <c r="F50" s="30" t="str" cm="1">
+        <f t="array" aca="1" ref="F50" ca="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ConvertGasElementalToMolecular_Data(),Table_GasToMolecularConversionFactor[[#Headers],[Gas]], 0)</f>
+        <v/>
+      </c>
+      <c r="G50" s="30" t="str" cm="1">
+        <f t="array" aca="1" ref="G50" ca="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ConvertGasElementalToMolecular_Data(),Table_GasToMolecularConversionFactor[[#Headers],[Gas]], 0)</f>
+        <v/>
+      </c>
+      <c r="H50" s="30" t="e">
+        <f ca="1">Table_GasToMolecularConversionFactor[[#This Row],[Conversion factor 1]]/Table_GasToMolecularConversionFactor[[#This Row],[Conversion factor 2]]</f>
+        <v>#VALUE!</v>
+      </c>
+    </row>
+    <row r="51" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A51"/>
       <c r="D51" s="30" t="str" cm="1">
-        <f t="array" ref="D51">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ConvertGasElementalToMolecular_Data(),Table_GasToMolecularConversionFactor[[#Headers],[Gas]], 0)</f>
-        <v>Nox</v>
+        <f t="array" aca="1" ref="D51" ca="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ConvertGasElementalToMolecular_Data(),Table_GasToMolecularConversionFactor[[#Headers],[Gas]], 0)</f>
+        <v/>
       </c>
       <c r="E51" s="30" t="str" cm="1">
-        <f t="array" ref="E51">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ConvertGasElementalToMolecular_Data(),Table_GasToMolecularConversionFactor[[#Headers],[Gas]], 0)</f>
-        <v>46/14</v>
-      </c>
-      <c r="F51" s="30" cm="1">
-        <f t="array" ref="F51">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ConvertGasElementalToMolecular_Data(),Table_GasToMolecularConversionFactor[[#Headers],[Gas]], 0)</f>
-        <v>46</v>
-      </c>
-      <c r="G51" s="30" cm="1">
-        <f t="array" ref="G51">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ConvertGasElementalToMolecular_Data(),Table_GasToMolecularConversionFactor[[#Headers],[Gas]], 0)</f>
-        <v>14</v>
-      </c>
-      <c r="H51" s="30">
-        <f>Table_GasToMolecularConversionFactor[[#This Row],[Conversion factor 1]]/Table_GasToMolecularConversionFactor[[#This Row],[Conversion factor 2]]</f>
-        <v>3.2857142857142856</v>
-      </c>
-    </row>
-    <row r="52" spans="4:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+        <f t="array" aca="1" ref="E51" ca="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ConvertGasElementalToMolecular_Data(),Table_GasToMolecularConversionFactor[[#Headers],[Gas]], 0)</f>
+        <v/>
+      </c>
+      <c r="F51" s="30" t="str" cm="1">
+        <f t="array" aca="1" ref="F51" ca="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ConvertGasElementalToMolecular_Data(),Table_GasToMolecularConversionFactor[[#Headers],[Gas]], 0)</f>
+        <v/>
+      </c>
+      <c r="G51" s="30" t="str" cm="1">
+        <f t="array" aca="1" ref="G51" ca="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ConvertGasElementalToMolecular_Data(),Table_GasToMolecularConversionFactor[[#Headers],[Gas]], 0)</f>
+        <v/>
+      </c>
+      <c r="H51" s="30" t="e">
+        <f ca="1">Table_GasToMolecularConversionFactor[[#This Row],[Conversion factor 1]]/Table_GasToMolecularConversionFactor[[#This Row],[Conversion factor 2]]</f>
+        <v>#VALUE!</v>
+      </c>
+    </row>
+    <row r="52" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A52"/>
       <c r="D52" s="30" t="str" cm="1">
-        <f t="array" ref="D52">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ConvertGasElementalToMolecular_Data(),Table_GasToMolecularConversionFactor[[#Headers],[Gas]], 0)</f>
-        <v>CO</v>
+        <f t="array" aca="1" ref="D52" ca="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ConvertGasElementalToMolecular_Data(),Table_GasToMolecularConversionFactor[[#Headers],[Gas]], 0)</f>
+        <v/>
       </c>
       <c r="E52" s="30" t="str" cm="1">
-        <f t="array" ref="E52">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ConvertGasElementalToMolecular_Data(),Table_GasToMolecularConversionFactor[[#Headers],[Gas]], 0)</f>
-        <v>28/12</v>
-      </c>
-      <c r="F52" s="30" cm="1">
-        <f t="array" ref="F52">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ConvertGasElementalToMolecular_Data(),Table_GasToMolecularConversionFactor[[#Headers],[Gas]], 0)</f>
-        <v>28</v>
-      </c>
-      <c r="G52" s="30" cm="1">
-        <f t="array" ref="G52">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ConvertGasElementalToMolecular_Data(),Table_GasToMolecularConversionFactor[[#Headers],[Gas]], 0)</f>
-        <v>12</v>
-      </c>
-      <c r="H52" s="30">
-        <f>Table_GasToMolecularConversionFactor[[#This Row],[Conversion factor 1]]/Table_GasToMolecularConversionFactor[[#This Row],[Conversion factor 2]]</f>
-        <v>2.3333333333333335</v>
-      </c>
-    </row>
-    <row r="53" spans="4:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+        <f t="array" aca="1" ref="E52" ca="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ConvertGasElementalToMolecular_Data(),Table_GasToMolecularConversionFactor[[#Headers],[Gas]], 0)</f>
+        <v/>
+      </c>
+      <c r="F52" s="30" t="str" cm="1">
+        <f t="array" aca="1" ref="F52" ca="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ConvertGasElementalToMolecular_Data(),Table_GasToMolecularConversionFactor[[#Headers],[Gas]], 0)</f>
+        <v/>
+      </c>
+      <c r="G52" s="30" t="str" cm="1">
+        <f t="array" aca="1" ref="G52" ca="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ConvertGasElementalToMolecular_Data(),Table_GasToMolecularConversionFactor[[#Headers],[Gas]], 0)</f>
+        <v/>
+      </c>
+      <c r="H52" s="30" t="e">
+        <f ca="1">Table_GasToMolecularConversionFactor[[#This Row],[Conversion factor 1]]/Table_GasToMolecularConversionFactor[[#This Row],[Conversion factor 2]]</f>
+        <v>#VALUE!</v>
+      </c>
+    </row>
+    <row r="53" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A53"/>
       <c r="D53" s="30" t="str" cm="1">
-        <f t="array" ref="D53">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ConvertGasElementalToMolecular_Data(),Table_GasToMolecularConversionFactor[[#Headers],[Gas]], 0)</f>
-        <v>CO2 Lime</v>
+        <f t="array" aca="1" ref="D53" ca="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ConvertGasElementalToMolecular_Data(),Table_GasToMolecularConversionFactor[[#Headers],[Gas]], 0)</f>
+        <v/>
       </c>
       <c r="E53" s="30" t="str" cm="1">
-        <f t="array" ref="E53">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ConvertGasElementalToMolecular_Data(),Table_GasToMolecularConversionFactor[[#Headers],[Gas]], 0)</f>
-        <v>44/12</v>
-      </c>
-      <c r="F53" s="30" cm="1">
-        <f t="array" ref="F53">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ConvertGasElementalToMolecular_Data(),Table_GasToMolecularConversionFactor[[#Headers],[Gas]], 0)</f>
-        <v>44</v>
-      </c>
-      <c r="G53" s="30" cm="1">
-        <f t="array" ref="G53">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ConvertGasElementalToMolecular_Data(),Table_GasToMolecularConversionFactor[[#Headers],[Gas]], 0)</f>
-        <v>12</v>
-      </c>
-      <c r="H53" s="30">
-        <f>Table_GasToMolecularConversionFactor[[#This Row],[Conversion factor 1]]/Table_GasToMolecularConversionFactor[[#This Row],[Conversion factor 2]]</f>
-        <v>3.6666666666666665</v>
-      </c>
-    </row>
-    <row r="54" spans="4:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+        <f t="array" aca="1" ref="E53" ca="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ConvertGasElementalToMolecular_Data(),Table_GasToMolecularConversionFactor[[#Headers],[Gas]], 0)</f>
+        <v/>
+      </c>
+      <c r="F53" s="30" t="str" cm="1">
+        <f t="array" aca="1" ref="F53" ca="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ConvertGasElementalToMolecular_Data(),Table_GasToMolecularConversionFactor[[#Headers],[Gas]], 0)</f>
+        <v/>
+      </c>
+      <c r="G53" s="30" t="str" cm="1">
+        <f t="array" aca="1" ref="G53" ca="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ConvertGasElementalToMolecular_Data(),Table_GasToMolecularConversionFactor[[#Headers],[Gas]], 0)</f>
+        <v/>
+      </c>
+      <c r="H53" s="30" t="e">
+        <f ca="1">Table_GasToMolecularConversionFactor[[#This Row],[Conversion factor 1]]/Table_GasToMolecularConversionFactor[[#This Row],[Conversion factor 2]]</f>
+        <v>#VALUE!</v>
+      </c>
+    </row>
+    <row r="54" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A54"/>
       <c r="D54" s="30" t="str" cm="1">
-        <f t="array" ref="D54">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ConvertGasElementalToMolecular_Data(),Table_GasToMolecularConversionFactor[[#Headers],[Gas]], 0)</f>
-        <v>NMVOC</v>
+        <f t="array" aca="1" ref="D54" ca="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ConvertGasElementalToMolecular_Data(),Table_GasToMolecularConversionFactor[[#Headers],[Gas]], 0)</f>
+        <v/>
       </c>
       <c r="E54" s="30" t="str" cm="1">
-        <f t="array" ref="E54">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ConvertGasElementalToMolecular_Data(),Table_GasToMolecularConversionFactor[[#Headers],[Gas]], 0)</f>
-        <v>14/12</v>
-      </c>
-      <c r="F54" s="30" cm="1">
-        <f t="array" ref="F54">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ConvertGasElementalToMolecular_Data(),Table_GasToMolecularConversionFactor[[#Headers],[Gas]], 0)</f>
-        <v>14</v>
-      </c>
-      <c r="G54" s="30" cm="1">
-        <f t="array" ref="G54">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ConvertGasElementalToMolecular_Data(),Table_GasToMolecularConversionFactor[[#Headers],[Gas]], 0)</f>
-        <v>12</v>
-      </c>
-      <c r="H54" s="30">
-        <f>Table_GasToMolecularConversionFactor[[#This Row],[Conversion factor 1]]/Table_GasToMolecularConversionFactor[[#This Row],[Conversion factor 2]]</f>
-        <v>1.1666666666666667</v>
-      </c>
-    </row>
-    <row r="55" spans="4:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="56" spans="4:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="57" spans="4:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+        <f t="array" aca="1" ref="E54" ca="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ConvertGasElementalToMolecular_Data(),Table_GasToMolecularConversionFactor[[#Headers],[Gas]], 0)</f>
+        <v/>
+      </c>
+      <c r="F54" s="30" t="str" cm="1">
+        <f t="array" aca="1" ref="F54" ca="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ConvertGasElementalToMolecular_Data(),Table_GasToMolecularConversionFactor[[#Headers],[Gas]], 0)</f>
+        <v/>
+      </c>
+      <c r="G54" s="30" t="str" cm="1">
+        <f t="array" aca="1" ref="G54" ca="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ConvertGasElementalToMolecular_Data(),Table_GasToMolecularConversionFactor[[#Headers],[Gas]], 0)</f>
+        <v/>
+      </c>
+      <c r="H54" s="30" t="e">
+        <f ca="1">Table_GasToMolecularConversionFactor[[#This Row],[Conversion factor 1]]/Table_GasToMolecularConversionFactor[[#This Row],[Conversion factor 2]]</f>
+        <v>#VALUE!</v>
+      </c>
+    </row>
+    <row r="55" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A55"/>
+    </row>
+    <row r="56" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A56"/>
+    </row>
+    <row r="57" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A57"/>
       <c r="D57" s="2" t="str" cm="1">
         <f t="array" ref="D57">Common_SourceData.Common_SourceData_WetAndDryZones_Title()</f>
         <v>VEERG Australian wet and dry zones</v>
       </c>
     </row>
-    <row r="58" spans="4:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="58" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A58"/>
       <c r="D58" s="28" t="str" cm="1">
         <f t="array" ref="D58">Common_SourceData.Common_SourceData_WetAndDryZones_Source()</f>
         <v>VEERG 2026: Table 1.2: Translating climate zones to wet and dry zones</v>
       </c>
     </row>
-    <row r="59" spans="4:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="59" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A59"/>
       <c r="D59" s="36" t="str" cm="1">
         <f t="array" ref="D59:D61">"⚠️" &amp; Common_SourceData.Common_SourceData_WetAndDryZones_Variation()</f>
         <v>⚠️VARIATION OF SOURCE DATA:</v>
       </c>
     </row>
-    <row r="60" spans="4:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="60" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A60"/>
       <c r="D60" s="36" t="str">
         <v>⚠️Added warm / cool temperate moist / dry - low frost and high temp classes to accommodate climate scenarios excluded by VEERG criteria.</v>
       </c>
     </row>
-    <row r="61" spans="4:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="61" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A61"/>
       <c r="D61" s="36" t="str">
         <v>⚠️Fixed typo - Changed 'Fry' to 'Dry'.</v>
       </c>
     </row>
-    <row r="62" spans="4:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="63" spans="4:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="62" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A62"/>
+    </row>
+    <row r="63" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A63"/>
       <c r="D63" s="30" t="s">
         <v>33</v>
       </c>
@@ -8296,189 +8481,219 @@
         <v>34</v>
       </c>
     </row>
-    <row r="64" spans="4:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="64" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A64"/>
       <c r="D64" s="30" t="str" cm="1">
-        <f t="array" ref="D64">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_WetAndDryZones_Data(), Table_SourceData_WetDryZones[[#Headers],[Climate zone]], 0)</f>
-        <v>Tropical montane</v>
+        <f t="array" aca="1" ref="D64" ca="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_WetAndDryZones_Data(), Table_SourceData_WetDryZones[[#Headers],[Climate zone]], 0)</f>
+        <v/>
       </c>
       <c r="E64" s="30" t="str" cm="1">
-        <f t="array" ref="E64">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_WetAndDryZones_Data(), Table_SourceData_WetDryZones[[#Headers],[Climate zone]], 0)</f>
-        <v>Wet climate zone</v>
-      </c>
-    </row>
-    <row r="65" spans="4:5" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+        <f t="array" aca="1" ref="E64" ca="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_WetAndDryZones_Data(), Table_SourceData_WetDryZones[[#Headers],[Climate zone]], 0)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="65" spans="1:5" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A65"/>
       <c r="D65" s="30" t="str" cm="1">
-        <f t="array" ref="D65">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_WetAndDryZones_Data(), Table_SourceData_WetDryZones[[#Headers],[Climate zone]], 0)</f>
-        <v>Tropical wet</v>
+        <f t="array" aca="1" ref="D65" ca="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_WetAndDryZones_Data(), Table_SourceData_WetDryZones[[#Headers],[Climate zone]], 0)</f>
+        <v/>
       </c>
       <c r="E65" s="30" t="str" cm="1">
-        <f t="array" ref="E65">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_WetAndDryZones_Data(), Table_SourceData_WetDryZones[[#Headers],[Climate zone]], 0)</f>
-        <v>Wet climate zone</v>
-      </c>
-    </row>
-    <row r="66" spans="4:5" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+        <f t="array" aca="1" ref="E65" ca="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_WetAndDryZones_Data(), Table_SourceData_WetDryZones[[#Headers],[Climate zone]], 0)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="66" spans="1:5" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A66"/>
       <c r="D66" s="30" t="str" cm="1">
-        <f t="array" ref="D66">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_WetAndDryZones_Data(), Table_SourceData_WetDryZones[[#Headers],[Climate zone]], 0)</f>
-        <v>Tropical moist</v>
+        <f t="array" aca="1" ref="D66" ca="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_WetAndDryZones_Data(), Table_SourceData_WetDryZones[[#Headers],[Climate zone]], 0)</f>
+        <v/>
       </c>
       <c r="E66" s="30" t="str" cm="1">
-        <f t="array" ref="E66">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_WetAndDryZones_Data(), Table_SourceData_WetDryZones[[#Headers],[Climate zone]], 0)</f>
-        <v>Wet climate zone</v>
-      </c>
-    </row>
-    <row r="67" spans="4:5" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+        <f t="array" aca="1" ref="E66" ca="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_WetAndDryZones_Data(), Table_SourceData_WetDryZones[[#Headers],[Climate zone]], 0)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="67" spans="1:5" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A67"/>
       <c r="D67" s="30" t="str" cm="1">
-        <f t="array" ref="D67">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_WetAndDryZones_Data(), Table_SourceData_WetDryZones[[#Headers],[Climate zone]], 0)</f>
-        <v>Tropical dry</v>
+        <f t="array" aca="1" ref="D67" ca="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_WetAndDryZones_Data(), Table_SourceData_WetDryZones[[#Headers],[Climate zone]], 0)</f>
+        <v/>
       </c>
       <c r="E67" s="30" t="str" cm="1">
-        <f t="array" ref="E67">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_WetAndDryZones_Data(), Table_SourceData_WetDryZones[[#Headers],[Climate zone]], 0)</f>
-        <v>Dry climate zone</v>
-      </c>
-    </row>
-    <row r="68" spans="4:5" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+        <f t="array" aca="1" ref="E67" ca="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_WetAndDryZones_Data(), Table_SourceData_WetDryZones[[#Headers],[Climate zone]], 0)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="68" spans="1:5" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A68"/>
       <c r="D68" s="30" t="str" cm="1">
-        <f t="array" ref="D68">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_WetAndDryZones_Data(), Table_SourceData_WetDryZones[[#Headers],[Climate zone]], 0)</f>
-        <v>Warm temperate moist</v>
+        <f t="array" aca="1" ref="D68" ca="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_WetAndDryZones_Data(), Table_SourceData_WetDryZones[[#Headers],[Climate zone]], 0)</f>
+        <v/>
       </c>
       <c r="E68" s="30" t="str" cm="1">
-        <f t="array" ref="E68">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_WetAndDryZones_Data(), Table_SourceData_WetDryZones[[#Headers],[Climate zone]], 0)</f>
-        <v>Wet climate zone</v>
-      </c>
-    </row>
-    <row r="69" spans="4:5" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+        <f t="array" aca="1" ref="E68" ca="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_WetAndDryZones_Data(), Table_SourceData_WetDryZones[[#Headers],[Climate zone]], 0)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="69" spans="1:5" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A69"/>
       <c r="D69" s="30" t="str" cm="1">
-        <f t="array" ref="D69">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_WetAndDryZones_Data(), Table_SourceData_WetDryZones[[#Headers],[Climate zone]], 0)</f>
-        <v>Warm temperate dry</v>
+        <f t="array" aca="1" ref="D69" ca="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_WetAndDryZones_Data(), Table_SourceData_WetDryZones[[#Headers],[Climate zone]], 0)</f>
+        <v/>
       </c>
       <c r="E69" s="30" t="str" cm="1">
-        <f t="array" ref="E69">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_WetAndDryZones_Data(), Table_SourceData_WetDryZones[[#Headers],[Climate zone]], 0)</f>
-        <v>Dry climate zone</v>
-      </c>
-    </row>
-    <row r="70" spans="4:5" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+        <f t="array" aca="1" ref="E69" ca="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_WetAndDryZones_Data(), Table_SourceData_WetDryZones[[#Headers],[Climate zone]], 0)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="70" spans="1:5" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A70"/>
       <c r="D70" s="30" t="str" cm="1">
-        <f t="array" ref="D70">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_WetAndDryZones_Data(), Table_SourceData_WetDryZones[[#Headers],[Climate zone]], 0)</f>
-        <v>Cool temperate moist</v>
+        <f t="array" aca="1" ref="D70" ca="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_WetAndDryZones_Data(), Table_SourceData_WetDryZones[[#Headers],[Climate zone]], 0)</f>
+        <v/>
       </c>
       <c r="E70" s="30" t="str" cm="1">
-        <f t="array" ref="E70">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_WetAndDryZones_Data(), Table_SourceData_WetDryZones[[#Headers],[Climate zone]], 0)</f>
-        <v>Wet climate zone</v>
-      </c>
-    </row>
-    <row r="71" spans="4:5" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+        <f t="array" aca="1" ref="E70" ca="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_WetAndDryZones_Data(), Table_SourceData_WetDryZones[[#Headers],[Climate zone]], 0)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="71" spans="1:5" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A71"/>
       <c r="D71" s="30" t="str" cm="1">
-        <f t="array" ref="D71">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_WetAndDryZones_Data(), Table_SourceData_WetDryZones[[#Headers],[Climate zone]], 0)</f>
-        <v>Cool temperate dry</v>
+        <f t="array" aca="1" ref="D71" ca="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_WetAndDryZones_Data(), Table_SourceData_WetDryZones[[#Headers],[Climate zone]], 0)</f>
+        <v/>
       </c>
       <c r="E71" s="30" t="str" cm="1">
-        <f t="array" ref="E71">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_WetAndDryZones_Data(), Table_SourceData_WetDryZones[[#Headers],[Climate zone]], 0)</f>
-        <v>Dry climate zone</v>
-      </c>
-    </row>
-    <row r="72" spans="4:5" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+        <f t="array" aca="1" ref="E71" ca="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_WetAndDryZones_Data(), Table_SourceData_WetDryZones[[#Headers],[Climate zone]], 0)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="72" spans="1:5" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A72"/>
       <c r="D72" s="30" t="str" cm="1">
-        <f t="array" ref="D72">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_WetAndDryZones_Data(), Table_SourceData_WetDryZones[[#Headers],[Climate zone]], 0)</f>
-        <v>Warm temperate moist - low frost</v>
+        <f t="array" aca="1" ref="D72" ca="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_WetAndDryZones_Data(), Table_SourceData_WetDryZones[[#Headers],[Climate zone]], 0)</f>
+        <v/>
       </c>
       <c r="E72" s="30" t="str" cm="1">
-        <f t="array" ref="E72">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_WetAndDryZones_Data(), Table_SourceData_WetDryZones[[#Headers],[Climate zone]], 0)</f>
-        <v>Wet climate zone</v>
-      </c>
-    </row>
-    <row r="73" spans="4:5" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+        <f t="array" aca="1" ref="E72" ca="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_WetAndDryZones_Data(), Table_SourceData_WetDryZones[[#Headers],[Climate zone]], 0)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="73" spans="1:5" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A73"/>
       <c r="D73" s="30" t="str" cm="1">
-        <f t="array" ref="D73">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_WetAndDryZones_Data(), Table_SourceData_WetDryZones[[#Headers],[Climate zone]], 0)</f>
-        <v>Warm temperate dry - low frost</v>
+        <f t="array" aca="1" ref="D73" ca="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_WetAndDryZones_Data(), Table_SourceData_WetDryZones[[#Headers],[Climate zone]], 0)</f>
+        <v/>
       </c>
       <c r="E73" s="30" t="str" cm="1">
-        <f t="array" ref="E73">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_WetAndDryZones_Data(), Table_SourceData_WetDryZones[[#Headers],[Climate zone]], 0)</f>
-        <v>Dry climate zone</v>
-      </c>
-    </row>
-    <row r="74" spans="4:5" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+        <f t="array" aca="1" ref="E73" ca="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_WetAndDryZones_Data(), Table_SourceData_WetDryZones[[#Headers],[Climate zone]], 0)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="74" spans="1:5" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A74"/>
       <c r="D74" s="30" t="str" cm="1">
-        <f t="array" ref="D74">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_WetAndDryZones_Data(), Table_SourceData_WetDryZones[[#Headers],[Climate zone]], 0)</f>
-        <v>Warm temperate moist - high temp</v>
+        <f t="array" aca="1" ref="D74" ca="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_WetAndDryZones_Data(), Table_SourceData_WetDryZones[[#Headers],[Climate zone]], 0)</f>
+        <v/>
       </c>
       <c r="E74" s="30" t="str" cm="1">
-        <f t="array" ref="E74">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_WetAndDryZones_Data(), Table_SourceData_WetDryZones[[#Headers],[Climate zone]], 0)</f>
-        <v>Wet climate zone</v>
-      </c>
-    </row>
-    <row r="75" spans="4:5" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+        <f t="array" aca="1" ref="E74" ca="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_WetAndDryZones_Data(), Table_SourceData_WetDryZones[[#Headers],[Climate zone]], 0)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="75" spans="1:5" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A75"/>
       <c r="D75" s="30" t="str" cm="1">
-        <f t="array" ref="D75">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_WetAndDryZones_Data(), Table_SourceData_WetDryZones[[#Headers],[Climate zone]], 0)</f>
-        <v>Warm temperate dry - high temp</v>
+        <f t="array" aca="1" ref="D75" ca="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_WetAndDryZones_Data(), Table_SourceData_WetDryZones[[#Headers],[Climate zone]], 0)</f>
+        <v/>
       </c>
       <c r="E75" s="30" t="str" cm="1">
-        <f t="array" ref="E75">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_WetAndDryZones_Data(), Table_SourceData_WetDryZones[[#Headers],[Climate zone]], 0)</f>
-        <v>Dry climate zone</v>
-      </c>
-    </row>
-    <row r="76" spans="4:5" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+        <f t="array" aca="1" ref="E75" ca="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_WetAndDryZones_Data(), Table_SourceData_WetDryZones[[#Headers],[Climate zone]], 0)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="76" spans="1:5" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A76"/>
       <c r="D76" s="30" t="str" cm="1">
-        <f t="array" ref="D76">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_WetAndDryZones_Data(), Table_SourceData_WetDryZones[[#Headers],[Climate zone]], 0)</f>
-        <v>Cool temperate moist - low frost</v>
+        <f t="array" aca="1" ref="D76" ca="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_WetAndDryZones_Data(), Table_SourceData_WetDryZones[[#Headers],[Climate zone]], 0)</f>
+        <v/>
       </c>
       <c r="E76" s="30" t="str" cm="1">
-        <f t="array" ref="E76">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_WetAndDryZones_Data(), Table_SourceData_WetDryZones[[#Headers],[Climate zone]], 0)</f>
-        <v>Wet climate zone</v>
-      </c>
-    </row>
-    <row r="77" spans="4:5" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+        <f t="array" aca="1" ref="E76" ca="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_WetAndDryZones_Data(), Table_SourceData_WetDryZones[[#Headers],[Climate zone]], 0)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="77" spans="1:5" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A77"/>
       <c r="D77" s="30" t="str" cm="1">
-        <f t="array" ref="D77">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_WetAndDryZones_Data(), Table_SourceData_WetDryZones[[#Headers],[Climate zone]], 0)</f>
-        <v>Cool temperate dry - low frost</v>
+        <f t="array" aca="1" ref="D77" ca="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_WetAndDryZones_Data(), Table_SourceData_WetDryZones[[#Headers],[Climate zone]], 0)</f>
+        <v/>
       </c>
       <c r="E77" s="30" t="str" cm="1">
-        <f t="array" ref="E77">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_WetAndDryZones_Data(), Table_SourceData_WetDryZones[[#Headers],[Climate zone]], 0)</f>
-        <v>Dry climate zone</v>
-      </c>
-    </row>
-    <row r="78" spans="4:5" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="79" spans="4:5" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="80" spans="4:5" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="81" spans="4:20" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+        <f t="array" aca="1" ref="E77" ca="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_WetAndDryZones_Data(), Table_SourceData_WetDryZones[[#Headers],[Climate zone]], 0)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="78" spans="1:5" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A78"/>
+    </row>
+    <row r="79" spans="1:5" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A79"/>
+    </row>
+    <row r="80" spans="1:5" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A80"/>
+    </row>
+    <row r="81" spans="1:20" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A81"/>
       <c r="D81" s="2" t="str" cm="1">
         <f t="array" ref="D81">Common_SourceData.Common_SourceData_ClimateZones_Title()</f>
         <v>VEERG Australian climate zones</v>
       </c>
     </row>
-    <row r="82" spans="4:20" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="82" spans="1:20" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A82"/>
       <c r="D82" s="28" t="str" cm="1">
         <f t="array" ref="D82">Common_SourceData.Common_SourceData_ClimateZones_Source()</f>
         <v>VEERG 2026: Table 1.3: Climate and Rainfall zone classifications and definitions</v>
       </c>
     </row>
-    <row r="83" spans="4:20" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="83" spans="1:20" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A83"/>
       <c r="D83" s="36" t="str" cm="1">
         <f t="array" ref="D83:D87">"⚠️" &amp; Common_SourceData.Common_SourceData_ClimateZones_Variation()</f>
         <v>⚠️VARIATION OF SOURCE DATA:</v>
       </c>
     </row>
-    <row r="84" spans="4:20" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="84" spans="1:20" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A84"/>
       <c r="D84" s="36" t="str">
         <v>⚠️Added warm / cool temperate moist / dry - low frost and high temp classes to accommodate climate scenarios excluded by VEERG criteria.</v>
       </c>
     </row>
-    <row r="85" spans="4:20" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="85" spans="1:20" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A85"/>
       <c r="D85" s="36" t="str">
         <v>⚠️Fixed typo in MAT value for warm temperate dry - changed 10 to 11.</v>
       </c>
     </row>
-    <row r="86" spans="4:20" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="86" spans="1:20" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A86"/>
       <c r="D86" s="36" t="str">
         <v>⚠️Added min and max columns for MAT, MAP, frost days per year, elevation, MAP:PET to calculate zones from real climate data.</v>
       </c>
     </row>
-    <row r="87" spans="4:20" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="87" spans="1:20" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A87"/>
       <c r="D87" s="36" t="str">
         <v>⚠️GAF accepts rainfall as a proxy for precipitation.</v>
       </c>
     </row>
-    <row r="88" spans="4:20" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="89" spans="4:20" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="88" spans="1:20" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A88"/>
+    </row>
+    <row r="89" spans="1:20" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A89"/>
       <c r="D89" s="30" t="s">
         <v>33</v>
       </c>
@@ -8529,588 +8744,611 @@
       </c>
       <c r="T89" s="30"/>
     </row>
-    <row r="90" spans="4:20" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="90" spans="1:20" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A90"/>
       <c r="D90" s="30" t="str" cm="1">
-        <f t="array" ref="D90">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ClimateZones_Data(), Table_SourceData_ClimateZones[[#Headers],[Climate zone]], 0)</f>
-        <v>Tropical montane</v>
+        <f t="array" aca="1" ref="D90" ca="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ClimateZones_Data(), Table_SourceData_ClimateZones[[#Headers],[Climate zone]], 0)</f>
+        <v/>
       </c>
       <c r="E90" s="30" t="str" cm="1">
-        <f t="array" ref="E90">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ClimateZones_Data(), Table_SourceData_ClimateZones[[#Headers],[Climate zone]], 0)</f>
-        <v>&gt; 18 C</v>
+        <f t="array" aca="1" ref="E90" ca="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ClimateZones_Data(), Table_SourceData_ClimateZones[[#Headers],[Climate zone]], 0)</f>
+        <v/>
       </c>
       <c r="F90" s="30" t="str" cm="1">
-        <f t="array" ref="F90">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ClimateZones_Data(), Table_SourceData_ClimateZones[[#Headers],[Climate zone]], 0)</f>
-        <v>Any</v>
+        <f t="array" aca="1" ref="F90" ca="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ClimateZones_Data(), Table_SourceData_ClimateZones[[#Headers],[Climate zone]], 0)</f>
+        <v/>
       </c>
       <c r="G90" s="30" t="str" cm="1">
-        <f t="array" ref="G90">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ClimateZones_Data(), Table_SourceData_ClimateZones[[#Headers],[Climate zone]], 0)</f>
-        <v>≤ 7</v>
+        <f t="array" aca="1" ref="G90" ca="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ClimateZones_Data(), Table_SourceData_ClimateZones[[#Headers],[Climate zone]], 0)</f>
+        <v/>
       </c>
       <c r="H90" s="30" t="str" cm="1">
-        <f t="array" ref="H90">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ClimateZones_Data(), Table_SourceData_ClimateZones[[#Headers],[Climate zone]], 0)</f>
-        <v>&gt; 1000 m</v>
+        <f t="array" aca="1" ref="H90" ca="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ClimateZones_Data(), Table_SourceData_ClimateZones[[#Headers],[Climate zone]], 0)</f>
+        <v/>
       </c>
       <c r="I90" s="30" t="str" cm="1">
-        <f t="array" ref="I90">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ClimateZones_Data(), Table_SourceData_ClimateZones[[#Headers],[Climate zone]], 0)</f>
-        <v>Any</v>
-      </c>
-      <c r="J90" s="30" cm="1">
-        <f t="array" ref="J90">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ClimateZones_Data(), Table_SourceData_ClimateZones[[#Headers],[Climate zone]], 0)</f>
-        <v>18.001000000000001</v>
-      </c>
-      <c r="K90" s="30" cm="1">
-        <f t="array" ref="K90">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ClimateZones_Data(), Table_SourceData_ClimateZones[[#Headers],[Climate zone]], 0)</f>
-        <v>999999</v>
-      </c>
-      <c r="L90" s="30" cm="1">
-        <f t="array" ref="L90">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ClimateZones_Data(), Table_SourceData_ClimateZones[[#Headers],[Climate zone]], 0)</f>
-        <v>-999999</v>
-      </c>
-      <c r="M90" s="30" cm="1">
-        <f t="array" ref="M90">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ClimateZones_Data(), Table_SourceData_ClimateZones[[#Headers],[Climate zone]], 0)</f>
-        <v>999999</v>
-      </c>
-      <c r="N90" s="30" cm="1">
-        <f t="array" ref="N90">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ClimateZones_Data(), Table_SourceData_ClimateZones[[#Headers],[Climate zone]], 0)</f>
-        <v>-999999</v>
-      </c>
-      <c r="O90" s="30" cm="1">
-        <f t="array" ref="O90">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ClimateZones_Data(), Table_SourceData_ClimateZones[[#Headers],[Climate zone]], 0)</f>
-        <v>7</v>
-      </c>
-      <c r="P90" s="30" cm="1">
-        <f t="array" ref="P90">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ClimateZones_Data(), Table_SourceData_ClimateZones[[#Headers],[Climate zone]], 0)</f>
-        <v>1000</v>
-      </c>
-      <c r="Q90" s="30" cm="1">
-        <f t="array" ref="Q90">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ClimateZones_Data(), Table_SourceData_ClimateZones[[#Headers],[Climate zone]], 0)</f>
-        <v>999999</v>
-      </c>
-      <c r="R90" s="30" cm="1">
-        <f t="array" ref="R90">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ClimateZones_Data(), Table_SourceData_ClimateZones[[#Headers],[Climate zone]], 0)</f>
-        <v>-999999</v>
-      </c>
-      <c r="S90" s="30" cm="1">
-        <f t="array" ref="S90">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ClimateZones_Data(), Table_SourceData_ClimateZones[[#Headers],[Climate zone]], 0)</f>
-        <v>999999</v>
+        <f t="array" aca="1" ref="I90" ca="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ClimateZones_Data(), Table_SourceData_ClimateZones[[#Headers],[Climate zone]], 0)</f>
+        <v/>
+      </c>
+      <c r="J90" s="30" t="str" cm="1">
+        <f t="array" aca="1" ref="J90" ca="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ClimateZones_Data(), Table_SourceData_ClimateZones[[#Headers],[Climate zone]], 0)</f>
+        <v/>
+      </c>
+      <c r="K90" s="30" t="str" cm="1">
+        <f t="array" aca="1" ref="K90" ca="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ClimateZones_Data(), Table_SourceData_ClimateZones[[#Headers],[Climate zone]], 0)</f>
+        <v/>
+      </c>
+      <c r="L90" s="30" t="str" cm="1">
+        <f t="array" aca="1" ref="L90" ca="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ClimateZones_Data(), Table_SourceData_ClimateZones[[#Headers],[Climate zone]], 0)</f>
+        <v/>
+      </c>
+      <c r="M90" s="30" t="str" cm="1">
+        <f t="array" aca="1" ref="M90" ca="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ClimateZones_Data(), Table_SourceData_ClimateZones[[#Headers],[Climate zone]], 0)</f>
+        <v/>
+      </c>
+      <c r="N90" s="30" t="str" cm="1">
+        <f t="array" aca="1" ref="N90" ca="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ClimateZones_Data(), Table_SourceData_ClimateZones[[#Headers],[Climate zone]], 0)</f>
+        <v/>
+      </c>
+      <c r="O90" s="30" t="str" cm="1">
+        <f t="array" aca="1" ref="O90" ca="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ClimateZones_Data(), Table_SourceData_ClimateZones[[#Headers],[Climate zone]], 0)</f>
+        <v/>
+      </c>
+      <c r="P90" s="30" t="str" cm="1">
+        <f t="array" aca="1" ref="P90" ca="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ClimateZones_Data(), Table_SourceData_ClimateZones[[#Headers],[Climate zone]], 0)</f>
+        <v/>
+      </c>
+      <c r="Q90" s="30" t="str" cm="1">
+        <f t="array" aca="1" ref="Q90" ca="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ClimateZones_Data(), Table_SourceData_ClimateZones[[#Headers],[Climate zone]], 0)</f>
+        <v/>
+      </c>
+      <c r="R90" s="30" t="str" cm="1">
+        <f t="array" aca="1" ref="R90" ca="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ClimateZones_Data(), Table_SourceData_ClimateZones[[#Headers],[Climate zone]], 0)</f>
+        <v/>
+      </c>
+      <c r="S90" s="30" t="str" cm="1">
+        <f t="array" aca="1" ref="S90" ca="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ClimateZones_Data(), Table_SourceData_ClimateZones[[#Headers],[Climate zone]], 0)</f>
+        <v/>
       </c>
       <c r="T90" s="30"/>
     </row>
-    <row r="91" spans="4:20" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="91" spans="1:20" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A91"/>
       <c r="D91" s="30" t="str" cm="1">
-        <f t="array" ref="D91">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ClimateZones_Data(), Table_SourceData_ClimateZones[[#Headers],[Climate zone]], 0)</f>
-        <v>Tropical wet</v>
+        <f t="array" aca="1" ref="D91" ca="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ClimateZones_Data(), Table_SourceData_ClimateZones[[#Headers],[Climate zone]], 0)</f>
+        <v/>
       </c>
       <c r="E91" s="30" t="str" cm="1">
-        <f t="array" ref="E91">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ClimateZones_Data(), Table_SourceData_ClimateZones[[#Headers],[Climate zone]], 0)</f>
-        <v>&gt; 18 C</v>
+        <f t="array" aca="1" ref="E91" ca="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ClimateZones_Data(), Table_SourceData_ClimateZones[[#Headers],[Climate zone]], 0)</f>
+        <v/>
       </c>
       <c r="F91" s="30" t="str" cm="1">
-        <f t="array" ref="F91">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ClimateZones_Data(), Table_SourceData_ClimateZones[[#Headers],[Climate zone]], 0)</f>
-        <v>&gt; 2000 mm</v>
+        <f t="array" aca="1" ref="F91" ca="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ClimateZones_Data(), Table_SourceData_ClimateZones[[#Headers],[Climate zone]], 0)</f>
+        <v/>
       </c>
       <c r="G91" s="30" t="str" cm="1">
-        <f t="array" ref="G91">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ClimateZones_Data(), Table_SourceData_ClimateZones[[#Headers],[Climate zone]], 0)</f>
-        <v>≤ 7</v>
+        <f t="array" aca="1" ref="G91" ca="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ClimateZones_Data(), Table_SourceData_ClimateZones[[#Headers],[Climate zone]], 0)</f>
+        <v/>
       </c>
       <c r="H91" s="30" t="str" cm="1">
-        <f t="array" ref="H91">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ClimateZones_Data(), Table_SourceData_ClimateZones[[#Headers],[Climate zone]], 0)</f>
-        <v>≤ 1000 m</v>
+        <f t="array" aca="1" ref="H91" ca="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ClimateZones_Data(), Table_SourceData_ClimateZones[[#Headers],[Climate zone]], 0)</f>
+        <v/>
       </c>
       <c r="I91" s="30" t="str" cm="1">
-        <f t="array" ref="I91">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ClimateZones_Data(), Table_SourceData_ClimateZones[[#Headers],[Climate zone]], 0)</f>
-        <v>Any</v>
-      </c>
-      <c r="J91" s="30" cm="1">
-        <f t="array" ref="J91">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ClimateZones_Data(), Table_SourceData_ClimateZones[[#Headers],[Climate zone]], 0)</f>
-        <v>18.001000000000001</v>
-      </c>
-      <c r="K91" s="30" cm="1">
-        <f t="array" ref="K91">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ClimateZones_Data(), Table_SourceData_ClimateZones[[#Headers],[Climate zone]], 0)</f>
-        <v>999999</v>
-      </c>
-      <c r="L91" s="30" cm="1">
-        <f t="array" ref="L91">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ClimateZones_Data(), Table_SourceData_ClimateZones[[#Headers],[Climate zone]], 0)</f>
-        <v>2000.001</v>
-      </c>
-      <c r="M91" s="30" cm="1">
-        <f t="array" ref="M91">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ClimateZones_Data(), Table_SourceData_ClimateZones[[#Headers],[Climate zone]], 0)</f>
-        <v>999999</v>
-      </c>
-      <c r="N91" s="30" cm="1">
-        <f t="array" ref="N91">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ClimateZones_Data(), Table_SourceData_ClimateZones[[#Headers],[Climate zone]], 0)</f>
-        <v>-999999</v>
-      </c>
-      <c r="O91" s="30" cm="1">
-        <f t="array" ref="O91">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ClimateZones_Data(), Table_SourceData_ClimateZones[[#Headers],[Climate zone]], 0)</f>
-        <v>7</v>
-      </c>
-      <c r="P91" s="30" cm="1">
-        <f t="array" ref="P91">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ClimateZones_Data(), Table_SourceData_ClimateZones[[#Headers],[Climate zone]], 0)</f>
-        <v>-999999</v>
-      </c>
-      <c r="Q91" s="30" cm="1">
-        <f t="array" ref="Q91">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ClimateZones_Data(), Table_SourceData_ClimateZones[[#Headers],[Climate zone]], 0)</f>
-        <v>999.99900000000002</v>
-      </c>
-      <c r="R91" s="30" cm="1">
-        <f t="array" ref="R91">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ClimateZones_Data(), Table_SourceData_ClimateZones[[#Headers],[Climate zone]], 0)</f>
-        <v>-999999</v>
-      </c>
-      <c r="S91" s="30" cm="1">
-        <f t="array" ref="S91">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ClimateZones_Data(), Table_SourceData_ClimateZones[[#Headers],[Climate zone]], 0)</f>
-        <v>999999</v>
+        <f t="array" aca="1" ref="I91" ca="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ClimateZones_Data(), Table_SourceData_ClimateZones[[#Headers],[Climate zone]], 0)</f>
+        <v/>
+      </c>
+      <c r="J91" s="30" t="str" cm="1">
+        <f t="array" aca="1" ref="J91" ca="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ClimateZones_Data(), Table_SourceData_ClimateZones[[#Headers],[Climate zone]], 0)</f>
+        <v/>
+      </c>
+      <c r="K91" s="30" t="str" cm="1">
+        <f t="array" aca="1" ref="K91" ca="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ClimateZones_Data(), Table_SourceData_ClimateZones[[#Headers],[Climate zone]], 0)</f>
+        <v/>
+      </c>
+      <c r="L91" s="30" t="str" cm="1">
+        <f t="array" aca="1" ref="L91" ca="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ClimateZones_Data(), Table_SourceData_ClimateZones[[#Headers],[Climate zone]], 0)</f>
+        <v/>
+      </c>
+      <c r="M91" s="30" t="str" cm="1">
+        <f t="array" aca="1" ref="M91" ca="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ClimateZones_Data(), Table_SourceData_ClimateZones[[#Headers],[Climate zone]], 0)</f>
+        <v/>
+      </c>
+      <c r="N91" s="30" t="str" cm="1">
+        <f t="array" aca="1" ref="N91" ca="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ClimateZones_Data(), Table_SourceData_ClimateZones[[#Headers],[Climate zone]], 0)</f>
+        <v/>
+      </c>
+      <c r="O91" s="30" t="str" cm="1">
+        <f t="array" aca="1" ref="O91" ca="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ClimateZones_Data(), Table_SourceData_ClimateZones[[#Headers],[Climate zone]], 0)</f>
+        <v/>
+      </c>
+      <c r="P91" s="30" t="str" cm="1">
+        <f t="array" aca="1" ref="P91" ca="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ClimateZones_Data(), Table_SourceData_ClimateZones[[#Headers],[Climate zone]], 0)</f>
+        <v/>
+      </c>
+      <c r="Q91" s="30" t="str" cm="1">
+        <f t="array" aca="1" ref="Q91" ca="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ClimateZones_Data(), Table_SourceData_ClimateZones[[#Headers],[Climate zone]], 0)</f>
+        <v/>
+      </c>
+      <c r="R91" s="30" t="str" cm="1">
+        <f t="array" aca="1" ref="R91" ca="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ClimateZones_Data(), Table_SourceData_ClimateZones[[#Headers],[Climate zone]], 0)</f>
+        <v/>
+      </c>
+      <c r="S91" s="30" t="str" cm="1">
+        <f t="array" aca="1" ref="S91" ca="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ClimateZones_Data(), Table_SourceData_ClimateZones[[#Headers],[Climate zone]], 0)</f>
+        <v/>
       </c>
       <c r="T91" s="30"/>
     </row>
-    <row r="92" spans="4:20" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="92" spans="1:20" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A92"/>
       <c r="D92" s="30" t="str" cm="1">
-        <f t="array" ref="D92">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ClimateZones_Data(), Table_SourceData_ClimateZones[[#Headers],[Climate zone]], 0)</f>
-        <v>Tropical moist</v>
+        <f t="array" aca="1" ref="D92" ca="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ClimateZones_Data(), Table_SourceData_ClimateZones[[#Headers],[Climate zone]], 0)</f>
+        <v/>
       </c>
       <c r="E92" s="30" t="str" cm="1">
-        <f t="array" ref="E92">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ClimateZones_Data(), Table_SourceData_ClimateZones[[#Headers],[Climate zone]], 0)</f>
-        <v>&gt; 18 C</v>
+        <f t="array" aca="1" ref="E92" ca="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ClimateZones_Data(), Table_SourceData_ClimateZones[[#Headers],[Climate zone]], 0)</f>
+        <v/>
       </c>
       <c r="F92" s="30" t="str" cm="1">
-        <f t="array" ref="F92">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ClimateZones_Data(), Table_SourceData_ClimateZones[[#Headers],[Climate zone]], 0)</f>
-        <v>&gt; 1000 mm - ≤ 2000 mm</v>
+        <f t="array" aca="1" ref="F92" ca="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ClimateZones_Data(), Table_SourceData_ClimateZones[[#Headers],[Climate zone]], 0)</f>
+        <v/>
       </c>
       <c r="G92" s="30" t="str" cm="1">
-        <f t="array" ref="G92">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ClimateZones_Data(), Table_SourceData_ClimateZones[[#Headers],[Climate zone]], 0)</f>
-        <v>≤ 7</v>
+        <f t="array" aca="1" ref="G92" ca="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ClimateZones_Data(), Table_SourceData_ClimateZones[[#Headers],[Climate zone]], 0)</f>
+        <v/>
       </c>
       <c r="H92" s="30" t="str" cm="1">
-        <f t="array" ref="H92">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ClimateZones_Data(), Table_SourceData_ClimateZones[[#Headers],[Climate zone]], 0)</f>
-        <v>≤ 1000 m</v>
+        <f t="array" aca="1" ref="H92" ca="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ClimateZones_Data(), Table_SourceData_ClimateZones[[#Headers],[Climate zone]], 0)</f>
+        <v/>
       </c>
       <c r="I92" s="30" t="str" cm="1">
-        <f t="array" ref="I92">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ClimateZones_Data(), Table_SourceData_ClimateZones[[#Headers],[Climate zone]], 0)</f>
-        <v>Any</v>
-      </c>
-      <c r="J92" s="30" cm="1">
-        <f t="array" ref="J92">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ClimateZones_Data(), Table_SourceData_ClimateZones[[#Headers],[Climate zone]], 0)</f>
-        <v>18.001000000000001</v>
-      </c>
-      <c r="K92" s="30" cm="1">
-        <f t="array" ref="K92">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ClimateZones_Data(), Table_SourceData_ClimateZones[[#Headers],[Climate zone]], 0)</f>
-        <v>999999</v>
-      </c>
-      <c r="L92" s="30" cm="1">
-        <f t="array" ref="L92">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ClimateZones_Data(), Table_SourceData_ClimateZones[[#Headers],[Climate zone]], 0)</f>
-        <v>1000.001</v>
-      </c>
-      <c r="M92" s="30" cm="1">
-        <f t="array" ref="M92">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ClimateZones_Data(), Table_SourceData_ClimateZones[[#Headers],[Climate zone]], 0)</f>
-        <v>2000</v>
-      </c>
-      <c r="N92" s="30" cm="1">
-        <f t="array" ref="N92">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ClimateZones_Data(), Table_SourceData_ClimateZones[[#Headers],[Climate zone]], 0)</f>
-        <v>-999999</v>
-      </c>
-      <c r="O92" s="30" cm="1">
-        <f t="array" ref="O92">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ClimateZones_Data(), Table_SourceData_ClimateZones[[#Headers],[Climate zone]], 0)</f>
-        <v>7</v>
-      </c>
-      <c r="P92" s="30" cm="1">
-        <f t="array" ref="P92">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ClimateZones_Data(), Table_SourceData_ClimateZones[[#Headers],[Climate zone]], 0)</f>
-        <v>-999999</v>
-      </c>
-      <c r="Q92" s="30" cm="1">
-        <f t="array" ref="Q92">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ClimateZones_Data(), Table_SourceData_ClimateZones[[#Headers],[Climate zone]], 0)</f>
-        <v>999.99900000000002</v>
-      </c>
-      <c r="R92" s="30" cm="1">
-        <f t="array" ref="R92">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ClimateZones_Data(), Table_SourceData_ClimateZones[[#Headers],[Climate zone]], 0)</f>
-        <v>-999999</v>
-      </c>
-      <c r="S92" s="30" cm="1">
-        <f t="array" ref="S92">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ClimateZones_Data(), Table_SourceData_ClimateZones[[#Headers],[Climate zone]], 0)</f>
-        <v>999999</v>
+        <f t="array" aca="1" ref="I92" ca="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ClimateZones_Data(), Table_SourceData_ClimateZones[[#Headers],[Climate zone]], 0)</f>
+        <v/>
+      </c>
+      <c r="J92" s="30" t="str" cm="1">
+        <f t="array" aca="1" ref="J92" ca="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ClimateZones_Data(), Table_SourceData_ClimateZones[[#Headers],[Climate zone]], 0)</f>
+        <v/>
+      </c>
+      <c r="K92" s="30" t="str" cm="1">
+        <f t="array" aca="1" ref="K92" ca="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ClimateZones_Data(), Table_SourceData_ClimateZones[[#Headers],[Climate zone]], 0)</f>
+        <v/>
+      </c>
+      <c r="L92" s="30" t="str" cm="1">
+        <f t="array" aca="1" ref="L92" ca="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ClimateZones_Data(), Table_SourceData_ClimateZones[[#Headers],[Climate zone]], 0)</f>
+        <v/>
+      </c>
+      <c r="M92" s="30" t="str" cm="1">
+        <f t="array" aca="1" ref="M92" ca="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ClimateZones_Data(), Table_SourceData_ClimateZones[[#Headers],[Climate zone]], 0)</f>
+        <v/>
+      </c>
+      <c r="N92" s="30" t="str" cm="1">
+        <f t="array" aca="1" ref="N92" ca="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ClimateZones_Data(), Table_SourceData_ClimateZones[[#Headers],[Climate zone]], 0)</f>
+        <v/>
+      </c>
+      <c r="O92" s="30" t="str" cm="1">
+        <f t="array" aca="1" ref="O92" ca="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ClimateZones_Data(), Table_SourceData_ClimateZones[[#Headers],[Climate zone]], 0)</f>
+        <v/>
+      </c>
+      <c r="P92" s="30" t="str" cm="1">
+        <f t="array" aca="1" ref="P92" ca="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ClimateZones_Data(), Table_SourceData_ClimateZones[[#Headers],[Climate zone]], 0)</f>
+        <v/>
+      </c>
+      <c r="Q92" s="30" t="str" cm="1">
+        <f t="array" aca="1" ref="Q92" ca="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ClimateZones_Data(), Table_SourceData_ClimateZones[[#Headers],[Climate zone]], 0)</f>
+        <v/>
+      </c>
+      <c r="R92" s="30" t="str" cm="1">
+        <f t="array" aca="1" ref="R92" ca="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ClimateZones_Data(), Table_SourceData_ClimateZones[[#Headers],[Climate zone]], 0)</f>
+        <v/>
+      </c>
+      <c r="S92" s="30" t="str" cm="1">
+        <f t="array" aca="1" ref="S92" ca="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ClimateZones_Data(), Table_SourceData_ClimateZones[[#Headers],[Climate zone]], 0)</f>
+        <v/>
       </c>
       <c r="T92" s="30"/>
     </row>
-    <row r="93" spans="4:20" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="93" spans="1:20" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A93"/>
       <c r="D93" s="30" t="str" cm="1">
-        <f t="array" ref="D93">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ClimateZones_Data(), Table_SourceData_ClimateZones[[#Headers],[Climate zone]], 0)</f>
-        <v>Tropical dry</v>
+        <f t="array" aca="1" ref="D93" ca="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ClimateZones_Data(), Table_SourceData_ClimateZones[[#Headers],[Climate zone]], 0)</f>
+        <v/>
       </c>
       <c r="E93" s="30" t="str" cm="1">
-        <f t="array" ref="E93">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ClimateZones_Data(), Table_SourceData_ClimateZones[[#Headers],[Climate zone]], 0)</f>
-        <v>&gt; 18 C</v>
+        <f t="array" aca="1" ref="E93" ca="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ClimateZones_Data(), Table_SourceData_ClimateZones[[#Headers],[Climate zone]], 0)</f>
+        <v/>
       </c>
       <c r="F93" s="30" t="str" cm="1">
-        <f t="array" ref="F93">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ClimateZones_Data(), Table_SourceData_ClimateZones[[#Headers],[Climate zone]], 0)</f>
-        <v>≤ 1000 mm</v>
+        <f t="array" aca="1" ref="F93" ca="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ClimateZones_Data(), Table_SourceData_ClimateZones[[#Headers],[Climate zone]], 0)</f>
+        <v/>
       </c>
       <c r="G93" s="30" t="str" cm="1">
-        <f t="array" ref="G93">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ClimateZones_Data(), Table_SourceData_ClimateZones[[#Headers],[Climate zone]], 0)</f>
-        <v>≤ 7</v>
+        <f t="array" aca="1" ref="G93" ca="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ClimateZones_Data(), Table_SourceData_ClimateZones[[#Headers],[Climate zone]], 0)</f>
+        <v/>
       </c>
       <c r="H93" s="30" t="str" cm="1">
-        <f t="array" ref="H93">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ClimateZones_Data(), Table_SourceData_ClimateZones[[#Headers],[Climate zone]], 0)</f>
-        <v>≤ 1000 m</v>
+        <f t="array" aca="1" ref="H93" ca="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ClimateZones_Data(), Table_SourceData_ClimateZones[[#Headers],[Climate zone]], 0)</f>
+        <v/>
       </c>
       <c r="I93" s="30" t="str" cm="1">
-        <f t="array" ref="I93">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ClimateZones_Data(), Table_SourceData_ClimateZones[[#Headers],[Climate zone]], 0)</f>
-        <v>Any</v>
-      </c>
-      <c r="J93" s="30" cm="1">
-        <f t="array" ref="J93">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ClimateZones_Data(), Table_SourceData_ClimateZones[[#Headers],[Climate zone]], 0)</f>
-        <v>18.001000000000001</v>
-      </c>
-      <c r="K93" s="30" cm="1">
-        <f t="array" ref="K93">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ClimateZones_Data(), Table_SourceData_ClimateZones[[#Headers],[Climate zone]], 0)</f>
-        <v>999999</v>
-      </c>
-      <c r="L93" s="30" cm="1">
-        <f t="array" ref="L93">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ClimateZones_Data(), Table_SourceData_ClimateZones[[#Headers],[Climate zone]], 0)</f>
-        <v>-999999</v>
-      </c>
-      <c r="M93" s="30" cm="1">
-        <f t="array" ref="M93">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ClimateZones_Data(), Table_SourceData_ClimateZones[[#Headers],[Climate zone]], 0)</f>
-        <v>1000</v>
-      </c>
-      <c r="N93" s="30" cm="1">
-        <f t="array" ref="N93">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ClimateZones_Data(), Table_SourceData_ClimateZones[[#Headers],[Climate zone]], 0)</f>
-        <v>-999999</v>
-      </c>
-      <c r="O93" s="30" cm="1">
-        <f t="array" ref="O93">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ClimateZones_Data(), Table_SourceData_ClimateZones[[#Headers],[Climate zone]], 0)</f>
-        <v>7</v>
-      </c>
-      <c r="P93" s="30" cm="1">
-        <f t="array" ref="P93">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ClimateZones_Data(), Table_SourceData_ClimateZones[[#Headers],[Climate zone]], 0)</f>
-        <v>-999999</v>
-      </c>
-      <c r="Q93" s="30" cm="1">
-        <f t="array" ref="Q93">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ClimateZones_Data(), Table_SourceData_ClimateZones[[#Headers],[Climate zone]], 0)</f>
-        <v>999.99900000000002</v>
-      </c>
-      <c r="R93" s="30" cm="1">
-        <f t="array" ref="R93">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ClimateZones_Data(), Table_SourceData_ClimateZones[[#Headers],[Climate zone]], 0)</f>
-        <v>-999999</v>
-      </c>
-      <c r="S93" s="30" cm="1">
-        <f t="array" ref="S93">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ClimateZones_Data(), Table_SourceData_ClimateZones[[#Headers],[Climate zone]], 0)</f>
-        <v>999999</v>
+        <f t="array" aca="1" ref="I93" ca="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ClimateZones_Data(), Table_SourceData_ClimateZones[[#Headers],[Climate zone]], 0)</f>
+        <v/>
+      </c>
+      <c r="J93" s="30" t="str" cm="1">
+        <f t="array" aca="1" ref="J93" ca="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ClimateZones_Data(), Table_SourceData_ClimateZones[[#Headers],[Climate zone]], 0)</f>
+        <v/>
+      </c>
+      <c r="K93" s="30" t="str" cm="1">
+        <f t="array" aca="1" ref="K93" ca="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ClimateZones_Data(), Table_SourceData_ClimateZones[[#Headers],[Climate zone]], 0)</f>
+        <v/>
+      </c>
+      <c r="L93" s="30" t="str" cm="1">
+        <f t="array" aca="1" ref="L93" ca="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ClimateZones_Data(), Table_SourceData_ClimateZones[[#Headers],[Climate zone]], 0)</f>
+        <v/>
+      </c>
+      <c r="M93" s="30" t="str" cm="1">
+        <f t="array" aca="1" ref="M93" ca="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ClimateZones_Data(), Table_SourceData_ClimateZones[[#Headers],[Climate zone]], 0)</f>
+        <v/>
+      </c>
+      <c r="N93" s="30" t="str" cm="1">
+        <f t="array" aca="1" ref="N93" ca="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ClimateZones_Data(), Table_SourceData_ClimateZones[[#Headers],[Climate zone]], 0)</f>
+        <v/>
+      </c>
+      <c r="O93" s="30" t="str" cm="1">
+        <f t="array" aca="1" ref="O93" ca="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ClimateZones_Data(), Table_SourceData_ClimateZones[[#Headers],[Climate zone]], 0)</f>
+        <v/>
+      </c>
+      <c r="P93" s="30" t="str" cm="1">
+        <f t="array" aca="1" ref="P93" ca="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ClimateZones_Data(), Table_SourceData_ClimateZones[[#Headers],[Climate zone]], 0)</f>
+        <v/>
+      </c>
+      <c r="Q93" s="30" t="str" cm="1">
+        <f t="array" aca="1" ref="Q93" ca="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ClimateZones_Data(), Table_SourceData_ClimateZones[[#Headers],[Climate zone]], 0)</f>
+        <v/>
+      </c>
+      <c r="R93" s="30" t="str" cm="1">
+        <f t="array" aca="1" ref="R93" ca="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ClimateZones_Data(), Table_SourceData_ClimateZones[[#Headers],[Climate zone]], 0)</f>
+        <v/>
+      </c>
+      <c r="S93" s="30" t="str" cm="1">
+        <f t="array" aca="1" ref="S93" ca="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ClimateZones_Data(), Table_SourceData_ClimateZones[[#Headers],[Climate zone]], 0)</f>
+        <v/>
       </c>
       <c r="T93" s="30"/>
     </row>
-    <row r="94" spans="4:20" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="94" spans="1:20" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A94"/>
       <c r="D94" s="30" t="str" cm="1">
-        <f t="array" ref="D94">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ClimateZones_Data(), Table_SourceData_ClimateZones[[#Headers],[Climate zone]], 0)</f>
-        <v>Warm temperate moist</v>
+        <f t="array" aca="1" ref="D94" ca="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ClimateZones_Data(), Table_SourceData_ClimateZones[[#Headers],[Climate zone]], 0)</f>
+        <v/>
       </c>
       <c r="E94" s="30" t="str" cm="1">
-        <f t="array" ref="E94">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ClimateZones_Data(), Table_SourceData_ClimateZones[[#Headers],[Climate zone]], 0)</f>
-        <v>&gt; 10 C</v>
+        <f t="array" aca="1" ref="E94" ca="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ClimateZones_Data(), Table_SourceData_ClimateZones[[#Headers],[Climate zone]], 0)</f>
+        <v/>
       </c>
       <c r="F94" s="30" t="str" cm="1">
-        <f t="array" ref="F94">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ClimateZones_Data(), Table_SourceData_ClimateZones[[#Headers],[Climate zone]], 0)</f>
-        <v>Any</v>
+        <f t="array" aca="1" ref="F94" ca="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ClimateZones_Data(), Table_SourceData_ClimateZones[[#Headers],[Climate zone]], 0)</f>
+        <v/>
       </c>
       <c r="G94" s="30" t="str" cm="1">
-        <f t="array" ref="G94">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ClimateZones_Data(), Table_SourceData_ClimateZones[[#Headers],[Climate zone]], 0)</f>
-        <v>Any</v>
+        <f t="array" aca="1" ref="G94" ca="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ClimateZones_Data(), Table_SourceData_ClimateZones[[#Headers],[Climate zone]], 0)</f>
+        <v/>
       </c>
       <c r="H94" s="30" t="str" cm="1">
-        <f t="array" ref="H94">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ClimateZones_Data(), Table_SourceData_ClimateZones[[#Headers],[Climate zone]], 0)</f>
-        <v>Any</v>
+        <f t="array" aca="1" ref="H94" ca="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ClimateZones_Data(), Table_SourceData_ClimateZones[[#Headers],[Climate zone]], 0)</f>
+        <v/>
       </c>
       <c r="I94" s="30" t="str" cm="1">
-        <f t="array" ref="I94">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ClimateZones_Data(), Table_SourceData_ClimateZones[[#Headers],[Climate zone]], 0)</f>
-        <v>&gt; 1</v>
-      </c>
-      <c r="J94" s="30" cm="1">
-        <f t="array" ref="J94">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ClimateZones_Data(), Table_SourceData_ClimateZones[[#Headers],[Climate zone]], 0)</f>
-        <v>10.000999999999999</v>
-      </c>
-      <c r="K94" s="30" cm="1">
-        <f t="array" ref="K94">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ClimateZones_Data(), Table_SourceData_ClimateZones[[#Headers],[Climate zone]], 0)</f>
-        <v>999999</v>
-      </c>
-      <c r="L94" s="30" cm="1">
-        <f t="array" ref="L94">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ClimateZones_Data(), Table_SourceData_ClimateZones[[#Headers],[Climate zone]], 0)</f>
-        <v>-999999</v>
-      </c>
-      <c r="M94" s="30" cm="1">
-        <f t="array" ref="M94">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ClimateZones_Data(), Table_SourceData_ClimateZones[[#Headers],[Climate zone]], 0)</f>
-        <v>999999</v>
-      </c>
-      <c r="N94" s="30" cm="1">
-        <f t="array" ref="N94">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ClimateZones_Data(), Table_SourceData_ClimateZones[[#Headers],[Climate zone]], 0)</f>
-        <v>-999999</v>
-      </c>
-      <c r="O94" s="30" cm="1">
-        <f t="array" ref="O94">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ClimateZones_Data(), Table_SourceData_ClimateZones[[#Headers],[Climate zone]], 0)</f>
-        <v>999999</v>
-      </c>
-      <c r="P94" s="30" cm="1">
-        <f t="array" ref="P94">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ClimateZones_Data(), Table_SourceData_ClimateZones[[#Headers],[Climate zone]], 0)</f>
-        <v>-999999</v>
-      </c>
-      <c r="Q94" s="30" cm="1">
-        <f t="array" ref="Q94">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ClimateZones_Data(), Table_SourceData_ClimateZones[[#Headers],[Climate zone]], 0)</f>
-        <v>999999</v>
-      </c>
-      <c r="R94" s="30" cm="1">
-        <f t="array" ref="R94">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ClimateZones_Data(), Table_SourceData_ClimateZones[[#Headers],[Climate zone]], 0)</f>
-        <v>1.0009999999999999</v>
-      </c>
-      <c r="S94" s="30" cm="1">
-        <f t="array" ref="S94">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ClimateZones_Data(), Table_SourceData_ClimateZones[[#Headers],[Climate zone]], 0)</f>
-        <v>999999</v>
+        <f t="array" aca="1" ref="I94" ca="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ClimateZones_Data(), Table_SourceData_ClimateZones[[#Headers],[Climate zone]], 0)</f>
+        <v/>
+      </c>
+      <c r="J94" s="30" t="str" cm="1">
+        <f t="array" aca="1" ref="J94" ca="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ClimateZones_Data(), Table_SourceData_ClimateZones[[#Headers],[Climate zone]], 0)</f>
+        <v/>
+      </c>
+      <c r="K94" s="30" t="str" cm="1">
+        <f t="array" aca="1" ref="K94" ca="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ClimateZones_Data(), Table_SourceData_ClimateZones[[#Headers],[Climate zone]], 0)</f>
+        <v/>
+      </c>
+      <c r="L94" s="30" t="str" cm="1">
+        <f t="array" aca="1" ref="L94" ca="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ClimateZones_Data(), Table_SourceData_ClimateZones[[#Headers],[Climate zone]], 0)</f>
+        <v/>
+      </c>
+      <c r="M94" s="30" t="str" cm="1">
+        <f t="array" aca="1" ref="M94" ca="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ClimateZones_Data(), Table_SourceData_ClimateZones[[#Headers],[Climate zone]], 0)</f>
+        <v/>
+      </c>
+      <c r="N94" s="30" t="str" cm="1">
+        <f t="array" aca="1" ref="N94" ca="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ClimateZones_Data(), Table_SourceData_ClimateZones[[#Headers],[Climate zone]], 0)</f>
+        <v/>
+      </c>
+      <c r="O94" s="30" t="str" cm="1">
+        <f t="array" aca="1" ref="O94" ca="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ClimateZones_Data(), Table_SourceData_ClimateZones[[#Headers],[Climate zone]], 0)</f>
+        <v/>
+      </c>
+      <c r="P94" s="30" t="str" cm="1">
+        <f t="array" aca="1" ref="P94" ca="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ClimateZones_Data(), Table_SourceData_ClimateZones[[#Headers],[Climate zone]], 0)</f>
+        <v/>
+      </c>
+      <c r="Q94" s="30" t="str" cm="1">
+        <f t="array" aca="1" ref="Q94" ca="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ClimateZones_Data(), Table_SourceData_ClimateZones[[#Headers],[Climate zone]], 0)</f>
+        <v/>
+      </c>
+      <c r="R94" s="30" t="str" cm="1">
+        <f t="array" aca="1" ref="R94" ca="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ClimateZones_Data(), Table_SourceData_ClimateZones[[#Headers],[Climate zone]], 0)</f>
+        <v/>
+      </c>
+      <c r="S94" s="30" t="str" cm="1">
+        <f t="array" aca="1" ref="S94" ca="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ClimateZones_Data(), Table_SourceData_ClimateZones[[#Headers],[Climate zone]], 0)</f>
+        <v/>
       </c>
       <c r="T94" s="30"/>
     </row>
-    <row r="95" spans="4:20" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="95" spans="1:20" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A95"/>
       <c r="D95" s="30" t="str" cm="1">
-        <f t="array" ref="D95">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ClimateZones_Data(), Table_SourceData_ClimateZones[[#Headers],[Climate zone]], 0)</f>
-        <v>Warm temperate dry</v>
+        <f t="array" aca="1" ref="D95" ca="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ClimateZones_Data(), Table_SourceData_ClimateZones[[#Headers],[Climate zone]], 0)</f>
+        <v/>
       </c>
       <c r="E95" s="30" t="str" cm="1">
-        <f t="array" ref="E95">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ClimateZones_Data(), Table_SourceData_ClimateZones[[#Headers],[Climate zone]], 0)</f>
-        <v>&gt; 10 C</v>
+        <f t="array" aca="1" ref="E95" ca="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ClimateZones_Data(), Table_SourceData_ClimateZones[[#Headers],[Climate zone]], 0)</f>
+        <v/>
       </c>
       <c r="F95" s="30" t="str" cm="1">
-        <f t="array" ref="F95">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ClimateZones_Data(), Table_SourceData_ClimateZones[[#Headers],[Climate zone]], 0)</f>
-        <v>Any</v>
+        <f t="array" aca="1" ref="F95" ca="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ClimateZones_Data(), Table_SourceData_ClimateZones[[#Headers],[Climate zone]], 0)</f>
+        <v/>
       </c>
       <c r="G95" s="30" t="str" cm="1">
-        <f t="array" ref="G95">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ClimateZones_Data(), Table_SourceData_ClimateZones[[#Headers],[Climate zone]], 0)</f>
-        <v>Any</v>
+        <f t="array" aca="1" ref="G95" ca="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ClimateZones_Data(), Table_SourceData_ClimateZones[[#Headers],[Climate zone]], 0)</f>
+        <v/>
       </c>
       <c r="H95" s="30" t="str" cm="1">
-        <f t="array" ref="H95">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ClimateZones_Data(), Table_SourceData_ClimateZones[[#Headers],[Climate zone]], 0)</f>
-        <v>Any</v>
+        <f t="array" aca="1" ref="H95" ca="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ClimateZones_Data(), Table_SourceData_ClimateZones[[#Headers],[Climate zone]], 0)</f>
+        <v/>
       </c>
       <c r="I95" s="30" t="str" cm="1">
-        <f t="array" ref="I95">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ClimateZones_Data(), Table_SourceData_ClimateZones[[#Headers],[Climate zone]], 0)</f>
-        <v>≤ 1</v>
-      </c>
-      <c r="J95" s="30" cm="1">
-        <f t="array" ref="J95">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ClimateZones_Data(), Table_SourceData_ClimateZones[[#Headers],[Climate zone]], 0)</f>
-        <v>10.000999999999999</v>
-      </c>
-      <c r="K95" s="30" cm="1">
-        <f t="array" ref="K95">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ClimateZones_Data(), Table_SourceData_ClimateZones[[#Headers],[Climate zone]], 0)</f>
-        <v>999999</v>
-      </c>
-      <c r="L95" s="30" cm="1">
-        <f t="array" ref="L95">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ClimateZones_Data(), Table_SourceData_ClimateZones[[#Headers],[Climate zone]], 0)</f>
-        <v>-999999</v>
-      </c>
-      <c r="M95" s="30" cm="1">
-        <f t="array" ref="M95">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ClimateZones_Data(), Table_SourceData_ClimateZones[[#Headers],[Climate zone]], 0)</f>
-        <v>999999</v>
-      </c>
-      <c r="N95" s="30" cm="1">
-        <f t="array" ref="N95">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ClimateZones_Data(), Table_SourceData_ClimateZones[[#Headers],[Climate zone]], 0)</f>
-        <v>-999999</v>
-      </c>
-      <c r="O95" s="30" cm="1">
-        <f t="array" ref="O95">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ClimateZones_Data(), Table_SourceData_ClimateZones[[#Headers],[Climate zone]], 0)</f>
-        <v>999999</v>
-      </c>
-      <c r="P95" s="30" cm="1">
-        <f t="array" ref="P95">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ClimateZones_Data(), Table_SourceData_ClimateZones[[#Headers],[Climate zone]], 0)</f>
-        <v>-999999</v>
-      </c>
-      <c r="Q95" s="30" cm="1">
-        <f t="array" ref="Q95">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ClimateZones_Data(), Table_SourceData_ClimateZones[[#Headers],[Climate zone]], 0)</f>
-        <v>999999</v>
-      </c>
-      <c r="R95" s="30" cm="1">
-        <f t="array" ref="R95">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ClimateZones_Data(), Table_SourceData_ClimateZones[[#Headers],[Climate zone]], 0)</f>
-        <v>-999999</v>
-      </c>
-      <c r="S95" s="30" cm="1">
-        <f t="array" ref="S95">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ClimateZones_Data(), Table_SourceData_ClimateZones[[#Headers],[Climate zone]], 0)</f>
-        <v>1</v>
+        <f t="array" aca="1" ref="I95" ca="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ClimateZones_Data(), Table_SourceData_ClimateZones[[#Headers],[Climate zone]], 0)</f>
+        <v/>
+      </c>
+      <c r="J95" s="30" t="str" cm="1">
+        <f t="array" aca="1" ref="J95" ca="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ClimateZones_Data(), Table_SourceData_ClimateZones[[#Headers],[Climate zone]], 0)</f>
+        <v/>
+      </c>
+      <c r="K95" s="30" t="str" cm="1">
+        <f t="array" aca="1" ref="K95" ca="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ClimateZones_Data(), Table_SourceData_ClimateZones[[#Headers],[Climate zone]], 0)</f>
+        <v/>
+      </c>
+      <c r="L95" s="30" t="str" cm="1">
+        <f t="array" aca="1" ref="L95" ca="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ClimateZones_Data(), Table_SourceData_ClimateZones[[#Headers],[Climate zone]], 0)</f>
+        <v/>
+      </c>
+      <c r="M95" s="30" t="str" cm="1">
+        <f t="array" aca="1" ref="M95" ca="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ClimateZones_Data(), Table_SourceData_ClimateZones[[#Headers],[Climate zone]], 0)</f>
+        <v/>
+      </c>
+      <c r="N95" s="30" t="str" cm="1">
+        <f t="array" aca="1" ref="N95" ca="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ClimateZones_Data(), Table_SourceData_ClimateZones[[#Headers],[Climate zone]], 0)</f>
+        <v/>
+      </c>
+      <c r="O95" s="30" t="str" cm="1">
+        <f t="array" aca="1" ref="O95" ca="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ClimateZones_Data(), Table_SourceData_ClimateZones[[#Headers],[Climate zone]], 0)</f>
+        <v/>
+      </c>
+      <c r="P95" s="30" t="str" cm="1">
+        <f t="array" aca="1" ref="P95" ca="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ClimateZones_Data(), Table_SourceData_ClimateZones[[#Headers],[Climate zone]], 0)</f>
+        <v/>
+      </c>
+      <c r="Q95" s="30" t="str" cm="1">
+        <f t="array" aca="1" ref="Q95" ca="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ClimateZones_Data(), Table_SourceData_ClimateZones[[#Headers],[Climate zone]], 0)</f>
+        <v/>
+      </c>
+      <c r="R95" s="30" t="str" cm="1">
+        <f t="array" aca="1" ref="R95" ca="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ClimateZones_Data(), Table_SourceData_ClimateZones[[#Headers],[Climate zone]], 0)</f>
+        <v/>
+      </c>
+      <c r="S95" s="30" t="str" cm="1">
+        <f t="array" aca="1" ref="S95" ca="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ClimateZones_Data(), Table_SourceData_ClimateZones[[#Headers],[Climate zone]], 0)</f>
+        <v/>
       </c>
       <c r="T95" s="30"/>
     </row>
-    <row r="96" spans="4:20" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="96" spans="1:20" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A96"/>
       <c r="D96" s="30" t="str" cm="1">
-        <f t="array" ref="D96">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ClimateZones_Data(), Table_SourceData_ClimateZones[[#Headers],[Climate zone]], 0)</f>
-        <v>Cool temperate moist</v>
+        <f t="array" aca="1" ref="D96" ca="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ClimateZones_Data(), Table_SourceData_ClimateZones[[#Headers],[Climate zone]], 0)</f>
+        <v/>
       </c>
       <c r="E96" s="30" t="str" cm="1">
-        <f t="array" ref="E96">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ClimateZones_Data(), Table_SourceData_ClimateZones[[#Headers],[Climate zone]], 0)</f>
-        <v>&gt; 0 C - ≤ 10 C</v>
+        <f t="array" aca="1" ref="E96" ca="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ClimateZones_Data(), Table_SourceData_ClimateZones[[#Headers],[Climate zone]], 0)</f>
+        <v/>
       </c>
       <c r="F96" s="30" t="str" cm="1">
-        <f t="array" ref="F96">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ClimateZones_Data(), Table_SourceData_ClimateZones[[#Headers],[Climate zone]], 0)</f>
-        <v>Any</v>
+        <f t="array" aca="1" ref="F96" ca="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ClimateZones_Data(), Table_SourceData_ClimateZones[[#Headers],[Climate zone]], 0)</f>
+        <v/>
       </c>
       <c r="G96" s="30" t="str" cm="1">
-        <f t="array" ref="G96">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ClimateZones_Data(), Table_SourceData_ClimateZones[[#Headers],[Climate zone]], 0)</f>
-        <v>Any</v>
+        <f t="array" aca="1" ref="G96" ca="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ClimateZones_Data(), Table_SourceData_ClimateZones[[#Headers],[Climate zone]], 0)</f>
+        <v/>
       </c>
       <c r="H96" s="30" t="str" cm="1">
-        <f t="array" ref="H96">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ClimateZones_Data(), Table_SourceData_ClimateZones[[#Headers],[Climate zone]], 0)</f>
-        <v>Any</v>
+        <f t="array" aca="1" ref="H96" ca="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ClimateZones_Data(), Table_SourceData_ClimateZones[[#Headers],[Climate zone]], 0)</f>
+        <v/>
       </c>
       <c r="I96" s="30" t="str" cm="1">
-        <f t="array" ref="I96">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ClimateZones_Data(), Table_SourceData_ClimateZones[[#Headers],[Climate zone]], 0)</f>
-        <v>&gt; 1</v>
-      </c>
-      <c r="J96" s="30" cm="1">
-        <f t="array" ref="J96">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ClimateZones_Data(), Table_SourceData_ClimateZones[[#Headers],[Climate zone]], 0)</f>
-        <v>-999999</v>
-      </c>
-      <c r="K96" s="30" cm="1">
-        <f t="array" ref="K96">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ClimateZones_Data(), Table_SourceData_ClimateZones[[#Headers],[Climate zone]], 0)</f>
-        <v>10</v>
-      </c>
-      <c r="L96" s="30" cm="1">
-        <f t="array" ref="L96">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ClimateZones_Data(), Table_SourceData_ClimateZones[[#Headers],[Climate zone]], 0)</f>
-        <v>-999999</v>
-      </c>
-      <c r="M96" s="30" cm="1">
-        <f t="array" ref="M96">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ClimateZones_Data(), Table_SourceData_ClimateZones[[#Headers],[Climate zone]], 0)</f>
-        <v>999999</v>
-      </c>
-      <c r="N96" s="30" cm="1">
-        <f t="array" ref="N96">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ClimateZones_Data(), Table_SourceData_ClimateZones[[#Headers],[Climate zone]], 0)</f>
-        <v>-999999</v>
-      </c>
-      <c r="O96" s="30" cm="1">
-        <f t="array" ref="O96">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ClimateZones_Data(), Table_SourceData_ClimateZones[[#Headers],[Climate zone]], 0)</f>
-        <v>999999</v>
-      </c>
-      <c r="P96" s="30" cm="1">
-        <f t="array" ref="P96">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ClimateZones_Data(), Table_SourceData_ClimateZones[[#Headers],[Climate zone]], 0)</f>
-        <v>-999999</v>
-      </c>
-      <c r="Q96" s="30" cm="1">
-        <f t="array" ref="Q96">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ClimateZones_Data(), Table_SourceData_ClimateZones[[#Headers],[Climate zone]], 0)</f>
-        <v>999999</v>
-      </c>
-      <c r="R96" s="30" cm="1">
-        <f t="array" ref="R96">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ClimateZones_Data(), Table_SourceData_ClimateZones[[#Headers],[Climate zone]], 0)</f>
-        <v>1.0009999999999999</v>
-      </c>
-      <c r="S96" s="30" cm="1">
-        <f t="array" ref="S96">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ClimateZones_Data(), Table_SourceData_ClimateZones[[#Headers],[Climate zone]], 0)</f>
-        <v>999999</v>
+        <f t="array" aca="1" ref="I96" ca="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ClimateZones_Data(), Table_SourceData_ClimateZones[[#Headers],[Climate zone]], 0)</f>
+        <v/>
+      </c>
+      <c r="J96" s="30" t="str" cm="1">
+        <f t="array" aca="1" ref="J96" ca="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ClimateZones_Data(), Table_SourceData_ClimateZones[[#Headers],[Climate zone]], 0)</f>
+        <v/>
+      </c>
+      <c r="K96" s="30" t="str" cm="1">
+        <f t="array" aca="1" ref="K96" ca="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ClimateZones_Data(), Table_SourceData_ClimateZones[[#Headers],[Climate zone]], 0)</f>
+        <v/>
+      </c>
+      <c r="L96" s="30" t="str" cm="1">
+        <f t="array" aca="1" ref="L96" ca="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ClimateZones_Data(), Table_SourceData_ClimateZones[[#Headers],[Climate zone]], 0)</f>
+        <v/>
+      </c>
+      <c r="M96" s="30" t="str" cm="1">
+        <f t="array" aca="1" ref="M96" ca="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ClimateZones_Data(), Table_SourceData_ClimateZones[[#Headers],[Climate zone]], 0)</f>
+        <v/>
+      </c>
+      <c r="N96" s="30" t="str" cm="1">
+        <f t="array" aca="1" ref="N96" ca="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ClimateZones_Data(), Table_SourceData_ClimateZones[[#Headers],[Climate zone]], 0)</f>
+        <v/>
+      </c>
+      <c r="O96" s="30" t="str" cm="1">
+        <f t="array" aca="1" ref="O96" ca="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ClimateZones_Data(), Table_SourceData_ClimateZones[[#Headers],[Climate zone]], 0)</f>
+        <v/>
+      </c>
+      <c r="P96" s="30" t="str" cm="1">
+        <f t="array" aca="1" ref="P96" ca="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ClimateZones_Data(), Table_SourceData_ClimateZones[[#Headers],[Climate zone]], 0)</f>
+        <v/>
+      </c>
+      <c r="Q96" s="30" t="str" cm="1">
+        <f t="array" aca="1" ref="Q96" ca="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ClimateZones_Data(), Table_SourceData_ClimateZones[[#Headers],[Climate zone]], 0)</f>
+        <v/>
+      </c>
+      <c r="R96" s="30" t="str" cm="1">
+        <f t="array" aca="1" ref="R96" ca="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ClimateZones_Data(), Table_SourceData_ClimateZones[[#Headers],[Climate zone]], 0)</f>
+        <v/>
+      </c>
+      <c r="S96" s="30" t="str" cm="1">
+        <f t="array" aca="1" ref="S96" ca="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ClimateZones_Data(), Table_SourceData_ClimateZones[[#Headers],[Climate zone]], 0)</f>
+        <v/>
       </c>
       <c r="T96" s="30"/>
     </row>
-    <row r="97" spans="4:20" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="97" spans="1:20" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A97"/>
       <c r="D97" s="30" t="str" cm="1">
-        <f t="array" ref="D97">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ClimateZones_Data(), Table_SourceData_ClimateZones[[#Headers],[Climate zone]], 0)</f>
-        <v>Cool temperate dry</v>
+        <f t="array" aca="1" ref="D97" ca="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ClimateZones_Data(), Table_SourceData_ClimateZones[[#Headers],[Climate zone]], 0)</f>
+        <v/>
       </c>
       <c r="E97" s="30" t="str" cm="1">
-        <f t="array" ref="E97">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ClimateZones_Data(), Table_SourceData_ClimateZones[[#Headers],[Climate zone]], 0)</f>
-        <v>&gt; 0 C - ≤ 10 C</v>
+        <f t="array" aca="1" ref="E97" ca="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ClimateZones_Data(), Table_SourceData_ClimateZones[[#Headers],[Climate zone]], 0)</f>
+        <v/>
       </c>
       <c r="F97" s="30" t="str" cm="1">
-        <f t="array" ref="F97">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ClimateZones_Data(), Table_SourceData_ClimateZones[[#Headers],[Climate zone]], 0)</f>
-        <v>Any</v>
+        <f t="array" aca="1" ref="F97" ca="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ClimateZones_Data(), Table_SourceData_ClimateZones[[#Headers],[Climate zone]], 0)</f>
+        <v/>
       </c>
       <c r="G97" s="30" t="str" cm="1">
-        <f t="array" ref="G97">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ClimateZones_Data(), Table_SourceData_ClimateZones[[#Headers],[Climate zone]], 0)</f>
-        <v>Any</v>
+        <f t="array" aca="1" ref="G97" ca="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ClimateZones_Data(), Table_SourceData_ClimateZones[[#Headers],[Climate zone]], 0)</f>
+        <v/>
       </c>
       <c r="H97" s="30" t="str" cm="1">
-        <f t="array" ref="H97">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ClimateZones_Data(), Table_SourceData_ClimateZones[[#Headers],[Climate zone]], 0)</f>
-        <v>Any</v>
+        <f t="array" aca="1" ref="H97" ca="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ClimateZones_Data(), Table_SourceData_ClimateZones[[#Headers],[Climate zone]], 0)</f>
+        <v/>
       </c>
       <c r="I97" s="30" t="str" cm="1">
-        <f t="array" ref="I97">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ClimateZones_Data(), Table_SourceData_ClimateZones[[#Headers],[Climate zone]], 0)</f>
-        <v>≤ 1</v>
-      </c>
-      <c r="J97" s="30" cm="1">
-        <f t="array" ref="J97">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ClimateZones_Data(), Table_SourceData_ClimateZones[[#Headers],[Climate zone]], 0)</f>
-        <v>-999999</v>
-      </c>
-      <c r="K97" s="30" cm="1">
-        <f t="array" ref="K97">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ClimateZones_Data(), Table_SourceData_ClimateZones[[#Headers],[Climate zone]], 0)</f>
-        <v>10</v>
-      </c>
-      <c r="L97" s="30" cm="1">
-        <f t="array" ref="L97">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ClimateZones_Data(), Table_SourceData_ClimateZones[[#Headers],[Climate zone]], 0)</f>
-        <v>-999999</v>
-      </c>
-      <c r="M97" s="30" cm="1">
-        <f t="array" ref="M97">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ClimateZones_Data(), Table_SourceData_ClimateZones[[#Headers],[Climate zone]], 0)</f>
-        <v>999999</v>
-      </c>
-      <c r="N97" s="30" cm="1">
-        <f t="array" ref="N97">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ClimateZones_Data(), Table_SourceData_ClimateZones[[#Headers],[Climate zone]], 0)</f>
-        <v>-999999</v>
-      </c>
-      <c r="O97" s="30" cm="1">
-        <f t="array" ref="O97">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ClimateZones_Data(), Table_SourceData_ClimateZones[[#Headers],[Climate zone]], 0)</f>
-        <v>999999</v>
-      </c>
-      <c r="P97" s="30" cm="1">
-        <f t="array" ref="P97">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ClimateZones_Data(), Table_SourceData_ClimateZones[[#Headers],[Climate zone]], 0)</f>
-        <v>-999999</v>
-      </c>
-      <c r="Q97" s="30" cm="1">
-        <f t="array" ref="Q97">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ClimateZones_Data(), Table_SourceData_ClimateZones[[#Headers],[Climate zone]], 0)</f>
-        <v>999999</v>
-      </c>
-      <c r="R97" s="30" cm="1">
-        <f t="array" ref="R97">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ClimateZones_Data(), Table_SourceData_ClimateZones[[#Headers],[Climate zone]], 0)</f>
-        <v>-999999</v>
-      </c>
-      <c r="S97" s="30" cm="1">
-        <f t="array" ref="S97">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ClimateZones_Data(), Table_SourceData_ClimateZones[[#Headers],[Climate zone]], 0)</f>
-        <v>1</v>
+        <f t="array" aca="1" ref="I97" ca="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ClimateZones_Data(), Table_SourceData_ClimateZones[[#Headers],[Climate zone]], 0)</f>
+        <v/>
+      </c>
+      <c r="J97" s="30" t="str" cm="1">
+        <f t="array" aca="1" ref="J97" ca="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ClimateZones_Data(), Table_SourceData_ClimateZones[[#Headers],[Climate zone]], 0)</f>
+        <v/>
+      </c>
+      <c r="K97" s="30" t="str" cm="1">
+        <f t="array" aca="1" ref="K97" ca="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ClimateZones_Data(), Table_SourceData_ClimateZones[[#Headers],[Climate zone]], 0)</f>
+        <v/>
+      </c>
+      <c r="L97" s="30" t="str" cm="1">
+        <f t="array" aca="1" ref="L97" ca="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ClimateZones_Data(), Table_SourceData_ClimateZones[[#Headers],[Climate zone]], 0)</f>
+        <v/>
+      </c>
+      <c r="M97" s="30" t="str" cm="1">
+        <f t="array" aca="1" ref="M97" ca="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ClimateZones_Data(), Table_SourceData_ClimateZones[[#Headers],[Climate zone]], 0)</f>
+        <v/>
+      </c>
+      <c r="N97" s="30" t="str" cm="1">
+        <f t="array" aca="1" ref="N97" ca="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ClimateZones_Data(), Table_SourceData_ClimateZones[[#Headers],[Climate zone]], 0)</f>
+        <v/>
+      </c>
+      <c r="O97" s="30" t="str" cm="1">
+        <f t="array" aca="1" ref="O97" ca="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ClimateZones_Data(), Table_SourceData_ClimateZones[[#Headers],[Climate zone]], 0)</f>
+        <v/>
+      </c>
+      <c r="P97" s="30" t="str" cm="1">
+        <f t="array" aca="1" ref="P97" ca="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ClimateZones_Data(), Table_SourceData_ClimateZones[[#Headers],[Climate zone]], 0)</f>
+        <v/>
+      </c>
+      <c r="Q97" s="30" t="str" cm="1">
+        <f t="array" aca="1" ref="Q97" ca="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ClimateZones_Data(), Table_SourceData_ClimateZones[[#Headers],[Climate zone]], 0)</f>
+        <v/>
+      </c>
+      <c r="R97" s="30" t="str" cm="1">
+        <f t="array" aca="1" ref="R97" ca="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ClimateZones_Data(), Table_SourceData_ClimateZones[[#Headers],[Climate zone]], 0)</f>
+        <v/>
+      </c>
+      <c r="S97" s="30" t="str" cm="1">
+        <f t="array" aca="1" ref="S97" ca="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ClimateZones_Data(), Table_SourceData_ClimateZones[[#Headers],[Climate zone]], 0)</f>
+        <v/>
       </c>
       <c r="T97" s="30"/>
     </row>
-    <row r="98" spans="4:20" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="99" spans="4:20" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="98" spans="1:20" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A98"/>
+    </row>
+    <row r="99" spans="1:20" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A99"/>
       <c r="D99" s="16" t="str" cm="1">
         <f t="array" ref="D99:D102">Common_SourceData.Common_SourceData_ClimateZones_Appendices()</f>
         <v>Note:</v>
       </c>
     </row>
-    <row r="100" spans="4:20" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="100" spans="1:20" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A100"/>
       <c r="D100" s="16" t="str">
         <v>MAT = mean annual temperature</v>
       </c>
     </row>
-    <row r="101" spans="4:20" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="101" spans="1:20" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A101"/>
       <c r="D101" s="16" t="str">
         <v>MAP = mean annual precipitation</v>
       </c>
     </row>
-    <row r="102" spans="4:20" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="102" spans="1:20" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A102"/>
       <c r="D102" s="16" t="str">
         <v>PET = potential evapotranspiration</v>
       </c>
     </row>
-    <row r="103" spans="4:20" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="103" spans="1:20" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A103"/>
       <c r="D103" s="16"/>
     </row>
-    <row r="104" spans="4:20" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="105" spans="4:20" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="104" spans="1:20" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A104"/>
+    </row>
+    <row r="105" spans="1:20" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A105"/>
       <c r="D105" s="2" t="str" cm="1">
         <f t="array" ref="D105">Common_SourceData.Common_SourceData_TemperatureZones_Title()</f>
         <v>VEERG Australian temperature zones</v>
       </c>
     </row>
-    <row r="106" spans="4:20" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="106" spans="1:20" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A106"/>
       <c r="D106" s="28" t="str" cm="1">
         <f t="array" ref="D106">Common_SourceData.Common_SourceData_TemperatureZones_Source()</f>
         <v>VEERG 2026: Table 1.3: Climate and Rainfall zone classifications and definitions</v>
       </c>
     </row>
-    <row r="107" spans="4:20" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="107" spans="1:20" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A107"/>
       <c r="D107" s="36" t="str" cm="1">
         <f t="array" ref="D107">"⚠️" &amp; Common_SourceData.Common_SourceData_TemperatureZones_Variation()</f>
         <v>⚠️VARIATION OF SOURCE DATA: Added extra MAT min and MAT max columns to calculate zone from real temperature data.</v>
       </c>
     </row>
-    <row r="108" spans="4:20" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="109" spans="4:20" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="108" spans="1:20" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A108"/>
+    </row>
+    <row r="109" spans="1:20" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A109"/>
       <c r="D109" s="30" t="s">
         <v>50</v>
       </c>
@@ -9124,87 +9362,99 @@
         <v>52</v>
       </c>
     </row>
-    <row r="110" spans="4:20" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="110" spans="1:20" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A110"/>
       <c r="D110" s="30" t="str" cm="1">
-        <f t="array" ref="D110">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_TemperatureZones_Data(),Table_SourceData_TemperatureZones[[#Headers],[Temperature Zone]],0)</f>
-        <v>Warm</v>
+        <f t="array" aca="1" ref="D110" ca="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_TemperatureZones_Data(),Table_SourceData_TemperatureZones[[#Headers],[Temperature Zone]],0)</f>
+        <v/>
       </c>
       <c r="E110" s="30" t="str" cm="1">
-        <f t="array" ref="E110">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_TemperatureZones_Data(),Table_SourceData_TemperatureZones[[#Headers],[Temperature Zone]],0)</f>
-        <v>≥ 26 C</v>
-      </c>
-      <c r="F110" s="30" cm="1">
-        <f t="array" ref="F110">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_TemperatureZones_Data(),Table_SourceData_TemperatureZones[[#Headers],[Temperature Zone]],0)</f>
-        <v>26</v>
-      </c>
-      <c r="G110" s="30" cm="1">
-        <f t="array" ref="G110">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_TemperatureZones_Data(),Table_SourceData_TemperatureZones[[#Headers],[Temperature Zone]],0)</f>
-        <v>999999</v>
-      </c>
-    </row>
-    <row r="111" spans="4:20" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+        <f t="array" aca="1" ref="E110" ca="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_TemperatureZones_Data(),Table_SourceData_TemperatureZones[[#Headers],[Temperature Zone]],0)</f>
+        <v/>
+      </c>
+      <c r="F110" s="30" t="str" cm="1">
+        <f t="array" aca="1" ref="F110" ca="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_TemperatureZones_Data(),Table_SourceData_TemperatureZones[[#Headers],[Temperature Zone]],0)</f>
+        <v/>
+      </c>
+      <c r="G110" s="30" t="str" cm="1">
+        <f t="array" aca="1" ref="G110" ca="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_TemperatureZones_Data(),Table_SourceData_TemperatureZones[[#Headers],[Temperature Zone]],0)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="111" spans="1:20" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A111"/>
       <c r="D111" s="30" t="str" cm="1">
-        <f t="array" ref="D111">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_TemperatureZones_Data(),Table_SourceData_TemperatureZones[[#Headers],[Temperature Zone]],0)</f>
-        <v>Temperate</v>
+        <f t="array" aca="1" ref="D111" ca="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_TemperatureZones_Data(),Table_SourceData_TemperatureZones[[#Headers],[Temperature Zone]],0)</f>
+        <v/>
       </c>
       <c r="E111" s="30" t="str" cm="1">
-        <f t="array" ref="E111">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_TemperatureZones_Data(),Table_SourceData_TemperatureZones[[#Headers],[Temperature Zone]],0)</f>
-        <v>15 - 25 C</v>
-      </c>
-      <c r="F111" s="30" cm="1">
-        <f t="array" ref="F111">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_TemperatureZones_Data(),Table_SourceData_TemperatureZones[[#Headers],[Temperature Zone]],0)</f>
-        <v>15</v>
-      </c>
-      <c r="G111" s="30" cm="1">
-        <f t="array" ref="G111">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_TemperatureZones_Data(),Table_SourceData_TemperatureZones[[#Headers],[Temperature Zone]],0)</f>
-        <v>25.998999999999999</v>
-      </c>
-    </row>
-    <row r="112" spans="4:20" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+        <f t="array" aca="1" ref="E111" ca="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_TemperatureZones_Data(),Table_SourceData_TemperatureZones[[#Headers],[Temperature Zone]],0)</f>
+        <v/>
+      </c>
+      <c r="F111" s="30" t="str" cm="1">
+        <f t="array" aca="1" ref="F111" ca="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_TemperatureZones_Data(),Table_SourceData_TemperatureZones[[#Headers],[Temperature Zone]],0)</f>
+        <v/>
+      </c>
+      <c r="G111" s="30" t="str" cm="1">
+        <f t="array" aca="1" ref="G111" ca="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_TemperatureZones_Data(),Table_SourceData_TemperatureZones[[#Headers],[Temperature Zone]],0)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="112" spans="1:20" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A112"/>
       <c r="D112" s="30" t="str" cm="1">
-        <f t="array" ref="D112">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_TemperatureZones_Data(),Table_SourceData_TemperatureZones[[#Headers],[Temperature Zone]],0)</f>
-        <v>Cool</v>
+        <f t="array" aca="1" ref="D112" ca="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_TemperatureZones_Data(),Table_SourceData_TemperatureZones[[#Headers],[Temperature Zone]],0)</f>
+        <v/>
       </c>
       <c r="E112" s="30" t="str" cm="1">
-        <f t="array" ref="E112">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_TemperatureZones_Data(),Table_SourceData_TemperatureZones[[#Headers],[Temperature Zone]],0)</f>
-        <v>≤ 14 C</v>
-      </c>
-      <c r="F112" s="30" cm="1">
-        <f t="array" ref="F112">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_TemperatureZones_Data(),Table_SourceData_TemperatureZones[[#Headers],[Temperature Zone]],0)</f>
-        <v>-999999</v>
-      </c>
-      <c r="G112" s="30" cm="1">
-        <f t="array" ref="G112">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_TemperatureZones_Data(),Table_SourceData_TemperatureZones[[#Headers],[Temperature Zone]],0)</f>
-        <v>14.999000000000001</v>
-      </c>
-    </row>
-    <row r="113" spans="4:66" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="114" spans="4:66" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="115" spans="4:66" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+        <f t="array" aca="1" ref="E112" ca="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_TemperatureZones_Data(),Table_SourceData_TemperatureZones[[#Headers],[Temperature Zone]],0)</f>
+        <v/>
+      </c>
+      <c r="F112" s="30" t="str" cm="1">
+        <f t="array" aca="1" ref="F112" ca="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_TemperatureZones_Data(),Table_SourceData_TemperatureZones[[#Headers],[Temperature Zone]],0)</f>
+        <v/>
+      </c>
+      <c r="G112" s="30" t="str" cm="1">
+        <f t="array" aca="1" ref="G112" ca="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_TemperatureZones_Data(),Table_SourceData_TemperatureZones[[#Headers],[Temperature Zone]],0)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="113" spans="1:66" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A113"/>
+    </row>
+    <row r="114" spans="1:66" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A114"/>
+    </row>
+    <row r="115" spans="1:66" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A115"/>
       <c r="D115" s="2" t="str" cm="1">
         <f t="array" ref="D115">Common_SourceData.Common_SourceData_RainfallZones_Title()</f>
         <v>VEERG Australian rainfall zones</v>
       </c>
       <c r="BN115" s="32"/>
     </row>
-    <row r="116" spans="4:66" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="116" spans="1:66" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A116"/>
       <c r="D116" s="28" t="str" cm="1">
         <f t="array" ref="D116">Common_SourceData.Common_SourceData_RainfallZones_Source()</f>
         <v>VEERG 2026: Table 1.3: Climate and Rainfall zone classifications and definitions</v>
       </c>
       <c r="BN116" s="32"/>
     </row>
-    <row r="117" spans="4:66" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="117" spans="1:66" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A117"/>
       <c r="D117" s="36" t="str" cm="1">
         <f t="array" ref="D117">"⚠️" &amp; Common_SourceData.Common_SourceData_RainfallZones_Variation()</f>
         <v>⚠️VARIATION OF SOURCE DATA: Added extra Rainfall min and Rainfall max columns to calculate zone from real rainfall data.</v>
       </c>
       <c r="BN117" s="32"/>
     </row>
-    <row r="118" spans="4:66" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="118" spans="1:66" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A118"/>
       <c r="BN118" s="32"/>
     </row>
-    <row r="119" spans="4:66" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="119" spans="1:66" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A119"/>
       <c r="D119" s="30" t="s">
         <v>53</v>
       </c>
@@ -9219,62 +9469,72 @@
       </c>
       <c r="BN119" s="32"/>
     </row>
-    <row r="120" spans="4:66" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="120" spans="1:66" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A120"/>
       <c r="D120" s="30" t="str" cm="1">
-        <f t="array" ref="D120">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_RainfallZones_Data(),Table_SourceData_RainfallZones[[#Headers],[Rainfall Zone]],0)</f>
-        <v>High rainfall</v>
+        <f t="array" aca="1" ref="D120" ca="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_RainfallZones_Data(),Table_SourceData_RainfallZones[[#Headers],[Rainfall Zone]],0)</f>
+        <v/>
       </c>
       <c r="E120" s="30" t="str" cm="1">
-        <f t="array" ref="E120">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_RainfallZones_Data(),Table_SourceData_RainfallZones[[#Headers],[Rainfall Zone]],0)</f>
-        <v>Annual rainfall &gt; 600mm</v>
-      </c>
-      <c r="F120" s="30" cm="1">
-        <f t="array" ref="F120">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_RainfallZones_Data(),Table_SourceData_RainfallZones[[#Headers],[Rainfall Zone]],0)</f>
-        <v>600.00099999999998</v>
-      </c>
-      <c r="G120" s="30" cm="1">
-        <f t="array" ref="G120">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_RainfallZones_Data(),Table_SourceData_RainfallZones[[#Headers],[Rainfall Zone]],0)</f>
-        <v>999999</v>
+        <f t="array" aca="1" ref="E120" ca="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_RainfallZones_Data(),Table_SourceData_RainfallZones[[#Headers],[Rainfall Zone]],0)</f>
+        <v/>
+      </c>
+      <c r="F120" s="30" t="str" cm="1">
+        <f t="array" aca="1" ref="F120" ca="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_RainfallZones_Data(),Table_SourceData_RainfallZones[[#Headers],[Rainfall Zone]],0)</f>
+        <v/>
+      </c>
+      <c r="G120" s="30" t="str" cm="1">
+        <f t="array" aca="1" ref="G120" ca="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_RainfallZones_Data(),Table_SourceData_RainfallZones[[#Headers],[Rainfall Zone]],0)</f>
+        <v/>
       </c>
       <c r="BN120" s="32"/>
     </row>
-    <row r="121" spans="4:66" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="121" spans="1:66" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A121"/>
       <c r="D121" s="30" t="str" cm="1">
-        <f t="array" ref="D121">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_RainfallZones_Data(),Table_SourceData_RainfallZones[[#Headers],[Rainfall Zone]],0)</f>
-        <v>Low rainfall</v>
+        <f t="array" aca="1" ref="D121" ca="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_RainfallZones_Data(),Table_SourceData_RainfallZones[[#Headers],[Rainfall Zone]],0)</f>
+        <v/>
       </c>
       <c r="E121" s="30" t="str" cm="1">
-        <f t="array" ref="E121">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_RainfallZones_Data(),Table_SourceData_RainfallZones[[#Headers],[Rainfall Zone]],0)</f>
-        <v>Annual rainfall ≤ 600mm</v>
-      </c>
-      <c r="F121" s="30" cm="1">
-        <f t="array" ref="F121">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_RainfallZones_Data(),Table_SourceData_RainfallZones[[#Headers],[Rainfall Zone]],0)</f>
-        <v>-999999</v>
-      </c>
-      <c r="G121" s="30" cm="1">
-        <f t="array" ref="G121">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_RainfallZones_Data(),Table_SourceData_RainfallZones[[#Headers],[Rainfall Zone]],0)</f>
-        <v>600</v>
+        <f t="array" aca="1" ref="E121" ca="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_RainfallZones_Data(),Table_SourceData_RainfallZones[[#Headers],[Rainfall Zone]],0)</f>
+        <v/>
+      </c>
+      <c r="F121" s="30" t="str" cm="1">
+        <f t="array" aca="1" ref="F121" ca="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_RainfallZones_Data(),Table_SourceData_RainfallZones[[#Headers],[Rainfall Zone]],0)</f>
+        <v/>
+      </c>
+      <c r="G121" s="30" t="str" cm="1">
+        <f t="array" aca="1" ref="G121" ca="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_RainfallZones_Data(),Table_SourceData_RainfallZones[[#Headers],[Rainfall Zone]],0)</f>
+        <v/>
       </c>
       <c r="BN121" s="32"/>
     </row>
-    <row r="122" spans="4:66" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="122" spans="1:66" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A122"/>
       <c r="BN122" s="32"/>
     </row>
-    <row r="123" spans="4:66" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="124" spans="4:66" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="123" spans="1:66" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A123"/>
+    </row>
+    <row r="124" spans="1:66" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A124"/>
       <c r="D124" s="2" t="str" cm="1">
         <f t="array" ref="D124">Common_SourceData.Common_SourceData_LeachingZones_Title()</f>
         <v>VEERG Australian leaching zones</v>
       </c>
     </row>
-    <row r="125" spans="4:66" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="125" spans="1:66" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A125"/>
       <c r="D125" s="28" t="str" cm="1">
         <f t="array" ref="D125">Common_SourceData.Common_SourceData_LeachingZones_Source()</f>
         <v>VEERG 2026: Table 1.3: Climate and Rainfall zone classifications and definitions</v>
       </c>
     </row>
-    <row r="126" spans="4:66" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="127" spans="4:66" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="126" spans="1:66" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A126"/>
+    </row>
+    <row r="127" spans="1:66" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A127"/>
       <c r="D127" s="30" t="s">
         <v>55</v>
       </c>
@@ -9282,43 +9542,52 @@
         <v>56</v>
       </c>
     </row>
-    <row r="128" spans="4:66" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="128" spans="1:66" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A128"/>
       <c r="D128" s="30" t="str" cm="1">
-        <f t="array" ref="D128">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_LeachingZones_Data(), Table_SourceData_LeachingZones[[#Headers],[Leaching Zone]], 0)</f>
-        <v>Leaching occurs</v>
+        <f t="array" aca="1" ref="D128" ca="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_LeachingZones_Data(), Table_SourceData_LeachingZones[[#Headers],[Leaching Zone]], 0)</f>
+        <v/>
       </c>
       <c r="E128" s="30" t="str" cm="1">
-        <f t="array" ref="E128">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_LeachingZones_Data(), Table_SourceData_LeachingZones[[#Headers],[Leaching Zone]], 0)</f>
-        <v>Σ(𝑟𝑎𝑖𝑛)&gt;Σ(𝐸𝑇0)+𝑠𝑜𝑖𝑙 𝑤𝑎𝑡𝑒𝑟 ℎ𝑜𝑙𝑑𝑖𝑛𝑔 𝑐𝑎𝑝𝑎𝑐𝑖𝑡𝑦</v>
-      </c>
-    </row>
-    <row r="129" spans="4:77" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+        <f t="array" aca="1" ref="E128" ca="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_LeachingZones_Data(), Table_SourceData_LeachingZones[[#Headers],[Leaching Zone]], 0)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="129" spans="1:77" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A129"/>
       <c r="D129" s="30" t="str" cm="1">
-        <f t="array" ref="D129">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_LeachingZones_Data(), Table_SourceData_LeachingZones[[#Headers],[Leaching Zone]], 0)</f>
-        <v>Leaching does not occur</v>
+        <f t="array" aca="1" ref="D129" ca="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_LeachingZones_Data(), Table_SourceData_LeachingZones[[#Headers],[Leaching Zone]], 0)</f>
+        <v/>
       </c>
       <c r="E129" s="30" t="str" cm="1">
-        <f t="array" ref="E129">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_LeachingZones_Data(), Table_SourceData_LeachingZones[[#Headers],[Leaching Zone]], 0)</f>
-        <v>Σ(𝑟𝑎𝑖𝑛)≤Σ(𝐸𝑇0)+𝑠𝑜𝑖𝑙 𝑤𝑎𝑡𝑒𝑟 ℎ𝑜𝑙𝑑𝑖𝑛𝑔 𝑐𝑎𝑝𝑎𝑐𝑖𝑡𝑦</v>
-      </c>
-    </row>
-    <row r="130" spans="4:77" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="131" spans="4:77" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="132" spans="4:77" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+        <f t="array" aca="1" ref="E129" ca="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_LeachingZones_Data(), Table_SourceData_LeachingZones[[#Headers],[Leaching Zone]], 0)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="130" spans="1:77" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A130"/>
+    </row>
+    <row r="131" spans="1:77" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A131"/>
+    </row>
+    <row r="132" spans="1:77" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A132"/>
       <c r="D132" s="2" t="str" cm="1">
         <f t="array" ref="D132">Common_SourceData.Common_SourceData_FracWET_Title()</f>
         <v>Fraction of N that is available for leaching and runoff</v>
       </c>
       <c r="E132" s="9"/>
     </row>
-    <row r="133" spans="4:77" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="133" spans="1:77" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A133"/>
       <c r="D133" s="28" t="str" cm="1">
         <f t="array" ref="D133">Common_SourceData.Common_SourceData_FracWET_Source()</f>
         <v>VEERG 2026:5.5.2.3 Constant Parameters</v>
       </c>
       <c r="E133" s="9"/>
     </row>
-    <row r="134" spans="4:77" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="134" spans="1:77" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A134"/>
       <c r="D134" t="s">
         <v>57</v>
       </c>
@@ -9326,28 +9595,33 @@
         <v>58</v>
       </c>
     </row>
-    <row r="135" spans="4:77" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="135" spans="1:77" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A135"/>
       <c r="D135" t="str" cm="1">
-        <f t="array" ref="D135">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_FracWET_Data(),Table_SourceData_FracWET[[#Headers],[Is in leaching zone]],0)</f>
-        <v>Yes - in leaching zone</v>
-      </c>
-      <c r="E135" cm="1">
-        <f t="array" ref="E135">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_FracWET_Data(),Table_SourceData_FracWET[[#Headers],[Is in leaching zone]],0)</f>
-        <v>1</v>
-      </c>
-    </row>
-    <row r="136" spans="4:77" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+        <f t="array" aca="1" ref="D135" ca="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_FracWET_Data(),Table_SourceData_FracWET[[#Headers],[Is in leaching zone]],0)</f>
+        <v/>
+      </c>
+      <c r="E135" t="str" cm="1">
+        <f t="array" aca="1" ref="E135" ca="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_FracWET_Data(),Table_SourceData_FracWET[[#Headers],[Is in leaching zone]],0)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="136" spans="1:77" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A136"/>
       <c r="D136" s="1" t="str" cm="1">
-        <f t="array" ref="D136">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_FracWET_Data(),Table_SourceData_FracWET[[#Headers],[Is in leaching zone]],0)</f>
-        <v>No - not in leaching zone</v>
-      </c>
-      <c r="E136" s="30" cm="1">
-        <f t="array" ref="E136">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_FracWET_Data(),Table_SourceData_FracWET[[#Headers],[Is in leaching zone]],0)</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="137" spans="4:77" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="138" spans="4:77" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+        <f t="array" aca="1" ref="D136" ca="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_FracWET_Data(),Table_SourceData_FracWET[[#Headers],[Is in leaching zone]],0)</f>
+        <v/>
+      </c>
+      <c r="E136" s="30" t="str" cm="1">
+        <f t="array" aca="1" ref="E136" ca="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_FracWET_Data(),Table_SourceData_FracWET[[#Headers],[Is in leaching zone]],0)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="137" spans="1:77" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A137"/>
+    </row>
+    <row r="138" spans="1:77" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A138"/>
       <c r="BN138" s="32"/>
       <c r="BO138" s="32"/>
       <c r="BP138" s="32"/>
@@ -9361,7 +9635,8 @@
       <c r="BX138" s="32"/>
       <c r="BY138" s="32"/>
     </row>
-    <row r="139" spans="4:77" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="139" spans="1:77" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A139"/>
       <c r="D139" s="2" t="str" cm="1">
         <f t="array" ref="D139">Common_SourceData.Common_SourceData_FracWETIrrigation_Title()</f>
         <v>FracWET for irrigation types</v>
@@ -9379,7 +9654,8 @@
       <c r="BX139" s="32"/>
       <c r="BY139" s="32"/>
     </row>
-    <row r="140" spans="4:77" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="140" spans="1:77" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A140"/>
       <c r="D140" s="28" t="str" cm="1">
         <f t="array" ref="D140">Common_SourceData.Common_SourceData_FracWETIrrigation_Source()</f>
         <v>VEERG 2026: Chapter 1, section 1.8.2 Leaching, climate and rainfall zones</v>
@@ -9397,14 +9673,16 @@
       <c r="BX140" s="32"/>
       <c r="BY140" s="32"/>
     </row>
-    <row r="141" spans="4:77" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="141" spans="1:77" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A141"/>
       <c r="D141" s="36" t="str" cm="1">
         <f t="array" ref="D141">Common_SourceData.Common_SourceData_FracWETIrrigation_Variation()</f>
         <v>VARIATION FROM SOURCE DATA: Table created based on VEERG text 'Areas are subject to leaching (i.e., in the leaching zone) when... the land is irrigated (except drip irrigation).'</v>
       </c>
       <c r="BN141" s="32"/>
     </row>
-    <row r="142" spans="4:77" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="142" spans="1:77" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A142"/>
       <c r="D142" s="30" t="s">
         <v>59</v>
       </c>
@@ -9413,85 +9691,96 @@
       </c>
       <c r="BN142" s="32"/>
     </row>
-    <row r="143" spans="4:77" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="143" spans="1:77" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A143"/>
       <c r="D143" s="30" t="str" cm="1">
-        <f t="array" ref="D143">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_FracWETIrrigation_Data(), Table_SourceData_FracWETIrrigation[[#Headers],[Irrigation type i]], 0)</f>
-        <v>Not irrigated</v>
-      </c>
-      <c r="E143" s="30" cm="1">
-        <f t="array" ref="E143">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_FracWETIrrigation_Data(), Table_SourceData_FracWETIrrigation[[#Headers],[Irrigation type i]], 0)</f>
-        <v>0</v>
+        <f t="array" aca="1" ref="D143" ca="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_FracWETIrrigation_Data(), Table_SourceData_FracWETIrrigation[[#Headers],[Irrigation type i]], 0)</f>
+        <v/>
+      </c>
+      <c r="E143" s="30" t="str" cm="1">
+        <f t="array" aca="1" ref="E143" ca="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_FracWETIrrigation_Data(), Table_SourceData_FracWETIrrigation[[#Headers],[Irrigation type i]], 0)</f>
+        <v/>
       </c>
       <c r="BN143" s="32"/>
     </row>
-    <row r="144" spans="4:77" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="144" spans="1:77" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A144"/>
       <c r="D144" s="1" t="str" cm="1">
-        <f t="array" ref="D144">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_FracWETIrrigation_Data(), Table_SourceData_FracWETIrrigation[[#Headers],[Irrigation type i]], 0)</f>
-        <v>Drip irrigation</v>
-      </c>
-      <c r="E144" s="30" cm="1">
-        <f t="array" ref="E144">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_FracWETIrrigation_Data(), Table_SourceData_FracWETIrrigation[[#Headers],[Irrigation type i]], 0)</f>
-        <v>0</v>
+        <f t="array" aca="1" ref="D144" ca="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_FracWETIrrigation_Data(), Table_SourceData_FracWETIrrigation[[#Headers],[Irrigation type i]], 0)</f>
+        <v/>
+      </c>
+      <c r="E144" s="30" t="str" cm="1">
+        <f t="array" aca="1" ref="E144" ca="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_FracWETIrrigation_Data(), Table_SourceData_FracWETIrrigation[[#Headers],[Irrigation type i]], 0)</f>
+        <v/>
       </c>
       <c r="BN144" s="32"/>
     </row>
-    <row r="145" spans="4:66" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="145" spans="1:66" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A145"/>
       <c r="D145" s="1" t="str" cm="1">
-        <f t="array" ref="D145">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_FracWETIrrigation_Data(), Table_SourceData_FracWETIrrigation[[#Headers],[Irrigation type i]], 0)</f>
-        <v>Sprinkler irrigation</v>
-      </c>
-      <c r="E145" s="30" cm="1">
-        <f t="array" ref="E145">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_FracWETIrrigation_Data(), Table_SourceData_FracWETIrrigation[[#Headers],[Irrigation type i]], 0)</f>
-        <v>1</v>
+        <f t="array" aca="1" ref="D145" ca="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_FracWETIrrigation_Data(), Table_SourceData_FracWETIrrigation[[#Headers],[Irrigation type i]], 0)</f>
+        <v/>
+      </c>
+      <c r="E145" s="30" t="str" cm="1">
+        <f t="array" aca="1" ref="E145" ca="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_FracWETIrrigation_Data(), Table_SourceData_FracWETIrrigation[[#Headers],[Irrigation type i]], 0)</f>
+        <v/>
       </c>
       <c r="BN145" s="32"/>
     </row>
-    <row r="146" spans="4:66" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="146" spans="1:66" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A146"/>
       <c r="D146" s="1" t="str" cm="1">
-        <f t="array" ref="D146">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_FracWETIrrigation_Data(), Table_SourceData_FracWETIrrigation[[#Headers],[Irrigation type i]], 0)</f>
-        <v>Surface irrigation</v>
-      </c>
-      <c r="E146" s="30" cm="1">
-        <f t="array" ref="E146">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_FracWETIrrigation_Data(), Table_SourceData_FracWETIrrigation[[#Headers],[Irrigation type i]], 0)</f>
-        <v>1</v>
+        <f t="array" aca="1" ref="D146" ca="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_FracWETIrrigation_Data(), Table_SourceData_FracWETIrrigation[[#Headers],[Irrigation type i]], 0)</f>
+        <v/>
+      </c>
+      <c r="E146" s="30" t="str" cm="1">
+        <f t="array" aca="1" ref="E146" ca="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_FracWETIrrigation_Data(), Table_SourceData_FracWETIrrigation[[#Headers],[Irrigation type i]], 0)</f>
+        <v/>
       </c>
       <c r="BN146" s="32"/>
     </row>
-    <row r="147" spans="4:66" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="147" spans="1:66" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A147"/>
       <c r="D147" s="1" t="str" cm="1">
-        <f t="array" ref="D147">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_FracWETIrrigation_Data(), Table_SourceData_FracWETIrrigation[[#Headers],[Irrigation type i]], 0)</f>
-        <v>Other irrigation</v>
-      </c>
-      <c r="E147" s="30" cm="1">
-        <f t="array" ref="E147">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_FracWETIrrigation_Data(), Table_SourceData_FracWETIrrigation[[#Headers],[Irrigation type i]], 0)</f>
-        <v>1</v>
+        <f t="array" aca="1" ref="D147" ca="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_FracWETIrrigation_Data(), Table_SourceData_FracWETIrrigation[[#Headers],[Irrigation type i]], 0)</f>
+        <v/>
+      </c>
+      <c r="E147" s="30" t="str" cm="1">
+        <f t="array" aca="1" ref="E147" ca="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_FracWETIrrigation_Data(), Table_SourceData_FracWETIrrigation[[#Headers],[Irrigation type i]], 0)</f>
+        <v/>
       </c>
       <c r="BN147" s="32"/>
     </row>
-    <row r="148" spans="4:66" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="148" spans="1:66" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A148"/>
       <c r="BN148" s="32"/>
     </row>
-    <row r="149" spans="4:66" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="149" spans="1:66" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A149"/>
       <c r="BN149" s="32"/>
     </row>
-    <row r="150" spans="4:66" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="150" spans="1:66" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A150"/>
       <c r="D150" s="2" t="str" cm="1">
         <f t="array" ref="D150">Common_SourceData.Common_SourceData_DataScores_Scope3_Title()</f>
         <v>Australian data scores for scope 3</v>
       </c>
       <c r="BN150" s="32"/>
     </row>
-    <row r="151" spans="4:66" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="151" spans="1:66" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A151"/>
       <c r="D151" s="28" t="str" cm="1">
         <f t="array" ref="D151">Common_SourceData.Common_SourceData_DataScores_Scope3_Source()</f>
         <v>VEERG 2026: XXXXXXXX</v>
       </c>
       <c r="BN151" s="32"/>
     </row>
-    <row r="152" spans="4:66" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="152" spans="1:66" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A152"/>
       <c r="BN152" s="32"/>
     </row>
-    <row r="153" spans="4:66" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="153" spans="1:66" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A153"/>
       <c r="D153" s="30" t="s">
         <v>60</v>
       </c>
@@ -9510,14 +9799,15 @@
       <c r="BL153" s="35"/>
       <c r="BM153" s="35"/>
     </row>
-    <row r="154" spans="4:66" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="154" spans="1:66" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A154"/>
       <c r="D154" s="30" t="str" cm="1">
-        <f t="array" ref="D154">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_DataScores_Scope3_Data(), Table_SourceData_DataScores_Scope3[[#Headers],[Data source]], 0)</f>
-        <v>International scope 3 database</v>
-      </c>
-      <c r="E154" s="30" cm="1">
-        <f t="array" ref="E154">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_DataScores_Scope3_Data(), Table_SourceData_DataScores_Scope3[[#Headers],[Data source]], 0)</f>
-        <v>1</v>
+        <f t="array" aca="1" ref="D154" ca="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_DataScores_Scope3_Data(), Table_SourceData_DataScores_Scope3[[#Headers],[Data source]], 0)</f>
+        <v/>
+      </c>
+      <c r="E154" s="30" t="str" cm="1">
+        <f t="array" aca="1" ref="E154" ca="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_DataScores_Scope3_Data(), Table_SourceData_DataScores_Scope3[[#Headers],[Data source]], 0)</f>
+        <v/>
       </c>
       <c r="BC154" s="35"/>
       <c r="BD154" s="35"/>
@@ -9531,14 +9821,15 @@
       <c r="BL154" s="35"/>
       <c r="BM154" s="35"/>
     </row>
-    <row r="155" spans="4:66" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="155" spans="1:66" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A155"/>
       <c r="D155" s="30" t="str" cm="1">
-        <f t="array" ref="D155">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_DataScores_Scope3_Data(), Table_SourceData_DataScores_Scope3[[#Headers],[Data source]], 0)</f>
-        <v>Australian scope 3 database</v>
-      </c>
-      <c r="E155" s="30" cm="1">
-        <f t="array" ref="E155">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_DataScores_Scope3_Data(), Table_SourceData_DataScores_Scope3[[#Headers],[Data source]], 0)</f>
-        <v>2</v>
+        <f t="array" aca="1" ref="D155" ca="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_DataScores_Scope3_Data(), Table_SourceData_DataScores_Scope3[[#Headers],[Data source]], 0)</f>
+        <v/>
+      </c>
+      <c r="E155" s="30" t="str" cm="1">
+        <f t="array" aca="1" ref="E155" ca="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_DataScores_Scope3_Data(), Table_SourceData_DataScores_Scope3[[#Headers],[Data source]], 0)</f>
+        <v/>
       </c>
       <c r="BC155" s="35"/>
       <c r="BD155" s="35"/>
@@ -9552,38 +9843,45 @@
       <c r="BL155" s="35"/>
       <c r="BM155" s="35"/>
     </row>
-    <row r="156" spans="4:66" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="156" spans="1:66" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A156"/>
       <c r="D156" s="30" t="str" cm="1">
-        <f t="array" ref="D156">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_DataScores_Scope3_Data(), Table_SourceData_DataScores_Scope3[[#Headers],[Data source]], 0)</f>
-        <v>State or regional scope 3 database</v>
-      </c>
-      <c r="E156" s="30" cm="1">
-        <f t="array" ref="E156">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_DataScores_Scope3_Data(), Table_SourceData_DataScores_Scope3[[#Headers],[Data source]], 0)</f>
-        <v>3</v>
-      </c>
-    </row>
-    <row r="157" spans="4:66" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+        <f t="array" aca="1" ref="D156" ca="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_DataScores_Scope3_Data(), Table_SourceData_DataScores_Scope3[[#Headers],[Data source]], 0)</f>
+        <v/>
+      </c>
+      <c r="E156" s="30" t="str" cm="1">
+        <f t="array" aca="1" ref="E156" ca="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_DataScores_Scope3_Data(), Table_SourceData_DataScores_Scope3[[#Headers],[Data source]], 0)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="157" spans="1:66" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A157"/>
       <c r="D157" s="30" t="str" cm="1">
-        <f t="array" ref="D157">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_DataScores_Scope3_Data(), Table_SourceData_DataScores_Scope3[[#Headers],[Data source]], 0)</f>
-        <v>Emissions intensity calculated from approved method</v>
-      </c>
-      <c r="E157" s="30" cm="1">
-        <f t="array" ref="E157">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_DataScores_Scope3_Data(), Table_SourceData_DataScores_Scope3[[#Headers],[Data source]], 0)</f>
-        <v>4</v>
-      </c>
-    </row>
-    <row r="158" spans="4:66" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+        <f t="array" aca="1" ref="D157" ca="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_DataScores_Scope3_Data(), Table_SourceData_DataScores_Scope3[[#Headers],[Data source]], 0)</f>
+        <v/>
+      </c>
+      <c r="E157" s="30" t="str" cm="1">
+        <f t="array" aca="1" ref="E157" ca="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_DataScores_Scope3_Data(), Table_SourceData_DataScores_Scope3[[#Headers],[Data source]], 0)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="158" spans="1:66" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A158"/>
       <c r="D158" s="30" t="str" cm="1">
-        <f t="array" ref="D158">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_DataScores_Scope3_Data(), Table_SourceData_DataScores_Scope3[[#Headers],[Data source]], 0)</f>
-        <v>Verified credential matching ISO14067</v>
-      </c>
-      <c r="E158" s="30" cm="1">
-        <f t="array" ref="E158">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_DataScores_Scope3_Data(), Table_SourceData_DataScores_Scope3[[#Headers],[Data source]], 0)</f>
-        <v>5</v>
-      </c>
-    </row>
-    <row r="159" spans="4:66" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="160" spans="4:66" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
+        <f t="array" aca="1" ref="D158" ca="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_DataScores_Scope3_Data(), Table_SourceData_DataScores_Scope3[[#Headers],[Data source]], 0)</f>
+        <v/>
+      </c>
+      <c r="E158" s="30" t="str" cm="1">
+        <f t="array" aca="1" ref="E158" ca="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_DataScores_Scope3_Data(), Table_SourceData_DataScores_Scope3[[#Headers],[Data source]], 0)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="159" spans="1:66" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A159"/>
+    </row>
+    <row r="160" spans="1:66" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A160"/>
+    </row>
     <row r="161" spans="4:68" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D161" s="2" t="str" cm="1">
         <f t="array" ref="D161">Common_SourceData.Common_SourceData_FracLEACH_Title()</f>
@@ -9783,288 +10081,288 @@
     </row>
     <row r="187" spans="4:68" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D187" s="30" t="str" cm="1">
-        <f t="array" ref="D187">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_EFN2O_Data(), Table_SourceData_Common_EFN2O[[#Headers],[Production system j]], 0)</f>
-        <v>Irrigated pasture</v>
-      </c>
-      <c r="E187" s="30" cm="1">
-        <f t="array" ref="E187">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_EFN2O_Data(), Table_SourceData_Common_EFN2O[[#Headers],[Production system j]], 0)</f>
-        <v>5.8999999999999999E-3</v>
+        <f t="array" aca="1" ref="D187" ca="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_EFN2O_Data(), Table_SourceData_Common_EFN2O[[#Headers],[Production system j]], 0)</f>
+        <v/>
+      </c>
+      <c r="E187" s="30" t="str" cm="1">
+        <f t="array" aca="1" ref="E187" ca="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_EFN2O_Data(), Table_SourceData_Common_EFN2O[[#Headers],[Production system j]], 0)</f>
+        <v/>
       </c>
       <c r="F187" s="30" t="str" cm="1">
-        <f t="array" ref="F187">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_EFN2O_Data(), Table_SourceData_Common_EFN2O[[#Headers],[Production system j]], 0)</f>
-        <v>Pasture</v>
+        <f t="array" aca="1" ref="F187" ca="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_EFN2O_Data(), Table_SourceData_Common_EFN2O[[#Headers],[Production system j]], 0)</f>
+        <v/>
       </c>
       <c r="G187" s="30" t="str" cm="1">
-        <f t="array" ref="G187">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_EFN2O_Data(), Table_SourceData_Common_EFN2O[[#Headers],[Production system j]], 0)</f>
-        <v>Any</v>
+        <f t="array" aca="1" ref="G187" ca="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_EFN2O_Data(), Table_SourceData_Common_EFN2O[[#Headers],[Production system j]], 0)</f>
+        <v/>
       </c>
       <c r="H187" s="30" t="str" cm="1">
-        <f t="array" ref="H187">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_EFN2O_Data(), Table_SourceData_Common_EFN2O[[#Headers],[Production system j]], 0)</f>
-        <v>Any</v>
+        <f t="array" aca="1" ref="H187" ca="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_EFN2O_Data(), Table_SourceData_Common_EFN2O[[#Headers],[Production system j]], 0)</f>
+        <v/>
       </c>
     </row>
     <row r="188" spans="4:68" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D188" s="30" t="str" cm="1">
-        <f t="array" ref="D188">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_EFN2O_Data(), Table_SourceData_Common_EFN2O[[#Headers],[Production system j]], 0)</f>
-        <v>Irrigated crop</v>
-      </c>
-      <c r="E188" s="30" cm="1">
-        <f t="array" ref="E188">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_EFN2O_Data(), Table_SourceData_Common_EFN2O[[#Headers],[Production system j]], 0)</f>
-        <v>7.0000000000000001E-3</v>
+        <f t="array" aca="1" ref="D188" ca="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_EFN2O_Data(), Table_SourceData_Common_EFN2O[[#Headers],[Production system j]], 0)</f>
+        <v/>
+      </c>
+      <c r="E188" s="30" t="str" cm="1">
+        <f t="array" aca="1" ref="E188" ca="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_EFN2O_Data(), Table_SourceData_Common_EFN2O[[#Headers],[Production system j]], 0)</f>
+        <v/>
       </c>
       <c r="F188" s="30" t="str" cm="1">
-        <f t="array" ref="F188">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_EFN2O_Data(), Table_SourceData_Common_EFN2O[[#Headers],[Production system j]], 0)</f>
-        <v>Crop</v>
+        <f t="array" aca="1" ref="F188" ca="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_EFN2O_Data(), Table_SourceData_Common_EFN2O[[#Headers],[Production system j]], 0)</f>
+        <v/>
       </c>
       <c r="G188" s="30" t="str" cm="1">
-        <f t="array" ref="G188">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_EFN2O_Data(), Table_SourceData_Common_EFN2O[[#Headers],[Production system j]], 0)</f>
-        <v>Any</v>
+        <f t="array" aca="1" ref="G188" ca="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_EFN2O_Data(), Table_SourceData_Common_EFN2O[[#Headers],[Production system j]], 0)</f>
+        <v/>
       </c>
       <c r="H188" s="30" t="str" cm="1">
-        <f t="array" ref="H188">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_EFN2O_Data(), Table_SourceData_Common_EFN2O[[#Headers],[Production system j]], 0)</f>
-        <v>Any</v>
+        <f t="array" aca="1" ref="H188" ca="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_EFN2O_Data(), Table_SourceData_Common_EFN2O[[#Headers],[Production system j]], 0)</f>
+        <v/>
       </c>
     </row>
     <row r="189" spans="4:68" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D189" s="30" t="str" cm="1">
-        <f t="array" ref="D189">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_EFN2O_Data(), Table_SourceData_Common_EFN2O[[#Headers],[Production system j]], 0)</f>
-        <v>Non-irrigated pasture</v>
-      </c>
-      <c r="E189" s="30" cm="1">
-        <f t="array" ref="E189">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_EFN2O_Data(), Table_SourceData_Common_EFN2O[[#Headers],[Production system j]], 0)</f>
-        <v>1.8E-3</v>
+        <f t="array" aca="1" ref="D189" ca="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_EFN2O_Data(), Table_SourceData_Common_EFN2O[[#Headers],[Production system j]], 0)</f>
+        <v/>
+      </c>
+      <c r="E189" s="30" t="str" cm="1">
+        <f t="array" aca="1" ref="E189" ca="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_EFN2O_Data(), Table_SourceData_Common_EFN2O[[#Headers],[Production system j]], 0)</f>
+        <v/>
       </c>
       <c r="F189" s="30" t="str" cm="1">
-        <f t="array" ref="F189">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_EFN2O_Data(), Table_SourceData_Common_EFN2O[[#Headers],[Production system j]], 0)</f>
-        <v>Pasture</v>
+        <f t="array" aca="1" ref="F189" ca="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_EFN2O_Data(), Table_SourceData_Common_EFN2O[[#Headers],[Production system j]], 0)</f>
+        <v/>
       </c>
       <c r="G189" s="30" t="str" cm="1">
-        <f t="array" ref="G189">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_EFN2O_Data(), Table_SourceData_Common_EFN2O[[#Headers],[Production system j]], 0)</f>
-        <v>Not irrigated</v>
+        <f t="array" aca="1" ref="G189" ca="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_EFN2O_Data(), Table_SourceData_Common_EFN2O[[#Headers],[Production system j]], 0)</f>
+        <v/>
       </c>
       <c r="H189" s="30" t="str" cm="1">
-        <f t="array" ref="H189">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_EFN2O_Data(), Table_SourceData_Common_EFN2O[[#Headers],[Production system j]], 0)</f>
-        <v>Low rainfall</v>
+        <f t="array" aca="1" ref="H189" ca="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_EFN2O_Data(), Table_SourceData_Common_EFN2O[[#Headers],[Production system j]], 0)</f>
+        <v/>
       </c>
     </row>
     <row r="190" spans="4:68" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D190" s="30" t="str" cm="1">
-        <f t="array" ref="D190">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_EFN2O_Data(), Table_SourceData_Common_EFN2O[[#Headers],[Production system j]], 0)</f>
-        <v>Non-irrigated pasture</v>
-      </c>
-      <c r="E190" s="30" cm="1">
-        <f t="array" ref="E190">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_EFN2O_Data(), Table_SourceData_Common_EFN2O[[#Headers],[Production system j]], 0)</f>
-        <v>1.8E-3</v>
+        <f t="array" aca="1" ref="D190" ca="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_EFN2O_Data(), Table_SourceData_Common_EFN2O[[#Headers],[Production system j]], 0)</f>
+        <v/>
+      </c>
+      <c r="E190" s="30" t="str" cm="1">
+        <f t="array" aca="1" ref="E190" ca="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_EFN2O_Data(), Table_SourceData_Common_EFN2O[[#Headers],[Production system j]], 0)</f>
+        <v/>
       </c>
       <c r="F190" s="30" t="str" cm="1">
-        <f t="array" ref="F190">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_EFN2O_Data(), Table_SourceData_Common_EFN2O[[#Headers],[Production system j]], 0)</f>
-        <v>Pasture</v>
+        <f t="array" aca="1" ref="F190" ca="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_EFN2O_Data(), Table_SourceData_Common_EFN2O[[#Headers],[Production system j]], 0)</f>
+        <v/>
       </c>
       <c r="G190" s="30" t="str" cm="1">
-        <f t="array" ref="G190">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_EFN2O_Data(), Table_SourceData_Common_EFN2O[[#Headers],[Production system j]], 0)</f>
-        <v>Not irrigated</v>
+        <f t="array" aca="1" ref="G190" ca="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_EFN2O_Data(), Table_SourceData_Common_EFN2O[[#Headers],[Production system j]], 0)</f>
+        <v/>
       </c>
       <c r="H190" s="30" t="str" cm="1">
-        <f t="array" ref="H190">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_EFN2O_Data(), Table_SourceData_Common_EFN2O[[#Headers],[Production system j]], 0)</f>
-        <v>High rainfall</v>
+        <f t="array" aca="1" ref="H190" ca="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_EFN2O_Data(), Table_SourceData_Common_EFN2O[[#Headers],[Production system j]], 0)</f>
+        <v/>
       </c>
     </row>
     <row r="191" spans="4:68" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D191" s="30" t="str" cm="1">
-        <f t="array" ref="D191">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_EFN2O_Data(), Table_SourceData_Common_EFN2O[[#Headers],[Production system j]], 0)</f>
-        <v>Non-irrigated crop (low rainfall)</v>
-      </c>
-      <c r="E191" s="30" cm="1">
-        <f t="array" ref="E191">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_EFN2O_Data(), Table_SourceData_Common_EFN2O[[#Headers],[Production system j]], 0)</f>
-        <v>2.8999999999999998E-3</v>
+        <f t="array" aca="1" ref="D191" ca="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_EFN2O_Data(), Table_SourceData_Common_EFN2O[[#Headers],[Production system j]], 0)</f>
+        <v/>
+      </c>
+      <c r="E191" s="30" t="str" cm="1">
+        <f t="array" aca="1" ref="E191" ca="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_EFN2O_Data(), Table_SourceData_Common_EFN2O[[#Headers],[Production system j]], 0)</f>
+        <v/>
       </c>
       <c r="F191" s="30" t="str" cm="1">
-        <f t="array" ref="F191">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_EFN2O_Data(), Table_SourceData_Common_EFN2O[[#Headers],[Production system j]], 0)</f>
-        <v>Crop</v>
+        <f t="array" aca="1" ref="F191" ca="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_EFN2O_Data(), Table_SourceData_Common_EFN2O[[#Headers],[Production system j]], 0)</f>
+        <v/>
       </c>
       <c r="G191" s="30" t="str" cm="1">
-        <f t="array" ref="G191">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_EFN2O_Data(), Table_SourceData_Common_EFN2O[[#Headers],[Production system j]], 0)</f>
-        <v>Not irrigated</v>
+        <f t="array" aca="1" ref="G191" ca="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_EFN2O_Data(), Table_SourceData_Common_EFN2O[[#Headers],[Production system j]], 0)</f>
+        <v/>
       </c>
       <c r="H191" s="30" t="str" cm="1">
-        <f t="array" ref="H191">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_EFN2O_Data(), Table_SourceData_Common_EFN2O[[#Headers],[Production system j]], 0)</f>
-        <v>Low rainfall</v>
+        <f t="array" aca="1" ref="H191" ca="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_EFN2O_Data(), Table_SourceData_Common_EFN2O[[#Headers],[Production system j]], 0)</f>
+        <v/>
       </c>
     </row>
     <row r="192" spans="4:68" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D192" s="30" t="str" cm="1">
-        <f t="array" ref="D192">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_EFN2O_Data(), Table_SourceData_Common_EFN2O[[#Headers],[Production system j]], 0)</f>
-        <v>Non-irrigated crop (high rainfall)</v>
-      </c>
-      <c r="E192" s="30" cm="1">
-        <f t="array" ref="E192">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_EFN2O_Data(), Table_SourceData_Common_EFN2O[[#Headers],[Production system j]], 0)</f>
-        <v>8.0000000000000002E-3</v>
+        <f t="array" aca="1" ref="D192" ca="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_EFN2O_Data(), Table_SourceData_Common_EFN2O[[#Headers],[Production system j]], 0)</f>
+        <v/>
+      </c>
+      <c r="E192" s="30" t="str" cm="1">
+        <f t="array" aca="1" ref="E192" ca="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_EFN2O_Data(), Table_SourceData_Common_EFN2O[[#Headers],[Production system j]], 0)</f>
+        <v/>
       </c>
       <c r="F192" s="30" t="str" cm="1">
-        <f t="array" ref="F192">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_EFN2O_Data(), Table_SourceData_Common_EFN2O[[#Headers],[Production system j]], 0)</f>
-        <v>Crop</v>
+        <f t="array" aca="1" ref="F192" ca="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_EFN2O_Data(), Table_SourceData_Common_EFN2O[[#Headers],[Production system j]], 0)</f>
+        <v/>
       </c>
       <c r="G192" s="30" t="str" cm="1">
-        <f t="array" ref="G192">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_EFN2O_Data(), Table_SourceData_Common_EFN2O[[#Headers],[Production system j]], 0)</f>
-        <v>Not irrigated</v>
+        <f t="array" aca="1" ref="G192" ca="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_EFN2O_Data(), Table_SourceData_Common_EFN2O[[#Headers],[Production system j]], 0)</f>
+        <v/>
       </c>
       <c r="H192" s="30" t="str" cm="1">
-        <f t="array" ref="H192">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_EFN2O_Data(), Table_SourceData_Common_EFN2O[[#Headers],[Production system j]], 0)</f>
-        <v>High rainfall</v>
+        <f t="array" aca="1" ref="H192" ca="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_EFN2O_Data(), Table_SourceData_Common_EFN2O[[#Headers],[Production system j]], 0)</f>
+        <v/>
       </c>
     </row>
     <row r="193" spans="4:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D193" s="30" t="str" cm="1">
-        <f t="array" ref="D193">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_EFN2O_Data(), Table_SourceData_Common_EFN2O[[#Headers],[Production system j]], 0)</f>
-        <v>Sugar</v>
-      </c>
-      <c r="E193" s="30" cm="1">
-        <f t="array" ref="E193">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_EFN2O_Data(), Table_SourceData_Common_EFN2O[[#Headers],[Production system j]], 0)</f>
-        <v>1.9900000000000001E-2</v>
+        <f t="array" aca="1" ref="D193" ca="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_EFN2O_Data(), Table_SourceData_Common_EFN2O[[#Headers],[Production system j]], 0)</f>
+        <v/>
+      </c>
+      <c r="E193" s="30" t="str" cm="1">
+        <f t="array" aca="1" ref="E193" ca="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_EFN2O_Data(), Table_SourceData_Common_EFN2O[[#Headers],[Production system j]], 0)</f>
+        <v/>
       </c>
       <c r="F193" s="30" t="str" cm="1">
-        <f t="array" ref="F193">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_EFN2O_Data(), Table_SourceData_Common_EFN2O[[#Headers],[Production system j]], 0)</f>
-        <v>Sugar</v>
+        <f t="array" aca="1" ref="F193" ca="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_EFN2O_Data(), Table_SourceData_Common_EFN2O[[#Headers],[Production system j]], 0)</f>
+        <v/>
       </c>
       <c r="G193" s="30" t="str" cm="1">
-        <f t="array" ref="G193">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_EFN2O_Data(), Table_SourceData_Common_EFN2O[[#Headers],[Production system j]], 0)</f>
-        <v>Any</v>
+        <f t="array" aca="1" ref="G193" ca="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_EFN2O_Data(), Table_SourceData_Common_EFN2O[[#Headers],[Production system j]], 0)</f>
+        <v/>
       </c>
       <c r="H193" s="30" t="str" cm="1">
-        <f t="array" ref="H193">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_EFN2O_Data(), Table_SourceData_Common_EFN2O[[#Headers],[Production system j]], 0)</f>
-        <v>Any</v>
+        <f t="array" aca="1" ref="H193" ca="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_EFN2O_Data(), Table_SourceData_Common_EFN2O[[#Headers],[Production system j]], 0)</f>
+        <v/>
       </c>
     </row>
     <row r="194" spans="4:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D194" s="30" t="str" cm="1">
-        <f t="array" ref="D194">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_EFN2O_Data(), Table_SourceData_Common_EFN2O[[#Headers],[Production system j]], 0)</f>
-        <v>Cotton</v>
-      </c>
-      <c r="E194" s="30" cm="1">
-        <f t="array" ref="E194">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_EFN2O_Data(), Table_SourceData_Common_EFN2O[[#Headers],[Production system j]], 0)</f>
-        <v>5.3E-3</v>
+        <f t="array" aca="1" ref="D194" ca="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_EFN2O_Data(), Table_SourceData_Common_EFN2O[[#Headers],[Production system j]], 0)</f>
+        <v/>
+      </c>
+      <c r="E194" s="30" t="str" cm="1">
+        <f t="array" aca="1" ref="E194" ca="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_EFN2O_Data(), Table_SourceData_Common_EFN2O[[#Headers],[Production system j]], 0)</f>
+        <v/>
       </c>
       <c r="F194" s="30" t="str" cm="1">
-        <f t="array" ref="F194">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_EFN2O_Data(), Table_SourceData_Common_EFN2O[[#Headers],[Production system j]], 0)</f>
-        <v>Cotton</v>
+        <f t="array" aca="1" ref="F194" ca="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_EFN2O_Data(), Table_SourceData_Common_EFN2O[[#Headers],[Production system j]], 0)</f>
+        <v/>
       </c>
       <c r="G194" s="30" t="str" cm="1">
-        <f t="array" ref="G194">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_EFN2O_Data(), Table_SourceData_Common_EFN2O[[#Headers],[Production system j]], 0)</f>
-        <v>Any</v>
+        <f t="array" aca="1" ref="G194" ca="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_EFN2O_Data(), Table_SourceData_Common_EFN2O[[#Headers],[Production system j]], 0)</f>
+        <v/>
       </c>
       <c r="H194" s="30" t="str" cm="1">
-        <f t="array" ref="H194">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_EFN2O_Data(), Table_SourceData_Common_EFN2O[[#Headers],[Production system j]], 0)</f>
-        <v>Any</v>
+        <f t="array" aca="1" ref="H194" ca="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_EFN2O_Data(), Table_SourceData_Common_EFN2O[[#Headers],[Production system j]], 0)</f>
+        <v/>
       </c>
     </row>
     <row r="195" spans="4:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D195" s="30" t="str" cm="1">
-        <f t="array" ref="D195">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_EFN2O_Data(), Table_SourceData_Common_EFN2O[[#Headers],[Production system j]], 0)</f>
-        <v>Horticultural crops</v>
-      </c>
-      <c r="E195" s="30" cm="1">
-        <f t="array" ref="E195">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_EFN2O_Data(), Table_SourceData_Common_EFN2O[[#Headers],[Production system j]], 0)</f>
-        <v>6.4000000000000003E-3</v>
+        <f t="array" aca="1" ref="D195" ca="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_EFN2O_Data(), Table_SourceData_Common_EFN2O[[#Headers],[Production system j]], 0)</f>
+        <v/>
+      </c>
+      <c r="E195" s="30" t="str" cm="1">
+        <f t="array" aca="1" ref="E195" ca="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_EFN2O_Data(), Table_SourceData_Common_EFN2O[[#Headers],[Production system j]], 0)</f>
+        <v/>
       </c>
       <c r="F195" s="30" t="str" cm="1">
-        <f t="array" ref="F195">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_EFN2O_Data(), Table_SourceData_Common_EFN2O[[#Headers],[Production system j]], 0)</f>
-        <v>Horticultural crops</v>
+        <f t="array" aca="1" ref="F195" ca="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_EFN2O_Data(), Table_SourceData_Common_EFN2O[[#Headers],[Production system j]], 0)</f>
+        <v/>
       </c>
       <c r="G195" s="30" t="str" cm="1">
-        <f t="array" ref="G195">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_EFN2O_Data(), Table_SourceData_Common_EFN2O[[#Headers],[Production system j]], 0)</f>
-        <v>Any</v>
+        <f t="array" aca="1" ref="G195" ca="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_EFN2O_Data(), Table_SourceData_Common_EFN2O[[#Headers],[Production system j]], 0)</f>
+        <v/>
       </c>
       <c r="H195" s="30" t="str" cm="1">
-        <f t="array" ref="H195">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_EFN2O_Data(), Table_SourceData_Common_EFN2O[[#Headers],[Production system j]], 0)</f>
-        <v>Any</v>
+        <f t="array" aca="1" ref="H195" ca="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_EFN2O_Data(), Table_SourceData_Common_EFN2O[[#Headers],[Production system j]], 0)</f>
+        <v/>
       </c>
     </row>
     <row r="196" spans="4:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D196" s="30" t="str" cm="1">
-        <f t="array" ref="D196">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_EFN2O_Data(), Table_SourceData_Common_EFN2O[[#Headers],[Production system j]], 0)</f>
-        <v>Rice (continuous flooding)</v>
-      </c>
-      <c r="E196" s="30" cm="1">
-        <f t="array" ref="E196">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_EFN2O_Data(), Table_SourceData_Common_EFN2O[[#Headers],[Production system j]], 0)</f>
-        <v>3.0000000000000001E-3</v>
+        <f t="array" aca="1" ref="D196" ca="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_EFN2O_Data(), Table_SourceData_Common_EFN2O[[#Headers],[Production system j]], 0)</f>
+        <v/>
+      </c>
+      <c r="E196" s="30" t="str" cm="1">
+        <f t="array" aca="1" ref="E196" ca="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_EFN2O_Data(), Table_SourceData_Common_EFN2O[[#Headers],[Production system j]], 0)</f>
+        <v/>
       </c>
       <c r="F196" s="30" t="str" cm="1">
-        <f t="array" ref="F196">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_EFN2O_Data(), Table_SourceData_Common_EFN2O[[#Headers],[Production system j]], 0)</f>
-        <v>Rice</v>
+        <f t="array" aca="1" ref="F196" ca="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_EFN2O_Data(), Table_SourceData_Common_EFN2O[[#Headers],[Production system j]], 0)</f>
+        <v/>
       </c>
       <c r="G196" s="30" t="str" cm="1">
-        <f t="array" ref="G196">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_EFN2O_Data(), Table_SourceData_Common_EFN2O[[#Headers],[Production system j]], 0)</f>
-        <v>Continuous flooding</v>
+        <f t="array" aca="1" ref="G196" ca="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_EFN2O_Data(), Table_SourceData_Common_EFN2O[[#Headers],[Production system j]], 0)</f>
+        <v/>
       </c>
       <c r="H196" s="30" t="str" cm="1">
-        <f t="array" ref="H196">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_EFN2O_Data(), Table_SourceData_Common_EFN2O[[#Headers],[Production system j]], 0)</f>
-        <v>Any</v>
+        <f t="array" aca="1" ref="H196" ca="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_EFN2O_Data(), Table_SourceData_Common_EFN2O[[#Headers],[Production system j]], 0)</f>
+        <v/>
       </c>
     </row>
     <row r="197" spans="4:8" x14ac:dyDescent="0.25">
       <c r="D197" s="30" t="str" cm="1">
-        <f t="array" ref="D197">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_EFN2O_Data(), Table_SourceData_Common_EFN2O[[#Headers],[Production system j]], 0)</f>
-        <v>Rice (single and multiple drainage, or alternate wetting and drying)</v>
-      </c>
-      <c r="E197" s="30" cm="1">
-        <f t="array" ref="E197">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_EFN2O_Data(), Table_SourceData_Common_EFN2O[[#Headers],[Production system j]], 0)</f>
-        <v>5.0000000000000001E-3</v>
+        <f t="array" aca="1" ref="D197" ca="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_EFN2O_Data(), Table_SourceData_Common_EFN2O[[#Headers],[Production system j]], 0)</f>
+        <v/>
+      </c>
+      <c r="E197" s="30" t="str" cm="1">
+        <f t="array" aca="1" ref="E197" ca="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_EFN2O_Data(), Table_SourceData_Common_EFN2O[[#Headers],[Production system j]], 0)</f>
+        <v/>
       </c>
       <c r="F197" s="30" t="str" cm="1">
-        <f t="array" ref="F197">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_EFN2O_Data(), Table_SourceData_Common_EFN2O[[#Headers],[Production system j]], 0)</f>
-        <v>Rice</v>
+        <f t="array" aca="1" ref="F197" ca="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_EFN2O_Data(), Table_SourceData_Common_EFN2O[[#Headers],[Production system j]], 0)</f>
+        <v/>
       </c>
       <c r="G197" s="30" t="str" cm="1">
-        <f t="array" ref="G197">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_EFN2O_Data(), Table_SourceData_Common_EFN2O[[#Headers],[Production system j]], 0)</f>
-        <v>Single and multiple drainage, or alternate wetting and drying</v>
+        <f t="array" aca="1" ref="G197" ca="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_EFN2O_Data(), Table_SourceData_Common_EFN2O[[#Headers],[Production system j]], 0)</f>
+        <v/>
       </c>
       <c r="H197" s="30" t="str" cm="1">
-        <f t="array" ref="H197">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_EFN2O_Data(), Table_SourceData_Common_EFN2O[[#Headers],[Production system j]], 0)</f>
-        <v>Any</v>
+        <f t="array" aca="1" ref="H197" ca="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_EFN2O_Data(), Table_SourceData_Common_EFN2O[[#Headers],[Production system j]], 0)</f>
+        <v/>
       </c>
     </row>
     <row r="198" spans="4:8" x14ac:dyDescent="0.25">
       <c r="D198" s="30" t="str" cm="1">
-        <f t="array" ref="D198">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_EFN2O_Data(), Table_SourceData_Common_EFN2O[[#Headers],[Production system j]], 0)</f>
-        <v>Aquaculture</v>
-      </c>
-      <c r="E198" s="30" cm="1">
-        <f t="array" ref="E198">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_EFN2O_Data(), Table_SourceData_Common_EFN2O[[#Headers],[Production system j]], 0)</f>
-        <v>2.5999999999999999E-3</v>
+        <f t="array" aca="1" ref="D198" ca="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_EFN2O_Data(), Table_SourceData_Common_EFN2O[[#Headers],[Production system j]], 0)</f>
+        <v/>
+      </c>
+      <c r="E198" s="30" t="str" cm="1">
+        <f t="array" aca="1" ref="E198" ca="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_EFN2O_Data(), Table_SourceData_Common_EFN2O[[#Headers],[Production system j]], 0)</f>
+        <v/>
       </c>
       <c r="F198" s="30" t="str" cm="1">
-        <f t="array" ref="F198">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_EFN2O_Data(), Table_SourceData_Common_EFN2O[[#Headers],[Production system j]], 0)</f>
-        <v>Aquaculture</v>
+        <f t="array" aca="1" ref="F198" ca="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_EFN2O_Data(), Table_SourceData_Common_EFN2O[[#Headers],[Production system j]], 0)</f>
+        <v/>
       </c>
       <c r="G198" s="30" t="str" cm="1">
-        <f t="array" ref="G198">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_EFN2O_Data(), Table_SourceData_Common_EFN2O[[#Headers],[Production system j]], 0)</f>
-        <v>Any</v>
+        <f t="array" aca="1" ref="G198" ca="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_EFN2O_Data(), Table_SourceData_Common_EFN2O[[#Headers],[Production system j]], 0)</f>
+        <v/>
       </c>
       <c r="H198" s="30" t="str" cm="1">
-        <f t="array" ref="H198">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_EFN2O_Data(), Table_SourceData_Common_EFN2O[[#Headers],[Production system j]], 0)</f>
-        <v>Any</v>
+        <f t="array" aca="1" ref="H198" ca="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_EFN2O_Data(), Table_SourceData_Common_EFN2O[[#Headers],[Production system j]], 0)</f>
+        <v/>
       </c>
     </row>
     <row r="199" spans="4:8" x14ac:dyDescent="0.25">
       <c r="D199" s="30" t="str" cm="1">
-        <f t="array" ref="D199">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_EFN2O_Data(), Table_SourceData_Common_EFN2O[[#Headers],[Production system j]], 0)</f>
-        <v>Forestry</v>
-      </c>
-      <c r="E199" s="30" cm="1">
-        <f t="array" ref="E199">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_EFN2O_Data(), Table_SourceData_Common_EFN2O[[#Headers],[Production system j]], 0)</f>
-        <v>1.8E-3</v>
+        <f t="array" aca="1" ref="D199" ca="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_EFN2O_Data(), Table_SourceData_Common_EFN2O[[#Headers],[Production system j]], 0)</f>
+        <v/>
+      </c>
+      <c r="E199" s="30" t="str" cm="1">
+        <f t="array" aca="1" ref="E199" ca="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_EFN2O_Data(), Table_SourceData_Common_EFN2O[[#Headers],[Production system j]], 0)</f>
+        <v/>
       </c>
       <c r="F199" s="30" t="str" cm="1">
-        <f t="array" ref="F199">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_EFN2O_Data(), Table_SourceData_Common_EFN2O[[#Headers],[Production system j]], 0)</f>
-        <v>Forestry</v>
+        <f t="array" aca="1" ref="F199" ca="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_EFN2O_Data(), Table_SourceData_Common_EFN2O[[#Headers],[Production system j]], 0)</f>
+        <v/>
       </c>
       <c r="G199" s="30" t="str" cm="1">
-        <f t="array" ref="G199">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_EFN2O_Data(), Table_SourceData_Common_EFN2O[[#Headers],[Production system j]], 0)</f>
-        <v>Any</v>
+        <f t="array" aca="1" ref="G199" ca="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_EFN2O_Data(), Table_SourceData_Common_EFN2O[[#Headers],[Production system j]], 0)</f>
+        <v/>
       </c>
       <c r="H199" s="30" t="str" cm="1">
-        <f t="array" ref="H199">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_EFN2O_Data(), Table_SourceData_Common_EFN2O[[#Headers],[Production system j]], 0)</f>
-        <v>Any</v>
+        <f t="array" aca="1" ref="H199" ca="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_EFN2O_Data(), Table_SourceData_Common_EFN2O[[#Headers],[Production system j]], 0)</f>
+        <v/>
       </c>
     </row>
     <row r="202" spans="4:8" ht="23.25" x14ac:dyDescent="0.25">
@@ -10101,22 +10399,22 @@
     </row>
     <row r="207" spans="4:8" x14ac:dyDescent="0.25">
       <c r="D207" s="30" t="str" cm="1">
-        <f t="array" ref="D207">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_EFPastureRangeAndPaddock_Data(), Table_SourceData_EFPastureRangeAndPaddock[[#Headers],[Climate zone]], 0)</f>
-        <v>Wet climate zone</v>
-      </c>
-      <c r="E207" s="30" cm="1">
-        <f t="array" ref="E207">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_EFPastureRangeAndPaddock_Data(), Table_SourceData_EFPastureRangeAndPaddock[[#Headers],[Climate zone]], 0)</f>
-        <v>6.0000000000000001E-3</v>
+        <f t="array" aca="1" ref="D207" ca="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_EFPastureRangeAndPaddock_Data(), Table_SourceData_EFPastureRangeAndPaddock[[#Headers],[Climate zone]], 0)</f>
+        <v/>
+      </c>
+      <c r="E207" s="30" t="str" cm="1">
+        <f t="array" aca="1" ref="E207" ca="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_EFPastureRangeAndPaddock_Data(), Table_SourceData_EFPastureRangeAndPaddock[[#Headers],[Climate zone]], 0)</f>
+        <v/>
       </c>
     </row>
     <row r="208" spans="4:8" x14ac:dyDescent="0.25">
       <c r="D208" s="1" t="str" cm="1">
-        <f t="array" ref="D208">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_EFPastureRangeAndPaddock_Data(), Table_SourceData_EFPastureRangeAndPaddock[[#Headers],[Climate zone]], 0)</f>
-        <v>Dry climate zone</v>
-      </c>
-      <c r="E208" s="30" cm="1">
-        <f t="array" ref="E208">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_EFPastureRangeAndPaddock_Data(), Table_SourceData_EFPastureRangeAndPaddock[[#Headers],[Climate zone]], 0)</f>
-        <v>2E-3</v>
+        <f t="array" aca="1" ref="D208" ca="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_EFPastureRangeAndPaddock_Data(), Table_SourceData_EFPastureRangeAndPaddock[[#Headers],[Climate zone]], 0)</f>
+        <v/>
+      </c>
+      <c r="E208" s="30" t="str" cm="1">
+        <f t="array" aca="1" ref="E208" ca="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_EFPastureRangeAndPaddock_Data(), Table_SourceData_EFPastureRangeAndPaddock[[#Headers],[Climate zone]], 0)</f>
+        <v/>
       </c>
     </row>
     <row r="211" spans="4:5" x14ac:dyDescent="0.25">
@@ -10135,122 +10433,122 @@
     </row>
     <row r="213" spans="4:5" x14ac:dyDescent="0.25">
       <c r="D213" s="30" t="str" cm="1">
-        <f t="array" ref="D213">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MonthsToSeasons_Data(), Table_SourceData_Common_MonthToSeason[[#Headers],[Month]], 0)</f>
-        <v>January</v>
+        <f t="array" aca="1" ref="D213" ca="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MonthsToSeasons_Data(), Table_SourceData_Common_MonthToSeason[[#Headers],[Month]], 0)</f>
+        <v/>
       </c>
       <c r="E213" s="30" t="str" cm="1">
-        <f t="array" ref="E213">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MonthsToSeasons_Data(), Table_SourceData_Common_MonthToSeason[[#Headers],[Month]], 0)</f>
-        <v>Summer</v>
+        <f t="array" aca="1" ref="E213" ca="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MonthsToSeasons_Data(), Table_SourceData_Common_MonthToSeason[[#Headers],[Month]], 0)</f>
+        <v/>
       </c>
     </row>
     <row r="214" spans="4:5" x14ac:dyDescent="0.25">
       <c r="D214" s="1" t="str" cm="1">
-        <f t="array" ref="D214">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MonthsToSeasons_Data(), Table_SourceData_Common_MonthToSeason[[#Headers],[Month]], 0)</f>
-        <v>February</v>
+        <f t="array" aca="1" ref="D214" ca="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MonthsToSeasons_Data(), Table_SourceData_Common_MonthToSeason[[#Headers],[Month]], 0)</f>
+        <v/>
       </c>
       <c r="E214" s="30" t="str" cm="1">
-        <f t="array" ref="E214">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MonthsToSeasons_Data(), Table_SourceData_Common_MonthToSeason[[#Headers],[Month]], 0)</f>
-        <v>Summer</v>
+        <f t="array" aca="1" ref="E214" ca="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MonthsToSeasons_Data(), Table_SourceData_Common_MonthToSeason[[#Headers],[Month]], 0)</f>
+        <v/>
       </c>
     </row>
     <row r="215" spans="4:5" x14ac:dyDescent="0.25">
       <c r="D215" s="1" t="str" cm="1">
-        <f t="array" ref="D215">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MonthsToSeasons_Data(), Table_SourceData_Common_MonthToSeason[[#Headers],[Month]], 0)</f>
-        <v>March</v>
+        <f t="array" aca="1" ref="D215" ca="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MonthsToSeasons_Data(), Table_SourceData_Common_MonthToSeason[[#Headers],[Month]], 0)</f>
+        <v/>
       </c>
       <c r="E215" s="30" t="str" cm="1">
-        <f t="array" ref="E215">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MonthsToSeasons_Data(), Table_SourceData_Common_MonthToSeason[[#Headers],[Month]], 0)</f>
-        <v>Autumn</v>
+        <f t="array" aca="1" ref="E215" ca="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MonthsToSeasons_Data(), Table_SourceData_Common_MonthToSeason[[#Headers],[Month]], 0)</f>
+        <v/>
       </c>
     </row>
     <row r="216" spans="4:5" x14ac:dyDescent="0.25">
       <c r="D216" s="1" t="str" cm="1">
-        <f t="array" ref="D216">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MonthsToSeasons_Data(), Table_SourceData_Common_MonthToSeason[[#Headers],[Month]], 0)</f>
-        <v>April</v>
+        <f t="array" aca="1" ref="D216" ca="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MonthsToSeasons_Data(), Table_SourceData_Common_MonthToSeason[[#Headers],[Month]], 0)</f>
+        <v/>
       </c>
       <c r="E216" s="30" t="str" cm="1">
-        <f t="array" ref="E216">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MonthsToSeasons_Data(), Table_SourceData_Common_MonthToSeason[[#Headers],[Month]], 0)</f>
-        <v>Autumn</v>
+        <f t="array" aca="1" ref="E216" ca="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MonthsToSeasons_Data(), Table_SourceData_Common_MonthToSeason[[#Headers],[Month]], 0)</f>
+        <v/>
       </c>
     </row>
     <row r="217" spans="4:5" x14ac:dyDescent="0.25">
       <c r="D217" s="1" t="str" cm="1">
-        <f t="array" ref="D217">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MonthsToSeasons_Data(), Table_SourceData_Common_MonthToSeason[[#Headers],[Month]], 0)</f>
-        <v>May</v>
+        <f t="array" aca="1" ref="D217" ca="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MonthsToSeasons_Data(), Table_SourceData_Common_MonthToSeason[[#Headers],[Month]], 0)</f>
+        <v/>
       </c>
       <c r="E217" s="30" t="str" cm="1">
-        <f t="array" ref="E217">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MonthsToSeasons_Data(), Table_SourceData_Common_MonthToSeason[[#Headers],[Month]], 0)</f>
-        <v>Autumn</v>
+        <f t="array" aca="1" ref="E217" ca="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MonthsToSeasons_Data(), Table_SourceData_Common_MonthToSeason[[#Headers],[Month]], 0)</f>
+        <v/>
       </c>
     </row>
     <row r="218" spans="4:5" x14ac:dyDescent="0.25">
       <c r="D218" s="1" t="str" cm="1">
-        <f t="array" ref="D218">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MonthsToSeasons_Data(), Table_SourceData_Common_MonthToSeason[[#Headers],[Month]], 0)</f>
-        <v>June</v>
+        <f t="array" aca="1" ref="D218" ca="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MonthsToSeasons_Data(), Table_SourceData_Common_MonthToSeason[[#Headers],[Month]], 0)</f>
+        <v/>
       </c>
       <c r="E218" s="30" t="str" cm="1">
-        <f t="array" ref="E218">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MonthsToSeasons_Data(), Table_SourceData_Common_MonthToSeason[[#Headers],[Month]], 0)</f>
-        <v>Winter</v>
+        <f t="array" aca="1" ref="E218" ca="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MonthsToSeasons_Data(), Table_SourceData_Common_MonthToSeason[[#Headers],[Month]], 0)</f>
+        <v/>
       </c>
     </row>
     <row r="219" spans="4:5" x14ac:dyDescent="0.25">
       <c r="D219" s="1" t="str" cm="1">
-        <f t="array" ref="D219">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MonthsToSeasons_Data(), Table_SourceData_Common_MonthToSeason[[#Headers],[Month]], 0)</f>
-        <v>July</v>
+        <f t="array" aca="1" ref="D219" ca="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MonthsToSeasons_Data(), Table_SourceData_Common_MonthToSeason[[#Headers],[Month]], 0)</f>
+        <v/>
       </c>
       <c r="E219" s="30" t="str" cm="1">
-        <f t="array" ref="E219">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MonthsToSeasons_Data(), Table_SourceData_Common_MonthToSeason[[#Headers],[Month]], 0)</f>
-        <v>Winter</v>
+        <f t="array" aca="1" ref="E219" ca="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MonthsToSeasons_Data(), Table_SourceData_Common_MonthToSeason[[#Headers],[Month]], 0)</f>
+        <v/>
       </c>
     </row>
     <row r="220" spans="4:5" x14ac:dyDescent="0.25">
       <c r="D220" s="1" t="str" cm="1">
-        <f t="array" ref="D220">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MonthsToSeasons_Data(), Table_SourceData_Common_MonthToSeason[[#Headers],[Month]], 0)</f>
-        <v>August</v>
+        <f t="array" aca="1" ref="D220" ca="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MonthsToSeasons_Data(), Table_SourceData_Common_MonthToSeason[[#Headers],[Month]], 0)</f>
+        <v/>
       </c>
       <c r="E220" s="30" t="str" cm="1">
-        <f t="array" ref="E220">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MonthsToSeasons_Data(), Table_SourceData_Common_MonthToSeason[[#Headers],[Month]], 0)</f>
-        <v>Winter</v>
+        <f t="array" aca="1" ref="E220" ca="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MonthsToSeasons_Data(), Table_SourceData_Common_MonthToSeason[[#Headers],[Month]], 0)</f>
+        <v/>
       </c>
     </row>
     <row r="221" spans="4:5" x14ac:dyDescent="0.25">
       <c r="D221" s="1" t="str" cm="1">
-        <f t="array" ref="D221">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MonthsToSeasons_Data(), Table_SourceData_Common_MonthToSeason[[#Headers],[Month]], 0)</f>
-        <v>September</v>
+        <f t="array" aca="1" ref="D221" ca="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MonthsToSeasons_Data(), Table_SourceData_Common_MonthToSeason[[#Headers],[Month]], 0)</f>
+        <v/>
       </c>
       <c r="E221" s="30" t="str" cm="1">
-        <f t="array" ref="E221">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MonthsToSeasons_Data(), Table_SourceData_Common_MonthToSeason[[#Headers],[Month]], 0)</f>
-        <v>Spring</v>
+        <f t="array" aca="1" ref="E221" ca="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MonthsToSeasons_Data(), Table_SourceData_Common_MonthToSeason[[#Headers],[Month]], 0)</f>
+        <v/>
       </c>
     </row>
     <row r="222" spans="4:5" x14ac:dyDescent="0.25">
       <c r="D222" s="1" t="str" cm="1">
-        <f t="array" ref="D222">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MonthsToSeasons_Data(), Table_SourceData_Common_MonthToSeason[[#Headers],[Month]], 0)</f>
-        <v>October</v>
+        <f t="array" aca="1" ref="D222" ca="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MonthsToSeasons_Data(), Table_SourceData_Common_MonthToSeason[[#Headers],[Month]], 0)</f>
+        <v/>
       </c>
       <c r="E222" s="30" t="str" cm="1">
-        <f t="array" ref="E222">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MonthsToSeasons_Data(), Table_SourceData_Common_MonthToSeason[[#Headers],[Month]], 0)</f>
-        <v>Spring</v>
+        <f t="array" aca="1" ref="E222" ca="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MonthsToSeasons_Data(), Table_SourceData_Common_MonthToSeason[[#Headers],[Month]], 0)</f>
+        <v/>
       </c>
     </row>
     <row r="223" spans="4:5" x14ac:dyDescent="0.25">
       <c r="D223" s="1" t="str" cm="1">
-        <f t="array" ref="D223">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MonthsToSeasons_Data(), Table_SourceData_Common_MonthToSeason[[#Headers],[Month]], 0)</f>
-        <v>November</v>
+        <f t="array" aca="1" ref="D223" ca="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MonthsToSeasons_Data(), Table_SourceData_Common_MonthToSeason[[#Headers],[Month]], 0)</f>
+        <v/>
       </c>
       <c r="E223" s="30" t="str" cm="1">
-        <f t="array" ref="E223">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MonthsToSeasons_Data(), Table_SourceData_Common_MonthToSeason[[#Headers],[Month]], 0)</f>
-        <v>Spring</v>
+        <f t="array" aca="1" ref="E223" ca="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MonthsToSeasons_Data(), Table_SourceData_Common_MonthToSeason[[#Headers],[Month]], 0)</f>
+        <v/>
       </c>
     </row>
     <row r="224" spans="4:5" x14ac:dyDescent="0.25">
       <c r="D224" s="1" t="str" cm="1">
-        <f t="array" ref="D224">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MonthsToSeasons_Data(), Table_SourceData_Common_MonthToSeason[[#Headers],[Month]], 0)</f>
-        <v>December</v>
+        <f t="array" aca="1" ref="D224" ca="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MonthsToSeasons_Data(), Table_SourceData_Common_MonthToSeason[[#Headers],[Month]], 0)</f>
+        <v/>
       </c>
       <c r="E224" s="30" t="str" cm="1">
-        <f t="array" ref="E224">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MonthsToSeasons_Data(), Table_SourceData_Common_MonthToSeason[[#Headers],[Month]], 0)</f>
-        <v>Summer</v>
+        <f t="array" aca="1" ref="E224" ca="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MonthsToSeasons_Data(), Table_SourceData_Common_MonthToSeason[[#Headers],[Month]], 0)</f>
+        <v/>
       </c>
     </row>
     <row r="227" spans="4:19" ht="23.25" x14ac:dyDescent="0.25">
@@ -10323,1256 +10621,1256 @@
     </row>
     <row r="232" spans="4:19" x14ac:dyDescent="0.25">
       <c r="D232" s="30" t="str" cm="1">
-        <f t="array" ref="D232">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
-        <v>Cool</v>
+        <f t="array" aca="1" ref="D232" ca="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
+        <v/>
       </c>
       <c r="E232" s="30" t="str" cm="1">
-        <f t="array" ref="E232">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
-        <v>≤10</v>
-      </c>
-      <c r="F232" s="30" cm="1">
-        <f t="array" ref="F232">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
-        <v>0.66</v>
-      </c>
-      <c r="G232" s="30" cm="1">
-        <f t="array" ref="G232">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
-        <v>0.1</v>
-      </c>
-      <c r="H232" s="30" cm="1">
-        <f t="array" ref="H232">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
-        <v>0.1</v>
-      </c>
-      <c r="I232" s="30" cm="1">
-        <f t="array" ref="I232">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
-        <v>1E-3</v>
-      </c>
-      <c r="J232" s="30" cm="1">
-        <f t="array" ref="J232">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
-        <v>5.0000000000000001E-3</v>
-      </c>
-      <c r="K232" s="30" cm="1">
-        <f t="array" ref="K232">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
-        <v>0.02</v>
-      </c>
-      <c r="L232" s="30" cm="1">
-        <f t="array" ref="L232">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
-        <v>0.03</v>
-      </c>
-      <c r="M232" s="30" cm="1">
-        <f t="array" ref="M232">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
-        <v>0.04</v>
-      </c>
-      <c r="N232" s="30" cm="1">
-        <f t="array" ref="N232">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
-        <v>1.4999999999999999E-2</v>
-      </c>
-      <c r="O232" s="30" cm="1">
-        <f t="array" ref="O232">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
-        <v>1.4999999999999999E-2</v>
-      </c>
-      <c r="P232" s="30" cm="1">
-        <f t="array" ref="P232">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
-        <v>0</v>
-      </c>
-      <c r="Q232" s="30" cm="1">
-        <f t="array" ref="Q232">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
-        <v>0</v>
-      </c>
-      <c r="R232" s="30" cm="1">
-        <f t="array" ref="R232">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
-        <v>4.7000000000000002E-3</v>
-      </c>
-      <c r="S232" s="30" cm="1">
-        <f t="array" ref="S232">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
-        <v>10</v>
+        <f t="array" aca="1" ref="E232" ca="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
+        <v/>
+      </c>
+      <c r="F232" s="30" t="str" cm="1">
+        <f t="array" aca="1" ref="F232" ca="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
+        <v/>
+      </c>
+      <c r="G232" s="30" t="str" cm="1">
+        <f t="array" aca="1" ref="G232" ca="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
+        <v/>
+      </c>
+      <c r="H232" s="30" t="str" cm="1">
+        <f t="array" aca="1" ref="H232" ca="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
+        <v/>
+      </c>
+      <c r="I232" s="30" t="str" cm="1">
+        <f t="array" aca="1" ref="I232" ca="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
+        <v/>
+      </c>
+      <c r="J232" s="30" t="str" cm="1">
+        <f t="array" aca="1" ref="J232" ca="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
+        <v/>
+      </c>
+      <c r="K232" s="30" t="str" cm="1">
+        <f t="array" aca="1" ref="K232" ca="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
+        <v/>
+      </c>
+      <c r="L232" s="30" t="str" cm="1">
+        <f t="array" aca="1" ref="L232" ca="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
+        <v/>
+      </c>
+      <c r="M232" s="30" t="str" cm="1">
+        <f t="array" aca="1" ref="M232" ca="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
+        <v/>
+      </c>
+      <c r="N232" s="30" t="str" cm="1">
+        <f t="array" aca="1" ref="N232" ca="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
+        <v/>
+      </c>
+      <c r="O232" s="30" t="str" cm="1">
+        <f t="array" aca="1" ref="O232" ca="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
+        <v/>
+      </c>
+      <c r="P232" s="30" t="str" cm="1">
+        <f t="array" aca="1" ref="P232" ca="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
+        <v/>
+      </c>
+      <c r="Q232" s="30" t="str" cm="1">
+        <f t="array" aca="1" ref="Q232" ca="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
+        <v/>
+      </c>
+      <c r="R232" s="30" t="str" cm="1">
+        <f t="array" aca="1" ref="R232" ca="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
+        <v/>
+      </c>
+      <c r="S232" s="30" t="str" cm="1">
+        <f t="array" aca="1" ref="S232" ca="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
+        <v/>
       </c>
     </row>
     <row r="233" spans="4:19" x14ac:dyDescent="0.25">
       <c r="D233" s="1" t="str" cm="1">
-        <f t="array" ref="D233">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
-        <v>Cool</v>
-      </c>
-      <c r="E233" s="30" cm="1">
-        <f t="array" ref="E233">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
-        <v>11</v>
-      </c>
-      <c r="F233" s="30" cm="1">
-        <f t="array" ref="F233">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
-        <v>0.68</v>
-      </c>
-      <c r="G233" s="30" cm="1">
-        <f t="array" ref="G233">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
-        <v>0.1</v>
-      </c>
-      <c r="H233" s="30" cm="1">
-        <f t="array" ref="H233">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
-        <v>0.11</v>
-      </c>
-      <c r="I233" s="30" cm="1">
-        <f t="array" ref="I233">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
-        <v>1E-3</v>
-      </c>
-      <c r="J233" s="30" cm="1">
-        <f t="array" ref="J233">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
-        <v>5.0000000000000001E-3</v>
-      </c>
-      <c r="K233" s="30" cm="1">
-        <f t="array" ref="K233">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
-        <v>0.02</v>
-      </c>
-      <c r="L233" s="30" cm="1">
-        <f t="array" ref="L233">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
-        <v>0.03</v>
-      </c>
-      <c r="M233" s="30" cm="1">
-        <f t="array" ref="M233">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
-        <v>0.04</v>
-      </c>
-      <c r="N233" s="30" cm="1">
-        <f t="array" ref="N233">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
-        <v>1.4999999999999999E-2</v>
-      </c>
-      <c r="O233" s="30" cm="1">
-        <f t="array" ref="O233">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
-        <v>1.4999999999999999E-2</v>
-      </c>
-      <c r="P233" s="30" cm="1">
-        <f t="array" ref="P233">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
-        <v>0</v>
-      </c>
-      <c r="Q233" s="30" cm="1">
-        <f t="array" ref="Q233">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
-        <v>0</v>
-      </c>
-      <c r="R233" s="30" cm="1">
-        <f t="array" ref="R233">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
-        <v>4.7000000000000002E-3</v>
-      </c>
-      <c r="S233" s="30" cm="1">
-        <f t="array" ref="S233">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
-        <v>11</v>
+        <f t="array" aca="1" ref="D233" ca="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
+        <v/>
+      </c>
+      <c r="E233" s="30" t="str" cm="1">
+        <f t="array" aca="1" ref="E233" ca="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
+        <v/>
+      </c>
+      <c r="F233" s="30" t="str" cm="1">
+        <f t="array" aca="1" ref="F233" ca="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
+        <v/>
+      </c>
+      <c r="G233" s="30" t="str" cm="1">
+        <f t="array" aca="1" ref="G233" ca="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
+        <v/>
+      </c>
+      <c r="H233" s="30" t="str" cm="1">
+        <f t="array" aca="1" ref="H233" ca="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
+        <v/>
+      </c>
+      <c r="I233" s="30" t="str" cm="1">
+        <f t="array" aca="1" ref="I233" ca="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
+        <v/>
+      </c>
+      <c r="J233" s="30" t="str" cm="1">
+        <f t="array" aca="1" ref="J233" ca="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
+        <v/>
+      </c>
+      <c r="K233" s="30" t="str" cm="1">
+        <f t="array" aca="1" ref="K233" ca="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
+        <v/>
+      </c>
+      <c r="L233" s="30" t="str" cm="1">
+        <f t="array" aca="1" ref="L233" ca="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
+        <v/>
+      </c>
+      <c r="M233" s="30" t="str" cm="1">
+        <f t="array" aca="1" ref="M233" ca="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
+        <v/>
+      </c>
+      <c r="N233" s="30" t="str" cm="1">
+        <f t="array" aca="1" ref="N233" ca="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
+        <v/>
+      </c>
+      <c r="O233" s="30" t="str" cm="1">
+        <f t="array" aca="1" ref="O233" ca="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
+        <v/>
+      </c>
+      <c r="P233" s="30" t="str" cm="1">
+        <f t="array" aca="1" ref="P233" ca="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
+        <v/>
+      </c>
+      <c r="Q233" s="30" t="str" cm="1">
+        <f t="array" aca="1" ref="Q233" ca="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
+        <v/>
+      </c>
+      <c r="R233" s="30" t="str" cm="1">
+        <f t="array" aca="1" ref="R233" ca="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
+        <v/>
+      </c>
+      <c r="S233" s="30" t="str" cm="1">
+        <f t="array" aca="1" ref="S233" ca="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
+        <v/>
       </c>
     </row>
     <row r="234" spans="4:19" x14ac:dyDescent="0.25">
       <c r="D234" s="1" t="str" cm="1">
-        <f t="array" ref="D234">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
-        <v>Cool</v>
-      </c>
-      <c r="E234" s="30" cm="1">
-        <f t="array" ref="E234">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
-        <v>12</v>
-      </c>
-      <c r="F234" s="30" cm="1">
-        <f t="array" ref="F234">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
-        <v>0.7</v>
-      </c>
-      <c r="G234" s="30" cm="1">
-        <f t="array" ref="G234">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
-        <v>0.1</v>
-      </c>
-      <c r="H234" s="30" cm="1">
-        <f t="array" ref="H234">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
-        <v>0.13</v>
-      </c>
-      <c r="I234" s="30" cm="1">
-        <f t="array" ref="I234">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
-        <v>1E-3</v>
-      </c>
-      <c r="J234" s="30" cm="1">
-        <f t="array" ref="J234">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
-        <v>5.0000000000000001E-3</v>
-      </c>
-      <c r="K234" s="30" cm="1">
-        <f t="array" ref="K234">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
-        <v>0.02</v>
-      </c>
-      <c r="L234" s="30" cm="1">
-        <f t="array" ref="L234">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
-        <v>0.03</v>
-      </c>
-      <c r="M234" s="30" cm="1">
-        <f t="array" ref="M234">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
-        <v>0.04</v>
-      </c>
-      <c r="N234" s="30" cm="1">
-        <f t="array" ref="N234">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
-        <v>1.4999999999999999E-2</v>
-      </c>
-      <c r="O234" s="30" cm="1">
-        <f t="array" ref="O234">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
-        <v>1.4999999999999999E-2</v>
-      </c>
-      <c r="P234" s="30" cm="1">
-        <f t="array" ref="P234">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
-        <v>0</v>
-      </c>
-      <c r="Q234" s="30" cm="1">
-        <f t="array" ref="Q234">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
-        <v>0</v>
-      </c>
-      <c r="R234" s="30" cm="1">
-        <f t="array" ref="R234">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
-        <v>4.7000000000000002E-3</v>
-      </c>
-      <c r="S234" s="30" cm="1">
-        <f t="array" ref="S234">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
-        <v>12</v>
+        <f t="array" aca="1" ref="D234" ca="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
+        <v/>
+      </c>
+      <c r="E234" s="30" t="str" cm="1">
+        <f t="array" aca="1" ref="E234" ca="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
+        <v/>
+      </c>
+      <c r="F234" s="30" t="str" cm="1">
+        <f t="array" aca="1" ref="F234" ca="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
+        <v/>
+      </c>
+      <c r="G234" s="30" t="str" cm="1">
+        <f t="array" aca="1" ref="G234" ca="